--- a/news_results_raw.xlsx
+++ b/news_results_raw.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E217"/>
+  <dimension ref="A1:E176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,22 +517,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sandoz Secures SBTi Validation For 2030 Climate Targets Across Operations And Suppliers</t>
+          <t>Earnings call transcript: Sandoz sees stock surge in Q1 2026 By Investing.com</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ESG News</t>
+          <t>Investing.com India</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNaHgwM2tGQmdvYUlic21xWXdRM3JlLXd1VHZEd1JBM1hhODc0a1JwTHRtRGRteHAxZHpYVVFNajRCNjFWRHNDbVhtNTFBVHU2aWR6MU9IZzRuN3h5WTAyUGtZYlNjdmVoVGtJZ2Y2OFFsMUxTTDdkYWpLUENrZm1WTDI4UG1wSG5MLXd5Q0lsN1JxS0ZyNmxRM3M5eWdEcERRbUtqbmFkLURLMXlu?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOUW1zaDgzbHQ3TUt6MVNRR0ZCcnhBSnE4aFY5eEQxalh3dGdPZ2JzdU9NV3I0eUVQX253Zld6Z25OTTdxTzh5ZWRScjZzSDQxV0dMZW9zSzhLZXlOaUUtYkZJUnNiSl9lT3B5MkNjRmtHVTZxOTJXNlJHdUJoVWpGaU9LNEctVnRTdmN5OGI3clhlekktVVZZNEhpVkdKLVNuYmxQR2pEVVU4TWdOMDREUkk2QlVJRVY2VzZHOQ?oc=5</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>08-05-2026 13:35 UTC</t>
+          <t>08-05-2026 12:07 UTC</t>
         </is>
       </c>
     </row>
@@ -544,22 +544,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Earnings call transcript: Sandoz sees stock surge in Q1 2026 By Investing.com</t>
+          <t>Sandoz Secures SBTi Validation For 2030 Climate Targets Across Operations And Suppliers</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Investing.com Australia</t>
+          <t>ESG News</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQREtHTHhjZUVrUUZnTF9VZFFzX3NpWldwb01fNzRsZGdFNk96NUdRR2ppUkkwRHV1MkFzVktnRlhpeTRNV1VYV3VUc01MWE00eFFtZFVmc2NXZ2ZZSGtfb01GZXA4QlA3WGJaTDk3X0lFcjdvY0d4R1F1dVVfMUgta0JiclVDNGJCTVVlbkxteHU2VUdMeU45dlg4S2ItRzNSQ2NDQTg5QW1SeWRkRGdfN3h2a3I4alhlclE3NA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNaHgwM2tGQmdvYUlic21xWXdRM3JlLXd1VHZEd1JBM1hhODc0a1JwTHRtRGRteHAxZHpYVVFNajRCNjFWRHNDbVhtNTFBVHU2aWR6MU9IZzRuN3h5WTAyUGtZYlNjdmVoVGtJZ2Y2OFFsMUxTTDdkYWpLUENrZm1WTDI4UG1wSG5MLXd5Q0lsN1JxS0ZyNmxRM3M5eWdEcERRbUtqbmFkLURLMXlu?oc=5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>08-05-2026 11:50 UTC</t>
+          <t>08-05-2026 13:35 UTC</t>
         </is>
       </c>
     </row>
@@ -571,22 +571,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Who’s Hired? Viatris Begins Search For New CFO</t>
+          <t>Sandoz to Launch Generic Version of Semaglutide in Canada, Brazil This Year, CEO Says</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Citeline News &amp; Insights</t>
+          <t>Moomoo</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxOM2p0ek05bVowRFBiZFU4OExlYVdlMnMtdnNJeXI0LWJlV25EalRyQlhXTUk5N094elpadXA1QWgxd0Y1Nml6SHF5ZTFQdUh1NnB1MDFlLUpTYTV6S2NpanE0RDlXQkZmWS1qSEtsYkVqN2k4MXlyaWsyRmVsaElmVkpGVlhVcFQ0dVJUd0hST05zY1hsbjZTeEdDZVVBbV9rNVgwQnV5aElRdndNcHRCU0RlNDY5N3BScHg4QmVUVDlrZ054cEFsa2FkWUhDcVNzeE83ZzR6Q3dHQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNX1hhUGMzX2pJcVdRYjNMRFFHTjM1OExKVjd4ZWs3b1lCME5YdnViNWYyWlFFXzFTb19xeEdWM2ltRUx4ZF81cks4aUFtVDd2YnpyalEwR2tqZFVRU1BnYUpDNHF1MzBDNkZrd2tiTDZsSTV3SDJzc2tlSGNhRURDY0RjNl9fZ2VxSlVoR2xXcFhYcmJXOVRBakRscmJQdy1yemc0aWtKY3c5QQ?oc=5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>08-05-2026 12:08 UTC</t>
+          <t>08-05-2026 14:40 UTC</t>
         </is>
       </c>
     </row>
@@ -598,103 +598,103 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sandoz Unveils New Operational, Supply Chain Climate Goals</t>
+          <t>Who’s Hired? Viatris Begins Search For New CFO</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ESG Today</t>
+          <t>Citeline News &amp; Insights</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQY0dEd2NBeWRZRV9GVnBqeEcxZFBMNmg2bWlHWk9YMVpwVUk2OERHS1l2dmQ2ckd6VV91dEduaUlGNEQzejl4cjBPR3poc0EyRnBsaW80bXg4Z0JrUGZyY0NTWkc0Ump2U005LVFJQmpGT2w3NFA2MnZ4aV9ZMzJWbUhRb1ZLQ20tdnJz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxOM2p0ek05bVowRFBiZFU4OExlYVdlMnMtdnNJeXI0LWJlV25EalRyQlhXTUk5N094elpadXA1QWgxd0Y1Nml6SHF5ZTFQdUh1NnB1MDFlLUpTYTV6S2NpanE0RDlXQkZmWS1qSEtsYkVqN2k4MXlyaWsyRmVsaElmVkpGVlhVcFQ0dVJUd0hST05zY1hsbjZTeEdDZVVBbV9rNVgwQnV5aElRdndNcHRCU0RlNDY5N3BScHg4QmVUVDlrZ054cEFsa2FkWUhDcVNzeE83ZzR6Q3dHQQ?oc=5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>07-05-2026 17:51 UTC</t>
+          <t>08-05-2026 12:08 UTC</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sandoz</t>
+          <t>Formycon</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Number of shareholders of Sandoz Group Ltd – AQUISUK:SDZZ</t>
+          <t>Formycon AG Stock (DE000A1EWVY8): Analyst Upgrade and Price Target Revision</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPbmJuT2p5S1RDanF4eVNkMjBsWXNpMVJPS0dHazNnMmlRRnphUzg0UHVjTzB6ellWWGdlMDZPTDB5RjVHazFBYkZxUDRRa05hcFN6blBTc2lQXzVhUmlBTjJoaE9XajV2alVaa3d1RXR2VGdXcFZWQWN2bmZnNG9xVUFuNHB1Rml4ZFBTd2FZS05rSFdmWDBPeUFveWxwR3NCS0hNVHlpdEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQekFSMzhrQ1pRVUlmRldJM1RJTkxHeEYwa3ViZjc5U3FndHV0cXMwekkybm5NNHRiaDNLLXhxSDJiOW1JLUdBSGpOZGZ0aHB2M3k2b3NoRkJ5cHZpMVF3cm1RU2NlR1pfdVptS0FLcWVpY0ZGSXNlYVdiNVE0czJnWTFkbFUxcDg3WE8wZGNQZXJOUlBEdS01ZjA1UjlJUGFDSEhWUHRTN0lXRGJRN2JITU9uZ0h2OVU0cnM5UGp0aw?oc=5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>07-05-2026 16:17 UTC</t>
+          <t>08-05-2026 13:34 UTC</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Formycon</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Formycon AG Stock (DE000A1EWVY8): Analyst Upgrade and Price Target Revision</t>
+          <t>AbbVie’s Skyrizi beats out J&amp;J’s Tremfya in April drug ad spending leaderboard</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>Fierce Pharma</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQekFSMzhrQ1pRVUlmRldJM1RJTkxHeEYwa3ViZjc5U3FndHV0cXMwekkybm5NNHRiaDNLLXhxSDJiOW1JLUdBSGpOZGZ0aHB2M3k2b3NoRkJ5cHZpMVF3cm1RU2NlR1pfdVptS0FLcWVpY0ZGSXNlYVdiNVE0czJnWTFkbFUxcDg3WE8wZGNQZXJOUlBEdS01ZjA1UjlJUGFDSEhWUHRTN0lXRGJRN2JITU9uZ0h2OVU0cnM5UGp0aw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOdVZiNFlTMEhBUmI0N1VOTGw5eWRkR00ySW9TTHdtOERxV1JMRTFMNTd4bjdjYk5UVUNqWXEyVXMyM05icnBKbG5tdThNbWcwckZ2QXBxM0FOdmM3OUZoODRoWjk1eWpvUWpNYmpMSzhFR2JwMlc1cHBFeUZWU0JkdTRURkUtcFM3WXJaZl8xRjROcFFQMFZHY0ROOUQ0ZHMyMjA5OTc1bTUyV2R2T3VTc0Z3?oc=5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>08-05-2026 13:34 UTC</t>
+          <t>08-05-2026 14:03 UTC</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Gedeon Richter</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>April 2026 — CDMO Opportunities And Threats Report</t>
+          <t>ARVO 2026 signals a turning point for retina innovations</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bioprocess Online</t>
+          <t>Eyes On Eyecare</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxQT0NqM0ZZWnRDenNHVHZkZTcwdnptbzRZallZU2hxRE1sVzBXbHU4MzZVcExaazZnR3BzMlJ2M3ZCNWJONmVrMHNqWEJGUldIVlJ5c3RXOEVsN0M4OGY3WGhCLTBkWFdqRy1Ec1F3aG9hc2s2bnZMMURoaXN5dWh3ZnROZmltcFVnLUtZUTcwZUtCWXR2?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxObnI5MGE2akM4aGtqRzNxTlZqX2hKSnVEOHA0RXV6V0p1ak1xSmdSV2diYVBveGk0Wmlxb3FPb3JzYnRKeWNxQ0pHa3QxcXdPbHZGazBkWjhDMklCRTB1N2RocWY4aEZrZVI1cGhVWTljSTlNeXJ5T0YwT3JKM1dGdlYyelpFZFdjUlhVWjJ4aHBRUEJ1MFlPbVFnREhkSTJuTnhHVHdLTEFGSGVPUFE?oc=5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>08-05-2026 05:18 UTC</t>
+          <t>08-05-2026 11:53 UTC</t>
         </is>
       </c>
     </row>
@@ -706,22 +706,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Click Therapeutics Secures $50M Series D Funding Deal</t>
+          <t>BioNTech’s €16.8 Billion War Chest Funds a Cancer Bet While COVID Revenues Crumble</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ventureburn</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxNN25Ld3lyVWtJQVBLb0FhNk1qeHo2TTlVck5HYUU0RVM0LVRleFpNRFJQX3JrcVJTVWNhRklScE54YmdVS1BlZXRJOUM4M2hIR2I2R081V28tOEdfaE1iWVhRUFlnYllRVWVFRUNiSFh6cFBMOGJQVFMyeW0yd2JNeWJTRdIBgwFBVV95cUxNN25Ld3lyVWtJQVBLb0FhNk1qeHo2TTlVck5HYUU0RVM0LVRleFpNRFJQX3JrcVJTVWNhRklScE54YmdVS1BlZXRJOUM4M2hIR2I2R081V28tOEdfaE1iWVhRUFlnYllRVWVFRUNiSFh6cFBMOGJQVFMyeW0yd2JNeWJTRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQMldmZkZZRlJHcGVFZHFrRGZsWVkwZHJYNjVMclB6THB2bmZEaFFWdGdtdVBQMGRjXzF6Xzd1TnBqN3VhQ3Iza0o2LWRLUjdRSDZFU2lET214N2x5YjhZa2F3czVxem8tbDVuLUVLZ0NrTFVIZGtLMDFaUFBtdXpPZ0R1YWdoeHZ0Zk5RRVg0cWJiN0cxQ3AwWVhDbFpoamFpMDAtZXZ6UHIzTmF5WjZQQi13bmZwVjg2Tzd5LTdaRl8?oc=5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>08-05-2026 05:02 UTC</t>
+          <t>08-05-2026 11:00 UTC</t>
         </is>
       </c>
     </row>
@@ -733,22 +733,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ribo And Boehringer Ingelheim Reach Third Milestone In siRNA Collaboration Targeting MASH Therapies</t>
+          <t>Irish company secures exclusive entry into China’s rapidly expanding veterinary 08 May 2026 Free</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BioPharma APAC</t>
+          <t>The Irish Field</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxQT19nV2Q4OF9qclN3b3hHZ3JYM0Y5UmRYYnFYMFc5Z1k2djdOXzB5aTJnVFhaV3lVaWlyTGFOdUN3MXVKcVJycmFlYVFneldZdHpEam1mWnRhQjdfS3ZTWk15YzQydE03YXRXZERGcG9YeDdIQl9wVGFCMXpaNkh6Y0oyNDBWMGp4S29KWEw5VmxPYi1ZZG4zMVRSajhENXRfZ2Zvb3Y0RlFaR2Rwc0t6UDN3RmszYWJmZk9MQ1hFcVJxdG1TMFhOQXNBd2Rhc0RGLXo2S3FXaTlIY1U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQdkFlSk9FUHlGdVVzcV9jREd5ck9xMTZkU0MyUHFVd2hvNlA0elZuaGpQYndncThyMEd2d0duR2thRGdPeWdwaHlNRWtiQTFVcVlWMThuakN6bjAzVEpDTFhua1hnZUxnaEp6aXdKWkVyUGRycnhXUzhoMjlxUGRyQzRNTUxNRkswMWQ5NkxwNjlPcllfdDhyVmswY2Qza2hwNU0tczA3aldTOHM3c0s1aVJYekh2SnVwT0FRWjgwS1JBYzFRTk9heHBUR3QxX0lzbTlxMWxNLWJPZHhkNV91WEM3bFQ2ZDJZ?oc=5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>07-05-2026 20:51 UTC</t>
+          <t>08-05-2026 16:53 UTC</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AbbVie’s Skyrizi beats out J&amp;J’s Tremfya in in April drug ad spending leaderboard</t>
+          <t>Robert Eugene Blair | 5/8/2026</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Fierce Pharma</t>
+          <t>Northwest MO Info</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOdVZiNFlTMEhBUmI0N1VOTGw5eWRkR00ySW9TTHdtOERxV1JMRTFMNTd4bjdjYk5UVUNqWXEyVXMyM05icnBKbG5tdThNbWcwckZ2QXBxM0FOdmM3OUZoODRoWjk1eWpvUWpNYmpMSzhFR2JwMlc1cHBFeUZWU0JkdTRURkUtcFM3WXJaZl8xRjROcFFQMFZHY0ROOUQ0ZHMyMjA5OTc1bTUyV2R2T3VTc0Z3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE9rVTFoV283SV8xc21qNS1kLUNoUW1fbzlJZWg1Smx3MkplQUFrZmpaNTk2Wm40MDg2al9qR0VyY0FKcHYtb0VFV0NFYTY4UlRqNXpfbWRBeGJOOGNyaTZwTVBfeThVM0xXaW92Q2gtUE5NMmJBRlBCNFduVXI?oc=5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>08-05-2026 14:03 UTC</t>
+          <t>08-05-2026 18:55 UTC</t>
         </is>
       </c>
     </row>
@@ -787,22 +787,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>April 2026 — CDMO Opportunities And Threats Report</t>
+          <t>Cardiometabolic Therapeutics Market Size, Share and Forecast Study 2026 to 2035</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bioprocess Online</t>
+          <t>Insightace Analytic</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxQT0NqM0ZZWnRDenNHVHZkZTcwdnptbzRZallZU2hxRE1sVzBXbHU4MzZVcExaazZnR3BzMlJ2M3ZCNWJONmVrMHNqWEJGUldIVlJ5c3RXOEVsN0M4OGY3WGhCLTBkWFdqRy1Ec1F3aG9hc2s2bnZMMURoaXN5dWh3ZnROZmltcFVnLUtZUTcwZUtCWXR2?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxQUWxoRzRFSXhCckRGN3pqblF3VG9nUjhxZ3NYLWpoRVNoUkY1ZUhqSVZnSGNqS1NEWWNBejlfOG42S0hTNXBCWmItMEdlakFXQVBiUVhmSTNYdHJkcnlMcFFJbkZNQVlodmxXTVJ0ZDJYNGlSajI4Zm9EV21YeE9ObEgzVXB3c1E1c3c?oc=5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>08-05-2026 05:18 UTC</t>
+          <t>08-05-2026 12:57 UTC</t>
         </is>
       </c>
     </row>
@@ -814,22 +814,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Zealand Pharma Q1 2026 slides: obesity drug advances, $700M milestones</t>
+          <t>6th Rare &amp; Genetic Kidney Disease Drug Development Summit</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Investing.com India</t>
+          <t>pharmaphorum</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQOVZqblJNYlh6Vm5OUmtYYU16NlVIVG43UjJXNWVkdGxXM2U3N1kxY3FPQ1c4RkZWY0xYRklVTVRnV3Rnb1FlUWJzdHpEa3FqWXVCbWJ4bzBaXzZ0aTNhWm0xclpfSS1aeWF1dlhyckF1c21KSnJEallNMzFpV19ybVZ4ZmJOT3psLVlxNXljT2NseTVmbUNUYW4zalI5QzBkYWZRc2poMlc4MjhwajhCeWhIdEhZa3dzbDlpVWxlbmE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNa3JyclcyWmF3SXUxTnlwdjdFQ2ZxbXFPRkd3dy05U1NPRmpYQldYYWhlTS0zNUVLQTNhM0p0MFNsbTRkbU52NW5feklwa3pjNXlyeUVnWGlDQ2ptdGx2WFBYOHREVnRFOGNleVZPVUZxUGM3ZmtkQVRtN3h3YVJkbGJ2NnZKVWVyamIybkFNdw?oc=5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>07-05-2026 17:41 UTC</t>
+          <t>08-05-2026 10:40 UTC</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BioNTech’s €16.8 Billion War Chest Funds a Cancer Bet While COVID Revenues Crumble</t>
+          <t>German pharma faces “historic” squeeze as Merz targets €40B deficit</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>Investing.com UK</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQMldmZkZZRlJHcGVFZHFrRGZsWVkwZHJYNjVMclB6THB2bmZEaFFWdGdtdVBQMGRjXzF6Xzd1TnBqN3VhQ3Iza0o2LWRLUjdRSDZFU2lET214N2x5YjhZa2F3czVxem8tbDVuLUVLZ0NrTFVIZGtLMDFaUFBtdXpPZ0R1YWdoeHZ0Zk5RRVg0cWJiN0cxQ3AwWVhDbFpoamFpMDAtZXZ6UHIzTmF5WjZQQi13bmZwVjg2Tzd5LTdaRl8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQWFdPdXFZb2tVelgzZVBIay1xU3ltUmdvVGw1aFh4VG90UXViakF4TEUyODNzOWdNQUdmUmhpZXpFX2V0MGlVTkhlS3RNSmRvaG12UDRhUEFBSFNkTk9DYm5IV3MzdW1CLUJzaWdzSUU3LW42QlhlUzFFckM0bHRFNmNFaEdVcUxQU1NDMHhiMXJidDA1dlRnLTBFeEFSaFplZ1AxWEwtdXJHWmM4UHd5ZWJaTnZUdnVQRGx0XzJWLVJadHVpNGc?oc=5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>08-05-2026 11:00 UTC</t>
+          <t>09-05-2026 05:55 UTC</t>
         </is>
       </c>
     </row>
@@ -868,130 +868,130 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>6th Rare &amp; Genetic Kidney Disease Drug Development Summit</t>
+          <t>Steve Pakola and the Long Game of Gene Therapy</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>pharmaphorum</t>
+          <t>North Penn Now</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNa3JyclcyWmF3SXUxTnlwdjdFQ2ZxbXFPRkd3dy05U1NPRmpYQldYYWhlTS0zNUVLQTNhM0p0MFNsbTRkbU52NW5feklwa3pjNXlyeUVnWGlDQ2ptdGx2WFBYOHREVnRFOGNleVZPVUZxUGM3ZmtkQVRtN3h3YVJkbGJ2NnZKVWVyamIybkFNdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOeUVKTFNBXzZuWmpvTlFGNlNrQTZZMDZKeXAwNkZTUkM2V3BReWFjVE5Gcm5xeHZCcEJaSWtOVlRvV1pCRVQ2YzBHRk80WWg2UEI3alJlMlVvQ2l1VVBtWkh2VzI4c0hiTjZuTVpfc3pTMXNsTS12cnVFLXlYck5JZHBiMDhWU3RzYVgxYmMwYWY5ODQ?oc=5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>08-05-2026 10:40 UTC</t>
+          <t>08-05-2026 11:32 UTC</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Hikma</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Scleroderma Therapeutics Market Size, Share | Industry [2034]</t>
+          <t>Hikma Pharmaceuticals PLC stock (GB00B128J450): Dividend payer with buyback and growth plan to 2030</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Fortune Business Insights</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxNanc4Umt2b0Vfcm9xOTExajNVVGFrOF9aZFRnV1hUaWJha0ItODZwTW1PMS1VTHVqa0hyelcxYWtVQlBEdWRTWXZHc3ROLVJONlVmTFp0QWRBempxR04yOG5JY3pyUDczYy1wUmlyNG1kdGtfWlROalV1Yk9yMDhwNURyd0U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOUUp2Uno3MHpvcFQ1YWdPVmxFTER5UEVIZ3l4Z0tINHFrdV9xV1NVVHBxWDQwR2hydy0zNjg2QzNHYktrcE9wNXpZb2w1UjJqMFlIaGd6RFJPdXlPMUdNbU5IU0gzbWxicDRrdm9hVW05VlE4UDRXd2FSa3A2SHpFRXYzczAwUTZ0TnluOWhhRXB2T1g3N09sX2gtMEx1c3dXYm52dzhxOXdRdEp2dG5WaWNvX211OG9aVmU0M2U3dWE?oc=5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>08-05-2026 03:29 UTC</t>
+          <t>09-05-2026 07:53 UTC</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Hikma</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Saxo on Zealand Pharma: Keep investment case in mind before celebrating stock price</t>
+          <t>BioLargo Subsidiary Clyra Medical Signs Exclusive Distribution Agreement with Al- Hikma FZCO for ViaCLYR(TM) Across the Middle East, North Africa, and Adjacent Markets</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>medwatch.com</t>
+          <t>ACCESS Newswire</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTFBURWlRd0RjZGxWWDMxWnN5Q01hUEY0eVVrU19leEtfaVFKZXVHVkpLbDk1YmdzZWtIRjMzUDZmR3ZWTDFUemNmWjlGRnBUVWc3YjNGWHFLVXdXUWRHX3VaVXdGRG5tVHFF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxQLVNxU2Vzd2R2dWxBamRzc3hOLWZaQ0pYU2RLR282cU1FR1BQSnJ4NnVUVHFSU01JeC03U2RacktmdlhKeXMtUlFkQU9wb21aX0l0Q1NkbjNKcDZ3eHJxZDc4SDdwdXV1QnA0Q3pmcUsxNGVLMmx0T1lZX3BqRmxZb2lQT2l0TU5RcEVXb3BoMXRzN2h3MUFNemo3Nm4xMXFzc25mTVllRVVMX1ZpUm9BRGR3TGgyWW9sclZGV2lqNWZIdzJLaVFFbTVuT2ZocFowTGMwY1d0My1oQlNkQ3VmNndMWTE?oc=5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>08-05-2026 13:10 UTC</t>
+          <t>09-05-2026 05:56 UTC</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Hikma</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Steve Pakola and the Long Game of Gene Therapy</t>
+          <t>WATCH: Interview with Mythili Markowski, director at Regeneron</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>North Penn Now</t>
+          <t>Life Sciences Intellectual Property Review</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOeUVKTFNBXzZuWmpvTlFGNlNrQTZZMDZKeXAwNkZTUkM2V3BReWFjVE5Gcm5xeHZCcEJaSWtOVlRvV1pCRVQ2YzBHRk80WWg2UEI3alJlMlVvQ2l1VVBtWkh2VzI4c0hiTjZuTVpfc3pTMXNsTS12cnVFLXlYck5JZHBiMDhWU3RzYVgxYmMwYWY5ODQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPaEUzTkV6QmFQdEJpRFRFTUE5Xy1iVXM0M1lLcTF3WG04Y2Zscm4yRWtCWk5fVnY5bVFTaEdKZWM1MXhDbExPVzRqQ0VIcjFudzhhSGJOeGF0WXRTa2ExMEtDTXZVdS1YSlJ5N2JvS0Uwc05OMlJCU3diU21SLUc3alZrZUxjT0E3b3ZXdGFZTU82YU1RdGVSYzBkM2FxUQ?oc=5</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>08-05-2026 11:32 UTC</t>
+          <t>09-05-2026 03:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Hikma</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Eli Lilly Shares Lag Market Despite Surging 2026 Revenue Guidance</t>
+          <t>Siga Technologies Q1 Earnings Call Highlights</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>HarianBasis.co</t>
+          <t>MarketBeat</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE9aNkluaXRDRjJlUktuSkVIelBSc29RMFRuNEloNTFfakw2cHhnRDM5bGFnTXRSTnJVa0w4aDFtMlpkcDZQc2VoSGNPTXA0OFJrZFNibWg3dG9Ka3pSajlwSGJPQTc0VTdGT1oxSk41cVZMUWZYb2h1OGVWWGVENWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPNFgtOWhTbGk1cXphdi1vdjhyT0pDYlVkdTdueHpjNUpVUGZrQmt3a2QzSFV4LU9oR1BTRWY2cjdDNThIS2QySl9oc0xSRXEwd285dkRJdWFmQldNUjRPSVRfeGRsODFNbWxfNzJhM3VNRW5IRnhVRFdLUVI5MDlvanVXVE1fNWtyRUtGV0FRaVgzUW9GeVpaa2xBRk11cU9B?oc=5</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>07-05-2026 23:22 UTC</t>
+          <t>09-05-2026 01:12 UTC</t>
         </is>
       </c>
     </row>
@@ -1003,130 +1003,130 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BioLargo Subsidiary Clyra Medical Signs Exclusive Distribution Agreement with Al- Hikma FZCO for ViaCLYR(TM) Across the Middle East, North Africa, and Adjacent Markets</t>
+          <t>SIGA Technologies Projects Revenue Growth and Strategic Expansion for 2026</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ACCESS Newswire</t>
+          <t>HarianBasis.co</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxQLVNxU2Vzd2R2dWxBamRzc3hOLWZaQ0pYU2RLR282cU1FR1BQSnJ4NnVUVHFSU01JeC03U2RacktmdlhKeXMtUlFkQU9wb21aX0l0Q1NkbjNKcDZ3eHJxZDc4SDdwdXV1QnA0Q3pmcUsxNGVLMmx0T1lZX3BqRmxZb2lQT2l0TU5RcEVXb3BoMXRzN2h3MUFNemo3Nm4xMXFzc25mTVllRVVMX1ZpUm9BRGR3TGgyWW9sclZGV2lqNWZIdzJLaVFFbTVuT2ZocFowTGMwY1d0My1oQlNkQ3VmNndMWTE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOX1cxRllScFFOaG5SakZHT3pFbTBaSGY5UmhmU1RVMTNGNnB6WU9CSEpYSlMwS3dkVjlzQ0pnd1JLYV9pYkVpcFFiS08wbWQwdDc0N0VSUFdPQ3pZVzNiY0ZrUzJoazVIX0pJeWgxS2RmTVhsQks4bWRUcnc5T3JIYjFxWTVYLWN1MFAxUHFxREU?oc=5</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>08-05-2026 03:23 UTC</t>
+          <t>09-05-2026 07:38 UTC</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Hikma</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SIGA Reports Financial Results for Three Months Ended March 31, 2026 and Provides Business Update</t>
+          <t>Is Amgen Stock Poised for a Rally?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>The Manila Times</t>
+          <t>Trefis</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAJBVV95cUxONThrcFlRdGJiWWwyMEVENlRheXkwb0Z1MHJQRllTYVB4Y2FXS1ZEZk4yX3dWd1V4VXN4OUY4UjFkdzYyc2RTa3Rkd09ock14V2lydFZCWUJzWWZ1MFBENV9IOW84UThwNFZnNnJKU0VjUGIzSWNMR0l6QnNxVlFmQTJsNFN3VUVlTjhMRW5WbVRPQXloUTZkSllyeENjakVQUjB0TkZWTjQzLVFKRnFzNGt6eXdMQ1NEaWc3TU9KczRva3ZlM1BqVFlEZHdRTWFpT3JNLWw5OVRIaERUUUFCVFBla0Nsc1EwX1VadHh5SE93c3BnZkVpS0FEa2RrWjhlb1p5M9IBhAJBVV95cUxONThrcFlRdGJiWWwyMEVENlRheXkwb0Z1MHJQRllTYVB4Y2FXS1ZEZk4yX3dWd1V4VXN4OUY4UjFkdzYyc2RTa3Rkd09ock14V2lydFZCWUJzWWZ1MFBENV9IOW84UThwNFZnNnJKU0VjUGIzSWNMR0l6QnNxVlFmQTJsNFN3VUVlTjhMRW5WbVRPQXloUTZkSllyeENjakVQUjB0TkZWTjQzLVFKRnFzNGt6eXdMQ1NEaWc3TU9KczRva3ZlM1BqVFlEZHdRTWFpT3JNLWw5OVRIaERUUUFCVFBla0Nsc1EwX1VadHh5SE93c3BnZkVpS0FEa2RrWjhlb1p5Mw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNcFdKMmk0TXo5QWVRUU5RSDNHVGJiZjdvR09uZGxsdlFzZjZKOTI4RHhkRU8xTVlFU0hGUTdfOVR3MTdySmdWSzVnV3J1QXIybVV5UENEZHRJNHVKcEtzUnQ3T2lqZkJZdFRxSnBxMlF0Qmc4VmJqM3dxT1F3LUZaYlg5OW91TDRCeVJaZk4zWGttYkprdDhLNGZwbUx4QQ?oc=5</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>07-05-2026 20:06 UTC</t>
+          <t>08-05-2026 17:43 UTC</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hikma</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Earnings call transcript: SIGA Technologies reports Q1 2026 loss, anticipates Q2 revenue boost</t>
+          <t>Is It Time To Reassess Amgen (AMGN) After A Steady Share Price And Strong DCF Case</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Investing.com Canada</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxNdklLTDZkalk3ME5OcFZVV08xdnVhU3ZsdVUzQlRNdW9uZXNrSHFjNmV5c3JCczdfYldKRG5qT0RQSDBibHJVblJnV01FYVVhclFuejlBVlNZaWpGdktkS1VYbHVlalR3X2RUTmNXeUtyZ2FGUjVtWGw2ZF9INUhWdERWVl9sZncxcHY3ZXdHRXhFTnRwRUFJRTM2ZjVzMFNFeFVXRE9uQUxGM0ZiUGJDWmEyRzVDV2dBaUx1T0h4eTdaNmEzdU1oS0lpcEFOOF9KRC1hdFZHT2ZBdkY0M1hZTUw2MzJNMFhR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxQRE4tVS1pWFJya2JZbVVzVmkwRkJCRlNxMjd3RXoybnk0ejNJWFF5WWhvNG1tNENHRlJVWmo2NXZFc29qeXE1ZWthbER6ZUllRDhVV3BsVkVzRjNFNV9GY3lZN3U4WG1NREdDcVRHdUcwelRLY2UtY0MxQ3Atbk54ZjRfaFlkaVppcG53WmlfaFNyUzhvUFh6MzhsV1NGaGxGWkJNT3hmalJKeVhaNF9pY3pUbXlKZ19WWloxOHVIQjMzWVRkeVRxZUVrZWZDcGN1WVlldEFpVVMxQknSAdsBQVVfeXFMUEROLVUtaVhScmtiWW1Vc1ZpMEZCQkZTcTI3d0V6Mm55NHozSVhReVlobzRtbTRDR0ZSVVpqNjV2RXNvanlxNWVrYWxEemVJZUQ4VVdwbFZFc0YzRTVfRmN5WTd1OFhtTURHQ3FUR3VHMHpUS2NlLWNDMUNwLW5OeGY0X2hZZGlaaXBud1ppX2hTclM4b1BYejM4bFdTRmhsRlpCTU94ZmpSSnlYWjRfaWN6VG15SmdfVlpaMTh1SEIzM1lUZHlUcWVFa2VmQ3BjdVlZZXRBaVVTMUJJ?oc=5</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>08-05-2026 01:08 UTC</t>
+          <t>09-05-2026 01:03 UTC</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Hikma</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Siga Technologies Earnings Call: Cash-Rich, Orders Ahead</t>
+          <t>Amgen quarterly earnings beat but stock drops sharply, MarketWise reports</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>Traders Union</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNb2ZtUzFnS0Z0WEVOUlhxWG8tYTZzelJGd1RoQ1RhQ09jeFpWd1lJbVdOdjE1OWg1cTZtNkJWSS1Zb0V5Z05XNlVoNkpTWHl2WEZDdEpoNnNNNjR4OFc2cEFnbjhWazFjSHRsWTE4QWIweUpKeS1kU0ZtNW0zZGptZW9sYkRCeGU2R3JxYWVCb3NPcWU1aW1MTGpOTUtxTURvWHREeU9SdEZfdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE9mZEtia2R1ME9vUV9nMkdoaXppN1dLOUs0WlU4S2dnU2NxeGlqZWx0NFNWQXFUWWpyalBXRG1tWU5Ha05NT0tNR0V4UnRmQjlzLUE5TWlydURfSHVaNVNPbWtFbE5GNy12T3hRcDBHY2dpaXUxa00yVzEwMk1uMXc?oc=5</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>08-05-2026 02:41 UTC</t>
+          <t>08-05-2026 17:25 UTC</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Hikma</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Igbajo Polytechnic ND Weekend/Daily Part-Time Admission Form for 2026/2027 Academic Session</t>
+          <t>Amgen Inc. Stock (US0311621009): Shares Dip After Strong Q1 2026 Earnings Beat and Analyst Downgrade</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MySchoolGist</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTFB6ZGJpb0VLZTlOcDkzSFJ1clNhbDlmbllJLTl2aHBvNVByc1l0Q2ZLN0pKWWlGM29OQUszVWpKZkhnZDk2NFBmU3dkWGNhOEZEb0ZJMWU1WloxNDRDSkh0cjl0MUplcVhxT0RETGplMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxONmlOQnhETkloS1Y4eHJJaTk2bDNacldPN1FhODB6NlBHa2FnZnlmUDl5MkhoSkNCQW5NLU9SdlZyeUt1UlBPdHA3b2VQNDFpTy1RQk9UTE12TlZWRkhGN1Y3N3RDZ0ZKUmtYaU5fLWZwYUY5aXBqUEFDT0lWTHprV0tPaFlpb1YzOXZUWFdHdlVqQnV0ZHRPVFRwWXZseHBuTUJ4LUpsejV5Y2tYX3RpajJUT204bVg4eVZ3NWpvaTlEVTc5NFRr?oc=5</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>07-05-2026 21:23 UTC</t>
+          <t>08-05-2026 11:17 UTC</t>
         </is>
       </c>
     </row>
@@ -1138,22 +1138,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>AMGEN TO PRESENT AT THE BANK OF AMERICA MERRILL LYNCH GLOBAL HEALTHCARE CONFERENCE</t>
+          <t>2 Dividend Stocks to Double Up On Right Now</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>PR Newswire</t>
+          <t>The Motley Fool</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPcldIVU5iSjdvUWstWVZuTXUwTjdZWmdKS1FzM0duSzNzbGlxU1hVenI5NkFSTXhqVFF6aE40RTBGNVg4WGNyZU5CanhMdV9rTll3TGFMbUpvQmRsaC1zUHNFNjZVdVU4emRhS2VYckVSYXZubVl1NFZ3SUVrRVlFc2FzdWxydDEyYlJ5V1dRUFAxT01ScVNKOGdzNVZkNC1rTXplcVJuWFMyZ2wzS2ZhelA0S2FJNndZUlp1dUt1Nkc0QzJtQ0RkbWFTclBtVmR3WVQzVA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQdGpvWFJKQllXUmg4TmcyM0hZMWwtUmFsdGxWcGdfVGVBOWxwNnlqdEVMaTQxVG96dTNGLWlKZDM2RkYzZk9HZ2VlVTRLTUJ0dHBaQ2t0eGdJZmUxRi1OX1VuQjdDUUUtS0RmNmYtOHltRWFZbW9aVWR0TS1peE9CMmk1cXU1Mmx1Mkp2dVJDWQ?oc=5</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>07-05-2026 20:01 UTC</t>
+          <t>08-05-2026 18:30 UTC</t>
         </is>
       </c>
     </row>
@@ -1165,22 +1165,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Amgen Inc. stock (US0311621009): Rating upgrade and Q1 beat amid tax and regulatory overhangs</t>
+          <t>FY2026 EPS Estimates for Amgen Boosted by Erste Group Bank</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>MarketBeat</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNZEJQQnJSd0pxb1cxY19BLWhUUHk4d3pVTUpWMTZILXU2R0pxSEF1MHliQ25CTzVPTHYzcXRIVnFUcFFmMlk0V21TSHFzRl9qVDlfSWtDTXhPQ1RINFNCX3VMLTNwWFUwbWdCUWZZQzRyRmNkM0d3RnF2WmFNT19NNkxMdEFLYWdwWHdiRmdRNkZPOU9KX3U1MU54bVpLWUNMUmFOOWJYeVJfd1JwbEJlTWZfbktEVFV2QjFXRFVxQkhfYlJWZEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNNVRfVlRCZUhNcXJqUENRNVRwMU1NWmZjNXZZNnVDaXo4Q1ZEWkhRUXBVRG1RR3loRnRWNHNmNGhUbHhQbkpUOUtHbXNQVWMyRXE1SjF4QVN1dTRXQ2xkZmdIdDhSQTRvYVJXa0U4cVo2RVlnR2t3M29vRWw1d09LeGxDUjg2bXVTdGV1VW1aTVVaeS0tTFRMNUdOb0tOV0twa2JVNHRUYkRaUWgwSjBtanpR?oc=5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>08-05-2026 10:58 UTC</t>
+          <t>08-05-2026 12:42 UTC</t>
         </is>
       </c>
     </row>
@@ -1192,22 +1192,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Amgen (NASDAQ:AMGN) Stock Rating Upgraded by Freedom Capital</t>
+          <t>Guggenheim Trims Amgen Price Target to $340: Is the Biotech Giant Losing Its Edge?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MarketBeat</t>
+          <t>AOL.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxONk16NnJSWXhHbE8wcV9mM09URE1peDFPR1lWdVhpNktQcEhITC1waW9QZmYzWkJlMDNYUl9BN3hVZHY2ak1MX1BZR1U3MUgtVDlLUFJHdHl1Ty1ueW4wdUpOeGl6d09jLXNPaXpqNTFJTEZDakRlQkt6WVYwSkRGbmtRcFJnSjdIcWpIbGx6Y0g2MVlxNVZqUS1fQ3ZUWmEtcThicG0zTjY2QjBjRlhSTg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOY0hXVG42cEhDME1pX1RMZ1RCaVNWNmttczBxRUdVRlJUaGpGdVNEeE03dWsxSDF3TWloeFFUaU9qYlFDcEtFd1JDdlh0MS1MZUxGLThtcHVCaHpMc3k2X2EwV2ItVnVqdU1LSFlwZWpPNHhjcEkxZWZaZ1JpZmhLc0hYdFpsdw?oc=5</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>08-05-2026 09:47 UTC</t>
+          <t>08-05-2026 18:32 UTC</t>
         </is>
       </c>
     </row>
@@ -1219,22 +1219,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Amgen Stock Falls Despite Strong Earnings: What's Driving the Decline?</t>
+          <t>Puerto Rico attracts manufacturing investment with Amgen expansion</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MarketWise</t>
+          <t>WJournalpr</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxPUVA1dWVwNXJuTWdBc19IbDluYkVPbmI2MnNkdXdCRmdXWVZxRkZZNkNPR2NNQWdlSE94bThmQTN5OTNsZUNWdjY0ck9jVDBaTklMR2pNckt2bXBvVW9wMTc0NVA4RGZpTVFMTUk0bm9qaVJQUVdRRjRYQkN3a1FyUFlSZTEtcW02bDUzY1NR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxNTFdhNy1iell0NUFZQUlrMUhsYndJZzJ4WlJXa2l0MERjbnlVZzBBaldBNFpHUTFtNEVLV0FOT1lMUHVONF9Gd1lMY0NVWnhlX0liZ1Y4TEFSR0RxM3NnRU52Nng3U1kxQ0NVbFF6c2NZQTJFNTB6LVpIczhKbUF2QkY5NXR0VUVVWENGQmFQa3ZtM2NoN3gyd1VfSHZNUEkyQ2dESXRlbGdNdDFQeUFSOW5ac1BPRF80YkM5SlE5bEFrMTVUV01yenJld0FWN29kQUVzM0FGcWU2U0FnMHFHZnBOV1BGUDA?oc=5</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>07-05-2026 19:15 UTC</t>
+          <t>08-05-2026 10:00 UTC</t>
         </is>
       </c>
     </row>
@@ -1246,22 +1246,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Puerto Rico attracts manufacturing investment with Amgen expansion</t>
+          <t>Amgen Halts Phase 2 HZN-1116 Trial in Sjögren’s: What Investors Should Know</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>WJournalpr</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxNTFdhNy1iell0NUFZQUlrMUhsYndJZzJ4WlJXa2l0MERjbnlVZzBBaldBNFpHUTFtNEVLV0FOT1lMUHVONF9Gd1lMY0NVWnhlX0liZ1Y4TEFSR0RxM3NnRU52Nng3U1kxQ0NVbFF6c2NZQTJFNTB6LVpIczhKbUF2QkY5NXR0VUVVWENGQmFQa3ZtM2NoN3gyd1VfSHZNUEkyQ2dESXRlbGdNdDFQeUFSOW5ac1BPRF80YkM5SlE5bEFrMTVUV01yenJld0FWN29kQUVzM0FGcWU2U0FnMHFHZnBOV1BGUDA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQNUNQNElnVzlNTDlDV0dIMHhJWC1XMVV0eXB4SGRsdjhnb0c2eUpXazR1eGhDN252LVRuVVNaV2NmdnQ5eXkyYnNGdGFaUWFPZDdHYXAwMnlPVkFOSmJEX09PRUdUSHZuZXhBU28zT3RNaUJyNjlYUGtWc1YxMkFZZ2Z6dVdsXzJRc2RIRl85UFRyZjhEVk0wVENzenJzaklhcHF2empEem9fWU5zUjBjSTh5MVQyRnFtRTM4b1RNMnFJMnc?oc=5</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>08-05-2026 10:00 UTC</t>
+          <t>08-05-2026 16:38 UTC</t>
         </is>
       </c>
     </row>
@@ -1273,22 +1273,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Amgen finance and R&amp;D chiefs will speak in a public webcast May 13</t>
+          <t>Amgen Inc. stock (US0311621009): Rating upgrade and Q1 beat amid tax and regulatory overhangs</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Stock Titan</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNSWxzODIxSk5CNEwxUWJLU0JZb3ZhOWhWcVFSZHZqOFVTcDVZc29zeVBFdU9QRWcycTRvSXVHa1ZHT2ZENUU0MkdnS2JhOEpMaGFYb2ZPVG9HVGo3aERJTkNnT01jWnhaWGpCRlNuWVo5cDNyVnozVHFqUnpmWVMtQ3pMUGhYSENWaGhFRzI2Q2dXTHJvTHBsQVBpaDRXMHdtYWR0dUFPSmF3TFkydGlVVGZqd1E3dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNZEJQQnJSd0pxb1cxY19BLWhUUHk4d3pVTUpWMTZILXU2R0pxSEF1MHliQ25CTzVPTHYzcXRIVnFUcFFmMlk0V21TSHFzRl9qVDlfSWtDTXhPQ1RINFNCX3VMLTNwWFUwbWdCUWZZQzRyRmNkM0d3RnF2WmFNT19NNkxMdEFLYWdwWHdiRmdRNkZPOU9KX3U1MU54bVpLWUNMUmFOOWJYeVJfd1JwbEJlTWZfbktEVFV2QjFXRFVxQkhfYlJWZEE?oc=5</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>07-05-2026 20:11 UTC</t>
+          <t>08-05-2026 10:58 UTC</t>
         </is>
       </c>
     </row>
@@ -1300,22 +1300,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Amgen stock rating upgraded to buy at Freedom Broker on growth</t>
+          <t>Amgen (NASDAQ:AMGN) Stock Rating Upgraded by Freedom Capital</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Investing.com UK</t>
+          <t>MarketBeat</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNNGlvX2twWWhyX1ZnVkVPM2tXcTlFS2ljUkFNcHdNWE5uTG1udFQ5bFFMaS1STldQQnI4ZkpNcERQa3dNcU9iOE9neF9uaTE4alRsbzNiTHFiQzJDNGdGd2tYeWU1bjhhS3h6M1JHanlhNWR6TEpqLWZmTlU5aW5UQUlZSDJLclVqVTBRbWUta2xwVE9ELUo5VjZ6MkZxc3hKclc2clk1clpWbnFKbm9oZlVCeUJTRXpUb1I5b2JLY01QWjRmMzhDOFowbWRIRGhh?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxONk16NnJSWXhHbE8wcV9mM09URE1peDFPR1lWdVhpNktQcEhITC1waW9QZmYzWkJlMDNYUl9BN3hVZHY2ak1MX1BZR1U3MUgtVDlLUFJHdHl1Ty1ueW4wdUpOeGl6d09jLXNPaXpqNTFJTEZDakRlQkt6WVYwSkRGbmtRcFJnSjdIcWpIbGx6Y0g2MVlxNVZqUS1fQ3ZUWmEtcThicG0zTjY2QjBjRlhSTg?oc=5</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>08-05-2026 02:13 UTC</t>
+          <t>08-05-2026 09:47 UTC</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FY2026 EPS Estimates for Amgen Boosted by Erste Group Bank</t>
+          <t>Generali Asset Management SPA SGR Raises Stake in Amgen Inc. $AMGN</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNNVRfVlRCZUhNcXJqUENRNVRwMU1NWmZjNXZZNnVDaXo4Q1ZEWkhRUXBVRG1RR3loRnRWNHNmNGhUbHhQbkpUOUtHbXNQVWMyRXE1SjF4QVN1dTRXQ2xkZmdIdDhSQTRvYVJXa0U4cVo2RVlnR2t3M29vRWw1d09LeGxDUjg2bXVTdGV1VW1aTVVaeS0tTFRMNUdOb0tOV0twa2JVNHRUYkRaUWgwSjBtanpR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxONkJZZEpMU3BjYU5nbzRUT0tUYjFtcjdEdjdDMWFoeXg1TzRtWHg2QjZpLTNWTXNncExCcHZxdktLb3dkbjJLdHhfNzF1NTN0SElyT0hjR0JFdm13TndST3NXRXpmcUwxQ1ZmU3NHSDRnRGV6c3puWkt0dlhmSlA4ZVlFUTZmV1VmMjlVNC1NWnpCY3dkM1ZOMTNjVE5EdFpqS3R2aGhPc0sxODlhOWtfbl9Na2pSQlNtandEM1dfLVlHb1k?oc=5</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>08-05-2026 12:42 UTC</t>
+          <t>08-05-2026 09:04 UTC</t>
         </is>
       </c>
     </row>
@@ -1354,22 +1354,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Amgen (NASDAQ: AMGN) director Omar Ishrak granted new stock award</t>
+          <t>GRIMES &amp; Co WEALTH MANAGEMENT LLC Sells 4,111 Shares of Amgen Inc. $AMGN</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Stock Titan</t>
+          <t>MarketBeat</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOMmxzeFVmMW5MOUJTY0V6bjhmdkV5emRJd25WNnY0U042UDdNeHJhaGJuZTZKOXNHMTVGNDFGWEt0a055YUVJQXFwRHgzeHVSNlBlS09tNUo0ZzBNN0RfWXNCU29BY0c4dXI4VGpxTnVGenJ3aUFHMkpEdm05WFJhYkJqWndkb2Z3Q1NuckxvU2J0VUs1UEhNRFVEeDZja1lDU2h3Z2VR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNNk9vNzA1Sk1xQkZVM1NQNWk0Mk5ZbkNrclZUZHhKNGg5ZElMNGJmcjdHajFoenVEV3pTMkJSdWozbjhSLUdYeTZIVkV4S0VuX3ZvZzhJbGpYeVk4a1BuRWc2OHh4S2E5RVRabUV2Y0t4bDg4NnhzbEYxUTBOVUFsVXdfOGc0Q0p5dDlVYlI3RXJWX1NwdVNHeDNkRmJ2SFVEeGxHekZHQTBJM3NYMlg3SFIzcnNGT0prVm1zS0VNdnc4Uzh5Vks0?oc=5</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>08-05-2026 00:50 UTC</t>
+          <t>08-05-2026 09:04 UTC</t>
         </is>
       </c>
     </row>
@@ -1381,34 +1381,34 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Generali Asset Management SPA SGR Raises Stake in Amgen Inc. $AMGN</t>
+          <t>Atrial Fibrillation Drugs Market Set to Boom Rapidly,</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MarketBeat</t>
+          <t>openPR.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxONkJZZEpMU3BjYU5nbzRUT0tUYjFtcjdEdjdDMWFoeXg1TzRtWHg2QjZpLTNWTXNncExCcHZxdktLb3dkbjJLdHhfNzF1NTN0SElyT0hjR0JFdm13TndST3NXRXpmcUwxQ1ZmU3NHSDRnRGV6c3puWkt0dlhmSlA4ZVlFUTZmV1VmMjlVNC1NWnpCY3dkM1ZOMTNjVE5EdFpqS3R2aGhPc0sxODlhOWtfbl9Na2pSQlNtandEM1dfLVlHb1k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQOVNuVVV4d3oxcnhoZzV3dktjaDFuVnVJUFpYYjdRaXktUDl0Zkl2NHprRGtva3FsdThlV1BPTGl5OHNSMXprSVFicUpnbmVNQnBmMEtDdE9nMFl1RUlOZmJNN3FTcDV1WGEzQ0trczc4dlhITm5ZajJFUGk3ZDF2RTZmTjRSaTUySnJ5OWFoR0RzZw?oc=5</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>08-05-2026 09:04 UTC</t>
+          <t>08-05-2026 12:51 UTC</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Amneal Kashiv Biosciences</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Amgen (NASDAQ: AMGN) director receives stock award and updates holdings</t>
+          <t>Amneal (NYSE: AMRX) director exercises 48,747 RSUs and receives 30,837-unit grant</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1418,39 +1418,39 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQMm1zZ21NRlFlWERjb09jNE9ob1dURUU1WEtBSy1pMlFFdE1tVWVkQUs0bFhGRl9DVThpWGdJTGVkQTNlUEUwdkU1ajJkbHBmYndmcjdkZWVBd0xSZmRYOGNKcFdEUzE5a25LOWVIZHdESm9oOVJsVEJibkpES29obXpZV0hrcm9DaXZUQng1NThrZGlkTHc2eHQzUU5BQzZyRnZOdDdB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxObFJ0MVBUOU54OFdjX3ZhLXFOMXYtN0J3eHpnQUpSQmhfMFJVYkJ2cmNJVHpmZzRaR1Rja3dGM1d2TW1JN2pETm9EcUFoVUdjdThuYzZaMmJNQ3JPamZjQlBBUW5GSC1CNkY3RVhzT2w1djlPUklHa29kNFFmRXViZm9fQ0NUTTdyWmpGOTJLR0hRTHRYbVhtODVkYVFHdi1qWkZ5ay1BVFUtV2hBVDN2RGM1TEp2NFFCOG1QZA?oc=5</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>08-05-2026 00:50 UTC</t>
+          <t>08-05-2026 20:22 UTC</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Amneal Kashiv Biosciences</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GRIMES &amp; Co WEALTH MANAGEMENT LLC Sells 4,111 Shares of Amgen Inc. $AMGN</t>
+          <t>Amneal (NYSE: AMRX) director settles RSUs, now holds 128,479 shares</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MarketBeat</t>
+          <t>Stock Titan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNNk9vNzA1Sk1xQkZVM1NQNWk0Mk5ZbkNrclZUZHhKNGg5ZElMNGJmcjdHajFoenVEV3pTMkJSdWozbjhSLUdYeTZIVkV4S0VuX3ZvZzhJbGpYeVk4a1BuRWc2OHh4S2E5RVRabUV2Y0t4bDg4NnhzbEYxUTBOVUFsVXdfOGc0Q0p5dDlVYlI3RXJWX1NwdVNHeDNkRmJ2SFVEeGxHekZHQTBJM3NYMlg3SFIzcnNGT0prVm1zS0VNdnc4Uzh5Vks0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPRzBISHVCNmhqc2JZUHljSkprOWFpUDBSUHlCTGMwZ2VldGdnYXJKcUV2V2R2UnAyYkRMVE9QR3RHVWF5Uk1QQmpiMWlIQ1lFNHJ1ZXlPSjhrcGtZNVdmcERiaFB6X0Y0Nk5GMXlNZWFTU2NYbno4ZU50dWlQVVM3MGlVNXd5M2dPRzlFQl9fTEl2QVZld0FEYmszbUcyUEFqN2Z0MG9CWGJodjhENFpQVXZJYkdEMHpuWXZydA?oc=5</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>08-05-2026 09:04 UTC</t>
+          <t>08-05-2026 20:28 UTC</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Amneal Pharmaceuticals (NASDAQ: AMRX) posts Q1 profit surge and inks $375M Kashiv acquisition</t>
+          <t>Director boosts stake with 34,819 shares in Amneal (NYSE: AMRX)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1472,12 +1472,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQSzZubmgzTWJxdVRtSmZNRHR3ZGIzWFNZdFpLVnJING1rMUhQa2NxbnBKRnU3bDhNa1lzN2U5dGhOM2lNOUw5YUFyZ3BCZG4waldTU0lFdEM4ZTFpTm5PZndud0Q5WDNvUnpNbzRZd29WTFZZcjNiMHJ0LWN2VFNQMF84VGVlTF9kdTN2UUthTjcycWt0Wi1KWFdQRXkwbDh5a1BlSGxhMTFhZ3k2UHFsM2JjV3VncnJPWi1B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQUmY5d1VmNXNpVzJkZlU0aUlBbndYMC1rck9CWnRLVVVPMFpnVlJEN2VxYUZqNWhyWER2dWtQLVh6UU5TTklRbkUwOTRxNXp0SllXUkliZFBCazlSY2ZCb2FSMUs0RXV2Z1VMN3JXUVM3VFd0WGhwLTVZRldpMzBtN241MEowa2t5WC1VSnBwN191RVc1WDA4bEkxcWtHb2xvQW4xc00yQXNyMVRfaEZOZTlSaDM4N0dmblFYQQ?oc=5</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>07-05-2026 20:22 UTC</t>
+          <t>08-05-2026 20:23 UTC</t>
         </is>
       </c>
     </row>
@@ -1489,22 +1489,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Amneal (AMRX) Q1 2026 Earnings Transcript</t>
+          <t>Amneal (NYSE: AMRX) director converts RSUs to shares and gets new grant</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AOL.com</t>
+          <t>Stock Titan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTFBXbVhic1dDRk1rUzM4TnJKLW9mbGlJYk9ER1h0SVo4LWlkbmVEV0hyWTlZR0hCdWRzN2VPRURJWER2ckxKdXVWeU5pd1FPZzBhajB5cmttSzBFQ0dIWFhBbU81VzVUWFBaRnZIWXRBVlpGWnNHQUYwQTZzdXk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQLU9LV3Q4NUM1SWZlSHlwajJZbnQtNjFFbk0zTkZoSHJyUHk0VnFzWnZFZG5MRm9xcDZ2QVpFeDhJbC1QbU5ITVFIX18wMTRyUDhUdTV0TEFvMjR1RnB5N3ozNUh5aXBBUmswbDEzcjAwOE5GcWtvdXlLMF9Zb1RWVXpCR29WR1FJN3BCV1l2MkNLdHNQMGtHQ0JYZVprM2V2cXAtNTh2S2dxQlM4T2pwMnNxSFFGVllhdFItbg?oc=5</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>08-05-2026 01:26 UTC</t>
+          <t>08-05-2026 20:22 UTC</t>
         </is>
       </c>
     </row>
@@ -1516,22 +1516,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Amneal Reports First Quarter 2026 Financial Results</t>
+          <t>Amneal (NYSE: AMRX) director exercises 34,819 RSUs and receives new grant</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>GlobeNewswire</t>
+          <t>Stock Titan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOQlRoRnhpRGV4NTZSWXhtX0stcnBiRi1yN2tUUUxkaHpJWGd0SnhPaDRuOERvN0pzcUlzUklVbXZWQ3oweDNfN1YzNXVCRlpBQk9zczNxZXdEYnpqRE5vSjBSejlnSDNoR3VqNEVyRU14QnozTVA4R0NyTkRUMzdtZ2RzdGpxR0ZTNXF5YUpQRFJ2Und4MnlkMGFwbEFFVW5pWklkeFdVcEcxLXNjS2lUX1ZFdlNjNldwRmQwNkl1QUo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOVDJlSU1KMzF0WUZjekFjMVkyaFVoUUFKWnVlR3JOR2xVdEgyZnczZ3lTMFU4akE1QTNfOGxLTG44Q011RllveS1EcVRSLVBTZjhHUE5aMDdTNjA5SHlSVm1pcVNPV0gyenRVRUtfZ014cUhQSjZZNzBYcHVYMF9BRDQtS2c5M3JoenhhbTUtVUdweGd2TXZXREFsQnFPQmt0OEc4ZlRTN0tQcXYySkZySXFEVWpjMlZuZGJwcQ?oc=5</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>07-05-2026 20:01 UTC</t>
+          <t>08-05-2026 20:29 UTC</t>
         </is>
       </c>
     </row>
@@ -1543,22 +1543,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Lakshmee Foundation accelerates healthcare expansion with Rs 90 Cr contribution from Avantel Founder</t>
+          <t>Amneal (AMRX) director exercises RSUs, now holds 260,252 shares</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>BioSpectrum India</t>
+          <t>Stock Titan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxQMjVUbmdhY2tpbjVETTUtM3htS0xPT003aFhVOWp1NGh6czBKT0tvOUVkWERZbU1wQTZoQkZ1Y3VSNFBaNGVveHlmdTRHNU1JZVhZamJDMTJqUWpTQ3BvTGJxMGZtdThpcVJGM05zOHpySTlNSGQ0eDY2SGE4blN6R0hhRUZJSEo0VUN2LVQwSXBhc1hQUDJZc083bTlaMFMxYnZrX2tQcXRwcDMydGVkbXAwOWhXT2lacU1VZ1NrTnFHSTF1WTFQZlRrNkNEVEo4SFFTNUtsb2NZRU9NdDQtMG90c3pEY2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPeHdoVS1nc3ROQkNndThyWXpaYUlJb2otdzVSTlVPSTJ2ckV6di1JS01mai03MTFDZXc1RGZldFoxWkJFcjZUZzdnMi15SHFrWVh5RDFYQnhFT1d3N3RRWU14dWg1a0UzdXpSU19PX3NQRGlnQ21mTW9KeEhfY0tKamUwLTllbTVKaE1GaUpZQ1E0cFVMUFNPWjJzR0VUTUd4cmEwYnVkaG9pOGh3QXhZeUlscDJTdU9lWC1mUQ?oc=5</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>07-05-2026 16:57 UTC</t>
+          <t>08-05-2026 20:24 UTC</t>
         </is>
       </c>
     </row>
@@ -1570,238 +1570,238 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Amneal Pharmaceuticals reports Q1 EPS 27c, consensus 17c</t>
+          <t>Amneal (AMRX) director Jeffrey George exercises 34,819 RSUs, receives 19,824 new units</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>Stock Titan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNQnFkU293c2F2c0V0OFNZZWxENnZWQUpGc2QwNEN2ZmpTM3dPUzNDc3h1b1pMV3k2WEtCQk11SjRINzVOaXlublRCSjZCdnZyRVhWY1VHQmg4YzB1ZXgyQVBMb2JjM2Eyb2NWMDFiUFBTTVJTMlowSWY3NmJyYVZuZ0xSOTh4VU40WVNWTkJXdnRhVXpIeDNGbUtUMU13b1p5Qm55MWstNl8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNY0lHZnVFdXdjM29rODZLUWZDS1NpdFRNTkdJWkR0WXJVazJRZndTQ0Y4cmpCVThkNUg0VXZrQk1sN3pwNF9MT09PUXc1b0pEb1RCZjR4RkIzUEg4TGt1N3dIOHVwMXE3U2pIOXVqN3VaTHIyTllCbm9TaldPQ0wxT2F2TW9DT0RMNHhGdTdJUnlyQkJpN1c3OEpVVlV2VEFVNHR4OGhYNU9McDhKYUd1S2pMLThhUmxxOFJrUA?oc=5</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>07-05-2026 21:45 UTC</t>
+          <t>08-05-2026 20:27 UTC</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Amneal Kashiv Biosciences</t>
+          <t>Apotex</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Amneal (NASDAQ: AMRX) investors back directors, say-on-pay and EY as auditor</t>
+          <t>Generic Ozempic approvals signal a turning point for Canadian benefit plans</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Stock Titan</t>
+          <t>hcamag.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxOV2s2YVJUbmMzZEVZLXM1THJxX1FNTmtBU1o1dzNRbWpJc3RxWnJDV3M2S3VkY1lJaldySHFXOHUzeHpuQmRGRkJlaHdXY2FnZ2JGRm92VlN4YkhYVi1SVkZIb3dGUVhzZjdvY1JKZEt0YmZpZWJRMG9CWVhVNXNDS3ZTSHVYZ3I4S0N0N09leFF4YjdVWkdUTWszMUtBbjhfYzd5b3FLaTZ0MllaRE15OWxwbzk3dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNelZjNFFmYVlMVmNYX0Uxb1hSRzI2NmdWLW9SbVRIN2Uxcm5IcFFyWDhZZmR6b2FpQk5DRnhBbU8tdjIzZ1BJSUxaZUFlNmY5QW1sanBtc1Y0UEw5d2xtZU5hdE1vdm15NGRKWC1tS3EyXzZheGhWQzNGOTdxLS1ldWJjU1M4SC02U2hFY0FZRmFIbHZQeHFYeDhRVHpwY2hqSHZEaFlUNHFQTUpkNUtVSG9VWVdpOHl1czgtcUE0MkR5d2lrZlZXX3hOZU8?oc=5</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>07-05-2026 20:15 UTC</t>
+          <t>08-05-2026 18:48 UTC</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Amneal Kashiv Biosciences</t>
+          <t>Apotex</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Cipla launches next-generation oscillometer device Ciposcillo® for respiratory diagnostics</t>
+          <t>The Week in Canadian Press Releases: 10 Stories You Need to See</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>BioSpectrum India</t>
+          <t>Weekly Voice</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOSFA5cDFaSHBGTmtvcUVTZzlkd2JqTU8yQVVFQXR4SHlGeFRoWFM0UkpqRHB0VzNFUmwzakkxM2VfMnQ5NjBJSTctRjRBclp3MThwUTJLMF8wVmFzUnBVSlhzZjBzN1FEa213VWgwVmhla2l3c0FoNWI5ZUUwNVhkR0F5bGtJaFhETWpDaXU0QkRpQkNLRVRJZnFTbTJONFd2MG93UHFHb1RnTXYyYTJQV0QyN1hXOWQwWnRORThZYk5ib28teFJBUlRVOGJ4VHZWNkNjZ2NIZzY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxQRy1CMnVzQUlLb3ZYOWE1ZGdtOS0xMWJtNzNldWFFcExXbzhRZklwSjlScDNzaVNTSG5ZVERmeXc5b2lySTM3Y1dSeHNNZzZ5XzNFT1ZLZ3RnMjZ3ZjVzaXEtOGEtOXBvX2d0QVBSb3hTZ082c3VnWXBUNGMzeWtBV1lYRjFaZVF1NE9VNzlsMVJpWkpL?oc=5</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>07-05-2026 17:46 UTC</t>
+          <t>08-05-2026 10:24 UTC</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Assessing Organon (OGN) Valuation After A Sharp Recent Share Price Move</t>
+          <t>Plant Stress and Unique cAMP Signaling</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>simplywall.st</t>
+          <t>Institute of Science and Technology Austria (ISTA)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxQeW9pQ2FpSlp4QkxhLU8yZ3VwODVab0N5S2lGc1JhcWhDYjB4eUhnY01XQ1B1N0xNV195MnY1b1psTHdiWl8wUDQzdFAyU0hTMUFJZFdlZHdJZUJtUjVUaUFwMEtMaWtDajgzTDFuSGlKbERBZGZ1eC13c3Q4VEZFYTRLR3lpdFp4cDJqQXhGUTN6YlJVa1NwNHBFR2d6bnEyTDZreVpJLVZtZFlpUHZUU041Z2FaaUxBZUFrTXBJUElIMkxUanhJVENXSlphYmtXVV9MQtIB2gFBVV95cUxNVnRncnBoU3NsNmtLQUx5Zmg2YmdiVkFQcmxtdkptOWVVRDRpV0NJVnFVVTRyTGxIX0oxLW1jX2U4WHZFUV9kYTVaeXNMSnR2NVdPU0xIeFRSWXdLcXhpLTZseV9FUVFDYmNLc0N6T18ycENSemUycl9yWC1rQ0wwcFJQeUtxN0RnUXlmUWVHVkpGd2owWU1KX1lJc2pOZXlaME1lUFRPdE4xcGJSc3BZbE9GWnhMazdNQWo5RzFRZ0JBa0pwS1d4XzdkazBveXh6WmQ4Zm1vQzJEZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE41cHo1U1NreUJJN05xSlJacDFuYVhnVjJRZ2dKMEl1YldPOVN3eEtKb1hSWnk0MENrTnBzeV81VGdNcVM5VEtzNmNCMFJrQW5wYmVZU2xCSVJIVjVoMFozNkNnc0xPazZIRUVfWEo1Y3NlUkZX?oc=5</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>07-05-2026 18:03 UTC</t>
+          <t>08-05-2026 18:04 UTC</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Organon SVP, corporate controller Holzbaur sells $353,080 stock</t>
+          <t>Plants evolved distinct functions for two forms of a fundamental signaling molecule, study shows</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Investing.com</t>
+          <t>Phys.org</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxONERiY2FMb0szb1FIcGgxYnQ0bUQybHczT2liY2ltSm9TaG1hRXhLRmwyMjhkWWZvcl9JbHBubGQxTlE4SFoyOFhaZ3BkX0dvRWRmbHFnZllHZ2ZheTVqVXAya0VXam1oOWc4S3hZTGNsdzBhR0lxM2lBTzZFOENSVGYzV1VRNFZPaUF6WV9PQWNQb2FHY2IxTmp0TC1fX1pVWEw1ZUJTeVFxY1g5V3hnZl9vQnVGTFl1T1B2alNXVk5LOWNMVnFyUmxoZU41Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxORjFLM1JnOXVGd0hOM0VoU0RyUThPTFpXRXZXNnFLdjFUckhoZE05Qi1tNlVSRVd4WlF2ZWRsZUpzT0lTMDZjZDRBcTgwR3M3RFNpeldRTnVFMzVpQktvbkRZcXY5aGlTQXV5RGNHRVdUZmRhRTZSV0NEU0cwS0JPZThUVlFQcnY5alE?oc=5</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>07-05-2026 20:04 UTC</t>
+          <t>08-05-2026 18:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Organon (OGN) controller sells 26,448 shares, ends direct stake</t>
+          <t>Biofuels: Bayer and BP Form Strategic Alliance</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Stock Titan</t>
+          <t>CHEManager</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNYUlIaVc4MXR1UVJQVHpxSnJta3V3OXBiVVJQV0NlRXp0ZjBhOTZ5SHhnanNmTU1NajFVcFNjbHJYNGctT2dFZS1VZmZVTVJINXdyMk5INmJwaFhQZl9uY3pyd2VTTk0wNS1tQ0JmU2NhT1RSNTVlU1c3R3BOdHRscXU2d0REOXlBbEhTZnRsUTRPNUhwS1gtLW9qM08wOW5tSnpmRmRFSnk2RjVzNlBoZ0pSQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxOZjEzY0ZHVFN2SG02ZnhWN203Q2xLakg4d1BhVFY3NUlQTG5KRjFhcmJVcFY5NTFXeVZZNS0wU2R6aHFmVmdlRnFfV3ppN1RqOElOVFJFbjBLZjVQX014SzNONDZOckNxQ2o5aGRHQUlQRzhnMWYyWjcyTEhabzVhR2tQZGU3ZEVoRHF3?oc=5</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>07-05-2026 20:00 UTC</t>
+          <t>08-05-2026 09:26 UTC</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Top Organon Executive Makes Bold Move With Major Stock Purchase</t>
+          <t>Honda suspends EV plant construction indefinitely</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>qz.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPQW40NUtzZjluRGlVUUxnSTI2QzdKZWVBbGJHQzJNZmRteWFEa1FOb19jLXhQMWFydG1wN2FKRGhCQlh4RktxS1ZaVkwwenBnN21OMVpjbGpZLVdZNERXS19EMnZEOUhWZ0ZDQ0xqY0x5a0tLeDJ5NV9LV01raEVGNW94RGlpR2Y0aGVPcTYtaHJCcVlic2dPaVNMX2dBRS1lbGVyT3pDSURPLXRSMXJHNUlNMmYtWDlHbHlZaTFaRlMyalBkemEtRTdR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5OZTNITTNIdFZ5ZlJwWGljWFdEUDVWY3d4TEc4clNnTTktc0FqdWUxUmstUFVpaUNUR3ktUW1FUWd3akpGcnpZTTcxOWtDSlVMajhNRjZ1b0dmQQ?oc=5</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>08-05-2026 02:11 UTC</t>
+          <t>08-05-2026 17:25 UTC</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Apotex</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Healthy Returns: First Ozempic generics in Canada will be a test case for Novo Nordisk</t>
+          <t>Cool beans, smart roots: Scientists discover a new cell that helps seedlings survive drought-battered and nutrient-poor soils</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>University of Arizona News</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPUTVjQVNuLTZLbENlVDc1T0ZjU2duNFFJSzNiaTJVSlk4MC1SY21kejRyMGNGaE1HSmJSRThHMXcwMDVvWWpDc2YyR1UyMXlBTTRTcVRfZEZqQ2JPRHZ4ZFhCNEpQLXNSU0pVcWl6YlZwaXhjeWF0enhkSkdFQjhFYlczbUFVeC05NXA2Q2VCdDZKdkFyTmJjVGs0RkV2dWxw0gGmAUFVX3lxTFBmSmhNTmpYSXlKSmZBaEVNQklsclZnclk2cDBFeXV0dzBFRnBZZmF0c3hRdFRhRWFGNThUVnVKbjFvUl9taE5NdFdHV2RBRkpTUEs0M2JxcElnX3lJMkVIckQwcFh5a19Odl90WUJvVHQwSHI2LWlpeHJZZEZickM1eXhiZlk5ZUtRTzVrWnNRdXkxRjYybC1EZWRnZjV0VDhjTlF2MHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOWWNqUHNoc2lmdVk0YzN4VFNXR1pSN1g5ZzIzbFZGQk1PSE8xclFmNnl0WXQ4STJaN0l0cHFTdmpPRDFyZGljX2FTWHBuNE5uSWR6MmcxZWphWG9pTE0xRDd4SEs4ZDg4dTR0aVl3Q1JlSHlCc2Q5UlpHc1dhcTF4VzBoOTI4S21ZTGsyZy00Mk9lRV9jVWFnYWdGVVVOQjhUR05TanVvb0N3d3IwMGhCOFhtXzdKVkctNmhGV0Uybw?oc=5</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>07-05-2026 18:33 UTC</t>
+          <t>08-05-2026 18:40 UTC</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Apotex</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>The Week in Canadian Press Releases: 10 Stories You Need to See</t>
+          <t>Northern Discom to strengthen workforce safety with ‘One Minute Rule’</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Weekly Voice</t>
+          <t>The Hindu</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxQRy1CMnVzQUlLb3ZYOWE1ZGdtOS0xMWJtNzNldWFFcExXbzhRZklwSjlScDNzaVNTSG5ZVERmeXc5b2lySTM3Y1dSeHNNZzZ5XzNFT1ZLZ3RnMjZ3ZjVzaXEtOGEtOXBvX2d0QVBSb3hTZ082c3VnWXBUNGMzeWtBV1lYRjFaZVF1NE9VNzlsMVJpWkpL?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNUC02YTdWTk5iTk5sRDNGS09DY1FRTDR3dEhwVVVVYndDcjlGVEJMYW5FZVdYYWVhbWlPZHVpcTdOLXFTR0xrMnVHYjE3R3YwZmk5NWpwSHk2ZDBRTzdPWmtJYTJrY3ItWmM3REdFQzBtX21tQXV4d1FRSm1oRkszeldkc0YzMUlpS05jY0dGU3RnMlFaWVlGR1gzYTQwak45N3EzSHFCRzdCa0l3eWtmSEsteFBYZUprS0FJeUJkc2lVd3JsUDBlc2hNa1NyWEEzN2tMZXExb2nSAdgBQVVfeXFMTVAtNmE3Vk5OYk5ObEQzRktPQ2NRUUw0d3RIcFVVVWJ3Q3I5RlRCTGFuRWVXWGFlYW1pT2R1aXE3Ti1xU0dMazJ1R2IxN0d2MGZpOTVqcEh5NmQwUU83T1prSWEya2NyLVpjN0RHRUMwbV9tbUF1eHdRUUptaEZLM3pXZHNGMzFJaUtOY2NHRlN0ZzJRWllZRkdYM2E0MGpOOTdxM0hxQkc3QmtJd3lrZkhLLXhQWGVKa0tBSXlCZHNpVXdybFAwZXNoTWtTclhBMzdrTGVxMW9p?oc=5</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>08-05-2026 10:24 UTC</t>
+          <t>08-05-2026 15:17 UTC</t>
         </is>
       </c>
     </row>
@@ -1813,22 +1813,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Biofuels: Bayer and BP Form Strategic Alliance</t>
+          <t>Is This Edible Flower the Future of Protein? Scientists Think So</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CHEManager</t>
+          <t>AOL.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxOZjEzY0ZHVFN2SG02ZnhWN203Q2xLakg4d1BhVFY3NUlQTG5KRjFhcmJVcFY5NTFXeVZZNS0wU2R6aHFmVmdlRnFfV3ppN1RqOElOVFJFbjBLZjVQX014SzNONDZOckNxQ2o5aGRHQUlQRzhnMWYyWjcyTEhabzVhR2tQZGU3ZEVoRHF3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxOV1VYVDJnM1Fhc3Y5MmdJc3NjZmRJWHhTNDhpOXpJR1MwREZJTm5wQTNDNzN1WGM1bVZza3piMjV2Q0tqVFJ3WGRQaU8yWDhjZlBjNTlUaGxfY000RGUzU3hSWThaR1FGVzBaRl9JNlVLcUFpbkJlakQzcnRHNV9XUnBuaUV5VVJLU3pR?oc=5</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>08-05-2026 09:26 UTC</t>
+          <t>09-05-2026 02:30 UTC</t>
         </is>
       </c>
     </row>
@@ -1894,22 +1894,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Sound Waves Create Mist that Can Act Like ‘Plant Sunscreen’</t>
+          <t>Silicon-based biostimulant receives EU certification for pan-European rollout</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AZoM</t>
+          <t>Hortidaily</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTFBEd256eFNWeGtsa1ZoODRvSnExY3NpbUwwdWZtRGc5SnhNVW5LNVlFZmxBRlFCY2x0dmY1ZlU5bElZNTgteXpaMkxHYlF5TUZuYmhZWEt3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNZXNRWTBzcGdpQ1FDTnE4M3MtWmRzUS0zRVlzRUdQbGtpWkNoekFMUVcwM2NJaUpvZU5NRGxEZEI4a2M2ZVpfeXZENElES1JIbWl4RDB4YTRQaVhPVy1RVWdidV9LTXlZMk9OVHVSVGMwaXJPblpVYkFoak1oNlJOOWxZeTIzaUVMY25TTmFISk1HR1ZPMS05ckNKTnFMSjc2NTQzeUtCb2s3cFBYMzFOSUotaWZ6dXA4STlOUDNR?oc=5</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>08-05-2026 04:18 UTC</t>
+          <t>08-05-2026 11:44 UTC</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Pune to Introduce SOPs for RMC Plants to Curb Rising Pollution Concerns</t>
+          <t>Happy Mother’s Day from this potted plant parent: Our Best Life</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>The Bridge Chronicle</t>
+          <t>Cleveland.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOSFhna3BCRllLWXJNU3JwWk9aOGxzMFhNMWoyOERjR3J6c2FJeUtEelNWY2V5VFhDZkhVaVZtYTA5NGtEa1ppd05FX19GQlNjTEktSHQxSjFmMUdUakd5RDhMY1JsQTYtdzdBNE1QMm45Q3E1MEhpemZ2cjloZ01iVkNqQjlKOGNpZ3JlU2dhSzhvVDlzMjdQdNIBpgFBVV95cUxNR1htMWZsbkE5cmdEd2M0V0tQWmtnOW5ucGc5R3piSVhJVEQ5OWpqQkp0eHNSbzA1Z2hOSV80VE9ackRrVkNIdEl3Smw5STFlakhSMVUtZG1nUEhQczIwTmRwS0o5a2VIQzh0MXhzNWRYeXZCeDhvZWlpdlNqS0xzbnVWTUVzdlhVZTVSY3RnUjhKZmJJUjN1RHAyenYxcVVQX0VfelRR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNZ3Uwa3VocUVDWmNjU25SbHNVYzc2SVlYZGxkQUdPRzc5ZE1QSUZBcDhnTGx2Rm9FXzRxRGhiUVJrTmZ6SGlZdGFvUkRJUzNXODZlWll2N1FTWVEwRkd2cXFWLVF2UmJHai1hSTFDZWZBcm0xV2plczVnbmpxTng1OC10THlVRDk5elpkeTQxZ1NNMjVYa3FtQWRTclpVVFRERFRMR3VwS1DSAbwBQVVfeXFMTmhIb2czeW9JZ3U2RnAwckJGMHdkZlFNeEFOaDJ1NDlZVFV1SjcxeVV6T3lEbUwxWE1vRjI2X2hULV9icEgxS241TTV4V2RHQjV2djh1YXI3VDRPWW9sdWt5Nm16ZllYaERsaFBJd20xQXNWWTN1THBSTlhlcG9xTkFYemFhQzJzOElyT1N5RUFpQ0RjbzY4aFlqdVRqQWxkX3o1NjR6OWgwRU9lX2J4MUZrb0pDbjdTMjRLc08?oc=5</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>08-05-2026 03:27 UTC</t>
+          <t>08-05-2026 14:00 UTC</t>
         </is>
       </c>
     </row>
@@ -1948,22 +1948,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Gardening Pros Explain Why Your Begonias Aren’t Blooming—And the Secret to More Flowers</t>
+          <t>TGRPDCL CMD urges farmers to avail solar power scheme</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>The Spruce</t>
+          <t>The Hans India</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQTzhVUk1tU1dNc0RBTFZidFN3X3VLTl8zLWYtdlFsUVlBeGVQVjhIUmQzZ0lyUzFRaFNLVEkwTjljYWx2U1RCTGxjbGRvTDBvaUFvb21wY0stckJaOHltc3NoNTVOR1JwLVpyWGNPV1RGWWNkRXE4RUtHeTlTcWhmWl92UUFiUms2czB6SEFB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNNklUQ0JSX093eEN4Qm9HQmFHdnhLVmJuZUVKdVIxT3FycGNnUXN1NUl5aG9jUEROaGN5V2NfWU00akQ1dFlXTXQzNEV5VFpVT3NINDlERFhmZHBLVi1ERkdJd2NOa2taLVEzaWhZZm5kdTBCRmd5SXZfQ242RGRoTVg0d1RmNUlac1NPdkM3Q0R3MC1RZTdoYnkySWlYY21WVHfSAacBQVVfeXFMTU5oc3dOelRPQnQtMU5uZzlwZnJaaXFQM0R3RkFoSUIyQmd0X3VIM0hKWUE0TkxRLVRDTmMyUGJyR2tVaERBUk1Jd1U1eWRRWHp1T3pyc2RMOXIyTk1fdm1kNjVvZ2o0MEpaY1I2YkhZM21Gc3plVDh3OU8tUkVLNF9uN3QwVkFCWUhTS29JZFQxN3VkOXBJdXdCeEpsRHVlRFJkbGRhd2s?oc=5</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>08-05-2026 10:18 UTC</t>
+          <t>09-05-2026 03:42 UTC</t>
         </is>
       </c>
     </row>
@@ -1975,22 +1975,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Silicon-based biostimulant receives EU certification for pan-European rollout</t>
+          <t>Europe and Canada together can form major market for innovative firms, German minister says</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Hortidaily</t>
+          <t>The Logic</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNZXNRWTBzcGdpQ1FDTnE4M3MtWmRzUS0zRVlzRUdQbGtpWkNoekFMUVcwM2NJaUpvZU5NRGxEZEI4a2M2ZVpfeXZENElES1JIbWl4RDB4YTRQaVhPVy1RVWdidV9LTXlZMk9OVHVSVGMwaXJPblpVYkFoak1oNlJOOWxZeTIzaUVMY25TTmFISk1HR1ZPMS05ckNKTnFMSjc2NTQzeUtCb2s3cFBYMzFOSUotaWZ6dXA4STlOUDNR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQR2hsNzZFMC13R3dBNUpRanBWUkw3VWRTb3N3aHZsQjJpRy1sMlNIM3E1QXRXcFlWSkFjb3F6RFFEb2JjNVlaSjE4ZGlMZHd4eGFtTXFsZWNXaEtRVzgyQ3FMdzlhY2l1TTB2eU9scUpDeFY1cElldnNzMzR0dnFnRnFqakFjLVFfVXFSeHNPMG5ya2F2WnQ5S2wtSVBqcWxQOVYxaHhJUHVQQkxCMEc5a1RVUmEzOGJwZUc2aA?oc=5</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>08-05-2026 11:44 UTC</t>
+          <t>08-05-2026 19:58 UTC</t>
         </is>
       </c>
     </row>
@@ -2002,88 +2002,88 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Sony and TSMC form joint venture for image sensors in Japan</t>
+          <t>This Substance Is 1,000 Times More Potent Than the World’s Spiciest Pepper — and It Could Provide Pain Relief</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>qz.com</t>
+          <t>Discover Magazine</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE45WUtyNFlIUElaMTVldFdjYWJDRW9HTndObXhjN2h4cG1MYXhrNHV4clU1OFk0ZDJzYm5YdXpRdXBZTGtLTEZFRnd4V0t1Q2dfNHhleWdkYktHTXk4Y2xBZm0zZHlDdmlxY1V2bU9PTWZibm8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxOcXNxTDRtSHBhU0V0QXdVMElRMUpHOV84M0FZTFpwdHFrZHpOWkx6M1VRa2RpSFVSaW5LaEFsY08yM0pVVi1kOW1jMFdUaXpoVVEtSFdWMk9ZOHJSeFpmbkNBYXYwZW1KOTF1bWExN0JwZXNFZnhoSlAyLU40RmJ6SDhmNzB5TVhMVDJWVDhYelBvUERtTTVWRmYzdFF3S3JaOU1RcGVUQlZsTEdfLXExaXJheVdKOHhBSGxuWjY4WVBvNDRGTkNNYWF0UDROd1d3WkwzaWJUVWRGMGhZaHBr?oc=5</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>08-05-2026 14:13 UTC</t>
+          <t>08-05-2026 22:53 UTC</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Happy Mother’s Day from this potted plant parent: Our Best Life</t>
+          <t>-3.15% for Pfizer stock as new share registration weighs on outlook</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Cleveland.com</t>
+          <t>Traders Union</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNZ3Uwa3VocUVDWmNjU25SbHNVYzc2SVlYZGxkQUdPRzc5ZE1QSUZBcDhnTGx2Rm9FXzRxRGhiUVJrTmZ6SGlZdGFvUkRJUzNXODZlWll2N1FTWVEwRkd2cXFWLVF2UmJHai1hSTFDZWZBcm0xV2plczVnbmpxTng1OC10THlVRDk5elpkeTQxZ1NNMjVYa3FtQWRTclpVVFRERFRMR3VwS1DSAbwBQVVfeXFMTmhIb2czeW9JZ3U2RnAwckJGMHdkZlFNeEFOaDJ1NDlZVFV1SjcxeVV6T3lEbUwxWE1vRjI2X2hULV9icEgxS241TTV4V2RHQjV2djh1YXI3VDRPWW9sdWt5Nm16ZllYaERsaFBJd20xQXNWWTN1THBSTlhlcG9xTkFYemFhQzJzOElyT1N5RUFpQ0RjbzY4aFlqdVRqQWxkX3o1NjR6OWgwRU9lX2J4MUZrb0pDbjdTMjRLc08?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQbkZXcjdsUExxNlEwbWU2aFpPZmdhSGFsdWc5TUgyVVo2ZFF2MzNCM2pPVTlOSFA1b1U0cXBPeWY5OHNTMHlFcElKS0hoMXZaTnp1bGhwVHI4aWlNWFdpcFFJektDNFhTNzhmMDlITE9ZUEVfMFZLVHc0M1o1a2YzVndSeGpkREROMnhXV2xBNllkMjFleTRPag?oc=5</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>08-05-2026 14:00 UTC</t>
+          <t>08-05-2026 20:08 UTC</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Sony, TSMC form Japanese joint venture to push image sensors into automotive and robotics</t>
+          <t>Here is Why Pfizer (PFE) One of the Best High Volume Stocks to Invest In</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>digitimes</t>
+          <t>Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQYVA5TkxKOVlVUFhEYV9kU3N2RWlTSE9UdjMtUEJsaTZRc01FY1BpVmdVdHBKMS1Wd3NOQmRHZko4UE1yTEpXR1ZQRlBnMFVCb2R2Y0xPNUNnUVVjS3FtME5kaldCTm5vVmJ5SjFoRnhGQ09MU2VzTzZSbmpwdWFtRlBPbXR5LTEydWdMQ1U4bWxJR0hCVzd5cFhHUlppTkk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE5JWEhkSjZUODA5THFlVjRTQUVhZF9UUnU3a25uRjhYc3VxVC1DSWJta1BGOGs5LWxjQS1tWW1FMFRXVHBTSkVsOVZmQmUwb2otREMwUnh4dXR1N3pMQ2VqNHZPeVUxak1mR2hYM2hUOGNtalVibW5zaGVmcXI?oc=5</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>08-05-2026 07:40 UTC</t>
+          <t>09-05-2026 04:57 UTC</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Sony, TSMC plan new Japan joint venture for next-generation image sensors</t>
+          <t>Fact Check: Hantavirus infection is not a confirmed side effect of Pfizer’s COVID-19 vaccine</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2093,174 +2093,174 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOUjZaZ2JnZGh6RUYtNzBfQjFLV1ZfaWJ3M3RmOEI4dG12UlEzanVsRDZDcXhPOUhicldoSWctRDRxZzJxc1hDQmlNTEJwY0x5LWw2REpUU29RUFBnc0FVWDExLWI3WjJjWG4zZnZ6NW5DVGpTWFJxbE9uQWNZaVpsbkVpSTBKSngyNC11aGhTZmFHb1hOaVY0eE5ZSUZyRHlPeC1wTlI3ZmpTRDd0OEJuaWZyemp0ZldOZndHNVdoOUY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPQjAxUjYtNmQ1TUt6Mm9DTGdlaGt3R3pjcjNWcUtNb3BNVGZNN2tNdGhBY0VCc05lQ05JOGtDSlJOdjhyMGZvNVYzZTVFS0k2N0pTSk55OFo1aEJfOWxXYmFvSEpSaXBVRWJQUlotMExaUTZUSTctdkRQekpYMmlHUll1RUkzejZVdGZ6ZVVJWWUxc2JrZFlrQ3lBdjJYUzUxUVpMZ2RDZjk3MFVRTHM0akZXeTNYcGdkVDY2TlR3?oc=5</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>08-05-2026 08:39 UTC</t>
+          <t>08-05-2026 17:09 UTC</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Fusion consortium established to advance private-sector fusion</t>
+          <t>Pfizer’s Lyme disease vaccine shows 70% efficacy; Texas man sentenced to 12.5 years in $61.5M Medicare telemarketing fraud scheme; Novo Nordisk launches Wegovy subscription model – Morning Medical Update</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>American Nuclear Society -- ANS</t>
+          <t>Medical Economics</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOYXlSd2pjdjJBcFVtNUlIMi02Y2swbWl6YzRSd3JiS0pkSDlrTWFiQlB6RFZIX1Z2YnhrbTRYLWZMTmtKWEFXbU92Vzd1SWVPUTlCSlhZWjVIdWhOand0ZnJMaE9WX3Y3VmNwU2QzMEJsZS1pMmtYYUgwQ2FsRDZScjlUM1hLeUVDQ0NRNEJGQmNPcmE4TklhUXZ3YmhXNl96c2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gJBVV95cUxPVnU1X0hLdnNoem8xSWwtUm9LQ28wXzM4aUFsUUN2U1ZsM0Fwb2dIWmNPdGphRVd3cm9RUzBtT0gzYVlyYUV5aHBnOEt4ck9CVnV0NEs5NTJkV2d1WnZSaGs3bUJYUHlzVVBMV2xwRDhnakZiWVlkNG5kTFBmTm0zNHJGNDlhdHhNcVNEQUtaX0ppdlZ1SFlXekZ0Z0Rtemh4TktrWGdPN1VIYnhGZmZnWURLWlhQTjNhUXN0RkV5eE01ZnhhVHd0RXlFNm5PNDBQTjQyOWpHMWRpTUJfV0Y5NjBqcmJvZ0FGWGtZQjdtZW5LcFI4S3U5ZHV6Zl9uc0NZQkpEcDQ1TjRiTnk3MjBGYS1RdjhNaVhvQjVveW5FRFpWQkVicHE1MVlLbURUZTFObTZtS19qN3JrdDF5c0RHb19WZzNTQW5OcWU2MEdGR3pqREVjQWc?oc=5</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>07-05-2026 18:47 UTC</t>
+          <t>08-05-2026 17:46 UTC</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>We developed a biodegradable wash that can remove pesticides and keep fruit fresh longer</t>
+          <t>Fact Check: Hantavirus Outbreak Viral Claims - From ‘The Simpsons’ Prediction, Pfizer COVID 19 Vaccine to The Economist, Betsy Arakawa Death &amp; Hantavirus Pulmonary Syndrome</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>The Conversation</t>
+          <t>The Sunday Guardian</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNZWs2UThUc2tuNHI4LUpvakh3b1JmOHpLbEdvWk13XzdPbHBKd1BOOGVZdWRXWE9uSFFka1JtVDJqR0JveVhVZGEtNDBKZ1pqa01KT1kwYmpLMFNEeGo0ckh3NzJST1lhNjNWeE1OZWFoQ1BzOERjUWF1SEs5ZDBXT3dVd3JuTTFNYWttTjZvOHFKVWpzWDV5bV9ESElKME5tN21NbjE0dlEyUXZLWmV6ZXpVU29Ec2JkcXhYT0lmMEs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgJBVV95cUxQREpXaDJBbldvemlHSVNiRDY0cmkzNlFLaHZ1cl9DYkVWb21vSG1Rbi1mOUVFckljTlRjVmt6TVRrZ2hVVGI4a2VvcURzSF9pMDVBTzJwSFpsR3k4MWwtdlBFam9IVjlwOVFsdDU3VWtsMWF5U0xpYXEzWHpGLWl4X3ZrX0E5UWF0aGtqZV8wbFVZLWxEQ0RIQkdPZnZvbVNHTEVNcjV6SnliOExyZWVPcWpQTXh6ejdZa2h5S3RjMVU4SHFIWWFBRXZzSFNLdkhjMkI4TEt4NXBwWHA1alZCaWd3Zll6czk5ZEVZVDh0cS1GVTlaWjhWd3JJal95Q1psekFGSUhQV0lfS05rMEEtZzVnMUdnbU9JOEdwS3RTMTlhcUc5MHJDNHctVU53TzN4X0hnNGNn?oc=5</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>07-05-2026 16:46 UTC</t>
+          <t>09-05-2026 07:50 UTC</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Boise State scientist co-authors landmark study on the world’s most irreplaceable plants</t>
+          <t>Pfizer Inc (PFE) Shares Fall 3.0% -- What GF Score of 76 Tells I</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Boise State University</t>
+          <t>GuruFocus</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQbkpXM044ZF9KQUNIeXI0Z1hJVk1ZM0FxU3UzT0t6UzR4MUlzR2cwVHp0SmpmaWQwWnB2TGZ3WVBnQ0VNNDI1blE0ZWVyV01YaW5JcjFjTjlUX2RTc0o4akRTRGVvY1FwU1o4c1VITkN0aFl5R1diTDF4cnNiZ25icHZmLUpES1MxNFBsTHA1OHZzRV9SWkthcGozM0N1Q25sU0c4bnUyUUt6dFc5bHYzd0RfYWJNaU16dUFzUzRZZ2Z4dVdLeUxqcDJFNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOS2prNW1waGtmNEpjY2JZTGtWWGlmaG0xT0tlbm9nVU9Lb2Y1SHl4OWE1Smt3SkV6MFl5U1FtMkZHM1N5S1ZzMVpuaEJ0N1F4QTIyVUM3c1ZFWU1zS1lTMG1VLXVMMjk0U180cnV3Z3lmU0RIekZFeEZ2d001Nm9tYzBYNUhIT0pfbGEzcGpFVE9HOWFaU28xMXFTTXhyZjQ4YjB5RXZzaW9BRjFwbDZQR3RIZkNYa1E?oc=5</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>07-05-2026 21:05 UTC</t>
+          <t>08-05-2026 22:36 UTC</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>UKSSSC Livestock Extension Officer Recruitment 2026 - Apply Online for 120 Posts</t>
+          <t>Hantavirus is not listed as a side effect of Pfizer’s Covid-19 vaccine</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>FreeJobAlert.Com</t>
+          <t>Full Fact</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQMnZuQTc5VjJ0blFVN0Z0Tlc3SGNpd21oX3g2bk5OTXRXNzR5N0FvVFlqY1NESmM0Z1lLVkl1ZFhjSGR3RlljMlVPYzg0dElZT19IVEJDeDN1Z0lzbnpLWTlZdEVuTkJYdUdyTFJKUUh4OGkwTjM4alpaWkRoNGQyWUVVVlMzYnp2TkJPcUJJMnZsMTQ5ZmJjVnJlSzZVWnRfR0FUNzZaNm1waTJPdFZ6Z2pfMTFKZnBPZnBfX1d5a3owZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxOQXdZaDRXZ3dUd01kemx4TmJrQVF3Tkd4S29hVEx2cC1fY3VlMV9jZFI3X05BWmlOdVdEdjVLTi1HcV8wa0k2MHMxRzFSMGZ3VndZU3Z6cXVuSFhmcmFrck1Jd0duNENNQ1BCYXdEcjkzRHJnRnV1N2tfUkFCVFpIVEc3eXEyNlUwNHJ2TnVPOA?oc=5</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>08-05-2026 12:23 UTC</t>
+          <t>08-05-2026 16:28 UTC</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Viatris-Mylan</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Viatris Q1 2026 slides: earnings beat drives shares higher</t>
+          <t>Pfizer Viagra stock: What health-conscious consumers should know before considering alternatives</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Investing.com</t>
+          <t>Portal CNJ</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOYTJER0pNZDUwRVhVY0dPdlNUM3M1cmF2cnFDMzYwSVZxX3Vob0FCazJsY0VJbzZXdlg0bnpJZVplTllGYWxpWXpodE1pdkRSc2RIZEJXM1ZTQTlRUkV1QmNVbjFTR2Vvc2tYYUprdW1MVldZdjBxNWxmVmxfQzVLZ0tsYjNNNU5GY0lWZC1FZlhOcUctV0NjSFlaeG9ZSXRDNks5S3dVaE1WSVdSeTVIbjl2T2s?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAJBVV95cUxPZGdqUGIwcVY3NlpISG1ULWNyQlZOVW51bVgycHc2RUlYWXlIbE5jazdUQ2t3NFlvYVRkWjFXRVMzMWdVVm9adDVFMlRQRmhMSFdwUDhWTXRreUlqTFpfRXd1ZUxwNG5DeE1qdmxXaDZMUWlWOXVWbHlqT3NqUURucXFkNjVzLUVlRjMzeHpOa1JJRzliZUMteksxcG45X1dfQlBVODR1ZWQ2NnZ1NERka3J5cUdUY0Ezb3VjR29Ucm95N05td3lMRXVNMHhrRVRZRTZzS0hqajR1MzhTOXVRVDNsY0NqV01QWlpyZlBHODRwMHB3clVhaERUV1NpeUk0VV9tZEt6dU56ZmJL?oc=5</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>07-05-2026 17:32 UTC</t>
+          <t>08-05-2026 14:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Viatris-Mylan</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Viatris (NASDAQ: VTRS) returns to profit as sales rise in Q1 2026</t>
+          <t>Novavax Stock Jumps As Pfizer Deal Cash Puts Vaccine Turnaround Back In Focus</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Stock Titan</t>
+          <t>TechStock²</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNbHVuNE0tTUlGUHNobTA4OERYQjR5XzlXRXdoOVdHSHpsdW9OTDgyeXI2Y2R0VS1TTUNTYmZLWm1nZjBha09tRmE4Qm4tXzVmZ3FNUmdNcE5sNkhLTzhDTm9FNU0zSmNkeVg1ZG4xVTZpZjRrREd5VDJTYzlCMlVwSW5CQzBIR0ttRE1QaTZkUlNfbjV5WktLSUp3bkRmYWVYSnpWaTRtNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPdjdLQXA5dEc4TnJ5b3ZiUFBZUWJGbzBEUE5acG9DdFZJb1VzUkVZUWJLRXZtYXotcDNHX2lqbjV5TmVaUjQxWFcyNHVOUjlKTjRyRmtMWm9kOUhlMkpMOFZkNnlQOTN1WTZMaWt2ajZYcWtzdHZLRVFwTXBacGVpZnJzRGxMQzJPaEFKNTBnd1JUdTJPa0tnU0hoTDFnSGc?oc=5</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>07-05-2026 20:03 UTC</t>
+          <t>08-05-2026 17:55 UTC</t>
         </is>
       </c>
     </row>
@@ -2272,22 +2272,22 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Pfizer Ltd. is Rated Sell</t>
+          <t>Earnings recap: Airbnb, AMD, Shopify, Pfizer, Uber, Arm, Disney…</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Markets Mojo</t>
+          <t>Proactive financial news</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxPNjZmUEJDWWM2RnE1Y1hRcklDcGhva3YwdkFTcVVzUXUwbTVKSldISWZHRDdWSlJuc2duTFVNUnIxTXphU2J3X2k5TWozSWwyZ3dVenZXeVJ5MjlyTFZkcmpLVFVRdnViQXhkekxWbGc0VE5wcDJCUmJIM2h5NXlfODRDTkFBaktHdW13d3gyOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPZXlwNFZaVmVDWWpOV0ZIcFFtTF92TllLclFMMDhVaHFPTVhCaVRnM09HU1JpQmRZLXJwR1dsb2tadUJINm0xSGZDZDlTYkdKU09mN2VJd2VmWGVfRmdXYnZwSEJROFFRZVNQOXNtLTVNanFiQlFVYWVDS095cjctWnhzX1ZNTzRqeFU5b3RMc29pUlpyUlBYVWlSREtMVy0wQzhRRXhJcnZ0N1BVaHEyWF9QcWUyQzJPTlhmbFZZTXRNMDN1dGc?oc=5</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>08-05-2026 06:45 UTC</t>
+          <t>08-05-2026 15:30 UTC</t>
         </is>
       </c>
     </row>
@@ -2299,22 +2299,22 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Assessing Pfizer’s (PFE) Valuation As Shares Hover Near Recent Levels</t>
+          <t>Novavax Inc stock (US66987V1098): Shares jump on Q1 beat and Pfizer deal momentum</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>simplywall.st</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPWG84cDJKWW54R1JuOEt2b082V2VhVmtvYW4wUEJIVHcwVUVoVzJiOVRJdE4xeU5RU3NHR1huNVFLb0JZbTk1Tlc1eUpkU2tZaHlnQ0VTcmEtbkZHRmtjVWtxdmlQY1VWTXdVYzlXWW9ZOEp4a0hDSk5waE1TSXdENUJnM3VVNU9UM1FwdXg0WTJQY2xjV0VkMVBOYWJYd3pqdV9CVms4SWxIaGlKMmNYWWpZczFtZVlUY05CZTBtYXdOQVBLRTVFYTMzb1BmMEdLeFHSAdcBQVVfeXFMTS1qbFhORzE2Q3p3UGtXYkI1Y3A2RDVzTGo1QWlsQmFPdHR4Q0xIMGxMekdpUXFtMjFSUWJYdnExLTNBNHFJYnZoU0p3Z2JfNzloVkhHRnVXeEFDWEcyWTY4d0s4NFI3bTlQS2dlajZTRUdxV0VvR1gwZVdZSEZBTEJkWkEtMlN1TDJoWEpzUm12WTJzSFlOcDktbl9UbFdENXhVWjlZd2k2MzNjV2FIR2FsQ2ZGQVdKUDFnZHBHRk9ILXpvWlpfcDFnamNYSGljendoZE5YZ0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQZ0FtY213TTlvVDI5OW40Z19UZDlKczhIbjdsaVVRNzFEQ3BpZVdZVXAzNG1pd0wzWjhyck81dzFzTDg2R2FCVzRCdVJKRFMyXzAxWFBuWjFvYzdFR3ZnZEJQNjVVZ0lWMk5yX2JqSGRXSkk1T2l6Rmxfd0dGdTlLWGQ3RUY1QWF0UzVuSzNhLTFBRUJPemJzTnhweHZnSHR0bWNWSTZiZXZXY1ctYXFBZUs4SVRFX3Q3dEJiR3l1RUtHeEJfODIw?oc=5</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>08-05-2026 07:52 UTC</t>
+          <t>08-05-2026 20:04 UTC</t>
         </is>
       </c>
     </row>
@@ -2326,22 +2326,22 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Pfizer Stock: Still Priced Like It's Dead Money</t>
+          <t>Mixed options sentiment in Pfizer with shares down 1.52%</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>AOL.com</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE9KdGk4V3ZCendkVkNDbHowZ1FPdDhfbERpdVVuWDJnQ0FoTWYwRXZDVWZ2RGVmRC00b2NQLVJ6RHFrMGgyU2JnNW9QaU8zUFh5UTBMaTZSVjRtQnBwOVp2c0VSM1lNYVpzQkx3YTFlSHJpLUY3WHp6cGszTk1qdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQa093Q0RkNm1icGIzeE9XcFNYVFI3X09TZWpXQ0tDRkJmOUJ0MXJMWi14eFhfQkNhMTB5ZVpJckdOWWJOa0NNeU9HY3FPQmRrZ2J5NjFia2t3dWxTMVd4NDlVeU5yOFcyNUtESFZCNzJFVWpNelJvZkx6ZzJwVG96OWVYRHY4QWdjRUg5Rm9pQy1wZExMNncxU2VwaElNRTRkWks0OHFsUEI?oc=5</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>08-05-2026 11:24 UTC</t>
+          <t>08-05-2026 23:35 UTC</t>
         </is>
       </c>
     </row>
@@ -2353,22 +2353,22 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Is Pfizer’s 6.5% Dividend a Yield Trap? Q1 Results Put Speculation to Rest</t>
+          <t>Trump Promised Cheaper Drugs. Some Prices Dropped. Many Others Shot Up.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>NAI500</t>
+          <t>KOTA Territory News</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPNm5McUJ1WENuSHM0Q3FhMFVLNmVIV25ZMWFvSmRqOWtrZm1MNWh6RTc0RGZhRm1KTXFLNUFvc3I2X1UtaHlMeGFDWk44bmduODlwWXlhT3B4N1hIdlN1cV9wTVBVX2hMZTE3emY3NmdKb3RHS2J1UjVEMEhHQXVVQVYwanpYc1c5X1M2MU53NUFjaktCSm9EOGdWSlFQUFZJYmtGMl8xQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPMll4MGgxR3JBQWpMdDdLbkdJc2FqQU1nUEgxbnVtSkRtQkU3UmRVVFpoNDJ0RXA5OE80c3lNMjVscHl1RURqTUxYQTZmQ1c1YUhlaUdRS0Q1bVFKQWRvaUZPN3ZMNWdQbHlvbk8xYnlmMFNKdWVwNFoxYWpWaTBzNEdqb1h0Z0pyc0FMdXdLYTJ6akxZSXQ1Q19vYzAwdmYwS1dWNlZR0gG6AUFVX3lxTE9RVG5udjNsLUZGaS1oVko5X3FDRTVUamJ4YXd4bmhmbzBORXBpcXhwcmNCNS14VGJUR3hUS0JEenVqS3BjMFRGUnhOd2dEWGR1MlpvZ2NJNjdvVVhwRE9QUWx5ZFFMbjRtZ3RkUzNFaEYtaXZaLXYtZEUzSUNNSVRvVjYwWVdERER3RXJWNTRydVdtSWtxTFpWbzNQUFFXRG5iMWpVTUk4YmFjY3ZYV0NYR0ZrWWdxdGI4Zw?oc=5</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>08-05-2026 02:30 UTC</t>
+          <t>09-05-2026 02:00 UTC</t>
         </is>
       </c>
     </row>
@@ -2380,211 +2380,211 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Depo-Provera MDL Sees Massive Influx of Lawsuits, Pfizer Doubles Down on Argument to Dismiss Cases</t>
+          <t>Pfizer Options Spot-On: On May 8th, 207.87K Contracts Were Traded, With 2.63 Million Open Interest</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>The Legal Examiner</t>
+          <t>富途牛牛</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxNakhSd3RMUVgyTlVnZzZWRlN1ZUUxNmR1NS02SlhybG1PWmZ0akZvOFlrOF8yRGZia2ZBUExxTmZmYzhCY1VPbGpxckdhb2JjeHNKWk5fazFveEhVd0NrVEkzallxcmFLTVBiakNnbmI3S0ZyRkctam1sbWQ1NjllZFpZT3p4Q0pESEM5d1NySGliQV9IUVRnUlQ2RnhCWlJoWmRDdkxneXFDTzAweEdIR1VrbnRGZUFSNF9RQVl6OE1iV2VlSUVGMUVJVUJJbXkwY1V3R3RR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNb3hQa2RodDZPcHlmSzFLV1htcmRnV0R2NmYxYndOcW5YX1ZnS0RmQUJlTmoxTkcwQ0pJQllYejYxSU80aXc5cDdYNXRTYTJuRDdPV0dvM3RwREVDV3AwUHB6U3FpYW9CVnBFZVlLODVnNmdnV0o0MkY0dE1vb19BcG5XSnhkUjl2MjJXRUx3dkFnTkRrZHVv?oc=5</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>08-05-2026 15:43 UTC</t>
+          <t>08-05-2026 20:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Best Pharmaceutical Stocks for 2026 and How to Invest</t>
+          <t>Eisai, Biogen Receive Extended FDA Review for Lecanemab Subcutaneous Starting Dose</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>The Motley Fool</t>
+          <t>BioPharm International</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPZlFCRE0tR09IcFR6RXFhYmRTeTcyRTVrT3ByNHUzRXN4VFFBZExzMGtmNkNwa09NX0VFd3EzaUhSVmZpSTJkRFlqOFBuYVNpWHNBLWE3WjlkMjM2bWVhYS1zYTllbnRHb1JKV0l5ZlQzTEFaSmUzYW5pS2NiRkowZVZLU183Z0dsM2psTjZhVG5UNDdBTzM4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQZE13SWpQdUlEamNKSGExdEJmQi1jVU00aFZTckhtZXU3S3RoOTRiTzFUbVF2bjhobXgtU091RXJYRzluci1VN1J6ZzU5R3c4aUtISF9VUVBSeXBuWTVyNFJtMmpnVU9ST294WHdQc2p0ZHlQNGVaUkFMYTc3YXVvZVgzVzF4VE1idFB1TWlMN19XeVNqVW43czNOV3g5OEQyd3V4bTdGOEVmTFV6T1UwSFgycFduMk5VbU9yaUtCZFVSdw?oc=5</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>08-05-2026 02:01 UTC</t>
+          <t>08-05-2026 16:47 UTC</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Bio Pharma Market Set to Witness Rapid Growth Through 2033| Pfizer, Johnson &amp; Johnson , Roche, Novartis</t>
+          <t>Eisai, Biogen face delay to subcutaneous Leqembi</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>openPR.com</t>
+          <t>pharmaphorum</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPYzA4R0NCblRPN2NyMEluRkNDc096dEtvMGpqaEw2aHV0blVhbmFVRE1PRlhkT0JNUF9tUGxDRzVWUkNSajhUa2dBSnlhZDJoMGFoZmNnR0NFTlJING9KbG1oLW1oYjY3b1FOdUkxb0xhMUJnYTRCTmktb3lDekRfc1JZTGNoSTJjU05FcjdLRFdQTy03SnZzdVJR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1tdnFZUjBhTEpjUTMyNzVFV1JmYnA5b0p1OV83c21uaDMtZ0FwVG9KYVE1TXdfS1JhcjRpQ3k4SmdqRExHbTdFdXJEVEQ4bzk4Nnp0eUVtamExMXdSYVc0emNOZlNPV3JPWWlFQmhqcXZwbTFjMGgweUh3Yk5HNlU?oc=5</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>08-05-2026 12:49 UTC</t>
+          <t>08-05-2026 12:15 UTC</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Pfizer Inc.:</t>
+          <t>Biogen, Eisai hit with 3-month delay for starting SubQ Alzheimer’s therapy</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>marketscreener.com</t>
+          <t>BioSpace</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTFBCODlCZ0RfN0gwdmFxUEVmSElFVGhjU3JnSlEzcUZmN3p3TElUUnpxTlA5UkotV1NvdElPbTFqMTZzNndYZVNTdFNsak5yUi1vVThWaHF6dmRsaGl3eWRyQU8yYk1GOFhmdGNCZ3VXNHRNbFk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOUnBJU0wtcjZtTmlUaDhzc09hcEdmMUw4WlEtZUFGclVLYUk5SlFoSTZucDZDZlhuWE55NHBZR1hHeDhJSE9ENDVkYldBSUJDUDRnUmJyUHFla2xxVTZWR0I0Z2RKMHc4SkFBU2ZMLVBzZXg5eUdvVUZfdFRyakI3NTZab2J1ZHpMc2hfQXpHX05Cd0dtV3pyRnBhLXBzcGNlYUtr?oc=5</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>07-05-2026 22:00 UTC</t>
+          <t>08-05-2026 12:47 UTC</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Judge Knocks Out Pfizer Partner's Vax Case Against GSK</t>
+          <t>Assessing Biogen (BIIB) Valuation After Recent Share Price Momentum And Pipeline Prospects</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Law360</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE5GVTBoZllzbnlPLWEwQ3RyTDg1ZXVKNmhIX21jZkJSc0dVMGhRMm9MVzhfQ2lnV1ZKRHY4azU1VFZEYVJkWFBOa09RaTNTc09wWnpTWkp30gFWQVVfeXFMTkZVMGhmWXNueU8tYTBDdHJMODVldUo2aEhfbWNmQlJzR1UwaFEyb0xXOF9DaWdXVkpEdjhrNTVUVkRhUmRYUE5rT1FpM1NzT3BaelNaSnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxNOG1vVTZLUnZtWm1Zb3BPaWUycVFORXExbW9WdVExdVNMM3dHaTBpV0tVU19HWWJNWFZDTENzYzZ1aWVxQ1BIU0x4aF9ObF9YRkZDa1QxRV9sa3NPMC0tb1Q0b2lOTHB2SGhaWmVpME5zTi1Gc3FDYl91ZUlLa0hVNE51Z0RwUjZqX0l1VTBud0RJSHhtU3hiU0VaX3V5YWR2Tzh3M2huN2VnQWFiTTdkYXJMdUVUNktBbWZWUVQ0X3lGYXZ3Xy1VcTBuWVEtVUdrSDNteDZjSUJxLWNr0gHcAUFVX3lxTE04bW9VNktSdm1abVlvcE9pZTJxUU5FcTFtb1Z1UTF1U0wzd0dpMGlXS1VTX0dZYk1YVkNMQ3NjNnVpZXFDUEhTTHhoX05sX1hGRkNrVDFFX2xrc08wLS1vVDRvaU5McHZIaFpaZWkwTnNOLUZzcUNiX3VlSUtrSFU0TnVnRHBSNmpfSXVVMG53RElIeG1TeGJTRVpfdXlhZHZPOHczaG43ZWdBYWJNN2Rhckx1RVQ2S0FtZlZRVDRfeUZhdndfLVVxMG5ZUS1VR2tIM214NmNJQnEtY2s?oc=5</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>07-05-2026 22:57 UTC</t>
+          <t>08-05-2026 18:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>PAC retracts 'insider stock trading' ad – but Mo Brooks' STOCK Act violation over pandemic-era Pfizer trades while in office remains</t>
+          <t>Biogen Stock Gains Despite Extended FDA Review For Alzheimer's Therapy</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Yellowhammer News</t>
+          <t>Benzinga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxOUGRENVZpR3ZMN0syTGhyVHNRZHNrZF9iN0hqZGVYbkJlbTJHeUJYR085a0pjUVdWUS1xVXVBS3lKOXFBMUFtbkV1U1R4QVpHVVdaOTBqZDAwb3o3b1pFNW9jLWtqNnpLdmFsdzkyaEFUWWg4azBTM1Z6NzVHaEhTYnZjTzlqUFpvR3g3YlNNME1KRDl6ZkdmSlpubXY0OW9qNFpoa2lvTnVJV1ZBTTlFQ01Td2JLdkV1RTY5aHhOOHphd1R5RC1mVHNOWHdWWE9pWFNGYWNuaTdhaXBUclJCNTlmOVNJdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQZzBhQmNrbXV3cGlBcHlnX21CdFg4QzBhUXdab25wVUZDWFBEWi16TW9hbE9WZnR5b25td0lKTGI0NWJuQ2NselhvNFN5R1Vxak9xN01kZml4SVhTUVhXckJnWWxRYzBMOElFUnlPMVBkUU1HSWFjeDE1ZS1PeldRVlZob09vcjRjRXVLRnMwY2pOa053UU9USXB6WThKOERkSUpQZmRCZ3BCTEZWTHptczRNMGxjMlNmeHc?oc=5</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>08-05-2026 14:41 UTC</t>
+          <t>08-05-2026 15:31 UTC</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Small Molecule Drug Discovery Market Is Going to Boom Rapidly | Pfizer Inc., Merck &amp; Co., Inc., Novartis AG</t>
+          <t>Why Biogen Stock Was a Winner on Wednesday</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>openPR.com</t>
+          <t>AOL.com</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQZG9XVWZIRzY1TmtrVFBGUlpYRFJsamtkVXA2S0lwWk5EUWZIREg0SmlBbmNtRVdzaWNONzdWWkdsaEhPVWIxVVF6R21XTEV1NmVUU2M5NzF0c09IRjJsLUVBc0lEamJpR0E3UHRDMFVzN1g4M1habGkzdnhKWk9oeExEYXUzczllQlBKaDBENXQwbE12WmNGcS01SE9YZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxOOWp4b2pHaFdQQTNXYWxiRE5Iekw0V05zRmJ1dlBFMDhUczYyT1g1ekxoXzdaUVlTVlZJbkdDMHhIYVRNRmY4M0dwQjF2UlRPNnB1Nms2VDRybXAtaE1IdzNYM01oUXowMHBtR0UzSGxTVGZwbjd1RFcwbnl1ZkdteEhGVQ?oc=5</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>08-05-2026 07:31 UTC</t>
+          <t>08-05-2026 22:29 UTC</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Pfizer Just Scored a Win That Wall Street Can't Ignore</t>
+          <t>Alteogen posts strong Q1 earnings on GSK, Biogen licensing deals</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AOL.com</t>
+          <t>koreabiomed.com</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTFA3M3dadkdGRzNhdDc3V2pBWTVhWFZ2SHp1QTdBQTVsLWU4TFFwOW5LSGtERWFwcDlzcS1SdEtxZGpQdUNsNk95T29BQXVWa2k2N0JOQS1kdTJEQ3VacXpYeHBjTHRINkJUZ3hERksxSVAtT253WldEazhqMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE4zSF8tczZrbmZ0eTJWUDB0c2QybTlzZXc2c1N6bkUxLVJ5Y255ZW9GVldQTUM5aktPcEdWWkh5UERvVjBNaFJhVGtObUVvaTEzUV9rUDdPcFdBSUlwTW9uZjRKZnlfRHBSZzQtNk0xXzVrd9IBckFVX3lxTE4zSF8tczZrbmZ0eTJWUDB0c2QybTlzZXc2c1N6bkUxLVJ5Y255ZW9GVldQTUM5aktPcEdWWkh5UERvVjBNaFJhVGtObUVvaTEzUV9rUDdPcFdBSUlwTW9uZjRKZnlfRHBSZzQtNk0xXzVrdw?oc=5</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>07-05-2026 23:22 UTC</t>
+          <t>08-05-2026 08:28 UTC</t>
         </is>
       </c>
     </row>
@@ -2596,22 +2596,22 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Update on FDA Priority Review of LEQEMBI® IQLIK™ (lecanemab-irmb) Subcutaneous Injection as a Starting Dose for Early Alzheimer’s Disease</t>
+          <t>Eisai, Biogen announce FDA extension of review period for lecanemab-irmb sBLA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQd1JkMUwtM0lxWF9nQTF3UEpYTTlwWFZfOXhkcE5WVjVTUmZfUWxoN2Jqa0RhdkhTM1hwX1M5dC01bEtTSV9hM2h2NEJYekxaczlJVkNmSTYzS2tkZW5HdE1nMkFHbXlwVUpjazhsMEJZX3E2LWZiVVBSXzhZTnJReVJDV253NTVvMVNFb3c0VnZ6T3VCbmpDaVRZVlJvY1BzVmRWMTBVSVo5VWdJUVF0aFVXRnJ2bXZFQnNtOTRSbw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxOTnZWRGtwb1VNbF9UTEc0cmk5dllHVW91UkRVSGVIajAwOENUTjFLLXdVV1ZqcW9idVFLQVRvc0JMbmtBMndpajBBczlMMlhhblBoN0RYdTcybHgwU0tYWEtsY2UzN0Juc29fSUNkUnJVenhQN0EwQmNDQ2xGZE5yVkNZajJsNFdMOVZIWW5qZTNPRk1hc29oQ0YwRE9OTENSVHBqcVl2aFF3VGZHRXJuM1JxSmgwOWw2WmN4NnE3bGZteDhXRnhVQktMNnk2Zzd3eFg4anlGNEZTN2J2?oc=5</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>08-05-2026 06:35 UTC</t>
+          <t>08-05-2026 18:30 UTC</t>
         </is>
       </c>
     </row>
@@ -2623,22 +2623,22 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>FDA extends review period for Eisai, Biogen Alzheimer’s drug By Investing.com</t>
+          <t>William Blair Maintains Biogen(BIIB.US) With Buy Rating</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Investing.com India</t>
+          <t>富途牛牛</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOcU41Q003aDBDczlaRUdsNnZNZ3lBWlhETkhCRC12em9PQi1rejJ3N2ZmLXpseXpuZGFlQzcycVVfMlQtVGhaelhydVJZWnZaY0NHWEplTzRLR1dqcE5OdTE1V2d6cE5HZU9PWE1iVGptd0lQTVBWSzA5bmtKS0VEX1NnbllUOGFZVFhSN1JIN3dBeWdOaTRxRXJYS0lMZG9LT3pUSzBOT3F4X3pEZnB6TjJ2M1VqMG5nSjdsVkpUdDItdkdUZEJHRHpITQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQaFlxSTcwWTFVMlducW5URDcyRDhua2M4ekYxZGtXcEdHbEdNOE85ajJZTlBoZThQMnBpTWhFQUNyMko0SF80ZGJFUTB0M2l1RTFDcTljUTl0QzluYjBTeVFkNFdLbDExbXFJU1d6ZmRKaDNPcFAwY2V0TExJVkdQQ0tjd0dVZWJsWVloYUdrOUVrNzVUdERwXzl3?oc=5</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>08-05-2026 07:13 UTC</t>
+          <t>08-05-2026 19:54 UTC</t>
         </is>
       </c>
     </row>
@@ -2650,22 +2650,22 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Eisai, Biogen face delay to subcutaneous Leqembi</t>
+          <t>FDA pushes back weekly Alzheimer's shot decision to Aug. 24</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>pharmaphorum</t>
+          <t>Stock Titan</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1tdnFZUjBhTEpjUTMyNzVFV1JmYnA5b0p1OV83c21uaDMtZ0FwVG9KYVE1TXdfS1JhcjRpQ3k4SmdqRExHbTdFdXJEVEQ4bzk4Nnp0eUVtamExMXdSYVc0emNOZlNPV3JPWWlFQmhqcXZwbTFjMGgweUh3Yk5HNlU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPcE1jekJISE9ZUmhZMllGX0lTaHJzVkdOMHc1VUEzN3ZRanlyenVZLTlrNjVsempZV0tKT3F0TWpmS2pja3RMSUY4X2x3Zk5iQlkwdlNNZC1Lalp0ZVdDOHp1RmhpV3IwUmtTSWE3dkJWd1IzQnQ1d1NUcEdxQ2p3RERXTTY0TGgzLXpQV3l3ZlZxZnJpUkY5b1pfT0VCNUs2MGtseTBLdHRfOGJNWTlaallPbEV1MkRDOEE?oc=5</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>08-05-2026 12:15 UTC</t>
+          <t>08-05-2026 09:01 UTC</t>
         </is>
       </c>
     </row>
@@ -2677,22 +2677,22 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Biogen, Eisai forced to wait as FDA extends review of subcutaneous Leqembi starting dose</t>
+          <t>FDA Extends Review for Biogen's Lecanemab Treatment (BIIB)</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>FirstWord Pharma</t>
+          <t>GuruFocus</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTE41SHFJSWNBN3FjbkZUWWZGWHBneUdZS2RCSTgyQTRmcEduLTlnTWJnQ0pubzQzeERGWExIMkJVVzdxZTN3aXdNMy1kcWZ3S0kzTlk0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNdi04em5aRjg5VWdQT0J6Qy1zY0p2LTRGVzJGeWZsN044OTBveTA5LXNDYkFfWXdhdHRzWG04blUzalVLQVFVYjRBWk5KM1pabDlyOTczNXVERVJKX2NyZFUyNWdNRHRZeXUtV2huX0xiUmJXNWw0Wk1qUVdFR3pkRDVIUENxV0phNE1kRHRfOWNvbGxlcVNRUU9nY2hTRVZmUnRyR3dZU2lodw?oc=5</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>08-05-2026 07:54 UTC</t>
+          <t>08-05-2026 12:11 UTC</t>
         </is>
       </c>
     </row>
@@ -2704,22 +2704,22 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Biogen Pharmachem Industries Ltd Falls to 52-Week Low of Rs 0.44 as Sell-Off Deepens</t>
+          <t>Biogen (BIIB) FDA Extends Review of Leqembi IQLIK for Alzheimer's Treatment</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Markets Mojo</t>
+          <t>GuruFocus</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOSmEyNGcxcDVRTW9IOWtKWGJVT3I5YlY4MXRLNFlBV3lrVjRLbFdwdGotQ21oRTNjLVFmdXk3SnhRcEx3RGc3eWNRX1hQdnFJdERsUHFiSGZ1VXBkN3htNUpnUlJDQnRBX1R2djkxQ0duV1FPS04zbHdhb1ZkR3NvSXpOSHZGWWg3dWdCd2k3WVhnbkJrR2FDTnVIQVZNVzVkeWVvXzFWRE5XRExILUJjc05FdzhzYmItMnQ0aw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPOG9BYjFiYVNsclRPMTRadkQ0R2FJZUhEenlTV2JOS0lqVWszREVqVVNRUWE0aDN6M3dxM3RzMExCa29ZaHhMbHJtc3FyT1M5LTY0NUtBdGhKVm4yOTNBaFg5MHVtRWJCdkJxRzU5c0JRT1kzbnJaVWJCWGh6d0d4dXc1TzBYWUFJdzRaVGI2WTE1LWw0YTJTc3NndVJ2ZzlGWUx5M21HY3NxWTlvUzgzZTMyOXhkRnozQk9ZTnhqcWY?oc=5</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>08-05-2026 07:17 UTC</t>
+          <t>08-05-2026 10:30 UTC</t>
         </is>
       </c>
     </row>
@@ -2731,22 +2731,22 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Biogen, Eisai hit with 3-month delay for starting SubQ Alzheimer’s therapy</t>
+          <t>FDA Extends Review of Subcutaneous Starting Dose for Lecanemab in Early Alzheimer Disease</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>BioSpace</t>
+          <t>Neurology Live</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOUnBJU0wtcjZtTmlUaDhzc09hcEdmMUw4WlEtZUFGclVLYUk5SlFoSTZucDZDZlhuWE55NHBZR1hHeDhJSE9ENDVkYldBSUJDUDRnUmJyUHFla2xxVTZWR0I0Z2RKMHc4SkFBU2ZMLVBzZXg5eUdvVUZfdFRyakI3NTZab2J1ZHpMc2hfQXpHX05Cd0dtV3pyRnBhLXBzcGNlYUtr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQTXhvdGQzV0cwSGNMU3VzYzJhRlZiOEZzTVJCel9mNEdJc3Y2elNDcjQ1WFlldks4ZGRtU0l1WHdFUXludFg1QTYzd1NDUGEyaFZ3NmZ2U2NsN3ViUVVrdml4TzdIeXBlLXNibWhseUhvT0FHQ05WWlJGQkE5WHJzM2VSREhDeUZJRFI0Ny1hb2VFeXZwUzl4NVRHSXp2Sm45MXAxOVh1QnJSbjJxdy1sUEpSUE8?oc=5</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>08-05-2026 12:47 UTC</t>
+          <t>08-05-2026 18:09 UTC</t>
         </is>
       </c>
     </row>
@@ -2758,3532 +2758,2425 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Alteogen posts strong Q1 earnings on GSK, Biogen licensing deals</t>
+          <t>FDA Extends Priority Review of Leqembi Iqlik Subcutaneous Injection</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>koreabiomed.com</t>
+          <t>Pharmaceutical Executive</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE8ySngzYV8zUkJLYkJQdTdvT1NHMFNUcDI4cFRFRHk4Q0Fwbkc5OWs5QVg3YkJ6OHFER0FLR2t4Ui12dTdQNmNrMXVkQVVWOW9vWnRpSXNFSi1HZTlHUVhzbGJiamJOM3RwS050QlV30gFyQVVfeXFMTjNIXy1zNmtuZnR5MlZQMHRzZDJtOXNldzZzU3puRTEtUnljbnllb0ZWV1BNQzlqS09wR1ZaSHlQRG9WME1oUmFUa05tRW9pMTNRX2tQN09wV0FJSXBNb25mNEpmeV9EcFJnNC02TTFfNWt3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPc0ZqZFBlUzFmMXl3ZkN0ekIxT1JjNHNXd3JvUG93aEEwRHlCZzNETzhiT1NKT1NLZFpxMWprNkduc2ZoVWVwSF9RZkRnMkhrektKSVdsWHdwNzBPc21kNWJwQUxFclJTakE2eE1qSkU5QjdUd0d4eHZrbW9hOHVjOFlxODdWOVBSV0QxVVliclhBcUhibU1DSGp5MA?oc=5</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>08-05-2026 08:08 UTC</t>
+          <t>08-05-2026 23:18 UTC</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Libbs Farmaceutica</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Biogen Stock Gains Despite Extended FDA Review For Alzheimer's Therapy</t>
+          <t>Semaglutide Biosimilar and Generic Market Size, Share and Latest Trends 2026 to 2035</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Benzinga</t>
+          <t>Insightace Analytic</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQZzBhQmNrbXV3cGlBcHlnX21CdFg4QzBhUXdab25wVUZDWFBEWi16TW9hbE9WZnR5b25td0lKTGI0NWJuQ2NselhvNFN5R1Vxak9xN01kZml4SVhTUVhXckJnWWxRYzBMOElFUnlPMVBkUU1HSWFjeDE1ZS1PeldRVlZob09vcjRjRXVLRnMwY2pOa053UU9USXB6WThKOERkSUpQZmRCZ3BCTEZWTHptczRNMGxjMlNmeHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQckkyWlpVRUgwWk1lSWF4cHVjZE13TWpqdk4xZnotYVlPaGpNdGI5djdSaDBuSnJmS3NtVF9SUXNjeThBMFlLdDhBcktrb0ZlMVhTa2FfRXRPekQ3MTBtSE9PUEFBUWJqMkZDRk5vQURfZDRMVzQ3QU5jN0hNYTI5SjZlUGc2SnhLbktYcnB5cFFtZw?oc=5</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>08-05-2026 15:31 UTC</t>
+          <t>08-05-2026 14:27 UTC</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Blau Farmaceutica</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>FDA Extends Review for Biogen's Lecanemab Treatment (BIIB)</t>
+          <t>Blau Farmaceutica Q1 2026 slides: 17% revenue growth, zero leverage</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>GuruFocus</t>
+          <t>Investing.com</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNdi04em5aRjg5VWdQT0J6Qy1zY0p2LTRGVzJGeWZsN044OTBveTA5LXNDYkFfWXdhdHRzWG04blUzalVLQVFVYjRBWk5KM1pabDlyOTczNXVERVJKX2NyZFUyNWdNRHRZeXUtV2huX0xiUmJXNWw0Wk1qUVdFR3pkRDVIUENxV0phNE1kRHRfOWNvbGxlcVNRUU9nY2hTRVZmUnRyR3dZU2lodw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOd0luWGNUam9MUlA2N3pBU3hZeXJoX0R5NVNrdThOc0s3TWlSV3JDZEp2dnVfS1hNeGJZdzlNQWdtSTMySnlOMGFJY3FXVjhydzF5OFRLNW0yZGNvdlhmcS1FTmlIb2g1eGlicS1uNm1YbW05UVpyYjFwaklmOVhFTi03bHlVUjhkY05vMDlvU2h4SjctcEFZVG5nV1YzV09nOUJGZzlGSXBHVFJsakJEOXZJSW81UTF3aUlhRjdn?oc=5</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>08-05-2026 12:11 UTC</t>
+          <t>08-05-2026 23:47 UTC</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Blau Farmaceutica</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Biogen (BIIB) FDA Extends Review of Leqembi IQLIK for Alzheimer's Treatment</t>
+          <t>Earnings call transcript: Blau Farmaceutica misses Q1 2026 earnings expectations</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>GuruFocus</t>
+          <t>Investing.com</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPOG9BYjFiYVNsclRPMTRadkQ0R2FJZUhEenlTV2JOS0lqVWszREVqVVNRUWE0aDN6M3dxM3RzMExCa29ZaHhMbHJtc3FyT1M5LTY0NUtBdGhKVm4yOTNBaFg5MHVtRWJCdkJxRzU5c0JRT1kzbnJaVWJCWGh6d0d4dXc1TzBYWUFJdzRaVGI2WTE1LWw0YTJTc3NndVJ2ZzlGWUx5M21HY3NxWTlvUzgzZTMyOXhkRnozQk9ZTnhqcWY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOVlJIWnFlWXo2TjdzQmxPZWYyeXk2c2NfRHVwdWliajZUSEZiSUhJSlAtT0o5MENTYzZMdGEyMEJPejVoX2dsLWNYQ0d6c1UxbHZGYW1qWUFNSDVNSHhhRW5vQ2liV2xMbUZWZ2hBT3ZMd2dBNkJVU0ZmUG9ENmRKejdIdjktY2RXNWloeUNvUWN4Y3hJd3kyZlpKMHZTQy1zclZETmQ0aHhRd09yVF9oM0ZqbzI4ZzRicFZQTzRna0xqWTNvUjl6TVRGbzV3a0M5?oc=5</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>08-05-2026 10:30 UTC</t>
+          <t>08-05-2026 21:40 UTC</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>FDA Extends Priority Review of Leqembi Iqlik Subcutaneous Injection</t>
+          <t>Dr. Reddy’s-Nestlé Health Science Launch Celevida® GLP+ to Support Patients on GLP-1/GIP Therapy</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Pharmaceutical Executive</t>
+          <t>The Indian Practitioner</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPc0ZqZFBlUzFmMXl3ZkN0ekIxT1JjNHNXd3JvUG93aEEwRHlCZzNETzhiT1NKT1NLZFpxMWprNkduc2ZoVWVwSF9RZkRnMkhrektKSVdsWHdwNzBPc21kNWJwQUxFclJTakE2eE1qSkU5QjdUd0d4eHZrbW9hOHVjOFlxODdWOVBSV0QxVVliclhBcUhibU1DSGp5MA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQNUlZRGNfUVg0NXFGNm1ydkYyYkxRMkozR0hkQjd6T0dMYVRBZnZldS1HQ0ZvQ004bV9uSmhVaWUtcUtSLTZHdHNON18td08tdTJIN1V1OV8yUFUwNHd5aEhldm8zZkQ1TnpleGJsS0xTalM1UkxtZmZnOV9BVTRiaXdWLVVUa1Y4X1dfSXlyd0tReUJ4Y0VzSGh2NmVhSzlocTBiNmxWcXVpQnktUW1nUm1sdk9odXcteHA0dWlVN3lLS2dOVXc?oc=5</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>08-05-2026 15:53 UTC</t>
+          <t>08-05-2026 12:52 UTC</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>The FDA’s Approval of High-Dose Nusinersen: What Doctors Should Know</t>
+          <t>Dr. Reddy's Laboratories slips Friday, underperforms market</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>CGTLive®</t>
+          <t>MarketWatch</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE8xQkJzazlldUhIX0xpcGZwUVZvVnh6U2pQZEJzX1Z2cnZRMVlsVXltVExZTGc2Unc0M0ZJcllRVWFfbWhVR2NncmhUVFJzOFg1ZmtKb3hDQlBYd05NYUExRkhkdFljajNlQnN5eUFzY1AwMlV2ejhiYWpOLXM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPVnRxYWF5YzVBNXF5cU56TjlzSmgyc0ZsMmtGenA1OVJWMEVBYzJSWFRpZUZ0dTRpb0Z2WTh3aUZXVmdtZGZSMjF0YWRNOHNhUXZ0dGlONzlTZ3pKRmlibXRKdWp4Y2I5eE9TS2VRWmtNdUdzTktiUUN3Q19HMkpraldTcEhVdjF0TWdRZEZfY1RrLVhkeDhfeDc3LU1ZWVJCRUxab1lLZWFBOGtBaEYtWU5xOA?oc=5</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>07-05-2026 20:50 UTC</t>
+          <t>08-05-2026 10:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Alteogen Q1 Revenue Reaches 71.6 Billion Won, Reflecting Technology Out-Licensing to GSK and Biogen</t>
+          <t>BioTecNika Times- 08-05-2026: FREE Career Boost! Govt Research Jobs + Novartis, ExxonMobil &amp; Dr. Reddy’s Openings Revealed</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>아시아경제</t>
+          <t>BioTecNika</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE42S2xsbWJrcHZDRm8wQzVhbUtpMlVIZmZ1QmRRM0licGpHXzVtdVdoWU9PMTlteXpYRE1JZkMzdnkwMkZxaGZ3cHNTeEdSZ0hfODc4LWRZRlJoNkxTTTV4Y2c1WVc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5NWTdnX0JZS0VMaXVoWlhVUVhsRkxxaTI0WUJEM3NjYTRMRl9Oa0haQ3MxVVh5R2hvY2VPeG55TzJqR3daNjE0VUdPX0VkSy1WRkxkaGRrcmxzMm1aY2xLZnYxWjhmdXUtcldhWUlQY0LSAXZBVV95cUxNZk0zYzQ4LUdDZlJQdGJGVzQ3NUdpRF8yOWsyc18ybW4ydHY1Uzc2MWRFX0FmR0h5WFFLYkZNb1Nuc3JGLU1pZ0tRN0k5Wll0SkFYajlfNzV6N0M3RkhhY3g1WlhDRm1CS0lNNmVpeGg2NzBoNjJB?oc=5</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>08-05-2026 04:52 UTC</t>
+          <t>08-05-2026 12:49 UTC</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Alteogen recorded sales of 70 billion won and operating profit of more than 50% in the first quarter..</t>
+          <t>Consultation Workshop on Bharat Soil Health Policy Organised at ICAR-CRIDA, Hyderabad</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>매일경제</t>
+          <t>Indian Council of Agricultural Research</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiS0FVX3lxTE9DWE5QVnpFNFRXYmtzckZVYWEtSEtlSTNaOE9zR0ZmbTg3RzNXSXJKRTJGcnVjOUNOVUhDZmxnazFET3pMeHloc3BxMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOQ3huOWxZb212UjhNV05neEtFX3ZiZm1mdkIxSjBFaXRoNVBweVlzbVFXdU01RHQ0ZHVNcE43cUlZMWEyTW42ZTRQTVItdWNyLUU2bU9od2FwN1pMcUJobnJSQjUwRWFKM1E1T196LUZxaHFoMzNmbTZsUDNQclk0U1hudHJLZGxPLTNHVzFFb3BENDgwcmFtR0gyeDdsUzV0T1FR?oc=5</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>08-05-2026 07:30 UTC</t>
+          <t>08-05-2026 10:43 UTC</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Libbs Farmaceutica</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Semaglutide Biosimilar and Generic Market Size, Share and Latest Trends 2026 to 2035</t>
+          <t>Biocon shifts focus to margins, capacity utilisation after expansion phase</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Insightace Analytic</t>
+          <t>ETPharma.com</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQckkyWlpVRUgwWk1lSWF4cHVjZE13TWpqdk4xZnotYVlPaGpNdGI5djdSaDBuSnJmS3NtVF9SUXNjeThBMFlLdDhBcktrb0ZlMVhTa2FfRXRPekQ3MTBtSE9PUEFBUWJqMkZDRk5vQURfZDRMVzQ3QU5jN0hNYTI5SjZlUGc2SnhLbktYcnB5cFFtZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxOcTVDV29rYVlZLWZmX0RQbUVaeXFQTWtwZl9nV2VGTFo4UTN5bnVzRnFhM3NVcjhuX3R0cGlDTXU2cF9JSGZQUzdxQURTdnkwalVhMWVsYThUU0NpMWRqSXp5NlFUcm4xWFdhOXI5ZDZScEpHdUxKaVotTWpWZkNLSk5qZXNPbjNEelNKSEk4S1ktb3RNYnJvOFRXVVRxY2Q0WWYwUFNzUTVlTXBoQU5pUmdPQkVfWmFmc2NlT19saW9sRk5QWTRnUElTN05rSW91dE9ZbFEtaF80dTRuNXpnVllkQUxFTUXSAecBQVVfeXFMTnE1Q1dva2FZWS1mZl9EUG1FWnlxUE1rcGZfZ1dlRkxaOFEzeW51c0ZxYTNzVXI4bl90dHBpQ011NnBfSUhmUFM3cUFEU3Z5MGpVYTFlbGE4VFNDaTFkakl6eTZRVHJuMVhXYTlyOWQ2UnBKR3VMSmlaLU1qVmZDS0pOamVzT24zRHpTSkhJOEtZLW90TWJybzhUV1VUcWNkNFlmMFBTc1E1ZU1waEFOaVJnT0JFX1phZnNjZU9fbGlvbEZOUFk0Z1BJUzdOa0lvdXRPWWxRLWhfNHU0bjV6Z1ZZZEFMRU1F?oc=5</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>08-05-2026 14:27 UTC</t>
+          <t>09-05-2026 02:46 UTC</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Dr. Reddy’s-Nestlé Health Science Launch Celevida® GLP+ to Support Patients on GLP-1/GIP Therapy</t>
+          <t>Biocon registers net profit rise of 5% in fourth quarter at Rs 126 crore</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>The Indian Practitioner</t>
+          <t>Deccan Herald</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQNUlZRGNfUVg0NXFGNm1ydkYyYkxRMkozR0hkQjd6T0dMYVRBZnZldS1HQ0ZvQ004bV9uSmhVaWUtcUtSLTZHdHNON18td08tdTJIN1V1OV8yUFUwNHd5aEhldm8zZkQ1TnpleGJsS0xTalM1UkxtZmZnOV9BVTRiaXdWLVVUa1Y4X1dfSXlyd0tReUJ4Y0VzSGh2NmVhSzlocTBiNmxWcXVpQnktUW1nUm1sdk9odXcteHA0dWlVN3lLS2dOVXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPNWkxaHJod2ZSSW5yMTI4dGVWRHNsRlVnQUc2RFd2eTM4S3M3VlJMM21hSnBGamNPUzRObTlUVXhRdEhweFBfWVVOLUktSk56bzdHWGZ5cG1ENXlQc1E4NGxPd2QybENHUkY4eHZrZXF0MTltRnpLTXFEZHEyRHN5WHZOX0lUdE1tSlVpU0hDSDBHRlo5RFFfd0NoNk0tTnVpZ3otOWhmMDNZMkZvci1rYW5ONXBnSDZXS0JER3IwWjVqNUVDNVE?oc=5</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>08-05-2026 12:52 UTC</t>
+          <t>08-05-2026 19:21 UTC</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Dr. Reddy’s and Nestlé Health Science launch Celevida GLP+ for people undergoing GLP-1/GIP therapy in India</t>
+          <t>Biocon shifts focus to margins, capacity utilisation after expansion phase</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Express Pharma</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxPTjFpMFZCWWF1YW9WRGY2S1cyNWlCQ3JHNmlPcHN2cEh6aFV0V1ZlaUk4Q3Nva19ucWtENWFEZnB4UXlqVnp2akFvWGxzYkJteTZQcDk5TW0wOWVDUWRjYy1JdnA2eDFocDZxR2ZsZlhYZ0F3WU9xeW1nazh1dDdIWElrQTFjdkR1Q1ZxbFFoWUNobUNGaUZlNUxzTnptRFdvV3VOa2lhbS1XXzNVZjZBOFg4Y2s1RF9HTWo5RXYzY0o1NDl3VFJuOU9oWTZVMlnSAdQBQVVfeXFMT3pQYzBFYW5HQmlfbVFvb2ZFejEwS3FtZ0R1THJkVHMzOGhzdWRvVnFiT1kxU0cweExvUXdQZW9ob1lENU52QUxONDZEdXhEaTA4TTF6bW1TRll2TG5LUHN2UV9xUjBLZ09VSWhNam83QWNxa1FhRjRDQ3ZsSGtfVGRJSlBMRThkNHZqazlyOVFIVFI0a1F5N296WTZNTXEzcm9qS0gtRVBLbVRpVk5MLTVMQlA3N1pqb3lQdlRQbWhUUTJKWjV5TlBQQzBSSm9yYlBxVVI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxPQlh6SHhGNjRWV0dlMzdCeEdwejZFWWFsWmFZdjNOSjJweW5lQ2NIT3RVVHRNM1FyUk1wRC0zRlVOYTlEQkllRkFhYWdCWmp2V1Y2eUVSend2bkUtME4zLVpyUTF6THVIRXFJZ0E2WTYybndvTm5xa2ZvVklHOEZ6ZjFuUDZFMUdDbFNaeUw0TFNqVWQwVFZhZ3VKSW5iMy0wVTloUXhCelNzcFdwYV92WXZQWWh1SmRDamxlNUp4VGpxTXZmZmlwYWJCSlV5UXRaQVhHd0lIOUNUNHYxQm9BaFY2NXlKUGFXOHdV0gHwAUFVX3lxTE9IQU1hM1IwSDRZUDhwb3hrSW10eDNnR1JHNmx4eVNuXy1FdENnaXlPN005dGx0WlVuQWM5N1N2VFNQSFB6QWRUYVB3cmNFN290RmpYb0pYX2s3R3NYenV5RTRwTnk1TG85YTlZNTJhc0xROFNNXzE3Smx0ZU50MHh4Q19kVWdOMjY5eFBTcHJHeXN5UVpTVGY4VFE0RnlDLXpsNkk2eXNLbTR3SVBSdEVWQndjdnAyT3FGVVpaX2dFbk1kRjU1MFdHTFhQaWNlbEE1VDFhbWZoSVNqUG9Pazk3ZE5kaUZ2bEZoR3ctMmNqLQ?oc=5</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>08-05-2026 05:44 UTC</t>
+          <t>08-05-2026 16:49 UTC</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Dr. Reddy's Laboratories slips Friday, underperforms market</t>
+          <t>Biocon Ka Profit 74% Gira! Ab Margins Par Full Dhyan, Naye Drug Ki Umeed</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>MarketWatch</t>
+          <t>Whalesbook</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxNc3J5STlSazVqak9JX00zcXRDc0hPUHlYQ1lSb2xVc2JtZUdoNWhLT0d6N2NKU1FVY0hBa3p3cDhJUE9LaXB5QUszc0Q1QW5uUnRlSW1TUVNYRVc2aXNuR3AtX09ObVVHdC1DMDBLdDRSTnVEUmI2YmhuY3VLUzF0Mmc0Y0pFSjFqZGFESWRHQlgtQmVlMWt1cW9pMEVPT05rRXZnRVQ4Y1NRYzVTeXVVT0d3OGFpNnhwaGplaE8taVctYWZuSmZBTkc5blpFMlQ3Y0pSX3k0VEVjUDZq?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxOWmVwaVVDaThRbGZhMElYc3J6OTNxQnZxYzgwV25CdzNXSTZsS3dzdUp6ak5yYTg0U2hyWlAtQ3pBYjRFMHBhMDVlNEdOS2pCVUtGRjhpVXkzOG9hbVdqeFZiN3phZUdPX3puQ0JlV1dGa0FkcUhpbVhPZkxRN2RkaHA1eFZweHRubmRYNkw0S18zZWRMNVhZTElNY3Z0RG5WOWdCVTdZV3lzSlVCUEZWRC1QN1diTkZ4VGVzQTVyYjlSLUJ0MmlQc0RFVmJaRFhYUkhTYkJHUTUxQllUNzc1Mw?oc=5</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>08-05-2026 10:30 UTC</t>
+          <t>08-05-2026 18:06 UTC</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Dr Reddy’s, Nestlé Health Science strengthens presence in diabetes, obesity nutrition space</t>
+          <t>Claire has what it takes to lead Biocon forward: Kiran Mazumdar-Shaw</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>FFOODS Spectrum</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxORG12cU53WXhMaXVwYzR6bDdXZ2pRbWJ1NjJzNE16Z1RiZ29CSGZRSkdYcVBVM2E0cHA3RDBnUmNKTUtzb2E1b3NRLVoxbmxsVFlHSG5vbVFGQlQwVE5lbDRSb2doTThOVVc5MG5PaXN4VzZhVlhwRkZvbjFaamUyaUxXQno0b2Q1MFRWazl3elJNdDdTT1JyeExuZmFURDl4bmdzc1FZeXdzczlBU0FtWkhpUWlrUkpBcWgxaU9HSEpHaUk1UU9oM1BRQy01dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPbjBFVFhlWmZYd1A0a3doeWtOVFBHYS05Tm9BbEw4WnRHU2tDYnVndEEtc3I5R2hqbms3UG5kcmJmR19oZFFDcGpka1NncXdmZFQtYVRVc2pMek1LYU9yUjU0ZWtiR1M5QWw5WXVuSThTQlg4ZHRuZjdscFJOVTg3V1duMGhZcDRvOVAxdW54d2ZzTC1yWVFmS0d1ZGU4ei1oWWlvR1B4NFBpX0lnSzZqVzhYbzFTLW96ci1SNEc0b19tczhEMFlyb1Jpb2JDaURTVEdJc0RTVHE5QdIB2gFBVV95cUxPbjBFVFhlWmZYd1A0a3doeWtOVFBHYS05Tm9BbEw4WnRHU2tDYnVndEEtc3I5R2hqbms3UG5kcmJmR19oZFFDcGpka1NncXdmZFQtYVRVc2pMek1LYU9yUjU0ZWtiR1M5QWw5WXVuSThTQlg4ZHRuZjdscFJOVTg3V1duMGhZcDRvOVAxdW54d2ZzTC1yWVFmS0d1ZGU4ei1oWWlvR1B4NFBpX0lnSzZqVzhYbzFTLW96ci1SNEc0b19tczhEMFlyb1Jpb2JDaURTVEdJc0RTVHE5QQ?oc=5</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>08-05-2026 04:32 UTC</t>
+          <t>08-05-2026 18:15 UTC</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>BioTecNika Times- 08-05-2026: FREE Career Boost! Govt Research Jobs + Novartis, ExxonMobil &amp; Dr. Reddy’s Openings Revealed</t>
+          <t>Kiran Mazumdar-Shaw says family will stay on Biocon boards, professionals will run operations</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>BioTecNika</t>
+          <t>CNBC TV18</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5NWTdnX0JZS0VMaXVoWlhVUVhsRkxxaTI0WUJEM3NjYTRMRl9Oa0haQ3MxVVh5R2hvY2VPeG55TzJqR3daNjE0VUdPX0VkSy1WRkxkaGRrcmxzMm1aY2xLZnYxWjhmdXUtcldhWUlQY0LSAXZBVV95cUxNZk0zYzQ4LUdDZlJQdGJGVzQ3NUdpRF8yOWsyc18ybW4ydHY1Uzc2MWRFX0FmR0h5WFFLYkZNb1Nuc3JGLU1pZ0tRN0k5Wll0SkFYajlfNzV6N0M3RkhhY3g1WlhDRm1CS0lNNmVpeGg2NzBoNjJB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxQSk9sYzlWNkUyckJmOUd6aW5nX0Jwd3hPV3hjSTBNZVBHbC1MdG9oQ1ZEWVJyQUFvVE5ITXhhYXVhSVlrZDhNUUt1YTZnM1p1SmNqcHJhdmdKNm1CRWFCazlJQldSeGJZNXYzZzBtTGpmUWkzMDhHZ1cySzFOTzdzZUhzUW9aeHdGQy1oRDMxMTBnRVREaFhFbHlvUzFxMnh3R2hOa1ZYVU5TOFRxZmVKQVVkVHhKT3NRVVd3bk90TE1scWdmc0lNZkxERGItcTN6dDBjdGhZcWJmeFJh0gHiAUFVX3lxTE9jWHYwOEp6dVNIWGRsdUIyZjNpNi0zLVpGTTUwZVBXMk5nc1lDUVRvTVFmTDdWSkNSWjN6T0dmd19Hc3BGcmRhMmNVSFlYeWxPcjhHZU94anZXQnZkOWVnMVo3a1lkTk54cnVTdFlRUlE1b3hLODlUM2dvX2Vhc0VCUmpyV2FkUnNEVnV0bFZzOHRkd0Ruam1GbktLTmtRd1JuMWRkWk03ZllRQXRvOS0xNHhLRTgxUDBRY0F3SFl5VGZ4NWhvY25pcUVESFhTUUVDendJYzB2QmFzVWhVZGFzM0E?oc=5</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>08-05-2026 12:49 UTC</t>
+          <t>08-05-2026 13:23 UTC</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Dr. Reddy’s and Nestle Health Science launch Celevida GLP for optimized nutritional support</t>
+          <t>Biocon reports 63% YoY fall in Q4 profit, final dividend of Rs. 0.50 recommended</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Indian Pharma Post</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxNUHpqeEY1RW9zV1FNLUJlUHJ4eTZ1RDBlbkx5Q0dtWnZZaktwbmh4QmlyTE1QWlFOOTQ5Um4ySDJwVHBUM0poWHlKTDlZeU4tMUdGYW56TU5ISWg5cTNWWk5sMDJFckFobUVjTktHY0IxX2g1T3Rvem9HTXBXUHJSODNuVmczOWNVZzVOeUNBU2pfbFlvb3dxVFVtektKazY3SnVBWkhYdm94Mm1KVlBCaC1UTzZtQW5wczVGOU04ZXdXSl80YUg4Qkc5RTd3S3BVc29CYUN30gHcAUFVX3lxTE4ydmthSl9vai1EV2t6TkxmMEFncC1weVdrZVBIMWZ1ZGk0akVoRUl1NFhtbkt4V09Rc0JOQVR4eE9hcDc1ZGZIN3A4dXJrY2VoeS1idzRXeWpCM0JiVjdUaFd6aUtyQ3hoNnNjNjBoQ0FzRUZPRjA4NHNuTTM3bnU4TGZvT1lHWWUtOHZTZzN1M0FmeUZZQ01QNVNwUkdGWXNKQTM0aEZfWGtJRnZDSmthTVZva0pia0txQ2xqLXRFSmc3OXAtRUVkWlZ1dGh6dlhuQ3d3eUUxd1I2Uzg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxPWWVrTmpvZE83YjI5NFp1djBMczliVmROVVdxeVlnaWFkZmk0bWVLUGdCU2VWMlQ2WEotUWlQYmlrWmY2aGVISGhjaDh4aTlzTnJuQV9WREVGelVob29GbUV2ZnBSNGM2WmU0Q2MxUHVqWjB6WWJoT1lGUS1wTV8xaDlRNVl2R2hldlJGa1RnU0ZENlhwb3pTaDJQQUg4RTBnWFhyUWhMdmxGa2JKb2xTSkdnYjBWZ0U1ZU5jRkZqWHF4aWpyWUpVUTREcE9lbHBWZVJ3enFmbk9ob0hnSy1pYlNpMkZQTTdibkhR0gHwAUFVX3lxTE1kNHVlZDFzaHZpbUd4U1c3VWd1WEVlc1Y3X2NNT2lENGVOSEJBdEt5NElTMGRLcnBjUlVGLXl4RGdDeGh1TDdRTW5abGR3OWUzeFRCSzQxQU0tTTlFRTJwMVBxWExBRXZXV1JFeTJ2VnZXZjExMDJnZVJMeXprbWh3aUJlOWNTekVaMmxhZm0zeDV3ZW5uNmJKVU1oaElDeDkyZ3lmUU5TYWlNRDNqSDJ0VkdUc1ZLelNaTkJTTzFWcjhYQmc2LS1tbWdpS05OWHEtZHBiWXI0LXAwME1EeXhPZEpLMDNfbnhOeEl4VktweA?oc=5</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>08-05-2026 06:01 UTC</t>
+          <t>08-05-2026 10:58 UTC</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Dr. Reddy’s and Nestlé Launch Celevida GLP+ in India for GLP-1/GIP Therapy Patients</t>
+          <t>Biocon sees strong biosimilars momentum, expects merger synergies to aid margins: CEO Shreehas Tambe</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>geneonline.com</t>
+          <t>CNBC TV18</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxORFotYkN2ZHpTNDhZaklhT0MxWkUtNVdRWE9Tdl9pN0pUZDBkTk1TQ0N6Mm9qU3k0X3AxaFhJWTd4UGRCcTBSeEh5ZnpvelRpTmZ0eGp0bDRSZXZRS2FyNW4tN1pNVWNOMkNXWnJfZFlKMV9xdHRmN1RWOXZxaXhuU1h5N3JqdlZFV3BBUFJDbENIcVlEOFpka1VCdHlscG5McXhKSl80NzJZRktI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNQWNjT1pKMGdobW5udlRONHQ3X3VPa21kQnQ2NXNzYk1jR3hPeXozU2s1QmxRMzZOeVVCN1l3clgwTmlEY2R1RkRTQkRQa3gyYl8xMDRYTXBYOU1VY1M0YTd0akl5U2FKMHNYNjl3WFhIeG5WTUpMOWRzSGpSbDRHSWpmb2hzZlpiMjNaQXpVY05KSGFiYkwyU3I4ZmRhLTNCM1BmZkJJcXZJUE5PZ0J6eERvQdIBuAFBVV95cUxQNHZGTGJDeTFFRmo2dG1Ia3F2Q1N0Z1ktTkRKZVM1V2R3aFlFZmdUNEVneElwZEtUVTZUOHpiRVNwVm9CZmU3RzRhaWpOOVphMjJyakRjSE1WNkRqaC12Q2p5cWJ6MzhKSWx6MU9rWXpYamFZcFJON0U3YXhCLXoyY2xnUGEwQlRSN2RleXJkQk9lZTZZdURlbnQ2aUVOWGlpUWNwOWk3Nkszb0dLaHB4NklUUDB1eTBm?oc=5</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>08-05-2026 06:08 UTC</t>
+          <t>08-05-2026 10:50 UTC</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Semaglutide Biosimilar and Generic Market Size, Share and Latest Trends 2026 to 2035</t>
+          <t>Biocon eyes in-licensing deals to expand biosimilars portfolio in FY27</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Insightace Analytic</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQckkyWlpVRUgwWk1lSWF4cHVjZE13TWpqdk4xZnotYVlPaGpNdGI5djdSaDBuSnJmS3NtVF9SUXNjeThBMFlLdDhBcktrb0ZlMVhTa2FfRXRPekQ3MTBtSE9PUEFBUWJqMkZDRk5vQURfZDRMVzQ3QU5jN0hNYTI5SjZlUGc2SnhLbktYcnB5cFFtZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxQcUhDX3BBemNPc1RTTGhHUU1PUkZUR05iS1RNbFJwSFg5dktHcnphX052QjdKc19uOF9GVnZhRlhoT2czRWNERFI3YXh2RTZLU3FKTG0taWNCREhiM1I3cmFYVm5uWjE3WGM3dU10dEZKWmhsbFVGd3RuTnFYdVBOTzFxUVBldnlRbmU3Nkg2SDBucDNvbGpieHRKZlE2RnE1Q0dzWWUtMzVDbGhMbUpDb2Zzb2pEakg1OFpTNV9zMnp0Qmp4bFg2NzZjMDVXYkpucXhqMlJXZndQR1XSAdsBQVVfeXFMUHFIQ19wQXpjT3NUU0xoR1FNT1JGVEdOYktUTWxScEhYOXZLR3J6YV9OdkI3SnNfbjhfRlZ2YUZYaE9nM0VjRERSN2F4dkU2S1NxSkxtLWljQkRIYjNSN3JhWFZubloxN1hjN3VNdHRGSlpobGxVRnd0bk5xWHVQTk8xcVFQZXZ5UW5lNzZINkgwbnAzb2xqYnh0SmZRNkZxNUNHc1llLTM1Q2xoTG1KQ29mc29qRGpINThaUzVfczJ6dEJqeGxYNjc2YzA1V2JKbnF4ajJSV2Z3UEdV?oc=5</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>08-05-2026 14:27 UTC</t>
+          <t>08-05-2026 12:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Dr Reddy’s, Nestle Health Science launch GLP-1 nutrition product in India</t>
+          <t>Aurobindo Pharma Completes Buyback of 54,23,728 Equity Shares at ₹1,475 Per Share for ₹800 Crore</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>CNBC TV18</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOU2NoeWkwdjhnalFMLVA2WG9paExIYUtZWVlRelhvUFktc2lYNThwbi10Y05WTk1UQ3lsY1RMckFmYUVEZDJ5enN5RUwzYk1CZ1dUSUF3b09HQjV2Y0p2T3pwZlozUGNPWTFkZENzX2N2eGl5S05SeExySnR6OTJreWVfczk1cllzbDJtVU95QTRodnZrNVVhdEIyV1dpWnZySFIzOXF2RGdaVnlRcFQ1M1FSZW5lZ2Vrb09oUFR4UWc5SjRXb0ZQbFpyQml1QdIB0wFBVV95cUxPRUd6UmtlUzFlaGVyUF9zN0N1VW9FWWVGSmwwY2Jjc2hBeHBDM1BEN1dGM29LNEdvMUlKX0ZoWFF1UzYzRGlEMmpWLWdXbEpsUWRReS1oQXAwX0NfXzJsdHpsUUNTemJoYnRpcUZldXR0WTlnUjdFNXRDRnROYVQ5b01td2tLd09GSVpNbjV5THZKSTJLTlpvYVhVVURiU0RkN0RQc2ZVYWx6ZmZyVHRxczlMcDZwSGQ1TkpHSFNhYXlhZ1pxZGdHcUQtN29QbVVXbk1J?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxOQThLZTY2aURBa3lTV3UzUkFaTzNpYlRSTWx6VTNsS3pPeXFXWmF0VFBrazdwWUFIdENVRVJ0X1F4cVgyM0dXd28xb0hFY0c3MW8zdDJSVTRTOVdVaDN6N3dXbk9wcHZtNy1jMDBKOFNoWFZFX1g4RzlVX0ZwWkJsSEpVOGxuSzV2SVFRWnMzZi00YjltY1lhelAxQTZJNk5hbHFvRVhtNHpkX01BWE5zRWYySDZyVU1Kc1dxTmx2eGQ5ZFdHZklmMjg5M3c1UDBkQmM5LTdyakRrSWRFVXBKeDlWNkY1Zw?oc=5</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>07-05-2026 17:17 UTC</t>
+          <t>08-05-2026 16:42 UTC</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Dr Reddys Stock Split I Dr Reddy's Share Latest News Today I Dr Reddy Result I DRREDDY (tDm4oRFLYl)</t>
+          <t>📈 Aurobindo Pharma Zooms After Getting EIR for Telangana Unit</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>fathomjournal.org</t>
+          <t>indiaherald.com</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBCMWY5bkJ3ampCTHo4RHdBUjEyVGVQQ2UtbFhNeUI1MUtPRGR2Sm05MEs1N0lYOE0ycTc4bmFHUE5SNDNVLVlQVEI4R2pmZURxY19wWDJEYlF6WHBJX0VCR0VabzdLa1puQThCQkk5YXg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOY1pWODB2QkdCX3EwV1dsS2M3VTBDT0V3NGVqRllLbDNYM0JqaUlTUXZmZFpzWnVmMVJRY19CcVdhX2owcldYVDFsUWNoajZRaENvXzk3dDlBaWtUdGh5TEVwZjdsaTdNY3Z6RlprbmhlQ1BzaEw2UHN5cy1fcjNZaldTbnc2b1gxRk5xZ2tjRm96am5mcld5ZktIRXRSQXlHX2M3TFFnNTZlekhRMUHSAa4BQVVfeXFMTmNaVjgwdkJHQl9xMFdXbEtjN1UwQ09FdzRlakZZS2wzWDNCamlJU1F2ZmRac1p1ZjFSUWNfQnFXYV9qMHJXWFQxbFFjaGo2UWhDb185N3Q5QWlrVHRoeUxFcGY3bGk3TWN2ekZaa25oZUNQc2hMNlBzeXMtX3IzWWpXU253Nm9YMUZOcWdrY0ZvempuZnJXeWZLSEV0UkF5R19jN0xRZzU2ZXpIUTFB?oc=5</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>08-05-2026 07:08 UTC</t>
+          <t>09-05-2026 06:04 UTC</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Dr. Reddy's Laboratories - KPIT Technologies among 5 F&amp;O stocks with a sharp rise in futures open interest</t>
+          <t>Budget 2026 Ka Kamaal: India Mein Share Buyback Ka Trend Chhaaya, IT aur Pharma Sabse Aage!</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>Whalesbook</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwJBVV95cUxNeENZZlZoRkxGMl9GbW1ZOG1qYzRrNHE4d0tjZDZXdkNQNDhobVlCbkZBLUpNM0tqS09QLV81YW5NRExtakl0NmwzZzM5bFcySDRSV2N5UVBrMXJxWGVkdjlDUXBNWUh3V2pVUnA4UV9mcGJncWJ1ZGthZENCbExzOHhaNkhadmlnWWZPd252OVVpN2JuWDZud1Z5cFdZb0lUc0lMY1FIcnZfME4zdEtqd1dLd2hqS3luOHFUMTZJMDZUVWZGRFR6VnI2UnlUMGRBSXhSZUpRdFRtZTZ0ZF9oWHNXaUlGVWV5M05NX3BuMy1RbVljU1VRSWVuVzBxRG84NlVB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxOYkZEYjdKUEc1X2kxLTY2azYwREFzUU4zYWE3YVk2eGFxTlEzWTRoa0ZXNkxuVi0zWmVsaFRZSzR5OGh0WVRnZFdsWnNGMTA5dXFyZ2VkSjV5cFdBNDduNVptM0FIUXpWZjlicEd0NER3YkczYVZkLVA2dWI5WVdReWRSR3k4S1hON19vTzhUUUU1NUUwZGxNc0dlYmRlNURneGxTSWlKTUNaZ2pxYXlIZ2JLUFY0bzF6elBJYmZuYVVMYWpiLVVCTFl4MThvOFNiYkQxV0VBYUp3bGhpRUVOTEtNendqQ3B5OWxGMnNB?oc=5</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>08-05-2026 04:41 UTC</t>
+          <t>08-05-2026 08:50 UTC</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Dr Reddy's, Nestle Health Science launch Celevida GLP+ in India</t>
+          <t>India Tax Law Shift Sparks Buyback Boom: IT, Pharma Lead Repurchases</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>NewsBytes</t>
+          <t>Whalesbook</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOdVpNNjBJRFZyNTlaaXJ3WENVVE93U1NxdWZQVG9HWUZHRU9OMzEzdnVLQWk2VGpmX29IV3ZUNnRSamJiOFZjQVVPaFJtY1BCNFNCWVBSNFl5Ykw5TE9jWDFpNmUxQmpGWFZ3aHBKMDJJT2RsMXZFSHRRSFQwVWhiR19qMFJWWVdLTmlNVFN3Z1FXSHViWDU1S04wdkdabDE5b01Rc0RDX3E5YUt6?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxPdUZjYTM0cVpNRzFlNDB4dnU5bjVLRjFCNFlVMEdCalZGNnphU0xMVFpCLVE2RUhzSDdjOEVLV19PSGdEVHpYMjNPOEVtbWUzY2oxUHNzWHJiNUZ4Rjk2SENTQmVGSl9XN3NuZ0FYNmUwNnoxQ205NFV1UU1tNEhDU1R2YXlNSFIzZkd0Qk5WUjJXUEVRVmZUbzdEQmJoemZhMlpFWFNRMW1HTDZaYWF6dzZVTGpGR1pkbGtwRkNXMks1UkFUcW8zOGN0b2JYUXZfcVJIeXliUmZIS0VYNnJ4QnhickRuZGdKYm9FZA?oc=5</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>07-05-2026 17:41 UTC</t>
+          <t>08-05-2026 08:50 UTC</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Consultation Workshop on Bharat Soil Health Policy Organised at ICAR-CRIDA, Hyderabad</t>
+          <t>Buy capital goods on dips, stay cautious on IT and consumption: Sudip Bandyopadhyay</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Indian Council of Agricultural Research</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOQ3huOWxZb212UjhNV05neEtFX3ZiZm1mdkIxSjBFaXRoNVBweVlzbVFXdU01RHQ0ZHVNcE43cUlZMWEyTW42ZTRQTVItdWNyLUU2bU9od2FwN1pMcUJobnJSQjUwRWFKM1E1T196LUZxaHFoMzNmbTZsUDNQclk0U1hudHJLZGxPLTNHVzFFb3BENDgwcmFtR0gyeDdsUzV0T1FR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxNdUxyczlqYXVoSWxPd24tQ0ZRdGJjU3JOUmNFNHh5QjlDNFhaQUFqZXlldnJNQmQzZFRwZlc4cHE5dEcxLWozdE9WeDlBVFdhNTlaQ2VBZWFORm9zT2tDY0ZEWVNzYVRnUDNqWUVzeXh3blQzWTlmckdIejRIWjVZdUF4R3BCM0tMZ1RQSWFlMEkxOFBiRWxMSXBQbHdJMWtrOThtTW4tWTFWb0Fha0ExZG5WV2otOHpwYU9IMkVaMW5LSlBHZ2NLYnl0ZFl1Z1ZlZnZJOEFtd0V5OHJhVFMzUFdKZ19IeE16RFVUaTYxU27SAfABQVVfeXFMTXVMcnM5amF1aElsT3duLUNGUXRiY1NyTlJjRTR4eUI5QzRYWkFBamV5ZXZyTUJkM2RUcGZXOHBxOXRHMS1qM3RPVng5QVRXYTU5WkNlQWVhTkZvc09rQ2NGRFlTc2FUZ1AzallFc3l4d25UM1k5ZnJHSHo0SFo1WXVBeEdwQjNLTGdUUElhZTBJMThQYkVsTElwUGx3STFrazk4bU1uLVkxVm9BYWtBMWRuVldqLTh6cGFPSDJFWjFuS0pQR2djS2J5dGRZdWdWZWZ2SThBbXdFeThyYVRTM1BXSmdfSHhNekRVVGk2MVNu?oc=5</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>08-05-2026 10:43 UTC</t>
+          <t>09-05-2026 05:45 UTC</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Biocon Q4FY26 Total Income at Rs 4,569 Cr EBITDA at Rs 1,073 Cr; Net Profit</t>
+          <t>India announces record $20.5 billion investment in US at SelectUSA 2026</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>The American Bazaar</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBKcXVWQTlVUjN5aklyZnp2eVVuNTNrSWxsZWlBV2hPREpUUGhJR05tamtwVlEzTWQ2bmMxMEtKUDdqQkRIVnpXUDdpOHJaNUxGbWR5RENfcFc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOR1VaS1VaMHVqVkNQbkhkRTVyN3B0LThfRXZyZUNKbXBNQ085dlhZbHVQanJRU04wVzRWWVE0ejhFOHlLTUZ3OVFSSm40cHRhdmp2UDFlRVV5MldFVVIxTk1fVUZRNlN5N1ZnSk8zdXRDXzBOeTMtdkRYdEdGaW43UE1sLXRKWnRWV2F3bndJa2FwWXpwYTFHd3Z6bnN6a2U0QkFrY1MtRE1SUUtrSVgyLTRJZw?oc=5</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>07-05-2026 18:22 UTC</t>
+          <t>08-05-2026 10:45 UTC</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Biocon reports 63% YoY fall in Q4 profit, final dividend of Rs. 0.50 recommended</t>
+          <t>Indian Pharma, Tech, Engineering Firms Pledge $20.5 Billion In Investments Across US</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>IndiaWest</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxPWWVrTmpvZE83YjI5NFp1djBMczliVmROVVdxeVlnaWFkZmk0bWVLUGdCU2VWMlQ2WEotUWlQYmlrWmY2aGVISGhjaDh4aTlzTnJuQV9WREVGelVob29GbUV2ZnBSNGM2WmU0Q2MxUHVqWjB6WWJoT1lGUS1wTV8xaDlRNVl2R2hldlJGa1RnU0ZENlhwb3pTaDJQQUg4RTBnWFhyUWhMdmxGa2JKb2xTSkdnYjBWZ0U1ZU5jRkZqWHF4aWpyWUpVUTREcE9lbHBWZVJ3enFmbk9ob0hnSy1pYlNpMkZQTTdibkhR0gHwAUFVX3lxTE1kNHVlZDFzaHZpbUd4U1c3VWd1WEVlc1Y3X2NNT2lENGVOSEJBdEt5NElTMGRLcnBjUlVGLXl4RGdDeGh1TDdRTW5abGR3OWUzeFRCSzQxQU0tTTlFRTJwMVBxWExBRXZXV1JFeTJ2VnZXZjExMDJnZVJMeXprbWh3aUJlOWNTekVaMmxhZm0zeDV3ZW5uNmJKVU1oaElDeDkyZ3lmUU5TYWlNRDNqSDJ0VkdUc1ZLelNaTkJTTzFWcjhYQmc2LS1tbWdpS05OWHEtZHBiWXI0LXAwME1EeXhPZEpLMDNfbnhOeEl4VktweA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNREoxRU5pYko1aW00NVVwSUNBUzFHRlMtSHphUmRNdjg0Uk1YRnR6WnhPdkFKei1rU2d3UnJhbGVyMkZ5ZG1KLVN4anZjb0xjd0R1TGJZTTgwbFNtRVM5a21hY2xHamJkZW8zRm96SjlCTmNCMEl2VFVkQ2k3TFVDaHNoQnZZclBSSlFlREh5WWFTX0d1WVZ1ZnA0YXZoaFAwODVtNGdvVQ?oc=5</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>08-05-2026 10:58 UTC</t>
+          <t>08-05-2026 18:14 UTC</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Biocon eyes in-licensing deals to expand biosimilars portfolio in FY27</t>
+          <t>India Ratings Affirms Eris Lifesciences 'IND AA' Rating on Strong FY25 Performance</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>Whalesbook</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxQcUhDX3BBemNPc1RTTGhHUU1PUkZUR05iS1RNbFJwSFg5dktHcnphX052QjdKc19uOF9GVnZhRlhoT2czRWNERFI3YXh2RTZLU3FKTG0taWNCREhiM1I3cmFYVm5uWjE3WGM3dU10dEZKWmhsbFVGd3RuTnFYdVBOTzFxUVBldnlRbmU3Nkg2SDBucDNvbGpieHRKZlE2RnE1Q0dzWWUtMzVDbGhMbUpDb2Zzb2pEakg1OFpTNV9zMnp0Qmp4bFg2NzZjMDVXYkpucXhqMlJXZndQR1XSAdsBQVVfeXFMUHFIQ19wQXpjT3NUU0xoR1FNT1JGVEdOYktUTWxScEhYOXZLR3J6YV9OdkI3SnNfbjhfRlZ2YUZYaE9nM0VjRERSN2F4dkU2S1NxSkxtLWljQkRIYjNSN3JhWFZubloxN1hjN3VNdHRGSlpobGxVRnd0bk5xWHVQTk8xcVFQZXZ5UW5lNzZINkgwbnAzb2xqYnh0SmZRNkZxNUNHc1llLTM1Q2xoTG1KQ29mc29qRGpINThaUzVfczJ6dEJqeGxYNjc2YzA1V2JKbnF4ajJSV2Z3UEdV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwJBVV95cUxQOTBHNkVjOTlaRi1Ia1R5M3hxZm5YQWhpZXFBdkFNTC1QSVVhclFadHB3VzZsdTdXTkhSaDJDSnl3RGY2enB6NktUWHBFcjhzOXhIMUdmcmVHbjd0UFNfX2RVNmJtb0xLakk3cW40enptcmR5QzYybXdTWXg2VkVEa2d2bXVEdVBiU0E3dmdGV3ZadFFtRWNhSFN5b2djcXNEUGlTY29xU0NzLWFybi1CSC1tQzdFWFlEVFhMZkwxd3kxVTAtQ29uWUpnZFJ3S0U2RW9jZDFGajR0RkpXcEJjdGFxMEZCelI5c016U2s2WVpQaGFLVnFCWmx6eThRSmNqTW5Z?oc=5</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>08-05-2026 12:54 UTC</t>
+          <t>08-05-2026 11:57 UTC</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Zydus Biotech</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>The handover will happen over 5 years. Kiran Mazumdar Shaw lays out the roadmap — Claire Mazumdar will transition over the next 5 years, stepping into board-level roles across the Biocon Group before taking the reins. Ekta Batra | Kiran Mazumdar Shaw |</t>
+          <t>Zydus Lifesciences Board Meeting Scheduled for May 19, 2026 to Consider Q4FY26 Results and Final Dividend</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQSkQ2ODJvd1BFd3BDd21vbHVDZzQ3YWUwSm41XzVESjZ3V0pVV1VOMkN0a2Q0RmZ5bFEzcU9TNEttZFBaSWFKRHF5UlBCOHJOX3ZmYnNNNkkwR0FldXNLbkctdkVaWTdscktjbHRqVkFMUnFZNEwtdHRLNThKMHAxUEthcnZWTy0tQ2NQOTBCS3F6YnFGX0tlWDNRTy11LTlXMjV2N0Npa0VIVnpPMHVWQ1JOeWxlRHhi?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxOaXNBTm50RkIyTHVsS0UyajVqdkVMMkRuMm5yWjl5aEwyMW5UbE5JZ1ZHNEVPZUVNM2V5SWVwYlFmQ09lMXRkN0s3ZnY3VzdtaVZmd2dLQ2QwdzFlMjBnYVlZbFF6Sy1fS1Z4dHp5ZmExSG9ybERJRlh6aWxNejJxSnVNeXgzY1JGeWV3ck05MEM5aC16V0JuZUN6aW1ETlZ4N2ZmNFhyWllYcUgwQzl5TGlscWZlYlhYOGljUFh0NTRzeHVPMFRyQ1UzRTFJZnJRRW9hc2xyRDJWdWlLTGRnVzdkLUpmQ1NlTUpiX2dRaXNILUU?oc=5</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>08-05-2026 09:41 UTC</t>
+          <t>08-05-2026 14:17 UTC</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Shilpa Biologicals</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Biocon shares gain 4% despite net profit declining 57%; check all Q4 numbers</t>
+          <t>Fareva Pilots New GMP Unit at Pau Site</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Upstox</t>
+          <t>Contract Pharma</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNdFRaMlZqLUI5dFVneHFLSS13ZHlySnFyT3FCZjZ4UXhaaGdZT1dQMzIyak5kYVhZS2hmRkNxZVdsVjNJZ09MSmJaTkxhRkw0Ny1TU0h4QXI2M0tCRFpDRHBseWRGeE43ZFVFVmhycERMOGYwNF96Wk50dkRNb1AwQkxLb25xVlFpTjkzSEsxYU9jY25FMGtPNVVKYi02LWIwOFlqT2JqVHlDQW9IWmRrOUFqX2FkOEFiaUpMdTFNUWo0Yko1SGV6aC1lR0I?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxOQmdTaTVpaW5IcVc3R3JEREl2VlVuTFlkRC1Ua3M0cjVtVElkcjhRQ3VrUDVxWkNVYnFDdzg3clZERGVaajRiQ3UxMm52MjQ5QmFzb1RtLVBHVld5c2xNVl9qakR1NnRxQjNHS09IRGszNmZtTVJyR2pCSlhTR3g0QzZlZHdMQ0dpcHJtcVZEVQ?oc=5</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>08-05-2026 07:03 UTC</t>
+          <t>08-05-2026 09:06 UTC</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Biocon sees strong biosimilars momentum, expects merger synergies to aid margins: CEO Shreehas Tambe</t>
+          <t>Samsung Galaxy A57 Review | Dependable everyday performance at sub-flagship price</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>CNBC TV18</t>
+          <t>The Hindu</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNQWNjT1pKMGdobW5udlRONHQ3X3VPa21kQnQ2NXNzYk1jR3hPeXozU2s1QmxRMzZOeVVCN1l3clgwTmlEY2R1RkRTQkRQa3gyYl8xMDRYTXBYOU1VY1M0YTd0akl5U2FKMHNYNjl3WFhIeG5WTUpMOWRzSGpSbDRHSWpmb2hzZlpiMjNaQXpVY05KSGFiYkwyU3I4ZmRhLTNCM1BmZkJJcXZJUE5PZ0J6eERvQdIBuAFBVV95cUxQNHZGTGJDeTFFRmo2dG1Ia3F2Q1N0Z1ktTkRKZVM1V2R3aFlFZmdUNEVneElwZEtUVTZUOHpiRVNwVm9CZmU3RzRhaWpOOVphMjJyakRjSE1WNkRqaC12Q2p5cWJ6MzhKSWx6MU9rWXpYamFZcFJON0U3YXhCLXoyY2xnUGEwQlRSN2RleXJkQk9lZTZZdURlbnQ2aUVOWGlpUWNwOWk3Nkszb0dLaHB4NklUUDB1eTBm?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxNUi1Demo2bnllaldTM2Ytc2pMdUlwY1pJNlNscmthR1k5enlIOFk3UU1ubUZUN0xQREtyTFJwZUhnb1V1YXZWRmRjbUR4T0Y0dl9GdnY2dWZsYnN5OXc1eUwyblV6dGxKRVA5d2NhTmNVdkMwckFDTUEyUDRyM2dVcVpKWlk5bWRJeEVmUXNjV282cmlmc3k4SHU2YmRsaS03ajAxNVVmV2lmTmQ0LVFfYm90cmFfb05fVkdGRU04TlMzZXNkeU1rT2JQR09vTTE4bXFfVXhRQ2tneXlhOUNoTmQycmwyY2c?oc=5</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>08-05-2026 10:50 UTC</t>
+          <t>09-05-2026 02:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Biocon Q4 FY26: Profit Recovery Masks Persistent Margin Weakness</t>
+          <t>Samsung One UI 9.0: Everything you need to know</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Markets Mojo</t>
+          <t>SamMobile</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQcGNuck1qeWdNTlJmZGtLNTVtQUJKV2pnaGd1bGZVQnNmeGtwWklyLXhCTWhKNlVVNVlpQlJDZy1EVDFNVnVSaDFfY3NLdlFJVG1Gb3ZuOWVtUnVmY2YtSy1UNmE2Zkk5RHRPaEJBYnRpdnJ6MGI5LXd4Uy1LMkNvMjBUbTk2M0dFQks1NXlXYUNYQkpCdFJqMlVGZG92TER6YVJZM21FVC1FcEswNmcyd2dPMndzTmFwVGtuRg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE41VDROWW1SaVZpZTlKMjhMQ0FQRmJjWmIycGxlelhRSzJlanA2T0xPenlUaTBlYjVXN2hIUjRMRlY0X1VfWDlPN21EUW1FRHFuaDI5Njd5bGZhaXZWSXhFX05DWjBVa1ZNS0Q3aWxsT1pDR3JXa2c?oc=5</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>08-05-2026 13:58 UTC</t>
+          <t>08-05-2026 19:12 UTC</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>As Kiran Mazumdar-Shaw plans succession, Biocon bets on biosimilars and obesity drugs for next growth wave</t>
+          <t>Samsung launches fifth edition of Solve for Tomorrow, raises winning grants to ₹2 crore | Business News</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Business Today</t>
+          <t>Hindustan Times</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxQVjNPcE1hTy1nWTZhQWJXc3RXaVNjSDZuTDVzOEwtLUFkU0lZNnFWYXNRUWhHTGFVenNoSzlsTVRuSVd4RU94Ykt6T0xzY3JTdUVIcTFkc29uRVlyUlc3RkhXWEwyenZkaU8tVXNYQV9nRXFlRWpHb1NQRjFUVEFsaTBoTko3YzItWU9keTFqRWZ2NzZSMTE4eklGWG9PLTZORUw0R0dlaDV0V0pUR1NfZ25kbE1KbjVfREdmNm1zOE1LTWRIRXNaUE5tYVIxaXpIWjB5TnFqSTRrYWExYXZvYnB0Wi0wTXFqZ25YNjhEeWxRTDJyMDJVVWsxNlI0RlFMUjloY3dn0gGLAkFVX3lxTE4zVUgzX29EOGxfTGZzOURyU3ZFb19Fa1htVzk3X2JaT1BsYVVXaUp5NjRpbmtnVkN3NVM0bDRiVnl2RWRySHRDV2dBMDl5ZHcyNVptTVZpX2JUQ01rYUl3dnB2RjlHYlZqTlctaEo5RDNta25RZG9zaG9ncFpOTkVTNGtqOXl3WGJ1VjNjQ2pPLXN0ZFdJUVFrYUc4Mk9iWENzejBhWnY3UXZOYmRBcG1PWVVDWDNabDZiMU9hVUdxcWpaVUdDcFlCUWdKZ08xYkZjU0U1NTQ1TTNDcDU5WGZUTjlPQV9ZRHkyc1JNMVQ4WkVrNkh0NjlLb1RaX3E4dFBiWXN1V1hHWkVpRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxQQTl1aXUzX2lZWDBCdFJBTl9QQS1SNVp6bHFzSWxuX245RU5rWTk3Y1JiTHhXYVNFQzVVYnNVZjdzVkZQRHlGQ2h2ckhteHZPblBaY3ZzeHItSVdrRGJfNldfTVNqSU4wUHhTZHBacW93TXB6c3NVdmhGSEZNOFBGdnpLZFc3NlNHeEtVbExNTDl1N3I3djBnVy1rRUJuOFN0Wk42Y05WdHRmeVJrLU5UUXd4VzJNMHNiVlFtTU9mZ3lzNXRWT2xvWTNvWHNnZzY1NEdsN0tybUhpdWFqR3Nv0gHkAUFVX3lxTE9nVU9pRm9IdUVGMXJ4M0xrdnBvczVsdGRmVGpUSlE3YWpmM1NMSHZ4OWx0dkI2WGdQRktBV2x3NTRuQzFfa2lXN1dGUmNINlhTM0xrNW4yMFJPS0NNYnFPenVFTGgwUW9NTFZweEZmcUl1ejVRSE51V0tJbmotNXFRRy04YTQ2Yk1aZ09HcmRLbkIyNzlBTnRCZjN6bEN1dThiRUE4S2dkVEhCNTRmZ1hUeHE4dTFVX2trQ3FTaEdEYjY0SXJUd1BUc25waVloUWMtMUxKc3JfMDBYUzNzXzljWGdwbA?oc=5</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>08-05-2026 11:04 UTC</t>
+          <t>09-05-2026 07:29 UTC</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Biocon succession plan: ‘Claire has done an outstanding job', 'she is a worthy successor,’ says Kiran Mazumdar</t>
+          <t>Samsung Galaxy S25 Ultra 5G price drops below Rs 95,000 in Amazon Great Summer Sale</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>ET Now</t>
+          <t>Moneycontrol.com</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxPWXJYcVFhMzMxanFHSjBKbkhFWnZCcWtIRlIwYXNlenVVWXQ5WUNaZXoyMEN1QTdGRWhXaGF0ZFpsSUcwa015Um51WTNhQmowUUJNeVA2Z2YyLU5LaTJsdDBtS2VWR3pLRTdyajdKbkJzOUlZSG8wUVlDWnQ2dHlGRzJZNWQyNXJDWmdVaXpMcVZsSm5JSjhQeUN4WW1kQV9pRmRVY3lFZkpwZDlxQXctbTZqRVBJb0Z1Qjk2TTBrOVhfd3lISlpjaDA0MEZfTDUxRHhXeGZ0NlpsdDUtd0MybjZOSHcxbzE5ZjVmWjVR0gHzAUFVX3lxTE51QlhNeWctTHpsNm41UHVTTGZheFk1Q0cyaElpR3ZYcGlLVUhWelZ6RDF6NXdDcTI0VU1jRnhpM1Y5VVRKbzFDWnRTNUlScW83MkJTZVAyaWFWUTFGRUpjejN3RkFnMk9FMGpvRU1ZWFdTUFNTZ3RxM0hKZTg3VkxKWGhOSnRYc2dmRDl3R3pncy1hb0VZR3NkY2l4WmN6WndsUU9leWNFSVJCSEd1bjV2VjhtUWhOTWdUUFdRWmp3TlBmcC04UU9DOFVYcUlMcjBQMHBEVnNnV0puQUROaGMtcTVYOEVNMUxBbW1oSF92RFFPcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxPd1Y5cVBqYnFkUUd1d3hhNjFWZDVWLU9XWnZJZXU5NVNtWWlVWXVwX3NRM0xScDd1RmZHMDNJX21LSFB3VEpvQ3RzalprRXNGNmdpeFRLYjhVMXJDVGFLUloxM0wtT3F2V0RkRk8wZkY5b2VLV1VFTHphWWFaQlNMS05zdnJsZ3J5d3g2ZGRGS3lxdnVFRDZ1Sm9QUFNBUGI0cTFsQktaemxoRVlGOFBHTDZCOUF6d1VmUHVENDRsWWNVYzMtMjVLazN3NUp5MFdJTHVyUVcxU2ZoRmxaTlHSAeMBQVVfeXFMTmlJRTFIZGhzTllVWkRfUHJuMW9GejVpMVlFZDU5emNxLV9zeGJ3NDFZMWw4TzhZWUx6aUZzZUtvbXAyTjFJVk1xYjBLOUxKVGhDdjI1dWE4czFULVl3WW91Tng5S3FjaGNHaVpwQmFpLVVxVEN5eTBhbjB6MWtoV2c0eHRqT205M285bXdYQUh2a2d0ZDc5X2lTY1IzTm5adE9mWExpZldLSW8wN19nQVMzV1oyZGV6SWx6b1NBVmZ3aGdDZWNINEJwaU56NnJGX1NSMy14UTZsRDVJcUk5R2hZd28?oc=5</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>08-05-2026 10:26 UTC</t>
+          <t>09-05-2026 06:09 UTC</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Why Biocon Shares Climbed Even After A Sharp Fall In Q4 Profit</t>
+          <t>Samsung Electronics Announces New Leadership at the Visual Display Business</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>outlookbusiness.com</t>
+          <t>samsung.com</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOeHpyenVNTk15eHp5aEw3S3pfWUpLQUNhM093YUtnU3A0UEJmUk5ZR3FVOHN2ekZkSFlscVFVNnJGX0FQeUJJbks1RjVUWk5EZXJTY3Q5d0pUTlRLVERaTDJUWnVBQkNMQmRYNGRNM1lFc2ZHM21OT3RNMHcyUXE1X0x1WU9oUmI0eWN2eXpHRjRpSlM3Zjc4V0xoRnJpcERtS0NSWNIBsgFBVV95cUxPMzdfNW0wMHA2LXpqMzFwX3VkTlhsVW9vVUVCcnNFWE15Z2k0RUVVUFFsOExyZUtBNGVreVVlRTNCZmRwZVl0b3NFdTc3UG1KUzlpQ2xtRi1pdHg4eGNkY0lZTnR1M1hlTDNGUGxTOWlvUk1UeWgzdUdweTVLTkFnNWd4eEI2YVd6UU1QekFaU2hkbHBIZHZMOEp4b1dBRzhGSEhWTzJERkx5M1lEN2hGUy13?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNUnNYd1lueDk5RFc5WlBWOUpTcmpvblFjVnFDT1ZMWGFTeWY4QldaUDYyY3dsQkJjY1RvZnBkbHBYbWRvS3ZVa2EwanlzQUt0blJSQTBES3VuaTlkZXk3RWdCbVhJcVotZ3Z3a0F1WlNOZnVRdEJrYTNoNi1KRURjQmU2S3BuMkxUT2Fhelp5U1BTSFlvb0dFTG1SeUpuSDRlNzFieDRn?oc=5</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>08-05-2026 07:37 UTC</t>
+          <t>08-05-2026 22:52 UTC</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Biocon Q4: Net profit slumps 57% to Rs 198 crore amid higher costs in FY26.</t>
+          <t>Compare Samsung Z560 vs. Nokia N71</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Deccan Herald</t>
+          <t>GSMArena.com</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQUmxtM3ZjRlJpMzBNM2tRcThyWHZfTm5VLXNsSTVPd2IxUnFMZzBwNHozWlZ2dnM5R2hMbVI2WWRRV1NoZXlUdVJyUjNOR2RjODN0RXJyb05JT2JSZURCNnFEbElCSHdXZDRiSC10T3VEUFZ4UVBOdmhiYjYzamd5V3E4NVhqcGRFT19xbGlTRUtickdOZ0RWNXNRZmNnUm1NS01Pdg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE9zOGRqS3dCWFhVVGI2amkzX0pXRmVyUzI2TWtLUl9uYmFKLWptN1RhYnUwS3MwQk54ZlRnLWE5U0ZraDlZY3pYMWduWW1kNTc3OGVDM3o0dFE5Wm1abjdyUTJZSHZjYmtNbzh0bnJpVGFfNEk?oc=5</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>08-05-2026 04:31 UTC</t>
+          <t>09-05-2026 05:46 UTC</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Biocon Shares Rally Despite Net Profit Falling Over 60% In Q4 Earnings — Here's Why</t>
+          <t>Galaxy Z Flip 8 leaks show a wider, lighter flip phone</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>NDTV Profit</t>
+          <t>Mashable</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPR0E5SURHMWVnNktWb3YzTE5FLTNfTy02cXRySllQV2NidmdrN0E3RVVVUEVRclI1RVJWd2dNUmtUQjMzV2ZWX1Q2d25TWlRSdnQ4SjFvMnNUczNmaDczNHN2SlVEbEZQWWY3eTZnckFVa2JnOG56bU1mdmNwNDREUWJtLThSQWhXZE1kWHVwY0xjNENBZkFwZElvalRMdUprOEZxYzZ0Q3YxMm9sQ3fSAbYBQVVfeXFMTUJCVWk2NjhQR3hVNDQ5bFhfYkJBWU43eGgzU0QyZ2Fkem5nSVZSTElmQWlWbkxoanRpaU5ZcEtfWlJINUFaaXVtbjgyc3JoUF92T1pPMldrRE00RWlkaWJKcjhwWkJuTHJ4UFVvQVFtR296aWMwY255VnR4N0EwSE5GTmR2ZDA0QklKeVdqaFhoNndhaF9JeXdCRDFXZFBoOURKLWxmSHJxejlpRWFhMXRfZXdNYVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxQSDItaTNPWmhLMmUwaENESHhpX3hxLXpWLXJJQ2FtNGZEdnBJNURyYXkxS0tsRG9vejUwTXgzVWxEWGFucGtlUnNUR2pTZGRCY0pEeU1ZU0VMU3F3SVd1ejVXRXFEWk1YenZmVVJ0SDV2aVdDYk9iVnhPTTBjWkxRbWR2RQ?oc=5</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>08-05-2026 04:29 UTC</t>
+          <t>08-05-2026 23:25 UTC</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Biocon Q4FY26 &amp; FY26 Results: Revenue Up 10% YoY; EBITDA Margin at 22.59%</t>
+          <t>Amazon Great Summer Sale Continues: Best AC Deals From LG, Samsung And More Brands</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>News18</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxQUDdSRFlsM3FJM3hrZ29QOWVZc093YVRoVUJoZjlGejRKS2NyN3dXaFJ2cXhUR3RHLUNkcG15WEZ0WkUtM3VpTWNONzdyczcydnR2Smt0Z1JfZFVRbzNpZGxrWlhEcWs1dklzRHg1aVdmdmllREFxYVJJSjlMUE9CU1dPT1BmZHFTQ1VMZ2hJX0w4T2l1ODF0MFdqMUlIaFNHSGRIb2NvU0wyemJhenJnTnVCVUlmQ1k1dmpENUVraWhEYU1ZZVMtdV9Za3BVXzRmWk83a3VSTVQxYjcwdDZGZFM2bjZPWU94cjRRVG93ME9ncTZEZ0R6SHFQV2MyNjFxUVZFa0RZaFA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxOcnVXeHJZcktXMi1ISUVBWEg1ekdpNUIxQkdsbnJSZ3pRbTBvSlpSUkdYS1gxcWFmVGdHV2UyZ0RLLXZNM0pIYmt5VTBOUDF1bVUxdVlJYk83ZFoyWHJqdXBNLVhFVnduU1pUbDNOUGtTWFF0dHhjOXkySmFVZ29UZS1zdW9QNU9ydVROOXhQM0RYTGpQNngyN1FRdHRMeFRtYTUtU2U2dUhRRjNCWFpfUUhDcDYxVkxZb0VGTXlpTTdpT1RBMFFDUk9aOFUwLTNPbVNQd3UyZmw1d3gtSzlpTllQYWY3RUnSAecBQVVfeXFMTnJ1V3hyWXJLVzItSElFQVhINXpHaTVCMUJHbG5yUmd6UW0wb0paUlJHWEtYMXFhZlRnR1dlMmdESy12TTNKSGJreVUwTlAxdW1VMXVZSWJPN2RaMlhyanVwTS1YRVZ3blNaVGwzTlBrU1hRdHR4Yzl5MkphVWdvVGUtc3VvUDVPcnVUTjl4UDNEWExqUDZ4MjdRUXR0THhUbWE1LVNlNnVIUUYzQlhaX1FIQ3A2MVZMWW9FRk15aU03aU9UQTBRQ1JPWjhVMC0zT21TUHd1MmZsNXd4LUs5aU5ZUGFmN0VJ?oc=5</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>08-05-2026 08:48 UTC</t>
+          <t>09-05-2026 05:45 UTC</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Biocon Q4 net profit falls 63% to Rs 126 crore as one-off costs weigh on earnings</t>
+          <t>Samsung Galaxy A57 picks up a fresh firmware update</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Moneycontrol.com</t>
+          <t>Sammy Fans</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxPczdBdEVoZ0pRbktPeFdFU1I3aUpMYTZXQm1UcDV4cXhBY0ZDdlNQb2tmQkFkTEZNTUVZUm95VG9aQVlYTzNVdXVnNFdrNjk1UjNMR0M5TFQydGhHNVh4U1E2VmZlcjFYZmZxc2xBZUhQUDhZUTE0WFF1MjdOdDFkRHlDTzlxRnRaTkhpWjE2VzFicGc5YTZ0SG9LcnljUEpzamZmSmNRV2Q5bEdJUEx4TENCZUdHajZWbl9oT3ZYNlIzeHpYOXBaOEQtajQtaEMxLXluMXB30gHbAUFVX3lxTE1DUjBBMThZTTJBb1pEMnhNemh2dlJIWnd2VkNkVmdOWkRWNHFQbmtRQVNNbVNGdmFWaU5Rc3BabFpUdWE0a1RmT3VlUlpGbF9RaVVtZG1aV2lIQXBMZnF6T2ZubGJSZjgxTVJVZnhuU25UckdvMGpZajEtUmZKbUxHeHRTVXpYcG1nS0xZdE9qNTRfME5WeXdsVmtmcFJkN2dTaXFqSmxEclR2cHFveFVSbUV6c3ZkYUkxM01TQTMtazV2bElfVXJHUGpCWjEtZk81R3VJWmhyUUJVUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNellqSUpmUUY2OW1vRXdRVzZBMExJbHYwblZ6ODlvM05KMTNtN21zT3hBTzdTLVVBUU9xdFp2eXF0dG1oQjQ4TEFLZmtMc2QweEpPaEN4eEJ2ZUd3ejV1TEYzZ2RibVk2S1VqRDlZb3hoNUpLaHQ2SWR3bG5xTVhDc0EwNGJsN1VlMlpDcnFNR2xEbXfSAZgBQVVfeXFMTlBLeGNaamVtQUdUZUFrSURKZkZ5MDZLOGhyWnhwMjlHalh2bXFET3JMUVJXZXRzcmlNV0szV0phUGZfSG5QOE1UTjVMZ21NZnBRSUs1d0xCWEVjeDRzeWZQZGk0VnkxOWtjVkk4RVNaRVc3NkE5QkhRT1RpUXRqT0Y5OXRXT094RXp5RlZQdlQxQ2hTeV9vdGY?oc=5</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>08-05-2026 04:09 UTC</t>
+          <t>09-05-2026 03:42 UTC</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Biocon Profit Falls 63% Despite Biosimilar Gains; Leadership Transition Underway</t>
+          <t>Samsung Display unveils brighter EL-QD (NanoLED) prototypes</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Whalesbook</t>
+          <t>FlatpanelsHD</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_AFBVV95cUxQWUVWU0R6QzRGS01QVDVaYW1FRlRsSkhkSm1EV1d1SENFQjJGZVJCd0JKbFg1UV9nUDR3SnA2cGhMQ1hLaS1KQjNfN3MtZm1HQjFQZ3czR3dLdy1SZTY1eTdPUm9NY2xVa3d2ZWhZb1BZX1FPZmd5c29oRGlib1k2RXg3Q1R4V2M4UjU5bTJmS2JQYWZzVmFoZTN6QVF2Y1pKQ1Y0TTVmOXVFd0hvNElrX2IwdzFGc1dHbkRnRkVBb0xrRXlLTUwtM2RZd0NTNWVLVS1YZW45ZzRaSE55N1JfZHVhZUhvWV9hbm1tazlFc1hvbktCdzF1ZDBWSXA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE9ZX2NGcDlrXzM0SkNXMVR4VEtOWmhfcGdDM21zV3JnTDFmQVRVWGhETXZxVVR2N2owVWtmNE1GSWZ5R1gtZV9zd2p3bng3Nnd1dUh1ZWQxU3hqbjJfMURRcXl1NW1sSzB2ZllDSTRkeHhNUUxhY0swaW13?oc=5</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>08-05-2026 02:29 UTC</t>
+          <t>08-05-2026 20:16 UTC</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Broad-Based Technical Strength Lifts Aurobindo Pharma Ltd. to 52-Week High of Rs 1504</t>
+          <t>This Samsung watch may know you’ll faint before you do. Know all details</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Markets Mojo</t>
+          <t>Indiablooms</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxORGNMOGZNdkNzYVZMcFhWX2NTZmM5TXFrcWZpd2NwbXRhZEFSMHlGYVZiRFpoTWxKWHN2OUZTTzEtZE11TEF1aUxEU1VqcnVRd184NE43eGw1MlNPNERXUjFMRU5DMkNKRWRoZVFwdmczek1JTXVvUnN0NzBYNldHUDdMdzFhVW5heXQ5c2JmZWpVY3BURzQ2OGFPUE0wSWdyY1NMTDV6UEY4YWpwdFI0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOZWhtTkFUWkNyaTh3T2JRWUpReDZJWk5NcEhCNGZyQUkydjZUUkpJbl93TklRNVZvZGQzWllrUkFfcFRmUU1hb2o5Z1AyYUh3ZHhmZ2lOUE1nam5maWNRSzZUaTJiSThJTndWVDZ1dG5EV0w1NVNJcWFMWWFpT2JueWpvYzBYdGlpY09DYVRNaDFBY1p0YnVyUG5uY2F3X0swVy1ITXlnWDZoODdUT0VXZw?oc=5</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>08-05-2026 05:28 UTC</t>
+          <t>09-05-2026 03:46 UTC</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Rs 1,00,000 crore Buyback rush: Cash-rich IT, pharma set to lead – Wipro, Aurobindo, TCS in focus</t>
+          <t>Samsung warns memory shortage will be worse next year</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>financialexpress.com</t>
+          <t>Mashable</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxQdHR5QmRZUVpZZzJNY04wdXVPTmpuUHp4RFFUaXhrN0thODlsNkxhYkxzTXdIV0diYnlHZHljZjU4X3E0WFRSQ2xBeVVpSW9pcGdFdkZTWkUyNV93dE82X1UtLVRsZTFIZE5ZandSa0VOZE5hdjZhWnJ2X3cyU3NuR2NmdVZLb29tTWhfYXZtRjdqU3dCQW1MMW5iOHdzWXJJVXZ5S2dPOGRReTROamFBZUszNVhuajlSU0Y3QTdmQzJISHMwNjN4SUlJMG50QWlpS2dJb9IB2wFBVV95cUxNUjZhaVNFS0Frb1JManRVdXdPelAtcXpjQmxacnBKQUJNQUlqTTA2UVJ4T014UjN6NG5pUzU3QmlQbm5PWUZBazNoQ2lqUUtpNFFaZ1psU3FKdm9KTzg1d2NpNDktaGFRdU1VU0lHUWk2a2JVb2hLX3h2eUNfWE02MW1mZDVLQ21aNW9lSVA2QkF5S3FwemdzLUMxUjYyM3FUNjMwbHVhcV9pQ21zQTNQeUhaSFBRNlBFeUpTUkN4ZWo3NGt0TUVNbl9FMkEtaGhuejVORkk1eUhMa1U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE90WmJKZVlramVwRm5ZWVVwMk4xOWpneG9nby1Ja016aFNIYmNpeWlKUWQ2TXJJTDlzMUJOcE1qblFaOUVDX29kQlQ3QzF1NG52RmNjNjB5SFpVWG9wQVhRNHpPSnpjZkpEOEZiZmY4a1FEcjBaWV9hVkFn?oc=5</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>08-05-2026 08:16 UTC</t>
+          <t>08-05-2026 15:16 UTC</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Budget 2026 Ka Kamaal: India Mein Share Buyback Ka Trend Chhaaya, IT aur Pharma Sabse Aage!</t>
+          <t>Celltrion Inc stock (KR7068270008): Buyback wraps up as Q1 profit soars on high-margin drugs</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Whalesbook</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxOYkZEYjdKUEc1X2kxLTY2azYwREFzUU4zYWE3YVk2eGFxTlEzWTRoa0ZXNkxuVi0zWmVsaFRZSzR5OGh0WVRnZFdsWnNGMTA5dXFyZ2VkSjV5cFdBNDduNVptM0FIUXpWZjlicEd0NER3YkczYVZkLVA2dWI5WVdReWRSR3k4S1hON19vTzhUUUU1NUUwZGxNc0dlYmRlNURneGxTSWlKTUNaZ2pxYXlIZ2JLUFY0bzF6elBJYmZuYVVMYWpiLVVCTFl4MThvOFNiYkQxV0VBYUp3bGhpRUVOTEtNendqQ3B5OWxGMnNB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQRDNjQ2pBOWE2SGVwTHlLcjlKclYyUDRrNGRlbXdpdExOelIxdWNZY1RpVUMxMGFpcFpVS2xYSXJIcWUydmlMZG0zVUg5RHRsZld3dng0THgyZk02OC1reDRwSFd3QTVzdTdIRlloUTFhMmhwZUY2dnFGbmZqaVNxaFg0dVdrNUhvMzhRRDRaYWVZRHkyUEUtMWdSU0RXY2kwa3lHTGVVb2pXU1liYWZPNExMd0MxZzFSdFR5YjAzc05qYzFnQmhFLS1n?oc=5</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>08-05-2026 08:50 UTC</t>
+          <t>09-05-2026 07:21 UTC</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Prestige Biopharma</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Torrent Pharma Captures 38% Share in India’s Generic Weight-Loss Drug Market</t>
+          <t>OneSource Pharma Stock: GLP-1 Ka Gold Rush Ya Valuation Ka Trap?</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>outlookbusiness.com</t>
+          <t>Whalesbook</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOdlplMWpYZGJLWmhnOWJqczRQbTFoY09Qb2lWWEJfU0Q3b3JBbGhGM054ZXFjNGFfdkdZM052ZTJ4bXJrWHZDU2lzeVZUNFRiTlpkc09YVEM5eEtKd3JGX1FELTdJNGIzWjRra2FXY1lhb0FJODNISGF2MFdjTnMtbU9EU3lJc2RVZlRPVGtvLW9VZHfSAaABQVVfeXFMT0FxemNsdi1rNE9MVzAxOUdaV01tZENuV25oZzdTSUtsNzRjdnlrN0ZnN0gxazIxb3ItUWdQaGhFME5CX0lKWERWNDkxV1BkWmF4WFd5MnhtUEtoSVljTlBNRlJsdEpwczdQYmVKQXRQZTllZ1FxaGNkVmNfcU5GLW9BZ1NXUHZWZXJnVmE2Q0pJcjV5eEJSQzVpVDNBcDRZeg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxPc3BoaWg4SUtEbXlyLVhGUkdiMkVNX0JfblJyYS0xT1FsZjZ0cHlLUmhzbURTYmJUUHJpQ3BNRkF1WllOLUQ0QnV6QllzcUJVbjBaN0szTzBkcWtzU0ZuY0ZLX0RlYlJJT1BGMDM3akd6cGpqbTJVWmhiNkhlOWJfbU9HSnhNQ25LRFQ3ZHBFX2lwekIyU1QySk9qc1ZjeUlTV2lSbHRRcml4QktIVUt5bGtyWU5DU2JBTVljNzhxV1VXTEg0QjVENE9BeU5INk94bEhfMTdoTmdxR1ox?oc=5</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>08-05-2026 07:58 UTC</t>
+          <t>09-05-2026 02:29 UTC</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Prestige Biopharma</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>India announces record $20.5 billion investment in US at SelectUSA 2026</t>
+          <t>OneSource Specialty Pharma: GLP-1 Gold Rush or Valuation Trap?</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>The American Bazaar</t>
+          <t>Whalesbook</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOR1VaS1VaMHVqVkNQbkhkRTVyN3B0LThfRXZyZUNKbXBNQ085dlhZbHVQanJRU04wVzRWWVE0ejhFOHlLTUZ3OVFSSm40cHRhdmp2UDFlRVV5MldFVVIxTk1fVUZRNlN5N1ZnSk8zdXRDXzBOeTMtdkRYdEdGaW43UE1sLXRKWnRWV2F3bndJa2FwWXpwYTFHd3Z6bnN6a2U0QkFrY1MtRE1SUUtrSVgyLTRJZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxPTURwNmY2djF5MS1rSEFTUHdHazVRcm01Sm9ud0J4OXc1Q1FNdDlJVDI5eGE2dGwza09vcFE3cld4U3pCdV9oWGlrVW44TEtJbDYySG9hTU1VRzBsb0ZoQXU2encwRWtTUURHNkFXZkhicFQ3dlhSR1F2ZHo2NzNIS3plUThBRFl0REpfdFBLbWFSbWhZMVRuOFlFZFBwSG9TZ3RuQTVqZ2dmXzVmaWFwTy02UXZNVHFGenFqOGFFemRhRld1azFTRm50VzdCOWp2VUk5Q1pFRURWOWM?oc=5</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>08-05-2026 10:45 UTC</t>
+          <t>09-05-2026 02:29 UTC</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Biocon Q4 result: Profit down 56.8% at ₹198.6 cr; revenue at ₹4,516.6 cr</t>
+          <t>Daiichi Sankyo takes $610M hit tied to ADC manufacturing losses</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>Fierce Pharma</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxOSlpaZkRhS0ZaRjE3NzZ5M210UEFidFFkcXQ3VUFDQXRyVEJZeU5IUEtUZ0w1Y3Z3RFRzVkJoWjdwYmZLZXFRMDlpMHhYTkl1RkZHV1VUS2F4SndnckE3Vl9ReDRYRUtiQnJsVGNPLWpyYlI2bzMwQnB1c2lTTVFRRkNxc0VHNHRSX0xEWWNNYXhvMXNWLVY3NVgzZWFoZC0xUnNYMWcyWGpUME9wa185Tm5oMUJjY2pqVGRkNU9SbUVsY2l5Z2kxOFdwYlRZLVdvWEHSAdcBQVVfeXFMTUc2ejFLdUNmZzUzcXd4OVNnanNUR1BhdWlrd2p0cGZkZzVhYkhETnc0eTB1MTFpeERDOFZoRUFyNXhrbDNxbUZNcXlFTFp5WExUbmZDdHd6WHdXWF9jcFFRNG0zaWZaUS1fNlBRVjRkZVRBbXJzOGJNYlNhN1NZZldkeThVRnJ1c1hMSjVGU1k4T01NSzVFVjJaWmJGak9DNk5nMGZTOXltSUs3aFNkM3dPWmhhZHBlQjc2LUEzRlhBRTdzTUxjMmx2aExBWFNVeURZME1pekk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPdGY5SFBfV1hyN0R1TUxMdkp3a3RJS1VXM1Vzal94YldVMUQ0SzZrdzVzZ21JODdpRnBjODY0OXlSLS05TzlkS3A5VVk1MFp6SW1NU2VzdGhGcDJpSUNiNUQ4SUluT0JfMUdKQUttRzhQRXVOeWZDWVEyN09UTDh0UkpxbWtOWGd3UzA3VjNMekZCNFpQSlpPR0VGV2I0NEpkSTJmaDdaRQ?oc=5</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>08-05-2026 04:09 UTC</t>
+          <t>08-05-2026 14:47 UTC</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>India Tax Law Shift Sparks Buyback Boom: IT, Pharma Lead Repurchases</t>
+          <t>Daiichi Sankyo posts 'extraordinary loss' of nearly $1B after overestimating need for ADC capacity</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Whalesbook</t>
+          <t>Endpoints News</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxPdUZjYTM0cVpNRzFlNDB4dnU5bjVLRjFCNFlVMEdCalZGNnphU0xMVFpCLVE2RUhzSDdjOEVLV19PSGdEVHpYMjNPOEVtbWUzY2oxUHNzWHJiNUZ4Rjk2SENTQmVGSl9XN3NuZ0FYNmUwNnoxQ205NFV1UU1tNEhDU1R2YXlNSFIzZkd0Qk5WUjJXUEVRVmZUbzdEQmJoemZhMlpFWFNRMW1HTDZaYWF6dzZVTGpGR1pkbGtwRkNXMks1UkFUcW8zOGN0b2JYUXZfcVJIeXliUmZIS0VYNnJ4QnhickRuZGdKYm9FZA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxPZFFOZzJTRUhKZlZ3b0d4c1RvdHpiWmV2YlN4R1ZIbkVBMWdpeHBwaFRtdXVpZzRxa2taSERheDdkcWxxWll6YkxOazhUeGFBRmtxNnYtOFMwRmFRY1pfR3BrRlNPWS0tWmtFM1ZZYlV3cXlJa3ktN1NEVnhkSmpsUzZ3?oc=5</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>08-05-2026 08:50 UTC</t>
+          <t>08-05-2026 17:16 UTC</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Lupin Q4 Profit ₹1468 Cr, FY26 Revenue Climbs 23% on Acquisitions</t>
+          <t>Daiichi's ADC miscalculation leads to compensation of over $480M to CMOs</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Whalesbook</t>
+          <t>FirstWord Pharma</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAJBVV95cUxPUVpkN2l4dGpNZkpZQjc1b3lxYVZyRXFNRFZJSjdJLS1nMFZEbk9SM0puU3NzamtzTE42TG9aUlZESjNlRm5DWi1saE9hR1V2akRHanlBVTRnMG9SdFpENFNlaURERGQxLVdpaWtLa0JiRFdzdjRiSVg1bXVSNzc3cjhWTEtIb19hcC1QUEZkOE5fcjAtUG1NUlc1elVPNUlJQ3hIUEpaUUx4M2pwSkQ1aWFFSHp6TC10ODBmY0ZJWXhHOXlqVDhkMzdYUXdxcTNjdFROTlZINWJKYVdINUZ1XzA2SEh1Rk9ZaU04QjA3NDlEcGhyZUczMUVhYjZEZUZjbUE0bg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTE9wWmtjeTRjeFIzbDlqeUhRYmpEcnFMRWRxNmZjOG40T01SVEUwVFRLeURlUjFORGZOdjM1emw0NEpBeHBoREpuZVhoYTZFMzZwTmxJ?oc=5</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>07-05-2026 16:36 UTC</t>
+          <t>08-05-2026 15:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Zydus Biotech</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Zydus Ahmedabad Biologics Plant Under USFDA Lens, Inspection Closes with 7 Observations</t>
+          <t>Daiichi Sankyo – Cleanroom fit-out for the fill &amp; finish area</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Medical Dialogues</t>
+          <t>Cleanroom Technology</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxNUDBxSVFpdklXTm5xQzEyUkFncXlEeDRzWVQyOXVjTzNDZWpTQTdiXzhOM053dzlwQVYtdjNVMzM5V2dVUDZESVZZQTFvb2kyZ0E5aVJ2VFQxOWYtcTZEZjk5RjdFOXFUZ2gtVG1GZkNmSUxqSTZjU3FzVjZzdHhTb3JVVks0SDhYTG1LaWlud29ibm5BYW51bVZkZ1J5dXdRRDI1VUNUV3JlUU5EdlZIdzZUeEszQ1YzeGZaSjZ2NUp1NHJDY1I2SGJMRjg5b05FRkRObFdNd1E5UdIB3wFBVV95cUxQdWxWa0UtdXNtZHJ1X1B3aEtzZUlOYlM4NTBmVFg1Y3M1dExZLW1DcDhYei1CWTNwZVYwbkJyLThudUxaZmEzenhLZ09SQkVBdE1kZW5LdXBITmk5QnF0YmE1Q2ZuZVI0T01HWVkzMElfaFBfZEpNQ3lFWnNCUXVEZ0hSNW9XNWQ1dE5rYjJQWHNOemNuaE1zeU1oNXViR0pDQWhUSlJHOU5ncjJnM2dsWWZaR0pnMmV2cXJFeG9ZaU5ET1owSDhZTTQtcFA4cnJPMUExdkRjY2M0ZXBNb2tr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxPQndjUGlfVVY2QWw0eWFrSUFEUW5ReGw3SlVIUFlMUnFHRGl2bjQxVVhnX0ttN1VQT0dIZkZHOVlVWGY5Sm1aSjVObzJiSEhkOWhnRjZXUFJ5OThKQUlWODBOSS1rZllEeHlzbzRnMXNobHJfTXk4ajRiQ0hpOEtHMFR3?oc=5</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>07-05-2026 17:37 UTC</t>
+          <t>08-05-2026 11:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Zydus Biotech</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Zydus Lifesciences Board Meeting Scheduled for May 19, 2026 to Consider Q4FY26 Results and Final Dividend</t>
+          <t>Manufacturing hangover drives Daiichi Sankyo into the red</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>pharmaphorum</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxOaXNBTm50RkIyTHVsS0UyajVqdkVMMkRuMm5yWjl5aEwyMW5UbE5JZ1ZHNEVPZUVNM2V5SWVwYlFmQ09lMXRkN0s3ZnY3VzdtaVZmd2dLQ2QwdzFlMjBnYVlZbFF6Sy1fS1Z4dHp5ZmExSG9ybERJRlh6aWxNejJxSnVNeXgzY1JGeWV3ck05MEM5aC16V0JuZUN6aW1ETlZ4N2ZmNFhyWllYcUgwQzl5TGlscWZlYlhYOGljUFh0NTRzeHVPMFRyQ1UzRTFJZnJRRW9hc2xyRDJWdWlLTGRnVzdkLUpmQ1NlTUpiX2dRaXNILUU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxQWWtOdXVOWjFyOS1QUmttQ25DdThPY1d6TVBpdVByV09qbnZscHZJUlJQdlc4d3lFcmJmZ21odVd1am16d0ltU0hIN2hlZWw1VWxMcXd6NDhPSVNfMzBuVVF3bVh2YnUyU09fNGRILTAyTFRXbmx6TERpN3VoMWJKZV9Jckc?oc=5</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>08-05-2026 14:17 UTC</t>
+          <t>08-05-2026 09:10 UTC</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Zydus Biotech</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Life Sciences Job Openings at Zydus Lifescience Limited | Walk-In Interview 2026</t>
+          <t>Merck : Statement on Daiichi Sankyo Update to Manufacturing and Supply Plan - Merck.com</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>BioTecNika</t>
+          <t>marketscreener.com</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOWUZBVG4zREhESXpZSHdsQUt1TWYxb28yUUw5SlFBTW5FSERfSTRCeDlwNVd5RkJXRVZuZE4wZjd2aUU4Z0NsRXlTWjJLX0VhQ2JsWG1RUDVuVTdzaF9NLVVWSDNiN3oxZDZiTm5fblExMnRXU2tGTVdoTDd6M2hydHQ3ajRfQTFIQllhUE9fSWFCWGtQQkcwakViQVB6OU02OTVxbGtaTGNQYTZCLW56TkNEb1TSAboBQVVfeXFMUFFkcTJwZkktVVdqVnR6QWJJWnMxQjdGYVRtTWVzRDJhd0pBZnV6bWZocnVSb2VfZTRMemF0cU12S2xjRlBrNm45U2g4VTlQVDNsOEZXeWlCUUZidF9QeG02SUtLUnktclhXcnR2S3JMWVRkNFZoODNvVEduWDNCMWwtWEVHVGJCdlJaTGQzb3JKc1p2dW9JTUQzVXdXRHMxZXJIQTJ1Q3psMWdJeldXTjFPVEZhMkowU3JB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQd2w0T3UwdXY1b1hNem1Dd1d2N0U4WURZNVdOV09BZi02TDJ4OWF6Y21GRnlsN2FmV3lHSk5xRjU4TE5EdGY4MUZNRnhsNWgwb2N5aHZhM1NST2ZBdHk4S2pMVWh1NVhUN0EtTGJGb3E5dXA1LU9HcllyNzB6eExJdjJVd2hPSFhkLXRzRERKNlAxVzZId0F2bkFRM2pYdVhCWktBRnpTaVJDZDZ1OW5uVjNXQ0pnZ1RLRU1TMFNfQkpsTkZLVGFKWHNaV3hZYnVlZnc?oc=5</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>08-05-2026 06:51 UTC</t>
+          <t>08-05-2026 10:37 UTC</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Zydus Biotech</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Semaglutide race: Torrent grabs 38% market share</t>
+          <t>Is It Time To Revisit Daiichi Sankyo (TSE:4568) After This Year’s 26% Share Price Slide?</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxOUWJfR3BZTFI3c0VEdUJTbUhCTkduazZsX1VPY1BvSXJuR25jb25FeWgyZWVtWUctTUVTSURSQTRPUnFkaVBDMlZ3aWw4bWZiRmM4UzFPYjJNcE5pWlgyRF9zcWFaZmlMRTZJMDFsbDg2Zkhxd185b0s0UEVBbkFHcDVXOVJ6cXJfY01DbVJrZ1RCY2dwM2dmaHNURGJoSjk5ekdiV3RrQXZQTWd5NTEyTXNvWkxlSHNLQnRZSTdKSjhHekVtekVBeDYxTktrYWYydHoyTG1YOVRPallf0gHiAUFVX3lxTE5pNGJZZk8zUjRSVnJpWll6OVJ1QkFUNmQweWI1VF9udlRjS1JBbGtGX2dxR1I3dXM0dG1wSWhqRDlOUUZNT0tKX2plRzhjckplVUx5QVItZ0xtaTF4YV9MWjNSTVVNZmhmQ1JNLTBEM1B0cWoxTF9KOTBBMGNkUWo3SG5JY0d2QWtmSXlJRjdhcThaWVNURW9tVjdLVWFIZU5FanBMRmx1MktDcjJkZHczZmVoY0psckVLSld5SUotMUJ3X0g0SVY4TEdwWVBRWlgtZjZnQU9vSk5YY3NYdTRLZWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxPRmJRTUdBNnpmVkZxWlZEenZJclNoZHRNMUJfRDJNSWNLaHhSSTUtbjExNlhWZEU1eG1jSkVZcXRJMkNzaWdaSERnSUZGeDhzTENNOUItRkw4M09JZThrN2Y2VkF5UjlYc3FnRks0MW1obnhTWnVPTjNBTmRfTnFuaGxyTGY2SVNrbllmcDl4RXVYTjBDY2FYU2pZcUROQzdTT0VSdDFCY1dyM3I0TDVHSnYzWWE1MWZXeTBrN3pCbGlQaWVyZDg4aFlvWlR5bjBfcWp2dU9JOTlJMmNQUVpPS295em9IV0HSAewBQVVfeXFMTmZDOGRmU3p3MEdUdElldVBTalZjTTRtX0w4bzNfeVp1OHNHTTBBVnFTLXFmRlNpWG9zT3BZd1V1YjV2VzlNVXhWWVdYdDNRYTFUdkRqdlRIZmxTSGdLci1ZY3p4Nk50a2pDdjNCRy1OdWJIdm04VzBBdFVtTTB5bW5VU0dJQmlNUC0tSzBKNnp4N280MXRmWnBtdFZfMjZTcWM3ckhkaFZ5Uy16bldkcGxjQmNDUTZaVUlFYmFSTTB1N1JJR3lZUkhRMlpiNkU0bDlMQlM5cDkwZTJGajVoQzBibUhEZm1kR2Q2T1E?oc=5</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>08-05-2026 04:05 UTC</t>
+          <t>08-05-2026 11:13 UTC</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Zydus Biotech</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Biocon Share Price: Profit **63%** Gira, Par Biosimilar Ki Dum! Leadership Change Bhi Taiyar</t>
+          <t>Obesity Therapeutics Market Set to Record US$ 63.75 Billion</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Whalesbook</t>
+          <t>openPR.com</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxQVGJYSDVXc1pucGdrQ1g3VDQ3aFFKTU80aUdzdG9zcnNmRzI1Y0sxRVQyOXlvSm5WWVBFZlNmS2J6RUZwakxrUU4xVGYyUW53WHZWNzlKN181cUNGVk5uT2x1Ml9ldlRNNUxQd3RtUlFzeUlwTlNBOUpVSjVPcndXZE5Ub3NsMkltYlBnUmlnS1A2NnprUE92akJ1eVBBMVo4WlkyRUM0b044bjFSakhNUmJPTnRSQzB0OG1WeUdyRzlrRTdqZ1VPU2JaUWtydVdVU3hOUENnY3dXR3RMd1FsRUx3SXdnZnMzUHBsLXJhOGx4WHBUYTlmSUNXUTczZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOMlFPVGduRjZsYkR4N1p1cTRoUkRzTmVCZGpwWU1NaVE1Z05RMWZXTlJmWGZaT2xQSmVyYll5dTAyUElucnFOeEUzQlBaVGUyY2hTOVJLOHhVUTNLd2k3a09CSW1fYnpMNUJzck5iVERTXzhUYlZIN1F2ZUJCUVVLYXFnVzBmTC1hSTdVR3BDSnZPY082NmZMaVdR?oc=5</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>08-05-2026 02:29 UTC</t>
+          <t>08-05-2026 12:57 UTC</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Hetero Biopharma</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Angelini Pharma’s $4B Acquisition Adds Rare Disease Drugs to a Global Growth Strategy</t>
+          <t>Giants of Cancer Care® announces the 14th annual class of inductees</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>MedCity News</t>
+          <t>The Manila Times</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPVFUxTWhCLTVxaWVVTHd5amx3VThRNlJDN0E5TzhrWUpwbnZ2SzFwZjFUd0JjcEE0eVFNd2xBSkhHb1ZHZDczS05jcVpsU1JrRzdGdTlQOGtQb3dnNjN2OUtYcXlHdlQ3aUlZaGhJdWp5SWdtQVVBRVpiZlh3RTI2UG5XOF9kRWRMNFRNalNoWnhaMVdlOVA5RHdsZThac2c2YXVzSHdRU3lpZ2txUlduOC1HdE9fZWhZeTVWMXFwRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxNX2s0R29tRXBBR1BsV2p5OXF4MVVMTTVUbGZHOTR6UGRmSl9wMUE0am1qZlg4LUVvTkUybVJqRHFNRDcxMkphTnc3UkxndC1KRTV6WmpvYVlpR0RSSk9UaG9nQ1ZuV0FhbWowcU1KTFBSOFIwNEE1di1fak5ZcG9iVHVsX1phRWl1WV9uUDVURFNPTFMwYTdKQXZHaUZBUXBldHBGZV8zTnc4MVF2eUdkOVlzdzVsbFlQZ25wU3o0OV9ITWsyS3JaSGxpUDkyTEs0TE9YeVc2Qk9EUkt40gHcAUFVX3lxTE1fazRHb21FcEFHUGxXank5cXgxVUxNNVRsZkc5NHpQZGZKX3AxQTRqbWpmWDgtRW9ORTJtUmpEcU1ENzEySmFOdzdSTGd0LUpFNXpaam9hWWlHRFJKT1Rob2dDVm5XQWFtajBxTUpMUFI4UjA0QTV2LV9qTllwb2JUdWxfWmFFaXVZX25QNVREU09MUzBhN0pBdkdpRkFRcGV0cEZlXzNOdzgxUXZ5R2Q5WXN3NWxsWVBnbnBTejQ5X0hNazJLclpIbGlQOTJMSzRMT1h5VzZCT0RSS3g?oc=5</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>07-05-2026 20:48 UTC</t>
+          <t>08-05-2026 15:22 UTC</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Dong A ST - Meiji Seika</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Samsung Galaxy S26 Ultra price drops to lowest: Details inside</t>
+          <t>BTgen expands global CMO push, boosts capacity and eyes Korea IPO - CHOSUNBIZ</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>India Today</t>
+          <t>Chosunbiz</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNc1ZiSkNuYjNReTZwOXA5Q0tucTlVaUdsbDhTQTM2aE1SZnluUHlNZGJ1YmsxbmNrYW0tajhrWDJYVTNDZkpvdWhEcEJYNDYzTkZmUnZoUzdCVTc3eXhXQkg4TjMzZ2xPMEZuY0pkeWwteFhYQ2pMTXBVb2FBaVJTdlRUX0p2cWlxYk1XXzBmTTdjbmlEbmZHY21zSEh1T1FOU1VMVE1rcFVvTlNDSFVzakFWd3RzczNIYWVaNGc2and1cXky0gHEAUFVX3lxTE1zVmJKQ25iM1F5NnA5cDlDS25xOVVpR2xsOFNBMzZoTVJmeW5QeU1kYnViazFuY2thbS1qOGtYMlhVM0NmSm91aERwQlg0NjNORmZSdmhTN0JVNzd5eFdCSDhOMzNnbE8wRm5jSmR5bC14WFhDakxNcFVvYUFpUlN2VFRfSnZxaXFiTVdfMGZNN2NuaURuZkdjbXNISHVPUU5TVUxUTWtwVW9OU0NIVXNqQVZ3dHNzM0hhZVo0ZzZqd3VxeTI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQczhRTUYwVV9nOW1zZjhSbHFVQjNsU1IycmdoVWlXelNlb2pxcEw2b195UmxMcEQtdzdWeW1INnlGckZQLXh4M3JGZjJYODUweFV1RFdBRFN2ZWJweDVSdlFRWHM2Z2N6MGMzclc1LTNtYi1aR1Jpd3NjQnVUZ1B1YtIBlAFBVV95cUxNUHgtczd2N1pkUWVKcWZKNEFyNmdnaVZDYjhQMlp5aUU5SnZ5YjlVLXVnUmQ0bmxuQW1rRXRYVUQzdnFsY2hxemRMZTNYbUs3ejgwNVpSdWlPZ3VPQXBvVW12RUJIbktkRGdDeVZRX1pJZUZob0pFOEF6Tm9ES1RjQ25CN2ozaHZrZGJyR1lCdXZJLUtl?oc=5</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>08-05-2026 12:35 UTC</t>
+          <t>08-05-2026 22:08 UTC</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Kyowa Kirin</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Samsung launches 5th edition flagship innovation, education programme in India</t>
+          <t>Kyowa Kirin (TSE:4151) Margin Improvement To 13.5% Reinforces Profitability Focus Narratives</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxQdDhxR2pMWWQtUmFtcVNrMWNjSW93a3M0SldONHhTUjBiaHo2RnBxaFVIbG1qZUtldHZ0Q1NSU3l3MHBwaEtqNzRUT2VJRDF1a05Ma0VENmt2bG9ST0ZFalVzb1cwNE1GdXNGTzUyOWtqUGhYV1B2YUhCektBR0J6d09lSldOS3lRd1FaUjNROFJSbENMR1dmMDNUdndUaEJENkoyenIyam4ybVN6czl0cERtU05jcVl0dFA2ZU5uM3N0WEFHa045UnAyTWFTMGhFRDdjTnR6em9zUE50cThxYUpBWDVMLXhpOVhLdFhNRjZLVWx1MkpJMjV30gH_AUFVX3lxTFBfbEEtRlprcHVjam9rUzdwa1lSMkhZd0x3WkdmLTgwM3JERE1NMmcyaFhLTU1wTmt4eGoyUjl4U2t1WUNhWTdNVEJpOWZxcWFnZWlGd3JIR3RrZGpSWndQMHpwM2dqdzBmem1VWXFwd3NUeHlGamFGN0k5UkF5ZS1PVEE5TjJoM1h2b2NVZGtuVmFrQWJLem1CSlNSaXdWMS01VXFrbFhvT1lDb3pTR2d6WVV1aEM5QTlLODQ2TDBmLVNZU1FYTzJWOHVKeFFvZ0RsekdnSko3bUVDeW5DakhIZDVxTW9xWWt1aW5ZZTE4aFl6WWZ5eWNLa2FQV21hcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxPRGxMN3Q1RVBsbnFsN1Nja1JtaVlVclBCNUtSUWRibEZOYkJkYUZGS2Myc2I3eGw4NEREZF84SnpHajRTY0hDMG1kWGZURTR5TVVOLTV4UW1zOUM0U3pEX3lrcDNTbVNmUFRhWVFldFVjWWp3VUZ1SGdxa1Q2dU1Cc0lCNGJiTHVfWnFFemZMdVVyWlNFbzJIR2VpekJJZFRqUC1PbmRKcEY5UWhoNldHVzNJTExSNFRsWS1vMGtjclVncWtRVGFvM0Q4WGREc29hVUFSZ0hFSjI1Y0Rtblg2c3pVSFB1alFT0gHoAUFVX3lxTE9EbEw3dDVFUGxucWw3U2NrUm1pWVVyUEI1S1JRZGJsRk5iQmRhRkZLYzJzYjd4bDg0RERkXzhKekdqNFNjSEMwbWRYZlRFNHlNVU4tNXhRbXM5QzRTekRfeWtwM1NtU2ZQVGFZUWV0VWNZandVRnVIZ3FrVDZ1TUJzSUI0YmJMdV9acUV6Zkx1VXJaU0VvMkhHZWl6QklkVGpQLU9uZEpwRjlRaGg2V0dXM0lMTFI0VGxZLW8wa2NyVWdxa1FUYW8zRDhYZERzb2FVQVJnSEVKMjVjRG1uWDZzelVIUHVqUVM?oc=5</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>08-05-2026 15:44 UTC</t>
+          <t>08-05-2026 08:59 UTC</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Kyowa Kirin</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Samsung Unveils Next-Gen Vision AI-Powered Mini LED TVs for Enhanced Viewing in India</t>
+          <t>Aevi Genomic Medicine LLC Share Price Today (CBOE: GNMX) - Aevi Genomic Medicine LLC Stock Price Live Quote</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>samsung.com</t>
+          <t>INDmoney</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOZlNSaWhodkcwcFl3b29tbzJjb3RhZER0WFM4TFh1dWtFZkJ4QXFiWS1yeXBWTExaRHlwMGZzVnV2V1ZlQlRfSUV2R252MlFvaEM0aHpCeWg5WXFoWmhMejk0dFc2eDRyLUdFczJPcmVOMVZGSjUwcENvNVR4NktpWEZzUmtxT3FURDFETDR5WEhrRVVBUHZMYVJzYW1CZDc2ejk4TEh5ajZ0MlNQOHh4MnJiMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE1IRzI1aW5Ld1dmbnVROTMyNFNqQWdERXpiRk41bE1rXzRzUG45bWVwenJTaHczX1ZzTl9XY2QzaGpUWkNEUUNWLW9xMTl1MWtPdHlVZnBSYw?oc=5</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>08-05-2026 05:03 UTC</t>
+          <t>09-05-2026 03:16 UTC</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>JCR Pharma</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Samsung launches AI-powered Mini LED TV range in India</t>
+          <t>Italfarmaco’s new CEO and commitment to rare disease R&amp;D</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>t2ONLINE</t>
+          <t>The Pharma Letter</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQbVJ0LUtrZzBuQU9sREVadHM2UU9yQWZsYVIza1BVcURDcXY3djR0U2dHOXk5b0pXWnlRRW1qa0l1NDB5MTNrUkZpSE9JOEROSy1VOEE0R0Z2T1FObS05OVNOZlN3aTNXTHlCY2xPS1dyMWFNcVNwNWFrbTdXVlhqM05jUWU3SGJvWS1Wd0c4b2pfYnVHVE1pbEpZYUlqUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOejNqNlhzSUx3cGRHcGFpZzhLR3hxNF9KU0RNNlN4SUkySWRhMkNocHVFeXQ4M2FpVHN4d1prLTdNbHpObE1kcWx5TnFXeEh1Z3kzNzM4NS1UNjBfQ2s0OFZVTG9WcGpSQWkyeHBGNUJjb2RnVW9EYVdsTUV3Qm53R2ppelVLbE9fWXNkOXdyRko4a19GbTZ0SktrSXVjUWdnYUE?oc=5</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>08-05-2026 11:14 UTC</t>
+          <t>08-05-2026 19:26 UTC</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Samsung strengthens enterprise push with AI-powered Business Experience Studio in Gurugram</t>
+          <t>Fresenius SE &amp; Co. KGaA stock (DE0005785604): Healthcare group reports Q1 2026 results and confirms</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Indiatimes</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxPajViVUtwcTNEVnVGWnhLQW9ZVl9YNHZKSEF6TFUzSW9NU2hOU2Nic0N5by0xQUpHRm5fdnFLaGtWYWZfTnNMX2FvXzI0MnFWVGtOWms2NW42RE9oVlY5WmpNLXlCTGtBQzYzSFF1WUl0Q1ZvazRNZnpKNnNyTk8tb1hQSjBrVXZub1NSc1hVT3FhTEVDX1RPZDhTLWp2dFAxdTVXS2YyOV9xLThVNVdXNGxmekRKaVBOZEtwc05aWDJyZ2R6MGxjYmkxMW82aEFIWUdHMVJwNnVqRU1VdnR3alNSSDIxeGdUZ3VfakJ5Y3VVQUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQemRza0Z6SFdmSlhmRl9jbmdzZ2VTdHNJcDFKLUloSDlEblE0TnhyMzJ4STdLeGZJNzdlb25IWHNSV2szRlFmTlVRQzZjZVYwVWlJbkZ2ZHluLTZCLUNWLWFKNTNqZ2lqSVJIQ3E1QzkyWDBjOUYxaUd4VzQ2LTZRaFpNUzVwQ1JrRDBJdXg1c3RQVE5ZM0NtUHpUc3BvM2dNMHk2WERVVkU0N0t3ZGlFYlB5ZENYZEJnU3J1LUZzSFhKRjJ3S3c?oc=5</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>08-05-2026 12:30 UTC</t>
+          <t>09-05-2026 07:53 UTC</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>OnePlus Nord CE 6 vs Vivo T5 Pro vs Samsung Galaxy A37 5G: Price in India, Specifications Compared</t>
+          <t>Fresenius SE &amp; Co. KGaA stock (DE0005785604): Guidance reconfirmed after strong start to 2026</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Gadgets 360</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxOdVdYQ0FUSkhSYUJJVTY3Wnl1WHB6a2JwSDVJal9WOWxSbG1fcExscjNkQUFDZUxoMjUzcnRTQlBXaWFnSS0za0tDbUx2cFNjSEw1TkNvSHQza3lXWkg5enhsSzNxWmgycklwTmhoTUttWWlOVUIteE5sRlpxS2RCYXY2dExMM0FiX1c3R2YzVk5MQmgtaldqWHZYQzZlYWJGcVhnWUQyR3d3bE55Y3BuTFJwdzZQVTVQTV8yNUx6cDlDbXVlQ2Z2eTZ1NjZIcVZyNjM1R0hBNGhRdmRBRmRtMEpERHl0UTAxTEtXeFFrLVpiaUgyRGxPdXR1NXpDQUdmZ0HSAYcCQVVfeXFMUHdibGxHT3gzU0ttdG1fZ3d3RnZRMllRT2RfZS1Lck1VSG82TmpSZEE1dUFPSkFYTDhpQjhlR1VzNzBTUzJScm5DOTZ1WmFEMllISVI0TGlDUG1OM2FJM2VxN1hyOFNmQjFMMlh6NXNyOTMtSEdBTUZQY01PcFV4ZUdoTjcyWkhNQ2F2Qkw1dGk4cWJZT3ZHaVNOaGFhUkY0NkZnbzFWYzlsdW9jX296QkpCQ2dLUDJKY3Q2X3JEMEZMYkhTcVl4SXFlT1o2NllJNDNMbXJYWlY0TUZQaUtHT0tRVy1XbkJ6VzE4RlZCUVh5TVZkU1NTMUZJSThNM3RSTnBqcHFpMlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQZDcwZlNOTnZMRURpTVVyU2VlX0J4cndUQ3JoYUU0UUpwaFVORDNZbGRpVGlabW9zSkdpaW9NMUNieDdXa294R3R6S25PRGhsRXNBVGlaRUNIaG8zVG1qRDR1YUU0bDI3UkI1OGZIWTRFemVjTGVHMTBzNkVjTjhqMExSZ0dIZTBlQ0JkVHNqa19yaURZVlAtWVBBbGlOMGozOTdSYnhDeU1EelRLbHJMbWltVDBiczkxM1FXa1N2Y2U?oc=5</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>08-05-2026 12:52 UTC</t>
+          <t>09-05-2026 05:06 UTC</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Samsung Launches Fifth Edition of ‘Solve for Tomorrow’ Innovation Programme in India</t>
+          <t>Fresenius SE &amp; Co. KGaA stock (DE0005785604): Healthcare group eyes growth amid restructuring</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Kashmir Convener</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNNzFtbktBdEMwcy0xVHJCaXpFbXdGM3N5OWVPSGN0NXlmdTFOM0RYTEJoTVljaHVVNTFGZUJwZFF1QmRjdDVVLXRQYjhsY1pGQlliQXZqS0NBZU5IeE1rREl1SDJsSW5XclJCMUptRFJvSGdHLVlRd3p0TVVJME5GV29OWGlXX0lyalVBaDZPYTg3Y1JkNnFPZmxMWm9xcndQNWdxN1h6S3JUb3FZR0pJWA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPTFJUb2hNMG1QVDNjYXZFMWY3VHNfOHdKa1BaS1pqNGhzOXhmZlRRZjlfSU5hZWN3VGZwRFZwcnROSUYwbmZ3a3FKaEs2ekZWd283MWs4QkFETWc3SWhJX3R6Z0dOS3gxa3BWZFJuR2ZyS2M2bEF0YWxjMEQ5NXBhaUVpMUFuMjdXaHBBSnpEanJjeTFXWHNFcjVYdmxQLTlIdUZrcThPeWlQRVJjY0ViZHVGOUtDWXdoZDJMRXpRS09sUQ?oc=5</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>08-05-2026 14:59 UTC</t>
+          <t>08-05-2026 11:57 UTC</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Samsung Galaxy Watch Achieves World-First Breakthrough In Fainting Prediction</t>
+          <t>Caplin Steriles Gets USFDA Nod for Generic Calcium Gluconate Injection in Multiple Strengths</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>ETV Bharat</t>
+          <t>ChemAnalyst</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOZnpXV09DdENfdmMwZll3aHYzVW9XMkVBS0hmY05HbG9qRlhxbk93czFReW94UEdTUDBlNzB4MXl5cFRWZUNrZjllX2h6TUFYbjgwa1pmbVRsNlltdm03clRzdDJacHdqenFMS3NYQWNJU0p0aU1RYXVORm9hMmpVVGhkSWtMSmlmNDE0ZDZra2dPRFF1U3AycXlBTHFHckVhSjRtTXloZXJkUHRBbkdYbEN0MjZ6cldQc0hJbUMwSHJBajlvalY3R3ZuWXbSAdIBQVVfeXFMTnE4V0oxTl9FUXYyRkxUT1QzZ0JLNmNHNFR0bWpUREtPc21XVEt1LXRNcTFKOW92QUZBdzk4UVMzSFJ4OVVrS192S19vdHRhWk5MTWdwc3dRXzQwbDhwYTBueVJoSG14cmZKVlBaMmNwcWdaaXBRb0dpTkVveG9MUGNiLWRrSnFhcEx5SmNoMmVBRGp3dmZIQ0xueXhjRFBjeHlFSWkteGRoWEZpSGNMNURxaG00d2UxUVFmTkVUUWtweU5CNWx5dTRyeG1QNWp4LW93?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQVDJNREZxUE0zR1laMXp2REg3ZzIydG1uVklZazlGLUdRU1dMYWhCNk9PX3FDZW1MWjk5eDZKeWs3YkZSUDJ6VlRuUmtOMTBNb2FFTVZSbThKWUZyQmoxZ1Z1S0RjU1lKTU5CaTZXVFFaamNKem9RSGpWQ3JHQmlnbzh6bldkaFdBWVotYy1UMHJSRVd1WmJWb2tRMUxEaXpUUmN4VFZSOE12bFB3WXEzekloaHZYYzA0bGN6SnZMV3NINHJyR1o5aw?oc=5</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>08-05-2026 12:51 UTC</t>
+          <t>08-05-2026 15:53 UTC</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Samsung Galaxy S25 FE now available at the lowest price, details here</t>
+          <t>Who’s Hired? Viatris Begins Search For New CFO</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>India Today</t>
+          <t>Citeline News &amp; Insights</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxNSWhFQU1aMnEteGpzRnh6UjNUQTNrbWk0V3lnRnoySXdxRFdOTVJlVVlGb1c3NW1JTVVGczZIcUxUQWVCMmhMWjVSWFFlcWJjNkxvT2I2Y1ZRUnRyZHZiVkRycm5Tc2tNMmdRSUgxN04xay1zMHFWdWhzV0V3dGZFM0c2Z2owY0lyNnYxLW9OYm1wd1FTdGtZR0dHdjhMSGRtYjJMRmpaZHo5N3dNT3VzSkNqTnItN3VDOEFvWHdrbnBGTVRaZWVsSWI4TThhU0VBUmU1OFln0gHWAUFVX3lxTE1JaEVBTVoycS14anNGeHpSM1RBM2ttaTRXeWdGejJJd3FEV05NUmVVWUZvVzc1bUlNVUZzNkhxTFRBZUIyaExaNVJYUWVxYmM2TG9PYjZjVlFSdHJkdmJWRHJyblNza00yZ1FJSDE3TjFrLXMwcVZ1aHNXRXd0ZkUzRzZnajBjSXI2djEtb05ibXB3UVN0a1lHR0d2OExIZG1iMkxGalpkejk3d01PdXNKQ2pOci03dUM4QW9Yd2tucEZNVFplZWxJYjhNOGFTRUFSZTU4WWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxOM2p0ek05bVowRFBiZFU4OExlYVdlMnMtdnNJeXI0LWJlV25EalRyQlhXTUk5N094elpadXA1QWgxd0Y1Nml6SHF5ZTFQdUh1NnB1MDFlLUpTYTV6S2NpanE0RDlXQkZmWS1qSEtsYkVqN2k4MXlyaWsyRmVsaElmVkpGVlhVcFQ0dVJUd0hST05zY1hsbjZTeEdDZVVBbV9rNVgwQnV5aElRdndNcHRCU0RlNDY5N3BScHg4QmVUVDlrZ054cEFsa2FkWUhDcVNzeE83ZzR6Q3dHQQ?oc=5</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>08-05-2026 13:08 UTC</t>
+          <t>08-05-2026 12:08 UTC</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Samsung Announces World-First Breakthrough in Fainting Prediction With Galaxy Watch</t>
+          <t>Semaglutide Biosimilar and Generic Market Size, Share and Latest Trends 2026 to 2035</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>samsung.com</t>
+          <t>Insightace Analytic</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQMTJ0a0tuclZRbnQzbEVzME45OFZaMWYwcmhBOGpRM3NmWVViMnMxTlBCbmF0LWNOeHJvVm5ETW1abGpNN05aV2lvRWdud0EtbTRoYXpBZENIRmJSbFQtbE5JRnRGN0NSalVydVQ0SE12OUZkVmVld21xeGFHcHVWS3dIUUFNcHcwSWo4dWVxbHRsY2xUY1NFY1dmVENpSEh6R2VOVTZUbzRwMmNaXzA3UA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQckkyWlpVRUgwWk1lSWF4cHVjZE13TWpqdk4xZnotYVlPaGpNdGI5djdSaDBuSnJmS3NtVF9SUXNjeThBMFlLdDhBcktrb0ZlMVhTa2FfRXRPekQ3MTBtSE9PUEFBUWJqMkZDRk5vQURfZDRMVzQ3QU5jN0hNYTI5SjZlUGc2SnhLbktYcnB5cFFtZw?oc=5</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>08-05-2026 12:35 UTC</t>
+          <t>08-05-2026 14:27 UTC</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Samsung Galaxy S25 Ultra price drops by Rs 30,000: Full details</t>
+          <t>Infusion Therapy Market Is Going to Boom | Baxter International, B. Braun Melsungen AG, Fresenius Kabi AG</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>India Today</t>
+          <t>openPR.com</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQendFTDNuMVpHZ0VRZ0xVeXQ4WnJuT2ZydTk4QTBtd0t4NklPSkJwSVlHeWtTT0o4a0xzN0xSNlFseGNzVEdkTkdOVjJ1TmNLS3AzX2NsaXIxVTJuUW9yNnM2aVdwNlVQcTZEY2RJZk5CYUZwaXdPaFBkWEwxajBSZV9nZUd6NHFobDV2Z0xYamhQLS1DNlptaXRleExOYUtsSS1TZHZyMnFoZFAxRWtwbUk4V3JUTkR4X2YtLUxqSWZLUGM0alZMMDhB0gHKAUFVX3lxTFB6d0VMM24xWkdnRVFnTFV5dDhacm5PZnJ1OThBMG13S3g2SU9KQnBJWUd5a1NPSjhrTHM3TFI2UWx4Y3NUR2ROR05WMnVOY0tLcDNfY2xpcjFVMm5Rb3I2czZpV3A2VVBxNkRjZElmTkJhRnBpd09oUGRYTDFqMFJlX2dlR3o0cWhsNXZnTFhqaFAtLUM2Wm1pdGV4TE5hS2xJLVNkdnIycWhkUDFFa3BtSThXclRORHhfZi0tTGpJZktQYzRqVkwwOEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOSUQxSmFjRG9xUWJPSXhGMzhYVnkxNk52dXNvalRVSG1FNmVFbkRMY2FQSnBjcGZfMDRWTk9sQVN5cGppY1hDcjFVeHdFWXpaU21wWnlGTU9KdGZHOW9xMncwZXEzbl9OWE5Qa01QY2VnRk5Bdm5fTVFSZ00tMVFZQmNTckhhdzlBWE9BNi1yTXktSDV2MzkyX3Y2bE9rZw?oc=5</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>08-05-2026 12:17 UTC</t>
+          <t>08-05-2026 11:31 UTC</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>[Interview] When a Washer Becomes Furniture: Meet the Designers Behind the Red Dot Design Award 2026</t>
+          <t>Small Manufacturers Face Tariff Survival Threat</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>samsung.com</t>
+          <t>Legis1</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQNkM0aHhrQTkzRXNSS2xoeHBUZENEOE1laUp5TnpNOU9KSXJNbDFZU2hKNE42dmotWnFyYVBpTkh0bkZQSFdBMEQ4VVhyd3RLVUFDREF3SWlDTHF2ZnJXYTlhOTZCMWZLYWwtcFM2V29OdVBoZ3Zfdm1sS19NS052X1VQbXVBYnhhOC1GSThyc1dQemNnVTcwalNreEE5T2F3QjZRZDFUZjR2S1YzY0JnVzZ3N01RTDRvRzIxN1ZJVmN0X2dsdVlHSw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE9ueUdTMTRDRW9iakhreVdZUXRNeUxKaTliR01JaXRpM1FfQ0Ytbk4tdGhsck5JemZWQXBMazduX0YxSWE2cU9sblhubExsTnV3a0dRYUdCS0hYZC1Jc0RqZF96VmlmbUFLYnR2UzlSTENCVWpVdWFKQ191RXo?oc=5</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>08-05-2026 01:00 UTC</t>
+          <t>08-05-2026 18:08 UTC</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Celltrions U.S. Strategy Boosts Sales of Jimpenetra, Achieving Record Prescriptions</t>
+          <t>Blood Bags Market To Reach USD 956.4 Mn By 2035 | Healthcare</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>aju press</t>
+          <t>openPR.com</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE5YeDRtQlNlbDVNQjQyWXdCVEJnaHJBdGYtMDlnMFFoWFFsVlIyeVVpczZrVWZPVzBYcjhwMzV1cEsySVgySGM3WU9qN2xvTFg2YjltU0pIWURpMU3SAVdBVV95cUxQWURTd3Rmc2hYVmdQOGFfUlhQT1BxdVY5RUFFZkZXQ1FyUldCWW92Nld1NjdhZDZlcW1UTk9NWmN3UUxJSWlBd0V6Q01HS0YwY052c21uNjg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPYk5UeERzX0xWbW1Lem1IcWwtaGpvTDZsYV96Q1ZRSnRhTGIybC1RWlRsNVpkMmRQM0gwX3ZmNXdfYWwzZWhuUHJxdEtTcjNZU0x4U3ZvTVVacEplWE0zSzVvSGQ1QXdYcXlBdGs1ZURTSWRfeXM1WWVOUDFkdzZscWs2ZDl2SHlydnZYak9TYUNUOTQ3cGFKSDFR?oc=5</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>08-05-2026 04:33 UTC</t>
+          <t>08-05-2026 13:41 UTC</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Tranche Update on Celltrion, Inc.'s Equity Buyback Plan announced on April 22, 2026.</t>
+          <t>FRE.SW Stock Plunges 31.8% in Pre-Market Trading on May 9</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>marketscreener.com</t>
+          <t>Meyka</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxNSWxOU1MtWDFnLWx5RFNHVmQxZFdYdExoR3BTdGVFQUp3aXVURFlWQ29BRmhZRUVUdE9QOWJTUklpdzI2dmtTSU5OWVh0ZDhvdDdydXVrREJSZnRpd19sekJXdmFtbEltYm05MHlnS2p5NjRENjlXSXo2TU5DOURPUEpGc1hkeDR5NXR2SE42OXdCZ0RBVzlXWFhlNlluaWsyUnc0X05YOG9NSFNNMEZmMVpRVjhRLUJOTDRaNjJvNzJhQkx1Q0tkUFowOG5wZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxPenRpTHVPa21IVmtsYm1HajV4QTVXaFBBWml3NmhiTElIcm51LThhSEJXWm5RenM0U0ZQQmRFSjBZUkJEZEMyWWVGdmdtV0liZXJNSElvQm5Wc1lNZ3JmME12WnV2cFMxaGlROGdNcXBwZ1JpVjk2b2U4RDhBY2tMYklRaVF5bFAtdF84?oc=5</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>08-05-2026 05:50 UTC</t>
+          <t>09-05-2026 01:15 UTC</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Celltrion’s Zymfentra sees 185% surge in US prescriptions</t>
+          <t>Sun Pharmaceutical Appoints Ms. Satyavati Berera as Independent Director Following Postal Ballot</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>The Korea Herald</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTFB2S3Ywbk1sdzdmMDJvUVNveFk5TndQN2tSSnBGU1M1d2FUbktZVHYxTWRJdTQ0NF8wZG1SalQ0Z3A2Mkx3ZF9CXy1vMnQxeVdZM0xhVXROVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxQMFdmMXc0bll4WF9mNFVfaEVNVUtCNThTX0JDM1hqT1pBZmhleHducDRWQnl1SlNXUUZRX1hTN3VRV2FpSGZvb1hJaHhjc3d3ZkhEQ0xpMkE2ejduMzQ2T2NMNmJxbV9Tb19QS0poZFd2QlNmR3loZDNTM05qeGxIVFlER0VfZm00RjZVQk5qdVZHSW9KNE0tMExmWm1oVkZVMzRkdTdxMHdnMDlZMnJ0bTY2dUkzLUdHQ2xWdmRHcW1lUFE2RDNNQjMxdmNrMVF6Sk9xd1ltSE91SmYtYU5PWW9peHIxeTg?oc=5</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>08-05-2026 02:26 UTC</t>
+          <t>08-05-2026 21:48 UTC</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Celltrion's Zymfentra Achieves Record Quarterly Prescriptions</t>
+          <t>Accretion Pharma Reports FY26 Results; Appoints Auditors</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Seoul Economic Daily</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQOXFjR2czODJ1RXBTNkc1cm1oZl9hb0Z6NTJqLXdWUThOZ1ZBVEpxaEVvaUFaeWhKN3Z6ekR3aWdrTmJRT2VuTFJKUzJnQ3k4OUJtcTRPcWREWjhHVDlpMlUxdV9lRGg5R0hzNXJya0FnbjJ6ZXNZdHdqOW92SFVTdnVVbTdMdlU5dEM4UEZ0UnFFMzNmSE8tdHh6S0JHLTNKclNXOQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxNSnRWTnh5S2wweHBxSVl6WWF4SGhYYWxhQ0FuUDR3WWw3RXh5V3FtRk1TN1BsbloyWlBpeFZiZ0tCNjFFUzIxdExmOURpcnZONWF2M09YWGdhVHBCeDJ3ZV90XzlGelBreHZsMmlpQ1c5S0RvaXdsUWRaaDJBbGthZFExVml5ejk3SF9sZWNEbHRLNHdiaU1VZzgyMWtVbVRKWWxseXB6WnktOURtTS1CUTZMdTRta3BQblFtNzBlemxFTWtWTlF0VHl6WjFLQVhLUmdWZHRWaUk0cE0?oc=5</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>08-05-2026 02:54 UTC</t>
+          <t>09-05-2026 07:23 UTC</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Celltrion drives US Zymfentra surge, posts record quarterly sales - CHOSUNBIZ</t>
+          <t>Mississippi to receive $41 million from settlement with defunct pharmaceutical company</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Chosunbiz</t>
+          <t>SuperTalk Mississippi Media</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNclZKLVhpMGx5R0hhWVgxNXE2VzBGcmZ6OE9JZ3I3TVp4MUpRbjN4U0oxbG5kdWVXTkNKdmYzTWVhM0dmLVY5V01kSTl0YkV3bExjbk5aVXVTN3dvZ3o2N05MRVdUZzVhVW45d190OXZoYTI3clV1bW1FTEVPeVhlWNIBlAFBVV95cUxPQTJxZjltUXVoZFJUNk50QXB4OFJlREd2UXZEaDROemM5YWt6cUFfSmhmckp3ZTc4ZW9FbnRVZHpjMkdvOVN0V2FhRWFzTGtDd2hWeEltczhYLVpvNDN5RkVJUUJTNHlzYkdFOUo0a0VhVW5Kd2p1MEhOdDZtQWZjREZwSlFUYU1hNmw5TnFRbE5WdnJq?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNM01xSlowWWlzYmpXLXFNZ2tnN3FLMTd2enhRcktmS2pfc3dEc3Z2UF9tUmYyWFYwb08tcHgyMmQtYXQ4T1JBOWNJNjFGRjRxYmI1VTlXOXVERXpoNXhpQ084V2hkTmRRSHFOeWZJXzdmTkxvX293WEV1U1Zlc3JPQ2hzVDJrU24zZldJUUsxc3RaM2M4Q2hXVFdYVU9CZUJmZjFVSFNNVXpZMnlXWFl0cg?oc=5</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>08-05-2026 00:13 UTC</t>
+          <t>08-05-2026 15:40 UTC</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Chinese tanker takes hit near Hormuz as Gulf tensions paralyze shipping - CHOSUNBIZ</t>
+          <t>BridgeBio Pharma: Q1 Earnings Snapshot</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Chosunbiz</t>
+          <t>theheraldreview.com</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPd0VKYWZuNDlIVGs4WnVLcmxMRDJsVTd6bUVHUWppM3BuZlVCRklMbUZjUFQwYWhDVnFJUkF6aUxjXzJ0eTQyNGhLamh3T1BuUmUzNGFCeTRVYi1lcGpxN0hrMzhLTHRHRVl6bVZYSzdUaHpnOWtaSWtta3NzblJNTTlDSzhucWlqU0xuQnQ2WWhhd2Q1LWVCUTFjZkjSAZwBQVVfeXFMT3dFSmFmbjQ5SFRrOFp1S3JsTEQybFU3em1FR1FqaTNwbmZVQkZJTG1GY1BUMGFoQ1ZxSVJBemlMY18ydHk0MjRoS2pod09QblJlMzRhQnk0VWItZXBqcTdIazM4S0x0R0VZem1WWEs3VGh6ZzlrWklrbWtzc25STU05Q0s4bnFpalNMbkJ0NlloYXdkNS1lQlExY2ZI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOSWtNejdrek1QbVpuUWJtWWgxUTBZUWl2SEhKVWJnU0QzMlFTRThfVzVvN2JGZGI0MXljZ3FiSWN5V3ZBZmpLVVl6VTN3cnlmWExrNkZLdFg0RDZzbHdJLTNRcGlwbFF3QTVsM0ZDdTcta1c1YkZVeG5ncERjR04tNWR2R3dEb2o1dDU1Wnc0U0RaTVRyR3BTUjhzbmxkTHhX?oc=5</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>08-05-2026 02:19 UTC</t>
+          <t>08-05-2026 09:08 UTC</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Younghoon, Lee Ruda, Kim Dong-jun star in Korea's time‑crossing romance Love WiFi-gung - CHOSUNBIZ</t>
+          <t>Systematix Corporate Services Appoints Ms. Rupam Lal Das as Joint Managing Director</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Chosunbiz</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQZmlvR0k5REJKVHJ0MmVJX3lCSXV5ZVhPUjJiRlpOOHdDZjIwOTlKVjdWX1RSQlhYQ3FhRnQ0QkxDZG96bXRLWVBSUFhid0dBWUpzQU5ZS0txQ1ZLN2xSVm9xU1ptbkVFb1JnUWxqV1FZOTVYLTVwcE1NeHpJa0lBTXRiaUtURF9ydHBTYmg2eUZkMVotcFcxWjlRbkfSAZwBQVVfeXFMUGZpb0dJOURCSlRydDJlSV95Qkl1eWVYT1IyYkZaTjh3Q2YyMDk5SlY3Vl9UUkJYWENxYUZ0NEJMQ2Rvem10S1lQUlBYYndHQVlKc0FOWUtLcUNWSzdsUlZvcVNabW5FRW9SZ1FsaldRWTk1WC01cHBNTXh6SWtJQU10YmlLVERfcnRwU2JoNnlGZDFaLXBXMVo5UW5H?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxPQmx2TTFEZlJTZnB2UzltX3pzX2dLcS1hWE9MS2NFMnV6empyU1N4LXVHSV92T2thMGRFU3VUYzEtblNGTUJYd0JxSHFtSU92d083LWlnT3ZrbXhHUDdVNVVYWnFPNTkxdUYzLTgtUV80a3NNcWNsZ1VYd2FEb0VEVFllU3pBUFBKTzRXVDF1MnFGN0tDVl9RMU9kY3pXV0tnakpGUmNFcUgtZ18yMXNJeGcxOEx6djVzUFoxTlJkai1qVjVnQ0lIUXVtUWJVTUNxb1ZXZnh3?oc=5</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>08-05-2026 02:28 UTC</t>
+          <t>08-05-2026 17:42 UTC</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Court jails ex-division commander Lim Seong-geun 3 years in marine death case - CHOSUNBIZ</t>
+          <t>Sun Pharma shareholders approve postal ballot, appoint new independent director</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Chosunbiz</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOTGxHUFVBejRLN29BVVpCUVAwUUZEMXE2dU9SM09WYWYxQTBrMjdsWDNJazg0bmVxUkluZ2NrUkRoa1N3dEdjNnQ1SDJCa0p5VzZLVTVRc0lPR2c3VHZ1M0swNUtMaEN2a2NMT1EwWjZvUGYyRWdJeHk0dGZla05WWEY3WkZZQVMydmNpaUZEYl8wZThS0gGUAUFVX3lxTE5MbEdQVUF6NEs3b0FVWkJRUDBRRkQxcTZ1T1IzT1ZhZjFBMGsyN2xYM0lrODRuZXFSSW5nY2tSRGhrU3d0R2M2dDVIMkJrSnlXNktVNVFzSU9HZzdUdnUzSzA1S0xoQ3ZrY0xPUTBaNm9QZjJFZ0l4eTR0ZmVrTlZYRjdaRllBUzJ2Y2lpRkRiXzBlOFI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPeklUY2tPZ0NGQTUxeTFEUGdOZmRCcXhIV3BhdDVpYnB6RGo3MldKakM2YUM2QVFNZVBYZnJqMzRJYWdIMThKLV9DWGZMeGE1cDZXUXRPTm1vejlZMFAyWV9scWZOaHRWV19nRnl2OWVHZDJPdXFHRDJWT3RGbGVESEtVd012THUzWEc2NkhSd1JkQzVJeWpONjUybnRMRzh4clBtQTlSVWtSdm9Xdkx4b001QXBSbnZ6YXlpZ2FITDVvZlVDOWJON2pR?oc=5</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>08-05-2026 02:21 UTC</t>
+          <t>08-05-2026 15:19 UTC</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Alvotech</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Singer Chuu sings anthem, throws first pitch to rally Hanwha in Daejeon - CHOSUNBIZ</t>
+          <t>A Look At Alvotech (NasdaqGM:ALVO) Valuation After Weak Q1 2026 Results And Biosimilar Pipeline Updates</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Chosunbiz</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQdDVwZm9lMkcyaVF6VWM4ZHc1UTF5Z2RON1NDVTJueUJtZGtlRDFRc2tqLUk1V1BIenBfcV9obkx5S1RzdklYZDZzWXNoQUl0WEFPVy1hTXBwei01aUhYQjlvLVVxSjhHY1hqT3lPdkNxY2JJU0FFMm5MWTRLTW1NVmxRVndZTXJxNG9IWm1hN1hHcnhkWFVtUFlVQ1XSAZwBQVVfeXFMUHQ1cGZvZTJHMmlRelVjOGR3NVExeWdkTjdTQ1UybnlCbWRrZUQxUXNrai1JNVdQSHpwX3FfaG5MeUtUc3ZJWGQ2c1lzaEFJdFhBT1ctYU1wcHotNWlIWEI5by1VcUo4R2NYak95T3ZDcWNiSVNBRTJuTFk0S01tTVZsUVZ3WU1ycTRvSFptYTdYR3J4ZFhVbVBZVUNV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxQMHdvT3dNRE92aWp1MmgzSks2Zm4zbU5VemhvYnJ4S2s2aWhCX19lc25BTXlZdGpFSVBrckJDRjdoWTFyRS1XdFdZSVlvOEl3YU1nUGluRVpiTDlQTHRWZWhuSkEtQ0pVQWlIQkxlQjFjMmFFVWhPS0xsSkcyNWNVMk9rRTRxRG9mVUgwZFlXRFYxNkhJNVdDR2Vvd0Rzb1htZnJjVkh2RXVzWjNUQlFNZ2Nib2FWcXVPUjdzWEF5aENHNm54dWlsVzlvVXRyRGZ6UnhQSVZSazU5Zw?oc=5</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>08-05-2026 02:21 UTC</t>
+          <t>09-05-2026 05:06 UTC</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Alvotech</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Park Mi-sun returns after cancer treatment, says chemo impaired her eyesight - CHOSUNBIZ</t>
+          <t>Alvotech Earnings Call Balances Risk and Growth</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Chosunbiz</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNeTlvd2g2OFJ2d3U3VkM5TVYzcHhTT0t4UUZKcnBiRXVLQzRIdEVhR0dnR0x5SUVvXzZuTUtwWmpWOXkwWGxpVk5Bb29UWjFxOW5wdkI2aTlPQlN5Q2w3ZkxsWEVMck10UDlUbHhIWkw4c1IwNm9PckJQbFhaekNjVXpWdG8tN0pEckJ2d1ZBYXloRG9yRjJzSlVwbmLSAZwBQVVfeXFMTXk5b3doNjhSdnd1N1ZDOU1WM3B4U09LeFFGSnJwYkV1S0M0SHRFYUdHZ0dMeUlFb182bk1LcFpqVjl5MFhsaVZOQW9vVFoxcTlucHZCNmk5T0JTeUNsN2ZMbFhFTHJNdFA5VGx4SFpMOHNSMDZvT3JCUGxYWnpDY1V6VnRvLTdKRHJCdndWQWF5aERvckYyc0pVcG5i?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNVzBGaFlLOG1RZkFIOWRBYnd3M0tDTUU5dXZLWGU2LVBrR2hGaVBHcnFGTV9SYzdwWkVxeGlfenVwcDUyQUlpSnRxTldnREpIRTlpSl90ZEtGZmZ5dG55V2FGMXBaVW9XWE94NGxRN1dLTFZDNFdtVU1Hc1lUVFdyX2JONzBQWnQtLTc2a3NvdkdNT2V1Q2QxQ2RhenJiOHo1?oc=5</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>07-05-2026 20:28 UTC</t>
+          <t>09-05-2026 02:07 UTC</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Alvotech</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Lee Ji Hye recalls failing Korean Air interview after nightclub fame - CHOSUNBIZ</t>
+          <t>Alvotech (ALVO) Q1 2026 Earnings Transcript</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Chosunbiz</t>
+          <t>AOL.com</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOMWY4LVRaTFRjbUE4cEJFaUQ4SkR6cUhVdEhVOXRyS0daUHA4NzRQQ3poVnN5eVZNcEwtYzJwYkVURXUtU3RuRW5EcHFHa2VSZjNWeVdvOXJzb3Z0UkEtdWtFQW5JZG9kZnV4TnUwbkFEcHhtX0N5QW5SQUUtaVJMcjdjS2o4bzZNWFNxREI1N1ExeGRKOElRQnlGV1_SAZwBQVVfeXFMTjFmOC1UWkxUY21BOHBCRWlEOEpEenFIVXRIVTl0cktHWlBwODc0UEN6aFZzeXlWTXBMLWMycGJFVEV1LVN0bkVuRHBxR2tlUmYzVnlXbzlyc292dFJBLXVrRUFuSWRvZGZ1eE51MG5BRHB4bV9DeUFuUkFFLWlSTHI3Y0tqOG82TVhTcURCNTdRMXhkSjhJUUJ5Rldf?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1NTHp4RmJRVXNtRC1nYWMwNlh5MzV1SjhWZzY2ck5VY0NTeko4MVVBWHNTcXhnZVk3NFoyX1M2NVhSbGtiTVZ5aWVmdTRZVG91Mm1qWmNfV1BjY2NJMzFwQVdFVXFwS1AzZ2FPSlkzUDB5VHphdTZCb01lc2x5RHc?oc=5</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>08-05-2026 02:21 UTC</t>
+          <t>08-05-2026 15:32 UTC</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Alvotech</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Billlie drives global buzz with dark fantasy hits ZAP and WORK - CHOSUNBIZ</t>
+          <t>Alvotech Q1 2026 slides: revenue dips 20%, EBITDA rises on mix shift</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Chosunbiz</t>
+          <t>Investing.com Australia</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQYmhheVl6alBTSTVjem9LaTRZQjY5RF9WOGhBNTVDZ2NiNjhZY3FBTVdQbGZaTFU4U0FhbkZCM1FxLThtY1NUZGFzdTVsbXlJYzlWQTZJelFZenJ5bWtFVThuNFlPWG4tNVFldE5BRGJQS0M5U0JMUW80dW1RelhyRGtBYWRPb3VmeHZpZ2FISkJiUFVYTGd4b3dhVmHSAZwBQVVfeXFMUGJoYXlZempQU0k1Y3pvS2k0WUI2OURfVjhoQTU1Q2djYjY4WWNxQU1XUGxmWkxVOFNBYW5GQjNRcS04bWNTVGRhc3U1bG15SWM5VkE2SXpRWXpyeW1rRVU4bjRZT1huLTVRZXROQURiUEtDOVNCTFFvNHVtUXpYckRrQWFkT291Znh2aWdhSEpCYlBVWExneG93YVZh?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPdmZOYlZveWVsQklZNl93RzVEeVBScF9MUnlHeUlxMlRUOE9QY2RLcE5IYmxicm5QblJYSHVsUkhpNUlJUHNEcnc5bnlpMG1vX3FNSVI4V1hJZzgyRVJJczJYVUI1c2UwOVgyVXdTaG5aQm9uS2ptY19sYTlaWmFYekxoUXpkT2Noa0FoV2dMZmlNWkV4WXlHUWZiR3FXb1I5eWFUUkNFdjAwbTJOb1Q0V1lyQWt0TXFqWUJSdXJ3?oc=5</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>08-05-2026 02:28 UTC</t>
+          <t>08-05-2026 12:20 UTC</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Alvotech</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Han Ga-in praises Taean gukbap after Yeon Jung-hoon brings it home - CHOSUNBIZ</t>
+          <t>Who’s Hired? Viatris Begins Search For New CFO</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Chosunbiz</t>
+          <t>Citeline News &amp; Insights</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNSEhwaFk3VnNxNmV6WDBEaUY2XzlNNHFqY3FHUFFyUV9feTVpaWJVQzVwT1AyLXVOaFE3VlhCaU5sakJRSmRfMXFzRk9ER1lkYTJGQkhaNnhxQU80SXRQRnBrWmRiQ3Y5N1ZEclBTTFlxdjlia1VlYTRlWUR0S1FzOWRaeGF1akh5NWE1a0tmd2F3dXVuWjJuX29IenHSAZwBQVVfeXFMTUhIcGhZN1ZzcTZlelgwRGlGNl85TTRxamNxR1BRclFfX3k1aWliVUM1cE9QMi11TmhRN1ZYQmlObGpCUUpkXzFxc0ZPREdZZGEyRkJIWjZ4cUFPNEl0UEZwa1pkYkN2OTdWRHJQU0xZcXY5YmtVZWE0ZVlEdEtRczlkWnhhdWpIeTVhNWtLZndhd3V1bloybl9vSHpx?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxOM2p0ek05bVowRFBiZFU4OExlYVdlMnMtdnNJeXI0LWJlV25EalRyQlhXTUk5N094elpadXA1QWgxd0Y1Nml6SHF5ZTFQdUh1NnB1MDFlLUpTYTV6S2NpanE0RDlXQkZmWS1qSEtsYkVqN2k4MXlyaWsyRmVsaElmVkpGVlhVcFQ0dVJUd0hST05zY1hsbjZTeEdDZVVBbV9rNVgwQnV5aElRdndNcHRCU0RlNDY5N3BScHg4QmVUVDlrZ054cEFsa2FkWUhDcVNzeE83ZzR6Q3dHQQ?oc=5</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>07-05-2026 20:42 UTC</t>
+          <t>08-05-2026 12:08 UTC</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Seongnam seeks consecutive home win against Jeonnam after Yongin victory - CHOSUNBIZ</t>
+          <t>Eric Michael Teva</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Chosunbiz</t>
+          <t>Jomo Kenyatta University of Agriculture and Technology</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPR2VqWUFJYzBnU2s0WnBpNzIzN0Iwd3dzWjZ4dGx1MjNWcWZIakthTXgyamZ1Q3ZUZVF1eVhJMThrODlYVkdJTEVEWUE3ZERzVGhEYV95ZlRJaWJPY0RfUlNzbXpEZTFnRDVtWV9GaTVjRC1NRHdoSHBfSWVGYWRUdi1zYmhTeGF6ZU9oZUlGQjY5TmvSAZMBQVVfeXFMT0dlallBSWMwZ1NrNFpwaTcyMzdCMHd3c1o2eHRsdTIzVnFmSGpLYU14MmpmdUN2VGVRdXlYSTE4azg5WFZHSUxFRFlBN2REc1RoRGFfeWZUSWliT2NEX1JTc216RGUxZ0Q1bVlfRmk1Y0QtTUR3aEhwX0llRmFkVHYtc2JoU3hhemVPaGVJRkI2OU5r?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNVTBmUDFfdUpDMk1VWUJ5aEV2SXpPZlVUd0w4VmEwNWFELW8yZWNFVHkwbkNaY0cya0JTalU0ZFhuUmxZRlBzb0VnSDBGNUd0UHRLZTFKR05xUnhpeTlQWi1NZnFuNzd3YnNXNHlMWWQ5RS1jdGRGbGZXWHZEY09tVmphMmk0aFdBWnc?oc=5</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>08-05-2026 02:28 UTC</t>
+          <t>08-05-2026 14:14 UTC</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo takes $610M profit hit linked to ADC manufacturing overbuild</t>
+          <t>OmniAb Q1 Earnings Call Highlights</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Fierce Pharma</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPdGY5SFBfV1hyN0R1TUxMdkp3a3RJS1VXM1Vzal94YldVMUQ0SzZrdzVzZ21JODdpRnBjODY0OXlSLS05TzlkS3A5VVk1MFp6SW1NU2VzdGhGcDJpSUNiNUQ4SUluT0JfMUdKQUttRzhQRXVOeWZDWVEyN09UTDh0UkpxbWtOWGd3UzA3VjNMekZCNFpQSlpPR0VGV2I0NEpkSTJmaDdaRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOTzF2OFVWa0NmWVUxZWZUX2tVbEtsenF1SkJKVk1jclRmUFUzZzg0TEZTVFZwRF9SSy1hR3hnbHc3UktYUmtVaWJNUWZLQVBfRG1NZUhqRnJGa1d1UVFoblpheUJ0RDRWZE1rdzhaeUM0U1NXblNFbHA0OThJTzI3MDhTbG1oLXVtOHZiZTNVOENIcVVodWlTSjk2RQ?oc=5</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>08-05-2026 14:47 UTC</t>
+          <t>08-05-2026 11:07 UTC</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Daiichi's ADC miscalculation leads to compensation of over $480M to CMOs</t>
+          <t>10 Walking Shoe Sales That’ll Make Long Days on Your Feet Better</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>FirstWord Pharma</t>
+          <t>Good Housekeeping</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTE9wWmtjeTRjeFIzbDlqeUhRYmpEcnFMRWRxNmZjOG40T01SVEUwVFRLeURlUjFORGZOdjM1emw0NEpBeHBoREpuZVhoYTZFMzZwTmxJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQWlZob0JzdzR4c3FLSVZudWpVMTZlSWtCX1U2T2NRWXBrTzJ0VG0zSWJkcm5LMTZNeGN4WVlBNGJoMGlhZGVDcUpfdmF0ZXNjM0ZjREF3LV9lRjhyLThnU0N5blJRbHplOHpzZmUxX0c4b3BKY19CVlZwckp2Vm55V0IzbF9yU3RHNTA0LUpHZkpjaHM?oc=5</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>08-05-2026 15:30 UTC</t>
+          <t>08-05-2026 20:42 UTC</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo – Cleanroom fit-out for the fill &amp; finish area</t>
+          <t>Who’s Hired? Viatris Begins Search For New CFO</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Cleanroom Technology</t>
+          <t>Citeline News &amp; Insights</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxPQndjUGlfVVY2QWw0eWFrSUFEUW5ReGw3SlVIUFlMUnFHRGl2bjQxVVhnX0ttN1VQT0dIZkZHOVlVWGY5Sm1aSjVObzJiSEhkOWhnRjZXUFJ5OThKQUlWODBOSS1rZllEeHlzbzRnMXNobHJfTXk4ajRiQ0hpOEtHMFR3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxOM2p0ek05bVowRFBiZFU4OExlYVdlMnMtdnNJeXI0LWJlV25EalRyQlhXTUk5N094elpadXA1QWgxd0Y1Nml6SHF5ZTFQdUh1NnB1MDFlLUpTYTV6S2NpanE0RDlXQkZmWS1qSEtsYkVqN2k4MXlyaWsyRmVsaElmVkpGVlhVcFQ0dVJUd0hST05zY1hsbjZTeEdDZVVBbV9rNVgwQnV5aElRdndNcHRCU0RlNDY5N3BScHg4QmVUVDlrZ054cEFsa2FkWUhDcVNzeE83ZzR6Q3dHQQ?oc=5</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>08-05-2026 11:30 UTC</t>
+          <t>08-05-2026 12:08 UTC</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Manufacturing hangover drives Daiichi Sankyo into the red</t>
+          <t>Why Every Disney Adult Is Buying Tevas From Amazon Today</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>pharmaphorum</t>
+          <t>AllEars.Net</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxQWWtOdXVOWjFyOS1QUmttQ25DdThPY1d6TVBpdVByV09qbnZscHZJUlJQdlc4d3lFcmJmZ21odVd1am16d0ltU0hIN2hlZWw1VWxMcXd6NDhPSVNfMzBuVVF3bVh2YnUyU09fNGRILTAyTFRXbmx6TERpN3VoMWJKZV9Jckc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPZjVOcDN6TVR0SENpUHJSN0UwZXJBX3o2SUlkSHI2RGNNX1d2VGk2TjhWZGdZZWQtNW5JVXY0R1VOb2VsTzZleWg0eUtuVUtoMWtFWnNQUzJwdFJGdnU3aXdTNjVjV1BTbVRFQXdqOFc0dmdGMTZIN3Y3aHpyM2Q3VnQ2dUYtU0U4SEdNNzFVRW5LQXAx?oc=5</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>08-05-2026 09:10 UTC</t>
+          <t>08-05-2026 19:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo : Listed on the Dow Jones Best-in-Class Asia Pacific Index</t>
+          <t>Sciatica Treatment Market Expands Across North America &amp; Asia-Pacific | Pfizer, Novartis, Teva</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>marketscreener.com</t>
+          <t>openPR.com</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPTFcwLUk0di0xbHhQRHp4Qi10S2szdnI5MFVHWlBlbjJsMXhtWHRqc2J3TC1WN0lQM1k2SnNYZ3RjTXlaclB6dFFrajhnQ1Y1QThETVZ2R3JjVDBmMUhFLXlxSWJfdjlsLVZNWE83bTI3bW5hWVBGRVVjSDB6ZzZ5RldzWDFONy1namRIN1JaZjlieXVGc1dOMjkzWXNvbE5Lblp0ZVVxOUh0RVBuZS1DV1dON0RSdmJiNmwySmVmSGxhdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPcDVHRk9TcGo2SDRsUG81c3hEd2hydVI3ekhNWmo4al9FOG5fTDNzWFJWQkdVOHNZRVJMb1h4UWFOM3RjT1FsUGhnX1gwVGVhZXp4TEpYUHdSTUJpUWJGX2JBdVNlR1VRRnFBc0lGWEU0VzlIb2g5dmhtREJfekFOWTF0c1p0OXpLbC1sNzhmRmJWWkR1?oc=5</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>08-05-2026 07:45 UTC</t>
+          <t>08-05-2026 19:21 UTC</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Is It Time To Revisit Daiichi Sankyo (TSE:4568) After This Year’s 26% Share Price Slide?</t>
+          <t>A Podiatrist Warns This Popular Sandal Style 'Lacks Proper Support'—and 8 Shock-Absorbing Pairs to Buy Instead</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>simplywall.st</t>
+          <t>Real Simple</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxPRmJRTUdBNnpmVkZxWlZEenZJclNoZHRNMUJfRDJNSWNLaHhSSTUtbjExNlhWZEU1eG1jSkVZcXRJMkNzaWdaSERnSUZGeDhzTENNOUItRkw4M09JZThrN2Y2VkF5UjlYc3FnRks0MW1obnhTWnVPTjNBTmRfTnFuaGxyTGY2SVNrbllmcDl4RXVYTjBDY2FYU2pZcUROQzdTT0VSdDFCY1dyM3I0TDVHSnYzWWE1MWZXeTBrN3pCbGlQaWVyZDg4aFlvWlR5bjBfcWp2dU9JOTlJMmNQUVpPS295em9IV0HSAewBQVVfeXFMTmZDOGRmU3p3MEdUdElldVBTalZjTTRtX0w4bzNfeVp1OHNHTTBBVnFTLXFmRlNpWG9zT3BZd1V1YjV2VzlNVXhWWVdYdDNRYTFUdkRqdlRIZmxTSGdLci1ZY3p4Nk50a2pDdjNCRy1OdWJIdm04VzBBdFVtTTB5bW5VU0dJQmlNUC0tSzBKNnp4N280MXRmWnBtdFZfMjZTcWM3ckhkaFZ5Uy16bldkcGxjQmNDUTZaVUlFYmFSTTB1N1JJR3lZUkhRMlpiNkU0bDlMQlM5cDkwZTJGajVoQzBibUhEZm1kR2Q2T1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNRnB0VWtuaEMwTEJPaDBaMncyRGtTV0NoT3E3bU8wWENUUDFjS3RiT0FEaTRSS0ZEQm9lVl9PSDdkSWtRbDFiYmJITEdCenpvckdwc3pLaXpiWDJRODdIcnl2dzNiUFhLZkktZFo4eDVGcjhtT2lVOGVEVEh3c1NEdzJpTU1vTld0SVJCTWhEaw?oc=5</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>08-05-2026 11:13 UTC</t>
+          <t>08-05-2026 10:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Merck : Statement on Daiichi Sankyo Update to Manufacturing and Supply Plan - Merck.com</t>
+          <t>Crocs Shoes Cost</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>marketscreener.com</t>
+          <t>Jomo Kenyatta University of Agriculture and Technology</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQd2w0T3UwdXY1b1hNem1Dd1d2N0U4WURZNVdOV09BZi02TDJ4OWF6Y21GRnlsN2FmV3lHSk5xRjU4TE5EdGY4MUZNRnhsNWgwb2N5aHZhM1NST2ZBdHk4S2pMVWh1NVhUN0EtTGJGb3E5dXA1LU9HcllyNzB6eExJdjJVd2hPSFhkLXRzRERKNlAxVzZId0F2bkFRM2pYdVhCWktBRnpTaVJDZDZ1OW5uVjNXQ0pnZ1RLRU1TMFNfQkpsTkZLVGFKWHNaV3hZYnVlZnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPUDdMTG1sU29saENmcEpST2Y1aEZSZnJsZUFBTU1FWmY2b2dMZnBNUXB0LTdNbS1DNEhoSUNoOHRpc3d1emJVN0tnZXRXaG56VTJuZlZqWTd6UWFGd2NkUW1ZSWdMZnA5NEd0ZXhLRG5rMXBpTjFHOTVLVUxDSVhYOEZLRmpEakRo?oc=5</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>08-05-2026 10:37 UTC</t>
+          <t>08-05-2026 11:13 UTC</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo : Presentation Material PDF</t>
+          <t>Emerald Coast Foot and Ankle’s Dr. Carl Speer Talks InvisiFoot</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>marketscreener.com</t>
+          <t>AOL.com</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNN0UwVkhBcTM5MWFEam1DaXNMN1ZFMnRBZmNlNDBTNy1QOTMyTkpkYXg1QlBIOE5MYmVJYkRITVBZaTBIQ1hYM0d1YmFqLVk2WmRDSUwxa2hZUXNWTENKUmJfMHVLZjloSmF0dzRkQlU3a0tOMFJBYkt6UHh2RGttYlRiYnJ1dGVEd2pLVzdkZTZoc3dfOTg4bg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTFBLejM2OE50Nlp5RGladmk3djlWNGo3Q1NrWFJkZW5LVGxBeEYxUkNCYkZWY0hLbG9NRmxlYlh0YTYtaWlYd1FWTTNOMjl5TGRSaFpLeFpsTEhHb01JUXNVWG40RDhNdExaNTNXeG5FcDFjcmo0c2c?oc=5</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>08-05-2026 07:45 UTC</t>
+          <t>08-05-2026 09:16 UTC</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo : Announces Occurrence of Losses Related to Review of Product Supply Plans and Revision of Consolidated Financial Forecast for Fiscal Year Ending March 31, 2026</t>
+          <t>Havaianas Latest Design</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>marketscreener.com</t>
+          <t>Jomo Kenyatta University of Agriculture and Technology</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxPa0ZTTDB4NUFBRTVhQld0bkFaNDdwYzJnTThQWFhFY0RaRWR4RnN4WVh0VVRXbjFzZVlZd0x1M1lHR2lSVHc5aUx3ZkJHQ1ZiWE0tOUhJc3R3dGs3X3dDdDJaWkM5Mmw0VmZmNVNRS3VycFJjVjJ6WHZheXNLRjhCUy1vNjQxekFNQW5CRjV1bGZTQXpmTWFKVERCSExCM1RCYVJsbE9DNHZrTzRoSThQQ0J3bWxZQmZNRGRETnpiQ21JZGlSdl9ael85V1JXVklJUnNSNnhpbjBMQkd5UkxsMk82dHF2QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOOHNyb1dMMjlhZGpCX1Vyckcyd3llQ0M3NFpKejJsaXU4MlBVYllESUk2WGkxNy1OSTRPTHBrYzhwUXlNTjgzeEZmMU1mdkYtcFVEb3pobGYxTVFHREpuWm1oVkF2aFFyU0NuQ1o2NDk0N2ZZYXlaLW5BVWE2UmF6bnlGSmFVbkhvRlJoZmdZZ3h1QQ?oc=5</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>08-05-2026 07:45 UTC</t>
+          <t>08-05-2026 08:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo Co Ltd - Occurrence of losses related to review of product supply plans</t>
+          <t>How Teva (TEVA) revenue breaks down and what it means (Near Lows) 2026-05-08 - Verified Stock Signals</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>marketscreener.com</t>
+          <t>newser.com</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxOejZmX1RON0hJMHZ0TFE1eDhTS21fZ0dielYxY0NJcWFSakp5LVY4MDZaWkJsbExocHk3aVdZTk9WTW5CdnM1c0FKM1F5UkdCd21QemFBTFZELUZGd2xob1ZoajQxSEl6eTdMN0V4X2k0RjlSRVVyc1hIc2ozYnZVS3MxQThYZGxGODhXb1llaENPd3hHNGRhSXU3cElZbVgwTEFVblFPOXlDM1JzUDRmRjROVktTUE5zUVhtUEFHNTJ0eDNXQTV5UktvR3c3eEdtRHFr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNeTMxM19VWXRKbS1yTkdvajFEOWRxYWRYejNmdlZudVhCb0FlMGNzanZyUTgxdzNJM2ZCcWM0UjR6MHVXYzlVbGRvZzhqb24xWHdqOUQtc0N5bmhkQnNGaE9HOGFDY0x3dXE2aDRYTjZHWkFPS1ExblduYkQwcjlLcnIxc2hjQWpZanAwdmpiRzUyc3ZpVG1SM0JDNWtIWnpyZHdYTG91dHJIMzFIb3VLSmhqNjV5S2c?oc=5</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>08-05-2026 04:09 UTC</t>
+          <t>08-05-2026 08:43 UTC</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>Samsung Bioepis</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Kyowa Kirin (TSE:4151) Margin Improvement To 13.5% Reinforces Profitability Focus Narratives</t>
+          <t>Semaglutide Biosimilar and Generic Market Size, Share and Latest Trends 2026 to 2035</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>simplywall.st</t>
+          <t>Insightace Analytic</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxPRGxMN3Q1RVBsbnFsN1Nja1JtaVlVclBCNUtSUWRibEZOYkJkYUZGS2Myc2I3eGw4NEREZF84SnpHajRTY0hDMG1kWGZURTR5TVVOLTV4UW1zOUM0U3pEX3lrcDNTbVNmUFRhWVFldFVjWWp3VUZ1SGdxa1Q2dU1Cc0lCNGJiTHVfWnFFemZMdVVyWlNFbzJIR2VpekJJZFRqUC1PbmRKcEY5UWhoNldHVzNJTExSNFRsWS1vMGtjclVncWtRVGFvM0Q4WGREc29hVUFSZ0hFSjI1Y0Rtblg2c3pVSFB1alFT0gHoAUFVX3lxTE9EbEw3dDVFUGxucWw3U2NrUm1pWVVyUEI1S1JRZGJsRk5iQmRhRkZLYzJzYjd4bDg0RERkXzhKekdqNFNjSEMwbWRYZlRFNHlNVU4tNXhRbXM5QzRTekRfeWtwM1NtU2ZQVGFZUWV0VWNZandVRnVIZ3FrVDZ1TUJzSUI0YmJMdV9acUV6Zkx1VXJaU0VvMkhHZWl6QklkVGpQLU9uZEpwRjlRaGg2V0dXM0lMTFI0VGxZLW8wa2NyVWdxa1FUYW8zRDhYZERzb2FVQVJnSEVKMjVjRG1uWDZzelVIUHVqUVM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQckkyWlpVRUgwWk1lSWF4cHVjZE13TWpqdk4xZnotYVlPaGpNdGI5djdSaDBuSnJmS3NtVF9SUXNjeThBMFlLdDhBcktrb0ZlMVhTa2FfRXRPekQ3MTBtSE9PUEFBUWJqMkZDRk5vQURfZDRMVzQ3QU5jN0hNYTI5SjZlUGc2SnhLbktYcnB5cFFtZw?oc=5</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>08-05-2026 08:59 UTC</t>
+          <t>08-05-2026 14:27 UTC</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>Samsung Bioepis</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Kyowa Kirin Co., Ltd. 2026 Q1 - Results - Earnings Call Presentation (OTCMKTS:KYKOY) 2026-05-07</t>
+          <t>Quotable: Words Of Wisdom From Our Recent APAC Coverage</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Seeking Alpha</t>
+          <t>Citeline News &amp; Insights</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQXzNlQnpLa3A5RGlId3U0REFCUTlfZ3U0TGZkSE8xd3pGQlZxQmNnX3BrcFN4WDVKeF9FNHBqYzhPWmJ1ZXVEUTRzNWtFcVc1R0Nkd213VlU5YnlRZWotOTdwSlBtZXNONE5meEtJell1MEgySzV5MVhFb01BNXVwcXlLVVB3RElKcnh2aXVSaDZQTmQ2MmhUWlVSalhVS01sQVd4MllsTUt2VXM5VjFwdFF2MHhRdnlseWF6RjhJYkVaelQ0NFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNWk54R1plQ3AxU1V4UWhFNzhLSmNWQnZQdnI0TUwwQzZZX3NrR3gyN1lGOXJ4MVI1NkdIb0N3N3lqbXlNZGN3OU42SEpjSE44OWNBbmplMzcyNV81eFdXV00zREFSVFdjN2I3bWZQbEljZDFydXEtLXM2eWhBVzJ1bDlwWnMtQkNkazhBOEtBYy1nVFdEZWlqUHBqRmFxQ0p6UjJTVEFsRTBHc1hqLXNsem1Ebm5ySm83Q3lRaFNMXzhWN2pxQWFCc3piRzU?oc=5</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>08-05-2026 02:48 UTC</t>
+          <t>08-05-2026 08:39 UTC</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>Samsung Bioepis</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Kyowa Kirin Co., Ltd. 2026 Q1 - Results - Earnings Call Presentation (OTCMKTS:KYKOY) 2026-05-07</t>
+          <t>Deal Watch: GSK Calls On Halozyme’s Enhanze In Cancer ADC Administration</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Seeking Alpha</t>
+          <t>Citeline News &amp; Insights</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNWEtCOEpfZjk1VEtvLVIxVHFKWXc5R1JTR2FOZ0s0T25CZVloeVBBQTdsc1k5RG44TFBzYUljUzdGUlZQOGRjTHMxZXdrYzFqUG5LbUJUVzBnQ3d2cWVEYWlDUkNGcWEtOGJYcGk4cmprMl9qMXZyVWphUjVRZUdEb0UyalQyWDYxUzc2c29hZ3JsQmxSZnBwSEdqMHc1Q1FMdEUxQw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxPY2dPMkt1YXBoUzV6dGs3UzhhYmZNTExNUG1PNzdtemFyMDIwS0FnaGlZME5VUUZkSDNVQnFxdGhjcV96T1AxQTlCcUZXMU1oWmFKelBjOHhYLVdPT09oR0tHMkFOeTBVVnhkNjREcG52dXNrSlRxTV91NDd4cVRTZ1MxRVlwdGNISXRzVTJtNmhGQ0ZzeHJpeVlrVkE5SldVa2t1Y0tuWWFpZXRmamxBMkNwZzRuNlJ6cGtpVEc4ZE9NRGZqcTB4bFEtc2xrdDVwcFVrZHNrTno4WFZqazJIRTQtR2VwLWppQ3I1Y2NjMnAyUmlFSERfOU1R?oc=5</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>08-05-2026 02:48 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>Kyowa Kirin</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>Scleroderma Therapeutics Market Size, Share | Industry [2034]</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>Fortune Business Insights</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxNanc4Umt2b0Vfcm9xOTExajNVVGFrOF9aZFRnV1hUaWJha0ItODZwTW1PMS1VTHVqa0hyelcxYWtVQlBEdWRTWXZHc3ROLVJONlVmTFp0QWRBempxR04yOG5JY3pyUDczYy1wUmlyNG1kdGtfWlROalV1Yk9yMDhwNURyd0U?oc=5</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>08-05-2026 03:29 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>Kyowa Kirin</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>Ohayo Japan | Wall Street Retreats From Record Highs as Oil Rebounds on Iran Uncertainty</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>Smartkarma</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQWlVuRkF4NkR2dTZLQ3RDUmpiTUtaYmV2c0RGaHA1cEtRQ2kyc2JjZW1VRVcxQkpvSmRVcVN5a0NwMjhFbl9paDBqdlEzUFNjUWNyX1hvcnAzYnZFQl9pVk4tbDFObkdxU29LbzNQWHFBM3ZVRkdzbmJUY3NSQWZDUFdNVmdJTjd3YXJVenBERGU0Tm8yaGxLaC14SHlVcnRUbnNsX1lIb09UY201Ul8wNlN6TmtXdGZYUFRPQTlnSjlwakdLblZtT3QzMV9fLXptRnJoSTJtc1paalFRM0lpY1JKRW5yS2lw?oc=5</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>07-05-2026 23:11 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>Kyowa Kirin</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>4151.T Kyowa Kirin Earnings Miss: EPS Down 16%</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>Meyka</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE8yWUdycjlEU0dYdkNoczQ4NWNXZGRTRDZrU3lzZHRyV1BHSUt2SHprQTZVcWhDNDNCcFdTZ3dBSjA4N3RxNW53Z1phektXdmNCazJRSG9BS0gtbHByUjlsSm54RUFEbERaaWZ1NzZ5X0dlS2NnUzdkcjdjSW8?oc=5</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>08-05-2026 07:56 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>JCR Pharma</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>Acumen executives take Bank of America health care stage May 14</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>Stock Titan</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPNVpac1B4YUNpUmFoVjlFamhFdDNkTnU3QjZtSmN0SVkzUTNiWTVGNUpQZVZHcTBIN1F6YkZEdnZWVFdqTHYzUHRxU2VCVnpteTdFMHRNZGlSUHZwei13a1ZBTVhlRmMySDNhZEdjZjdqbnhoNURUYzNvWnc3QUc2U1p3bk15R1B1QWtBclRORnE0VVhYT2lVc21xU19EWUhpcFd1Q1N2VGxnTG5zd1BxZzNRc3pzUQ?oc=5</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>07-05-2026 20:03 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>Mochida Pharmaceutical</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>LG Chem launches progesterone injection Eutipro for infertility treatment support</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>koreabiomed.com</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE0yS2hDc083Rl9nRDhERU0wNzdqVFRnc0Ixd3c5VU12WmRuLWk4UEczZ3B5Y2pPRXFOSHpTanhFVno1VnZfUHN4LXQyR0FQYm5xZnk2Ynk1UWNtVlU5dEozY0ZEOFRMSUJpTXpUcFp5SDVaUdIBckFVX3lxTE0yS2hDc083Rl9nRDhERU0wNzdqVFRnc0Ixd3c5VU12WmRuLWk4UEczZ3B5Y2pPRXFOSHpTanhFVno1VnZfUHN4LXQyR0FQYm5xZnk2Ynk1UWNtVlU5dEozY0ZEOFRMSUJpTXpUcFp5SDVaUQ?oc=5</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>08-05-2026 03:07 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>Fresenius Kabi</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>Fresenius SE &amp; Co. KGaA stock (DE0005785604): Healthcare group eyes growth amid restructuring</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>AD HOC NEWS</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPTFJUb2hNMG1QVDNjYXZFMWY3VHNfOHdKa1BaS1pqNGhzOXhmZlRRZjlfSU5hZWN3VGZwRFZwcnROSUYwbmZ3a3FKaEs2ekZWd283MWs4QkFETWc3SWhJX3R6Z0dOS3gxa3BWZFJuR2ZyS2M2bEF0YWxjMEQ5NXBhaUVpMUFuMjdXaHBBSnpEanJjeTFXWHNFcjVYdmxQLTlIdUZrcThPeWlQRVJjY0ViZHVGOUtDWXdoZDJMRXpRS09sUQ?oc=5</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>08-05-2026 11:57 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>Fresenius Kabi</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>Caplin Steriles Gets USFDA Nod for Generic Calcium Gluconate Injection in Multiple Strengths</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>ChemAnalyst</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQVDJNREZxUE0zR1laMXp2REg3ZzIydG1uVklZazlGLUdRU1dMYWhCNk9PX3FDZW1MWjk5eDZKeWs3YkZSUDJ6VlRuUmtOMTBNb2FFTVZSbThKWUZyQmoxZ1Z1S0RjU1lKTU5CaTZXVFFaamNKem9RSGpWQ3JHQmlnbzh6bldkaFdBWVotYy1UMHJSRVd1WmJWb2tRMUxEaXpUUmN4VFZSOE12bFB3WXEzekloaHZYYzA0bGN6SnZMV3NINHJyR1o5aw?oc=5</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>08-05-2026 15:53 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>Fresenius Kabi</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>Semaglutide Biosimilar and Generic Market Size, Share and Latest Trends 2026 to 2035</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>Insightace Analytic</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQckkyWlpVRUgwWk1lSWF4cHVjZE13TWpqdk4xZnotYVlPaGpNdGI5djdSaDBuSnJmS3NtVF9SUXNjeThBMFlLdDhBcktrb0ZlMVhTa2FfRXRPekQ3MTBtSE9PUEFBUWJqMkZDRk5vQURfZDRMVzQ3QU5jN0hNYTI5SjZlUGc2SnhLbktYcnB5cFFtZw?oc=5</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>08-05-2026 14:27 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>Fresenius Kabi</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>Who’s Hired? Viatris Begins Search For New CFO</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>Citeline News &amp; Insights</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxOM2p0ek05bVowRFBiZFU4OExlYVdlMnMtdnNJeXI0LWJlV25EalRyQlhXTUk5N094elpadXA1QWgxd0Y1Nml6SHF5ZTFQdUh1NnB1MDFlLUpTYTV6S2NpanE0RDlXQkZmWS1qSEtsYkVqN2k4MXlyaWsyRmVsaElmVkpGVlhVcFQ0dVJUd0hST05zY1hsbjZTeEdDZVVBbV9rNVgwQnV5aElRdndNcHRCU0RlNDY5N3BScHg4QmVUVDlrZ054cEFsa2FkWUhDcVNzeE83ZzR6Q3dHQQ?oc=5</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>08-05-2026 12:08 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>Fresenius Kabi</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>Caplin Steriles Gets USFDA Nod for Generic Calcium Gluconate Injection in Multiple Strengths</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>Medical Dialogues</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxQYk1xeHIzMURYeGJKU3RIUHM3eDJRdXhmamhyMXgtNVE3LU1kLWNEaHRQUFhFNmk0WEpDVlNzczBDQzBpUkYxeTVzaHY3NWxNSzR5a0FucjNub1IyTXRWd1ZuQlV4Wk1SMkZnd193STloZlp5NzlZTmdMWFNta0stYW5MYjNJcDdwOXlXX3NQS2ZEYXA1YjBZN2ZlX1lfZHYzSGZCSXRmeFhjbGRZc2RlR281aG4tS0JxeVFqYWhBaTNEZHlGQ291ZXJXNFBZclVQSjZpbjJncTY5TTFmQmhCVHln0gHnAUFVX3lxTE5PUGpKTDlMd0RYOFJqNmswOXpWX09XOGpBSi15X2ttbzNERTM2SUY4bmtGWmpXOGttZWxhLTZ6d2pyVVJ0Ny1DSkJsSjVuMzA5a1l0YzhlQjUwVF9rY3Vnd2gyc0pURXB6OUJha3RmMEpXQjBiMGVUTFk3ak54RE5XaW9YbUhsRDd0VzZzMTZPam1NNlBDWWs5S2NTYlFpU25wdEJUZ1FfOGlTWGZRZjFsX1JUUW1EVVg5bW1VZVJkaFBsSVBxYnhIWHRJc2FRSk81YTMtY0Nic1BnbWtOLWtabVQ1WUdWWQ?oc=5</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>07-05-2026 17:45 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>Fresenius Kabi</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>Infusion Therapy Market Is Going to Boom | Baxter International, B. Braun Melsungen AG, Fresenius Kabi AG</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>openPR.com</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOSUQxSmFjRG9xUWJPSXhGMzhYVnkxNk52dXNvalRVSG1FNmVFbkRMY2FQSnBjcGZfMDRWTk9sQVN5cGppY1hDcjFVeHdFWXpaU21wWnlGTU9KdGZHOW9xMncwZXEzbl9OWE5Qa01QY2VnRk5Bdm5fTVFSZ00tMVFZQmNTckhhdzlBWE9BNi1yTXktSDV2MzkyX3Y2bE9rZw?oc=5</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>08-05-2026 11:31 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>Fresenius Kabi</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>Global Local Anesthesia Drugs Market Grows in North America | Pfizer, Aspen, Fresenius Kabi Lead Demand</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>openPR.com</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNZVRYbW1xdEZKZEdKdm8zWXRxN1pZZnFMS0QwQUZOa1VtQ2sxa1o0TlAxQzhLZFpFR3k2dmhTRUZ0UmNfV2RQaTM2bGRGVjVJOXJYV0s5QnVaUU45MVdyV0JkYmdwcjBjamI2emZGTXBjUExvNGhuZGRYQlFueVd0dUhFQ3hFd2k2MWd4RmVmeUd6dEl6VmI1Ti11bw?oc=5</t>
-        </is>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>08-05-2026 08:03 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>Fresenius Kabi</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>Blood Bags Market To Reach USD 956.4 Mn By 2035 | Healthcare</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>openPR.com</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPYk5UeERzX0xWbW1Lem1IcWwtaGpvTDZsYV96Q1ZRSnRhTGIybC1RWlRsNVpkMmRQM0gwX3ZmNXdfYWwzZWhuUHJxdEtTcjNZU0x4U3ZvTVVacEplWE0zSzVvSGQ1QXdYcXlBdGs1ZURTSWRfeXM1WWVOUDFkdzZscWs2ZDl2SHlydnZYak9TYUNUOTQ3cGFKSDFR?oc=5</t>
-        </is>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>08-05-2026 13:41 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>Fresenius Kabi</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>Dysphagia Supplement Market to Reach $2.1B by 2035 at 7.5% CAGR,</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>openPR.com</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNczBsajlmWUpuN3JKalRwRWtpR0czOFRTcm1Bd0xqdVR6SUdRWTIyUGxKWVdRQXZ0SWRVbW9RNHh0MWt6QjIwNWtNb1JwaGdTdjl4SUdWZ2Z5Z0FEUk9uZndOS1pJWDlRSXJtS2ZBV3o1TjNmYzVpcFY3TkVMUDRld3hyaEdFSEpVVUhIMFR1R2d2WUJ3QkFlMGF0dVk2dw?oc=5</t>
-        </is>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>07-05-2026 16:23 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>MS Pharma</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>Sun Pharma shareholders approve postal ballot, appoint new independent director</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>TipRanks</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPeklUY2tPZ0NGQTUxeTFEUGdOZmRCcXhIV3BhdDVpYnB6RGo3MldKakM2YUM2QVFNZVBYZnJqMzRJYWdIMThKLV9DWGZMeGE1cDZXUXRPTm1vejlZMFAyWV9scWZOaHRWV19nRnl2OWVHZDJPdXFHRDJWT3RGbGVESEtVd012THUzWEc2NkhSd1JkQzVJeWpONjUybnRMRzh4clBtQTlSVWtSdm9Xdkx4b001QXBSbnZ6YXlpZ2FITDVvZlVDOWJON2pR?oc=5</t>
-        </is>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>08-05-2026 15:19 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>MS Pharma</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>Mississippi to receive $41 million from settlement with defunct pharmaceutical company</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>SuperTalk Mississippi Media</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNM01xSlowWWlzYmpXLXFNZ2tnN3FLMTd2enhRcktmS2pfc3dEc3Z2UF9tUmYyWFYwb08tcHgyMmQtYXQ4T1JBOWNJNjFGRjRxYmI1VTlXOXVERXpoNXhpQ084V2hkTmRRSHFOeWZJXzdmTkxvX293WEV1U1Zlc3JPQ2hzVDJrU24zZldJUUsxc3RaM2M4Q2hXVFdYVU9CZUJmZjFVSFNNVXpZMnlXWFl0cg?oc=5</t>
-        </is>
-      </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>08-05-2026 15:40 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>MS Pharma</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>BridgeBio Pharma: Q1 Earnings Snapshot</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>theheraldreview.com</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOSWtNejdrek1QbVpuUWJtWWgxUTBZUWl2SEhKVWJnU0QzMlFTRThfVzVvN2JGZGI0MXljZ3FiSWN5V3ZBZmpLVVl6VTN3cnlmWExrNkZLdFg0RDZzbHdJLTNRcGlwbFF3QTVsM0ZDdTcta1c1YkZVeG5ncERjR04tNWR2R3dEb2o1dDU1Wnc0U0RaTVRyR3BTUjhzbmxkTHhX?oc=5</t>
-        </is>
-      </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>08-05-2026 09:08 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>MS Pharma</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>The winners of the 2026 PRWeek Healthcare Awards</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>PRWeek</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxPZDVBSHZKdVJZdDBNdy1WUE82c1d1LWhyZDlLSC1BbVJUb3FDMlc1MG5Gc3kzOHRNZDBNcG52ZW11Q3NIdTZucDA4Uk9vYnZNZ0hsWUVhUk9Lb3Y0QkpOWUN3SUY0TTlobTNnQ0Y4c3NESmFNY09EZEFIWGVuOEVRZjNR?oc=5</t>
-        </is>
-      </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>08-05-2026 00:32 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>Alvotech</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>Alvotech Q1 2026 slides: revenue dips 20%, EBITDA rises on mix shift</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>Investing.com Canada</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQQVJIODRkT2tUdGZTWUZaRk9NQkcwZXJubDNTUWpsUVY0bG83blNwdGdJbHFVemkyblIwQW5EYV84S0JBTkwyWGp6Q3NpOURxWHBTVWxRTDc0Y0lDNVRoVXYtWlNuSmJvMkF4ckU3Z21mSTZIWVRYM2duamVKM1FtUnVYSnZ3d2l6MmVwMm5EYVFJR2syWDhHZDNZQWlOWjZSR2RyNXh0alA0RUJiWnRmRFZJWmdsdFVGQ01EODdn?oc=5</t>
-        </is>
-      </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>08-05-2026 10:27 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>Alvotech</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>Alvotech (ALVO) Q1 2026 Earnings Transcript</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>AOL.com</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE9NbWUxOWZRZUtiRkVIa3FWelZCbTBkOW5kX09qVFF2c0ZjT05QdFdmYTd6N2FWMWFmUzl3UlZHVm5ycGl3Nm9XbmRjdU1EUzdHQkc4bkg5ZkduV1lIWmxYSjNYcjNsWXZ2WEFSc2dTaHBmdXlXWlV5LUdEMUMwNnc?oc=5</t>
-        </is>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>08-05-2026 15:30 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>Alvotech</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>Alvotech’s Earnings Swing And Counsel Exit Might Change The Case For Investing In ALVO</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>Yahoo Finance UK</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNZXNlckJpZ25BajhXWlJQVU0xOHMwaW5YTlVZRXMyNnBKUGFwNkN6bGlpQUhsNHVabEZUMGFpR1k0bzFvZVhEdWFqSjZ2dGxSRmM4UTRWQVpXZkZXcURGdUxmVWY4ZGF0N3ZIOVZrV09lNGhVc09nOGhySTVZTWh6MWhPOVVBSWx0QW1jaG5n?oc=5</t>
-        </is>
-      </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>08-05-2026 03:15 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>Alvotech</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>Alvotech (NASDAQ:ALVO) Shares Gap Down - Time to Sell?</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>MarketBeat</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOZVVVQXlHM2xwY0EwNlVSbW92UlBrRjV1YmlmUm41dmpfYTFHT1lDR3lzb3k2eTlHaWhSSGgxT1pybXhMcU91MEpfLVhKd2lVYkREVE9mRDNMSkxHZU9ZdFRZcXdLd0dGSzhQLUk3dUxTOVhIaXZHcE54RWUtUU9taHJCdHZ5SGR6Q0VuR2p5amhfSzZQcTFaaURfZUNhR0h5cnItWA?oc=5</t>
-        </is>
-      </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>07-05-2026 20:21 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>Alvotech</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>Who’s Hired? Viatris Begins Search For New CFO</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>Citeline News &amp; Insights</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxOM2p0ek05bVowRFBiZFU4OExlYVdlMnMtdnNJeXI0LWJlV25EalRyQlhXTUk5N094elpadXA1QWgxd0Y1Nml6SHF5ZTFQdUh1NnB1MDFlLUpTYTV6S2NpanE0RDlXQkZmWS1qSEtsYkVqN2k4MXlyaWsyRmVsaElmVkpGVlhVcFQ0dVJUd0hST05zY1hsbjZTeEdDZVVBbV9rNVgwQnV5aElRdndNcHRCU0RlNDY5N3BScHg4QmVUVDlrZ054cEFsa2FkWUhDcVNzeE83ZzR6Q3dHQQ?oc=5</t>
-        </is>
-      </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>08-05-2026 12:08 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>Fuji Pharma</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>Full Amount – TSE Stocks Eligible for Japan Securities Depository Center Margin Trading (3) (4439–6305) (Application Date: May 7) (Settlement Date: May 11)</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>Moomoo</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxNcEJUWng5RkVmUTV6a1lLLTl4NFNZQVV2XzJudzJodTVaRk9tVVItZDlYN2VZUkhZYUlyQkNXRnJzeE5IN3g5MDZWMkhacnRNZDNKSkluZjZYMkJEa1gtVHZWX3NLbWdyMjEwNWk5UVNqRTVWTVpzY3NESm5LeFBnYUpDSUtIVXNfV09jcFdXaVZzMVNGNWlvaF9nT01acUJmNTFMX2NNY0h0SzRJemlsNDFuc3FkcTNpOXZ5Z2djTVJwZEc3Tm9ucGhUdGlJQXB0ZVZZWkdidnNDWVU2OUl1ZA?oc=5</t>
-        </is>
-      </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>08-05-2026 08:03 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>Insider Sell: Amir Weiss Sells Shares of Teva Pharmaceutical Ind</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>GuruFocus</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxON19HYXJ1Q1VmdHdGYkFGTTcyZldrclp5SkhmY2hZYW1CMnNob0xqQUlJOUJkTzgtVkNuWGVwbkFRQ0NGVkhpcDVOY3cwbWkzUTRWeHBhX3BMQUVwazUzUTRaOUd4eFVRYUl0NWFfYzBhOXM1YnV0eWpOWmJmaFRsMWNpLUs4eWt5ZXRJbmo1Zm8yQzRGNGZmdngzczlJd0Q3V2pGTG4yMzRWckM4dWtFLUZlVkN3aEl2VEE?oc=5</t>
-        </is>
-      </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>07-05-2026 22:34 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>Teva can pursue monopoly claims over rival’s ‘exclusive pharmacy deal’</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>Life Sciences Intellectual Property Review</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQQTNnUFVOTzhtN0RkNnBSQzFPWndBZkV4SGJIeFM1QWYweVdXYU9HUS1fX2NrSkVFdWFtM0RjNWxtNW84NG9aZVU4TC1VaUVfMzZJekRpTFdaQ3VETEpPTl82UTZPcG5ZMDE1SVRFREhFM1pEaFRwWUdQbmxhLUxMQXdCTHQ1VFAzcFVhS2ZLYTdUX0lhbVpIbGdaUXNJOXZQMEwxYUt1N2txSWt1aWtaZkhDaw?oc=5</t>
-        </is>
-      </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>07-05-2026 21:04 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>Insider Selling: Teva Pharmaceutical Industries (NYSE:TEVA) EVP Sells 30,000 Shares of Stock</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>MarketBeat</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOT2tvNHJnZm1iOHBtbXhaLUl4MTdRbVQxUlYtbVlaOFZ2TFRBajcxX1JkZU5DbExOQklVRXFfQVE5c0JDSktTTExwS0VlQ01zWEJZYXZtSjZyaEM0S3BrNUtkZzVYWVkxQmtPRDczMWZBdlRnY2tON1c0RUVIbEhfZzdLdnBYNWIxMTM0dDk2a3ZBM3h6QXROa1JXUUdSM3NzWHY4VHlwWlVQbTlBWmRpSHlpVjU4Y21LWUJEeXhIWWZPUWdlNG1CYWhjcU1XU2xlLUNmc0NSSFI?oc=5</t>
-        </is>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>07-05-2026 20:21 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>Who’s Hired? Viatris Begins Search For New CFO</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>Citeline News &amp; Insights</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxOM2p0ek05bVowRFBiZFU4OExlYVdlMnMtdnNJeXI0LWJlV25EalRyQlhXTUk5N094elpadXA1QWgxd0Y1Nml6SHF5ZTFQdUh1NnB1MDFlLUpTYTV6S2NpanE0RDlXQkZmWS1qSEtsYkVqN2k4MXlyaWsyRmVsaElmVkpGVlhVcFQ0dVJUd0hST05zY1hsbjZTeEdDZVVBbV9rNVgwQnV5aElRdndNcHRCU0RlNDY5N3BScHg4QmVUVDlrZ054cEFsa2FkWUhDcVNzeE83ZzR6Q3dHQQ?oc=5</t>
-        </is>
-      </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>08-05-2026 12:08 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>Teva (NYSE: TEVA) EVP Richard Daniell sells 30,000 shares in open-market trade</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>Stock Titan</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxPSnhoV1MtclpGM0JJQ19RWnh0djJkMTA4d19FM1ctXy1QeFZ5MGhMQ2ZzVk1IYkZoMHpNNGdCRlQtZzN1U1RMTTF0ZVVyN0J0Y3g2ZExYSU44ZWJOSWktYm94MjVXUUdFenpKUU1vOGVNWDNsUFlPaE9LV1M5OGJHYi15aGE0aVZGN3FUOUxDWV9jMkZ0bUw2SjZmUUxJX3ZaLXdKVXJSTUlQenJ2WDZmSlNqVFpaamtpWll0Z0RXcTQxcFN2X0p3?oc=5</t>
-        </is>
-      </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>07-05-2026 20:01 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>Teva Pharmaceutical Industries Insider Sold Shares Worth $1,062,000, According to a Recent SEC Filing</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>Moomoo</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxQV1M4UUhPR2Q5RnZhWEtvVmtMYzN1VEYzVHZPX2hGUHVQb091eU5OUDFTUWRXZkdBZVgwNC1ITjVBV2R4N0VXVDVQb3BCM1NBajZfUTRzRFBTWmNXaENyLUZNY2dvWk1idmk0LVNyc1NXSzZCN3Z0VmRtNDhfdF9EVWloeU91SVd0RzlBeThEQ004YjlHVTEzM3lyRW1PbE1LYlVoNGlOR1NjTXBFWkJFX3lmb2VtcFctSWFmVUZybW56TE1FaXlST0U0c2ZMTnRlWUJseEgwTmx0NFB6VDBzQThGSG1hNlJROWc?oc=5</t>
-        </is>
-      </c>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>07-05-2026 22:20 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>Top Teva Executives Cash Out in Major Insider Stock Moves</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>TipRanks</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPY1Z6UUgzOVhOaTVSTk53STJ6ZkIwSXNLbDJXTTVBa0xLVXNRU1o2bmljekhySmdmOWFuOEFieEFheGdPcEJpTVBVYWhja2FxbHFFVzd3NmMtV1dYYWpzUl9mT0ZrUndqOWJacEp0b1VOV2loRXE2OWVsQlZRY3hDVHZrNU4yNG9OdTJvVnFsN1h6XzI5TVFneU8xblRncFFSZVJENHpETm92TEtQc3daX2pWd1BEYzZGRnppZjF4clk0UQ?oc=5</t>
-        </is>
-      </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>08-05-2026 02:50 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>Insider Selling: Teva Pharmaceutical Industries (NYSE:TEVA) CAO Sells 10,679 Shares of Stock</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>MarketBeat</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxPazBVY2dfdUtjVm8zeGhYREhmRWptTURhTDdmZS1Ja2llbXozMkkxLTNxR1lNYjd2NTM4OC1sc01yMUFGYnZqd1VXR2hnb2hySjNJS1RtS0VmTlM5MW1PdEU5bUFiSFhaeUhRMFdQNUQzdk9mUllERjEtbHJheThOUXFlSTNLVXpsWGt2OTBIX0RNSDkzNjN6LTYwOUlzc3lSM2lzUHlHZ2w4R2ZuTVhWYzlfQ0pmSVBRVFYxbW5feGFTZDlMVHVXZTN0UHlsa29sYTFaQzh3cGI?oc=5</t>
-        </is>
-      </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>07-05-2026 20:21 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>TEVA (NYSE: TEVA) accounting chief sells 10,679 shares at $36 in open market</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>Stock Titan</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNOEtxX0dIOTdwOG81a0R2cnVMdTJkdnowcWwzclozcnBBMDJ6eFRLZ2htbmZQdzJ0TXFwcFBCcjVyV0xtV3JvMHdVWDVkaEItdG9pSFhjaFotVVpsQUVwSm9ONXJNWkI5TUtpamtyWkZRLW1WX3VEV1lvZHFqbVpfWUktaGJEbkVGMEpaay1YUHFCUnVZMGlrMlN5RnFUS1VQN1BFeGRwQkZTQmFpcDd2dEtNd1FIN0VDMjZtN0pTcFRVdzBjNV9v?oc=5</t>
-        </is>
-      </c>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>07-05-2026 20:03 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>Crocs Shoes Cost</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>Jomo Kenyatta University of Agriculture and Technology</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPUDdMTG1sU29saENmcEpST2Y1aEZSZnJsZUFBTU1FWmY2b2dMZnBNUXB0LTdNbS1DNEhoSUNoOHRpc3d1emJVN0tnZXRXaG56VTJuZlZqWTd6UWFGd2NkUW1ZSWdMZnA5NEd0ZXhLRG5rMXBpTjFHOTVLVUxDSVhYOEZLRmpEakRo?oc=5</t>
-        </is>
-      </c>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>08-05-2026 11:13 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>Earnings call transcript: OmniAb Q1 2026 sees revenue surge, stock climbs</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>Investing.com Canada</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQbW8wYUFlVGE1VnAxQ2lyRTNnTXZ1T2UtVEUtMVhnRW1ld2pQTXZ3MjIwNGRQQm1aOGNTZWR4TWxZbjk4MjUtWDZlZVVjMGNfbWlURi1pdXRlYWR0WVJZRlN5Zkx4cnNob3E1X2tJbVpjdEFLbElyTlBKOVpZcjJ4c3RETF9wNi13cThmM0ExQ0pFWEdrZTZ0R3hiMVRpZ19DVGU3LUpFbEp1UkUzTFdNUFB1VzBpT1IyS2pXZmhxTGxKcWJKeU9NZFZneFU?oc=5</t>
-        </is>
-      </c>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>08-05-2026 01:08 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>A Podiatrist Warns This Popular Sandal Style 'Lacks Proper Support'—and 8 Shock-Absorbing Pairs to Buy Instead</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>Real Simple</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNRnB0VWtuaEMwTEJPaDBaMncyRGtTV0NoT3E3bU8wWENUUDFjS3RiT0FEaTRSS0ZEQm9lVl9PSDdkSWtRbDFiYmJITEdCenpvckdwc3pLaXpiWDJRODdIcnl2dzNiUFhLZkktZFo4eDVGcjhtT2lVOGVEVEh3c1NEdzJpTU1vTld0SVJCTWhEaw?oc=5</t>
-        </is>
-      </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>08-05-2026 10:30 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>11 Flip-Flops for Men We Actually Approve Of</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>AOL.com</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE1VdjFQRENDY193eE5yN2gyZkVBeDBicW5NNGZYZ01xUjB2U0FPR0JjTXM3RXlPZ0pWZ1RnMTUxb1JjNWdjSGdDaVRGVUVNYXMzTGwzWGF0aUxkUFNZTC14ZWxJcWVWTmJnTmtTMVQ4NUtDdXJ4UVdZUnZ3?oc=5</t>
-        </is>
-      </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>07-05-2026 19:57 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>Emerald Coast Foot and Ankle’s Dr. Carl Speer Talks InvisiFoot</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>AOL.com</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTFBLejM2OE50Nlp5RGladmk3djlWNGo3Q1NrWFJkZW5LVGxBeEYxUkNCYkZWY0hLbG9NRmxlYlh0YTYtaWlYd1FWTTNOMjl5TGRSaFpLeFpsTEhHb01JUXNVWG40RDhNdExaNTNXeG5FcDFjcmo0c2c?oc=5</t>
-        </is>
-      </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>08-05-2026 09:16 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>Samsung Bioepis</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>Cartography Biosciences Secures Strategic Investment From Samsung Ventures To Advance Precision Oncology Pipeline</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>BioPharma APAC</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxNekYxT2tMV20zSURQNjk1RFlERnM3bHY5RF9mRXplcnA3LXgzODFqQ1dpdXhDeFFySmxEbEdPVFpGN096bHhNNDlOV0E2bXA5VEs0SHpaX3k5Y3dkS0RUU3dVRlNIUDdpUUU3OW9zRGVjbW5iM1psWVRmTG5NYXBuNC1ISTVRZm9fLXl1Mm9WNDZQSFYzUy1XT0RkTzJEWjVOQWdHVFZGT0lEcUJfeEszbXdFUjIzcldUZVZEOGIzTjZjWTN5R092Q1RWTVBtN3hFRG53MmhZNnBoV0Q3TWllZGUteUlQNl9FYi1uRWdR?oc=5</t>
-        </is>
-      </c>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>07-05-2026 23:30 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>Samsung Bioepis</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>Semaglutide Biosimilar and Generic Market Size, Share and Latest Trends 2026 to 2035</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>Insightace Analytic</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQckkyWlpVRUgwWk1lSWF4cHVjZE13TWpqdk4xZnotYVlPaGpNdGI5djdSaDBuSnJmS3NtVF9SUXNjeThBMFlLdDhBcktrb0ZlMVhTa2FfRXRPekQ3MTBtSE9PUEFBUWJqMkZDRk5vQURfZDRMVzQ3QU5jN0hNYTI5SjZlUGc2SnhLbktYcnB5cFFtZw?oc=5</t>
-        </is>
-      </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>08-05-2026 14:27 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>Samsung Bioepis</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>Cartography Biosciences: Strategic Investment From Samsung Ventures To Advance Oncology Pipeline</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>Pulse 2.0</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOb2sxbzdJYzBFcUdrWmlPZDZTdi1ILTJpNV9JN084WXBrNW9ndEN2WTgyWWpVYVZFb0RiaXRCN29TUnFWSm1iM2FlZ3FyemdsWk5WVTM3T3BPZmp2VU9MMVl4RTRiVmJHZEV3eVNrT1ZMUlJ2aWhPZHRRU2ItWHpuNzNwNUc3TFZFamNrRXVMSjJXZm1mellrVE4tTWswR1Q0ay00bHktVnJqSGNNOVJaYkV3Tl9kVVRoX2ow0gG7AUFVX3lxTE5vazFvN0ljMEVxR2taaU9kNlN2LUgtMmk1X0k3TzhZcGs1b2d0Q3ZZODJZalVhVkVvRGJpdEI3b1NScVZKbWIzYWVncXJ6Z2xaTlZVMzdPcE9manZVT0wxWXhFNGJWYkdkRXd5U2tPVkxSUnZpaE9kdFFTYi1Yem43M3A1RzdMVkVqY2tFdUxKMldmbWZ6WWtUTi1NazBHVDRrLTRseS1WcmpIY005UlpiRXdOX2RVVGhfajA?oc=5</t>
-        </is>
-      </c>
-      <c r="E217" t="inlineStr">
-        <is>
-          <t>08-05-2026 03:46 UTC</t>
+          <t>08-05-2026 22:01 UTC</t>
         </is>
       </c>
     </row>

--- a/news_results_raw.xlsx
+++ b/news_results_raw.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E176"/>
+  <dimension ref="A1:E139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,22 +463,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sandoz CEO Says Size of Weight-Loss Generics Market Is Unknown</t>
+          <t>Aarti A Kapoor Joins Sandoz as Head of People &amp; Organization Operations for Region International</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>WSJ</t>
+          <t>hrtoday.in</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQZUR0LXdsMlNCVENXM1BoeDU0eFNlWHhqVXpxdEVNUERmdGZKb0htZmoyZWtCNmJEYnAya0ZVbzI5Z0NhTXAtek9GOE5XbjR2WFhNNkxGakwwX1B2Mk1sTTN5Wi1MdmF6WVk5UHhjTEZqMl9KX29XU3lYd1dxZVJUTmYxbE5wRGlaSDhOOUZOWXBrbUhpOVdUcllWQkFUMUN4dGx3RTlrRUg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNbTNUaWpydDduWXgwVlVPQzYxSHZHZjA5enA4aHdZeE5QR1RfcWNlREhOVW91N1ZOSmdaUzA5ck1mckExSHV4bXpyVE5vZFd3OTllVWVJZXJzQVIyNjd3REFVRlhMNm8xS3pBMEZqTmtPd2F1Yll1dUJyMmtIZGNrQThTU0J4b3JqQjUxT0tHNVBfcVM3MEktd3dIM3VLYWV4SlNSVTZEVTN1OE5TOVFvcUlIV3o?oc=5</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>08-05-2026 13:15 UTC</t>
+          <t>09-05-2026 07:25 UTC</t>
         </is>
       </c>
     </row>
@@ -517,22 +517,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Earnings call transcript: Sandoz sees stock surge in Q1 2026 By Investing.com</t>
+          <t>Novartis AG stock (CH0012005267): Pharma giant eyes growth in weight-loss and cancer drugs</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Investing.com India</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOUW1zaDgzbHQ3TUt6MVNRR0ZCcnhBSnE4aFY5eEQxalh3dGdPZ2JzdU9NV3I0eUVQX253Zld6Z25OTTdxTzh5ZWRScjZzSDQxV0dMZW9zSzhLZXlOaUUtYkZJUnNiSl9lT3B5MkNjRmtHVTZxOTJXNlJHdUJoVWpGaU9LNEctVnRTdmN5OGI3clhlekktVVZZNEhpVkdKLVNuYmxQR2pEVVU4TWdOMDREUkk2QlVJRVY2VzZHOQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxOU25LNXBac2dEVGpvdFIyZVQtdmllQ0Jia09DeDlWZ29iV2RXNDBaakpkd05EdlFOU3VSZjhqRmtJR252b0tqYUhpLXlUbmJSRE5LTDhwdkFydHprLWpJeVNzUW9OOUw1RWcyb09oQ3VLdG9lRU5qLXFkUFdiV183V2lOT2xlb3dBVm9Lc0ZUR2pmSHFWM1J0LVB2ZFBpMV9WRXVQTXpCOWZZNF9ubEFwNTRQS1cxVVBnUTdSRXpEZ3ZfdlZSTXlKOA?oc=5</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>08-05-2026 12:07 UTC</t>
+          <t>09-05-2026 13:47 UTC</t>
         </is>
       </c>
     </row>
@@ -544,103 +544,103 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sandoz Secures SBTi Validation For 2030 Climate Targets Across Operations And Suppliers</t>
+          <t>Evotec SE stock (DE0005664809): Q1 2026 revenue drops 22% as transformation accelerates</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ESG News</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNaHgwM2tGQmdvYUlic21xWXdRM3JlLXd1VHZEd1JBM1hhODc0a1JwTHRtRGRteHAxZHpYVVFNajRCNjFWRHNDbVhtNTFBVHU2aWR6MU9IZzRuN3h5WTAyUGtZYlNjdmVoVGtJZ2Y2OFFsMUxTTDdkYWpLUENrZm1WTDI4UG1wSG5MLXd5Q0lsN1JxS0ZyNmxRM3M5eWdEcERRbUtqbmFkLURLMXlu?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxONVNzbm5QOTBxbWVGM083djlNWkE3UkdvVDZaVHRTdE1aUWZUYXJJaUxocXVHTFVpS3lJS1gyQ1pKeV94VGRBeVNPcGlodTF4LTNkdmhXd2NDM2VRZ1VQNXBnTjFyVTBIWWlEbVpwWlZuYVBFN2VwZ0FpSnpIMllHbFZpQ1MzM2tGNVM5TUhqTGRGWmpoSTVkdGhwVEktSWdOOElUMlVQaXlGM2hEdlpNNnhyUzJQUUFlbGhGdjNodjA?oc=5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>08-05-2026 13:35 UTC</t>
+          <t>09-05-2026 13:36 UTC</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sandoz</t>
+          <t>Formycon</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sandoz to Launch Generic Version of Semaglutide in Canada, Brazil This Year, CEO Says</t>
+          <t>Formycon AG stock (DE000A1EWVY8): Biosimilar developer eyes growth amid new launches and partnership</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Moomoo</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNX1hhUGMzX2pJcVdRYjNMRFFHTjM1OExKVjd4ZWs3b1lCME5YdnViNWYyWlFFXzFTb19xeEdWM2ltRUx4ZF81cks4aUFtVDd2YnpyalEwR2tqZFVRU1BnYUpDNHF1MzBDNkZrd2tiTDZsSTV3SDJzc2tlSGNhRURDY0RjNl9fZ2VxSlVoR2xXcFhYcmJXOVRBakRscmJQdy1yemc0aWtKY3c5QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPbnV3UzQzWDB4ZnUxSUtkaXVQQ1Zrd3FwQ1IyY25FZldEWFVKbnEwblB6WEFVVHppUDlYR0tjWHlMeUxZeV9FYVgzWVpSdTl4LUFWQS16TWVfRElDV2RacGdka3dNR2NtT0tMMDVxOGJmeDYyc0VtQUUtOF9fcWNLUEJZbzNHaXM0NFd0VVo3cFU0c0F3X0hpdGMwNEU4NjhSTUJBNDNXU0NYa0ZsdnRHY24yUW9INXZGWkFleFFscnhkcFNUNkE?oc=5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>08-05-2026 14:40 UTC</t>
+          <t>09-05-2026 14:08 UTC</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sandoz</t>
+          <t>Gedeon Richter</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Who’s Hired? Viatris Begins Search For New CFO</t>
+          <t>Richter Expands Rheumatology Portfolio with EU-Approved Medicine</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Citeline News &amp; Insights</t>
+          <t>Hungary Today</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxOM2p0ek05bVowRFBiZFU4OExlYVdlMnMtdnNJeXI0LWJlV25EalRyQlhXTUk5N094elpadXA1QWgxd0Y1Nml6SHF5ZTFQdUh1NnB1MDFlLUpTYTV6S2NpanE0RDlXQkZmWS1qSEtsYkVqN2k4MXlyaWsyRmVsaElmVkpGVlhVcFQ0dVJUd0hST05zY1hsbjZTeEdDZVVBbV9rNVgwQnV5aElRdndNcHRCU0RlNDY5N3BScHg4QmVUVDlrZ054cEFsa2FkWUhDcVNzeE83ZzR6Q3dHQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNV2c0Tzh0bkRONDdNX3doQmtZMUdVc0ZJQ0FiVFY0ZHdPbGJKVUpieUFpN3Q0aTc4cHMtdWdicWowZ0h4a0FnaGRjSldZLXdMWWZLUG5WV1REcFlWbnZCQnhlWHlWZ29IYlRJZVZLdE83N0hicWp5X2RfZnhabldpaS1ReU5HNXZqYTE1SWFtUVVuNmc?oc=5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>08-05-2026 12:08 UTC</t>
+          <t>09-05-2026 07:03 UTC</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Formycon</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Formycon AG Stock (DE000A1EWVY8): Analyst Upgrade and Price Target Revision</t>
+          <t>Boehringer Ingelheim group comments on export prospects of Kazakhstan-made FMD vaccines (Exclusive)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>trend.az</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQekFSMzhrQ1pRVUlmRldJM1RJTkxHeEYwa3ViZjc5U3FndHV0cXMwekkybm5NNHRiaDNLLXhxSDJiOW1JLUdBSGpOZGZ0aHB2M3k2b3NoRkJ5cHZpMVF3cm1RU2NlR1pfdVptS0FLcWVpY0ZGSXNlYVdiNVE0czJnWTFkbFUxcDg3WE8wZGNQZXJOUlBEdS01ZjA1UjlJUGFDSEhWUHRTN0lXRGJRN2JITU9uZ0h2OVU0cnM5UGp0aw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE9XRVFhQVgyZjFwWm9aYmVPb2c2MzFFa19UVzgzdXpmM3N6YVp6RkhIWmpUanZlTjJPQldZdjI0ZjRnNnE3VWx6TVUzMEZrQVRwaG13UUtaMVBfTlkxRW5B?oc=5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>08-05-2026 13:34 UTC</t>
+          <t>09-05-2026 09:15 UTC</t>
         </is>
       </c>
     </row>
@@ -652,22 +652,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AbbVie’s Skyrizi beats out J&amp;J’s Tremfya in April drug ad spending leaderboard</t>
+          <t>German pharma faces “historic” squeeze as Merz targets €40B deficit</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fierce Pharma</t>
+          <t>Investing.com UK</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOdVZiNFlTMEhBUmI0N1VOTGw5eWRkR00ySW9TTHdtOERxV1JMRTFMNTd4bjdjYk5UVUNqWXEyVXMyM05icnBKbG5tdThNbWcwckZ2QXBxM0FOdmM3OUZoODRoWjk1eWpvUWpNYmpMSzhFR2JwMlc1cHBFeUZWU0JkdTRURkUtcFM3WXJaZl8xRjROcFFQMFZHY0ROOUQ0ZHMyMjA5OTc1bTUyV2R2T3VTc0Z3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQWFdPdXFZb2tVelgzZVBIay1xU3ltUmdvVGw1aFh4VG90UXViakF4TEUyODNzOWdNQUdmUmhpZXpFX2V0MGlVTkhlS3RNSmRvaG12UDRhUEFBSFNkTk9DYm5IV3MzdW1CLUJzaWdzSUU3LW42QlhlUzFFckM0bHRFNmNFaEdVcUxQU1NDMHhiMXJidDA1dlRnLTBFeEFSaFplZ1AxWEwtdXJHWmM4UHd5ZWJaTnZUdnVQRGx0XzJWLVJadHVpNGc?oc=5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>08-05-2026 14:03 UTC</t>
+          <t>09-05-2026 05:55 UTC</t>
         </is>
       </c>
     </row>
@@ -679,22 +679,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ARVO 2026 signals a turning point for retina innovations</t>
+          <t>Irish company secures exclusive entry into China’s rapidly expanding veterinary 08 May 2026 Free</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Eyes On Eyecare</t>
+          <t>The Irish Field</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxObnI5MGE2akM4aGtqRzNxTlZqX2hKSnVEOHA0RXV6V0p1ak1xSmdSV2diYVBveGk0Wmlxb3FPb3JzYnRKeWNxQ0pHa3QxcXdPbHZGazBkWjhDMklCRTB1N2RocWY4aEZrZVI1cGhVWTljSTlNeXJ5T0YwT3JKM1dGdlYyelpFZFdjUlhVWjJ4aHBRUEJ1MFlPbVFnREhkSTJuTnhHVHdLTEFGSGVPUFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQdkFlSk9FUHlGdVVzcV9jREd5ck9xMTZkU0MyUHFVd2hvNlA0elZuaGpQYndncThyMEd2d0duR2thRGdPeWdwaHlNRWtiQTFVcVlWMThuakN6bjAzVEpDTFhua1hnZUxnaEp6aXdKWkVyUGRycnhXUzhoMjlxUGRyQzRNTUxNRkswMWQ5NkxwNjlPcllfdDhyVmswY2Qza2hwNU0tczA3aldTOHM3c0s1aVJYekh2SnVwT0FRWjgwS1JBYzFRTk9heHBUR3QxX0lzbTlxMWxNLWJPZHhkNV91WEM3bFQ2ZDJZ?oc=5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>08-05-2026 11:53 UTC</t>
+          <t>08-05-2026 16:53 UTC</t>
         </is>
       </c>
     </row>
@@ -706,22 +706,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BioNTech’s €16.8 Billion War Chest Funds a Cancer Bet While COVID Revenues Crumble</t>
+          <t>Robert Eugene Blair | 5/8/2026</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>Northwest MO Info</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQMldmZkZZRlJHcGVFZHFrRGZsWVkwZHJYNjVMclB6THB2bmZEaFFWdGdtdVBQMGRjXzF6Xzd1TnBqN3VhQ3Iza0o2LWRLUjdRSDZFU2lET214N2x5YjhZa2F3czVxem8tbDVuLUVLZ0NrTFVIZGtLMDFaUFBtdXpPZ0R1YWdoeHZ0Zk5RRVg0cWJiN0cxQ3AwWVhDbFpoamFpMDAtZXZ6UHIzTmF5WjZQQi13bmZwVjg2Tzd5LTdaRl8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE9rVTFoV283SV8xc21qNS1kLUNoUW1fbzlJZWg1Smx3MkplQUFrZmpaNTk2Wm40MDg2al9qR0VyY0FKcHYtb0VFV0NFYTY4UlRqNXpfbWRBeGJOOGNyaTZwTVBfeThVM0xXaW92Q2gtUE5NMmJBRlBCNFduVXI?oc=5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>08-05-2026 11:00 UTC</t>
+          <t>08-05-2026 18:55 UTC</t>
         </is>
       </c>
     </row>
@@ -733,22 +733,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Irish company secures exclusive entry into China’s rapidly expanding veterinary 08 May 2026 Free</t>
+          <t>Pet Economy: China sees new trend as people increasingly seek emotional comfort in animal companionship</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>The Irish Field</t>
+          <t>news.cgtn.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQdkFlSk9FUHlGdVVzcV9jREd5ck9xMTZkU0MyUHFVd2hvNlA0elZuaGpQYndncThyMEd2d0duR2thRGdPeWdwaHlNRWtiQTFVcVlWMThuakN6bjAzVEpDTFhua1hnZUxnaEp6aXdKWkVyUGRycnhXUzhoMjlxUGRyQzRNTUxNRkswMWQ5NkxwNjlPcllfdDhyVmswY2Qza2hwNU0tczA3aldTOHM3c0s1aVJYekh2SnVwT0FRWjgwS1JBYzFRTk9heHBUR3QxX0lzbTlxMWxNLWJPZHhkNV91WEM3bFQ2ZDJZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE5za00ybmNUenFBN0RFbjNLaHotQ0tfUWpER2RtdVl3YU5UOUl2YS1mSlN6dnFxOGNNekluNDBWd05XMHA2NmlydThrQkt0dHFZcE91cko5ck1JMjVkWGhEaFVhbDdISTdydU9lay1kemQwcDE4dEllSA?oc=5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>08-05-2026 16:53 UTC</t>
+          <t>09-05-2026 08:26 UTC</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Robert Eugene Blair | 5/8/2026</t>
+          <t>UAE Medical Day spotlights AI-powered healthcare revolution</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Northwest MO Info</t>
+          <t>Gulf News</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE9rVTFoV283SV8xc21qNS1kLUNoUW1fbzlJZWg1Smx3MkplQUFrZmpaNTk2Wm40MDg2al9qR0VyY0FKcHYtb0VFV0NFYTY4UlRqNXpfbWRBeGJOOGNyaTZwTVBfeThVM0xXaW92Q2gtUE5NMmJBRlBCNFduVXI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPYzlHUzRKei1jRk1LT0MydndUTWw4dnZsT25KMmwwSEhqYW1GekVrTmlHeEp1MnBBMWtiX0JLdDFkWmxfUi1zdHRWTWVuV3Z2NHZRa1NxSTBxQ2FjX2FCS1RaMWlUSlpqa0VodVAwYXQxM0pHSEdSSmlQRm9wcDBWVFVTSG5KNFRXZWFCbVNEUVV2QXdmOWlKalJ0cFhRUnNCTTVJWlVKbTIyUjdBNXhMYjc1dXZrandN0gG4AUFVX3lxTE9jOUdTNEp6LWNGTUtPQzJ2d1RNbDh2dmxPbkoybDBISGphbUZ6RWtOaUd4SnUycEExa2JfQkt0MWRabF9SLXN0dFZNZW5XdnY0dlFrU3FJMHFDYWNfYUJLVFoxaVRKWmprRWh1UDBhdDEzSkdIR1JKaVBGb3BwMFZUVVNIbko0VFdlYUJtU0RRVXZBd2Y5aUpqUnRwWFFSc0JNNUlaVUptMjJSN0E1eExiNzV1dmtqd00?oc=5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>08-05-2026 18:55 UTC</t>
+          <t>09-05-2026 07:59 UTC</t>
         </is>
       </c>
     </row>
@@ -787,103 +787,103 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cardiometabolic Therapeutics Market Size, Share and Forecast Study 2026 to 2035</t>
+          <t>"Emirates Medical Day." An embodiment of the state's commitment to building an advanced and sustainable health system</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Insightace Analytic</t>
+          <t>صوت الإمارات</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxQUWxoRzRFSXhCckRGN3pqblF3VG9nUjhxZ3NYLWpoRVNoUkY1ZUhqSVZnSGNqS1NEWWNBejlfOG42S0hTNXBCWmItMEdlakFXQVBiUVhmSTNYdHJkcnlMcFFJbkZNQVlodmxXTVJ0ZDJYNGlSajI4Zm9EV21YeE9ObEgzVXB3c1E1c3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxQUXFFY0RlX0ppR2dBX0EwNmdpVlE5dF9JT0hJbTdndHotWkg4ZnN4Rm5aejlEUUVLNHAwdmlsVGpGZnlLWUJscDNYc3Q4X1NoZ1dGVG9aMDJ5X3dtYjdQQVJyRlJRd3JZZS0yNlFQd1pqcUE1MFhWdFRkVGRIcktWQ3RtRTJhMFRDSjZ0bjZwblpKQnVvZmNMb2ZIbmR5OTRINmo2blcyNDVramNVUzVJM0tOenl5MTByTEVZS2tLUDVkSm5VaUROMjM4SEVPTC1uX0d5NkJnN0VSUFlPUHJzdzlTaVBLcGF4eUlPTGRWYzI0VjNiVG5TRXp1SzRGdw?oc=5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>08-05-2026 12:57 UTC</t>
+          <t>09-05-2026 10:14 UTC</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Hikma</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>6th Rare &amp; Genetic Kidney Disease Drug Development Summit</t>
+          <t>Hikma Pharmaceuticals PLC stock (GB00B128J450): Dividend payer with buyback and growth plan to 2030</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>pharmaphorum</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNa3JyclcyWmF3SXUxTnlwdjdFQ2ZxbXFPRkd3dy05U1NPRmpYQldYYWhlTS0zNUVLQTNhM0p0MFNsbTRkbU52NW5feklwa3pjNXlyeUVnWGlDQ2ptdGx2WFBYOHREVnRFOGNleVZPVUZxUGM3ZmtkQVRtN3h3YVJkbGJ2NnZKVWVyamIybkFNdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOUUp2Uno3MHpvcFQ1YWdPVmxFTER5UEVIZ3l4Z0tINHFrdV9xV1NVVHBxWDQwR2hydy0zNjg2QzNHYktrcE9wNXpZb2w1UjJqMFlIaGd6RFJPdXlPMUdNbU5IU0gzbWxicDRrdm9hVW05VlE4UDRXd2FSa3A2SHpFRXYzczAwUTZ0TnluOWhhRXB2T1g3N09sX2gtMEx1c3dXYm52dzhxOXdRdEp2dG5WaWNvX211OG9aVmU0M2U3dWE?oc=5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>08-05-2026 10:40 UTC</t>
+          <t>09-05-2026 07:53 UTC</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Hikma</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>German pharma faces “historic” squeeze as Merz targets €40B deficit</t>
+          <t>BioLargo Subsidiary Clyra Medical Signs Exclusive Distribution Agreement with Al- Hikma FZCO for ViaCLYR(TM) Across the Middle East, North Africa, and Adjacent Markets</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Investing.com UK</t>
+          <t>ACCESS Newswire</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQWFdPdXFZb2tVelgzZVBIay1xU3ltUmdvVGw1aFh4VG90UXViakF4TEUyODNzOWdNQUdmUmhpZXpFX2V0MGlVTkhlS3RNSmRvaG12UDRhUEFBSFNkTk9DYm5IV3MzdW1CLUJzaWdzSUU3LW42QlhlUzFFckM0bHRFNmNFaEdVcUxQU1NDMHhiMXJidDA1dlRnLTBFeEFSaFplZ1AxWEwtdXJHWmM4UHd5ZWJaTnZUdnVQRGx0XzJWLVJadHVpNGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxQLVNxU2Vzd2R2dWxBamRzc3hOLWZaQ0pYU2RLR282cU1FR1BQSnJ4NnVUVHFSU01JeC03U2RacktmdlhKeXMtUlFkQU9wb21aX0l0Q1NkbjNKcDZ3eHJxZDc4SDdwdXV1QnA0Q3pmcUsxNGVLMmx0T1lZX3BqRmxZb2lQT2l0TU5RcEVXb3BoMXRzN2h3MUFNemo3Nm4xMXFzc25mTVllRVVMX1ZpUm9BRGR3TGgyWW9sclZGV2lqNWZIdzJLaVFFbTVuT2ZocFowTGMwY1d0My1oQlNkQ3VmNndMWTE?oc=5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>09-05-2026 05:55 UTC</t>
+          <t>09-05-2026 05:56 UTC</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Hikma</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Steve Pakola and the Long Game of Gene Therapy</t>
+          <t>WATCH: Interview with Mythili Markowski, director at Regeneron</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>North Penn Now</t>
+          <t>Life Sciences Intellectual Property Review</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOeUVKTFNBXzZuWmpvTlFGNlNrQTZZMDZKeXAwNkZTUkM2V3BReWFjVE5Gcm5xeHZCcEJaSWtOVlRvV1pCRVQ2YzBHRk80WWg2UEI3alJlMlVvQ2l1VVBtWkh2VzI4c0hiTjZuTVpfc3pTMXNsTS12cnVFLXlYck5JZHBiMDhWU3RzYVgxYmMwYWY5ODQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPaEUzTkV6QmFQdEJpRFRFTUE5Xy1iVXM0M1lLcTF3WG04Y2Zscm4yRWtCWk5fVnY5bVFTaEdKZWM1MXhDbExPVzRqQ0VIcjFudzhhSGJOeGF0WXRTa2ExMEtDTXZVdS1YSlJ5N2JvS0Uwc05OMlJCU3diU21SLUc3alZrZUxjT0E3b3ZXdGFZTU82YU1RdGVSYzBkM2FxUQ?oc=5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>08-05-2026 11:32 UTC</t>
+          <t>09-05-2026 03:08 UTC</t>
         </is>
       </c>
     </row>
@@ -895,22 +895,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Hikma Pharmaceuticals PLC stock (GB00B128J450): Dividend payer with buyback and growth plan to 2030</t>
+          <t>Siga Technologies Q1 Earnings Call Highlights</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>MarketBeat</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOUUp2Uno3MHpvcFQ1YWdPVmxFTER5UEVIZ3l4Z0tINHFrdV9xV1NVVHBxWDQwR2hydy0zNjg2QzNHYktrcE9wNXpZb2w1UjJqMFlIaGd6RFJPdXlPMUdNbU5IU0gzbWxicDRrdm9hVW05VlE4UDRXd2FSa3A2SHpFRXYzczAwUTZ0TnluOWhhRXB2T1g3N09sX2gtMEx1c3dXYm52dzhxOXdRdEp2dG5WaWNvX211OG9aVmU0M2U3dWE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPNFgtOWhTbGk1cXphdi1vdjhyT0pDYlVkdTdueHpjNUpVUGZrQmt3a2QzSFV4LU9oR1BTRWY2cjdDNThIS2QySl9oc0xSRXEwd285dkRJdWFmQldNUjRPSVRfeGRsODFNbWxfNzJhM3VNRW5IRnhVRFdLUVI5MDlvanVXVE1fNWtyRUtGV0FRaVgzUW9GeVpaa2xBRk11cU9B?oc=5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>09-05-2026 07:53 UTC</t>
+          <t>09-05-2026 01:12 UTC</t>
         </is>
       </c>
     </row>
@@ -922,103 +922,103 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BioLargo Subsidiary Clyra Medical Signs Exclusive Distribution Agreement with Al- Hikma FZCO for ViaCLYR(TM) Across the Middle East, North Africa, and Adjacent Markets</t>
+          <t>SIGA Technologies Projects Revenue Growth and Strategic Expansion for 2026</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ACCESS Newswire</t>
+          <t>HarianBasis.co</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxQLVNxU2Vzd2R2dWxBamRzc3hOLWZaQ0pYU2RLR282cU1FR1BQSnJ4NnVUVHFSU01JeC03U2RacktmdlhKeXMtUlFkQU9wb21aX0l0Q1NkbjNKcDZ3eHJxZDc4SDdwdXV1QnA0Q3pmcUsxNGVLMmx0T1lZX3BqRmxZb2lQT2l0TU5RcEVXb3BoMXRzN2h3MUFNemo3Nm4xMXFzc25mTVllRVVMX1ZpUm9BRGR3TGgyWW9sclZGV2lqNWZIdzJLaVFFbTVuT2ZocFowTGMwY1d0My1oQlNkQ3VmNndMWTE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOX1cxRllScFFOaG5SakZHT3pFbTBaSGY5UmhmU1RVMTNGNnB6WU9CSEpYSlMwS3dkVjlzQ0pnd1JLYV9pYkVpcFFiS08wbWQwdDc0N0VSUFdPQ3pZVzNiY0ZrUzJoazVIX0pJeWgxS2RmTVhsQks4bWRUcnc5T3JIYjFxWTVYLWN1MFAxUHFxREU?oc=5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>09-05-2026 05:56 UTC</t>
+          <t>09-05-2026 07:38 UTC</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Hikma</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>WATCH: Interview with Mythili Markowski, director at Regeneron</t>
+          <t>Mounia Benbelkacem: Advancing Translational Research Through the Amgen Experience</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Life Sciences Intellectual Property Review</t>
+          <t>Oncodaily</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPaEUzTkV6QmFQdEJpRFRFTUE5Xy1iVXM0M1lLcTF3WG04Y2Zscm4yRWtCWk5fVnY5bVFTaEdKZWM1MXhDbExPVzRqQ0VIcjFudzhhSGJOeGF0WXRTa2ExMEtDTXZVdS1YSlJ5N2JvS0Uwc05OMlJCU3diU21SLUc3alZrZUxjT0E3b3ZXdGFZTU82YU1RdGVSYzBkM2FxUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE90REE2dGRKVnJmcFRudURVQnU1OTgwNzZPc0F4dFNkaWZ2QzE1YUJJZzEyVXJzNWJOSGtXaTJ3OXRxSG5zV3o4eFFKY1Y5TWpfR3o4cDM5b215cFJ2Q0FleWlLMDA?oc=5</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>09-05-2026 03:00 UTC</t>
+          <t>09-05-2026 08:39 UTC</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Hikma</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Siga Technologies Q1 Earnings Call Highlights</t>
+          <t>Amgen Inc. stock (US0311621009): Biotech giant eyes growth amid patent cliffs and pipeline bets</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MarketBeat</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPNFgtOWhTbGk1cXphdi1vdjhyT0pDYlVkdTdueHpjNUpVUGZrQmt3a2QzSFV4LU9oR1BTRWY2cjdDNThIS2QySl9oc0xSRXEwd285dkRJdWFmQldNUjRPSVRfeGRsODFNbWxfNzJhM3VNRW5IRnhVRFdLUVI5MDlvanVXVE1fNWtyRUtGV0FRaVgzUW9GeVpaa2xBRk11cU9B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPS0VvTzJmZm9WYUY1YUVrcnJXdmtldlNEbGw1UmJEZWkyRkRVOXlFb3FDbmV5YXl6dnRhajJUTFB5Q2dybEVIaEFDaVhZakQxOG1jaXRSRF93cGdHSkItTlV3b2Y1b1IxSkdPZVFONEpQSUxLN3VJNTFFZVpBSGd0dDluOUotRHcwb0RQbmg4UW9KTk12WFZWNjJKNWZfdDhQZmJHV1VaTHBJcmNDbk41UnlFdUYtd2EzUkdlUzdDZUNNQzg?oc=5</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>09-05-2026 01:12 UTC</t>
+          <t>09-05-2026 11:08 UTC</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Hikma</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SIGA Technologies Projects Revenue Growth and Strategic Expansion for 2026</t>
+          <t>Amgen Inc. $AMGN Shares Acquired by Wesbanco Bank Inc.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>HarianBasis.co</t>
+          <t>MarketBeat</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOX1cxRllScFFOaG5SakZHT3pFbTBaSGY5UmhmU1RVMTNGNnB6WU9CSEpYSlMwS3dkVjlzQ0pnd1JLYV9pYkVpcFFiS08wbWQwdDc0N0VSUFdPQ3pZVzNiY0ZrUzJoazVIX0pJeWgxS2RmTVhsQks4bWRUcnc5T3JIYjFxWTVYLWN1MFAxUHFxREU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPUjNOZ25oNFdGMTc2Y29HNlRuXzdyVk1HRVVRb0p2Rnh1Q0R2TTF6TkR4Z01BQTBTeEp5WWVMN2pJRkV1WjM1bDc1NDhhdUpIUzIyVHdBb0F1N3I3clJVRVpmQnpKSTB6bnhaRlpuVVQ4SVk5OUNhSXdNWWl4bEdoS2dQLVhRclBGOEI5NkJNS0tVLWxNVVQwTmNKaVR1N19kV3puWktmQTAxaDBMeV9rV1F3?oc=5</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>09-05-2026 07:38 UTC</t>
+          <t>09-05-2026 12:05 UTC</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Amgen Inc. Stock (US0311621009): Shares Dip After Strong Q1 2026 Earnings Beat and Analyst Downgrade</t>
+          <t>Amgen Inc. stock (US0311621009): U.S. manufacturing push and Q1 2026 results in focus</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxONmlOQnhETkloS1Y4eHJJaTk2bDNacldPN1FhODB6NlBHa2FnZnlmUDl5MkhoSkNCQW5NLU9SdlZyeUt1UlBPdHA3b2VQNDFpTy1RQk9UTE12TlZWRkhGN1Y3N3RDZ0ZKUmtYaU5fLWZwYUY5aXBqUEFDT0lWTHprV0tPaFlpb1YzOXZUWFdHdlVqQnV0ZHRPVFRwWXZseHBuTUJ4LUpsejV5Y2tYX3RpajJUT204bVg4eVZ3NWpvaTlEVTc5NFRr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNTjlvSWVSZENTSEk4VzJRdXpQLWNLU3NWcWN0WmY0cGpCSi0zOWIzcmRnM3gyZUQzSmsyQXhteU5Vd3B0SGdFa2Q4RTI5dmFBRnlDVnVuZHRjRDFCRC1EOGQ5Ul91Nll0SVlqcFZBbjdhMVRGX25MNURIaERtWnlaTHhEZGdqU2lvY0hNSko5dTVVNXJJVUFWZVFKVi0wWkRSb1pRdk1BRS1hN3F1blJnOV9sdnVNaVZNaWZRd3pROA?oc=5</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>08-05-2026 11:17 UTC</t>
+          <t>09-05-2026 13:49 UTC</t>
         </is>
       </c>
     </row>
@@ -1138,22 +1138,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2 Dividend Stocks to Double Up On Right Now</t>
+          <t>Ethic Inc. Boosts Stock Position in Amgen Inc. $AMGN</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>The Motley Fool</t>
+          <t>MarketBeat</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQdGpvWFJKQllXUmg4TmcyM0hZMWwtUmFsdGxWcGdfVGVBOWxwNnlqdEVMaTQxVG96dTNGLWlKZDM2RkYzZk9HZ2VlVTRLTUJ0dHBaQ2t0eGdJZmUxRi1OX1VuQjdDUUUtS0RmNmYtOHltRWFZbW9aVWR0TS1peE9CMmk1cXU1Mmx1Mkp2dVJDWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNamNaUl9jR1p6bkRKbnhxUXVueTBmN25hUHZ0Q1YzWXhwcGNKWGlRVzRReGhlejQzbFFXeDBQNUtMREVYNDBPWUpKblNCalpLWFpuQklwMXVoR2hYS2t3cUZ4clZtMXJZR3VPZjNQVUxCMXNCUk5hTVJIOU9Pci1UTWw4NExBNnlOUG9rbGYxalJOa0JvN0tKOXlFY1lIdVR2ZkVwSThWME1TWmpMejR3?oc=5</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>08-05-2026 18:30 UTC</t>
+          <t>09-05-2026 08:34 UTC</t>
         </is>
       </c>
     </row>
@@ -1165,22 +1165,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>FY2026 EPS Estimates for Amgen Boosted by Erste Group Bank</t>
+          <t>2 Dividend Stocks to Double Up On Right Now</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MarketBeat</t>
+          <t>The Motley Fool</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNNVRfVlRCZUhNcXJqUENRNVRwMU1NWmZjNXZZNnVDaXo4Q1ZEWkhRUXBVRG1RR3loRnRWNHNmNGhUbHhQbkpUOUtHbXNQVWMyRXE1SjF4QVN1dTRXQ2xkZmdIdDhSQTRvYVJXa0U4cVo2RVlnR2t3M29vRWw1d09LeGxDUjg2bXVTdGV1VW1aTVVaeS0tTFRMNUdOb0tOV0twa2JVNHRUYkRaUWgwSjBtanpR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQdGpvWFJKQllXUmg4TmcyM0hZMWwtUmFsdGxWcGdfVGVBOWxwNnlqdEVMaTQxVG96dTNGLWlKZDM2RkYzZk9HZ2VlVTRLTUJ0dHBaQ2t0eGdJZmUxRi1OX1VuQjdDUUUtS0RmNmYtOHltRWFZbW9aVWR0TS1peE9CMmk1cXU1Mmx1Mkp2dVJDWQ?oc=5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>08-05-2026 12:42 UTC</t>
+          <t>08-05-2026 18:30 UTC</t>
         </is>
       </c>
     </row>
@@ -1192,22 +1192,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Guggenheim Trims Amgen Price Target to $340: Is the Biotech Giant Losing Its Edge?</t>
+          <t>Amgen Halts Phase 2 HZN-1116 Trial in Sjögren’s: What Investors Should Know</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AOL.com</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOY0hXVG42cEhDME1pX1RMZ1RCaVNWNmttczBxRUdVRlJUaGpGdVNEeE03dWsxSDF3TWloeFFUaU9qYlFDcEtFd1JDdlh0MS1MZUxGLThtcHVCaHpMc3k2X2EwV2ItVnVqdU1LSFlwZWpPNHhjcEkxZWZaZ1JpZmhLc0hYdFpsdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQNUNQNElnVzlNTDlDV0dIMHhJWC1XMVV0eXB4SGRsdjhnb0c2eUpXazR1eGhDN252LVRuVVNaV2NmdnQ5eXkyYnNGdGFaUWFPZDdHYXAwMnlPVkFOSmJEX09PRUdUSHZuZXhBU28zT3RNaUJyNjlYUGtWc1YxMkFZZ2Z6dVdsXzJRc2RIRl85UFRyZjhEVk0wVENzenJzaklhcHF2empEem9fWU5zUjBjSTh5MVQyRnFtRTM4b1RNMnFJMnc?oc=5</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>08-05-2026 18:32 UTC</t>
+          <t>08-05-2026 16:38 UTC</t>
         </is>
       </c>
     </row>
@@ -1219,184 +1219,184 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Puerto Rico attracts manufacturing investment with Amgen expansion</t>
+          <t>Crossmark Global Holdings Inc. Has $15.62 Million Stock Position in Amgen Inc. $AMGN</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>WJournalpr</t>
+          <t>MarketBeat</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxNTFdhNy1iell0NUFZQUlrMUhsYndJZzJ4WlJXa2l0MERjbnlVZzBBaldBNFpHUTFtNEVLV0FOT1lMUHVONF9Gd1lMY0NVWnhlX0liZ1Y4TEFSR0RxM3NnRU52Nng3U1kxQ0NVbFF6c2NZQTJFNTB6LVpIczhKbUF2QkY5NXR0VUVVWENGQmFQa3ZtM2NoN3gyd1VfSHZNUEkyQ2dESXRlbGdNdDFQeUFSOW5ac1BPRF80YkM5SlE5bEFrMTVUV01yenJld0FWN29kQUVzM0FGcWU2U0FnMHFHZnBOV1BGUDA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxQQlJLWnQ2cHpETDROblRuYzRVRlVDV3Z3RHVfODdUdVplWUF0RGh6MzJkbV91TG5FLWpkR1RhUzE5TXV2WDB1NFJvNkR3SXBOekVHaW9hUmUzZ1Q1U1dpRWZfS3lZWGZpUWVyc19YenJIRkxUR3RJOXlILWMzRnpNQ2JfVFpteHlDREo4c1NTUF9VUE5YZFdBbUhUVGdGU1k1ZUtXbTNfcGk0cVlIQ3hHd2pGSENURVBTTmNfLWFCS2lhZTF5MEZSNTlVQ3lCSG9WY0FobnZWWQ?oc=5</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>08-05-2026 10:00 UTC</t>
+          <t>09-05-2026 08:43 UTC</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Amneal Kashiv Biosciences</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Amgen Halts Phase 2 HZN-1116 Trial in Sjögren’s: What Investors Should Know</t>
+          <t>Amneal (NYSE: AMRX) director exercises 48,747 RSUs and receives 30,837-unit grant</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>Stock Titan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQNUNQNElnVzlNTDlDV0dIMHhJWC1XMVV0eXB4SGRsdjhnb0c2eUpXazR1eGhDN252LVRuVVNaV2NmdnQ5eXkyYnNGdGFaUWFPZDdHYXAwMnlPVkFOSmJEX09PRUdUSHZuZXhBU28zT3RNaUJyNjlYUGtWc1YxMkFZZ2Z6dVdsXzJRc2RIRl85UFRyZjhEVk0wVENzenJzaklhcHF2empEem9fWU5zUjBjSTh5MVQyRnFtRTM4b1RNMnFJMnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxObFJ0MVBUOU54OFdjX3ZhLXFOMXYtN0J3eHpnQUpSQmhfMFJVYkJ2cmNJVHpmZzRaR1Rja3dGM1d2TW1JN2pETm9EcUFoVUdjdThuYzZaMmJNQ3JPamZjQlBBUW5GSC1CNkY3RVhzT2w1djlPUklHa29kNFFmRXViZm9fQ0NUTTdyWmpGOTJLR0hRTHRYbVhtODVkYVFHdi1qWkZ5ay1BVFUtV2hBVDN2RGM1TEp2NFFCOG1QZA?oc=5</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>08-05-2026 16:38 UTC</t>
+          <t>08-05-2026 20:22 UTC</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Amneal Kashiv Biosciences</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Amgen Inc. stock (US0311621009): Rating upgrade and Q1 beat amid tax and regulatory overhangs</t>
+          <t>Amneal (NYSE: AMRX) director settles RSUs, now holds 128,479 shares</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>Stock Titan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNZEJQQnJSd0pxb1cxY19BLWhUUHk4d3pVTUpWMTZILXU2R0pxSEF1MHliQ25CTzVPTHYzcXRIVnFUcFFmMlk0V21TSHFzRl9qVDlfSWtDTXhPQ1RINFNCX3VMLTNwWFUwbWdCUWZZQzRyRmNkM0d3RnF2WmFNT19NNkxMdEFLYWdwWHdiRmdRNkZPOU9KX3U1MU54bVpLWUNMUmFOOWJYeVJfd1JwbEJlTWZfbktEVFV2QjFXRFVxQkhfYlJWZEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPRzBISHVCNmhqc2JZUHljSkprOWFpUDBSUHlCTGMwZ2VldGdnYXJKcUV2V2R2UnAyYkRMVE9QR3RHVWF5Uk1QQmpiMWlIQ1lFNHJ1ZXlPSjhrcGtZNVdmcERiaFB6X0Y0Nk5GMXlNZWFTU2NYbno4ZU50dWlQVVM3MGlVNXd5M2dPRzlFQl9fTEl2QVZld0FEYmszbUcyUEFqN2Z0MG9CWGJodjhENFpQVXZJYkdEMHpuWXZydA?oc=5</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>08-05-2026 10:58 UTC</t>
+          <t>08-05-2026 20:28 UTC</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Amneal Kashiv Biosciences</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Amgen (NASDAQ:AMGN) Stock Rating Upgraded by Freedom Capital</t>
+          <t>Director boosts stake with 34,819 shares in Amneal (NYSE: AMRX)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MarketBeat</t>
+          <t>Stock Titan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxONk16NnJSWXhHbE8wcV9mM09URE1peDFPR1lWdVhpNktQcEhITC1waW9QZmYzWkJlMDNYUl9BN3hVZHY2ak1MX1BZR1U3MUgtVDlLUFJHdHl1Ty1ueW4wdUpOeGl6d09jLXNPaXpqNTFJTEZDakRlQkt6WVYwSkRGbmtRcFJnSjdIcWpIbGx6Y0g2MVlxNVZqUS1fQ3ZUWmEtcThicG0zTjY2QjBjRlhSTg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQUmY5d1VmNXNpVzJkZlU0aUlBbndYMC1rck9CWnRLVVVPMFpnVlJEN2VxYUZqNWhyWER2dWtQLVh6UU5TTklRbkUwOTRxNXp0SllXUkliZFBCazlSY2ZCb2FSMUs0RXV2Z1VMN3JXUVM3VFd0WGhwLTVZRldpMzBtN241MEowa2t5WC1VSnBwN191RVc1WDA4bEkxcWtHb2xvQW4xc00yQXNyMVRfaEZOZTlSaDM4N0dmblFYQQ?oc=5</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>08-05-2026 09:47 UTC</t>
+          <t>08-05-2026 20:23 UTC</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Amneal Kashiv Biosciences</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Generali Asset Management SPA SGR Raises Stake in Amgen Inc. $AMGN</t>
+          <t>Amneal (NYSE: AMRX) director converts RSUs to shares and gets new grant</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MarketBeat</t>
+          <t>Stock Titan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxONkJZZEpMU3BjYU5nbzRUT0tUYjFtcjdEdjdDMWFoeXg1TzRtWHg2QjZpLTNWTXNncExCcHZxdktLb3dkbjJLdHhfNzF1NTN0SElyT0hjR0JFdm13TndST3NXRXpmcUwxQ1ZmU3NHSDRnRGV6c3puWkt0dlhmSlA4ZVlFUTZmV1VmMjlVNC1NWnpCY3dkM1ZOMTNjVE5EdFpqS3R2aGhPc0sxODlhOWtfbl9Na2pSQlNtandEM1dfLVlHb1k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQLU9LV3Q4NUM1SWZlSHlwajJZbnQtNjFFbk0zTkZoSHJyUHk0VnFzWnZFZG5MRm9xcDZ2QVpFeDhJbC1QbU5ITVFIX18wMTRyUDhUdTV0TEFvMjR1RnB5N3ozNUh5aXBBUmswbDEzcjAwOE5GcWtvdXlLMF9Zb1RWVXpCR29WR1FJN3BCV1l2MkNLdHNQMGtHQ0JYZVprM2V2cXAtNTh2S2dxQlM4T2pwMnNxSFFGVllhdFItbg?oc=5</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>08-05-2026 09:04 UTC</t>
+          <t>08-05-2026 20:22 UTC</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Amneal Kashiv Biosciences</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GRIMES &amp; Co WEALTH MANAGEMENT LLC Sells 4,111 Shares of Amgen Inc. $AMGN</t>
+          <t>Amneal (NYSE: AMRX) director exercises 34,819 RSUs and receives new grant</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MarketBeat</t>
+          <t>Stock Titan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNNk9vNzA1Sk1xQkZVM1NQNWk0Mk5ZbkNrclZUZHhKNGg5ZElMNGJmcjdHajFoenVEV3pTMkJSdWozbjhSLUdYeTZIVkV4S0VuX3ZvZzhJbGpYeVk4a1BuRWc2OHh4S2E5RVRabUV2Y0t4bDg4NnhzbEYxUTBOVUFsVXdfOGc0Q0p5dDlVYlI3RXJWX1NwdVNHeDNkRmJ2SFVEeGxHekZHQTBJM3NYMlg3SFIzcnNGT0prVm1zS0VNdnc4Uzh5Vks0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOVDJlSU1KMzF0WUZjekFjMVkyaFVoUUFKWnVlR3JOR2xVdEgyZnczZ3lTMFU4akE1QTNfOGxLTG44Q011RllveS1EcVRSLVBTZjhHUE5aMDdTNjA5SHlSVm1pcVNPV0gyenRVRUtfZ014cUhQSjZZNzBYcHVYMF9BRDQtS2c5M3JoenhhbTUtVUdweGd2TXZXREFsQnFPQmt0OEc4ZlRTN0tQcXYySkZySXFEVWpjMlZuZGJwcQ?oc=5</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>08-05-2026 09:04 UTC</t>
+          <t>08-05-2026 20:29 UTC</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Amneal Kashiv Biosciences</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Atrial Fibrillation Drugs Market Set to Boom Rapidly,</t>
+          <t>Amneal (AMRX) director exercises RSUs, now holds 260,252 shares</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>openPR.com</t>
+          <t>Stock Titan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQOVNuVVV4d3oxcnhoZzV3dktjaDFuVnVJUFpYYjdRaXktUDl0Zkl2NHprRGtva3FsdThlV1BPTGl5OHNSMXprSVFicUpnbmVNQnBmMEtDdE9nMFl1RUlOZmJNN3FTcDV1WGEzQ0trczc4dlhITm5ZajJFUGk3ZDF2RTZmTjRSaTUySnJ5OWFoR0RzZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPeHdoVS1nc3ROQkNndThyWXpaYUlJb2otdzVSTlVPSTJ2ckV6di1JS01mai03MTFDZXc1RGZldFoxWkJFcjZUZzdnMi15SHFrWVh5RDFYQnhFT1d3N3RRWU14dWg1a0UzdXpSU19PX3NQRGlnQ21mTW9KeEhfY0tKamUwLTllbTVKaE1GaUpZQ1E0cFVMUFNPWjJzR0VUTUd4cmEwYnVkaG9pOGh3QXhZeUlscDJTdU9lWC1mUQ?oc=5</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>08-05-2026 12:51 UTC</t>
+          <t>08-05-2026 20:24 UTC</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Amneal (NYSE: AMRX) director exercises 48,747 RSUs and receives 30,837-unit grant</t>
+          <t>Amneal (AMRX) director Jeffrey George exercises 34,819 RSUs, receives 19,824 new units</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1418,24 +1418,24 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxObFJ0MVBUOU54OFdjX3ZhLXFOMXYtN0J3eHpnQUpSQmhfMFJVYkJ2cmNJVHpmZzRaR1Rja3dGM1d2TW1JN2pETm9EcUFoVUdjdThuYzZaMmJNQ3JPamZjQlBBUW5GSC1CNkY3RVhzT2w1djlPUklHa29kNFFmRXViZm9fQ0NUTTdyWmpGOTJLR0hRTHRYbVhtODVkYVFHdi1qWkZ5ay1BVFUtV2hBVDN2RGM1TEp2NFFCOG1QZA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNY0lHZnVFdXdjM29rODZLUWZDS1NpdFRNTkdJWkR0WXJVazJRZndTQ0Y4cmpCVThkNUg0VXZrQk1sN3pwNF9MT09PUXc1b0pEb1RCZjR4RkIzUEg4TGt1N3dIOHVwMXE3U2pIOXVqN3VaTHIyTllCbm9TaldPQ0wxT2F2TW9DT0RMNHhGdTdJUnlyQkJpN1c3OEpVVlV2VEFVNHR4OGhYNU9McDhKYUd1S2pMLThhUmxxOFJrUA?oc=5</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>08-05-2026 20:22 UTC</t>
+          <t>08-05-2026 20:27 UTC</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Amneal Kashiv Biosciences</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Amneal (NYSE: AMRX) director settles RSUs, now holds 128,479 shares</t>
+          <t>OGN (OGN) Form 144: multiple RSU vestings and dividend-equivalent share listings</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1445,201 +1445,201 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPRzBISHVCNmhqc2JZUHljSkprOWFpUDBSUHlCTGMwZ2VldGdnYXJKcUV2V2R2UnAyYkRMVE9QR3RHVWF5Uk1QQmpiMWlIQ1lFNHJ1ZXlPSjhrcGtZNVdmcERiaFB6X0Y0Nk5GMXlNZWFTU2NYbno4ZU50dWlQVVM3MGlVNXd5M2dPRzlFQl9fTEl2QVZld0FEYmszbUcyUEFqN2Z0MG9CWGJodjhENFpQVXZJYkdEMHpuWXZydA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxOODZSaVB2X2ZYQnVkRHZlcWRKa3liUUhqTTNhNVhtX0RQWlJIeTlIUTQtY21ZZzJuVDR3cE82ZElaYTNXU2hObl9qU01UMjMzOUVra0VoUVlfNnlXUnRfUzk4NndhM2NMWE1WNzd0YlBoZmtjRTJQQXduNUQ5OVBlVWFhejN5SWlmOUFvZk9pWQ?oc=5</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>08-05-2026 20:28 UTC</t>
+          <t>09-05-2026 00:35 UTC</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Amneal Kashiv Biosciences</t>
+          <t>Apotex</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Director boosts stake with 34,819 shares in Amneal (NYSE: AMRX)</t>
+          <t>Generic Ozempic approvals signal a turning point for Canadian benefit plans</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Stock Titan</t>
+          <t>hcamag.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQUmY5d1VmNXNpVzJkZlU0aUlBbndYMC1rck9CWnRLVVVPMFpnVlJEN2VxYUZqNWhyWER2dWtQLVh6UU5TTklRbkUwOTRxNXp0SllXUkliZFBCazlSY2ZCb2FSMUs0RXV2Z1VMN3JXUVM3VFd0WGhwLTVZRldpMzBtN241MEowa2t5WC1VSnBwN191RVc1WDA4bEkxcWtHb2xvQW4xc00yQXNyMVRfaEZOZTlSaDM4N0dmblFYQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNelZjNFFmYVlMVmNYX0Uxb1hSRzI2NmdWLW9SbVRIN2Uxcm5IcFFyWDhZZmR6b2FpQk5DRnhBbU8tdjIzZ1BJSUxaZUFlNmY5QW1sanBtc1Y0UEw5d2xtZU5hdE1vdm15NGRKWC1tS3EyXzZheGhWQzNGOTdxLS1ldWJjU1M4SC02U2hFY0FZRmFIbHZQeHFYeDhRVHpwY2hqSHZEaFlUNHFQTUpkNUtVSG9VWVdpOHl1czgtcUE0MkR5d2lrZlZXX3hOZU8?oc=5</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>08-05-2026 20:23 UTC</t>
+          <t>08-05-2026 18:48 UTC</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Amneal Kashiv Biosciences</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Amneal (NYSE: AMRX) director converts RSUs to shares and gets new grant</t>
+          <t>Plant Stress and Unique cAMP Signaling</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Stock Titan</t>
+          <t>Institute of Science and Technology Austria (ISTA)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQLU9LV3Q4NUM1SWZlSHlwajJZbnQtNjFFbk0zTkZoSHJyUHk0VnFzWnZFZG5MRm9xcDZ2QVpFeDhJbC1QbU5ITVFIX18wMTRyUDhUdTV0TEFvMjR1RnB5N3ozNUh5aXBBUmswbDEzcjAwOE5GcWtvdXlLMF9Zb1RWVXpCR29WR1FJN3BCV1l2MkNLdHNQMGtHQ0JYZVprM2V2cXAtNTh2S2dxQlM4T2pwMnNxSFFGVllhdFItbg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE41cHo1U1NreUJJN05xSlJacDFuYVhnVjJRZ2dKMEl1YldPOVN3eEtKb1hSWnk0MENrTnBzeV81VGdNcVM5VEtzNmNCMFJrQW5wYmVZU2xCSVJIVjVoMFozNkNnc0xPazZIRUVfWEo1Y3NlUkZX?oc=5</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>08-05-2026 20:22 UTC</t>
+          <t>08-05-2026 18:04 UTC</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Amneal Kashiv Biosciences</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Amneal (NYSE: AMRX) director exercises 34,819 RSUs and receives new grant</t>
+          <t>Plants evolved distinct functions for two forms of a fundamental signaling molecule, study shows</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Stock Titan</t>
+          <t>Phys.org</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOVDJlSU1KMzF0WUZjekFjMVkyaFVoUUFKWnVlR3JOR2xVdEgyZnczZ3lTMFU4akE1QTNfOGxLTG44Q011RllveS1EcVRSLVBTZjhHUE5aMDdTNjA5SHlSVm1pcVNPV0gyenRVRUtfZ014cUhQSjZZNzBYcHVYMF9BRDQtS2c5M3JoenhhbTUtVUdweGd2TXZXREFsQnFPQmt0OEc4ZlRTN0tQcXYySkZySXFEVWpjMlZuZGJwcQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxORjFLM1JnOXVGd0hOM0VoU0RyUThPTFpXRXZXNnFLdjFUckhoZE05Qi1tNlVSRVd4WlF2ZWRsZUpzT0lTMDZjZDRBcTgwR3M3RFNpeldRTnVFMzVpQktvbkRZcXY5aGlTQXV5RGNHRVdUZmRhRTZSV0NEU0cwS0JPZThUVlFQcnY5alE?oc=5</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>08-05-2026 20:29 UTC</t>
+          <t>08-05-2026 18:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Amneal Kashiv Biosciences</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Amneal (AMRX) director exercises RSUs, now holds 260,252 shares</t>
+          <t>TSMC, Sony to form joint venture for next-generation image sensors</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Stock Titan</t>
+          <t>NewsBytes</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPeHdoVS1nc3ROQkNndThyWXpaYUlJb2otdzVSTlVPSTJ2ckV6di1JS01mai03MTFDZXc1RGZldFoxWkJFcjZUZzdnMi15SHFrWVh5RDFYQnhFT1d3N3RRWU14dWg1a0UzdXpSU19PX3NQRGlnQ21mTW9KeEhfY0tKamUwLTllbTVKaE1GaUpZQ1E0cFVMUFNPWjJzR0VUTUd4cmEwYnVkaG9pOGh3QXhZeUlscDJTdU9lWC1mUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOU0RSTWQ1eVRnakYwdTZGSnRyeWEyVFg0aEdWaGQ4dTRWYk00b2s0eGNlWkJwV3NBbHVmd3EtVDRUanBlTVFtdWRMb1BmTXRNTzAtd0hsdlNNRUotbUxWbHMtZXhaeWU0X2F4MVE1S1NOQl9RQjJIOG1TVGJLczRLZXRyeW1Pd0cxazRTZ3V2dElfM1U?oc=5</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>08-05-2026 20:24 UTC</t>
+          <t>09-05-2026 12:25 UTC</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Amneal Kashiv Biosciences</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Amneal (AMRX) director Jeffrey George exercises 34,819 RSUs, receives 19,824 new units</t>
+          <t>Honda suspends EV plant construction indefinitely</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Stock Titan</t>
+          <t>qz.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNY0lHZnVFdXdjM29rODZLUWZDS1NpdFRNTkdJWkR0WXJVazJRZndTQ0Y4cmpCVThkNUg0VXZrQk1sN3pwNF9MT09PUXc1b0pEb1RCZjR4RkIzUEg4TGt1N3dIOHVwMXE3U2pIOXVqN3VaTHIyTllCbm9TaldPQ0wxT2F2TW9DT0RMNHhGdTdJUnlyQkJpN1c3OEpVVlV2VEFVNHR4OGhYNU9McDhKYUd1S2pMLThhUmxxOFJrUA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5OZTNITTNIdFZ5ZlJwWGljWFdEUDVWY3d4TEc4clNnTTktc0FqdWUxUmstUFVpaUNUR3ktUW1FUWd3akpGcnpZTTcxOWtDSlVMajhNRjZ1b0dmQQ?oc=5</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>08-05-2026 20:27 UTC</t>
+          <t>09-05-2026 05:03 UTC</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Apotex</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Generic Ozempic approvals signal a turning point for Canadian benefit plans</t>
+          <t>These sunflowers bloom nonstop all summer: George’s Plant Pick of the Week</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>hcamag.com</t>
+          <t>PennLive.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNelZjNFFmYVlMVmNYX0Uxb1hSRzI2NmdWLW9SbVRIN2Uxcm5IcFFyWDhZZmR6b2FpQk5DRnhBbU8tdjIzZ1BJSUxaZUFlNmY5QW1sanBtc1Y0UEw5d2xtZU5hdE1vdm15NGRKWC1tS3EyXzZheGhWQzNGOTdxLS1ldWJjU1M4SC02U2hFY0FZRmFIbHZQeHFYeDhRVHpwY2hqSHZEaFlUNHFQTUpkNUtVSG9VWVdpOHl1czgtcUE0MkR5d2lrZlZXX3hOZU8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxONFg2Z1c4SmJCcW1GR3o5NFBHMVhiMEs1b1NwUUE4RUswMUJmQTUzTWh4ZFNwQ0Z6VWNZSmdIS3l6US1qT1BsSlRZZWZmVXFuU0hvMER6UVVIRTBOd0RrU0JCcnRHQ2VyTFpTelJxeWRFOHc0Q0ZlZEtzZ0xIZ0I2QTdIWnhrRXNfYldPZ1padVdYSmVISHhDOVROLXhDcHBnNkd0M1QySjdiejRYa1dOQ0dQNy1jTk05dmZ5QtIB0AFBVV95cUxPRnJybVlSMk5FcU85TUhmdXM1V0x1bTczeXpOWVpWOWRoZVdRSGxkRGlXOVJlVzk0UWI5RkdkVGhoWUZOQk9aNDJob0NNd0dTejQ3dS1tNHpWaHNyWWFpVjJSMEw1RDl1RFVsamcyNGs3ODFaX1lUMnB2dEFKVEdSaWhPS1ZLTDVNSnh3Y1JLbW5GOExKM0Z0YThkNmZwUE43NUY2anR4VHNkUDBCZHRNR3RCSGhaZFJna2c0b2ZaZV9LZmVJdWRyRHB4WHlnTTFE?oc=5</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>08-05-2026 18:48 UTC</t>
+          <t>09-05-2026 10:01 UTC</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Apotex</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>The Week in Canadian Press Releases: 10 Stories You Need to See</t>
+          <t>Is This Edible Flower the Future of Protein? Scientists Think So</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Weekly Voice</t>
+          <t>AOL.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxQRy1CMnVzQUlLb3ZYOWE1ZGdtOS0xMWJtNzNldWFFcExXbzhRZklwSjlScDNzaVNTSG5ZVERmeXc5b2lySTM3Y1dSeHNNZzZ5XzNFT1ZLZ3RnMjZ3ZjVzaXEtOGEtOXBvX2d0QVBSb3hTZ082c3VnWXBUNGMzeWtBV1lYRjFaZVF1NE9VNzlsMVJpWkpL?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxOV1VYVDJnM1Fhc3Y5MmdJc3NjZmRJWHhTNDhpOXpJR1MwREZJTm5wQTNDNzN1WGM1bVZza3piMjV2Q0tqVFJ3WGRQaU8yWDhjZlBjNTlUaGxfY000RGUzU3hSWThaR1FGVzBaRl9JNlVLcUFpbkJlakQzcnRHNV9XUnBuaUV5VVJLU3pR?oc=5</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>08-05-2026 10:24 UTC</t>
+          <t>09-05-2026 12:33 UTC</t>
         </is>
       </c>
     </row>
@@ -1651,22 +1651,22 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Plant Stress and Unique cAMP Signaling</t>
+          <t>GHV Infra Projects Receives LOI for €630 Million EPC Order for Cameroon Tyres Factory</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Institute of Science and Technology Austria (ISTA)</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE41cHo1U1NreUJJN05xSlJacDFuYVhnVjJRZ2dKMEl1YldPOVN3eEtKb1hSWnk0MENrTnBzeV81VGdNcVM5VEtzNmNCMFJrQW5wYmVZU2xCSVJIVjVoMFozNkNnc0xPazZIRUVfWEo1Y3NlUkZX?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxPU0xYTGJpRkxndEYwQ19OTFZtQjRwdU93bDJwU05qRkp6Vy1LVlQ5UEQ1bDVoOUpwSm42R21LV1laQ0VrbExSR21sSjgwd1NPTENtQVV0TndINEtsWlpwRDVSY0hLYU5TdVR4ZnFMdjhUbTFLNTZTaXFOVEhWVWthZ1VFLXBHWEx6UVhHUHduV1NZRnROOFVMT2NZWWFLcmxNb3drY1Y2M3lfOFFzaklsZ0NKdXotT3EzNy1oSXpreTVNcHVib3FBWlNnTGxBQWg3OGhEUFdDNm9xRjI4VVRSUFh3MFMwaUtGaHc?oc=5</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>08-05-2026 18:04 UTC</t>
+          <t>09-05-2026 13:54 UTC</t>
         </is>
       </c>
     </row>
@@ -1678,22 +1678,22 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Plants evolved distinct functions for two forms of a fundamental signaling molecule, study shows</t>
+          <t>Cool beans, smart roots: Scientists discover a new cell that helps seedlings survive drought-battered and nutrient-poor soils</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Phys.org</t>
+          <t>University of Arizona News</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxORjFLM1JnOXVGd0hOM0VoU0RyUThPTFpXRXZXNnFLdjFUckhoZE05Qi1tNlVSRVd4WlF2ZWRsZUpzT0lTMDZjZDRBcTgwR3M3RFNpeldRTnVFMzVpQktvbkRZcXY5aGlTQXV5RGNHRVdUZmRhRTZSV0NEU0cwS0JPZThUVlFQcnY5alE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOWWNqUHNoc2lmdVk0YzN4VFNXR1pSN1g5ZzIzbFZGQk1PSE8xclFmNnl0WXQ4STJaN0l0cHFTdmpPRDFyZGljX2FTWHBuNE5uSWR6MmcxZWphWG9pTE0xRDd4SEs4ZDg4dTR0aVl3Q1JlSHlCc2Q5UlpHc1dhcTF4VzBoOTI4S21ZTGsyZy00Mk9lRV9jVWFnYWdGVVVOQjhUR05TanVvb0N3d3IwMGhCOFhtXzdKVkctNmhGV0Uybw?oc=5</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>08-05-2026 18:00 UTC</t>
+          <t>08-05-2026 18:40 UTC</t>
         </is>
       </c>
     </row>
@@ -1705,22 +1705,22 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Biofuels: Bayer and BP Form Strategic Alliance</t>
+          <t>Northern Discom to strengthen workforce safety with ‘One Minute Rule’</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CHEManager</t>
+          <t>The Hindu</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxOZjEzY0ZHVFN2SG02ZnhWN203Q2xLakg4d1BhVFY3NUlQTG5KRjFhcmJVcFY5NTFXeVZZNS0wU2R6aHFmVmdlRnFfV3ppN1RqOElOVFJFbjBLZjVQX014SzNONDZOckNxQ2o5aGRHQUlQRzhnMWYyWjcyTEhabzVhR2tQZGU3ZEVoRHF3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNUC02YTdWTk5iTk5sRDNGS09DY1FRTDR3dEhwVVVVYndDcjlGVEJMYW5FZVdYYWVhbWlPZHVpcTdOLXFTR0xrMnVHYjE3R3YwZmk5NWpwSHk2ZDBRTzdPWmtJYTJrY3ItWmM3REdFQzBtX21tQXV4d1FRSm1oRkszeldkc0YzMUlpS05jY0dGU3RnMlFaWVlGR1gzYTQwak45N3EzSHFCRzdCa0l3eWtmSEsteFBYZUprS0FJeUJkc2lVd3JsUDBlc2hNa1NyWEEzN2tMZXExb2nSAdgBQVVfeXFMTVAtNmE3Vk5OYk5ObEQzRktPQ2NRUUw0d3RIcFVVVWJ3Q3I5RlRCTGFuRWVXWGFlYW1pT2R1aXE3Ti1xU0dMazJ1R2IxN0d2MGZpOTVqcEh5NmQwUU83T1prSWEya2NyLVpjN0RHRUMwbV9tbUF1eHdRUUptaEZLM3pXZHNGMzFJaUtOY2NHRlN0ZzJRWllZRkdYM2E0MGpOOTdxM0hxQkc3QmtJd3lrZkhLLXhQWGVKa0tBSXlCZHNpVXdybFAwZXNoTWtTclhBMzdrTGVxMW9p?oc=5</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>08-05-2026 09:26 UTC</t>
+          <t>08-05-2026 15:17 UTC</t>
         </is>
       </c>
     </row>
@@ -1732,22 +1732,22 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Honda suspends EV plant construction indefinitely</t>
+          <t>Telangana to boost renewable energy to 29,645 MW by 2029-30: TGRPDCL chief Faruqui</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>qz.com</t>
+          <t>Dailyhunt</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5OZTNITTNIdFZ5ZlJwWGljWFdEUDVWY3d4TEc4clNnTTktc0FqdWUxUmstUFVpaUNUR3ktUW1FUWd3akpGcnpZTTcxOWtDSlVMajhNRjZ1b0dmQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwJBVV95cUxNM2hFbmFZR3BZbkxBZFlTNDZyRGRETmNlV0NBMVdzTHpOVGxIVkFpUGJCbmlwVG42TThyX2NlN3ZZd0FoX19HbXM5VVpId0ppRDBuVm1seFk5YWlQQThubTBEOHNRN04xTEZJMUsxSVRVZGZxckxnNmdVVTZ6dWRhWk9jSkwtdGZ5VktGek1VZ2FTLUFQLXpaeVBfM2hURkRHc1Qtc3J1cWQyb05udU9ZR21fQ2oycW9JUk5MYk5KdHp5dzZhM0RuajdFUUZ0ZUplN3JfWFdFRmNoLUhySWxza19acU5GYnRoWGVnQ0djeWtqQ1ExZ0FsWHhfbERCYTJOb084a3I4aUVNQTQ?oc=5</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>08-05-2026 17:25 UTC</t>
+          <t>09-05-2026 06:41 UTC</t>
         </is>
       </c>
     </row>
@@ -1759,22 +1759,22 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Cool beans, smart roots: Scientists discover a new cell that helps seedlings survive drought-battered and nutrient-poor soils</t>
+          <t>TGRPDCL CMD urges farmers to avail solar power scheme</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>University of Arizona News</t>
+          <t>The Hans India</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOWWNqUHNoc2lmdVk0YzN4VFNXR1pSN1g5ZzIzbFZGQk1PSE8xclFmNnl0WXQ4STJaN0l0cHFTdmpPRDFyZGljX2FTWHBuNE5uSWR6MmcxZWphWG9pTE0xRDd4SEs4ZDg4dTR0aVl3Q1JlSHlCc2Q5UlpHc1dhcTF4VzBoOTI4S21ZTGsyZy00Mk9lRV9jVWFnYWdGVVVOQjhUR05TanVvb0N3d3IwMGhCOFhtXzdKVkctNmhGV0Uybw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNTmhzd056VE9CdC0xTm5nOXBmclppcVAzRHdGQWhJQjJCZ3RfdUgzSEpZQTROTFEtVENOYzJQYnJHa1VoREFSTUl3VTV5ZFFYenVPenJzZEw5cjJOTV92bWQ2NW9najQwSlpjUjZiSFkzbUZzemVUOHc5Ty1SRUs0X243dDBWQUJZSFNLb0lkVDE3dWQ5cEl1d0J4SmxEdWVEUmRsZGF3a9IBpwFBVV95cUxNTmhzd056VE9CdC0xTm5nOXBmclppcVAzRHdGQWhJQjJCZ3RfdUgzSEpZQTROTFEtVENOYzJQYnJHa1VoREFSTUl3VTV5ZFFYenVPenJzZEw5cjJOTV92bWQ2NW9najQwSlpjUjZiSFkzbUZzemVUOHc5Ty1SRUs0X243dDBWQUJZSFNLb0lkVDE3dWQ5cEl1d0J4SmxEdWVEUmRsZGF3aw?oc=5</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>08-05-2026 18:40 UTC</t>
+          <t>09-05-2026 03:42 UTC</t>
         </is>
       </c>
     </row>
@@ -1786,22 +1786,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Northern Discom to strengthen workforce safety with ‘One Minute Rule’</t>
+          <t>UK Infinity Fusion Consortium launched to commercialise fusion</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>The Hindu</t>
+          <t>Enlit World</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNUC02YTdWTk5iTk5sRDNGS09DY1FRTDR3dEhwVVVVYndDcjlGVEJMYW5FZVdYYWVhbWlPZHVpcTdOLXFTR0xrMnVHYjE3R3YwZmk5NWpwSHk2ZDBRTzdPWmtJYTJrY3ItWmM3REdFQzBtX21tQXV4d1FRSm1oRkszeldkc0YzMUlpS05jY0dGU3RnMlFaWVlGR1gzYTQwak45N3EzSHFCRzdCa0l3eWtmSEsteFBYZUprS0FJeUJkc2lVd3JsUDBlc2hNa1NyWEEzN2tMZXExb2nSAdgBQVVfeXFMTVAtNmE3Vk5OYk5ObEQzRktPQ2NRUUw0d3RIcFVVVWJ3Q3I5RlRCTGFuRWVXWGFlYW1pT2R1aXE3Ti1xU0dMazJ1R2IxN0d2MGZpOTVqcEh5NmQwUU83T1prSWEya2NyLVpjN0RHRUMwbV9tbUF1eHdRUUptaEZLM3pXZHNGMzFJaUtOY2NHRlN0ZzJRWllZRkdYM2E0MGpOOTdxM0hxQkc3QmtJd3lrZkhLLXhQWGVKa0tBSXlCZHNpVXdybFAwZXNoTWtTclhBMzdrTGVxMW9p?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPamVUZ25OT3d2OER6dWVRbV9NTnVpT0JQUmRYbWJZYVNURGppY0RYWURsbjhrNTJOdjhILXBDVV9nUXJ4RWM4c2ltQTZJblhLMzVLa3V5aUQxYWlDT0YxQ0NJcTY2TXU5OWZjLTg0d2VPRjhZS3ZhREtUUnhDM2tJd1QzZG5Zbk5LSDhtQW9hZ3pHTHJ5dWltc25B?oc=5</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>08-05-2026 15:17 UTC</t>
+          <t>08-05-2026 15:13 UTC</t>
         </is>
       </c>
     </row>
@@ -1813,22 +1813,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Is This Edible Flower the Future of Protein? Scientists Think So</t>
+          <t>This Substance Is 1,000 Times More Potent Than the World’s Spiciest Pepper — and It Could Provide Pain Relief</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AOL.com</t>
+          <t>Discover Magazine</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxOV1VYVDJnM1Fhc3Y5MmdJc3NjZmRJWHhTNDhpOXpJR1MwREZJTm5wQTNDNzN1WGM1bVZza3piMjV2Q0tqVFJ3WGRQaU8yWDhjZlBjNTlUaGxfY000RGUzU3hSWThaR1FGVzBaRl9JNlVLcUFpbkJlakQzcnRHNV9XUnBuaUV5VVJLU3pR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxOcXNxTDRtSHBhU0V0QXdVMElRMUpHOV84M0FZTFpwdHFrZHpOWkx6M1VRa2RpSFVSaW5LaEFsY08yM0pVVi1kOW1jMFdUaXpoVVEtSFdWMk9ZOHJSeFpmbkNBYXYwZW1KOTF1bWExN0JwZXNFZnhoSlAyLU40RmJ6SDhmNzB5TVhMVDJWVDhYelBvUERtTTVWRmYzdFF3S3JaOU1RcGVUQlZsTEdfLXExaXJheVdKOHhBSGxuWjY4WVBvNDRGTkNNYWF0UDROd1d3WkwzaWJUVWRGMGhZaHBr?oc=5</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>09-05-2026 02:30 UTC</t>
+          <t>08-05-2026 22:53 UTC</t>
         </is>
       </c>
     </row>
@@ -1840,184 +1840,184 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Aecom forms partnership with two nuclear fusion organisations to develop UK's first private power plant</t>
+          <t>16 Flowers To Plant In May For Beautiful Summer Blooms</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New Civil Engineer</t>
+          <t>AOL.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxNMGxqT0pSWXlNNXZ3dDZCREdjdW8wLW1FLWh1eUd3dDIwMC1oaXBnaURlbmY5aVk5VldTZlZXMnRqVmxIUzd5N195TXdmNWpmNmVhSWYtQWo0MFhRUDc1N2J6MTdOM3RqZFl6SmYwX1ZnX1dyRTNmY211cHJCdzdGeUVaenJ2czJRX3NSa3ExZnRhMEJDaWtRR1cwemNuRk5RVW5iTF9HUk52dlc1bDZ0QUNLaVpoSlc4REhtSXBoSXBvWlpZSzJDTmZCWG0waHlFMGtPZUw4TzNxRndwWkZtTkUtUmlmSElfVkE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1aWXgzcGwyc2ljblRxZy1iYnVyYU44NnU1emYyY0VoRm9ONFd1S2xIeERqTDlrcElCNTlsTmUwV1U3Q0NYNnV2TDV3VFVnU2JvNy1nRkIxOXJTejBtZl9LaTlBSkRMTzc2M00zMnNYZlMwY3NYS1d3Smxvc0R6RTg?oc=5</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>08-05-2026 12:46 UTC</t>
+          <t>09-05-2026 05:35 UTC</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>UK Infinity Fusion Consortium launched to commercialise fusion</t>
+          <t>Meet the People of PGS: Julie</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Enlit World</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPamVUZ25OT3d2OER6dWVRbV9NTnVpT0JQUmRYbWJZYVNURGppY0RYWURsbjhrNTJOdjhILXBDVV9nUXJ4RWM4c2ltQTZJblhLMzVLa3V5aUQxYWlDT0YxQ0NJcTY2TXU5OWZjLTg0d2VPRjhZS3ZhREtUUnhDM2tJd1QzZG5Zbk5LSDhtQW9hZ3pHTHJ5dWltc25B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE13Rzl5MkNtWnRRTVkxRkljMHpSNm1ZUTItYktwRGxfTE1jMUgydFc1UjlFRmhUY3JVR0dPaGJxMnlMNWlBS0xnMmlGQmlFamcyLVhUTjlSMUh4bHRJUHR5ZVRraElkQUp6YUE?oc=5</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>08-05-2026 15:13 UTC</t>
+          <t>09-05-2026 06:41 UTC</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Silicon-based biostimulant receives EU certification for pan-European rollout</t>
+          <t>-3.15% for Pfizer stock as new share registration weighs on outlook</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Hortidaily</t>
+          <t>Traders Union</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNZXNRWTBzcGdpQ1FDTnE4M3MtWmRzUS0zRVlzRUdQbGtpWkNoekFMUVcwM2NJaUpvZU5NRGxEZEI4a2M2ZVpfeXZENElES1JIbWl4RDB4YTRQaVhPVy1RVWdidV9LTXlZMk9OVHVSVGMwaXJPblpVYkFoak1oNlJOOWxZeTIzaUVMY25TTmFISk1HR1ZPMS05ckNKTnFMSjc2NTQzeUtCb2s3cFBYMzFOSUotaWZ6dXA4STlOUDNR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQbkZXcjdsUExxNlEwbWU2aFpPZmdhSGFsdWc5TUgyVVo2ZFF2MzNCM2pPVTlOSFA1b1U0cXBPeWY5OHNTMHlFcElKS0hoMXZaTnp1bGhwVHI4aWlNWFdpcFFJektDNFhTNzhmMDlITE9ZUEVfMFZLVHc0M1o1a2YzVndSeGpkREROMnhXV2xBNllkMjFleTRPag?oc=5</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>08-05-2026 11:44 UTC</t>
+          <t>08-05-2026 20:08 UTC</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Happy Mother’s Day from this potted plant parent: Our Best Life</t>
+          <t>Pfizer Inc. stock (US7170811035): Q1 2026 results and recent share price move</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Cleveland.com</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNZ3Uwa3VocUVDWmNjU25SbHNVYzc2SVlYZGxkQUdPRzc5ZE1QSUZBcDhnTGx2Rm9FXzRxRGhiUVJrTmZ6SGlZdGFvUkRJUzNXODZlWll2N1FTWVEwRkd2cXFWLVF2UmJHai1hSTFDZWZBcm0xV2plczVnbmpxTng1OC10THlVRDk5elpkeTQxZ1NNMjVYa3FtQWRTclpVVFRERFRMR3VwS1DSAbwBQVVfeXFMTmhIb2czeW9JZ3U2RnAwckJGMHdkZlFNeEFOaDJ1NDlZVFV1SjcxeVV6T3lEbUwxWE1vRjI2X2hULV9icEgxS241TTV4V2RHQjV2djh1YXI3VDRPWW9sdWt5Nm16ZllYaERsaFBJd20xQXNWWTN1THBSTlhlcG9xTkFYemFhQzJzOElyT1N5RUFpQ0RjbzY4aFlqdVRqQWxkX3o1NjR6OWgwRU9lX2J4MUZrb0pDbjdTMjRLc08?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNeEh3d3FGeXBJeUlBUnRDRnowblNwNWtxQTkyRHp4OWRNT2dxQUtlYzZ6WXhscmtBUW5fVjl1N0MxTGc0a0trTDR4a2ZzajNUSnc0QjNXc3lfQVF1Q01tQTNnS19hOUx2R2lmT3JYY1lza3VodDU3MTdiM29wRUZxRjh1dDBXSmN1SGdzemVHWUZnekVIOWstUkFPcWxVY0JKaDJsT1NaVnZpNzFqbmQtcm9kRmVhdUpNam00ZGFCZXhDLV8waUE?oc=5</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>08-05-2026 14:00 UTC</t>
+          <t>09-05-2026 08:57 UTC</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>TGRPDCL CMD urges farmers to avail solar power scheme</t>
+          <t>Here is Why Pfizer (PFE) One of the Best High Volume Stocks to Invest In</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>The Hans India</t>
+          <t>Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNNklUQ0JSX093eEN4Qm9HQmFHdnhLVmJuZUVKdVIxT3FycGNnUXN1NUl5aG9jUEROaGN5V2NfWU00akQ1dFlXTXQzNEV5VFpVT3NINDlERFhmZHBLVi1ERkdJd2NOa2taLVEzaWhZZm5kdTBCRmd5SXZfQ242RGRoTVg0d1RmNUlac1NPdkM3Q0R3MC1RZTdoYnkySWlYY21WVHfSAacBQVVfeXFMTU5oc3dOelRPQnQtMU5uZzlwZnJaaXFQM0R3RkFoSUIyQmd0X3VIM0hKWUE0TkxRLVRDTmMyUGJyR2tVaERBUk1Jd1U1eWRRWHp1T3pyc2RMOXIyTk1fdm1kNjVvZ2o0MEpaY1I2YkhZM21Gc3plVDh3OU8tUkVLNF9uN3QwVkFCWUhTS29JZFQxN3VkOXBJdXdCeEpsRHVlRFJkbGRhd2s?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE5JWEhkSjZUODA5THFlVjRTQUVhZF9UUnU3a25uRjhYc3VxVC1DSWJta1BGOGs5LWxjQS1tWW1FMFRXVHBTSkVsOVZmQmUwb2otREMwUnh4dXR1N3pMQ2VqNHZPeVUxak1mR2hYM2hUOGNtalVibW5zaGVmcXI?oc=5</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>09-05-2026 03:42 UTC</t>
+          <t>09-05-2026 04:57 UTC</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Europe and Canada together can form major market for innovative firms, German minister says</t>
+          <t>Pfizer vs Moderna: Only One Pharma Giant Is a Winner In The Post-Covid Era</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>The Logic</t>
+          <t>AOL.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQR2hsNzZFMC13R3dBNUpRanBWUkw3VWRTb3N3aHZsQjJpRy1sMlNIM3E1QXRXcFlWSkFjb3F6RFFEb2JjNVlaSjE4ZGlMZHd4eGFtTXFsZWNXaEtRVzgyQ3FMdzlhY2l1TTB2eU9scUpDeFY1cElldnNzMzR0dnFnRnFqakFjLVFfVXFSeHNPMG5ya2F2WnQ5S2wtSVBqcWxQOVYxaHhJUHVQQkxCMEc5a1RVUmEzOGJwZUc2aA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTFBUUlNVMmVOeE82bDdjNDdadDBSb1ZIV1dVUVBLaEpMTHRFclVVU0EwYXlBNG40STNNSDZNcEVlN0xLOXcxVG41WVBMczd0c1FPX3RvdzY4QlJ3a1VvZjlPUDVHYVplUlRKbjhTVGtfdFIzcXExRzFKakRR?oc=5</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>08-05-2026 19:58 UTC</t>
+          <t>09-05-2026 11:16 UTC</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>This Substance Is 1,000 Times More Potent Than the World’s Spiciest Pepper — and It Could Provide Pain Relief</t>
+          <t>Fact Check: Hantavirus Outbreak Viral Claims - From ‘The Simpsons’ Prediction, Pfizer COVID 19 Vaccine to The Economist, Betsy Arakawa Death &amp; Hantavirus Pulmonary Syndrome</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Discover Magazine</t>
+          <t>The Sunday Guardian</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxOcXNxTDRtSHBhU0V0QXdVMElRMUpHOV84M0FZTFpwdHFrZHpOWkx6M1VRa2RpSFVSaW5LaEFsY08yM0pVVi1kOW1jMFdUaXpoVVEtSFdWMk9ZOHJSeFpmbkNBYXYwZW1KOTF1bWExN0JwZXNFZnhoSlAyLU40RmJ6SDhmNzB5TVhMVDJWVDhYelBvUERtTTVWRmYzdFF3S3JaOU1RcGVUQlZsTEdfLXExaXJheVdKOHhBSGxuWjY4WVBvNDRGTkNNYWF0UDROd1d3WkwzaWJUVWRGMGhZaHBr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgJBVV95cUxQREpXaDJBbldvemlHSVNiRDY0cmkzNlFLaHZ1cl9DYkVWb21vSG1Rbi1mOUVFckljTlRjVmt6TVRrZ2hVVGI4a2VvcURzSF9pMDVBTzJwSFpsR3k4MWwtdlBFam9IVjlwOVFsdDU3VWtsMWF5U0xpYXEzWHpGLWl4X3ZrX0E5UWF0aGtqZV8wbFVZLWxEQ0RIQkdPZnZvbVNHTEVNcjV6SnliOExyZWVPcWpQTXh6ejdZa2h5S3RjMVU4SHFIWWFBRXZzSFNLdkhjMkI4TEt4NXBwWHA1alZCaWd3Zll6czk5ZEVZVDh0cS1GVTlaWjhWd3JJal95Q1psekFGSUhQV0lfS05rMEEtZzVnMUdnbU9JOEdwS3RTMTlhcUc5MHJDNHctVU53TzN4X0hnNGNn?oc=5</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>08-05-2026 22:53 UTC</t>
+          <t>09-05-2026 07:50 UTC</t>
         </is>
       </c>
     </row>
@@ -2029,22 +2029,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>-3.15% for Pfizer stock as new share registration weighs on outlook</t>
+          <t>Fact Check: Hantavirus infection is not a confirmed side effect of Pfizer’s COVID-19 vaccine</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Traders Union</t>
+          <t>Reuters</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQbkZXcjdsUExxNlEwbWU2aFpPZmdhSGFsdWc5TUgyVVo2ZFF2MzNCM2pPVTlOSFA1b1U0cXBPeWY5OHNTMHlFcElKS0hoMXZaTnp1bGhwVHI4aWlNWFdpcFFJektDNFhTNzhmMDlITE9ZUEVfMFZLVHc0M1o1a2YzVndSeGpkREROMnhXV2xBNllkMjFleTRPag?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPQjAxUjYtNmQ1TUt6Mm9DTGdlaGt3R3pjcjNWcUtNb3BNVGZNN2tNdGhBY0VCc05lQ05JOGtDSlJOdjhyMGZvNVYzZTVFS0k2N0pTSk55OFo1aEJfOWxXYmFvSEpSaXBVRWJQUlotMExaUTZUSTctdkRQekpYMmlHUll1RUkzejZVdGZ6ZVVJWWUxc2JrZFlrQ3lBdjJYUzUxUVpMZ2RDZjk3MFVRTHM0akZXeTNYcGdkVDY2TlR3?oc=5</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>08-05-2026 20:08 UTC</t>
+          <t>08-05-2026 16:45 UTC</t>
         </is>
       </c>
     </row>
@@ -2056,22 +2056,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Here is Why Pfizer (PFE) One of the Best High Volume Stocks to Invest In</t>
+          <t>Pfizer’s Lyme disease vaccine shows 70% efficacy; Texas man sentenced to 12.5 years in $61.5M Medicare telemarketing fraud scheme; Novo Nordisk launches Wegovy subscription model – Morning Medical Update</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Yahoo Finance UK</t>
+          <t>Medical Economics</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE5JWEhkSjZUODA5THFlVjRTQUVhZF9UUnU3a25uRjhYc3VxVC1DSWJta1BGOGs5LWxjQS1tWW1FMFRXVHBTSkVsOVZmQmUwb2otREMwUnh4dXR1N3pMQ2VqNHZPeVUxak1mR2hYM2hUOGNtalVibW5zaGVmcXI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gJBVV95cUxPVnU1X0hLdnNoem8xSWwtUm9LQ28wXzM4aUFsUUN2U1ZsM0Fwb2dIWmNPdGphRVd3cm9RUzBtT0gzYVlyYUV5aHBnOEt4ck9CVnV0NEs5NTJkV2d1WnZSaGs3bUJYUHlzVVBMV2xwRDhnakZiWVlkNG5kTFBmTm0zNHJGNDlhdHhNcVNEQUtaX0ppdlZ1SFlXekZ0Z0Rtemh4TktrWGdPN1VIYnhGZmZnWURLWlhQTjNhUXN0RkV5eE01ZnhhVHd0RXlFNm5PNDBQTjQyOWpHMWRpTUJfV0Y5NjBqcmJvZ0FGWGtZQjdtZW5LcFI4S3U5ZHV6Zl9uc0NZQkpEcDQ1TjRiTnk3MjBGYS1RdjhNaVhvQjVveW5FRFpWQkVicHE1MVlLbURUZTFObTZtS19qN3JrdDF5c0RHb19WZzNTQW5OcWU2MEdGR3pqREVjQWc?oc=5</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>09-05-2026 04:57 UTC</t>
+          <t>08-05-2026 17:46 UTC</t>
         </is>
       </c>
     </row>
@@ -2083,22 +2083,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Fact Check: Hantavirus infection is not a confirmed side effect of Pfizer’s COVID-19 vaccine</t>
+          <t>Pfizer Inc (PFE) Shares Fall 3.0% -- What GF Score of 76 Tells I</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Reuters</t>
+          <t>GuruFocus</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPQjAxUjYtNmQ1TUt6Mm9DTGdlaGt3R3pjcjNWcUtNb3BNVGZNN2tNdGhBY0VCc05lQ05JOGtDSlJOdjhyMGZvNVYzZTVFS0k2N0pTSk55OFo1aEJfOWxXYmFvSEpSaXBVRWJQUlotMExaUTZUSTctdkRQekpYMmlHUll1RUkzejZVdGZ6ZVVJWWUxc2JrZFlrQ3lBdjJYUzUxUVpMZ2RDZjk3MFVRTHM0akZXeTNYcGdkVDY2TlR3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOS2prNW1waGtmNEpjY2JZTGtWWGlmaG0xT0tlbm9nVU9Lb2Y1SHl4OWE1Smt3SkV6MFl5U1FtMkZHM1N5S1ZzMVpuaEJ0N1F4QTIyVUM3c1ZFWU1zS1lTMG1VLXVMMjk0U180cnV3Z3lmU0RIekZFeEZ2d001Nm9tYzBYNUhIT0pfbGEzcGpFVE9HOWFaU28xMXFTTXhyZjQ4YjB5RXZzaW9BRjFwbDZQR3RIZkNYa1E?oc=5</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>08-05-2026 17:09 UTC</t>
+          <t>08-05-2026 22:36 UTC</t>
         </is>
       </c>
     </row>
@@ -2110,22 +2110,22 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Pfizer’s Lyme disease vaccine shows 70% efficacy; Texas man sentenced to 12.5 years in $61.5M Medicare telemarketing fraud scheme; Novo Nordisk launches Wegovy subscription model – Morning Medical Update</t>
+          <t>Pfizer Inc. stock underperforms Friday when compared to competitors</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Medical Economics</t>
+          <t>MarketWatch</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gJBVV95cUxPVnU1X0hLdnNoem8xSWwtUm9LQ28wXzM4aUFsUUN2U1ZsM0Fwb2dIWmNPdGphRVd3cm9RUzBtT0gzYVlyYUV5aHBnOEt4ck9CVnV0NEs5NTJkV2d1WnZSaGs3bUJYUHlzVVBMV2xwRDhnakZiWVlkNG5kTFBmTm0zNHJGNDlhdHhNcVNEQUtaX0ppdlZ1SFlXekZ0Z0Rtemh4TktrWGdPN1VIYnhGZmZnWURLWlhQTjNhUXN0RkV5eE01ZnhhVHd0RXlFNm5PNDBQTjQyOWpHMWRpTUJfV0Y5NjBqcmJvZ0FGWGtZQjdtZW5LcFI4S3U5ZHV6Zl9uc0NZQkpEcDQ1TjRiTnk3MjBGYS1RdjhNaVhvQjVveW5FRFpWQkVicHE1MVlLbURUZTFObTZtS19qN3JrdDF5c0RHb19WZzNTQW5OcWU2MEdGR3pqREVjQWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxPUDVGSFNMTHBBdk9ZaHdmc1NBY1dqOF92WDdEWXJVZ2ZEdWluejkxVFJtNTlYcnlBQ2Nib2tCdFJmcTJkNVJNTUNYd3lLeWQyNFdkd2NHN0NTcWdDNmoyOGFEQ2NQaEdicTR4aFk5S1RkblFRRS1odGpRTlZWRlBDbU4zUlpXSjhvMGdaSDJURWJmVmJmdk5yOGlzejFMR0phaHBVbUduSmd6b2tWcGNuTERPX1F0RGdzUUtqVlhwUV9DQmVK?oc=5</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>08-05-2026 17:46 UTC</t>
+          <t>08-05-2026 20:36 UTC</t>
         </is>
       </c>
     </row>
@@ -2137,22 +2137,22 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Fact Check: Hantavirus Outbreak Viral Claims - From ‘The Simpsons’ Prediction, Pfizer COVID 19 Vaccine to The Economist, Betsy Arakawa Death &amp; Hantavirus Pulmonary Syndrome</t>
+          <t>Best Pharmaceutical Stocks for 2026 and How to Invest</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>The Sunday Guardian</t>
+          <t>The Motley Fool</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgJBVV95cUxQREpXaDJBbldvemlHSVNiRDY0cmkzNlFLaHZ1cl9DYkVWb21vSG1Rbi1mOUVFckljTlRjVmt6TVRrZ2hVVGI4a2VvcURzSF9pMDVBTzJwSFpsR3k4MWwtdlBFam9IVjlwOVFsdDU3VWtsMWF5U0xpYXEzWHpGLWl4X3ZrX0E5UWF0aGtqZV8wbFVZLWxEQ0RIQkdPZnZvbVNHTEVNcjV6SnliOExyZWVPcWpQTXh6ejdZa2h5S3RjMVU4SHFIWWFBRXZzSFNLdkhjMkI4TEt4NXBwWHA1alZCaWd3Zll6czk5ZEVZVDh0cS1GVTlaWjhWd3JJal95Q1psekFGSUhQV0lfS05rMEEtZzVnMUdnbU9JOEdwS3RTMTlhcUc5MHJDNHctVU53TzN4X0hnNGNn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPZlFCRE0tR09IcFR6RXFhYmRTeTcyRTVrT3ByNHUzRXN4VFFBZExzMGtmNkNwa09NX0VFd3EzaUhSVmZpSTJkRFlqOFBuYVNpWHNBLWE3WjlkMjM2bWVhYS1zYTllbnRHb1JKV0l5ZlQzTEFaSmUzYW5pS2NiRkowZVZLU183Z0dsM2psTjZhVG5UNDdBTzM4?oc=5</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>09-05-2026 07:50 UTC</t>
+          <t>08-05-2026 20:11 UTC</t>
         </is>
       </c>
     </row>
@@ -2164,238 +2164,238 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Pfizer Inc (PFE) Shares Fall 3.0% -- What GF Score of 76 Tells I</t>
+          <t>Vaccine and blood thinner help drive Pfizer to quarterly earnings beat</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>GuruFocus</t>
+          <t>AOL.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOS2prNW1waGtmNEpjY2JZTGtWWGlmaG0xT0tlbm9nVU9Lb2Y1SHl4OWE1Smt3SkV6MFl5U1FtMkZHM1N5S1ZzMVpuaEJ0N1F4QTIyVUM3c1ZFWU1zS1lTMG1VLXVMMjk0U180cnV3Z3lmU0RIekZFeEZ2d001Nm9tYzBYNUhIT0pfbGEzcGpFVE9HOWFaU28xMXFTTXhyZjQ4YjB5RXZzaW9BRjFwbDZQR3RIZkNYa1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQalp6Unljel83ZnRVMF9McnpwMWNQaEV3bHlVOFNXNlpEQ25SUzBzRERaZzl4YWFZdmpTanp0YkdtUmVtNHVuMER4QkZMQUZFS2o4bHJRYXZKRUlSNFkyVVR4VEpjTThVSUgxZnNrTGtpVFVOaDFiM1R0dWV5RE9SYm9sT1h5eEVRdjh3Q09HUWt3WXE3dFlv?oc=5</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>08-05-2026 22:36 UTC</t>
+          <t>09-05-2026 08:23 UTC</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Hantavirus is not listed as a side effect of Pfizer’s Covid-19 vaccine</t>
+          <t>Eisai, Biogen Receive Extended FDA Review for Lecanemab Subcutaneous Starting Dose</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Full Fact</t>
+          <t>BioPharm International</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxOQXdZaDRXZ3dUd01kemx4TmJrQVF3Tkd4S29hVEx2cC1fY3VlMV9jZFI3X05BWmlOdVdEdjVLTi1HcV8wa0k2MHMxRzFSMGZ3VndZU3Z6cXVuSFhmcmFrck1Jd0duNENNQ1BCYXdEcjkzRHJnRnV1N2tfUkFCVFpIVEc3eXEyNlUwNHJ2TnVPOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQZE13SWpQdUlEamNKSGExdEJmQi1jVU00aFZTckhtZXU3S3RoOTRiTzFUbVF2bjhobXgtU091RXJYRzluci1VN1J6ZzU5R3c4aUtISF9VUVBSeXBuWTVyNFJtMmpnVU9ST294WHdQc2p0ZHlQNGVaUkFMYTc3YXVvZVgzVzF4VE1idFB1TWlMN19XeVNqVW43czNOV3g5OEQyd3V4bTdGOEVmTFV6T1UwSFgycFduMk5VbU9yaUtCZFVSdw?oc=5</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>08-05-2026 16:28 UTC</t>
+          <t>08-05-2026 16:47 UTC</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Pfizer Viagra stock: What health-conscious consumers should know before considering alternatives</t>
+          <t>Biogen Inc. stock (US09062X1037): Q1 earnings beat but guidance cut weighs on sentiment</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Portal CNJ</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAJBVV95cUxPZGdqUGIwcVY3NlpISG1ULWNyQlZOVW51bVgycHc2RUlYWXlIbE5jazdUQ2t3NFlvYVRkWjFXRVMzMWdVVm9adDVFMlRQRmhMSFdwUDhWTXRreUlqTFpfRXd1ZUxwNG5DeE1qdmxXaDZMUWlWOXVWbHlqT3NqUURucXFkNjVzLUVlRjMzeHpOa1JJRzliZUMteksxcG45X1dfQlBVODR1ZWQ2NnZ1NERka3J5cUdUY0Ezb3VjR29Ucm95N05td3lMRXVNMHhrRVRZRTZzS0hqajR1MzhTOXVRVDNsY0NqV01QWlpyZlBHODRwMHB3clVhaERUV1NpeUk0VV9tZEt6dU56ZmJL?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxPMndzbFgteVpacmNvRUNrRkdUX0dkcVBWcGt3cU9pZEFPVEkwTEt0U0lHWnhZVmNsTEFBWmNOWFdOM2FRNHdnSzRZQlpJdmxCdFZ3emt4LWY2Z3o1eGRwUEMwZ1dhVy1EYWR3M1dyMEFtUG1yWE9uMDR3TnM0UjNsNkdGZElTSDFkUTMyNjhTVVpvODBYVm1RN1ZQYmw3RHFtT3NuNzVMeHdyb0V6MHh5aHk3R3hzQXpTaHZQV3ZCTDVSaHNRd2JjNA?oc=5</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>08-05-2026 14:54 UTC</t>
+          <t>09-05-2026 10:56 UTC</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Novavax Stock Jumps As Pfizer Deal Cash Puts Vaccine Turnaround Back In Focus</t>
+          <t>Biogen to Participate in the Bank of America Securities 2026 Health Care Conference</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>TechStock²</t>
+          <t>Moomoo</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPdjdLQXA5dEc4TnJ5b3ZiUFBZUWJGbzBEUE5acG9DdFZJb1VzUkVZUWJLRXZtYXotcDNHX2lqbjV5TmVaUjQxWFcyNHVOUjlKTjRyRmtMWm9kOUhlMkpMOFZkNnlQOTN1WTZMaWt2ajZYcWtzdHZLRVFwTXBacGVpZnJzRGxMQzJPaEFKNTBnd1JUdTJPa0tnU0hoTDFnSGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNSXFtaUhnV2lEY2p0T0gzWGQ0UEYtYjM3Nm5JUG5CMjRkbGZFYUNKWmdJbHZDNWxBT01iV21VRjNLVUJaUUxaYWd3WWVTWVMzRGRObko4THRFSDl2T3ByZjd1YThoX3Jmc0ZKWkM0STVnQVozb1ZnTGZBZGh0bG9Ra3M1VEpBMmt4c080bVVTd1FEVUh5enJRWTlnbVlFNlZaRTZsMw?oc=5</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>08-05-2026 17:55 UTC</t>
+          <t>09-05-2026 08:58 UTC</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Earnings recap: Airbnb, AMD, Shopify, Pfizer, Uber, Arm, Disney…</t>
+          <t>Biogen Inc. stock outperforms competitors on strong trading day</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Proactive financial news</t>
+          <t>MarketWatch</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPZXlwNFZaVmVDWWpOV0ZIcFFtTF92TllLclFMMDhVaHFPTVhCaVRnM09HU1JpQmRZLXJwR1dsb2tadUJINm0xSGZDZDlTYkdKU09mN2VJd2VmWGVfRmdXYnZwSEJROFFRZVNQOXNtLTVNanFiQlFVYWVDS095cjctWnhzX1ZNTzRqeFU5b3RMc29pUlpyUlBYVWlSREtMVy0wQzhRRXhJcnZ0N1BVaHEyWF9QcWUyQzJPTlhmbFZZTXRNMDN1dGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQcGtNS3E1MV9xbnJiX3pxT1Uxb09CY0k5Zi05M19VMC05cHZBSThzUURYb3VFdUpMS2Fyb2hiRWVING9wM0VLZVVYTDMxR3F6ajZWOWM0MUVBc3JtbnQyQktrY3FYeEhrSmNmYllUUHFVWWp3OVVBN1lVbkVmZnVSanNwYmd1UDNMSGhqbF9vN0pEQ0RreEdGRHlZOWEycDJCbXlMdVFRUVNuaEl0aGs4SjdxbXh3ak1ISVBCdTRfNA?oc=5</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>08-05-2026 15:30 UTC</t>
+          <t>08-05-2026 21:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Novavax Inc stock (US66987V1098): Shares jump on Q1 beat and Pfizer deal momentum</t>
+          <t>Assessing Biogen (BIIB) Valuation After Recent Share Price Momentum And Pipeline Prospects</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQZ0FtY213TTlvVDI5OW40Z19UZDlKczhIbjdsaVVRNzFEQ3BpZVdZVXAzNG1pd0wzWjhyck81dzFzTDg2R2FCVzRCdVJKRFMyXzAxWFBuWjFvYzdFR3ZnZEJQNjVVZ0lWMk5yX2JqSGRXSkk1T2l6Rmxfd0dGdTlLWGQ3RUY1QWF0UzVuSzNhLTFBRUJPemJzTnhweHZnSHR0bWNWSTZiZXZXY1ctYXFBZUs4SVRFX3Q3dEJiR3l1RUtHeEJfODIw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxNOG1vVTZLUnZtWm1Zb3BPaWUycVFORXExbW9WdVExdVNMM3dHaTBpV0tVU19HWWJNWFZDTENzYzZ1aWVxQ1BIU0x4aF9ObF9YRkZDa1QxRV9sa3NPMC0tb1Q0b2lOTHB2SGhaWmVpME5zTi1Gc3FDYl91ZUlLa0hVNE51Z0RwUjZqX0l1VTBud0RJSHhtU3hiU0VaX3V5YWR2Tzh3M2huN2VnQWFiTTdkYXJMdUVUNktBbWZWUVQ0X3lGYXZ3Xy1VcTBuWVEtVUdrSDNteDZjSUJxLWNr0gHcAUFVX3lxTE04bW9VNktSdm1abVlvcE9pZTJxUU5FcTFtb1Z1UTF1U0wzd0dpMGlXS1VTX0dZYk1YVkNMQ3NjNnVpZXFDUEhTTHhoX05sX1hGRkNrVDFFX2xrc08wLS1vVDRvaU5McHZIaFpaZWkwTnNOLUZzcUNiX3VlSUtrSFU0TnVnRHBSNmpfSXVVMG53RElIeG1TeGJTRVpfdXlhZHZPOHczaG43ZWdBYWJNN2Rhckx1RVQ2S0FtZlZRVDRfeUZhdndfLVVxMG5ZUS1VR2tIM214NmNJQnEtY2s?oc=5</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>08-05-2026 20:04 UTC</t>
+          <t>08-05-2026 18:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Mixed options sentiment in Pfizer with shares down 1.52%</t>
+          <t>FDA Extends Review of Eisai, Biogen Alzheimer’s Drug</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>International Business Times</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQa093Q0RkNm1icGIzeE9XcFNYVFI3X09TZWpXQ0tDRkJmOUJ0MXJMWi14eFhfQkNhMTB5ZVpJckdOWWJOa0NNeU9HY3FPQmRrZ2J5NjFia2t3dWxTMVd4NDlVeU5yOFcyNUtESFZCNzJFVWpNelJvZkx6ZzJwVG96OWVYRHY4QWdjRUg5Rm9pQy1wZExMNncxU2VwaElNRTRkWks0OHFsUEI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPQi0ybkVGWE9LaG1sbUxiRWdYSXdTam96WS02RHpBdE9zVWhJNGlnYXQ2Zk5kblFRM0hpX0dzMUZRakIyM08wMkRuaEZ6eGlQdzloano4Mko3aWhHZDJSeFJhbWNBeEJZWEI1ZlhfSWV3c2FuSzhyUGdCUGoyWDhsREhORjhKdw?oc=5</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>08-05-2026 23:35 UTC</t>
+          <t>09-05-2026 14:05 UTC</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Trump Promised Cheaper Drugs. Some Prices Dropped. Many Others Shot Up.</t>
+          <t>Why Biogen Stock Was a Winner on Wednesday</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>KOTA Territory News</t>
+          <t>AOL.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPMll4MGgxR3JBQWpMdDdLbkdJc2FqQU1nUEgxbnVtSkRtQkU3UmRVVFpoNDJ0RXA5OE80c3lNMjVscHl1RURqTUxYQTZmQ1c1YUhlaUdRS0Q1bVFKQWRvaUZPN3ZMNWdQbHlvbk8xYnlmMFNKdWVwNFoxYWpWaTBzNEdqb1h0Z0pyc0FMdXdLYTJ6akxZSXQ1Q19vYzAwdmYwS1dWNlZR0gG6AUFVX3lxTE9RVG5udjNsLUZGaS1oVko5X3FDRTVUamJ4YXd4bmhmbzBORXBpcXhwcmNCNS14VGJUR3hUS0JEenVqS3BjMFRGUnhOd2dEWGR1MlpvZ2NJNjdvVVhwRE9QUWx5ZFFMbjRtZ3RkUzNFaEYtaXZaLXYtZEUzSUNNSVRvVjYwWVdERER3RXJWNTRydVdtSWtxTFpWbzNQUFFXRG5iMWpVTUk4YmFjY3ZYV0NYR0ZrWWdxdGI4Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxOOWp4b2pHaFdQQTNXYWxiRE5Iekw0V05zRmJ1dlBFMDhUczYyT1g1ekxoXzdaUVlTVlZJbkdDMHhIYVRNRmY4M0dwQjF2UlRPNnB1Nms2VDRybXAtaE1IdzNYM01oUXowMHBtR0UzSGxTVGZwbjd1RFcwbnl1ZkdteEhGVQ?oc=5</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>09-05-2026 02:00 UTC</t>
+          <t>08-05-2026 22:29 UTC</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Pfizer Options Spot-On: On May 8th, 207.87K Contracts Were Traded, With 2.63 Million Open Interest</t>
+          <t>Biogen Stock Gains Despite Extended FDA Review For Alzheimer's Therapy</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>富途牛牛</t>
+          <t>Benzinga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNb3hQa2RodDZPcHlmSzFLV1htcmRnV0R2NmYxYndOcW5YX1ZnS0RmQUJlTmoxTkcwQ0pJQllYejYxSU80aXc5cDdYNXRTYTJuRDdPV0dvM3RwREVDV3AwUHB6U3FpYW9CVnBFZVlLODVnNmdnV0o0MkY0dE1vb19BcG5XSnhkUjl2MjJXRUx3dkFnTkRrZHVv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQZzBhQmNrbXV3cGlBcHlnX21CdFg4QzBhUXdab25wVUZDWFBEWi16TW9hbE9WZnR5b25td0lKTGI0NWJuQ2NselhvNFN5R1Vxak9xN01kZml4SVhTUVhXckJnWWxRYzBMOElFUnlPMVBkUU1HSWFjeDE1ZS1PeldRVlZob09vcjRjRXVLRnMwY2pOa053UU9USXB6WThKOERkSUpQZmRCZ3BCTEZWTHptczRNMGxjMlNmeHc?oc=5</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>08-05-2026 20:30 UTC</t>
+          <t>08-05-2026 15:31 UTC</t>
         </is>
       </c>
     </row>
@@ -2407,22 +2407,22 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Eisai, Biogen Receive Extended FDA Review for Lecanemab Subcutaneous Starting Dose</t>
+          <t>Eisai, Biogen announce FDA extension of review period for lecanemab-irmb sBLA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>BioPharm International</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQZE13SWpQdUlEamNKSGExdEJmQi1jVU00aFZTckhtZXU3S3RoOTRiTzFUbVF2bjhobXgtU091RXJYRzluci1VN1J6ZzU5R3c4aUtISF9VUVBSeXBuWTVyNFJtMmpnVU9ST294WHdQc2p0ZHlQNGVaUkFMYTc3YXVvZVgzVzF4VE1idFB1TWlMN19XeVNqVW43czNOV3g5OEQyd3V4bTdGOEVmTFV6T1UwSFgycFduMk5VbU9yaUtCZFVSdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxOTnZWRGtwb1VNbF9UTEc0cmk5dllHVW91UkRVSGVIajAwOENUTjFLLXdVV1ZqcW9idVFLQVRvc0JMbmtBMndpajBBczlMMlhhblBoN0RYdTcybHgwU0tYWEtsY2UzN0Juc29fSUNkUnJVenhQN0EwQmNDQ2xGZE5yVkNZajJsNFdMOVZIWW5qZTNPRk1hc29oQ0YwRE9OTENSVHBqcVl2aFF3VGZHRXJuM1JxSmgwOWw2WmN4NnE3bGZteDhXRnhVQktMNnk2Zzd3eFg4anlGNEZTN2J2?oc=5</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>08-05-2026 16:47 UTC</t>
+          <t>08-05-2026 18:30 UTC</t>
         </is>
       </c>
     </row>
@@ -2434,1654 +2434,1654 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Eisai, Biogen face delay to subcutaneous Leqembi</t>
+          <t>William Blair Maintains Biogen(BIIB.US) With Buy Rating</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>pharmaphorum</t>
+          <t>富途牛牛</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1tdnFZUjBhTEpjUTMyNzVFV1JmYnA5b0p1OV83c21uaDMtZ0FwVG9KYVE1TXdfS1JhcjRpQ3k4SmdqRExHbTdFdXJEVEQ4bzk4Nnp0eUVtamExMXdSYVc0emNOZlNPV3JPWWlFQmhqcXZwbTFjMGgweUh3Yk5HNlU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQaFlxSTcwWTFVMlducW5URDcyRDhua2M4ekYxZGtXcEdHbEdNOE85ajJZTlBoZThQMnBpTWhFQUNyMko0SF80ZGJFUTB0M2l1RTFDcTljUTl0QzluYjBTeVFkNFdLbDExbXFJU1d6ZmRKaDNPcFAwY2V0TExJVkdQQ0tjd0dVZWJsWVloYUdrOUVrNzVUdERwXzl3?oc=5</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>08-05-2026 12:15 UTC</t>
+          <t>08-05-2026 19:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Blau Farmaceutica</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Biogen, Eisai hit with 3-month delay for starting SubQ Alzheimer’s therapy</t>
+          <t>Blau Farmaceutica Q1 2026 slides: 17% revenue growth, zero leverage By Investing.com</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>BioSpace</t>
+          <t>Investing.com Australia</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOUnBJU0wtcjZtTmlUaDhzc09hcEdmMUw4WlEtZUFGclVLYUk5SlFoSTZucDZDZlhuWE55NHBZR1hHeDhJSE9ENDVkYldBSUJDUDRnUmJyUHFla2xxVTZWR0I0Z2RKMHc4SkFBU2ZMLVBzZXg5eUdvVUZfdFRyakI3NTZab2J1ZHpMc2hfQXpHX05Cd0dtV3pyRnBhLXBzcGNlYUtr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPWi1XVGtENkQ1Ui1SVWxzdXlfOXpDeUJ0VmNYX1ZZN1U4Umt6ZXpYSnFmUF8tZE42SHkxOFBQVEROcVd2VFl6OGlRSmJHTDRPRmNrWThjalB4Tnp1U0xzR1luek93TFQ4c3JhMm5KSVhWQUFKeWRQV3FxOTlib2Y5QmpLbU5GbE9MYmVSOThjWVRxNTFlSXpxVmp2ZWY4ck9NY0lzUlQwcm1kM3l1X0MtNXNocUtiOWd6SmhpTg?oc=5</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>08-05-2026 12:47 UTC</t>
+          <t>09-05-2026 05:28 UTC</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Blau Farmaceutica</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Assessing Biogen (BIIB) Valuation After Recent Share Price Momentum And Pipeline Prospects</t>
+          <t>Earnings call transcript: Blau Farmaceutica misses Q1 2026 earnings expectations By Investing.com</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>simplywall.st</t>
+          <t>Investing.com Australia</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxNOG1vVTZLUnZtWm1Zb3BPaWUycVFORXExbW9WdVExdVNMM3dHaTBpV0tVU19HWWJNWFZDTENzYzZ1aWVxQ1BIU0x4aF9ObF9YRkZDa1QxRV9sa3NPMC0tb1Q0b2lOTHB2SGhaWmVpME5zTi1Gc3FDYl91ZUlLa0hVNE51Z0RwUjZqX0l1VTBud0RJSHhtU3hiU0VaX3V5YWR2Tzh3M2huN2VnQWFiTTdkYXJMdUVUNktBbWZWUVQ0X3lGYXZ3Xy1VcTBuWVEtVUdrSDNteDZjSUJxLWNr0gHcAUFVX3lxTE04bW9VNktSdm1abVlvcE9pZTJxUU5FcTFtb1Z1UTF1U0wzd0dpMGlXS1VTX0dZYk1YVkNMQ3NjNnVpZXFDUEhTTHhoX05sX1hGRkNrVDFFX2xrc08wLS1vVDRvaU5McHZIaFpaZWkwTnNOLUZzcUNiX3VlSUtrSFU0TnVnRHBSNmpfSXVVMG53RElIeG1TeGJTRVpfdXlhZHZPOHczaG43ZWdBYWJNN2Rhckx1RVQ2S0FtZlZRVDRfeUZhdndfLVVxMG5ZUS1VR2tIM214NmNJQnEtY2s?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOMURvc3R6SWxia3IwR01FLVBUZ211TVROT2s4N2hTcmI5VW9ORTNOUWE3STNraTZac3ZMTDBKcEEyUHJsZkhiQzJOMnh5el9PQ0NDcFBwM2hmMkItSERyU1pZRk1XOXhodVRuX0dOT2RKSUtteDhyaGFlNTBTR0Z3cElZeTFIbjBseG9FcnNOR2dIdFo0ZXBfUXVDNGxPSkVXUER5ZTFUTy1KbVlfMlhhX2swMHAwN0x0VS12Z0h6VzZmLUI1Undpa21FRm5kZXFKOFUxUGpoYw?oc=5</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>08-05-2026 18:54 UTC</t>
+          <t>08-05-2026 21:42 UTC</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Biogen Stock Gains Despite Extended FDA Review For Alzheimer's Therapy</t>
+          <t>Dr Reddys Laboratories Ltd Technical Momentum Shifts Signal Bullish Outlook</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Benzinga</t>
+          <t>Markets Mojo</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQZzBhQmNrbXV3cGlBcHlnX21CdFg4QzBhUXdab25wVUZDWFBEWi16TW9hbE9WZnR5b25td0lKTGI0NWJuQ2NselhvNFN5R1Vxak9xN01kZml4SVhTUVhXckJnWWxRYzBMOElFUnlPMVBkUU1HSWFjeDE1ZS1PeldRVlZob09vcjRjRXVLRnMwY2pOa053UU9USXB6WThKOERkSUpQZmRCZ3BCTEZWTHptczRNMGxjMlNmeHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxORmRqVGtSb1gySlNPZ0dRRk80YjBnNmt5UVRSLTNDUFBVdlZhS1RPWlgyLThtemlHQzdBQmRsdk0xU215dEwwdlRRY0R4a3FrMzU2SEVBMkl3WjVXMUtrdk5qU1IxZzlDMm9HazB3cjBoMVpEYnV5RmNyLVdGWVRiR2V2cndQUW1GdjdKRm5IbWp1dmZUWldKbFJtcUwtSUFzNlhXUVlpQkFnQURQMFJ2VlRHNVRmQndjcXhXSXZnWUFLVkFUWHJIVTY2S2pzQQ?oc=5</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>08-05-2026 15:31 UTC</t>
+          <t>09-05-2026 10:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Why Biogen Stock Was a Winner on Wednesday</t>
+          <t>Dr Reddy's Share News | Dr Reddy Share Latest News | Dr Reddy Share Latest News Today (7tUaFMHsUE)</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>AOL.com</t>
+          <t>Fathom Journal</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxOOWp4b2pHaFdQQTNXYWxiRE5Iekw0V05zRmJ1dlBFMDhUczYyT1g1ekxoXzdaUVlTVlZJbkdDMHhIYVRNRmY4M0dwQjF2UlRPNnB1Nms2VDRybXAtaE1IdzNYM01oUXowMHBtR0UzSGxTVGZwbjd1RFcwbnl1ZkdteEhGVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE10Wm9zY09jbHdKMGJJNzR6OHZJTHN1V2FIVnZoamYxOGtLcVRmSmVYZW5vaGZzZ1RydTJTa3lacnB0STd3YW9FbURuLWduc3BPLW5yckVTM1lweEp0UGlEMURkLVNJbGttS2d4RlBib0s?oc=5</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>08-05-2026 22:29 UTC</t>
+          <t>09-05-2026 06:47 UTC</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Alteogen posts strong Q1 earnings on GSK, Biogen licensing deals</t>
+          <t>Dr Reddy's Share News | Dr Reddy Share Latest News | Dr Reddy Share Latest News Today (5kmIsDEMbP)</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>koreabiomed.com</t>
+          <t>Fathom Journal</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE4zSF8tczZrbmZ0eTJWUDB0c2QybTlzZXc2c1N6bkUxLVJ5Y255ZW9GVldQTUM5aktPcEdWWkh5UERvVjBNaFJhVGtObUVvaTEzUV9rUDdPcFdBSUlwTW9uZjRKZnlfRHBSZzQtNk0xXzVrd9IBckFVX3lxTE4zSF8tczZrbmZ0eTJWUDB0c2QybTlzZXc2c1N6bkUxLVJ5Y255ZW9GVldQTUM5aktPcEdWWkh5UERvVjBNaFJhVGtObUVvaTEzUV9rUDdPcFdBSUlwTW9uZjRKZnlfRHBSZzQtNk0xXzVrdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE1WaXRZT2dtRmFuRE1fRmNEWHRTQXNocFZvWUpxNllOVWNreXBvNFl0QVBna3J4RlBndEo0bEtKaDYwQ3pleDE0VlROOEZPd1NFdWhNN3RqY1hCcVBYVm1qY0h6NVpQSmtQUHFkOTAyNUV3aExOdFE?oc=5</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>08-05-2026 08:28 UTC</t>
+          <t>09-05-2026 05:03 UTC</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Eisai, Biogen announce FDA extension of review period for lecanemab-irmb sBLA</t>
+          <t>Dr Reddy's Share News | Dr Reddy Share Latest News | Dr Reddy Share Latest News Today (uqC6xl9C4m)</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>Fathom Journal</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxOTnZWRGtwb1VNbF9UTEc0cmk5dllHVW91UkRVSGVIajAwOENUTjFLLXdVV1ZqcW9idVFLQVRvc0JMbmtBMndpajBBczlMMlhhblBoN0RYdTcybHgwU0tYWEtsY2UzN0Juc29fSUNkUnJVenhQN0EwQmNDQ2xGZE5yVkNZajJsNFdMOVZIWW5qZTNPRk1hc29oQ0YwRE9OTENSVHBqcVl2aFF3VGZHRXJuM1JxSmgwOWw2WmN4NnE3bGZteDhXRnhVQktMNnk2Zzd3eFg4anlGNEZTN2J2?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTFBhQU1TRl9pS0tHYXM2SmlTRVNUVGtNdDh1cDJ5eFYtYng1V1Nfb2JoLVN4NGNaekFVX25lYXVpSlF2UURxdEFGNlNub0daS3BuTEEtVHN3RFRWR0R0d2Y0WllwaTBlNUFQSWZvWl9lc1U0bUNvT3c?oc=5</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>08-05-2026 18:30 UTC</t>
+          <t>08-05-2026 20:19 UTC</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>William Blair Maintains Biogen(BIIB.US) With Buy Rating</t>
+          <t>Natural Biocon (India) Limited Reports Net Loss of ₹4.00 Lakhs for FY26 as Revenue Declines Sharply</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>富途牛牛</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQaFlxSTcwWTFVMlducW5URDcyRDhua2M4ekYxZGtXcEdHbEdNOE85ajJZTlBoZThQMnBpTWhFQUNyMko0SF80ZGJFUTB0M2l1RTFDcTljUTl0QzluYjBTeVFkNFdLbDExbXFJU1d6ZmRKaDNPcFAwY2V0TExJVkdQQ0tjd0dVZWJsWVloYUdrOUVrNzVUdERwXzl3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxPTVFVV2FrSXF3cGk5UGVkaW1JS3FTa3dCMHExdkZQQ1R3TGRUc3JoRDlad01VN2NBcENJNkFlM3BpLUtkTWEtdGNTZ0dDWFhHVXJMNnVidm1JVnQ1NUE4dFcybjBtRkc3N0hYWmIwbjR3bnRpRHZnaVA2NHdlY1FrOWlmSjFmblU4MHZzWnRubjk5VTlhSlRWLWpKOE5xb29Sdm0yX1d1Ri1IdlpaRUlIOTZqQUtwVGF1bElTbmt2eFBTMzJ5eElEbEhfdU16VGhLZmE1Rm8zOUZ6OG0wZl9GeDFqNHJtZkpH?oc=5</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>08-05-2026 19:54 UTC</t>
+          <t>09-05-2026 13:44 UTC</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>FDA pushes back weekly Alzheimer's shot decision to Aug. 24</t>
+          <t>Biocon shifts focus to margins, capacity utilisation after expansion phase</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Stock Titan</t>
+          <t>ETPharma.com</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPcE1jekJISE9ZUmhZMllGX0lTaHJzVkdOMHc1VUEzN3ZRanlyenVZLTlrNjVsempZV0tKT3F0TWpmS2pja3RMSUY4X2x3Zk5iQlkwdlNNZC1Lalp0ZVdDOHp1RmhpV3IwUmtTSWE3dkJWd1IzQnQ1d1NUcEdxQ2p3RERXTTY0TGgzLXpQV3l3ZlZxZnJpUkY5b1pfT0VCNUs2MGtseTBLdHRfOGJNWTlaallPbEV1MkRDOEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxOcTVDV29rYVlZLWZmX0RQbUVaeXFQTWtwZl9nV2VGTFo4UTN5bnVzRnFhM3NVcjhuX3R0cGlDTXU2cF9JSGZQUzdxQURTdnkwalVhMWVsYThUU0NpMWRqSXp5NlFUcm4xWFdhOXI5ZDZScEpHdUxKaVotTWpWZkNLSk5qZXNPbjNEelNKSEk4S1ktb3RNYnJvOFRXVVRxY2Q0WWYwUFNzUTVlTXBoQU5pUmdPQkVfWmFmc2NlT19saW9sRk5QWTRnUElTN05rSW91dE9ZbFEtaF80dTRuNXpnVllkQUxFTUXSAecBQVVfeXFMTnE1Q1dva2FZWS1mZl9EUG1FWnlxUE1rcGZfZ1dlRkxaOFEzeW51c0ZxYTNzVXI4bl90dHBpQ011NnBfSUhmUFM3cUFEU3Z5MGpVYTFlbGE4VFNDaTFkakl6eTZRVHJuMVhXYTlyOWQ2UnBKR3VMSmlaLU1qVmZDS0pOamVzT24zRHpTSkhJOEtZLW90TWJybzhUV1VUcWNkNFlmMFBTc1E1ZU1waEFOaVJnT0JFX1phZnNjZU9fbGlvbEZOUFk0Z1BJUzdOa0lvdXRPWWxRLWhfNHU0bjV6Z1ZZZEFMRU1F?oc=5</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>08-05-2026 09:01 UTC</t>
+          <t>09-05-2026 02:46 UTC</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>FDA Extends Review for Biogen's Lecanemab Treatment (BIIB)</t>
+          <t>India Billionaires</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>GuruFocus</t>
+          <t>Business Today</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNdi04em5aRjg5VWdQT0J6Qy1zY0p2LTRGVzJGeWZsN044OTBveTA5LXNDYkFfWXdhdHRzWG04blUzalVLQVFVYjRBWk5KM1pabDlyOTczNXVERVJKX2NyZFUyNWdNRHRZeXUtV2huX0xiUmJXNWw0Wk1qUVdFR3pkRDVIUENxV0phNE1kRHRfOWNvbGxlcVNRUU9nY2hTRVZmUnRyR3dZU2lodw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE5lN1hzTldqb2xheHgzZEtfQkFreHNCYklvbExxSzNlX1lYNzhtY0lNRmd3LU5oOV92NnVuT2xxcERVaG14bktaUTA3VzhkOFVoVndJVE9jcXdfV0ZabTQ2MXhYNHY0TzNDUGNXQkxPcFk2R1NPNFE?oc=5</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>08-05-2026 12:11 UTC</t>
+          <t>09-05-2026 11:58 UTC</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Biogen (BIIB) FDA Extends Review of Leqembi IQLIK for Alzheimer's Treatment</t>
+          <t>Biocon registers net profit rise of 5% in fourth quarter at Rs 126 crore</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>GuruFocus</t>
+          <t>Deccan Herald</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPOG9BYjFiYVNsclRPMTRadkQ0R2FJZUhEenlTV2JOS0lqVWszREVqVVNRUWE0aDN6M3dxM3RzMExCa29ZaHhMbHJtc3FyT1M5LTY0NUtBdGhKVm4yOTNBaFg5MHVtRWJCdkJxRzU5c0JRT1kzbnJaVWJCWGh6d0d4dXc1TzBYWUFJdzRaVGI2WTE1LWw0YTJTc3NndVJ2ZzlGWUx5M21HY3NxWTlvUzgzZTMyOXhkRnozQk9ZTnhqcWY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPNWkxaHJod2ZSSW5yMTI4dGVWRHNsRlVnQUc2RFd2eTM4S3M3VlJMM21hSnBGamNPUzRObTlUVXhRdEhweFBfWVVOLUktSk56bzdHWGZ5cG1ENXlQc1E4NGxPd2QybENHUkY4eHZrZXF0MTltRnpLTXFEZHEyRHN5WHZOX0lUdE1tSlVpU0hDSDBHRlo5RFFfd0NoNk0tTnVpZ3otOWhmMDNZMkZvci1rYW5ONXBnSDZXS0JER3IwWjVqNUVDNVE?oc=5</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>08-05-2026 10:30 UTC</t>
+          <t>08-05-2026 19:21 UTC</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>FDA Extends Review of Subcutaneous Starting Dose for Lecanemab in Early Alzheimer Disease</t>
+          <t>Who is Kiran Mazumdar Shaw? Inside her Rs 30 crore Glenmore Villa in Bengaluru, her education, career, Biocon journey, $3.4 billion net worth and more</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Neurology Live</t>
+          <t>ET Now</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQTXhvdGQzV0cwSGNMU3VzYzJhRlZiOEZzTVJCel9mNEdJc3Y2elNDcjQ1WFlldks4ZGRtU0l1WHdFUXludFg1QTYzd1NDUGEyaFZ3NmZ2U2NsN3ViUVVrdml4TzdIeXBlLXNibWhseUhvT0FHQ05WWlJGQkE5WHJzM2VSREhDeUZJRFI0Ny1hb2VFeXZwUzl4NVRHSXp2Sm45MXAxOVh1QnJSbjJxdy1sUEpSUE8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAJBVV95cUxNWWtkUll2MWxsT3lXWlByUEFHZVVnSEZoRUQ0SE8tbkFSOTZFOGlqSXpLdnBmdUlKVnR5QUthNkU5ZUxwck5vNGNmaG9UbjBRTGFINVR1REdkLWc3SWl5a2pEcDMtRlFZRS1EdWZNQVdSM0JCel9Zd2tqVURVamVHVV9uZTJYWUFrYlYteFRGSEx6RmYtRXpBRS1KQ0hlTkdoYzRSN1psYVJiZ2xYT09lbk04cTg1NnBZSzhfc0tfOTh4SVdsVjFlSkFyR2ZwZ2pyM2ozczRLMnFqTWlxdjcxUkhfYlFQMy1lbVRScDNESTRWbWdmVUhtR0k0RkdPeFJpWjJpRkpob3QwUHExUVVPUDVjcWw2VExQbWE0N2V6UEdndy1DdlF6dkhleHDSAawCQVVfeXFMTVlrZFJZdjFsbE95V1pQclBBR2VVZ0hGaEVENEhPLW5BUjk2RThpakl6S3ZwZnVJSlZ0eUFLYTZFOWVMcHJObzRjZmhvVG4wUUxhSDVUdURHZC1nN0lpeWtqRHAzLUZRWUUtRHVmTUFXUjNCQnpfWXdralVEVWplR1VfbmUyWFlBa2JWLXhURkhMekZmLUV6QUUtSkNIZU5HaGM0UjdabGFSYmdsWE9PZW5NOHE4NTZwWUs4X3NLXzk4eElXbFYxZUpBckdmcGdqcjNqM3M0SzJxak1pcXY3MVJIX2JRUDMtZW1UUnAzREk0Vm1nZlVIbUdJNEZHT3hSaVoyaUZKaG90MFBxMVFVT1A1Y3FsNlRMUG1hNDdlelBHZ3ctQ3ZRenZIZXhw?oc=5</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>08-05-2026 18:09 UTC</t>
+          <t>09-05-2026 08:31 UTC</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>FDA Extends Priority Review of Leqembi Iqlik Subcutaneous Injection</t>
+          <t>Biocon Ka Profit 74% Gira! Ab Margins Par Full Dhyan, Naye Drug Ki Umeed</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Pharmaceutical Executive</t>
+          <t>Whalesbook</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPc0ZqZFBlUzFmMXl3ZkN0ekIxT1JjNHNXd3JvUG93aEEwRHlCZzNETzhiT1NKT1NLZFpxMWprNkduc2ZoVWVwSF9RZkRnMkhrektKSVdsWHdwNzBPc21kNWJwQUxFclJTakE2eE1qSkU5QjdUd0d4eHZrbW9hOHVjOFlxODdWOVBSV0QxVVliclhBcUhibU1DSGp5MA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxOWmVwaVVDaThRbGZhMElYc3J6OTNxQnZxYzgwV25CdzNXSTZsS3dzdUp6ak5yYTg0U2hyWlAtQ3pBYjRFMHBhMDVlNEdOS2pCVUtGRjhpVXkzOG9hbVdqeFZiN3phZUdPX3puQ0JlV1dGa0FkcUhpbVhPZkxRN2RkaHA1eFZweHRubmRYNkw0S18zZWRMNVhZTElNY3Z0RG5WOWdCVTdZV3lzSlVCUEZWRC1QN1diTkZ4VGVzQTVyYjlSLUJ0MmlQc0RFVmJaRFhYUkhTYkJHUTUxQllUNzc1Mw?oc=5</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>08-05-2026 23:18 UTC</t>
+          <t>08-05-2026 18:06 UTC</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Libbs Farmaceutica</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Semaglutide Biosimilar and Generic Market Size, Share and Latest Trends 2026 to 2035</t>
+          <t>Biocon shifts focus to margins, capacity utilisation after expansion phase</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Insightace Analytic</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQckkyWlpVRUgwWk1lSWF4cHVjZE13TWpqdk4xZnotYVlPaGpNdGI5djdSaDBuSnJmS3NtVF9SUXNjeThBMFlLdDhBcktrb0ZlMVhTa2FfRXRPekQ3MTBtSE9PUEFBUWJqMkZDRk5vQURfZDRMVzQ3QU5jN0hNYTI5SjZlUGc2SnhLbktYcnB5cFFtZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxPQlh6SHhGNjRWV0dlMzdCeEdwejZFWWFsWmFZdjNOSjJweW5lQ2NIT3RVVHRNM1FyUk1wRC0zRlVOYTlEQkllRkFhYWdCWmp2V1Y2eUVSend2bkUtME4zLVpyUTF6THVIRXFJZ0E2WTYybndvTm5xa2ZvVklHOEZ6ZjFuUDZFMUdDbFNaeUw0TFNqVWQwVFZhZ3VKSW5iMy0wVTloUXhCelNzcFdwYV92WXZQWWh1SmRDamxlNUp4VGpxTXZmZmlwYWJCSlV5UXRaQVhHd0lIOUNUNHYxQm9BaFY2NXlKUGFXOHdV0gHwAUFVX3lxTE9IQU1hM1IwSDRZUDhwb3hrSW10eDNnR1JHNmx4eVNuXy1FdENnaXlPN005dGx0WlVuQWM5N1N2VFNQSFB6QWRUYVB3cmNFN290RmpYb0pYX2s3R3NYenV5RTRwTnk1TG85YTlZNTJhc0xROFNNXzE3Smx0ZU50MHh4Q19kVWdOMjY5eFBTcHJHeXN5UVpTVGY4VFE0RnlDLXpsNkk2eXNLbTR3SVBSdEVWQndjdnAyT3FGVVpaX2dFbk1kRjU1MFdHTFhQaWNlbEE1VDFhbWZoSVNqUG9Pazk3ZE5kaUZ2bEZoR3ctMmNqLQ?oc=5</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>08-05-2026 14:27 UTC</t>
+          <t>08-05-2026 16:49 UTC</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Blau Farmaceutica</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Blau Farmaceutica Q1 2026 slides: 17% revenue growth, zero leverage</t>
+          <t>Claire has what it takes to lead Biocon forward: Kiran Mazumdar-Shaw</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Investing.com</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOd0luWGNUam9MUlA2N3pBU3hZeXJoX0R5NVNrdThOc0s3TWlSV3JDZEp2dnVfS1hNeGJZdzlNQWdtSTMySnlOMGFJY3FXVjhydzF5OFRLNW0yZGNvdlhmcS1FTmlIb2g1eGlicS1uNm1YbW05UVpyYjFwaklmOVhFTi03bHlVUjhkY05vMDlvU2h4SjctcEFZVG5nV1YzV09nOUJGZzlGSXBHVFJsakJEOXZJSW81UTF3aUlhRjdn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPbjBFVFhlWmZYd1A0a3doeWtOVFBHYS05Tm9BbEw4WnRHU2tDYnVndEEtc3I5R2hqbms3UG5kcmJmR19oZFFDcGpka1NncXdmZFQtYVRVc2pMek1LYU9yUjU0ZWtiR1M5QWw5WXVuSThTQlg4ZHRuZjdscFJOVTg3V1duMGhZcDRvOVAxdW54d2ZzTC1yWVFmS0d1ZGU4ei1oWWlvR1B4NFBpX0lnSzZqVzhYbzFTLW96ci1SNEc0b19tczhEMFlyb1Jpb2JDaURTVEdJc0RTVHE5QdIB2gFBVV95cUxPbjBFVFhlWmZYd1A0a3doeWtOVFBHYS05Tm9BbEw4WnRHU2tDYnVndEEtc3I5R2hqbms3UG5kcmJmR19oZFFDcGpka1NncXdmZFQtYVRVc2pMek1LYU9yUjU0ZWtiR1M5QWw5WXVuSThTQlg4ZHRuZjdscFJOVTg3V1duMGhZcDRvOVAxdW54d2ZzTC1yWVFmS0d1ZGU4ei1oWWlvR1B4NFBpX0lnSzZqVzhYbzFTLW96ci1SNEc0b19tczhEMFlyb1Jpb2JDaURTVEdJc0RTVHE5QQ?oc=5</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>08-05-2026 23:47 UTC</t>
+          <t>08-05-2026 18:15 UTC</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Blau Farmaceutica</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Earnings call transcript: Blau Farmaceutica misses Q1 2026 earnings expectations</t>
+          <t>Aurobindo Pharma Arm Apitoria Pharma CEO Dr Sanjay Chaturvedi Resigns</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Investing.com</t>
+          <t>Medical Dialogues</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOVlJIWnFlWXo2TjdzQmxPZWYyeXk2c2NfRHVwdWliajZUSEZiSUhJSlAtT0o5MENTYzZMdGEyMEJPejVoX2dsLWNYQ0d6c1UxbHZGYW1qWUFNSDVNSHhhRW5vQ2liV2xMbUZWZ2hBT3ZMd2dBNkJVU0ZmUG9ENmRKejdIdjktY2RXNWloeUNvUWN4Y3hJd3kyZlpKMHZTQy1zclZETmQ0aHhRd09yVF9oM0ZqbzI4ZzRicFZQTzRna0xqWTNvUjl6TVRGbzV3a0M5?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOSUxfV2YzSVRsd0xLNDBPVU9GSUdsSDZUWmlaUDRsYWFSXzZ2M1BQZi1Bc0VRY1h2UjVKVWZ0WjZmR1BKX3FuZWF6bnFXNUs5NzgxUVNQY0pmbXVTdERZSVptZG5QbGxoQlhfdDVqMXBtb0FLc1dWQUdoNng1YWJTbXpLQ09RMkJGYnVpR3V0WnRJUmZ1amNOVEVPOExTeTduTTd0Y2Z0T2RUcURta2VJdWo0QzhtbjdQbE5LS1FaYlRyZzjSAcgBQVVfeXFMT2lVX3Y2UUQyNTNqZW1zY3pyS2ozM2JldnhuaTN0SEJuaEVocU54ODJ4X3FqV1I3c0FSU1dqZXF1MERoejBGY0dJUU9vRlAzQ0xjem42MTFLZC1WSjBWdW9Tbm9yNUdmX3JCODlNWnAxR0U1X056dTZvbnNJMHlLR0dRMlFwZ2V6T3VwUDRCM0lZV3lOcldDQXNiRGZBcGF4Vm92R3RFSERyazByTy1zRTRSbHM1S2tkdnVaSHVMWEY5bWt2OHRMcE4?oc=5</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>08-05-2026 21:40 UTC</t>
+          <t>09-05-2026 11:10 UTC</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Dr. Reddy’s-Nestlé Health Science Launch Celevida® GLP+ to Support Patients on GLP-1/GIP Therapy</t>
+          <t>Aurobindo Pharma Completes Buyback of 54,23,728 Equity Shares at ₹1,475 Per Share for ₹800 Crore</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>The Indian Practitioner</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQNUlZRGNfUVg0NXFGNm1ydkYyYkxRMkozR0hkQjd6T0dMYVRBZnZldS1HQ0ZvQ004bV9uSmhVaWUtcUtSLTZHdHNON18td08tdTJIN1V1OV8yUFUwNHd5aEhldm8zZkQ1TnpleGJsS0xTalM1UkxtZmZnOV9BVTRiaXdWLVVUa1Y4X1dfSXlyd0tReUJ4Y0VzSGh2NmVhSzlocTBiNmxWcXVpQnktUW1nUm1sdk9odXcteHA0dWlVN3lLS2dOVXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxOQThLZTY2aURBa3lTV3UzUkFaTzNpYlRSTWx6VTNsS3pPeXFXWmF0VFBrazdwWUFIdENVRVJ0X1F4cVgyM0dXd28xb0hFY0c3MW8zdDJSVTRTOVdVaDN6N3dXbk9wcHZtNy1jMDBKOFNoWFZFX1g4RzlVX0ZwWkJsSEpVOGxuSzV2SVFRWnMzZi00YjltY1lhelAxQTZJNk5hbHFvRVhtNHpkX01BWE5zRWYySDZyVU1Kc1dxTmx2eGQ5ZFdHZklmMjg5M3c1UDBkQmM5LTdyakRrSWRFVXBKeDlWNkY1Zw?oc=5</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>08-05-2026 12:52 UTC</t>
+          <t>08-05-2026 16:42 UTC</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Dr. Reddy's Laboratories slips Friday, underperforms market</t>
+          <t>📈 Aurobindo Pharma Zooms After Getting EIR for Telangana Unit</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>MarketWatch</t>
+          <t>indiaherald.com</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPVnRxYWF5YzVBNXF5cU56TjlzSmgyc0ZsMmtGenA1OVJWMEVBYzJSWFRpZUZ0dTRpb0Z2WTh3aUZXVmdtZGZSMjF0YWRNOHNhUXZ0dGlONzlTZ3pKRmlibXRKdWp4Y2I5eE9TS2VRWmtNdUdzTktiUUN3Q19HMkpraldTcEhVdjF0TWdRZEZfY1RrLVhkeDhfeDc3LU1ZWVJCRUxab1lLZWFBOGtBaEYtWU5xOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOY1pWODB2QkdCX3EwV1dsS2M3VTBDT0V3NGVqRllLbDNYM0JqaUlTUXZmZFpzWnVmMVJRY19CcVdhX2owcldYVDFsUWNoajZRaENvXzk3dDlBaWtUdGh5TEVwZjdsaTdNY3Z6RlprbmhlQ1BzaEw2UHN5cy1fcjNZaldTbnc2b1gxRk5xZ2tjRm96am5mcld5ZktIRXRSQXlHX2M3TFFnNTZlekhRMUHSAa4BQVVfeXFMTmNaVjgwdkJHQl9xMFdXbEtjN1UwQ09FdzRlakZZS2wzWDNCamlJU1F2ZmRac1p1ZjFSUWNfQnFXYV9qMHJXWFQxbFFjaGo2UWhDb185N3Q5QWlrVHRoeUxFcGY3bGk3TWN2ekZaa25oZUNQc2hMNlBzeXMtX3IzWWpXU253Nm9YMUZOcWdrY0ZvempuZnJXeWZLSEV0UkF5R19jN0xRZzU2ZXpIUTFB?oc=5</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>08-05-2026 10:30 UTC</t>
+          <t>09-05-2026 06:04 UTC</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>BioTecNika Times- 08-05-2026: FREE Career Boost! Govt Research Jobs + Novartis, ExxonMobil &amp; Dr. Reddy’s Openings Revealed</t>
+          <t>Buy capital goods on dips, stay cautious on IT and consumption: Sudip Bandyopadhyay</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>BioTecNika</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5NWTdnX0JZS0VMaXVoWlhVUVhsRkxxaTI0WUJEM3NjYTRMRl9Oa0haQ3MxVVh5R2hvY2VPeG55TzJqR3daNjE0VUdPX0VkSy1WRkxkaGRrcmxzMm1aY2xLZnYxWjhmdXUtcldhWUlQY0LSAXZBVV95cUxNZk0zYzQ4LUdDZlJQdGJGVzQ3NUdpRF8yOWsyc18ybW4ydHY1Uzc2MWRFX0FmR0h5WFFLYkZNb1Nuc3JGLU1pZ0tRN0k5Wll0SkFYajlfNzV6N0M3RkhhY3g1WlhDRm1CS0lNNmVpeGg2NzBoNjJB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxOS3BJRzVsdmFOLXBRYmdkUmVMejQ0NjVYdy1uY3ZmOGxfLVFCZnFkMHNNZkJGZE5LVW9DcjZMTXhhVGNqcEdvT2U4cDEtZ3FiZ0dGd1dLeFpuLTE1YUFQSkNqWkFkd0tfcEFySnBhTjRVZGZzVXU1aGJIak11RFVxRGNLMHRGeS01N05jdk95UmRXOWZVUDF4U1g3TU1xeFh5NmlPX2ppcUZnYjUwa29pN1FkT19TeFJVSXEyVTEzNW1UMzNVbnVKSVdkQ1l1cTdkMHVNTEJJeDE0V29YcHpkZDYycksyZFVKdy1v0gHwAUFVX3lxTE11THJzOWphdWhJbE93bi1DRlF0YmNTck5SY0U0eHlCOUM0WFpBQWpleWV2ck1CZDNkVHBmVzhwcTl0RzEtajN0T1Z4OUFUV2E1OVpDZUFlYU5Gb3NPa0NjRkRZU3NhVGdQM2pZRXN5eHduVDNZOWZyR0h6NEhaNVl1QXhHcEIzS0xnVFBJYWUwSTE4UGJFbExJcFBsd0kxa2s5OG1Nbi1ZMVZvQWFrQTFkblZXai04enBhT0gyRVoxbktKUEdnY0tieXRkWXVnVmVmdkk4QW13RXk4cmFUUzNQV0pnX0h4TXpEVVRpNjFTbg?oc=5</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>08-05-2026 12:49 UTC</t>
+          <t>09-05-2026 05:45 UTC</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Consultation Workshop on Bharat Soil Health Policy Organised at ICAR-CRIDA, Hyderabad</t>
+          <t>Indian Pharma, Tech, Engineering Firms Pledge $20.5 Billion In Investments Across US</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Indian Council of Agricultural Research</t>
+          <t>IndiaWest</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOQ3huOWxZb212UjhNV05neEtFX3ZiZm1mdkIxSjBFaXRoNVBweVlzbVFXdU01RHQ0ZHVNcE43cUlZMWEyTW42ZTRQTVItdWNyLUU2bU9od2FwN1pMcUJobnJSQjUwRWFKM1E1T196LUZxaHFoMzNmbTZsUDNQclk0U1hudHJLZGxPLTNHVzFFb3BENDgwcmFtR0gyeDdsUzV0T1FR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNREoxRU5pYko1aW00NVVwSUNBUzFHRlMtSHphUmRNdjg0Uk1YRnR6WnhPdkFKei1rU2d3UnJhbGVyMkZ5ZG1KLVN4anZjb0xjd0R1TGJZTTgwbFNtRVM5a21hY2xHamJkZW8zRm96SjlCTmNCMEl2VFVkQ2k3TFVDaHNoQnZZclBSSlFlREh5WWFTX0d1WVZ1ZnA0YXZoaFAwODVtNGdvVQ?oc=5</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>08-05-2026 10:43 UTC</t>
+          <t>08-05-2026 18:14 UTC</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Biocon shifts focus to margins, capacity utilisation after expansion phase</t>
+          <t>Pharma Executive Duped of Rs 7 Lakh in Fake CBI-Style Digital Arrest Fraud</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ETPharma.com</t>
+          <t>Medical Dialogues</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxOcTVDV29rYVlZLWZmX0RQbUVaeXFQTWtwZl9nV2VGTFo4UTN5bnVzRnFhM3NVcjhuX3R0cGlDTXU2cF9JSGZQUzdxQURTdnkwalVhMWVsYThUU0NpMWRqSXp5NlFUcm4xWFdhOXI5ZDZScEpHdUxKaVotTWpWZkNLSk5qZXNPbjNEelNKSEk4S1ktb3RNYnJvOFRXVVRxY2Q0WWYwUFNzUTVlTXBoQU5pUmdPQkVfWmFmc2NlT19saW9sRk5QWTRnUElTN05rSW91dE9ZbFEtaF80dTRuNXpnVllkQUxFTUXSAecBQVVfeXFMTnE1Q1dva2FZWS1mZl9EUG1FWnlxUE1rcGZfZ1dlRkxaOFEzeW51c0ZxYTNzVXI4bl90dHBpQ011NnBfSUhmUFM3cUFEU3Z5MGpVYTFlbGE4VFNDaTFkakl6eTZRVHJuMVhXYTlyOWQ2UnBKR3VMSmlaLU1qVmZDS0pOamVzT24zRHpTSkhJOEtZLW90TWJybzhUV1VUcWNkNFlmMFBTc1E1ZU1waEFOaVJnT0JFX1phZnNjZU9fbGlvbEZOUFk0Z1BJUzdOa0lvdXRPWWxRLWhfNHU0bjV6Z1ZZZEFMRU1F?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQbTFCRU9LWXNCcUUwNm5lNU15a2dMQlloQ0tBeVZRX2hVWU1VelJFNHVxNG1NMGFsOE50V2IzaTZnYWdMNUpuRFF3eTVOVk93SUNuMFZEcEdqTTd2cXB4dEZWaEZUMVNxbldVc3ZsektZZVVoNE9ILXdMdjlURHdHMjgxRlBfUmFGTVhaS2gtNVFvZXdvWTdnSURPVU02T1VKTWVwX1hIY2pfZ0F0YUxuWmo1R1FhMC1waTZreUxvQ1hHUGVGWkVzb1BUMmNnbTjSAc8BQVVfeXFMUG0xQkVPS1lzQnFFMDZuZTVNeWtnTEJZaENLQXlWUV9oVVlNVXpSRTR1cTRtTTBhbDhOdFdiM2k2Z2FnTDVKbkRRd3k1TlZPd0lDbjBWRHBHak03dnFweHRGVmhGVDFTcW5XVXN2bHpLWWVVaDRPSC13THY5VER3RzI4MUZQX1JhRk1YWktoLTVRb2V3b1k3Z0lET1VNNk9VSk1lcF9YSGNqX2dBdGFMblpqNUdRYTAtcGk2a3lMb0NYR1BlRlpFc29QVDJjZ204?oc=5</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>09-05-2026 02:46 UTC</t>
+          <t>09-05-2026 11:29 UTC</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Biocon registers net profit rise of 5% in fourth quarter at Rs 126 crore</t>
+          <t>Torrent Emerges Early Leader in India's Generic Semaglutide Race with 38% Market Share: Report</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Deccan Herald</t>
+          <t>Medical Dialogues</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPNWkxaHJod2ZSSW5yMTI4dGVWRHNsRlVnQUc2RFd2eTM4S3M3VlJMM21hSnBGamNPUzRObTlUVXhRdEhweFBfWVVOLUktSk56bzdHWGZ5cG1ENXlQc1E4NGxPd2QybENHUkY4eHZrZXF0MTltRnpLTXFEZHEyRHN5WHZOX0lUdE1tSlVpU0hDSDBHRlo5RFFfd0NoNk0tTnVpZ3otOWhmMDNZMkZvci1rYW5ONXBnSDZXS0JER3IwWjVqNUVDNVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxOVEpmS290Z0FVbnQ2cUFXZVRPY3BKM2JkVVp6VDh5RkZnb3k3X1RTazVuLTU0WDl2N1J0M3ZRVk8xNmU1SHFseWQ0LUtvYm9jM3l6VU9Pc043c0ZhNEJDdThJV2hmYWYyR2piSklOOUtSUEU2ZjE2MWw3dHU4d3d6TVpLYkVDclllZV9YakNrT1B3SkNaSHNIUnd1LXdDTU52TEx6cllmbDQ3SWp1U2RuTE00M01JQzFUTFFBVTdUM2lxOE9RYW1McXlDUzh2UWIwUUkyemFQSnF3ckl5U1lpR1RGLTc0UdIB5gFBVV95cUxOVEpmS290Z0FVbnQ2cUFXZVRPY3BKM2JkVVp6VDh5RkZnb3k3X1RTazVuLTU0WDl2N1J0M3ZRVk8xNmU1SHFseWQ0LUtvYm9jM3l6VU9Pc043c0ZhNEJDdThJV2hmYWYyR2piSklOOUtSUEU2ZjE2MWw3dHU4d3d6TVpLYkVDclllZV9YakNrT1B3SkNaSHNIUnd1LXdDTU52TEx6cllmbDQ3SWp1U2RuTE00M01JQzFUTFFBVTdUM2lxOE9RYW1McXlDUzh2UWIwUUkyemFQSnF3ckl5U1lpR1RGLTc0UQ?oc=5</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>08-05-2026 19:21 UTC</t>
+          <t>09-05-2026 11:53 UTC</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Biocon shifts focus to margins, capacity utilisation after expansion phase</t>
+          <t>Samsung Galaxy S25 available at its lowest price: Details inside</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>India Today</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxPQlh6SHhGNjRWV0dlMzdCeEdwejZFWWFsWmFZdjNOSjJweW5lQ2NIT3RVVHRNM1FyUk1wRC0zRlVOYTlEQkllRkFhYWdCWmp2V1Y2eUVSend2bkUtME4zLVpyUTF6THVIRXFJZ0E2WTYybndvTm5xa2ZvVklHOEZ6ZjFuUDZFMUdDbFNaeUw0TFNqVWQwVFZhZ3VKSW5iMy0wVTloUXhCelNzcFdwYV92WXZQWWh1SmRDamxlNUp4VGpxTXZmZmlwYWJCSlV5UXRaQVhHd0lIOUNUNHYxQm9BaFY2NXlKUGFXOHdV0gHwAUFVX3lxTE9IQU1hM1IwSDRZUDhwb3hrSW10eDNnR1JHNmx4eVNuXy1FdENnaXlPN005dGx0WlVuQWM5N1N2VFNQSFB6QWRUYVB3cmNFN290RmpYb0pYX2s3R3NYenV5RTRwTnk1TG85YTlZNTJhc0xROFNNXzE3Smx0ZU50MHh4Q19kVWdOMjY5eFBTcHJHeXN5UVpTVGY4VFE0RnlDLXpsNkk2eXNLbTR3SVBSdEVWQndjdnAyT3FGVVpaX2dFbk1kRjU1MFdHTFhQaWNlbEE1VDFhbWZoSVNqUG9Pazk3ZE5kaUZ2bEZoR3ctMmNqLQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPdUxET3ExRXVaZFNUTXM5aGZkUHJfdnU1NmFpVV9sa0dxSXFwbkwyQVc4UlJPMFlnTW9TVXlEaDRieVcteE43bDBQTGY3c0gzajh2Ukdnb3R5MEVGejhVems0U2dtRjFVdHoxLVVJNDVMdm14MkN6Mng5UGt6WEdnTkJqUG1XNWV2WjN5NExhSV9nUEhVbU5NR2NJWk1rUGliLUE4MFI5WFgxQVJOSy0wU1dydFp5N0tkUXA1QTdBUEhpR3BMRzFNVFEteWjSAcwBQVVfeXFMT3VMRE9xMUV1WmRTVE1zOWhmZFByX3Z1NTZhaVVfbGtHcUlxcG5MMkFXOFJSTzBZZ01vU1V5RGg0YnlXLXhON2wwUExmN3NIM2o4dlJHZ290eTBFRno4VXprNFNnbUYxVXR6MS1VSTQ1THZteDJDejJ4OVBrelhHZ05CalBtVzVldlozeTRMYUlfZ1BIVW1OTUdjSVpNa1BpYi1BODBSOVhYMUFSTkstMFNXcnRaeTdLZFFwNUE3QVBIaUdwTEcxTVRRLXlo?oc=5</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>08-05-2026 16:49 UTC</t>
+          <t>09-05-2026 12:29 UTC</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Biocon Ka Profit 74% Gira! Ab Margins Par Full Dhyan, Naye Drug Ki Umeed</t>
+          <t>Samsung Mobile Phones Under 10000: Best Models &amp; Price List May, 2026</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Whalesbook</t>
+          <t>Gadgets 360</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxOWmVwaVVDaThRbGZhMElYc3J6OTNxQnZxYzgwV25CdzNXSTZsS3dzdUp6ak5yYTg0U2hyWlAtQ3pBYjRFMHBhMDVlNEdOS2pCVUtGRjhpVXkzOG9hbVdqeFZiN3phZUdPX3puQ0JlV1dGa0FkcUhpbVhPZkxRN2RkaHA1eFZweHRubmRYNkw0S18zZWRMNVhZTElNY3Z0RG5WOWdCVTdZV3lzSlVCUEZWRC1QN1diTkZ4VGVzQTVyYjlSLUJ0MmlQc0RFVmJaRFhYUkhTYkJHUTUxQllUNzc1Mw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE16RG1FVTZORm9zREg4dm1LaUZIcnVJOFE3OU5DSHZ1clRIZ2JzX0haT3BGa3pBV1ZnU3M5RlFnWHd6U19odzRPbno0czJuT3dFR3BaN2xGRkFLd1ozYkxPZldpdzRZN3NVLWlYdXBia3Q3T0ZSa2N3b2ZR?oc=5</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>08-05-2026 18:06 UTC</t>
+          <t>09-05-2026 04:52 UTC</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Claire has what it takes to lead Biocon forward: Kiran Mazumdar-Shaw</t>
+          <t>Samsung Galaxy A57 Review | Dependable everyday performance at sub-flagship price</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>The Hindu</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPbjBFVFhlWmZYd1A0a3doeWtOVFBHYS05Tm9BbEw4WnRHU2tDYnVndEEtc3I5R2hqbms3UG5kcmJmR19oZFFDcGpka1NncXdmZFQtYVRVc2pMek1LYU9yUjU0ZWtiR1M5QWw5WXVuSThTQlg4ZHRuZjdscFJOVTg3V1duMGhZcDRvOVAxdW54d2ZzTC1yWVFmS0d1ZGU4ei1oWWlvR1B4NFBpX0lnSzZqVzhYbzFTLW96ci1SNEc0b19tczhEMFlyb1Jpb2JDaURTVEdJc0RTVHE5QdIB2gFBVV95cUxPbjBFVFhlWmZYd1A0a3doeWtOVFBHYS05Tm9BbEw4WnRHU2tDYnVndEEtc3I5R2hqbms3UG5kcmJmR19oZFFDcGpka1NncXdmZFQtYVRVc2pMek1LYU9yUjU0ZWtiR1M5QWw5WXVuSThTQlg4ZHRuZjdscFJOVTg3V1duMGhZcDRvOVAxdW54d2ZzTC1yWVFmS0d1ZGU4ei1oWWlvR1B4NFBpX0lnSzZqVzhYbzFTLW96ci1SNEc0b19tczhEMFlyb1Jpb2JDaURTVEdJc0RTVHE5QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxNUi1Demo2bnllaldTM2Ytc2pMdUlwY1pJNlNscmthR1k5enlIOFk3UU1ubUZUN0xQREtyTFJwZUhnb1V1YXZWRmRjbUR4T0Y0dl9GdnY2dWZsYnN5OXc1eUwyblV6dGxKRVA5d2NhTmNVdkMwckFDTUEyUDRyM2dVcVpKWlk5bWRJeEVmUXNjV282cmlmc3k4SHU2YmRsaS03ajAxNVVmV2lmTmQ0LVFfYm90cmFfb05fVkdGRU04TlMzZXNkeU1rT2JQR09vTTE4bXFfVXhRQ2tneXlhOUNoTmQycmwyY2c?oc=5</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>08-05-2026 18:15 UTC</t>
+          <t>09-05-2026 02:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Kiran Mazumdar-Shaw says family will stay on Biocon boards, professionals will run operations</t>
+          <t>Android Circuit: Samsung Reveals New Galaxy, Pixel 11 Specs, Apple Squeezes Ultra Flagships</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>CNBC TV18</t>
+          <t>Forbes</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxQSk9sYzlWNkUyckJmOUd6aW5nX0Jwd3hPV3hjSTBNZVBHbC1MdG9oQ1ZEWVJyQUFvVE5ITXhhYXVhSVlrZDhNUUt1YTZnM1p1SmNqcHJhdmdKNm1CRWFCazlJQldSeGJZNXYzZzBtTGpmUWkzMDhHZ1cySzFOTzdzZUhzUW9aeHdGQy1oRDMxMTBnRVREaFhFbHlvUzFxMnh3R2hOa1ZYVU5TOFRxZmVKQVVkVHhKT3NRVVd3bk90TE1scWdmc0lNZkxERGItcTN6dDBjdGhZcWJmeFJh0gHiAUFVX3lxTE9jWHYwOEp6dVNIWGRsdUIyZjNpNi0zLVpGTTUwZVBXMk5nc1lDUVRvTVFmTDdWSkNSWjN6T0dmd19Hc3BGcmRhMmNVSFlYeWxPcjhHZU94anZXQnZkOWVnMVo3a1lkTk54cnVTdFlRUlE1b3hLODlUM2dvX2Vhc0VCUmpyV2FkUnNEVnV0bFZzOHRkd0Ruam1GbktLTmtRd1JuMWRkWk03ZllRQXRvOS0xNHhLRTgxUDBRY0F3SFl5VGZ4NWhvY25pcUVESFhTUUVDendJYzB2QmFzVWhVZGFzM0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPbDhtWHlvaEE4MGdLVUNkbWVVTGluTHJFTFgwUjlEcHNLZGlwOGpJR1c4ZnJsaUl5dkNBcDB1UjZ5Ul9MUms3ZlJESkplZWtMTWhFY3NwRlBOanN1YV9vSmY5Y0E3QUhPZ0ItczBpTGkwcWlNV3NqbWhnVEVMRFdIVVdVbzM1amwwdThubHpiZXJWUmQtVzBKMGhJQTRqR2FtTlM5RFNGVV9EeVJRRkxjMW13UTdxOENxZVhocTJ4UDI?oc=5</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>08-05-2026 13:23 UTC</t>
+          <t>09-05-2026 10:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Biocon reports 63% YoY fall in Q4 profit, final dividend of Rs. 0.50 recommended</t>
+          <t>Samsung launches next-generation AI Mini LED TVs with smart features</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>Kalinga TV</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxPWWVrTmpvZE83YjI5NFp1djBMczliVmROVVdxeVlnaWFkZmk0bWVLUGdCU2VWMlQ2WEotUWlQYmlrWmY2aGVISGhjaDh4aTlzTnJuQV9WREVGelVob29GbUV2ZnBSNGM2WmU0Q2MxUHVqWjB6WWJoT1lGUS1wTV8xaDlRNVl2R2hldlJGa1RnU0ZENlhwb3pTaDJQQUg4RTBnWFhyUWhMdmxGa2JKb2xTSkdnYjBWZ0U1ZU5jRkZqWHF4aWpyWUpVUTREcE9lbHBWZVJ3enFmbk9ob0hnSy1pYlNpMkZQTTdibkhR0gHwAUFVX3lxTE1kNHVlZDFzaHZpbUd4U1c3VWd1WEVlc1Y3X2NNT2lENGVOSEJBdEt5NElTMGRLcnBjUlVGLXl4RGdDeGh1TDdRTW5abGR3OWUzeFRCSzQxQU0tTTlFRTJwMVBxWExBRXZXV1JFeTJ2VnZXZjExMDJnZVJMeXprbWh3aUJlOWNTekVaMmxhZm0zeDV3ZW5uNmJKVU1oaElDeDkyZ3lmUU5TYWlNRDNqSDJ0VkdUc1ZLelNaTkJTTzFWcjhYQmc2LS1tbWdpS05OWHEtZHBiWXI0LXAwME1EeXhPZEpLMDNfbnhOeEl4VktweA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQSnNaLVVjRU5qMk1PUmZYbHUyYlpvRFJWaUY5ZW9DSlk4WXB5OVgzWVpGNEVENm1RZm1pNlpqZV9CVERrb3lMSmNFMzc4d2hfOUs5SmQtcTlEVXlETFBnMkRpWEpjNUV0OVlKOHloZFNxZXI3QlhwYXpNSHBWN2dzRkpEeHItTXpQYnlQWEVPQTJKaG5BaVJ1dl9TQW51U24ycjZVTQ?oc=5</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>08-05-2026 10:58 UTC</t>
+          <t>09-05-2026 09:37 UTC</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Biocon sees strong biosimilars momentum, expects merger synergies to aid margins: CEO Shreehas Tambe</t>
+          <t>Samsung One UI 9.0: Everything you need to know</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>CNBC TV18</t>
+          <t>SamMobile</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNQWNjT1pKMGdobW5udlRONHQ3X3VPa21kQnQ2NXNzYk1jR3hPeXozU2s1QmxRMzZOeVVCN1l3clgwTmlEY2R1RkRTQkRQa3gyYl8xMDRYTXBYOU1VY1M0YTd0akl5U2FKMHNYNjl3WFhIeG5WTUpMOWRzSGpSbDRHSWpmb2hzZlpiMjNaQXpVY05KSGFiYkwyU3I4ZmRhLTNCM1BmZkJJcXZJUE5PZ0J6eERvQdIBuAFBVV95cUxQNHZGTGJDeTFFRmo2dG1Ia3F2Q1N0Z1ktTkRKZVM1V2R3aFlFZmdUNEVneElwZEtUVTZUOHpiRVNwVm9CZmU3RzRhaWpOOVphMjJyakRjSE1WNkRqaC12Q2p5cWJ6MzhKSWx6MU9rWXpYamFZcFJON0U3YXhCLXoyY2xnUGEwQlRSN2RleXJkQk9lZTZZdURlbnQ2aUVOWGlpUWNwOWk3Nkszb0dLaHB4NklUUDB1eTBm?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE41VDROWW1SaVZpZTlKMjhMQ0FQRmJjWmIycGxlelhRSzJlanA2T0xPenlUaTBlYjVXN2hIUjRMRlY0X1VfWDlPN21EUW1FRHFuaDI5Njd5bGZhaXZWSXhFX05DWjBVa1ZNS0Q3aWxsT1pDR3JXa2c?oc=5</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>08-05-2026 10:50 UTC</t>
+          <t>08-05-2026 19:12 UTC</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Biocon eyes in-licensing deals to expand biosimilars portfolio in FY27</t>
+          <t>Samsung Galaxy Ring 2 Launch Reportedly Pushed to 2027</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>IT Voice Media Pvt. Ltd.</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxQcUhDX3BBemNPc1RTTGhHUU1PUkZUR05iS1RNbFJwSFg5dktHcnphX052QjdKc19uOF9GVnZhRlhoT2czRWNERFI3YXh2RTZLU3FKTG0taWNCREhiM1I3cmFYVm5uWjE3WGM3dU10dEZKWmhsbFVGd3RuTnFYdVBOTzFxUVBldnlRbmU3Nkg2SDBucDNvbGpieHRKZlE2RnE1Q0dzWWUtMzVDbGhMbUpDb2Zzb2pEakg1OFpTNV9zMnp0Qmp4bFg2NzZjMDVXYkpucXhqMlJXZndQR1XSAdsBQVVfeXFMUHFIQ19wQXpjT3NUU0xoR1FNT1JGVEdOYktUTWxScEhYOXZLR3J6YV9OdkI3SnNfbjhfRlZ2YUZYaE9nM0VjRERSN2F4dkU2S1NxSkxtLWljQkRIYjNSN3JhWFZubloxN1hjN3VNdHRGSlpobGxVRnd0bk5xWHVQTk8xcVFQZXZ5UW5lNzZINkgwbnAzb2xqYnh0SmZRNkZxNUNHc1llLTM1Q2xoTG1KQ29mc29qRGpINThaUzVfczJ6dEJqeGxYNjc2YzA1V2JKbnF4ajJSV2Z3UEdV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxQNHZBSENVZ0FNclBvdHpISnNIbGhFdFV0TGhXWFZwUzVhbUVid2RXT2lzenBCd2swUzhvSnR4WlI5OTd6am02cWN0dXl5cVNpUFVvMzFkUmF3a1hBUHM3VHVGT1RDX1Q1S2JoU1NyR2pYbWJJM2hQSFVYbWRnWjYzNi1idw?oc=5</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>08-05-2026 12:54 UTC</t>
+          <t>09-05-2026 12:12 UTC</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma Completes Buyback of 54,23,728 Equity Shares at ₹1,475 Per Share for ₹800 Crore</t>
+          <t>Samsung Stops Selling TVs and Home Appliances in China — Here’s Why</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>Gizmochina</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxOQThLZTY2aURBa3lTV3UzUkFaTzNpYlRSTWx6VTNsS3pPeXFXWmF0VFBrazdwWUFIdENVRVJ0X1F4cVgyM0dXd28xb0hFY0c3MW8zdDJSVTRTOVdVaDN6N3dXbk9wcHZtNy1jMDBKOFNoWFZFX1g4RzlVX0ZwWkJsSEpVOGxuSzV2SVFRWnMzZi00YjltY1lhelAxQTZJNk5hbHFvRVhtNHpkX01BWE5zRWYySDZyVU1Kc1dxTmx2eGQ5ZFdHZklmMjg5M3c1UDBkQmM5LTdyakRrSWRFVXBKeDlWNkY1Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNNlRtcHRiNF9pMjRyLXhuMlpsekhybUdqS0ZRaTFaV0llVVFjVjNMb2VyTURtRXRIODY5WDVXVmdsaGI5emRtREZaWXpUOU10UGRqUGR6RW5DSkh6Z0VzdEhTeFJNMGhZOGMxSW5mODg3bzJUeTlKT0N0eEhxSkF6aml2cy1NeklfaDNTd0dLcw?oc=5</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>08-05-2026 16:42 UTC</t>
+          <t>09-05-2026 13:07 UTC</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>📈 Aurobindo Pharma Zooms After Getting EIR for Telangana Unit</t>
+          <t>Samsung launches fifth edition of Solve for Tomorrow, raises winning grants to ₹2 crore | Business News</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>indiaherald.com</t>
+          <t>Hindustan Times</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOY1pWODB2QkdCX3EwV1dsS2M3VTBDT0V3NGVqRllLbDNYM0JqaUlTUXZmZFpzWnVmMVJRY19CcVdhX2owcldYVDFsUWNoajZRaENvXzk3dDlBaWtUdGh5TEVwZjdsaTdNY3Z6RlprbmhlQ1BzaEw2UHN5cy1fcjNZaldTbnc2b1gxRk5xZ2tjRm96am5mcld5ZktIRXRSQXlHX2M3TFFnNTZlekhRMUHSAa4BQVVfeXFMTmNaVjgwdkJHQl9xMFdXbEtjN1UwQ09FdzRlakZZS2wzWDNCamlJU1F2ZmRac1p1ZjFSUWNfQnFXYV9qMHJXWFQxbFFjaGo2UWhDb185N3Q5QWlrVHRoeUxFcGY3bGk3TWN2ekZaa25oZUNQc2hMNlBzeXMtX3IzWWpXU253Nm9YMUZOcWdrY0ZvempuZnJXeWZLSEV0UkF5R19jN0xRZzU2ZXpIUTFB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxQQTl1aXUzX2lZWDBCdFJBTl9QQS1SNVp6bHFzSWxuX245RU5rWTk3Y1JiTHhXYVNFQzVVYnNVZjdzVkZQRHlGQ2h2ckhteHZPblBaY3ZzeHItSVdrRGJfNldfTVNqSU4wUHhTZHBacW93TXB6c3NVdmhGSEZNOFBGdnpLZFc3NlNHeEtVbExNTDl1N3I3djBnVy1rRUJuOFN0Wk42Y05WdHRmeVJrLU5UUXd4VzJNMHNiVlFtTU9mZ3lzNXRWT2xvWTNvWHNnZzY1NEdsN0tybUhpdWFqR3Nv0gHkAUFVX3lxTE9nVU9pRm9IdUVGMXJ4M0xrdnBvczVsdGRmVGpUSlE3YWpmM1NMSHZ4OWx0dkI2WGdQRktBV2x3NTRuQzFfa2lXN1dGUmNINlhTM0xrNW4yMFJPS0NNYnFPenVFTGgwUW9NTFZweEZmcUl1ejVRSE51V0tJbmotNXFRRy04YTQ2Yk1aZ09HcmRLbkIyNzlBTnRCZjN6bEN1dThiRUE4S2dkVEhCNTRmZ1hUeHE4dTFVX2trQ3FTaEdEYjY0SXJUd1BUc25waVloUWMtMUxKc3JfMDBYUzNzXzljWGdwbA?oc=5</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>09-05-2026 06:04 UTC</t>
+          <t>09-05-2026 07:29 UTC</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Budget 2026 Ka Kamaal: India Mein Share Buyback Ka Trend Chhaaya, IT aur Pharma Sabse Aage!</t>
+          <t>Samsung Galaxy Z Flip 8 vs. Galaxy Z Flip 7: Maybe not worth the wait?</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Whalesbook</t>
+          <t>Android Central</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxOYkZEYjdKUEc1X2kxLTY2azYwREFzUU4zYWE3YVk2eGFxTlEzWTRoa0ZXNkxuVi0zWmVsaFRZSzR5OGh0WVRnZFdsWnNGMTA5dXFyZ2VkSjV5cFdBNDduNVptM0FIUXpWZjlicEd0NER3YkczYVZkLVA2dWI5WVdReWRSR3k4S1hON19vTzhUUUU1NUUwZGxNc0dlYmRlNURneGxTSWlKTUNaZ2pxYXlIZ2JLUFY0bzF6elBJYmZuYVVMYWpiLVVCTFl4MThvOFNiYkQxV0VBYUp3bGhpRUVOTEtNendqQ3B5OWxGMnNB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPajJpcXpmY09UNmIwMXZpZ3ltM3hhZDdsUU5EMnBzMk53SmJjYkQ3RTBBVlAyckVpUHgwQW9zVzhQZXQ1Z0xhRUZ6M2tCUnNsV1N2RUUzV1l2UGJxWFhMcThfSGRaOFNtREVLUkVKZEFFM09HMnB6Y1RZTzd4cG9EMTZYOTFoUndpUEhNUTNxRzEzMEhSZ2tVN1dyaw?oc=5</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>08-05-2026 08:50 UTC</t>
+          <t>09-05-2026 12:10 UTC</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>India Tax Law Shift Sparks Buyback Boom: IT, Pharma Lead Repurchases</t>
+          <t>Celltrion Inc stock (KR7068270008): Buyback wraps up as Q1 profit soars on high-margin drugs</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Whalesbook</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxPdUZjYTM0cVpNRzFlNDB4dnU5bjVLRjFCNFlVMEdCalZGNnphU0xMVFpCLVE2RUhzSDdjOEVLV19PSGdEVHpYMjNPOEVtbWUzY2oxUHNzWHJiNUZ4Rjk2SENTQmVGSl9XN3NuZ0FYNmUwNnoxQ205NFV1UU1tNEhDU1R2YXlNSFIzZkd0Qk5WUjJXUEVRVmZUbzdEQmJoemZhMlpFWFNRMW1HTDZaYWF6dzZVTGpGR1pkbGtwRkNXMks1UkFUcW8zOGN0b2JYUXZfcVJIeXliUmZIS0VYNnJ4QnhickRuZGdKYm9FZA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQRDNjQ2pBOWE2SGVwTHlLcjlKclYyUDRrNGRlbXdpdExOelIxdWNZY1RpVUMxMGFpcFpVS2xYSXJIcWUydmlMZG0zVUg5RHRsZld3dng0THgyZk02OC1reDRwSFd3QTVzdTdIRlloUTFhMmhwZUY2dnFGbmZqaVNxaFg0dVdrNUhvMzhRRDRaYWVZRHkyUEUtMWdSU0RXY2kwa3lHTGVVb2pXU1liYWZPNExMd0MxZzFSdFR5YjAzc05qYzFnQmhFLS1n?oc=5</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>08-05-2026 08:50 UTC</t>
+          <t>09-05-2026 07:21 UTC</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Prestige Biopharma</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Buy capital goods on dips, stay cautious on IT and consumption: Sudip Bandyopadhyay</t>
+          <t>OneSource Pharma Stock: GLP-1 Ka Gold Rush Ya Valuation Ka Trap?</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>Whalesbook</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxNdUxyczlqYXVoSWxPd24tQ0ZRdGJjU3JOUmNFNHh5QjlDNFhaQUFqZXlldnJNQmQzZFRwZlc4cHE5dEcxLWozdE9WeDlBVFdhNTlaQ2VBZWFORm9zT2tDY0ZEWVNzYVRnUDNqWUVzeXh3blQzWTlmckdIejRIWjVZdUF4R3BCM0tMZ1RQSWFlMEkxOFBiRWxMSXBQbHdJMWtrOThtTW4tWTFWb0Fha0ExZG5WV2otOHpwYU9IMkVaMW5LSlBHZ2NLYnl0ZFl1Z1ZlZnZJOEFtd0V5OHJhVFMzUFdKZ19IeE16RFVUaTYxU27SAfABQVVfeXFMTXVMcnM5amF1aElsT3duLUNGUXRiY1NyTlJjRTR4eUI5QzRYWkFBamV5ZXZyTUJkM2RUcGZXOHBxOXRHMS1qM3RPVng5QVRXYTU5WkNlQWVhTkZvc09rQ2NGRFlTc2FUZ1AzallFc3l4d25UM1k5ZnJHSHo0SFo1WXVBeEdwQjNLTGdUUElhZTBJMThQYkVsTElwUGx3STFrazk4bU1uLVkxVm9BYWtBMWRuVldqLTh6cGFPSDJFWjFuS0pQR2djS2J5dGRZdWdWZWZ2SThBbXdFeThyYVRTM1BXSmdfSHhNekRVVGk2MVNu?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxPc3BoaWg4SUtEbXlyLVhGUkdiMkVNX0JfblJyYS0xT1FsZjZ0cHlLUmhzbURTYmJUUHJpQ3BNRkF1WllOLUQ0QnV6QllzcUJVbjBaN0szTzBkcWtzU0ZuY0ZLX0RlYlJJT1BGMDM3akd6cGpqbTJVWmhiNkhlOWJfbU9HSnhNQ25LRFQ3ZHBFX2lwekIyU1QySk9qc1ZjeUlTV2lSbHRRcml4QktIVUt5bGtyWU5DU2JBTVljNzhxV1VXTEg0QjVENE9BeU5INk94bEhfMTdoTmdxR1ox?oc=5</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>09-05-2026 05:45 UTC</t>
+          <t>09-05-2026 02:29 UTC</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Prestige Biopharma</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>India announces record $20.5 billion investment in US at SelectUSA 2026</t>
+          <t>OneSource Specialty Pharma: GLP-1 Gold Rush or Valuation Trap?</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>The American Bazaar</t>
+          <t>Whalesbook</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOR1VaS1VaMHVqVkNQbkhkRTVyN3B0LThfRXZyZUNKbXBNQ085dlhZbHVQanJRU04wVzRWWVE0ejhFOHlLTUZ3OVFSSm40cHRhdmp2UDFlRVV5MldFVVIxTk1fVUZRNlN5N1ZnSk8zdXRDXzBOeTMtdkRYdEdGaW43UE1sLXRKWnRWV2F3bndJa2FwWXpwYTFHd3Z6bnN6a2U0QkFrY1MtRE1SUUtrSVgyLTRJZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxPTURwNmY2djF5MS1rSEFTUHdHazVRcm01Sm9ud0J4OXc1Q1FNdDlJVDI5eGE2dGwza09vcFE3cld4U3pCdV9oWGlrVW44TEtJbDYySG9hTU1VRzBsb0ZoQXU2encwRWtTUURHNkFXZkhicFQ3dlhSR1F2ZHo2NzNIS3plUThBRFl0REpfdFBLbWFSbWhZMVRuOFlFZFBwSG9TZ3RuQTVqZ2dmXzVmaWFwTy02UXZNVHFGenFqOGFFemRhRld1azFTRm50VzdCOWp2VUk5Q1pFRURWOWM?oc=5</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>08-05-2026 10:45 UTC</t>
+          <t>09-05-2026 02:29 UTC</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Indian Pharma, Tech, Engineering Firms Pledge $20.5 Billion In Investments Across US</t>
+          <t>Daiichi Sankyo takes $610M hit tied to ADC manufacturing losses</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>IndiaWest</t>
+          <t>Fierce Pharma</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNREoxRU5pYko1aW00NVVwSUNBUzFHRlMtSHphUmRNdjg0Uk1YRnR6WnhPdkFKei1rU2d3UnJhbGVyMkZ5ZG1KLVN4anZjb0xjd0R1TGJZTTgwbFNtRVM5a21hY2xHamJkZW8zRm96SjlCTmNCMEl2VFVkQ2k3TFVDaHNoQnZZclBSSlFlREh5WWFTX0d1WVZ1ZnA0YXZoaFAwODVtNGdvVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPdGY5SFBfV1hyN0R1TUxMdkp3a3RJS1VXM1Vzal94YldVMUQ0SzZrdzVzZ21JODdpRnBjODY0OXlSLS05TzlkS3A5VVk1MFp6SW1NU2VzdGhGcDJpSUNiNUQ4SUluT0JfMUdKQUttRzhQRXVOeWZDWVEyN09UTDh0UkpxbWtOWGd3UzA3VjNMekZCNFpQSlpPR0VGV2I0NEpkSTJmaDdaRQ?oc=5</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>08-05-2026 18:14 UTC</t>
+          <t>08-05-2026 14:47 UTC</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>India Ratings Affirms Eris Lifesciences 'IND AA' Rating on Strong FY25 Performance</t>
+          <t>Daiichi Sankyo Co Ltd stock (JP3475350009): Profit hit from ADC manufacturing losses weighs on outlo</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Whalesbook</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwJBVV95cUxQOTBHNkVjOTlaRi1Ia1R5M3hxZm5YQWhpZXFBdkFNTC1QSVVhclFadHB3VzZsdTdXTkhSaDJDSnl3RGY2enB6NktUWHBFcjhzOXhIMUdmcmVHbjd0UFNfX2RVNmJtb0xLakk3cW40enptcmR5QzYybXdTWXg2VkVEa2d2bXVEdVBiU0E3dmdGV3ZadFFtRWNhSFN5b2djcXNEUGlTY29xU0NzLWFybi1CSC1tQzdFWFlEVFhMZkwxd3kxVTAtQ29uWUpnZFJ3S0U2RW9jZDFGajR0RkpXcEJjdGFxMEZCelI5c016U2s2WVpQaGFLVnFCWmx6eThRSmNqTW5Z?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOdGJSMVFMLVRQT3VqUV9FejNabkxFTEJ3dVFIN0pDcGxicVZVN1NKaTZnNjFWeEM3dXkySTVPXzhWNFhRaXM3VDR1dEJzckNJa2gtYktBRTB2b0VJN2dSSjVlOUc3QWM5MXJXWDZmbHJ0cHZmSjFhbEd6cWxQby12dDhwbnd4by0xYjYzdkM4TVJVQVAwQnpOUm5OZkg4bkpQcXNfZXh0cjBnVVJRdTBkekNOSnBvR0hEdFk4?oc=5</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>08-05-2026 11:57 UTC</t>
+          <t>09-05-2026 08:53 UTC</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Zydus Biotech</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Zydus Lifesciences Board Meeting Scheduled for May 19, 2026 to Consider Q4FY26 Results and Final Dividend</t>
+          <t>Daiichi Sankyo posts 'extraordinary loss' of nearly $1B after overestimating need for ADC capacity</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>Endpoints News</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxOaXNBTm50RkIyTHVsS0UyajVqdkVMMkRuMm5yWjl5aEwyMW5UbE5JZ1ZHNEVPZUVNM2V5SWVwYlFmQ09lMXRkN0s3ZnY3VzdtaVZmd2dLQ2QwdzFlMjBnYVlZbFF6Sy1fS1Z4dHp5ZmExSG9ybERJRlh6aWxNejJxSnVNeXgzY1JGeWV3ck05MEM5aC16V0JuZUN6aW1ETlZ4N2ZmNFhyWllYcUgwQzl5TGlscWZlYlhYOGljUFh0NTRzeHVPMFRyQ1UzRTFJZnJRRW9hc2xyRDJWdWlLTGRnVzdkLUpmQ1NlTUpiX2dRaXNILUU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxPZFFOZzJTRUhKZlZ3b0d4c1RvdHpiWmV2YlN4R1ZIbkVBMWdpeHBwaFRtdXVpZzRxa2taSERheDdkcWxxWll6YkxOazhUeGFBRmtxNnYtOFMwRmFRY1pfR3BrRlNPWS0tWmtFM1ZZYlV3cXlJa3ktN1NEVnhkSmpsUzZ3?oc=5</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>08-05-2026 14:17 UTC</t>
+          <t>08-05-2026 17:16 UTC</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Fareva Pilots New GMP Unit at Pau Site</t>
+          <t>Daiichi's ADC miscalculation leads to compensation of over $480M to CMOs</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Contract Pharma</t>
+          <t>FirstWord Pharma</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxOQmdTaTVpaW5IcVc3R3JEREl2VlVuTFlkRC1Ua3M0cjVtVElkcjhRQ3VrUDVxWkNVYnFDdzg3clZERGVaajRiQ3UxMm52MjQ5QmFzb1RtLVBHVld5c2xNVl9qakR1NnRxQjNHS09IRGszNmZtTVJyR2pCSlhTR3g0QzZlZHdMQ0dpcHJtcVZEVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTE9wWmtjeTRjeFIzbDlqeUhRYmpEcnFMRWRxNmZjOG40T01SVEUwVFRLeURlUjFORGZOdjM1emw0NEpBeHBoREpuZVhoYTZFMzZwTmxJ?oc=5</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>08-05-2026 09:06 UTC</t>
+          <t>08-05-2026 15:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Samsung Galaxy A57 Review | Dependable everyday performance at sub-flagship price</t>
+          <t>MindMed Q1 2026 Financial Results: Key Phase III Trial Milestones for MDD and GAD - News and Statistics</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>The Hindu</t>
+          <t>IndexBox</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxNUi1Demo2bnllaldTM2Ytc2pMdUlwY1pJNlNscmthR1k5enlIOFk3UU1ubUZUN0xQREtyTFJwZUhnb1V1YXZWRmRjbUR4T0Y0dl9GdnY2dWZsYnN5OXc1eUwyblV6dGxKRVA5d2NhTmNVdkMwckFDTUEyUDRyM2dVcVpKWlk5bWRJeEVmUXNjV282cmlmc3k4SHU2YmRsaS03ajAxNVVmV2lmTmQ0LVFfYm90cmFfb05fVkdGRU04TlMzZXNkeU1rT2JQR09vTTE4bXFfVXhRQ2tneXlhOUNoTmQycmwyY2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQSXY1a1kzdkUtS0FUcmFMSURLODNUZ0FrLVBwVm5iRTVnWFVWaXNWTXNNTFNvZnBiSlhaT1h2MTZEQXc0Y19yUHh3Ym0wSzVCOW43bGkyY1hGZ3RKQXhBYUdxSDhJNlFhRVFQemJ0OGIyRFFuS3B4RTBSTjRyQjl3V004S25uR3dCNFZBdEdoTnlNM0FMUkJDSk93?oc=5</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>09-05-2026 02:30 UTC</t>
+          <t>08-05-2026 23:20 UTC</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Samsung One UI 9.0: Everything you need to know</t>
+          <t>Angelini Pharma to acquire Catalyst Pharmaceuticals for equity value of $4.1bn</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>SamMobile</t>
+          <t>Pharmaceutical Business review -</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE41VDROWW1SaVZpZTlKMjhMQ0FQRmJjWmIycGxlelhRSzJlanA2T0xPenlUaTBlYjVXN2hIUjRMRlY0X1VfWDlPN21EUW1FRHFuaDI5Njd5bGZhaXZWSXhFX05DWjBVa1ZNS0Q3aWxsT1pDR3JXa2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOT1poWVNpcEtQOTlaWWJNQXR4ZmkzS3BBYlFxTmFwV082TGZVYTg4LWFrQmdOc3d5cHlJejFZOGlzZXRFSUN4elFtR0tFR0VHZjlqVG5rMUl4Z1JlOVQ4VjBCNEotejdBRUhabm5RRHRrYTV3dXVRbGhqOEI5MXVfc2hhejduVzl6Q09HM3J4WkdodzlCVURBaQ?oc=5</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>08-05-2026 19:12 UTC</t>
+          <t>08-05-2026 16:48 UTC</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Samsung launches fifth edition of Solve for Tomorrow, raises winning grants to ₹2 crore | Business News</t>
+          <t>Giants of Cancer Care® announces the 14th annual class of inductees</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Hindustan Times</t>
+          <t>The Manila Times</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxQQTl1aXUzX2lZWDBCdFJBTl9QQS1SNVp6bHFzSWxuX245RU5rWTk3Y1JiTHhXYVNFQzVVYnNVZjdzVkZQRHlGQ2h2ckhteHZPblBaY3ZzeHItSVdrRGJfNldfTVNqSU4wUHhTZHBacW93TXB6c3NVdmhGSEZNOFBGdnpLZFc3NlNHeEtVbExNTDl1N3I3djBnVy1rRUJuOFN0Wk42Y05WdHRmeVJrLU5UUXd4VzJNMHNiVlFtTU9mZ3lzNXRWT2xvWTNvWHNnZzY1NEdsN0tybUhpdWFqR3Nv0gHkAUFVX3lxTE9nVU9pRm9IdUVGMXJ4M0xrdnBvczVsdGRmVGpUSlE3YWpmM1NMSHZ4OWx0dkI2WGdQRktBV2x3NTRuQzFfa2lXN1dGUmNINlhTM0xrNW4yMFJPS0NNYnFPenVFTGgwUW9NTFZweEZmcUl1ejVRSE51V0tJbmotNXFRRy04YTQ2Yk1aZ09HcmRLbkIyNzlBTnRCZjN6bEN1dThiRUE4S2dkVEhCNTRmZ1hUeHE4dTFVX2trQ3FTaEdEYjY0SXJUd1BUc25waVloUWMtMUxKc3JfMDBYUzNzXzljWGdwbA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxNX2s0R29tRXBBR1BsV2p5OXF4MVVMTTVUbGZHOTR6UGRmSl9wMUE0am1qZlg4LUVvTkUybVJqRHFNRDcxMkphTnc3UkxndC1KRTV6WmpvYVlpR0RSSk9UaG9nQ1ZuV0FhbWowcU1KTFBSOFIwNEE1di1fak5ZcG9iVHVsX1phRWl1WV9uUDVURFNPTFMwYTdKQXZHaUZBUXBldHBGZV8zTnc4MVF2eUdkOVlzdzVsbFlQZ25wU3o0OV9ITWsyS3JaSGxpUDkyTEs0TE9YeVc2Qk9EUkt40gHcAUFVX3lxTE1fazRHb21FcEFHUGxXank5cXgxVUxNNVRsZkc5NHpQZGZKX3AxQTRqbWpmWDgtRW9ORTJtUmpEcU1ENzEySmFOdzdSTGd0LUpFNXpaam9hWWlHRFJKT1Rob2dDVm5XQWFtajBxTUpMUFI4UjA0QTV2LV9qTllwb2JUdWxfWmFFaXVZX25QNVREU09MUzBhN0pBdkdpRkFRcGV0cEZlXzNOdzgxUXZ5R2Q5WXN3NWxsWVBnbnBTejQ5X0hNazJLclpIbGlQOTJMSzRMT1h5VzZCT0RSS3g?oc=5</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>09-05-2026 07:29 UTC</t>
+          <t>08-05-2026 15:22 UTC</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Samsung Galaxy S25 Ultra 5G price drops below Rs 95,000 in Amazon Great Summer Sale</t>
+          <t>AstraZeneca plc stock (GB0009895292): Pharma giant eyes growth amid pipeline progress and pricing pr</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Moneycontrol.com</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxPd1Y5cVBqYnFkUUd1d3hhNjFWZDVWLU9XWnZJZXU5NVNtWWlVWXVwX3NRM0xScDd1RmZHMDNJX21LSFB3VEpvQ3RzalprRXNGNmdpeFRLYjhVMXJDVGFLUloxM0wtT3F2V0RkRk8wZkY5b2VLV1VFTHphWWFaQlNMS05zdnJsZ3J5d3g2ZGRGS3lxdnVFRDZ1Sm9QUFNBUGI0cTFsQktaemxoRVlGOFBHTDZCOUF6d1VmUHVENDRsWWNVYzMtMjVLazN3NUp5MFdJTHVyUVcxU2ZoRmxaTlHSAeMBQVVfeXFMTmlJRTFIZGhzTllVWkRfUHJuMW9GejVpMVlFZDU5emNxLV9zeGJ3NDFZMWw4TzhZWUx6aUZzZUtvbXAyTjFJVk1xYjBLOUxKVGhDdjI1dWE4czFULVl3WW91Tng5S3FjaGNHaVpwQmFpLVVxVEN5eTBhbjB6MWtoV2c0eHRqT205M285bXdYQUh2a2d0ZDc5X2lTY1IzTm5adE9mWExpZldLSW8wN19nQVMzV1oyZGV6SWx6b1NBVmZ3aGdDZWNINEJwaU56NnJGX1NSMy14UTZsRDVJcUk5R2hZd28?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNclRsV2dfZExRYzRSOS1XMzZ5UWtHVlhGYkRuLWxGR1N2aWhIdjhiOEdITXlIbGNrQWlXMTd6QkczVkIyRzc3MFdwSVZCZ0VxbzR6VXM4cHFvM2lfdDAwaFhmaXRsMmFWSENzVDhzLURFdlRZendZdFRmUnRscDV0N0gyVzZQbmt3bEN0RVhCUWxSdW9UZGxjUW1mOGIxdE5YUEUwRHl6YXFiTE55YTFvS2p6eU9GNGEtRURjLU5tNHg?oc=5</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>09-05-2026 06:09 UTC</t>
+          <t>09-05-2026 12:07 UTC</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Dong A ST - Meiji Seika</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Samsung Electronics Announces New Leadership at the Visual Display Business</t>
+          <t>BTgen expands global CMO push, boosts capacity and eyes Korea IPO - CHOSUNBIZ</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>samsung.com</t>
+          <t>Chosunbiz</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNUnNYd1lueDk5RFc5WlBWOUpTcmpvblFjVnFDT1ZMWGFTeWY4QldaUDYyY3dsQkJjY1RvZnBkbHBYbWRvS3ZVa2EwanlzQUt0blJSQTBES3VuaTlkZXk3RWdCbVhJcVotZ3Z3a0F1WlNOZnVRdEJrYTNoNi1KRURjQmU2S3BuMkxUT2Fhelp5U1BTSFlvb0dFTG1SeUpuSDRlNzFieDRn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQczhRTUYwVV9nOW1zZjhSbHFVQjNsU1IycmdoVWlXelNlb2pxcEw2b195UmxMcEQtdzdWeW1INnlGckZQLXh4M3JGZjJYODUweFV1RFdBRFN2ZWJweDVSdlFRWHM2Z2N6MGMzclc1LTNtYi1aR1Jpd3NjQnVUZ1B1YtIBlAFBVV95cUxNUHgtczd2N1pkUWVKcWZKNEFyNmdnaVZDYjhQMlp5aUU5SnZ5YjlVLXVnUmQ0bmxuQW1rRXRYVUQzdnFsY2hxemRMZTNYbUs3ejgwNVpSdWlPZ3VPQXBvVW12RUJIbktkRGdDeVZRX1pJZUZob0pFOEF6Tm9ES1RjQ25CN2ozaHZrZGJyR1lCdXZJLUtl?oc=5</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>08-05-2026 22:52 UTC</t>
+          <t>08-05-2026 22:08 UTC</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Kyowa Kirin</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Compare Samsung Z560 vs. Nokia N71</t>
+          <t>Aevi Genomic Medicine LLC Share Price Today (CBOE: GNMX) - Aevi Genomic Medicine LLC Stock Price Live Quote</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>GSMArena.com</t>
+          <t>INDmoney</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE9zOGRqS3dCWFhVVGI2amkzX0pXRmVyUzI2TWtLUl9uYmFKLWptN1RhYnUwS3MwQk54ZlRnLWE5U0ZraDlZY3pYMWduWW1kNTc3OGVDM3o0dFE5Wm1abjdyUTJZSHZjYmtNbzh0bnJpVGFfNEk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE1IRzI1aW5Ld1dmbnVROTMyNFNqQWdERXpiRk41bE1rXzRzUG45bWVwenJTaHczX1ZzTl9XY2QzaGpUWkNEUUNWLW9xMTl1MWtPdHlVZnBSYw?oc=5</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>09-05-2026 05:46 UTC</t>
+          <t>09-05-2026 03:16 UTC</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>JCR Pharma</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Galaxy Z Flip 8 leaks show a wider, lighter flip phone</t>
+          <t>Italfarmaco’s new CEO and commitment to rare disease R&amp;D</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Mashable</t>
+          <t>The Pharma Letter</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxQSDItaTNPWmhLMmUwaENESHhpX3hxLXpWLXJJQ2FtNGZEdnBJNURyYXkxS0tsRG9vejUwTXgzVWxEWGFucGtlUnNUR2pTZGRCY0pEeU1ZU0VMU3F3SVd1ejVXRXFEWk1YenZmVVJ0SDV2aVdDYk9iVnhPTTBjWkxRbWR2RQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOejNqNlhzSUx3cGRHcGFpZzhLR3hxNF9KU0RNNlN4SUkySWRhMkNocHVFeXQ4M2FpVHN4d1prLTdNbHpObE1kcWx5TnFXeEh1Z3kzNzM4NS1UNjBfQ2s0OFZVTG9WcGpSQWkyeHBGNUJjb2RnVW9EYVdsTUV3Qm53R2ppelVLbE9fWXNkOXdyRko4a19GbTZ0SktrSXVjUWdnYUE?oc=5</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>08-05-2026 23:25 UTC</t>
+          <t>08-05-2026 19:26 UTC</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Mochida Pharmaceutical</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Amazon Great Summer Sale Continues: Best AC Deals From LG, Samsung And More Brands</t>
+          <t>Richter Expands Rheumatology Portfolio with EU-Approved Medicine</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>News18</t>
+          <t>Hungary Today</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxOcnVXeHJZcktXMi1ISUVBWEg1ekdpNUIxQkdsbnJSZ3pRbTBvSlpSUkdYS1gxcWFmVGdHV2UyZ0RLLXZNM0pIYmt5VTBOUDF1bVUxdVlJYk83ZFoyWHJqdXBNLVhFVnduU1pUbDNOUGtTWFF0dHhjOXkySmFVZ29UZS1zdW9QNU9ydVROOXhQM0RYTGpQNngyN1FRdHRMeFRtYTUtU2U2dUhRRjNCWFpfUUhDcDYxVkxZb0VGTXlpTTdpT1RBMFFDUk9aOFUwLTNPbVNQd3UyZmw1d3gtSzlpTllQYWY3RUnSAecBQVVfeXFMTnJ1V3hyWXJLVzItSElFQVhINXpHaTVCMUJHbG5yUmd6UW0wb0paUlJHWEtYMXFhZlRnR1dlMmdESy12TTNKSGJreVUwTlAxdW1VMXVZSWJPN2RaMlhyanVwTS1YRVZ3blNaVGwzTlBrU1hRdHR4Yzl5MkphVWdvVGUtc3VvUDVPcnVUTjl4UDNEWExqUDZ4MjdRUXR0THhUbWE1LVNlNnVIUUYzQlhaX1FIQ3A2MVZMWW9FRk15aU03aU9UQTBRQ1JPWjhVMC0zT21TUHd1MmZsNXd4LUs5aU5ZUGFmN0VJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNV2c0Tzh0bkRONDdNX3doQmtZMUdVc0ZJQ0FiVFY0ZHdPbGJKVUpieUFpN3Q0aTc4cHMtdWdicWowZ0h4a0FnaGRjSldZLXdMWWZLUG5WV1REcFlWbnZCQnhlWHlWZ29IYlRJZVZLdE83N0hicWp5X2RfZnhabldpaS1ReU5HNXZqYTE1SWFtUVVuNmc?oc=5</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>09-05-2026 05:45 UTC</t>
+          <t>09-05-2026 07:03 UTC</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Samsung Galaxy A57 picks up a fresh firmware update</t>
+          <t>Fresenius SE &amp; Co. KGaA stock (DE0005785604): Healthcare group reports Q1 2026 results and confirms</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Sammy Fans</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNellqSUpmUUY2OW1vRXdRVzZBMExJbHYwblZ6ODlvM05KMTNtN21zT3hBTzdTLVVBUU9xdFp2eXF0dG1oQjQ4TEFLZmtMc2QweEpPaEN4eEJ2ZUd3ejV1TEYzZ2RibVk2S1VqRDlZb3hoNUpLaHQ2SWR3bG5xTVhDc0EwNGJsN1VlMlpDcnFNR2xEbXfSAZgBQVVfeXFMTlBLeGNaamVtQUdUZUFrSURKZkZ5MDZLOGhyWnhwMjlHalh2bXFET3JMUVJXZXRzcmlNV0szV0phUGZfSG5QOE1UTjVMZ21NZnBRSUs1d0xCWEVjeDRzeWZQZGk0VnkxOWtjVkk4RVNaRVc3NkE5QkhRT1RpUXRqT0Y5OXRXT094RXp5RlZQdlQxQ2hTeV9vdGY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQemRza0Z6SFdmSlhmRl9jbmdzZ2VTdHNJcDFKLUloSDlEblE0TnhyMzJ4STdLeGZJNzdlb25IWHNSV2szRlFmTlVRQzZjZVYwVWlJbkZ2ZHluLTZCLUNWLWFKNTNqZ2lqSVJIQ3E1QzkyWDBjOUYxaUd4VzQ2LTZRaFpNUzVwQ1JrRDBJdXg1c3RQVE5ZM0NtUHpUc3BvM2dNMHk2WERVVkU0N0t3ZGlFYlB5ZENYZEJnU3J1LUZzSFhKRjJ3S3c?oc=5</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>09-05-2026 03:42 UTC</t>
+          <t>09-05-2026 07:53 UTC</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Samsung Display unveils brighter EL-QD (NanoLED) prototypes</t>
+          <t>Fresenius SE &amp; Co. KGaA stock (DE0005785604): Guidance reconfirmed after strong start to 2026</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>FlatpanelsHD</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE9ZX2NGcDlrXzM0SkNXMVR4VEtOWmhfcGdDM21zV3JnTDFmQVRVWGhETXZxVVR2N2owVWtmNE1GSWZ5R1gtZV9zd2p3bng3Nnd1dUh1ZWQxU3hqbjJfMURRcXl1NW1sSzB2ZllDSTRkeHhNUUxhY0swaW13?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQZDcwZlNOTnZMRURpTVVyU2VlX0J4cndUQ3JoYUU0UUpwaFVORDNZbGRpVGlabW9zSkdpaW9NMUNieDdXa294R3R6S25PRGhsRXNBVGlaRUNIaG8zVG1qRDR1YUU0bDI3UkI1OGZIWTRFemVjTGVHMTBzNkVjTjhqMExSZ0dIZTBlQ0JkVHNqa19yaURZVlAtWVBBbGlOMGozOTdSYnhDeU1EelRLbHJMbWltVDBiczkxM1FXa1N2Y2U?oc=5</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>08-05-2026 20:16 UTC</t>
+          <t>09-05-2026 05:06 UTC</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>This Samsung watch may know you’ll faint before you do. Know all details</t>
+          <t>Caplin Steriles Gets USFDA Nod for Generic Calcium Gluconate Injection in Multiple Strengths</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Indiablooms</t>
+          <t>ChemAnalyst</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOZWhtTkFUWkNyaTh3T2JRWUpReDZJWk5NcEhCNGZyQUkydjZUUkpJbl93TklRNVZvZGQzWllrUkFfcFRmUU1hb2o5Z1AyYUh3ZHhmZ2lOUE1nam5maWNRSzZUaTJiSThJTndWVDZ1dG5EV0w1NVNJcWFMWWFpT2JueWpvYzBYdGlpY09DYVRNaDFBY1p0YnVyUG5uY2F3X0swVy1ITXlnWDZoODdUT0VXZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQVDJNREZxUE0zR1laMXp2REg3ZzIydG1uVklZazlGLUdRU1dMYWhCNk9PX3FDZW1MWjk5eDZKeWs3YkZSUDJ6VlRuUmtOMTBNb2FFTVZSbThKWUZyQmoxZ1Z1S0RjU1lKTU5CaTZXVFFaamNKem9RSGpWQ3JHQmlnbzh6bldkaFdBWVotYy1UMHJSRVd1WmJWb2tRMUxEaXpUUmN4VFZSOE12bFB3WXEzekloaHZYYzA0bGN6SnZMV3NINHJyR1o5aw?oc=5</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>09-05-2026 03:46 UTC</t>
+          <t>08-05-2026 15:53 UTC</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Samsung warns memory shortage will be worse next year</t>
+          <t>Small Manufacturers Face Tariff Survival Threat</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Mashable</t>
+          <t>Legis1</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE90WmJKZVlramVwRm5ZWVVwMk4xOWpneG9nby1Ja016aFNIYmNpeWlKUWQ2TXJJTDlzMUJOcE1qblFaOUVDX29kQlQ3QzF1NG52RmNjNjB5SFpVWG9wQVhRNHpPSnpjZkpEOEZiZmY4a1FEcjBaWV9hVkFn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE9ueUdTMTRDRW9iakhreVdZUXRNeUxKaTliR01JaXRpM1FfQ0Ytbk4tdGhsck5JemZWQXBMazduX0YxSWE2cU9sblhubExsTnV3a0dRYUdCS0hYZC1Jc0RqZF96VmlmbUFLYnR2UzlSTENCVWpVdWFKQ191RXo?oc=5</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>08-05-2026 15:16 UTC</t>
+          <t>08-05-2026 18:08 UTC</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Celltrion Inc stock (KR7068270008): Buyback wraps up as Q1 profit soars on high-margin drugs</t>
+          <t>FRE.SW Stock Plunges 31.8% in Pre-Market Trading on May 9</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>Meyka</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQRDNjQ2pBOWE2SGVwTHlLcjlKclYyUDRrNGRlbXdpdExOelIxdWNZY1RpVUMxMGFpcFpVS2xYSXJIcWUydmlMZG0zVUg5RHRsZld3dng0THgyZk02OC1reDRwSFd3QTVzdTdIRlloUTFhMmhwZUY2dnFGbmZqaVNxaFg0dVdrNUhvMzhRRDRaYWVZRHkyUEUtMWdSU0RXY2kwa3lHTGVVb2pXU1liYWZPNExMd0MxZzFSdFR5YjAzc05qYzFnQmhFLS1n?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxPenRpTHVPa21IVmtsYm1HajV4QTVXaFBBWml3NmhiTElIcm51LThhSEJXWm5RenM0U0ZQQmRFSjBZUkJEZEMyWWVGdmdtV0liZXJNSElvQm5Wc1lNZ3JmME12WnV2cFMxaGlROGdNcXBwZ1JpVjk2b2U4RDhBY2tMYklRaVF5bFAtdF84?oc=5</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>09-05-2026 07:21 UTC</t>
+          <t>09-05-2026 01:15 UTC</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Prestige Biopharma</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>OneSource Pharma Stock: GLP-1 Ka Gold Rush Ya Valuation Ka Trap?</t>
+          <t>Sun Pharmaceutical Appoints Ms. Satyavati Berera as Independent Director Following Postal Ballot</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Whalesbook</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxPc3BoaWg4SUtEbXlyLVhGUkdiMkVNX0JfblJyYS0xT1FsZjZ0cHlLUmhzbURTYmJUUHJpQ3BNRkF1WllOLUQ0QnV6QllzcUJVbjBaN0szTzBkcWtzU0ZuY0ZLX0RlYlJJT1BGMDM3akd6cGpqbTJVWmhiNkhlOWJfbU9HSnhNQ25LRFQ3ZHBFX2lwekIyU1QySk9qc1ZjeUlTV2lSbHRRcml4QktIVUt5bGtyWU5DU2JBTVljNzhxV1VXTEg0QjVENE9BeU5INk94bEhfMTdoTmdxR1ox?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxQMFdmMXc0bll4WF9mNFVfaEVNVUtCNThTX0JDM1hqT1pBZmhleHducDRWQnl1SlNXUUZRX1hTN3VRV2FpSGZvb1hJaHhjc3d3ZkhEQ0xpMkE2ejduMzQ2T2NMNmJxbV9Tb19QS0poZFd2QlNmR3loZDNTM05qeGxIVFlER0VfZm00RjZVQk5qdVZHSW9KNE0tMExmWm1oVkZVMzRkdTdxMHdnMDlZMnJ0bTY2dUkzLUdHQ2xWdmRHcW1lUFE2RDNNQjMxdmNrMVF6Sk9xd1ltSE91SmYtYU5PWW9peHIxeTg?oc=5</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>09-05-2026 02:29 UTC</t>
+          <t>08-05-2026 21:48 UTC</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Prestige Biopharma</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>OneSource Specialty Pharma: GLP-1 Gold Rush or Valuation Trap?</t>
+          <t>Systematix Corporate Services Appoints Ms. Rupam Lal Das as Joint Managing Director</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Whalesbook</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxPTURwNmY2djF5MS1rSEFTUHdHazVRcm01Sm9ud0J4OXc1Q1FNdDlJVDI5eGE2dGwza09vcFE3cld4U3pCdV9oWGlrVW44TEtJbDYySG9hTU1VRzBsb0ZoQXU2encwRWtTUURHNkFXZkhicFQ3dlhSR1F2ZHo2NzNIS3plUThBRFl0REpfdFBLbWFSbWhZMVRuOFlFZFBwSG9TZ3RuQTVqZ2dmXzVmaWFwTy02UXZNVHFGenFqOGFFemRhRld1azFTRm50VzdCOWp2VUk5Q1pFRURWOWM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxPQmx2TTFEZlJTZnB2UzltX3pzX2dLcS1hWE9MS2NFMnV6empyU1N4LXVHSV92T2thMGRFU3VUYzEtblNGTUJYd0JxSHFtSU92d083LWlnT3ZrbXhHUDdVNVVYWnFPNTkxdUYzLTgtUV80a3NNcWNsZ1VYd2FEb0VEVFllU3pBUFBKTzRXVDF1MnFGN0tDVl9RMU9kY3pXV0tnakpGUmNFcUgtZ18yMXNJeGcxOEx6djVzUFoxTlJkai1qVjVnQ0lIUXVtUWJVTUNxb1ZXZnh3?oc=5</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>09-05-2026 02:29 UTC</t>
+          <t>08-05-2026 17:42 UTC</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo takes $610M hit tied to ADC manufacturing losses</t>
+          <t>Mississippi to receive $41 million from settlement with defunct pharmaceutical company</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Fierce Pharma</t>
+          <t>SuperTalk Mississippi Media</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPdGY5SFBfV1hyN0R1TUxMdkp3a3RJS1VXM1Vzal94YldVMUQ0SzZrdzVzZ21JODdpRnBjODY0OXlSLS05TzlkS3A5VVk1MFp6SW1NU2VzdGhGcDJpSUNiNUQ4SUluT0JfMUdKQUttRzhQRXVOeWZDWVEyN09UTDh0UkpxbWtOWGd3UzA3VjNMekZCNFpQSlpPR0VGV2I0NEpkSTJmaDdaRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNM01xSlowWWlzYmpXLXFNZ2tnN3FLMTd2enhRcktmS2pfc3dEc3Z2UF9tUmYyWFYwb08tcHgyMmQtYXQ4T1JBOWNJNjFGRjRxYmI1VTlXOXVERXpoNXhpQ084V2hkTmRRSHFOeWZJXzdmTkxvX293WEV1U1Zlc3JPQ2hzVDJrU24zZldJUUsxc3RaM2M4Q2hXVFdYVU9CZUJmZjFVSFNNVXpZMnlXWFl0cg?oc=5</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>08-05-2026 14:47 UTC</t>
+          <t>08-05-2026 15:40 UTC</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo posts 'extraordinary loss' of nearly $1B after overestimating need for ADC capacity</t>
+          <t>Sun Pharma shareholders approve postal ballot, appoint new independent director</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Endpoints News</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxPZFFOZzJTRUhKZlZ3b0d4c1RvdHpiWmV2YlN4R1ZIbkVBMWdpeHBwaFRtdXVpZzRxa2taSERheDdkcWxxWll6YkxOazhUeGFBRmtxNnYtOFMwRmFRY1pfR3BrRlNPWS0tWmtFM1ZZYlV3cXlJa3ktN1NEVnhkSmpsUzZ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPeklUY2tPZ0NGQTUxeTFEUGdOZmRCcXhIV3BhdDVpYnB6RGo3MldKakM2YUM2QVFNZVBYZnJqMzRJYWdIMThKLV9DWGZMeGE1cDZXUXRPTm1vejlZMFAyWV9scWZOaHRWV19nRnl2OWVHZDJPdXFHRDJWT3RGbGVESEtVd012THUzWEc2NkhSd1JkQzVJeWpONjUybnRMRzh4clBtQTlSVWtSdm9Xdkx4b001QXBSbnZ6YXlpZ2FITDVvZlVDOWJON2pR?oc=5</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>08-05-2026 17:16 UTC</t>
+          <t>08-05-2026 15:19 UTC</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Alvotech</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Daiichi's ADC miscalculation leads to compensation of over $480M to CMOs</t>
+          <t>A Look At Alvotech (NasdaqGM:ALVO) Valuation After Weak Q1 2026 Results And Biosimilar Pipeline Updates</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>FirstWord Pharma</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTE9wWmtjeTRjeFIzbDlqeUhRYmpEcnFMRWRxNmZjOG40T01SVEUwVFRLeURlUjFORGZOdjM1emw0NEpBeHBoREpuZVhoYTZFMzZwTmxJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxQMHdvT3dNRE92aWp1MmgzSks2Zm4zbU5VemhvYnJ4S2s2aWhCX19lc25BTXlZdGpFSVBrckJDRjdoWTFyRS1XdFdZSVlvOEl3YU1nUGluRVpiTDlQTHRWZWhuSkEtQ0pVQWlIQkxlQjFjMmFFVWhPS0xsSkcyNWNVMk9rRTRxRG9mVUgwZFlXRFYxNkhJNVdDR2Vvd0Rzb1htZnJjVkh2RXVzWjNUQlFNZ2Nib2FWcXVPUjdzWEF5aENHNm54dWlsVzlvVXRyRGZ6UnhQSVZSazU5Zw?oc=5</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>08-05-2026 15:30 UTC</t>
+          <t>09-05-2026 05:06 UTC</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Alvotech</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo – Cleanroom fit-out for the fill &amp; finish area</t>
+          <t>Alvotech Earnings Call Balances Risk and Growth</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Cleanroom Technology</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxPQndjUGlfVVY2QWw0eWFrSUFEUW5ReGw3SlVIUFlMUnFHRGl2bjQxVVhnX0ttN1VQT0dIZkZHOVlVWGY5Sm1aSjVObzJiSEhkOWhnRjZXUFJ5OThKQUlWODBOSS1rZllEeHlzbzRnMXNobHJfTXk4ajRiQ0hpOEtHMFR3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNVzBGaFlLOG1RZkFIOWRBYnd3M0tDTUU5dXZLWGU2LVBrR2hGaVBHcnFGTV9SYzdwWkVxeGlfenVwcDUyQUlpSnRxTldnREpIRTlpSl90ZEtGZmZ5dG55V2FGMXBaVW9XWE94NGxRN1dLTFZDNFdtVU1Hc1lUVFdyX2JONzBQWnQtLTc2a3NvdkdNT2V1Q2QxQ2RhenJiOHo1?oc=5</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>08-05-2026 11:30 UTC</t>
+          <t>09-05-2026 02:07 UTC</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Alvotech</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Manufacturing hangover drives Daiichi Sankyo into the red</t>
+          <t>Alvotech (ALVO) Q1 2026 Earnings Transcript</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>pharmaphorum</t>
+          <t>AOL.com</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxQWWtOdXVOWjFyOS1QUmttQ25DdThPY1d6TVBpdVByV09qbnZscHZJUlJQdlc4d3lFcmJmZ21odVd1am16d0ltU0hIN2hlZWw1VWxMcXd6NDhPSVNfMzBuVVF3bVh2YnUyU09fNGRILTAyTFRXbmx6TERpN3VoMWJKZV9Jckc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE9jMjdOT3hjWFdlSjAyLWhDSDM3aUtIUEp6R0ZWOTY5SXZ3Snl3TGh4dDYxVEtEV290a2FEMllPMVJWVmRYNFBjV1BIMG9rV1NtVGVCbUhTbG44V2hpNDRoNkpOTU1yY3plbTFOVHZybU9sMEVMbVF4ajFHa2Z0UQ?oc=5</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>08-05-2026 09:10 UTC</t>
+          <t>08-05-2026 15:32 UTC</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Merck : Statement on Daiichi Sankyo Update to Manufacturing and Supply Plan - Merck.com</t>
+          <t>Formycon AG stock (DE000A1EWVY8): Biosimilar developer eyes growth amid new launches and partnership</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>marketscreener.com</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQd2w0T3UwdXY1b1hNem1Dd1d2N0U4WURZNVdOV09BZi02TDJ4OWF6Y21GRnlsN2FmV3lHSk5xRjU4TE5EdGY4MUZNRnhsNWgwb2N5aHZhM1NST2ZBdHk4S2pMVWh1NVhUN0EtTGJGb3E5dXA1LU9HcllyNzB6eExJdjJVd2hPSFhkLXRzRERKNlAxVzZId0F2bkFRM2pYdVhCWktBRnpTaVJDZDZ1OW5uVjNXQ0pnZ1RLRU1TMFNfQkpsTkZLVGFKWHNaV3hZYnVlZnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPbnV3UzQzWDB4ZnUxSUtkaXVQQ1Zrd3FwQ1IyY25FZldEWFVKbnEwblB6WEFVVHppUDlYR0tjWHlMeUxZeV9FYVgzWVpSdTl4LUFWQS16TWVfRElDV2RacGdka3dNR2NtT0tMMDVxOGJmeDYyc0VtQUUtOF9fcWNLUEJZbzNHaXM0NFd0VVo3cFU0c0F3X0hpdGMwNEU4NjhSTUJBNDNXU0NYa0ZsdnRHY24yUW9INXZGWkFleFFscnhkcFNUNkE?oc=5</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>08-05-2026 10:37 UTC</t>
+          <t>09-05-2026 14:08 UTC</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Is It Time To Revisit Daiichi Sankyo (TSE:4568) After This Year’s 26% Share Price Slide?</t>
+          <t>10 Walking Shoe Sales That’ll Make Long Days on Your Feet Better</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>simplywall.st</t>
+          <t>Good Housekeeping</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxPRmJRTUdBNnpmVkZxWlZEenZJclNoZHRNMUJfRDJNSWNLaHhSSTUtbjExNlhWZEU1eG1jSkVZcXRJMkNzaWdaSERnSUZGeDhzTENNOUItRkw4M09JZThrN2Y2VkF5UjlYc3FnRks0MW1obnhTWnVPTjNBTmRfTnFuaGxyTGY2SVNrbllmcDl4RXVYTjBDY2FYU2pZcUROQzdTT0VSdDFCY1dyM3I0TDVHSnYzWWE1MWZXeTBrN3pCbGlQaWVyZDg4aFlvWlR5bjBfcWp2dU9JOTlJMmNQUVpPS295em9IV0HSAewBQVVfeXFMTmZDOGRmU3p3MEdUdElldVBTalZjTTRtX0w4bzNfeVp1OHNHTTBBVnFTLXFmRlNpWG9zT3BZd1V1YjV2VzlNVXhWWVdYdDNRYTFUdkRqdlRIZmxTSGdLci1ZY3p4Nk50a2pDdjNCRy1OdWJIdm04VzBBdFVtTTB5bW5VU0dJQmlNUC0tSzBKNnp4N280MXRmWnBtdFZfMjZTcWM3ckhkaFZ5Uy16bldkcGxjQmNDUTZaVUlFYmFSTTB1N1JJR3lZUkhRMlpiNkU0bDlMQlM5cDkwZTJGajVoQzBibUhEZm1kR2Q2T1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQWlZob0JzdzR4c3FLSVZudWpVMTZlSWtCX1U2T2NRWXBrTzJ0VG0zSWJkcm5LMTZNeGN4WVlBNGJoMGlhZGVDcUpfdmF0ZXNjM0ZjREF3LV9lRjhyLThnU0N5blJRbHplOHpzZmUxX0c4b3BKY19CVlZwckp2Vm55V0IzbF9yU3RHNTA0LUpHZkpjaHM?oc=5</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>08-05-2026 11:13 UTC</t>
+          <t>08-05-2026 20:42 UTC</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Obesity Therapeutics Market Set to Record US$ 63.75 Billion</t>
+          <t>Sciatica Treatment Market Expands Across North America &amp; Asia-Pacific | Pfizer, Novartis, Teva</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4091,1090 +4091,91 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOMlFPVGduRjZsYkR4N1p1cTRoUkRzTmVCZGpwWU1NaVE1Z05RMWZXTlJmWGZaT2xQSmVyYll5dTAyUElucnFOeEUzQlBaVGUyY2hTOVJLOHhVUTNLd2k3a09CSW1fYnpMNUJzck5iVERTXzhUYlZIN1F2ZUJCUVVLYXFnVzBmTC1hSTdVR3BDSnZPY082NmZMaVdR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPcDVHRk9TcGo2SDRsUG81c3hEd2hydVI3ekhNWmo4al9FOG5fTDNzWFJWQkdVOHNZRVJMb1h4UWFOM3RjT1FsUGhnX1gwVGVhZXp4TEpYUHdSTUJpUWJGX2JBdVNlR1VRRnFBc0lGWEU0VzlIb2g5dmhtREJfekFOWTF0c1p0OXpLbC1sNzhmRmJWWkR1?oc=5</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>08-05-2026 12:57 UTC</t>
+          <t>08-05-2026 19:21 UTC</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Giants of Cancer Care® announces the 14th annual class of inductees</t>
+          <t>Why Every Disney Adult Is Buying Tevas From Amazon Today</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>The Manila Times</t>
+          <t>AllEars.Net</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxNX2s0R29tRXBBR1BsV2p5OXF4MVVMTTVUbGZHOTR6UGRmSl9wMUE0am1qZlg4LUVvTkUybVJqRHFNRDcxMkphTnc3UkxndC1KRTV6WmpvYVlpR0RSSk9UaG9nQ1ZuV0FhbWowcU1KTFBSOFIwNEE1di1fak5ZcG9iVHVsX1phRWl1WV9uUDVURFNPTFMwYTdKQXZHaUZBUXBldHBGZV8zTnc4MVF2eUdkOVlzdzVsbFlQZ25wU3o0OV9ITWsyS3JaSGxpUDkyTEs0TE9YeVc2Qk9EUkt40gHcAUFVX3lxTE1fazRHb21FcEFHUGxXank5cXgxVUxNNVRsZkc5NHpQZGZKX3AxQTRqbWpmWDgtRW9ORTJtUmpEcU1ENzEySmFOdzdSTGd0LUpFNXpaam9hWWlHRFJKT1Rob2dDVm5XQWFtajBxTUpMUFI4UjA0QTV2LV9qTllwb2JUdWxfWmFFaXVZX25QNVREU09MUzBhN0pBdkdpRkFRcGV0cEZlXzNOdzgxUXZ5R2Q5WXN3NWxsWVBnbnBTejQ5X0hNazJLclpIbGlQOTJMSzRMT1h5VzZCT0RSS3g?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPZjVOcDN6TVR0SENpUHJSN0UwZXJBX3o2SUlkSHI2RGNNX1d2VGk2TjhWZGdZZWQtNW5JVXY0R1VOb2VsTzZleWg0eUtuVUtoMWtFWnNQUzJwdFJGdnU3aXdTNjVjV1BTbVRFQXdqOFc0dmdGMTZIN3Y3aHpyM2Q3VnQ2dUYtU0U4SEdNNzFVRW5LQXAx?oc=5</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>08-05-2026 15:22 UTC</t>
+          <t>08-05-2026 19:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Dong A ST - Meiji Seika</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>BTgen expands global CMO push, boosts capacity and eyes Korea IPO - CHOSUNBIZ</t>
+          <t>I’m a Fashion Editor and Mom—These 7 Comfy-Chic Shoes From $14 Will Get My Tired Feet Through Summer</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Chosunbiz</t>
+          <t>instyle.com</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQczhRTUYwVV9nOW1zZjhSbHFVQjNsU1IycmdoVWlXelNlb2pxcEw2b195UmxMcEQtdzdWeW1INnlGckZQLXh4M3JGZjJYODUweFV1RFdBRFN2ZWJweDVSdlFRWHM2Z2N6MGMzclc1LTNtYi1aR1Jpd3NjQnVUZ1B1YtIBlAFBVV95cUxNUHgtczd2N1pkUWVKcWZKNEFyNmdnaVZDYjhQMlp5aUU5SnZ5YjlVLXVnUmQ0bmxuQW1rRXRYVUQzdnFsY2hxemRMZTNYbUs3ejgwNVpSdWlPZ3VPQXBvVW12RUJIbktkRGdDeVZRX1pJZUZob0pFOEF6Tm9ES1RjQ25CN2ozaHZrZGJyR1lCdXZJLUtl?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTFBtd2hWUmVNbFVxaVdvZUpldUg2RDdpWnd4T1cySEhtLXAxMG9KQkc2UG1hUzNsRDBDMnUxOHdNTmtDUDdiWlI4S3ZXcHFWa1QzOUlRUTRsc2tpRVk0NlNubmFRNGtyNUltbXRjSkNrYVBhV0t0d3d6QW53?oc=5</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>08-05-2026 22:08 UTC</t>
+          <t>09-05-2026 10:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>Samsung Bioepis</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Kyowa Kirin (TSE:4151) Margin Improvement To 13.5% Reinforces Profitability Focus Narratives</t>
+          <t>Deal Watch: GSK Calls On Halozyme’s Enhanze In Cancer ADC Administration</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>simplywall.st</t>
+          <t>Citeline News &amp; Insights</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxPRGxMN3Q1RVBsbnFsN1Nja1JtaVlVclBCNUtSUWRibEZOYkJkYUZGS2Myc2I3eGw4NEREZF84SnpHajRTY0hDMG1kWGZURTR5TVVOLTV4UW1zOUM0U3pEX3lrcDNTbVNmUFRhWVFldFVjWWp3VUZ1SGdxa1Q2dU1Cc0lCNGJiTHVfWnFFemZMdVVyWlNFbzJIR2VpekJJZFRqUC1PbmRKcEY5UWhoNldHVzNJTExSNFRsWS1vMGtjclVncWtRVGFvM0Q4WGREc29hVUFSZ0hFSjI1Y0Rtblg2c3pVSFB1alFT0gHoAUFVX3lxTE9EbEw3dDVFUGxucWw3U2NrUm1pWVVyUEI1S1JRZGJsRk5iQmRhRkZLYzJzYjd4bDg0RERkXzhKekdqNFNjSEMwbWRYZlRFNHlNVU4tNXhRbXM5QzRTekRfeWtwM1NtU2ZQVGFZUWV0VWNZandVRnVIZ3FrVDZ1TUJzSUI0YmJMdV9acUV6Zkx1VXJaU0VvMkhHZWl6QklkVGpQLU9uZEpwRjlRaGg2V0dXM0lMTFI0VGxZLW8wa2NyVWdxa1FUYW8zRDhYZERzb2FVQVJnSEVKMjVjRG1uWDZzelVIUHVqUVM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxQdFVpU0s3aURnTkFiVC1MX2pOT19ONDNXcEhVWjR1d0xkTnZvb2FpT0lFN3RJeFVlTlpESGlaVF9xcERYX3hvRHBPSkRXRHlFMEpOUDZXUS1oSG1YUTk4MEkxNFR2U3FIVThfLTVnUmc2NDFHYUlhMUtVOG9nZTR1SEZPSjNBM0NDZk5wREVlQmxEWV9WWTk3Y2JFTzZTN2l2WmJDQ1p6SS1kY2pYcVI2T2l0d0kxV1ZMZW05TklPemlIX3NmU2NWUXM4TkFxZU40ajBSOTEtMmhjdW1FZDI5WUMxcFZjTzJZanBmMElsQmZBZw?oc=5</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
-        <is>
-          <t>08-05-2026 08:59 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Kyowa Kirin</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Aevi Genomic Medicine LLC Share Price Today (CBOE: GNMX) - Aevi Genomic Medicine LLC Stock Price Live Quote</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>INDmoney</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE1IRzI1aW5Ld1dmbnVROTMyNFNqQWdERXpiRk41bE1rXzRzUG45bWVwenJTaHczX1ZzTl9XY2QzaGpUWkNEUUNWLW9xMTl1MWtPdHlVZnBSYw?oc=5</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>09-05-2026 03:16 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>JCR Pharma</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Italfarmaco’s new CEO and commitment to rare disease R&amp;D</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>The Pharma Letter</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOejNqNlhzSUx3cGRHcGFpZzhLR3hxNF9KU0RNNlN4SUkySWRhMkNocHVFeXQ4M2FpVHN4d1prLTdNbHpObE1kcWx5TnFXeEh1Z3kzNzM4NS1UNjBfQ2s0OFZVTG9WcGpSQWkyeHBGNUJjb2RnVW9EYVdsTUV3Qm53R2ppelVLbE9fWXNkOXdyRko4a19GbTZ0SktrSXVjUWdnYUE?oc=5</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>08-05-2026 19:26 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Fresenius Kabi</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Fresenius SE &amp; Co. KGaA stock (DE0005785604): Healthcare group reports Q1 2026 results and confirms</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>AD HOC NEWS</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQemRza0Z6SFdmSlhmRl9jbmdzZ2VTdHNJcDFKLUloSDlEblE0TnhyMzJ4STdLeGZJNzdlb25IWHNSV2szRlFmTlVRQzZjZVYwVWlJbkZ2ZHluLTZCLUNWLWFKNTNqZ2lqSVJIQ3E1QzkyWDBjOUYxaUd4VzQ2LTZRaFpNUzVwQ1JrRDBJdXg1c3RQVE5ZM0NtUHpUc3BvM2dNMHk2WERVVkU0N0t3ZGlFYlB5ZENYZEJnU3J1LUZzSFhKRjJ3S3c?oc=5</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>09-05-2026 07:53 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Fresenius Kabi</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Fresenius SE &amp; Co. KGaA stock (DE0005785604): Guidance reconfirmed after strong start to 2026</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>AD HOC NEWS</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQZDcwZlNOTnZMRURpTVVyU2VlX0J4cndUQ3JoYUU0UUpwaFVORDNZbGRpVGlabW9zSkdpaW9NMUNieDdXa294R3R6S25PRGhsRXNBVGlaRUNIaG8zVG1qRDR1YUU0bDI3UkI1OGZIWTRFemVjTGVHMTBzNkVjTjhqMExSZ0dIZTBlQ0JkVHNqa19yaURZVlAtWVBBbGlOMGozOTdSYnhDeU1EelRLbHJMbWltVDBiczkxM1FXa1N2Y2U?oc=5</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>09-05-2026 05:06 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Fresenius Kabi</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Fresenius SE &amp; Co. KGaA stock (DE0005785604): Healthcare group eyes growth amid restructuring</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>AD HOC NEWS</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPTFJUb2hNMG1QVDNjYXZFMWY3VHNfOHdKa1BaS1pqNGhzOXhmZlRRZjlfSU5hZWN3VGZwRFZwcnROSUYwbmZ3a3FKaEs2ekZWd283MWs4QkFETWc3SWhJX3R6Z0dOS3gxa3BWZFJuR2ZyS2M2bEF0YWxjMEQ5NXBhaUVpMUFuMjdXaHBBSnpEanJjeTFXWHNFcjVYdmxQLTlIdUZrcThPeWlQRVJjY0ViZHVGOUtDWXdoZDJMRXpRS09sUQ?oc=5</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>08-05-2026 11:57 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Fresenius Kabi</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Caplin Steriles Gets USFDA Nod for Generic Calcium Gluconate Injection in Multiple Strengths</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>ChemAnalyst</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQVDJNREZxUE0zR1laMXp2REg3ZzIydG1uVklZazlGLUdRU1dMYWhCNk9PX3FDZW1MWjk5eDZKeWs3YkZSUDJ6VlRuUmtOMTBNb2FFTVZSbThKWUZyQmoxZ1Z1S0RjU1lKTU5CaTZXVFFaamNKem9RSGpWQ3JHQmlnbzh6bldkaFdBWVotYy1UMHJSRVd1WmJWb2tRMUxEaXpUUmN4VFZSOE12bFB3WXEzekloaHZYYzA0bGN6SnZMV3NINHJyR1o5aw?oc=5</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>08-05-2026 15:53 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Fresenius Kabi</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Who’s Hired? Viatris Begins Search For New CFO</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Citeline News &amp; Insights</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxOM2p0ek05bVowRFBiZFU4OExlYVdlMnMtdnNJeXI0LWJlV25EalRyQlhXTUk5N094elpadXA1QWgxd0Y1Nml6SHF5ZTFQdUh1NnB1MDFlLUpTYTV6S2NpanE0RDlXQkZmWS1qSEtsYkVqN2k4MXlyaWsyRmVsaElmVkpGVlhVcFQ0dVJUd0hST05zY1hsbjZTeEdDZVVBbV9rNVgwQnV5aElRdndNcHRCU0RlNDY5N3BScHg4QmVUVDlrZ054cEFsa2FkWUhDcVNzeE83ZzR6Q3dHQQ?oc=5</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>08-05-2026 12:08 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Fresenius Kabi</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Semaglutide Biosimilar and Generic Market Size, Share and Latest Trends 2026 to 2035</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Insightace Analytic</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQckkyWlpVRUgwWk1lSWF4cHVjZE13TWpqdk4xZnotYVlPaGpNdGI5djdSaDBuSnJmS3NtVF9SUXNjeThBMFlLdDhBcktrb0ZlMVhTa2FfRXRPekQ3MTBtSE9PUEFBUWJqMkZDRk5vQURfZDRMVzQ3QU5jN0hNYTI5SjZlUGc2SnhLbktYcnB5cFFtZw?oc=5</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>08-05-2026 14:27 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Fresenius Kabi</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Infusion Therapy Market Is Going to Boom | Baxter International, B. Braun Melsungen AG, Fresenius Kabi AG</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>openPR.com</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOSUQxSmFjRG9xUWJPSXhGMzhYVnkxNk52dXNvalRVSG1FNmVFbkRMY2FQSnBjcGZfMDRWTk9sQVN5cGppY1hDcjFVeHdFWXpaU21wWnlGTU9KdGZHOW9xMncwZXEzbl9OWE5Qa01QY2VnRk5Bdm5fTVFSZ00tMVFZQmNTckhhdzlBWE9BNi1yTXktSDV2MzkyX3Y2bE9rZw?oc=5</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>08-05-2026 11:31 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Fresenius Kabi</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Small Manufacturers Face Tariff Survival Threat</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Legis1</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE9ueUdTMTRDRW9iakhreVdZUXRNeUxKaTliR01JaXRpM1FfQ0Ytbk4tdGhsck5JemZWQXBMazduX0YxSWE2cU9sblhubExsTnV3a0dRYUdCS0hYZC1Jc0RqZF96VmlmbUFLYnR2UzlSTENCVWpVdWFKQ191RXo?oc=5</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>08-05-2026 18:08 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Fresenius Kabi</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Blood Bags Market To Reach USD 956.4 Mn By 2035 | Healthcare</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>openPR.com</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPYk5UeERzX0xWbW1Lem1IcWwtaGpvTDZsYV96Q1ZRSnRhTGIybC1RWlRsNVpkMmRQM0gwX3ZmNXdfYWwzZWhuUHJxdEtTcjNZU0x4U3ZvTVVacEplWE0zSzVvSGQ1QXdYcXlBdGs1ZURTSWRfeXM1WWVOUDFkdzZscWs2ZDl2SHlydnZYak9TYUNUOTQ3cGFKSDFR?oc=5</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>08-05-2026 13:41 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Fresenius Kabi</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>FRE.SW Stock Plunges 31.8% in Pre-Market Trading on May 9</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Meyka</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxPenRpTHVPa21IVmtsYm1HajV4QTVXaFBBWml3NmhiTElIcm51LThhSEJXWm5RenM0U0ZQQmRFSjBZUkJEZEMyWWVGdmdtV0liZXJNSElvQm5Wc1lNZ3JmME12WnV2cFMxaGlROGdNcXBwZ1JpVjk2b2U4RDhBY2tMYklRaVF5bFAtdF84?oc=5</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>09-05-2026 01:15 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>MS Pharma</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Sun Pharmaceutical Appoints Ms. Satyavati Berera as Independent Director Following Postal Ballot</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>scanx.trade</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxQMFdmMXc0bll4WF9mNFVfaEVNVUtCNThTX0JDM1hqT1pBZmhleHducDRWQnl1SlNXUUZRX1hTN3VRV2FpSGZvb1hJaHhjc3d3ZkhEQ0xpMkE2ejduMzQ2T2NMNmJxbV9Tb19QS0poZFd2QlNmR3loZDNTM05qeGxIVFlER0VfZm00RjZVQk5qdVZHSW9KNE0tMExmWm1oVkZVMzRkdTdxMHdnMDlZMnJ0bTY2dUkzLUdHQ2xWdmRHcW1lUFE2RDNNQjMxdmNrMVF6Sk9xd1ltSE91SmYtYU5PWW9peHIxeTg?oc=5</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>08-05-2026 21:48 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>MS Pharma</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Accretion Pharma Reports FY26 Results; Appoints Auditors</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>scanx.trade</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxNSnRWTnh5S2wweHBxSVl6WWF4SGhYYWxhQ0FuUDR3WWw3RXh5V3FtRk1TN1BsbloyWlBpeFZiZ0tCNjFFUzIxdExmOURpcnZONWF2M09YWGdhVHBCeDJ3ZV90XzlGelBreHZsMmlpQ1c5S0RvaXdsUWRaaDJBbGthZFExVml5ejk3SF9sZWNEbHRLNHdiaU1VZzgyMWtVbVRKWWxseXB6WnktOURtTS1CUTZMdTRta3BQblFtNzBlemxFTWtWTlF0VHl6WjFLQVhLUmdWZHRWaUk0cE0?oc=5</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>09-05-2026 07:23 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>MS Pharma</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Mississippi to receive $41 million from settlement with defunct pharmaceutical company</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>SuperTalk Mississippi Media</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNM01xSlowWWlzYmpXLXFNZ2tnN3FLMTd2enhRcktmS2pfc3dEc3Z2UF9tUmYyWFYwb08tcHgyMmQtYXQ4T1JBOWNJNjFGRjRxYmI1VTlXOXVERXpoNXhpQ084V2hkTmRRSHFOeWZJXzdmTkxvX293WEV1U1Zlc3JPQ2hzVDJrU24zZldJUUsxc3RaM2M4Q2hXVFdYVU9CZUJmZjFVSFNNVXpZMnlXWFl0cg?oc=5</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>08-05-2026 15:40 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>MS Pharma</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>BridgeBio Pharma: Q1 Earnings Snapshot</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>theheraldreview.com</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOSWtNejdrek1QbVpuUWJtWWgxUTBZUWl2SEhKVWJnU0QzMlFTRThfVzVvN2JGZGI0MXljZ3FiSWN5V3ZBZmpLVVl6VTN3cnlmWExrNkZLdFg0RDZzbHdJLTNRcGlwbFF3QTVsM0ZDdTcta1c1YkZVeG5ncERjR04tNWR2R3dEb2o1dDU1Wnc0U0RaTVRyR3BTUjhzbmxkTHhX?oc=5</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>08-05-2026 09:08 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>MS Pharma</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>Systematix Corporate Services Appoints Ms. Rupam Lal Das as Joint Managing Director</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>scanx.trade</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxPQmx2TTFEZlJTZnB2UzltX3pzX2dLcS1hWE9MS2NFMnV6empyU1N4LXVHSV92T2thMGRFU3VUYzEtblNGTUJYd0JxSHFtSU92d083LWlnT3ZrbXhHUDdVNVVYWnFPNTkxdUYzLTgtUV80a3NNcWNsZ1VYd2FEb0VEVFllU3pBUFBKTzRXVDF1MnFGN0tDVl9RMU9kY3pXV0tnakpGUmNFcUgtZ18yMXNJeGcxOEx6djVzUFoxTlJkai1qVjVnQ0lIUXVtUWJVTUNxb1ZXZnh3?oc=5</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>08-05-2026 17:42 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>MS Pharma</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Sun Pharma shareholders approve postal ballot, appoint new independent director</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>TipRanks</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPeklUY2tPZ0NGQTUxeTFEUGdOZmRCcXhIV3BhdDVpYnB6RGo3MldKakM2YUM2QVFNZVBYZnJqMzRJYWdIMThKLV9DWGZMeGE1cDZXUXRPTm1vejlZMFAyWV9scWZOaHRWV19nRnl2OWVHZDJPdXFHRDJWT3RGbGVESEtVd012THUzWEc2NkhSd1JkQzVJeWpONjUybnRMRzh4clBtQTlSVWtSdm9Xdkx4b001QXBSbnZ6YXlpZ2FITDVvZlVDOWJON2pR?oc=5</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>08-05-2026 15:19 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>Alvotech</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>A Look At Alvotech (NasdaqGM:ALVO) Valuation After Weak Q1 2026 Results And Biosimilar Pipeline Updates</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>simplywall.st</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxQMHdvT3dNRE92aWp1MmgzSks2Zm4zbU5VemhvYnJ4S2s2aWhCX19lc25BTXlZdGpFSVBrckJDRjdoWTFyRS1XdFdZSVlvOEl3YU1nUGluRVpiTDlQTHRWZWhuSkEtQ0pVQWlIQkxlQjFjMmFFVWhPS0xsSkcyNWNVMk9rRTRxRG9mVUgwZFlXRFYxNkhJNVdDR2Vvd0Rzb1htZnJjVkh2RXVzWjNUQlFNZ2Nib2FWcXVPUjdzWEF5aENHNm54dWlsVzlvVXRyRGZ6UnhQSVZSazU5Zw?oc=5</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>09-05-2026 05:06 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>Alvotech</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Alvotech Earnings Call Balances Risk and Growth</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>TipRanks</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNVzBGaFlLOG1RZkFIOWRBYnd3M0tDTUU5dXZLWGU2LVBrR2hGaVBHcnFGTV9SYzdwWkVxeGlfenVwcDUyQUlpSnRxTldnREpIRTlpSl90ZEtGZmZ5dG55V2FGMXBaVW9XWE94NGxRN1dLTFZDNFdtVU1Hc1lUVFdyX2JONzBQWnQtLTc2a3NvdkdNT2V1Q2QxQ2RhenJiOHo1?oc=5</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>09-05-2026 02:07 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>Alvotech</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>Alvotech (ALVO) Q1 2026 Earnings Transcript</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>AOL.com</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1NTHp4RmJRVXNtRC1nYWMwNlh5MzV1SjhWZzY2ck5VY0NTeko4MVVBWHNTcXhnZVk3NFoyX1M2NVhSbGtiTVZ5aWVmdTRZVG91Mm1qWmNfV1BjY2NJMzFwQVdFVXFwS1AzZ2FPSlkzUDB5VHphdTZCb01lc2x5RHc?oc=5</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>08-05-2026 15:32 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>Alvotech</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>Alvotech Q1 2026 slides: revenue dips 20%, EBITDA rises on mix shift</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Investing.com Australia</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPdmZOYlZveWVsQklZNl93RzVEeVBScF9MUnlHeUlxMlRUOE9QY2RLcE5IYmxicm5QblJYSHVsUkhpNUlJUHNEcnc5bnlpMG1vX3FNSVI4V1hJZzgyRVJJczJYVUI1c2UwOVgyVXdTaG5aQm9uS2ptY19sYTlaWmFYekxoUXpkT2Noa0FoV2dMZmlNWkV4WXlHUWZiR3FXb1I5eWFUUkNFdjAwbTJOb1Q0V1lyQWt0TXFqWUJSdXJ3?oc=5</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>08-05-2026 12:20 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>Alvotech</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Who’s Hired? Viatris Begins Search For New CFO</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>Citeline News &amp; Insights</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxOM2p0ek05bVowRFBiZFU4OExlYVdlMnMtdnNJeXI0LWJlV25EalRyQlhXTUk5N094elpadXA1QWgxd0Y1Nml6SHF5ZTFQdUh1NnB1MDFlLUpTYTV6S2NpanE0RDlXQkZmWS1qSEtsYkVqN2k4MXlyaWsyRmVsaElmVkpGVlhVcFQ0dVJUd0hST05zY1hsbjZTeEdDZVVBbV9rNVgwQnV5aElRdndNcHRCU0RlNDY5N3BScHg4QmVUVDlrZ054cEFsa2FkWUhDcVNzeE83ZzR6Q3dHQQ?oc=5</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>08-05-2026 12:08 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>Eric Michael Teva</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>Jomo Kenyatta University of Agriculture and Technology</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNVTBmUDFfdUpDMk1VWUJ5aEV2SXpPZlVUd0w4VmEwNWFELW8yZWNFVHkwbkNaY0cya0JTalU0ZFhuUmxZRlBzb0VnSDBGNUd0UHRLZTFKR05xUnhpeTlQWi1NZnFuNzd3YnNXNHlMWWQ5RS1jdGRGbGZXWHZEY09tVmphMmk0aFdBWnc?oc=5</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>08-05-2026 14:14 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>OmniAb Q1 Earnings Call Highlights</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOTzF2OFVWa0NmWVUxZWZUX2tVbEtsenF1SkJKVk1jclRmUFUzZzg0TEZTVFZwRF9SSy1hR3hnbHc3UktYUmtVaWJNUWZLQVBfRG1NZUhqRnJGa1d1UVFoblpheUJ0RDRWZE1rdzhaeUM0U1NXblNFbHA0OThJTzI3MDhTbG1oLXVtOHZiZTNVOENIcVVodWlTSjk2RQ?oc=5</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>08-05-2026 11:07 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>10 Walking Shoe Sales That’ll Make Long Days on Your Feet Better</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>Good Housekeeping</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQWlZob0JzdzR4c3FLSVZudWpVMTZlSWtCX1U2T2NRWXBrTzJ0VG0zSWJkcm5LMTZNeGN4WVlBNGJoMGlhZGVDcUpfdmF0ZXNjM0ZjREF3LV9lRjhyLThnU0N5blJRbHplOHpzZmUxX0c4b3BKY19CVlZwckp2Vm55V0IzbF9yU3RHNTA0LUpHZkpjaHM?oc=5</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>08-05-2026 20:42 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>Who’s Hired? Viatris Begins Search For New CFO</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>Citeline News &amp; Insights</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxOM2p0ek05bVowRFBiZFU4OExlYVdlMnMtdnNJeXI0LWJlV25EalRyQlhXTUk5N094elpadXA1QWgxd0Y1Nml6SHF5ZTFQdUh1NnB1MDFlLUpTYTV6S2NpanE0RDlXQkZmWS1qSEtsYkVqN2k4MXlyaWsyRmVsaElmVkpGVlhVcFQ0dVJUd0hST05zY1hsbjZTeEdDZVVBbV9rNVgwQnV5aElRdndNcHRCU0RlNDY5N3BScHg4QmVUVDlrZ054cEFsa2FkWUhDcVNzeE83ZzR6Q3dHQQ?oc=5</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>08-05-2026 12:08 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>Why Every Disney Adult Is Buying Tevas From Amazon Today</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>AllEars.Net</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPZjVOcDN6TVR0SENpUHJSN0UwZXJBX3o2SUlkSHI2RGNNX1d2VGk2TjhWZGdZZWQtNW5JVXY0R1VOb2VsTzZleWg0eUtuVUtoMWtFWnNQUzJwdFJGdnU3aXdTNjVjV1BTbVRFQXdqOFc0dmdGMTZIN3Y3aHpyM2Q3VnQ2dUYtU0U4SEdNNzFVRW5LQXAx?oc=5</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>08-05-2026 19:00 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>Sciatica Treatment Market Expands Across North America &amp; Asia-Pacific | Pfizer, Novartis, Teva</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>openPR.com</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPcDVHRk9TcGo2SDRsUG81c3hEd2hydVI3ekhNWmo4al9FOG5fTDNzWFJWQkdVOHNZRVJMb1h4UWFOM3RjT1FsUGhnX1gwVGVhZXp4TEpYUHdSTUJpUWJGX2JBdVNlR1VRRnFBc0lGWEU0VzlIb2g5dmhtREJfekFOWTF0c1p0OXpLbC1sNzhmRmJWWkR1?oc=5</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>08-05-2026 19:21 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>A Podiatrist Warns This Popular Sandal Style 'Lacks Proper Support'—and 8 Shock-Absorbing Pairs to Buy Instead</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>Real Simple</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNRnB0VWtuaEMwTEJPaDBaMncyRGtTV0NoT3E3bU8wWENUUDFjS3RiT0FEaTRSS0ZEQm9lVl9PSDdkSWtRbDFiYmJITEdCenpvckdwc3pLaXpiWDJRODdIcnl2dzNiUFhLZkktZFo4eDVGcjhtT2lVOGVEVEh3c1NEdzJpTU1vTld0SVJCTWhEaw?oc=5</t>
-        </is>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>08-05-2026 10:30 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>Crocs Shoes Cost</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>Jomo Kenyatta University of Agriculture and Technology</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPUDdMTG1sU29saENmcEpST2Y1aEZSZnJsZUFBTU1FWmY2b2dMZnBNUXB0LTdNbS1DNEhoSUNoOHRpc3d1emJVN0tnZXRXaG56VTJuZlZqWTd6UWFGd2NkUW1ZSWdMZnA5NEd0ZXhLRG5rMXBpTjFHOTVLVUxDSVhYOEZLRmpEakRo?oc=5</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>08-05-2026 11:13 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>Emerald Coast Foot and Ankle’s Dr. Carl Speer Talks InvisiFoot</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>AOL.com</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTFBLejM2OE50Nlp5RGladmk3djlWNGo3Q1NrWFJkZW5LVGxBeEYxUkNCYkZWY0hLbG9NRmxlYlh0YTYtaWlYd1FWTTNOMjl5TGRSaFpLeFpsTEhHb01JUXNVWG40RDhNdExaNTNXeG5FcDFjcmo0c2c?oc=5</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>08-05-2026 09:16 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>Havaianas Latest Design</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>Jomo Kenyatta University of Agriculture and Technology</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOOHNyb1dMMjlhZGpCX1Vyckcyd3llQ0M3NFpKejJsaXU4MlBVYllESUk2WGkxNy1OSTRPTHBrYzhwUXlNTjgzeEZmMU1mdkYtcFVEb3pobGYxTVFHREpuWm1oVkF2aFFyU0NuQ1o2NDk0N2ZZYXlaLW5BVWE2UmF6bnlGSmFVbkhvRlJoZmdZZ3h1QQ?oc=5</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>08-05-2026 08:54 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>How Teva (TEVA) revenue breaks down and what it means (Near Lows) 2026-05-08 - Verified Stock Signals</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>newser.com</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNeTMxM19VWXRKbS1yTkdvajFEOWRxYWRYejNmdlZudVhCb0FlMGNzanZyUTgxdzNJM2ZCcWM0UjR6MHVXYzlVbGRvZzhqb24xWHdqOUQtc0N5bmhkQnNGaE9HOGFDY0x3dXE2aDRYTjZHWkFPS1ExblduYkQwcjlLcnIxc2hjQWpZanAwdmpiRzUyc3ZpVG1SM0JDNWtIWnpyZHdYTG91dHJIMzFIb3VLSmhqNjV5S2c?oc=5</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>08-05-2026 08:43 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>Samsung Bioepis</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>Semaglutide Biosimilar and Generic Market Size, Share and Latest Trends 2026 to 2035</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>Insightace Analytic</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQckkyWlpVRUgwWk1lSWF4cHVjZE13TWpqdk4xZnotYVlPaGpNdGI5djdSaDBuSnJmS3NtVF9SUXNjeThBMFlLdDhBcktrb0ZlMVhTa2FfRXRPekQ3MTBtSE9PUEFBUWJqMkZDRk5vQURfZDRMVzQ3QU5jN0hNYTI5SjZlUGc2SnhLbktYcnB5cFFtZw?oc=5</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>08-05-2026 14:27 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>Samsung Bioepis</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>Quotable: Words Of Wisdom From Our Recent APAC Coverage</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>Citeline News &amp; Insights</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNWk54R1plQ3AxU1V4UWhFNzhLSmNWQnZQdnI0TUwwQzZZX3NrR3gyN1lGOXJ4MVI1NkdIb0N3N3lqbXlNZGN3OU42SEpjSE44OWNBbmplMzcyNV81eFdXV00zREFSVFdjN2I3bWZQbEljZDFydXEtLXM2eWhBVzJ1bDlwWnMtQkNkazhBOEtBYy1nVFdEZWlqUHBqRmFxQ0p6UjJTVEFsRTBHc1hqLXNsem1Ebm5ySm83Q3lRaFNMXzhWN2pxQWFCc3piRzU?oc=5</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>08-05-2026 08:39 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>Samsung Bioepis</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>Deal Watch: GSK Calls On Halozyme’s Enhanze In Cancer ADC Administration</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>Citeline News &amp; Insights</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxPY2dPMkt1YXBoUzV6dGs3UzhhYmZNTExNUG1PNzdtemFyMDIwS0FnaGlZME5VUUZkSDNVQnFxdGhjcV96T1AxQTlCcUZXMU1oWmFKelBjOHhYLVdPT09oR0tHMkFOeTBVVnhkNjREcG52dXNrSlRxTV91NDd4cVRTZ1MxRVlwdGNISXRzVTJtNmhGQ0ZzeHJpeVlrVkE5SldVa2t1Y0tuWWFpZXRmamxBMkNwZzRuNlJ6cGtpVEc4ZE9NRGZqcTB4bFEtc2xrdDVwcFVrZHNrTno4WFZqazJIRTQtR2VwLWppQ3I1Y2NjMnAyUmlFSERfOU1R?oc=5</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
         <is>
           <t>08-05-2026 22:01 UTC</t>
         </is>

--- a/news_results_raw.xlsx
+++ b/news_results_raw.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E105"/>
+  <dimension ref="A1:E106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,34 +463,34 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Antibiotics: Europe at risk with fragile supplies and heavy dependence on Asia</t>
+          <t>Harmony Biosciences Expands Patent Protection for Sleep Medicine</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>HarianBasis.co</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOeXVQZFVhWHY3Uy1hQkNvX3JxdW5FLUEtVklxMUNnRTNNSlZ5UVRrSHFNRGdScUV2ZnpQMzNDM1g5T0FQVlpseE5idW9Ccy10TWxvTUhXSDJVZU9KU205STNNT1Rvek8tTGZWVjFObnkzQk0zWUlFTDhnYk4yblpnOWljeS1oMF9zZjFscUd0ekdqenpGZkNXeE1iclAzS2JxZ0tSaldIRzcyS20xLWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNMV9FT2NJdFVXREZfV19HNUxYM0lxeXFoeVRMR0tnNWpMczVheVFmdF9wNWtEVUhvWk0wbVA3NTdFcXFJMHMwUGZQcFdqWkV1Q1RhY1ZPQTlheWhmNzFVVnZFQTlKQ2JqR0hYZW9aVWxKcmNEcFl1VzhtazVJVUVfSA?oc=5</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>09-05-2026 14:50 UTC</t>
+          <t>10-05-2026 02:59 UTC</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sandoz</t>
+          <t>Gedeon Richter</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Novartis AG stock (CH0012005267): Pharma giant eyes growth in weight-loss and cancer drugs</t>
+          <t>Richter Gedeon Nyrt. stock (HU0000123096): Shares rise on strong quarterly performance and dividend</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -500,282 +500,282 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxOU25LNXBac2dEVGpvdFIyZVQtdmllQ0Jia09DeDlWZ29iV2RXNDBaakpkd05EdlFOU3VSZjhqRmtJR252b0tqYUhpLXlUbmJSRE5LTDhwdkFydHprLWpJeVNzUW9OOUw1RWcyb09oQ3VLdG9lRU5qLXFkUFdiV183V2lOT2xlb3dBVm9Lc0ZUR2pmSHFWM1J0LVB2ZFBpMV9WRXVQTXpCOWZZNF9ubEFwNTRQS1cxVVBnUTdSRXpEZ3ZfdlZSTXlKOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxPcXB6eUswMWowQVB3QkMzLXJBYnFuNkJzMW5xaVp3dlBKcWdnVGdvQXFJdDQtYVlIbHdmM3NYaUtjLXc2X1U0UDl1cFB3SG50Z3dCMEdxNXMxMXZaU3dwX21jcU5NQWVmUTFIYVpzandrUWZLb2lmV0RXUFoyRDl0bnNYNXU0ZU9uS014dmppWnozLXhUa19TVmlCa3dZclBoek5nRWpEb1drYnRldkdBOHZJUUg0WjFSekZyNF9CZFZnWTBkZE1Saw?oc=5</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>09-05-2026 13:47 UTC</t>
+          <t>10-05-2026 08:02 UTC</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sandoz</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Evotec SE stock (DE0005664809): Q1 2026 revenue drops 22% as transformation accelerates</t>
+          <t>VIDEO: Bevy of psoriasis data at AAD 2026 promises more to come</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>Healio</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxONVNzbm5QOTBxbWVGM083djlNWkE3UkdvVDZaVHRTdE1aUWZUYXJJaUxocXVHTFVpS3lJS1gyQ1pKeV94VGRBeVNPcGlodTF4LTNkdmhXd2NDM2VRZ1VQNXBnTjFyVTBIWWlEbVpwWlZuYVBFN2VwZ0FpSnpIMllHbFZpQ1MzM2tGNVM5TUhqTGRGWmpoSTVkdGhwVEktSWdOOElUMlVQaXlGM2hEdlpNNnhyUzJQUUFlbGhGdjNodjA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPSHk3UEkxRkh0dFp5VWppQVFRaHJKSkZfRG5fYnB5czJXN0I4dU95MlNqUkdQTm1XSUh3WmxIbnNVcW0xSjI5T3d5U0VTZG9vdUk1WUd6Q2NOT3dJdGs3V1Q3ZTZSUUNmMkRLV1J2OFltU2RUc3FyOUNPemlsckp6am16LTNZdldyNFhZdlpMNDhoaXd0LWNvSTJQazE1cVc2VFVxTm81NlVGZWZaRi0zRw?oc=5</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>09-05-2026 13:36 UTC</t>
+          <t>10-05-2026 12:43 UTC</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sandoz</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Harmony Biosciences Expands Patent Protection for Sleep Medicine</t>
+          <t>World Ruminant Vaccines - Market Analysis, Forecast, Size, Trends and Insights</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>HarianBasis.co</t>
+          <t>IndexBox</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNMV9FT2NJdFVXREZfV19HNUxYM0lxeXFoeVRMR0tnNWpMczVheVFmdF9wNWtEVUhvWk0wbVA3NTdFcXFJMHMwUGZQcFdqWkV1Q1RhY1ZPQTlheWhmNzFVVnZFQTlKQ2JqR0hYZW9aVWxKcmNEcFl1VzhtazVJVUVfSA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQQ1hsc2F6TlRnV3oydWZzVmdYc2hjWE5HWDZ0dUJJX2NiNGNxOEVwQTJKSWZWcmJhZVJwTzhkek1sZi02TzFhOHBYWHRxaFBXdDZzY1NGSnNJZk11QmtkM0hxNm1GMGh6bWtlelhUNzlFOWY1TUJpdHdreEQtMlI0QWRNelpqVklsRmlJUkRqVktPWHVwTURFSWZCSzlyZUotQzNYbEowSUkwWm4zdlRyQmRESktWRmtCaEROYlpkTG5KR1BDLVNaYw?oc=5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>10-05-2026 02:59 UTC</t>
+          <t>09-05-2026 16:16 UTC</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Formycon</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Formycon AG stock (DE000A1EWVY8): Biosimilar developer eyes growth amid new launches and partnership</t>
+          <t>How Germany is tackling a €40 billion drug shortage</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>logos-pres.md</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPbnV3UzQzWDB4ZnUxSUtkaXVQQ1Zrd3FwQ1IyY25FZldEWFVKbnEwblB6WEFVVHppUDlYR0tjWHlMeUxZeV9FYVgzWVpSdTl4LUFWQS16TWVfRElDV2RacGdka3dNR2NtT0tMMDVxOGJmeDYyc0VtQUUtOF9fcWNLUEJZbzNHaXM0NFd0VVo3cFU0c0F3X0hpdGMwNEU4NjhSTUJBNDNXU0NYa0ZsdnRHY24yUW9INXZGWkFleFFscnhkcFNUNkE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxQY0VxZHRPQlFsWm15NktCQTFNa3RMOXlBMnhuNHRkV0VBbEdYeEVhOGdSY0IySFVBN1FJNVJkTDBWQ0JSWU01T085TE9mSl96M2VHUVBGTEtNS0EyWTlkWm9feDhCenE4aTZGX21ycTh0ZWppRi1WZm5qMkpmNHdLSG91QzZubElfekE?oc=5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>09-05-2026 14:08 UTC</t>
+          <t>09-05-2026 18:44 UTC</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Gedeon Richter</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Richter Gedeon Nyrt. stock (HU0000123096): Shares rise on strong quarterly performance and dividend</t>
+          <t>Zai Lab Q1 Earnings Call Highlights</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>sharewise.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxPcXB6eUswMWowQVB3QkMzLXJBYnFuNkJzMW5xaVp3dlBKcWdnVGdvQXFJdDQtYVlIbHdmM3NYaUtjLXc2X1U0UDl1cFB3SG50Z3dCMEdxNXMxMXZaU3dwX21jcU5NQWVmUTFIYVpzandrUWZLb2lmV0RXUFoyRDl0bnNYNXU0ZU9uS014dmppWnozLXhUa19TVmlCa3dZclBoek5nRWpEb1drYnRldkdBOHZJUUg0WjFSekZyNF9CZFZnWTBkZE1Saw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNYklqX21HcGR1UmNTY0REUjA3X0UzUHZtYThrTS1RX2dmazBaMzdLYWt2SHNJQjlha29wMHhPVjBlTEtKejBrNVVSWGc1ME5iWWtZdmRCZHN1TC1xalVLaWFTNHRZcFNMWF9sUmhBVnJZUnY5UHFsZXV0S29mUnpWWUhFc1oycHl5VGtkMkV4RUZHM0Q5RkxjamN4bHRRNVh3Z29vMEJB?oc=5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>10-05-2026 08:02 UTC</t>
+          <t>09-05-2026 17:24 UTC</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Hikma</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>World Ruminant Vaccines - Market Analysis, Forecast, Size, Trends and Insights</t>
+          <t>SIGA (SIGA) Q1 2026 Earnings Call Transcript</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>IndexBox</t>
+          <t>AOL.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQQ1hsc2F6TlRnV3oydWZzVmdYc2hjWE5HWDZ0dUJJX2NiNGNxOEVwQTJKSWZWcmJhZVJwTzhkek1sZi02TzFhOHBYWHRxaFBXdDZzY1NGSnNJZk11QmtkM0hxNm1GMGh6bWtlelhUNzlFOWY1TUJpdHdreEQtMlI0QWRNelpqVklsRmlJUkRqVktPWHVwTURFSWZCSzlyZUotQzNYbEowSUkwWm4zdlRyQmRESktWRmtCaEROYlpkTG5KR1BDLVNaYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE5wOHp2X3ZZTXJZOE9UeXh3cFB4c1hFQ1QxSFFqNFM1M0tGbnZscEp0TXZmc3lrM1BRRWhQSkExLWFtUWQ1ZmU5dllzR0NlbHp1U0RETVdVMWRrX3B4YjFKUjhHa0FkMjBnY2RDNzQ1bTJDZUJKX2liNTJR?oc=5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>09-05-2026 16:16 UTC</t>
+          <t>09-05-2026 23:38 UTC</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Hikma</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>How Germany is tackling a €40 billion drug shortage</t>
+          <t>Al-Hakim: PM-designate can help Iraq break oil dependence</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>logos-pres.md</t>
+          <t>شفق نيوز</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxQY0VxZHRPQlFsWm15NktCQTFNa3RMOXlBMnhuNHRkV0VBbEdYeEVhOGdSY0IySFVBN1FJNVJkTDBWQ0JSWU01T085TE9mSl96M2VHUVBGTEtNS0EyWTlkWm9feDhCenE4aTZGX21ycTh0ZWppRi1WZm5qMkpmNHdLSG91QzZubElfekE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNV2FfYjVQbE5DakMtTnNTTExZdWVPbk5VbEQ5R2hINUpfTUx4Zll1bEI0ZVZvXzVfb2lkOUpQX2RBbHNnYVpDaC1IM2x2TGxRdjczN3hkQ0VwSjJWa0ItYTFDMlo4bkZ2N3l2SDd3SGZWdXFyNU9DQ0lObGtOVTlCejdaSzRfSGYxNmtn?oc=5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>09-05-2026 18:44 UTC</t>
+          <t>09-05-2026 18:29 UTC</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>"Emirates Medical Day." An embodiment of the state's commitment to building an advanced and sustainable health system</t>
+          <t>Standing Bone Strong: Introducing a New Awareness Symbol for Osteoporosis</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>صوت الإمارات</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxQUXFFY0RlX0ppR2dBX0EwNmdpVlE5dF9JT0hJbTdndHotWkg4ZnN4Rm5aejlEUUVLNHAwdmlsVGpGZnlLWUJscDNYc3Q4X1NoZ1dGVG9aMDJ5X3dtYjdQQVJyRlJRd3JZZS0yNlFQd1pqcUE1MFhWdFRkVGRIcktWQ3RtRTJhMFRDSjZ0bjZwblpKQnVvZmNMb2ZIbmR5OTRINmo2blcyNDVramNVUzVJM0tOenl5MTByTEVZS2tLUDVkSm5VaUROMjM4SEVPTC1uX0d5NkJnN0VSUFlPUHJzdzlTaVBLcGF4eUlPTGRWYzI0VjNiVG5TRXp1SzRGdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQRDRCa2dnZkdVYlZoYzd0OXpJYy1NV3ZFalNSdnZQdWk0bDRXMUtWWS1hMUtKU1lob05hNFp5U3pSN3FLRWRoUkZLM0xvWnNQdmp3NTRiMWc4cFBOdDFSTXkyQ2FKVkVZVUtDOFRsU1RVOVN0UXNEd0RaMEM5cGIwRTNSUTljeWRDdHhocVMxZDJzRUFQQ09QNjVfbnlhaVZiNjZXNHpSalNMcmM3cTJj?oc=5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>09-05-2026 10:14 UTC</t>
+          <t>09-05-2026 23:01 UTC</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Zai Lab Q1 Earnings Call Highlights</t>
+          <t>Amgen’s Real Time FDA Trial Pilot Puts Oncology Execution In Focus</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>sharewise.com</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNYklqX21HcGR1UmNTY0REUjA3X0UzUHZtYThrTS1RX2dmazBaMzdLYWt2SHNJQjlha29wMHhPVjBlTEtKejBrNVVSWGc1ME5iWWtZdmRCZHN1TC1xalVLaWFTNHRZcFNMWF9sUmhBVnJZUnY5UHFsZXV0S29mUnpWWUhFc1oycHl5VGtkMkV4RUZHM0Q5RkxjamN4bHRRNVh3Z29vMEJB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPVnRLUzdjbDhzMVJKcVJLLXFlM0RaaGFra2JvVllMYnZtb2lsdkE5bUFDT1hjTUtRY0YxaW96bWZONmc4RWVrQUNPUlFZR3pkbEVIbXBaN3FfZU0yTlRieGc0bnJ3dFF6WVV0M0tySXh6cWZFVmZ5bjI1SDBqa0M1MTFFLTA1bnVMNjdQN0wzZjg2T0FEcUg5UlBR?oc=5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>09-05-2026 17:24 UTC</t>
+          <t>10-05-2026 14:09 UTC</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Hikma</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SIGA (SIGA) Q1 2026 Earnings Call Transcript</t>
+          <t>Inside Amgen’s Next-Generation Labs: Powering Faster, Smarter Small Molecule Drug Discovery</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AOL.com</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE5wOHp2X3ZZTXJZOE9UeXh3cFB4c1hFQ1QxSFFqNFM1M0tGbnZscEp0TXZmc3lrM1BRRWhQSkExLWFtUWQ1ZmU5dllzR0NlbHp1U0RETVdVMWRrX3B4YjFKUjhHa0FkMjBnY2RDNzQ1bTJDZUJKX2liNTJR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxOTWxMdmxiLUhRT3lrMWRmWDByeE9vU0J2UmYwSVE3cGV5eXR5dWJmZ1phUkJnaG91WE5RaXlkWjJodHA2X0xRRlhxLWNPd0V5eWRfcERIb1hJd29PX3NnaWMtaVo3Q1QzVEZiZW5vV19JRW5rbDd6V2UzaE9FTUZGbGxvdXFZY3JNS1ZVa2Y0d0EySXRRd2lLYlpqelBELXRmQnItSXAyN2s2aDd5ZlRZVlEyeF93R3ozRlltemdFc2l1WDlH?oc=5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>09-05-2026 23:38 UTC</t>
+          <t>09-05-2026 22:09 UTC</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Hikma</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Al-Hakim: PM-designate can help Iraq break oil dependence</t>
+          <t>Earnings call transcript: Amgen Q1 2026 beats EPS forecast, stock dips</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>شفق نيوز</t>
+          <t>Investing.com India</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNV2FfYjVQbE5DakMtTnNTTExZdWVPbk5VbEQ5R2hINUpfTUx4Zll1bEI0ZVZvXzVfb2lkOUpQX2RBbHNnYVpDaC1IM2x2TGxRdjczN3hkQ0VwSjJWa0ItYTFDMlo4bkZ2N3l2SDd3SGZWdXFyNU9DQ0lObGtOVTlCejdaSzRfSGYxNmtn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNTkYtdUZIUmhVb3N1RUdGU3loOUp4VDBTeG5nR0s2dEhlUlFXb0Q0ZjBtU1Q0N0VSNjVnTllQdzR0d0k1UEVSczE1NE0tdENuZHlWc1RMazRoV1Y4LXVyZGwxa2JyWUhkYTBFdE1BTFJ3Nk9pVm1rLWxmNjdlWUh4Q0hxdWl2WWpjeHJxQ19mS3ZodUdERTc5d1lRdGRpYm5KS2V0eU5BSGZZcDZBVjZNZHhZcWRqVEdaa1dIQ2NUVmpUYzRRNGF3SQ?oc=5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>09-05-2026 18:29 UTC</t>
+          <t>09-05-2026 15:12 UTC</t>
         </is>
       </c>
     </row>
@@ -787,22 +787,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Standing Bone Strong: Introducing a New Awareness Symbol for Osteoporosis</t>
+          <t>NewEdge Wealth LLC Acquires 7,521 Shares of Amgen Inc. $AMGN</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>MarketBeat</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQRDRCa2dnZkdVYlZoYzd0OXpJYy1NV3ZFalNSdnZQdWk0bDRXMUtWWS1hMUtKU1lob05hNFp5U3pSN3FLRWRoUkZLM0xvWnNQdmp3NTRiMWc4cFBOdDFSTXkyQ2FKVkVZVUtDOFRsU1RVOVN0UXNEd0RaMEM5cGIwRTNSUTljeWRDdHhocVMxZDJzRUFQQ09QNjVfbnlhaVZiNjZXNHpSalNMcmM3cTJj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPNVY3RVZvTzd2Y25lWHJUdlpQVVpqYjQ4TkdQSWJEeHl4Ykotai1Gd3A3QWVfRVhBNjY4Mk1tRm5oSFJoRnl1OWpDaXdMRmdFWmJoUFNKa2JZVlhWc2UzUFNjZHI3QWhmX3d3ZUFrbUJTVG5KSVk4bmFlUlU1TGItWFBLdkZDWjdyLUg1Y2ViX0tpUndJc2owZEpNa3pKTlpkUEtNdkR5Um9qUXBkNzlSUnVCcWRzczRrTnc?oc=5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>09-05-2026 23:01 UTC</t>
+          <t>10-05-2026 10:04 UTC</t>
         </is>
       </c>
     </row>
@@ -814,22 +814,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Earnings call transcript: Amgen Q1 2026 beats EPS forecast, stock dips</t>
+          <t>Amgen Q1 2026 slides: six growth drivers fuel 24% expansion By Investing.com</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Investing.com India</t>
+          <t>Investing.com Nigeria</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNTkYtdUZIUmhVb3N1RUdGU3loOUp4VDBTeG5nR0s2dEhlUlFXb0Q0ZjBtU1Q0N0VSNjVnTllQdzR0d0k1UEVSczE1NE0tdENuZHlWc1RMazRoV1Y4LXVyZGwxa2JyWUhkYTBFdE1BTFJ3Nk9pVm1rLWxmNjdlWUh4Q0hxdWl2WWpjeHJxQ19mS3ZodUdERTc5d1lRdGRpYm5KS2V0eU5BSGZZcDZBVjZNZHhZcWRqVEdaa1dIQ2NUVmpUYzRRNGF3SQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOWUJYTzdTb29ibWd0ZklYUFpzcS1RVng2YlRLQ0hYdzFaQ3NtZ3Z5RnJNTXZNVkhLQjJNeEptNEN4Y0JLbzA5SFVaWjRZNng2LUlWSUYxbVMxUFRTX09EN21ydGtuRUtUM0pOWFVrY1ZoSFpIN3lYME1BckdKYVpBd3pKWlAwSk4ycGliSEc1YnJQVWVEWjhzaEtKVExFYVhOd2NaTHBkY3JHRk13RUtteFgwMA?oc=5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>09-05-2026 15:12 UTC</t>
+          <t>09-05-2026 21:27 UTC</t>
         </is>
       </c>
     </row>
@@ -841,184 +841,184 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Inside Amgen’s Next-Generation Labs: Powering Faster, Smarter Small Molecule Drug Discovery</t>
+          <t>Why (AMGN) Price Action Is Critical for Tactical Trading</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Stock Traders Daily</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxOTWxMdmxiLUhRT3lrMWRmWDByeE9vU0J2UmYwSVE3cGV5eXR5dWJmZ1phUkJnaG91WE5RaXlkWjJodHA2X0xRRlhxLWNPd0V5eWRfcERIb1hJd29PX3NnaWMtaVo3Q1QzVEZiZW5vV19JRW5rbDd6V2UzaE9FTUZGbGxvdXFZY3JNS1ZVa2Y0d0EySXRRd2lLYlpqelBELXRmQnItSXAyN2s2aDd5ZlRZVlEyeF93R3ozRlltemdFc2l1WDlH?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQalozZ19OM2YzbURma3FncWUyMnE0cUpXWEd1NFF4UWhYREtjWWNVSFdHdVdCV0lWSzVqaWRXY2o3cWZOZnYxdXhjZTh0RFNuZmpvaklNQzRNUTY0a3NNMW9YazFVTHlLRno3Q2VoMTRkN2tkUmtaVEZXcUN4cFBZMk1hck5qV09kT2RpSWJ2eFlEaFdIeFRuaHU5NlFiWi1uc1I2ZFlUM2pDNkVEZmhtM2tsNk5kR2VYR2pxWDU2d1J5SVF1aGZSUWtTOWw1czQ?oc=5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>09-05-2026 22:09 UTC</t>
+          <t>10-05-2026 08:16 UTC</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Amgen Inc. stock (US0311621009): Biotech giant eyes growth amid patent cliffs and pipeline bets</t>
+          <t>Sun Pharmaceutical Industries $12B Organon Deal Marks Innovation Shift</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>Business Viewpoint Magazine</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPS0VvTzJmZm9WYUY1YUVrcnJXdmtldlNEbGw1UmJEZWkyRkRVOXlFb3FDbmV5YXl6dnRhajJUTFB5Q2dybEVIaEFDaVhZakQxOG1jaXRSRF93cGdHSkItTlV3b2Y1b1IxSkdPZVFONEpQSUxLN3VJNTFFZVpBSGd0dDluOUotRHcwb0RQbmg4UW9KTk12WFZWNjJKNWZfdDhQZmJHV1VaTHBJcmNDbk41UnlFdUYtd2EzUkdlUzdDZUNNQzg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTFBZdDRfUUNvd0JuLVd0ek80U3N1eG11ZGtEbS1BenBjWU5LMmtXczdCM2V1NmoxZGRpQTNnUXBXa1o1VjQwTlBnSkhjYmthejRaNjBFWnJhZ0I5TzRkaE8tTTZIVE5HRjFTZ0hHV09ZMnRNYnhtc2N5S293?oc=5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>09-05-2026 11:08 UTC</t>
+          <t>10-05-2026 06:07 UTC</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Amgen Q1 2026 slides: six growth drivers fuel 24% expansion By Investing.com</t>
+          <t>Pharma Companies Invest In US While India Still Depends On China For APIs</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Investing.com Nigeria</t>
+          <t>Deccan Chronicle</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOWUJYTzdTb29ibWd0ZklYUFpzcS1RVng2YlRLQ0hYdzFaQ3NtZ3Z5RnJNTXZNVkhLQjJNeEptNEN4Y0JLbzA5SFVaWjRZNng2LUlWSUYxbVMxUFRTX09EN21ydGtuRUtUM0pOWFVrY1ZoSFpIN3lYME1BckdKYVpBd3pKWlAwSk4ycGliSEc1YnJQVWVEWjhzaEtKVExFYVhOd2NaTHBkY3JHRk13RUtteFgwMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPR2RWLUpSRXVYZU53SWVGb1B1a1FreHBoUi0tbzhDR1JfVFFnVl9Sdy1xNzJHVlJzbHZWVEpNQV9kdnA1N3Z1U2Zyc0FJdXdYTEFTZC1hTjA5TE9iQzg5Wk10dHBSYUQ1V2hocUQwanE2bDUwQm1LS2tjUlNjS3huRzkzSkYxVEJIOS1pMDFDX1hTb0xVcmxrRU94VVAzRWpIazRqVmcybjZlSXJlb3VtYmp2X1FpX24wcUQyRFc4NNIBxAFBVV95cUxQMWp2a093dHlaMUxSNFR3b1l6SUhZejFuVVVMSEl4akZsby0xU2F5Yk1wZFJ4RDdpczAtVS1vOHg1czkwcUt0bmQ5eEZBNVhGc1hDZ0U0OGZSTVAyaWhfdGw3bW1CWmxOZzNKQk1JSTl3c1lMZE1zUVVmT29zeVFyRUd6WVg2MEx4U1JfU21BdlNiTmRNTW5sZEdFRkFpejhTOVlkUmowRTFaWktnY3RsbER4bU1DQ2pmVTU5WEFGTVpHckNj?oc=5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>09-05-2026 21:27 UTC</t>
+          <t>10-05-2026 12:53 UTC</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Amgen Inc. $AMGN Shares Acquired by Wesbanco Bank Inc.</t>
+          <t>12 Flowers That Bloom All Summer—No Matter The Heat</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MarketBeat</t>
+          <t>AOL.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPUjNOZ25oNFdGMTc2Y29HNlRuXzdyVk1HRVVRb0p2Rnh1Q0R2TTF6TkR4Z01BQTBTeEp5WWVMN2pJRkV1WjM1bDc1NDhhdUpIUzIyVHdBb0F1N3I3clJVRVpmQnpKSTB6bnhaRlpuVVQ4SVk5OUNhSXdNWWl4bEdoS2dQLVhRclBGOEI5NkJNS0tVLWxNVVQwTmNKaVR1N19kV3puWktmQTAxaDBMeV9rV1F3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTFBHLU1RS19JRG9VSnFCbVVNeldsVE1kLS1jMVFsZDZBeHBWMzJEakpRMjNNWjBOYVd1RmxldXdBSjJsV0RqN3B2bXkxT2F2ZUMtdkpZUnZMYzNUNzV2ZGtDSmxLNEhkVFNzZEpYZW80N09RWnZLMy02bXln?oc=5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>09-05-2026 12:05 UTC</t>
+          <t>10-05-2026 12:05 UTC</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Amgen Inc. stock (US0311621009): U.S. manufacturing push and Q1 2026 results in focus</t>
+          <t>Climate change is forcing plants to move, but many have nowhere left to go</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>Earth.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNTjlvSWVSZENTSEk4VzJRdXpQLWNLU3NWcWN0WmY0cGpCSi0zOWIzcmRnM3gyZUQzSmsyQXhteU5Vd3B0SGdFa2Q4RTI5dmFBRnlDVnVuZHRjRDFCRC1EOGQ5Ul91Nll0SVlqcFZBbjdhMVRGX25MNURIaERtWnlaTHhEZGdqU2lvY0hNSko5dTVVNXJJVUFWZVFKVi0wWkRSb1pRdk1BRS1hN3F1blJnOV9sdnVNaVZNaWZRd3pROA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPQXktNjFfWHFjWEF5SFpHSkIyb2xzSXgzbHFVVG11XzZHcHJmaHZFMmtFTFo2MUhWcklXWW9IX3hxaUtXTjdsQUxfRmRBWk1kWnlLbWhLMGMtTGdUaDdmWmRyc2Z5b3J1UWtodm1sTzh3QjIyMDB1NGpIZ09XTnExMU10MUlLdEtIQTVlNnVYVmFkZExsXzRPZDVrM01tUTlnajlv?oc=5</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>09-05-2026 13:49 UTC</t>
+          <t>09-05-2026 17:33 UTC</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sun Pharma chairman calls Organon deal both happy and anxious moment</t>
+          <t>Gardening: Prune, cut and clear – Do you have the right tools for the job?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dailyhunt</t>
+          <t>Marco Eagle</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_AFBVV95cUxONTh4cmQzV016WTZ6RTZpeXV1dFhaMWx0Y29OaDJpNHhoZHkxTzNDY0hKV2s2eFdGUENqdFRxVmFQMmNIUUFSX09USlF0T1J2Zkl4dmJWVEtzZ0N5Z3FBdklSRnpjOENvQjFxc2d2N01obUFjWEN2M05hcXgzNG1EZ2hEZFM3dVdYZk9Zc0M0bkRSRHN5aW4yV0puRHpwV0swak12X2xCbHNRMzBWdURNTS1rcTNYUGhhOW1aMjFVYmdPQlVPNlVPMXFaZTJ2ZW5lU0RnU1gzTjJzYmk1dFFTZnJweWdPbWhVRTJoQ2NLWGtWTHhXLVdHdDZDbmI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPQ2EtdVBHdVlQRUUwVV9hUk5HR2tMbzFQakxsWlVhVml4RDczZTJESDNvTDRRVG9ydVhrbHFULXFmYWhzU0VqaDhaNHdDYzhZZFphZ0d6Q19MYk5IQUVBZ3pBUm40VWhmYnZQRmRFSnVhSnFsVEJUUl84cTBRVnRlWDhvZ0UyN1o3Q2w0VS1SYURqMDRfSW84OHU5Qng0dWo5akNPWHJHZm1aeDlwUE9heUwzS2dZbDFnYVh6a0V0NC1aNW8xYWdZT1RB?oc=5</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>09-05-2026 14:18 UTC</t>
+          <t>09-05-2026 23:49 UTC</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sun Pharmaceutical Industries $12B Organon Deal Marks Innovation Shift</t>
+          <t>Gardening Pros Explain Why Your Begonias Aren’t Blooming—And the Secret to More Flowers</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Business Viewpoint Magazine</t>
+          <t>AOL.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTFBZdDRfUUNvd0JuLVd0ek80U3N1eG11ZGtEbS1BenBjWU5LMmtXczdCM2V1NmoxZGRpQTNnUXBXa1o1VjQwTlBnSkhjYmthejRaNjBFWnJhZ0I5TzRkaE8tTTZIVE5HRjFTZ0hHV09ZMnRNYnhtc2N5S293?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxPVThPbGx3eTVtZ2t4RFVrak1sSkZyN3hMVGFTM1Y1cUZBUmNHcDN3ZVFKSC00dEoxNWg2cHNYVmk0NWJDUGNMVTVGNkdhN2l0aDAxNGZBTXFXZlNKWEotVmZPdmV1QmljY3MwSFRjN0ZlTGwwMXdxbWE0ZU9wRlNZa2RXaUNPNms?oc=5</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>10-05-2026 06:07 UTC</t>
+          <t>10-05-2026 12:08 UTC</t>
         </is>
       </c>
     </row>
@@ -1030,22 +1030,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Gardening: Prune, cut and clear – Do you have the right tools for the job?</t>
+          <t>Monty Don's tomato-growing tips for May will give you trusses of fruit this summer</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Marco Eagle</t>
+          <t>The Mirror</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPQ2EtdVBHdVlQRUUwVV9hUk5HR2tMbzFQakxsWlVhVml4RDczZTJESDNvTDRRVG9ydVhrbHFULXFmYWhzU0VqaDhaNHdDYzhZZFphZ0d6Q19MYk5IQUVBZ3pBUm40VWhmYnZQRmRFSnVhSnFsVEJUUl84cTBRVnRlWDhvZ0UyN1o3Q2w0VS1SYURqMDRfSW84OHU5Qng0dWo5akNPWHJHZm1aeDlwUE9heUwzS2dZbDFnYVh6a0V0NC1aNW8xYWdZT1RB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNdi0wdVBmUUhlS1VwRURjVU9ILWVCazhObXFJYTRVUkVIS0pZNlFKblYyNGNYMjgwWlphTW85N2pRTDRJQ0dWcHBWVmRxS2FKcHVpNzdpMFZCMm4wRVF6NXlIelZtLW9oQVBDQ3Q3bnFDRjVJbGFvSk5sVGpCamZPbU5oektRSVZERFhaatIBkgFBVV95cUxNajh3ZHNPOHBUSTcyWTFSc1NTNnF3cUM0aUl3ZkpHWnF1eWp3SUtpQ1hYSG5vVlV6MlhTTlJTY1R1NlVjanF3cTlobGhOWldtd0ZQU05FTWRmSnJCdGNqSGt0QkFVNlhJOGNtWkpibVlWU2RMRGFmV1c2NDNuQUthbElXMWYxWllzd0VYeW1EYU9GZw?oc=5</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>09-05-2026 23:49 UTC</t>
+          <t>10-05-2026 07:03 UTC</t>
         </is>
       </c>
     </row>
@@ -1057,22 +1057,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>15 of the Best Water Garden Plants to Grow</t>
+          <t>Does Shilajit Increase Penis Growth? A Straight Look at the Claims</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AOL.com</t>
+          <t>Portal CNJ</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE5qZkw3TWxIVThkbHFMUUtySEJUdTc3UjFTclBXWWRDeW52M1gzbkozMlVFdjJLRHY4NnNzbkRSUUdkV0VJRVd2RmlXTF9VcGpaTkJGMmIteUJ6VGFaOGhtN25TdHN3TVlpVGhmbnROTXl3LV9CNkF6clVfNVI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAJBVV95cUxOYVVNVUk1OVlqN3NoaVhjd2VkcTduXzR3S1BZZXJLTkNaaUZjWGIyZndDdWVoVGJZVWI1N1dxNDNpMFc3MGtlb09qMGR1MURoNFpJTm02RldUT1kyWHdqOFN3N3daYXBrOU9CaDVjZWtHNUJ1T3VURGZXQnZFMGRnb1FjeGljdWh6cEZtUEJobjdoREtOSGtZVzFjQVBrRDd6TVNhSmlpaENEX1c5bGRJYVFPaEJOczFBZmRKcVZ4MDdpVWpBN1ZMUjRUVWQ0ZjhmWlJQYkpBSVFUZnZzREVHNXk3NkhScVNvbzlwTlVwTUVtRXN6Y0JyRmNBUHcyeUJJNmtpSTdCQ255X213?oc=5</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>10-05-2026 03:24 UTC</t>
+          <t>10-05-2026 01:59 UTC</t>
         </is>
       </c>
     </row>
@@ -1084,22 +1084,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Honda suspends EV plant construction indefinitely</t>
+          <t>‘Pest detectives’ spot problem plant</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>qz.com</t>
+          <t>Otago Daily Times</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5OZTNITTNIdFZ5ZlJwWGljWFdEUDVWY3d4TEc4clNnTTktc0FqdWUxUmstUFVpaUNUR3ktUW1FUWd3akpGcnpZTTcxOWtDSlVMajhNRjZ1b0dmQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNR3dORl94Mk84RGdjdEhIc3lHWG1haVRJU0h0bTNjenlTZWdNZW50UEJVX0FQZWRFVmx4Vms2M0puREF4eDlITTYtbnVQZE1wTmZEMDIwT1BFYy1QTjNfd1dHblFJTzV1YU9vZ2h2Z3hGUUpabVlsVkg5SEpWY25HdmtNOWIweDZiMTN2UTBUWEJmV3h2dmd0YTRR?oc=5</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>09-05-2026 09:27 UTC</t>
+          <t>09-05-2026 16:30 UTC</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>TSMC, Sony to form joint venture for next-generation image sensors</t>
+          <t>Purple leaves of Persian shield will steal the show in your garden</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>NewsBytes</t>
+          <t>AOL.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOU0RSTWQ1eVRnakYwdTZGSnRyeWEyVFg0aEdWaGQ4dTRWYk00b2s0eGNlWkJwV3NBbHVmd3EtVDRUanBlTVFtdWRMb1BmTXRNTzAtd0hsdlNNRUotbUxWbHMtZXhaeWU0X2F4MVE1S1NOQl9RQjJIOG1TVGJLczRLZXRyeW1Pd0cxazRTZ3V2dElfM1U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxNVlhETHVEWW5hOUVxc0tKVFVQNzFUN0Z6NF80dmZoYXloQVJ2T2ZwdzZQMWlaM1l3SElpdngxaG9OVy1QU1g1WUFxUUt6LW9GVVNMUmtKT0ZIbHc4RS1DWEZ3SV9fU0ZKVXJWeUFrQTlMUmZxWnE4dnFocUs4ZFpneU1JNzg?oc=5</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>09-05-2026 12:25 UTC</t>
+          <t>10-05-2026 09:13 UTC</t>
         </is>
       </c>
     </row>
@@ -1138,22 +1138,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Monty Don's tomato-growing tips for May will give you trusses of fruit this summer</t>
+          <t>25 Easy Evergreen Shrubs For Foundation Planting That Look Good Year-Round</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>The Mirror</t>
+          <t>AOL.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNdi0wdVBmUUhlS1VwRURjVU9ILWVCazhObXFJYTRVUkVIS0pZNlFKblYyNGNYMjgwWlphTW85N2pRTDRJQ0dWcHBWVmRxS2FKcHVpNzdpMFZCMm4wRVF6NXlIelZtLW9oQVBDQ3Q3bnFDRjVJbGFvSk5sVGpCamZPbU5oektRSVZERFhaatIBkgFBVV95cUxNajh3ZHNPOHBUSTcyWTFSc1NTNnF3cUM0aUl3ZkpHWnF1eWp3SUtpQ1hYSG5vVlV6MlhTTlJTY1R1NlVjanF3cTlobGhOWldtd0ZQU05FTWRmSnJCdGNqSGt0QkFVNlhJOGNtWkpibVlWU2RMRGFmV1c2NDNuQUthbElXMWYxWllzd0VYeW1EYU9GZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE1ZUHdzVk5RX3lOX2R2bXU1em1SLXBNUzBPOUdJR3JPNV9OWTY0bWtoQmhma2lwTGtRNEJzaFptM3RVWnhkaUxlLUlSYlJMYWcyQ0dabkJzbXBPUVEwSXVWZzl6TVNtNWpjbG9jM2xyMDdEUUc5R3puel9R?oc=5</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>10-05-2026 07:03 UTC</t>
+          <t>10-05-2026 12:40 UTC</t>
         </is>
       </c>
     </row>
@@ -1165,22 +1165,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>These sunflowers bloom nonstop all summer: George’s Plant Pick of the Week</t>
+          <t>Need help choosing plants for your garden? These award programs can help</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>PennLive.com</t>
+          <t>AOL.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxONFg2Z1c4SmJCcW1GR3o5NFBHMVhiMEs1b1NwUUE4RUswMUJmQTUzTWh4ZFNwQ0Z6VWNZSmdIS3l6US1qT1BsSlRZZWZmVXFuU0hvMER6UVVIRTBOd0RrU0JCcnRHQ2VyTFpTelJxeWRFOHc0Q0ZlZEtzZ0xIZ0I2QTdIWnhrRXNfYldPZ1padVdYSmVISHhDOVROLXhDcHBnNkd0M1QySjdiejRYa1dOQ0dQNy1jTk05dmZ5QtIB0AFBVV95cUxPRnJybVlSMk5FcU85TUhmdXM1V0x1bTczeXpOWVpWOWRoZVdRSGxkRGlXOVJlVzk0UWI5RkdkVGhoWUZOQk9aNDJob0NNd0dTejQ3dS1tNHpWaHNyWWFpVjJSMEw1RDl1RFVsamcyNGs3ODFaX1lUMnB2dEFKVEdSaWhPS1ZLTDVNSnh3Y1JLbW5GOExKM0Z0YThkNmZwUE43NUY2anR4VHNkUDBCZHRNR3RCSGhaZFJna2c0b2ZaZV9LZmVJdWRyRHB4WHlnTTFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxQNXU1YW9IZmtESElWM0llUFBDbkRkd2diemhTZDJmM2Z0QXRfVWU5MUg1V2hzMVFmUm05WEV3cHNmZk0ta1lha0pCajZEdHNTenVfbUs4S3ZNbXNKYkc2QTJkQkNqZFgyb25meWYwOFNLZnBCOUplamdobHBEZERXV3o3NA?oc=5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>09-05-2026 10:01 UTC</t>
+          <t>10-05-2026 08:36 UTC</t>
         </is>
       </c>
     </row>
@@ -1192,22 +1192,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>How to Spot Problem Plants (and Avoid Wrecking Your Landscape) at the Garden Center</t>
+          <t>People who always pack their own snacks for road trips, flights, and long meetings often aren't being controlling, many grew up understanding that being hungry in front of other people was its own quiet form of vulnerability</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>bobvila.com</t>
+          <t>VegOut</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE9ZX1p1WGk3Ymc0YnI0Y1pma21fZXJsallNR2hZbnUwWWVfUjdFWlRRSGg0OFlzalBVenJUTjBDUFNpcWgtNHhxY0JKVXAwUjBTRm0ydFZiTU9vazc1RnNv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAJBVV95cUxOUFprQXBfbXpWSk1iM3Y4VVVkd3V2MkhGMFd1TEVVUWl3SWJHcUJMWE1hMGdHb19NOXdycjFjaUVhUUlMeGR1OTZzYkowNy01aERRWDNaZmQ1MjRSZEpaYVZVcWpYVGtzdjNjejk5UjBjUVUwQ0JHXzBzUFBLT1J2ak5HdW9UYUR4QUw4dnMwLXhnTmJ1S0l1c2R3QVJLR3ZlcVVFTEZVNVhkUWIyVXgwLVVDRXZBbXh2eFlQYmZ1bUI2bF9aY1lQM3QtVGt3Z09oendLY1h4MkRKMUF4b1k1Z2xuelcxS3lFNGY2bHAya0JpRzlFaDE3MHhlTWdhMkZjYjdObnlNc3BIa25TQ1JQTFVkOEk2VXBzb3hKdnBKbW1UZWg4dGtyVHI4cGVRdFpWaUdvckFyaVNPd2V2MC1yNWtCQm1BckVqaGE1ZA?oc=5</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>09-05-2026 14:00 UTC</t>
+          <t>10-05-2026 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -1219,22 +1219,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>‘Pest detectives’ spot problem plant</t>
+          <t>Is This Edible Flower the Future of Protein? Scientists Think So</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Otago Daily Times</t>
+          <t>AOL.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNR3dORl94Mk84RGdjdEhIc3lHWG1haVRJU0h0bTNjenlTZWdNZW50UEJVX0FQZWRFVmx4Vms2M0puREF4eDlITTYtbnVQZE1wTmZEMDIwT1BFYy1QTjNfd1dHblFJTzV1YU9vZ2h2Z3hGUUpabVlsVkg5SEpWY25HdmtNOWIweDZiMTN2UTBUWEJmV3h2dmd0YTRR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxOV1VYVDJnM1Fhc3Y5MmdJc3NjZmRJWHhTNDhpOXpJR1MwREZJTm5wQTNDNzN1WGM1bVZza3piMjV2Q0tqVFJ3WGRQaU8yWDhjZlBjNTlUaGxfY000RGUzU3hSWThaR1FGVzBaRl9JNlVLcUFpbkJlakQzcnRHNV9XUnBuaUV5VVJLU3pR?oc=5</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>09-05-2026 16:30 UTC</t>
+          <t>09-05-2026 23:16 UTC</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Purple leaves of Persian shield will steal the show in your garden</t>
+          <t>15 of the Best Water Garden Plants to Grow</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1hMlRVNzNEbk0zQy1BeFRzUW1ZdW4xRkd6TWQxWWNyaS1iYkNlMWVGSklReFZpU3NIRzZlZWg0MEdYTnAwdzFKN2Rqbkdfc09pMUh6bXd1WjYyM0p0dWhXVzlfcXViT01Tc2xKT0RHZlZHempUR05GM2J2b2tXV28?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE5qZkw3TWxIVThkbHFMUUtySEJUdTc3UjFTclBXWWRDeW52M1gzbkozMlVFdjJLRHY4NnNzbkRSUUdkV0VJRVd2RmlXTF9VcGpaTkJGMmIteUJ6VGFaOGhtN25TdHN3TVlpVGhmbnROTXl3LV9CNkF6clVfNVI?oc=5</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>10-05-2026 03:34 UTC</t>
+          <t>10-05-2026 03:24 UTC</t>
         </is>
       </c>
     </row>
@@ -1295,54 +1295,54 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Don't Let One Cold Night Wipe Out Your Entire Garden: How to Protect Your Plants from Late Spring Frosts</t>
+          <t>Pfizer Ltd. is Rated Sell</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AOL.com</t>
+          <t>Markets Mojo</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTFAwbllLejgtMzVEUXB3bng0RU00T3puSEc2bGRBRDFzekthRThFVjZDVHJGOVZyVlhTZ1ZvZXFYUGpoNk96ZVZnVzJzY21PZ0xfVkNqS21IcTdEVGFHNTAzNjJoOXZHWEp6ZlhJTmdfdHEzS1JJTDFV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxPNjZmUEJDWWM2RnE1Y1hRcklDcGhva3YwdkFTcVVzUXUwbTVKSldISWZHRDdWSlJuc2duTFVNUnIxTXphU2J3X2k5TWozSWwyZ3dVenZXeVJ5MjlyTFZkcmpLVFVRdnViQXhkekxWbGc0VE5wcDJCUmJIM2h5NXlfODRDTkFBaktHdW13d3gyOA?oc=5</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>09-05-2026 17:56 UTC</t>
+          <t>10-05-2026 11:03 UTC</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>15 Dwarf Hydrangeas Perfect For Small Yards And Tight Garden Spaces</t>
+          <t>Pfizer’s Lyme disease vaccine shows 70% efficacy; Texas man sentenced to 12.5 years in $61.5M Medicare telemarketing fraud scheme; Novo Nordisk launches Wegovy subscription model – Morning Medical Update</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AOL.com</t>
+          <t>Medical Economics</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE03eW94UFRKUmg4OTdlWE9HVEFsRFplMG5OS1ktcGRpamp1ellOOTFYbGF2LWJQUlE4S3dSZU1xdUtIdXFBZDlVcXM5SmxISVBVcHByYzVRbDFrQW14dnBVQ1hEbzNIUHA2R05KTzhkQ2NkS2dQSHpj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gJBVV95cUxPVnU1X0hLdnNoem8xSWwtUm9LQ28wXzM4aUFsUUN2U1ZsM0Fwb2dIWmNPdGphRVd3cm9RUzBtT0gzYVlyYUV5aHBnOEt4ck9CVnV0NEs5NTJkV2d1WnZSaGs3bUJYUHlzVVBMV2xwRDhnakZiWVlkNG5kTFBmTm0zNHJGNDlhdHhNcVNEQUtaX0ppdlZ1SFlXekZ0Z0Rtemh4TktrWGdPN1VIYnhGZmZnWURLWlhQTjNhUXN0RkV5eE01ZnhhVHd0RXlFNm5PNDBQTjQyOWpHMWRpTUJfV0Y5NjBqcmJvZ0FGWGtZQjdtZW5LcFI4S3U5ZHV6Zl9uc0NZQkpEcDQ1TjRiTnk3MjBGYS1RdjhNaVhvQjVveW5FRFpWQkVicHE1MVlLbURUZTFObTZtS19qN3JrdDF5c0RHb19WZzNTQW5OcWU2MEdGR3pqREVjQWc?oc=5</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>10-05-2026 00:31 UTC</t>
+          <t>10-05-2026 10:38 UTC</t>
         </is>
       </c>
     </row>
@@ -1381,22 +1381,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Bust Fake News With Bangalore Mirror: Hantavirus infection is not a confirmed side effect of Pfizer’s CO</t>
+          <t>Pfizer (PFE) Surpasses Q1 Earnings Expectations, Reaffirms 2026 Sales Guidance</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bangalore Mirror</t>
+          <t>GuruFocus</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAJBVV95cUxOX3hraFZBVmo5ZDFWUzhObVdYQWlPRGQ3NnBrampUQUpWdXBXN2I0WHZHY01WUHMxV3g5dkliaTlyN0Vsd3J0WXpBeXY0Nm5yZ05MQVk5WUdFMXhKYVFlSVZKcVdlUjd4N0VpeUxpWUZIRXM5czByVHNPQUgzMWczeWQzWW9USGVyLWQtaW5fbTkzd3NrYUJBTjRyaGtTblAxQnlreXFNOUdlb1ZmbnNYMWJOOWVXTlNFYUk3dk9QWERVbkQ5ZW1aTElna2g2X3JOdUpxRUM0bWdPb0d4am9rLWx2LVFqVjRVaTBSdHB0UGhnWFpqWWdMckJzR3JXSEJTeVJZVFVBVmJ6QVl6clRTOGR5dUVSdTNSdEFSS09BdmlCQXc00gGqAkFVX3lxTFB3MmxMamJIWF9fUG5IbmxRamtnUUREa2J4LXVFWUVZbjV0RGo0NnBjWmZxWTMtMW1tMDlUNDN3aEE2R2w5Z2RiNUN4MWlTZWdqbng1dFBENlY5THJubnctMjNSQ2x3d3VuNlNOOERnbHRSTktMMmdpREp5VU5yY0NNVGM5cDF5OGZFUnZIVHlaTW5vTWp1aGVmM2p0VllFRE9PZ0R3bS00WGltdEtCNmpENTdjMWNKTUhMZTAwOElLc0Nnb2dQM1VqMzV3eWUxTm51blFqNlV0WXVlQ2JPWUR5TGNYOE9UeWp3OUlrbXBpY25pZkdxM0VQSGR4emU1NWFPRDRQa1U4Yi1jQ3dDWF9NSDlRX2tfZUo2RF9FaHU3cW1yeXdoem5QalE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPdG1kSm1tR3JiNVYyVEJZVDJYaXlJUlY0OXFaSUFjM2N0QUpxaldaVW9iSGx0b21USmRualRuMGhhTFg4YVE1bGh6bVU4MzY2ZEJhQjkzaDVqcFhDaklvVE8yc1llVGhqZG5WYzVyYm92ZUJYdDJCVTU3dkhSUDNDekVBTk02MGltNldIRU5xaVpmYmNGUUlKUTd4WU1MUlhzMWhIeExGeXBwbHpmRkg1cTZaVFc?oc=5</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>10-05-2026 00:30 UTC</t>
+          <t>10-05-2026 14:26 UTC</t>
         </is>
       </c>
     </row>
@@ -1408,22 +1408,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Pfizer (PFE) Beats EPS Estimates, Reaffirms Full-Year Outlook</t>
+          <t>Does Pfizer Vaccine Cause Erectile Dysfunction?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>GuruFocus</t>
+          <t>Portal CNJ</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNRlRlcFYybUFZNVlVS0FxWUVNYjNZNEEwRjhyUDQ5WnB3Tk5NZlM1Rk4wYVRHVm0yVkp4dGhHRkxiZHhkVVU1bFo0UlhYcG9pY0tqY21VaVJRZmQzMC0wMkdXRjNJUVQ4b1JzT0NJbWc4VjVjcEZqcDJQcWlGSU9vbHF4eW9pOFBNNEZPakZuTGJacDJjX0ExTXdBUUpNbXhqdDVzTm1jZ0J1dWU5?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAJBVV95cUxQRHU2VmdHcVpTd2tQRi1TZFgtT1pSSWNzbmpoa0ZvOEVWRlhzcExiRlNUMThFZFpPQktTRDJ6UmNldDlwS21nQURkOGNHVXNfbk1ia1NVTC00czN2ejZEZTdBT09jY0hUNXJwV2NJT2t3ZjllbFNyOHlKQUxhSnNKVzBSQUNWUUVCT1R4VDVuSTFvUVZpS0ZscXBZV0xId2poTUh4R0xrbk9RMktKNFVyTENRSjhFbVNsTDdkQW5aZzRRLUdtZU00NjljR2tOc1R6bUVjM19yU3MybTBjWVdpWHU5cENpYnBCemREMTNnSmJ2RDQ4SzFlSktDOGhJRGRMeWFSU2E4aENfTUNo?oc=5</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>10-05-2026 01:02 UTC</t>
+          <t>10-05-2026 09:35 UTC</t>
         </is>
       </c>
     </row>
@@ -1435,22 +1435,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Pfizer vs Moderna: Only One Pharma Giant Is a Winner In The Post-Covid Era</t>
+          <t>Bust Fake News With Bangalore Mirror: Hantavirus infection is not a confirmed side effect of Pfizer’s CO</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AOL.com</t>
+          <t>Bangalore Mirror</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTFBUUlNVMmVOeE82bDdjNDdadDBSb1ZIV1dVUVBLaEpMTHRFclVVU0EwYXlBNG40STNNSDZNcEVlN0xLOXcxVG41WVBMczd0c1FPX3RvdzY4QlJ3a1VvZjlPUDVHYVplUlRKbjhTVGtfdFIzcXExRzFKakRR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAJBVV95cUxOX3hraFZBVmo5ZDFWUzhObVdYQWlPRGQ3NnBrampUQUpWdXBXN2I0WHZHY01WUHMxV3g5dkliaTlyN0Vsd3J0WXpBeXY0Nm5yZ05MQVk5WUdFMXhKYVFlSVZKcVdlUjd4N0VpeUxpWUZIRXM5czByVHNPQUgzMWczeWQzWW9USGVyLWQtaW5fbTkzd3NrYUJBTjRyaGtTblAxQnlreXFNOUdlb1ZmbnNYMWJOOWVXTlNFYUk3dk9QWERVbkQ5ZW1aTElna2g2X3JOdUpxRUM0bWdPb0d4am9rLWx2LVFqVjRVaTBSdHB0UGhnWFpqWWdMckJzR3JXSEJTeVJZVFVBVmJ6QVl6clRTOGR5dUVSdTNSdEFSS09BdmlCQXc00gGqAkFVX3lxTFB3MmxMamJIWF9fUG5IbmxRamtnUUREa2J4LXVFWUVZbjV0RGo0NnBjWmZxWTMtMW1tMDlUNDN3aEE2R2w5Z2RiNUN4MWlTZWdqbng1dFBENlY5THJubnctMjNSQ2x3d3VuNlNOOERnbHRSTktMMmdpREp5VU5yY0NNVGM5cDF5OGZFUnZIVHlaTW5vTWp1aGVmM2p0VllFRE9PZ0R3bS00WGltdEtCNmpENTdjMWNKTUhMZTAwOElLc0Nnb2dQM1VqMzV3eWUxTm51blFqNlV0WXVlQ2JPWUR5TGNYOE9UeWp3OUlrbXBpY25pZkdxM0VQSGR4emU1NWFPRDRQa1U4Yi1jQ3dDWF9NSDlRX2tfZUo2RF9FaHU3cW1yeXdoem5QalE?oc=5</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>10-05-2026 01:39 UTC</t>
+          <t>10-05-2026 00:30 UTC</t>
         </is>
       </c>
     </row>
@@ -1462,22 +1462,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Fact Check: Hantavirus infection is not a confirmed side effect of Pfizer’s COVID-19 vaccine</t>
+          <t>Pfizer vs Moderna: Only One Pharma Giant Is a Winner In The Post-Covid Era</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>The Express Tribune</t>
+          <t>AOL.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQQ3VRbkk3T1BTMjdNbGhlMXBZNEhweDBZcVE1OUVIal82dzNoWG9tMG04UTFBT3hfUnFydklRcEhSenMxTDh1aGc3MWtWYV9qYVg1Tmo3YjZPNFYtUzlEN3ZCZk14WDBpSVFjWXI3b25obTVPVzM3S0cwR0g2aDBybjJLbkpJTlliS2c4QmJBemhycXozMlJfZHB3Rm1uaXQyb2FGbFFxdnE3UktJQmZKZmFuVDk0SjFTZTVGMW5XMzh4RlhpeXfSAc4BQVVfeXFMTVhQdEtYQzV5ZldvNFdWWkxGdjFnaEJFd0NGUlJwUE5rbzlscFA4WGxuUnN0bTJsMU1sVzlSbWNiempIalFub1ljSGNQall0NHhiRzI3bzYtQUFwZWVraE00dkpfRmNvZnlpNms4dWNUSzFaR0lWUHFSTmp6SnFOb1VUOVlJal9hRUNOZ0hJa2d0MFBCbkozc3RrMlk5Q3RQN01wdUlqTzJmbHkzSkk0YkVuZUhfYmZHdTBjQTQ4R2R4YjFxTEpJTGNLWEdZQWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTFBUUlNVMmVOeE82bDdjNDdadDBSb1ZIV1dVUVBLaEpMTHRFclVVU0EwYXlBNG40STNNSDZNcEVlN0xLOXcxVG41WVBMczd0c1FPX3RvdzY4QlJ3a1VvZjlPUDVHYVplUlRKbjhTVGtfdFIzcXExRzFKakRR?oc=5</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>09-05-2026 18:39 UTC</t>
+          <t>10-05-2026 01:39 UTC</t>
         </is>
       </c>
     </row>
@@ -1489,22 +1489,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Could Buying This Beaten-Down Healthcare Stock Make You Rich If It Recovers?</t>
+          <t>Pfizer (PFE) Beats EPS Estimates, Reaffirms Full-Year Outlook</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>GuruFocus</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNdW5RdnRxc2w3dUthb2t1b09OUThsWmg4ZGtleS05ZGxsdEw0bXBHYWVRU2pETnRpR1lqZllWRGhtcGV2el9zZVFQbHdteDhNYzhaTnpTdU1tcTRWUDBTVTB2N2h0WjB0c3VReF9TSUU2UkR4Q0ZxRFdjdnpvLVlvYXNOYzRMRFZyTDk0VENCWk9zRk9ZSmdtcFRyLWN6NEJCOW9JZGNoTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNRlRlcFYybUFZNVlVS0FxWUVNYjNZNEEwRjhyUDQ5WnB3Tk5NZlM1Rk4wYVRHVm0yVkp4dGhHRkxiZHhkVVU1bFo0UlhYcG9pY0tqY21VaVJRZmQzMC0wMkdXRjNJUVQ4b1JzT0NJbWc4VjVjcEZqcDJQcWlGSU9vbHF4eW9pOFBNNEZPakZuTGJacDJjX0ExTXdBUUpNbXhqdDVzTm1jZ0J1dWU5?oc=5</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>09-05-2026 16:35 UTC</t>
+          <t>10-05-2026 01:02 UTC</t>
         </is>
       </c>
     </row>
@@ -1516,22 +1516,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>$PFE Stock Analysis #pfe #pfizer (TxKafd2ezp)</t>
+          <t>The empresa farmacéutica que creó el viagra and what it means for modern wellness choices</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Fathom Journal</t>
+          <t>Portal CNJ</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE9CY21NZFQxXzNuc2lKNHFZSnZFWEZja3hXUUtzSUZhRlN5YnpqVUQ4N08xRVhUci1KWjhZT19oOGFSNHVKYm1xbjBwdnBiWWJnSFJuY0Zhb3VNUzJ2azBkZi1oOU1WTnlwVW5OZFAwVkQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAJBVV95cUxQUlJuUnpienRyb1R5NFA5MnpDUkhNWTZ4V1ZNdTF3SVdNQUd5dHBOSEVTQjY5eWNBeUktVW5XZll6OFRocVJEOTFEWHpkc3RPb0IzNk10OFlPeHpfSHJFbVlhd2otbFpmY21tS0otMDBoUzhyTlRRdTg4NXFvU2tGeWxfak9hdVNRclFzREpCdm8zNzIyRkNHWmxsVVlNV3BaeUJONmwxWnl0R2pJN0RjaVcweWt0eXFqM0FmcmhFZjVhZW9UVXNrWGlJYmF0OFZBSVc1cXdaczlFMHZabHk3VktGektlNnJYRWlJVmJWdUZfWC1PUWpxRGJjdnY1ZTVGWDZaWFE0azM1c09L?oc=5</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>09-05-2026 20:51 UTC</t>
+          <t>10-05-2026 08:24 UTC</t>
         </is>
       </c>
     </row>
@@ -1543,22 +1543,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Viagra vs generic: what actually matters when choosing between them</t>
+          <t>History Suggests These 3 Stocks Are Due for a Major Rebound</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Portal CNJ</t>
+          <t>AOL.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAJBVV95cUxNdll0Sk1Jd0RuWVJMaW1CaHJpU1NLVVU5Vk5odktwSWY1Zk1YMGZOQVk0YkV0NDVfRzRPOVp6QlNRSHVqRVVyREdtbmI4bkVWN29VcmxhSHVNbVVmTWtwaVNQUlh5SkNLV1dPcTdINGdKZjJNQV9RYmRxYjZReDZqa19PT1ZlX2FMUVhTeUh4bDNIY2NuTnRJUTktUnZXa2VpSG10cmtpSGZKTHNOT21sMGhHSDZrR043aHJ0TkJvaDNaNzZYbThHemwwODVMT0tBLW52cTZCdEYzS1VlWkFOX2FjVjBIUnpmSHJtd2t2WEozWldnTFJvODdzaHBTdWx1RW9oeW1Xdi12VW1n?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE5PS1ZBRkFzZkIwY2lJTXotUkREcDE2R0V5cnZraW9lT3pNZUtYVVBmVkhwX2hvZ1RpX044NVdtRl9RSm1pRzl1anFlMmJ3bFpuZ2hSODhpY0FfdnNpZ01FRDBpLWZwdDJKd1VWdlE5b1N5cjUycG1UMGp3R0w?oc=5</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>10-05-2026 02:37 UTC</t>
+          <t>10-05-2026 07:24 UTC</t>
         </is>
       </c>
     </row>
@@ -1570,22 +1570,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>History Suggests These 3 Stocks Are Due for a Major Rebound</t>
+          <t>Pfizer Viagra 50mg review</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AOL.com</t>
+          <t>Portal CNJ</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE5PS1ZBRkFzZkIwY2lJTXotUkREcDE2R0V5cnZraW9lT3pNZUtYVVBmVkhwX2hvZ1RpX044NVdtRl9RSm1pRzl1anFlMmJ3bFpuZ2hSODhpY0FfdnNpZ01FRDBpLWZwdDJKd1VWdlE5b1N5cjUycG1UMGp3R0w?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAJBVV95cUxPRVRyTEdvTkdoQWdsS2hHU0tWZjV5VHowbGJjcWNvXzJPYmlSSW0tVW1BM19mb1dkaFN1NkI2NWRrbkJtaTkxRVNxYzcyc05WSk9lS3puRnhwYzM4dDdBNFJzbFYtMDlHd3IxSl9HMFdsTUFpN1ZjdXQ1d29fY0FwN1lwU3dCWnNyTnhtN1RPY21hLU53OHpXNnlHQmVKdzFSbm55WTQxczJQOVppWWo3TDRYRk5jbWpJam50bDVnb3M2WFBscVJRYU1JVEtBbUpDVDQ5SkFVS3I2U3gzUng5QVU5M095b0llNXp1N0l4QS03T0tzMjd4bnhiTkV2Y1hPcmFwSHk0cXZRQjN4?oc=5</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>10-05-2026 07:24 UTC</t>
+          <t>10-05-2026 08:51 UTC</t>
         </is>
       </c>
     </row>
@@ -1624,22 +1624,22 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Biogen Inc. stock (US09062X1037): Q1 earnings beat but guidance cut weighs on sentiment</t>
+          <t>Apellis set to report earnings ahead of Biogen deal closes</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>Investing.com India</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxPMndzbFgteVpacmNvRUNrRkdUX0dkcVBWcGt3cU9pZEFPVEkwTEt0U0lHWnhZVmNsTEFBWmNOWFdOM2FRNHdnSzRZQlpJdmxCdFZ3emt4LWY2Z3o1eGRwUEMwZ1dhVy1EYWR3M1dyMEFtUG1yWE9uMDR3TnM0UjNsNkdGZElTSDFkUTMyNjhTVVpvODBYVm1RN1ZQYmw3RHFtT3NuNzVMeHdyb0V6MHh5aHk3R3hzQXpTaHZQV3ZCTDVSaHNRd2JjNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQNVhaSFZCMFV4bVpZdTA2VEdLM3JlZkQ3anRaWDZPQnE3aUhNTmc5Uy1DM0xxSU55YWZNZzhBTGZvMUZjNmU0YUxOY0FnbEo4MjVDMFVkMFZmS0FKQThRY3c2VGZFeS0yQ2d6aVJ4ZDB2QTNQdzIyY0FvMmI1REhrYjF5M3hycW91N1BDeDU5TTV6b1I3dU11RzFLemJ1S0VsVUhjQkFYd1lIaGtiVUU4?oc=5</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>09-05-2026 10:56 UTC</t>
+          <t>10-05-2026 13:41 UTC</t>
         </is>
       </c>
     </row>
@@ -1651,22 +1651,22 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Stocks in Focus: 3 Stocks Set to Trade Ex-Bonus and Ex-Split Next Week</t>
+          <t>Biogen: FDA Delay on Subcutaneous Lecanemab Seen as Timing Issue; Hold Rating Reiterated with Unchanged $203 Price Target</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Trade Brains</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPZm1sejE2V3VVTmRsSm80R1h1ODRpcW9fUXBGMjFLZjdydzZwZmhrU0djZjUxa2s5R0IwX3VXX0RuUERvM2t5MTRjRkJrWVl3YWpPdXQ3cmNmVldVRkNfTndORkJqNUtmdllPYlBpT25DdEg0eEhRRXJzSE9WZUFtWmdnN3NrVUs4ZHk3UDFLb2VPQ1BHZXNWSg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxNQzNsenViTVBUb05nZXBHNHVsNEc2cDNLOHZocFV6V1pJaEE2aG8wYV9oRTQzYnhpZk4xNEJ4bExUS2x3Y1ZmNklKVFRtbWVSRWFEZHJkMFoyaUZkOVZIcWlRSGZRMVp2RkhlRTNkS040b2RxaTk2Ym1OVUVWTEdUTXpRSkVfeENkQmFfZnBTY2lyZFlzR2RfM0Y1Mk9HQzRIUFpJbHpmMWI5b2FwVllrYzAtc3FNcXpfNTZ4QVNHZWVyQ1lnbjl1MGNVSHM4Q0hBeTZlTGlXS3J1SmFYQ3VKamgyQXd5ZnFxTmVhVkJjcG5QTURLOGxsM1U0NDZZUQ?oc=5</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>09-05-2026 11:30 UTC</t>
+          <t>10-05-2026 13:39 UTC</t>
         </is>
       </c>
     </row>
@@ -1678,22 +1678,22 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>FDA Extends Review of Eisai, Biogen Alzheimer’s Drug</t>
+          <t>Can You Enlarge Penis Size? A Realistic Look at What Works and What Doesn't</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>International Business Times</t>
+          <t>Portal CNJ</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPQi0ybkVGWE9LaG1sbUxiRWdYSXdTam96WS02RHpBdE9zVWhJNGlnYXQ2Zk5kblFRM0hpX0dzMUZRakIyM08wMkRuaEZ6eGlQdzloano4Mko3aWhHZDJSeFJhbWNBeEJZWEI1ZlhfSWV3c2FuSzhyUGdCUGoyWDhsREhORjhKdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAJBVV95cUxOLXFGOXlfeEFKdmtCcVNjZlZudVlKZ2pQd3RoMHBhZTJnMldJVGtjMjBoUkh4MzB4eFM5Mk1HbEV0eGxsTVdJU3JrQTlBRWdYRGpZZkhqWmE3N2ZlNmNia0pQY0NZVHZTdXZwNjhtaVUzX05Jd1Ywc1pxcWxtcE02cm15Ymp2MHJFRm1YbG1RNUhnUlJISjZMNGZ3Yl9xcjdwelBGWmVLT0ltQ2NlTlhPOE1GcU5iOEh0R0JkcFNmNEFSLVV1b2ROSC0xeFpocTI2OVF4ODhZNV91UnFScjdQblNhVXZvT3Q5dkdhU1BqYTVUZ2ZaS0ZKSUFkNUVKSG1iWEZsVGNjS2ZvUFVa?oc=5</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>09-05-2026 14:05 UTC</t>
+          <t>09-05-2026 19:33 UTC</t>
         </is>
       </c>
     </row>
@@ -1705,49 +1705,49 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Natera (NTRA) Gets a Buy from Canaccord Genuity</t>
+          <t>Milestone in the fight against ALS: new treatment makes patients better</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>The Globe and Mail</t>
+          <t>lnginnorthernbc.ca</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNUHdxWHc5ajhuSzlNY0JucWZjenp0VWZueWZVSGpzUFh5QUZHYU1fc3hYN3lGT0ZsTmQ4aFhRdk02eTJ2WmJRZGRWRFBEcEQtLTNqTjRJNEE1WDVPYVl2YXRKc0lwSGRMTEdZT3pENjNsSllLQWlqdzcyLThLVWNtM005LUMxcTFaYWhjOU1KamVuNmozOXdaR2tJd0FVc2ZzYTJTc01BbEV2MnE2OEhHUUdZV2RuTDJ3Zm9oWGdrWVpVXzFrclA4V1FmZW8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOQWZhckp5UngzZWI0aFZ0dkI3NTlncjNYQW5Uajc3WVpBUDNjdXJFc1o0d0kzZloyUjczUExjYzVoZGpwc1h3a0FxdnBnZkFxZjJiVzRQWC1TN25RcFQtQTV5Zlk2S2YtMDZGbldGMjhkbmNLUXhrbE9VSWJEWmRVbF94cjR6SkZ0VTRpdXloUHRLRjdUQm1aNG5rdHdJLURPMzA4N05vZmdVdjRsaFE?oc=5</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>09-05-2026 11:52 UTC</t>
+          <t>09-05-2026 14:45 UTC</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Blau Farmaceutica</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Milestone in the fight against ALS: new treatment makes patients better</t>
+          <t>Blau Farmacêutica S.A. stock (BRBLAUACNOR1): Brazilian pharma firm eyes growth amid sector tailwind</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>lnginnorthernbc.ca</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOQWZhckp5UngzZWI0aFZ0dkI3NTlncjNYQW5Uajc3WVpBUDNjdXJFc1o0d0kzZloyUjczUExjYzVoZGpwc1h3a0FxdnBnZkFxZjJiVzRQWC1TN25RcFQtQTV5Zlk2S2YtMDZGbldGMjhkbmNLUXhrbE9VSWJEWmRVbF94cjR6SkZ0VTRpdXloUHRLRjdUQm1aNG5rdHdJLURPMzA4N05vZmdVdjRsaFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxOc1Z1UEtqMjFKN0wydVJOVEZmRUc1emY1aWZEY2oyekEtMDc3X0dkMTN6M1pjckotajczLWVnamE1LWx4ZHVMX2FGN3pzM3N6ajl4b0hReGtEaGVLWldiRXhqeUdqSWtIVERLZ2gyei1pUi14YlJXVnhONUhQb0NrdzM3U3BENDA4TXZ0cE85MUFYTXpFelBUZDhFUVFRbW83VkJvV1B6MTdpQTFTanZYektFb1ZaZ20yQjRweFZKUDdNYWQ4?oc=5</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>09-05-2026 14:45 UTC</t>
+          <t>10-05-2026 12:01 UTC</t>
         </is>
       </c>
     </row>
@@ -1786,22 +1786,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Number of shareholders of Dr. Reddy's Laboratories Ltd. – NSE:DRREDDY</t>
+          <t>Pharma Companies Invest In US While India Still Depends On China For APIs</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>Deccan Chronicle</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPSUViaWhsakVaXzV4WXRodWVVaXVJbjFIeXJKSC1IRzJmNUEtQi1zUlI2TG9CVVEyVGNiTG9DWTFZM3pweTUzWGVzYjdpdUIzdFZZYU5pYThvdDAzaEtNZHhjbHRwRHhYMVh2UkpNNG83Uml0V1c2ZlY5bGJjUkczRWxKVTN0ZURrc0ZqaWdHZXY0aUlJd2hpOHdxZ05tSGtSN1ZFaERJcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPR2RWLUpSRXVYZU53SWVGb1B1a1FreHBoUi0tbzhDR1JfVFFnVl9Sdy1xNzJHVlJzbHZWVEpNQV9kdnA1N3Z1U2Zyc0FJdXdYTEFTZC1hTjA5TE9iQzg5Wk10dHBSYUQ1V2hocUQwanE2bDUwQm1LS2tjUlNjS3huRzkzSkYxVEJIOS1pMDFDX1hTb0xVcmxrRU94VVAzRWpIazRqVmcybjZlSXJlb3VtYmp2X1FpX24wcUQyRFc4NNIBxAFBVV95cUxQMWp2a093dHlaMUxSNFR3b1l6SUhZejFuVVVMSEl4akZsby0xU2F5Yk1wZFJ4RDdpczAtVS1vOHg1czkwcUt0bmQ5eEZBNVhGc1hDZ0U0OGZSTVAyaWhfdGw3bW1CWmxOZzNKQk1JSTl3c1lMZE1zUVVmT29zeVFyRUd6WVg2MEx4U1JfU21BdlNiTmRNTW5sZEdFRkFpejhTOVlkUmowRTFaWktnY3RsbER4bU1DQ2pmVTU5WEFGTVpHckNj?oc=5</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>09-05-2026 23:15 UTC</t>
+          <t>10-05-2026 12:53 UTC</t>
         </is>
       </c>
     </row>
@@ -1813,22 +1813,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Dr. Reddy's Laboratories Ltd stock (INE089A01023): Margin expansion and steady growth in generics</t>
+          <t>Q4 results 2026: Bharti Airtel to HAL among companies to declare Q4 results next week; full list here</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>Mint</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxOSTJscEpVQ21QcTJKMTZ2eTZEeGlaUDA2aFBNcmVZbG1vbzVXNC1xWnFWbWJwQ2ZCcVc4MUJZd2xOalVXSmZRLXhpM085VVV4SmN3empKQ05ZNXU4RFNoNGpHTW1KRENVWXQ2a3Q0cEltdkhqUzZWZG5WQjV4UHc4Sm5xck9BOWVCeXJHazJsSWg2S0FOZjBBczZvU0lMSHlfN1BlV1VvMVpRM09SVERwNlF0eEp4dmZUT0hycm5Eb3A4RFBw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxPY0RWdXZTZzJaa1lxSVR1TEZscllnSnhYSko1NmhWazNwUGZvSk1wVGt3Qm5qLS0xZ0FMTHdiUmpnN25XTXJCU2hmbXNWRG85WldjLXlDWlBWaVVBSDVsYXZLbmM2azF6TWtKbWtta1pHM0pQWkI0MVFGZVhyTXM3WnZvbERPUVdCS2wzVzBXV3FiUTZzblZnVFNpU1hPRjdTaWl5aER0bFlDbWpoclk2MzhQUlh4T0pNQ18zcHJiRU9jemI4NEdkVGdXM3BQc2ZUV1YxZ0xrc3dNV0RZTmdDYlA1ZnB4Vms2eU5SS0JvQk90UUtmWEcyckVTWnY5d9IBgwJBVV95cUxPcEN1eG5sVlo4VFRON3BPdGw4SDlhdm5ycXFEcmRnVVpVTk1FdllxTjZuaEJLVkdYeXVLbkJNRWtESjdxZWcxYjdvRmgyNEtNN1N2QlFhOW9RSV85R2tFemFGOURhZm9VZC00QVFhcDBHUjFId3FhdXNia2dyQlY0MngzMGYzakVFTVM5V1lRMDZyNjFNVURsYUJpdG9NZW1ZT2N2dFI0RGNWR25Ib0lZREpxODRuell4SzRtZHZ3ZzRpNDdSZEdxUE5KMzhEd2xPLXBsaHNPODNtZlkwS3QzRy1DUmM2MUR0S1Vlb0xmSllsZVBLaG0zZWdHelNuQ3B4YmZN?oc=5</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>09-05-2026 17:26 UTC</t>
+          <t>10-05-2026 10:28 UTC</t>
         </is>
       </c>
     </row>
@@ -1840,22 +1840,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Govt Releases Updated List of Approved COVID-19 Vaccines in India for 2026</t>
+          <t>Number of shareholders of Dr. Reddy's Laboratories Ltd. – NSE:DRREDDY</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Medical Dialogues</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPN3lEb29oTGNzZlhTR1I4dGVGWHJ1VnV3blNscm5oV1NDdi1yR0J3bE5XOWRVeEtfSmRlMDVzcFEwNG5wMEhxT2FEeFlHVmgzVzdBZU5oRGszeGRpT1NTendJSTE3RjgzaDdRdVFvNjFGOTJINThEV05uSTNoZ2pKWUVWRGszLVhEUE9nRzlnZm4xOFdLaUFLRDZzQXFpek5STDdWQ21ncEVUYWFxSXJJLTNVQ1NsM2tacDhxTkx0Z2JXQ05PVzlxajRB0gHPAUFVX3lxTE9qS0diZkRvZmh1aUhuYlV6QTAzQmVyWU5VVWx4cjRGRGYyWTAyY2FQM3ItaERaZ1o0a3lGNzVYRDR1UEd5M3lXT3VzWkZ2V2o4UFk2b0ZJLWYzZS1YT3ZhcTlGUDdGYmJlNFdFZy1TbTBtUGhmZ1BqTjRWSnJJQzVZcTBPRnZDZ2dwdkFpY2FFa2tzbThEbjhFM3pYdVEtUUJkTklzcHZrR0U0MmhnbTlYTkZLYUVHX1NQOG45TW9qWkE0S0VmbFFKUUhOcmJ1Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPSUViaWhsakVaXzV4WXRodWVVaXVJbjFIeXJKSC1IRzJmNUEtQi1zUlI2TG9CVVEyVGNiTG9DWTFZM3pweTUzWGVzYjdpdUIzdFZZYU5pYThvdDAzaEtNZHhjbHRwRHhYMVh2UkpNNG83Uml0V1c2ZlY5bGJjUkczRWxKVTN0ZURrc0ZqaWdHZXY0aUlJd2hpOHdxZ05tSGtSN1ZFaERJcw?oc=5</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>10-05-2026 05:00 UTC</t>
+          <t>09-05-2026 23:15 UTC</t>
         </is>
       </c>
     </row>
@@ -1867,22 +1867,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Dr Reddys Laboratories Ltd Technical Momentum Shifts Signal Bullish Outlook</t>
+          <t>Upcoming Q4 results this week: Tata Motors, Bharti Airtel, PFC, HAL, ITC Hotels, Cipla, DLF, and more</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Markets Mojo</t>
+          <t>Upstox</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxORmRqVGtSb1gySlNPZ0dRRk80YjBnNmt5UVRSLTNDUFBVdlZhS1RPWlgyLThtemlHQzdBQmRsdk0xU215dEwwdlRRY0R4a3FrMzU2SEVBMkl3WjVXMUtrdk5qU1IxZzlDMm9HazB3cjBoMVpEYnV5RmNyLVdGWVRiR2V2cndQUW1GdjdKRm5IbWp1dmZUWldKbFJtcUwtSUFzNlhXUVlpQkFnQURQMFJ2VlRHNVRmQndjcXhXSXZnWUFLVkFUWHJIVTY2S2pzQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxOWW5xQUdPcDh4U0RPdmx4MlRGckxJYW1SWEx3ZHhibW1EVWsxSEEzTW1vdDBrUnVzUTZib2l2WFNnQmVDTXAzVFJVYWtsS0RBYmppSF91dmlTcUdXZ2czdGd3SU9WajlSd1Vab0kxdHEyMWdBdERPVWZmVzJMdWlVNHFaUVRoeThRNHZ0TkhkdHhtTXdkQ2JZRFkyQWthcHJVcDJHTll6dnQ1b3JiVl9rS1N0Q0NLNE1VXzI3aWE3c0c4T3FYQmhjMkRjQ0JEY3QycnJCcFlYS0l1Y1J2VHJZZVNreThBdk1OQVE?oc=5</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>09-05-2026 22:40 UTC</t>
+          <t>10-05-2026 11:17 UTC</t>
         </is>
       </c>
     </row>
@@ -1894,22 +1894,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Sensex, Nifty rally in early trade on West Asia de-escalation hopes, poll trends</t>
+          <t>Dr Reddy's Share News | Dr Reddy Share Latest News | Dr Reddy Share Latest News Today (fw3PeuTrGV)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>DD News</t>
+          <t>Fathom Journal</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPNGxNQkluVVFmM2pMem1xdktZVnRjWFYyTTZiWkMwNWxYejhSaDNHbVJjeUdTenVqOWVSVnplMnQ0a3M2SWVsLWd3MlFSaWpXcnhnRzFhRkppY1JRdUJjNnA5bHhqUG5jT3dLYXRKcmNDTVU1N1lNdTZaalJHbm1KX244ZS1XQjFZdGtHek9pczVjNzBub2dYc256ckZWTjd2Vko3YVNmWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBCdmxtelpBVlpvckJta0FqRkZ2NHQ1THRyQmhpcFhrNjJuM1BMYXBBV29HMUxsT2VGd1JnbHJLY3ZEZUszOHBJS0FrZHU0X3k5UnBiUGFpWU1ITVZtSTdwdWZvamFYUkkyUkEtM3lETUI?oc=5</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>10-05-2026 01:36 UTC</t>
+          <t>10-05-2026 12:24 UTC</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Dr Reddy's Share News | Dr Reddy Share Latest News | Dr Reddy Share Latest News Today (zbSc1piGOH)</t>
+          <t>China Cancer Drugs Cut India Prices, Disrupting Western Pharma</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Fathom Journal</t>
+          <t>Whalesbook</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE02MEtyUUlneDczTm56Zm1tTjNaUl9VY293NGt2LXI4ZG50YzdEd1ZtTXR1RGg2bWhlMkNkR1pDT3hicEp3YzZ1VDFSQm1jQ3VaWU1oaDhDb2hucmdrXzYzWTAwZF81RDhDNWwtTXFYNzZLOU5WUkE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxQMzBud1hCLVNfQ3YxTnRIY295dUNBaWFkWTlvOHdub3RnMjRIU2tFY2pIaWFLdDhqYVNjVHp5WEF3aF90c0F0QmN2Ykk4cUtVOW5nODkwVDRXemEtdEFJV1l6TVMyeUVQMHlxT050ak9vekhERVhZTFdyQnNCbEdCSS11WlBNV1dfVEMxbnNSYWRTWGdxZGVtMU40UFQ5bjJldldRZE1NUTRXWmpBR2dRRlBseHNhSnVudW1rSkRFRlY5RGUxTXEzWnIxOG94QjRzWWVnclBPMXU5TFdK?oc=5</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>09-05-2026 13:34 UTC</t>
+          <t>10-05-2026 03:45 UTC</t>
         </is>
       </c>
     </row>
@@ -1948,22 +1948,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Sensex, Nifty closed in red; investors waiting for RBI decision on rate cut says experts</t>
+          <t>Dr. Reddy's Laboratories Ltd stock (INE089A01023): Margin expansion and steady growth in generics</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Dailyhunt</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwJBVV95cUxNUHUxdXNPaFp1UER2LXRRYWVNUDkyUWRRbUJZZEZsdGFzWExUNkFPRGI3eDZwa0p1R3J0ZTRWYi1FOFJBNmtSQVY4MnBucWhRMVNIZXRkRGtwNkxFQ0QtUnYzaDRzeWhVd19HVERXNkVyNmpzeVNXWmJONDhYVVp3dExPMFNUcEpiSzk1aTRVaF94cHZNUFRINGs2RExoaU5aR1Vyd29Xa1dySWRjbUppN25DN0xQZm5mNUxlSDN0OE1rVmhLc1ByOE5UV2toQ2liQnFIOFd5eFFLLWJ0RjdlbC1yVWdpZVItdjZ2aTczTGFvRnBleWxSeFBTMENDaDJHM2Fz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxOSTJscEpVQ21QcTJKMTZ2eTZEeGlaUDA2aFBNcmVZbG1vbzVXNC1xWnFWbWJwQ2ZCcVc4MUJZd2xOalVXSmZRLXhpM085VVV4SmN3empKQ05ZNXU4RFNoNGpHTW1KRENVWXQ2a3Q0cEltdkhqUzZWZG5WQjV4UHc4Sm5xck9BOWVCeXJHazJsSWg2S0FOZjBBczZvU0lMSHlfN1BlV1VvMVpRM09SVERwNlF0eEp4dmZUT0hycm5Eb3A4RFBw?oc=5</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>10-05-2026 00:35 UTC</t>
+          <t>09-05-2026 17:26 UTC</t>
         </is>
       </c>
     </row>
@@ -1975,22 +1975,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>WAIT! Before You Touch Dr Reddy Stock - Watch This! 😱 // Dr Reddy Share Latest News Today (veXdwvKBQd)</t>
+          <t>Dr Reddys Laboratories Ltd Technical Momentum Shifts Signal Bullish Outlook</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Fathom Journal</t>
+          <t>Markets Mojo</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE1FS3BqakpScEZfbFFWZkY2NnUtNGNtaXRxLTJ0YV9OTWkyVUJjSHo1MlA5WFcySmdfYWhqR0NfUzJxeU1kR3pIX2R3SWRnNUlYdWh1LWxXOHJKaEVaVFRyVVdZckNoS0dabEY1cjRra3BsSTJkcXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxORmRqVGtSb1gySlNPZ0dRRk80YjBnNmt5UVRSLTNDUFBVdlZhS1RPWlgyLThtemlHQzdBQmRsdk0xU215dEwwdlRRY0R4a3FrMzU2SEVBMkl3WjVXMUtrdk5qU1IxZzlDMm9HazB3cjBoMVpEYnV5RmNyLVdGWVRiR2V2cndQUW1GdjdKRm5IbWp1dmZUWldKbFJtcUwtSUFzNlhXUVlpQkFnQURQMFJ2VlRHNVRmQndjcXhXSXZnWUFLVkFUWHJIVTY2S2pzQQ?oc=5</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>09-05-2026 10:47 UTC</t>
+          <t>09-05-2026 22:40 UTC</t>
         </is>
       </c>
     </row>
@@ -2002,22 +2002,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Q4 earnings, crude oil, FII action among 8 factors to steer D-Street this week</t>
+          <t>Sensex, Nifty closed in red; investors waiting for RBI decision on rate cut says experts</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>Dailyhunt</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxOcFJ0RmlBYnl4N0tSeUY0QzZ0QjlfZ3NkeUktQ2NBS0pTakZMNDVONXZPY08wSUJCQlR5ZEpPaEtqR19vTXlTSWdFbWlMNkdEbndPbzhFNTBtNlZQSXNMalFjdmppMHJPbk5nNlhfamZaa0YxZzBhaVUzaFVrTHlPeDdnYjFWRUtQRjY2QjFVMEZlYkN0WGl0NVQyY1RnSTB3T2prVFpNNnJqNEYxSGxsVWNad1RYTndzcWJrbk4zVEtkblRyR05VUHNuNTlQVGNHWnRLTFluS0czQ0RNTzhoMkRaZWnSAeoBQVVfeXFMTXQ1WGtDRTFpdk9qWk16OHdYQl9tUVlfUVk2SE8xOWM0X3VpRU5rS21TYUk1ZWZVSGplN0d5cFFUbHpid0VjNWYza2RzNWZFdFdkV3Z2M3dsN3dSLXpmUFlpVmpJVDNIUzIzN3VJek44SEd6T2RIVEpwSXhqN2NyYWRaYU9IVmNzaUp5QjFEM1Z2Ti0wNy1YeERuSUNSNUZ0VS1ucHB5ZE5QZ19TdDAyM2loN3FENk5aZ0hpaTFIT3puc0JFM1Y2eE5mbVkzMUlNY3JkNnhVTURWeXdBN1c3VkMzaUZxbXdtODV3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwJBVV95cUxNUHUxdXNPaFp1UER2LXRRYWVNUDkyUWRRbUJZZEZsdGFzWExUNkFPRGI3eDZwa0p1R3J0ZTRWYi1FOFJBNmtSQVY4MnBucWhRMVNIZXRkRGtwNkxFQ0QtUnYzaDRzeWhVd19HVERXNkVyNmpzeVNXWmJONDhYVVp3dExPMFNUcEpiSzk1aTRVaF94cHZNUFRINGs2RExoaU5aR1Vyd29Xa1dySWRjbUppN25DN0xQZm5mNUxlSDN0OE1rVmhLc1ByOE5UV2toQ2liQnFIOFd5eFFLLWJ0RjdlbC1yVWdpZVItdjZ2aTczTGFvRnBleWxSeFBTMENDaDJHM2Fz?oc=5</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>10-05-2026 04:06 UTC</t>
+          <t>10-05-2026 00:35 UTC</t>
         </is>
       </c>
     </row>
@@ -2029,22 +2029,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Wockhardt: The Journey of Transformation</t>
+          <t>Q4 Results Next Week: From Dixon, Tata Steel, Bharti Airtel to ITC Hotels - Here are the major companies to declare quarterly earnings</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>The Financial World</t>
+          <t>Dailyhunt</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1PbmZWdUtyVzhIM3lOQ1NUWF96UVdYRVZXZGJrM2ZKZFFUTWRjOXpyeWhpWTVoZTlpaUszbzB6NGhWeHB6X1Fjano3Y0Z5X1c0Q3Eta1NVbGRyZmFRZTdTZHhQYnM4dUZCMHZ6ZEVwY2FZS2FqVVctU0FoR2VMaTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswJBVV95cUxNOXNacDBUSWVRXzNVSUxCZmlOWkk1QkJlb0t1TU02U1Yzb3ZTTk11b3dvM2tpeHByajRwc2E2cE5rQ05EWTl3c1dia1JmTldPSUVLUl83amlyNEVvTTRhYnh6S2FpUHkxcDhaVEJTUjl2UmwzOHZ6TGFRNkEyZXhrY2NaVXlrNVV4MXpPcV9TdXZwaE53dTBrQk5KajM5X20yWDdHWkQ5WFNZQW9kLUgtQzcwbzBmWTVLaHpTMi1LRkFMR3p0V1JhMTVCSDM2YXMyVFdTYkFRcC05MG54YXlubjN4Y2RPMF90TWU1UklCRS1qc3BFWVFRR2phZTFMZEM5Z2JJZ0tGWXk5ZGt5VmVmLUVEdHV4ZUlJNlkwOEp1YlFRRGZiSGRBTFBrZnJpb2Fwd1U0?oc=5</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>10-05-2026 07:19 UTC</t>
+          <t>09-05-2026 22:30 UTC</t>
         </is>
       </c>
     </row>
@@ -2056,22 +2056,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Chinese medicines bring relief to India’s cancer patients</t>
+          <t>Sensex, Nifty slip after mild start on geopolitical tensions</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>DD News</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxPU3ZlU3JwSVB3YmxNTXZ2akNaY19pNzRVZGk0WXloRTZGZ2t3VW52ZFp4TUtMWmR0SGxxaVhTdW01V2hBa0RJT3pMZWw1ZDFyd0RBdm0xNUlBc0FHNHNCaWJvZnJFT05xMGVYdFFmeFRVellZQVJLcE53TGZwOFM4Y09aMjBrTHdta3kwYi01eTRXTlJwYm51aUMzUkZiNDZBcFpXVDdQaTJxSkxtYWI1Ymg0V3RlbzZjc19IX1FUaW1mVVJmalM4V3NGZmpMZ3FkNEdqTW5DMW5JenI3WWlrLUYtMnBQQ1Fs0gHoAUFVX3lxTE9TdmVTcnBJUHdibE1NdnZqQ1pjX2k3NFVkaTRZeWhFNkZna3dVbnZkWnhNS0xaZHRIbHFpWFN1bTVXaEFrRElPekxlbDVkMXJ3REF2bTE1SUFzQUc0c0JpYm9mckVPTnEwZVh0UWZ4VFV6WVlBUktwTndMZnA4UzhjT1oyMGtMd21reTBiLTV5NFdOUnBibnVpQzNSRmI0NkFwWldUN1BpMnFKTG1hYjViaDRXdGVvNmNzX0hfUVRpbWZVUmZqUzhXc0ZmakxncWQ0R2pNbkMxbkl6cjdZaWstRi0ycFBDUWw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOLVNuMTk1NXJKdExweUpSLWd5Y0NpZ1N1SENDSEpWcEVIUHlGZTR1MnE1UTdxQ3BvbFZpOFo5RDIyUFR5R0ZjOTZrbUQ1cU1WOE1lclZkMHdzMnFSSTV6SXg5T3JmQXlFQ25JbHZvTjU2XzNHTDJvdXRGdEwzclM4ZDdtOV9Rd0VCeS1KcDRB?oc=5</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>10-05-2026 03:20 UTC</t>
+          <t>10-05-2026 03:40 UTC</t>
         </is>
       </c>
     </row>
@@ -2083,76 +2083,76 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>From Domestic Growth to Global Dominance: India’s $20.5B investment push strengthens US economic ties</t>
+          <t>Chinese medicines bring relief to India’s cancer patients</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Organiser</t>
+          <t>ETPharma.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxPLWVIQXZFNWFYejNaNHdfdkNSdWRBRWZJUUhMZU9SVnZlelBiWUZoNGJ1NkZoOTR1VHpVcGhsZFoxU1U2NXpfYU9Id0tBZ0lQTVZ2N1NzTjJId2RQZzJ5WkNXX24zUTZJTHdiclVjVXlMbW96MlRnZUI2YUN5ckFodGczQzR6STRJcEpEUGV6ck9JN3gxa3ljMkl1S2N2ZnpfY3BaNlpVRTZ2LTRTMzlIb1hZQVZJT2c3LWdvQk9GWE0yZWNlTmFBaGdSa0NVOUlQaGNPYV85OWg2QjJ6NVdZ0gHkAUFVX3lxTE1waWpPcWkyckpuMHJBeWdQN29lMThWY3hTWlFsczBIOVNrY0xYdm5jN0MwMWJTam5fNldnVm82dWc4V1ZoOXhfcG9mRENPMnQ4WDd4SlBEV2hrX2JKaUlrTFE1b0Q1SkN1dDlwYng2aTFHeEV4cjNQVUxLUExoVXpDdDBMQXBCQjByWEpfRXR3Z0dLbmpXU0NfZTY5YVkzNFd2UkZsZmxQMXRWRHg4eGVsYUxpNVh0aDBjbm15TUExbU9GX3Nra2t0VDdVSHA3d18tbE1RckhKaVNsWmtZN2w1Yml0UA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOWXBQTEIxejVickl5NDBCbVgtcjc3Mmh5a29OU3hIWFhOQWUwbmJvcEltbjMwd0ZKWTN0RS1xNkg5RHR0N2pIWGE0UmZ6UVh2VXpsZjZlaXRFcV85Z3VuWHNSNjB0SkFIUkEzNllpRzk5MVhXU1BWcTFRcWZWbU5iMWtZc0ZNNGFSMUI0YkZEWDNsMV8xc0NlakdlYURYY09XSGd6b3J5TGU1Uk1oYVNMbkJnNUdnTl8yYXVhTVB3QUx0WVlyaG9qMXFrUdIB0AFBVV95cUxNal9kUmxTX0FLMmlNYVJmUFRZLUdRZE9ZbDRjQ0gyT0d4UFB3WWJPTHJfNmFFZTk2a3RMU2t2YllKS1FSQ1BuZURyWFlZUHQ4SWRETGRlVFgyblRVZG5aWU5wdDJGNDZFMVhRU2ZKenh1eVQ2N0o0UldXSE1RTTlVdmt5YURFVGsyOUVMUm5rWkJlSzNnbWZBbjFvSkVjZnRkWVZvSkl6d09CMXJnTzNYZFM1OEZ6SFEzeXEzbW9scUU5c2ZCd3pYQjFKMmtZaGx3?oc=5</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>09-05-2026 14:36 UTC</t>
+          <t>10-05-2026 07:42 UTC</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Intas</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Xbrane and Intas Revise Financing Terms for Opdivo Biosimilar Xdivane</t>
+          <t>Govt Releases Updated List of Approved COVID-19 Vaccines in India for 2026</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>Medical Dialogues</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPZGJqb0dfeG5Db2NCV2JiYXcweFpDWTA4Z3dMYVJPZHlCbDZjNVZXUWFXdHd3Zi0yTlJjczduRUxnaVM2aUFxb0ljbHdCS3BVRmpEYVMzWVZybnJ5RkRfWWJDVVJlM2FYTi1ibHZZcjVsVGcyZTFXOFZJUlRnZzRjSUtaTmR0cGRQRTVMV094QkFxM19ybHlZQmg1aE5ITzNISnllMDFNVWVtd0dUbmNObEU5VlhTb0JHdlo1T3ZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPN3lEb29oTGNzZlhTR1I4dGVGWHJ1VnV3blNscm5oV1NDdi1yR0J3bE5XOWRVeEtfSmRlMDVzcFEwNG5wMEhxT2FEeFlHVmgzVzdBZU5oRGszeGRpT1NTendJSTE3RjgzaDdRdVFvNjFGOTJINThEV05uSTNoZ2pKWUVWRGszLVhEUE9nRzlnZm4xOFdLaUFLRDZzQXFpek5STDdWQ21ncEVUYWFxSXJJLTNVQ1NsM2tacDhxTkx0Z2JXQ05PVzlxajRB0gHPAUFVX3lxTE9qS0diZkRvZmh1aUhuYlV6QTAzQmVyWU5VVWx4cjRGRGYyWTAyY2FQM3ItaERaZ1o0a3lGNzVYRDR1UEd5M3lXT3VzWkZ2V2o4UFk2b0ZJLWYzZS1YT3ZhcTlGUDdGYmJlNFdFZy1TbTBtUGhmZ1BqTjRWSnJJQzVZcTBPRnZDZ2dwdkFpY2FFa2tzbThEbjhFM3pYdVEtUUJkTklzcHZrR0U0MmhnbTlYTkZLYUVHX1NQOG45TW9qWkE0S0VmbFFKUUhOcmJ1Zw?oc=5</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>10-05-2026 03:58 UTC</t>
+          <t>10-05-2026 05:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Intas</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>From a garage venture to an industry bellwether: Biocon under Kiran Shaw</t>
+          <t>Xbrane and Intas Revise Financing Terms for Opdivo Biosimilar Xdivane</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>The Hindu</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNWDlmQVhxLVUzak81SmJXWWFrTjdaVnIxM0NsNU9weUMxVUJYNkpPRWt6S1JoX0lvQ2ZVTWp3Q1N5N3lOejJreU44OWdlRkRUN1hqdnpqMW5DTWxRMEZRSzBVWi1DZVlaMjJSRkpTQzdZUVdVU1JaSlZ1NTRVVUR3TnJEc0Z4dVRqcENKRFZoQWVTNmFyenYwbXhoazNVd0JteHlLZTFXcC1TNGluaGRPclRvX3c0S25OcG5rQ09neUFfeFA3VXJTWS1B0gHKAUFVX3lxTE1YOWZBWHEtVTNqTzVKYldZYWtON1pWcjEzQ2w1T3B5QzFVQlg2Sk9Fa3pLUmhfSW9DZlVNandDU3k3eU56Mmt5Tjg5Z2VGRFQ3WGp2emoxbkNNbFEwRlFLMFVaLUNlWVoyMlJGSlNDN1lRV1VTUlpKVnU1NFVVRHdOckRzRnh1VGpwQ0pEVmhBZVM2YXJ6djBteGhrM1V3Qm14eUtlMVdwLVM0aW5oZE9yVG9fdzRLbk5wbmtDT2d5QV94UDdVclNZLUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPZGJqb0dfeG5Db2NCV2JiYXcweFpDWTA4Z3dMYVJPZHlCbDZjNVZXUWFXdHd3Zi0yTlJjczduRUxnaVM2aUFxb0ljbHdCS3BVRmpEYVMzWVZybnJ5RkRfWWJDVVJlM2FYTi1ibHZZcjVsVGcyZTFXOFZJUlRnZzRjSUtaTmR0cGRQRTVMV094QkFxM19ybHlZQmg1aE5ITzNISnllMDFNVWVtd0dUbmNObEU5VlhTb0JHdlo1T3ZR?oc=5</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>10-05-2026 03:13 UTC</t>
+          <t>10-05-2026 03:58 UTC</t>
         </is>
       </c>
     </row>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Succession and the road ahead at Biocon</t>
+          <t>Fortune India Exclusive: Succession and the road ahead at Biocon</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>10-05-2026 09:08 UTC</t>
+          <t>10-05-2026 09:09 UTC</t>
         </is>
       </c>
     </row>
@@ -2191,22 +2191,22 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Biocon Q4FY26 &amp; FY26 Results: Revenue Up 10% YoY; Key Corporate Actions Approved</t>
+          <t>From a garage venture to an industry bellwether: Biocon under Kiran Shaw</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>The Hindu</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxQUDdSRFlsM3FJM3hrZ29QOWVZc093YVRoVUJoZjlGejRKS2NyN3dXaFJ2cXhUR3RHLUNkcG15WEZ0WkUtM3VpTWNONzdyczcydnR2Smt0Z1JfZFVRbzNpZGxrWlhEcWs1dklzRHg1aVdmdmllREFxYVJJSjlMUE9CU1dPT1BmZHFTQ1VMZ2hJX0w4T2l1ODF0MFdqMUlIaFNHSGRIb2NvU0wyemJhenJnTnVCVUlmQ1k1dmpENUVraWhEYU1ZZVMtdV9Za3BVXzRmWk83a3VSTVQxYjcwdDZGZFM2bjZPWU94cjRRVG93ME9ncTZEZ0R6SHFQV2MyNjFxUVZFa0RZaFA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNWDlmQVhxLVUzak81SmJXWWFrTjdaVnIxM0NsNU9weUMxVUJYNkpPRWt6S1JoX0lvQ2ZVTWp3Q1N5N3lOejJreU44OWdlRkRUN1hqdnpqMW5DTWxRMEZRSzBVWi1DZVlaMjJSRkpTQzdZUVdVU1JaSlZ1NTRVVUR3TnJEc0Z4dVRqcENKRFZoQWVTNmFyenYwbXhoazNVd0JteHlLZTFXcC1TNGluaGRPclRvX3c0S25OcG5rQ09neUFfeFA3VXJTWS1B0gHKAUFVX3lxTE1YOWZBWHEtVTNqTzVKYldZYWtON1pWcjEzQ2w1T3B5QzFVQlg2Sk9Fa3pLUmhfSW9DZlVNandDU3k3eU56Mmt5Tjg5Z2VGRFQ3WGp2emoxbkNNbFEwRlFLMFVaLUNlWVoyMlJGSlNDN1lRV1VTUlpKVnU1NFVVRHdOckRzRnh1VGpwQ0pEVmhBZVM2YXJ6djBteGhrM1V3Qm14eUtlMVdwLVM0aW5oZE9yVG9fdzRLbk5wbmtDT2d5QV94UDdVclNZLUE?oc=5</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>09-05-2026 20:50 UTC</t>
+          <t>10-05-2026 03:13 UTC</t>
         </is>
       </c>
     </row>
@@ -2218,22 +2218,22 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Biocon’s Kiran Mazumdar-Shaw Plans Succession; Claire Mazumdar Tipped As Next Chair</t>
+          <t>Biocon Q4FY26 &amp; FY26 Results: Revenue Up 10% YoY; Key Corporate Actions Approved</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>BW Businessworld</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQaG9PVkZfbEV6RWpLdkhTMUNXcnVZNkNWR2s0dk1ESFJoZVplbDdLQjRQTWZ3VTNJQ2RYWkFMdWE1YUJtVS12cHdBbGxOZS1waU5QMjI1Y3doMzJXc3NMV3dTdjVqLW55amN4a00wVC04Z0Y2VElQeFUtTUtCNVR0SjU1M1ZzZGVCREV5RTdGSUpjTWJsWWhrOHdCdGQ4STRHUklVVlJjNXNWdC12allBVk9kMVFrb2NTZ2JPWjItdDl1OFZUSWR5Wg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxQUDdSRFlsM3FJM3hrZ29QOWVZc093YVRoVUJoZjlGejRKS2NyN3dXaFJ2cXhUR3RHLUNkcG15WEZ0WkUtM3VpTWNONzdyczcydnR2Smt0Z1JfZFVRbzNpZGxrWlhEcWs1dklzRHg1aVdmdmllREFxYVJJSjlMUE9CU1dPT1BmZHFTQ1VMZ2hJX0w4T2l1ODF0MFdqMUlIaFNHSGRIb2NvU0wyemJhenJnTnVCVUlmQ1k1dmpENUVraWhEYU1ZZVMtdV9Za3BVXzRmWk83a3VSTVQxYjcwdDZGZFM2bjZPWU94cjRRVG93ME9ncTZEZ0R6SHFQV2MyNjFxUVZFa0RZaFA?oc=5</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>09-05-2026 15:59 UTC</t>
+          <t>09-05-2026 20:50 UTC</t>
         </is>
       </c>
     </row>
@@ -2245,22 +2245,22 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>The next 10 years will be about high-value innovation, says Kiran Mazumdar-Shaw</t>
+          <t>Biocon’s Kiran Mazumdar-Shaw Plans Succession; Claire Mazumdar Tipped As Next Chair</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Fortune India</t>
+          <t>BW Businessworld</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQWlhtQlhWSjllNWJpVjRzQjR3bHdXTnlUdHhXbWRRZkhLQkhRVUhnVWp3SVQtQkpxT0owMTdsSE5fcjBzTlpIX1pnZ04wX0kwYmRJaWdzY0hUV3lPMUdFbzc1dmhBaHFQN1Rfekk5T3dFamFHbElNakhtMkc4OEdva2oxQWZ5SlM5dFlLU19rV2hnYXFmbmNwSzR2REpURVE4VERZVnc4NUllZDZWUGZwVWJ4c2FvOUtFZ2NWZXNPbWlzaWvSAdABQVVfeXFMTlhHOXpPWm9oQnhYbk4wc1FXYlVhTWZtX2JBTXZ1MzJ2YWNwVzlHd1ZsTFZZU1BfcDd5aGVZa3VEQktEWFU3QTlQV08wMEpRWjJJZ1pwc3ZXSFhJVTFqa0t6NzJNaDN1dUdiUUV0X0N6VDZUX084WFZMMGxWckRLUDRNaUFXbUZnZWtUaXN2cUdWSVpweEZpSUZFUDA0NGxvVTVDeXZJeTNOZXYtcHF3SG8tUi0yLVEyT0l2OUZRS0Fha1pxZm00M2p6YjNvS0kyNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQaG9PVkZfbEV6RWpLdkhTMUNXcnVZNkNWR2s0dk1ESFJoZVplbDdLQjRQTWZ3VTNJQ2RYWkFMdWE1YUJtVS12cHdBbGxOZS1waU5QMjI1Y3doMzJXc3NMV3dTdjVqLW55amN4a00wVC04Z0Y2VElQeFUtTUtCNVR0SjU1M1ZzZGVCREV5RTdGSUpjTWJsWWhrOHdCdGQ4STRHUklVVlJjNXNWdC12allBVk9kMVFrb2NTZ2JPWjItdDl1OFZUSWR5Wg?oc=5</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>10-05-2026 09:14 UTC</t>
+          <t>09-05-2026 15:59 UTC</t>
         </is>
       </c>
     </row>
@@ -2272,22 +2272,22 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Natural Biocon (India) Limited Reports Net Loss of ₹4.00 Lakhs for FY26 as Revenue Declines Sharply</t>
+          <t>The next 10 years will be about high-value innovation, says Kiran Mazumdar-Shaw</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>Fortune India</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxPTVFVV2FrSXF3cGk5UGVkaW1JS3FTa3dCMHExdkZQQ1R3TGRUc3JoRDlad01VN2NBcENJNkFlM3BpLUtkTWEtdGNTZ0dDWFhHVXJMNnVidm1JVnQ1NUE4dFcybjBtRkc3N0hYWmIwbjR3bnRpRHZnaVA2NHdlY1FrOWlmSjFmblU4MHZzWnRubjk5VTlhSlRWLWpKOE5xb29Sdm0yX1d1Ri1IdlpaRUlIOTZqQUtwVGF1bElTbmt2eFBTMzJ5eElEbEhfdU16VGhLZmE1Rm8zOUZ6OG0wZl9GeDFqNHJtZkpH?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOWEc5ek9ab2hCeFhuTjBzUVdiVWFNZm1fYkFNdnUzMnZhY3BXOUd3VmxMVllTUF9wN3loZVlrdURCS0RYVTdBOVBXTzAwSlFaMklnWnBzdldIWElVMWprS3o3Mk1oM3V1R2JRRXRfQ3pUNlRfTzhYVkwwbFZyREtQNE1pQVdtRmdla1Rpc3ZxR1ZJWnB4RmlJRkVQMDQ0bG9VNUN5dkl5M05ldi1wcXdIby1SLTItUTJPSXY5RlFLQWFrWnFmbTQzanpiM29LSTI00gHQAUFVX3lxTE5YRzl6T1pvaEJ4WG5OMHNRV2JVYU1mbV9iQU12dTMydmFjcFc5R3dWbExWWVNQX3A3eWhlWWt1REJLRFhVN0E5UFdPMDBKUVoySWdacHN2V0hYSVUxamtLejcyTWgzdXVHYlFFdF9DelQ2VF9POFhWTDBsVnJES1A0TWlBV21GZ2VrVGlzdnFHVklacHhGaUlGRVAwNDRsb1U1Q3l2SXkzTmV2LXBxd0hvLVItMi1RMk9JdjlGUUtBYWtacWZtNDNqemIzb0tJMjQ?oc=5</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>09-05-2026 14:25 UTC</t>
+          <t>10-05-2026 09:14 UTC</t>
         </is>
       </c>
     </row>
@@ -2299,22 +2299,22 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Aurobindo Arm CuraTeQ Clears Key CDSCO Hurdle for Bevacizumab Cancer Biosimilar</t>
+          <t>Pharma Companies Invest In US While India Still Depends On China For APIs</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Medical Dialogues</t>
+          <t>Deccan Chronicle</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxPRy1BejAtcDlsbm9rLWtQSklFR203YTRrS1lrYXJlOHBOTEtQLXB4VHJmQkdjVk96WWlrWDdvN19KWnNvdHFWZmVCU2daQWlIcnl4VUNqX2VFLWxVUWozOTNCUlV4MEZ4MEhvS2FrajJHRl9wSXR4VWU5NTE1MUJRM2lGdmdoUEVvOERNMGRFNkYxbW1YazhMczNuT2w0d1lVaDRSV2tvRkl0WmNsUFpPX0dWeUxXREFEamtqYzBUOWVjQ2dLLVlSVDJCdjdCRDBNZ0lNWHA2QW7SAd4BQVVfeXFMT0x4dHpndTBndHhNUVpMQUFiMlZpZFdVbXFMLXp0dV8wYnJ4aW1WeTVEbUJPN2ppQ2FiM1AtTjAwYkthUFBIeXZSSmwtZ1V4N2dwVUZCd2JBb1N2bEkwSFNteFlXbXRPNUxDRHlJRXY1ZDNmLUZUV3ZKeXZNU0czMkdnNF9RdlZFNEptZE41OE5aMFBJbHRkODQtRGFEUUdhQmx0bVhBbDh0eDVvS1RzMXJUR3dNLTVJS0hYcE1ad1hGMWJleEZrNEZvbnM1UGF5UmFCUnNGQ0xxbnJrSDZB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPR2RWLUpSRXVYZU53SWVGb1B1a1FreHBoUi0tbzhDR1JfVFFnVl9Sdy1xNzJHVlJzbHZWVEpNQV9kdnA1N3Z1U2Zyc0FJdXdYTEFTZC1hTjA5TE9iQzg5Wk10dHBSYUQ1V2hocUQwanE2bDUwQm1LS2tjUlNjS3huRzkzSkYxVEJIOS1pMDFDX1hTb0xVcmxrRU94VVAzRWpIazRqVmcybjZlSXJlb3VtYmp2X1FpX24wcUQyRFc4NNIBxAFBVV95cUxQMWp2a093dHlaMUxSNFR3b1l6SUhZejFuVVVMSEl4akZsby0xU2F5Yk1wZFJ4RDdpczAtVS1vOHg1czkwcUt0bmQ5eEZBNVhGc1hDZ0U0OGZSTVAyaWhfdGw3bW1CWmxOZzNKQk1JSTl3c1lMZE1zUVVmT29zeVFyRUd6WVg2MEx4U1JfU21BdlNiTmRNTW5sZEdFRkFpejhTOVlkUmowRTFaWktnY3RsbER4bU1DQ2pmVTU5WEFGTVpHckNj?oc=5</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>10-05-2026 04:30 UTC</t>
+          <t>10-05-2026 12:53 UTC</t>
         </is>
       </c>
     </row>
@@ -2326,22 +2326,22 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Sensex, Nifty extend gains for second straight session as metal, auto stocks lead</t>
+          <t>Aurobindo Arm CuraTeQ Clears Key CDSCO Hurdle for Bevacizumab Cancer Biosimilar</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>INDIA New England News</t>
+          <t>Medical Dialogues</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPWVlNeVJfd2xFV0JxRFVhdEZjbmQ5UllSYk9lZFdUVjRwUVpoUno3bWI2YjlxelpVeHBDVkkwRUlKZGJ1dm42UUNqNzJHLTU4dkxYak1jZnVOT1NOaHA3NjZ5cGNpRVozb2xDYkJLME1SNFNLdjNidEt2WFR0UWFCWlpTNnlQUEE4eGstdnNnSWdjMzE1VHRsUU1maGVMOTd2Mjc0by16UXVNX3JK?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxPRy1BejAtcDlsbm9rLWtQSklFR203YTRrS1lrYXJlOHBOTEtQLXB4VHJmQkdjVk96WWlrWDdvN19KWnNvdHFWZmVCU2daQWlIcnl4VUNqX2VFLWxVUWozOTNCUlV4MEZ4MEhvS2FrajJHRl9wSXR4VWU5NTE1MUJRM2lGdmdoUEVvOERNMGRFNkYxbW1YazhMczNuT2w0d1lVaDRSV2tvRkl0WmNsUFpPX0dWeUxXREFEamtqYzBUOWVjQ2dLLVlSVDJCdjdCRDBNZ0lNWHA2QW7SAd4BQVVfeXFMT0x4dHpndTBndHhNUVpMQUFiMlZpZFdVbXFMLXp0dV8wYnJ4aW1WeTVEbUJPN2ppQ2FiM1AtTjAwYkthUFBIeXZSSmwtZ1V4N2dwVUZCd2JBb1N2bEkwSFNteFlXbXRPNUxDRHlJRXY1ZDNmLUZUV3ZKeXZNU0czMkdnNF9RdlZFNEptZE41OE5aMFBJbHRkODQtRGFEUUdhQmx0bVhBbDh0eDVvS1RzMXJUR3dNLTVJS0hYcE1ad1hGMWJleEZrNEZvbnM1UGF5UmFCUnNGQ0xxbnJrSDZB?oc=5</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>10-05-2026 07:22 UTC</t>
+          <t>10-05-2026 04:30 UTC</t>
         </is>
       </c>
     </row>
@@ -2353,22 +2353,22 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Nifty, Sensex open flat as investors in wait and watch mode before RBI rate cut</t>
+          <t>Sensex, Nifty extend gains for second straight session as metal, auto stocks lead</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Dailyhunt</t>
+          <t>INDIA New England News</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxQNXJEU0Rib3JrQmVjRVItNFlTS3lfWWlEWUtMV3NQVGJmcWVaY05Cb2pyUGlWal92YWJYcmhyY0pFelY2cXN1ZFFsZHpRdElKdTRqb2V3cFdJenJSdjZsdnhYeXNiQzgxa19waU8zRldTMWdOcUxjeWpNQVhqc1E5Tm8xZ3FKak8zN3FxeGs2Y0V2Z3c3dnpwNzJnSHA5b2J6cE5iMWZkTkZlTXU0UkVEcTZYQmVBVjluTUhkTWxwSVk5ang2Y0dVNEZSRnBoRUxid0JXeTR3eldSQ2YwUlhaRkhyOXo2OVQ2cVgzOGdCMU1ZY1QtSmwycA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPWVlNeVJfd2xFV0JxRFVhdEZjbmQ5UllSYk9lZFdUVjRwUVpoUno3bWI2YjlxelpVeHBDVkkwRUlKZGJ1dm42UUNqNzJHLTU4dkxYak1jZnVOT1NOaHA3NjZ5cGNpRVozb2xDYkJLME1SNFNLdjNidEt2WFR0UWFCWlpTNnlQUEE4eGstdnNnSWdjMzE1VHRsUU1maGVMOTd2Mjc0by16UXVNX3JK?oc=5</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>10-05-2026 02:18 UTC</t>
+          <t>10-05-2026 07:22 UTC</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2390,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxNVGE3M1dJQ2h5SWhRdmNPNnJEdy1iazhxR3p4Z1pGOWo1UEJSR281UG1vUENVc2xkeFppanEwRG4ybDF1QUNCUFl0Z2xzVFZmbW5HS2VpSU1HcVNrc0VwaEpjMWl2Y3BkdU41R0hmMEdVUFRaYmtCTk9ndVUyZno5SUVuTUlrRllFYXFYTjFsQ21xcWJHV091d3l6R2RFQWFYWTFCa0tPNDBfNWN4MDNwQUp6Wk5HaUZQOHdUOWJqa25Oc3NDZVhXc09VeVlOenZNb3pUOHRDT1JfUUx4bWRUY01FcVdvUnRZeDVv0gHrAUFVX3lxTE1UYTczV0lDaHlJaFF2Y082ckR3LWJrOHFHenhnWkY5ajVQQlJHbzVQbW9QQ1VzbGR4WmlqcTBEbjJsMXVBQ0JQWXRnbHNUVmZtbkdLZWlJTUdxU2tzRXBoSmMxaXZjcGR1TjVHSGYwR1VQVFpia0JOT2d1VTJmejlJRW5NSWtGWUVhcVhOMWxDbXFxYkdXT3V3eXpHZEVBYVhZMUJrS080MF81Y3gwM3BBSnpaTkdpRlA4d1Q5Ymprbk5zc0NlWFdzT1V5WU56dk1velQ4dENPUl9RTHhtZFRjTUVxV29SdFl4NW8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxQOUQyYmFvSUZYSUZZRl9lUWZBV2hBOWVoOF9xNEQ3T0pxVnoyNV95UnJxNU5ycXhnN0FEQW1PU1EyUFZBSkVGQUt6R3pEeldCT3MzTEZBTmFtdjFjUUVqdldoU0xOdnltRFJpSHBOamJmS3V4c2o4Y3ZNUVZQaXFSdTExLVVfSzFYOTd3MXVTR3JMVHdtTjYtRl9tUjZiQlBHZ1NvWWp0YTFjNF93b1R2eXgtNXl1X3NRZWYxVzYzaDFMeVBRODFBSFRDNVJ6V1BmaTV0c1M0cVFOeHZRbVBVMHVQdTfSAesBQVVfeXFMTVRhNzNXSUNoeUloUXZjTzZyRHctYms4cUd6eGdaRjlqNVBCUkdvNVBtb1BDVXNsZHhaaWpxMERuMmwxdUFDQlBZdGdsc1RWZm1uR0tlaUlNR3FTa3NFcGhKYzFpdmNwZHVONUdIZjBHVVBUWmJrQk5PZ3VVMmZ6OUlFbk1Ja0ZZRWFxWE4xbENtcXFiR1dPdXd5ekdkRUFhWFkxQmtLTzQwXzVjeDAzcEFKelpOR2lGUDh3VDliamtuTnNzQ2VYV3NPVXlZTnp2TW96VDh0Q09SX1FMeG1kVGNNRXFXb1J0WXg1bw?oc=5</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2407,22 +2407,22 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Bombay HC Grants Relief to Sun Pharma, Restrains OTIDE Mark Over Similarity with OCTRIDE</t>
+          <t>Nifty, Sensex open flat as investors in wait and watch mode before RBI rate cut</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Medical Dialogues</t>
+          <t>Dailyhunt</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPVjhsQmhrWmIzQkkyYnZ1X2xZLUQtdzZUUjl2bDV3M2x4MTZXZmNyX2tOeG04RVVpTWg5Um5zN24xZjdTblFtUkN0Q0xUMXVIR0NoQlkybGxVTHcyQnVmeHFBNlZiOUxSbWJiQjlNMFN1U0ZyeDdFQ0xlaVBzaGNWSElEdEtJX2dYaEktLWNkaGV0eDM4cC1HU3dtX01tQ3NCbUpXYUx0bVgwSzZmN04ybmE0MU9hRGk2cmxHMUtEdjVoM19tZFdPTmtlSFd2MWtSb3FpZ2J5MVB1MHhtUmNyZNIB4AFBVV95cUxPVjhsQmhrWmIzQkkyYnZ1X2xZLUQtdzZUUjl2bDV3M2x4MTZXZmNyX2tOeG04RVVpTWg5Um5zN24xZjdTblFtUkN0Q0xUMXVIR0NoQlkybGxVTHcyQnVmeHFBNlZiOUxSbWJiQjlNMFN1U0ZyeDdFQ0xlaVBzaGNWSElEdEtJX2dYaEktLWNkaGV0eDM4cC1HU3dtX01tQ3NCbUpXYUx0bVgwSzZmN04ybmE0MU9hRGk2cmxHMUtEdjVoM19tZFdPTmtlSFd2MWtSb3FpZ2J5MVB1MHhtUmNyZA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxQNXJEU0Rib3JrQmVjRVItNFlTS3lfWWlEWUtMV3NQVGJmcWVaY05Cb2pyUGlWal92YWJYcmhyY0pFelY2cXN1ZFFsZHpRdElKdTRqb2V3cFdJenJSdjZsdnhYeXNiQzgxa19waU8zRldTMWdOcUxjeWpNQVhqc1E5Tm8xZ3FKak8zN3FxeGs2Y0V2Z3c3dnpwNzJnSHA5b2J6cE5iMWZkTkZlTXU0UkVEcTZYQmVBVjluTUhkTWxwSVk5ang2Y0dVNEZSRnBoRUxid0JXeTR3eldSQ2YwUlhaRkhyOXo2OVQ2cVgzOGdCMU1ZY1QtSmwycA?oc=5</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>10-05-2026 05:00 UTC</t>
+          <t>10-05-2026 02:18 UTC</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma Arm Apitoria Pharma CEO Dr Sanjay Chaturvedi Resigns</t>
+          <t>Bombay HC Grants Relief to Sun Pharma, Restrains OTIDE Mark Over Similarity with OCTRIDE</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2444,12 +2444,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOSUxfV2YzSVRsd0xLNDBPVU9GSUdsSDZUWmlaUDRsYWFSXzZ2M1BQZi1Bc0VRY1h2UjVKVWZ0WjZmR1BKX3FuZWF6bnFXNUs5NzgxUVNQY0pmbXVTdERZSVptZG5QbGxoQlhfdDVqMXBtb0FLc1dWQUdoNng1YWJTbXpLQ09RMkJGYnVpR3V0WnRJUmZ1amNOVEVPOExTeTduTTd0Y2Z0T2RUcURta2VJdWo0QzhtbjdQbE5LS1FaYlRyZzjSAcgBQVVfeXFMT2lVX3Y2UUQyNTNqZW1zY3pyS2ozM2JldnhuaTN0SEJuaEVocU54ODJ4X3FqV1I3c0FSU1dqZXF1MERoejBGY0dJUU9vRlAzQ0xjem42MTFLZC1WSjBWdW9Tbm9yNUdmX3JCODlNWnAxR0U1X056dTZvbnNJMHlLR0dRMlFwZ2V6T3VwUDRCM0lZV3lOcldDQXNiRGZBcGF4Vm92R3RFSERyazByTy1zRTRSbHM1S2tkdnVaSHVMWEY5bWt2OHRMcE4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPVjhsQmhrWmIzQkkyYnZ1X2xZLUQtdzZUUjl2bDV3M2x4MTZXZmNyX2tOeG04RVVpTWg5Um5zN24xZjdTblFtUkN0Q0xUMXVIR0NoQlkybGxVTHcyQnVmeHFBNlZiOUxSbWJiQjlNMFN1U0ZyeDdFQ0xlaVBzaGNWSElEdEtJX2dYaEktLWNkaGV0eDM4cC1HU3dtX01tQ3NCbUpXYUx0bVgwSzZmN04ybmE0MU9hRGk2cmxHMUtEdjVoM19tZFdPTmtlSFd2MWtSb3FpZ2J5MVB1MHhtUmNyZNIB4AFBVV95cUxPVjhsQmhrWmIzQkkyYnZ1X2xZLUQtdzZUUjl2bDV3M2x4MTZXZmNyX2tOeG04RVVpTWg5Um5zN24xZjdTblFtUkN0Q0xUMXVIR0NoQlkybGxVTHcyQnVmeHFBNlZiOUxSbWJiQjlNMFN1U0ZyeDdFQ0xlaVBzaGNWSElEdEtJX2dYaEktLWNkaGV0eDM4cC1HU3dtX01tQ3NCbUpXYUx0bVgwSzZmN04ybmE0MU9hRGk2cmxHMUtEdjVoM19tZFdPTmtlSFd2MWtSb3FpZ2J5MVB1MHhtUmNyZA?oc=5</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>09-05-2026 11:10 UTC</t>
+          <t>10-05-2026 05:00 UTC</t>
         </is>
       </c>
     </row>
@@ -2515,22 +2515,22 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Abbott India Ltd: Valuation Shift Signals Price Attractiveness Decline Amidst Sector Comparisons</t>
+          <t>Govt Releases Updated List of Approved COVID-19 Vaccines in India for 2026</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Markets Mojo</t>
+          <t>Medical Dialogues</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxPZ1VOVkJmN3ZORFRYU1d5d0Exb0piUWdJbTFDWktEOERWcDZCV2QxZDF4ekJtcjBkZHhRWlFObjgzR3BrV000VzRsRmFOZzhFSzltaFUteEtzZGhsTWRHMzR5ZlpieEo4ejhwNWR1eG9aN1RVanBnNWlWRXBuMFdESmJ1LXJoYW9rWjJ2ZU5xc2xzV0JSdHpJbGFhUzI1UFFUNlBXY3RQOGJnM3ZJR2hfUTdSOUtaYndaanBnNGlNNFAtRnlxUUVoVXhZOTlFS1REMDRDbmo5VFNMX2VxUFBCM0Y1bk9qaTFi?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxPaktHYmZEb2ZodWlIbmJVekEwM0JlcllOVVVseHI0RkRmMlkwMmNhUDNyLWhEWmdaNGt5Rjc1WEQ0dVBHeTN5V091c1pGdldqOFBZNm9GSS1mM2UtWE92YXE5RlA3RmJiZTRXRWctU20wbVBoZmdQak40VkpySUM1WXEwT0Z2Q2dncHZBaWNhRWtrc204RG44RTN6WHVRLVFCZE5Jc3B2a0dFNDJoZ205WE5GS2FFR19TUDhuOU1valpBNEtFZmxRSlFITnJidWfSAc8BQVVfeXFMT2pLR2JmRG9maHVpSG5iVXpBMDNCZXJZTlVVbHhyNEZEZjJZMDJjYVAzci1oRFpnWjRreUY3NVhENHVQR3kzeVdPdXNaRnZXajhQWTZvRkktZjNlLVhPdmFxOUZQN0ZiYmU0V0VnLVNtMG1QaGZnUGpONFZKcklDNVlxME9GdkNnZ3B2QWljYUVra3NtOERuOEUzelh1US1RQmROSXNwdmtHRTQyaGdtOVhORkthRUdfU1A4bjlNb2paQTRLRWZsUUpRSE5yYnVn?oc=5</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>10-05-2026 00:57 UTC</t>
+          <t>10-05-2026 05:00 UTC</t>
         </is>
       </c>
     </row>
@@ -2542,61 +2542,61 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Govt Releases Updated List of Approved COVID-19 Vaccines in India for 2026</t>
+          <t>Abbott India Ltd: Valuation Shift Signals Price Attractiveness Decline Amidst Sector Comparisons</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Medical Dialogues</t>
+          <t>Markets Mojo</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxPaktHYmZEb2ZodWlIbmJVekEwM0JlcllOVVVseHI0RkRmMlkwMmNhUDNyLWhEWmdaNGt5Rjc1WEQ0dVBHeTN5V091c1pGdldqOFBZNm9GSS1mM2UtWE92YXE5RlA3RmJiZTRXRWctU20wbVBoZmdQak40VkpySUM1WXEwT0Z2Q2dncHZBaWNhRWtrc204RG44RTN6WHVRLVFCZE5Jc3B2a0dFNDJoZ205WE5GS2FFR19TUDhuOU1valpBNEtFZmxRSlFITnJidWfSAc8BQVVfeXFMT2pLR2JmRG9maHVpSG5iVXpBMDNCZXJZTlVVbHhyNEZEZjJZMDJjYVAzci1oRFpnWjRreUY3NVhENHVQR3kzeVdPdXNaRnZXajhQWTZvRkktZjNlLVhPdmFxOUZQN0ZiYmU0V0VnLVNtMG1QaGZnUGpONFZKcklDNVlxME9GdkNnZ3B2QWljYUVra3NtOERuOEUzelh1US1RQmROSXNwdmtHRTQyaGdtOVhORkthRUdfU1A4bjlNb2paQTRLRWZsUUpRSE5yYnVn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxPZ1VOVkJmN3ZORFRYU1d5d0Exb0piUWdJbTFDWktEOERWcDZCV2QxZDF4ekJtcjBkZHhRWlFObjgzR3BrV000VzRsRmFOZzhFSzltaFUteEtzZGhsTWRHMzR5ZlpieEo4ejhwNWR1eG9aN1RVanBnNWlWRXBuMFdESmJ1LXJoYW9rWjJ2ZU5xc2xzV0JSdHpJbGFhUzI1UFFUNlBXY3RQOGJnM3ZJR2hfUTdSOUtaYndaanBnNGlNNFAtRnlxUUVoVXhZOTlFS1REMDRDbmo5VFNMX2VxUFBCM0Y1bk9qaTFi?oc=5</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>10-05-2026 05:00 UTC</t>
+          <t>10-05-2026 00:57 UTC</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Zydus Biotech</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>From Domestic Growth to Global Dominance: India’s $20.5B investment push strengthens US economic ties</t>
+          <t>Govt Releases Updated List of Approved COVID-19 Vaccines in India for 2026</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Organiser</t>
+          <t>Medical Dialogues</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxPLWVIQXZFNWFYejNaNHdfdkNSdWRBRWZJUUhMZU9SVnZlelBiWUZoNGJ1NkZoOTR1VHpVcGhsZFoxU1U2NXpfYU9Id0tBZ0lQTVZ2N1NzTjJId2RQZzJ5WkNXX24zUTZJTHdiclVjVXlMbW96MlRnZUI2YUN5ckFodGczQzR6STRJcEpEUGV6ck9JN3gxa3ljMkl1S2N2ZnpfY3BaNlpVRTZ2LTRTMzlIb1hZQVZJT2c3LWdvQk9GWE0yZWNlTmFBaGdSa0NVOUlQaGNPYV85OWg2QjJ6NVdZ0gHkAUFVX3lxTE1waWpPcWkyckpuMHJBeWdQN29lMThWY3hTWlFsczBIOVNrY0xYdm5jN0MwMWJTam5fNldnVm82dWc4V1ZoOXhfcG9mRENPMnQ4WDd4SlBEV2hrX2JKaUlrTFE1b0Q1SkN1dDlwYng2aTFHeEV4cjNQVUxLUExoVXpDdDBMQXBCQjByWEpfRXR3Z0dLbmpXU0NfZTY5YVkzNFd2UkZsZmxQMXRWRHg4eGVsYUxpNVh0aDBjbm15TUExbU9GX3Nra2t0VDdVSHA3d18tbE1RckhKaVNsWmtZN2w1Yml0UA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPN3lEb29oTGNzZlhTR1I4dGVGWHJ1VnV3blNscm5oV1NDdi1yR0J3bE5XOWRVeEtfSmRlMDVzcFEwNG5wMEhxT2FEeFlHVmgzVzdBZU5oRGszeGRpT1NTendJSTE3RjgzaDdRdVFvNjFGOTJINThEV05uSTNoZ2pKWUVWRGszLVhEUE9nRzlnZm4xOFdLaUFLRDZzQXFpek5STDdWQ21ncEVUYWFxSXJJLTNVQ1NsM2tacDhxTkx0Z2JXQ05PVzlxajRB0gHPAUFVX3lxTE9qS0diZkRvZmh1aUhuYlV6QTAzQmVyWU5VVWx4cjRGRGYyWTAyY2FQM3ItaERaZ1o0a3lGNzVYRDR1UEd5M3lXT3VzWkZ2V2o4UFk2b0ZJLWYzZS1YT3ZhcTlGUDdGYmJlNFdFZy1TbTBtUGhmZ1BqTjRWSnJJQzVZcTBPRnZDZ2dwdkFpY2FFa2tzbThEbjhFM3pYdVEtUUJkTklzcHZrR0U0MmhnbTlYTkZLYUVHX1NQOG45TW9qWkE0S0VmbFFKUUhOcmJ1Zw?oc=5</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>09-05-2026 14:36 UTC</t>
+          <t>10-05-2026 05:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Hetero Biopharma</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Pharma Executive Duped of Rs 7 Lakh in Fake CBI-Style Digital Arrest Fraud</t>
+          <t>Govt Releases Updated List of Approved COVID-19 Vaccines in India for 2026</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2606,93 +2606,93 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQbTFCRU9LWXNCcUUwNm5lNU15a2dMQlloQ0tBeVZRX2hVWU1VelJFNHVxNG1NMGFsOE50V2IzaTZnYWdMNUpuRFF3eTVOVk93SUNuMFZEcEdqTTd2cXB4dEZWaEZUMVNxbldVc3ZsektZZVVoNE9ILXdMdjlURHdHMjgxRlBfUmFGTVhaS2gtNVFvZXdvWTdnSURPVU02T1VKTWVwX1hIY2pfZ0F0YUxuWmo1R1FhMC1waTZreUxvQ1hHUGVGWkVzb1BUMmNnbTjSAc8BQVVfeXFMUG0xQkVPS1lzQnFFMDZuZTVNeWtnTEJZaENLQXlWUV9oVVlNVXpSRTR1cTRtTTBhbDhOdFdiM2k2Z2FnTDVKbkRRd3k1TlZPd0lDbjBWRHBHak03dnFweHRGVmhGVDFTcW5XVXN2bHpLWWVVaDRPSC13THY5VER3RzI4MUZQX1JhRk1YWktoLTVRb2V3b1k3Z0lET1VNNk9VSk1lcF9YSGNqX2dBdGFMblpqNUdRYTAtcGk2a3lMb0NYR1BlRlpFc29QVDJjZ204?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPN3lEb29oTGNzZlhTR1I4dGVGWHJ1VnV3blNscm5oV1NDdi1yR0J3bE5XOWRVeEtfSmRlMDVzcFEwNG5wMEhxT2FEeFlHVmgzVzdBZU5oRGszeGRpT1NTendJSTE3RjgzaDdRdVFvNjFGOTJINThEV05uSTNoZ2pKWUVWRGszLVhEUE9nRzlnZm4xOFdLaUFLRDZzQXFpek5STDdWQ21ncEVUYWFxSXJJLTNVQ1NsM2tacDhxTkx0Z2JXQ05PVzlxajRB0gHPAUFVX3lxTE9qS0diZkRvZmh1aUhuYlV6QTAzQmVyWU5VVWx4cjRGRGYyWTAyY2FQM3ItaERaZ1o0a3lGNzVYRDR1UEd5M3lXT3VzWkZ2V2o4UFk2b0ZJLWYzZS1YT3ZhcTlGUDdGYmJlNFdFZy1TbTBtUGhmZ1BqTjRWSnJJQzVZcTBPRnZDZ2dwdkFpY2FFa2tzbThEbjhFM3pYdVEtUUJkTklzcHZrR0U0MmhnbTlYTkZLYUVHX1NQOG45TW9qWkE0S0VmbFFKUUhOcmJ1Zw?oc=5</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>09-05-2026 11:29 UTC</t>
+          <t>10-05-2026 05:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Torrent Emerges Early Leader in India's Generic Semaglutide Race with 38% Market Share: Report</t>
+          <t>Samsung Mobile Phones Under 10000: Best Models &amp; Price List May, 2026</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Medical Dialogues</t>
+          <t>Gadgets 360</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxOVEpmS290Z0FVbnQ2cUFXZVRPY3BKM2JkVVp6VDh5RkZnb3k3X1RTazVuLTU0WDl2N1J0M3ZRVk8xNmU1SHFseWQ0LUtvYm9jM3l6VU9Pc043c0ZhNEJDdThJV2hmYWYyR2piSklOOUtSUEU2ZjE2MWw3dHU4d3d6TVpLYkVDclllZV9YakNrT1B3SkNaSHNIUnd1LXdDTU52TEx6cllmbDQ3SWp1U2RuTE00M01JQzFUTFFBVTdUM2lxOE9RYW1McXlDUzh2UWIwUUkyemFQSnF3ckl5U1lpR1RGLTc0UdIB5gFBVV95cUxOVEpmS290Z0FVbnQ2cUFXZVRPY3BKM2JkVVp6VDh5RkZnb3k3X1RTazVuLTU0WDl2N1J0M3ZRVk8xNmU1SHFseWQ0LUtvYm9jM3l6VU9Pc043c0ZhNEJDdThJV2hmYWYyR2piSklOOUtSUEU2ZjE2MWw3dHU4d3d6TVpLYkVDclllZV9YakNrT1B3SkNaSHNIUnd1LXdDTU52TEx6cllmbDQ3SWp1U2RuTE00M01JQzFUTFFBVTdUM2lxOE9RYW1McXlDUzh2UWIwUUkyemFQSnF3ckl5U1lpR1RGLTc0UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE16RG1FVTZORm9zREg4dm1LaUZIcnVJOFE3OU5DSHZ1clRIZ2JzX0haT3BGa3pBV1ZnU3M5RlFnWHd6U19odzRPbno0czJuT3dFR3BaN2xGRkFLd1ozYkxPZldpdzRZN3NVLWlYdXBia3Q3T0ZSa2N3b2ZR?oc=5</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>09-05-2026 11:53 UTC</t>
+          <t>10-05-2026 13:11 UTC</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Zydus Biotech</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Govt Releases Updated List of Approved COVID-19 Vaccines in India for 2026</t>
+          <t>Samsung Electronics Announces First Quarter 2026 Results</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Medical Dialogues</t>
+          <t>samsung.com</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPN3lEb29oTGNzZlhTR1I4dGVGWHJ1VnV3blNscm5oV1NDdi1yR0J3bE5XOWRVeEtfSmRlMDVzcFEwNG5wMEhxT2FEeFlHVmgzVzdBZU5oRGszeGRpT1NTendJSTE3RjgzaDdRdVFvNjFGOTJINThEV05uSTNoZ2pKWUVWRGszLVhEUE9nRzlnZm4xOFdLaUFLRDZzQXFpek5STDdWQ21ncEVUYWFxSXJJLTNVQ1NsM2tacDhxTkx0Z2JXQ05PVzlxajRB0gHPAUFVX3lxTE9qS0diZkRvZmh1aUhuYlV6QTAzQmVyWU5VVWx4cjRGRGYyWTAyY2FQM3ItaERaZ1o0a3lGNzVYRDR1UEd5M3lXT3VzWkZ2V2o4UFk2b0ZJLWYzZS1YT3ZhcTlGUDdGYmJlNFdFZy1TbTBtUGhmZ1BqTjRWSnJJQzVZcTBPRnZDZ2dwdkFpY2FFa2tzbThEbjhFM3pYdVEtUUJkTklzcHZrR0U0MmhnbTlYTkZLYUVHX1NQOG45TW9qWkE0S0VmbFFKUUhOcmJ1Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOWUVwY3RuMVpmN0E2LXdudkFMWjl3VjN6MWp3Vnk4VUUzTnkzdGVRNi0wWXN1MnpRODQ2c0RGWE9Wbjg5Y0RfejdZZUVjZGJGdi1GdDVCdzlzWjBNU0hQbVVtTGJab3lNakR2S1RKSzdOVTVrVDZVV0xoWU45ZFFoVjVZUDdsTTRqai0tVQ?oc=5</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>10-05-2026 05:00 UTC</t>
+          <t>10-05-2026 08:08 UTC</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Hetero Biopharma</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Govt Releases Updated List of Approved COVID-19 Vaccines in India for 2026</t>
+          <t>Samsung Galaxy S25 Ultra price drops to 96,499 on Amazon sale, how the deal works</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Medical Dialogues</t>
+          <t>India Today</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPN3lEb29oTGNzZlhTR1I4dGVGWHJ1VnV3blNscm5oV1NDdi1yR0J3bE5XOWRVeEtfSmRlMDVzcFEwNG5wMEhxT2FEeFlHVmgzVzdBZU5oRGszeGRpT1NTendJSTE3RjgzaDdRdVFvNjFGOTJINThEV05uSTNoZ2pKWUVWRGszLVhEUE9nRzlnZm4xOFdLaUFLRDZzQXFpek5STDdWQ21ncEVUYWFxSXJJLTNVQ1NsM2tacDhxTkx0Z2JXQ05PVzlxajRB0gHPAUFVX3lxTE9qS0diZkRvZmh1aUhuYlV6QTAzQmVyWU5VVWx4cjRGRGYyWTAyY2FQM3ItaERaZ1o0a3lGNzVYRDR1UEd5M3lXT3VzWkZ2V2o4UFk2b0ZJLWYzZS1YT3ZhcTlGUDdGYmJlNFdFZy1TbTBtUGhmZ1BqTjRWSnJJQzVZcTBPRnZDZ2dwdkFpY2FFa2tzbThEbjhFM3pYdVEtUUJkTklzcHZrR0U0MmhnbTlYTkZLYUVHX1NQOG45TW9qWkE0S0VmbFFKUUhOcmJ1Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxQQ0dXT0hKSzd2QklBb1IyRVJYd29nNjBfRGdUQ2N4WWRfZlhfZEhhdC11MGJIME1ZZDBPMnowUm0xTjhsblFVSlpqMTFpXzdWekJVUzJNdFFYN1J6eW5BM0FQX1Rfd1MxaFZEWHV6U1FmamRuVW5VTlQ0UHNvQzJoNGJWWFRXT1JaVXRWRnpTX2pHMUh5ZXJQMlB0b2taOEJ0Slk2ZjFna1AzUXFoNmRWU05UdU9zODJzSWc0WWxzUGNGOElTVVV4c3ZhOVUyRjgtUmlwclYtZlpUbVhYdG9B0gHkAUFVX3lxTE1NckNwSTFrS0xhQWNDV2NkU3ZxLWZUZWZiQUJITkFOSnNHM085UzBzaThIRUdOZFJaa0FjNS13MzgtMVl1U0YwaXluVWMzN0RaTzRmOENzbkNJOFYzY0ozN01WemRrcVVoQkR3Z24xU2FUNXJJOFBIZ2x3cWE3blRVR0JnSlE1SnVDQTk3cEwxVnVRcmNxUXlQMmhVdTMwdDk3dENtbFQyTGliTDhLenduN3VzQUc0U1RKUm9Eb0N4dEFlclVUWm1PVjBnMHVCcm0tRzNIakR6M29LbzlBMWxEZWkzNw?oc=5</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>10-05-2026 05:00 UTC</t>
+          <t>10-05-2026 11:20 UTC</t>
         </is>
       </c>
     </row>
@@ -2704,22 +2704,22 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Dua Lipa sues Samsung, claims company used her face to sell TVs without permission</t>
+          <t>I've moved over from the Samsung Galaxy S26 Ultra — and I'm really surprised at this one tool I miss</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>The Hindu</t>
+          <t>Android Police</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxOS3Q0N0FvZUVOdFhUSUdIWVc4VnJZWnZkNUhQY2x4NVZuY0hxWXVRenM2T1FPMjhWNnYzckRzNzdVZWZFdXpBOW15WU1PS0JvaEJybEdDSy1TNU9IazJ3Sy1xdnUyUVR4a01hWG1KRFJud0huN2pSMDNLLUhEOVJtZ2RFck11bXVXWjc1RXZaaXU4WVdULU9VREJKUlE1TnhCQ2gzWDFpbWlNWnFtY3NuSXNpcnVFYnR0OE94T29ZM3VoT0JDampTTF83OFp3ZDJpWnF1VmpJcXFRTkF0b1ow0gHmAUFVX3lxTE0tZjgybjladk10NzJtY1pkUUs1STV5Y3V6QUIwc2xER0xOaFM5R0tIT3JhTmVpbDlobnctUnhvLTR4U012V0dHNWVjcHZPMlI2NEZDeHhPTUhEcUlpMkp3WEFUcEo1ajQ1VU5yQkdMWTRxLVBOR2lTYzBkYU5aTTZBZDMteFdNTU1BZlNrYm1QZTZJT1pzVi14MnlEUFZhYWVUMlJ3NDNIUjEzRXdlX0pTZURnNTQyQ1RpLTlPY2YzXzVoZ2FVY204SjdXdEoxc2tRSnpveUFOVmt5aXpiS25uN3BKQml3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQYjhrYW4tQkpabGhPalI5N21ZczJSR3BLb1dZM21JdmVNajlUdXh6UkhXZWFsVFdGWGF2dUhOUXN5LUNSNGR0RzFxeG1HSnVhSmVwT3RybW9nTXdWYkhlUGlSTXhhWG11MmJZZnhNTHcxWFFFenp0SFRmUTdJOFI4MnJlMFY1Vnk0M1V0MmJITk5ZRHkySVFlN1lxVGdNaU9NNDN5aA?oc=5</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>10-05-2026 06:51 UTC</t>
+          <t>10-05-2026 10:01 UTC</t>
         </is>
       </c>
     </row>
@@ -2731,22 +2731,22 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Galaxy S23 Ultra Users: New Samsung Update Shows It’s Time To Sell</t>
+          <t>Dua Lipa sues Samsung for $15 million lawsuit over unauthorised image use</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Forbes</t>
+          <t>Mint</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQQ2daeTJnNU9QM3ptWmVIWlZjRktlOU12a0NUYkdmM1FIa2xGcEV6RGE0WDJTbWljZVlCNlktZ2hlZE53SmtvVUMwT1BxUmo4Y3B1cEljdzFnSFFYRGs0a3lkcUFPWGlNTlZubEIyeFM4MGktYnV3TFliWVl0dHpSemJNRnhzandNQXB1eENLdHBpMzJoNGtzaTZXRk9HVC0ydnE5cw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPTzFTUXVRSEtmblVWQ2RCVFlBVWdTNVRiNWpEbi1XYXl3cVJUVFBYdTNQQ0ZSWW9feXJZa3RFMGd6ZWNlWlBCMUg3NUlCRGpRQnM3V0t3R2VuR3NRQmttNnZzbHZwd1dQREw3M184eXh0eWE1R3hLbERWdHBRUEdKdmpDNTlwNEdXQU5yYUQxQVg0d1dSdUVuXzZVb0toNnh4dGN3cHpodGNpczY4c0Z0cFl2Vld0bm9uMlVwdHRGeVhXWGExcXFtUlFB0gHPAUFVX3lxTE1ETXZ6cFJKTERxajl1Mnp1aUY3TjkxcUR5WDh1UTF0ZXlGZXhYM3RMelh6cE1mR2g4WnJhQ3ZXQU9xN2tTc3lXT2w5X2JpcmNYMVd4UUNQWnhwdkFCb1d1ZHNabTlTTnZPUzliY3hKRHFqZXROVGtPQWplRXRFQ2tyUDA4aGxvU2tkN29saV9vSFRIZ3ZyV05LV3FWaGt4MDhMbEw5ZTVxNjJlaDFDaG9NbW01aC03ZHQ3dHBuNHhtdnI2SFF4UHhLRHVpUHVzZw?oc=5</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>09-05-2026 20:14 UTC</t>
+          <t>10-05-2026 06:19 UTC</t>
         </is>
       </c>
     </row>
@@ -2758,22 +2758,22 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Samsung launches 5th edition flagship innovation, education programme in India</t>
+          <t>Dua Lipa Files 15 Million Lawsuit Against Samsung</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ET Education</t>
+          <t>Daily Pioneer</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxOUmtsQXlWd3hWcTIyMXIxNzJ3N3k1MHhxQnlpbzJMWHF6MzVsdFhsZDFkOTVzUnlBVzN0RFprVFBwQnZNWEdYXzhWNUNDMXpVQWYxSWdyOFluQ1RsM21obmh5c2NVc0F5cUY4dlVTQnd1OGlwb2M0cFJ0Y0VJWHh6ek1OM3dRN2dQMndLLVVRcFZLUkZTQWo5aDNRTjZyTW5UVVVqR3ktQnhKdmsyME1ndGxZakNtbW1SOEdQTUlYOVI5V3JVc1ltOXcybjdQUUcxX1NIWVRUU0prZVUzQWhUNHg1V25lSHFKTVdiSVRNcXRYbkUySnhZdUJEONIBgAJBVV95cUxNMGczV2oxSXFoTU9JLTU2TWZ6dDdxeWpoU3N1NjJSSFoxbEtNbWw3aXNGOW5vUDg3N1ZnaHRXeGhYdVBoajRra2h6U2lyQXVRR2NyZklxVVA2VjNSLVJsYU5SOXBYWWxMbnN4T0k5MC1Hek13YnRKUHZkeENtS2UyaGxvQV9jUUpZMTVhUlpVYUowaUIwbzZkQXdVMDdSWDVWVjczX2NOZFBoNzNUc0hMb0NFQmRtU1RleXQxWmlvbEowbTF1VVdQSzRaUHNMbGhDWklYOF80T2FpamtmRVFCb2Rodjl0WFFEd0Y2OC15QTRKMVdLVHpIM05NanREVlha?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNbEZPQkx5a0JJd19Cdk4zY3RUZW9ENFJWcXhYeXQxVHUwZ2FWWFB6NDFtY29BTXdPQkhfbTdfbWd4MU92TTVIamV0dVplTEptaWo5RGZGdk84bHlVTVg5TGVsWGJzQVJQN1BzazNWSEFrQVMtVkVFVzg1NW1INEJNNVBXbVk0a29SVUVCRmdveGNnOFlXaF9yVXVxOGpRczNZSy1kUG5QNFhhYkVjZzVHRU9RX09WdUZWZ3J2ME53VmM?oc=5</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>10-05-2026 05:21 UTC</t>
+          <t>10-05-2026 11:21 UTC</t>
         </is>
       </c>
     </row>
@@ -2785,22 +2785,22 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Dua Lipa files 15 million USD lawsuit against Samsung over alleged unauthorised use of image</t>
+          <t>Free gift card deal: Save $30 on Samsung Galaxy Buds 4 Pro</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Telangana Today</t>
+          <t>Mashable</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPaTR5VDVLVjlOdkhYY1h1V2dhbm0xSWk2cjZYaF9zcTNJWDJHU2hFMm9lWWM5azU1Q1JNdmI1TlBvekQ0QzAyRk9mZWtXVDVyX2dBSkJ3dHBvTWVjU0oyTjhNZlczblpERFBnUkRtS3g4Z1lTajlWNWFYTkRJemxmRUE2bXY4WHVBenBkMFoxT0xmMUx0bHZIdUNPa2lSRWc0c2VDaExiR2ZOTVlmUXV1LTE0QVpIWGNyM1BR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQRVd0cE5KRk5rdWZGSzh6c0YteEhJeGVVdjZaeDVZRmlPNkYycDZORnc0aUhsLTZpeVR1X0R5OUVUUXBGS19ScmRVWnd4ejJXQTljS1VBeFRTUjFmY3NQNGo4MTJBVEJaOENTTTFkRDNaQnVFV1JMYnFoOUtVRVN1djVaenI3WlU?oc=5</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>10-05-2026 06:58 UTC</t>
+          <t>10-05-2026 11:50 UTC</t>
         </is>
       </c>
     </row>
@@ -2812,22 +2812,22 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Dua Lipa sues Samsung for $15 million lawsuit over unauthorised image use</t>
+          <t>Dua Lipa sues Samsung, claims company used her face to sell TVs without permission</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Mint</t>
+          <t>The Hindu</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPTzFTUXVRSEtmblVWQ2RCVFlBVWdTNVRiNWpEbi1XYXl3cVJUVFBYdTNQQ0ZSWW9feXJZa3RFMGd6ZWNlWlBCMUg3NUlCRGpRQnM3V0t3R2VuR3NRQmttNnZzbHZwd1dQREw3M184eXh0eWE1R3hLbERWdHBRUEdKdmpDNTlwNEdXQU5yYUQxQVg0d1dSdUVuXzZVb0toNnh4dGN3cHpodGNpczY4c0Z0cFl2Vld0bm9uMlVwdHRGeVhXWGExcXFtUlFB0gHPAUFVX3lxTE1ETXZ6cFJKTERxajl1Mnp1aUY3TjkxcUR5WDh1UTF0ZXlGZXhYM3RMelh6cE1mR2g4WnJhQ3ZXQU9xN2tTc3lXT2w5X2JpcmNYMVd4UUNQWnhwdkFCb1d1ZHNabTlTTnZPUzliY3hKRHFqZXROVGtPQWplRXRFQ2tyUDA4aGxvU2tkN29saV9vSFRIZ3ZyV05LV3FWaGt4MDhMbEw5ZTVxNjJlaDFDaG9NbW01aC03ZHQ3dHBuNHhtdnI2SFF4UHhLRHVpUHVzZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxOS3Q0N0FvZUVOdFhUSUdIWVc4VnJZWnZkNUhQY2x4NVZuY0hxWXVRenM2T1FPMjhWNnYzckRzNzdVZWZFdXpBOW15WU1PS0JvaEJybEdDSy1TNU9IazJ3Sy1xdnUyUVR4a01hWG1KRFJud0huN2pSMDNLLUhEOVJtZ2RFck11bXVXWjc1RXZaaXU4WVdULU9VREJKUlE1TnhCQ2gzWDFpbWlNWnFtY3NuSXNpcnVFYnR0OE94T29ZM3VoT0JDampTTF83OFp3ZDJpWnF1VmpJcXFRTkF0b1ow0gHmAUFVX3lxTE0tZjgybjladk10NzJtY1pkUUs1STV5Y3V6QUIwc2xER0xOaFM5R0tIT3JhTmVpbDlobnctUnhvLTR4U012V0dHNWVjcHZPMlI2NEZDeHhPTUhEcUlpMkp3WEFUcEo1ajQ1VU5yQkdMWTRxLVBOR2lTYzBkYU5aTTZBZDMteFdNTU1BZlNrYm1QZTZJT1pzVi14MnlEUFZhYWVUMlJ3NDNIUjEzRXdlX0pTZURnNTQyQ1RpLTlPY2YzXzVoZ2FVY204SjdXdEoxc2tRSnpveUFOVmt5aXpiS25uN3BKQml3?oc=5</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>10-05-2026 06:19 UTC</t>
+          <t>10-05-2026 06:51 UTC</t>
         </is>
       </c>
     </row>
@@ -2839,22 +2839,22 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Samsung warns memory shortage will be worse next year</t>
+          <t>Air taxi patent wars; China ZTE-Samsung rate setting; FBI warns of AI-enabled IP theft; landmark Xoma buyout; Access Advance CEO interview; plus much more</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Mashable</t>
+          <t>IAM Media</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE90WmJKZVlramVwRm5ZWVVwMk4xOWpneG9nby1Ja016aFNIYmNpeWlKUWQ2TXJJTDlzMUJOcE1qblFaOUVDX29kQlQ3QzF1NG52RmNjNjB5SFpVWG9wQVhRNHpPSnpjZkpEOEZiZmY4a1FEcjBaWV9hVkFn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPX3hyQVZCSmIxdWJ4Vkx5WE1wbTM1a2FxU3VKZ0U5V3VTLXZDZlc1Sk1pUFd4Qk81d01kNGh3MXBuSFdrUkZucnBneUhaMXhpQ3oxajA5eUc3QXd4aTlQNEhMU3BuYktTYktMM0EwcWhwSFZRbTNBR3hOcExmTjdnbXJ3ZUJEa0VzdkNGMkhnTlNQY3NFT0dzc3UwVUVqZC00dm1BX1RtcFRCQ201OTdDWG01R25CMnEtdHhJd1JfMkJqT3VSRUVTMXhWbnVCZmEydGc?oc=5</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>09-05-2026 19:51 UTC</t>
+          <t>10-05-2026 10:35 UTC</t>
         </is>
       </c>
     </row>
@@ -2866,22 +2866,22 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Compare Samsung Galaxy S10+ vs. Google Pixel 4 XL vs. Huawei Mate 30 Pro</t>
+          <t>Dua Lipa Sues Samsung For $15 Million Over Alleged Unauthorised Image Use</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>GSMArena.com</t>
+          <t>NDTV Profit</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPT3VTT1lPdnV1UEFwMFlDMDJlZHJESmNwRXdPUVRwNU9INzJTRkNqUHl4alJ2c1MwektVUW8yWW40dW1VOG5yS1JRMExCZnNkb25HSTN5bzZMTVJ1LXlsVzZ4aEJLeGRVb0xBYXE3OWxtSXo1YXp4VHVLX1JLTGhlVHNrTXhQZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxQamQ5YnA2M05YTy1SNmoxeFVLa0hkZzNBTlNxTnFTY3ZTWkJJbjdTTWtSdWpzUmJYQ1lxejE2MXkxRTlKaWpnWnEtNVRYUVVGcm5lM0tZRTBLZTRxNjJnTkxwVGJSX1lKVGhzSmw5RWdKM3ZkZERpbmFZaTA0TldENWdZdm5EdVFoN1Nuek9fMmFBeFp1S19FV1RuOF9rem5wbGlBczNEY0xZYlR0S1FyY1hwVTR5alVlNzNBd1JFdEFTdjlfMGlEQTZwYURmaU95RDcxZDdVeFBDTnFSTmlRZ2RrQUJFcTNrS2FaTEF30gHuAUFVX3lxTFBqZDlicDYzTlhPLVI2ajF4VUtrSGRnM0FOU3FOcVNjdlNaQkluN1NNa1J1anNSYlhDWXF6MTYxeTFFOUppamdacS01VFhRVUZybmUzS1lFMEtlNHE2MmdOTHBUYlJfWUpUaHNKbDlFZ0ozdmRkRGluYVlpMDROV0Q1Z1l2bkR1UWg3U256T18yYUF4WnVLX0VXVG44X2t6bnBsaUFzM0RjTFliVHRLUXJjWHBVNHlqVWU3M0F3UkV0QVN2OV8waURBNnBhRGZpT3lENzFkN1V4UENOcVJOaVFnZGtBQkVxM2tLYVpMQXc?oc=5</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>10-05-2026 04:33 UTC</t>
+          <t>10-05-2026 10:58 UTC</t>
         </is>
       </c>
     </row>
@@ -2893,22 +2893,22 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>At Samsung, even best engineers are fighting to believe in staying</t>
+          <t>This $250 tablet might be the iPad alternative you're looking for</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>theinvestor.co.kr</t>
+          <t>Pocket-lint</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5zT1lMemxXOVpUYmRjWFpFSGlpSmVvQlQ0N2RYQ19RODZVWXk1bC1DeU9mMmV4VFR0cEJocW1WTTFPZ2lxOVNhUzAwR0tJSnNPdVVSMy1vbHBzdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTFAxWTNneDNKazlvOFNQY0ZvWDdVLS1QRVRzWFRpODk5VmpZQm9GN29BejFBMUVNcm1vZGp0Ni0xU05tTkQxcFV2bVJDTFgxYWtsUXFNZm82NnN6Mjl5SWZLMWQ2T0N6MHZkWUE?oc=5</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>10-05-2026 07:00 UTC</t>
+          <t>10-05-2026 11:00 UTC</t>
         </is>
       </c>
     </row>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Samsung Announces Breakthrough in Fainting Prediction With Galaxy Watch</t>
+          <t>Dua Lipa suing Samsung over use of image on TV packaging, Variety says</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>samsung.com</t>
+          <t>Korea JoongAng Daily</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQcUdHdDdiUmRmT2RVVi1RcndRM2VvNFN2cVB1T29NdW1oSkxocnlic1VQcXdTUzBsZWZIY1NRVzhwczI4dWN3cGlYY1ozM0hWcHplaGdJY3FNRzlpek1tZEFsTjZvVXVON1VpUURoYloxUDBEaWZ5V1loTWVSYjlPVUg3aEEwRkRobHNrNE9Gd0t0UkFJOWJ5UGJRc0ZXRkxR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxOcHdZTVpkZHcweDFtYXQ0c01PVHBkOWNJczk0Z0xTRm1fOFc3QWtmWTYxRTZ0RDliY19lVGx5REozamxWSjdpNVphUGVwbm52UU51Qy1SME1SVUsyZEJPaHlVSEVCc3hjemRnc09hb2xOUVRNUk8zTWoxcGpBQjlUbTZocTNIWW9mRnVGQ3EzQVdLYUQ4NDdEWEJ6VjRQT1pOdFd6S0JBdjhDVGVZUWhTbVhwZXpkaXQyWlJQNHlCUFBMcXhidjN0eXBZd3NLQ3BoSDZVODZhZVlTLTdwMmcwcHVGNzhJNlE?oc=5</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>09-05-2026 23:48 UTC</t>
+          <t>10-05-2026 11:20 UTC</t>
         </is>
       </c>
     </row>
@@ -2947,22 +2947,22 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Galaxy Z Flip 8 leaks show a wider, lighter flip phone</t>
+          <t>Galaxy S23 Ultra Users: New Samsung Update Shows It’s Time To Sell</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Mashable</t>
+          <t>Forbes</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxQSDItaTNPWmhLMmUwaENESHhpX3hxLXpWLXJJQ2FtNGZEdnBJNURyYXkxS0tsRG9vejUwTXgzVWxEWGFucGtlUnNUR2pTZGRCY0pEeU1ZU0VMU3F3SVd1ejVXRXFEWk1YenZmVVJ0SDV2aVdDYk9iVnhPTTBjWkxRbWR2RQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQQ2daeTJnNU9QM3ptWmVIWlZjRktlOU12a0NUYkdmM1FIa2xGcEV6RGE0WDJTbWljZVlCNlktZ2hlZE53SmtvVUMwT1BxUmo4Y3B1cEljdzFnSFFYRGs0a3lkcUFPWGlNTlZubEIyeFM4MGktYnV3TFliWVl0dHpSemJNRnhzandNQXB1eENLdHBpMzJoNGtzaTZXRk9HVC0ydnE5cw?oc=5</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>09-05-2026 23:24 UTC</t>
+          <t>09-05-2026 20:14 UTC</t>
         </is>
       </c>
     </row>
@@ -2974,22 +2974,22 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Free gift card deal: Save $30 on Samsung Galaxy Buds 4 Pro</t>
+          <t>Samsung launches 5th edition flagship innovation, education programme in India</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Mashable</t>
+          <t>ET Education</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQRVd0cE5KRk5rdWZGSzh6c0YteEhJeGVVdjZaeDVZRmlPNkYycDZORnc0aUhsLTZpeVR1X0R5OUVUUXBGS19ScmRVWnd4ejJXQTljS1VBeFRTUjFmY3NQNGo4MTJBVEJaOENTTTFkRDNaQnVFV1JMYnFoOUtVRVN1djVaenI3WlU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxOUmtsQXlWd3hWcTIyMXIxNzJ3N3k1MHhxQnlpbzJMWHF6MzVsdFhsZDFkOTVzUnlBVzN0RFprVFBwQnZNWEdYXzhWNUNDMXpVQWYxSWdyOFluQ1RsM21obmh5c2NVc0F5cUY4dlVTQnd1OGlwb2M0cFJ0Y0VJWHh6ek1OM3dRN2dQMndLLVVRcFZLUkZTQWo5aDNRTjZyTW5UVVVqR3ktQnhKdmsyME1ndGxZakNtbW1SOEdQTUlYOVI5V3JVc1ltOXcybjdQUUcxX1NIWVRUU0prZVUzQWhUNHg1V25lSHFKTVdiSVRNcXRYbkUySnhZdUJEONIBgAJBVV95cUxNMGczV2oxSXFoTU9JLTU2TWZ6dDdxeWpoU3N1NjJSSFoxbEtNbWw3aXNGOW5vUDg3N1ZnaHRXeGhYdVBoajRra2h6U2lyQXVRR2NyZklxVVA2VjNSLVJsYU5SOXBYWWxMbnN4T0k5MC1Hek13YnRKUHZkeENtS2UyaGxvQV9jUUpZMTVhUlpVYUowaUIwbzZkQXdVMDdSWDVWVjczX2NOZFBoNzNUc0hMb0NFQmRtU1RleXQxWmlvbEowbTF1VVdQSzRaUHNMbGhDWklYOF80T2FpamtmRVFCb2Rodjl0WFFEd0Y2OC15QTRKMVdLVHpIM05NanREVlha?oc=5</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>09-05-2026 23:18 UTC</t>
+          <t>10-05-2026 05:21 UTC</t>
         </is>
       </c>
     </row>
@@ -3001,22 +3001,22 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Samsung boosts Galaxy S26 Ultra, A17 output as Q2 slowdown looms</t>
+          <t>Dua Lipa files 15 million USD lawsuit against Samsung over alleged unauthorised use of image</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>digitimes</t>
+          <t>Telangana Today</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOcWtlYmRiWEpyd2RUM0JZNnRKQTdWMGJuem9IczFqRHFvRndhODVUQW5fU3c4MG1nM0s2TkNoT19sYnRQQkF0YjAyWF8wUGFRellsemo4YmtaUWRQaUctUnZXNGRISDVIWVl3QlBxSEthT0N0MDItU1gwcjA0bnFsYl9UaFNDc2pJaGQta0lSWU5ZN1U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPaTR5VDVLVjlOdkhYY1h1V2dhbm0xSWk2cjZYaF9zcTNJWDJHU2hFMm9lWWM5azU1Q1JNdmI1TlBvekQ0QzAyRk9mZWtXVDVyX2dBSkJ3dHBvTWVjU0oyTjhNZlczblpERFBnUkRtS3g4Z1lTajlWNWFYTkRJemxmRUE2bXY4WHVBenBkMFoxT0xmMUx0bHZIdUNPa2lSRWc0c2VDaExiR2ZOTVlmUXV1LTE0QVpIWGNyM1BR?oc=5</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>09-05-2026 23:17 UTC</t>
+          <t>10-05-2026 06:58 UTC</t>
         </is>
       </c>
     </row>
@@ -3163,103 +3163,130 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>AstraZeneca plc stock (GB0009895292): Pharma giant eyes growth amid pipeline progress and pricing pr</t>
+          <t>Earnings call transcript: Nuvation Bio Q1 2026 revenue beats forecast, stock jumps</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>Investing.com Nigeria</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNclRsV2dfZExRYzRSOS1XMzZ5UWtHVlhGYkRuLWxGR1N2aWhIdjhiOEdITXlIbGNrQWlXMTd6QkczVkIyRzc3MFdwSVZCZ0VxbzR6VXM4cHFvM2lfdDAwaFhmaXRsMmFWSENzVDhzLURFdlRZendZdFRmUnRscDV0N0gyVzZQbmt3bEN0RVhCUWxSdW9UZGxjUW1mOGIxdE5YUEUwRHl6YXFiTE55YTFvS2p6eU9GNGEtRURjLU5tNHg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQNWdUSmJ2YnQyVHUyd3gtbjJaT2V0RGZFNHpUTHg3RUpwbU81YWpOeUZhejJxTTVXNEpGNUdsalFNdjVrTUI3M0YwOWV0Yk0tSHZvcDF6cHZIcVZfTkVFc3lVZ2QwTjByaDFKZFpTMW5EV0d6TzljNGM1QVZGWTJwallCNnQtRG8wbzRqWkF1TEhnNzJOZ2ppRDVBLURTTkppN1pkeDg1YXplLXpvZGg3TUFXZHNlTFlEZXdvSU4ydkV0MFdyRHNLQ0ZJdXhUTEhRVHNZZWhSRk8?oc=5</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>09-05-2026 12:07 UTC</t>
+          <t>10-05-2026 11:45 UTC</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Kyowa Kirin Co., Ltd. Just Missed EPS By 16%: Here's What Analysts Think Will Happen Next</t>
+          <t>The Wall Street Bot - How Hedge Funds Are Replacing Junior Analysts with Fine-Tuned LLMs</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>simplywall.st</t>
+          <t>ABC Money</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxPZnN2amVaQ3hBMFpPRkp0aHNIZUhWdWk1WFpOSnFySDg4REZmU0VFdHExTjZHaldyS0F2OGQ5NVZYaHFVcWZrNFVxOWw4RXpNM0hSZEZ5M2p1aFo5Tmc0WnlpTzdPMGNUWm15QUNTTENfQ0Z4WEU4dXJvN0t6QWllYXZheW5ZVjZibEs0Nk0zZFVBUmM2ZWZHYmdCb2RRRkRyYkFvakpHdjZtRllWanVXclZ3V2FLT3lxT05SNmFvTnlwcjRZZWIzOE05NFFKZFUwbVNKSzFXQzlTZGIwQThJVVkzTdIB6AFBVV95cUxORnM2M3QwTkV1OTh4eVhWbGRiMXRSM0w2MnJKTWhVbkR1WlY3UGJ1b2g2RzlWc0d5bFhqVkxGVnVRSFJEMEoxNzZJVS0wai1PNm1MSFpyUDNwRHZtZVh2bkZOSnFhTXRiVlBNbWI1aDhoanB5VEZoYkFXRjRFU2hsczM0ZWJrNUZxdHZ5Uzl1N3JmVnFZTHY2bUI2dUdXZ1MtalhoZnNBQWlSeFRyLVhfaENiQVZWVjBXckJOQ3E1LVRhSmRXczZvWkRDSzRHdjF4MDJVUGNVTE5ibGdPN2dEOGZHTXNSTkRE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQSWtEenhMTmQ5R3lxZGxTREdPYzVWeU52ekxFVnRFMFBKU1VjMkJ0RzEzTkRIOExPYThzVi1jbm5TdTdmdm4wam1HNFI2dUNock54d0FwbVQ3dEc2eDd2a0tULUhIZ2plS3JZd0xIOVhWZGQ2T2VOSTdiaHJjUDAwOFVnMVBkMVdBMlJabHUtZjdmb0RtQTYtV2V6blgyMlhYNWMxeE5Zd2pNb29KUHVla1lxdjhNbUlGMjNTMG83QQ?oc=5</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>09-05-2026 23:23 UTC</t>
+          <t>10-05-2026 09:20 UTC</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Kyowa Kirin</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Teva, Upstart, Bloom, Corning, Seagate Insider Shock</t>
+          <t>Kyowa Kirin Co., Ltd. Just Missed EPS By 16%: Here's What Analysts Think Will Happen Next</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNR2VuZE5XQ2IwdDFBMGh0Q0w4d2VtRWh6SWpKTHNIMDZyQThZRmFkZV95Y2pBR3dzYlN4OEdiYXUxakpGTmcySUxHRlhhTVFTRDNhSUN1Y3JQdndRLWthbzI0Y0hNSXV1d244aDA4M1dfS3RfZmQ4YWNuX2g4cmwwSDdONDNSOVA2VThTYjVGTHB5MVJ2UWpLdjh3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxPZnN2amVaQ3hBMFpPRkp0aHNIZUhWdWk1WFpOSnFySDg4REZmU0VFdHExTjZHaldyS0F2OGQ5NVZYaHFVcWZrNFVxOWw4RXpNM0hSZEZ5M2p1aFo5Tmc0WnlpTzdPMGNUWm15QUNTTENfQ0Z4WEU4dXJvN0t6QWllYXZheW5ZVjZibEs0Nk0zZFVBUmM2ZWZHYmdCb2RRRkRyYkFvakpHdjZtRllWanVXclZ3V2FLT3lxT05SNmFvTnlwcjRZZWIzOE05NFFKZFUwbVNKSzFXQzlTZGIwQThJVVkzTdIB6AFBVV95cUxORnM2M3QwTkV1OTh4eVhWbGRiMXRSM0w2MnJKTWhVbkR1WlY3UGJ1b2g2RzlWc0d5bFhqVkxGVnVRSFJEMEoxNzZJVS0wai1PNm1MSFpyUDNwRHZtZVh2bkZOSnFhTXRiVlBNbWI1aDhoanB5VEZoYkFXRjRFU2hsczM0ZWJrNUZxdHZ5Uzl1N3JmVnFZTHY2bUI2dUdXZ1MtalhoZnNBQWlSeFRyLVhfaENiQVZWVjBXckJOQ3E1LVRhSmRXczZvWkRDSzRHdjF4MDJVUGNVTE5ibGdPN2dEOGZHTXNSTkRE?oc=5</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>09-05-2026 13:09 UTC</t>
+          <t>09-05-2026 23:23 UTC</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
+          <t>Fresenius Kabi</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Fresenius Kabi Nutrition Solutions: What U.S. Patients and Providers Need to Know Now</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>AD HOC NEWS</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOWFpQZ3dFUllPVlpnQXhfX2k0MnRUMkwybTFTb3FRMEhvcTB3clFQTTFudWkxbHVwaTVYN1IyOGQ0VmdrMWV5WE1zdWRQWHNjOGEzdFhkM0pnYUJuNllIUXpnRTBGWUF6Z1FHTUt1cHJOalptLWlrQXpFZGNDQjBYaEtHSkg3a0YwNkczX181RXNRYWgwQkc3bVM3d0N0YjNnNVdRV2xqT3J3akM3dXo4Sm9NcVc3eU1SeXNBV2dCUVpCV2taVDU3U1VR?oc=5</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>10-05-2026 11:49 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
           <t>Teva</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Formycon AG stock (DE000A1EWVY8): Biosimilar developer eyes growth amid new launches and partnership</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>AD HOC NEWS</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPbnV3UzQzWDB4ZnUxSUtkaXVQQ1Zrd3FwQ1IyY25FZldEWFVKbnEwblB6WEFVVHppUDlYR0tjWHlMeUxZeV9FYVgzWVpSdTl4LUFWQS16TWVfRElDV2RacGdka3dNR2NtT0tMMDVxOGJmeDYyc0VtQUUtOF9fcWNLUEJZbzNHaXM0NFd0VVo3cFU0c0F3X0hpdGMwNEU4NjhSTUJBNDNXU0NYa0ZsdnRHY24yUW9INXZGWkFleFFscnhkcFNUNkE?oc=5</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>09-05-2026 14:08 UTC</t>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Teva Pharmaceutical Industries Ltd. $TEVA Position Boosted by Mitsubishi UFJ Asset Management Co. Ltd.</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>MarketBeat</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxNcFpLVDBBQTVkVkx5TDNoQkFhTUpnRjVXeldGVlRFY2tiVVlaQWxSTm1KM2xaakY2TG9JaTIxUXBLLU1Wby1Pa1pOdkwzQWhWRE1POWx6ZDV6am1vZkJ3SDJHNk5kaThGZkdNTnoySGF3VzEtOXJTM29QQnZzanhOQTNNVGN5TzM0NEs0dmNqUUZkd1E0d2ZNeWdIN1FkVWE1X3FEOWJCSkstMTAtWjBsWmxycW5hS2pESFdpYkR5RW9RTzdqOUpXa1hucW1ndVpPaW1OQ240ZS1qMVctUUNJeFhtTkNacEFJT2p3RG5mdUg?oc=5</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>10-05-2026 09:32 UTC</t>
         </is>
       </c>
     </row>

--- a/news_results_raw.xlsx
+++ b/news_results_raw.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E170"/>
+  <dimension ref="A1:E188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,22 +490,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Aarti A Kapoor appointed as Head of People &amp; Organisation Operations for Region International, Sandoz</t>
+          <t>5 Questions For Sandoz Global Head Of IP Julia Pike</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ETHRWorld.com</t>
+          <t>Law360</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQbFpZdVNRWElIdm5TbmQwaTN1TnBuS1d3eGY3T2g1V05UNnpFVmJXTDgzRUtUTk05UFR0M01RZUs5Y2F1Q2FVcEhzTDh1aWh1Yl9FVEJzUWc4bjkybXBXd0ZLTTdlWWFGanF0XzBIdlZ1SHhXblUyZzgxR0VVUm1ReTJrWlV0ZF9qNWVNUUkzWXVEbHFUekd2TUQwdHE2a2x6WkdTY0FaUVdlX1hvVUdXTGhWd3ZiOWUtRHhOcEJJWVg5dEE5ZlBERnd2YUNIZ9IB0wFBVV95cUxQQ2RHZVFlR3ptc2VveXV6WlMyTUtyWkI4SERPaXRpbFpMa2FBQW5IZVc4ajdheGVBN0o4NUU0Vm1vVzcwZmdDa1FlRnFQdGhPaWJEUXdhVVhJczBCTy1ERDJnSEc1VHRwTVZRbXBsaHFtNFNaMEw5b25RSnpUTmJsUjR2TG9PUV9QVFNHQjBwdE5ZTEFLN3lzNG80OFRwajhJRXd0b0k5NkFLcE5qQi1MYXZCblN1WHh0R0tfWmtMM2ZNdmFmNDVuR3BOVTJoWEtJVURF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQa1FmSUtHdXBtNC1JR25DYjRvWVpIQXRFd3I3eHNvMDFtNnNUajhhbFA3aXZzWFlkVTJsMk1OYkRuU21wVmo5WUZWZ3V2akVRaU1vaW93eUZSS1Bid1VjWDRmQmY2OU1BMXl4dm5TYklUUHlCRnNPM3BHRHR3cnpvUEVULURCMC1sbC1ULWtvQnYyaGhSSHfSAVZBVV95cUxPc2pFeDJlbkxZN2xkQVNhRTlZbEJ2MlJ0ek1WblFYNWRvbE0tU0tkamdWellHZDhERnNDd2N3THJ2WUVaUUY2SFRGdTBtRXBsbUtEMmxJZw?oc=5</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>10-05-2026 17:33 UTC</t>
+          <t>11-05-2026 18:03 UTC</t>
         </is>
       </c>
     </row>
@@ -517,22 +517,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>This Day in History - May 11: Mari Sandoz born in Sheridan County</t>
+          <t>Today in History - May 11: Author Mari Sandoz born in Nebraska</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>KOLN | Nebraska Local News, Weather, Sports | Lincoln, NE</t>
+          <t>WOWT</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPV0JmNDMxY3NkRmdhNURaV2oyUldfbWp1TXZoU0lSM09DbnBfV2MxY1hwV0Z2ejhzMURDSi1scUdMRWpTTjFmZTZ0Y1lZRGRUcG1FMUY2dTlXT01XeG9mdEpvUnBqVU1oczJhNmJmdW5SVHFHck40YmRsYmctbE8xUGJZQmFJZjJmdjBNbXd0dUFPSXl0cEpv0gGrAUFVX3lxTE1Wc0ZaNk9CZ0xZWmF6T1FGWlBpWV9wLXpqbVJVTFRlRkxkS3ZQVDk5TEpoUHhLNDlKUHRWWXhNeTk2ZWxJQ1ZUbFBQbUJsQl9rZGFUeUFRN05iSFBkY3pjMGtoRGJJcFViTThIMURzYXMyTkhyLThBdU93dzJBcHgyY0lmMWF5bkJ6WEhiWTROckhNdWFzeGNKdjZ1SFdWMjNMR3NMeDd1QTFwRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNQURtUk1NZjVNaVBocWRjSGxfbW11MUVKeWVjVlpFdWJRMnA1akd1Z2FPR2pfc3VNQW0taFNPaUFsaS1xWHQ4VkdrZnRKWk5qaUQ3Y0o3S3E3N1pNS2RDdGtvWTZuTFVHRDJVRTBPTzZaQjZ5LWQxcUtRLS1fZ05IUUk3ODMwSzRZV1Qta3g0bw?oc=5</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>11-05-2026 13:12 UTC</t>
+          <t>11-05-2026 16:55 UTC</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNZ3JnQWZRbUhHZ01oZ2RZR2NzTV9LbnJNekZyNjdKRzlkQW1mZ2pobHZjakRuaHl0cDJkdktneUpfZWVGT0doRGRVcFcxejNUaWxWQ0Z1cUthcS05N1JrV1ZqbGExMTVCclVPbkUxMWtSLV83Qmo1eGc3UUR4bWlrYXNNcnFIYUg3NGRCbVM3UE1laV94c1ppeHA4V1RCb0k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPV0JmNDMxY3NkRmdhNURaV2oyUldfbWp1TXZoU0lSM09DbnBfV2MxY1hwV0Z2ejhzMURDSi1scUdMRWpTTjFmZTZ0Y1lZRGRUcG1FMUY2dTlXT01XeG9mdEpvUnBqVU1oczJhNmJmdW5SVHFHck40YmRsYmctbE8xUGJZQmFJZjJmdjBNbXd0dUFPSXl0cEpv0gGrAUFVX3lxTE1Wc0ZaNk9CZ0xZWmF6T1FGWlBpWV9wLXpqbVJVTFRlRkxkS3ZQVDk5TEpoUHhLNDlKUHRWWXhNeTk2ZWxJQ1ZUbFBQbUJsQl9rZGFUeUFRN05iSFBkY3pjMGtoRGJJcFViTThIMURzYXMyTkhyLThBdU93dzJBcHgyY0lmMWF5bkJ6WEhiWTROckhNdWFzeGNKdjZ1SFdWMjNMR3NMeDd1QTFwRQ?oc=5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -571,184 +571,184 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Global shortage of ADHD meds means some patients may miss out</t>
+          <t>Novartis AG stock (CH0012005267): Global pharma leader navigates patent cliffs</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Te Waha Nui</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiY0FVX3lxTE9DNDllNjdhd3BfSXpieGdjNmRlcy0tOVdUNEp4OWphb2IyNElxZkxURm1YUlhUQ29nRTlYbWQwRUJtVEc4X0RmQndWcTAtcDZ1MHRMYUhnXzlOYXV5Qms5TFFVYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOY2JmMmxHd3RwbWZ0SEhmWVJDbWdOeDViN1c5dGxvWjV3bTVwWWNyZm5EdThQTzQ4ZlRwU3E0M3Z0b0habXNDQ2V6X25LVklacTY2YjFvR1BMdC1uRW44UXMtNzl6WG1VSHBRZEs5dGNwY2RIaVJHT2duaTdfLWNVYlhmOG5YczdYTTZzZGxJeFhSSGxsa1VkLXJSXzZzS2d6LUdYYU5oSVF2WURMTngxUWlWN2ptWTIzMTFxZkRnNHpuYjF0dmc?oc=5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>11-05-2026 03:59 UTC</t>
+          <t>11-05-2026 14:01 UTC</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Formycon</t>
+          <t>Sandoz</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Formycon AG stock (DE000A1EWVY8): Down 0.4% on Xetra Monday morning</t>
+          <t>Today in History - May 11: Author Mari Sandoz born in Nebraska</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>WOWT</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNdzJxWGpQVV9vTDJBYzlGdXhpZUF0cV9VX1VBdkllOEhiQ0lFTU4zbVJzT0lzRF9UNHBpdG42MXdBb3REQWhzb0VvaVVzckxzTVNzVExDYkdTazJYREpVWjR4dk8xS1JlUldCOWZxSFdUa2QzS0dhUTZTZ0puNzIyVDdQX1lJRGZxcmdKbEh0ZXhBVEp5MzEzUm5POUJUd0hjclVCLWVrYzg0SzROWlIwcnZKMGREZHVJc0FMV3pQMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOR0NvamVpcnVmOU1HWDhNby1RWlR5RzF1ckdKQWZLY01SU0JfS2l5dFI0UTQ4VWRhYzVybFdwUjZjRGZVUXFrd2R5Y1pOYkpNdi1lTEVoT0ppU3dYSEdRaGlLSTdXMzhKaWw4OGZPUkREXzFvMWdqYVVjeW5fNFhfT2E1SV9WNHFQbVc3OV9BMTdJV1piZ2VV?oc=5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>11-05-2026 10:25 UTC</t>
+          <t>11-05-2026 16:57 UTC</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Gedeon Richter</t>
+          <t>Sandoz</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Free cash flow per share of Gedeon Richter Ltd – OTC:GEDSF</t>
+          <t>This Day in History - May 11: Mari Sandoz born in Sheridan County</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>KOLN | Nebraska Local News, Weather, Sports | Lincoln, NE</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNSmtYNWxmUXBxSk1ET2tUT1NHQTI2RWRWdXYtelQxQUNhQ1h4SEV6VllBY00xQUVwSEpVYXd3MVFPcGp0MnlIMjN1a0E1ODh2aW43X1dyeGZVNUJQVlpXcVJqNFl4UThaY2JQa3FqVUgxSEQ3R0plSTZQWlJ2c0dUcWhtSnR0aEJZRVZWNUNqTlpPYlZTZXhweUtFaVFjRkhkandzcEFEdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNZ3JnQWZRbUhHZ01oZ2RZR2NzTV9LbnJNekZyNjdKRzlkQW1mZ2pobHZjakRuaHl0cDJkdktneUpfZWVGT0doRGRVcFcxejNUaWxWQ0Z1cUthcS05N1JrV1ZqbGExMTVCclVPbkUxMWtSLV83Qmo1eGc3UUR4bWlrYXNNcnFIYUg3NGRCbVM3UE1laV94c1ppeHA4V1RCb0k?oc=5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>11-05-2026 01:36 UTC</t>
+          <t>11-05-2026 13:12 UTC</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Sandoz</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AI in Life Science Market worth $69.34 billion by 2031</t>
+          <t>Liquidia Corp 1Q 2026: Revenue $132.87M, Net income $52.86M, EPS $0.52— 10-Q Summary</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MarketsandMarkets</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE5WQ0x0NUlaUldUU1VucmNKS1plazRoZVNsZ1pjU3Rxd0szMEpIWXZ4RF84bjJGVXdmMHMxYWxaUlg4MFZDaHdnNjhza0NPRTJQRi05UzUySVZUT0NaQ0VzMDRUR011ek5fZGRURVJ0cHNNSnR6aDFTc0x3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxPR0NXUUNIYmNrR2lpNXVSOGItTllsZHBETzd3VmFWMG9CNlVmUXI0TjVVRE01MldhdkhLak1zZ0J0aW8yZ0ZhQ2RiaHAwVjdVcUtVLVhDUVlybk5XZEN1cG8yUHlEejVOQU11cWNVaDF4c0ZCZlotalJsc0ZBdGlTN20tUUpvclgxc1VkODQ0dVhTb3oyUGYyd3d0Q3F1b2ctT1pFdHdJTXV2aXp0czBIbTNOTDF5dm03MXh3cm5PSS0xdzh1eGM1Ul9QTWFFMHdYX1Zsd0t3?oc=5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>11-05-2026 09:04 UTC</t>
+          <t>11-05-2026 11:11 UTC</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Sandoz</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>From discovery to commercial HQ: Switzerland's talent advantage</t>
+          <t>WATCH: Morning Pulse with Craig Allison May 11, 2026</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>S-GE</t>
+          <t>KOLN | Nebraska Local News, Weather, Sports | Lincoln, NE</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOT2RhTWN6dGVfVjlDeGxhUjZ4aUxodktyWkwzV3R3MVlWWUJsWnB2cjhUQWhtdFczRzJMeXZBcC1EX3ZsVEc0elJZaGJlM25GSEtmd1VhRzlyU1FsWlNtMUphUnRMbDJBWTZUZFlnRFFhVURQMldxMVpMeC16bVZCYU9yVUdEMEg4OUFoeC1sWktGWkIyR2l6NDI2cXB4aGNEWWxhbmZmeFloRW1TSEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPMWVtWGowUGNYSjJIeUxkLTM4YXFRak82ai1icGZZLVdsZlBrV0NJZTZBM2tWc1BDYnFUN1hRUnlRMjFBazhvNUxWcU9YNlNuZC1lMmRqUWxNaXZnUEN0clVfMUlpTDVXRklSVFhoWmNrTmljZkMwNTdQQ2MzSDlpcTZJeE9MNVhaelNUZnlEeDAzX0gtN1hYNnFUVDJ6cFFaUFNWQm9COEkzMHM?oc=5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>11-05-2026 11:25 UTC</t>
+          <t>11-05-2026 14:19 UTC</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Formycon</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Clever Culture growth strategy gains traction</t>
+          <t>Formycon AG stock (DE000A1EWVY8): Down 0.4% on Xetra Monday morning</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>The Australian</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAJBVV95cUxQbFgxRjA0RjRqNVlkbXk2QTlwblFZdVdlUWlCVG1hUzNJQ3JVVmZXb0d6cXRXTXVEeS1DUHhvR1ViY2Y3cnJVRTducWRsUGM1OHdqUHJOU3Rxc3BRdnp5ZDdjZkQzZHQ1X2RSbWZESVplZGhHRkg2ajRJU3Uwa2lubDBETUwxeFBZb2JQOS1Lb1JzZ2ZzZWFWRWZPbTFSenU2Nk9ldWRodzEwQTlILVBIWW9PWHJrRV9TTmE0Wmc0aUI4Y1RWQnQteVhBcEtJakVtR293N3dYMk5GYWJENGVabEZmRjB5TWpiOGN3VzBNOVg1MlRTSzdiWF93UjNyRWdZWUw3Y3pLRklCQWVKUURYQml4Y0ZfSy1jZmJNSklxM3JKa2FkUk5WZNIBqAJBVV95cUxQbFgxRjA0RjRqNVlkbXk2QTlwblFZdVdlUWlCVG1hUzNJQ3JVVmZXb0d6cXRXTXVEeS1DUHhvR1ViY2Y3cnJVRTducWRsUGM1OHdqUHJOU3Rxc3BRdnp5ZDdjZkQzZHQ1X2RSbWZESVplZGhHRkg2ajRJU3Uwa2lubDBETUwxeFBZb2JQOS1Lb1JzZ2ZzZWFWRWZPbTFSenU2Nk9ldWRodzEwQTlILVBIWW9PWHJrRV9TTmE0Wmc0aUI4Y1RWQnQteVhBcEtJakVtR293N3dYMk5GYWJENGVabEZmRjB5TWpiOGN3VzBNOVg1MlRTSzdiWF93UjNyRWdZWUw3Y3pLRklCQWVKUURYQml4Y0ZfSy1jZmJNSklxM3JKa2FkUk5WZA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNdzJxWGpQVV9vTDJBYzlGdXhpZUF0cV9VX1VBdkllOEhiQ0lFTU4zbVJzT0lzRF9UNHBpdG42MXdBb3REQWhzb0VvaVVzckxzTVNzVExDYkdTazJYREpVWjR4dk8xS1JlUldCOWZxSFdUa2QzS0dhUTZTZ0puNzIyVDdQX1lJRGZxcmdKbEh0ZXhBVEp5MzEzUm5POUJUd0hjclVCLWVrYzg0SzROWlIwcnZKMGREZHVJc0FMV3pQMA?oc=5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>11-05-2026 00:09 UTC</t>
+          <t>11-05-2026 10:25 UTC</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Gedeon Richter</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Our favorite photos from April 2026 at NorthJersey.com and The Record</t>
+          <t>Free cash flow per share of Gedeon Richter Ltd – OTC:GEDSF</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bergen Record</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxNM2Q5ZzBVU0VMcjkzb09LVXVYNmZ3VXp0OVhKX1I0X200bm1Tdk02YWNlS2VtQXd3aU5ZbS1WdThKTGVxUTdoZU9ibFl2aGtFOFJEZGIxTTAzQ0J0cTNRNVhfeHFBOGIzcE9McDRFMXVYZENMN1Q4T3g1YTFGMVZxa0tJXzlyWXlJam1mT2NVcmMwQUwyZTFUaTZvOGdxcUZUeG1IVXh5bGp4RE41Ti1kQmdZTDFtaHpQdXl4QzU3OXRId01Wbzg1Mm5YWW1sT1FCY2w3R3E4aXRwZGk4dl9NX1pCNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNSmtYNWxmUXBxSk1ET2tUT1NHQTI2RWRWdXYtelQxQUNhQ1h4SEV6VllBY00xQUVwSEpVYXd3MVFPcGp0MnlIMjN1a0E1ODh2aW43X1dyeGZVNUJQVlpXcVJqNFl4UThaY2JQa3FqVUgxSEQ3R0plSTZQWlJ2c0dUcWhtSnR0aEJZRVZWNUNqTlpPYlZTZXhweUtFaVFjRkhkandzcEFEdw?oc=5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>11-05-2026 13:05 UTC</t>
+          <t>11-05-2026 01:36 UTC</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ASEAN, EU leaders call for bold sustainability action in Cebu</t>
+          <t>Department of Medical Service Administration, Boehringer Ingelheim sign cooperation programme on NCDs prevention</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Daily Guardian</t>
+          <t>vietnamnews.vn</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNWjZVcXktMFdfOFJNUm5fMEszTl8xd3I1NTRtVXN3aVBMYzE5ZE95NnNjanRXUGF5cWlCbWpmUEN0VXdYNHVsU3BqczBVbFUwVkZLcjlEeHp5RGZLY09UeFJIU1dIcC1xSnR2Tk1WLU9iUzFMNGw1QmljQjNValhYb1Babkp4clZBRWJSTHl5V1lndk85QlpWSEJn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxNeFNkYlZobVZMeldmNmpZdkozZVItWXNaZ2dvczMwQkdpM29rTFhkNVJjbGxhTml1Zi03enRGUTFtVjlKNWliSWt1a3AwV3hMTi1NaWRZcC1uRmpDWW55V21fOEM1RE1IVDVCRGI5TnZaek9KZGdkY0lhNlZqeXoyVWUzTElpQlNxOWRvQ0Z3WWtXX0w1bVdQekMtQTBoeHVMRFk4QmZIcExzOFdHa0JjUFJUSWc5NTRfRWVmYUZuVFZhWjNXa3JBajdUU2t0U2UzVE1UdUZpWXNraURxTjFNYVJrRzBJMF9FblNF?oc=5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>10-05-2026 16:47 UTC</t>
+          <t>11-05-2026 13:33 UTC</t>
         </is>
       </c>
     </row>
@@ -787,22 +787,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Partner’s Bizengri cleared by FDA for ultra-rare cancer days after winning priority voucher</t>
+          <t>Ribo and Boehringer Ingelheim achieve third milestone in siRNA program</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BioSpace</t>
+          <t>Scientist Live</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxObUJKWlE5RkFUcnBxMEFBLUdWUTctdUhrbVFUZXF2bzRxaHFRS2FRdXFWaV9jNW5Qd3FkREF2aTljUFBqUjJZN25fdTcyUTZBaVI2dzc2Zlo4MDRqYmlKdERXdlQwRjdBN3Q0YjhCU09OT29DRW1WSUJ5RWNHTjhlLXFkb0UySFhPS3ZEYUxyb1kzLVdqU0p0UWV2b2ZIWkhXN0JjZVdLcHg1RURPb053emlhdEl2eHBhbnZj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPeTBwdUwzSGpuR1g4SjRRU3J4TmRFX25sX2E0bHBDZUxEZV8zSGpkaTZwcWNfSkpzQ1VJdXY4ZzlCal9UTmM5YjNQVmota2JqNE1FVTFuWmlIZUQ2blcxUlBRNGV3YW1QdVdic0pobFg4NnBmRFRpeXN2S1I1TVh5TE5TTl9oSVZuakNMcEo4dU1WenhPWDUxYTJEckQyaGxla0hj?oc=5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>11-05-2026 11:26 UTC</t>
+          <t>11-05-2026 15:11 UTC</t>
         </is>
       </c>
     </row>
@@ -814,22 +814,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>IQVIA Q1 Earnings Call Highlights</t>
+          <t>From discovery to commercial HQ: Switzerland's talent advantage</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>sharewise.com</t>
+          <t>S-GE</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPdjF5MFRVdTZQWWdzUi1IaWdvWDhxa1JpU2FuOWc1WjhFZ3k2WFFrTnc4VGZIbTFmQVNMMXoxUXprTlFUbnNGbWMyWEZqaG5lczBKMVhka0J0ZUdEV09lUWs4Z1pTSlhMWVJKckktVW11NmVwT2lTdDdCZWJmSzVCaXlNZ1lJSmpZcVpDV2hYanpnMy03eU9mR3kwTW9kMEpVVHdV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOT2RhTWN6dGVfVjlDeGxhUjZ4aUxodktyWkwzV3R3MVlWWUJsWnB2cjhUQWhtdFczRzJMeXZBcC1EX3ZsVEc0elJZaGJlM25GSEtmd1VhRzlyU1FsWlNtMUphUnRMbDJBWTZUZFlnRFFhVURQMldxMVpMeC16bVZCYU9yVUdEMEg4OUFoeC1sWktGWkIyR2l6NDI2cXB4aGNEWWxhbmZmeFloRW1TSEE?oc=5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>11-05-2026 05:07 UTC</t>
+          <t>11-05-2026 11:25 UTC</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sino Biopharmaceutical and GSK Announce Exclusive Strategic Collaboration to Launch Bepirovirsen for Hepatitis B in China</t>
+          <t>AI in Life Science Market worth $69.34 billion by 2031</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Minichart</t>
+          <t>MarketsandMarkets</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxNaUpQVzdQX2NuVnJfWmNOV0REY1JCck4xdWZQRXNZQjBXQTF0OU1MT2M4VHpEb0E3cHROaXFNcUdocDZadFRpMzM3NktXbTIxR29yNlRwLUJ4cVRjV2FjTlZxbDlTaDlMSDdTTm1EWEtiQV9lUlR0dHV2TmVSckZ4a0N6YXNHLWhfTGFsQUllMDV2MEo5TUcwbG13bVlwTjR5aFFJVFlTVlI0NHV5XzJUZmtVREpwTmcya0I2WWlIR2JvcmdHLUlNOVc4RGpRZm94UTlQYVVFaGRadUVZNWtPUzJDNEtMX1NoNWFPWDd6TlhUXzh3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE5WQ0x0NUlaUldUU1VucmNKS1plazRoZVNsZ1pjU3Rxd0szMEpIWXZ4RF84bjJGVXdmMHMxYWxaUlg4MFZDaHdnNjhza0NPRTJQRi05UzUySVZUT0NaQ0VzMDRUR011ek5fZGRURVJ0cHNNSnR6aDFTc0x3?oc=5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>11-05-2026 08:21 UTC</t>
+          <t>11-05-2026 09:04 UTC</t>
         </is>
       </c>
     </row>
@@ -868,427 +868,427 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Caliber Launches Talent Intelligence Platform Talent 360</t>
+          <t>IQVIA Q1 Earnings Call Highlights</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bolsamania</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNOHNEWS1FS3pMcko3R2dRLXFkeERpaWJRUGl5YndqdGFIaFlibFJSd2V5Nk1RMU5MSUpPVWlIS2Y3cTVWN0lLbUFqcTJfSkkxTU1md0xER2pIZEs2cUVLaUx2MF91UE5HWVozb0ZRSTg0Y0lmOVJlYW5kY0d2azl1T09fR0pyT0FhMDBFRlUwQTdPd1VpRzI1eGdVR0FoeGM1X1o1Uy1SN0hJdkEwUEJwVGw0bUIyYmx3YTE1UExYXzVBVlBL0gHEAUFVX3lxTE04c0RZLUVLekxySjdHZ1EtcWR4RGlpYlFQaXlid2p0YUhoWWJsUlJ3ZXk2TVExTkxJSk9VaUhLZjdxNVY3SUttQWpxMl9KSTFNTWZ3TERHakhkSzZxRUtpTHYwX3VQTkdZWjNvRlFJODRjSWY5UmVhbmRjR3ZrOXVPT19HSnJPQWEwMEVGVTBBN093VWlHMjV4Z1VHQWh4YzVfWjVTLVI3SEl2QTBQQnBUbDRtQjJibHdhMTVQTFhfNUFWUEs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNbzFiSEtTRUNBbmFzeEd0bW1lSjZKR3ItTzdFaHhkMXAyaEYtbTEtM0NMT3huWllWZEVhSUktUlI3WkV0ZW9uSmdVUk1SVVBOeXNnU2U5V3c4UlpwSXdXMHRJSHFYV2llN3BYWGNYYVpSVXZodkRuWENTdERkSm9wbUZ6TUlJdEdKeEFHNFZZcFdjNThtYmFKX2l3?oc=5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>11-05-2026 11:05 UTC</t>
+          <t>11-05-2026 04:04 UTC</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Hikma</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Hikma Pharmaceuticals PLC stock (GB00B128J450): Dividend payer with buyback and growth plan to 2030</t>
+          <t>Lung Cancer Therapeutics Market is expected to Hit US$ 55.09</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>openPR.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOSzhCTk9DbGp4RUpKUVZGekV1VDNBLUJkRGZrbWl2U05hN3p3clM0NXQ2UDN0RDUzRk1rMlBNUWxla2RZZFVwbDhhRlRsbk9XODJ6SFVja1NyVnhYbVZ2ZlFERzVJRllsNHc3STcwX19LZTRfTXp5NEpxeVNYTmxGdVdtN3FFVVZqMzlwOXdwWFpRRkloSTFrRWFrQmpGT0ZVVmJHQkpoQWlOZmhxSDR5enpaNnRGQmZMYjRsUTVITFM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNdmN5WFFLUXhLYXlkVmZmRzlPeHhYNy1xZkFyY0ZDRHpoYXowc0RKVUx1ZFQtS2NfVkVTamg3Rl9lOGpadWhwWFZ1eWZ1UkpZYVJGNkFVS0xzRzgxZE9LcHgzRjBYVk01NzVjODN6cE4zNHB4Y28zeXVnSEc1X3ZOX3I0Q1pqamFPY09nN1k4SEh0clBaZGFQWjB6bw?oc=5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>11-05-2026 08:03 UTC</t>
+          <t>11-05-2026 12:55 UTC</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Hikma</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Hikma Advances $250m Buyback, Tightening Share Count</t>
+          <t>Our favorite photos from April 2026 at NorthJersey.com and The Record</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>Bergen Record</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxON0JtU2huZ2RTcEYwaUNRSE1fTlNxT2dPVzBwektDckx3b05zSTBPSHZPYzhIRzhRSmx4UlJlLXFNNm00bExlVW83NjFHZnhham0wbnY1WEkyU3gwRDBFZTA5NU9SaUwwLXF2Ti1fYVV2UzhpYkpNU3Y3UU9wZktkN2RzZjgwcUF6WUdwWm0tNVlwSVhheVk0YUpPYmJnMnRwU1Jkcg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxNM2Q5ZzBVU0VMcjkzb09LVXVYNmZ3VXp0OVhKX1I0X200bm1Tdk02YWNlS2VtQXd3aU5ZbS1WdThKTGVxUTdoZU9ibFl2aGtFOFJEZGIxTTAzQ0J0cTNRNVhfeHFBOGIzcE9McDRFMXVYZENMN1Q4T3g1YTFGMVZxa0tJXzlyWXlJam1mT2NVcmMwQUwyZTFUaTZvOGdxcUZUeG1IVXh5bGp4RE41Ti1kQmdZTDFtaHpQdXl4QzU3OXRId01Wbzg1Mm5YWW1sT1FCY2w3R3E4aXRwZGk4dl9NX1pCNA?oc=5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>11-05-2026 12:25 UTC</t>
+          <t>11-05-2026 13:05 UTC</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Hikma</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Kurds, Sunnis reach cabinet deal as US blocks armed factions: Official</t>
+          <t>Partner's bispecific Bizengri nabs FDA national priority nod in rare bile duct cancer</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>rudaw.net</t>
+          <t>Fierce Pharma</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTFBkWEFYNWFQZlJzeXgwcFlXbUZnRFREcTBhSFZYS3BtV2ZBYmY0UjNCb1dXYW1US2gwUnBNamNjWXByYy1NUGtXLU81SUVTTTB1SnVlcHZiSnNxOUpHVzlTOHlENlltUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPX05UVUhGVkNiYlpRanV0LUk1QUVMWm1SdlVWVkFVcHFETjRnZWRQbmtZR0hLYkl2ZG81OHBoa1k5Y0Vib1NDc09YRmdJdlFZSGx4UE1YUWxnSDJkODFRaTRrZEZnTXpRTExadVBtcXBIeTBKNFNSUWV0a21wUk40NnNrZWlNY1lwdG45YXNuYTA2SmtQcnVBVHJvdG9Zd2FWV2JLaGNvYjJtVGFKN3VzZlpzT1BLOHg1dVB5bkFB?oc=5</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>10-05-2026 15:01 UTC</t>
+          <t>11-05-2026 15:08 UTC</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Hikma</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Dexamethasone Market Size Accelerates at 6.8% CAGR Through 2033</t>
+          <t>FDA Grants Fast Track Designation to Zai Lab’s DLL3-Targeting ADC for epNECs</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>openPR.com</t>
+          <t>BioPharm International</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOVjF6aFlJS3FFZzVVNUl6a0VKRGhFeFdhS3ZEcFVRaFdMRjIxSk5mUkxFaERCdGdTOVRyVFI5LXliUk1ydUxybXdUT3hhY3RSMnFYUFhudmtmVW5tcGM2V1prNXFSLXlKQTU3Q1laVVg3cWtPMF8taGZWTm1tREpFNElIOGwwYkNNQ1JCZzVZQUh6VDVjRld2emVhUTNzNTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOX3hnNU1ybU0zbjFLeFAxbVU2WEU2RGZYZzNlbWFyU0lMQVdodWdxdjEzNGE1cjVxbVp5Z2RDRVdqclRjdHlqUGN0RzhQUkJZT1dUblZfM3pESzdLSmNrSDgyWmc4WFh5Z2dUQXlCRWlqemZUWXhRbG52ZjNMVjZtUHNMN0JOc1NmcDNSR2hhWF9FSlRiYUZ0N2xfdHBjbl9nVERtOFZRVHcxeHFNX2NBazQ1VkhERDJsMHBV?oc=5</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>11-05-2026 07:53 UTC</t>
+          <t>11-05-2026 13:21 UTC</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Hikma</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Al Ahli Benghazi hold Athens training camp ahead of BAL6 finals</t>
+          <t>BioNTech’s Triple Transformation: Factory Closures, Founder Exit and a Make-or-Break Cancer Trial</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>The Libya Observer</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOaTBBeDN6cXdMc1NVS3VQOFp4UFVtVHRxVllLNFBqRVFlaml1ZXF6R3RJaU5pOTFUd01WdHVEbGJtUjF3OUdXYm1zN0RrWXZpSmUxdXkzeU0xekxIX29xYUdKTkdvQ3dhY1ZNdXFJcEw0Y3prTU9jdThIUmk0NHVZUVJYdGtZR3RMQldBOU10M2YycUpnZGww?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPOVFLRl9XaVhTY3Z5TWMzaWJmWXNrRjItOG5rYWV2SW9TdnpJcmhGb2ZVQXRyYmYyT05nVC14cFZJTUpBbGJ0Vk04Y3RIbUJSNDBqcUxvRFpTQU5vUjhTQkVzdmQ3cUpDdkhiZC1tYU1GS3JqT1dLUlBUZ25fR2lDem5ZUmVkRDdkS1oyX3JyNkpiVzljaUJwNDFjenlWei14elE3QzBmdFdaaU16a2FZVkYweVQ3bGx2blVZamZqWWwxYTJmd0E?oc=5</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>11-05-2026 13:05 UTC</t>
+          <t>11-05-2026 15:44 UTC</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Hikma</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Women's Charity in Northern Jordan Valley to Hold Free Medical Day on Monday</t>
+          <t>Progressive Pulmonary Fibrosis Therapeutics Market Size in</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>وكالة الانباء الاردنية</t>
+          <t>openPR.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPNzRBMl8wRWpkSWRUNW41Nk5NNU5YckRmVFRwdnZabjhTa0Q1bVp5cEdwUGtrSkVHZzhGUWhCOFNSZzZxeklZQm82Qi1nQzd3OXlibUpPNW16cXUxNGR0NVVsMlpDTHZZeHlVaWQ5d0kyRG13bTdfN291VU1Cejc4SGlGY0NRelpyMngya3h2Zlh6YWYtM0o5YmVyWEdKMlNfaE1zdlpMNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQdkFXSzVnekpUejR3TlFvRmFIQUlfRW1Dd0xZZWpWZ2ZteTZlSzNqYXgxVUxrN2p5R01XdUJoQlZVN25peHRXbGNMeXFUdWdlZzVwVDJVVXp0eUtSb0QwbVRsN0p6UlF3cTJxeTJ3Sms3d1o4RnlNYWNaY0NqYzU2YUdyVGxBMW16cjh5UFMzOG5NSkJJbWFLUmFB?oc=5</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>10-05-2026 20:42 UTC</t>
+          <t>11-05-2026 14:02 UTC</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Amgen’s New Puerto Rico Biologics Investment Might Change The Case For Investing In Amgen (AMGN)</t>
+          <t>Clever Culture growth strategy gains traction</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>simplywall.st</t>
+          <t>The Australian</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxOWU5WUG1OQjNmak1YTEdFWWROVmM4eHpYT2ZtZEd2Ukplb3F4VDM1UzRRek5xWHJrUGJua0tCbTgybm9CTlFTTHBZUE9FbHVUVHNJOVRvMVRlNEYyQjd1eFJ1MmdZZGRMRWRfOXZ1UmVVLTI3dWFtVWZWRncySnFMR1BRLVhsZVh3Q29YcDB0SzZXQUlQZ1Y5MTdaZkxfLTg3UWNxaTBvY0tqdUllc05VYWhjRVpjUmZJN3BiSVZuRGF2RFJ4Mm9wZjJPRE1FaVZzaTEycEZR0gHbAUFVX3lxTE1LcTVjOEpzY09BQmtjNlJNOGIxUHN4U3d6aG1ESDRjRzNkX3ZxQ0NhVVUzLVg2dFA2N0szc1BscGpHcUVaZHlCUWM4bFBfcDlGWVF0OTN4ZU8xbVdHX2hRMmhJOXd3WXIxLS1TQ0VMZjNKNnJ4U2ZkRk4xWDZvUXQzbjBONlpKUmRNcGFsdUQzc0ZOY0lOV2lncmYxemFmX2xtZDdTM3JUcGZoRk1WZE5uZUtqaUdGUl8yY0xHbGNZWVM1VHJxWVlhMW1wamV6MmpnSDZJaUlCbE9xbw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowJBVV95cUxQWERUTXJKeHpqRUlweDE5Tkk4ZjZObS1TWXhrMDFtajZtUGkySERraHQxak1WNEJEMHdWRng2ZWo3YTN1eVRRdnBpb0NZTlRRXzJMT1hkaXF0bU5LRExxRm52WWVHYThOQU5CSmFURnY0eHFwR2VHZ2JMUEJ3N1Fva2ZyWG1KNDhwQmRXaUxGaTZYeDJ4N0c2SDViRVEyVThYbElUSmE5TFhiZ1pzaURWX1I1WUNOaW9qeUhXYXBFc1BXQ3p2SEUwOUF1RlNRM2JpaVRlV2lLektTbHZEM0F3THZCZ2RaVlRySHpIb3cwOThENE1MZlUzMFJNZ0hoenN6NXpkOThaSENHTnVPcHM3bThDb1NLWjl5WTMzSG1ycnBielXSAagCQVVfeXFMUGxYMUYwNEY0ajVZZG15NkE5cG5RWXVXZVFpQlRtYVMzSUNyVVZmV29HenF0V011RHktQ1B4b0dVYmNmN3JyVUU3bnFkbFBjNTh3alByTlN0cXNwUXZ6eWQ3Y2ZEM2R0NV9kUm1mRElaZWRoR0ZINmo0SVN1MGtpbmwwRE1MMXhQWW9iUDktS29Sc2dmc2VhVkVmT20xUnp1NjZPZXVkaHcxMEE5SC1QSFlvT1hya0VfU05hNFpnNGlCOGNUVkJ0LXlYQXBLSWpFbUdvdzd3WDJORmFiRDRlWmxGZkYweU1qYjhjd1cwTTlYNTJUU0s3Ylhfd1IzckVnWVlMN2N6S0ZJQkFlSlFEWEJpeGNGX0stY2ZiTUpJcTNySmthZFJOVmQ?oc=5</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>11-05-2026 08:38 UTC</t>
+          <t>11-05-2026 00:09 UTC</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Amgen stock (US0311621009): Pharma giant navigates C-suite transition and Q1 growth</t>
+          <t>Sino Biopharmaceutical and GSK Announce Exclusive Strategic Collaboration to Launch Bepirovirsen for Hepatitis B in China</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>Minichart</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQbkkzdWNSV1I5X0FIaFdPQjFnTnYyeDRId1VfZFlkRzVNMXd2NFZ3UVpjT1QxbUFYYW4tSXQ2MXljSzBBU2pXZ29Sa3JZeGVHQ0ZFMHl0dHZneHVXclZvYmFFS3dodS04ODg1VzdSM01fQ2w5QVNQWG5UdjBoaVZRT1A2djFpVFlFakg2NjdSb1lpdV9PNkZsY0FLMmp6MWJfVjVrek85Z0VLWktlaXNHdE0xYTJaaXF6VjdLcDN0Q01FeHd1QWoyVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxNaUpQVzdQX2NuVnJfWmNOV0REY1JCck4xdWZQRXNZQjBXQTF0OU1MT2M4VHpEb0E3cHROaXFNcUdocDZadFRpMzM3NktXbTIxR29yNlRwLUJ4cVRjV2FjTlZxbDlTaDlMSDdTTm1EWEtiQV9lUlR0dHV2TmVSckZ4a0N6YXNHLWhfTGFsQUllMDV2MEo5TUcwbG13bVlwTjR5aFFJVFlTVlI0NHV5XzJUZmtVREpwTmcya0I2WWlIR2JvcmdHLUlNOVc4RGpRZm94UTlQYVVFaGRadUVZNWtPUzJDNEtMX1NoNWFPWDd6TlhUXzh3?oc=5</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>11-05-2026 12:13 UTC</t>
+          <t>11-05-2026 08:21 UTC</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Merck, Amgen double down on bad cholesterol to vanquish number 1 killer</t>
+          <t>Caliber Launches Talent Intelligence Platform Talent 360</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BioSpace</t>
+          <t>Bolsamania</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOLUkyMmlZQVVxOFhvbWY5cHkxSUJXZUY5dHZHWlhxSmQ5cnRsWGZ5N3pZUVc4LUMwOVhKNEVOal85c3FoOW9tYUpkSHFKTEZ0eDlBWmJ4NlhnYVlsOUZybFdLYmgxSjd3empoOU9QdDBfVVBaZjlGOXpQZlQ5cFl1RmdiTFF2UTlFeG5uVlFGSTM2ckF5LWJ5ZElHS0IxZ3RPcFktcDNvNENzRThsLWhmYjB3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNOHNEWS1FS3pMcko3R2dRLXFkeERpaWJRUGl5YndqdGFIaFlibFJSd2V5Nk1RMU5MSUpPVWlIS2Y3cTVWN0lLbUFqcTJfSkkxTU1md0xER2pIZEs2cUVLaUx2MF91UE5HWVozb0ZRSTg0Y0lmOVJlYW5kY0d2azl1T09fR0pyT0FhMDBFRlUwQTdPd1VpRzI1eGdVR0FoeGM1X1o1Uy1SN0hJdkEwUEJwVGw0bUIyYmx3YTE1UExYXzVBVlBL0gHEAUFVX3lxTE04c0RZLUVLekxySjdHZ1EtcWR4RGlpYlFQaXlid2p0YUhoWWJsUlJ3ZXk2TVExTkxJSk9VaUhLZjdxNVY3SUttQWpxMl9KSTFNTWZ3TERHakhkSzZxRUtpTHYwX3VQTkdZWjNvRlFJODRjSWY5UmVhbmRjR3ZrOXVPT19HSnJPQWEwMEVGVTBBN093VWlHMjV4Z1VHQWh4YzVfWjVTLVI3SEl2QTBQQnBUbDRtQjJibHdhMTVQTFhfNUFWUEs?oc=5</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>11-05-2026 04:06 UTC</t>
+          <t>11-05-2026 11:05 UTC</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Hikma</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Swiss Life Asset Management Ltd Reduces Stake in Amgen Inc. $AMGN</t>
+          <t>Hikma Pharmaceuticals PLC stock (GB00B128J450): Dividend payer with buyback and growth plan to 2030</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MarketBeat</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOZXBLd2hiRlVKTmplMEZGYVQyY0I4QmNjRnJaMUFSckQzbWVtbkdqcUVueTluano2UG5NSy1KOXllSHRFdEtVX1g3VUlqT2ZzVEVkUU5hMFRQYTVnSjFjUkFtTGFjOWRZME1XNTlDS0JUVE5zanBEZHZ2ZkZ0ZkQxbjc3YkcwS1FhNHFNRHh4ZzRlMzdna2JuTzY0Q1dwQ1ZhSVV3NmFYalRaZGxEeDZyY3M0RkJveUJ5X0VOUzBsT2ZKZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOSzhCTk9DbGp4RUpKUVZGekV1VDNBLUJkRGZrbWl2U05hN3p3clM0NXQ2UDN0RDUzRk1rMlBNUWxla2RZZFVwbDhhRlRsbk9XODJ6SFVja1NyVnhYbVZ2ZlFERzVJRllsNHc3STcwX19LZTRfTXp5NEpxeVNYTmxGdVdtN3FFVVZqMzlwOXdwWFpRRkloSTFrRWFrQmpGT0ZVVmJHQkpoQWlOZmhxSDR5enpaNnRGQmZMYjRsUTVITFM?oc=5</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>11-05-2026 12:08 UTC</t>
+          <t>11-05-2026 08:03 UTC</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Hikma</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Will FDA-Backed Real-Time Trials in SCLC Reframe Amgen's (AMGN) R&amp;D Narrative?</t>
+          <t>Hikma Advances $250m Buyback, Tightening Share Count</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNelByRm5wQTFfSVNZYVhVQlB4TFZxdGhnVHZ4aTRTQkhEdGcxMUxHTVNXX3Eza1haVHJSWDJfVE53eENqSnQxSDlzT2d4d1d5cTN6blhXWWl0VXJKaGNPbmRZRnNkNUdWY0tEYkFaLVk0aUJwYkpGUTNFblhzaFhkYTBtX0VhamR3UmYyMEo2cHFaWUo0eUZzUUxPeWo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxON0JtU2huZ2RTcEYwaUNRSE1fTlNxT2dPVzBwektDckx3b05zSTBPSHZPYzhIRzhRSmx4UlJlLXFNNm00bExlVW83NjFHZnhham0wbnY1WEkyU3gwRDBFZTA5NU9SaUwwLXF2Ti1fYVV2UzhpYkpNU3Y3UU9wZktkN2RzZjgwcUF6WUdwWm0tNVlwSVhheVk0YUpPYmJnMnRwU1Jkcg?oc=5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>10-05-2026 23:09 UTC</t>
+          <t>11-05-2026 12:25 UTC</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Hikma</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Amgen stock (US0311621009): $300M Puerto Rico investment signals manufacturing expansion</t>
+          <t>Dexamethasone Market Size Accelerates at 6.8% CAGR Through 2033</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>openPR.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOOXZPZzk5SWRDMlY2UVZFb1VSVWRnYXh6dzc5aDBreWlyeTJOcGswTlVGZHdYS1hubkVrTndpZG1mS0VKenlzVnp1YWFaUzZCOGQyLXBvN2dBUExfZlR1Y0pZcC1mSU12OGlYcDJqNGJoU1BLbmR6czA3R0hHbzdPamxtcWJ0RkttOUVTbWt5bmVUamdEVm0wUGpLN3VCT0RNcUFiUTMtT3VwRjVXdUozT25HN1BzZDNBVzRn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOVjF6aFlJS3FFZzVVNUl6a0VKRGhFeFdhS3ZEcFVRaFdMRjIxSk5mUkxFaERCdGdTOVRyVFI5LXliUk1ydUxybXdUT3hhY3RSMnFYUFhudmtmVW5tcGM2V1prNXFSLXlKQTU3Q1laVVg3cWtPMF8taGZWTm1tREpFNElIOGwwYkNNQ1JCZzVZQUh6VDVjRld2emVhUTNzNTA?oc=5</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>11-05-2026 11:41 UTC</t>
+          <t>11-05-2026 07:53 UTC</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Hikma</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Amgen Inc. $AMGN Shares Sold by Securian Asset Management Inc.</t>
+          <t>Al Ahli Benghazi hold Athens training camp ahead of BAL6 finals</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MarketBeat</t>
+          <t>The Libya Observer</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOaFZYUDhac3FiT2xUM3hjVnJQcTAyUWxITWU0QVFZUFIyTDFuMk82NFhVbHJDd3ZwZ0g2LXB6d2stcXhlNGdnbkkxWU9DcUkxVnlQRmIzcGszTm10d1Q3MVlCTWJLUEF6ejBsNy1GT1R2a3RnUFY3eFlnb1VsT2RDVGwxLXp0MWZZTDk5ZnpURE4xSGcxLWhZNF9tSW5hSGZtNFp3aC1EbklaeHF5cG53dlhUbjBxY3c1SmxjVA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOaTBBeDN6cXdMc1NVS3VQOFp4UFVtVHRxVllLNFBqRVFlaml1ZXF6R3RJaU5pOTFUd01WdHVEbGJtUjF3OUdXYm1zN0RrWXZpSmUxdXkzeU0xekxIX29xYUdKTkdvQ3dhY1ZNdXFJcEw0Y3prTU9jdThIUmk0NHVZUVJYdGtZR3RMQldBOU10M2YycUpnZGww?oc=5</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>11-05-2026 10:34 UTC</t>
+          <t>11-05-2026 13:05 UTC</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Hikma</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>AMGN Fairly Valued by DCF at $292</t>
+          <t>Iraq cabinet talks spotlight finance ministry candidates and banking allegations</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>GuruFocus</t>
+          <t>شفق نيوز</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE5FTllKLVFtRGNsMXVlX2lXQkJmazJNSERYMWRqUTEtRUxjeENoOGx6bFJqelVJeENfMVN3dGtLcENVeVg4SE12dnBBSnJjWVdQOHpLYURwVjZ4MWlNVHdSbVYySVJIZU5HVDFhQWxxSVhjMllhd3I0aVh0bw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOdy1tLV9VZVBvSkxybkhvNkUxQnlTYTR6VktUOHpreWFfZm8wbTF0d3JNcnNfalNzRVZOWXprbmtqY3F0TTZkSkpnajBTMkU5Q2NPT2FIeGN6WjNWMWVsV3BsRDF4YkxVdlJGMFViQ05BbUFOMGNXbzZjQkNlWnVJa1d5WTdVc1pIdUhKSXgtVi1rc2FvZl9rZ0Q4UEVFNTFMVWhBR0o5ZENFdWdjM3dvRA?oc=5</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>11-05-2026 12:22 UTC</t>
+          <t>11-05-2026 11:04 UTC</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Hikma</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Amgen stock (US0311621009): Biotech leader navigates patent cliffs and pipeline momentum</t>
+          <t>Women's Charity in Northern Jordan Valley to Hold Free Medical Day on Monday</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>وكالة الانباء الاردنية</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNQzNpM2wyREV1OWlpY1FBRzJ5MUtFWHJuOUxYa0h6dkhWaVNWcDRzeWpFei0welI4NklfN2x5bHB4czFPczlwMnQ5aWYtaDFneXZUWUNnekphMkxIcHp6RFFZdVJ0Q2s5dW44Tk1Ob2dYTDVHVmlFX0cteTBOOTNoVUxXTUV6Q1N0VUxaMWRDQmFPQ1NJRmY0b3lqdFdzbE9DMmR2UFRmVE8xWWc3dURscXpXamhPQThkeGxqbjRVcHNyT3lu?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPNzRBMl8wRWpkSWRUNW41Nk5NNU5YckRmVFRwdnZabjhTa0Q1bVp5cEdwUGtrSkVHZzhGUWhCOFNSZzZxeklZQm82Qi1nQzd3OXlibUpPNW16cXUxNGR0NVVsMlpDTHZZeHlVaWQ5d0kyRG13bTdfN291VU1Cejc4SGlGY0NRelpyMngya3h2Zlh6YWYtM0o5YmVyWEdKMlNfaE1zdlpMNA?oc=5</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>11-05-2026 11:13 UTC</t>
+          <t>10-05-2026 20:42 UTC</t>
         </is>
       </c>
     </row>
@@ -1300,22 +1300,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nicholas Company Inc. Makes New Investment in Amgen Inc. $AMGN</t>
+          <t>Amgen’s New Puerto Rico Biologics Investment Might Change The Case For Investing In Amgen (AMGN)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MarketBeat</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQTHdnTXp1NF9qVnFWbFNxTlphVjBlNGN6QTdzWm1UeXJjM0I0c0pJY0w0MmxaSGFLckZDWEVxZmRMZU5yUXQwS184NHROQzNsTEt1bm0tUkpMSzZ1UjBqYWNHMEZDQ0ZpS1lONWtEYTRuaG1jWFZCMWVQb05mUmdOTjFEU2dMSUdsUHlXNEFJQ0RnZUU5R3pxbzlRMFg3UEJ6OE50QmFNWjJBZjVLOWx6SHN0R0RDOU9adWFRZg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxOWU5WUG1OQjNmak1YTEdFWWROVmM4eHpYT2ZtZEd2Ukplb3F4VDM1UzRRek5xWHJrUGJua0tCbTgybm9CTlFTTHBZUE9FbHVUVHNJOVRvMVRlNEYyQjd1eFJ1MmdZZGRMRWRfOXZ1UmVVLTI3dWFtVWZWRncySnFMR1BRLVhsZVh3Q29YcDB0SzZXQUlQZ1Y5MTdaZkxfLTg3UWNxaTBvY0tqdUllc05VYWhjRVpjUmZJN3BiSVZuRGF2RFJ4Mm9wZjJPRE1FaVZzaTEycEZR0gHbAUFVX3lxTE1LcTVjOEpzY09BQmtjNlJNOGIxUHN4U3d6aG1ESDRjRzNkX3ZxQ0NhVVUzLVg2dFA2N0szc1BscGpHcUVaZHlCUWM4bFBfcDlGWVF0OTN4ZU8xbVdHX2hRMmhJOXd3WXIxLS1TQ0VMZjNKNnJ4U2ZkRk4xWDZvUXQzbjBONlpKUmRNcGFsdUQzc0ZOY0lOV2lncmYxemFmX2xtZDdTM3JUcGZoRk1WZE5uZUtqaUdGUl8yY0xHbGNZWVM1VHJxWVlhMW1wamV6MmpnSDZJaUlCbE9xbw?oc=5</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>11-05-2026 10:59 UTC</t>
+          <t>11-05-2026 08:38 UTC</t>
         </is>
       </c>
     </row>
@@ -1327,22 +1327,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Amgen’s Real Time FDA Trial Pilot Puts Oncology Execution In Focus</t>
+          <t>Amgen stock (US0311621009): Pharma giant navigates C-suite transition and Q1 growth</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPVnRLUzdjbDhzMVJKcVJLLXFlM0RaaGFra2JvVllMYnZtb2lsdkE5bUFDT1hjTUtRY0YxaW96bWZONmc4RWVrQUNPUlFZR3pkbEVIbXBaN3FfZU0yTlRieGc0bnJ3dFF6WVV0M0tySXh6cWZFVmZ5bjI1SDBqa0M1MTFFLTA1bnVMNjdQN0wzZjg2T0FEcUg5UlBR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQbkkzdWNSV1I5X0FIaFdPQjFnTnYyeDRId1VfZFlkRzVNMXd2NFZ3UVpjT1QxbUFYYW4tSXQ2MXljSzBBU2pXZ29Sa3JZeGVHQ0ZFMHl0dHZneHVXclZvYmFFS3dodS04ODg1VzdSM01fQ2w5QVNQWG5UdjBoaVZRT1A2djFpVFlFakg2NjdSb1lpdV9PNkZsY0FLMmp6MWJfVjVrek85Z0VLWktlaXNHdE0xYTJaaXF6VjdLcDN0Q01FeHd1QWoyVQ?oc=5</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>10-05-2026 14:09 UTC</t>
+          <t>11-05-2026 12:13 UTC</t>
         </is>
       </c>
     </row>
@@ -1354,22 +1354,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Cue Biopharma appoints Shao-Lee Lin as CEO, President and Director</t>
+          <t>Merck, Amgen double down on bad cholesterol to vanquish number 1 killer</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>PMLiVE</t>
+          <t>BioSpace</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPUkFKbGFqZjBldWtKODl5Nk9IcjE0WUFXZnNfMXdJWkFjaWNhUXAyZGRlY0NIaG9PMGhza2Fha0xwTFAwakQ3b0Z1MDhmTDVOd0xyNnd4YTRJN2R5VXI5dUZVTktwbkNJRXlIeER4WnhkN1JDUjU3eGhiOU9iREVHUEpPYVBRWV9nX25TVUNidnAwNzMtbmh5YktQalA3WlVtSVIwME4yaDI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOLUkyMmlZQVVxOFhvbWY5cHkxSUJXZUY5dHZHWlhxSmQ5cnRsWGZ5N3pZUVc4LUMwOVhKNEVOal85c3FoOW9tYUpkSHFKTEZ0eDlBWmJ4NlhnYVlsOUZybFdLYmgxSjd3empoOU9QdDBfVVBaZjlGOXpQZlQ5cFl1RmdiTFF2UTlFeG5uVlFGSTM2ckF5LWJ5ZElHS0IxZ3RPcFktcDNvNENzRThsLWhmYjB3?oc=5</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>11-05-2026 12:30 UTC</t>
+          <t>11-05-2026 04:06 UTC</t>
         </is>
       </c>
     </row>
@@ -1381,22 +1381,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>LA500 2026: Robert Bradway</t>
+          <t>Swiss Life Asset Management Ltd Reduces Stake in Amgen Inc. $AMGN</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Los Angeles Business Journal</t>
+          <t>MarketBeat</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNZzBHdTN1VFpDbjc1M2xxelAwcHVtVWVRNE1UZGRXTWxTZ3RjOGJUYkZmVzFLeGVDYndKalNZd3ZUX25lSThnV1BNNWFZVmtleTNhRWpNMkR5bjB6RTdsX21XdkRlTXBwMHc5TnVZTzF3TlpUUFRHZFhwTnBhVDJSckNTTDRIeEZFaUpKRw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOZXBLd2hiRlVKTmplMEZGYVQyY0I4QmNjRnJaMUFSckQzbWVtbkdqcUVueTluano2UG5NSy1KOXllSHRFdEtVX1g3VUlqT2ZzVEVkUU5hMFRQYTVnSjFjUkFtTGFjOWRZME1XNTlDS0JUVE5zanBEZHZ2ZkZ0ZkQxbjc3YkcwS1FhNHFNRHh4ZzRlMzdna2JuTzY0Q1dwQ1ZhSVV3NmFYalRaZGxEeDZyY3M0RkJveUJ5X0VOUzBsT2ZKZw?oc=5</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>11-05-2026 12:38 UTC</t>
+          <t>11-05-2026 12:08 UTC</t>
         </is>
       </c>
     </row>
@@ -1408,319 +1408,319 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Merck, Amgen double down on bad cholesterol to vanquish number 1 killer</t>
+          <t>Guggenheim Trims Amgen Price Target to $340: Is the Biotech Giant Losing Its Edge?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Voice of Healthcare</t>
+          <t>AOL.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNamZyckpCZVZlZlFoVDBlcF9aUUNJNnZ5ZGlXR2dKZlp1ZjBRVEpUYlJMSlQ3UjBEYk10aU8xSGh4Nmc1LTF5UEx1bUpmZkNvbGRzMjlyX3dZWkRUdzRDRk9GcjRTQWN6eXV2WVJTRTVDTXA4Nm9ZWks2TU9oeGxtdEcxcWY0Y2JqNllDaWl1dGJOOW41M2VTSGJNMUhpRUp5el9IYmxwU3RYZ1BQMU1LZEI3QVdtTDk2Y3dFUWlMQzZvV0dPTXVKVlJ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOY0hXVG42cEhDME1pX1RMZ1RCaVNWNmttczBxRUdVRlJUaGpGdVNEeE03dWsxSDF3TWloeFFUaU9qYlFDcEtFd1JDdlh0MS1MZUxGLThtcHVCaHpMc3k2X2EwV2ItVnVqdU1LSFlwZWpPNHhjcEkxZWZaZ1JpZmhLc0hYdFpsdw?oc=5</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>11-05-2026 06:02 UTC</t>
+          <t>11-05-2026 14:42 UTC</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Organon deal impact: Sun Pharma surges 16% in 10 days, nears record high</t>
+          <t>Will FDA-Backed Real-Time Trials in SCLC Reframe Amgen's (AMGN) R&amp;D Narrative?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQTTVubEJfOHU1WnRwYTlWQ21HS3ZMVWlUVlpJMGlIa290U0FaVlE5aHZxbkpnMXB2Rl9wRTdiRTBJZXYzc3JpV2JhbnF3VnFFWTlMMEE5bkl6M25rMF9neGs0MW1NVU5pcFNxUWFYdkVvZ3VfRnRibG1ZWEd4RGNiWWJkV0dJbTkteF9zSTJJQ1BEUkR1bGljNUh2SHZuc3VnM1FKYjFsZUVJbVZPTWJGSDJMUzdTakNKcmloOGtnM2g2ZG92SjVNdnE0VzNWWXN4VmfSAdcBQVVfeXFMTWdGcDk0cXJxMEo0aXdaVzZJRzQzd1FwaUM3T1BvTzVyRG05QlYySW92OF81VHN2OE5maW1pa0pGX29JbFdhNlFZX0JveEJuWGJzNDJjYXV4LURxZ1ItMmFxTzhaekdzTGM5Z19QOUlhRVJXY0lpdTQ0SUxrV0lhT3hZRi1DWHF6VkFSclpkbFhkUXlfbnhDR0RXVHIwYlI1bkt0QkNIY1BXUlcwMFZzTV82Z2wwMzN5TWtIZ1oxb0hSUGFhZXRYSFdnWlY5YVRwYlJOcFp4bDQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNelByRm5wQTFfSVNZYVhVQlB4TFZxdGhnVHZ4aTRTQkhEdGcxMUxHTVNXX3Eza1haVHJSWDJfVE53eENqSnQxSDlzT2d4d1d5cTN6blhXWWl0VXJKaGNPbmRZRnNkNUdWY0tEYkFaLVk0aUJwYkpGUTNFblhzaFhkYTBtX0VhamR3UmYyMEo2cHFaWUo0eUZzUUxPeWo?oc=5</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>11-05-2026 06:43 UTC</t>
+          <t>10-05-2026 23:09 UTC</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Sun Pharma’s $11.75 Billion Organon Deal: Dilip Shanghvi’s Bold Move Taking India to the World</t>
+          <t>Amgen stock (US0311621009): $300M Puerto Rico investment signals manufacturing expansion</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Open Magazine</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTFBEU2t3bEJ0OGMwZWRRNWVVMW9QaG1NYjIwdWY4QUFWSHBZdWctbkcwdDI2Rko2M2ptLW1EdGk2cGpoQ3pFWXBncjB4STBQaDlqdHhmMU55V0NuUHA0dWsxQWhZcEZHWnllTWw2dXA1aw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOOXZPZzk5SWRDMlY2UVZFb1VSVWRnYXh6dzc5aDBreWlyeTJOcGswTlVGZHdYS1hubkVrTndpZG1mS0VKenlzVnp1YWFaUzZCOGQyLXBvN2dBUExfZlR1Y0pZcC1mSU12OGlYcDJqNGJoU1BLbmR6czA3R0hHbzdPamxtcWJ0RkttOUVTbWt5bmVUamdEVm0wUGpLN3VCT0RNcUFiUTMtT3VwRjVXdUozT25HN1BzZDNBVzRn?oc=5</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>10-05-2026 15:50 UTC</t>
+          <t>11-05-2026 11:41 UTC</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Sun Pharmaceutical Industries $12B Organon Deal Marks Innovation Shift</t>
+          <t>Amgen Inc. $AMGN Shares Sold by Securian Asset Management Inc.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Business Viewpoint Magazine</t>
+          <t>MarketBeat</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTFBZdDRfUUNvd0JuLVd0ek80U3N1eG11ZGtEbS1BenBjWU5LMmtXczdCM2V1NmoxZGRpQTNnUXBXa1o1VjQwTlBnSkhjYmthejRaNjBFWnJhZ0I5TzRkaE8tTTZIVE5HRjFTZ0hHV09ZMnRNYnhtc2N5S293?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOaFZYUDhac3FiT2xUM3hjVnJQcTAyUWxITWU0QVFZUFIyTDFuMk82NFhVbHJDd3ZwZ0g2LXB6d2stcXhlNGdnbkkxWU9DcUkxVnlQRmIzcGszTm10d1Q3MVlCTWJLUEF6ejBsNy1GT1R2a3RnUFY3eFlnb1VsT2RDVGwxLXp0MWZZTDk5ZnpURE4xSGcxLWhZNF9tSW5hSGZtNFp3aC1EbklaeHF5cG53dlhUbjBxY3c1SmxjVA?oc=5</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>11-05-2026 06:06 UTC</t>
+          <t>11-05-2026 10:34 UTC</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Risk-reward less attractive for Indian stocks vs Asian peers: Goldman Sachs</t>
+          <t>AMGN Fairly Valued by DCF at $292</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>GuruFocus</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNQV8wdGNDR0ZpNURpXzdWQmdrNmQtVFU2RmdTUnp2RnJOakpGSlFjMHBpUWZ2bWNwbkh2N2kwb2VCempUMDRWSm5CNTNEOXplc1AzN05JOGIzcUMzTGQ1M0RQM0tWWnAyUXVQb2tTQl9QTzdXT1VsT3dSSEVCRlc2RXFjNUM0bXpUUDJpUGpuUzRJUmNoX0JremdPQlJnUzdkNnl1SlNxS3JWclc5SmtPbHFQOHVFN1lEZTlQRDdqaUFaaDlySUt1bmZnVDYtRUlrdGZUYjBlMkvSAd4BQVVfeXFMTUV5aVlVUGN0UnlkeEFKblNFaVFYNTl1QlZzNTh0ZzVaeTR3b1BlblR4d0VCUWVOaEFUckZ3bVlYeW5MSXlRQmlESy03SVdXZEZwWF8td0V4YzFYR0FqdmtTX19US2IxWGx0eGhNVUNrSjNXTm9CZlNUckpXYWQycC04SkdNbUJqMnRCNC1vV1NNdVU5NXdGVXJmRE9IcVJWaE5WUUZJemJKTXVoTDNQbWJtWmlkNllSM0RTZ2ZfNTV5RmZNeUlVTEhqRFV2cEQ5VElySUtHSDNDa0Z4OHhR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE5FTllKLVFtRGNsMXVlX2lXQkJmazJNSERYMWRqUTEtRUxjeENoOGx6bFJqelVJeENfMVN3dGtLcENVeVg4SE12dnBBSnJjWVdQOHpLYURwVjZ4MWlNVHdSbVYySVJIZU5HVDFhQWxxSVhjMllhd3I0aVh0bw?oc=5</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>11-05-2026 05:13 UTC</t>
+          <t>11-05-2026 12:22 UTC</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>US FDA flags three observations at Piramal Pharma's Sellersville plant</t>
+          <t>Amgen stock (US0311621009): Biotech leader navigates patent cliffs and pipeline momentum</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ETLegalWorld.com</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxPT3lOWHVPTlpEdHN6a3NpTE01ZGdkQ3RmRHhnVFhucFNsTUFlSkRSTHB6VVpuMnQ4My1xLUxZbE05QkdvODVWNHBnMzlJRFZveGdEN0J1R3pNY01fcDFodkpNVkhDX0ZUa0Y4aHpKcGxMLXdoVlZKQVNXUG04dEFZcGdjdWdGdEUtX1dnNldERlk5QW1WeVNrd1pTQm02MEhpZHBOelNuVGVBUlMyZUpWQURXSDRUWjRiUlh0bFRlYzZnRU1h0gHKAUFVX3lxTE5udGxGSGt2OThKbHZ2WmZ0SnY4bHBhVkJsZ2VqcGg4TTd2c0hyRWM2RnFtZmsxNV9FTmRDWkxvUVBlNXh2X2VCTDA1WkdLMEhQMVBLSklmOEIwMWtvbkt0Z3BqSUFYLWphRHEwQm1EQWhfaWNJdzJOS0t6VkFwRVhjc2ZyTkxTaDdHSkFhUEN3dkxoM0xvWGpZbjdsQ2hrWS1sNlUyRUg2bTlXOGU5aVh3MGtSSmVzN0ZpVjhJM3lubWFzODNXb2JNVlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNQzNpM2wyREV1OWlpY1FBRzJ5MUtFWHJuOUxYa0h6dkhWaVNWcDRzeWpFei0welI4NklfN2x5bHB4czFPczlwMnQ5aWYtaDFneXZUWUNnekphMkxIcHp6RFFZdVJ0Q2s5dW44Tk1Ob2dYTDVHVmlFX0cteTBOOTNoVUxXTUV6Q1N0VUxaMWRDQmFPQ1NJRmY0b3lqdFdzbE9DMmR2UFRmVE8xWWc3dURscXpXamhPQThkeGxqbjRVcHNyT3lu?oc=5</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>11-05-2026 06:55 UTC</t>
+          <t>11-05-2026 11:13 UTC</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Protists and bacteria form secret alliance to stop Fusarium wilt | Newswise</t>
+          <t>Nicholas Company Inc. Makes New Investment in Amgen Inc. $AMGN</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Newswise</t>
+          <t>MarketBeat</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQb1lDbXdTOGNWcmRCZjdEckgwR3k0bU9aM05ieWY1UjVITWdmQTdvZDZwd2IxZHA1bXVJcDFaTU03bmxfWkk0WkV6Y2dNd2l5T3lnQWVuMzU1TXpYOWl4NEI4RXpLTnJROGwzcVlad1pmQ1ZEZzhVaTYtODJOeEQ5WkM2Nkl0UTdKdE4zY2NBUjhXaTZ4Y1d4OXNEUXNzMEXSAZ8BQVVfeXFMUG9ZQ213UzhjVnJkQmY3RHJIMEd5NG1PWjNOYnlmNVI1SE1nZkE3b2Q2cHdiMWRwNW11SXAxWk1NN25sX1pJNFpFemNnTXdpeU95Z0FlbjM1NU16WDlpeDRCOEV6S05yUThsM3FZWndaZkNWRGc4VWk2LTgyTnhEOVpDNjZJdFE3SnROM2NjQVI4V2k2eGNXeDlzRFFzczBF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQTHdnTXp1NF9qVnFWbFNxTlphVjBlNGN6QTdzWm1UeXJjM0I0c0pJY0w0MmxaSGFLckZDWEVxZmRMZU5yUXQwS184NHROQzNsTEt1bm0tUkpMSzZ1UjBqYWNHMEZDQ0ZpS1lONWtEYTRuaG1jWFZCMWVQb05mUmdOTjFEU2dMSUdsUHlXNEFJQ0RnZUU5R3pxbzlRMFg3UEJ6OE50QmFNWjJBZjVLOWx6SHN0R0RDOU9adWFRZg?oc=5</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>11-05-2026 12:40 UTC</t>
+          <t>11-05-2026 10:59 UTC</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Flipkart Sasa Lele Sale: Power your summer fitness goals with exciting deals on top-quality health supplements | Hindustan Times</t>
+          <t>URI Leads Hands-On Biotechnology Program for High School Students – College of the Environment and Life Sciences</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Hindustan Times</t>
+          <t>The University of Rhode Island</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAJBVV95cUxPajZyd0ZJbUhINHhiMkkxeUVBX21qTzJhTlFQZjJDUGVYZXZ2SmkyQVlWLTVrNjJ0RkxjcElzMUItd005anRWeXYtSS1KeG9rZXB5RUFKUGpIVllzenJybDA3MTQtbF9ad01aVlVydDlDU19wZkR4YkZNbWU0WUhnT3R6d1d6TGk1WXJLdEotOEFRLWlfcTF4TlZVYUxjcFBiVk9mdHdzamZaejBMd2ZjMk5mS0F0ZjZpck9CcXFpcFl4M1dOYWp4MFFUeFpscUphMk1ZcUVfSDBhMGxmSTRZenliUmJJQXZGaTJsUzNiNGxkRE1DUnZPWkF6eXNVdXJwOExLVVc5WkdEUC04MUtMMHBQWVA1ejJNUXJveklCRGbSAaACQVVfeXFMT2o2cndGSW1ISDR4YjJJMXlFQV9tak8yYU5RUGYyQ1BlWGV2dkppMkFZVi01azYydEZMY3BJczFCLXdNOWp0Vnl2LUktSnhva2VweUVBSlBqSFZZc3pycmwwNzE0LWxfWndNWlZVcnQ5Q1NfcGZEeGJGTW1lNFlIZ090endXekxpNVlyS3RKLThBUS1pX3ExeE5WVWFMY3BQYlZPZnR3c2pmWnowTHdmYzJOZktBdGY2aXJPQnFxaXBZeDNXTmFqeDBRVHhabHFKYTJNWXFFX0gwYTBsZkk0WXp5YlJiSUF2RmkybFMzYjRsZERNQ1J2T1pBenlzVXVycDhMS1VXOVpHRFAtODFLTDBwUFlQNXoyTVFyb3pJQkRm?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE96YlNxYzdJaGc3RlF5Q1VhT1VneGZnM1Z5R0xPUFpmYVdkYTFxSDdWVVQtVWU2aXFrLVhRU1dkdmNLR1c2WnR2ZDYyOU9QUjdEQTJsc1E0RWhuTlJhWTZTUl9kNldkNmM?oc=5</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>11-05-2026 09:30 UTC</t>
+          <t>11-05-2026 16:04 UTC</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Toyota To Make FJ Cruiser At Its New Maharashtra Plant In 2029</t>
+          <t>Cue Biopharma appoints Shao-Lee Lin as CEO, President and Director</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ABP News</t>
+          <t>PMLiVE</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQeWxqSVFBS2N4dHRNeThwc3REelNLSFNCZ01vaU5aaU4xV1d4WFV4di10cjBNVTNIZEl4MmRiVmR5N3A5UDdmVjFpdThPMFN2SEk0SUYxT3ZSQnNzNm9aSTRROUR4TWt3dFA0czdkVlFoZ08teUl3d1JoR0t3RGNaZVFzdHpROHBkdXZTVDhhcVNRbXJNZEcxVWNlUWxyWW5wMWZ5VDJxQdIBpwFBVV95cUxQeWxqSVFBS2N4dHRNeThwc3REelNLSFNCZ01vaU5aaU4xV1d4WFV4di10cjBNVTNIZEl4MmRiVmR5N3A5UDdmVjFpdThPMFN2SEk0SUYxT3ZSQnNzNm9aSTRROUR4TWt3dFA0czdkVlFoZ08teUl3d1JoR0t3RGNaZVFzdHpROHBkdXZTVDhhcVNRbXJNZEcxVWNlUWxyWW5wMWZ5VDJxQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPUkFKbGFqZjBldWtKODl5Nk9IcjE0WUFXZnNfMXdJWkFjaWNhUXAyZGRlY0NIaG9PMGhza2Fha0xwTFAwakQ3b0Z1MDhmTDVOd0xyNnd4YTRJN2R5VXI5dUZVTktwbkNJRXlIeER4WnhkN1JDUjU3eGhiOU9iREVHUEpPYVBRWV9nX25TVUNidnAwNzMtbmh5YktQalA3WlVtSVIwME4yaDI?oc=5</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>11-05-2026 09:04 UTC</t>
+          <t>11-05-2026 12:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Standard Lithium (NYSE: SLI) inks first Trafigura offtake and targets 2026 FID</t>
+          <t>Organon deal impact: Sun Pharma surges 16% in 10 days, nears record high</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Stock Titan</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNdjNhSXJOeXhVcEx4TWQxdWt3ZW5EWVZYMWc3dTJsY1hENHhlcjQ0bHV5Y1NRNWVxM0pDbDlyZlBXU1dSNWhHQWp3dUw4OUs3WXFmeHliOUNreEk3RTloMDVXaGEzbzdWWngxcHdmWlpVb0RPMGh6dXdzeEJYVXNHMDRHd2lBUUVqMEJ4TkJjSXNlXzJ2VDY2WWNRSjJZR0VyVWNlR2cxTml2UUZ2UGg0ckJPaFFudw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQTTVubEJfOHU1WnRwYTlWQ21HS3ZMVWlUVlpJMGlIa290U0FaVlE5aHZxbkpnMXB2Rl9wRTdiRTBJZXYzc3JpV2JhbnF3VnFFWTlMMEE5bkl6M25rMF9neGs0MW1NVU5pcFNxUWFYdkVvZ3VfRnRibG1ZWEd4RGNiWWJkV0dJbTkteF9zSTJJQ1BEUkR1bGljNUh2SHZuc3VnM1FKYjFsZUVJbVZPTWJGSDJMUzdTakNKcmloOGtnM2g2ZG92SjVNdnE0VzNWWXN4VmfSAdcBQVVfeXFMTWdGcDk0cXJxMEo0aXdaVzZJRzQzd1FwaUM3T1BvTzVyRG05QlYySW92OF81VHN2OE5maW1pa0pGX29JbFdhNlFZX0JveEJuWGJzNDJjYXV4LURxZ1ItMmFxTzhaekdzTGM5Z19QOUlhRVJXY0lpdTQ0SUxrV0lhT3hZRi1DWHF6VkFSclpkbFhkUXlfbnhDR0RXVHIwYlI1bkt0QkNIY1BXUlcwMFZzTV82Z2wwMzN5TWtIZ1oxb0hSUGFhZXRYSFdnWlY5YVRwYlJOcFp4bDQ?oc=5</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>11-05-2026 12:15 UTC</t>
+          <t>11-05-2026 06:43 UTC</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Assam Guv invites Himanta to form govt</t>
+          <t>Organon &amp; Co. Opens with 23.72% Gain, Surpassing S&amp;P 500's 0.8% Rise</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>The Hans India</t>
+          <t>Markets Mojo</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQblhTZzhsX1VVSW1NMXdHdkNIRG44TXJfREZfbjN1b25kN3dYWmdMVWR6dUhoNkVkQXVHRjVsZkRZbVBIZ3dJa2tjZGQ1TVhGXzM2bS1FREt6bXNkZHB4LTFnYnl4QkxBVll1QnV2RDRNVURPT3NsbkdaRXdLM0g2azB6YVNnTXBPeWt3c3FuYm1qcER4UVdSLdIBmAFBVV95cUxQblhTZzhsX1VVSW1NMXdHdkNIRG44TXJfREZfbjN1b25kN3dYWmdMVWR6dUhoNkVkQXVHRjVsZkRZbVBIZ3dJa2tjZGQ1TVhGXzM2bS1FREt6bXNkZHB4LTFnYnl4QkxBVll1QnV2RDRNVURPT3NsbkdaRXdLM0g2azB6YVNnTXBPeWt3c3FuYm1qcER4UVdSLQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNNlVNbkRWRm5TWjE4MDI0ZTYxd25uWWtYNXBaYXlvOTlIZXV0dW1rWUNqTXc3dlEyOC1RaEpDTXpOcVF2UFI0SmU0MzJzZnh1ZkNBVmZnNm1tNUZGSTIzUTdNUDBISVhfZUMwcktGWjJ5c2xKMFFmSUkwdElkWS1MZmhWWWNqSU9DWFlwZFJURDVIVGZDY2lWanhwM01BbzlRTnAwTlYwWi1pR3JsOGYzWWhYMU9mYTA?oc=5</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>11-05-2026 00:50 UTC</t>
+          <t>11-05-2026 09:46 UTC</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Toyota expands India footprint with new SUV plant planned for 2029</t>
+          <t>Sun Pharmaceutical Industries $12B Organon Deal Marks Innovation Shift</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>sundayworld.co.za</t>
+          <t>Business Viewpoint Magazine</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNZHVrS1dQNVdTNXNjMWt1bU9Mblc4M29nbEI0V2FMQkR0cGRjenBBeDViVlZCa0xGc3FVbmxHSW1uVmNid2RFdkNza3BVaDZaRHR0VE83LVotZUVWblRDWjM5X2xiZWc2NTRoRGY3UGZOVnliUGNkZjE4cXd2Z3JtaFZPSk5YZWhNMHh1R2lpUWFhRTJ6QlBKTnpycFNqb2lfWGFXcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTFBZdDRfUUNvd0JuLVd0ek80U3N1eG11ZGtEbS1BenBjWU5LMmtXczdCM2V1NmoxZGRpQTNnUXBXa1o1VjQwTlBnSkhjYmthejRaNjBFWnJhZ0I5TzRkaE8tTTZIVE5HRjFTZ0hHV09ZMnRNYnhtc2N5S293?oc=5</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>11-05-2026 11:00 UTC</t>
+          <t>11-05-2026 06:06 UTC</t>
         </is>
       </c>
     </row>
@@ -1732,22 +1732,22 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Piramal Pharma's US Plant Gets 3 FDA Voluntary Action Observations</t>
+          <t>Experts Reveal the BEST Way to Grow Tomato Plants so They Thrive All Season Long</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Whalesbook</t>
+          <t>House Beautiful</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxNQVRfR0NiZlNhS1Z0OU9HXzlUbXNrWjBLQWNxUVFhQ2psOVZ4NjlyQ04tbHVsalNrZVFHVm95NUtBUTFPVlY5c3JBZVZHMnF5dGJMMlJXSWpmdzNibjVIZS1jSkR3R0NJdlZoX1RQejNmMGRZajFSaHNOOS16WWI5SzhXQmREcUItYWl6cXc4UDBObzlwc1BzeEdyTmdGaGd5aEVCdG1ydFJac01WS3dDdHItV0E2Ukl0b0lUcGxkMWNvQlYyb2ZTMXB4LUpweno5ZG5MZHFQNXNjNXgtX2tF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOcU8xcFp1bkxTSWRTOVVTYmctSF9KMzFiLXhZeUV2MHVyV3JuQ09WdDd0ZGNrRjduTkdtRjhhamRQSkNWYXBUaWt5MTZjZDRNSjhyQ2gtQkh2dWhIcmpXNzEwV3ROclFielBPc2JpM3ZqT0Vqak9QUVNHV0FJMmYxQ0pKOVp6REF0TUtoWTh3?oc=5</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>10-05-2026 16:54 UTC</t>
+          <t>11-05-2026 16:47 UTC</t>
         </is>
       </c>
     </row>
@@ -1759,22 +1759,22 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Plant Talk with Brett Battle: The month of May brings the garden to life</t>
+          <t>Protists and bacteria form secret alliance to stop Fusarium wilt | Newswise</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>501 LIFE Magazine</t>
+          <t>Newswise</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPVEM1dFlTUHZaZXlRQmJwWlJqeHhUbnJKZ2dmZ0U1cDNIWHZrWVJEZVNSbVQtRnpzNUxDN3JEbWNKaXBZUkZkTHBERzlyNjJabjNaSDBsMlFmN2RsbTVpOUJ6bVIzR3ZBOGZBenAtc0xYVG83dXdKSmlpZTJoYklNYTdFNzV4eDBYbEx1UWk3enFvUk9NYVgxS2VlSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQb1lDbXdTOGNWcmRCZjdEckgwR3k0bU9aM05ieWY1UjVITWdmQTdvZDZwd2IxZHA1bXVJcDFaTU03bmxfWkk0WkV6Y2dNd2l5T3lnQWVuMzU1TXpYOWl4NEI4RXpLTnJROGwzcVlad1pmQ1ZEZzhVaTYtODJOeEQ5WkM2Nkl0UTdKdE4zY2NBUjhXaTZ4Y1d4OXNEUXNzMEXSAZ8BQVVfeXFMUG9ZQ213UzhjVnJkQmY3RHJIMEd5NG1PWjNOYnlmNVI1SE1nZkE3b2Q2cHdiMWRwNW11SXAxWk1NN25sX1pJNFpFemNnTXdpeU95Z0FlbjM1NU16WDlpeDRCOEV6S05yUThsM3FZWndaZkNWRGc4VWk2LTgyTnhEOVpDNjZJdFE3SnROM2NjQVI4V2k2eGNXeDlzRFFzczBF?oc=5</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>11-05-2026 01:44 UTC</t>
+          <t>11-05-2026 12:40 UTC</t>
         </is>
       </c>
     </row>
@@ -1786,22 +1786,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Is This Edible Flower the Future of Protein? Scientists Think So</t>
+          <t>US FDA flags three observations at Piramal Pharma's Sellersville plant</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AOL.com</t>
+          <t>ETLegalWorld.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxOV1VYVDJnM1Fhc3Y5MmdJc3NjZmRJWHhTNDhpOXpJR1MwREZJTm5wQTNDNzN1WGM1bVZza3piMjV2Q0tqVFJ3WGRQaU8yWDhjZlBjNTlUaGxfY000RGUzU3hSWThaR1FGVzBaRl9JNlVLcUFpbkJlakQzcnRHNV9XUnBuaUV5VVJLU3pR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxObnRsRkhrdjk4Smx2dlpmdEp2OGxwYVZCbGdlanBoOE03dnNIckVjNkZxbWZrMTVfRU5kQ1pMb1FQZTV4dl9lQkwwNVpHSzBIUDFQS0pJZjhCMDFrb25LdGdwaklBWC1qYURxMEJtREFoX2ljSXcyTktLelZBcEVYY3Nmck5MU2g3R0pBYVBDd3ZMaDNMb1hqWW43bENoa1ktbDZVMkVINm05VzhlOWlYdzBrUkplczdGaVY4STN5bm1hczgzV29iTVZR0gHKAUFVX3lxTE5udGxGSGt2OThKbHZ2WmZ0SnY4bHBhVkJsZ2VqcGg4TTd2c0hyRWM2RnFtZmsxNV9FTmRDWkxvUVBlNXh2X2VCTDA1WkdLMEhQMVBLSklmOEIwMWtvbkt0Z3BqSUFYLWphRHEwQm1EQWhfaWNJdzJOS0t6VkFwRVhjc2ZyTkxTaDdHSkFhUEN3dkxoM0xvWGpZbjdsQ2hrWS1sNlUyRUg2bTlXOGU5aVh3MGtSSmVzN0ZpVjhJM3lubWFzODNXb2JNVlE?oc=5</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>10-05-2026 22:06 UTC</t>
+          <t>11-05-2026 06:55 UTC</t>
         </is>
       </c>
     </row>
@@ -1813,22 +1813,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Growing Corn in a Small Garden | Napa Master Gardener Column</t>
+          <t>Toyota To Make FJ Cruiser At Its New Maharashtra Plant In 2029</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>UC Agriculture and Natural Resources</t>
+          <t>ABP News</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPcEV3NnZUQlo5amhSWGlTY1Y3djR1bmlzRXpPS3hLSG00QXptbzEtNEg1TDc0TGV0UEFUcHlHSjNZZTRxMmZxTjBNc0dGVEx4RlNhclZ1RElyMFA0cHBvdnU2NWYzQV9aM0p2YUNkYXpUZTc1OXQwYy1uemJ5bTk0QjVSRXM5U1NCRnVYUw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPdnRtdl9KQ25tUXo1SUN2RnNNMnd4eEZ5WGxDY3dERVU5eG4xSTk0SlRtVmFLeGVvTFRZQzlXUnZ2QThKNHNKMHVrRGNidnE5RjhGX0FETUdZVkExeDFkOHFFZGtjdTJKUHBsQmxUNk55TG04OFpWekxIZXZhTmNOMnhXVFZqS0VMbERNM3FmLUMyYkpLbFB6T3Q0LXFLR2R2a2fSAacBQVVfeXFMUHlsaklRQUtjeHR0TXk4cHN0RHpTS0hTQmdNb2lOWmlOMVdXeFhVeHYtdHIwTVUzSGRJeDJkYlZkeTdwOVA3ZlYxaXU4TzBTdkhJNElGMU92UkJzczZvWkk0UTlEeE1rd3RQNHM3ZFZRaGdPLXlJd3dSaEdLd0RjWmVRc3R6UThwZHV2U1Q4YXFTUW1yTWRHMVVjZVFscllucDFmeVQycUE?oc=5</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>10-05-2026 17:53 UTC</t>
+          <t>11-05-2026 09:04 UTC</t>
         </is>
       </c>
     </row>
@@ -1840,22 +1840,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Brookfield Adds The Nuclear Company for V C Summer</t>
+          <t>Sigma plastics recycling plant ‘total loss’ after fire</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Neutron Bytes</t>
+          <t>Plastics News</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQX2drVUtiUjBXSTRtUGtwTnZSRGtXTDgwV0plVVlXTjdTR2NWWU5sXzFNeTJ0R0NZRThoWllfNkJXQlM0Y3F0Y2p2cnlQSGVtYUxIdnR0ODMtWmJGWVJ5UzlBR1l6Y3NzcEhiTjZWTnc4cm9aOTgyVFBKYnJBc2FwemRmVDJQZm1NcEp1SDhUUFM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOLXVZbGF1SU1VU1hFM1ZncUZaYl81Z1Npay1td2RWaVFPQ1IyTWtiYXpxanRRZnpDNlNKYl83bnZDWFRNUW9wZWdQNzg5X1I5Wks5Rk5ac3ZJNkxJTUxPU2tFR0RIelhnWHZlMmk2V0REOFlxRTRlam4tUHk2OHozTGtRTHoyQQ?oc=5</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>10-05-2026 15:49 UTC</t>
+          <t>11-05-2026 14:55 UTC</t>
         </is>
       </c>
     </row>
@@ -1867,22 +1867,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Piramal Pharma Receives FDA Form 483 With VAI Observations at U.S. Plant</t>
+          <t>5 Foods with More Omega-3s Than Tuna, Recommended by Dietitians</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>EatingWell</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPZDNraU1iNFM4N09wRU5POThUTWIxM2xpMFlGczNzczVxOTRhcjZ1QkE4RHZ3WTFOeUVlN0dSWkkwTWlIOUJYSU9xS0Y5UnVGNkNiNE5uMTRzR2xDdjJ5akxvT25hUk8tT1RDLUl4bGhTd1ZrbDFNTTRQUng3VkF6ektxa1RwbGlHM3NBMlhPZTN6dldaZWVaeHJvSHNySTIzS0RfQkxfU3FfWndwdlRjcmlGVXNhMURXOXhIYUJoVEY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE41Mk8tZTU3ZUdGdlp2dW9rcWZnSU94ZWpGcjFjZjNzc1l4OFEySHI1Z21iTjdKUG9QZndkcWR5WV8xcHhHS21PLTBsamNuelA1aTQ5VVZmSnBRTVBLMm1XSlcxR1l3YWNEYXpPdUlWQ2tlaG0xYjJHb2tn?oc=5</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>10-05-2026 20:54 UTC</t>
+          <t>11-05-2026 13:30 UTC</t>
         </is>
       </c>
     </row>
@@ -1894,292 +1894,292 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Drones deployed amid leopard scare</t>
+          <t>Standard Lithium (NYSE: SLI) inks first Trafigura offtake and targets 2026 FID</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>The Hans India</t>
+          <t>Stock Titan</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPTnpmSnQ0U1ZVbkFwVDBvQ0JaQlBVQXdFYVM3UlIwMTlxaEthN05WZ0xsWVByTUs5VVlmMnczeGoyaWdseWp2dXZrMWNmQTY5S3RTMjFPQXBQRVB4MFRmcW5HS1dsME50b2lWd1c3eXZmQXdXV293WU9ISHpkYjl1UlpTVW0wdE5QTENVYUNDQUtfRnPSAZMBQVVfeXFMT056Zkp0NFNWVW5BcFQwb0NCWkJQVUF3RWFTN1JSMDE5cWhLYTdOVmdMbFlQck1LOVVZZjJ3M3hqMmlnbHlqdnV2azFjZkE2OUt0UzIxT0FwUEVQeDBUZnFuR0tXbDBOdG9pVndXN3l2ZkF3V1dvd1lPSEh6ZGI5dVJaU1VtMHROUExDVWFDQ0FLX0Zz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNdjNhSXJOeXhVcEx4TWQxdWt3ZW5EWVZYMWc3dTJsY1hENHhlcjQ0bHV5Y1NRNWVxM0pDbDlyZlBXU1dSNWhHQWp3dUw4OUs3WXFmeHliOUNreEk3RTloMDVXaGEzbzdWWngxcHdmWlpVb0RPMGh6dXdzeEJYVXNHMDRHd2lBUUVqMEJ4TkJjSXNlXzJ2VDY2WWNRSjJZR0VyVWNlR2cxTml2UUZ2UGg0ckJPaFFudw?oc=5</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>11-05-2026 00:51 UTC</t>
+          <t>11-05-2026 12:15 UTC</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Viatris-Mylan</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>3 Unprofitable Stocks That Fall Short</t>
+          <t>Sweet discoverie­s in a new locale</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>StockStory</t>
+          <t>PressReader</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQVjIzUkxZYTBlTVdIS0FMU01lZEVPU2d0Q1J5MkVSRzdnTEJ6VjNWeUZqMTdTX2pPLTNWS2JMaXR6ZUxHUWtMY3lIdjBKamJwZEpMS2FOa0JVSTRSU3N6anF4RGJ3T1F5T0ZFWTdVZGhhMzQ2aWxzSTNoUTZtTTliSll4aS1HZXBjbkk1VzZEYXpuVG12NHdqZU1BeUVQc2Nr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE8xYWlFaWVVOUlzaktPOE0wWGhiWTdscGpfNFhESjJuWFhxSXRldW5MVVRXZ2VOLThxVWl2dnRvUnUzbEZaaTZVNmtnZnV1UFhxbG5FcnBLcXNLSnY4S1JUb0h3VTlHTkc1Y2ZhdTAtaWR2VDcxMFEtbENhT0xSMWc?oc=5</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>11-05-2026 10:52 UTC</t>
+          <t>11-05-2026 15:23 UTC</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Fact Check: Hantavirus Infection Is Not A Confirmed Side Effect Of Pfizer’s COVID-19 Vaccine</t>
+          <t>Ellen M Mikulski Obituary May 8, 2026</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Republic World</t>
+          <t>Stellato Funeral Homes</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxQM3BfaUJ2YTl6SXprLWxLZUJNUUR1QlFVeURmYUItZnI1cU9oMWN5R2dVVWtNdldnQlh1VnJuOGoxMjNDYzBiS0pqby1xX2tOMkZHM0p6Nk1FcFNqZXB0SWFkcjZWSVNCM190d1JONm5lM1VvUHluU0toSG5mTlB4RlRPZ19qYkRHWGlRQm51RjgzMG9oZ0ZhOGhMLVE3SjdPZS1HaDUzVC1UTGFSaW9iMnl0cHFhQ09yN3BzUkVRcjJITWcxRXdMRnQ5OVdkajliLVpCQmc0Nm42VVFEd0HSAeMBQVVfeXFMTkJneU13YUtYalg2STc5R3ZucC01NkJ5S1VBQ29XSzFTcEk2TmdtM1BIN3ZTSGRRU0lKSFdYTlhnR2lSTXFqdFBfN1cyRUF2eVpXNjZHakRVd3VhZS1tRnY4YlNnUUo3NE9iVmhXU05DN1oxLWRnWFhja045MUMxS1JiSWl6ai1XM3otZTJ1ejZuc1NHU2dlTngzMVFTbkl6R2otd3FuZDVjQnV3RUh4S0p3bUxTREpyVlBpZDlFWnRHWEpCVkRUSzRQMkc0eUsxaGMwNkRPLUQ5YThoRDZPcjFCYVU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE9NVVNQQkRvTE9GQXdoNzZmTjJOU0Zrb0szZ3VGa183T2hiOTY2T0lrZHJlcmJodXc3YnZ6RWZjR3BSNjZ6SWx4SDZNZHhJaDYyZUZvNTJaMlpmb2ZrRlkyVFNMM2k1VnNKbUxncFBBQQ?oc=5</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>11-05-2026 07:50 UTC</t>
+          <t>11-05-2026 15:50 UTC</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Pfizer vs Eli Lilly: Different Bets on Pharma M&amp;A</t>
+          <t>Gardening Experts Swear by the “Chelsea Chop” for More Blooms</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>24/7 Wall St.</t>
+          <t>AOL.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOSXdkOUZGSTNfNEFfNTdQcVdFX2NUWHRIdW1wMVZUVmY5b09BUThCcHRxdk9VejU5elh6NWhldnl0WnZCRzU5ZGJVVEllempCa1NVY0dmaG1yNVhPazh0Rl8yaGIzanJQMkN6Mzl6VXdaYWI5aHREU2tOX0JZbU1jeE15ejZ5QlNNelVUMjZlOEp6NWVXQUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxPd3YxOVVjUHQ4dEFma2UzamRXbjlReWJqREgzZnZQZkZOU3laWEFydU9PeTFUczgxNE1jRjJpNzlTa2t2amJxSW5uVlhsMGRIY1JSQWpTUnZQWHRkQWNJSnZQc2J3c19CN3N1a2FNM2NhcDlJblZfT0tCLU1pRGc1d09lSmpKblE?oc=5</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>11-05-2026 13:05 UTC</t>
+          <t>11-05-2026 18:07 UTC</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Pfizer Ltd. is Rated Sell by MarketsMOJO</t>
+          <t>Toyota expands India footprint with new SUV plant planned for 2029</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Markets Mojo</t>
+          <t>sundayworld.co.za</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOdWQ0d2c2NDdDd2ZTOFg4cEFxWnNTbnU3U3RLeVlIV25NdWF3c0d6UWVpS0R4OHVUeTRUaXFKT21MN3Rva0JLd2V2TThQNmZ6SEF1dW1JQTFfaTlzcmFlalVpUkV6aWpfV1Vyem9FbENyMjFYX0JqdlFoUXVrcUs2VDJrNkQzeU41TXg2dVB1eHh4TFhkMDFJMEFmRGRCZFZQck1r?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNZHVrS1dQNVdTNXNjMWt1bU9Mblc4M29nbEI0V2FMQkR0cGRjenBBeDViVlZCa0xGc3FVbmxHSW1uVmNid2RFdkNza3BVaDZaRHR0VE83LVotZUVWblRDWjM5X2xiZWc2NTRoRGY3UGZOVnliUGNkZjE4cXd2Z3JtaFZPSk5YZWhNMHh1R2lpUWFhRTJ6QlBKTnpycFNqb2lfWGFXcw?oc=5</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>11-05-2026 04:40 UTC</t>
+          <t>11-05-2026 11:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Novavax (NVAX) Valuation Check After Pfizer Licensing Deal And Partnership-Led Earnings Beat</t>
+          <t>‘Daughters of the Forest’ Documentary Review: The Importance of Indigenous Knowledge -</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>simplywall.st</t>
+          <t>Movies We Texted About</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNQUl3akM4dUJFVndFY29Lc1NjRDhhd2lDNm56dGJINUdVUTd6ZjdnRWVBOHRpa1pQMzB2cGc0ejJlZUR3aDBkQzk4aWNFRkpOS05hYlNiUFBZWkVnY1pJaHRJYlJMYVB3c3lYYjN3YzVJU2xZWEcwMDlxN2p1UVhFcWl6eHhuSkZDbUJLUnYzb25EYzZZZC1oSmJYRzFEWXdXemRPdG5laUF1ZnUtOHlablhhbXlBQlEtaFNlTm8wX1BjWlYwMUhIRGdIUFVPVFFSRUZ0dThfUTXSAd4BQVVfeXFMUFJrZFA3TUpoajg3TENMRldwdlFDOWs4VDNIMG02dGgwamlKUEk4TUhpUTFXSEZyaFVnMlI5d1dxSXpCOUFjTjg3MTJXMjM4cHBMYlFBbFJUSFltbS1Rb28ydVJZdVQxT0UxVEVIN1JvcW9XcndCa2hITDR4Qk50X2xTejNQY0E1a0xfcm9oaGhfRWxhdU5oUThTbThocjJTcGxKZE9OeHpoS25mbE1xZ19oVmFkR0EtQ0ZTalVzN0Q0VURNaUM5dklYeGxIcXpqRDdwRE5vNm9FdzN3N2pR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNVHJzQVA0RUxVTmwtTDUzU1hRS0lUSHlKSHVrNVZiUmpOMm5fWGxyWnprc3YwM2l6RUU3d2NLRC00SEk0OEpuZXpHbkZUUm1NUzYtX0dpQnhMWVlqUzR5dnNvU1YxcFRQRHdQanQwYjNFaHFtekM0Z0lFZlRGUHZhWnFXSEFwTnprdjdZUXNQcmxsWlUzdHhHeG9fdVZUYmlYYUNNTU0zejQxZVlHMFRYMjVvd08?oc=5</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>11-05-2026 08:40 UTC</t>
+          <t>11-05-2026 13:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Pfizer (PFE) Stock; Edges Lower as Investors Weigh Ongoing COVID Franchise Pressure</t>
+          <t>Drones deployed amid leopard scare</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MEXC</t>
+          <t>The Hans India</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiSEFVX3lxTE05enJBdV9aXzFpYkFEck04UGp1eFprMVFwNGhta1VmaVE0RzFGQUxWQ1lndlBDeUdoSUg5ZWI1VTh3Y0Nsbll1Ng?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPTnpmSnQ0U1ZVbkFwVDBvQ0JaQlBVQXdFYVM3UlIwMTlxaEthN05WZ0xsWVByTUs5VVlmMnczeGoyaWdseWp2dXZrMWNmQTY5S3RTMjFPQXBQRVB4MFRmcW5HS1dsME50b2lWd1c3eXZmQXdXV293WU9ISHpkYjl1UlpTVW0wdE5QTENVYUNDQUtfRnPSAZMBQVVfeXFMT056Zkp0NFNWVW5BcFQwb0NCWkJQVUF3RWFTN1JSMDE5cWhLYTdOVmdMbFlQck1LOVVZZjJ3M3hqMmlnbHlqdnV2azFjZkE2OUt0UzIxT0FwUEVQeDBUZnFuR0tXbDBOdG9pVndXN3l2ZkF3V1dvd1lPSEh6ZGI5dVJaU1VtMHROUExDVWFDQ0FLX0Zz?oc=5</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>11-05-2026 11:29 UTC</t>
+          <t>11-05-2026 00:51 UTC</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Pfizer (PFE): Faces Fresh COVID Patent Overhang After Delaware Court Dismisses GSK-Linked Challenge to Comirnaty Claims</t>
+          <t>Plant Talk with Brett Battle: The month of May brings the garden to life</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>parameter.io</t>
+          <t>501 LIFE Magazine</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNREdLdkZPRFF0RTdNOE0xc3Y4b3E5dWVPb09fa1JPZnlXZ1lPMGxRd08zVE9ycTk3SkgyaXpvN3FwdUxDR09udzBZYWhNck9hVHBmOHhBdWpFVWFhZlZ4RnhZZEFQTjRoQXBLVDVZNUt5QTFqRnZwbTU2SE1iXzNvNVFMcm1TRHNwRmJBTUxPU3RrZzdXSVFOOFVmNHY3cmlGVnhhNnVzVFpCV05McXE1Ykl4U1pZZTRsMElVT3cxMGRpTm5PTnRHTHo2dlMwMWg3cUNiRA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPVEM1dFlTUHZaZXlRQmJwWlJqeHhUbnJKZ2dmZ0U1cDNIWHZrWVJEZVNSbVQtRnpzNUxDN3JEbWNKaXBZUkZkTHBERzlyNjJabjNaSDBsMlFmN2RsbTVpOUJ6bVIzR3ZBOGZBenAtc0xYVG83dXdKSmlpZTJoYklNYTdFNzV4eDBYbEx1UWk3enFvUk9NYVgxS2VlSQ?oc=5</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>11-05-2026 07:04 UTC</t>
+          <t>11-05-2026 01:44 UTC</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Coherus Biosciences</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Pfizer Strategist Andrew Baum Shifts to Senior Advisor Role Under Bourla</t>
+          <t>Guggenheim starts Coherus with Buy on anti-tumor potential</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>thekeyexecutives.com</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPc0o4ZFNrT0lNZ05QeWdoNTRESU14MjRXRl9IYnNuTlZCMzhaUnEwNkowWXVsVWZNQ1RzSXpVNFE5TGg5MUFwT2VsUnh2TFluMzhXRmE3SFpXMUpwLVBZUXdrSWIyWlN2WWo2WFFSaEJwekVmT193ZTNwNDhHV1A1dVdyTmhGU3R0T21GellrNktLcmdNMUdIcm4xeG1jakl4cVRQaDZ6bnhHX3cyNGY1Z251dENGTjY5?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOYmlHSDR1bmlPYjBlZmplbGI2Wl9ZenFaN2hFYWZmeUVLbzQtc3NnaVFSYk5OajVENy0wcWVEbWtabFIzel94cThCYVF3SGgwb0R1Y3N4SE0tb0VodUtDdFBMWGdSQThRVktKdHREZ21RX1VXY3k1dXpZekhqX2tYX0xzWnVSZjgzNXB4MnNDRjhKME5FQUtfdEpONFI1YVZqU25aQTd1dTg3RXp5?oc=5</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>11-05-2026 08:00 UTC</t>
+          <t>11-05-2026 14:03 UTC</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Coherus Biosciences</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Pfizer Advances Oncology Portfolio While Extending Vyndamax Cash Flow Visibility</t>
+          <t>Ranibizumab Market Research and Global Forecasts, 2020-2025, 2025-2030F, 2035F</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>One News Page</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPUmxSaTdmOHJESG5HaGh3NW5TUWZyeWJsRjlTYkhEbXhOdXZkVVU1NlQyQjVrMWJweE1uQ0dQUm5mNzVEcnRSSEJxeXpndGEteHdudkVrVXdxNWRNLVV2THI5d0RKTU91NzZvbExyUl9fc0RQcnNWd0NuSnN1cUZ4MTZwaVA1M0wtMG5FMVYtVDFjSV9rbHdBREtqUnNPUWJORU1nVXdEQ3NFVEhjU3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPOGV1dUdjbV82TVJlMXphdkJzbHpsTWJZak5fZlZLUkFaQUJJX2F5T29WaG1SdTRvUXZNVW4xMEVZYmFLM0lvdjRaaXhMSkVfVjJrM2d1aW5DNjJRQy1BWGZEQWtsT0xPZnYwNkVTXzBpcGs1T2FvdFdhWWhrY3ZaUnY5TTVvOHQtMFlDT1ZpMDFSTTZTNXpnMW05VFo4TjEzY0wxQ0NkdDJhbk9pQ01JSUotZXprekpkS3c?oc=5</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>10-05-2026 15:11 UTC</t>
+          <t>11-05-2026 14:52 UTC</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Viatris-Mylan</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Pfizer vs Moderna: Only One Pharma Giant Is a Winner In The Post-Covid Era</t>
+          <t>3 Unprofitable Stocks That Fall Short</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AOL.com</t>
+          <t>StockStory</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTFBUUlNVMmVOeE82bDdjNDdadDBSb1ZIV1dVUVBLaEpMTHRFclVVU0EwYXlBNG40STNNSDZNcEVlN0xLOXcxVG41WVBMczd0c1FPX3RvdzY4QlJ3a1VvZjlPUDVHYVplUlRKbjhTVGtfdFIzcXExRzFKakRR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQVjIzUkxZYTBlTVdIS0FMU01lZEVPU2d0Q1J5MkVSRzdnTEJ6VjNWeUZqMTdTX2pPLTNWS2JMaXR6ZUxHUWtMY3lIdjBKamJwZEpMS2FOa0JVSTRSU3N6anF4RGJ3T1F5T0ZFWTdVZGhhMzQ2aWxzSTNoUTZtTTliSll4aS1HZXBjbkk1VzZEYXpuVG12NHdqZU1BeUVQc2Nr?oc=5</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>10-05-2026 19:53 UTC</t>
+          <t>11-05-2026 10:52 UTC</t>
         </is>
       </c>
     </row>
@@ -2191,22 +2191,22 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Pfizer Stock Faces a Fresh COVID Patent Overhang as Investors Wait for Its Next Growth Act</t>
+          <t>Is Most-Watched Stock Pfizer Inc. (PFE) Worth Betting on Now?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>TechStock²</t>
+          <t>Yahoo Finance Singapore</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQY3RROTNhdlFNTTJ2NEdHSXZVTDVJNUdzV0RfQ2ZyaVFoc2VBaGJQLXpRV0dyZzhZRjBPbDg3NENBb3R4YnV1NG96T1YtZFlELTd2MXhNT1pYeFVOeDlHUkJCVktaazlmNHJ5RnBxWkZ5Z2dhVkN1M3ZWNDVVa3RuWWxxSm1CSmtJUlNvRFVHQ3lIR1pFTnpuRjhraVluR2Y5cTF1TVZRS0IwN3NtWWN0Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxPXzRLRUd2WWtRZGpWemQ1dUFWY2x5c19HeElPWnNuSWNSdjZ2ZVNvZmpRcFdRdWlqMi1BeWFNaklLUzdMUkhYVVRfQ2d2cWRWZWtpaC1lSHptNTQxbW1lQ2d5UTNNX3kwdURnWXBBeUJuZVliRXZUcFlNWmlLdmltV0NsSWU?oc=5</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>10-05-2026 23:04 UTC</t>
+          <t>11-05-2026 13:00 UTC</t>
         </is>
       </c>
     </row>
@@ -2218,22 +2218,22 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Intranasal Drug Delivery Market to Reach US$ 24.1 Billion by 2033</t>
+          <t>Fact Check: Hantavirus Infection Is Not A Confirmed Side Effect Of Pfizer’s COVID-19 Vaccine</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>openPR.com</t>
+          <t>Republic World</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNREtYUG8zc3FrMEtGNnQzZlYxOC15WFBlekVBRG1sYUZOSlQzaXFNZDQtY2hnZENKSjRyeG9iS04xdVBUU3E5X1NNazBRMTd5WWlQVk1aRjl2N25XaENPRzFRbDYyaFh2S0VjNUJQWURub25tSXlVaDQwZzlOc1VZb3dLRElGUC1yU1NnNFV2Nm5Fcmx1cEJYX2Z1NDkyNl9nV3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxQM3BfaUJ2YTl6SXprLWxLZUJNUUR1QlFVeURmYUItZnI1cU9oMWN5R2dVVWtNdldnQlh1VnJuOGoxMjNDYzBiS0pqby1xX2tOMkZHM0p6Nk1FcFNqZXB0SWFkcjZWSVNCM190d1JONm5lM1VvUHluU0toSG5mTlB4RlRPZ19qYkRHWGlRQm51RjgzMG9oZ0ZhOGhMLVE3SjdPZS1HaDUzVC1UTGFSaW9iMnl0cHFhQ09yN3BzUkVRcjJITWcxRXdMRnQ5OVdkajliLVpCQmc0Nm42VVFEd0HSAeMBQVVfeXFMTkJneU13YUtYalg2STc5R3ZucC01NkJ5S1VBQ29XSzFTcEk2TmdtM1BIN3ZTSGRRU0lKSFdYTlhnR2lSTXFqdFBfN1cyRUF2eVpXNjZHakRVd3VhZS1tRnY4YlNnUUo3NE9iVmhXU05DN1oxLWRnWFhja045MUMxS1JiSWl6ai1XM3otZTJ1ejZuc1NHU2dlTngzMVFTbkl6R2otd3FuZDVjQnV3RUh4S0p3bUxTREpyVlBpZDlFWnRHWEpCVkRUSzRQMkc0eUsxaGMwNkRPLUQ5YThoRDZPcjFCYVU?oc=5</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>11-05-2026 10:16 UTC</t>
+          <t>11-05-2026 07:50 UTC</t>
         </is>
       </c>
     </row>
@@ -2245,22 +2245,22 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Pfizer (PFE) Surpasses Q1 Earnings Expectations, Reaffirms 2026 Sales Guidance</t>
+          <t>Pfizer Stock Rebound Bet: Why the Beaten-Down Healthcare Giant Is Back in Focus</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>GuruFocus</t>
+          <t>TechStock²</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPdG1kSm1tR3JiNVYyVEJZVDJYaXlJUlY0OXFaSUFjM2N0QUpxaldaVW9iSGx0b21USmRualRuMGhhTFg4YVE1bGh6bVU4MzY2ZEJhQjkzaDVqcFhDaklvVE8yc1llVGhqZG5WYzVyYm92ZUJYdDJCVTU3dkhSUDNDekVBTk02MGltNldIRU5xaVpmYmNGUUlKUTd4WU1MUlhzMWhIeExGeXBwbHpmRkg1cTZaVFc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQYnlmR2pzcExsY1Q5WTRSc3ZzNUc2WC1rVk5PSUxWX05Vdk5YazJGOHplMXZsbWxjd3FkSko2S0JmOTVSeV9leXA3dGM4c1VWcHVDcG9nVnZYbUlRa1g5N1lMc3RqaExWLUZoRkh2bUtxUkFSQVNjLWVaN3poSXFFQXhPVWlkYWNmeno1U3U0TGtUdmUyUl9nUk90amphYWhx?oc=5</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>10-05-2026 14:26 UTC</t>
+          <t>11-05-2026 15:30 UTC</t>
         </is>
       </c>
     </row>
@@ -2272,34 +2272,34 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Pfizer (PFE) Stock Update | Price, P/E, Dividend, 52-Week High/Low | Pfizer Stock Share Price Today (G6OIQgUiUH)</t>
+          <t>Fact-check: Is hantavirus a side effect of Covid-19 vaccine?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Fathom Journal</t>
+          <t>Firstpost</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBEZTlLNVkyYlNqTnhzTHFxWWc0Vlk0ckc5MTRiMDhiZFM2WlBmcGVEMHl6dXoyR2l3aW12VDhsVTRyWkVXLWJpc2hlU1RRM203UnMzcGFPRmlGWXU5NllGbEFwVUpNeERjamJtSVN1eGw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPV3Vta0hyVTg3bUtRd09vZlotcW4zZk12d3QybXl4eGRqV0FmY25Ed0ZRVmEyaGJQc0ZGNTl4R0FoWjU2eGlyb3ZDYnpNTHcydFIzYXdvMDhrSU9JdDlkMUp0X0lxOUNMUVhHbUpCZ1k1TXVjY0V4amVGSURKVGVCZjhkZk1MVXZ0dGU2OWhYSXE1eWM1aTNVeTBmUkFKaUlYRkpOcXBldFQ2c1pNVW54cnNMSdIBswFBVV95cUxPV3Vta0hyVTg3bUtRd09vZlotcW4zZk12d3QybXl4eGRqV0FmY25Ed0ZRVmEyaGJQc0ZGNTl4R0FoWjU2eGlyb3ZDYnpNTHcydFIzYXdvMDhrSU9JdDlkMUp0X0lxOUNMUVhHbUpCZ1k1TXVjY0V4amVGSURKVGVCZjhkZk1MVXZ0dGU2OWhYSXE1eWM1aTNVeTBmUkFKaUlYRkpOcXBldFQ2c1pNVW54cnNMSQ?oc=5</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>10-05-2026 22:48 UTC</t>
+          <t>11-05-2026 15:25 UTC</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Markets Rally, But Biogen Pharmachem Industries Ltd Sinks to 52-Week Low in Stock-Specific Sell-Off</t>
+          <t>Pfizer Ltd. is Rated Sell by MarketsMOJO</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2309,336 +2309,336 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQZjU2N01PZnNRTlg2ODVmNVRJSGlfMC1JdVJndFhyQmg5Y19aZG9iZHFXVW9Ub0dWTlJabUlPVFFrbFNjZmp0YnBDQlpSLVFfSk95bXVXc1ZRWjBEUjl1Z2NXVS1vUWN5VVJwYURYWkg2TTlselN6REY4amRkRFF5RFNlRFZpa2tzN0lpSV9BNndVQ2VHWHhrenNDTFh2M24zM1ZVZFc0Y1ByU2owQkFiUmRxTDgtMzh6T2sxbQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOdWQ0d2c2NDdDd2ZTOFg4cEFxWnNTbnU3U3RLeVlIV25NdWF3c0d6UWVpS0R4OHVUeTRUaXFKT21MN3Rva0JLd2V2TThQNmZ6SEF1dW1JQTFfaTlzcmFlalVpUkV6aWpfV1Vyem9FbENyMjFYX0JqdlFoUXVrcUs2VDJrNkQzeU41TXg2dVB1eHh4TFhkMDFJMEFmRGRCZFZQck1r?oc=5</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>11-05-2026 10:11 UTC</t>
+          <t>11-05-2026 04:40 UTC</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Apellis set to report earnings ahead of Biogen deal closes By Investing.com</t>
+          <t>Novavax (NVAX) Valuation Check After Pfizer Licensing Deal And Partnership-Led Earnings Beat</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Investing.com Nigeria</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNdTNDWWZ6VXNYN1pqaVZvQURxM2NSREFYVlBjVlFSR3ktRk15SVdESWpWRzhmeVZrLV93d0NqU0wxUFBpRmdNQ0YwLWgwSVhjRDM0QjZnc1h2VFd2eXJzaXFzdmFBd1N0WVZ1bFlkaUZGX2hBTmtMOUJja1laZDZkMldWVjVyeTZJbzZrY2xrSVBwVDh1OG5aMUozci15WlRVQ1VfSk5oSjNSVTU4QnVB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNQUl3akM4dUJFVndFY29Lc1NjRDhhd2lDNm56dGJINUdVUTd6ZjdnRWVBOHRpa1pQMzB2cGc0ejJlZUR3aDBkQzk4aWNFRkpOS05hYlNiUFBZWkVnY1pJaHRJYlJMYVB3c3lYYjN3YzVJU2xZWEcwMDlxN2p1UVhFcWl6eHhuSkZDbUJLUnYzb25EYzZZZC1oSmJYRzFEWXdXemRPdG5laUF1ZnUtOHlablhhbXlBQlEtaFNlTm8wX1BjWlYwMUhIRGdIUFVPVFFSRUZ0dThfUTXSAd4BQVVfeXFMUFJrZFA3TUpoajg3TENMRldwdlFDOWs4VDNIMG02dGgwamlKUEk4TUhpUTFXSEZyaFVnMlI5d1dxSXpCOUFjTjg3MTJXMjM4cHBMYlFBbFJUSFltbS1Rb28ydVJZdVQxT0UxVEVIN1JvcW9XcndCa2hITDR4Qk50X2xTejNQY0E1a0xfcm9oaGhfRWxhdU5oUThTbThocjJTcGxKZE9OeHpoS25mbE1xZ19oVmFkR0EtQ0ZTalVzN0Q0VURNaUM5dklYeGxIcXpqRDdwRE5vNm9FdzN3N2pR?oc=5</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>10-05-2026 13:41 UTC</t>
+          <t>11-05-2026 08:40 UTC</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Biogen: FDA Delay on Subcutaneous Lecanemab Seen as Timing Issue; Hold Rating Reiterated with Unchanged $203 Price Target</t>
+          <t>Moderna Stock Is Up 6% Today: Is It Outperforming Other Vaccine Stocks Like Pfizer and Novavax?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>24/7 Wall St.</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxNQzNsenViTVBUb05nZXBHNHVsNEc2cDNLOHZocFV6V1pJaEE2aG8wYV9oRTQzYnhpZk4xNEJ4bExUS2x3Y1ZmNklKVFRtbWVSRWFEZHJkMFoyaUZkOVZIcWlRSGZRMVp2RkhlRTNkS040b2RxaTk2Ym1OVUVWTEdUTXpRSkVfeENkQmFfZnBTY2lyZFlzR2RfM0Y1Mk9HQzRIUFpJbHpmMWI5b2FwVllrYzAtc3FNcXpfNTZ4QVNHZWVyQ1lnbjl1MGNVSHM4Q0hBeTZlTGlXS3J1SmFYQ3VKamgyQXd5ZnFxTmVhVkJjcG5QTURLOGxsM1U0NDZZUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPalpSVDM3LWI4OVFBZUh6b2RBbjNEM3hVaGU5STFybW5NLVYyanBhczZSYmltWERmTEVQdFkxbFZVbjlLTEJUUHVzOWw4emFoRS13RlM1UWNEOGZNcTZsRjZfUmhYTzFRSm0ta0l0Qkxxa1N4c2hURlFISGNuU2Q2aTB5alYzQXh6UDUySmtRVFNzQU9TVW9TT0FOVjJCOEVyTG1hUmtRM3NTVXFSZHFoUUdPOHhvbENBR0dISXdIb2dFNE5OTkxrWE80bXFfMGVhY3c?oc=5</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>10-05-2026 13:39 UTC</t>
+          <t>11-05-2026 14:53 UTC</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Apellis set to report earnings ahead of Biogen deal closes</t>
+          <t>Pfizer vs Eli Lilly: Different Bets on Pharma M&amp;A</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Investing.com</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQS3AxVU5UanZBazhNcE5ZNGNHNEZnS1hfZVZlSzNNSmttbm9PLXh0Ui1pNHY1cWh2THI3YWc2eWRhQkllaC1mUVAwNFlTcnFSSXpmX1NMcGEtWUM4WURtQnpoSjZfVmo4UkJELVdJbVRqTmpPR24yWnhwcFdVT1JkMXc4WVpmbVNzcExKLTNLejA3UWtZTzY5RlJYWktkNWRyanFEMTM1Q05SZUg1VmdwUjM3Z3NYZEoycnhJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNSEFPZGZOM05pZWRTYlpCT25VbHRfWkhhci12aFBZcUpKc0QwYXJJX1hJNzY4d09IdU5yc1VXZmxkQmFVcDZUTE95MFh4TTdjcDJHcS1mcjlOdVdfLUxjU2lPWnY3OEQtYllnVXFUSzMzUGhSUEpKay1nUlhBZF9DVW5qSGxsNm9JQVJON01XdHRUS1pIMzY0d0xZcUZCblk?oc=5</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>10-05-2026 13:39 UTC</t>
+          <t>11-05-2026 13:05 UTC</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Dr Reddy’s Q4 Preview: Dip in revenue, net profit likely</t>
+          <t>Pfizer (PFE) Stock; Edges Lower as Investors Weigh Ongoing COVID Franchise Pressure</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>BusinessLine</t>
+          <t>MEXC</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxONnA0SXA5RDR1VmlnLVAxclB1NXhRUXpOaHotbG40MlBrWVQtOVRVUVNyYVhuc3FEWHdSNDZrU0dXNWxNNkJwWGt6cUV2WGRLYnNTLXlCTExrTWI5cUo1SHJ5ZDhBR1ZMRUt2Ry1wWjVUTm9ndkFUVkVlNWJJV1ZuZHBiXzMzLWZwRjhkbWgzcXRRTU5ZQmg4Ym50dFN2V3N1ZUdRWk9WTi1RWFFpMkFzRVh3NmhjQdIBvAFBVV95cUxNY2RVaDRDZ21lQlVrWWZEdHdWUVdUbFNwYzBqZ3JzbWpFSU1nb2ZYbTR2Y1BRZm9vNTBVRS12dHFQZmhzN2M4YTg4TjdxNi1ycm42cTBrUkFKSTUwcG5OWVRJN0UyR20wd1BVQ3V2aWRaakowcGJNY09BdWRKTEwyenNzWGR4N2QweGVXRDBnd2p0MllKQnBIdjRfSXNGdmxhYm1XUTFWa3lXNzBxOWRrdWNDUUVISjlXQ012VQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiSEFVX3lxTE05enJBdV9aXzFpYkFEck04UGp1eFprMVFwNGhta1VmaVE0RzFGQUxWQ1lndlBDeUdoSUg5ZWI1VTh3Y0Nsbll1Ng?oc=5</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>11-05-2026 10:41 UTC</t>
+          <t>11-05-2026 11:29 UTC</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Dr Reddy's Q4 preview: Lower US sales to drag earnings; profit may dip 34%</t>
+          <t>Pfizer (PFE): Faces Fresh COVID Patent Overhang After Delaware Court Dismisses GSK-Linked Challenge to Comirnaty Claims</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>parameter.io</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPTVpUbTRiRFJWSXZCaFJnNHhZX2dBelRkMnR5X3RtcDJBSDhRSzZRYlVYdEVic0V3YktqclJWX1FYeTJoWmc5UFZBRmlmMVpTSUxVMGdsLUp2dVJyLVFMcVUwV3lvYVN6a0lNOHpfU2VsZlZ5U1d6ZzFfNnJvVndoelZVcDQwTjU4ZU15UTVvcGMxcmstTnFVYm11bHljTEpoM3E5TVRBUUZmREtMc3VMemg1eWczVkVNV1dNTTJ5NGpKQzRSRzlVYXBnY1R5V2pMZHgwN9IB2gFBVV95cUxOVEdITUlxcURoZjZTV0Jlb1Z5Zkxqc1JYZlhGV2ZBaG9lOGx6NGs0cGxBcWVBa2twc1FneDhWeTl3dUQ0NFNIWFFLcW5GbGhQNU1MVU1Wc2JlWnNvbDFYc0pCX250T251SHF1VjhiOE04S0RrWjZHNXBzd2x0cWIzRkxxaThHbWdpdFhZZnM4Q1Y2Mk5MaFdlRk5SR2dTLVpwZjJTMTdHZmttSlUyZFlEWEZtUHlwWmFpQ2dsUHZtNHRxX3dqTVpyMkFWUVRjcEhtQmNWU3pyQVNYUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNREdLdkZPRFF0RTdNOE0xc3Y4b3E5dWVPb09fa1JPZnlXZ1lPMGxRd08zVE9ycTk3SkgyaXpvN3FwdUxDR09udzBZYWhNck9hVHBmOHhBdWpFVWFhZlZ4RnhZZEFQTjRoQXBLVDVZNUt5QTFqRnZwbTU2SE1iXzNvNVFMcm1TRHNwRmJBTUxPU3RrZzdXSVFOOFVmNHY3cmlGVnhhNnVzVFpCV05McXE1Ykl4U1pZZTRsMElVT3cxMGRpTm5PTnRHTHo2dlMwMWg3cUNiRA?oc=5</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>11-05-2026 08:49 UTC</t>
+          <t>11-05-2026 07:04 UTC</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>IDA Recognises Dr Vijay Anand Reddy For Cancer Care</t>
+          <t>BMO Capital Maintains Pfizer(PFE.US) With Buy Rating, Maintains Target Price $34</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>SMEStreet</t>
+          <t>富途牛牛</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQR3VpX0l5ZVhjQzk5ZjlVOFJ3Q3BsaUVCZEo5amZyVXV5c05nRFhPTjE4Zi1BS1VJZlk5NUZ5cmtiNGN3emRJZGdlQW9sT0Y1MTNmOGVBSnZ0VjBFNFRIOGVwWEtYWDVOSWpkVUdFaTlQRzRuSHdQaXBNUjhZR3NKNWEyTFR3NXUwdUhyM09aNnJvd2vSAZMBQVVfeXFMUEd1aV9JeWVYY0M5OWY5VThSd0NwbGlFQmRKOWpmclV1eXNOZ0RYT04xOGYtQUtVSWZZOTVGeXJrYjRjd3pkSWRnZUFvbE9GNTEzZjhlQUp2dFYwRTRUSDhlcFhLWFg1TklqZFVHRWk5UEc0bkh3UGlwTVI4WUdzSjVhMkxUdzV1MHVIcjNPWjZyb3dr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOMUhjTUFPSTlGSXlMMTU0X01KTVhkUFp6Mk0xdjFMMjkyeDRIRHI3cVVqQkNKRVFfSUNSWEpsSTh6eEJHdk1BcmVIZEVqMG81enZ6VlM4VFNMckxMalg3SEVrbHFZQkRKUHZzVGZlZ2tGOEN4TmQtNzdUVzdWeHZ3THRVQWhObENaR0dQSUpDX2x1QUNMa3VLbW5NR2htUmQxV20xVUZObXFrMlFh?oc=5</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>11-05-2026 04:46 UTC</t>
+          <t>11-05-2026 16:01 UTC</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Q4 Results This Week: Bharti Airtel, HPCL, Dixon, among 200 companies reporting numbers</t>
+          <t>Pfizer Strategist Andrew Baum Shifts to Senior Advisor Role Under Bourla</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>CNBC TV18</t>
+          <t>thekeyexecutives.com</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxOUkFlTkw0aEpsbWVIRGhvdURjVEJNUTkxSW1YNkljRHlTRVBRVVpOdnpNaE9PT05IN01rLU95dW1RLUU0VlQzc1ptczgyVzRodC1FUmRvVTN5ZmxidnlyT2wwc2JXWFEybU5fVi13NXI2VFdpekRXX2ctcVg4NWsxQ2JrejM5bXdZZldNMjZZTGtrWWpwbzcyQmp3Yld0dlZUSTVubGpTMzFidWE5ZDdxdWgzVFN0NWVVUmV1Ym5aOXRBbGpNS1pUN0d4bWlXRmdfVGhRN0FzZXBIQU1PQ1d5aXhmU1pKTWlKbWd2NWIwYXbSAfYBQVVfeXFMUEZTelYwemVFZmdoTkMzM0xGMUxfb3dfa0I0QnVNeDBreFl0cUxPdW5sRmQ4dFAyOU5WWjRYTjB6bXJNNjBYTHU0ckJkbDBpOGt5UEI2Z1ZfRHlULXdnRmg5cXdOVFA3XzNCX19kTG1jYkpESGptaFhiVWdTZXdDRzhFc1ZIZHNRcmZkSHprMGpydGVTaTVKenBVdXhYUzJscjEyWU1hY3J6Uk1uT3lYSC10Q3lZTHU1SjJsajZ1OGdGb1JzVGk5dVhHX2xmeXZ3cmtpUTdSdnljQ0hpTG9jNWRmaDFHNkJEbXFmejhNYVRrT1I2RjlR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPc0o4ZFNrT0lNZ05QeWdoNTRESU14MjRXRl9IYnNuTlZCMzhaUnEwNkowWXVsVWZNQ1RzSXpVNFE5TGg5MUFwT2VsUnh2TFluMzhXRmE3SFpXMUpwLVBZUXdrSWIyWlN2WWo2WFFSaEJwekVmT193ZTNwNDhHV1A1dVdyTmhGU3R0T21GellrNktLcmdNMUdIcm4xeG1jakl4cVRQaDZ6bnhHX3cyNGY1Z251dENGTjY5?oc=5</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>10-05-2026 23:26 UTC</t>
+          <t>11-05-2026 08:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Centre plans nationwide crackdown on illegal sexual enhancement drugs, calls it threat to public safety, social dignity</t>
+          <t>Markets Rally, But Biogen Pharmachem Industries Ltd Sinks to 52-Week Low in Stock-Specific Sell-Off</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Mint</t>
+          <t>Markets Mojo</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQMWxjQ0VxMjV1N09FRVNQWXZUWng1LVFibm4zYTNiOTRwSHA3RWNHenFwdjhUY3duS0V5VnQzSEU5cDVKRFN5OXNWRzc3WXlSN3VyUXBxYUZ0YmxOdzR5RkU2UnZCcGF5OER6QXNJVzNEa3F0X25oS1R3eTJXNWhtdjlpT1NteWpWd2IyU0Z2cUFTNTVUUmVYeFZJZ00yOGlEenQ4SklpMWlaYmZYMlRkMG82RXBBVXNZNjMwaVdvVzfSAcYBQVVfeXFMT3Q2MHlNc0RlTXl3N1ViWG9hc3g3R1BjOVhFR3NSY2NXZ0c2VC1sTTVCUGxKdzZDRjhHaHlmZjNhaERfbldMd2o2UmdVaHE1LWFCaFFicHNTeWFwbjczSnlNVTRQckZvdTRPQklfaERLTUhyM3Z6MkpFa0tZbXFVUER4VzQ0ZmtCR0VSdkExb2hvLWYySjFIRDc5UTlVdm4ydVBaSTdNTllqakVuS0Zma0RRVnNQNHRlZkRzc3c1dUh1bjZwS1l3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQZjU2N01PZnNRTlg2ODVmNVRJSGlfMC1JdVJndFhyQmg5Y19aZG9iZHFXVW9Ub0dWTlJabUlPVFFrbFNjZmp0YnBDQlpSLVFfSk95bXVXc1ZRWjBEUjl1Z2NXVS1vUWN5VVJwYURYWkg2TTlselN6REY4amRkRFF5RFNlRFZpa2tzN0lpSV9BNndVQ2VHWHhrenNDTFh2M24zM1ZVZFc0Y1ByU2owQkFiUmRxTDgtMzh6T2sxbQ?oc=5</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>11-05-2026 00:30 UTC</t>
+          <t>11-05-2026 10:11 UTC</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Dr Reddy's Share News | Dr Reddy Share Latest News | Dr Reddy Share Latest News Today (uqC6xl9C4m)</t>
+          <t>Should FDA’s LEQEMBI IQLIK Review Delay Reshape How Biogen (BIIB) Investors View Alzheimer’s Strategy?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Fathom Journal</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE1YelhSYm55ejQ1dXEtY2IyOXVtXzZPTkg3eVJORkpWVktRMEM3MHFKUldCU29mNnB4VldRQUlPcjVKVW5aSmV1T2ttOWV3MnlENWpHdk1RYnNVc2hjdGswTDAzcTdxVU00VTBqcXJfVjc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxNU21MZ1FwejFnVUF3d3h2dWR4Sjd3SGFUVG5OZXNrbDJyU1R3QVpWUFhkbzFub2otems4ZW51OEl2NWRVUkVvMkp5Qkc3ZDBqa1ozMFg1aVN5clZoTDBtVy1jeGVPXy1vNGpfM2ViVGRqWlZSMUVhbzNVTVlTNkpVeEdmM3Nyc0F4T0Jncl9pVXZXOGUzcnVwVG5QTWF0RTBUa05lcVdrZEpRalNtMWJETjBwYWs2TXRhM2NwLUV6NVRoYmJaZUl2cE0xT2hHN2ZlQ1VzWWdxRdIB3AFBVV95cUxOWlhVM2FwX1VKR2JFc0pMUm9NZVBuamdwaDhTVVBIREJNcGNOS282UVUwWkZGbGNxNHRZUk1sQXRGb2JuWGYtUFNYemxMNjY5Y3FWamJqOTNOV1ZoT3U1NGhiSUh0S09wQTUxS2dObThwX0dKM1d1TVlSRlA4N08yYVRlZmtGR0h0UjNFYm84enRNVXRmbHBOMGZsZS1NRUItaWQxNnFJTllkWEJoRWFEeldfM3VIcHdJYmhhUWVob3FPbnZSclp4Z1dCMDVPRzQzNm9iQlVtenA0UjI1?oc=5</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>10-05-2026 15:55 UTC</t>
+          <t>11-05-2026 16:56 UTC</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Tata Power, Bharti Airtel, and 8 Other Stocks Set to Announce Their Q4 Results Next Week</t>
+          <t>3 Healthcare Stocks We’re Skeptical Of</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Trade Brains</t>
+          <t>StockStory</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPU011MzdacXVmV3Yyb0dkRnkyY2JTZ0pIeUVZU2hvWjVSTUpYdVNQQjZMSWhjMnFKY2JFR1N4eDkyN18tUUFmQWpTd3JQcEdQS0pfOHVBRG5IdWEwbVpSVTUwM2Zja3F6WExoaHpSUnZaU3JqbzdlcmdBOW1PT2FKUUpZNVRaeFdwTjJTX2hveTBMd1NsbktEZUxsV1pMcmZVVzVsS0tzQ1lmMFhtenVF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNMmRmcThwU09YREpLaFd1X2ZKcVp1WlRZT2tnR1RpU0gtT3BsN1JHMzFLSTFKb2pzems0cWotZ2J4NXdUcTkwVHBIU3plOFlFZlpySEZieF9MYjcyb3UtUUJvTFFxS182ckR5WUxtMlJ4Y2p3YVhkWTliZDNfWjg2dzRrRGI5WG5feldPQXI3dVl4S3VvUzFNc0EzNS1KY0hq?oc=5</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>10-05-2026 15:30 UTC</t>
+          <t>11-05-2026 10:47 UTC</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>PVR INOX posts Q4FY26 net profit of ₹186 crore; revenue rises 25.8%</t>
+          <t>5 Best Biotech Stocks to Invest In According to Billionaire Steve Cohen</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>Insider Monkey</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxOMEJuMTVPTmpkbzBjTmctMHAzODRKek1WQVFHUlRsaVo0SVloUkMzVDNNb09pcXhsbnRkcHdKc1ZEZmk5cUJTNU5wUHZweTVVdGgwU0F5bFh0MF9UeWQ5dDJ1dE00Mkl1RWItWEo5SWQzMERfV1FRWF9jQUMxcnc4WDFQZzFpblBHUUdNWmdUMW9NYUNVckl2eDJWanp3OEpGS0VNenEtRGlNSHFsbkRVWHVwekUwZnhxVmd3TWw5dHZJeDc2el9yc0hSa1V4MjJhSmpxWGU4XzVLWVJ2Y191VHRPb9IB6AFBVV95cUxNZGhVb0lYLWJYdmxvMXJaWnUwMWZjaE9uZ3hGOHdvVm1mcHhpckF1RjBqUm1jaWgwN0RJZUM0a0d2WlVyRUNqdG43SUhaYXV2WDQ5djJBOW9JT1hhNWtHSHRGWU5TYVl4Y3RCME55ek5QejhNS3d5Vm1mT2ZDUDRfLUotWVNMSkdBRnZsdDZCa0pWY3VSN2RfREotaldPWEwwM2V4dU1pbnk2dTRad0pDaXNKQUk3ZDUwejRLNkpBQWczNDlPaWc0MUF5NGZ5dTYzSlVPdWJ6RmdUenAwR2c5MGlScU45aTJm?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQMjg1MlFfNllZWWtDSHVHc3hlUmFOcjVRZUllNFRraTBGcTJfd2FlVWFfR0ZEVXNPR2lIcDF6Nk15T3gwaVVsUHRHdEZiX29td2pDOTk4TXJ2dVhWbzhLY2gzaWZnRkdmQW5VVmp6OHJiSk9IWEFTMjBMMm1VekpxWjRMUG1OczNZV2piSlA5STVkdHZuMzlZemkyc2F0X1N2X2ViZ3phblJYRE9wNW03ZFQ1aUw2X2s?oc=5</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>11-05-2026 11:14 UTC</t>
+          <t>11-05-2026 04:16 UTC</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Hotel stocks slide up to 5% on PM remarks; analysts optimistic, back IHCL</t>
+          <t>WATCH: Longford siblings with rare disease who 'don't have time' issue HSE plea for drug</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>Ireland Live</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQeWZtNGdkeGRGQnlNekRST0lqWUlWc09JNmE0VGFmb2UzSDU0SEVVVmthbGJYSXVGRmpZMTI5d0diS1pMdTlDNHI3N3FIeDdxTmVxdmJfdzY0TXJlRUlOdUtDdWNXaXV6Y1NwQmpsMld5Mk9KVVgtOG1OdlhCLUM3RlQwS2xiMF9peDdUQTJUOFN3d2NwYnY3cFRMMV9EY0thQWoxTFo0UXpVUHA2Y0ZiQ2NlSGd2ei03QWhISmVycjZNQk1pQzRvYUJaU3B2Z1dDLWd30gHYAUFVX3lxTE8xOUdSQ3gzUGNnSHhFNlRYbkJzOWxmdUNFU0t6WlBmQXpTc1BNaTdFc3VDM2N4RG1fNHlLeUFualhnMmxNVkRVTTBWejZzeEQ3WjJidEVZWmFNZDJ0Yy01cU82V29HMFYxamhSWkR6bGFxX085d0lrRkVSUGdsRHdKXy1DT2RlNUc1QTlFVXlvbmcwckFyVlhZZWJaTkVvdmlwSzJ4Q1paZW9PaDIyRkNEMHJyaW0tdWJMTElwbFBWTTVub2JjQkZ6ZkxGRWFZVU1tR2lEMEZmSw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxNbVQ3YzJUcWNLVHBUa0s2UkxQSFh0eUJRSVlpMUN6bDM2dTFzUzdHN1RhenpUREQ4SHBZOHJoMG5HRjdkdC0xNjY2Qm1DRUNTTjhPM0NJZDg2MjcyQ21WYjMwX3RtV1BSYkdLSWttWVgwd2M5cVpZVUw5VndIZlp1cVFIaUUxMjRaVW1naUZ5Q29nZEd1cEx4aE80RkpRYlY0dHRrU2xWNlo4dHBNMmxKSjdUbkdQd0lidVdLdzI3ZjVhTFlCQW5Sc0twdk9oTndnTlMtTU5kVjVyTzRDZ2RF?oc=5</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>11-05-2026 08:35 UTC</t>
+          <t>11-05-2026 17:41 UTC</t>
         </is>
       </c>
     </row>
@@ -2650,22 +2650,22 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>This Dolly Khanna portfolio stock defies weak markets; jumps 17% on Q1 show</t>
+          <t>Dr. Reddy’s grants new ESOP and ADR options | RDY SEC Filing - Form 6-K</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>Stock Titan</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOaWxsU3ZBZEk5eWlrNjRXUDdPZUR3T0hWaFdWOElvcFd5WDlBcFVTNDBqRmpvMUxJQi1zZDlwazNiOGtST0oxTFNVSTZiZFIwbnRnb2x4SU8wYTZwc25rSnA2b1RuQnE4M0ZHMmZpSDFUT29iLXRaWkR6RkExcktSengtVHhqNHRNZVpxbVVyR2g0YmJQTmdoZEhaWlo3RTRFWF9lRFZWTXdoLWNZbnlVVEJlRENhekM4X1hlWDA0aGFwdXFSczV0OUlDQldFWWNubVV2N2dLNNIB3AFBVV95cUxOeFZTVjY5VHp1S3hGX01oUlptUllVdjJPdDhGYkU5RlZmY1hKMG9nTHdHUEFEY1FZQ2tZUnR1OUlIRFJrY1llVmlkYlpEQTZqNU5HUUVoVlZLdDNBVFBkTFdlRXpQODdsbVFJX3dwVlRsdlpocnBrYnpHMlF0bHBGM3M3bmZHLVAwc3FjeUZsVkVfTFRHNUlVbzQ2b01GWXFJRXJrdjRFSElxc3l2M3VoVWtBTWRFTzF2emxtS3A0TzdzUTFjcTkyQnJXbkcybUlwVjJUajBjR0lJbnUy?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQSkdyclJ3cFJ2X1BOeVdKaktnc25CdEdLUTc5T21VRlVuMHBQNUJRbk5TZkJob0xwV3hsODM0OWpSNXNxMkV1YnE2OWQ4elBjVHpSU1dqSklIVmJsQi1nVVV1TTdBakVLb2FheXlTdDVIUEhkUFBIZVpGbTQ3YU5tQW5yRVhuSVptajE0M1VFZEx3YWVEM2xybzZnZXBKX0JFMGx1Z1d1Y3ZNTk92RmFKLVdSck5faFByb0d0Z2x3?oc=5</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>11-05-2026 09:24 UTC</t>
+          <t>11-05-2026 16:48 UTC</t>
         </is>
       </c>
     </row>
@@ -2677,22 +2677,22 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Canara Bank stock falls 4% as Q4 profit falls 10%; asset quality improves</t>
+          <t>Dr Reddy’s Q4 Preview: Dip in revenue, net profit likely</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>BusinessLine</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxPa1ByNy1nS3VyV0Z3SGJVNDAwZUw2YmpqWW9scTRDTkhOVGF6QVhJbXF1MW5ZakFXYlpVQ0FjREhyQ2R2ZFRsemVtZC1ZazNVTnZTazdwR0oyNGUwcDhlaWt6VmI4OXZHcUlEOVdtRnRrSmwzcFViNFVCN2hYUkZFQmFhUjdoQldBNDNNS0hwSnZaQ0lpc0cxa1pLLUxZelRiWVBQdWJ4LUNwRVhnS19ldlZ3SzRlTVlmZWpLYXU4NmotcThCaUxya2VRd3lxT01CZElr0gHYAUFVX3lxTE4xXy03ZjhlajhSR1ZqQlJLM0p3dWFPN0l4TThhZWJaMGVVVEc2OVczYk9EZzRIR3lJeDNHTGVMMzFoTXpveTMxNlBteGFuMXZ2a0Y4VVpYYWRsRTR0YTVxRGo3bGhPQnphYlB0SktYYkxCOTVWYVl5cklPWVROX1ZPQi1pVnZGT0V0MXdHalVXOU00TjRnVGUxYXgtS1F0cWJPaWNyM1BMaUNHQWpHNzFQRlZNRU5VcjFyVzhIcWhTOTZCYktzelBFNVJDV3d5WG5vWmxkdDEwcQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxONnA0SXA5RDR1VmlnLVAxclB1NXhRUXpOaHotbG40MlBrWVQtOVRVUVNyYVhuc3FEWHdSNDZrU0dXNWxNNkJwWGt6cUV2WGRLYnNTLXlCTExrTWI5cUo1SHJ5ZDhBR1ZMRUt2Ry1wWjVUTm9ndkFUVkVlNWJJV1ZuZHBiXzMzLWZwRjhkbWgzcXRRTU5ZQmg4Ym50dFN2V3N1ZUdRWk9WTi1RWFFpMkFzRVh3NmhjQdIBvAFBVV95cUxNY2RVaDRDZ21lQlVrWWZEdHdWUVdUbFNwYzBqZ3JzbWpFSU1nb2ZYbTR2Y1BRZm9vNTBVRS12dHFQZmhzN2M4YTg4TjdxNi1ycm42cTBrUkFKSTUwcG5OWVRJN0UyR20wd1BVQ3V2aWRaakowcGJNY09BdWRKTEwyenNzWGR4N2QweGVXRDBnd2p0MllKQnBIdjRfSXNGdmxhYm1XUTFWa3lXNzBxOWRrdWNDUUVISjlXQ012VQ?oc=5</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>11-05-2026 09:25 UTC</t>
+          <t>11-05-2026 10:41 UTC</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Marico, Nestle, Laurus, Grasim and 15 others from Nifty 500 hit new highs</t>
+          <t>Dr Reddy's Q4 preview: Lower US sales to drag earnings; profit may dip 34%</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNX0hsdXNSakMzLThVRHFvY0dXckV3enFlM3ltNXpVY2tXdDFNSE1PWERHcGtYUTNPYnRRcUp1d3FwVTJvbWhfRl9xN3NfbVhpOFlCSlVvQXIzaTN0RExDek1HeWFGSzFVWU1BQTVuaGVQWnRTeTJWWkNHcnVUUDBTVHBtNFVNWlpoLTNQNTkyUlBpeWZMWWd5M2FWSlI5akwyb0hkTTdDQWpDd0s4cFNXa3EtaEJleHdsUEo3X291ckozTkJiSjFsS21peFhWWHJMaXow?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPTVpUbTRiRFJWSXZCaFJnNHhZX2dBelRkMnR5X3RtcDJBSDhRSzZRYlVYdEVic0V3YktqclJWX1FYeTJoWmc5UFZBRmlmMVpTSUxVMGdsLUp2dVJyLVFMcVUwV3lvYVN6a0lNOHpfU2VsZlZ5U1d6ZzFfNnJvVndoelZVcDQwTjU4ZU15UTVvcGMxcmstTnFVYm11bHljTEpoM3E5TVRBUUZmREtMc3VMemg1eWczVkVNV1dNTTJ5NGpKQzRSRzlVYXBnY1R5V2pMZHgwN9IB2gFBVV95cUxOVEdITUlxcURoZjZTV0Jlb1Z5Zkxqc1JYZlhGV2ZBaG9lOGx6NGs0cGxBcWVBa2twc1FneDhWeTl3dUQ0NFNIWFFLcW5GbGhQNU1MVU1Wc2JlWnNvbDFYc0pCX250T251SHF1VjhiOE04S0RrWjZHNXBzd2x0cWIzRkxxaThHbWdpdFhZZnM4Q1Y2Mk5MaFdlRk5SR2dTLVpwZjJTMTdHZmttSlUyZFlEWEZtUHlwWmFpQ2dsUHZtNHRxX3dqTVpyMkFWUVRjcEhtQmNWU3pyQVNYUQ?oc=5</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>11-05-2026 09:25 UTC</t>
+          <t>11-05-2026 08:49 UTC</t>
         </is>
       </c>
     </row>
@@ -2731,319 +2731,319 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Bears howling: Sensex dives 1,300pts intraday, Nifty at 23,800; key reasons</t>
+          <t>Dr. Reddy's Laboratories slips Monday, still outperforms market</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>MarketWatch</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxNM05YZ21qN3B6NzZoZjlFamhFY2VxMWRsQ3Ffb2JyTGdWT1dCUDlzMzNqbXlqUE14Z1JCeUgxalRXRG4zQXJBbkRYUm1MY0FQTVY5Q012NzVLMEZTaEZucUdMM0lIQWM2dXREWURrVDJZazkwanotWUQ5YzNMTlFzTW9IVTNoNHNuQVJ3VGw0X28yLTk1YnJjaWN0a3VzSkRGd2NiNHA4cnBhTVJadFdEV0Y4ckJlOW90YUpnWEwzTDVpemljTFdyTkJITXd6Ny1lTkxQc2p30gHbAUFVX3lxTE9wT3dMWkM0Ry1GXzhwbGhWc3M2SEdZcUFYaVJLcDBuQnRlcEs1RmctQTJmQ0p4SGRKVU42T1dWYmRwMDR6ZkZ4MTRqS0J0T3VTSjlkZmk4S3QxOXd4ZVdiQkNJLU9Bb1NZcGN2MG5uSmVnenVaQ0RGNHhQYXVTWU9zeXprSFlfWlhVdE9lbW9ZWWNXWU9IM25HMlZBa2NlTFVvQmRCNWFhd2NDeEpobWk1OXp5SjdYbW5XZGlOZGdjVS1FRWxEaVJYRXRPNjlmYmtLTmRoQVhBcGozQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxQYTRDb3FLWG9Cb1BkR3RTb2dVb013S005QjBPVDFNbGZFU1pQU2xwRDB2U0YxbHJSZHlnYXRONFRFQ1RLZS1xQ0d4UFlFdUNBTnkyaWx1N1p4MENSM2pobVlXZDIyTDFjZzJKUW9VRmFPUkhwd20xTWlaQzRaU1RTVUlISGJ3NVlkaVlKbG5iMUVKeUhOQk44S1k0dXRFQXgzQnV3eGdnUjBCdWtzSV9WQWhWYmV4NXE5Z0VtY0RmOHhyMmxwYS1ua1NkeFhKNGZlTVNsdHBrdllLV2VG?oc=5</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>11-05-2026 04:57 UTC</t>
+          <t>11-05-2026 10:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Biocon Profit Falls Despite Revenue Growth | News</t>
+          <t>Dr Reddy's: India Strength, New Drugs Offset US Decline</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Chemical Industry Digest</t>
+          <t>Whalesbook</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNV243eGlIUTFyZmNWTVp5QlhYMGpnbXJJVklBV3VtenJRamFOenJhcnhlMUlxcGlNYzBhRGNJSzJBV0RBcEt6cDFvVlAyZmI3THkwMkl1Znp3ZFNBc3hVaFFLVkxsRm4zaF9JbHp2S2dhbWdFa0VpMTNPQm9EcS1UcmlXaFNiUlN6and0clZHWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxPRklpbDYwNEg5bnNNclAyQTRZZkpRRUtybjd1c1FQY3h4cGw2YmpoVm9CV1JBY3gxa0swWUtCellwbC1RNTNfWkhBSjl4T0pZVFpkMXVTQXRMZmVGTnZneC1idWZaSkpGS3h6UnZkOXJuNElhMFJpOUVDX2tPVzlaNWROTjZJWWluRkw4U1hSYTQ3Y2swZ0RVdEpuQzhlMXBRbk95c1hCeGI0SjQtalFKX0hDcHlWT3NvRnVWNEl5dk9oelg1NnhMWkdPVGRVUXFS?oc=5</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>11-05-2026 11:11 UTC</t>
+          <t>11-05-2026 09:09 UTC</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Biocon eyes in-licensing deals to accelerate biosimilars growth</t>
+          <t>Dr. Reddy’s and Nestlé Health Science Introduce Celevida GLP+ for Diabetes and Weight Care</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Moneycontrol.com</t>
+          <t>This Week India</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOd2RZemZXcl8yUTRZbzZBdFcySld2ZVFLUHZKaTZ6R21UX3BGRjc1YTg3NG9XUExnYVVGYzZjZU0zUG45bTJwNTJjcmNLNl9VWHVHaS1oQVJzb25XVm1ubXZKQnlLUFVWMEs5ZXFQUXpacEJjS0ozaGFVVm05TDB3WVVGYnNRRU96MTJsQXllZ1NSVUk3Ykc0bmVpaDA4SG9ESVNrRWtWX0MxazBUWDNNaDd0TjlVOWkxMU44Ti1iSFQ0UdIBwgFBVV95cUxOd2RZemZXcl8yUTRZbzZBdFcySld2ZVFLUHZKaTZ6R21UX3BGRjc1YTg3NG9XUExnYVVGYzZjZU0zUG45bTJwNTJjcmNLNl9VWHVHaS1oQVJzb25XVm1ubXZKQnlLUFVWMEs5ZXFQUXpacEJjS0ozaGFVVm05TDB3WVVGYnNRRU96MTJsQXllZ1NSVUk3Ykc0bmVpaDA4SG9ESVNrRWtWX0MxazBUWDNNaDd0TjlVOWkxMU44Ti1iSFQ0UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNeXJpLVBheDJsQmFWVjViaTZUai1mUmdtQXE5TS1lakE0VEdTbUVuMlV2NWtad0hYbko0UmdsbnNFTElNWURDV0dxYllhZFFRR2VMc1JFRzlrSlhNenB4WkdQbXJoMUFYMEp5Z2hKbkd6ekFlUE9qbk42VmJoM1NZVGVSLXZSOHRvWHdmVmtybW5XR2tSUHJGZ3d6X2hGUmt2eEhBcGdRTHFMOC13cVNLaXR6ZTNuUQ?oc=5</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>11-05-2026 09:47 UTC</t>
+          <t>11-05-2026 16:39 UTC</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Biocon arm gets Health Canada nod for fungal infection treatment injection</t>
+          <t>Dr. Reddy’s Grants Over 1.19 Million Employee Stock Options Under ESOP and ADR Schemes</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxQZmJNQTk3NzFnUjZTamc0NDIxLWl4MkR2aDlScThjcHNHM0NPRjFXRHlaZmNhN0d5X0JuV3duZEZEb3o0ZDNUcko5eEs1bVVFTkowVnkwMXJYVkRUWHZEd19EbjBQcTRJSWF5a2tTVEZ0cnJNM29IZ3l3anZDRFltajE3emNzSjZrblcyWUhQSl9uOGIxMVB5dU5lMDVwR2pOX1dPTHdNcGVQRTVfQS1QUFRyXzZUei05dW5xaXlGSFE2ZGRhZjZKd0twZ2RGSlZHdmRzRFkxQU5iRDRLMkRjYUNCeVZwYjVUMFlPVTRNclVaTlVDVUNBak53cnpFOFl2VVHSAYcCQVVfeXFMT2pTakRkWU9KNlZkd3R0QXphcXFOWWx5X0ktT2xMMHBzdFgzNmMtY1MzcFhSYnFPZGdBbUNyMmZkRnNNMUZRdE9LajBySFRrYm9QNHJqazExZVFRLUJjTXF1ODUtY1laVlJabVYyRjFqZFVwTk9jLXVNZGZIbldwYWEwX0FldXlfNnFMa3huOEhQRE1DWnFibFREd2s5UGUwTVM0NmM2aHZIWjAxNGhHZjM1NDIwM285dnlMSmJRR1FENWVqVmJ4OU9ycGQ0ZmFKREpfVXlsbGN2cWdta0RBWUtyZlZjOWFyeGtwekEzWlYxaEU5bC1PcElPU3NDNEVGTUJuZWxtMnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPZlQyeHV2QlF1OS1iYmRwSTN4R21GOUZiaTRaZ1FVbXdDRE83eDM4TUdJWFhEZ0Y0ZTRGMm9DMW1WM0k2a2MySmYxWkl4aUZsZFFRM244b2tuSjNReXd1aG41Z0dUcHJoWHpxUG1TRV9vNFdHQVZOd0x4RjhKUE5pclhHckdKdXlaY0pPVVBuVjhiUkxDWXg2OHdBamtLcDJHYV95RzhaNXhjNlhKMm9IQm80bXdndTNYT2NueDZ3OW1ZenJZbjFaYmhaamdSV2pTWmc?oc=5</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>11-05-2026 05:33 UTC</t>
+          <t>11-05-2026 17:21 UTC</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>CXO Moves: Exec movements across Prasar Bharati, Omnicom, Biocon, Britannia, Epigamia and more</t>
+          <t>Dr. Reddy’s Laboratories Board Approves New Stock Option Grants for Employees</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Storyboard18</t>
+          <t>InvestyWise</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxONlBGdjFBOWhRdTE2aHJvWUI5VDFUVGNCQkdRazAyX1d2RWpRd3ZMR2VMQkRkUDVzcEc4SUhrYlpteVlub3N3dF96anNIbWxldHAwQnB4Yk84ajRwVGFoQTdENWd1QzBqZENQSXpYZW5QTFZKWkx5QTFRNWlkS0MtZUw0bThlanN5MjJVd1pMOVl3LW5ySFJDWWVzWXpTZVdlZS1JUnpFRUlIVkZtRXFDNW16QTRudWRlMUh3RXh2UlVRTzZBZk1UZk5ydnZtekw0dDF3VXJMRzTSAd4BQVVfeXFMTnNDRDVpR2pGSG1NcWlKT0tjWHlfYzlibzFGeFpkM2dqN1BJc242elJySFJvX1p1YlRCaTUwVGNCQXdPWno2WlU0cmE1WjhkY0tUWVZtbUliWWQ3VENId0RicEp3VC1mUHBpaTF0bVowaXhqQlpPUTh5U3p6bndzZ1lZVnQ0WFpETlNERHdIZ2xpQlpYWlB2TzZnWVQ3aVN0QlVUV3dUVmY3Y2tQX0VDUnJ1MzI0TVpHcGdZUUJrZG9ka3Jham0waUpwV0NmTGNLbEJGZWxyZXJfWmZSVFBB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTFA1cDZNTUNKQnpFMDZ5OEtMTzg5dURFNm13YU9CU3l1dkhfenROa25sbDNkc0xPbkZST1RGSFVPVGdYNmYtRm52LWtrODdwWDNHaTZzWFlOYlpWamp5NDJYNWRjZ0dZN1JlQlRMcjBBcWhyNm0xYTFrZkFn?oc=5</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>11-05-2026 06:58 UTC</t>
+          <t>11-05-2026 14:02 UTC</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Biocon shares gain after Health Canada approval for injection used in treating bloodstream infections</t>
+          <t>IDA Recognises Dr Vijay Anand Reddy For Cancer Care</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>CNBC TV18</t>
+          <t>SMEStreet</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxPS1NKVmlZSk90RnRiSmtZYUZxbTJUU0UwWk1jX0k2djgxWC1GaV9kWWNZQzNhakVOTDNuYVl2UmVLWWFxWk1PVHJZQllJTE5RVkhHRHZpNVB0S1pEYXk0ZVJyTm1jMDM4QWlCLTdZc0t6R3JpdXNzNWIwWmpJLThmTE9PZTEtaWFsSFY0S0JjeDBpenRBNmMxcjBzTWh0X3l1UjNNZ1VWclZJcW9rbXR3bjJ1d1FDcnpoXzBtTWtSMlRxb0Zpd0p1QXFJc0RDUW5wMC1vYjFMUdIB3AFBVV95cUxNeDM5NU85Tk5iWHJTSGhDZU4wZTl6WndXUXA5QUlmME54NmRaREtwRkFEVmRfUi13MWtLOGNCcmttWnVvXzVDejl5WURVYWZKZnlwM09QM0ZuWll6ZjlnU0NJbmdTZ05FT2pPRFhhSVd2MXBYRG1sRUtQQW1yZnVNaFUxSEpOeHVBdi11X1ZBOHNQeEF2MFRlWklrSU11QnV4SEFZbFQ4MGt3MGlyN1BVdGRpUUE2NDdGSTNMcy1zVUlsN2NvY2xYSEprTnFvQlJDRHAwMmtiUW94MEhh?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQR3VpX0l5ZVhjQzk5ZjlVOFJ3Q3BsaUVCZEo5amZyVXV5c05nRFhPTjE4Zi1BS1VJZlk5NUZ5cmtiNGN3emRJZGdlQW9sT0Y1MTNmOGVBSnZ0VjBFNFRIOGVwWEtYWDVOSWpkVUdFaTlQRzRuSHdQaXBNUjhZR3NKNWEyTFR3NXUwdUhyM09aNnJvd2vSAZMBQVVfeXFMUEd1aV9JeWVYY0M5OWY5VThSd0NwbGlFQmRKOWpmclV1eXNOZ0RYT04xOGYtQUtVSWZZOTVGeXJrYjRjd3pkSWRnZUFvbE9GNTEzZjhlQUp2dFYwRTRUSDhlcFhLWFg1TklqZFVHRWk5UEc0bkh3UGlwTVI4WUdzSjVhMkxUdzV1MHVIcjNPWjZyb3dr?oc=5</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>11-05-2026 04:58 UTC</t>
+          <t>11-05-2026 04:46 UTC</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Biocon Q4 Results: Net profit down 57% at Rs 198.6 crore</t>
+          <t>JSW Energy Q4FY26 results: Net profit rises over 38% to ₹574 crore</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>ETPharma.com</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxOU3ZVc1NOMTlaRncwRXdUUkxLYWhVQ3VyRURSMEc5RHZtOExqTjd0T19pNnhzN3hTd3pPckpzWHh6TXJoU09rNTdhWW5HamR0OU5sa090WklSTThnUXk0cGJsSTZJUm5wZ21OYUExZkNSVDFIUl8tRW1GX2g0M2JaOVVnYllva2drVkpaMGxiTDlKT05zS3pqd2NFeXBxbGtjeG5qMlJ3ZnB5UGVpNDhNX2I3aW56RzJWcXZianAzQllXU1lUWmpHcHpzdGZ5RUFuM2ZLc0RR0gHWAUFVX3lxTE5TdlVzU04xOVpGdzBFd1RSTEthaFVDdXJFRFIwRzlEdm04TGpON3RPX2k2eHM3eFN3ek9ySnNYeHpNcmhTT2s1N2FZbkdqZHQ5TmxrT3RaSVJNOGdReTRwYmxJNklSbnBnbU5hQTFmQ1JUMUhSXy1FbUZfaDQzYlo5VWdiWW9rZ2tWSlowbGJMOUpPTnNLemp3Y0V5cHFsa2N4bmoyUndmcHlQZWk0OE1fYjdpbnpHMlZxdmJqcDNCWVdTWVRaakdwenN0ZnlFQW4zZktzRFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxPN1dNcU5MQWFIZ1BtY3ZUcWpqUlRTU3lUbnA5azBhM0pBZnNKbkQzWVZOcHpsdlVHeGZfTkRLeDl3VlRsV0RaLXFabXN1MmpEemtmY3R3eFRYX0NVdkhPQWRHR0hBazVCWWZOYU1lYXlrU2steTlUVlYwNkxCdlp4U3NjQmdqWHFMam9ORkZhU0twT01QVi1OZldnV2tXQUJiSmVaZU00VlRwSHFuNl9jbWZ1TF9JZ0hZX2hkcFMzaEVhLTNPblJqUE5lTXAyd01IVVZGZEZrelZJOFR5T0HSAeMBQVVfeXFMTWcyeUN3UW5XRlA2bUlBcE5jc2tHYjdVdXpNT3RzMjhQZWxCWGd0N01VWlJZYlMtaXJNS3B3QmNJRk5YYXB3SmhfT0xHbUM0N2M2bXU3M3E4cml1VTJrOXFlakhMcXFXWFI1R0lWYzVIMFRaZVA5V1Jyb29uTlVleGM5aHdmM281ckRlR2dCRmdGVEFxUDYxWUJDSjBDR0ZvVk44TWZDVnJqS1lIVERERlI4aExpZFc2VFhhX2FBYVlMVTNBcU4tWEdIc2ZheEF3R29nS0tmSW83eGxVY0dZMWYyT0E?oc=5</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>11-05-2026 01:45 UTC</t>
+          <t>11-05-2026 11:55 UTC</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Biocon Pharma Limited Receives Health Canada Approval for Micafungin for Injection, USP, 50 MG and 100 MG</t>
+          <t>PVR INOX posts Q4FY26 net profit of ₹186 crore; revenue rises 25.8%</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxQTkJvLTVFWnZVYjUzdzlrUVo1S0czRFJPYmxicEhnbTAtWjluYWY4dVNxc0hhSWxvemZwNE1iY0pSNlZHNkQ1Y1hmT1V3TV9BZXRQdnBNRGNQMEtOSHEzdGZuVUdWTElPbFZnWDQ2cGdQLU5FZVF4S0pfSTRERUpUem1vRXc2eGFib1o0dGVWOGQwSFF3ZGZKUUN4bXBpeDdXWTFZc3loekkybGdCeXQtSWdvYnhBclhjLUw5NUswRFh0YWZYaGFIdVRzOWFmMGpBN05TWGJhRm5wUkxFUktRUWdRQmhHSEQyZ2tBQ1dibWczQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxOMEJuMTVPTmpkbzBjTmctMHAzODRKek1WQVFHUlRsaVo0SVloUkMzVDNNb09pcXhsbnRkcHdKc1ZEZmk5cUJTNU5wUHZweTVVdGgwU0F5bFh0MF9UeWQ5dDJ1dE00Mkl1RWItWEo5SWQzMERfV1FRWF9jQUMxcnc4WDFQZzFpblBHUUdNWmdUMW9NYUNVckl2eDJWanp3OEpGS0VNenEtRGlNSHFsbkRVWHVwekUwZnhxVmd3TWw5dHZJeDc2el9yc0hSa1V4MjJhSmpxWGU4XzVLWVJ2Y191VHRPb9IB6AFBVV95cUxNZGhVb0lYLWJYdmxvMXJaWnUwMWZjaE9uZ3hGOHdvVm1mcHhpckF1RjBqUm1jaWgwN0RJZUM0a0d2WlVyRUNqdG43SUhaYXV2WDQ5djJBOW9JT1hhNWtHSHRGWU5TYVl4Y3RCME55ek5QejhNS3d5Vm1mT2ZDUDRfLUotWVNMSkdBRnZsdDZCa0pWY3VSN2RfREotaldPWEwwM2V4dU1pbnk2dTRad0pDaXNKQUk3ZDUwejRLNkpBQWczNDlPaWc0MUF5NGZ5dTYzSlVPdWJ6RmdUenAwR2c5MGlScU45aTJm?oc=5</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>11-05-2026 03:21 UTC</t>
+          <t>11-05-2026 11:14 UTC</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Biocon Says Biocon Pharma Receives Health Canada Approval For Micafungin For Injection, USP, 50 Mg And 100 Mg</t>
+          <t>Hotel stocks slide up to 5% on PM remarks; analysts optimistic, back IHCL</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxOY0xPcmtzVzhzYVNxNlZmMDVuY0JfR3Y2cm1HUmZZVjk3SkdZNzFxVWtRZ2RWQk8ycDVIQ0VzRFdzQ0FaVGZYM1FfODVTWW81M2hBdVpqWllPeWpOVXBqVHQybWwteUdsZnYzYVNsU29iSWNTVmtZcXBhdy1JWHd4UFYzRDNqeWtuUWgxTm5oQ3kwYmVScEM3X0RKY0VrRGJ5RVU3VWN5MmkwcG9hMnRzWVJ2T0xTMTN1eDZhS1NnT2J2U0dLTFBFMjk4X0VFQ3ZrTXQwUzR2aHR1Y1JqR213bWI2bm9aSmRWVlFSVW4yQzVqSUFHUVhTMVpPRzBUVGE3N0pHR0U3d0k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQeWZtNGdkeGRGQnlNekRST0lqWUlWc09JNmE0VGFmb2UzSDU0SEVVVmthbGJYSXVGRmpZMTI5d0diS1pMdTlDNHI3N3FIeDdxTmVxdmJfdzY0TXJlRUlOdUtDdWNXaXV6Y1NwQmpsMld5Mk9KVVgtOG1OdlhCLUM3RlQwS2xiMF9peDdUQTJUOFN3d2NwYnY3cFRMMV9EY0thQWoxTFo0UXpVUHA2Y0ZiQ2NlSGd2ei03QWhISmVycjZNQk1pQzRvYUJaU3B2Z1dDLWd30gHYAUFVX3lxTE8xOUdSQ3gzUGNnSHhFNlRYbkJzOWxmdUNFU0t6WlBmQXpTc1BNaTdFc3VDM2N4RG1fNHlLeUFualhnMmxNVkRVTTBWejZzeEQ3WjJidEVZWmFNZDJ0Yy01cU82V29HMFYxamhSWkR6bGFxX085d0lrRkVSUGdsRHdKXy1DT2RlNUc1QTlFVXlvbmcwckFyVlhZZWJaTkVvdmlwSzJ4Q1paZW9PaDIyRkNEMHJyaW0tdWJMTElwbFBWTTVub2JjQkZ6ZkxGRWFZVU1tR2lEMEZmSw?oc=5</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>11-05-2026 03:05 UTC</t>
+          <t>11-05-2026 08:35 UTC</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Watch India's Biocon on Generic GLP-1 Push</t>
+          <t>This Dolly Khanna portfolio stock defies weak markets; jumps 17% on Q1 show</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Bloomberg.com</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQell5ZjBUZUdtVHEwX2pteVl3SmV2RFEzVkNrRmtHOVhORmRCczNaZEhlRV9jSW5CbmNBSzllYnhkVmhEOGNGcjNlSy1rcVJBa2V3UXE2ZlJsay1xRk1Lb0F6eWxWNEZoUWNnSFFUSFhCck9tX3NfTUtfNjMzeW5zUThycU9JQVdBLUZmXzdNbGcya0pMRWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOaWxsU3ZBZEk5eWlrNjRXUDdPZUR3T0hWaFdWOElvcFd5WDlBcFVTNDBqRmpvMUxJQi1zZDlwazNiOGtST0oxTFNVSTZiZFIwbnRnb2x4SU8wYTZwc25rSnA2b1RuQnE4M0ZHMmZpSDFUT29iLXRaWkR6RkExcktSengtVHhqNHRNZVpxbVVyR2g0YmJQTmdoZEhaWlo3RTRFWF9lRFZWTXdoLWNZbnlVVEJlRENhekM4X1hlWDA0aGFwdXFSczV0OUlDQldFWWNubVV2N2dLNNIB3AFBVV95cUxOeFZTVjY5VHp1S3hGX01oUlptUllVdjJPdDhGYkU5RlZmY1hKMG9nTHdHUEFEY1FZQ2tZUnR1OUlIRFJrY1llVmlkYlpEQTZqNU5HUUVoVlZLdDNBVFBkTFdlRXpQODdsbVFJX3dwVlRsdlpocnBrYnpHMlF0bHBGM3M3bmZHLVAwc3FjeUZsVkVfTFRHNUlVbzQ2b01GWXFJRXJrdjRFSElxc3l2M3VoVWtBTWRFTzF2emxtS3A0TzdzUTFjcTkyQnJXbkcybUlwVjJUajBjR0lJbnUy?oc=5</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>11-05-2026 00:00 UTC</t>
+          <t>11-05-2026 09:24 UTC</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Natural Biocon Standalone March 2026 Net Sales at Rs 0.88 crore, down 34.99% Y-o-Y</t>
+          <t>Canara Bank stock falls 4% as Q4 profit falls 10%; asset quality improves</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Moneycontrol.com</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxPZTVVb2I3dndmMjM1Nmh1d2Z2Y2RBbTgxWGQ4TVdNbWw5d1VWbnZ0T3hqMGxSdVpISThUU2x1Um5ySDVfQUdtM2pObDJYUHlMMEVDeDE5M1pEel9BcXdVY0pKTTdTTnB5a3JhZWRaTWt5RjAwNGtldWpScmJKYmoybTJzVkRMMGVtdlBHNnVLSkwzZjAyaGZxR1lFNDhocU9GR1kwN05kQkc0M19XTlQxZjc4NzZUNlFNbnBNTVhnTk13M1JJVDRjTFV0SGZjU0huMFp6dmhTUzJBd2U4eHNZ0gHkAUFVX3lxTE5EZ2x1YWtFMmpBQ1dSODI1c21uYU12ZEVsUFFVNnFWOGdaWFdHU1ZXMGhmVmg3X1U2TTh2VHhZdHhuWFl4OU13dnlmYUlDRnJfMVppelNqTXlGVWhSTEFXci1pSG5VQnNRMUJsOWVNUmxvaDg2UE1ZNTJMbTdpN0xJRTN5RzRpMDhha0g4OURiUXM2OWE1MjJnX3lGUXJ6V2FRVFRtLTBhNkFmWGhmLVE2Ymp4V3Y0NURESWZqbUhlX3JDcXdLSmF0M29WcmtXOFpLNGpWWkZtXzBnMlpHM2hLeWUxTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxPa1ByNy1nS3VyV0Z3SGJVNDAwZUw2YmpqWW9scTRDTkhOVGF6QVhJbXF1MW5ZakFXYlpVQ0FjREhyQ2R2ZFRsemVtZC1ZazNVTnZTazdwR0oyNGUwcDhlaWt6VmI4OXZHcUlEOVdtRnRrSmwzcFViNFVCN2hYUkZFQmFhUjdoQldBNDNNS0hwSnZaQ0lpc0cxa1pLLUxZelRiWVBQdWJ4LUNwRVhnS19ldlZ3SzRlTVlmZWpLYXU4NmotcThCaUxya2VRd3lxT01CZElr0gHYAUFVX3lxTE4xXy03ZjhlajhSR1ZqQlJLM0p3dWFPN0l4TThhZWJaMGVVVEc2OVczYk9EZzRIR3lJeDNHTGVMMzFoTXpveTMxNlBteGFuMXZ2a0Y4VVpYYWRsRTR0YTVxRGo3bGhPQnphYlB0SktYYkxCOTVWYVl5cklPWVROX1ZPQi1pVnZGT0V0MXdHalVXOU00TjRnVGUxYXgtS1F0cWJPaWNyM1BMaUNHQWpHNzFQRlZNRU5VcjFyVzhIcWhTOTZCYktzelBFNVJDV3d5WG5vWmxkdDEwcQ?oc=5</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>11-05-2026 05:17 UTC</t>
+          <t>11-05-2026 09:25 UTC</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Kiran Mazumdar-Shaw On Claire Mazumdar &amp; Biocon’s Future</t>
+          <t>Centre plans nationwide crackdown on illegal sexual enhancement drugs, calls it threat to public safety, social dignity</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Business Today</t>
+          <t>Mint</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNdW1qUktleWdJVlctbXdsamlBNUlmN1JyUVRraVhqQVRNT0x1eXp0bHEtSEVDUlRTcndrejFUbzE1X2l6dmlzZlBfRHBDdlhDaXpVSlkzNG9Kd1BUSE41M3ZXUlEwSmJlM2xOclJNdnZuSjc5WEVRNzVjYnNXRGhZMVVQZ09kZXZ6QTVHWW13d0RVQ3JJZTROVm8wSnU3MS0wNWFubTRwSC1fcFQzbUpjbmJyQkptS2JCR3hRTEZOTmFQWFZa0gHEAUFVX3lxTE11bWpSS2V5Z0lWVy1td2xqaUE1SWY3UnJRVGtpWGpBVE1PTHV5enRscS1IRUNSVFNyd2t6MVRvMTVfaXp2aXNmUF9EcEN2WENpelVKWTM0b0p3UFRITjUzdldSUTBKYmUzbE5yUk12dm5KNzlYRVE3NWNic1dEaFkxVVBnT2RldnpBNUdZbXd3RFVDckllNE5WbzBKdTcxLTA1YW5tNHBILV9wVDNtSmNuYnJCSm1LYkJHeFFMRk5OYVBYVlo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQMWxjQ0VxMjV1N09FRVNQWXZUWng1LVFibm4zYTNiOTRwSHA3RWNHenFwdjhUY3duS0V5VnQzSEU5cDVKRFN5OXNWRzc3WXlSN3VyUXBxYUZ0YmxOdzR5RkU2UnZCcGF5OER6QXNJVzNEa3F0X25oS1R3eTJXNWhtdjlpT1NteWpWd2IyU0Z2cUFTNTVUUmVYeFZJZ00yOGlEenQ4SklpMWlaYmZYMlRkMG82RXBBVXNZNjMwaVdvVzfSAcYBQVVfeXFMT3Q2MHlNc0RlTXl3N1ViWG9hc3g3R1BjOVhFR3NSY2NXZ0c2VC1sTTVCUGxKdzZDRjhHaHlmZjNhaERfbldMd2o2UmdVaHE1LWFCaFFicHNTeWFwbjczSnlNVTRQckZvdTRPQklfaERLTUhyM3Z6MkpFa0tZbXFVUER4VzQ0ZmtCR0VSdkExb2hvLWYySjFIRDc5UTlVdm4ydVBaSTdNTllqakVuS0Zma0RRVnNQNHRlZkRzc3c1dUh1bjZwS1l3?oc=5</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>11-05-2026 08:07 UTC</t>
+          <t>11-05-2026 00:30 UTC</t>
         </is>
       </c>
     </row>
@@ -3055,979 +3055,979 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Kiran Mazumdar-Shaw Reveals Biocon Succession Plan In First Interview After Announcement</t>
+          <t>Biocon arm gets Health Canada nod for fungal infection treatment injection</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Business Today</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxQZ3NNMU9HVjlPeEFlOHRyYW9BRkVlaTNWLVB3V3VSc3NHeklXVzBYVTgzUDVORFFCNk5ueENHVUozRndVbG5KQkhwTEFRN2lxNk01SHA1dFBqdTJtVDJLRG9lazQyUEpSaXhmOVB0VlJIeEsyTkxMbjU4U2pvdVllQm1CTW9yNmJvLXF1a3BqQWRnamU3ZFF4YXJzWnZQZ1Bhd2ZrbXQxaExJS0ZjMmliX1VoTUJqaF9wRVFsUlNLeWh4dTRlakw1WGVOa2txeWRTYUlMY0luQ0hGdDZoaTVEMHhRYnZ0VDh1WUdFbnc3eEJnbzTSAfMBQVVfeXFMUGdzTTFPR1Y5T3hBZTh0cmFvQUZFZWkzVi1Qd1d1UnNzR3pJV1cwWFU4M1A1TkRRQjZObnhDR1VKM0Z3VWxuSkJIcExBUTdpcTZNNUhwNXRQanUybVQyS0RvZWs0MlBKUml4ZjlQdFZSSHhLMk5MTG41OFNqb3VZZUJtQk1vcjZiby1xdWtwakFkZ2plN2RReGFyc1p2UGdQYXdma210MWhMSUtGYzJpYl9VaE1CamhfcEVRbFJTS3loeHU0ZWpMNVhlTmtrcXlkU2FJTGNJbkNIRnQ2aGk1RDB4UWJ2dFQ4dVlHRW53N3hCZ280?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxQZmJNQTk3NzFnUjZTamc0NDIxLWl4MkR2aDlScThjcHNHM0NPRjFXRHlaZmNhN0d5X0JuV3duZEZEb3o0ZDNUcko5eEs1bVVFTkowVnkwMXJYVkRUWHZEd19EbjBQcTRJSWF5a2tTVEZ0cnJNM29IZ3l3anZDRFltajE3emNzSjZrblcyWUhQSl9uOGIxMVB5dU5lMDVwR2pOX1dPTHdNcGVQRTVfQS1QUFRyXzZUei05dW5xaXlGSFE2ZGRhZjZKd0twZ2RGSlZHdmRzRFkxQU5iRDRLMkRjYUNCeVZwYjVUMFlPVTRNclVaTlVDVUNBak53cnpFOFl2VVHSAYcCQVVfeXFMT2pTakRkWU9KNlZkd3R0QXphcXFOWWx5X0ktT2xMMHBzdFgzNmMtY1MzcFhSYnFPZGdBbUNyMmZkRnNNMUZRdE9LajBySFRrYm9QNHJqazExZVFRLUJjTXF1ODUtY1laVlJabVYyRjFqZFVwTk9jLXVNZGZIbldwYWEwX0FldXlfNnFMa3huOEhQRE1DWnFibFREd2s5UGUwTVM0NmM2aHZIWjAxNGhHZjM1NDIwM285dnlMSmJRR1FENWVqVmJ4OU9ycGQ0ZmFKREpfVXlsbGN2cWdta0RBWUtyZlZjOWFyeGtwekEzWlYxaEU5bC1PcElPU3NDNEVGTUJuZWxtMnc?oc=5</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>11-05-2026 07:48 UTC</t>
+          <t>11-05-2026 05:33 UTC</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma Ltd: Valuation Shift Signals Price Attractiveness Change Amid Strong Returns</t>
+          <t>Biocon Profit Falls Despite Revenue Growth | News</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Markets Mojo</t>
+          <t>Chemical Industry Digest</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxPdmdZaHJ1cDN6SWNZMU1MZ1lIeTJrRElxUFhkRlV5clNWZHRuaHA1X2dNX3BiV2ZjT2szZ1I2ZFJrTWlLLW55X2xWRk1PWUdRSFFfVGstOHNSb0NWTU92YUdERXFxYTJRWFM0a0Y1ajdtalc0UlFUMDE4RG9kUmdWeFhWQ05rWVA4VTEyNkhVbUxhV3NvTFMyaEtONjR1S2o3S0NhSHJqdTNhVEs1NzYxb3pBMDN6UHBtdGhNZjg4ZWcxakFrX0FUcFh6YzBHZm9peFJyYUFUVnZzQ3U0WklDTzVrY00?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNV243eGlIUTFyZmNWTVp5QlhYMGpnbXJJVklBV3VtenJRamFOenJhcnhlMUlxcGlNYzBhRGNJSzJBV0RBcEt6cDFvVlAyZmI3THkwMkl1Znp3ZFNBc3hVaFFLVkxsRm4zaF9JbHp2S2dhbWdFa0VpMTNPQm9EcS1UcmlXaFNiUlN6and0clZHWQ?oc=5</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>11-05-2026 02:30 UTC</t>
+          <t>11-05-2026 11:11 UTC</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Indian pharma majors commit $19.1 billion to US expansion</t>
+          <t>Biocon eyes in-licensing deals to accelerate biosimilars growth</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>The Pharma Letter</t>
+          <t>Moneycontrol.com</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOZmRyeFRDbDFiYklqTmNqNE1QckpBQnVodFBqeUd3enN1c0ltcS15WUpvcWVOMnVrUUNrZUtkOFloZ0Mwd1UwNk4yblR0R0VtTkhtY0tFSUNVT2d6Qm9ZTzlBUWxSeVB2S3pJd0lZUkNOTVZDem8zVEg4blZLSVUwTi1oUFV2a2p1WlYteXk0eHF2RVl2dG56cE9ON2ZJbTZEaHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOd2RZemZXcl8yUTRZbzZBdFcySld2ZVFLUHZKaTZ6R21UX3BGRjc1YTg3NG9XUExnYVVGYzZjZU0zUG45bTJwNTJjcmNLNl9VWHVHaS1oQVJzb25XVm1ubXZKQnlLUFVWMEs5ZXFQUXpacEJjS0ozaGFVVm05TDB3WVVGYnNRRU96MTJsQXllZ1NSVUk3Ykc0bmVpaDA4SG9ESVNrRWtWX0MxazBUWDNNaDd0TjlVOWkxMU44Ti1iSFQ0UdIBwgFBVV95cUxOd2RZemZXcl8yUTRZbzZBdFcySld2ZVFLUHZKaTZ6R21UX3BGRjc1YTg3NG9XUExnYVVGYzZjZU0zUG45bTJwNTJjcmNLNl9VWHVHaS1oQVJzb25XVm1ubXZKQnlLUFVWMEs5ZXFQUXpacEJjS0ozaGFVVm05TDB3WVVGYnNRRU96MTJsQXllZ1NSVUk3Ykc0bmVpaDA4SG9ESVNrRWtWX0MxazBUWDNNaDd0TjlVOWkxMU44Ti1iSFQ0UQ?oc=5</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>11-05-2026 10:17 UTC</t>
+          <t>11-05-2026 09:47 UTC</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Global Oxycodone Drugs Market Size to Reach USD 9.21 Billion by 2035 – SNS Insider</t>
+          <t>Biocon Unit Gets Health Canada Approval for Antifungal Injection</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>GlobeNewswire</t>
+          <t>Whalesbook</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxPa2lWVGNmRTZkcDNjQ2piOXRPWWRBSC1VcFdlelM0VHhRV0h3V21TX0dkVXRLWTNDRVppMXB6YnVnXzUzY0gtc0JiS18tbGdTT0NLYVlER0hZamFKX2I2TklHTUJwbk5GOE5vVXdob3NTYnhyQlpVRVM0TUJsWTVRN1htTnVhbnBWSXBtMzEwTkl5ZzRpY3lrWWIxOXVTWk02VVlic3A5VlEzV0pyVS1YZGRvZC1aXzkteFVUUzVXVkJaakZYWkZKZzJqZjFUZEJHMGNIRWNvTnJGVVo1enY3cTcxaHdZR1k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxOQjhwX1h4UHdKWmJMa1RuUllsaThIYldkX3JTN0NjckFnaGdPcTZPLVkzUV9HSFpuSXBzN2RQT3hlUnRhaFZuWEZPQzVXTEZZekIxTDF4M180WnduY0RVZG1TM05zOXgzaUMxNjBLNm5pUDB2TjhkNEY0NnQ3dVB0XzBhUmtYTUpjb1JvNEpiRmpqX0RfMk5IeEdPVTFxUHNOQWNOQjhhRURvT2ItZUpjM0ZYLWlOMTFoaEIxOGtiN05BaDltc013Wk5XYzhIWnRpWXVyOTYzeWZsczlQNDFoU25nb2NrZ0VZRGdKcGRn?oc=5</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>11-05-2026 12:29 UTC</t>
+          <t>11-05-2026 03:09 UTC</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Vinod Jain Appointed as President – Investor Relation at KPI Green Energy Ltd</t>
+          <t>CXO Moves: Exec movements across Prasar Bharati, Omnicom, Biocon, Britannia, Epigamia and more</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>hrtoday.in</t>
+          <t>Storyboard18</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOYkJDelVhaTFzYUZxclQ0TGZPbDF4cGI4UGVEUnoyRjBGaWJ4RGNGUmVGWGY1Q1FOVVp0R2xQdXZCOXBPenoyalVfSmpHcVh3MzcyS2xta3BGRGdabWxfT2otbW9GX2hDdFJNVVVHR250emZueS1kd1dyTk14VTFqalZyZUxwQW00aTRqZGthR1ZzeDVvUGJaTHFQYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxONlBGdjFBOWhRdTE2aHJvWUI5VDFUVGNCQkdRazAyX1d2RWpRd3ZMR2VMQkRkUDVzcEc4SUhrYlpteVlub3N3dF96anNIbWxldHAwQnB4Yk84ajRwVGFoQTdENWd1QzBqZENQSXpYZW5QTFZKWkx5QTFRNWlkS0MtZUw0bThlanN5MjJVd1pMOVl3LW5ySFJDWWVzWXpTZVdlZS1JUnpFRUlIVkZtRXFDNW16QTRudWRlMUh3RXh2UlVRTzZBZk1UZk5ydnZtekw0dDF3VXJMRzTSAd4BQVVfeXFMTnNDRDVpR2pGSG1NcWlKT0tjWHlfYzlibzFGeFpkM2dqN1BJc242elJySFJvX1p1YlRCaTUwVGNCQXdPWno2WlU0cmE1WjhkY0tUWVZtbUliWWQ3VENId0RicEp3VC1mUHBpaTF0bVowaXhqQlpPUTh5U3p6bndzZ1lZVnQ0WFpETlNERHdIZ2xpQlpYWlB2TzZnWVQ3aVN0QlVUV3dUVmY3Y2tQX0VDUnJ1MzI0TVpHcGdZUUJrZG9ka3Jham0waUpwV0NmTGNLbEJGZWxyZXJfWmZSVFBB?oc=5</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>11-05-2026 07:41 UTC</t>
+          <t>11-05-2026 06:58 UTC</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Zydus Biotech</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>MSc Microbiology Job at Zydus Lifescience Limited | Walk-in Interview</t>
+          <t>Biocon Q4 Results: Net profit down 57% at Rs 198.6 crore</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>BioTecNika</t>
+          <t>ETPharma.com</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxONlJzZGtZMHBCMFctTjNud3dRck45WDJEWUNhczFYUGc5aGtFLUF0cnhXdjI5UlZYdWdvSkhWUklDR0tjYVhOM2NCdFhzdEU0eGRjck4tTEh4RzlfMDVlSF8tQ1FKV0lDNUNyNy1Vakx4aVo5YmpTR0Q5WDlpc3NqdzFOZUV2bDVULXhNNVZR0gGTAUFVX3lxTFBUWmNsSXItWklmRUhNZjF2NktwdlRWWnlBOWlhb1lHbTM3WUg2ZG5QZWZ1Um9lcDZfdEczb0VoZWVyVF85SlEyZ1ZuZDhFcXZ2TnlYRzNOTnpxaC1yU1FJWFhvQzZ3SVczN3dIOURxZnRlV0tZOTF2T2pVUEJyUXdRNjAtOFhxYkRsU3FCVWZ0NEhEWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxOU3ZVc1NOMTlaRncwRXdUUkxLYWhVQ3VyRURSMEc5RHZtOExqTjd0T19pNnhzN3hTd3pPckpzWHh6TXJoU09rNTdhWW5HamR0OU5sa090WklSTThnUXk0cGJsSTZJUm5wZ21OYUExZkNSVDFIUl8tRW1GX2g0M2JaOVVnYllva2drVkpaMGxiTDlKT05zS3pqd2NFeXBxbGtjeG5qMlJ3ZnB5UGVpNDhNX2I3aW56RzJWcXZianAzQllXU1lUWmpHcHpzdGZ5RUFuM2ZLc0RR0gHWAUFVX3lxTE5TdlVzU04xOVpGdzBFd1RSTEthaFVDdXJFRFIwRzlEdm04TGpON3RPX2k2eHM3eFN3ek9ySnNYeHpNcmhTT2s1N2FZbkdqZHQ5TmxrT3RaSVJNOGdReTRwYmxJNklSbnBnbU5hQTFmQ1JUMUhSXy1FbUZfaDQzYlo5VWdiWW9rZ2tWSlowbGJMOUpPTnNLemp3Y0V5cHFsa2N4bmoyUndmcHlQZWk0OE1fYjdpbnpHMlZxdmJqcDNCWVdTWVRaakdwenN0ZnlFQW4zZktzRFE?oc=5</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>11-05-2026 12:06 UTC</t>
+          <t>11-05-2026 01:45 UTC</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Zydus Biotech</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Zydus collaboration lifts Agenus (Nasdaq: AGEN) to Q1 2026 profit</t>
+          <t>Biocon shares gain after Health Canada approval for injection used in treating bloodstream infections</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Stock Titan</t>
+          <t>CNBC TV18</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNbHd5VEFOTk5FVHpDRWZicWx2SDNTUTZSZk1kd3dKTmFWUnU3RVlDVGFaT3dzd3NHZlFsN0ZZSXI1TFZqT1gwQW5ScEY4OHRmTGQ1dmFibEFxdTdMQW5uSjBreWdiVmFOd1NpV1Q0X3lTRExuRndNUnpjMVBoMEdoT0xYWjM5dnE3WmZqdndoTmJKWjFOOE5jbnFlekRSM0Z4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxPS1NKVmlZSk90RnRiSmtZYUZxbTJUU0UwWk1jX0k2djgxWC1GaV9kWWNZQzNhakVOTDNuYVl2UmVLWWFxWk1PVHJZQllJTE5RVkhHRHZpNVB0S1pEYXk0ZVJyTm1jMDM4QWlCLTdZc0t6R3JpdXNzNWIwWmpJLThmTE9PZTEtaWFsSFY0S0JjeDBpenRBNmMxcjBzTWh0X3l1UjNNZ1VWclZJcW9rbXR3bjJ1d1FDcnpoXzBtTWtSMlRxb0Zpd0p1QXFJc0RDUW5wMC1vYjFMUdIB3AFBVV95cUxNeDM5NU85Tk5iWHJTSGhDZU4wZTl6WndXUXA5QUlmME54NmRaREtwRkFEVmRfUi13MWtLOGNCcmttWnVvXzVDejl5WURVYWZKZnlwM09QM0ZuWll6ZjlnU0NJbmdTZ05FT2pPRFhhSVd2MXBYRG1sRUtQQW1yZnVNaFUxSEpOeHVBdi11X1ZBOHNQeEF2MFRlWklrSU11QnV4SEFZbFQ4MGt3MGlyN1BVdGRpUUE2NDdGSTNMcy1zVUlsN2NvY2xYSEprTnFvQlJDRHAwMmtiUW94MEhh?oc=5</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>11-05-2026 12:52 UTC</t>
+          <t>11-05-2026 04:58 UTC</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Samsung, labour union make last push to avert strike before May 21</t>
+          <t>Biocon Pharma Limited Receives Health Canada Approval for Micafungin for Injection, USP, 50 MG and 100 MG</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxQLWlKQVRwczFqWXpzZGpVMzA0bURITlp6WkN6WHEydDRGNWphdHQ4VndVNFFkckx4ZUFiV0NnX09RUUJTNU1uRWRtUzU5V0YxNFJqelY1dGljZEptYUdxdmFxNlRSRUNkVkh4NnJnRnpyZkNzc1hhTjVOVXJfa19Jc2ZBeXp0aWZOaUx4RWZQbzZjVTQ1TnMycUxnckx6cEZvWWl4MjRRZ0hfZG95SFNxeHFRcmFXeFhJNkMwT194Q2JoV3RsNjVMMXI0ZXQwOTBWRDJBVnVKaURPYjFFU3RJ0gHkAUFVX3lxTE5OVXVNMFZOcHA2VmgtSG9IeWNQUHI3VkVkNWNCajA5R1ZMRU1CeFBTaXdUeTlUVmp3SnpIQWFkMWZmN3FlMmpaRF9SWklDTTN2NXZpaUh6bnFPaDlsYXEyeVhaY2t0QnNFQjNLUk5kbklSM3JKOVpoTVRrcXRObnltb1lUNlFIMGhqbS1keDQtZ0NMaVlXczdIaDFrUGJLTll0QnJyTFFCalNRN2luNEF0Mk5fcnRkWWVHUTlIYlExY1pqWE9aNEgtWnVfWGhxMkxDNWItUWVKVTBDMm8tb09BdmNGSg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxQTkJvLTVFWnZVYjUzdzlrUVo1S0czRFJPYmxicEhnbTAtWjluYWY4dVNxc0hhSWxvemZwNE1iY0pSNlZHNkQ1Y1hmT1V3TV9BZXRQdnBNRGNQMEtOSHEzdGZuVUdWTElPbFZnWDQ2cGdQLU5FZVF4S0pfSTRERUpUem1vRXc2eGFib1o0dGVWOGQwSFF3ZGZKUUN4bXBpeDdXWTFZc3loekkybGdCeXQtSWdvYnhBclhjLUw5NUswRFh0YWZYaGFIdVRzOWFmMGpBN05TWGJhRm5wUkxFUktRUWdRQmhHSEQyZ2tBQ1dibWczQQ?oc=5</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>11-05-2026 08:30 UTC</t>
+          <t>11-05-2026 03:21 UTC</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Samsung Introduces ‘Certified Re-Newed’ Programme in India to Expand Access to Premium Galaxy Devices</t>
+          <t>Biocon Says Biocon Pharma Receives Health Canada Approval For Micafungin For Injection, USP, 50 Mg And 100 Mg</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>samsung.com</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQcWhuV0JTVUJFamRiakJFMVhJQkVNVmhiMVhoX3BPc3JVLUpnX0M2XzBxanRBS3RlMDl0ZXF3NHRBQTRJZ0JQaTU0eF8zVEViWXAxbzVycjVZd3FWekRCbkNNVEFWQlRsUlplZU44Y0pZM1VYd0lmQmpJRGkwdUNBOGxBNWpKTUNBVHFjR19SMXMxd3cyV212NVZLcjZGY2xwUk9lUWZWT0J4VTM2NC0zUnFSZTlkZnJESV8wN2k2Q2lId3hIZVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxOY0xPcmtzVzhzYVNxNlZmMDVuY0JfR3Y2cm1HUmZZVjk3SkdZNzFxVWtRZ2RWQk8ycDVIQ0VzRFdzQ0FaVGZYM1FfODVTWW81M2hBdVpqWllPeWpOVXBqVHQybWwteUdsZnYzYVNsU29iSWNTVmtZcXBhdy1JWHd4UFYzRDNqeWtuUWgxTm5oQ3kwYmVScEM3X0RKY0VrRGJ5RVU3VWN5MmkwcG9hMnRzWVJ2T0xTMTN1eDZhS1NnT2J2U0dLTFBFMjk4X0VFQ3ZrTXQwUzR2aHR1Y1JqR213bWI2bm9aSmRWVlFSVW4yQzVqSUFHUVhTMVpPRzBUVGE3N0pHR0U3d0k?oc=5</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>11-05-2026 09:48 UTC</t>
+          <t>11-05-2026 03:05 UTC</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Samsung Wide Fold design revealed in leaked images</t>
+          <t>Watch India's Biocon on Generic GLP-1 Push</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Mashable</t>
+          <t>Bloomberg</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE05cURzWE1uQ0ktU3ktLS1MZHIxZ1RsWWd6RnA0WHVGakozZmxIcnc1aTRJNmJmNHJhNTh4ZmxYWHRGVTdaZUtCZWlRRXpIQ2JzZEMwcmY1cGpualozbkxVYWxQMDQtR2Q0amc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQell5ZjBUZUdtVHEwX2pteVl3SmV2RFEzVkNrRmtHOVhORmRCczNaZEhlRV9jSW5CbmNBSzllYnhkVmhEOGNGcjNlSy1rcVJBa2V3UXE2ZlJsay1xRk1Lb0F6eWxWNEZoUWNnSFFUSFhCck9tX3NfTUtfNjMzeW5zUThycU9JQVdBLUZmXzdNbGcya0pMRWc?oc=5</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>11-05-2026 09:33 UTC</t>
+          <t>11-05-2026 00:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Samsung strike threat puts memory output at risk as 18-day walkout looms</t>
+          <t>Natural Biocon Standalone March 2026 Net Sales at Rs 0.88 crore, down 34.99% Y-o-Y</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>digitimes</t>
+          <t>Moneycontrol.com</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNZGstcnZ4ZlFnOWM1RFVJSmNIUUg1QmMwQXlzX2tZZWZuZi1iVUFZdUVpTWUzM3Z5Vm9QUDRlVWpNVmhfZ0FtWnZ1TlpkT1RSREwwaUYxVjl2cUpKek54Tm1XSmVtM1RRZ0FvQ2gtVTVuU0xYX3FHOWU2UDBOTzFFSGs4eEtZaVNNRjhTMmhsNDBabVk0T0RKTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxPZTVVb2I3dndmMjM1Nmh1d2Z2Y2RBbTgxWGQ4TVdNbWw5d1VWbnZ0T3hqMGxSdVpISThUU2x1Um5ySDVfQUdtM2pObDJYUHlMMEVDeDE5M1pEel9BcXdVY0pKTTdTTnB5a3JhZWRaTWt5RjAwNGtldWpScmJKYmoybTJzVkRMMGVtdlBHNnVLSkwzZjAyaGZxR1lFNDhocU9GR1kwN05kQkc0M19XTlQxZjc4NzZUNlFNbnBNTVhnTk13M1JJVDRjTFV0SGZjU0huMFp6dmhTUzJBd2U4eHNZ0gHkAUFVX3lxTE5EZ2x1YWtFMmpBQ1dSODI1c21uYU12ZEVsUFFVNnFWOGdaWFdHU1ZXMGhmVmg3X1U2TTh2VHhZdHhuWFl4OU13dnlmYUlDRnJfMVppelNqTXlGVWhSTEFXci1pSG5VQnNRMUJsOWVNUmxvaDg2UE1ZNTJMbTdpN0xJRTN5RzRpMDhha0g4OURiUXM2OWE1MjJnX3lGUXJ6V2FRVFRtLTBhNkFmWGhmLVE2Ymp4V3Y0NURESWZqbUhlX3JDcXdLSmF0M29WcmtXOFpLNGpWWkZtXzBnMlpHM2hLeWUxTA?oc=5</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>11-05-2026 09:14 UTC</t>
+          <t>11-05-2026 05:17 UTC</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Samsung launches four new Mini LED TVs in India</t>
+          <t>Kiran Mazumdar-Shaw On Claire Mazumdar &amp; Biocon’s Future</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>SamMobile</t>
+          <t>Business Today</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPRnJSLU9IbXBNcXdfc3JDSmtmVmx6T2U2elplQjVlZHNjbWRFWmRfbGxSTjNfWmtHMS11Ri1pU0ZVZnRFRUZxc2FfQXM1d1oySFRnYm5vRFAwdktlVnlYTmtiZjV5VVl3WGM1ajROZWNFQ0tNbm51eW12TUwyWXRvRXpIYzJRUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNdW1qUktleWdJVlctbXdsamlBNUlmN1JyUVRraVhqQVRNT0x1eXp0bHEtSEVDUlRTcndrejFUbzE1X2l6dmlzZlBfRHBDdlhDaXpVSlkzNG9Kd1BUSE41M3ZXUlEwSmJlM2xOclJNdnZuSjc5WEVRNzVjYnNXRGhZMVVQZ09kZXZ6QTVHWW13d0RVQ3JJZTROVm8wSnU3MS0wNWFubTRwSC1fcFQzbUpjbmJyQkptS2JCR3hRTEZOTmFQWFZa0gHEAUFVX3lxTE11bWpSS2V5Z0lWVy1td2xqaUE1SWY3UnJRVGtpWGpBVE1PTHV5enRscS1IRUNSVFNyd2t6MVRvMTVfaXp2aXNmUF9EcEN2WENpelVKWTM0b0p3UFRITjUzdldSUTBKYmUzbE5yUk12dm5KNzlYRVE3NWNic1dEaFkxVVBnT2RldnpBNUdZbXd3RFVDckllNE5WbzBKdTcxLTA1YW5tNHBILV9wVDNtSmNuYnJCSm1LYkJHeFFMRk5OYVBYVlo?oc=5</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>11-05-2026 05:12 UTC</t>
+          <t>11-05-2026 08:07 UTC</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Samsung Mobile Phones Under 40000: Best Models &amp; Price List May, 2026</t>
+          <t>Aurobindo Pharma Ltd: Valuation Shift Signals Price Attractiveness Change Amid Strong Returns</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Gadgets 360</t>
+          <t>Markets Mojo</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE81VlUwMzVHamZEVy14Y0JHSDllaWdQQjVDWGJvR0sySTlSU2RYUmdFVkxMQllyMkt0Q2pJQ0tXQzM2RHZyUzZuOEI2bjRXME5mZ2lRS2RmTHc3dnNVTHJSN05Xdm5PSlY0SEt1ei1mS2kyWTVaWlNWcjd3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxPdmdZaHJ1cDN6SWNZMU1MZ1lIeTJrRElxUFhkRlV5clNWZHRuaHA1X2dNX3BiV2ZjT2szZ1I2ZFJrTWlLLW55X2xWRk1PWUdRSFFfVGstOHNSb0NWTU92YUdERXFxYTJRWFM0a0Y1ajdtalc0UlFUMDE4RG9kUmdWeFhWQ05rWVA4VTEyNkhVbUxhV3NvTFMyaEtONjR1S2o3S0NhSHJqdTNhVEs1NzYxb3pBMDN6UHBtdGhNZjg4ZWcxakFrX0FUcFh6YzBHZm9peFJyYUFUVnZzQ3U0WklDTzVrY00?oc=5</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>11-05-2026 04:55 UTC</t>
+          <t>11-05-2026 02:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Dua Lipa sues Samsung for $15 million for allegedly using her image to sell TVs</t>
+          <t>Indian pharma majors commit $19.1 billion to US expansion</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Reuters</t>
+          <t>The Pharma Letter</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQM0NqTm5SWS1Ic2Y3MnpIbVZTdzY1dVg1dWpRY3N6blBrcnoyWGRJWTY4Y0FoN2ptS2p5a3RoaE40SUI1OXZrTmN5S004NHFQVFVHQjF1elg0eGFtSDhjLTE0QmpramN0d00zQVdkVzZ4dXhXVFZXZWlkSF9vR0xNMzVXblV5dk81ajBVODJqeXc2dXFxWTZ0eVVfaU9IU25wejFYdU9aLXIxN1pMMTJlTV9EWHhzc2x3MzAzSw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOZmRyeFRDbDFiYklqTmNqNE1QckpBQnVodFBqeUd3enN1c0ltcS15WUpvcWVOMnVrUUNrZUtkOFloZ0Mwd1UwNk4yblR0R0VtTkhtY0tFSUNVT2d6Qm9ZTzlBUWxSeVB2S3pJd0lZUkNOTVZDem8zVEg4blZLSVUwTi1oUFV2a2p1WlYteXk0eHF2RVl2dG56cE9ON2ZJbTZEaHc?oc=5</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>11-05-2026 12:50 UTC</t>
+          <t>11-05-2026 10:17 UTC</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Samsung's Next Big Android Update Is Out Now. Here Are the Phones That Will Get It</t>
+          <t>Biocon arm gets Health Canada nod for fungal infection treatment injection</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>PCMag</t>
+          <t>ETPharma.com</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNdTJlV0JLd0FSaDMyNGZ5RE9tRy16SmZUakFMX1JWRGZCdmtwMkViMGV2RlF5QmhGNUVVdlptYXZzeTJEaXo5MTFwOHlTV1BRWjlPME9lektsUTdPdmtjMzBURVZCS3FSMmlCa1VUa0xtNGgyM1JBVnpQamlhWU5MbXlRQjh2LXVfZDQ1NFBBYldHblRlNE9Yb2V2TS1mcmJ3SkE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxOd0w2SktnTU1UaUlOcVlNcm11NlhTcy1Hc3B1VVdJQmZoZmp1MzlMcThFVWZLM2xMTnl3NlpVcGtJREJBZzgxWFR1QWNocWRiOG1IQmxmZDlneklRTW5NVWJ2U3lLUDJObThDanJ2eHl0eGFOVFV4SkdKWUp0X0xlZDlsQ00wTDRtREcwRG83dnVhVnhiNVE3UTlyQk50d3JwNFN3Z3RCNV9MemM1bld5R0FqRUxWbWRIRm8wNWF2RHBveS1DcUhtaGZweVktdUZFMENCMGNReXFzY3pvem1uS2dXWTl3ckNNb25QRkpOcWF4a0phb3RRa9IB-AFBVV95cUxOd0w2SktnTU1UaUlOcVlNcm11NlhTcy1Hc3B1VVdJQmZoZmp1MzlMcThFVWZLM2xMTnl3NlpVcGtJREJBZzgxWFR1QWNocWRiOG1IQmxmZDlneklRTW5NVWJ2U3lLUDJObThDanJ2eHl0eGFOVFV4SkdKWUp0X0xlZDlsQ00wTDRtREcwRG83dnVhVnhiNVE3UTlyQk50d3JwNFN3Z3RCNV9MemM1bld5R0FqRUxWbWRIRm8wNWF2RHBveS1DcUhtaGZweVktdUZFMENCMGNReXFzY3pvem1uS2dXWTl3ckNNb25QRkpOcWF4a0phb3RRaw?oc=5</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>11-05-2026 10:24 UTC</t>
+          <t>11-05-2026 11:26 UTC</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Samsung cuts prices on Galaxy M and F series smartphones in India</t>
+          <t>Global Oxycodone Drugs Market Size to Reach USD 9.21 Billion by 2035 – SNS Insider</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>t2ONLINE</t>
+          <t>GlobeNewswire</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPVDJPMHdVbVdDOWZRMGxaQzFJZ2JoZFQ2bjJaRGJrN2FtRTdTeVJWR2ZIdmo1NDVRbWNsSllOYjJtYVN0RmhSSXNOZ1M4cndVZ21xNEI1dzV1by1oQmlxSloxdzM1MGttUUhMU2NsZkcwaTB6ZTZaT25qUmxfSXd3MDRPSzFzYmNaYlU4UF9GTW5ETnJhMjhFMXd5eDVWX1ZFR3N4YjR2VFJkVHJV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxNTGdNSXB6RnFHa3dyNFJ6WWd6MWtCSTdyYkhXTC1Kd0ZKLWw1Ymk5TFNyek1LQ0hLRXJJYk5yd1lrWFViUnRhcGNjU2NlbWk2T1BVd1NFTkRxck5qMlp0Zkl4MkpjTTJJLUV0OGhlZS1CbDQ2YUQ4VGtmd29LOXMwX2JaRkhiMlJIYjlfLVdvNXVibWF1c1o0RFRCTXg2MVBvTUowWkYzWXFhMU1VZWRiU2dmMEhGdWFLMEdwTGpxR1NZUFJ1ZVk4andwbDY1N0stemFrWTFYUFhZZXpJWmRTNXRqRm1MRWc?oc=5</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>11-05-2026 10:10 UTC</t>
+          <t>11-05-2026 12:29 UTC</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Samsung One UI 8.5 Release: Millions Get New Galaxy Features Today</t>
+          <t>Vinod Jain Appointed as President – Investor Relation at KPI Green Energy Ltd</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Forbes</t>
+          <t>hrtoday.in</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPb2dBQlEtbU9WUG9pSlJfRGR6clRTMGxTUjExWVVkX1YyeUE0LVMtWUQ0R0pseVpIOWhkQlQ1Z1ZIbnBHWDU5ZlUzeFlUS2NhRk1XQjZKczlPQWtuakpxQlZzeUxYY1FELWRJSEYxV2hCY0VBelRGcHVleUswNVZ3T2x4YjBZbjBEaWpPWHhFSmNYWEF6N2h5RnJR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOYkJDelVhaTFzYUZxclQ0TGZPbDF4cGI4UGVEUnoyRjBGaWJ4RGNGUmVGWGY1Q1FOVVp0R2xQdXZCOXBPenoyalVfSmpHcVh3MzcyS2xta3BGRGdabWxfT2otbW9GX2hDdFJNVVVHR250emZueS1kd1dyTk14VTFqalZyZUxwQW00aTRqZGthR1ZzeDVvUGJaTHFQYw?oc=5</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>11-05-2026 12:43 UTC</t>
+          <t>11-05-2026 07:41 UTC</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Samsung begins global rollout of One UI 8.5 update with new Galaxy AI features</t>
+          <t>Bajaj Electricals Receives Appellate Order Upholding GST Demand of ₹2.69 Crore Including Penalty</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Storyboard18</t>
+          <t>A2Z Taxcorp LLP</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQQ3ViM3RKTmZtTXlxYUxXZ2d4RWxUXzdLdmhmcWZvaEplQzQwVVlOMjQ0MlhRMzhTSjhmNWZEb0QzSHItcmpsQ0FMVkFuRFFzM3VZaWRxZEFuVkpxVFlLR0xzcEI1a05QeUI3U2JrbEFrc3VwN0NvVVFoMmVaVWFTc1cyd0ozamJ6UFo2X3FOWHNOUDRlYWFRenBNV2ZVT1Fvb19mTU5lNE5DcFpkMmpOaUY3dGttanBrc2Iyd0RmVXdZLW_SAcgBQVVfeXFMTkNzV3JkTVBERkhybFc5SWlITE9XeXRadUxlMk1rU3ZVcnQ2VndMTnB6Z2VlM1VxWjR2ZUVpR2t6aEt0MjYtc1RTbTdfQmNDY2F0UnhKSlVQLXhhdEFfNV9NZ1I3cjhPRHVPaklldS0xWktpMTNGRmpVM3RtcGZ3R0JhQjFtNmc3enFBM1FjcmREdWRrcmhMUzJYRFgyeWQxazc4ek5fU2NIUlB6Q2FWS3U4OVg2eUhrbHVYQncyNFRha25RdUVKcHk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxPMUU2LS1nWlFvTC1xNUNOa2Fxbi1yZUgyek15c0FTTDQ3WFNhX1BYMkh4M0lncmw3MjFrUTVNLUZoNlEwa0FfcW5ZLVBKS0ZXdUlrR0p5WUFBOG8xNnIyVkd0c1ZLUk8xTG1rZDNrR1B0clVsdWtmRkhNSkpScXM0X1BzWk1Lb1lFdlRaM2tvNDJqOE5XWS1JTHBpUU5RVUZmWFJsWGxBdGVtSHNPQTNCNU4zLXY5ckNjMXRSbV80VURMNGZ3WlBZ?oc=5</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>11-05-2026 10:27 UTC</t>
+          <t>11-05-2026 11:23 UTC</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Samsung launches ‘Certified Re-Newed’ programme in India for Galaxy devices</t>
+          <t>JioBlackRock Flexi Cap Fund exits 3 AMC stocks, HAL, and 13 others in April</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>The Times of India</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxNTkhyS2NfcGRhSzgwVDYtV3ctdUp1eTF6ak5GU3JON1VheEVCcFpLV1d3X2M2VG9kT3dnUFZuQ1RxOTJ3WUY2Y0NsRUZxbzh0MkZRTXI2S1RNbUVjUV9mcHBfaXdBZ2tLeVBGVm4xX1ZsclRvYzdSS1I2cUlRMDE3OEpOX1BTZWQxQmxZdXpjOTE4NHRaWXJXRWNSaDJfenEtSFpVQVN4TjJLWmQtRkxGQ0N1VkNLMzBRdkVkVDNtSHBKclp3aWRTV0JETTFWeGpNSG00SWtTemVGdXF0bDJrTEZnMFYxV1RnWEZ0OWF0bjTSAfYBQVVfeXFMTXlnbUc4SnMzRmJSb2wtNEdoaGdGRGtaYmE2SjJSdkdSZGZxSmJFSEN4NnJrdUxLSXgzZW9DV1k5UUF2aGRHS1hWdGcxdHl6cTdOZG9RLVBnTXpoNVlyN2t3R0hIOVVERmdTTkhyM2NvN1hYNVFCSDU1OXl1YkQteVRRekR3SzYxeDdFMkZodW5WWUJ1UWV0VU5ZaUNtTzN1S0JWWnJDbHhwU2JkYXZ0dGdWZXp1RXBZQ2JvZVFPOFljY0NicUJJblFSejdwS2Y3aUlSTmd6Z2JGZmZZQXd2NTFnY3A0OUtaQjdPZUdqN1VoN0NUY0t3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxPZjNyY3ZBR2pZVXpabDF2WFp2UEZoeFJmN0dYWHVadVp6bEJza1Y1Zy1HYW1ReVo3QXR6RDFlcFg4bDI2RkR4WjFhVTZYRkZCNzk4dlEzUmZmQUg4UWZxOXI5dU9kY2JkWUxONl9hT3dnZ3ZOWHFQZE1IaG9TTjRURGU0amxDeC1ZNGRqemhrckFqUjlPWnMzS0FOVXFkWWdkZ2k4ZXBTOFhIb2JOd0FIMFIyWko5bjJ3SUlpUlFCZUZfbGxDeVhaUnJZSjliZG5MeG5QZGRlWGY1X3fSAdsBQVVfeXFMT2YzcmN2QUdqWVV6WmwxdlhadlBGaHhSZjdHWFh1WnVaemxCc2tWNWctR2FtUXlaN0F0ekQxZXBYOGwyNkZEeFoxYVU2WEZGQjc5OHZRM1JmZkFIOFFmcTlyOXVPZGNiZFlMTjZfYU93Z2d2TlhxUGRNSGhvU040VERlNGpsQ3gtWTRkanpoa3JBalI5T1pzM0tBTlVxZFlnZGdpOGVwUzhYSG9iTndBSDBSMlpKOW4yd0lJaVJRQmVGX2xsQ3lYWlJyWUo5YmRuTHhuUGRkZVhmNV93?oc=5</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>11-05-2026 11:20 UTC</t>
+          <t>11-05-2026 06:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Samsung Electronics Announces First Quarter 2026 Results</t>
+          <t>Lupin Ltd. Valuation Shifts Signal Renewed Price Attractiveness Amid Sector Dynamics</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>samsung.com</t>
+          <t>Markets Mojo</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOWUVwY3RuMVpmN0E2LXdudkFMWjl3VjN6MWp3Vnk4VUUzTnkzdGVRNi0wWXN1MnpRODQ2c0RGWE9Wbjg5Y0RfejdZZUVjZGJGdi1GdDVCdzlzWjBNU0hQbVVtTGJab3lNakR2S1RKSzdOVTVrVDZVV0xoWU45ZFFoVjVZUDdsTTRqai0tVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOekRHZTU1QVZPZkEtQjZXS1NReHlJcXlTOXI3dlR5UnlvOXdfT2dWdHh0cXBGREJIcjdlYjdrM19ROFFuQ0lCQk9VWk0xX296ZWhCYndnTXFhdFdXZDZQbkdwNDhmUHlkRldpVTMwcE5WeDA1ZVktWUJKTHhwZVQ2ZUVyOWFGbzE0THVscGFGZVlNdVFnbmpoVExXYkE2cjhjSUFvaUdRaTV4TkJCZUcwOEl4TzJRam1jcW0zM2lmbW43ZUVhbEs4cEc1YlkwdzZXUDdlY1oxbFI?oc=5</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>11-05-2026 08:08 UTC</t>
+          <t>11-05-2026 02:50 UTC</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Samsung starts selling refurbished Galaxy phones in India</t>
+          <t>Pharma Stocks Today, May 11: Torrent Pharma up 3.77%, Lupin falls 4.50%, Biocon rises 3.36%</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>SamMobile</t>
+          <t>Business Upturn</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOd19HYURqcE8tV2JhLWdJU2l1VjU2T3VOVVVJc3FUdDNCdnVvUld1a2wwcnptdTZhYUlpSGJJTkpnWkUzVGNSTnFlWmd0MEhUaWN2VTR5RzNTVzVZNEV5Tk9ONVhycUZjb2RYTHp2aVJNWmpIS1hBS1pTM3dkamJTcUpPS1UxQmk4R2MtRzhn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQV2JfdzVNTkV4Qlk1X0xPeFNiRjh3MHUyZTI2dlhiZ0ZWaVp1WkNJXzNfLWttamg3SmNKMGxicjJLa1NYdExpcGpGVkJneWJaVkY5VWRvNEU5eGN0VmN1WUZOUVhtbGp4UHlfZTR3MXpTaDlUaW02SzhjTTRFUzExZVdEcGRJN1JfQWFUUy0zQWYyM3JkemRLUFh0Y1lXdXVzUUdVZkktZlhnTktBMWtOelR5NW5fck9IV1NsLXFWbDJHRVVVWDB6VllObi1wTWFnTm9J?oc=5</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>11-05-2026 11:27 UTC</t>
+          <t>11-05-2026 08:48 UTC</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Zydus Biotech</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Number of shareholders of Celltrion, Inc. – KRX:068270</t>
+          <t>MSc Microbiology Job at Zydus Lifescience Limited | Walk-in Interview</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>BioTecNika</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPc1NRNHllQ1MzczF2T2JCb0pQRHBjX1lTbjV5NDN5NTRGRW9Zekh5NVdyNndPSlotdHZYck8wUE0zRTE0T0NQVEVoMWpHWkVYbHNHWkFWbVN6S3hHSVIzNkx0M2JQV1pra1pOZm5mZllNNjBRaG1JSURuU09wNlZFc2habGJ6bmx0eko0Q0dqV0dMM1dfUFZVN0RuTmM3dndseXhaOXh3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxONlJzZGtZMHBCMFctTjNud3dRck45WDJEWUNhczFYUGc5aGtFLUF0cnhXdjI5UlZYdWdvSkhWUklDR0tjYVhOM2NCdFhzdEU0eGRjck4tTEh4RzlfMDVlSF8tQ1FKV0lDNUNyNy1Vakx4aVo5YmpTR0Q5WDlpc3NqdzFOZUV2bDVULXhNNVZR0gGTAUFVX3lxTFBUWmNsSXItWklmRUhNZjF2NktwdlRWWnlBOWlhb1lHbTM3WUg2ZG5QZWZ1Um9lcDZfdEczb0VoZWVyVF85SlEyZ1ZuZDhFcXZ2TnlYRzNOTnpxaC1yU1FJWFhvQzZ3SVczN3dIOURxZnRlV0tZOTF2T2pVUEJyUXdRNjAtOFhxYkRsU3FCVWZ0NEhEWQ?oc=5</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>11-05-2026 01:47 UTC</t>
+          <t>11-05-2026 12:06 UTC</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Zydus Biotech</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>"Confirmed Infection Within 20 Minutes" Celltrion to Launch COVID-19 Diagnostic Kit in July</t>
+          <t>Zydus collaboration lifts Agenus (Nasdaq: AGEN) to Q1 2026 profit</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>아시아경제</t>
+          <t>Stock Titan</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxPWk43Zk9VLXlTdENJWGRRMWhOZUNJWkRzU2NHOFdNUnVPeGd0NlZRRVI0S0lsTnNkeVBiVzYwNk9nZUpTYlVTcmZhOWZWMEw3dy1xM0hPYUthQk9uRGp6SEpVYktha0hCVHhobjYxeWlLblo3ei1vdXE2Q0tkbWduWHFybFZueTNVRUIxUHprRFJNUS05NUdOb2cxUk9tT21xd0lDOTI3cVRKR1FRMl96NXFDaGtSSWZ3bkpPT1JDaVVoOWZiTXRBY0JBa29BQjhtZTV3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNbHd5VEFOTk5FVHpDRWZicWx2SDNTUTZSZk1kd3dKTmFWUnU3RVlDVGFaT3dzd3NHZlFsN0ZZSXI1TFZqT1gwQW5ScEY4OHRmTGQ1dmFibEFxdTdMQW5uSjBreWdiVmFOd1NpV1Q0X3lTRExuRndNUnpjMVBoMEdoT0xYWjM5dnE3WmZqdndoTmJKWjFOOE5jbnFlekRSM0Z4?oc=5</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>10-05-2026 15:04 UTC</t>
+          <t>11-05-2026 12:52 UTC</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Japan's Daiichi Sankyo unveils five-year business plan focused on oncology innovation</t>
+          <t>Samsung Introduces ‘Certified Re-Newed’ Programme in India to Expand Access to Premium Galaxy Devices</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>BioSpectrum Asia</t>
+          <t>samsung.com</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxPdXFRYlJJUEZWV2w1U0djSGpHMFpGWmpSSnhnVktadVUzdW5HVy01WHRVWHlEMUplNkZpb1Y1Mng1eEl5b1F2dVJvb1VxOElyc0ZNSVJrZXJ1ZXJQcjJCSWVkS3I3a3lpQmZkQXdjaHpoak1DZFhKdUVvSndwZ2I0NFoxN05lYWJoNUNIeXdaNE1QTVhmci1OM3drcGlQQldhaE1hLXE0SXV1UVJRWEZ2MXNpcnlzaXFnMldNMVh6d2NLZVJzWFRsTF9zSUhFVk4w?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQcWhuV0JTVUJFamRiakJFMVhJQkVNVmhiMVhoX3BPc3JVLUpnX0M2XzBxanRBS3RlMDl0ZXF3NHRBQTRJZ0JQaTU0eF8zVEViWXAxbzVycjVZd3FWekRCbkNNVEFWQlRsUlplZU44Y0pZM1VYd0lmQmpJRGkwdUNBOGxBNWpKTUNBVHFjR19SMXMxd3cyV212NVZLcjZGY2xwUk9lUWZWT0J4VTM2NC0zUnFSZTlkZnJESV8wN2k2Q2lId3hIZVE?oc=5</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>11-05-2026 07:23 UTC</t>
+          <t>11-05-2026 09:48 UTC</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo posts Q4 revenue growth but reports operating loss</t>
+          <t>Dua Lipa sues Samsung for $15 million for allegedly using her image to sell TVs</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Investing.com India</t>
+          <t>Reuters</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNYkJIbzNZNDR2TXdYUkM0SHZfNEhZY0tCei11TGZTNjVWSF9vT1VnNTVlWEFhRnBQLTZnMURxa2o5VEQ1TkUxdGFuQmpPOVhKeklRNHhnNFFQOVFnZ2lwYW16TW42QjB6MUFTLU92VjFXeVdzVEE5TnZZaUhyUlU1N1NpQ25BTnRQaGdxN0pZcXlINmpqWk5vM2phYk95c29SaEpBZzlxT1JsZTRjUDZIWEdJMzNfdHNs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQM0NqTm5SWS1Ic2Y3MnpIbVZTdzY1dVg1dWpRY3N6blBrcnoyWGRJWTY4Y0FoN2ptS2p5a3RoaE40SUI1OXZrTmN5S004NHFQVFVHQjF1elg0eGFtSDhjLTE0QmpramN0d00zQVdkVzZ4dXhXVFZXZWlkSF9vR0xNMzVXblV5dk81ajBVODJqeXc2dXFxWTZ0eVVfaU9IU25wejFYdU9aLXIxN1pMMTJlTV9EWHhzc2x3MzAzSw?oc=5</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>11-05-2026 11:26 UTC</t>
+          <t>11-05-2026 14:36 UTC</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo Company: Strong revenue growth led by oncology, but operating profit impacted by one-time expenses</t>
+          <t>Samsung Galaxy S25 Series Gets One UI 8.5 Update Globally, Including India</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>Gadgets 360</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwJBVV95cUxNTzlFWE9Cdm9kZDNJRkdEM3ZBdzl0VEVVNjV4NHl4NE5DemFBT3VONWN4LV9MMXZPbXlSVHE4eEJMbnJXc0JhTjJiX0VHOWtaLXZuVElLdl9oUUlfOFcyb1RJbVZLcHpEYkk0c0xGZmw0WFBiaGZwUzdQcGF4NmVVS3JaOFJVMk5raUFfcUcwQ1FIb3A1Z0lobVBYRVI2X2EzeWN2YkxVaVgyV2xUU2ZTbHE5bk04eHBmaGh4NXZfU01HMnJZNTBHQjBaOGs3VkZISVBZeExoYkVyeHBqWTF0SEhkTFhwTm9zaVIyWUZnWXN1YldoOG9VMDE2elRCRzh2MExnZHhSUEdROFFYd2JJc2dyYy1abHpPTklvVUdzMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPY2JSdTdqcTNRNS1JWkJsajdGaGJWeEczUXc3bFFGcUFrOG1ISXVyRldmbEMtdUV3REV4MWJPeEdqZVVCc2cwWWlDZU1Jb0FxTVkzaWVUT3hOVHdiczFSTG1LN2xoYlJnSkY1U2xEMXRNQWdERUI5a19wSWJiRlAyUTk5T3dQcVZQRGR4WDVfWmpmQVNqbXNtUWlXR1VHdkg5NnpMVWZLNjNlS1VySW5HN0x30gG3AUFVX3lxTE5tLXVJOEYwNDNmaVpnc2otRUFLSGdKRWt5V0ZQbUxUWXJBWDBXbVRKT3d2RmdQeWdRdzYzR09CY1UxU2JlamxPNVEtY05Kc2ZoeEo4b3cyVzEtYjRoUTlFV2xDYjlEeG8tenAxalFnQklZMGNZbUpvcGw2ckhVeTBfR2NORS1FUjdEUVRBUDJ3ZXhrWkhEdDZrX0MtX2QxNTkzanNzOTNnSUxYN1VRcWRtNmZoUDZ6cw?oc=5</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>11-05-2026 06:40 UTC</t>
+          <t>11-05-2026 12:03 UTC</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo Unveils New Five-Year Business Plan Focused on Oncology Leadership and Innovation</t>
+          <t>Samsung One UI 8.5 Release: Millions Get New Galaxy Features Today</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Business Wire</t>
+          <t>Forbes</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxPYTFON3k2cG5HUUZxcVBUU1NaY0hIbVlZaWNQNjh1alIwN3o0WFFzQmFSU3FGSWcydHdYTGJWcW40VllGV2VVa3ZYeXVDQk96TE5ieUFTVUx3UWxlOWxYWTNXbmxVY25yaWRTc2tXb29xNF9IRGhvYTNHVlNXNnl1T2F0LVlwMnVYVjByTXc2UUxwUlMxME1tX2VaSlE2TFh2YXhLZ2ZTMTUteV95T0lZV1dmaFpfUGlGSTBEZTVZUkplcmZ4bHJEbnNfZTRSNkVBTXZWbGhZa09TODF5Q2F3ZFFGdmNiTGlV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPb2dBQlEtbU9WUG9pSlJfRGR6clRTMGxTUjExWVVkX1YyeUE0LVMtWUQ0R0pseVpIOWhkQlQ1Z1ZIbnBHWDU5ZlUzeFlUS2NhRk1XQjZKczlPQWtuakpxQlZzeUxYY1FELWRJSEYxV2hCY0VBelRGcHVleUswNVZ3T2x4YjBZbjBEaWpPWHhFSmNYWEF6N2h5RnJR?oc=5</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>11-05-2026 06:30 UTC</t>
+          <t>11-05-2026 12:43 UTC</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Daiichi aims for $14.6B in oncology sales by 2030</t>
+          <t>Samsung, labour union make last push to avert strike before May 21</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>FirstWord Pharma</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTE40UGF3RWRNUVhyRk9nMUtsTDF4SGNVcWdJTy1iTkI5WnJxakE5UExDZzdOakVqWjYyY1g3WjlLV2RnQUtNLXE2OHF0ampDRWM5VmE0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxQLWlKQVRwczFqWXpzZGpVMzA0bURITlp6WkN6WHEydDRGNWphdHQ4VndVNFFkckx4ZUFiV0NnX09RUUJTNU1uRWRtUzU5V0YxNFJqelY1dGljZEptYUdxdmFxNlRSRUNkVkh4NnJnRnpyZkNzc1hhTjVOVXJfa19Jc2ZBeXp0aWZOaUx4RWZQbzZjVTQ1TnMycUxnckx6cEZvWWl4MjRRZ0hfZG95SFNxeHFRcmFXeFhJNkMwT194Q2JoV3RsNjVMMXI0ZXQwOTBWRDJBVnVKaURPYjFFU3RJ0gHkAUFVX3lxTE5OVXVNMFZOcHA2VmgtSG9IeWNQUHI3VkVkNWNCajA5R1ZMRU1CeFBTaXdUeTlUVmp3SnpIQWFkMWZmN3FlMmpaRF9SWklDTTN2NXZpaUh6bnFPaDlsYXEyeVhaY2t0QnNFQjNLUk5kbklSM3JKOVpoTVRrcXRObnltb1lUNlFIMGhqbS1keDQtZ0NMaVlXczdIaDFrUGJLTll0QnJyTFFCalNRN2luNEF0Mk5fcnRkWWVHUTlIYlExY1pqWE9aNEgtWnVfWGhxMkxDNWItUWVKVTBDMm8tb09BdmNGSg?oc=5</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>11-05-2026 06:55 UTC</t>
+          <t>11-05-2026 08:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo's Attributable Profit Falls 12% in Fiscal Year 2025</t>
+          <t>Samsung's Next Big Android Update Is Out Now. Here Are the Phones That Will Get It</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>marketscreener.com</t>
+          <t>PCMag</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQVkNVMWJDLUVqTHk4azlzdmhWWkhZWU82ckZlTWN2ZG5UVkgtZ3llazdlRDA4YndKRU5jcDZJSm5vN3hsMm55UzdCMlZLT3RYUEJRRXkyQTA5eHJ5d25kdEV0RXFicmpFMVdidmhzUVY4TmxfZDJkdU1FQTZHbm9KY2NVb0Z0dmd0R1p6ekRlR2U3WlBOSXVSYXhMNmxnNFdENnZ1UERYbGl4U2ExLVphZGxSMDRlQ3FoM3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNdTJlV0JLd0FSaDMyNGZ5RE9tRy16SmZUakFMX1JWRGZCdmtwMkViMGV2RlF5QmhGNUVVdlptYXZzeTJEaXo5MTFwOHlTV1BRWjlPME9lektsUTdPdmtjMzBURVZCS3FSMmlCa1VUa0xtNGgyM1JBVnpQamlhWU5MbXlRQjh2LXVfZDQ1NFBBYldHblRlNE9Yb2V2TS1mcmJ3SkE?oc=5</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>11-05-2026 09:48 UTC</t>
+          <t>11-05-2026 16:17 UTC</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Daiichi cuts forecast after $606 million ADC supply-chain hit</t>
+          <t>Dua Lipa sues Samsung for $15m over use of her image on TV boxes</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>The Pharma Letter</t>
+          <t>The Guardian</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNTDhmdkZYODJ4d21IUHBoZHBrUkJoU1poZDhqa0d4MEVPZU51SU13X2ZkNDY3X1hyTTNrZnh0eV9YR1BlQm03dms4TV9qdTROQU1EN1NZeld0emRkdHdfMjFPNTZyUG5ZZnlWRDBDMTlHUThzeUN2RUQ5VlY3amktTl82MkhPSXhJZGZ5WmRzaVJMa3dzenBURWx0WDFFSk0yLWM1VjZnbw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPVWQ1eFQ4VVdxdmk0SWV1UmdaZERwV0lWSkJEbVNqY05tMXktTTdRQlA4QVBaZGxjU3YzNHBfU1pFOWY2emcycFVseFJGdk9IOFd2eFhCWlAyWHpGbXUtQzh1RVkyTHN5ZkNsQXBZVnZ4R0NucFhuUUJGSEdRNVhMNGxQb01xV202M3VnWW9zb3BMVkhFZ1NrTQ?oc=5</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>11-05-2026 10:17 UTC</t>
+          <t>11-05-2026 16:10 UTC</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo FY2025 slides: oncology surge drives 12.6% growth</t>
+          <t>Samsung Galaxy Buds Able: Clip-style open earbuds are likely on the horizon</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Investing.com</t>
+          <t>Mashable</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOcEQ0NVJzSzVHZzFmWEVHT0FOMXJBc0UxeDl6S25Jb0NMNHg5THF0aFY3QmNuTG9qRmpBZGV4S1pPZXNMNjlqbXhpcFhTd1Y1dWE5NHd5azFGcUNTSVhWX0ZTdDUyVjVXT21zcjdCcE4ydUkwRHBlVWxnaTNMMkdzTDQwck5ubHNkNlR4ZHNkQjdobGVUWWJ2OURlLVRfV1FxTXB0VHVCNzcxNUpsLTZlLWplNVd1bVh5a3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE1CY2NCR09oTy0xbE5xcnFXTHJPZ2tTR1ZZTlNGWW83NTktWDlBamhmZ1ZsRmh6bFlPekNjZ25UZjhHWElKQXRGOEkzaUxpbUhra01qTEdkUlk0a0kzNkY3UXRqY2VCMWx1T2VyLTZXdmFsN3ctRDJfYUk3WQ?oc=5</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>11-05-2026 13:18 UTC</t>
+          <t>11-05-2026 12:56 UTC</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo Company, Limited 2026 Q4 - Results - Earnings Call Presentation (OTCMKTS:DSNKY) 2026-05-11</t>
+          <t>Samsung launches four new Mini LED TVs in India</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Seeking Alpha</t>
+          <t>SamMobile</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQdjBCOGh4NmZCMnNnVWdISzlVRlRwUURGMWlFa0ktaWRZbnhCc0w5TUw0U1hLVjhCbUNQOHNYanVpX0RwVGt6TGpSRW9YRS1TWkhMTEdVVlM4c25QMUkxbTlyaGpLU1JwSWc1OHJHMUVFRV9WVlhPNEdPNlNYNG5RT2FuZmJLZXY4QjFZVEp1TjZ5c2tjWFByQ1loTzlCams5Ym5xZWd5bEZ6cUlsdjBoZTJJN0Q?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPRnJSLU9IbXBNcXdfc3JDSmtmVmx6T2U2elplQjVlZHNjbWRFWmRfbGxSTjNfWmtHMS11Ri1pU0ZVZnRFRUZxc2FfQXM1d1oySFRnYm5vRFAwdktlVnlYTmtiZjV5VVl3WGM1ajROZWNFQ0tNbm51eW12TUwyWXRvRXpIYzJRUQ?oc=5</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>11-05-2026 09:32 UTC</t>
+          <t>11-05-2026 05:12 UTC</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Daiichi takes $850M charge, axes facility investment as ADC demand forecast falls</t>
+          <t>Samsung strike threat puts memory output at risk as 18-day walkout looms</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>BioSpace</t>
+          <t>digitimes</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNTVBXRlc0eURfUU5Ec0MxY29TNk1STkFPMUl0NWZKZEdQQ191cmpkdVBJUGdDNnktbHl0cXZkbWc1ZnBWTW05T1R6MFNFSXFJV1JfcE53RkNiZ2JZZjJ2ckdSMGxEUHpkTklhRWF5RVJ4aFNjSzlMR0R5TFBXeTFKZkNodkV1YkpweXpFSms3ZEpsU2RKTHNWc0tQWFlZcllTU193b0Z0T2NUcmI1ZTVaa2sybw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNZGstcnZ4ZlFnOWM1RFVJSmNIUUg1QmMwQXlzX2tZZWZuZi1iVUFZdUVpTWUzM3Z5Vm9QUDRlVWpNVmhfZ0FtWnZ1TlpkT1RSREwwaUYxVjl2cUpKek54Tm1XSmVtM1RRZ0FvQ2gtVTVuU0xYX3FHOWU2UDBOTzFFSGs4eEtZaVNNRjhTMmhsNDBabVk0T0RKTA?oc=5</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>11-05-2026 13:21 UTC</t>
+          <t>11-05-2026 09:14 UTC</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo Company: Strong FY2025 growth in oncology drives new 5-year plan targeting &gt;3.0 Tn JPY revenue by 2030</t>
+          <t>Samsung cuts prices on Galaxy M and F series smartphones in India</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>t2ONLINE</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAJBVV95cUxQM2hscjA3d3ZyQXdwMUVXNmdRUlFncmJNNGVkR3ZNVzV0dDB6RF85M0lJalRJdTZFTmp6b2dtQVJtLUxfWjJKMGRkbG1vZWticm9WNnlXMnViUjQyWURFOWdvNmM5VlMtMWJ1WHgweThwbEZ4MHhXY25SU0xaY3VwUFY3dkxhTWZ4SVpleGJ1aFJJQVlnOWxkN1BpOVJHSmRXUktTcVotRkdaUDhxZDZOZjdDUDFQak91Q0pQREcwalYxaGRMUWFYZ0dzS0c5VTB6QXJxX0ZVcjR6WWRENU1OT3k2NHdlY0U4MHQ2SFNNOVRvR2NLY0RmSnI5b0czV3E1QnZpNVVpMklIeEtjcVlvVnBWNkVJMDJWblhvM1FIZGxrOWRh?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPVDJPMHdVbVdDOWZRMGxaQzFJZ2JoZFQ2bjJaRGJrN2FtRTdTeVJWR2ZIdmo1NDVRbWNsSllOYjJtYVN0RmhSSXNOZ1M4cndVZ21xNEI1dzV1by1oQmlxSloxdzM1MGttUUhMU2NsZkcwaTB6ZTZaT25qUmxfSXd3MDRPSzFzYmNaYlU4UF9GTW5ETnJhMjhFMXd5eDVWX1ZFR3N4YjR2VFJkVHJV?oc=5</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>11-05-2026 06:40 UTC</t>
+          <t>11-05-2026 10:10 UTC</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo’s Sales Rose, But Profit Slipped In Fiscal 2025</t>
+          <t>Samsung widely rolling out stable One UI 8.5 update, five months after the beta started</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Finimize</t>
+          <t>9to5Google</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOX0NsQmRhWGxlWVlMNUlXaHRoQ3FydHBxN0REa1FsRldBTWp6UUF3dURERThaQTNDckxTdE5NWGlZUERXY2cwa2JuQ1dWQ1htUmVGWWVoVHBlaERPcXpWdkFyWDM3RmhrZHVYWUs3QTJzN2dkT1N3b2d4eUFBRmJFeHhjUjVtd2hUREp6dFFSTUNaNUU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE9wd0xSaDF4bm80Q1VqTVhTTXFtRVlrU1dBMFYyNnNDczd1c1VIV0pSbFVnZHYxMlcxaE0zeVVyTElZZVpCcThwdnFnbloyTnFub3ZhSG1tbGVENzhwUDJZa2l3M2N5ZUNmalRpUGhlYS1DN2k2Zi13aHk4alY?oc=5</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>10-05-2026 23:55 UTC</t>
+          <t>11-05-2026 15:40 UTC</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo Co Ltd - to cancel 31,457,200 shares, 1.73% of issued shares</t>
+          <t>Samsung Mobile Phones Under 10000: Best Models &amp; Price List May, 2026</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>marketscreener.com</t>
+          <t>Gadgets 360</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQYWV3VXFzSmhlVkl2a3dGWDhKWFRNYlpFRi1HZzhEWm43bjFZS1pnR2tfdGhkQTdJbWlqbHBVbVZUbU14RlNhREYyU2JHZWNPQ3FEb19CVTllVl9aai0wcnZ4ajJwRExWbzM2cjQ4TFlrNEwzNzdQMEh2TThTbTlXV1d4MTktYUVJLW9MOUtCVDRNeFpXZ1hjYlNRMks5ZkhMMEdBRDA1RWRual9Cam1wTzA1Y08tS014elNMaTc2T25Zdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE16RG1FVTZORm9zREg4dm1LaUZIcnVJOFE3OU5DSHZ1clRIZ2JzX0haT3BGa3pBV1ZnU3M5RlFnWHd6U19odzRPbno0czJuT3dFR3BaN2xGRkFLd1ozYkxPZldpdzRZN3NVLWlYdXBia3Q3T0ZSa2N3b2ZR?oc=5</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>11-05-2026 06:38 UTC</t>
+          <t>11-05-2026 14:14 UTC</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo Co Ltd - To Cancel 31,457,200 Shares, 1.73% Of Issued Shares</t>
+          <t>Number of shareholders of Celltrion, Inc. – KRX:068270</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4037,12 +4037,12 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOQ01CQVVfZVVicnFnZlk0ZjltM3h6dWdpUlNQaXZiZllPM1RHTUx3RlY1UnlOZjFQSnBDaGVWNEFrUzlIMVhXVWEwaE1LZ0x1X3JRRUlZSnVEd2hZNlFDNU1pNENQRENmZWlBMjBMYXBKUXloV3dmM0RHazZtUjMzSUlEY1QyTXNfYnRCQVdsTkpaRnpFUUZNY0xfYUg1QjRDVkJsdkY5RVhjSFZNczlhT3IyTGY5enVmZ1NKWGFQNDhFMjVMN3kyLU16cFVrb2tFaUYwcVhyVXQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPc1NRNHllQ1MzczF2T2JCb0pQRHBjX1lTbjV5NDN5NTRGRW9Zekh5NVdyNndPSlotdHZYck8wUE0zRTE0T0NQVEVoMWpHWkVYbHNHWkFWbVN6S3hHSVIzNkx0M2JQV1pra1pOZm5mZllNNjBRaG1JSURuU09wNlZFc2habGJ6bmx0eko0Q0dqV0dMM1dfUFZVN0RuTmM3dndseXhaOXh3?oc=5</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>11-05-2026 06:31 UTC</t>
+          <t>11-05-2026 01:47 UTC</t>
         </is>
       </c>
     </row>
@@ -4054,965 +4054,1451 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Earnings call transcript: Daiichi Sankyo Q4 2025 results beat EPS expectations</t>
+          <t>Daiichi Sankyo targets global top 5 oncology rank by 2035, $1.3B efficiency drive in new 5-year plan</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Investing.com Canada</t>
+          <t>Fierce Pharma</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxOMEMtRDRtZFBXYWdnc28tVzlRUVlBenhxVjQybVJZTm9XSDBsZWpmalBIUWNMMk1VZzhiYTJiRkozb0hSalhVbkNQUURJU3FQenpheXdGRk5EUnB0NTllR3ExQm5zejBqMkZlRUxBQkQ2VDRTeUlMdHU0YlJrLTdXdl95d0hKUVprR0NXRUphdW5fWWJseHM3bG1vVmNtT1dtUF9UTlM3RlZLb192dGI4T0p1VVZTSUlmQURZR0xOOHhwUHN1Y2JQaFljclV2WU1SRUhlZA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNdkpSNE9GbGRxNWxvOVZQaTdQQUxSYVBhZzlqSWNvRjhTX0gxaWFoVHRGbjJIVHpwM1F6U1oydE5aRkZQQWlueDVzekQySVI4SElvNy1VSlBuMFVtVlNtMW1IblJBOW5zX2szbW1IWnpJaTNVbGFJN0FHeS0tRXVNV1YwT1lua1VHTDY4MjN4c0ZqajQ3U1NPQnBJM1RTc1FheTRqRmZPUndlWkE4aFB0VTZEZUU5dS0yelNIS0VtdU5wWlphTmc?oc=5</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>11-05-2026 11:58 UTC</t>
+          <t>11-05-2026 14:22 UTC</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Nichi-Iko</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Japan Compounded Sterile Preparations Market to Reach USD</t>
+          <t>Daiichi aims for $14.6B in oncology sales by 2030</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>openPR.com</t>
+          <t>FirstWord Pharma</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNTkdUcThBcVR0TDBzWnZYcDBmTUhVUFhzQzBGM2xRaHVKQ1gxM3N1cElRRGVRNXNscU43bXZXa3FXS3BuNUpLQTZvdFk4S2dBNXN6SHJxbUNPQ2RpejhJUWFHRlNhb08xVTNCTVhkblVqT2pmeEt5ZmRTdV8xbC01ZFRTMDVzck1HbVpad0JROTVJRnJSaHZzaQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTE40UGF3RWRNUVhyRk9nMUtsTDF4SGNVcWdJTy1iTkI5WnJxakE5UExDZzdOakVqWjYyY1g3WjlLV2RnQUtNLXE2OHF0ampDRWM5VmE0?oc=5</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>11-05-2026 09:21 UTC</t>
+          <t>11-05-2026 18:11 UTC</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Polpharma</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Polish pharma firm moves to acquire Romanian drugmaker</t>
+          <t>Daiichi Sankyo Company: Strong oncology-driven growth and ambitious 2030 targets define the new five-year plan</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>TVP World</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOR1FvZjVFYVRDZFNwYnJURERMZzhnVmhMLUJNVXBqaVEzR0dENGNEQ0h6OEFhS1hrSF83U0c3aWZBMmlZWWVqbHBzWEhlWDdVYUZadjZZcnd3TE5obVVfME9JejgzaFZqaXRKZS1DeGVselZHcVNrVldjZHAzb1hQdEFiYmJ0QnRPV2pERWUxbUw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogJBVV95cUxNUUpFNHVjdXR5V24za0VXLUUwbWV2ZzBuZFM0UjQtX25mUlFBdmtoZ0hyc3B5Q1JReVFkc3oyYlNpeVF6eHdBWmVhTWw2TUROclZXejY4c3BQbFlCdV9oLVZ2YzlNRWlIZ19nejBidXFGcTdvejVDRE1icnpPQUZpZDdUSTNBbDBwcXVfRGFXcnowWU1GWkROOHk5ODlWTUFlVU9BTXRJUEtLVDd6a19jWmhiMmNCZG5IbEh6SnNzX01uSGZPNlVWaVpfZ3ZwMFowTUkzcEc1T0JERWo3eFd2VjZtczRmMWY4NkI4Wmh5OWRqY3V3blFDT0hTTV9IdkFKMEZ5c3JfTFVmSEFLSzJmZk1NblpBbXhWUkMxcDlJeG05UQ?oc=5</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>11-05-2026 06:24 UTC</t>
+          <t>11-05-2026 14:20 UTC</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Polpharma</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Polish Pharma Firm Launches €270M Bid for Biofarm</t>
+          <t>Japan's Daiichi Sankyo unveils five-year business plan focused on oncology innovation</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>The Romania Journal</t>
+          <t>BioSpectrum Asia</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNU2xxb01lTG5HejdpUmZjd1kyZlJhZ0MxN1ExWC1vcFp3U19PRWlfdU5TWWh0dFJlZEh5UTFGWE1JSWFyVTlwbGlCRnE0el9vOUJnLWpMX2M0RlhGbGxWY01rQ0otcnpvVnBWaU5mcmxKYUw2SUo5YU1mQkliaEhmOXFZRmZzM1NvUDFQcW5KSFJFVTZHeFpYU9IBmAFBVV95cUxNU2xxb01lTG5HejdpUmZjd1kyZlJhZ0MxN1ExWC1vcFp3U19PRWlfdU5TWWh0dFJlZEh5UTFGWE1JSWFyVTlwbGlCRnE0el9vOUJnLWpMX2M0RlhGbGxWY01rQ0otcnpvVnBWaU5mcmxKYUw2SUo5YU1mQkliaEhmOXFZRmZzM1NvUDFQcW5KSFJFVTZHeFpYUw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxPdXFRYlJJUEZWV2w1U0djSGpHMFpGWmpSSnhnVktadVUzdW5HVy01WHRVWHlEMUplNkZpb1Y1Mng1eEl5b1F2dVJvb1VxOElyc0ZNSVJrZXJ1ZXJQcjJCSWVkS3I3a3lpQmZkQXdjaHpoak1DZFhKdUVvSndwZ2I0NFoxN05lYWJoNUNIeXdaNE1QTVhmci1OM3drcGlQQldhaE1hLXE0SXV1UVJRWEZ2MXNpcnlzaXFnMldNMVh6d2NLZVJzWFRsTF9zSUhFVk4w?oc=5</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>11-05-2026 08:48 UTC</t>
+          <t>11-05-2026 07:23 UTC</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Polpharma</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Romanian pharma group Dona reports 24% higher turnover in 2025, ponders entry into dental products market</t>
+          <t>Daiichi Sankyo unveils new five-year business plan</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Romania Insider</t>
+          <t>The Pharma Letter</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE0zUl9GQ1pWY21lTDlzUjZhZnVMb3FKRm5lcXBldEVMQ1J4eTVoNHNjdjUtMzhuak84WC1uejVIaEpwRW5lTTVGb0NfZkNzakVUWHN0LVBDVU0xSDZlY1U1QlowNDU5OHRPRjVkLTNSRXdBVjY2Mjg00gF8QVVfeXFMTjhPaHFhTldUUGszOGlDajZISUp6TV8yenpOQ1UwYlZjRkdpSmdRb0RiTjByMGFrWFluMmtRYzJZbTZsRzlLUVB5OXE2bG4tQlNtU3E2ckdoUzZiNjNGS1pSNGk0a0ZmaGszUFRoQ2RVZ3c1TFJpbHcwUnlrMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQTFE2UG9vVHlHREcyU3NxRXNXWXgyeFViSlNCQ2dzQjJ6RWxoRUJjdDNKTjlzeFhQNktxN2ozUW1ZdWFWR3R2M3RxUTNCY1A4MFJGNHFYTm9hWFVlRmtDQVFqTFQ4Y3psWHpJOFEzLXNEank3Rk9RbXVTLTNLR2VoSXRseUtnTFFRbHQ5ZjlXNzVxcFlacTRvelY2OA?oc=5</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>11-05-2026 12:30 UTC</t>
+          <t>11-05-2026 14:15 UTC</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Fresenius SE &amp; Co. KGaA stock (DE0005785604): Upcoming dividend payout</t>
+          <t>Daiichi Sankyo posts Q4 revenue growth but reports operating loss</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>Investing.com India</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOR3d1WW9KT1hhVTc2Mzl5VW00NVVFUURaeEhHTGZRbVVQcmJzaXhfWExNYXlHam1IRFlCbE5NSm1UVThEUU1YTHFUQ2Z0a19XN3FtMzJFSE5BeFhLRmtIVVVES2JBX2VGQXczdHRWMVROaFRSbXVNdl9HcklrSVQxQXhnNmNfdWlwXzh0dkRtSFhhMEMwOUMyUFdMM2xSRG8xNGQyYUgtcUdWVE50UFRVaGRpWWN4QUdTcjdsWG16c1JTQmp0anc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNYkJIbzNZNDR2TXdYUkM0SHZfNEhZY0tCei11TGZTNjVWSF9vT1VnNTVlWEFhRnBQLTZnMURxa2o5VEQ1TkUxdGFuQmpPOVhKeklRNHhnNFFQOVFnZ2lwYW16TW42QjB6MUFTLU92VjFXeVdzVEE5TnZZaUhyUlU1N1NpQ25BTnRQaGdxN0pZcXlINmpqWk5vM2phYk95c29SaEpBZzlxT1JsZTRjUDZIWEdJMzNfdHNs?oc=5</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>11-05-2026 09:06 UTC</t>
+          <t>11-05-2026 11:26 UTC</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Japan Compounded Sterile Preparations Market to Reach USD</t>
+          <t>Daiichi Sankyo Unveils New Five-Year Business Plan Focused on Oncology Leadership and Innovation</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>openPR.com</t>
+          <t>Business Wire</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNTkdUcThBcVR0TDBzWnZYcDBmTUhVUFhzQzBGM2xRaHVKQ1gxM3N1cElRRGVRNXNscU43bXZXa3FXS3BuNUpLQTZvdFk4S2dBNXN6SHJxbUNPQ2RpejhJUWFHRlNhb08xVTNCTVhkblVqT2pmeEt5ZmRTdV8xbC01ZFRTMDVzck1HbVpad0JROTVJRnJSaHZzaQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxPYTFON3k2cG5HUUZxcVBUU1NaY0hIbVlZaWNQNjh1alIwN3o0WFFzQmFSU3FGSWcydHdYTGJWcW40VllGV2VVa3ZYeXVDQk96TE5ieUFTVUx3UWxlOWxYWTNXbmxVY25yaWRTc2tXb29xNF9IRGhvYTNHVlNXNnl1T2F0LVlwMnVYVjByTXc2UUxwUlMxME1tX2VaSlE2TFh2YXhLZ2ZTMTUteV95T0lZV1dmaFpfUGlGSTBEZTVZUkplcmZ4bHJEbnNfZTRSNkVBTXZWbGhZa09TODF5Q2F3ZFFGdmNiTGlV?oc=5</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>11-05-2026 09:21 UTC</t>
+          <t>11-05-2026 06:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>UPL Board Approves Re-appointment of Ms. Naina Lal Kidwai as Independent Director for Second Five-Year Term</t>
+          <t>Daiichi eyes almost $15B in oncology sales by 2030 in ADC franchise push</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>Endpoints News</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxQUENvNkhCWW9zc1RfbHltZzlRUjRNUUNIeXZyTzBSVUdYUmxUM0s5cDQzMWVTcnczbVptNU0tQTRTM0dXcS1hR29rLTlpenh2TVA3cTM3ekZFN0tkX3Z6X2dUQll0WHVyaXdRQW5rd01tTFFlTmxvOWV6ZmFSQ3lQbFV6N0lCR2Vxc0lwcHFRNlNYM25DSXdzVndmUHhTaFdCTHg0VS1LTHV6bThNeE9oRmxlLWdDREd6OS1xNzVqS2FJWkUyckw0RDZGdGY4MHNDTnVDVUJGUUdqQ2dDSmYzcjRCSUlqVjRIQXlOVW5IcGUwSk05aXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQNkREeE1zMWN0NkExZWszdGFucWEySU1vbEppTlhSX3RhX0c1cDE3VHc0SHZZYjBJOXpzanFpdEtaTTQwVmZ0YmJZOUVtZUpESWg5VU1ZM01OSW5iR0RDVU9CcEdlSDZ1b3hNVWZua1lNRXZmQTRPWGpzSjFKLW1QcFRxNUhlaGNLeUlqVHpyZzZhbjcyMC01bmhVaw?oc=5</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>11-05-2026 08:42 UTC</t>
+          <t>11-05-2026 15:35 UTC</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>AI in pharma/biotech fundraising, partnering and finance</t>
+          <t>Daiichi Sankyo Expects FY Global Revenue From Lixiana Y325.4B Vs Y367.7B</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>GoingPublic.de</t>
+          <t>Moomoo</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNNHZzdFhnUm5JWUZCSDNzelREQmU3OVRSVmhJU3RlbXBrVDdzeDE1UldYWThQUUpCRFZTZHFWWVBxNndCVGtWVWlMNWlKV2NKUDU0eHRQeGJ1MUFKTV80MGxKR3lUTUpteU81THRiS18wLUNMTVFuMTI1ZXJNSm9KaUx2WkVUbVhIYzZDaWlDTk13cmZxN0ZmYWpLWnVCZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxOMU8zeUZCNUFwNnZxTEMweTlReWx1dUU4TEExNGtJQnpnT25jYUY4cFROa1c1bV9yZmJ5LU5seElwUTVWd050WEZpU0s5X0Y5SzduZGpObllKMXhwZUdodURQX0hNTzBfZF9KcnRCN1R0S05qOU5ySU5HN2hxNHJTYzI4RjlPLUZobkNYSkg2czJrNHFycE9tMU5pVlhQWEVrWG91M28zNEtSdmZnM2ZwMjJaZXotdzc2TWdkLUlQa1N1b3hUVTBhTjVYTUlGamUwQ0VSbA?oc=5</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>11-05-2026 13:18 UTC</t>
+          <t>11-05-2026 15:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Hansoh Pharma’s B7-H3-Targeted ADC HS-20093 Granted Breakthrough Therapy Designation by NMPA for Esophageal Cancer Treatment 1</t>
+          <t>Daiichi Sankyo's Attributable Profit Falls 12% in Fiscal Year 2025</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Minichart</t>
+          <t>marketscreener.com</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxQVndGUXVlUHp3ZUp2UUNxNEd3X3NOTGdoWG05aWxNT05SZzhkWDI2MHFxR01yNi1IZVZya0pVSjY0enVMZjZwNWhfRGkwY2cxcTI4cXJJQW5neVNDdEZyV3hsTnlmRlVCeURhNDNGaEVROUFJRlF1WHA4ajZHWWx6X1NPdllrOEItZnBySHlHeWhneWtfeUcySGNLc1VXQmdJWkl4Rm41c0Y2emFlWkR0eHFzV3FnR2h6V1NWT0JuZHNNRGxuT214Q05obE5yZVBZUDhSY3BCLVpqRFY0Y0UxZnQ2QUtQemhzVjZDcUhKNUpFLU5MQ3VWSkJ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQVkNVMWJDLUVqTHk4azlzdmhWWkhZWU82ckZlTWN2ZG5UVkgtZ3llazdlRDA4YndKRU5jcDZJSm5vN3hsMm55UzdCMlZLT3RYUEJRRXkyQTA5eHJ5d25kdEV0RXFicmpFMVdidmhzUVY4TmxfZDJkdU1FQTZHbm9KY2NVb0Z0dmd0R1p6ekRlR2U3WlBOSXVSYXhMNmxnNFdENnZ1UERYbGl4U2ExLVphZGxSMDRlQ3FoM3c?oc=5</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>11-05-2026 03:03 UTC</t>
+          <t>11-05-2026 09:48 UTC</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Alvotech</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Alvotech (NASDAQ: ALVO) reports FDA Form 483 but maintains 2026 BLA approval outlook</t>
+          <t>Daiichi Sankyo Company: Strong revenue growth led by oncology, but operating profit impacted by one-time expenses</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Stock Titan</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxON05jZTFyT1M2SVEzUmRoZHJYOTlUdVhWWTgxZ2Vld005ZFRkbG15MVBOUXJPWHZENUlKMTJrNFA0RE1HRU5FRmlXbDNnVW1yUTVaTW4yUDVOVk8zMVJNdmRVaUJzU0I0bm00V3ZfUFpiOTVUSmZiS1dGLW9tUTNqOUp6cDlzODJVamluZUhhSWdORWIyaXFMWkFyYWVfNDdrWkswMDFqTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwJBVV95cUxNTzlFWE9Cdm9kZDNJRkdEM3ZBdzl0VEVVNjV4NHl4NE5DemFBT3VONWN4LV9MMXZPbXlSVHE4eEJMbnJXc0JhTjJiX0VHOWtaLXZuVElLdl9oUUlfOFcyb1RJbVZLcHpEYkk0c0xGZmw0WFBiaGZwUzdQcGF4NmVVS3JaOFJVMk5raUFfcUcwQ1FIb3A1Z0lobVBYRVI2X2EzeWN2YkxVaVgyV2xUU2ZTbHE5bk04eHBmaGh4NXZfU01HMnJZNTBHQjBaOGs3VkZISVBZeExoYkVyeHBqWTF0SEhkTFhwTm9zaVIyWUZnWXN1YldoOG9VMDE2elRCRzh2MExnZHhSUEdROFFYd2JJc2dyYy1abHpPTklvVUdzMA?oc=5</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>11-05-2026 12:30 UTC</t>
+          <t>11-05-2026 06:40 UTC</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Alvotech</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>FDA completes inspection at Alvotech's Reykjavik facility; company on track for BLA resubmissions this quarter</t>
+          <t>Daiichi Sankyo Company: Strong FY2025 growth in oncology drives new 5-year plan targeting &gt;3.0 Tn JPY revenue by 2030</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Pluang</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQYnQyWm1zb1dXSTVzX3ZJZk9WUkZRSXpHVmNQVXZrRlpGTlVLdGR1OW93cllMbHo2ZW1TdURiMHRJcHJhS20yb2RmUUVHZDN6SjZ1R2tCQVJHY0hfWXpWNHJpaFgtREVOVWwtVmpDSjBJb0RWUmlpaXpBd0ZTNy1PaHRNTWZZTkdhVEh4QTFGX3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAJBVV95cUxQM2hscjA3d3ZyQXdwMUVXNmdRUlFncmJNNGVkR3ZNVzV0dDB6RF85M0lJalRJdTZFTmp6b2dtQVJtLUxfWjJKMGRkbG1vZWticm9WNnlXMnViUjQyWURFOWdvNmM5VlMtMWJ1WHgweThwbEZ4MHhXY25SU0xaY3VwUFY3dkxhTWZ4SVpleGJ1aFJJQVlnOWxkN1BpOVJHSmRXUktTcVotRkdaUDhxZDZOZjdDUDFQak91Q0pQREcwalYxaGRMUWFYZ0dzS0c5VTB6QXJxX0ZVcjR6WWRENU1OT3k2NHdlY0U4MHQ2SFNNOVRvR2NLY0RmSnI5b0czV3E1QnZpNVVpMklIeEtjcVlvVnBWNkVJMDJWblhvM1FIZGxrOWRh?oc=5</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>11-05-2026 09:53 UTC</t>
+          <t>11-05-2026 06:40 UTC</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Alvotech</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Alvotech announces completion of FDA surveillance inspection at Reykjavik facility</t>
+          <t>Daiichi Sankyo FY2025 slides: oncology surge drives 12.6% growth By Investing.com</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>The Manila Times</t>
+          <t>Investing.com Australia</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxNcG12d1pQMDEwcXdlQjUzZ1Q5WUlkZ21XckRlMEkwMXBQMWZQYUc2RlZ1RTRRZ0tHbjY1ZHpwWGY3WTFvSWF0ZFpraUhGcEJMaGZaSi1pVHFTYkN0T3R6MlFjM1Q4WnIyaDhrVWZyUy1scGRaa3I4QmNEc3Uxc29NazVQRlBkdl9pUXpudHVka0lJZmlVQWd4eENlQk5IQUdRT1gxLWtYY3hBc3BleVI2bjBiU19DNG85aUhSZW1fUDA4Tm1rdTNpYUlYSTBIWC1DUmZtdzhucV9RVGRnX0V2NTV2SXFKTGVxYjlDQdIB8gFBVV95cUxORjYtQ04wckdIWlpHU3BjTEszMzMteUprdG9WcDZPVEhUbHM3Tmc4VnpyQV9ZRmc0UFN0aVJIOVZNb0V4aW5TcG1iQlVQdGNuaEM2VkNJaUFkTDBhYk5yWlFaVWhsamJqVGkxaDk5MXVnQzVZMVdSdC1sWE5QN1dueEplRE5YWlh2NF9OUHNTaVNwNmIyOE9JWndDQWhMYl92U0ZzS3hFQ2lNeHlpMzJUcl9tY21ENl9KV0RUWThvMl9hM3lodXBMUGFxSTd1bnZJVVIybDFHcl9rdm9fTlFEVzhMNFVGcm1fT0VabVNDN05Ndw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOVHR1UE01dWVnaDNmZFlhc19uQ0tPTm5tVjZGU2RVUE5ab2Zha29YVWNTY0FKX1hfX3VQeVJNOWM1Z3g3dTF3YlZENHlxbWI3VVA2T2J1Uzk4T0ZNbXo3WHR1dVh0RDhjdjZENFlVcWx4bGRQckZjMFd3MDFpdmcxR3EtNXZkb2xvZFFTVy1TT0l0TVhKRWRkUXd4V2pHRTctNjYtNGh5TGNXY0xfbkhRY0xIS1VYR1d1?oc=5</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>11-05-2026 08:39 UTC</t>
+          <t>11-05-2026 13:25 UTC</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Alvotech</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Alvotech Clears Key FDA Inspection at Reykjavik Plant, Paving Way for 2026 BLA Resubmissions</t>
+          <t>Daiichi Sankyo Co Ltd - To Cancel 31,457,200 Shares, 1.73% Of Issued Shares</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxNandxQnRqaldUQlFjamJPdmlmb0JrNU9xMHB4NTZiMThBTWVKckczNDlLTktTako5OWJqWEozandKeWhNUHE5RUhaQ2lLajhMbDVOVXdqTng2anJkbFhUQndFVnRnNXFNVk5QRXlQdmEtelBTc3h0Sk54MFpBUy1CZmRuY3Fqc2pPNnkxcWZFZ1Y3TlNYZ2tCaTl5cFBIX3AwSkgtWE5sdy1UMWxHYzJndU5pN2NKd2JFQmNxb1FHVW1FeUd2Y0V6aFRDek9uVTNxbTl2cWtDNVNPYmM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOQ01CQVVfZVVicnFnZlk0ZjltM3h6dWdpUlNQaXZiZllPM1RHTUx3RlY1UnlOZjFQSnBDaGVWNEFrUzlIMVhXVWEwaE1LZ0x1X3JRRUlZSnVEd2hZNlFDNU1pNENQRENmZWlBMjBMYXBKUXloV3dmM0RHazZtUjMzSUlEY1QyTXNfYnRCQVdsTkpaRnpFUUZNY0xfYUg1QjRDVkJsdkY5RVhjSFZNczlhT3IyTGY5enVmZ1NKWGFQNDhFMjVMN3kyLU16cFVrb2tFaUYwcVhyVXQ?oc=5</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>11-05-2026 13:26 UTC</t>
+          <t>11-05-2026 06:31 UTC</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Alvotech</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>FDA issues Form 483 at Iceland plant; Alvotech still targets 2026 drug approvals</t>
+          <t>Earnings call transcript: Daiichi Sankyo Q4 2025 results beat EPS expectations</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Stock Titan</t>
+          <t>Investing.com Canada</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNYk9tQ2Q0VjRlUWtYci1wNlV3U1JEb1JoMGlXWXJKSWxLa3AwMDc0bFZhbHpPMUR6emZwc0VBeUNWX2c5RUNRZXFyS193amswSFdKSE1iSVkza3FYX2dMYTFTdmE2NEhlSFZvbjZoU0ZRc0hybF9ZcDBvVmZRT0JZR1c1S25hS2tpWlhwcTJtdzhIdUVPWDhmRGYwRFdpME51RVkzTHhlNG1GM0g2M3hVdEFzcVdQaVB5anc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxOMEMtRDRtZFBXYWdnc28tVzlRUVlBenhxVjQybVJZTm9XSDBsZWpmalBIUWNMMk1VZzhiYTJiRkozb0hSalhVbkNQUURJU3FQenpheXdGRk5EUnB0NTllR3ExQm5zejBqMkZlRUxBQkQ2VDRTeUlMdHU0YlJrLTdXdl95d0hKUVprR0NXRUphdW5fWWJseHM3bG1vVmNtT1dtUF9UTlM3RlZLb192dGI4T0p1VVZTSUlmQURZR0xOOHhwUHN1Y2JQaFljclV2WU1SRUhlZA?oc=5</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>11-05-2026 08:30 UTC</t>
+          <t>11-05-2026 12:05 UTC</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Alvotech</t>
+          <t>Nichi-Iko</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Alvotech reports completion of FDA inspection in Iceland</t>
+          <t>Japan Compounded Sterile Preparations Market to Reach USD</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>grafa.com</t>
+          <t>openPR.com</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQUDJOS3EwYTY5OWJqMFF5ZFpUVWt5dmlMa0pJWWJ2R3FKbGZlWE5MVXpTRnNNbzB6MHhrb0I0dkxPUUhsdUFpclpoSWpnTHozNldYZEtma1lrTGVVbnA5Q2R3UzEzeXJIVFF1dTRVbXBBTDQ5OElhLWREY0hJOENUazNqbUpxcnBTQnI0V2tESlQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNTkdUcThBcVR0TDBzWnZYcDBmTUhVUFhzQzBGM2xRaHVKQ1gxM3N1cElRRGVRNXNscU43bXZXa3FXS3BuNUpLQTZvdFk4S2dBNXN6SHJxbUNPQ2RpejhJUWFHRlNhb08xVTNCTVhkblVqT2pmeEt5ZmRTdV8xbC01ZFRTMDVzck1HbVpad0JROTVJRnJSaHZzaQ?oc=5</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>11-05-2026 00:00 UTC</t>
+          <t>11-05-2026 09:21 UTC</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Alvotech</t>
+          <t>Polpharma</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Alvotech stock (LU2557688560): Q1 2026 revenue dip and EBITDA rise on mix shift</t>
+          <t>Polish pharma firm moves to acquire Romanian drugmaker</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>TVP World</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQUUZCQy1qSjlDUm5Qdmg1eTRxZXBKQXo5NEczNzVCaFh4YTFPT2VUZjI3cWFveGJQOGprdmc3QldIMTBUWEVxLUFTdkVGOTBGMnBhZDRaMjN3dHFielFZVXcyNHZxV2N5Yy0xbmlkY0FNZEZBbUVCYVd1N0RMTG1YamFjdGVtUWVpaURQbEQ3TDRqa0g4VkEya0tTR0IzQ01kVFNkei0wdmp1WGpjMHVPYXIySmltQWkwbm9hSmJOc3ZTLV9QdWZ4OA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOR1FvZjVFYVRDZFNwYnJURERMZzhnVmhMLUJNVXBqaVEzR0dENGNEQ0h6OEFhS1hrSF83U0c3aWZBMmlZWWVqbHBzWEhlWDdVYUZadjZZcnd3TE5obVVfME9JejgzaFZqaXRKZS1DeGVselZHcVNrVldjZHAzb1hQdEFiYmJ0QnRPV2pERWUxbUw?oc=5</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>10-05-2026 19:55 UTC</t>
+          <t>11-05-2026 06:24 UTC</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Alvotech</t>
+          <t>Polpharma</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Alvotech Announces Completion of FDA Surveillance Inspection at Reykjavik Facility</t>
+          <t>Polish Pharma Firm Launches €270M Bid for Biofarm</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Bluefield Daily Telegraph</t>
+          <t>The Romania Journal</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxObU1IRmcwZGNsZWtfYnp3WW9Id1F2R05BTWljX1M1blo5NDJOdkdyckZrbjAwVUdVZl9fSllacnl5VG9ad2J5VHU0S192UHBWQTdMaVJNenNSWGY1cUtsXzdlWjVPRGQ0dUVPSjRROEN3emlzVEFmcGMyYk5VRVpEekZ3OHhtT1FUQ2x0STFoVUJGQmNLTXgwN04yaFRmR01vZV80RElVMGE3a3lOTFJwbXJ0V2ctUWNMY1NuTGJmNTh0U1RfNkE2Ul9SZnFwRlZ0eXlUUlJkLXp3bVdKVjVtTGo3dkRfdnBHdmpDX0haUEtDd1FhWlZQXw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNU2xxb01lTG5HejdpUmZjd1kyZlJhZ0MxN1ExWC1vcFp3U19PRWlfdU5TWWh0dFJlZEh5UTFGWE1JSWFyVTlwbGlCRnE0el9vOUJnLWpMX2M0RlhGbGxWY01rQ0otcnpvVnBWaU5mcmxKYUw2SUo5YU1mQkliaEhmOXFZRmZzM1NvUDFQcW5KSFJFVTZHeFpYU9IBmAFBVV95cUxNU2xxb01lTG5HejdpUmZjd1kyZlJhZ0MxN1ExWC1vcFp3U19PRWlfdU5TWWh0dFJlZEh5UTFGWE1JSWFyVTlwbGlCRnE0el9vOUJnLWpMX2M0RlhGbGxWY01rQ0otcnpvVnBWaU5mcmxKYUw2SUo5YU1mQkliaEhmOXFZRmZzM1NvUDFQcW5KSFJFVTZHeFpYUw?oc=5</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>11-05-2026 08:31 UTC</t>
+          <t>11-05-2026 08:48 UTC</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Alvotech</t>
+          <t>Polpharma</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>WisdomTree Multi Asset Issuer Public Limited Company Programme for the issuance of Collateralised ETP Securities</t>
+          <t>Romanian pharma group Dona reports 24% higher turnover in 2025, ponders entry into dental products market</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>The Manila Times</t>
+          <t>Romania Insider</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgJBVV95cUxOaVE0SEpMa05RektfZzVFdGFZR1dWXy1xNy1PdmQ5OUwySG56ZFQ0cm9Ma1ZQbExuZ3g2Y1I0T0ZiVFA1UjVSZkg3V29zZmpNNkxQcjNKcDhDamhYM1EwbC0yTVFuUkNIVDVZYXVMZkRZOTRRc0JEb05taGFtTGFIU3ZMdjlsWHp4Vy1RRmd4bmVna0hEalFYM0JqaUhTRThNSUl1cXhpaXdLR2xrQnAwTkNfX3d4MXRQbzF3Z2lJZHJiZHZUa09STFpkSl9aN2N2Q2pMOV9rMGJRZlBvSVd1d0hWeWFvaVA5Z29Id3I5bWpsc0pqZWctTG5aMElVRWJDalZLNHFDYXFsSW5Qb3JPb1hvMjE5TG9mRGfSAZoCQVVfeXFMTmlRNEhKTGtOUXpLX2c1RXRhWUdXVl8tcTctT3ZkOTlMMkhuemRUNHJvTGtWUGxMbmd4NmNSNE9GYlRQNVI1UmZIN1dvc2ZqTTZMUHIzSnA4Q2poWDNRMGwtMk1RblJDSFQ1WWF1TGZEWTk0UXNCRG9ObWhhbUxhSFN2THY5bFh6eFctUUZneG5lZ2tIRGpRWDNCamlIU0U4TUlJdXF4aWl3S0dsa0JwME5DX193eDF0UG8xd2dpSWRyYmR2VGtPUkxaZEpfWjdjdkNqTDlfazBiUWZQb0lXdXdIVnlhb2lQOWdvSHdyOW1qbHNKamVnLUxuWjBJVUViQ2pWSzRxQ2FxbEluUG9yT29YbzIxOUxvZkRn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE0zUl9GQ1pWY21lTDlzUjZhZnVMb3FKRm5lcXBldEVMQ1J4eTVoNHNjdjUtMzhuak84WC1uejVIaEpwRW5lTTVGb0NfZkNzakVUWHN0LVBDVU0xSDZlY1U1QlowNDU5OHRPRjVkLTNSRXdBVjY2Mjg00gF8QVVfeXFMTjhPaHFhTldUUGszOGlDajZISUp6TV8yenpOQ1UwYlZjRkdpSmdRb0RiTjByMGFrWFluMmtRYzJZbTZsRzlLUVB5OXE2bG4tQlNtU3E2ckdoUzZiNjNGS1pSNGk0a0ZmaGszUFRoQ2RVZ3c1TFJpbHcwUnlrMA?oc=5</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>11-05-2026 08:39 UTC</t>
+          <t>11-05-2026 12:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Alvotech</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Form 8.5 (EPT/RI) - Kore Potash Plc</t>
+          <t>Fresenius SE &amp; Co. KGaA stock (DE0005785604): Nutrition solutions gain traction in US market</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>The Manila Times</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPSHE5NTJYb1VBaUpJTjNMOTlXVk5neUJRU2J2Wk9BWGdPMTNXbE00WWczS1p0QmhrY2ZPbGx5UzZOS3FrUEFxb3JkZGJnR3FSNksyQk1kWkUxZklRaWxTRE5FNlM3bFZuSUJzaWh4OW1DSmNvMXpDYTRIN0ZoMFRFbE12ekF5WWdKTGlqUWVVZF9iOWllVENTek9wNGNDNEJfVzFrUlRmX1lXb3PSAasBQVVfeXFMT0hxOTUyWG9VQWlKSU4zTDk5V1ZOZ3lCUVNidlpPQVhnTzEzV2xNNFlnM0tadEJoa2NmT2xseVM2Tktxa1BBcW9yZGRiZ0dxUjZLMkJNZFpFMWZJUWlsU0RORTZTN2xWbklCc2loeDltQ0pjbzF6Q2E0SDdGaDBURWxNdnpBeVlnSkxpalFlVWRfYjlpZVRDU3pPcDRjQzRCX1cxa1JUZl9ZV29z?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPNjFFMUlScnlMN2wyNEtaRDZFRmpMZnRQOTZINE4zTW1SSWRPSHU3UDVUa0ZMVmZSUDdLR2hFUThBYjl2YTlLUnByZ3RzOV81SEVhdDM4T0VGM09XRXNOX1doNml2WU0wcnZ0RWZzdWV6blppRmlQM0VmRS1WZTlPdmhIT2N0d0pqdEFBVUFYNkpHbUZDcXQ3bU5YSTExNGZxX2lIYlljcU5yNHlHbDRsV0pHYi1SVlpiTjd1MVVZcC1jTDBUaHc?oc=5</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>11-05-2026 08:39 UTC</t>
+          <t>11-05-2026 11:29 UTC</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Alvotech</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Transactions in connection with share buy-back program</t>
+          <t>Japan Compounded Sterile Preparations Market to Reach USD</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>The Manila Times</t>
+          <t>openPR.com</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQZV91NG05eFlyNHlpUlhCbWFGNnpZR3ZlblZFdjVYUGRYeFF4T3VwaXJYZWhYdmVBdEtLckdCNFYzWlZGS1BnU3VIRktESFdiN0hWc05yX3daVHBTdDhSWE9iUzRyNDYtZWlaWDl0dERNMHJ6TDhsR09QV0l1bG5WaGlfRktuU1k0VlZoSlV0aExUTXRvT2lObUZZb2xvUXVXczB1a2FhQ2tvVTJmV3dKM2M5OV82emE3WS02ZVFEMjBIOVhHMlZfWVVSOF_SAcwBQVVfeXFMUGVfdTRtOXhZcjR5aVJYQm1hRjZ6WUd2ZW5WRXY1WFBkWHhReE91cGlyWGVoWHZlQXRLS3JHQjRWM1pWRktQZ1N1SEZLREhXYjdIVnNOcl93WlRwU3Q4UlhPYlM0cjQ2LWVpWlg5dHRETTByekw4bEdPUFdJdWxuVmhpX0ZLblNZNFZWaEpVdGhMVE10b09pTm1GWW9sb1F1V3MwdWthYUNrb1UyZld3SjNjOTlfNnphN1ktNmVRRDIwSDlYRzJWX1lVUjhf?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNTkdUcThBcVR0TDBzWnZYcDBmTUhVUFhzQzBGM2xRaHVKQ1gxM3N1cElRRGVRNXNscU43bXZXa3FXS3BuNUpLQTZvdFk4S2dBNXN6SHJxbUNPQ2RpejhJUWFHRlNhb08xVTNCTVhkblVqT2pmeEt5ZmRTdV8xbC01ZFRTMDVzck1HbVpad0JROTVJRnJSaHZzaQ?oc=5</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>11-05-2026 08:39 UTC</t>
+          <t>11-05-2026 09:21 UTC</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Alvotech</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Chinese AI inspection firm opens Silicon Valley HQ as US manufacturing reshores</t>
+          <t>Fresenius SE &amp; Co. KGaA stock (DE0005785604): Upcoming dividend payout</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>The Manila Times</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxNTkl6VHJnMFpVQXhXM0JiTklpLXZhek9Ca1V3NTVMWm96cXFyeFBzV3FrUGg0ODVzZm54SHBIbC1Gb3prU19iN2V0V3hFeGdkb3RHYUsyNHN2NkRmVG11LVZNVDFEY1p0cmFSNXp0QkRUbERVZGMtWmNabzVtZngtSW5YQWQyeWM1cHV5ZE1UQmdpNjE1M05STXVmMkYwcnMwRC04VnhZWHRaX2tfdGpBeEFVLVV2VmJCTTlmdGw5ejMwMjA2NDh0TzNhaFdKanZNcUdqNWxFMWs1Q1EwTE5NNHd1cUk4ZG1IWFhrbTBn0gHuAUFVX3lxTE1OSXpUcmcwWlVBeFczQmJOSWktdmF6T0JrVXc1NUxab3pxcXJ4UHNXcWtQaDQ4NXNmbnhIcEhsLUZvemtTX2I3ZXRXeEV4Z2RvdEdhSzI0c3Y2RGZUbXUtVk1UMURjWnRyYVI1enRCRFRsRFVkYy1aY1pvNW1meC1JblhBZDJ5YzVwdXlkTVRCZ2k2MTUzTlJNdWYyRjByczBELThWeFlYdFpfa190akF4QVUtVXZWYkJNOWZ0bDl6MzAyMDY0OHRPM2FoV0pqdk1xR2o1bEUxazVDUTBMTk00d3VxSThkbUhYWGttMGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOR3d1WW9KT1hhVTc2Mzl5VW00NVVFUURaeEhHTGZRbVVQcmJzaXhfWExNYXlHam1IRFlCbE5NSm1UVThEUU1YTHFUQ2Z0a19XN3FtMzJFSE5BeFhLRmtIVVVES2JBX2VGQXczdHRWMVROaFRSbXVNdl9HcklrSVQxQXhnNmNfdWlwXzh0dkRtSFhhMEMwOUMyUFdMM2xSRG8xNGQyYUgtcUdWVE50UFRVaGRpWWN4QUdTcjdsWG16c1JTQmp0anc?oc=5</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>11-05-2026 08:39 UTC</t>
+          <t>11-05-2026 09:06 UTC</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Alvotech</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Running to the future, China's robo-athletes showcase industrial capability</t>
+          <t>Bacil Pharma Schedules Board Meeting on May 22, 2026 to Approve Q4 FY26 Audited Financial Results</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>The Manila Times</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxNOEhtR215Qk16eVBJYjdpb2RhQTNyRTY4SXk5Vnl5WjFTXzY2TGlIYkJhdGRZSks3V2xVOFNrU1JGN0x4UjRrVzBHWVdfSk1uVEZRMGVwZjRwVjVONm85YVB4UU4wY1d2X2g3bHhQNDRMQ2RCak85ZDg1Rm9Na0p3T0luNHh1bS1yS3RoeXhvUGt2WEM2b3JKS3czLWxGRmpHQVp3cVJsY2ZBTnBJcmhSY0ZoZ3FQWWFRSU5ZdWRIaU1GRHdZdW9hVGp5aGRxb05DSU9jZWlEZE0wVV9QdHRORlJ4Vm1OQdIB5gFBVV95cUxNOEhtR215Qk16eVBJYjdpb2RhQTNyRTY4SXk5Vnl5WjFTXzY2TGlIYkJhdGRZSks3V2xVOFNrU1JGN0x4UjRrVzBHWVdfSk1uVEZRMGVwZjRwVjVONm85YVB4UU4wY1d2X2g3bHhQNDRMQ2RCak85ZDg1Rm9Na0p3T0luNHh1bS1yS3RoeXhvUGt2WEM2b3JKS3czLWxGRmpHQVp3cVJsY2ZBTnBJcmhSY0ZoZ3FQWWFRSU5ZdWRIaU1GRHdZdW9hVGp5aGRxb05DSU9jZWlEZE0wVV9QdHRORlJ4Vm1OQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOVHpJckdwa0N3MmM5MXF2MFhMWllULUVoX2RPLUhoaDdyZnhLX2NIcVVUWWExMjJEUUdjYlkwOXZPVjlyRWd0UGMxLVdrTWdjU1lGX1ZLUWpjZWFVbTF0cnMtTlJwajZyZlZFbS1lOTlkMVdWbVRMdHBwdWVfemw1UEh1emJ1UGkxVDZ0QWRwUnQzOTZ0WFotbHpjSldYc3dkcUUyV1BISlp5VFdNNUpFQUtqU1I0X1pvRmtlNVNDQkpSR2RIZ2dOUzRUR2pjMFU1aDNEcDY0TnE3WEpnbDc1Tzh2eHl2cTho?oc=5</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>11-05-2026 08:39 UTC</t>
+          <t>11-05-2026 15:17 UTC</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Alvotech</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Cia - Italian Farmers Assembly: 51% of consumers buy only Made in Italy, but almost half have already cut back on spending</t>
+          <t>UPL Board Approves Re-appointment of Ms. Naina Lal Kidwai as Independent Director for Second Five-Year Term</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>The Manila Times</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAJBVV95cUxOMHYyLWs2TFFnbWV4bldoOWJydTZQN01TRkwwQThlMGp6bW1qcWE1bmFfWUE1c2JHbDdMYXZXOUFfbHVNMWJFcnY2YnNYX0F5dnNWZDVPS0xrenlTZmRIOW82OE9TVlltTUVycWJOeHdRUWZndzBndUFaazBUZTZnSXM5N0xQQkNfV2E1YmdfOWRqRjg1Nkp5TXd6QjNrTHpJWHZmbjJQVF96Rk1ZR3F6anR3Tk8yZGtMNlQtUW5NUWVtQVhLRHhUODQxX3FuVGxOYUtJNFE1bmYtUzh1QzBSQjRXVTJNaUJmZUMwNHBLeTltNVBuenJnUXZaaWtEU1VIZTJUa0NZZGtIaTBqQzNpOW83OVluWEN4dkZQZVVqeXHSAaACQVVfeXFMTjB2Mi1rNkxRZ21leG5XaDlicnU2UDdNU0ZMMEE4ZTBqem1tanFhNW5hX1lBNXNiR2w3TGF2VzlBX2x1TTFiRXJ2NmJzWF9BeXZzVmQ1T0tMa3p5U2ZkSDlvNjhPU1ZZbU1FcnFiTnh3UVFmZ3cwZ3VBWmswVGU2Z0lzOTdMUEJDX1dhNWJnXzlkakY4NTZKeU13ekIza0x6SVh2Zm4yUFRfekZNWUdxemp0d05PMmRrTDZULVFuTVFlbUFYS0R4VDg0MV9xblRsTmFLSTRRNW5mLVM4dUMwUkI0V1UyTWlCZmVDMDRwS3k5bTVQbnpyZ1F2WmlrRFNVSGUyVGtDWWRrSGkwakMzaTlvNzlZblhDeHZGUGVVanlx?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxQUENvNkhCWW9zc1RfbHltZzlRUjRNUUNIeXZyTzBSVUdYUmxUM0s5cDQzMWVTcnczbVptNU0tQTRTM0dXcS1hR29rLTlpenh2TVA3cTM3ekZFN0tkX3Z6X2dUQll0WHVyaXdRQW5rd01tTFFlTmxvOWV6ZmFSQ3lQbFV6N0lCR2Vxc0lwcHFRNlNYM25DSXdzVndmUHhTaFdCTHg0VS1LTHV6bThNeE9oRmxlLWdDREd6OS1xNzVqS2FJWkUyckw0RDZGdGY4MHNDTnVDVUJGUUdqQ2dDSmYzcjRCSUlqVjRIQXlOVW5IcGUwSk05aXc?oc=5</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>11-05-2026 08:39 UTC</t>
+          <t>11-05-2026 08:42 UTC</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Alvotech</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Goliath Resources Strengthens Its Advisory Board With The Addition Of Alan Edwards</t>
+          <t>AI in pharma/biotech fundraising, partnering and finance</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>The Manila Times</t>
+          <t>GoingPublic.de</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxQcjFwVkNlbGxXUEk0YkR1UDg1Y2hocTYxM1NFdDhVc0V5WkNmdEwtTU1JOHNzR2p3T1pWb2FUOHVsTVQxaWRuUF9Eam5ENVM5a0h0YUJXd3dYWXlfQjlWSEQwd2ZEX2dSc3FXNkJyMGtvOUVtOHNVZXVoSEdkQndUUXd5ZWlZUWtDaVJQQUxzUjUwVlhqSDZIZFZhcmg3ak13bVVXWkRSejBsTzRabzkzZUVZV2JwMHdXYmRkeUU0cjYyQUZhYnNKNVNqY0lPM0JLMWJtUkJQMkNyank3TTNZMmVvTHl1RktuTnZvMjllNjdYQdIB8gFBVV95cUxQcjFwVkNlbGxXUEk0YkR1UDg1Y2hocTYxM1NFdDhVc0V5WkNmdEwtTU1JOHNzR2p3T1pWb2FUOHVsTVQxaWRuUF9Eam5ENVM5a0h0YUJXd3dYWXlfQjlWSEQwd2ZEX2dSc3FXNkJyMGtvOUVtOHNVZXVoSEdkQndUUXd5ZWlZUWtDaVJQQUxzUjUwVlhqSDZIZFZhcmg3ak13bVVXWkRSejBsTzRabzkzZUVZV2JwMHdXYmRkeUU0cjYyQUZhYnNKNVNqY0lPM0JLMWJtUkJQMkNyank3TTNZMmVvTHl1RktuTnZvMjllNjdYQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNNHZzdFhnUm5JWUZCSDNzelREQmU3OVRSVmhJU3RlbXBrVDdzeDE1UldYWThQUUpCRFZTZHFWWVBxNndCVGtWVWlMNWlKV2NKUDU0eHRQeGJ1MUFKTV80MGxKR3lUTUpteU81THRiS18wLUNMTVFuMTI1ZXJNSm9KaUx2WkVUbVhIYzZDaWlDTk13cmZxN0ZmYWpLWnVCZw?oc=5</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>11-05-2026 08:39 UTC</t>
+          <t>11-05-2026 13:18 UTC</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Teva’s CNS Portfolio Is Growing, But Valuation Is Stretched (NYSE:TEVA)</t>
+          <t>Hansoh Pharma’s B7-H3-Targeted ADC HS-20093 Granted Breakthrough Therapy Designation by NMPA for Esophageal Cancer Treatment 1</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Seeking Alpha</t>
+          <t>Minichart</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPbG52RlhSOTlUMjVFVTlYNHk0T2tMWThSVGFIWnRIVlFfUzFOZk5nQ2k1dVVBVlpEVm1NMXJ3clNOT3lGbWhaamJ4UlRSOHd5dFVnbUZfU2NjaUpmQWg1c2JDNnlibXJKZ2ZWVExNenI4SDlkejhacWN1OWNHeXM1cndGTG9LeUNNaHdveWxwd1J0ZWdORWYxNGd4RGZBQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxQVndGUXVlUHp3ZUp2UUNxNEd3X3NOTGdoWG05aWxNT05SZzhkWDI2MHFxR01yNi1IZVZya0pVSjY0enVMZjZwNWhfRGkwY2cxcTI4cXJJQW5neVNDdEZyV3hsTnlmRlVCeURhNDNGaEVROUFJRlF1WHA4ajZHWWx6X1NPdllrOEItZnBySHlHeWhneWtfeUcySGNLc1VXQmdJWkl4Rm41c0Y2emFlWkR0eHFzV3FnR2h6V1NWT0JuZHNNRGxuT214Q05obE5yZVBZUDhSY3BCLVpqRFY0Y0UxZnQ2QUtQemhzVjZDcUhKNUpFLU5MQ3VWSkJ3?oc=5</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>11-05-2026 12:34 UTC</t>
+          <t>11-05-2026 03:03 UTC</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Alvotech</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Russia expects further growth of generics share in domestic pharma market</t>
+          <t>Alvotech (ALVO) Is Down 7.4% After FDA Form 483 on Key Site Inspection Has The Bull Case Changed?</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>The Pharma Letter</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPUldZdGhhRzV4blVlS0NXWlczS0s4OTFiQ0lKTHRkcmJwemlnT1V6cFVhYlcwQmhyVzlYdDhoWmpsMzdpQlNOaXhpQ0kzZE1rLUhaY2NFbHotMGIxTXpQNlRua3MyQTJtNW1OeDZ5elVjMnNzelRvTjc5R2RQUlJDSm04M3RpbjNOYWJ6blpwcm1XdmVsZktKemJlSFBPUEtPWVQ0OUhESnE2QlVUNDJKbTZfY1JJUzBmTWIw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxNSC1Kd3B1ZlZSakJwak9WTF8xU09vZ3ZuU3N2Y2N4VFVoeGxRdFVlRkFFemZrS3pWTUtBMzBqdlFJaDFMV044SXo0bE5fTXk1U0xZbEFzMk42eHA5Mnkyam82R3NGLWdrcS1wZXkya202WmZlbUluaWp5ZGp0SUpld3lNWHpreXhEbzlwOW13TG9CUzJ1RVRVbURLYXI5VEZMMDc4LUdmRy1DWWdacWFINDBWcng0eUM5SlFuR1BQb0JZVzVEcXhGZUlBV0xrQ29LdjE2YkRBNFBhUdIB3wFBVV95cUxNSXYtZ0pWbWFmX0VZSGtSMUxqV3JrQUxBYlpfS3pvWHhsNXRaSzRYTjdMYUI4YXdEZTY3Y2tpVXpNaEkxOEVKQVVKdVloTjFVWHZpNkp1VW1qS1Z1R25YOGkyY2l4SFo3bkJPUGF5RVlFV0NiZ3B0N0d1d2tIOUV1X1l4TE1KdUVuWmpWcjNXVmN4ZXdVc3U4amtUeHdsR045NFppaHp3WGZIZnBmUXJDaGkzeDVqWXF1ajFwbHdHck9BNHlMNk9IcDRIeFNyMEpocWxtdHdzNnk1WFRTaFRn?oc=5</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>11-05-2026 10:17 UTC</t>
+          <t>11-05-2026 17:34 UTC</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Alvotech</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Liquidity Mapping Around (TEVA) Price Events</t>
+          <t>Alvotech (NASDAQ: ALVO) reports FDA Form 483 but maintains 2026 BLA approval outlook</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Stock Traders Daily</t>
+          <t>Stock Titan</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxObnpfWk5qbF9qcTVWZU1RTERhYTA3MFVPcXhVNlFvMS1faTFjYk4tMk42X3dQamh1U0lTa2tEV0hjMXkwVnVOOV9QbGg5ZXRWNC1ndmk4Qk1NTkJWLUZvOU0xbXRxaGhvWWJueTA3akFZaE9mWkN4SUJNMVNuZWhnUngyT1F4aDVSYllBX1p4cnJtVlRfMlNkaVdDOFB0SjFuWTlMT3dVcmFaT1NjVmpsRnFLUkwyTnFSZFk3UEZmUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxON05jZTFyT1M2SVEzUmRoZHJYOTlUdVhWWTgxZ2Vld005ZFRkbG15MVBOUXJPWHZENUlKMTJrNFA0RE1HRU5FRmlXbDNnVW1yUTVaTW4yUDVOVk8zMVJNdmRVaUJzU0I0bm00V3ZfUFpiOTVUSmZiS1dGLW9tUTNqOUp6cDlzODJVamluZUhhSWdORWIyaXFMWkFyYWVfNDdrWkswMDFqTQ?oc=5</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>11-05-2026 06:22 UTC</t>
+          <t>11-05-2026 12:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Alvotech</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Rheumatoid Arthritis Drugs Market Set to Record US$</t>
+          <t>FDA completes inspection at Alvotech's Reykjavik facility; company on track for BLA resubmissions this quarter</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>openPR.com</t>
+          <t>Pluang</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNQUNhcmRUZmd6a1o2R2ZwTTJNLTZHZ3kwTWhQX0YwM2NnZGdKUEdOcG8yb2ZMZFNZNmN6c19Xcm05Q0VoN0U5Z3JBNFZDb01FZzFPTWhyc2g0QndBODROMGJBRnJqYmtWcFZKSFFKOFVvYXlnRFFEZ2lOX3NfNHFibFJHbnlPa1czNVdtNE1mWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQYnQyWm1zb1dXSTVzX3ZJZk9WUkZRSXpHVmNQVXZrRlpGTlVLdGR1OW93cllMbHo2ZW1TdURiMHRJcHJhS20yb2RmUUVHZDN6SjZ1R2tCQVJHY0hfWXpWNHJpaFgtREVOVWwtVmpDSjBJb0RWUmlpaXpBd0ZTNy1PaHRNTWZZTkdhVEh4QTFGX3c?oc=5</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>11-05-2026 10:11 UTC</t>
+          <t>11-05-2026 09:53 UTC</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Alvotech</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Recycled Material Shoes Teva Men's Reember Fleece Loafers Recycled Material Indoor Outdoor Slip On Shoes</t>
+          <t>Alvotech Receives US FDA Observations Following Iceland Plant Inspection</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>aviglianonews.it</t>
+          <t>Moomoo</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPejVBWHdhcXgzZDdIaGxqdkdGM3ZJU1FDZ1hxcVl2aUpHYXFBMmdkT3gyM0E3Ykx4ZFJaQkFVNVhoeGI4eXNoakdYZl9NcEx2ZXdzWUtTWVBDanh0QWxmS1dBS1FCcUljdzB1OUpxcTdIekZRTWI5RnRlOVRfZ1I5ZFVnTHdUTnJZcnBWcFlESmtURWRVYjFXQ0tB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxONm9zZFpJRTVxaGdxRDdBMURDZXV0SEtHM3pxcnJvTDZITjRRVjVoUTYxQXNPeHV6RUQ0WXZWeGRIWEdWNkVPdzY4UU5nR0IwTEt1bU93TzJfeEVubER1WDhoTnVtVzR3dU10R3Q2eDdJYjRpWVZTSXlWUkw5NVdKYjZ5d1RyNFNGMTRCeGlXWjBrVGVmRlBpZnBxcGdybG93V254Sl9UZExLVWFGTWZQVEp6WFc?oc=5</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>11-05-2026 10:28 UTC</t>
+          <t>11-05-2026 13:33 UTC</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Alvotech</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Wilson's Disease Treatment Market to Reach US$ 1,022.4 Million</t>
+          <t>Alvotech announces completion of FDA surveillance inspection at Reykjavik facility</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>openPR.com</t>
+          <t>The Manila Times</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOeUxtTEE0alFDTEdldUpEOEtvUV9JQWc0cWN4M1Jfc3pha3Z6VzJxd2pPYXJlQzBXSWlhOG13N0JocnVPSVBvYUlOODNWMTkwQmQ4MFZfYzlCNlhfZG9fTm5jeHlYc2g5UGhhVDFXYlRLeFAxYzc0bXMxQzc5aURDV2ZBaDhPTW5TZnBMX09MUFVhMm95cGNyY2RtREtPQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxNcG12d1pQMDEwcXdlQjUzZ1Q5WUlkZ21XckRlMEkwMXBQMWZQYUc2RlZ1RTRRZ0tHbjY1ZHpwWGY3WTFvSWF0ZFpraUhGcEJMaGZaSi1pVHFTYkN0T3R6MlFjM1Q4WnIyaDhrVWZyUy1scGRaa3I4QmNEc3Uxc29NazVQRlBkdl9pUXpudHVka0lJZmlVQWd4eENlQk5IQUdRT1gxLWtYY3hBc3BleVI2bjBiU19DNG85aUhSZW1fUDA4Tm1rdTNpYUlYSTBIWC1DUmZtdzhucV9RVGRnX0V2NTV2SXFKTGVxYjlDQdIB8gFBVV95cUxORjYtQ04wckdIWlpHU3BjTEszMzMteUprdG9WcDZPVEhUbHM3Tmc4VnpyQV9ZRmc0UFN0aVJIOVZNb0V4aW5TcG1iQlVQdGNuaEM2VkNJaUFkTDBhYk5yWlFaVWhsamJqVGkxaDk5MXVnQzVZMVdSdC1sWE5QN1dueEplRE5YWlh2NF9OUHNTaVNwNmIyOE9JWndDQWhMYl92U0ZzS3hFQ2lNeHlpMzJUcl9tY21ENl9KV0RUWThvMl9hM3lodXBMUGFxSTd1bnZJVVIybDFHcl9rdm9fTlFEVzhMNFVGcm1fT0VabVNDN05Ndw?oc=5</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>11-05-2026 07:00 UTC</t>
+          <t>11-05-2026 08:39 UTC</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Alvotech</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Bisoprolol Market Size Accelerating at 8.57% CAGR |</t>
+          <t>Alvotech Clears Key FDA Inspection at Reykjavik Plant, Paving Way for 2026 BLA Resubmissions</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>openPR.com</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNMmtMdnN1YXVBQ2xJZUplSmtSNFYxWllzTENVNkxsRkdlWk9vaE9mTTk4dU9FN0RJTFc2LUtWUFJFS2RHT0xaLXNYOE9KejBKNHVVS2toX0hmd2dYNDd3NEdBZzZVdlZLZWpkNXVSY1UyUlZnNjY2YjFGV0toWmpRU0M2d3pPVV9MTjU5Yw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxNandxQnRqaldUQlFjamJPdmlmb0JrNU9xMHB4NTZiMThBTWVKckczNDlLTktTako5OWJqWEozandKeWhNUHE5RUhaQ2lLajhMbDVOVXdqTng2anJkbFhUQndFVnRnNXFNVk5QRXlQdmEtelBTc3h0Sk54MFpBUy1CZmRuY3Fqc2pPNnkxcWZFZ1Y3TlNYZ2tCaTl5cFBIX3AwSkgtWE5sdy1UMWxHYzJndU5pN2NKd2JFQmNxb1FHVW1FeUd2Y0V6aFRDek9uVTNxbTl2cWtDNVNPYmM?oc=5</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>11-05-2026 09:41 UTC</t>
+          <t>11-05-2026 13:26 UTC</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Alvotech</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Dexamethasone Market Size Accelerates at 6.8% CAGR Through 2033</t>
+          <t>Alvotech reports completion of FDA inspection in Iceland</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>openPR.com</t>
+          <t>grafa.com</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOVjF6aFlJS3FFZzVVNUl6a0VKRGhFeFdhS3ZEcFVRaFdMRjIxSk5mUkxFaERCdGdTOVRyVFI5LXliUk1ydUxybXdUT3hhY3RSMnFYUFhudmtmVW5tcGM2V1prNXFSLXlKQTU3Q1laVVg3cWtPMF8taGZWTm1tREpFNElIOGwwYkNNQ1JCZzVZQUh6VDVjRld2emVhUTNzNTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQUDJOS3EwYTY5OWJqMFF5ZFpUVWt5dmlMa0pJWWJ2R3FKbGZlWE5MVXpTRnNNbzB6MHhrb0I0dkxPUUhsdUFpclpoSWpnTHozNldYZEtma1lrTGVVbnA5Q2R3UzEzeXJIVFF1dTRVbXBBTDQ5OElhLWREY0hJOENUazNqbUpxcnBTQnI0V2tESlQ?oc=5</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>11-05-2026 07:53 UTC</t>
+          <t>11-05-2026 00:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>Alvotech</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>CORRECTING and REPLACING Samsung Epis Holdings Reports First Quarter 2026 Financial Results</t>
+          <t>FDA issues Form 483 at Iceland plant; Alvotech still targets 2026 drug approvals</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>The AI Journal</t>
+          <t>Stock Titan</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOX2JFZTAydDc0NHp6dXpMX2RKR20zNkR4bjVoc2g4UFo5RlhZcWE3YXpxTnh0eTl3RERRb1hNRjRiTTQyOW1lemdDcW4xQWp2V3RFUFpORjZxaVMzWkN1MXd6SGRGQ2JpbjBVY0xMN1k5dlp6M0lseHRUWV9OdndwX0k3OHB0VHFqSnZ1ODZCMHFNX3QyLVdnazBPX2NBQVpMZTV1SG9uNEJkYWJBNmdpVFlR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNYk9tQ2Q0VjRlUWtYci1wNlV3U1JEb1JoMGlXWXJKSWxLa3AwMDc0bFZhbHpPMUR6emZwc0VBeUNWX2c5RUNRZXFyS193amswSFdKSE1iSVkza3FYX2dMYTFTdmE2NEhlSFZvbjZoU0ZRc0hybF9ZcDBvVmZRT0JZR1c1S25hS2tpWlhwcTJtdzhIdUVPWDhmRGYwRFdpME51RVkzTHhlNG1GM0g2M3hVdEFzcVdQaVB5anc?oc=5</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>11-05-2026 05:26 UTC</t>
+          <t>11-05-2026 08:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>Alvotech</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>CORRECTING and REPLACING Samsung Epis Holdings Reports First Quarter 2026 Financial Results</t>
+          <t>Alvotech stock (LU2557688560): Q1 2026 revenue dip and EBITDA rise on mix shift</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Caledonian Record</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAJBVV95cUxObHhCZEUtU3k3MEpTOG5TTXp6UXVPZUU4a0tOYmdCTzI0VXYxdHVLdWdEUlRhekk3amVrREFBTmlRTXN0VDZ2TjRicGlSbExFUWE0djFhSWRhcGJFUnZSTlBEV0FhOFVFQlRoTzQwM1hpNXVhRTdQNXZudllrSlQ1aUFIMnUzTEtGRlNTMi1lQjRMTlVISVVoNGpfdUlpaHFWRVF3U1hnd0N4aXVtdWdEYjhmc2VIaUh1VU1Mdmw5NzFqZy13MExwR1VrSGNwMVlJdExMSmZlVExNMW5fRWNRMEJGT0haeF9XTVZ6NjJHRUZ3OTVRV2pGQW5yZFZrc3cxSU1HeQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQUUZCQy1qSjlDUm5Qdmg1eTRxZXBKQXo5NEczNzVCaFh4YTFPT2VUZjI3cWFveGJQOGprdmc3QldIMTBUWEVxLUFTdkVGOTBGMnBhZDRaMjN3dHFielFZVXcyNHZxV2N5Yy0xbmlkY0FNZEZBbUVCYVd1N0RMTG1YamFjdGVtUWVpaURQbEQ3TDRqa0g4VkEya0tTR0IzQ01kVFNkei0wdmp1WGpjMHVPYXIySmltQWkwbm9hSmJOc3ZTLV9QdWZ4OA?oc=5</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>11-05-2026 05:11 UTC</t>
+          <t>10-05-2026 19:55 UTC</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
+          <t>Alvotech</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Alvotech Announces Completion of FDA Surveillance Inspection at Reykjavik Facility</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Bluefield Daily Telegraph</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxObU1IRmcwZGNsZWtfYnp3WW9Id1F2R05BTWljX1M1blo5NDJOdkdyckZrbjAwVUdVZl9fSllacnl5VG9ad2J5VHU0S192UHBWQTdMaVJNenNSWGY1cUtsXzdlWjVPRGQ0dUVPSjRROEN3emlzVEFmcGMyYk5VRVpEekZ3OHhtT1FUQ2x0STFoVUJGQmNLTXgwN04yaFRmR01vZV80RElVMGE3a3lOTFJwbXJ0V2ctUWNMY1NuTGJmNTh0U1RfNkE2Ul9SZnFwRlZ0eXlUUlJkLXp3bVdKVjVtTGo3dkRfdnBHdmpDX0haUEtDd1FhWlZQXw?oc=5</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>11-05-2026 08:31 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Alvotech</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Alvotech announces cGMP surveillance inspection of Reykjavik facility</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>TipRanks</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPbkdhUHc3UmZ3cVoyZmN3VHhjSDZNY0t2LTlHWkI1ZTEzb3JMQWg1Qlh0b2xUT0hST2ZIdEdvQmk0SVI3UnVDWktEemZmcmZsdlVuME5Qb2dXRkNJQXl1eE4wTXBtdmRZLWZ4a2NoNWItSFU4V251MXJVX3ZrTllZd3dTNHBCUEdtaUFDdC1QeTdPOV9BM3E3ZUo0WWl6a0haMzVTU2pWRnRkV1ppRHVjblBWR2R6LTdOVVpF?oc=5</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>11-05-2026 09:58 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Alvotech</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>WisdomTree Multi Asset Issuer Public Limited Company Programme for the issuance of Collateralised ETP Securities</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>The Manila Times</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgJBVV95cUxOaVE0SEpMa05RektfZzVFdGFZR1dWXy1xNy1PdmQ5OUwySG56ZFQ0cm9Ma1ZQbExuZ3g2Y1I0T0ZiVFA1UjVSZkg3V29zZmpNNkxQcjNKcDhDamhYM1EwbC0yTVFuUkNIVDVZYXVMZkRZOTRRc0JEb05taGFtTGFIU3ZMdjlsWHp4Vy1RRmd4bmVna0hEalFYM0JqaUhTRThNSUl1cXhpaXdLR2xrQnAwTkNfX3d4MXRQbzF3Z2lJZHJiZHZUa09STFpkSl9aN2N2Q2pMOV9rMGJRZlBvSVd1d0hWeWFvaVA5Z29Id3I5bWpsc0pqZWctTG5aMElVRWJDalZLNHFDYXFsSW5Qb3JPb1hvMjE5TG9mRGfSAZoCQVVfeXFMTmlRNEhKTGtOUXpLX2c1RXRhWUdXVl8tcTctT3ZkOTlMMkhuemRUNHJvTGtWUGxMbmd4NmNSNE9GYlRQNVI1UmZIN1dvc2ZqTTZMUHIzSnA4Q2poWDNRMGwtMk1RblJDSFQ1WWF1TGZEWTk0UXNCRG9ObWhhbUxhSFN2THY5bFh6eFctUUZneG5lZ2tIRGpRWDNCamlIU0U4TUlJdXF4aWl3S0dsa0JwME5DX193eDF0UG8xd2dpSWRyYmR2VGtPUkxaZEpfWjdjdkNqTDlfazBiUWZQb0lXdXdIVnlhb2lQOWdvSHdyOW1qbHNKamVnLUxuWjBJVUViQ2pWSzRxQ2FxbEluUG9yT29YbzIxOUxvZkRn?oc=5</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>11-05-2026 08:39 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Alvotech</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Form 8.5 (EPT/RI) - PPHE Hotel Group Ltd</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>The Manila Times</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxQSFQ5NkFzQWI0bnlyLUlwdi1IbFo4S1VpRTF3R3NIU2pIX3ZGWUdRNExEdUlpWW80X0V0ejFRQUd6MjkwRVFSR0VRUE04b0Jld1l0Vm5PNjZMaXk4b3N1UGFOOTlLZUtkSnFERm0zR3RTTEhhR3RxcXg0Mnl4bGRaYzVGYy02bzFuT3NnSWJzY2ZkX1JwNVJITDhJeG1IWXNyVV9PMnVmMjh6cUdEMDYwZHVR0gGyAUFVX3lxTFBIVDk2QXNBYjRueXItSXB2LUhsWjhLVWlFMXdHc0hTakhfdkZZR1E0TER1SWlZbzRfRXR6MVFBR3oyOTBFUVJHRVFQTThvQmV3WXRWbk82NkxpeThvc3VQYU45OUtlS2RKcURGbTNHdFNMSGFHdHFxeDQyeXhsZFpjNUZjLTZvMW5Pc2dJYnNjZmRfUnA1UkhMOEl4bUhZc3JVX08ydWYyOHpxR0QwNjBkdVE?oc=5</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>11-05-2026 08:39 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Alvotech</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Transactions in connection with share buy-back program</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>The Manila Times</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQZV91NG05eFlyNHlpUlhCbWFGNnpZR3ZlblZFdjVYUGRYeFF4T3VwaXJYZWhYdmVBdEtLckdCNFYzWlZGS1BnU3VIRktESFdiN0hWc05yX3daVHBTdDhSWE9iUzRyNDYtZWlaWDl0dERNMHJ6TDhsR09QV0l1bG5WaGlfRktuU1k0VlZoSlV0aExUTXRvT2lObUZZb2xvUXVXczB1a2FhQ2tvVTJmV3dKM2M5OV82emE3WS02ZVFEMjBIOVhHMlZfWVVSOF_SAcwBQVVfeXFMUGVfdTRtOXhZcjR5aVJYQm1hRjZ6WUd2ZW5WRXY1WFBkWHhReE91cGlyWGVoWHZlQXRLS3JHQjRWM1pWRktQZ1N1SEZLREhXYjdIVnNOcl93WlRwU3Q4UlhPYlM0cjQ2LWVpWlg5dHRETTByekw4bEdPUFdJdWxuVmhpX0ZLblNZNFZWaEpVdGhMVE10b09pTm1GWW9sb1F1V3MwdWthYUNrb1UyZld3SjNjOTlfNnphN1ktNmVRRDIwSDlYRzJWX1lVUjhf?oc=5</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>11-05-2026 08:39 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Alvotech</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Chinese AI inspection firm opens Silicon Valley HQ as US manufacturing reshores</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>The Manila Times</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxNTkl6VHJnMFpVQXhXM0JiTklpLXZhek9Ca1V3NTVMWm96cXFyeFBzV3FrUGg0ODVzZm54SHBIbC1Gb3prU19iN2V0V3hFeGdkb3RHYUsyNHN2NkRmVG11LVZNVDFEY1p0cmFSNXp0QkRUbERVZGMtWmNabzVtZngtSW5YQWQyeWM1cHV5ZE1UQmdpNjE1M05STXVmMkYwcnMwRC04VnhZWHRaX2tfdGpBeEFVLVV2VmJCTTlmdGw5ejMwMjA2NDh0TzNhaFdKanZNcUdqNWxFMWs1Q1EwTE5NNHd1cUk4ZG1IWFhrbTBn0gHuAUFVX3lxTE1OSXpUcmcwWlVBeFczQmJOSWktdmF6T0JrVXc1NUxab3pxcXJ4UHNXcWtQaDQ4NXNmbnhIcEhsLUZvemtTX2I3ZXRXeEV4Z2RvdEdhSzI0c3Y2RGZUbXUtVk1UMURjWnRyYVI1enRCRFRsRFVkYy1aY1pvNW1meC1JblhBZDJ5YzVwdXlkTVRCZ2k2MTUzTlJNdWYyRjByczBELThWeFlYdFpfa190akF4QVUtVXZWYkJNOWZ0bDl6MzAyMDY0OHRPM2FoV0pqdk1xR2o1bEUxazVDUTBMTk00d3VxSThkbUhYWGttMGc?oc=5</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>11-05-2026 08:39 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Teva</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Teva’s CNS Portfolio Is Growing, But Valuation Is Stretched (NYSE:TEVA)</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Seeking Alpha</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPbG52RlhSOTlUMjVFVTlYNHk0T2tMWThSVGFIWnRIVlFfUzFOZk5nQ2k1dVVBVlpEVm1NMXJ3clNOT3lGbWhaamJ4UlRSOHd5dFVnbUZfU2NjaUpmQWg1c2JDNnlibXJKZ2ZWVExNenI4SDlkejhacWN1OWNHeXM1cndGTG9LeUNNaHdveWxwd1J0ZWdORWYxNGd4RGZBQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>11-05-2026 12:34 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Teva</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Liquidity Mapping Around (TEVA) Price Events</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Stock Traders Daily</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxObnpfWk5qbF9qcTVWZU1RTERhYTA3MFVPcXhVNlFvMS1faTFjYk4tMk42X3dQamh1U0lTa2tEV0hjMXkwVnVOOV9QbGg5ZXRWNC1ndmk4Qk1NTkJWLUZvOU0xbXRxaGhvWWJueTA3akFZaE9mWkN4SUJNMVNuZWhnUngyT1F4aDVSYllBX1p4cnJtVlRfMlNkaVdDOFB0SjFuWTlMT3dVcmFaT1NjVmpsRnFLUkwyTnFSZFk3UEZmUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>11-05-2026 06:22 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Teva</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>TradingKey</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>TradingKey</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE1KUDF3dXRUa1RRU05XLV9FMDJTanNvSkZZUmtlcHRkTDNaSEo2anRmTUZHanIzcVZoWTFFUGVmSkFGNGQyQlFGbTVXYUNHZFVmczhqRFpORmZtU2JqNHZ0aDVpdWRMUDZDUGdIQUNQSQ?oc=5</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>11-05-2026 15:00 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Teva</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Mon: Banks lead TASE losses - Globes</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Globes - Israel Business News</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE5HWHhLdm1pOU1JMGV5S255ZllYX2VrVjJ6MHBwbXRWLUFCVS0yc1VLSHJBY1BfVVA4WmJzOERjTkpqSmNqR294RGp0OEZ0TmZ2WTkxbEZyTkZwZWhSanNRVGJjbVdrVUFsNXktTFZsck1DTnhMaGRNVTNFLTI?oc=5</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>11-05-2026 15:49 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Teva</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Recycled Material Shoes Teva Men's Reember Fleece Loafers Recycled Material Indoor Outdoor Slip On Shoes</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>aviglianonews.it</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPejVBWHdhcXgzZDdIaGxqdkdGM3ZJU1FDZ1hxcVl2aUpHYXFBMmdkT3gyM0E3Ykx4ZFJaQkFVNVhoeGI4eXNoakdYZl9NcEx2ZXdzWUtTWVBDanh0QWxmS1dBS1FCcUljdzB1OUpxcTdIekZRTWI5RnRlOVRfZ1I5ZFVnTHdUTnJZcnBWcFlESmtURWRVYjFXQ0tB?oc=5</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>11-05-2026 10:28 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Teva</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Russia expects further growth of generics share in domestic pharma market</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>The Pharma Letter</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPUldZdGhhRzV4blVlS0NXWlczS0s4OTFiQ0lKTHRkcmJwemlnT1V6cFVhYlcwQmhyVzlYdDhoWmpsMzdpQlNOaXhpQ0kzZE1rLUhaY2NFbHotMGIxTXpQNlRua3MyQTJtNW1OeDZ5elVjMnNzelRvTjc5R2RQUlJDSm04M3RpbjNOYWJ6blpwcm1XdmVsZktKemJlSFBPUEtPWVQ0OUhESnE2QlVUNDJKbTZfY1JJUzBmTWIw?oc=5</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>11-05-2026 10:17 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Teva</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Bisoprolol Market Size Accelerating at 8.57% CAGR |</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>openPR.com</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNMmtMdnN1YXVBQ2xJZUplSmtSNFYxWllzTENVNkxsRkdlWk9vaE9mTTk4dU9FN0RJTFc2LUtWUFJFS2RHT0xaLXNYOE9KejBKNHVVS2toX0hmd2dYNDd3NEdBZzZVdlZLZWpkNXVSY1UyUlZnNjY2YjFGV0toWmpRU0M2d3pPVV9MTjU5Yw?oc=5</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>11-05-2026 09:41 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Teva</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Rheumatoid Arthritis Drugs Market Set to Record US$</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>openPR.com</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNQUNhcmRUZmd6a1o2R2ZwTTJNLTZHZ3kwTWhQX0YwM2NnZGdKUEdOcG8yb2ZMZFNZNmN6c19Xcm05Q0VoN0U5Z3JBNFZDb01FZzFPTWhyc2g0QndBODROMGJBRnJqYmtWcFZKSFFKOFVvYXlnRFFEZ2lOX3NfNHFibFJHbnlPa1czNVdtNE1mWQ?oc=5</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>11-05-2026 10:11 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Teva</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Dexamethasone Market Size Accelerates at 6.8% CAGR Through 2033</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>openPR.com</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOVjF6aFlJS3FFZzVVNUl6a0VKRGhFeFdhS3ZEcFVRaFdMRjIxSk5mUkxFaERCdGdTOVRyVFI5LXliUk1ydUxybXdUT3hhY3RSMnFYUFhudmtmVW5tcGM2V1prNXFSLXlKQTU3Q1laVVg3cWtPMF8taGZWTm1tREpFNElIOGwwYkNNQ1JCZzVZQUh6VDVjRld2emVhUTNzNTA?oc=5</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>11-05-2026 07:53 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Teva</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Wilson's Disease Treatment Market to Reach US$ 1,022.4 Million</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>openPR.com</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOeUxtTEE0alFDTEdldUpEOEtvUV9JQWc0cWN4M1Jfc3pha3Z6VzJxd2pPYXJlQzBXSWlhOG13N0JocnVPSVBvYUlOODNWMTkwQmQ4MFZfYzlCNlhfZG9fTm5jeHlYc2g5UGhhVDFXYlRLeFAxYzc0bXMxQzc5aURDV2ZBaDhPTW5TZnBMX09MUFVhMm95cGNyY2RtREtPQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>11-05-2026 07:00 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
           <t>Samsung Bioepis</t>
         </is>
       </c>
-      <c r="B170" t="inlineStr">
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>CORRECTING and REPLACING Samsung Epis Holdings Reports First Quarter 2026 Financial Results</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>The AI Journal</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOX2JFZTAydDc0NHp6dXpMX2RKR20zNkR4bjVoc2g4UFo5RlhZcWE3YXpxTnh0eTl3RERRb1hNRjRiTTQyOW1lemdDcW4xQWp2V3RFUFpORjZxaVMzWkN1MXd6SGRGQ2JpbjBVY0xMN1k5dlp6M0lseHRUWV9OdndwX0k3OHB0VHFqSnZ1ODZCMHFNX3QyLVdnazBPX2NBQVpMZTV1SG9uNEJkYWJBNmdpVFlR?oc=5</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>11-05-2026 05:00 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Samsung Bioepis</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>CORRECTING and REPLACING Samsung Epis Holdings Reports First Quarter 2026 Financial Results</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Caledonian Record</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihAJBVV95cUxObHhCZEUtU3k3MEpTOG5TTXp6UXVPZUU4a0tOYmdCTzI0VXYxdHVLdWdEUlRhekk3amVrREFBTmlRTXN0VDZ2TjRicGlSbExFUWE0djFhSWRhcGJFUnZSTlBEV0FhOFVFQlRoTzQwM1hpNXVhRTdQNXZudllrSlQ1aUFIMnUzTEtGRlNTMi1lQjRMTlVISVVoNGpfdUlpaHFWRVF3U1hnd0N4aXVtdWdEYjhmc2VIaUh1VU1Mdmw5NzFqZy13MExwR1VrSGNwMVlJdExMSmZlVExNMW5fRWNRMEJGT0haeF9XTVZ6NjJHRUZ3OTVRV2pGQW5yZFZrc3cxSU1HeQ?oc=5</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>11-05-2026 05:11 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Samsung Bioepis</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
         <is>
           <t>Rosen Law Firm Encourages Sportradar Group AG Investors to Inquire About Securities Class Action Investigation – SRAD</t>
         </is>
       </c>
-      <c r="C170" t="inlineStr">
+      <c r="C188" t="inlineStr">
         <is>
           <t>Weekly Voice</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr">
+      <c r="D188" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxQam9nUm9MUi0xNldBQzVuVm45elBmSlV2cUdvVnRpdkxrQ3NxTHJKRExpeG1rOGFlWUdQVWxkUVVEbU05bjhqYV9Ya1VncVE0T195b1RLUzVwc2ZTLVh4d1VjU0FKS0ZPOXNhd2d0TUh5T0U5SHI1SHRlUFkxeFdjU0h0RUxmOW9VT2dybEdJSC1YOTRpejlzN2EwWm9zWnB1MUM3cDJrbXhLLWppMC15cXd3RHQ4N21ha1IwS2xjQU1zU01Ma3BPemRJN3RxNk00cTJuUW5hNi1RQQ?oc=5</t>
         </is>
       </c>
-      <c r="E170" t="inlineStr">
+      <c r="E188" t="inlineStr">
         <is>
           <t>11-05-2026 05:22 UTC</t>
         </is>

--- a/news_results_raw.xlsx
+++ b/news_results_raw.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E196"/>
+  <dimension ref="A1:E215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,27 +458,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sandoz</t>
+          <t>Chime Biologics</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nevian Lifescience begins pharma exports to Canada</t>
+          <t>Recapping the “Must-Know” Information From the 2026 AAD Late-Breaker Sessions—Part 1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bangladesh Sangbad Sangstha (BSS)</t>
+          <t>Dermatology Times</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1BbGc1SDBDU3JxNzlUQm9WaThjTkhaNXhZOUlLUWd5UDV3ZkRmTld5dk54M1puOXotMXVsOUJwQ1ZlR0RCSzBZYW1tT0p6ODZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNZTJyb09pS1NON0N6SjRfd0thMnNWTFdwSmVzWi1uNlNGTEdVdThRQ25LV0p3RmdKMXo0ZFlVRmcxMHdNdVhWZmJ4TGtpSHA0Yk9zX3VaMzhqZTBHR05pY01JR0tYcUNHQWpvR29wX1psZVhza09OdmwxcUhva3U4LXV2RW1Tek5WOWhBZUdkVFZoenEtOG1OSzNfaGVlYVc4bWdxN1JFUHlwck9xc3FqU1puczNtZ3lUOEp4Rg?oc=5</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>13-05-2026 16:38 UTC</t>
+          <t>13-05-2026 20:00 UTC</t>
         </is>
       </c>
     </row>
@@ -490,22 +490,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>From Tongi to Canada: Nevien Life Science marks export milestone in global pharmaceutical supply chain</t>
+          <t>Nevian Lifescience begins pharma exports to Canada</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>The Business Standard</t>
+          <t>Bangladesh Sangbad Sangstha (BSS)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPV3hBT1AxUGRsdHhpOHF3SEFDcGl4d2Jkc2hOdm81cUNrVllRbXdabDRfQXAybzBlYlh0Q2ZDYTcyVTMtc1RpaGhJV29Eb3B5cDktOEJJLWZoQUE1cldtVnNpWVN2eGk5NTFtc3FkUU9TTGZjWUhha215RngwdnJVZFBiMFQ3UTBucVFOQldzRnprSWg3bjVOdnc5NVl6RzNLdy02QUhsQ21yQXA4aTJqQ1RaR2RzSmpjMmdXck1sNNIBvwFBVV95cUxPV3hBT1AxUGRsdHhpOHF3SEFDcGl4d2Jkc2hOdm81cUNrVllRbXdabDRfQXAybzBlYlh0Q2ZDYTcyVTMtc1RpaGhJV29Eb3B5cDktOEJJLWZoQUE1cldtVnNpWVN2eGk5NTFtc3FkUU9TTGZjWUhha215RngwdnJVZFBiMFQ3UTBucVFOQldzRnprSWg3bjVOdnc5NVl6RzNLdy02QUhsQ21yQXA4aTJqQ1RaR2RzSmpjMmdXck1sNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1BbGc1SDBDU3JxNzlUQm9WaThjTkhaNXhZOUlLUWd5UDV3ZkRmTld5dk54M1puOXotMXVsOUJwQ1ZlR0RCSzBZYW1tT0p6ODZw?oc=5</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>13-05-2026 15:45 UTC</t>
+          <t>13-05-2026 16:38 UTC</t>
         </is>
       </c>
     </row>
@@ -517,22 +517,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pharmaceutical industry key sector for diversifying export basket: Health Minister</t>
+          <t>From Tongi to Canada: Nevien Life Science marks export milestone in global pharmaceutical supply chain</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amader Barta</t>
+          <t>The Business Standard</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxObjBhdTQwMVNqdlcwSTBDSnZIN2RSNlc2Vng4eWFqaFdHM0JQZXV4TzFnb0VjMU1rUnotS2NnYkNIV0hOMVo2Ym1fZXNRS3pXVFVIRjlOalZSTnVFTzFWVE1LVGF5QXZJeTN5cDliM2FlQkJKUlk4a3lGZUlxNmlvempMQ0g5T2U1X0FxR3M0RTJQS0txY3JIYjJ4LWRkdzB3NmEyWmR0blMwUUlGdjdkenBhZUxGVFRLaU1EX1lwTVczUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPV3hBT1AxUGRsdHhpOHF3SEFDcGl4d2Jkc2hOdm81cUNrVllRbXdabDRfQXAybzBlYlh0Q2ZDYTcyVTMtc1RpaGhJV29Eb3B5cDktOEJJLWZoQUE1cldtVnNpWVN2eGk5NTFtc3FkUU9TTGZjWUhha215RngwdnJVZFBiMFQ3UTBucVFOQldzRnprSWg3bjVOdnc5NVl6RzNLdy02QUhsQ21yQXA4aTJqQ1RaR2RzSmpjMmdXck1sNNIBvwFBVV95cUxPV3hBT1AxUGRsdHhpOHF3SEFDcGl4d2Jkc2hOdm81cUNrVllRbXdabDRfQXAybzBlYlh0Q2ZDYTcyVTMtc1RpaGhJV29Eb3B5cDktOEJJLWZoQUE1cldtVnNpWVN2eGk5NTFtc3FkUU9TTGZjWUhha215RngwdnJVZFBiMFQ3UTBucVFOQldzRnprSWg3bjVOdnc5NVl6RzNLdy02QUhsQ21yQXA4aTJqQ1RaR2RzSmpjMmdXck1sNA?oc=5</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>13-05-2026 15:14 UTC</t>
+          <t>13-05-2026 15:45 UTC</t>
         </is>
       </c>
     </row>
@@ -544,238 +544,238 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Developments in R-R Multiple Sclerosis From AAN 2026</t>
+          <t>Pharmaceutical industry key sector for diversifying export basket: Health Minister</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Medscape</t>
+          <t>Amader Barta</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPdUJ5TkUwM0MwTnFQZ3lHM3hWbmxaREZ4dFk5Y3dZaklvanpBeEVGQVoxdEpWTERlemdaZmNCXzUtRWdfUGJ4SU40eU56NEFJSEZ5a1gxWWc1OEpGV2VSZDA3ckZQNjQwaDV1OXpYSENBcnc3aGZ1djBaVVdieTdsT0dQajhmUjFVMmVCSTZKaGhPT0doMEdyZDE5SDFFSE5OSENyb01xVkFCdHBQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxObjBhdTQwMVNqdlcwSTBDSnZIN2RSNlc2Vng4eWFqaFdHM0JQZXV4TzFnb0VjMU1rUnotS2NnYkNIV0hOMVo2Ym1fZXNRS3pXVFVIRjlOalZSTnVFTzFWVE1LVGF5QXZJeTN5cDliM2FlQkJKUlk4a3lGZUlxNmlvempMQ0g5T2U1X0FxR3M0RTJQS0txY3JIYjJ4LWRkdzB3NmEyWmR0blMwUUlGdjdkenBhZUxGVFRLaU1EX1lwTVczUQ?oc=5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12-05-2026 20:56 UTC</t>
+          <t>13-05-2026 15:14 UTC</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Formycon</t>
+          <t>Sandoz</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Formycon stock (DE000A1EWVY8): German biosimilar developer navigates competitive pipeline</t>
+          <t>This Day in History - May 13: Reporting done on polluted water and Tyson Foods</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>KOLN | Nebraska Local News, Weather, Sports | Lincoln, NE</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOeDlVVG5HQzJKVWg1NC1fRHBZeHBjYWlDcVB0c0NCNFdVZWFZb0RwTWcxUG93S1d3QzZBR3k0UWZaTXluRnVKaFphLU9WQ0FqdUp3NEd4MFBwWERrRGVMdWZicVYxTkdfYW91X3JXMXZnSmJaa21JU3Q0ZmRwMUstR3JNcFBYeGJCcExfUUJIWDQzMGhkcnZ5VzJmNU1OWUlsNGdtSVpmUVRjaTk5WlZPTEtVQmFQUTlyZlRDYzI0el9TQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOT3UxNUlCdWZIWjVxRHJaTjlpTVhGMTZEMkZvUEpSSHF3UFBVUGhsSjZqdGh4VUwxZ3RIQlZVM3hmNlB5WHNLOUVhdURVbkczT2I1eHQzcGpYcEI5akdUaUNXcEUyT2RtX1hWT253a2FhNmtERm9GVXAxdFJKTE1hd0Uyc2tqZ0F0Y2hBdktDQlNqU0pIS0RTWUl1VTZJbXFNOE9PUHZHZUJ4RmpKaXJVZWZOU3hnMjNBX0NVLVJnUQ?oc=5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>13-05-2026 12:51 UTC</t>
+          <t>13-05-2026 15:28 UTC</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Gedeon Richter</t>
+          <t>Sandoz</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Richter Gedeon Nyrt. stock (HU0000123096): Trading at 12,300 HUF with recent dip</t>
+          <t>Tony Chachere's stuffed bold burgers</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>WJHL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxONHg2ZlJyQ2NnZ0RDNllkb0FKbDlyaUFKakZZdVRXMnh2cWdBejlsTUlDWnVRSm14dG05Yml4ZjBOejFkR2N3NnhzX0plLVdGY1dyREdiVEhUNElPeFB3cW9sejNUSFFMOUZCUTZJMXlwSFJXaUVnMUtEdi1VdnNvNjNjWWpJN2FMLVdLR0VWaWlxbU1zTDdLeFlBb29RU1JQSHN2dWVSMVFfX05OSGxkZnViUlgyRi02bXppQWN4UXgtZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE1BOHR3TFJCREpnTkp1VXdLM1F0Sld1RFhxVlhzV2sxbXRIWXBkZmsxWkhPaUtQRFlEWjZYa0ZzMmE5Vl92MWpwUXMyYUNYVl8wVVV3WmQ5TU90bkFTMnhHX2ZxTktPNmZBWUJ0di1fM0p2NWtFUlhURm9lRGg?oc=5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>13-05-2026 13:54 UTC</t>
+          <t>13-05-2026 14:21 UTC</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Sandoz</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Brainomix and Boehringer Ingelheim continue partnership in pulmonary fibrosis</t>
+          <t>Tony Chachere's Corn Maque Choux</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Manufacturing Chemist</t>
+          <t>WJHL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPbGliS3lfVzhER3JUNW5va19pZG1QMmNZYTYwQUZYa0pTSXUzeTlIb0o1YmNXRl83N01sTDVsZU5MTU14Y256c2dzTm9zXzJaRmM0SHdmS05IRmNSamZWc1NLdHZxYW5RSU93eExYZGdjTk1UX19tVUVHSTYySVFtTFBvQWNEM2RpT3Z5NXR0ZFhOV1NWd0llTnB3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE1DLVBZZkZKY1VHeVhIMFc0SE9TWV9ud2FCdGVtbDZlNGJIQnVEZHEwbXN2V192bE1TczRSNU9aeTh1S2tHeGotNm9JZWk0Rk9vc21sM0kyOGd0QTgyWnBfV1hpY0tKaElsbE0weV9hSF9xbHJDeFZv?oc=5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>13-05-2026 13:36 UTC</t>
+          <t>13-05-2026 14:18 UTC</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Formycon</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim deepens AI imaging pact with Brainomix in new fibrosis study</t>
+          <t>Formycon AG stock (DE000A1EWVY8): Gains momentum on May 13</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FirstWord Pharma</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTE1kTkpPWGhPLUNXSnZIb2w1aXdnN2lPaVM2NW15MXNIZy1IbEUwY3N2bkQwQ01jbWp1UDFJOFRVaWtLeDJ3SGd0M2d4UWpzVGFRaXFV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOcDJyRWczT1B4RzZ1LWxqTEl6WWtVSG5ScnpYT1ZVaC1yRU4xMWVkUzRpakp3Vkg5cGtTLVhGaGJnQXdxdkZPeXl5Y2tHSzBaV25GMDByVHA4V29TT09Cdk01aVFiUjdoMDdCT2NMWEtoeWUwN2M1VTJPbUd1U2d6c2doRE9qeF9fbTJDMmtHRldCaVNEaU95aTJxT1lVczZhVVVhYVZvNDdnTlMzVGVSUUF2NGo?oc=5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>13-05-2026 03:12 UTC</t>
+          <t>14-05-2026 10:47 UTC</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Formycon</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Boehringer and Immunitas agree on licensing deal for chronic inflammatory and autoimmune diseases</t>
+          <t>Formycon stock (DE000A1EWVY8): German biosimilar developer navigates competitive pipeline</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PMLiVE</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxOQ0pzeENDSjZVUU9SX29rc2R5RW5qX1JDTmtEcVY2UXM5clRJb0w0alVTMmo1dEpwMDhCcUVsNmF3Q05LWkpKRW82UWFwVkZRbldaZGVNSG1tVXg5TG5TNDRQMXYtaVNaSUNhWW5QcEZjUDk1UUpiVzBHb2dHR014OHVaNlV4anEwLWY5Wnkyb3AyUWlhckttRzJYcXY5bnBLRzZyWWdUVnh6UGJmSV9IbC1mOUZnOXgtLWx2VDR4RTRQclRFN0NqTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOeDlVVG5HQzJKVWg1NC1fRHBZeHBjYWlDcVB0c0NCNFdVZWFZb0RwTWcxUG93S1d3QzZBR3k0UWZaTXluRnVKaFphLU9WQ0FqdUp3NEd4MFBwWERrRGVMdWZicVYxTkdfYW91X3JXMXZnSmJaa21JU3Q0ZmRwMUstR3JNcFBYeGJCcExfUUJIWDQzMGhkcnZ5VzJmNU1OWUlsNGdtSVpmUVRjaTk5WlZPTEtVQmFQUTlyZlRDYzI0el9TQQ?oc=5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>13-05-2026 12:02 UTC</t>
+          <t>13-05-2026 12:51 UTC</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Formycon</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Millions for Preclinical Immunology: Boehringer Teams Up with Immunitas</t>
+          <t>Formycon stock (DE000A1EWVY8): German biosimilar developer navigates pipeline progress</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>European Biotechnology Magazine</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPVzFqbWRuYWJkbWEwcUhRSm4tMkxyWFhhdU41ZWx1UGtrZnZKVmxGS3VqWXpvZlFjWVNHM2hfTTBJU2h4RWxJNVA3SDVJYjdsS2d2LWpyZnk2MlN2clJHMUNMMzFtajZpekhjallLdFJ2RktvcV9JYm9fcFpXTjh3ZDQ3eVZncUJESDByYnhTMzRjTVhPSjdFS2s2aTBXTGY2SzIyTTFFbzdmLWZDclpHRHNjamdrU18wR0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNTmZBVmpsYkdJdnR5Z05GUElPbU5lcm9SSFJYV2Vma2ZXellDVkxRZ2E3ZWVHcEtuT1ktMk50NnlEaEZMVXR2UG5tYkpTOGR1WE85Qy1MYmhxcjN3U1ZvdFpiZVlWV1VKbFgtMWdCYkwyYkMzVjFUX0FHMkVJeGFGYzFPMkJROG4za24wTm5VbmZSdGtIcEplLUtZd1o2anYyRjhvUk4xaWdXLVR1LXZoVEZnY2pibHdYN0szZVJ1UU1Fdw?oc=5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>13-05-2026 11:52 UTC</t>
+          <t>13-05-2026 13:04 UTC</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Gedeon Richter</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Boehringer licenses antibody program from Immunitas</t>
+          <t>Richter publishes Q1 2026 results</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>The Pharma Letter</t>
+          <t>Gedeon Richter Plc</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOa2djeHZQU1Z1OG9IRmVVbnZNM0ZTeFVPV3RlOUR2VTNqTG4yVEo4RHROTEU2X2g1bzk5b2h1ZS1lZ0MyclcxRzJYWFZQMk5rd3JKYUNCTjNBWUlWLVVRSDR4TldIUl91ZXB6WW5mNUNDRWdnYmhyTG1TaXhvVE1scnVRY2cwdThGTU5jSWhZbTk2VXQ2cjJpSTJMdmY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE5MeHNtY05Odlh0ODRab1BEcnplUFVDRDBUenZBU3dxeTdyU2YzUjVGekUxTUQxOTZQcnQ3TEh0TVh2VngzbjVZejM4aW1MQjN4d3FxZ3ZZSQ?oc=5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>13-05-2026 15:00 UTC</t>
+          <t>13-05-2026 16:46 UTC</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Gedeon Richter</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Brainomix to scale lung disease solution across US with Boehringer Ingelheim</t>
+          <t>Richter Gedeon Nyrt. stock (HU0000123096): Trading at 12,300 HUF with recent dip</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Business Weekly</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPMHRnbGdITy1GSTFFNFJZRzMtTlJxc245dDUxV05PcnZONDlhTjlHN3ZFUEkyYzJ5TDN5SGM1anNhUlJYWjIwS193dnRPcnlDTTdpbTdSc291UXpFUFppaUQxbzRlQ3dzN3VjTjRwdXIweTNJM2RQNFpyNG5CbWNuckpBQVBNVjM2UkxudHhSYlJxcF84SkVGSTA5aW9FbXZhRDZub1ZvempFVVZYZWdHZHRBeWlNQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxONHg2ZlJyQ2NnZ0RDNllkb0FKbDlyaUFKakZZdVRXMnh2cWdBejlsTUlDWnVRSm14dG05Yml4ZjBOejFkR2N3NnhzX0plLVdGY1dyREdiVEhUNElPeFB3cW9sejNUSFFMOUZCUTZJMXlwSFJXaUVnMUtEdi1VdnNvNjNjWWpJN2FMLVdLR0VWaWlxbU1zTDdLeFlBb29RU1JQSHN2dWVSMVFfX05OSGxkZnViUlgyRi02bXppQWN4UXgtZw?oc=5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>13-05-2026 03:02 UTC</t>
+          <t>13-05-2026 13:54 UTC</t>
         </is>
       </c>
     </row>
@@ -787,22 +787,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Brainomix, Boehringer expand pulmonary fibrosis imaging AI partnership</t>
+          <t>Brainomix and Boehringer Ingelheim continue partnership in pulmonary fibrosis</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AuntMinnie</t>
+          <t>Manufacturing Chemist</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQcUFyTXFVZXdpV1R4U3dsNVJha09NZkM2ZUNNRTd3c0ZjU0EwUnJJOGZDWkVTVEhUNmtuYzZkT281SHcwaERUaHZ0X2pGME1Lc0hRN3dJVHI2YVpaS2wyOHdzZmZhMmJmMm5CWVlSZWtTZm5wUXQ5Q2pPWngxWmVRanBKaWMwY094Z29vOExEaEN6TVFFdVVmUUNLbncwYmhfZ3dMaGJKalI1cFJSZzV0LVZIRkpBbWY0VEhaOW5rLVdieGZRb2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPbGliS3lfVzhER3JUNW5va19pZG1QMmNZYTYwQUZYa0pTSXUzeTlIb0o1YmNXRl83N01sTDVsZU5MTU14Y256c2dzTm9zXzJaRmM0SHdmS05IRmNSamZWc1NLdHZxYW5RSU93eExYZGdjTk1UX19tVUVHSTYySVFtTFBvQWNEM2RpT3Z5NXR0ZFhOV1NWd0llTnB3?oc=5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>12-05-2026 19:03 UTC</t>
+          <t>13-05-2026 13:36 UTC</t>
         </is>
       </c>
     </row>
@@ -814,22 +814,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Both the drug orforglipron and a probiotic supplement help patients with obesity maintain their weight loss, according to two independent clinical trials</t>
+          <t>Boehringer Ingelheim Secures Next-Generation Autoimmune Therapy Candidate</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Science Media Centre España</t>
+          <t>thelec.net</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxOYXpadmJKYXo5Qzh4VEdlNDdHc3M0bXNsWkJIVzIzS0o5bElXSVBuR0xsZVdsdzVEZTRuTXlMbjJJZFFTMEJ0TnFnY0FORXVsNnZyZkFBdndPVEw2SEhISHpoUUx6bkFBUndPalotXzJfNE1rbktySVpfZWJkd0NVWS1DOUpFWVhlX0djRGhaRk9rX0piNWhGTURVYWszSnpKX0ZrcThIVWlPZVZYZkp2U1pxdDFwUGM3OXhJcGpQY2puaHlnTmZrdA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE1uNktXM1JuSUg4Vm8xbUQ0YXFBS3Q4Q3Y0SVFmRy1KRzlvTHRFNlI3SGdrNUFrc0xORU1LajZJUWZmLUJ3empHOUV4cVpMdXhfbmF3TXRYWThtLTI2UDIwUW81QjVjLTQ?oc=5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>12-05-2026 22:00 UTC</t>
+          <t>13-05-2026 23:00 UTC</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>India's top court to rule on survival of revocation pleas for expired patents</t>
+          <t>Boehringer and Immunitas agree on licensing deal for chronic inflammatory and autoimmune diseases</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MLex</t>
+          <t>PMLiVE</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPMEFkMDRuMzJQeWYyUkNOY21rUVBZc2Rvb3R6UFNZamN6ejdzYmdYQkVqRVBkbnkzTmdEYW5WckVuakYxTzVGRnhZZFRFQ1VkZXhrWFdEVnhudTBDSDBoUk9tSDFRRkhFOUpjS3RqeVUtREFnaDVUei1qSmJ2Znl6Rk02dUlmeFJsVEhkU3B4SXJNNGtDM1FYdWpNQkhlUU9EaC1Obi1IdGYxWENteUFzVklvYXAxZ0VEMUFzMtIBWkFVX3lxTE9Rd1JROHVweGh6Zy0zQS02N3Q5MjZxWkpySE5iYk9halp4TlZXcFUzN0RNLXJINDhnT0VJbDl1TFV2Q29uZHVlUFpVanM5V2N5aktBXzdocU9KZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxOQ0pzeENDSjZVUU9SX29rc2R5RW5qX1JDTmtEcVY2UXM5clRJb0w0alVTMmo1dEpwMDhCcUVsNmF3Q05LWkpKRW82UWFwVkZRbldaZGVNSG1tVXg5TG5TNDRQMXYtaVNaSUNhWW5QcEZjUDk1UUpiVzBHb2dHR014OHVaNlV4anEwLWY5Wnkyb3AyUWlhckttRzJYcXY5bnBLRzZyWWdUVnh6UGJmSV9IbC1mOUZnOXgtLWx2VDR4RTRQclRFN0NqTA?oc=5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>13-05-2026 05:05 UTC</t>
+          <t>13-05-2026 12:02 UTC</t>
         </is>
       </c>
     </row>
@@ -868,22 +868,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Chronic Bronchitis Treatment Market to Reach US$ 8.1 Billion</t>
+          <t>Millions for Preclinical Immunology: Boehringer Teams Up with Immunitas</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>openPR.com</t>
+          <t>European Biotechnology Magazine</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNQktMRVZMOFVLQnRrSWZQOWwzdWc1dkJQdmRlU2hNaTgzbzNyNmdGZEwwMXRnaGtvNVF6T19BcUZPRVo2dElxb0ViV2Foal9XQlUtVzBxZ1V1NXlzUFFvSXhmUmwxeXIxRmVJVGY5MmFIMGJ3VWo4RXVBamVTMTJDX0ozQkFTRTI3dlNyaTd6cnd6ZzJYWm10eXlEcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPVzFqbWRuYWJkbWEwcUhRSm4tMkxyWFhhdU41ZWx1UGtrZnZKVmxGS3VqWXpvZlFjWVNHM2hfTTBJU2h4RWxJNVA3SDVJYjdsS2d2LWpyZnk2MlN2clJHMUNMMzFtajZpekhjallLdFJ2RktvcV9JYm9fcFpXTjh3ZDQ3eVZncUJESDByYnhTMzRjTVhPSjdFS2s2aTBXTGY2SzIyTTFFbzdmLWZDclpHRHNjamdrU18wR0E?oc=5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>13-05-2026 10:43 UTC</t>
+          <t>13-05-2026 11:52 UTC</t>
         </is>
       </c>
     </row>
@@ -895,22 +895,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Palatin plans weekly and oral obesity drug candidates for rare disorders</t>
+          <t>Boehringer Ingelheim licenses Immunitas antibody program</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Stock Titan</t>
+          <t>BioWorld News</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQcE5HTnFkMURTMV9BcllrSFgxQzhmNDJtdjVFWEx4ZzJiVmpFSlc2Y1hvU3VqSmgtNmMyTVh1UlQtZnEtZ2dZbEl2d0VuR1ZBZDBvdTNpZE9HZm45NURoa1JuMWdyWnBGTFpBZWNxc0RYYjRjS2JVcHdCR3ZFNnd0MGQyRDE1TkFNTlNfRjg2bEJfSGJrak9sVTFBa1lrdDBoNThCa3ZGQlpBSXRqTzRYVktTeGY5TlZF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOUGEyY2M3azJacGxKSUdtWlhSTHFhRVlCczJpd0hNeEp6UGdtTzl3anQwaUpCVHRQb0VDazkyYTk0ZmExLVl6bzBXOFZ4TlBHRkU1ODU4RXpNT2Z6czRhOVFkVVN2M1lpUXJNdVJ5OXE5WmhGRzFCbzJlVlRVRkhyYnNmVzBvNG5xYXBaY2xicXNzQkhzQ0RqWEctU1RDdw?oc=5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>13-05-2026 11:30 UTC</t>
+          <t>13-05-2026 13:00 UTC</t>
         </is>
       </c>
     </row>
@@ -922,22 +922,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Health Innovation Roundup - May 13, 2026</t>
+          <t>Boehringer licenses antibody program from Immunitas</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Taproot Edmonton</t>
+          <t>The Pharma Letter</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE51UFc5c1ZiTF9jYmdPeW90RUlnaWtyek1LZ3lUSkg0U1U2b2hNMDRuWnpZcGdHbHZTcVkyUy1sd0Z1VWFNc0JTcHhoOGFPV0dkWHZlemEtbENkazRJN2NFSmJiZFJwWG5abDB3U3BWX2dBaFlkVnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOa2djeHZQU1Z1OG9IRmVVbnZNM0ZTeFVPV3RlOUR2VTNqTG4yVEo4RHROTEU2X2g1bzk5b2h1ZS1lZ0MyclcxRzJYWFZQMk5rd3JKYUNCTjNBWUlWLVVRSDR4TldIUl91ZXB6WW5mNUNDRWdnYmhyTG1TaXhvVE1scnVRY2cwdThGTU5jSWhZbTk2VXQ2cjJpSTJMdmY?oc=5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>13-05-2026 13:04 UTC</t>
+          <t>13-05-2026 15:06 UTC</t>
         </is>
       </c>
     </row>
@@ -949,103 +949,103 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Pneumoconiosis Treatment Market to Reach USD 7.2 Billion by 2033</t>
+          <t>IPF patients call for greater awareness and treatment support</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>openPR.com</t>
+          <t>koreabiomed.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQNGZRZ2dKODFYWTJRdE9JN2RsTkdTeVN1eHhmalgwNUhCR0liNjRmTlNrYnoyQ2pNYU9saFF6NnhnZktQYlh5bHlhSlVzUHNMd0p2ZXVaLUlhVWhEdWNoYXFweGtUa1VYSV9HeDEwb3BnQWlmNE1faTZTWVVBR2NzREhwOWl6VWVBRUtzN1k0ek53Z05VbzhpckVSMmJVdHY5a0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE9Xc1k2RUJYRjNtWmVDa1dEVUo3ZDlOaGNCREJyeTcwRG9ocHJyZENSMS1hck5OMFd3SUwyMldwNll6clFPbjBzdTd6TmR2RXZhU0dGMnpodHJBX25keE5OZXpveHFyTm1INHBUbEN30gFyQVVfeXFMTTZBaGVDSDR5N1RIUTNGMHFGbENOa01oTF9aRmRLX1hlVUt3SWdlXzJwU0xmdFNyRjZOQTVFeklxMk5HenQwNXM0SGtNN3R6aFBOV1hwdU5nUmhQanp6NW9mdDluYTNrLVBPQWRZYlZhbjB3?oc=5</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>13-05-2026 11:02 UTC</t>
+          <t>14-05-2026 05:36 UTC</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Hikma</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Hikma Pharmaceuticals PLC stock (GB00B128J450): Active in growing psychedelics and iron drugs market</t>
+          <t>Veeva Commercial Summit to Feature Biopharma's AI Successes and the Path to Agentic Commercial</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>PR Newswire</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQR2hUQTZnWjdIUGZKb1pjOXJTWVdtZ25rVWdyNGY2dE5yRWxoU1VWNDJGdDNFYnlSMWNsUVJZSjR5Uy1aUFZnWm9lWTFOeWNXMHd2NWlVMFFfTk5lOXROM3hDVmNjajh3RHloMGtkT2lUa3lXQUljZDFDbURUZTRtMElRR2c3V0dWX1ZoelVxekRpRjFFdUhPRTVNQ0FXSzRlc3JwMVFvXzZydG5jNWp6SGZNS0h0b1RGUHphNzN3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQUmhIbGJjOHRJSGJUWUV4TV9VX2w5cWRRVW5pQ1d1NlNvcndGZ3ZjZy1tSDh0VGZqRjVQNmp3MVdhOHRRVHo3a2Jnd2h1Y2hMMVFEOVItYW5XZDhrT0g5LUh1N2Y5bkZxandFXzRBUHNadThNa3g0UXM5MkNuTEkwMDkwWUE4RVFwWXdjaGZLcUltLVdwTGZZQ2dTbG55a3VFaGZ6NkZUdEFfaVR0aWh1a1VxZHJMUGpfdTNvOUpfbGJRaUxRb0FPTjA5SDZEZ2sxaUdLVWQ4RjgxejdwRU1UemFsZw?oc=5</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>13-05-2026 12:43 UTC</t>
+          <t>14-05-2026 11:03 UTC</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Hikma</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Academic Accreditation Council receives application for Medicine &amp; Dentistry programs accreditation at Al-Hikma University</t>
+          <t>Companies testing AI analysis tool for early diagnosis of PF</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>saba.ye</t>
+          <t>Pulmonary Fibrosis News</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE1iLThraTIyQmJwOHkwT0JrTkhEYVpVbjZsa00wT1dSajEyNmw5RS03Tk5jaTE5dzhUa2Jvay14eXhNYUV4N2hjZExqcmE0R0U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPSzJKbjUzNVVfY1RmdXRZbG84SUp2TXRfV3U0STRoSHYxbFBtTFNrMV9KMFl5WWtZVTdiajRvOVYxcUQ0MG94blRiVm5QS1RrTEZUS2RZM01pdXlKbkhFY3JsYW0tUWFaMGZTbDF4Y3dLaWZLV3RKSEZGMUhpZ1pwelZrMmc0UFlCZmJOOUcwaEROakQyWnprQQ?oc=5</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>13-05-2026 14:55 UTC</t>
+          <t>13-05-2026 20:14 UTC</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Hikma</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Jamjoom Adds Scale As Saudi Localization Momentum Builds</t>
+          <t>Early BRD intervention leads to better outcomes for beef-on-dairy cattle</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Citeline News &amp; Insights</t>
+          <t>AGDAILY</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxPT0lKSmVCWmRhdzZZdjJsVVNiQS11TTRNSnl0Tm1FZFEtbnZiZmw4WmFSa3VybWlrZ29zZ01lbG1DZVptTlNTQVhJbldsV0xnOWhoOU5YZkFkV01IcERBTGszSUZleERNX2hsdW9BQzFCUHNFMGtRdVduXzF2MGF3S2VWZUNObE52WmJZUTA5WEkyVzhRWS1tZkxyM2g5bGRXdTVkUm9BVnBjZnppUTR2clBjYVNEMnpqb3lubi1iQ0c2RlZmQlZxeUVtWnRMbWxiSzlvdEllODJPSEhja0I3TFJ5ZDM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQSHBMUlBqWHdYeFh4X1FLN3lMOVNzOFExZW5SMDFCNFJ0TUNWSUM2U1N0RnVTajRZT3ZXUFV1MDkxZGtENHMzTEFZaGdWaV92bE1WQ3ppaHdPNjJheXZyLU00OHVka0tudWROY0xMRWp0R3Q0V1hwWU1jZWhDME5PVG5mQWY2THZFcUo2U3dnSlZzWlZaVUtoSnVtbzZYaVJxQUdLcEhR?oc=5</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>13-05-2026 12:24 UTC</t>
+          <t>13-05-2026 15:02 UTC</t>
         </is>
       </c>
     </row>
@@ -1057,34 +1057,34 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Incyte stock (US45337C1027): Patent win secures Jakafi protection</t>
+          <t>Hikma and Taqadum announce ministerial nominees for Zaidi cabinet</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>Iraqi News</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNQXcyNE9ZUUxLdjh5d0pNSk9RZEZ3NUVuMi05Nmx5cWxheGZwMGpMWFlwQndOcG9USFNQS2JISlJfdzJ0aUhWcWVZdlg5eS1GeFlfS0NFdi1QaWpqMzI2TGFVX004dXBIOFFoVkFiblpZWEVORC1oUktCU1lZWlVIRTlvT0hQckd4TXZNdktZQjhSMVIxQXBOaENadE5EclNrS0g2VXBGMTI0Tm1BdE0zaldTMF9qTlBZMC12Snh3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxOaDJOTHIwR28yNkNIWUNaSGZ3TkZtNGlxR1N3YkpHZlJQaWZ0RXRtRnZCbHpmV3NjdXN0RnF2Y05ScEItNlJhS1JwQ0JlVkpuVEhQVDlsamRwalNieUNNaUIxN293aFAzU3dNYXlmN0xYMHBpZ2d3Y3h1Q0NNQ1lWNQ?oc=5</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>13-05-2026 10:57 UTC</t>
+          <t>13-05-2026 20:14 UTC</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Hikma</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Amgen stock (US0311621009): Q1 earnings beat with revenue up 5.8%</t>
+          <t>Hikma Pharmaceuticals PLC stock (GB00B128J450): Active in growing psychedelics and iron drugs market</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1094,93 +1094,93 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQRDk2SjhDeUNYbUhCajRrR0hjSUk2UDZyQzNvZ1J5cmNJd2hFMDZLQWlmaXY2eXZQUkNsR3hwdmF1UnJ6dXlMWWtiT0VfZXpPUUJHbHgxOFdadDh6NHUwQVZ6VExxX00zNWVKMXowOE1iOU54SWNqQjQ1bW0xNkdLSlpyeEpTbG45SXhMTERZQTNaTE5Xd2RFbjhQQTFHV3Fnb1diZ185dTYzeUlmRFFCc1hPUmppRTRWamo2VzFaaVFueXpuQzQ0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQR2hUQTZnWjdIUGZKb1pjOXJTWVdtZ25rVWdyNGY2dE5yRWxoU1VWNDJGdDNFYnlSMWNsUVJZSjR5Uy1aUFZnWm9lWTFOeWNXMHd2NWlVMFFfTk5lOXROM3hDVmNjajh3RHloMGtkT2lUa3lXQUljZDFDbURUZTRtMElRR2c3V0dWX1ZoelVxekRpRjFFdUhPRTVNQ0FXSzRlc3JwMVFvXzZydG5jNWp6SGZNS0h0b1RGUHphNzN3?oc=5</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>13-05-2026 16:03 UTC</t>
+          <t>13-05-2026 12:43 UTC</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Hikma</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Daiwa Securities Group Has Lowered Expectations for Amgen (NASDAQ:AMGN) Stock Price</t>
+          <t>Academic Accreditation Council receives application for Medicine &amp; Dentistry programs accreditation at Al-Hikma University</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MarketBeat</t>
+          <t>saba.ye</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxOZmEzalpsWDJ6MGxMVE1oaVNBbThKRzBxZGU3aUJidDVIUy1ubGRPX1ZRbG1BQ190d2ZhYnhfTXl1aHJreDNNY1AwRGNKZ2pwWE1EeVIwcThFbFI3c25vNDhzMEFNRjZ3SzI2b3NaRVRtYTVoMVlISmQ4dm9PVmdOVHk2Vm5JcWJlaUM5dWF1YVBQT0ROakluUnBDY2JJamxGSWZTWWpINTNUd2dTMTRIaGtVVy1EcGwxWmQ1SlRLR1RxRGFLZzlxZXBGekRrOTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiSkFVX3lxTE5wUUZLY2dVRV9uQndXNmdvdjhuTEd0OFVXLUdWdXZ3NVJFR2U5VDlpd3IxdFZSMWpOME5WcFI4OHVTcGFPYWpXelZR?oc=5</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>13-05-2026 14:53 UTC</t>
+          <t>13-05-2026 14:55 UTC</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Hikma</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Daiwa Securities Adjusts Price Target on Amgen to $390 From $410, Maintains Outperform Rating</t>
+          <t>Jamjoom Adds Scale As Saudi Localization Momentum Builds</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Moomoo</t>
+          <t>Citeline News &amp; Insights</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPRlBNaklDVnVvSXpSOF90dGlxVlZLeHFWY1BfV0VyV0hzT2FHTWRQRjQ3WWZqNVZreW9VeXMydVp3LUxZY01JZGNrMkZER2JHZmxpd1JJaHgyVU9IamRTQU1raFE2N0ZGbTNrTHo5WENPUDgtMjRVYmxOOWJXN2o4S0RUWThkb1ctT21XQm9yNG9pTW5WejdvTGwtX2lpV0hBYlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxPT0lKSmVCWmRhdzZZdjJsVVNiQS11TTRNSnl0Tm1FZFEtbnZiZmw4WmFSa3VybWlrZ29zZ01lbG1DZVptTlNTQVhJbldsV0xnOWhoOU5YZkFkV01IcERBTGszSUZleERNX2hsdW9BQzFCUHNFMGtRdVduXzF2MGF3S2VWZUNObE52WmJZUTA5WEkyVzhRWS1tZkxyM2g5bGRXdTVkUm9BVnBjZnppUTR2clBjYVNEMnpqb3lubi1iQ0c2RlZmQlZxeUVtWnRMbWxiSzlvdEllODJPSEhja0I3TFJ5ZDM?oc=5</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>13-05-2026 11:53 UTC</t>
+          <t>13-05-2026 12:24 UTC</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Hikma</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Tezspire (tezepelumab-ekko) for the Treatment of Severe Asthma, US</t>
+          <t>Academic Accreditation Council receives application for Medicine &amp; Dentistry programs ...</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Clinical Trials Arena</t>
+          <t>saba.ye</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOYTdfUjB1SDNKbFJ4WDltZ1dNcThZNGFBZFd4T1o1b0pPaW5EN3Vwb1lFRFBHakwtLTU2RU9vc3ptUHRRRjA3YndJdVI2eVAzN29sdlFMMUtEaFM5X0lBQ2ZFclY5YzZESGZNNlNLZ2tRUTVSc2RDWlExR180ZF80NGlDcXhCbmNpYzRNM0pEQUZDYlNvZlZrVTQzcFV1ekZSU09oOUhST1FVVmJoajcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiTEFVX3lxTE5LMmhjSDlERExXMVdUaDJjcS1tdWp1MXRyeW9MZUtLRVlsRkZVa3hfdVVrdnF6ZUVERkNvRm9aVmtFYVBrLWFiVXQxTDk?oc=5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>13-05-2026 02:48 UTC</t>
+          <t>13-05-2026 15:38 UTC</t>
         </is>
       </c>
     </row>
@@ -1192,22 +1192,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Guggenheim Trims Amgen Price Target to $340: Is the Biotech Giant Losing Its Edge?</t>
+          <t>Amgen expands U.S. manufacturing footprint with additional $300m Puerto Rico investment</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AOL.com</t>
+          <t>The Manufacturer</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOY0hXVG42cEhDME1pX1RMZ1RCaVNWNmttczBxRUdVRlJUaGpGdVNEeE03dWsxSDF3TWloeFFUaU9qYlFDcEtFd1JDdlh0MS1MZUxGLThtcHVCaHpMc3k2X2EwV2ItVnVqdU1LSFlwZWpPNHhjcEkxZWZaZ1JpZmhLc0hYdFpsdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPcTlIckFocHo5eFNvTGJSS3ZVRE1BbElIZmlyNndMMHdXckZOLW82cVJ4UjFfR0s3Tm82Qi1pR3I0cTZCTDJ3cGtzMXBUMEw1LXlWMWlDR2ZGXzlWUDlzdkZ6VXE2YjVUaTNzMTJVVEQ3ZGdjNFRFSHRTU0JNc3A2T1ZBNERQSTJleVlxcFdaVC1sYnlVNWQtVThqNS1iMUc5NHFpSTF1UkRNMHUzMEtUNnkzM1VHWXptY3lieGhQYVNjamtBNXc?oc=5</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>13-05-2026 12:23 UTC</t>
+          <t>14-05-2026 05:08 UTC</t>
         </is>
       </c>
     </row>
@@ -1219,22 +1219,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Amgen Inc. stock outperforms competitors on strong trading day</t>
+          <t>Rayburn West Financial Services LLC Acquires New Position in Amgen Inc. $AMGN</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MarketWatch</t>
+          <t>MarketBeat</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxQSExNMl9BamprcTRSbDVrZnQ2cjBVUlZFbERXVmR4Nkw5aTZTa0gyOVRsdkV3ZnVDNzRDRTRtelFzSmpMNnl4VnZwN0MtZ0ItYTdSOVpJeGNreWNtVk9EZHEwdTNiV2JhUUxiOEo1U1FaSGUxVkhwOEZhZnprNXhPVC1GQVpvTlpuaDFKbHpndHRFcEFud2llMzNTcXZHWEpXcHRIUFJSbDZJQUFHWXBmc3ZlYUo2RkRHR19kT09IcHpDNUxrRnM2OHR5SGx4TF9JYTJ3akxR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxOS19HNFNZeWs4TDdGYVBoWkFQNmlRTE95ejNVS1hSN0NSaE5FRmRZSzlmMGlsMndDaVEtWXJ4VXdDWGw2VGI3eFdnNEc1ZVZDcDV6bGdINzVJQVVqbUJJX2cydHZ4RldpaFpaMUx2cDF6eGJqME0wb0hUR01IOVV5TlBaemRQcGNhSnZLRjhqaDY3Z3N6a1k2RUVWbTNIMFRHTDdKTDJfZ2ZJdHd3bmVaNEdGUDZqRHNJenhQOWZWSGtsb0FaeG9nLUtKZ0VJVzVNamc?oc=5</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>12-05-2026 20:34 UTC</t>
+          <t>14-05-2026 10:09 UTC</t>
         </is>
       </c>
     </row>
@@ -1246,22 +1246,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Join and Learn More About the Evolving Obesity Treatment Landscape at ECO26 – Amgen</t>
+          <t>A Look At Amgen (AMGN) Valuation After Q1 Beat Guidance Upgrade And US$300 Million US Expansion</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Oncodaily</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTE9wVU1VSGdDTmg3NXJZNmZBa1VEUEZOLUtYLU9yYzdibWdwR2NHcm52V2hHOXRIY3MtdHFTSE5ReThjNUFPSjVHVndwWkFHc2pzYnE4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxQbF9pVnlGNFRSVU1DTEdITl9CNl9NTGpOVGMtSkk1bExUeDRRSEpidExac0JmWnViUk1jcG9tcDR0QmNRWHhCajZmdnZzTmlLczZqNWdscGh3T3hHQmpkTlV2WnlWdGQxRWs0QXpGd0UtWDdrTTBwQllEaXRTMmQ2bkJHclhrN2Z2Q1h5cjVfQkZOaGg2bE02MDdoOTQwRVRwMEN1X0xmLThCb0ExbnFSWG5fWDNqX0NQQ3duRDhmMDVMSEZ1bXZEWEJEU01ZZHV0dC01VThR0gHbAUFVX3lxTFBkYTVRLWRDS3FRenZSTzVvaHJXOXhUZWxVams3WW9FSnJOMXBzOXNWZ0wyQjJuc2tmazhfOUtPZTVBaUxQNHBFNW9nb09FNXJiTXFHM3A5dE1wNURmNklobnA2cHgzUUZkLXhIQ2xtR1ZnN3JYQ0tJR2JQQTRQUFk1eFBmQVl6MmpLYWhVYkJxTUcwcDFZX0VPVFhGMmtHR0U5cm13V0NCQXA0UWxiTzE5NTBrcUlyUVlCcDEwV1FGWUlMSXlZUHh5T1VpUnFzT1FRd1YzMDJDZWJsOA?oc=5</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>12-05-2026 21:00 UTC</t>
+          <t>14-05-2026 01:07 UTC</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Amgen stock (US0311621009): Q1 2026 earnings show net income turnaround</t>
+          <t>Amgen stock (US0311621009): Q1 earnings beat with revenue up 5.8%</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1283,12 +1283,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPMk9yTk4yU2I1ZWRZSnBPWTJULVpUbS1oNkdaQ1hQUjBYX3RycHp5dnpQWmxJMnJVZk5WRU42bTlLWDc5MkQtb01sR2NjeTBWcHFCOXE0dzZLYXR5M0hLak9Fb3ZfYzRYR3FOX1pMekNBNUN0MFRMU1BTSkw4cHdFVVVZUjQ4N092YUdleXJkMV8xZzlSRFhBaEJfYVdSQTdkd1E4YTNTVTNSZFRQTVZyd0dSX21aMG5qRFB6YXFEWjNEY3ZEZ3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQRDk2SjhDeUNYbUhCajRrR0hjSUk2UDZyQzNvZ1J5cmNJd2hFMDZLQWlmaXY2eXZQUkNsR3hwdmF1UnJ6dXlMWWtiT0VfZXpPUUJHbHgxOFdadDh6NHUwQVZ6VExxX00zNWVKMXowOE1iOU54SWNqQjQ1bW0xNkdLSlpyeEpTbG45SXhMTERZQTNaTE5Xd2RFbjhQQTFHV3Fnb1diZ185dTYzeUlmRFFCc1hPUmppRTRWamo2VzFaaVFueXpuQzQ0?oc=5</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>13-05-2026 09:41 UTC</t>
+          <t>13-05-2026 16:03 UTC</t>
         </is>
       </c>
     </row>
@@ -1300,22 +1300,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Amgen stock (US0311621009): Q1 2026 earnings beat estimates with revenue up 5.8%</t>
+          <t>AMGN: Key products and pipeline assets drive growth, with major investments and strong Q1 results</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQZmY0MEtCSlpQbE5VMFpMUmk2YVpmOUphZTVwYzlfdENWUGNkaHZnODJRMmhqSHZLOFZ0Ymh3Z3I0OUxFc25Cem9ONVFrc21ESDJGVkQ0TWtnX2pMQkZmUGwybXY5aFBKWFpNcUhMRnBteHRBZTVqZ21sUTRPRjlDTkdEUUI3UjVKWHd5aW01M1cxN29NM3lMcUNjdGF0ZzJQQzcyYzZ6UE1nYjBSekJUNEF1MjF2R2tnTTh2Z2E0SXZwQzl3VnBv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwJBVV95cUxPMVExSnBUQVJtX2x6UjBhdERMTzlyaEs4SC1XMzRoRlhBVXJJTDRuTlZsMHJNVzJPaGtreDZPSVZ1azNhZGF0ZHhjOFU3bWN0NE9ac3R3bm9pZmVIM3kwMlozaV8yY1lvajdaNjFoY0tvZUxMa1dIR3JGRnVBQzVhTUp6blRUQ1JfYkZnVTdSY1p0Wi1JN1dNYXliYk5PQS16SnA0MUdkRHI2WHhGeFZIYkkyWXlVWFZ1cmlfblZKeW1kV1FUY2tQMjVWM0V0SVM2enZTMmVXRmFKSWZPZWU5SG5ZcWRQUC1IbzVPZGZQLU11X1lSOTNvVmxJb1FnaVhmQVdIME9VSm5YUVY3S2kw?oc=5</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>12-05-2026 19:51 UTC</t>
+          <t>13-05-2026 18:33 UTC</t>
         </is>
       </c>
     </row>
@@ -1327,22 +1327,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>The Dow Jones Index Opens 0.11% Higher</t>
+          <t>Summit Wealth Group LLC Co. Has $386,000 Holdings in Amgen Inc. $AMGN</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>MarketBeat</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPdDJ5ZklnbXJyQnZaVnBVVEF0Zkc1X2hXT2ZPTXhRV1I1TEFpbWF3ZlppZm9NdkE1Vk1qblRsWS1fejMwWF8xaWRKNmdURTRBdUV1X0huT3d3NW5QYWhXVmlfQlRYa3ZKRFN5enoteFFkbnJCWFJSVHRvR3NBTTBjZElPSXVGalpZcGFVQ2NFQ2lLZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQcjRlLWRuVnFhTU9BM2t2cXg3S2R2cFA3cFRYdG5PdUVEZFVUb2FmU3JCZEtRS1diMkR2bnNCeUtMeVM0ZjNRWGpkbG9JaTBWWVk2N0dkY3lQSTVreGRXX2s2akZfeUVfTEJTeGtnNzFjVkQwa3lTVEpqcU02T1RqRmVaVk5NUld5RmRqNHYta1JWS0d6bGxHWGZ6Si1Fckd3a19fVFBvQzhERFVZcEtsbHNEdUg3dXNZdlVzdTYwcmJwX2s?oc=5</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>13-05-2026 13:30 UTC</t>
+          <t>14-05-2026 09:47 UTC</t>
         </is>
       </c>
     </row>
@@ -1354,22 +1354,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Myasthenia Gravis Updates From AAN 2026</t>
+          <t>Sean Lybrand: Proud to Support the Always Innovating Campaign</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Medscape</t>
+          <t>Oncodaily</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxPZ0x0S3NOdjhXaFJjZnQyTVlfNmdBdkpPVXpsdDBCTEo1YUZBN3c1V3JWcEtvbHg0WE5wNGNUODRXMUJQLWw3VTctUXVyM0o1S0xETGJiamh0YS1HWllVWHFraDZmOWJRaHBxNlpFOHFrVHdDbnFiRzUxUkpLd0dnVTJ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE0wSWtlaEZhOVRGRWkycHkxVGxsZlNraTZsQWR5M1J2d1loYUt1VXZXRFZzOGZiRHFDQ21ZUjY5Mjc4VmFKZVQta3hmbFpMNzNUZFhwYkEyU3otd1VY?oc=5</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>12-05-2026 20:15 UTC</t>
+          <t>13-05-2026 18:48 UTC</t>
         </is>
       </c>
     </row>
@@ -1381,22 +1381,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nano-Cap Moleculin Biotech Approaches Key Leukemia Trial Data Unblinding</t>
+          <t>Daiwa Securities Adjusts Price Target on Amgen to $390 From $410, Maintains Outperform Rating</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Benzinga</t>
+          <t>Moomoo</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxPbTNDWlBsWmZWLWE4SzltNmtBMTVhLTdrSVJxaExSWF9OSk5kUEU0NW8zQkxocTBCQUNpcFdVMHIzcFJTM0E4cWZvTHNIQUVGZ3AxbWhtTU1LVXBLUmJibmo3TUFtSTdpWE5FcTA3V2M5UkU5eUdIU1N2S1BtRThmcVplcG96cFJjdXJkUW5DNzR6aTItOEJkODFOSVlfZFVzTHRNX3RmQWJsZW1GLUhQeVR2M1VkeXVnU2tLM1ZBS1pwUDdZNURVYg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPRlBNaklDVnVvSXpSOF90dGlxVlZLeHFWY1BfV0VyV0hzT2FHTWRQRjQ3WWZqNVZreW9VeXMydVp3LUxZY01JZGNrMkZER2JHZmxpd1JJaHgyVU9IamRTQU1raFE2N0ZGbTNrTHo5WENPUDgtMjRVYmxOOWJXN2o4S0RUWThkb1ctT21XQm9yNG9pTW5WejdvTGwtX2lpV0hBYlE?oc=5</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>13-05-2026 16:41 UTC</t>
+          <t>13-05-2026 11:53 UTC</t>
         </is>
       </c>
     </row>
@@ -1408,211 +1408,211 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Real-world TED data finds disease advances beyond acute phase</t>
+          <t>Nano-Cap Moleculin Biotech Approaches Key Leukemia Trial Data Unblinding</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Eyes On Eyecare</t>
+          <t>Benzinga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQNVVVRkduWDF2VEJIZlRPZTA5U2tBS2VfdjJJSmxkVExURy1RbW1yXzl2U2MwSWhrOFBGSms5aEpLMlFXLXAxYXNfSGZhU1FsNXVxTjFlcEw3YzU3YlJfT1g1cVBISFRLc1lpZmpkczJNMjU2R0ZNa040U2l3M28zRUpYX3BUUXdxRXlnZU42R2VPOVZPUml1Z3FyQkpUZWpTOG1VVm9ubHNXWUljU3ZZcjUweXlHVHlNWmktVWF3N3BUZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxPbTNDWlBsWmZWLWE4SzltNmtBMTVhLTdrSVJxaExSWF9OSk5kUEU0NW8zQkxocTBCQUNpcFdVMHIzcFJTM0E4cWZvTHNIQUVGZ3AxbWhtTU1LVXBLUmJibmo3TUFtSTdpWE5FcTA3V2M5UkU5eUdIU1N2S1BtRThmcVplcG96cFJjdXJkUW5DNzR6aTItOEJkODFOSVlfZFVzTHRNX3RmQWJsZW1GLUhQeVR2M1VkeXVnU2tLM1ZBS1pwUDdZNURVYg?oc=5</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>12-05-2026 18:39 UTC</t>
+          <t>13-05-2026 16:41 UTC</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Amneal Kashiv Biosciences</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Amneal (AMRX) director Deborah Autor sells 34,819 shares at $12.94 avg</t>
+          <t>AMGN: Key products and pipeline assets drive growth, with 2026 targeted as a pivotal transition year</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Stock Titan</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNNnhqeDdOQnBseGpRVVA2RzdfUkcxdU9rajg3UTRMOURTc1JsMXAyZEVGN2JJd1VHZVAybWFXNUlOMkFxTTJlZTJfWjFOcG03VDdXS0M5clFnLVlEUTZnUEVoOXdacFNGWGRxVEwyUl9VaElCSVZFNDNEcDhVYXRHSktwc2dOVm92SDd5YVN1MUswOFlqcU03X25YOTZjX1lZUk5UQkp1azV5a0dOd2p0RjFETDJvbTVuMHkzWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwJBVV95cUxPU0JDdmQ0dHlscl9Yc255dmRtd0tlRmh4bnc0ZFozeXNyOG43Q1FsTEdEOVhIWXlFdEctZGRXSV9tYjBkWld5NHExSnFOQmY0YlVpR24xajJhODdfWmpEcjI0WVgxRmw1T3plVUV1T1FYeEhCTjE5Z1pYRDY2ZzhVRklyVjlrN2RaVXdIV2JCdGFrUXlRWk5GMTRqZ3ZZd081YWc4SmVnYUlkWjl2SzVSWTRqSWdQQW51cjE2bk1QNG1pRk1wOUdWQk5ES3VjcEIyRG5nb1pzVXJYNVNQd01GVkYzdjlrWlBjelk1eFpTc3Z4aFRKaUd1bWRERGoxTzFoMXVPTXVncXVaRlpMcXNidUhlWQ?oc=5</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>12-05-2026 20:10 UTC</t>
+          <t>13-05-2026 18:04 UTC</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Amneal Kashiv Biosciences</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Insider Shake-Up at Amneal Pharmaceuticals as Director Offloads Significant Stake</t>
+          <t>Atria Investments Inc Buys 10,877 Shares of Amgen Inc. $AMGN</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>MarketBeat</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxNdWFhQUI5ZW5ROGFiaWxoclNLbklub3h4YmFpUVJYaWVCSzJyTEVnNUQ2N2drZ1RNUXBBdTBPYzdvOFpJTmN1RHpESUQ0WUVCSEhzNEhVRmQ3QXR3eFR4RUVnSHI4TzAxLUlPZ2dyRHdKOTBwZTdqMkZSQ05WMFZzVEZJNzM2TG1UQTUzLXhJaWNxMmlPcEpJVGhpWHlWOThLRzBJSWFEdTFPbTRteUc5ZC1XazlycTJZMjdnQ3VCNXZRemRiQmlpeVhydXBaS3E4SVNDU1lTVXVLa1NMT1VMRzBB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNVktkZDVuZjRBWHlUbzJmczR4eE9qeXhuZkRYQl9tWEx3RnBnWVY4VlRQWDktS1BLblZhWEE0NzhMRHlpRWM1TWF1dG82WTR0MEFfNVhJaXg0UllGTzlyTEFOMFlzQTZqN2FNU3AtcUZqVWo1b1ZQXy1YZFdfNTVLTzhjS1FJVDVhUlMyak9ab3hLN1RGaXhuaEp1V0l2OV93NW93Z1JmQkxoemN6VjRPc1JCSzloNGE4eGc?oc=5</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>13-05-2026 09:00 UTC</t>
+          <t>14-05-2026 07:32 UTC</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Aiming for the Sun: How the $11.75 billion Organon buy is cementing Dilip Shanghvi’s legacy</t>
+          <t>Angel Hidalgo Portillo</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Business Today</t>
+          <t>PGA Tour</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxNSnZOV1FkZk5fdDYwOXRlZm5uTW1rWk9kNE9YWmhUdlFMdTI0OWhyUDhmc1h0enpzWDRxN21zanY4SGxBeVlNblVNeXhFc0h6SzA1Wm9QSU9fOXhXaGJlYjN4ZU40amlrWE5TajEydjlkUEFlT0g0T2xJMFBxbEdQWS14UGVCLUtJWlZ3THZnQ3p3X3UwZlZESFlNNlF1eUUzd3lMV0sxQnBLeDMzSllvOElDSkY1X1J3U1hZVllqemNUcHBVSlZ2QlVxSkVseF9VbkxnU1lBOTZRSGVlb0k3YVhEWGZxYTBlenFsYi1ZOGVIWjFx0gH6AUFVX3lxTE5fR0I5R1ctbVRjTW9IUnVFaEhDLXBxUlZyaXI3c0E1Z054NERGMG45aG00MmtrMURJRG5iRjBJZVZmbXk3N3EtMmdBVE5lU25ISWJBaXNMRDBfYTZGWE53c2dKNmFVdDY3RHEtMUl5WWUwbWZxaHJrdUd0ZkoxczQxSzZNTjdyOURDMXo3dzNveDVVSjcwSHdiNVJ6S2FvQWlmZFZ5UDZhZnJVX29WUmRBZDRCb18xZngxZkpaZ2o3TjBzQklvNnBMTC12M3luWElMaFI1MjB4SkluT2ZZLU1FV0VOY1RZUnNiQnFNVzdvdDIxeWdacFVYeXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPaERYVHplT3hWYUh2dnZWakZCMUszNGFLSlEzN2RxQVhDZWMydk1IRkdyUkpfV0cwaVl3OTdrdXlWeGZjWDhaanlJSENxLTd6RmdycTZsTE1GZkx4X1VVMFpKVm1pSmZUVFdVU3o5RTF6M0swRmdkY3B6Rnl4S0NCLUpfR0gyU1pLX0FqS1hrdi1uYlNYQjJFTzdDVUJaZ0tHUHdTdF9VVWpRUEVoNkVyX21PcXB1WC1fR2V5Rw?oc=5</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>13-05-2026 13:54 UTC</t>
+          <t>13-05-2026 13:32 UTC</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>What Sparked Organon's Recent Stock Surge</t>
+          <t>The Dow Jones Index Opens 0.11% Higher</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Kavout</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxNUmtVcm12TkR6UzVzMmVfdWR0WDhFeTMtX1JLWmRZbTc0SFNnc2d6SDljN2R0N3JYMF8tb0FyYVh5MXFlS1pDSXdmVWY0MVlrTWoxTHVSSVRoeW9abXVBLWhmbUZPdWJkdWNMZXhmNC0zeFFremFDODRSRFlzUUNCZmZ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPdDJ5ZklnbXJyQnZaVnBVVEF0Zkc1X2hXT2ZPTXhRV1I1TEFpbWF3ZlppZm9NdkE1Vk1qblRsWS1fejMwWF8xaWRKNmdURTRBdUV1X0huT3d3NW5QYWhXVmlfQlRYa3ZKRFN5enoteFFkbnJCWFJSVHRvR3NBTTBjZElPSXVGalpZcGFVQ2NFQ2lLZw?oc=5</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>12-05-2026 19:49 UTC</t>
+          <t>13-05-2026 13:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Transforming Sun Pharma into a truly global pharma company</t>
+          <t>Daiwa Securities Group Has Lowered Expectations for Amgen (NASDAQ:AMGN) Stock Price</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Business Today</t>
+          <t>MarketBeat</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxOZndpVlA5Y1otTjc5NDdtRWxwb0x5NnduUmdqUlkwSEVaMXpTdnJZXzR0Vy0yVDV6VVhBRUNtUHBwcjlXUER4VDROcDJqaUFadjZlOU11Z3JOLWcyOEhLQlFsbzdDMFh4b0tuM19fV0FfTW5VdDRTYlFxNDZMWlFmbnNDMFdZeUxvamYwcGhwY2lFZEhhZWlXb0tBQnZZTkZpVXFZUXlVb2oxMGpkLXRwSG5SbzJ2UENoWUp2bGxQMElpS1B4Nm5XdG5zUXNaTHZiZVo00gHTAUFVX3lxTE5md2lWUDljWi1ONzk0N21FbHBvTHk2d25SZ2pSWTBIRVoxelN2cllfNHRXLTJUNXpVWEFFQ21QcHByOVdQRHhUNE5wMmppQVp2NmU5TXVnck4tZzI4SEtCUWxvN0MwWHhvS24zX19XQV9NblV0NFNiUXE0NkxaUWZuc0MwV1l5TG9qZjBwaHBjaUVkSGFlaVdvS0FCdllORmlVcVlReVVvajEwamQtdHBIblJvMnZQQ2hZSnZsbFAwSWlLUHg2bld0bnNRc1pMdmJlWjQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxOZmEzalpsWDJ6MGxMVE1oaVNBbThKRzBxZGU3aUJidDVIUy1ubGRPX1ZRbG1BQ190d2ZhYnhfTXl1aHJreDNNY1AwRGNKZ2pwWE1EeVIwcThFbFI3c25vNDhzMEFNRjZ3SzI2b3NaRVRtYTVoMVlISmQ4dm9PVmdOVHk2Vm5JcWJlaUM5dWF1YVBQT0ROakluUnBDY2JJamxGSWZTWWpINTNUd2dTMTRIaGtVVy1EcGwxWmQ1SlRLR1RxRGFLZzlxZXBGekRrOTQ?oc=5</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>13-05-2026 13:54 UTC</t>
+          <t>13-05-2026 14:53 UTC</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Apotex</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Dr Reddy’s set to scale up Semaglutide generic franchise, trims oncology pipeline</t>
+          <t>Eugene Braunwald’s Legacy Shaped Modern Cardiology</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ETPharma.com</t>
+          <t>Medscape</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxPQjJxeUVmdVg2M2E1ckpVdXR4cE1BQmloVEpVSUpJZzV5Y2pqT3BjRzhNU0xPMXhjMGczcnRLbzA0RXFKR2o4N0sxR2tiNk5rX0NuSXBTWEI2cVNLRXlGamhQVHRLb1dnX1VEQmlMUUJVXzFhb3J6cXdweFJOWHVVR05YRTF6ZWoyU3B5Vm43Mll3N3VMNVRyVlotUjhIWEFUcUkwaFFLd3h3VTY4c3l5S1RjM3RCS2hueDQ2VmNTV0VzdDEwTVdUX21PS1diQVd1d3h2MEdXY0dIWWRXYTMtdzNVSk1ZVDJaTl9FaGdza9IB7wFBVV95cUxPQjJxeUVmdVg2M2E1ckpVdXR4cE1BQmloVEpVSUpJZzV5Y2pqT3BjRzhNU0xPMXhjMGczcnRLbzA0RXFKR2o4N0sxR2tiNk5rX0NuSXBTWEI2cVNLRXlGamhQVHRLb1dnX1VEQmlMUUJVXzFhb3J6cXdweFJOWHVVR05YRTF6ZWoyU3B5Vm43Mll3N3VMNVRyVlotUjhIWEFUcUkwaFFLd3h3VTY4c3l5S1RjM3RCS2hueDQ2VmNTV0VzdDEwTVdUX21PS1diQVd1d3h2MEdXY0dIWWRXYTMtdzNVSk1ZVDJaTl9FaGdzaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNRm11SFJLclBaNl9yb1BTejRQOTVhMEtyWVc3VnlOUnMwalpCcjhSd25yVDg0RnhXZ2pENTY0bXFEYXBGVFd3bDdMYU1tb0RBNnJ0dmsxUzd6U1llZ2tieTFodUFXVkN1UXJrTHM5S0N2bFZSSlhrZmx2NHZpTWkycTBNQUFSd0tRazNCbFJtTE9iaUtQdW40SGdnZGpyVkxG?oc=5</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>13-05-2026 02:26 UTC</t>
+          <t>14-05-2026 09:13 UTC</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Apotex</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Jamjoom Adds Scale As Saudi Localization Momentum Builds</t>
+          <t>Aiming for the Sun: How the $11.75 billion Organon buy is cementing Dilip Shanghvi’s legacy</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Citeline News &amp; Insights</t>
+          <t>Business Today</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxPT0lKSmVCWmRhdzZZdjJsVVNiQS11TTRNSnl0Tm1FZFEtbnZiZmw4WmFSa3VybWlrZ29zZ01lbG1DZVptTlNTQVhJbldsV0xnOWhoOU5YZkFkV01IcERBTGszSUZleERNX2hsdW9BQzFCUHNFMGtRdVduXzF2MGF3S2VWZUNObE52WmJZUTA5WEkyVzhRWS1tZkxyM2g5bGRXdTVkUm9BVnBjZnppUTR2clBjYVNEMnpqb3lubi1iQ0c2RlZmQlZxeUVtWnRMbWxiSzlvdEllODJPSEhja0I3TFJ5ZDM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxNSnZOV1FkZk5fdDYwOXRlZm5uTW1rWk9kNE9YWmhUdlFMdTI0OWhyUDhmc1h0enpzWDRxN21zanY4SGxBeVlNblVNeXhFc0h6SzA1Wm9QSU9fOXhXaGJlYjN4ZU40amlrWE5TajEydjlkUEFlT0g0T2xJMFBxbEdQWS14UGVCLUtJWlZ3THZnQ3p3X3UwZlZESFlNNlF1eUUzd3lMV0sxQnBLeDMzSllvOElDSkY1X1J3U1hZVllqemNUcHBVSlZ2QlVxSkVseF9VbkxnU1lBOTZRSGVlb0k3YVhEWGZxYTBlenFsYi1ZOGVIWjFx0gH6AUFVX3lxTE5fR0I5R1ctbVRjTW9IUnVFaEhDLXBxUlZyaXI3c0E1Z054NERGMG45aG00MmtrMURJRG5iRjBJZVZmbXk3N3EtMmdBVE5lU25ISWJBaXNMRDBfYTZGWE53c2dKNmFVdDY3RHEtMUl5WWUwbWZxaHJrdUd0ZkoxczQxSzZNTjdyOURDMXo3dzNveDVVSjcwSHdiNVJ6S2FvQWlmZFZ5UDZhZnJVX29WUmRBZDRCb18xZngxZkpaZ2o3TjBzQklvNnBMTC12M3luWElMaFI1MjB4SkluT2ZZLU1FV0VOY1RZUnNiQnFNVzdvdDIxeWdacFVYeXc?oc=5</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>13-05-2026 12:24 UTC</t>
+          <t>13-05-2026 13:54 UTC</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Viatris Targets US GLP-1s With Auto-Injector Strategy</t>
+          <t>Jamjoom Adds Scale As Saudi Localization Momentum Builds</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1634,66 +1634,66 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxNQ0gycmh2M21KcFFTak93d3AtUUF0MWJHUDhMRGh2UFFmYmFsYUJJc1BkWUY4RzhLeEpuRENKRnNlMjAyRTBucnZIQ21qdVVaTHRGR3poTjhveU9pekV1cS1CU3FnSDEybEs1ZFlzZFQ3cXhxLWFBQk04bEZkQjhfUUtHVTJGdk0xQ0diNGpfTjdZdmllTkY0MW0xeXNUZldzd2hOSkhZMXhJVE12d2RjUGZOR2ZUdkh2dWxlX3J5VUdvUTk4bW1jSGpRTzE5MzlQQ0FwUDdFOHZDNTFhODMzb21TM3ZqamdmTlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxPT0lKSmVCWmRhdzZZdjJsVVNiQS11TTRNSnl0Tm1FZFEtbnZiZmw4WmFSa3VybWlrZ29zZ01lbG1DZVptTlNTQVhJbldsV0xnOWhoOU5YZkFkV01IcERBTGszSUZleERNX2hsdW9BQzFCUHNFMGtRdVduXzF2MGF3S2VWZUNObE52WmJZUTA5WEkyVzhRWS1tZkxyM2g5bGRXdTVkUm9BVnBjZnppUTR2clBjYVNEMnpqb3lubi1iQ0c2RlZmQlZxeUVtWnRMbWxiSzlvdEllODJPSEhja0I3TFJ5ZDM?oc=5</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>13-05-2026 13:40 UTC</t>
+          <t>13-05-2026 12:24 UTC</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Apotex</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>‘Nature’s algorithm’ found in Chinese money plants</t>
+          <t>Viatris Targets US GLP-1s With Auto-Injector Strategy</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Cold Spring Harbor Laboratory</t>
+          <t>Citeline News &amp; Insights</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE5rS18weFg0RnRwTHlQeWJZZUlZbXBHamw4VEcxeTVsT3Z6b01zWU5UbnpLbWpEQ1Y3SnNNbTNVSnlzQVBHMHFiQWZoelNZOF9mbG1zS3Y3MExNWC0yRkV1c0swdmpNYWVHVnFrVGROX3R6TlQxRnhXMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxNQ0gycmh2M21KcFFTak93d3AtUUF0MWJHUDhMRGh2UFFmYmFsYUJJc1BkWUY4RzhLeEpuRENKRnNlMjAyRTBucnZIQ21qdVVaTHRGR3poTjhveU9pekV1cS1CU3FnSDEybEs1ZFlzZFQ3cXhxLWFBQk04bEZkQjhfUUtHVTJGdk0xQ0diNGpfTjdZdmllTkY0MW0xeXNUZldzd2hOSkhZMXhJVE12d2RjUGZOR2ZUdkh2dWxlX3J5VUdvUTk4bW1jSGpRTzE5MzlQQ0FwUDdFOHZDNTFhODMzb21TM3ZqamdmTlE?oc=5</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>13-05-2026 08:48 UTC</t>
+          <t>13-05-2026 13:40 UTC</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Apotex</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CCMB researchers find molecular ‘glue’ that blocks viral spread in plants</t>
+          <t>Canadians can now get Ozempic, Wegovy delivered to their homes. Here’s how</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>The Hindu</t>
+          <t>Global News</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxPV0tkN1NWT185WTNOalkzY1lKN3lzZFQ4SWh4WjhDV2ZyTF83RWxOMVpvTTluZDk3RlVsdmFkOHFOTGFSekpJZVZiSktpdUNIcjZvQ21tV3dSR1hFQldnRWk1ZWpRWDQtZjkyeEJZcHRBSF9ZOE50Nm9WcEhEQ1F0S0pLOG90NU9TMEQxZ0dLeXlBamw2QUxsb1RJNEg3TGtrUDQ4Z0w3ZmVzbjJMNnljM0dHa3JwWGVXRzc4d3kwMG9vQ2w1THBZalRMdE1xN09GSlV4ZVd2OVQwemfSAdsBQVVfeXFMT1dLZDdTVk9fOVkzTmpZM2NZSjd5c2RUOEloeFo4Q1dmckxfN0VsTjFab005bmQ5N0ZVbHZhZDhxTkxhUnpKSWVWYkpLaXVDSHI2b0NtbVd3UkdYRUJXZ0VpNWVqUVg0LWY5MnhCWXB0QUhfWThOdDZvVnBIRENRdEtKSzhvdDVPUzBEMWdHS3l5QWpsNkFMbG9USTRIN0xra1A0OGdMN2Zlc24yTDZ5YzNHR2tycFhlV0c3OHd5MDBvb0NsNUxwWWpUTHRNcTdPRkpVeGVXdjlUMHpn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTFBmdVB2dkRCSi1DMXk5WXlxNUQzVklaUWNEd1dSR2s5Uy1tbW5pb2M4WC1YWjlZMFI4RmVaVGNMeHhXUThUdjVHYkp4eFlZZlNJLVptdkIxNW5vM0RFR2ZWTUJxUXZlNUptRm43QTdURXBuSG9C?oc=5</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>13-05-2026 13:47 UTC</t>
+          <t>13-05-2026 16:58 UTC</t>
         </is>
       </c>
     </row>
@@ -1705,22 +1705,22 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Screening Enzymes to Break Down Plant Waste and Produce Valuable Biofuels | Newswise</t>
+          <t>Scientists discover hidden math secret inside Chinese money plant leaves</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Newswise</t>
+          <t>ScienceDaily</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQXy1xOFhqTFRBRUMwd29OcXFYV2Fxb0FwZHU0d2NaQldtMzVzOW1vbVNsaURnY0pnNk9JQW5JYnlheGhMRktoVDVFZEhqbmU0WlNmWW81MkJlVDNUUlplVXZLSm5wc19qb0RNTk0wamppOGVvQVhQZGtDemFpOV9CWU1WLUNJYjI1cXNpYTF4dGlRdmxQeUNOS0hteEtBeWs0N09tb3ZBbmVMN0XSAasBQVVfeXFMUF8tcThYakxUQUVDMHdvTnFxWFdhcW9BcGR1NHdjWkJXbTM1czltb21TbGlEZ2NKZzZPSUFuSWJ5YXhoTEZLaFQ1RWRIam5lNFpTZllvNTJCZVQzVFJaZVV2S0pucHNfam9ETU5NMGpqaThlb0FYUGRrQ3phaTlfQllNVi1DSWIyNXFzaWExeHRpUXZsUHlDTktIbXhLQXlrNDdPbW92QW5lTDdF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE42WWlTcjVCVjZuOXBtVXhzMGYza094c0RTQ3l0V2tNTDNBQjh0QmVhZjQyTzZJbHZsVk1TS21SWUx4V0RrbVBudzhzUmM4RmVDTS0ya1BPeE42NlZvR1p3SGt4R3NOaV9LZTN0a09XOA?oc=5</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>13-05-2026 14:40 UTC</t>
+          <t>14-05-2026 07:49 UTC</t>
         </is>
       </c>
     </row>
@@ -1732,22 +1732,22 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>How Cinchona builds quinine</t>
+          <t>Plant-Based Protein Foods Market Size, Share | CAGR of 8.1%</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Nature</t>
+          <t>Market.us</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTFAzZ1lobW16RjV6bVBmaEJobDM1STVkZVhTOTRPYnRBRUZsMTZpdUJTai12aWx3QmJEeEFyZ09BZnh1RG9DbHlQc01SLVlCbTVLTWRnQVRjQThabkZBV2Fn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTFBfV1IwUEl3NUNtRWU3TUM3Q2gxT1pJbHl1X1J0a1hKcl9ZY0d6ZDc0Sk5QME1VYlh1a3NGeG1hXzBUT0NKTnhfSnBRN1VEdHBPcnp2RlI0NlN5bC1IYnZTOEVvbVhjTVdIdWc?oc=5</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>13-05-2026 09:26 UTC</t>
+          <t>14-05-2026 07:11 UTC</t>
         </is>
       </c>
     </row>
@@ -1759,22 +1759,22 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>HFCL Limited Schedules Institutional Investor Plant Visit at Hyderabad Facilities on May 18, 2026</t>
+          <t>In situ architecture of plasmodesmata in Physcomitrium patens resolved by cryo-electron tomography</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>Nature</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxPMGF3WTByR2FJeV9JamRMbUZRazB5OEhqX1JjdXpOWmZ0QjVSSHVON3dGMkFWM0xIUzNBdFNQMlQwWGNCQWZsRkNWZjZpYVdvX2Nid1p2TGtzQUkzVlVOeVRLX2cxTUhyX0ZMZmZTRVVYd3pSNmpaZ0djR1JPeFJ4OVNzcEpOckt3eGlvV2djc3k2STNIajBuTWx4R2FfWnNrRnk5YzNuWUVPZVI5ZzBpaDdOcU9nb3Q3bnVJT2ZnVFRGTnVSeFJmN0I1cVlybnJNS3k2SjlGWnhCYWZ2azdJazJXUnZ4OEpB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE9hQXdvczY4S1NJV1ZkbVV0b3Jxc1lfLWRWcTJMZ1RDczZRdzNYaUVzcjQ4Qk9vNTc4M3lNamlUbXFRQWJiVVdkTmkxR3QxSjN0SE96d1Y5YjNoSUxjZlJJ?oc=5</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>13-05-2026 14:35 UTC</t>
+          <t>14-05-2026 10:13 UTC</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>8 flowering shrubs that keep front yards looking bright even after summer blooms fade</t>
+          <t>What Indian gardeners should plant before the first rains hit</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_wFBVV95cUxQM2pTalJUZEZnRVBpMThVSlFWT21VanMzaUZONlc2LWFXZjlWTmNYTkNSY0hFQ3N1czVJYVdZRmhFdVpfTWxEQ0ZmNlNOQjFSV2tpNlpjakdtSHBQY21uMWxicFJMeDd0M1RfZnpHNkxMWEJYa20zTm15andYckhHU21nOEZ0Z0RVN2RDd0lzMndvYnl5SmtMNTFCcURRUU1yTEk0bHpBZk1mZHl5MXlBYVNHcndJQldoc2JLV1h1eTlGa21KN0FtY0t2YUk3M2JwMm9RamRxMFd2MFBSd2tJN29Pa0JjMXc0dkFxcGFJUEdVSnlfQS1kaXMxUTh1QTg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxQSVBOOF9LbVlWSWp6VGF6RTdZemhyOGZSLXNlYS14UXAxaVhWT2dzSXBET3JuMkZjRnZEYmVPWmdQME5wR1hkQjdhX1c5cXVyMGo1UXhEM1c4U003V1JlRzdhTlNoX2ludDlhMWhMcE00SnR0ZXhSd0ppNXRRZ0t1ZXpkeFFjN08wQzNfZmljZHg0eDVOcnhNOGNkdkVxS2VKR3FNcTlLSTlwWDF2TmxUWmdtdDlQd2k0RmstS1dTRFI3MGNHYmtoUlF1SDhGVEhSeWZCenM5X0o0VnNESWU00gHkAUFVX3lxTE5HRUhYNDFiYzJPODJ6Y1JPQXNVdDlILTF0SDFxN2JMYk9uXy1RYnRYeUdvT05yeWh6bDh0eHN6NXJ5SS0tMTBXNWNZZzhwZmJGOU02STFTT05Ua0RzYjlkTy1aclR3Z3BRNXktbzF1OHhKZ29xYXJValI5VjVZN24wcDh3X1BTU1VfWDRETjh0eGJ2azBMNUZCNHlfT3JFbXV0T09rMDhjT3JmWmtzZXBFTWk2UzhBMVFCQTNCa2VBS21aV3Y1cFdsMVczVWJsb19KUWtkdFZ1Q2lQcm5HdUx2TEx5Uw?oc=5</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>13-05-2026 10:53 UTC</t>
+          <t>14-05-2026 04:34 UTC</t>
         </is>
       </c>
     </row>
@@ -1813,22 +1813,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Money Plant Reveals Nature’s Hidden Algorithm</t>
+          <t>CCMB Scientists Decode Plant Defence Mechanism That Traps Viruses</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>seedworld.com</t>
+          <t>Deccan Chronicle</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE9ZNXZxLWJDTUptT1dlRmtYWk5PWjlrYlZoX0pxUHNiUGpZUWI0dXJXb1I4UWJDNlBXaHRYdW16cFJJNlhla3BsUlVZU1VwcVF4a3lOM216WlRaX3pPOVpXSTdvdG1KclE1clF4VHJmdmYyZjg3V1REeGhB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxObmZ2cjducG8tVWJHWXo1MWRIY0dodHhhbzktclVLcWwxc3Y1bzIxSlkteDd5cWRJWC1VQlRubWxfb0tPbHI5Z0EyMlRMRkZ3cFA2ekpQdTBRdFgyUVNHRjlhbW5NdVZaUGx5NU92OE5ZZC1CeklQYVhLMmp5SlpndnVyekZWb1pfR0RtTi1yUFFaTDM0U05ud1dQYzFPRVdZdHJMR3FMdl9UaUVCNTBmdjdDXzNjNlpOYTJ5dldBeDE2NlMzSE9HUl9FRdIB0AFBVV95cUxPMlFGTmhHSU5XOEx5WDFLMjB0d2dFNmVNTXJ3SzFNNVBWRmNsVlBOSXpOU0dxUXN3YjJMNmxPdk50ZlNROHpkNHo2NDBXZk96QnJqbXhRLV9RS3ZpbFMwYVFJclpjWl8wYWdOYW00aTBiY2VmVERqcHRBWEk1ZktzcFRaMzNlVGxRMkxJSU5SNGZHMUtuMHFlZVlxWDJ4VGxiTUMtQWJUMTBzRTNLOVFqMndWMjl6dzZkXzVBb1ljOFQtd1RVQU9RRV9QTktPalBo?oc=5</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>12-05-2026 20:10 UTC</t>
+          <t>13-05-2026 18:33 UTC</t>
         </is>
       </c>
     </row>
@@ -1840,22 +1840,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>‘Nature’s algorithm’ found in Chinese money plants</t>
+          <t>CCMB researchers find molecular ‘glue’ that blocks viral spread in plants</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>EurekAlert!</t>
+          <t>The Hindu</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTFByb0VDQ3RpTjhsbWxSdFdvb1Y2SHAweGEzblZoc0dIbENZR18zZWRWMFpVM0xMUTBXb0RESWJMaXpHSVAxSVMwQ1BwZkVPZ0dMS0ZvN0FHOS12VnN3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxPV0tkN1NWT185WTNOalkzY1lKN3lzZFQ4SWh4WjhDV2ZyTF83RWxOMVpvTTluZDk3RlVsdmFkOHFOTGFSekpJZVZiSktpdUNIcjZvQ21tV3dSR1hFQldnRWk1ZWpRWDQtZjkyeEJZcHRBSF9ZOE50Nm9WcEhEQ1F0S0pLOG90NU9TMEQxZ0dLeXlBamw2QUxsb1RJNEg3TGtrUDQ4Z0w3ZmVzbjJMNnljM0dHa3JwWGVXRzc4d3kwMG9vQ2w1THBZalRMdE1xN09GSlV4ZVd2OVQwemfSAdsBQVVfeXFMT1dLZDdTVk9fOVkzTmpZM2NZSjd5c2RUOEloeFo4Q1dmckxfN0VsTjFab005bmQ5N0ZVbHZhZDhxTkxhUnpKSWVWYkpLaXVDSHI2b0NtbVd3UkdYRUJXZ0VpNWVqUVg0LWY5MnhCWXB0QUhfWThOdDZvVnBIRENRdEtKSzhvdDVPUzBEMWdHS3l5QWpsNkFMbG9USTRIN0xra1A0OGdMN2Zlc24yTDZ5YzNHR2tycFhlV0c3OHd5MDBvb0NsNUxwWWpUTHRNcTdPRkpVeGVXdjlUMHpn?oc=5</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>12-05-2026 18:42 UTC</t>
+          <t>13-05-2026 13:47 UTC</t>
         </is>
       </c>
     </row>
@@ -1867,22 +1867,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Plant A Billion Trees (PABT) Leading a Collective Movement to Restore India's Green Cover</t>
+          <t>Bayer Crop Science Reports 17.9% EBITDA Growth in Q1 2026 as Soybean Seed and Traits Sales Double</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>iGrow News</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAJBVV95cUxQdmdkZ1JBb2FxMXZlUHZKMHkwZFBxR0Z5Vkg1ZTZtQjBoYTdTMXo3UEtXbFlubHF5SzFzbmN5UGp0WUZYd3k3Zlhqb2VJWnkwRENtaGF1VTJ2Q25ub0l2SXNsR1JrQXFiczBDNkdjU3Q0ZzFPdHhmZGoyaG40XzY3ZDVtRXZkNUkzUWd2eGJlQlByalRuWU42Q01aOVlud0U4TUhuRFNjajAtYlFDSXJUcW5RTlNIMGZQX0I0Rl90Zk1kcW01UVVobXAxenlnRFo0ZkpCSHF1d1dpY1lpTVpNdklXemVEU254Q0xiRzgtdWFoU2p0aEo0bmJuUUpPTXZQYktqWGUwVTNSc0c40gGMAkFVX3lxTFB2Z2RnUkFvYXExdmVQdkoweTBkUHFHRnlWSDVlNm1CMGhhN1MxejdQS1dsWW5scXlLMXNuY3lQanRZRlh3eTdmWGpvZUlaeTBEQ21oYXVVMnZDbm5vSXZJc2xHUmtBcWJzMEM2R2NTdDRnMU90eGZkajJobjRfNjdkNW1FdmQ1STNRZ3Z4YmVCUHJqVG5ZTjZDTVo5WW53RThNSG5EU2NqMC1iUUNJclRxblFOU0gwZlBfQjRGX3RmTWRxbTVRVWhtcDF6eWdEWjRmSkJIcXV3V2ljWWlNWk12SVd6ZURTbnhDTGJHOC11YWhTanRoSjRuYm5RSk9NdlBiS2pYZTBVM1JzRzg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFA0WVo5R3lhbW1qajlTdkVUc1Y4cFRxWlNOWGZ0N2xMWWJ2ajRUUnlXWG1qSmRyaVg4dUNYNGk1ZTVNVEthRUtESlFXQ2dXZ2VKSVRuaFdhWmZMUQ?oc=5</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>13-05-2026 11:05 UTC</t>
+          <t>14-05-2026 09:29 UTC</t>
         </is>
       </c>
     </row>
@@ -1894,22 +1894,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CCMB scientists decode plant proteins that trap viruses in sticky droplets</t>
+          <t>Let The Garden Season Begin! And Let's Avoid These Invasive Plants</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Hyderabad Mail</t>
+          <t>The Owen Sound Current</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNWjlNSHhwTkRnc1BwUm1JbzZXNWY1VUNoMVQ3NGtsOHhMNHh4ZU1FQXpnSlhaQ3pJWXJDd2ZvZE5DYl8tWWphclNaVUMyZTRwZnRibEIxUTZMQkM0MkJEODBZNDYtVG1BV2ExZWU5cGpONHEwR1NyTXdMbDhDanVPb3I3SlF2dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTFBhYzBac1hRc1AzeUNvcjN1bzhqLXExMEJxaWluaFA1SllBbk41cDAxWWx4b1RwUFNxZnNtRG1LdlN6MkF2ZHhpM0FBXzlBNVU2S3hROTUzRXR5WUNqRktMdzRweU5sZlN2WU0zY3RJbGhXZThDYVpaelZWSQ?oc=5</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>13-05-2026 06:15 UTC</t>
+          <t>14-05-2026 08:22 UTC</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>6 Flower Trends That Will Be in Full Bloom This Summer, According to Pro Gardeners</t>
+          <t>CCMB scientists in Hyderabad discover plant protein that may aid dementia, cancer treatment</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AOL.com</t>
+          <t>The New Indian Express</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE5VdjJxSjhBZ2ljWFlYZzhaTkR3VGJaajBIeDRMVGgyWHQ4Z0k0bkZqc1EtVTdDakZaRkp4X0pBMzU0YW01TkRfei1sY0JIcDJ1cDFhbHNrS3FhVmxKa0dwZ1pXRnBGb2s3R2o5SzhZRTdlTThxc1hJbXlR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxNU2ZJTDBmUk53MWJIckE3aVl1bXhBbExVcW5XU1g0bmtCODdHTE83ZlY0dmVqZHdXM0FSbjYzSDhWSW5yX0RkV3Vldmt2Y1pxODg0Tnd6RjBXcUtaOGZleHZXSW9CRU4zdzZZMDNSSUhoXzQ4REc0SWk5TE9MTU40bDdXbThwUTZRdmtNZ2VhcHR6QVpkRTlVaXJmZF9jSDdFbFVWc2NZOTJlMHUwa29ZckM3UXRxY0Y0TmstY184ckR0eXdUN2NhMGpxMW1sNk1qbXY1Z0plN3RVREhZWFhaZm5KazJLQ2_SAfQBQVVfeXFMTXBFdF9EUy1wRzJYZk5wYzdYRmVvSUVrdmI5dFBGOWs3VncwRlZYa0c1dG1MN0JRbDBvSHdLYnlYNHp3NTk5Qm5MZXJieElsSXdfUFVyUG1JWE4wYjByZlU0c0VXQkJWNkMwTG1ZSXBrUTRXMkxiZ2sxLXVMbi1TM1prUUw4UnZQcFVWT01sVFNqM2h5Y0lCSW5QRXFRYWEtaDdtMXRVbFdOWUczbGxUZHBNZmxwTWNNNF9tOTZadEdReHA3Uk1FdlV4THhKMGs2STNPVnp2eEZOM3BFQ3BlUjFUT1VPZkRDcWJsOURYbkprT2RVRQ?oc=5</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>13-05-2026 14:22 UTC</t>
+          <t>14-05-2026 03:22 UTC</t>
         </is>
       </c>
     </row>
@@ -1948,22 +1948,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Key anti-virus defence system in plants explored by CCMB researchers</t>
+          <t>As meat prices skyrocket, Tesco shoppers find plant-based mince now 29% cheaper than beef</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>The Hans India</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQSnBQUDRhV1VJR3ZPVldDVk02XzBiNXMyR1k0RThraTZtN25SWDBZV19ieWNnNnhzQVQ2YXd5TEVXYmhHdzBiNEx5TjltQkFzQjVXYklaRnVULVRPalp0ai1pQnRpMW1yTXRkWnZrMV9valM4bUFOMkJZdWxlX25CM1BPZDVPWXBkbjN6NVlsMjFyLTBSLUs5MWFPNjVsMkdJeHh4RTN5RXRiWTdHODRIeWJwWno2cVB1bWJGZW9fTVpnZzFKckHSAcsBQVVfeXFMUE5Xd1pINEFERDRid3dVUmxELTFIbG9raW00XzRpY1NURkw1UDRWZFRCaG9wei1ON3Zzd2ZXbk9IWUp2WkNtQkxLUkxMdWRpU0hCRkhxTHI4TXpjR3NZTFlLR3lUTE1xR1RqLVQzblMxWjdySUNLMGE5WlhnX2sxR2txQTN1WXhwQVcwSWhzeUE2ckx4RkZSeXkyYWVRXzlyU3dWX09uSXMxVU5Pd2F5WXVqM0RyWVRsUmRncGFHOXkyNXg5U0J5cERZY2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOZDJpVEJRYWJnSDlGeDVBZVZiWGVhbjAtbURDTEhmdGV4dnM0VkVWQkQ1R2QtYTVrUDdTSzNzVXZrT05uTFREQ21oNDI2NjlyUGMtX3Z3SFl5M1doS25SWWNPOFBWSG1mSVZ3LVVtUFFrOGRpZ3h2VDU1T2lxQTdMZG53aXJxTjdDRG94QlZiclZYR3R1eWZRcExEUHRmeVpfaFJZ?oc=5</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>13-05-2026 12:55 UTC</t>
+          <t>14-05-2026 00:00 UTC</t>
         </is>
       </c>
     </row>
@@ -1975,22 +1975,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>The deep roots and fragile future of biodiversity</t>
+          <t>NTPC Engineering Executive Trainee Recruitment 2026 (Through GATE), Notification Out for 52 Posts</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Knowable Magazine</t>
+          <t>Career Power</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQaUJfQnhLT0o2Z0pOSnBNNlNsT3ZoUVVTLWMyUEN4eGhiUzR6dktFZThUMnZqV1R3UFNhb1NueXNYaTgyalV2SFIxcldnNF9NWDBrT2tjTjN2WkxVU25jWm1SUWxWUkdlYkFHWVJ5cTRGVWN3R0tod0dhUW5oS19heE5xODQwMDBlb1ZQazJ0N3lKLUM5M2ViQnhTUlF5QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE1scjk5ZFB4bVpYZzF5a0ZvQ3R6UmNFaHpEbmpaTDNybGlCMkxkNFRFQXN0eUxDYkhXMnprOTFMNmd3ZFExUm9rVkxFVDhuc3VGRms4czh3a3lnMzV5TFZEVzE5V01XZUt3aDNfd2RjQVpqdG1PUDJ2SHZDaw?oc=5</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>12-05-2026 23:56 UTC</t>
+          <t>14-05-2026 06:20 UTC</t>
         </is>
       </c>
     </row>
@@ -2002,76 +2002,76 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>10 plants that will bring a calming Japanese-inspired look to your garden, from irises to Fatsia japonica</t>
+          <t>VW, Rafael near deal for iron dome production in Germany, report says</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>House Beautiful</t>
+          <t>Automotive News</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNOUZHZ2RxNFVqemVFSUNiN1BvZmtCODNXbEdUYkdqdW4wSzl2NEtvNVBjUzc5aUw2TlBRWDFnTmpoeDJqWFdJb2VrSTZwdHEtZnY1VGVMNEtsUHhhdlBUUUpWQk1pSWRQM1FwUVZERWtZVUZ3Q3pRSC1ISHZhT1ZGdFloaGNMNG9ieUNiMExQaU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPbGQ4Nlh4T1BoOUhHOFYtMkYzcVFxQjJJLV9iUmNMVndBalJXcEMweEdwbjNIZVVCcjN5bGRJSFlTcDR6eHRGRkQxWHdwWnNiakczYXdNWmM2QWt0Wl9tNDByWENpeWM4YVRZelQzWUFYWS1ka29yQ1RELUp6Tkt2eFV5cDU4TTFpRkE?oc=5</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>13-05-2026 06:07 UTC</t>
+          <t>14-05-2026 08:40 UTC</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Coherus Biosciences</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Coherus Biosciences Signals Confident Oncology Earnings Outlook</t>
+          <t>Cold Weather and Pests Are Impacting Strawberries, Orchards and Vegetable Crops</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>Lancaster Farming</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQMHFFVGJCVXE4cVdNSkpkWWdLODRwblZmc25VMmxRUTBSaE0xZ1dTaU4za0FETnI3NHQzeGg1cTd4WTdQV2NWUFJGVTY1V2tsUDlkX3NOM3kyekc4eTIta0xYVHhTakd4dmRIZ2RjVkNFWlB0LTRTbjFpR1JEbjZxT0dRRVpERHBGM19UU3hSMS03Y0RmbGxiaE0yYU9SVlR4Z3JZRjNrWUNpN3NWdEF5NjlvM0p0QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwJBVV95cUxQNFZWOFNuZVBnWHBrUWFkbXhSQVhNel9ua0ozNUNKakh4TDZ3eTBpM3BJUmczRXhvaVhYSmlFenQ1RlVOeUlBYkV4QzBXaTZpTzVyYkNPOTVtcjZBdWxiamhkZFJqV0NzaVREY2Z6VTFxSzFIV201WDNLbjdzUHFySzBrbTNqZzJQbUZkTXJ1cUZoN3RBMFFPaElUZE5UVmhBS2g3OHpTUG95TTBxXzFTTkhzcUM2SHBvN2xDUDMzQldLMGNVRHBoSHJ2YXVVY0xOaDQxUzBHckVyMkwyaGRBSGlteVJmYXdwWHIzVG9aaDYwTTdiQlJIbDlYZ2FNLXVZcnhCQUlMU3htR0NodjRR?oc=5</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>13-05-2026 00:19 UTC</t>
+          <t>14-05-2026 10:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>EC approves added indication for Pfizer’s Hympavzi</t>
+          <t>HFCL Limited Schedules Institutional Investor Plant Visit at Hyderabad Facilities on May 18, 2026</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>The Pharma Letter</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOWVdYS3laT01nMm5Fal81LXRaUHA2YUFOdFFSVFFVUUdiSHFpV0FBbWlWcnVQVWhnWkpnZEpoUE5LOGQ0U1RFSW44ekwwdDRDT2RKVElPYmRyOUhGV3lJcUFZemYzRDJVTUVNajY1anhWMy15WVVXUWpBenI3OVNMdXlOOXBXVHJWU05USURENU93c3puWlgwZUNGRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxPMGF3WTByR2FJeV9JamRMbUZRazB5OEhqX1JjdXpOWmZ0QjVSSHVON3dGMkFWM0xIUzNBdFNQMlQwWGNCQWZsRkNWZjZpYVdvX2Nid1p2TGtzQUkzVlVOeVRLX2cxTUhyX0ZMZmZTRVVYd3pSNmpaZ0djR1JPeFJ4OVNzcEpOckt3eGlvV2djc3k2STNIajBuTWx4R2FfWnNrRnk5YzNuWUVPZVI5ZzBpaDdOcU9nb3Q3bnVJT2ZnVFRGTnVSeFJmN0I1cVlybnJNS3k2SjlGWnhCYWZ2azdJazJXUnZ4OEpB?oc=5</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>13-05-2026 15:00 UTC</t>
+          <t>13-05-2026 14:35 UTC</t>
         </is>
       </c>
     </row>
@@ -2083,22 +2083,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Can Pfizer Achieve High Single-Digit Revenue CAGR From 2029?</t>
+          <t>Pfizer receives EC approval for Hympavzi to treat haemophilia</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>Pharmaceutical Technology</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxQVUxfRlhnNVdjcWkxeEZnUVl3aG81ZEE3R2NtNVR5X1BDLTZfNkowOFdjZnU1dkZ5cWY5Z1dKWnlnTk5ybDJ3X0E0Q0taaWEzSDI0amMwU09JSFJ5OGtaX3lEVWFWSFd0T1A2ZjY0MjBBWW1lZGgweWNLNUwyeXp5SFNPck0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOaVQwNGItRUpuZEJpZHhVMjVPR0NrMHRvQUVwa0hjYURXbjZzcGlaS3FheDZ6QlJfOGh1THJjX0dFbXJUcEFIUG90QXFtRHVQeURGQS12RU1CdTlqQ19adTBKNWdLVGM5ckFOa21yNUdXWThvZGwxdlVnaWFqVDhNa3hybVhfZnJJUi1CUQ?oc=5</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>13-05-2026 15:36 UTC</t>
+          <t>14-05-2026 08:51 UTC</t>
         </is>
       </c>
     </row>
@@ -2110,22 +2110,22 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Pfizer India Reports 6.3% Revenue Growth in Q4; Board Declares ₹75 Dividend</t>
+          <t>Pfizer Research Grant for Non-Hemophilic Bleeding Disorders</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Trade Brains</t>
+          <t>fundsforNGOs</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQODhUaGc0LXMzbVlYcTg3X2FuY0d2SUdEX0NrMV9BZUFtYVIxelRGR243U21FaGd4ZWU1UHhUSXQzOXVnREoxRHE3ek5XWTRuYXA2T0g3X0NtWDBZRVpvbnJsRl9POFpvaDVnLWl3b2xmZGtSWjBzZUpyMS05T3NLaXVIdmFzMExNb3NPMjJnQm9faEN2ek5RNF91QWs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNMDlDaGpZMGEwQUJBdEJTc1VENkVVa0tmZUpkSDYxUnJkRVNXVmRUY05tR2VRTjlXMlktNUZUZU1IeS05LVdxM09BQjFRMDNrYWxjdjBfcGNXS0VXaHQ1RUhZN1BnS0N5X3lyeTBzdjltN0FCeDFKZXFLck9RSS1PQWxPOFZIODlQTURSeVVvbzVrTmhiTG5KMVJiNWpnZ19pSlR6WEFhU0_SAagBQVVfeXFMTTA5Q2hqWTBhMEFCQXRCU3NVRDZFVWtLZmVKZEg2MVJyZEVTV1ZkVGNObUdlUU45VzJZLTVGVGVNSHktOS1XcTNPQUIxUTAza2FsY3YwX3BjV0tFV2h0NUVIWTdQZ0tDeV95cnkwc3Y5bTdBQngxSmVxS3JPUUktT0FsTzhWSDg5UE1EUnlVb281a05oYkxuSjFSYjVqZ2dfaUpUelhBYVNP?oc=5</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>13-05-2026 11:05 UTC</t>
+          <t>14-05-2026 05:29 UTC</t>
         </is>
       </c>
     </row>
@@ -2137,22 +2137,22 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>European Commission Approves Pfizer’S Hympavzi For The Treatment Of Adults And Adolescents With Hemophilia A Or B With Inhibitors</t>
+          <t>Pfizer’s Hympavzi Indication Expanded in EU for Treatment of Hemophilia A or B With Inhibitors</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>Contract Pharma</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAJBVV95cUxNdVpNdlA2azFlSVZGWERqX1JDT2FCN19rZ2pBRDh0ZnFzSzAtSHVVbTFGaVBWRnZja1kzT2hMT3hkREJLWFdBV0VmUkVqUDNPSEhvbDJKTV9hUlZkZWgzcjczTml4c3hmWWJJVk55MFlMSVhrRi1WQUFQaHRUSGF6SDlCNEtKLV91YVJhQkZybWhaWkhZOVNaVTliM3NSQTBVRXREMzIwTnBCS3hoQnFZY3VjT1ZQeWlVakxGbzJ1c1lVQ3lZaGZ3SVRNUDJtQ0ZDeUl6THB4aGp5NGgwNUVzcGlZOHlfS3RUbnZNREp2b0xzWUl2ekpZbnRObE5kZTltRWJobkZqSUd0Nkg4Q0ZXN3IzYWdVQnctZGQ5OVZZa0dzbHRi?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxPUXRvOXZMVlcxRl9EdTBFX2JJRi1vU2t1T0tFTTBYTjNVZEVtVWltNXBZZWJHUnZzTlBSOXNfMTVXbGQyZTRPZFF3LVh5V2lxMTdqa28yb2dHdjc4Wkh1SWlId2JSbW5fUUZ6LUVhOEdYNUM4UHdEcmhHc2w4b3VSU0psV3dobGVtWHNvY3BjbmVSNWtsY29jWFZuLVRycU01QXJWWkEzX1Z5YnJ4eHhzYWs4RTBCWUhCaS16Wm1vY1N6VzFBZC1wQlJONm04NHRuNHhSQXpB?oc=5</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>13-05-2026 10:46 UTC</t>
+          <t>13-05-2026 19:26 UTC</t>
         </is>
       </c>
     </row>
@@ -2164,22 +2164,22 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>European Commission Approves Pfizer’s HYMPAVZI for the Treatment of Adults and Adolescents with Hemophilia A or B With Inhibitors</t>
+          <t>From oncology to obesity, Pfizer bets big on India for its next growth wave</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Business Wire</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwJBVV95cUxQbno1THBMdlFTWVdJY0JMUWdNdTloRHplWEtqYmlrR3RUNU9RMFY5a3dUZ0tQb3poenZzcDBqaU9fS1IwdmxZek8xM0xpU3VObks4ZnhMUkhmTWJGYjlJa2x2Ti1iT0ttdWdFQkwzVzZOWERsMVdNT1BSSC1mS1FFZDlxNVBNQ2FjaC1Ma3VpeDdYUWxtYTAxMl9Gc1NMMGVDemJ2VTJrWUo1b0h1c3dMSU1pYXhId2R2VFpTa2g4UUpCa0ZxUDlfaFJvTklvVUQyTWZ5VFFYNG5qVXZqWXBERVNlaUduNEwxY2ZITU9kcm1WWUpFajRhTFVQb1V1aW1pQkt4dnhLNW9tRlhOWmFtQmlnQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxPc2ZfWjJ6bk5QajVUdnlTUXBXM1VkaVlmNG5nYUh0UTl1VC1XUlpReTQ5UEFfX2tzckRpWTlsNGhwQU05allXcHJ5TGc0bWcybk1HTk9XRWxjY3NFZUpJblZkeXpJYkQxQ0V3ZXhGQ0ZaQ3o1b0tpNEhGRmwxYWpQek81d2ZiVFU3WlIwNFhNU1p4U2ZPMTFDU2Y2ZVY2aGRLdExmMjhGSkl2RXhDSTBDWmJtbC1PdUxwN1pPMnE4ZEE4WEJBcmxZa21RdFdZRUFXNU05bFRXbEFIM3UyQjJEdUtGaDhvbVJ4NzBpNjBEYjdteEZ6QmxJZVRLS3JBYVRmcHfSAYcCQVVfeXFMTW1TR29qc3JXSS1QaXFFMnlQY0k4ZUg4Y1d1Ri1ueHUxRjhCYXlDNlpDUnI2MUlZSkxyWFA3ZlhUWnd2bzJrUHpubHlFVUJ2SXZEWWlGaVdpd0VUTzVvRWJ1OXY4QjctRWs1bGROcE5TWVhTYUtkM19idF9WLVVDT3JvSkpBSk5yampPWTFaV2hMZlpHSUNOaEpuaTNPbExxekJFcktZUml6c1VaZFVDVDQ5UmRtTjV2eEVUa21JYXNTWndTOEExank1c2k2T2tkVFg3a2ZnLUsxaENXa1lTMEJLd1VZVl9td3JiYUlrMVpGZWNUZ3pWTGlEUzRmMTVzZEYwaHF6UFU?oc=5</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>13-05-2026 10:45 UTC</t>
+          <t>13-05-2026 19:16 UTC</t>
         </is>
       </c>
     </row>
@@ -2191,22 +2191,22 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Pfizer stock (US7170811035): Q1 earnings beat estimates with $14.5B revenue</t>
+          <t>Should you buy pharma stocks? Dr Reddy's, Pfizer - Target prices after Q4 results</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>Business Today</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQNjZYTFU5clo5NVRrTVVHczJRQmw3SGt5aTV5cWxlSVNUdkowV3lnaGJDRnhxQnFvM3UwTWFPQWotS1A4YnJMYkN5ZzhldDRSVjd1bVg0a013RFBNUS1IUnNyeHdVNzZUbXJFczliSVoxMXZ3U3J4U3F5SHowUGVoUWhJdHhwWUhqSl9xYlNLbHpnWkVOaFczT3NleGxXYXl3OE84WmExMk9wWXVZVm1VamVkVXlucXFTaXA1MzRVNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxPaElkLVkydUJzeEV5Q3Atb25qbUVJQXJBU0lKYTlCS3ByQUd2LVcwSVo5QkJreVZOaUp0eHFZY2pNUkZlWXZBZVU3cnk1b0huZU96NXZxamFkSk5zbUtxZGpsN05YOVNKV3k5ZnRFZENXOXVNM3NPSFotbC1jeHp3WWp6Y19QdV9YMkZQbHhxMGFWSDllb21IQncwWVBYTkNRdlZwWEduam5ibUhQY1JLQlJybDZnSktkNXBOWWpLeGFPaUx1ME02aDBoeWJUd3Y4X1l30gHYAUFVX3lxTFBRZXBmMF9WdGdVRm1MbFlFY29sbzQ5TzFBM2NNS09uUGVBUXhGbi1qSkdXRUl0dWxRT253d3pMT1BoZTMxekRmaDJXa2FXTFZJUE9tV2JVNDJlNXFpcmpyNTZXd2l4RU5NZkhCQzJwRFl5MUZkRmNFYVpMVTNiZjJ5Zm1HQ3locmtYOGZxSldFak9KRElTLTBnWVpqM2xvVnhmTXFZTG81MUxqSFNJWXlkR01wS1ppeS1LYWFKdENWdnN2YmljLUVNdkdNN0JnNFFiTEEwazRZcg?oc=5</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>13-05-2026 15:30 UTC</t>
+          <t>14-05-2026 03:06 UTC</t>
         </is>
       </c>
     </row>
@@ -2218,22 +2218,22 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Can Pfizer Achieve High Single-Digit Revenue CAGR From 2029?</t>
+          <t>European Commission Approves Pfizer’s HYMPAVZI for the Treatment of Adults and Adolescents with Hemophilia A or B With Inhibitors</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Zacks Investment Research</t>
+          <t>BioSpace</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxOSDhZR3p3NFoySzc5ZUJLaDRmQ3ZIYWs5WnZac3dNaHNQSk53T2VuYXAtdWJkQnkzdldwaHFKQXlOU3hBSGN6ekF5VWZ0YUhhS3EteVlNNlRpSUxOQ2FCZ2tmVjh5X3lhWDF3TEhDNFcxRWc1R0xsclRGZE4wUHlFWWdFUHZldFVuVGM2dnVTTkY4UDVFSkNiYk5xajJja0J4b25FYUpMdktlUXlNMG9Xb2RHR1l2dGh4YktUbVQ0QkZoY0pUSjh2U3ItMUhEdGRaUEZlX3A0a2hyVVgxTnNuSkpZTGhtX25OeGdUcU1ScGU3LXZ2dlBvZjlmbEZGR3FQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_AFBVV95cUxQcGFBUEY5S2dqRWszckNWcXFld201QVhNenRCdzBzUDAzN3pnN3Eza3lpQVJEUGNlVm9UZy1VaW9JbXhjRWNvYmJkOTc2Q1M2OTRqTE02RHFPQklGQ2lITFFyYnc5LVEwWUVSRDVXZXI2UXZ5Z3JjTzRsRlFVNGtZaUNXWG5JR2dIYzkydDJGNURVbHA1NENKZ1RUZEpFd0plMkhDQkR5c25kT1d6MDJEWVhoNGF4MzNoWG9SY0JmcDJ6SDZiVVNrOUs5cDNwalpGZVhFNzRzbEdlVFJrdWl3bGVxQjBQM1JMTHJva1Q4S2MwcGZCUHN5eWlYbnQ?oc=5</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>13-05-2026 15:44 UTC</t>
+          <t>14-05-2026 01:58 UTC</t>
         </is>
       </c>
     </row>
@@ -2245,22 +2245,22 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Pfizer FY26 Revenue Rises; Declares Rs 75 Dividend</t>
+          <t>The Zacks Analyst Blog Meta, Pfizer, Salesforce and Smith-Midland</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>Yahoo Finance Singapore</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxNb2tqS0xXcV94V0pXeUNiZWVxSk96SFpYRnRMTWJkSE90ZTNFcWVFbUJESUE3VHFBTXc1TElnbnBXbTFtSkk1WUQyaWRpSllYVGphd05IV2drSTdOZUYzV0NFX2U1WHYtSngtNGNwUnFfUVQ1SElheXhPbWJvM1lFVDlPVGVfNDJERTczMU8wajdyMGZ5bllhWERqS25rMWc5R0RJTGVyTHhFS2tYOVRpcWhEVGVlMmpmUlhfUlBKRF9ETVJqRGdfbENhNHJBVEpLbWw4cnRia3BGemNkdlhDc1ExYWJDbTc4cHRtME9YaGZWUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOVGVya3BJVUxmb3hmN3ZVajdqVUxzSmZCMGh0eE9uQkxPdmxGQVdTQWdWUHpCa0Rvd3VaZjBENGJRUUZxMHJsQlZkRVU0VDV0b2oxR3dJTEJ2LWpsUGFqbUdGd29YSXpuWkJPQUJNU2ZfMzZockZERDh2bkx6QzZIRXhZT0owdw?oc=5</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>12-05-2026 22:19 UTC</t>
+          <t>14-05-2026 09:18 UTC</t>
         </is>
       </c>
     </row>
@@ -2272,22 +2272,22 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>European Commission approves Pfizer's Hympavzi for the treatment of adults and adolescents with hemophilia A or B with inhibitors</t>
+          <t>Rigel Pharmaceuticals Enters an Exclusive Global Licensing Agreement with Arvinas and Pfizer for Veppanu | PharmExec</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>marketscreener.com</t>
+          <t>Pharmaceutical Executive</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxPNVFFQlBOUF9NX3lXQ2ZRZ0w2X1ZUMFo0VkRVX21IdWZvRGlYbXJmQjFHbWctOHlRRGhYdlJ3NlFQNW1GUWNFTWZBQWhab25GOWZMMVBHLUk5Qk9zT1EzakdQY3ZfM0lCSWYxMHkzZU9vaks2QndYR1JENWpCWVczbXZ5Y1VUNWxGRm9Ua3BYRjRfSUJTQWpkMW5YWGs4akRUNkJvVWZ6bmV1SHpxN3RBbjM2cDdUUlhVS3JNcHVpV3V5RVo1c1pteG1Ybl9SazRHd3VLRERGTmNyNEd4dDJzSzhPeTd0d3N4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPdXpwSEt0WGNHSXBrV3VtLXNWbEFIZl9kRzh1ZnJtc0JPS1A1TEw4NVhmbDZwaHBucDFlNkxlbWZqWWdyZ0tPYzVPZEstMHJSLUZ2YWFxSGFQUG9QMDd5VjFYc1lKUUNncXo1aUE2eGFzTlVXTnIwM3p1NG9CMlAyNzlsR1I1am9HUmpYeGNIeGp2M1h5amh2NU5tdV85V19NUzRpVkx0SS1lYWZLRXc?oc=5</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>13-05-2026 11:44 UTC</t>
+          <t>13-05-2026 18:47 UTC</t>
         </is>
       </c>
     </row>
@@ -2299,22 +2299,22 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Pfizer Ltd. Share: Profit Gira, Par Dividend Bada? Investors Chinta Mein</t>
+          <t>Pfizer Hemophilia Drug Win In Europe Adds Weight To Undervalued Thesis</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Whalesbook</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxOampEN25TWndVT2FYMm9GckcyRzFDMEhDVW12MHZYTXBfbGhidTJ6cjdFWWZDR2JVSU1CZXh6amE4ejhLZ2FPODFPaFZuV2tUaHpaSnEzckFhRll1UWxxX1VQSy00aGZ5RTY3RTQwU0tBSFM0eWtnSTBpX2FiS2M1T3BNenZWYmM0aHNiMkpCYzkzTW5pMEgtNUV1VnJWUzN0em1lNjFBV0R1OWdZQXV0Q01rc1FkQ1Y3YjhnQ3kxdHpNM0tmWndPNDZ1Qkt6VE82NFpTVmF0bHZ1UW8yOE9WSFFndw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNQ1pHNEJUenZmWkdoYlpfN3VXdW94d2hTS184eV9lTDQ4QXZkbTZzcFRRQnVOOHdJYjVkXzhjSjhwbGpBMjI4YWNELThZaWZYZnpWQTUzNjk1N09JdlRRR2ZKa1d3eFVqWFJOM181bmRJUVFvcUhWR0NkeHVxSjBaMkpxV0czdDFpcW9QUkNVRmwwMmdRTzM3U2RkN3F4Rjk4aU1jUk9YbThuaERoLWRhQkxnVDJNS0w5U3RmZ05vT0s5dy1ILXpsSkU1U05DN2ZadW5F0gHYAUFVX3lxTE5YTkg1OEZfQ1p3NW9UckVoVnAwUFhxdGtTNUEwRHFfS05Zd2FmREZwcGU5enV1ZjZQekxNOEtYNTlQR3ZpQzFMREFhaG85V3RUX01nMmpxQ0xCZWdQUkx4dFo1YWIwbDlaVGNUalM0R1MxOEdMTXh2dWtjRnF1RTk5dDRzazhoWVItS19lSEpRQVZFcTdzMWZPSUxJY042NWJ3RGZHWTRYbGM5MXFHOWoyS3NDSnVJTGVWYXJJaGlrUWFfd2ZfdldzTGtQRHZWcWtSZXVfSEFqdg?oc=5</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>13-05-2026 03:32 UTC</t>
+          <t>14-05-2026 02:06 UTC</t>
         </is>
       </c>
     </row>
@@ -2326,22 +2326,22 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Pfizer PROTAC Licensing Deal With Rigel Adds Royalties To Valuation Story</t>
+          <t>EC approves added indication for Pfizer’s Hympavzi</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>simplywall.st</t>
+          <t>The Pharma Letter</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQelpsYWlfSU9MSUVGZjlkNDBlYWV2dGJJaXJPRnlaMjV3cGh2SEV3ZlVGUk1uMlJOQ3ZLUUlPUkIyWUZtYjZjeEhXZ2Q0eVpkanNOaktKdjZabnczX1FVMGt1UmVmai1zek1Hd0o2UEFxZzBUN1UzaFlJTkRjc3RpXzU2cG1NdGZEbGE3TDV5WnBjM1ZVRWFoQWxhN1RrdEVkYkp6Mk91Rmd4eFo3NVRPR05mRHZuX1M2SUI1Q1J1MG10VzNTZkhlS2dBU2lOWHpfVmUw0gHYAUFVX3lxTE1CLTdFcThDZ2g5b0VxdHpLbTFqeFNkeUhPcVRsbC14RTVSckVNb0FoN0JyVG9vcW11TnFWbFR1UnFVMnRWMU00Sk5uZzN4S094b2hfQkg3VGItNktPaHpnb0N2TjFaQU9jTlZ3c2wtTmw2cVZvUTlWU2Q4M0hiMG9vMWQ4eDBPQm9GWEVqaW1xRTZhemxJLXYzQkJ1cnh1OGlBT2o2YU1EdElEQWtaTUE4UTNKRW1wc0JlTjJWQk5WZW5QVUN0dUlHMDNHTk5fZlFnaTdfWVQ3aw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOWVdYS3laT01nMm5Fal81LXRaUHA2YUFOdFFSVFFVUUdiSHFpV0FBbWlWcnVQVWhnWkpnZEpoUE5LOGQ0U1RFSW44ekwwdDRDT2RKVElPYmRyOUhGV3lJcUFZemYzRDJVTUVNajY1anhWMy15WVVXUWpBenI3OVNMdXlOOXBXVHJWU05USURENU93c3puWlgwZUNGRQ?oc=5</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>13-05-2026 01:05 UTC</t>
+          <t>13-05-2026 15:06 UTC</t>
         </is>
       </c>
     </row>
@@ -2353,22 +2353,22 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Pfizer standalone net profit declines 39.62% in the March 2026 quarter</t>
+          <t>Valneva Q1 Earnings Call Highlights</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxOSUxaMnREeGtVYkhkLVNyYi05RU1MSkk5a1FEb290OW1abHc4MS1JUWNaX0Q3OV9zdC1hWnd1RHliaVRkVGxSSVBEaTJ6WnF0LVhYMWdPM3R3MVh4QjJWMGprempONkdrZEREUmt1MTZFdndBZTg3Tl9taEZteVduRlFoWkNTRHo4T2FWUVVwbHN2ZkNOc015elhMV05Vdm5XVk80VFZKdDVyc0s4cjlwTlVlX09yNTlXU1hMUjYyekx1RHZObHl5VENDTkszS0lQcUhRbjcwQWZGdUt3cDJFb2JHNEdiWklLQ2o40gHrAUFVX3lxTE5JTFoydER4a1ViSGQtU3JiLTlFTUxKSTlrUURvb3Q5bVpsdzgxLUlRY1pfRDc5X3N0LWFad3VEeWJpVGRUbFJJUERpMnpacXQtWFgxZ08zdHcxWHhCMlYwamt6ak42R2tkRERSa3UxNkV2d0FlODdOX21oRm15V25GUWhaQ1NEejhPYVZRVXBsc3ZmQ05zTXl6WExXTlV2bldWTzRUVkp0NXJzSzhyOXBOVWVfT3I1OVdTWExSNjJ6THVEdk5seXlUQ0NOSzNLSVBxSFFuNzBBZkZ1S3dwMkVvYkc0R2JaSUtDajg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQMDlOVzFieHc1WVhfVjZHNUVldHVQYWpVc0pZZngtdXZLVEtuTEdURmFKTGowUjQ1RE82NTJzdmQ4R0hCdks0ZUpWU1VpLXEydXlKZTNXWS00bkViWjZWRjhoblg3ZWJURHpfenpJSW9lZ0YyM1ZXU0hjckVNcWEyeUJZM3A5b1RISWVLLVJlSjdBaGVvdGpQRThmZS0?oc=5</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>13-05-2026 03:40 UTC</t>
+          <t>13-05-2026 19:10 UTC</t>
         </is>
       </c>
     </row>
@@ -2380,22 +2380,22 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Pfizer Shifts VEPPANU Rights To Rigel As Valuation Gap Persists</t>
+          <t>What sets apart MNC pharma companies from their Indian counterparts</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>Moneycontrol.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQeWtIazV0T3Njb05oU0pOUmEyODRtTXZRS0puUDR6M3pva1FMbF9xNFo0ZFNXM203amJSVktuSmhORmJVbFgtSjkyM3NtWVZDeTJobzhSZ1JKQTRaZk9GUzVnNTlwbHdyN2FKRTRMb2kycnpUOFRDUXVuemlJYzRUTHpmMDhBWk0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPMGRCZTFFSFpLNldXS0lDcHdQQmNUQ2otSTRibFNPRUZheHRwZTBuVFpkd0ZyZlNVS0Q1bjRTcGZkY3M1VDdIeHdnNHZRODdORUh2Z3o0aUNjOHR6ZVc4MEFSLXA5TXVncW9sTktLZFRkX2xQWGVDeFczWGozenEwVHpzZU1VSWRETkw2WkpGaG84NHRLeENEVDZENFVVbWUwOW1LZVY2RGo0OEgzbjF2b2ltRUtwcUZOc0lzTE1WUTjSAcYBQVVfeXFMTWFOdUItYXlHSWpjckdrUEVwRlpnX3RPTjZRTTU5ZUNrbU5SamhIbm1ScHNBVS1nMkpycUtodnpFU1dOaXNjUkhNNXNmd0xDM2l1QVpMN3dYVGJ6SGNTY2RFV0gxZ1VUaWRYM0NkX3JTcmsxMzNmM0lxcndTeU41djBtWUo4MnJLdVp2TGhwczZWNE85Qnd1d3cwYy1OcjFlUDFzQTdrSTYwTWVIMGEtdnVCTHhCd1NkQzdNY3EySXdJNHBtSWFR?oc=5</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>13-05-2026 08:17 UTC</t>
+          <t>14-05-2026 02:55 UTC</t>
         </is>
       </c>
     </row>
@@ -2407,49 +2407,49 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Pfizer Gets Expanded European OK for Hympavzi Hemophilia Drug</t>
+          <t>Pfizer stock (US7170811035): Q1 earnings beat estimates with $14.5B revenue</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>marketscreener.com</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOQk83T19veWd0Ri1FYnhaOEJBYklqcGNBSDhuMk9UNUh4VmtBNGtqM0ZrVlllalU5YUFISjNCdm45bEZnZHJraXpnZWV3TjF2R1pyQU9SWkJvT2FnWDFtZURzVW1KUXNsOVZSb3pwYTZwRzREbzJXc0llUVFNTHAwS3lwVEVQdXRDT0tPLUpPMlB0UXhET25qaW9aREJZeFdOUV8wVmREbmgzN1EyZDB6QUk0a0M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQNjZYTFU5clo5NVRrTVVHczJRQmw3SGt5aTV5cWxlSVNUdkowV3lnaGJDRnhxQnFvM3UwTWFPQWotS1A4YnJMYkN5ZzhldDRSVjd1bVg0a013RFBNUS1IUnNyeHdVNzZUbXJFczliSVoxMXZ3U3J4U3F5SHowUGVoUWhJdHhwWUhqSl9xYlNLbHpnWkVOaFczT3NleGxXYXl3OE84WmExMk9wWXVZVm1VamVkVXlucXFTaXA1MzRVNA?oc=5</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>13-05-2026 11:11 UTC</t>
+          <t>13-05-2026 15:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Biogen stock hits 52-week high at $202.64 By Investing.com</t>
+          <t>Can Pfizer Achieve High Single-Digit Revenue CAGR From 2029?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Investing.com India</t>
+          <t>Zacks Investment Research</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOMXY4S3VMQ3ZwZVF1bzVGWjh6ZGktV1VxMkZ3YkF1T2Jrbkhpc01jSWNVdFdzQlFSc3lPYU9jcUJCVFAxbXp3d1ctdE5KQmF4NDN2QzZOZG5iMEhaUjQwUkk3bUlFdnBDWHBfRC1qNmt2bUtXaEFROGpjU2MzOVNuV2kxb29sNWctMloyd2JJVGpNdFl6MjZ2Qkt3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxOSDhZR3p3NFoySzc5ZUJLaDRmQ3ZIYWs5WnZac3dNaHNQSk53T2VuYXAtdWJkQnkzdldwaHFKQXlOU3hBSGN6ekF5VWZ0YUhhS3EteVlNNlRpSUxOQ2FCZ2tmVjh5X3lhWDF3TEhDNFcxRWc1R0xsclRGZE4wUHlFWWdFUHZldFVuVGM2dnVTTkY4UDVFSkNiYk5xajJja0J4b25FYUpMdktlUXlNMG9Xb2RHR1l2dGh4YktUbVQ0QkZoY0pUSjh2U3ItMUhEdGRaUEZlX3A0a2hyVVgxTnNuSkpZTGhtX25OeGdUcU1ScGU3LXZ2dlBvZjlmbEZGR3FQ?oc=5</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>13-05-2026 13:48 UTC</t>
+          <t>13-05-2026 15:44 UTC</t>
         </is>
       </c>
     </row>
@@ -2461,22 +2461,22 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Biogen Pharmachem Industries Ltd Falls to 52-Week Low of Rs 0.42 as Sell-Off Deepens</t>
+          <t>Biogen stock jumps 10% on positive phase 2 diranersen data for Alzheimer’s</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Markets Mojo</t>
+          <t>Investing.com India</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPMERWRXZRZC1XeGl0M1Fjc1kwa3lReW1KY1QtUFM0VmU1S0hLVDNtSmZRcHREZWllTW40Q3ljX0VNcVUyZ0RpYi0yUV9Za0dqV0JHM2d0aW1udFJLN1p6T21xX1lsVkhXaUg2b25xOTlJZFpvekF0RE9xRVV5OGhOOHJMSlk5U3hWbDlHYlV1eFhaa2RzX2YzTUFYcWdDbUVNOWFtMUc0MWljY0dRZFAxQmpVOGtqdFg3NHh5UA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOQ3BBSm5UTjlYOXY1MUZ4dEp0S3lwdm44OTNxWWhHQ3lrcGRuNzFjX0NPUndpMGFqZlh5WnNDbzhNUXFNMEhnZXdPalZPTHdSalM4MnU5ZEpVSEEwUG5hcExsSC1pS21DM3dtMTBlRjYzVm9NeVk5TWlLaDhIX0ZRdXNzSjhhdXNZUGtVdVBDdENjQTdFeGx1TXZDTExSRFNIOFViRW82ekZnTlJZVDQ4T083alVRbXlGTjVHT2R4RjlkdUZHY19z?oc=5</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>13-05-2026 10:09 UTC</t>
+          <t>14-05-2026 11:13 UTC</t>
         </is>
       </c>
     </row>
@@ -2488,22 +2488,22 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1:6 Bonus Issue: Biogen Pharmachem stock hits 52-week low despite shareholder reward; check record date</t>
+          <t>Biogen's Alzheimer’s drug fails to meet mid-stage trial goal</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Zee Business</t>
+          <t>Reuters</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxNRXpna0lWUjFYdlpRbmpjM3hldVJIc25ucXVnZWJIQktXWVdVeHJTY1JDZTk0U0hfbUlyRHJyNzc4cllyYjJRNXZEak05TnVnUm9YZXVaN3VPSHhCdGxDbkFBdHlyTlBrNzRhd3NwckZSVGJtYUtLZDdZV05kU1hRU3FuUlB6Z3dlMlRLRnJHTHg0ZUxKN2NZWGdLbzRWRzFnN1pjNk1RdDZOb1B6X0xUNGFOcExDdHVXMmxIQnlxZFFFamluRGR2cTE1RUJlVFhya2VGMGV0cC1FNnkxNTNJdUlCQWp2QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPUHNzbmJucnlUdy1SRVA1RFlXcGN5MVZoODNGQ2E4alYwS2VIQ3o0NzF4RUZvS1dCR2xnTVZUelB1QzBpNmJWbDByVTFETkVRUjJxYWU3dDFCVURMdXM3TWcteUwzaVBLZ2VibkljbGlPN1oteFlDbDJSQ21yUHpqZHo0cUIxWUhLdlhVT25LRV9fWFpIWEtGNUh6bmpqRlNsdjNrMm95NWoyWGZlWWZLTzZoNWlQLWlTV2JpNHhtNkNJdnpfM0E?oc=5</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>13-05-2026 10:31 UTC</t>
+          <t>14-05-2026 11:03 UTC</t>
         </is>
       </c>
     </row>
@@ -2515,22 +2515,22 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Biogen Stock Rockets 6.6% With 7-Day Winning Streak</t>
+          <t>Ionis partner Biogen announces topline results from Phase 2 CELIA study of diranersen (BIIB080): first study to show reduction in tau pathology and cognitive benefit in patients with early Alzheimer’s disease</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Trefis</t>
+          <t>Yahoo Finance Singapore</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNY1BlQ2trSlE3VlozLUw5X1BCcU1EN0FISWtvUzl2d1VSN18zRGV2Yjl1THU3S2xnSmhfcTF1U0JYS21scGVvTC1mcUdpaldZbXZxMElLZVE1Q09NdDBRTXhQRm5MbUdQYWFhUktwU1B5bFVlZ0ItN20wejgwWlc5ZEF5VVV3RHR6MktOeUlHQVk0Y3BUdlNNbEhSTVM2aDN3dzhxWXh5aVVvTEthV1k5Qw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPNXVaaUJRLWVNNmk3RlN4X3h1cGUwVVRQNllwMktEU2pJLXRSM25wdWNNNFZmV1BoYjhLSFphajk3UE41dzdnSmVJaGNVbVdDSngwWE9zSV94eUlRYkN2ZkFsTlg1Y3ZMVk1EY05HM3RkazdEdmRtRDdwckh6N0oydV9JWGdMV3hlMWxjTGgxYWs?oc=5</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>13-05-2026 05:26 UTC</t>
+          <t>14-05-2026 11:05 UTC</t>
         </is>
       </c>
     </row>
@@ -2542,22 +2542,22 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Biogen Inc (BIIB) Shares Surge 3.1% -- What GF Score of 77 Tells Investors</t>
+          <t>Biogen Advances Novel Alzheimer’s Drug on Suggestion of Benefit</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>GuruFocus</t>
+          <t>Bloomberg.com</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNbTg3NDJVdFJTcVYwS2YxVEloajhBc3N4clZpNjAxNHpvanBZVUlnNU5OWGJ5RE9WMnV2dHFsTVRpZU9KVDlKMm5faDVHMGZ0ZERGc0VvUTJicjFlUEdIMXhMVG5neHBHM0lqcVB1aFRTS1VNX3NIT2VSNEJ2ZGFnMmFJV0FtRjV0Q2ZlcXdNYmU0aGlpaWxqaVRESTdWNV96SHFnSmJxUzZsQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQTGRoRkc2OHNybW9zZUxJX3hrX1ZUUkxsaE9iWlVEM3FiakdsRkNabngxYUgwMFJVQkZMb0FVZ3BKLUZ0VDNSdTFEaU9EZmxXODZMNUQ5ZnZuMDZja2lJcHBoMEo4d2xmbmVtR2hWZFRuMGhCejd4WmhvT2VNZ1RxLUFDTnJFS1NLVkFBRksxSzM5eVZrSE9OTzJ5dVMwdHpfR3Rydnp1M2FxUGFyWGpaRzVPSlprZnBFYm95TzY2M1dIZ3Y3SGlMWQ?oc=5</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>13-05-2026 01:52 UTC</t>
+          <t>14-05-2026 10:59 UTC</t>
         </is>
       </c>
     </row>
@@ -2569,22 +2569,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Biogen Stock On Fire: Up 6.6% With 7-Day Winning Streak</t>
+          <t>Markets Rally, But Biogen Pharmachem Industries Ltd Sinks to 52-Week Low in Stock-Specific Sell-Off</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Trefis</t>
+          <t>Markets Mojo</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQazJEVy1FZlRSR2Fka3ZQRThsUm9RQzNISU9BUmNWblk0THQ5MmU5cl9QM3pXaHk0bHNUdTNHbW93Q2l3SkN5cmNjelZURFd2bnA3dWNTSF8zNkxBckYxcWVXaU5oWjB0S29NemROLXRMWEwwY2F1WE1MQXBqS3I1aFR2MkdPMlBLc3NUNV9Tc0FETEIyaDZLU2FiMEVxNUJkbVhWU2N0QkhHZjl1cHdCaHRDcjdwR1E2NFFXMkVuLVo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOazJSRTZrM0dMYjJFU2NLbVVlTjllYnduVFBOYlFpOXZRZGZwbWNXVllhZlRIX0RfNk5aNXZwM3F2dzY3ZGl5VjB2WVRad2RORHg2WEJCUUdJYWpLc1BvWFVHSlVhMTVXMFo5WWxPcTg2SXdjWFdJc2pHY3NYeXUxTXBtQzE5WjFOWGNaS1ZPdjg3MFgzSlFhc2FQbHJTWkVJQmVqRTdramc5MnhOVkNra3dxUlMxZ0lteVRodQ?oc=5</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>13-05-2026 06:18 UTC</t>
+          <t>14-05-2026 05:49 UTC</t>
         </is>
       </c>
     </row>
@@ -2596,22 +2596,22 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Biogen Inc. stock (US09062X1037): Q1 milestone payment amid partner C4 Therapeutics earnings</t>
+          <t>Biogen’s tau-targeting Alzheimer’s drug posts mixed results in mid-stage study</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>statnews.com</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOclpWQ0dzSWstNk9OcERqTVE1cVJ4MFF6YXhISzhHUUpUd0RIVUxUN2FCenBrWUdxMVVyYS1jZnhMdXlTR215dVRRR0Q2c2Y1MEd1SHdhNmhCZ3RfM0g5Rko0c2NBYzQ0ajhERGxubzYyOWNpbmpZcnpHTGVBOVZFbkNabGxtSDF0Y0U2NnUyaURsYlhtZEhqbW9GVURKUk9aX3BuTlM3dHg1YTc0RXpMQ2pYeVdDYWdNUU9CektxZnVMLTg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNMEZDWGlKc0EzY3FuaDdFNldxYk5nTjQ4NTF5aU5rbmhCU2M0N0RrWVptOFJlc3JNYjhOTzdQSDdST3pkV19ldkxYWFRCU0tGTDVvZV94ZjNlbzdiQXFNVGRKcE5LMHJBREFBY2I5b1A5NUtKMlhoR1JGMTU5Wl9sUjRORVhhUzlXUHpSQXR5ckRBOTR1NGEyb3NPZEFYT28?oc=5</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>12-05-2026 18:41 UTC</t>
+          <t>14-05-2026 11:10 UTC</t>
         </is>
       </c>
     </row>
@@ -2623,22 +2623,22 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>High-Dose Nusinersen and the Future of SMA Treatment</t>
+          <t>Biogen Stock Surges 9.3%, With A 8-Day Winning Spree</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>NeurologyLive</t>
+          <t>Trefis</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxOaFFMcy1UYld2UnpfcUdGMzVZWHNmdV9DQkpnNEljZ21Tc2tacnZycVdEVDNUWkc3TlVvUGVsV1ZHY08yUXd2ZGhHZHNMSGdQd01iMlJuM2xYRW1xVDZFVDdaQm1OOEc2dkNla1Z4SHVWLWxoTHpTZ1BzenpiLUFCX3dR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPZXVNNW9Wb3J2YW15TFYzVUszWkVGcVROR1hxR3ZWNW5kdk5iaVVid25IcFFuZ1d2QmNMSVVsYngzOEtTZzJVdFFLREVRRE9iZVhFbHYwdjZXUGtFLTBWU1lDc1dZRVFSbFNLd2dGT3N5WTNwZ1J3YVdWOHhQV3hMZDAzWlEyNFIxVlVha29wUl90WVFXVGZyNzNTVkZoNjJvNlNFWVlVdk1MRUVvZS0taw?oc=5</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>13-05-2026 13:16 UTC</t>
+          <t>14-05-2026 05:26 UTC</t>
         </is>
       </c>
     </row>
@@ -2650,22 +2650,22 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Leqembi to Launch in Brazil for $2,255</t>
+          <t>Biogen Inc. stock underperforms Wednesday when compared to competitors despite daily gains</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>NAVLIN DAILY</t>
+          <t>MarketWatch</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNSF9pUlJVazF2YVdpUF9sT0c2OXE1V0tWaXhOQkY1cXJaRGJWcjkzN1J4LXJMUDltdmt2T0J4TkQ4RXhaS3NMbTBvd01QYVZ6LWFHbFFqRlN2Z0FvOEF3Z1pwcWFBdEdiSHFveUNpU3REWWYwSXBDY0xkX3BmUXppQ09CcTRFUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxPd0F3djdiSTE5SjluMkdMWEw4aUZiMjZoMlg0QTFNSmFpcFEzajhuMnVELU0tRVVLVmpxbG05dHBiWlJPWjhLWUU5bWZXb2FZdTdkQ2VDbWJ4ZFctV3JFTXNhc0hyQ1J6NGJHbzRXTk4wU0Y0bnEtb3dERTB5R1VVUWxFcUZHd2EtZWdRdFVCbDlxcmNsZW1paFFGTkkxb3JCSlNubE45M1VkSUItVW5meVkwVU9rRWUwYkpHMXZTZEtNMkJyYmpsX1hCSU1FTVg0NUc5QnJ3b0JkaGpoQUJMNldDMUJrYWJJTkxpUXp2ZGVNdW5DNHpkOWJQYw?oc=5</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>12-05-2026 18:55 UTC</t>
+          <t>13-05-2026 20:58 UTC</t>
         </is>
       </c>
     </row>
@@ -2677,34 +2677,34 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Amyotrophic Lateral Sclerosis (ALS) Market to Reach USD 1.22</t>
+          <t>Biogen Pharmachem Industries Ltd Falls to 52-Week Low of Rs 0.42 as Sell-Off Deepens</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>openPR.com</t>
+          <t>Markets Mojo</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPSFBmNHdRa1lhcW9tYkdBb2h0bGFrenp3TXlwWXNiM2dYSGt5RmNOcVN2dk1PZlFXbjI1X2E5UlA4NkRYblBNR3J0cEwyeGJDN09HNjlyVlV2NkRhVm5qa0JadmJ1bUlRd1pybWRucEVCVGdyS2lGSmlTa1h4YUY5UW5OSVVVRU50ejljWWQxNDJGVDdpajZYMlZn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPMERWRXZRZC1XeGl0M1Fjc1kwa3lReW1KY1QtUFM0VmU1S0hLVDNtSmZRcHREZWllTW40Q3ljX0VNcVUyZ0RpYi0yUV9Za0dqV0JHM2d0aW1udFJLN1p6T21xX1lsVkhXaUg2b25xOTlJZFpvekF0RE9xRVV5OGhOOHJMSlk5U3hWbDlHYlV1eFhaa2RzX2YzTUFYcWdDbUVNOWFtMUc0MWljY0dRZFAxQmpVOGtqdFg3NHh5UA?oc=5</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>13-05-2026 07:42 UTC</t>
+          <t>13-05-2026 20:16 UTC</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Blau Farmaceutica</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Blau Farmacêutica S.A. stock (BRBLAUACNOR1): Starts 2026 with revenue growth</t>
+          <t>Biogen stock (US09062X1037): Hits 52-week high at $202.64</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2714,93 +2714,93 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNcXFyMDFjLXRhM0pDcnZLZGttSzM2MW4zN09IV2hrUEN1LXV4eFNfeTltUm5oRERlOEFfQllrN3pJVkZtWGZBeEs1TGZsV0FQdGsxYW9BNWh5enZhTEN2bnJLWFZDanpBQWFaaDJLWHpFS3E2NnJTX3NHbGdRLUVfOWtaOXh3UEg3aHQyMGFPdFMyOVNWTkVpNG5JekM1VWJoZWhSWlZ5OVFQQ0Z0dHdjcnFveE44VEdqcDg2bTAwekVVZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPODZsaWYxV3pGODE4ajhET3FsU1dZR1YzdHE2bDJMWFNmOWl3UXVLUUxBWFhabkdnWkRKVjktRVZFUk5tNTZoUEtOYW9QbDY2N1hjRko3bHkxRnR1X2VVWHhZMUVUT2wxWkVkTkJYdWFNNS1MbXBSTzlkcFZGTUxTY2dOcXpZQ0NPS2dpMUxRa0JPTkN3MldSa0t6MWtHa0pqTGFKVU1lWWkxRmdfelBLanRn?oc=5</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>13-05-2026 10:20 UTC</t>
+          <t>13-05-2026 15:31 UTC</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Dr Reddy's Q4 Profit Crashes 86% to Rs 221 Crore as North America Generics Sales Slump</t>
+          <t>Biogen Stock Surges 9.3%, With A 8-Day Winning Spree</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Medical Dialogues</t>
+          <t>Trefis</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxNTFExREh4a044UGNwR3lhdnBiWUtvYjdTS0lHRUE3cGJJblItVkc2T3Awb190WkxIX0Zwejg0bUZxS3Jjc0FBbVhQc3BSdEd2dDNQRWduQXV1dVUyaXNscVZwQUd2VUNBQ1diNWtfYXQ5TGp6THE0UDV3eld5Z3pOUS02cThOWmpBSDdfOFF6d0dzY3I1cm05dHJZZW1ZbGgyRm43d2xZdTJpaTNySTItN0dCLUctTWhQbjdxV2RnT29JbERGYi1GNWlVZFBJVXAyeVF3VEFIY9IB3AFBVV95cUxQaGVOQi1xT3JnNjFYenhkejI1RlpySFJQOWU2Q1dzU3VwWGJkTXhQdmdENkpFU0tGVUNNY1NyNjJmUXVpUUJQYTE3UTRxbXBCT3FVSUljMVg0bk1nVWI4U3lFSG50bzVsaXgwNGhkZF9HUlFSTFVDNDA3ZXlxUTZQdjBkUHFQQXRHNi04OE9ENFVjR1lWcDFlOWxnRWlKZS11UDZ1UGtZTFFCTkVreDZhOFlVQWgybXNIUWdpQ3REVjVSVVFKd3YwMExXQko4ZlgtODktMDBhY0dOU3da?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQalA2ckVPLXJFRHhPTXJHOXlhWUdmcWRqVGotTHFVZFh1anhjekRaOTJMLWFSRVZkX1UwYmZKcDNYVU5CVW9iaFh3REJJSUp3MEtmaHRPVlNUQnV5Mm9sZ2VFaWYwMnBvUFQ4MHphMnR3RzB5SU1ZYllnNXZ5WDJBMGp4Sm9vQjA3NjZpZkZlS3F3bHlna3pWX3hpOTJ4NGhFNUpuYjdvSUUwYjBKTlZVQzdSSDM4bnNxWGpncw?oc=5</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>13-05-2026 15:23 UTC</t>
+          <t>14-05-2026 05:21 UTC</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Dr Reddy’s revives India business in FY26 with portfolio, productivity reset</t>
+          <t>Biogen plans registrational study for Alzheimer’s drug diranersen By Investing.com</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Moneycontrol.com</t>
+          <t>Investing.com Canada</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOSm5qT1JsS3REbnd2UnJfTTV3QlhPdGNtOG5kMkVPV2hOM09URXhOU1VVM0NMSWFOUHdFZUhxTGFSelp1X3loZUNJZ2hNbVBmemRxQWVEcWtfOGI1VTFxcFUtNVlGeHJmbHhoa21vM3phQU0zVG1YR1VabHJvMWhHT2d2RUlQRmRMa2lCMklsRXdyUkt5S2lkc0RmSDhYdkJ4bjFmNUFGZ0MzOXp4WXBtZDlkUWJqS08wSHVXTFBObkJXS0JQN2RwQzNXaG7SAdIBQVVfeXFMT2k5YllGaGt3aFZzZGtNc29DU0hMaThNaENFZWNlUDQ4SlE0ZzNwVnR5Yldab0dES3RqSlF2U193R2Zrd3RmWGxySWZfNnc5N0xNd0ZlNVNNM2IxNV9YczU5eGwzRzVDcF9jQnUwekE2dHBkOVE5dzRMcko3LS11NGt1Z1RrX0MxNUZ1c0piZ3Q0b1BVU1NYRFRjTHJPVEJZNl9rYWhCSktaTkFUOVllN29Ecm8zZ2pHUVpydm5pTGFDeEFqdHVobGlqcUV5aGlycGZ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNa2tidUxrODZCOF9sSjZuRXBCS0lua2p6ekVMRElQdEhId1o4Um5GTGhiOF9iQlNIWDFLU0htNzllY1dnVHlfV0w2dDBHOGhmTVcxcXYwYmNsM05jRDJLTFE4c3g1X0Zvb2V0bVJSbTJ4OUhwVXlLWEJOQW51Y3FtZmw3SXA3c2NDYVk4MEVwUXJqM2MxT3VvaEJQa2tjQzFFTXc5amJ4VDZQQ2hQUVp6c3ZUZU1rTFM3U1FDMnpRZi1WLW8?oc=5</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>13-05-2026 12:17 UTC</t>
+          <t>14-05-2026 11:15 UTC</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Dr. Reddy's Q4 Earnings and Revenues Miss Estimates, Stock Down</t>
+          <t>Biogen stock hits 52-week high at $202.64</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>Investing.com</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNR1dGQW5wazVaZXpCSXdqQ3gxSzhmVXhDYUYzODEwSmxUV1FZTUZKM0tVdWJVaWFnbDZvMWRLNU8wT0JDUFFWWkdFbjJfdzZSWTZEaEJ3a0lsODhuNi1lMXNzXzQ0VGhrOUxIeS1UTHBjOE9TcDRFcFNjSkVtakJCU1pMWmNrVUJxekV3dUJrVXMwUERxRGdzX21nWnVhaF9JTkhPQ0FGUXF5Qml1YTJHZm4wX0VSLURm?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNcW51Ty1ISTFQUzQ4Q0JfWmFXb2ZyVUJfbGU0dnJYVDE5QlRDZ1RkcVQ1YUFFYWVXRHdQOFpoRzlxNmxsMC0wN2JqYWVfNlhLanlQQTZqTXdFaG54S09PRUFPbXI5dkdGdV9DbUJJMFNfNC00Zmd0MC1kbElaTTdmQWU2a2pMRTgyZ3JtRTc3czlMZEtxSmd4NVVBTQ?oc=5</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>13-05-2026 15:23 UTC</t>
+          <t>13-05-2026 13:48 UTC</t>
         </is>
       </c>
     </row>
@@ -2812,22 +2812,22 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Dr Reddy's Laboratories shares: Poor Q4 show — Buy, sell or hold?</t>
+          <t>Margin revival, Semaglutide launch to drive Dr Reddy’s growth momentum in FY27</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Business Today</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQWko2OWIwUkVRSDN3dGw3b05pVjhLaGx4YlRFd0ZITXE2bE5QOU5qQmN1N2d5TGRXdDlzT29tVC10dU1JcXN5Mi1yN0xzajhZdW1aT2dGQ3JZY0hleUVGN01QV1F4bExjaE5xZTJRZ282bGFPZmhadnEyQnJBaHlPa2RfZmN0dmVGQ1VPZG9TaDlwQmFZRGM0SHlfVTVTeEh5TF96VWliMi1KTHpoRXU0ZFFqQkFUVE1jajM3WlFNY0RTaDlSRGfSAcsBQVVfeXFMTUJJS1M2RjNYWUdlWmpWcm5tV2RORmJKV2d0SXJ5X0JCSlJKS0JKdm42Y29CSVFUSmlBS09BT25HQzJMSGtzVTVuUEMtNG5rN3BxbHBZT1Z5aUpqdm0zb0lvc3BuZllfUE10WHhvV0VEb2xxVmtjTElPSkJXV0Y1MERpb0tQWVNudmlOSHY5am5DYW40TkkwdUx6aUNqYXROUndpcDBQNkVfVWxudlR5LUJXRjNFUXZ0c3lHWDNIRmhyMGtwNnBpU3ZPNWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxQMFhOQTd5Rk93OFlReHJGMVFoNlZlRGpJYmtydlpIRjREZ3Z2M2x4bEYtcHVFT1FtZjI5OXZfVVZGWEl5dVUtS2U0d0Nva0VOMnV1VHhCNnFJSV9YYVVyMnJmVUZob0ZxdmtsNHJ1U1BLZWJmYnBULTlLck1tMDFYWW9fV3NxUHRHV1NWRE04TUZkYmk1VzZ4cGZCai1LbmZWcTN5TVhOcHRVWnBOZlJ5YkJtbXhleEE3cndkZTIzOTNfVERLLVAyTklrakxVVlg2TU1sV1ZYNHhzTGlFaTBEQ0Y0MlhvelRYSnc?oc=5</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>13-05-2026 10:18 UTC</t>
+          <t>14-05-2026 00:44 UTC</t>
         </is>
       </c>
     </row>
@@ -2839,22 +2839,22 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Canada approves generic semaglutide from Dr. Reddy's, a G7 first enabled by Novo Nordisk's lapsed CAD$250 patent</t>
+          <t>Cipla, Dr Reddy’s Lab, Crompton Greaves: Nomura’s top picks with 17% to 26% upside potential</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>drugdiscoverytrends.com</t>
+          <t>financialexpress.com</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxPTW03ODZVV0ZCZ3lfUVk5Y2N1dUk4MExycC1jODhOMmlZZ0h6TWJrLUg5WWgyYUhtbkN1bWx6WDMyVE40dE5sVzRMSzVrTnNWMXUwRzlFTHF5TVhSaDJOOWpVcFpObG5nbHpNMzJISzl5cWpBRWFBSHlRdnJFN1kwSTFNVEhqN05oYkxneW1LTmFEZ09PS1VDS3pZdVh6OGtVVTdCT1pWd3JEbFp4N0dReDc1YXRzV3JENG1jWFg1ajRvNjVBTE1MdjBhVFMxaTJ0SGxGMTdXSklkTnNx?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxPUi1QS3FmeUNwbktRM1VOMHZRQUlHTldfb1pBSkpOanJTaTBrMlBBOWp0NHUtQU56SXVnOVdZeDFYanhOaUw3MHhlZ0FwM3N6RUtVc1dMd2s2Uy16RlhPN05reDdBTWpfTHFIekRqQk5NNVpTOGVjdk1lOW1weF81MW5YdzFUcXVIMjF4WUQ2TVRKblNHM0xPbWJaY1Joa3RYc08tbnhHeGJkMXIySk5pY1Y1OHV0LVpfY055ZzRJek9YckRiTkYwa0dnaEdTM1XSAdYBQVVfeXFMT25UTkVLNlRrVHVUWnVaRU8wRmhjY1JwV2xGWUl3QkZ6TEdPQy1vekplR0RKRUUyMmpyQnM1YkRNWENTT3NTRTRoeXl1RDVLd0liQzE2ZWtiQ0lNN2JDbFVKYm9JZzRtbnJQR2gwTEZwUHBuczFIekcwOTRpeEtqdUhRSkExQ3FqdUZGdVlXWUkwYWhLSmR3aEdWZEVnakhabzdvY3ktWkpyTDN1c2VscktjbjhpQkRxbUZBV2JZZDZDa05tVUdua2pkSzdYbjZkLWRSZmEzZw?oc=5</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>13-05-2026 16:11 UTC</t>
+          <t>14-05-2026 09:59 UTC</t>
         </is>
       </c>
     </row>
@@ -2866,22 +2866,22 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>4 reasons why analysts are bearish on Dr Reddy's Labs outlook after Q4</t>
+          <t>Dr. Reddy’s Laboratories Secures CDSCO Approval for Generic Oral Semaglutide in India</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>Chemical Industry Digest</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxQc0c4OW4wZXVVQUxJT1JhMmpFN19TamVxYms3NjE1eDZXZngzREgyOUs2TFotMlhBQUFQUHQtVGFGdnFFN2pHT1BYMjF2QUVScmJkQ2FhanJPV3N5WlhDYTkzMUNVdXRyaU41bkxwTUVVRHBTVGktaXhqWERDX3doZWZnUEQwbmlFMnYybzRkcWF3TlRocktXbmV5WW1jZHZHVzB0V2FDaHh0d2NkVDU1WUhJeU52MkV4VFFHRjFUZWtYTjBMaUVCR29NaThjN2NGSHlRSVR0bVlPZnQ4M3JfcnNKbWNPMFJjOW1N0gHwAUFVX3lxTE8tNjZYRjBFcnNjOHVsS1lSaDByTFdXaUVaWXBQdWdObHJ6LTAwd1VEeEJVWGM2REpsNUl2WkluQnFNUUNpVEo1dWVxOUZaelJOcXloSjFFbVNPLVVtYzlmSXJuVmJYYjR4cDF4eXpaSGVGc3VROE9ic3MwM1l3S1FjQWIxN19fRk5zX25qQ0NoWWVyZG9KdVdUWTNPYWhlbElyQm4xOXNQT1FDZ0R6RjFEd2lsanljNWpYTzNhRkdNd1BsRy04MmprY25wNUJyWWFjRmtWdURiOFNyQjlwQmlFd0NzbF9qUFVRMFpYYURrTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNbEJpUjRTMk9RWTEtOS0yRTNYcWdkSi1uZm95RExNZ09Pd0pQLUdWQ3pvbnJqaEV1UWUxR1k3eHR4a1pOT3RGTV93cTlJQXRlc0JWMnE0c25fYnJIRXlqSXZFZzdZWThOYWU4M21xcks1N3l1ckROa2ZfVFRMdGZaZFBMMzlsc2tUUjJDNm9BemRMVWRZb1BudjJSYUFrYld5Z295NHIzd3MyV0h4UUE?oc=5</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>13-05-2026 08:18 UTC</t>
+          <t>14-05-2026 07:29 UTC</t>
         </is>
       </c>
     </row>
@@ -2893,22 +2893,22 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Dr Reddy's Laboratories shares volatile after an 86% YoY decline in Q4 profit. Should you buy?</t>
+          <t>Dr Reddy's Q4 Profit Crashes 86% to Rs 221 Crore as North America Generics Sales Slump</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Mint</t>
+          <t>Medical Dialogues</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxQRVhFeng2aGl6ZE9nOEFfX2hZc21FR2J6RzlCbkFLR0Yxemw1aEpFRnNOUFhuNTdjY3VFWUo0X0U4a0VIdWNiYkZPZ2NWb0RQZFIxTFVGTjJHUUxQeXd1Nm5VVk9nWlM5bVZGN3g5MjZPSW0tb1J1U19tbEYxRjduSzM1elFaM1ZmVDZOWWhaZjI4QzlkcEZRYUVvNFBzQTZQel8zLUpSQ2R6YV9xSVQ4OUZGcFFXanZvZUVVNGNZZXFtUGNUWmJWaGRhS3BLNFVVTkVtZy1vd200NXZQ0gHiAUFVX3lxTFBOY0pJZzYtRGtTamQzeUhNb1BHYUluUDhaT0V6a2liS3YzOU9yR012eHFUbUtDOHM2Y1M0WXJoMjE1Y3hmNml1V2NsbHpGaVNwdVpZOGxqcVhOLU40NC1XX0dLbGNoaHI5SXFqZWFqWVlvQXl3MjQtVlBOTndCb3lJZkloVlI1MWJiQ3VDRkVURmtzdHFURTliQmp4X2R6a0xqSzRpZnZVM0VRTnkxN0Uzb2J6U01SYlBVUHlsb05TN3RjZGQ5bHE4LUF0SFdDYy1GUUJYbGttVlJxMmFFeGM1OXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxNTFExREh4a044UGNwR3lhdnBiWUtvYjdTS0lHRUE3cGJJblItVkc2T3Awb190WkxIX0Zwejg0bUZxS3Jjc0FBbVhQc3BSdEd2dDNQRWduQXV1dVUyaXNscVZwQUd2VUNBQ1diNWtfYXQ5TGp6THE0UDV3eld5Z3pOUS02cThOWmpBSDdfOFF6d0dzY3I1cm05dHJZZW1ZbGgyRm43d2xZdTJpaTNySTItN0dCLUctTWhQbjdxV2RnT29JbERGYi1GNWlVZFBJVXAyeVF3VEFIY9IB3AFBVV95cUxQaGVOQi1xT3JnNjFYenhkejI1RlpySFJQOWU2Q1dzU3VwWGJkTXhQdmdENkpFU0tGVUNNY1NyNjJmUXVpUUJQYTE3UTRxbXBCT3FVSUljMVg0bk1nVWI4U3lFSG50bzVsaXgwNGhkZF9HUlFSTFVDNDA3ZXlxUTZQdjBkUHFQQXRHNi04OE9ENFVjR1lWcDFlOWxnRWlKZS11UDZ1UGtZTFFCTkVreDZhOFlVQWgybXNIUWdpQ3REVjVSVVFKd3YwMExXQko4ZlgtODktMDBhY0dOU3da?oc=5</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>13-05-2026 05:33 UTC</t>
+          <t>13-05-2026 15:23 UTC</t>
         </is>
       </c>
     </row>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Dr. Reddy's Laboratories falls Wednesday, underperforms market</t>
+          <t>Indian drugmakers turn to buffers stocks, contract tweaks to tackle Iran war fallout</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>MarketWatch</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxPXzZBR1AzQWNiZWJORk1IalpxbW9BOXpxWnpPM0o1NTZVR0FuWFNMSFRkcTVmb0pjejljY0Z0SUJiUy1FX3RtaUVvOG00Y1YwVks0eEhyUUJuU2N1NThRV3hzS1luR1cxT0ZOTm01QUs4dEMzajFkbEhyZTlHOWtqdC11YkRRVFR2UURPWVBNTFNVcktlYm5fYXN2by1NdUhZaTF0WHZ1N1JjNG5KYjVWZVZOWlFiSWNhNmQ3WlBoZVh3VGk2UEhGLXJaQUpLQmU2SWtQRmdqYXhBVzQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxPTmNtd0lLbG9mYkt0dkU3VWhCU19DbmMwQ1d2Um4tS19vZldBaVp5Y01rMXk0T3dZaHlfSDdmR0llbTJwVm9hMTFyckZ2QzVEUjBIaFVaaC1XUkZKT0lsalZBQjlTVmlJMm40MUNzWWh0RWV3OURaUmhBbXI2OXZwTEE3VGNZRG8wNHo0U2Y5SmdmOVFmNjlNNTNBdDFRUVk0ZkpVMFNqWTVrdnlSSll2enZGS2EyaXBYMk1WMHMwTHgyeXhOcDBCUkF0S2NzUzNseXlEc0JJUWhpbzJiZ0hR?oc=5</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>13-05-2026 10:30 UTC</t>
+          <t>14-05-2026 03:38 UTC</t>
         </is>
       </c>
     </row>
@@ -2947,22 +2947,22 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Dr Reddy's shares in focus after Q4 net profit tumbles 86% YoY; Morgan Stanley, Goldman Sachs weigh in</t>
+          <t>Analysts recommend Dr Reddy’s, Zydus and Kotak Bank; Persistent Systems seen under pressure</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>CNBC TV18</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxNUVNmZlotU0gtVHpBa2xsdjM1T0NuU1FROUU3OGJuZkpZd25LeXBNOTlkV000dTQtalNKMm9FSzluMXNqdGNpYTZTRlNOcGxwUEJ1YWlNVnduZUJlX2Z6VlkzRWtnaGVBUEoxR1Z4SXRzd05BTzNqdFRCbFRBVnlxX01HUWtESENsSG5fbWUtQ1lsdmhtSE9YdVo4UjNZb1FoVWVEblk5WWlzOFE2QlpXeE5MdHZCd1V0Q3E0X1JMVTBCeVYzeG81S1E0VFo4NmVrVjhwRmtXdWZqeWw0TmRmVjg0LXhnZkp2dTdZaUNYTHp1Sm5wcENQeVItUVpyQ3JQY2fSAYcCQVVfeXFMUEtXVm9HSElHanh1YkREb2o5SHNsVGNVb2Z0OFRGRmlzZks3MGFTTnQtcFh0Rk44MW5uZlgwT3ktT0tBRVZWb3hmNDVOQnlaUmNCV2ZVOGx0YnZQRzdpRzh4bHZJcE5YZG01dTlGQkVsdnBpREk3YUhCaHFHR2lfRWROZVY3ZFJPb0NWNlgyX2c3cHRVQXpqVDlvbm5BMUwyS2lVTW9nbjdsbXVLR3MxLVJOcFFaLUh5RmNya2Q0b0lSc3hncXRZdzNBTDVtUDhBc1dYR2xLY1lCT2FKUWNVbnRhYTN4Zm5nU1c3a2Z4UVpFMkxubXFsbW1JUGM4Um5CakJNdVdsdEk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNSUktek9kVmhhVzl3Ml9hUDBHZ2RvSmxkSXhudzNXMXFLWXBWYVhCQ1lNQVVDZXNRU1FWSGF6UmNndElILVVicHhwNW92SnZ0clVKX1RnbVdjWFlaWDVIbEdJdGxodWREbDBKMFBmbk1GZ3VSa1RManR4Tmc3TFVDR0dBMUtyek9MejRoODVxc3BXeE5Sb3hILWFDNVdJcV9ZWVU1XzhzY2NyZEVaeGRfSnNXZXVES0N1amdSUGM0aFZUekhKcWJR0gHHAUFVX3lxTE1JSS16T2RWaGFXOXcyX2FQMEdnZG9KbGRJeG53M1cxcUtZcFZhWEJDWU1BVUNlc1FTUVZIYXpSY2d0SUgtVWJweHA1b3ZKdnRyVUpfVGdtV2NYWVpYNUhsR0l0bGh1ZERsMEowUGZuTUZndVJrVExqdHhOZzdMVUNHR0ExS3J6T0x6NGg4NXFzcFd4TlJveEgtYUM1V0lxX1lZVTVfOHNjY3JkRVp4ZF9Kc1dldURLQ3VqZ1JQYzRoVlR6SEpxYlE?oc=5</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>13-05-2026 03:40 UTC</t>
+          <t>14-05-2026 07:34 UTC</t>
         </is>
       </c>
     </row>
@@ -2974,22 +2974,22 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Dr. Reddy’s Q4 dips 86% on lower sales, multiple one offs to ₹221 cr.</t>
+          <t>Dr Reddy's, Dixon Technology &amp; more: Top stocks to watch on May 14</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>The Hindu</t>
+          <t>The Times of India</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOR1pLcGMzaktJb3FGUXZEM25xZmtzMG9fT1ZNMkFoRjRRRGQ3MHNacUwtNGpRcDY3cDJXbDRWSlhFMDh4WnZoLVdpSVVxNmV5VjA5elVyeXhySWVSRmlQblExMHNlS2FNTUU5RkFjZGZBd1RuaFM4V2xDcGxvNU5TSjZSR2dOYXpLNFByeDNUbzQ5ZllFcmFKZnh4WFhpYXBfenI2RXlTdjV4TVdMUGdWbENNeXpzdGdK0gG_AUFVX3lxTE5MazZMY1cxdzVIaWdqNG50OExoZ0ZSSmVzMmNSdFA3UENGTmRSNllfWWt2RjRRM0NQU0hSeUN2cW83NGJONFVwWEZSOUd4ZTkxTE15Y3MwV2EtOGFlaFdMZjRWbW91Y1BiNlo3YldHWGdyLVA4YnNNVnVHazVmLU5pOGJlcjNWcVRSdFN4d1hyY2phZVFsQ2pHLUF0NENyV19CSnZpaXhhM0ZLSWkyOU5kXzBsVWVCV2hEeURER2lR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxNdUk2RFRod0pBOURHMThoS2VzcDFMc1dNQlJQekNidjhRM2Q2b2NTMzhySVpyNDZOMWtNOUs5RnF4RHE3bVQ0VzVsa2RrLUFEdUJfZmw5ajZLVV91Zy1qaGtLUW1SMmE4ZWdqZlZBS1R5enowMkR2Q3cxUUREeGdJX0o1Qm56YUtVdnBleXRlMTF4QTNMamxtbFRxTzR2dm5tZ1A4dFVVZnl3RXhVQ3U0M3dWSENNTEYtNW5qZmVjcDVraGIxOUZzX0FPVTJ1NVZzV2cwV3FYS1dVZnlubkZxQVNocnA1Z9IB5gFBVV95cUxNdUk2RFRod0pBOURHMThoS2VzcDFMc1dNQlJQekNidjhRM2Q2b2NTMzhySVpyNDZOMWtNOUs5RnF4RHE3bVQ0VzVsa2RrLUFEdUJfZmw5ajZLVV91Zy1qaGtLUW1SMmE4ZWdqZlZBS1R5enowMkR2Q3cxUUREeGdJX0o1Qm56YUtVdnBleXRlMTF4QTNMamxtbFRxTzR2dm5tZ1A4dFVVZnl3RXhVQ3U0M3dWSENNTEYtNW5qZmVjcDVraGIxOUZzX0FPVTJ1NVZzV2cwV3FYS1dVZnlubkZxQVNocnA1Zw?oc=5</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>13-05-2026 01:30 UTC</t>
+          <t>14-05-2026 03:07 UTC</t>
         </is>
       </c>
     </row>
@@ -3001,22 +3001,22 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Dr Reddy's Q4 Disappoints Brokerages On Weak Quarter, Semaglutide Ramp-Up Delays — Check Targets</t>
+          <t>Dr Reddy's Laboratories Ltd (RDY) Stock Up 4.2% and Still Underv</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>NDTV Profit</t>
+          <t>GuruFocus</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNYklYckNzVWhOR2pNTDZkM1ZFZmRiZXk1UmMzdlRHX3RGbFVIVEJsWXlFcHF1cGYyeGR3YUMyN2I0VkwzSzZuNm1nSEE2djExalpDMTRXbUMtRl9vanlyWUM4M21lTlJaaGRGYjNVNDNwZWhCZ2wydWxlalk5SDdlLTVtQWNzSW1FOFQzbGIwYkJPUXRQYlVjT3RfdlB0a3lLZGxnaVdhMFVfYS1xTUhCZjlXQlYyU1FjYXVhLXN0YmhzcDgtYUVNdjd1NC11OTVTNnfSAdoBQVVfeXFMTlRXYU5Ca0VERXVkQ2p2SnNnaHlpVXUzZU94TXdta1hBSEZ2LThReHhYR05mS2FrYlVsYS1TQ1pNU1M1T1A5RkgycXpSaklPQ3hKNDQ5UnNSdWktUVc3NnUwZkdIWDZVNGxORFA3OUJsQW5UU1FqM2FxMm5OQXI5VzFfZm1GOHpDdjZJVzJEWTk2ZmUzS3lKU2ZXbVJsT1pWQlpYM1pLTjlKWnl4bU9CRE5hXzdEbWt3azQ0X2o2eGhyOGVscU50cHhqRTNJZDVCTTJRWEJ3bU9OWGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQUnp0d2R4eldJUndtZFNfaDVnZjludnNtS3NQTktSaFJNLWhqdUlUa3RLcVdCVHVoU0RBaDlHU0dHZ2JrT0xTTXNJa1BDM2tRSzBxdGNySGtPQ29LSjRtVnRYd2ZHUTdxdHhDXzBZWmpDNXZ5ODhwbXlHWnkzaGUwYkZ6SlhaelRLN3lXVXk4UDRLZFZVRW1kTVM4dnJqQWVuQlp0WVVNWlhLekt3OUt4Y1hjS0o4b05FVTdlcTBJSGxaVHh6d3RYVk5R?oc=5</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>13-05-2026 03:22 UTC</t>
+          <t>13-05-2026 22:30 UTC</t>
         </is>
       </c>
     </row>
@@ -3028,22 +3028,22 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Dr Reddy’s Sets Out Details Of Imminent Semaglutide Launch In Canada</t>
+          <t>Dr Reddy's Net Profit Plunges 86% to ₹220 Cr in Q4FY26 on One-Time Charges</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Citeline News &amp; Insights</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxOMVVEQW12cUlTOElKTi1KQkY2eVIzRVlFcmRlZ29XTjRmMGZ5Q0l3elFMNDVneVYyNU5KRU93ZVI0Smxpem1PbjE4NWVITGQwZktWeEFEa3dJNzdUSkpsdXhmRjFhanVzOUhEbnlFRmdETHg4T0h5dmYxZENqNnhMQlpISkFGTks4NnE3QlZ5Yk13TGdPYzNadWREaU1rMDZYSEh5bWNMSjhHampvaXhVV1RrZThnTllWaDIzUWdRNld0TnRKYVYyZTlLZzE4dGFXQVlrYm5ONGF6UVdHLW9HcEpDdmxEeUdzV0ZFdWt5MVlSdzg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxNSURqRmZKaWV1eW5Lc0FJa1UyS0xKdHNDWERXMVFoZGpTZV80cWtIalM1S01nNnhONWlURnZ5OTl5MExNcm5CRVgxbTRiUTFBSzBPeEZWVlh1T3dqRldNUDFPVE5QSThyMDdzMUxLWVZER0hGWHZyVkdEQzVjODZsUTB6UmRPNzFvSFpnMVh0azlsV2Y3WTREallEYVBuNWpDOHEtbkJvbFRCbll2cy15MUw0VktuaVhaUjdKeDJBdmhkMW5WdE8wR3dvZTMtLTF0ZXZ3a3FXeGZXaHNNT3h0TWo3TWJqVWM5T0RNZElHZWFSWGJ1TE9sRQ?oc=5</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>13-05-2026 16:41 UTC</t>
+          <t>13-05-2026 16:52 UTC</t>
         </is>
       </c>
     </row>
@@ -3055,22 +3055,22 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Dr. Reddy's Laboratories Ltd Stock 12‑Month Price Target Cut to $13.78, Implies 11% Upside</t>
+          <t>Dr Reddys Laboratories Ltd Surges 3.15% to Day's High of ...</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>Markets Mojo</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxNbE9aNHNzdXhnSWJqNlNUdC1haGJHWWZVYktxeDNmbkkyTktGSzFMSHNqMnlBNmJMZFU0c3Z3OUtTenV2XzVfQnF4RWFxTHZ3R1JQRC1JU3hnNFVIUG5BZFp5Ti1XdXdESnVKQlpyc2ZRV2ZrQWwyYXpRdmlnQWRrMzg4NGt2eUFJekJxLXZKLWJyVlNtRlQyRkNWOVFkUnZKOGJKdmdHRTN2U2pPbzlEODFVamV4eXFXWjVvMHhfWndyMmt0NFFwQ2JqcHB4Q3YtU25zamktWkhydWE2VHU0ZGN3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOMk1oQzBHOEJUNWpVbFRnVFVGQktwWWdZRl9LRWVqbERqTEg4Wk5UcVN1LVA5M2hFREFZSXJWamNMS1FqR2JWX3Z3SXFqU215Rm9wY2UwT3lmMHhob0xYNG5YUkI0eGQ3UHdQWjJUQ1RpM1laQndLeU5IS0FZbm5yUDRpa2pNWGw5YnhJMU5XejZXY1FyUW1qTnNvTnNzUEoyX2VLYUZTRDFQSExaRnpnZkw2al9nZWFDeFlrY1pZek1OdU5FRm5OVkRaYng2dw?oc=5</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>13-05-2026 09:20 UTC</t>
+          <t>14-05-2026 07:36 UTC</t>
         </is>
       </c>
     </row>
@@ -3082,49 +3082,49 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Dr. Reddy’s Q4 dips 86% on lower sales, multiple one offs to ₹221 crore</t>
+          <t>Dr. Reddy's Q4 Earnings and Revenues Miss Estimates, Stock Down</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>The Hindu</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxPQTdSVVNyVjNtenZWNGhsRkFCR2FOMVhoblZvcGs3Qm5RTDFkRFB1TTRJNXd1cjJpc254YU01QnBxUU9WR291aEFlTjhBYURyeDhWbVAyV3p4aDlELWRnNS1qQ0MxdEhORmRYRFFreGhsYS1lenFaR1liY01UOFByeFBtVkFMWGRybi1tNHQyaXdtbEFUT2Zvb2FxbWlUbWRucm9FVFpSWGZia3hyTlNyVzAyT0hxZUlYaks3WWVDSHZPaUpzZnhYcmpEUkRwWkXSAc8BQVVfeXFMT0E3UlVTclYzbXp2VjRobEZBQkdhTjFYaG5Wb3BrN0JuUUwxZERQdU00STV3dXIyaXNueGFNNUJwcVFPVkdvdWhBZU44QWFEcng4Vm1QMld6eGg5RC1kZzUtakNDMXRITkZkWERRa3hobGEtZXpxWkdZYmNNVDhQcnhQbVZBTFhkcm4tbTR0Mml3bWxBVE9mb29hcW1pVG1kbnJvRVRaUlhmYmt4ck5TclcwMk9IcWVJWGpLN1llQ0h2T2lKc2Z4WHJqRFJEcFpF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNR1dGQW5wazVaZXpCSXdqQ3gxSzhmVXhDYUYzODEwSmxUV1FZTUZKM0tVdWJVaWFnbDZvMWRLNU8wT0JDUFFWWkdFbjJfdzZSWTZEaEJ3a0lsODhuNi1lMXNzXzQ0VGhrOUxIeS1UTHBjOE9TcDRFcFNjSkVtakJCU1pMWmNrVUJxekV3dUJrVXMwUERxRGdzX21nWnVhaF9JTkhPQ0FGUXF5Qml1YTJHZm4wX0VSLURm?oc=5</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>13-05-2026 07:54 UTC</t>
+          <t>13-05-2026 15:23 UTC</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Intas</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Dr Reddy’s Drops CAR-T, Eyes GLP-1 Upside</t>
+          <t>Weekly take: Why AIPPI and INTA’s Dubai problem can’t be easily fixed</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Citeline News &amp; Insights</t>
+          <t>Managing Intellectual Property</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOZGl4YUlzUnpWWGpFQzlHTkVubGlMVnNLMXJFaEJxdTVwN2FTN0k5SkY1YVNfMmtJU0xka1ZHeVBYZTd1RnZzTzBaX3FsNlRBNjd2UHlHdU1SekVTUF9mcEFqWENWMkdNZWEyR3J1aml5WGFYRW5PV1UxWVVHQ1dqa0NpZzF3ZkRwcnY2Q185UHlRaUp4N2JULWJ2Zm14bnl3ODJtOFRHX0dHSDBhenFXcVhBazV1Q1pzQ3pFcldvTnI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxObm5lZFNMVVdpbVcxOThVX19pMHN3UW1MWHFCVU5jRko5bUI2TVVxckFVUDlMbmo4MVlOYzdwdXdWcW9UYm40RFcxTjduQ1dnQWxpdUhsVmpGTW43YWdRSVpKOTBEcDU5a0NKSHNrVV90aXNtbjRSNTM1SUVXcEsyR20tUUFmTHBtNGF1RHZ4WXhpMVozQWUxTTI1WkJ4UkJCZ1dkaW1Hd2RTSl9seTV0ZDRtSmRYQndoMHd1aFlIX1k1TnZ4clZiQU8yMA?oc=5</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>13-05-2026 12:33 UTC</t>
+          <t>14-05-2026 10:37 UTC</t>
         </is>
       </c>
     </row>
@@ -3136,22 +3136,22 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Biocon Arm Gets Health Canada Nod for Micafungin Injection to Treat Serious Fungal Infections</t>
+          <t>Five Stocks To Buy: ONGC, NTPC Green, Biocon And More | May 14, 2026</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Medical Dialogues</t>
+          <t>NDTV Profit</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxPeXZfaGNUQzUzNU83dVlFaHBFM0NJekhsY29CaTlFRURFNWxKT1RqOVJWSGg1UFFGYzVZc2dTRG9XZnJpcTlud1JuOUlrZnFCbWxYaUNfWTVPQVlwZzZsVXJkbHNoVlUzUmd6ZHVza09GcThSMjkxNGRUOUVhOXpGQkl2TmlndDF1Y3VTOEpEaG1DR3BpYTBVZG9oNV9iVFIzNmo1dm5ES1dKZXVuV1NWcWlWaWRieGtnUWt3d2RvVWp4ZExUcFNsc0IycTZGSkt2Ull6N0IzZjU1Y1lwT3Y0c2dhSdIB6AFBVV95cUxOX0xkRWlxOGlRMks4aEtRdmlheUxNWUxkY2JNeGE2OGNGeWNpdGNtUjFPcXd1SjMxdVJoVzVKUTBLUE91MnZoZmVmOGo1TFFhQzRYSmxHdjRuTFR1NFNyZi12cUt3OC01Z3NsZ2drb0I4LWZXamp1aTFTX21BSTdxaE9wQlUwZjNuYjVNOERRWnhXSkpOS0VQQkJmWTBsdXVnTWg1VHNseGo3anp6MmJNZG1kYVNKdERKNjlFVnBQT21Fa2djUVFVSTJSMGZBRWpjdnpfNFRhNTdIcVpIOUo3WDBzRWluSE55?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNOFVSY2pqS19nUjRUdV9TNWRyNXJodmRjVk4zY0tsTVVldVNJQXdZQkNaWUdGdmNFUWxHY0tBV0tlRVVkQVNKSW04VlR1bzdYZlFSWFhNeWxEMWFmZ1lvb2N6aUNJejRDOVpaMF94dklDNnpjQ1p4ck1RcUI1NnlWZ09nV1VPdFhEVDZBMTNNMDhOaG40bzdyb2F4UG9CMmlmbTBUdjlsX2lROUVuVTR5UEdNQllzX2ZkYlHSAcIBQVVfeXFMTjJwcHd2OE1ONHZmMXRjdlhicjhLS1dDbUlsVmtRUTRpcFdibW5sUjNqSk95Q2lrYmg3LW5aNnZmTnBEYk9FUFpYN1JCNUhPNC1iTzk3UzNrYllFZGJrTl9VMGVxclFybmU2OGtEdkl4cDlwX21KWHNia3oxeE9xMlQ0YkV2c0YzR3lFNTVsbzFtcVNHOXBCR2FxWVJKeWVfZjhXZ25WYm01bTJyWXBoR1psVGI3cXk2OWJCcWVVczdmeGc?oc=5</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>13-05-2026 15:08 UTC</t>
+          <t>14-05-2026 01:36 UTC</t>
         </is>
       </c>
     </row>
@@ -3163,22 +3163,22 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Sun Pharma, Biocon, others: Expert shares view on pharma pack | Daily Calls on BTTV</t>
+          <t>Baker Tilly advises CYGYC Biocon on its sale to WVT Group</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Business Today</t>
+          <t>Capital-Riesgo.es</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxObXFEdl94T2JQM1FKYnhxbnFiVWMtODZQcEtmSVdFUTdhVDVhdkhMc3ZFTG1aNkhTbEZaazYxMG90RGtuRnpJSTUzWExrQXh4TDNrcTY3YWNRWkFFUWJEYVhnQXRDb2h6aXY2TzNBeEJFdzhIUGxXeVZ2WlhCcXF1Y09nWnJsYzgtN0EtYXJiZktaOE52WWVUYnJ5QWEtNVFWci0tZnUyNDhWYzdtSkQzdVh5aEtnbFQta2JfekU4cm9TSFBXd2g2STBRQWVHVmI2UnFsQzZoekZXQzcyRkcw0gHkAUFVX3lxTE5iRFd1X3kxSmhoanVscWplMUt4Skh0b3BLR0tsalRoM2ZzV2NhRnYydXQ4eUlFVmE5RkxqNk4zVnZXT2doMWdldVpsRHZEbmoyaTV4ZTZiRktvcUNvRkVId3hrTmduekZraHc0N3ZBZnkzWHIxcVEtUlJ0QTB3aUlEejBRUV85MDFudnN5S1FxSUtJQVF0WUFtOXdLc3psNkxFUU53YWw0Ti1BUm1NT2VuWk9FZkVDMUpJZE0wTHlCazVVWU8tQ1ZJN3hzMy16d2g4aFg1eUo2Um44VFpkSVpNT1Yxcg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNX2RQRVVOYk5YcERpbHBzb1hpajBaVGl3elRycHp2VDBPUUpXR1hWNUk5allmR0c3YnlwRk1nT1ZlYWd1a04xZmZ5WVpqWkNKSV9GR2VtTWxIVnVsM1NVQ3ktZEF5MWRfVnlQbmFhX1QxMnFrWFpvM2pLVXhQbjVFMkFsOVZBQzhJWC13bXI5MEhmVjVzaDdaOXlKMkE?oc=5</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>13-05-2026 11:47 UTC</t>
+          <t>14-05-2026 05:06 UTC</t>
         </is>
       </c>
     </row>
@@ -3190,22 +3190,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Biocon soars 10% in 3 days, stock nears 52-week high; here's why</t>
+          <t>Biocon Ltd. Upgraded to Hold as Technicals Improve and Financials Show Mixed Signals</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>Markets Mojo</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQcXhjaUNSR1VhUW1TbnBhRk1NZGtqWEZCNU11ZkQ3QWVyaFkzZU84YVMzRDNRdjBHMEgwdF9QSm9oZTR6ZVk0MTJZRXVUTmNHMll6X0N0NW9qOEhMc1Z2aER6S0hxNlhvVnNxMDR5SWRzYW9LdlV3ZFBMMmFtckpLS2lGaTJOVExhZnloS3hfSEhLenpZUFkzVFkxQXFfazlxb3hpaWF4ZlA4bDVyZUZOSElIZEtub1k4STNGODdJcVVhNTdiOTNj0gHMAUFVX3lxTFBoYkdXN2ZDQUpPZFFjaE8xSDhwbV8zdjZTNFcyRk1XVHR1ZWNEbzdZQUlCUlE5UnVLMm8yeXBYZE56X2N5cFB3d0FkLUpXaTBmSUV5MDZBVWNZUFBTSXR5NXFCVHJER2t3bnNfcHViaG50MGdOVldIWS1uZURwNjBKV2Q2d0U3SlRDTWxnZGx4M25wcDFNNHpZdFN2WjVmdW1ERWZrZl82WnJQMG9SSHJtX0xjRXI0MmFFb0FsaHpMelczaGZneHBIdjJuZA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxOV3luVTFHRlQwVVZaUUh3Xy03OXVJRWEyYTZKYVZFV1hxQzNNMEFGZUVzQ2tjZ2lFSThFQnFaVGdhRzhXZXM2alZjakVlWkFaZ2g4VHNXZ0JlUDlnV09JbFdWWWF0Z3RkbUxKUnZYUGdRa3RHLWlkUzF0MHplWmhoMEdYQkVoclpNLS1EN1h0VzB1WFk1UzN1Q0puSE9HTEpMWjJCOFEyWXcyNEYtWktfSHBmMHEyMnJhYzFTTkJraHVvTWxJZWt4cXBMWjlhUXdfMmM3c3RLS3pxZmtkamc?oc=5</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>13-05-2026 08:24 UTC</t>
+          <t>13-05-2026 20:42 UTC</t>
         </is>
       </c>
     </row>
@@ -3217,22 +3217,22 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Biocon Ltd. Technical Momentum Shifts to Mildly Bullish Amid Strong Returns</t>
+          <t>Biocon Arm Gets Health Canada Nod for Micafungin Injection to Treat Serious Fungal Infections</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Markets Mojo</t>
+          <t>Medical Dialogues</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPLW1ETTJ4ODU3dTNhcUlnTmhybjVuSDNfVWU0X2h0NDF6U0tlOHp5WDFMZXpxcVZ6Q1BTM0dyZWNvdXVfb2hONngtb253ZV8zZ3BYekN2OVdPZlJHRWc3NUJYb0p0c3lac3pvYklmUkJFT3BYRGJYLTB3eWJxM0lad1pKRXRkU1FhWkdyWnNuY1dHbWU1eUJVUnRsalQ0dlhGLTVJcHYzcUFfR2NXZFVncDJlOUhrOGUtVTUzZ3VOQ3Y5dkwyQ09KLTI5MHo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxPeXZfaGNUQzUzNU83dVlFaHBFM0NJekhsY29CaTlFRURFNWxKT1RqOVJWSGg1UFFGYzVZc2dTRG9XZnJpcTlud1JuOUlrZnFCbWxYaUNfWTVPQVlwZzZsVXJkbHNoVlUzUmd6ZHVza09GcThSMjkxNGRUOUVhOXpGQkl2TmlndDF1Y3VTOEpEaG1DR3BpYTBVZG9oNV9iVFIzNmo1dm5ES1dKZXVuV1NWcWlWaWRieGtnUWt3d2RvVWp4ZExUcFNsc0IycTZGSkt2Ull6N0IzZjU1Y1lwT3Y0c2dhSdIB6AFBVV95cUxOX0xkRWlxOGlRMks4aEtRdmlheUxNWUxkY2JNeGE2OGNGeWNpdGNtUjFPcXd1SjMxdVJoVzVKUTBLUE91MnZoZmVmOGo1TFFhQzRYSmxHdjRuTFR1NFNyZi12cUt3OC01Z3NsZ2drb0I4LWZXamp1aTFTX21BSTdxaE9wQlUwZjNuYjVNOERRWnhXSkpOS0VQQkJmWTBsdXVnTWg1VHNseGo3anp6MmJNZG1kYVNKdERKNjlFVnBQT21Fa2djUVFVSTJSMGZBRWpjdnpfNFRhNTdIcVpIOUo3WDBzRWluSE55?oc=5</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>13-05-2026 02:31 UTC</t>
+          <t>13-05-2026 15:08 UTC</t>
         </is>
       </c>
     </row>
@@ -3244,22 +3244,22 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Biocon - ​Technical stock picks! 3 shares that could give up to 15% return this May. Do you own any?</t>
+          <t>Biocon Pharma Receives Health Canada Approval for Micafungin for Injection</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>Machine Maker</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxQQ2RRMk1sWkNaUHUyX0M1dXpFQkVGQkZyZ0hoNDZWYmRBQjdNMnF2akJZOFNXOGttbm9uRlVzNnVoWkxPYXZHT0xYNVBHdk15WFdNTUE1clQ2UFUxLUtBRFN6UG5QR3libjg4ZEVuMnU0RzQyV3FJelAwVzhKSDhNbzJDa2xBdjFOSXBBWXJPd0tRQkZqdVdFekNsWjloUWI4SUs0ZTRCSEtLdV9QN2Fsbi05NG1vdDFCOHJpS2JuT1VQZ2dkeG9kS0N2Z0lJYUctb19BdS16dFJ0SmUyUUVTX2Z3UUo2T2QzMGtXd0E4WmFFUjJ3Q0lCcA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOdlRWRnlqYVpJYnRvZzNmNVRzb1pZWnpFRGtvUjA1MTBUaV9NY3JxNUpMdnNyQ1lvVW9LNV8tdHpxTTgzeFotUW14ekEzeTBtaUVYZlNOWllHcjZ2QmtFX2hVa1d6TFZZelZBekoxT3dVbUU0QVNIRzhuV1VMVGd0NmVqN2JwRXZiRlF5ZFFqMXNXWmNNY1lySzZmbXZvdUIzOWhsVllZVmlMUURB?oc=5</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>13-05-2026 05:28 UTC</t>
+          <t>13-05-2026 12:28 UTC</t>
         </is>
       </c>
     </row>
@@ -3271,22 +3271,22 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Biocon Ltd spurts 3.7%, gains for third straight session</t>
+          <t>Biocon Ltd. Technical Momentum Shifts to Mildly Bullish Amid Strong Returns</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>Markets Mojo</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNN214QzZRbDVzemIyeFo1dFNDZ004VnZlQXl1QVp5clN4WHJKUTYyaW9JUUZmWWlkZW1kcGlnU0VycTFlNmdkcnlVMVNyVWtZc3pGWjdMMlB1OHNFeDBlTHJuN0tzaEdGZndPUDlCMXhVd0k3ZFcwaXRGQk5zS0RRcGpPdjBLaVhMTVo4c0lvdzI4UDlwanV0N3RQQmJ3TEJjbUh2bllaQnNad2QxVjA4Smw5Nk82MmJFaE15cDN6NWVXMFRvdzBvU1JSekJ4dDRibFHSAdcBQVVfeXFMTk9OQmUzeHVXbmw1RlFXZmRMUElHZmpad1AwN1ZlOGxxdDVwamZVMUlrLUxWNUpyNE1ueE41djE2Z1hQMkNvSFNScVJ1b0Y3UzM0US1nWW0zYXV6OGlTRUpQMkZJWDdDZ0h3QlJ6bkNiUFRWUkRoVV9qSWdCYmwxY2RiUHljTktKYnpqdTVVUFFiZmViaDY2ZkFoVmJQaVo5UVRQdXItZDUxQ180SUpBZDN2ZHNZd3J6LVFTNkFJa3ptbVJHa1NwZ0JRcWJWSzNLT3Y5andsaXM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPLW1ETTJ4ODU3dTNhcUlnTmhybjVuSDNfVWU0X2h0NDF6U0tlOHp5WDFMZXpxcVZ6Q1BTM0dyZWNvdXVfb2hONngtb253ZV8zZ3BYekN2OVdPZlJHRWc3NUJYb0p0c3lac3pvYklmUkJFT3BYRGJYLTB3eWJxM0lad1pKRXRkU1FhWkdyWnNuY1dHbWU1eUJVUnRsalQ0dlhGLTVJcHYzcUFfR2NXZFVncDJlOUhrOGUtVTUzZ3VOQ3Y5dkwyQ09KLTI5MHo?oc=5</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>13-05-2026 08:01 UTC</t>
+          <t>13-05-2026 20:41 UTC</t>
         </is>
       </c>
     </row>
@@ -3298,76 +3298,76 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Biocon Ltd. Upgraded to Hold as Technicals Improve and Financials Show Mixed Signals</t>
+          <t>Sun Pharma, Biocon, others: Expert shares view on pharma pack | Daily Calls on BTTV</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Markets Mojo</t>
+          <t>Business Today</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxOV3luVTFHRlQwVVZaUUh3Xy03OXVJRWEyYTZKYVZFV1hxQzNNMEFGZUVzQ2tjZ2lFSThFQnFaVGdhRzhXZXM2alZjakVlWkFaZ2g4VHNXZ0JlUDlnV09JbFdWWWF0Z3RkbUxKUnZYUGdRa3RHLWlkUzF0MHplWmhoMEdYQkVoclpNLS1EN1h0VzB1WFk1UzN1Q0puSE9HTEpMWjJCOFEyWXcyNEYtWktfSHBmMHEyMnJhYzFTTkJraHVvTWxJZWt4cXBMWjlhUXdfMmM3c3RLS3pxZmtkamc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxObXFEdl94T2JQM1FKYnhxbnFiVWMtODZQcEtmSVdFUTdhVDVhdkhMc3ZFTG1aNkhTbEZaazYxMG90RGtuRnpJSTUzWExrQXh4TDNrcTY3YWNRWkFFUWJEYVhnQXRDb2h6aXY2TzNBeEJFdzhIUGxXeVZ2WlhCcXF1Y09nWnJsYzgtN0EtYXJiZktaOE52WWVUYnJ5QWEtNVFWci0tZnUyNDhWYzdtSkQzdVh5aEtnbFQta2JfekU4cm9TSFBXd2g2STBRQWVHVmI2UnFsQzZoekZXQzcyRkcw0gHkAUFVX3lxTE5iRFd1X3kxSmhoanVscWplMUt4Skh0b3BLR0tsalRoM2ZzV2NhRnYydXQ4eUlFVmE5RkxqNk4zVnZXT2doMWdldVpsRHZEbmoyaTV4ZTZiRktvcUNvRkVId3hrTmduekZraHc0N3ZBZnkzWHIxcVEtUlJ0QTB3aUlEejBRUV85MDFudnN5S1FxSUtJQVF0WUFtOXdLc3psNkxFUU53YWw0Ti1BUm1NT2VuWk9FZkVDMUpJZE0wTHlCazVVWU8tQ1ZJN3hzMy16d2g4aFg1eUo2Um44VFpkSVpNT1Yxcg?oc=5</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>13-05-2026 03:40 UTC</t>
+          <t>13-05-2026 11:47 UTC</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Biocon, V2 Retail, Balrampur Chini: Stocks to trade— Check target prices, stop loss &amp; more</t>
+          <t>Aurobindo Pharma Ltd soars 1.15%</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Business Today</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxPNkVYbGcwWmRHV05udW1fbkVJVnd1RjdWSGg3eldGcDM5QWNmeDVpSE11WkNyZk5vU3FubWE4S1ZmOVRfbEYxNHpfOTh1ekw4YmVldnNkVmFENmZOVzFCR1RpazE1SDBidnEzaEhRSlJteWVuUzdPZWZSMG5KdVZTQkpqOXJmOFZTX0VBQnZWSWNYRkZ2bUpsRUhzX1VsT3NBOWFOdTB2RXBMaUl1ZDV3MDZDdExjeWloVUFYb3NyWnkzUUhQbGJsSnRweXBVXzNmald5dW9NVEhFVnNRMjljV3ZydFlFQdIB6wFBVV95cUxQSmFwUFZuRk9IY3YzWjhJbHFaZWc1bVNRRzhTNFZCSGtwY3pWX3hSYVhiRjdSMWdvaFZxX3Q5b3F6SnBKMTU1dGpTN1V0X1B6elc4dlNkc3dxRnUyV0lmYnNoX1l0dWNMX1ZZRlpIUzBJSkdtQlZDMGpaVlFPZEFRalRsVi1tbWs4MkRLdy1DbDhGQnVFWjlHamR0aGVGQnhXOC01WkZYeXdxRW9PZEtTb2xfYzhPLVFPVnFTc25YQWl1czBfZW9pcVd4ZkN5cDFKMGo3dGJzRHZLQ0FKR1Qtam5UcEI0X2EwT3VR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPaGdJdUtlMFQ3NG1RMVl3OExzOC1wZG5sRnhPWXBrSzRZRDF4dXpkaHNEd3NpN3JiYlpIaGx4SkVrY2NVbWxJWC1JX29Lel9waFI5WHoxRlJnalM0TDBTODFHT29GS2dSNXAtWExaVEp5akR1RTBTM0NvMW1wZGFMT1N1SmFlMGJUUlpRaHlGQ3J2VlNzeklURC05cjJ6ZlBqUkRoWm9IRUctbm15SDVZdnVvVdIBuAFBVV95cUxQWXBrOTJTZTJ3elJJdlN1TFBWR24wQnBkczctV2wzNGhCUVRNNnBqZXVKT0F4c0VGTGxEbi12c0x2QzdhaHB5Y1F4TVRNeEFyc3REUnpfSkRTZFdYWkdtZU9WTHF0dXk5X2lPaktoUzRkMFJGc1R4ZVJnX1ZldjJXcnBOblhid2dhc2ZsQVJjZDYtZ2VsSGVMUm1YWGRIOWxVY1R3Q3BldFdTUzh1cDlCVjJKa1ZFSGJi?oc=5</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>13-05-2026 03:18 UTC</t>
+          <t>14-05-2026 08:02 UTC</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Trade Spotlight: How should you trade Dabur, Max Financial Services, Anthem Biosciences, Biocon, HDFC...</t>
+          <t>Broad-Based Technical Strength Lifts Aurobindo Pharma Ltd. to 52-Week High of Rs 1525</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Moneycontrol.com</t>
+          <t>Markets Mojo</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgJBVV95cUxQek1WZ20tN3QxTFBENGVOSnd5S2w1eVItODEtMmpHUVhNaWlWc3JkaU1DMXhZOUloRy1UN3VzMVBTWEdwWVFPTHFBcm9ya210U2w1NGktYWItamVMeU9Fd3BpYzUwUy13bVBPYWgtWUlzZ1VRY3ZGYzNBU0dXUkxHX2RxRkdqZkw0Q1Q2MFh0dFZfMEc5VERaYk43dmc5bXVZSmRKcDllZnhTOFBnSHM3LWZ5UHJOVG9HSTB5M1lnMzZvSW01UGJicDNmUWJvbEU5WlUtVGIzcDRhbU8xczZ2eTlpX0R3S1AtSVVXTC11S2RUZ01uQmdVQjZSNV9GbEdmT0VpVmU4dmEzd09CS25tQ2lvQThVQdIBmwJBVV95cUxORHBTbHNXSEJpSi1kSEcyM2JXOXZpdWNhZnA2ZTNjRXJ5NTN2YWRqQ1pobG1FcTZFaldSMTNHaUlDWlZSblZXSjVHVGtaeG5KWHhwTVZyQVRab3JzVGhLblhZSjVfUWk2RXBlSmRiZncwbFRRT2RVS1diZlkwU0k0dzlfZ21Ba0xncTlxd3lrdl9Ddk9NOEZrM0Nfdk9RTDlwZTVIQXRQeV84bGFSZllGLWlsODhac1BZdFpIdEtVUXByZG9WM1N1M1lxMmlTV0pmRUNwdG8wWEdaRWlvcmpuS2tWNkU5RDlWV3lOODluYkpLMTI1dTMwZkgyQmQ4ZFZwUC1Gem5RM21OYXh2bXI5akUyYTRGWHdOdEtn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNeFFZUVFGU3JFSnlKdkExdkFxM0RCYjV4Wk91elFHSVYzbFFRd19MQk9RUmp3M2xrYzVSbzFNS2l5alZqekxRNm1aal8zVFBYSjVsbkN2V1lELVBtRzFXYkNmeWNTbGNyQmJYTlF4UldfSURqQVlEY29Fb1ZNS2IyeEVDbTZxdk56STM1SGlNNXFGand5cG1BdzZTZmVJX1FRYkQzS2FSVGx6dmk0VmRBeWpBaU84VDdFeHNkWEszWWJWRnM?oc=5</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>12-05-2026 20:46 UTC</t>
+          <t>14-05-2026 04:30 UTC</t>
         </is>
       </c>
     </row>
@@ -3379,22 +3379,22 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Pharma Quality Excellence Awards 2026 - Celebration and Conclusion</t>
+          <t>Nifty Pharma Live | NSE Nifty Pharma Index Today - S&amp;P CNX Nifty Pharma</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Siliconindia</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxOcTV3bWhuZ3VaZmRncmFHOENMX1NQaEV5M1phdVc5b25KNGxSTGxOcWl5eW5TaGZBbjBhdndWN1pvY3NualpsUjlpaHpTeG91a3QwWkg1SFZqaUp2SDBzN1h6U3RYTHRBbU9Cc19VOWpKZEVXM19yZXVjLUVheXdpZWFBZkp0LWFCRzFwazllWWpGSTZ4ejZIeG1Odk0tMFlVWERvdWxXNkpCS0YyaUZaQjlIaTlxYVZoZ0RNUE14bGwxdDJnTFhUdQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE1VU0xITWdsWmRfemUyWGEwYXNCYWE3NXBCV2ItNUpndFR5YzFMbDZLY1BwTzlJMU1xWk9xT0tUYXdYQkdrTXVCcll5YVVKbnhpekRMdHhxbFJ2Z2lORk9xYWlzMzdtWW5QYkE3RmZvOFBtcll2eWc?oc=5</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>13-05-2026 14:20 UTC</t>
+          <t>14-05-2026 07:46 UTC</t>
         </is>
       </c>
     </row>
@@ -3406,22 +3406,22 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Mutual Funds Bought Adani Ports, Suzlon, ICICI Bank; Sold RIL, Wipro, Persistent Systems In April</t>
+          <t>Stock picks: Analyst prefer Aurobindo Pharma, Sona BLW, Tata Steel</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>NDTV Profit</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQWThjQ2VEcC1OYlNVaFZEbmE4cEt2NllSRi05YjJSUXBqNkNVX3JGNTJBd0dkQW1FSGk4RkRCbmpFb1dSOFY0MnBXN29RYkpKMnpQUk5oWS1RTHJMYm14X3hPdXZYaTB3QldyWFN5aWFZVW1fRXZJZEhlS3RwZ2NDdkxteUNkZEJLZUdmWHh6MWJ0SWF6em1yX3ZpQXN6NFllazN1a0FzaEltbjFaNmNJR0ZjM05Ja2xVdVhiZzJrTnNKYUktSlZ6NndOV2tIMVJjd1A00gHbAUFVX3lxTE9GQ2EwZXNYdEJJbzJ1Y0FDdGdySDBEMklKTkJwUUZ3YXFGQ2hqNXdicFBjSkFSUzhweS1TQ04yZ2ZKOThsdTBPeXA1MG04UXhwaWp1cUNLMDIxMGtyNng0dlN1dkJVRkFfbVRES3lxUnVkck9zem9BVThjc3AwVFJuSEhFenk5TEhTcl9SX0dnSlpad1FJM0dVSlJzTU05dFF4VERPV2ZJLWtLbEw1S1NQZmxtRC10bjZadE5MM2U3R2xweGFKV2dEZTA1eFdITTA5a1V6UFBhYTQtbw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOTmtpMUR4MENaTFNsUGtQQVpEV3A3X3pESmJBc2dsS2kzeWNlaHd4V3pfTjFhbXNaSHlXUHYxN2JCeGpfTGptUk9hZkY4LUlpazRMQk15RXhLUHFCZ0M1a2Z6dVJNR1pnTFhGR1M1M3ByME1KbUdnUXdfVk9SdDZ4bWt6Z29FakFGMnM5ZDRZVjFMWUprZzBfUzhMeHFCM2s1d0F4dkU0SGFGVXhuLVBIbGE2X25PcFBwVnMyYktWNXdEUnF1VXUyMV9R0gHPAUFVX3lxTE9samtPMzBhdGw2Y1ptc0ViM0Z0Sk96bEl2WEhNbEQ1dlBuQkh2Ti0xYW04SG5PS240RHpMWkZUNXVqSEx5VE45ZG9feXNvb09oc0ZkTEJYM2d3X3VSUE16MG9FYkpKSVdGd3BpRDlvSlg0TlpzY1huYmJrSS13Szh6azlwODFlNXBpVDN2U0w1VWtnUTA1cGhXWFAtTTAwVVRRMjRPV3U5Z3g4eENzRHVKRUcwYU4tZjJzeF9SRktEcTN4TkFKZHRwbzUzS0xiNA?oc=5</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>13-05-2026 09:11 UTC</t>
+          <t>14-05-2026 02:10 UTC</t>
         </is>
       </c>
     </row>
@@ -3433,22 +3433,22 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Pharmaceutical Filling Machines Market Forecast to 2035: Growth Driven by Biologics and Automation - News and Statistics</t>
+          <t>Tilaknagar Industries arm receives govt. approval to commence production of its expanded facility</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>IndexBox</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9wFBVV95cUxNZVVCZG15WHBYYllMY0tYLWJ6Rl9MNXZqZmE1UXdndkNDaXVKWGQtZmxUS3cyYnNVUGZFaFZDNXJiallkMnp5MzlZOWVWcGNjaWZFRHJ0M2huM1dBOTJDNERKSGxhb094cHp2V2pjZWRpdGZOOGhhZkdiUXdBYXBuUTlkNnhuUkdmWjU4aEVYVWI2eDNhMmY1WUFnWmhvTGRHbnVMLUJFdUxRUlpZYTAzYWloZFZrazZobjE2M1JYbXJUY1MyMHBpSkxPYTBpeVZPQ3NOUW5YdzhuUm9Sd2Y2eVNJclJvcWlEM1h6WXR6QzgyZkhfMm1r?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigJBVV95cUxOYXhReTRMakM0cVhZVWVIcEpoNmttelB3V20wblphMFR5OW5PMzJrcld6RVBjN1FsbEV2M0h1WkhSZ09vS2hVdXJ5NXNqS2VEb2N0RHlsWVdsZ182dzVCLWdvQnhpVm5MQm1KdGJlMy1na3p6ZGM0TjhWNmRmaTktTEJvR25kUTdfbXcxXzZ2MDRseDZXUkp0bHUzQ3N2Z1FRUGRaWWZhcmFNVnNnVVVzdHZ0cGNUYmhpVlptQmo0ekRKY0dYRDUza0NxcWlkTWNra2RaN3FWRnctOU1WbF9BdHpheWtpdGxrVWJyQnBEc0ZvaFdCUkQxMFc0WV9vVlRVNXNVOUREWE5Ld9IBjwJBVV95cUxOQWtiUmlZYWpMY0VNX0YzSVpiUHZQMEpadnM0R0ZpbnkySFZnTG5hRmNUcFV3QzJwVmtLYWNVQ25GalJTQlVOWVljTkh6YzFhdFJ4amY5empmZ1o3Y3FpamlyZmF1dTRqb2lpVnJ1Uk5UWGRfYTk3bGlzaEx0Y1VEX3BncEFQRjBIRk1xcFl0RXRxY2dDVkpQeFdjOEpTOS1YWk9USWR6SmNLV1VMYUFCYW10MzJwU1Z5VmpzY1J4MzRYaGFyQXlYbmkzRGUtMkZWLVNhRU5VR1JPT0U4UmxlZTdYWlZZTkhBV1UtQTVlSlpnVmZUaXpLMGtUUE14akQycVBULUZGZzVjTFZ0NWww?oc=5</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>13-05-2026 13:31 UTC</t>
+          <t>14-05-2026 08:02 UTC</t>
         </is>
       </c>
     </row>
@@ -3460,22 +3460,22 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>HSBC Midcap vs SBI Midcap: How did these top funds reshuffle portfolios in April?</t>
+          <t>Pharma Quality Excellence Awards 2026 - Celebration and Conclusion</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Business Today</t>
+          <t>Siliconindia</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxOTTkxOTNjdVlIMXQwN1BxcXkxb0N3X2pMNmlneWNLRGU3eERtTGFtQ3Y5ZTd2RHgtQkZZT2tFSmxOXzBpaGRiRU94U0tNdWF1Qk85Z0VpUm4yQVZfMC1XUlBrRDI2ZTlMbXE0am1LbjFpN0Z4VmhObm9FX0FaN095S1Vaa3NZTFRZUFpDOUpjbGNiV0FVZWJBX0RGM09uYUotNkNOZmpNczdmVHhuS3JJcmppckw2b0o1Z1F1YV9kbEY4aUJreFZHelFXdXRzdU93Q2VSWGpCN3p5cDU1Wnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxOcTV3bWhuZ3VaZmRncmFHOENMX1NQaEV5M1phdVc5b25KNGxSTGxOcWl5eW5TaGZBbjBhdndWN1pvY3NualpsUjlpaHpTeG91a3QwWkg1SFZqaUp2SDBzN1h6U3RYTHRBbU9Cc19VOWpKZEVXM19yZXVjLUVheXdpZWFBZkp0LWFCRzFwazllWWpGSTZ4ejZIeG1Odk0tMFlVWERvdWxXNkpCS0YyaUZaQjlIaTlxYVZoZ0RNUE14bGwxdDJnTFhUdQ?oc=5</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>13-05-2026 03:50 UTC</t>
+          <t>13-05-2026 14:20 UTC</t>
         </is>
       </c>
     </row>
@@ -3487,22 +3487,22 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Abbott India Ltd. Downgraded to Sell Amid Valuation and Quality Concerns</t>
+          <t>Pharma, NBFCs see fresh mutual fund buying in April</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Markets Mojo</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxNWmduRjFKa25xR2R6d1pTdnctNFlZaGdtQTlsSlJfX20zbWhINU1MTFlGTmxJd3V6TTlhU2hRR3lrVlJxV3BQRkRpMk9ZeEFlUmVFMXlEX0t4QzZiWTAwbjJydkRhbnl0MlUxdDdoWWZxaXlHVmpHZ3FidFdmdzk1ODBIek9nTFZNUGp2QUhVNTN5UExyVWNLRVc4YmdlWXg0T2lYZlZtc0FxRnpNSS1OWENwSnpLMGhqUjlBMTBKMWtXbElfeUVXcGxBTlpXUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPUmJxbVZZcHBQbV9aYV9hMndrY3VPamkzdDd6c1ZaVkdWMjQtd2xjbVNqTUZaVUhRZ3lmazRTdlRRdmZqZUtpNktrWDRPRTM5bW5oOU1wSXlrUkhnNEFUa0ZIOGNpMHgxOTByQy1vbTJxTzVWMG5Fem1rdmpIdlRKSl9ZYlBiY1djVnRYNzRYSDhiVFc3Y3psZHZta1FtVzE1SDlIUzgwRkdobmlYajYtUXdwS1ozWnfSAbwBQVVfeXFMTVoxLVBKTWFyN1NobXZYM2JpVS1USFZSNDdMT2MxVDQ0dE50TW4tS0pCTU5ldWF5NElPWVp6S245WF9EdHFoeWFsMmV6TDJvVGdZMnZXWW4xaDdBWU5ZVl93YktjV0hHRXJIM09LbS12d0pUeFAydU5KOGVkdFI0WjhTSTRSQ0o0RmtmN0VuM1JuZkRPdGxkSFhTUkpOcEswbWVYLVhBRjdVekJMNG02M0gzNjRwSFY2ZHoxQTA?oc=5</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>13-05-2026 03:46 UTC</t>
+          <t>14-05-2026 00:59 UTC</t>
         </is>
       </c>
     </row>
@@ -3514,22 +3514,22 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>India Builds Stronger Medicine Surveillance Ecosystem Through IPC Partnerships</t>
+          <t>Technical picks: Asian Paints, Tata Steel among analyst's top picks</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>The Morning Voice</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOVVFzNVpWUDlDZ19iWDhtV296TDNCRzVabEJBZGJQX0VUTXZ4N1R0WDREbUlocDZmMHhCUVVfeV9mSDNmeTkwS3NxRHVOUE1LbVNLejFZUnd0RlN1YW5kTmFLUGZEdVJqLWNmZjhGN3dxb0dXQlY4eFVIdmFiemh1bmxFUHVHNk53YVd5LVhKMFI2WnM4cDJWa3ViRWtlb1BCek1kY1RZTzk5UVk2WG5UYUJHUXg3ZlFy?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxORmpYcndMeGFnSVlEclJTOU1jMlJNMW5Nb0w2dWNiT0swd01Pb0hJbWlRYzNQQzNCN0cyUjFqT0V5S0ZBUUlsd0hNcHotZlRLNVI2QkVXR3NvaDRvN3FTSm9DcFVDUlVMT0pzSWVuSHB4T1RNb19aMzlwMEdyM0hiSHhRdVAyTUtDakdHMXJneTd0WHRrRHdIODFsNVNLVUVNY084RVFmTFBhV09wNHl5XzVPQW5JMDdwcEhjQlZKR0RJRDlJSmczREROT2NtWngzNjNRaC1OdXcwX1owdEV5QnptSkhSX2hTOEhfadIB8gFBVV95cUxNMHRHTVFIS25oRjV5WlNwMnZMYTVxN2pSR3VMdUZtSjhuYjNYcGtiQWZKQWg1aW5CVk9PNFh5QjJjVUNHR2NnWXlPdUszZTZ5aTdMaTZfQ3YxTmRZZFRGWWgwZUUxNnFWMWFJYmJ5cjRzNEFvbTRBS3RyeUxSNEhOV2xpaE9NdG9WUlM3dXYtQ3RRSkJVblR1SVVGVno0U05iZEdOU1l3ODl5ZFJidXlza09scVNzT0VFdnp4cVJjRGQ0UjR2eHNuMHIyWlNRMzM3Tl9IcjF3Zld2cmgzSGVGVkJ3VkZOaHFxaVZkTHczU3Frdw?oc=5</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>12-05-2026 20:40 UTC</t>
+          <t>14-05-2026 03:04 UTC</t>
         </is>
       </c>
     </row>
@@ -3541,22 +3541,22 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>USPTO Must Address The Right Question In Sanofi Case</t>
+          <t>Cipla soars 8% despite disappointing Q4; what's driving pharma stock?</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Law360</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOOXVNaG1LbW5vNF9RUFRaY3R2c2pOaDItZTBITkdtMWJvTXk3WXJka01Ub0h2UkItSnVzdDB4RkpaZDA3MWRmMlcxT0RONkdVcFZCVUMzRk9PSFhHZ2t0bm4zenppclZVdGR4Tm1ubjN5YWEzSV9ucjRfTE92SUZKalYxUE04b1RIMmF0ODNneDgtYXZqbFU40gFWQVVfeXFMT085Tm1naU1zUXJSSnRuSmx1dHJPT01Oa0JGN21zaFdIRHNubFdobE1TUWZrWkRpSlVZaFJoWkJBdGVxd1FRVWtpWWlrdWkzUE5LbFdUWUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPX2gyRVFuYlc2Vm1uZmtmWi1YbXFvUk5aeGJZenJRRDlETmhjMkluZG55c3JTWmlpZlFmS1ZZRkhqM2lTdlJVLVM5VlJWUGpyTEZ2RWZTbjZKWVV3dDZNWXJ6M2Vaa19KYU4xWDUyaDI1LUZudW1DTW9CYWVHZEdjOWp0RnpLUGpXMU41ZjFhaUxqZEprQnNaOWEwLXNBUHp4MWNHeS1oMWlmZGl6UnBQMWxHbXZXZ0ZUQ3hoRXFiaEhzbm43TmdZbmV4TExzZ9IB0wFBVV95cUxQakZOZjgzQWxqR1MxMG84Nnp3ekQ3c1BrWDhsTXJYZG9nYTdyLWNBLWFNR2NYbGhlRTlfcW9vLVVpWGpoQy1DNFVjM0hVT1o4OHMybGdWV090em45R0R6NWdyMlBHUWRUVDAzRGVpcHVrTUxLU2dJbHBOTGZkOTJWcnNxOHRDZF9YNVFDZGYzNXZuTVN4bzhHR2RBSlRyZWFMdmVIZVUzSFk0d3BLSDZHbTNLWTNxWng3Rl83Tm5EazBLb1V4N0FOdGxtZVhGQ0xGQnEw?oc=5</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>12-05-2026 21:51 UTC</t>
+          <t>14-05-2026 04:30 UTC</t>
         </is>
       </c>
     </row>
@@ -3568,22 +3568,22 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Abbott India Ltd: Quality Grade Downgrade Reflects Mixed Business Fundamentals</t>
+          <t>Larsen &amp; Toubro partners with France-based Exail</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Markets Mojo</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNOURORGZ6Q3plczBJd1NjSmZ6X3VwSWRmX3lrQzZaa2l0UVFlM2Q2TkJxQ3FDNTlIcENzekpzWkxEdy05Zy1IUUk4THpnMHdQYV9YU2kwc0VJYVFJbFp2WWdIVk4xdERNUER4UW9INkQ0clJEb29WSVNaMDZxVUhEOVAyUHVYOWs2OVlDWURvNm5TTE0yclVjZ1FrVm5pOU9BX0JtbloyMlNnbWxGb0F6emFUNGJSbzFjSlJZQWFUOWwwaVdzcU9uSzZYQVdHNFZM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOSGx2c1FFeUV6b1dCOXZ1em9YMFFXaTIwTzI4eTJHY29wWUJCc2VqZjBNZC1fWkxYd1NxMUVfQkQ2Vmd6Uk1jcEQwTEVXUUR3WHZacUNWbDBtU3JkbVdqXzNBdnkxR1RDdEdrT2xLeTg4Qm96eTBvbXlPMkM4bG43Umh1QnY5c3JUc2djV0o0V1F5Zms3OWoxNFotUk85OU1sWTczVWllSFhrRjNJTDhXWFlrRTNoU2t0SGRhVVJzLWRVb2hBcy1V0gHMAUFVX3lxTE9YcmFVdEd6YmV0dGh4THNOLU1rd0tJTjZtZHRaRnBNWXpKZUhjR2g4SE5rMXRHR3E0d0pOVVVPeEZIUExqSVZpV3R2dURmTTZTYm9OSThBdTdXeUhTY3JUTVBQTGtJRm5XOEdRNWhjVWdQUDF3RDl1TTdIRDlxXzhCWXhZR1hWRzFkeDh3QWpCU1UzM2JOS0JMOHZNcUIyY2ZJOVhYVDhZdzd0WTBxZVlqR3FzZEpKSkdUZzh0a2JnQ2docTRyd0ZOdVBDRg?oc=5</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>13-05-2026 02:30 UTC</t>
+          <t>14-05-2026 08:02 UTC</t>
         </is>
       </c>
     </row>
@@ -3595,103 +3595,103 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Pharma Stocks Today, May 13: Wockhardt rises 1.97%, Orchid Pharma falls 1.79%, Biocon gains 1.38%</t>
+          <t>NLC India zooms 15%, hits all-time high on posting healthy Q4 results</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Business Upturn</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxNQjF2clp3Zk9zVGpYaHRoWHRSZzh5NnlDRnFmcHQ5V09Bb09kLUliTGZKVHZCZ3QwWENleDM5VUR4XzFCeUhtY1h5UVFMbE12T1paOU01Vlp6QVVNVURuako2M1F4cWN1LVNkNTNVR2ZOcEt0WTlSZlRGaVdJcG9GY2xXWEthSFFjRjFqYVBEUDhjbXROZU1zam1PbGFXX3pEQ0o5T05LOXYwRk1JclZHUFBtWlVzMjVicFFkMmJKVUZab1dtR3pEQ3EwZWdTZF94c1JvYU15S3UxQlU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxQN0FBV0gxcGhwZnBnaHFHYVlCcWVVY0VNV28ydFJsQW5zc3RLZktpVWRlaXE2cU5KWWc5VE9yal9STWxpSWFIbldXdDQxcEpnUGNWQm5TOUZxSEJaUmQ2VGpPQU9Pb0JVbGdrVzBPZnVObGVGY0N3V0JSdl9FcWRtWk5nY1MxYXB2aTdvNjl5M0g4VHBLLV9mc2xBaFhLMFA2NGhrUDRSSVdjLVdRUVhiSVJPZmZpbzRub2xaUDN2aHdwbTVWNDlmb21wS2FIRTNPR1VEZ0hzWjYyQdIB3wFBVV95cUxQaDFSMXV5SGRnbFNwamotN3I3ZVVjRTRJUVZaM2ZpeGx0cWZNWENKNlQ3cUFoc3M0WlJiZklGSVBJZ3o2N0tVUE9ZTTJfd1AxSmhSTkppZV8zQ25kbVhtX2JBN2xJQUkzSTdkZngwaUpOdXdwYkhqR0E2TGxKbDFSZjZEZVI0QjhlUEhJTURxSDJrekt5LWR2S285T1FGRzhyaXppQ3ZjVk80Y2JRM1hxTnB6aVJSX2pYZ0R0NTF5TEdtRnBQRHVoMktqU3Z6akcycE14UDFVaXBmcUZNNGdr?oc=5</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>13-05-2026 04:34 UTC</t>
+          <t>14-05-2026 05:13 UTC</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Zydus Biotech</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Zydus Lifesciences close to buying US oncology drug maker for $100 to 150 million: Sources</t>
+          <t>Gold duty hiked up to 15%: Titan well-placed to weather storm, says Nomura</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAJBVV95cUxOZFMzT1FGWXJqTWV0M3pPdm1tVlpZV0FkdWtXeGFVdXRlSUV6Y0J0QWNaM19ZNXlPdFlFMGR0R0N0cGZWUENZTGNNbUszMHlRQWJaZFhTR2pldzVlQXlLTDZmVkpxY1RhOFBDUEZ5Tjd4TjRwUzBjYmluWW1XYjFDajNuS0UyZzI5OHlwLTdrOVN4VXJsRG1laElHenRLa01EODVXQkZ1RV8zTEE5MDduUDB6S2ZXVmpTUmI1SkFULVNYOEF1QkdzZHgwNHFqQ3d4RUVCY1NhbnVuSEZRaFhKUUxjSml4SlVGMFo4S01NWnkweU9vLTRyUGRsZVMza05XcGV2SElmZFJFNkZkRUd4S1U0ZlnSAZoCQVVfeXFMTjh1N0FyT09CTGVYN1FIQjM0TjZEY1BleU5sZ0w4UkZvdm1XRllieG9HVXgwUG5kRGtkdUgySWRZS19zU1YxZmdPa1BmamhHcmFtVGpjV1ZCRXdCUEhjU0JCQm5zRkJpWS1ERmZZaUExS0Z4SXJDRlczM1NmSlFFZjJ3eWVscWVZMjhCMTVPUmd2cTFhaTBHMjJjVFVNYVVLcVQ4Z1hfMDF6cFBYbmdQNjJqUHF1NU5NQWoyZGJBaXJ4Nk96d0xvRTlxUTV3dWdlZjJxcldDaDRsbENSQ0d1bFhSVzVzYXlTakcxTzJtaXB6WGlEZVYya1RjelVSaDE1RDhoekJmRXpVbUt1eXAxT0dyZG5xYThOQmh3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxPc0tubEZMX2o0MnBRdlZLVmk2STh3TTJYNDJLMTRWYnliQTdOZ3JLUEFDRXEtd2RLQm00VW5hSHI4WTFnQkU2SXJ6N2kwTG9VVUxyMzRzc2w1NkVGTmwyQ2k1S0h6bXE2Q0FRTFVPX0xHOTFUdHpudHpqSmotUmM5Umc4VHljN1N6ejg5Q01sZzd4bzg5VktrdWVUNHBvMk9fVTl6ZkhleW9CcUdzaTVLUmhwU1d3ajNSZzdwVWJNVGF4YS1hdXRzRTdxVXR0d2NyblpDb0RTdzlDNDhKVlJV0gHkAUFVX3lxTE9xTG1COXVwdmh5N1UyeEM3eURQLWladXE3cG9EcXJxV09MQ3JYRnZUQnpkQzRuTkRuQlQyNGttb1RFMkVXcUF6akZvTXliY0VtcGJTSWZiNmZUYXBaUDRacnlleDhTRUhwblUtUzE0NVdYWU54eVhBM1p1RC1vdHlBR0xXZk9DZ2N0NWU5U0NBZU1LcTdsVU1HVTVYVUQybFpFUmpueWdaZE9QNjhTT0VLN01IenlSMk1wdEx3UEpjVHNybnJfRGlwZENXd2tlNHF0MC05bVYyZXBSelpTT3FOT2hWbg?oc=5</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>13-05-2026 12:15 UTC</t>
+          <t>14-05-2026 03:34 UTC</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Zydus Biotech</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Zydus to acquire US cancer drug company Assertio for $166.4 million in all-cash deal</t>
+          <t>Brent seen at $95-115; supply deficit to keep prices elevated: Analyst</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Mint</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPNHo0eXdBbnlfQnpoLWFfbG82aWJ1R2Izb09RX2xsY01RdEdRTEZJb21WaktlMTBMQ3Bualh4cVM5OTFId0F2aGx0a3JDZ0tDQmg4S0xTa0dKRG9iTms2WDBYOFNTMUZuc2VzbU9HZURMNzI5bGx5U2t3Wl9ISFVtMmU3cVBVZURuenpSWXF5bmFxbmtZY0ZsU3ZCSlMxeV9rckd3ZzlBLVBXanlmN1lF0gG0AUFVX3lxTE92MUk0aGVkYWQ2VDFvcG92bmVKUmthUXkyeWV3aGpOeXpYQzkwSFNUMnliUUF1eDB2d1k2Smo3aF9DRm53ZVlvS1NJaTh1LTViV2xWeXVBYWRvenJvQ3JDYnJVTUdKWXAwMGF0U19BU1htN2tydk0tS1psNnpDZm9aWWx5bGE4QW92dTR1aW54SUY3b25ROWRVVGtMRVM3Vm9TU25MQkZIdFJyNENmZzl4RktqVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQTGxtajFRQjhlRm5rOGJvLXZXdW0xZ0Q1Q0lLQ0NDSWNPS0pYZVVoMk9kdl80U0lQZWY2Rk1neGhKSmJzVEJ2S28xdFQzRTVNWTFiSEZFNzF1aUlhZHhLVXVQX0xPaHM0d3R2YVpvQTIyZS0tX2h1dkxOTFlvNnUzT2FwMlBJMDlWdFViOW9EWTBHYjdUd1ZrdTJPb0pWck83YTZIU0VxMWVETGJVUFZJMElMeTk4SW9VaWxQZFZPbFFYMlpJc1FRM0VBVk4xOVXSAdQBQVVfeXFMUEdlRjN0M0w3cks5azY1NThZR3NqMFo3bHFyeE9pSmc5NU54cEl5d0JBR0pEemZvb09Za1haNlFYQnNycmIwMGRKTFBzbF84WHpzS2tQSFhnYjlzQjhGbHo1aHNsUUJfS0ZGZUJwRWVEN3RsanJBYTR4TDM5RlJFTzNYb0puRWZmd1htSWxxbEphZGM3eUFMaEYxeHBndGV3UXRkZ2FUUlZENFE3SHFZREx3U1A2QWRQRXVJLUJ5SkxZSFlYLWxfWkFQZF9iM3RqRTNuVFc?oc=5</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>13-05-2026 16:24 UTC</t>
+          <t>14-05-2026 02:50 UTC</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Zydus Biotech</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Zydus Lifesciences Independent Director Mr. Apurva S. Diwanji Ceases Post Upon Tenure Completion</t>
+          <t>Max Estates unveils Rs 1,200 cr residential project in Gurugram</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxNSkdqRk9TSDBYcTRLRl8zTHYzdFNfQnRBN2hzRHdVWnVDRS1ydzFLOGs5Vjg0RlF6VWtaNGRwR1F1bzUxa0lRMkdNUnFreXFSVlRmbXpxQ0RWYWYtQXp6UHFvX0Nzb3ZNdm9tYmJ4b3oycXlqWHdIM09UcF9ZSHd5TkhJbmdqZ1BDYnhxeTVXdW5fS0JrdF91ai01bk51cXZWb2dpUnJFNWg4V04tTTVyMzVZY2FfT09SMnFhM3o0Y1ZlUXF6QzhqSnRuaVZ0UlZEeFUweHlCa1oyeVdkYWFXcVV6LUlQdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxPeDF1MXpQUENVdVA0TzZfMG9PYnFtM0J6d3VwdlBOWUt4Vkpwckl2QmVkS1BZa2p5aGNwRGs1bEVKWHdzTmM0OExmMTZqRFR4QlpnVEFRR2dHUmg1M2dYd3huZlVQanNLNzBCaWdlOUtoWVY1aDd1Y3N5eENXSkZWZGNPM0FDaEphVXh2ZGhseU95N3FCOWEyVzhjUnFXTFRIdURCQnJUU1BGUkpMc2lkOFRkWW8tejFyV19laUJqZ2l4Umw2SHR0Nmd4M2YzUWVjNjJLdHI5am1CVGhSanfSAeMBQVVfeXFMT2k3eFJEU0hhV21GbUI4Sm50VkhYZVRHYWVXTmhvZnhLVDV2LTJyRTExM2YtN0p4cVZkYjZjMFVyTTBjU1NFQ1VYVFlpTGtrNmpYMV9QUUVDTG5rOEsya0xQcFNVd09sOExET1RDQ3RvdVEwSFZYWC10d01XVm9nREYyREwxdFI3ZEFoaVc2UjQtcnNYY0Jha29Iemx6eE85Yll5bExJbExlVG11SFVKdWZtdFZJWFRGY3NkTjNSbmxwVWh6clY0TG94S0pMcXotUFRUSGVqY2lPcDJ5d25La1I1NE0?oc=5</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>13-05-2026 07:32 UTC</t>
+          <t>14-05-2026 02:34 UTC</t>
         </is>
       </c>
     </row>
@@ -3703,22 +3703,22 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Zydus to Acquire Assertio for $166 Million in Cash After Board Rejects Revised Garda Deal</t>
+          <t>Zydus to buy Assertio for $166.4 million</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>citybiz</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNRUU5UWxmdC0xSHRhMnF1X1J5c0FxSWpLNURHS1FBQy1TZzBwcVUwSXBBVlFaWlNjV2pKUTNSOFRuWkI3RVNxUDZZTDBuZFlObC1KWEhmSkllTk8teFkxWlVMSG10Q014RlJJU2dxeS1BUHRPVHNNNXNkMVZvSldEdjluUnJkY2JpYU5KNTliMExmcUNIeE0yTWI2RS16OHlNVnVNa3dYMjJUbktiSno4bTFXNTI4RWdraURzcUs2WVhTWHhmUnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPUHk3SXJBMDJvWVV6aExfeFVvVzZySGdiR2hLcUhCemRBWkpuajZVWXpUVXZ2dUR4djEzdnhoaFpXRkpNQkd3cFIzUWVnSE1XLU9yNWloM3lGTlRuTk54bXRibmZmN3N5Z3BjTkVwZHhyZVhrX2twa0lUZE82YXJnUTI1RWpSQWNuMWFORFRNNFFQLU0zZm9MTjl6bUJDNmt5eGtaV2FFNHFXbTNtRzN0ZGVxeUE4Ym4yRDJTbmxWZ1JieHh3b21LR09pamPSAdIBQVVfeXFMTXRTZERFeFhRWVMtX3Q2VzhZb1RHb056MVRNSHRSVHJoQ3VFUWJBNG1hNWg4cTdnZ3NyX2ZmeXNHNHl5UkF1SnBqS1AwVWY2dXFKa0hKX0dYWHJmN0NTRUlORDRaSU1EV3JhNkxXZ1VtZzhocVBYbGJnNGgzMWtjeE1lRE41cFRxb2NfMXVHVGs5bHlsTHZaU1FFRUtMcTBhSWpHb1l4R0U1MVVHSDJra2ZZU3ItUGtjc2lsc1FzNWp3T1ZnajgzUHNuTDJYR0pDZTZR?oc=5</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>13-05-2026 12:45 UTC</t>
+          <t>14-05-2026 05:45 UTC</t>
         </is>
       </c>
     </row>
@@ -3730,1357 +3730,1357 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Zydus Lifesciences to Acquire U.S. Oncology Player Assertio in USD 166 Million Deal</t>
+          <t>Zydus Lifesciences Arm to Acquire U.S.-Based Assertio for $166 Mn</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>Digital Health News</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNdU02LWwyd3NFdGNkc1JLUGJURDVhcHpwc1lEbkFuTmZOT2xDY1Q5U3FRNnVKYmlPdGxzM3E2N3c3cVpROWhiWmxmWHlWanlQNE1nNnNhakdsRm10UldNS0xNR1NERjZMRkJ4Mk0zU09JaW5TZ2QtelBDSnZaZkp0NVkxOTdINlNZZ2pCMS13SHFaU3B2dUxVSXItdHFfMWV3UE44aGI1djJwcGhpbG56VjNCS3VOdVM2UHBXSUo1cUJaM3ZDdTNxRlhQUGhHVkU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQeGw5VkxpTUZuLTlJN3NXdmpwSW1JZ3VUZUJZZV9STWpvTlZYYllOOVY2dDA3dXpGckNhQ0RNU1UxZU1NX19ieGF0a0lfcGNnaEZqS0hlWXlQQ2Rqbl80aEcxLW5YZGRRR01ST09UQTFxTHpQZzZWaEQ4eVk2bm1QOU92SmNkQm5KV1ZqMEtNYVRzSHlJcnEwTm5aT0RiUQ?oc=5</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>13-05-2026 16:14 UTC</t>
+          <t>14-05-2026 06:37 UTC</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Zydus Biotech</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Samsung Launches One UI 9 Beta for Galaxy S26 Series Users</t>
+          <t>Zydus Lifesciences acquires Assertio in ₹1,570 crore US expansion push</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>samsung.com</t>
+          <t>domain-b.com</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxOa3ZYNk8xZDA0Y3FCYm9xWTAxdDh4bDIwc3BSdnpNZFVtUWVZaVI1dXdVMGtyVFV0QjZmNmJKb2NmNERPWUlLRHBrUkY0Zkpwa2ZXakhnWFN5SXJxd0txZEFzeVpGMEFMV1NmeEptdDZmUUVwX1EtdUhzdk03TDlWSW00RnpYMnJBZ2ZnRkZsQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOY243Nkt6dWFub0RXMndUQ3RwWTU4OXN3TVFnb1pucTB4RmhVUU9rcmFqNWFQVlBJNF9icHFaclBJZGtlODZEb3NuN3V3N01qNEtlTHBzUVU4VHRoVTBkel8zNU1UUVFTTDc3eEExMmd1bDBuN0JoeDhhSzN3dFN5UmxxSzRqTWJDQ2tSS2MzSmVRRk5SVFJZcTBWX2FyM0Z6dG5aY1c4RdIBpwFBVV95cUxOY243Nkt6dWFub0RXMndUQ3RwWTU4OXN3TVFnb1pucTB4RmhVUU9rcmFqNWFQVlBJNF9icHFaclBJZGtlODZEb3NuN3V3N01qNEtlTHBzUVU4VHRoVTBkel8zNU1UUVFTTDc3eEExMmd1bDBuN0JoeDhhSzN3dFN5UmxxSzRqTWJDQ2tSS2MzSmVRRk5SVFJZcTBWX2FyM0Z6dG5aY1c4RQ?oc=5</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>13-05-2026 15:10 UTC</t>
+          <t>14-05-2026 07:40 UTC</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Zydus Biotech</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Samsung Galaxy A37 5G Phone Price, Specs, Comparison and Reviews (13th May 2026)</t>
+          <t>Zydus Lifesciences shares jump 6% on buyback buzz; co announces $166 mn Assertio acquisition</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Gadgets 360</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE1XRHhlUzc2dTFZV0NtTFExa1JtZzFWTjBGbGRKeFh3Z2Q4d1dzYjdPUEdMVGV5Mk5XMFgzSEh4M2Noa0tfdHBmczgza3lPVEJFQjRKRVViV2RJaWZRLUZCNmptbHpDUlBJMlNtakIybHFpZXYzZDNtNDNn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxNcThUeWRfNVNlWm1vQ1NkMHIzNmo3V0FETk1yYjF0cldWR0lLNVpuZjJEMnhKQldGOG8tTFo5V2pJNEgtNEMwZlA4eEk0N2FjVEY5RnBaN1RTaE1GRzdXTUM3cHltYWxXakFDWWxEQmFOdGI1bzNtQUUxZHFiWWFFSTFkM29JeV9hY2xJejhOTkdBZzJ1elNndmM2YmtidXdTVmtycEFCTlVmdUdtNThjV1Fncld4N3ctMWFqX2NsNjlUcVM2V0ZvYXRnQ0V5Z2Yyc215ZDRVNFdfVEYybXN2aXlSUk5wNWViVjJMS19vbGhCWnZFeWc?oc=5</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>13-05-2026 12:06 UTC</t>
+          <t>14-05-2026 07:49 UTC</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Zydus Biotech</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>’Buy the dip’ in Samsung despite strike fears, says JPMorgan</t>
+          <t>Zydus to acquire US cancer drug company Assertio for $166.4 million in all-cash deal</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Investing.com</t>
+          <t>Mint</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNMXJ3UE5SZ3Rsa0xQcmhQRmljVlF4aDRGVFNlMG5vTEw5UkthTl90bzNIWGQ0Zm1CS0hNNjBIUVROeUcwSmx5SDk4eTlvM09oaS1pNFA1bTh2Ym1rNjAwa20tQW83SFNyZG53MXR2SVpRVDB4amdOcWNSaXlBLTB1Vl94LVVDc1FSUVFEMExwUTlTZVppeFk5Q08xMkhlQkgybGdBVUt0a3NlYUZkM3JmWU5nejE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPNHo0eXdBbnlfQnpoLWFfbG82aWJ1R2Izb09RX2xsY01RdEdRTEZJb21WaktlMTBMQ3Bualh4cVM5OTFId0F2aGx0a3JDZ0tDQmg4S0xTa0dKRG9iTms2WDBYOFNTMUZuc2VzbU9HZURMNzI5bGx5U2t3Wl9ISFVtMmU3cVBVZURuenpSWXF5bmFxbmtZY0ZsU3ZCSlMxeV9rckd3ZzlBLVBXanlmN1lF0gG0AUFVX3lxTE92MUk0aGVkYWQ2VDFvcG92bmVKUmthUXkyeWV3aGpOeXpYQzkwSFNUMnliUUF1eDB2d1k2Smo3aF9DRm53ZVlvS1NJaTh1LTViV2xWeXVBYWRvenJvQ3JDYnJVTUdKWXAwMGF0U19BU1htN2tydk0tS1psNnpDZm9aWWx5bGE4QW92dTR1aW54SUY3b25ROWRVVGtMRVM3Vm9TU25MQkZIdFJyNENmZzl4RktqVQ?oc=5</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>13-05-2026 15:16 UTC</t>
+          <t>13-05-2026 16:24 UTC</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Zydus Biotech</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Samsung Electronics fails to reach deal with union; PM says strike must be averted</t>
+          <t>Zydus Life acquires US-based Assertio for $166 million cash</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>ETHRWorld.com</t>
+          <t>ETPharma.com</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxNZWljbzUzZXd1M2QwdTJaa2RxVEZPRmdEOUtZdnN5ZUMxUFhjWThna3R5em4tX0VCdHBpYkVIcms3dlhNWTBwNFBlYmd3eWx6VUpOeGFwcGhVVEdiclcyZXR5S1hNZTF2eUpzd3VVRG04bndMUHN3cGJjVzB5SnNQNzVzTTJOYl8wLUhGQ21lQTBZQ01kYkh6S051NXZRSk0xMUFKSWFCNXRLUkJjRGpwNG5TUTd6MG5RREg2ZUxqQWNIM2xyUkx3eGgxREhxcWNiWGQ4MTRiVEZoN1VUbExtMGpVR3FySGYyVS1PNUFqS05TcHFqNzNKMHVtSdIBgAJBVV95cUxQbEQ1MzhOUjVSWWxvWW5DV2dXck1nXzZ6bTR0SHM3ZDhwUXlacXVrdkFlSF9UUThjRTJGYzNDZEVDSzhOMWhjMjhXU3F5SV80cDc4Sm8zeGtvOEdZaFREeC1TYWxBZ1ltcEF2MVlKM3QtbDRNU25ldVpkU3pCdUc5a3BMNEcxZ2ZTREpEcFVULTNzZllIZ2QyUEFWMzZuTkVzUTludGszb1BfNXlfV21reF9oYTFEcUs4WDFJTzhkYW9pNmFhMGIzZkcwSHZsaXY3TW1Vd2pPQkE5bFVBZ0c3U3lOaHlGVUpINDNqSGR6ZGZQbEFxYlJWbHBpcDJ0dXJs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxNMWx1QmQ4WEE5bktod0JZR0x4MmdYUWgzUW43ZkZxNl9JZEpFMFdONW9lb0VSLW9JcjA1clJmZGIxZi1LeFJQaFV6YWZlYkdqYU5fYmZfemZxNFlhX25xREtobEQwSF9XMVNSSEZRN2Q0Zjk3XzBDNDVJblJEdmM0VjNBUlB3b21zeXlnMVMxVkIwbkM4NmtKYmFwVWp2M1gxRTdwNE16enhoUGV1a0hlVWNhejl0Nmk3a0JfR2hHLTVLT0V0V0dSSV9TYzZGUjdjWElCLVZJNUdZSzlsdm5z0gHfAUFVX3lxTE0xbHVCZDhYQTluS2h3QllHTHgyZ1hRaDNRbjdmRnE2X0lkSkUwV041b2VvRVItb0lyMDVyUmZkYjFmLUt4UlBoVXphZmViR2phTl9iZl96ZnE0WWFfbnFES2hsRDBIX1cxU1JIRlE3ZDRmOTdfMEM0NUluUkR2YzRWM0FSUHdvbXN5eWcxUzFWQjBuQzg2a0piYXBVanYzWDFFN3A0TXp6eGhQZXVrSGVVY2F6OXQ2aTdrQl9HaEctNUtPRXRXR1JJX1NjNkZSN2NYSUItVkk1R1lLOWx2bnM?oc=5</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>13-05-2026 14:30 UTC</t>
+          <t>14-05-2026 01:39 UTC</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Zydus Biotech</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Samsung begins One UI 9 beta rollout for Galaxy S26 series</t>
+          <t>Zydus Lifesciences acquires US pharma firm Assertio for $166 million</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>t2ONLINE</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNcXhNU3otbS1kRmlESUJCdS1kT0w4VGF2Sk52dXBhRHlHeU5hcGZFRE1ReTM1bkpqaC1QN1lmZmJ0M1lFVTR5MXZYLXViekUyel90elhieVYtRDN5Rk0wckxzZXJtZ3hMSTVyM01ZZURwVi1qenJoaC1aNDE2ZTB2Rlc1SDdKOXFjVWwzMmlLQXVtUUhBZG9Yallyd2pDbU9xWFJz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxNV01pck9FdDV2aWNwS19MZXY2MDZsMS1FU2N0OGlMSzlQT0NRU01UcFBQY25CbGVSbU1zaXhrMC1ZdG5yUXFwRnFtWUV0aktPemVoUUJOWUlEY19XZ1hRZmh6dUJqMmxTMDRTa05tYVlHUDRfb1Z6bm1lZV9BaUZIcDJhRmpTLWlIdDNZZ0pUQ1o2ek1DYmkxeWh6M1dtbTJTNEs1Si0xaWVlRGROVXNHbmFIaEVBU25vcmJBc2hvUVJSXzdBdVJqcU9PTWp6QUliVjJNbzBEc2ZEU0RSRXlPVHljeHlzMTdxNEpGVWpWOVlpaXRGbGM4Z9IB_gFBVV95cUxOZllxcmVCbk1MWjRqS1JxWnRaRDlMdXU4amU3NGMtWURHdjhweUpvWFktSmp5dU90WWFIVUR0YVhBdmxFQ1dRdHRtSjVzeE1va01SNDZ4eGJHRElkY2IxRzJtTFdRQ2FZcFNMVWNMREt4VVIxTDhydEc3ZWM0T1loaUZSUmxucmZMamkzdkZ5dENyajJydm5NbjNMZV8zZVFETVlURDh2SFBYNUNRdlE4VjBnNjNYSEx3emNBMU54blh1blNwaHdIMTNZVlZKXzRnUTEtdkR1U3A1WERUVXNOakRjTWpFSGpMamRDbkJ2WHVOLUtVUGZGZmhVT2k4Zw?oc=5</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>13-05-2026 10:53 UTC</t>
+          <t>13-05-2026 19:52 UTC</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Zydus Biotech</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Samsung Galaxy S26 price drops to lowest, details here</t>
+          <t>Stocks in news: HAL, TMPV, Bharti Airtel, Anant Raj, Zydus Life, Tata Motors</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>India Today</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQTWxHUGNVaGIzZEs5YnVWWXBoMnJzNFdWeDlVYmxSRUV3aW5LckxsdzRvWFdjbU92QmZIak8tT3FKVjRocVRFaVBZWEFiQTlRdmxkTHpUWkJTYXpWZWhRbF9NdGpaNm53M0x3ZkZPT3A5YVFFVmhVcXl0OWFKR1JkdnBsVHduVWY4YmEyR2R5Z1VFYWw3LTVCcmw4Z0dVLVBic1p1Qi0wMnFPRzVxQkRxbjROOWVKX1BfZXRPTHNIMNIBvwFBVV95cUxQTWxHUGNVaGIzZEs5YnVWWXBoMnJzNFdWeDlVYmxSRUV3aW5LckxsdzRvWFdjbU92QmZIak8tT3FKVjRocVRFaVBZWEFiQTlRdmxkTHpUWkJTYXpWZWhRbF9NdGpaNm53M0x3ZkZPT3A5YVFFVmhVcXl0OWFKR1JkdnBsVHduVWY4YmEyR2R5Z1VFYWw3LTVCcmw4Z0dVLVBic1p1Qi0wMnFPRzVxQkRxbjROOWVKX1BfZXRPTHNIMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxOdk1WVHNMQjlaYmxXdVdWSXlGN3pqWWdSbGxvQmFmbzktTVE2eGVrcXRjSTlReVo4c0tyLThvbDJhT3hwT3cwQlV2MHRzTGRRV1U3OTl4Vk5yOGdqYXNnVzZXYmV0M2RmUXV4WnNxYmNTOWtZcVBjcEkzaHFqVF9Wb3dSOWtoMnM3TVA4TTVVOGVrdk5iRFpUUUxqWWRvN3c1cmdrMGxUMzh6YTJuTXZQSFZfdzRyVmx3OGZXaGlTeWQtMXFjNGZ5NlNiTXJ1TnMyTlhLVzBnamYtWHJy0gHiAUFVX3lxTFBOck5QT2V5ajdIdlFxX2kzLVoyeWJUNHI3NThVdHNHVGdmUm5ucW5jMUpFZHRrLTdtWVRKMkVVSWFobXRzNGI3OVhxNUpfZE9YOVlUM3k3NXJTV1B1UGxZWW5rSjFWNC13V1FFMXZkYXpsT2RnQzFGMzR4d3dxYlZFcGxyaElaNy15M2IwZk1pWGdzV29lVnpQNG1Nc0ROSjdRRnRFdUZ0MUt5RzJudmR2OGNwTGpoZ1lMTmlfWUxQY1hRR3RsLTAwZXZZRjlDektFRllBU2ZFT2U4NXZDQ2FwRUE?oc=5</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>13-05-2026 11:20 UTC</t>
+          <t>14-05-2026 01:15 UTC</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Zydus Biotech</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Best TV deal: Save $50 on Samsung 55-Inch Class Crystal TV</t>
+          <t>Zydus Lifesciences close to buying US oncology drug maker for $100 to 150 million: Sources</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Mashable</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTE9DMWphcTlMZElqRkpJVVZiUEFuejFyaDRITDQ0OFI5dHFxQUxFQy16X0xmREN5eWxWT3RXYmVvZzJIdURpWG4wVkFyNjlYM3JQcG1DbE12MHVGajdYV2lVVw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAJBVV95cUxOZFMzT1FGWXJqTWV0M3pPdm1tVlpZV0FkdWtXeGFVdXRlSUV6Y0J0QWNaM19ZNXlPdFlFMGR0R0N0cGZWUENZTGNNbUszMHlRQWJaZFhTR2pldzVlQXlLTDZmVkpxY1RhOFBDUEZ5Tjd4TjRwUzBjYmluWW1XYjFDajNuS0UyZzI5OHlwLTdrOVN4VXJsRG1laElHenRLa01EODVXQkZ1RV8zTEE5MDduUDB6S2ZXVmpTUmI1SkFULVNYOEF1QkdzZHgwNHFqQ3d4RUVCY1NhbnVuSEZRaFhKUUxjSml4SlVGMFo4S01NWnkweU9vLTRyUGRsZVMza05XcGV2SElmZFJFNkZkRUd4S1U0ZlnSAZoCQVVfeXFMTjh1N0FyT09CTGVYN1FIQjM0TjZEY1BleU5sZ0w4UkZvdm1XRllieG9HVXgwUG5kRGtkdUgySWRZS19zU1YxZmdPa1BmamhHcmFtVGpjV1ZCRXdCUEhjU0JCQm5zRkJpWS1ERmZZaUExS0Z4SXJDRlczM1NmSlFFZjJ3eWVscWVZMjhCMTVPUmd2cTFhaTBHMjJjVFVNYVVLcVQ4Z1hfMDF6cFBYbmdQNjJqUHF1NU5NQWoyZGJBaXJ4Nk96d0xvRTlxUTV3dWdlZjJxcldDaDRsbENSQ0d1bFhSVzVzYXlTakcxTzJtaXB6WGlEZVYya1RjelVSaDE1RDhoekJmRXpVbUt1eXAxT0dyZG5xYThOQmh3?oc=5</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>13-05-2026 15:00 UTC</t>
+          <t>13-05-2026 12:15 UTC</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Zydus Biotech</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Samsung Electronics Announces First Quarter 2026 Results</t>
+          <t>Zydus to Acquire Assertio for $166 Million in Cash After Board Rejects Revised Garda Deal</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>samsung.com</t>
+          <t>citybiz</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOWUVwY3RuMVpmN0E2LXdudkFMWjl3VjN6MWp3Vnk4VUUzTnkzdGVRNi0wWXN1MnpRODQ2c0RGWE9Wbjg5Y0RfejdZZUVjZGJGdi1GdDVCdzlzWjBNU0hQbVVtTGJab3lNakR2S1RKSzdOVTVrVDZVV0xoWU45ZFFoVjVZUDdsTTRqai0tVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNRUU5UWxmdC0xSHRhMnF1X1J5c0FxSWpLNURHS1FBQy1TZzBwcVUwSXBBVlFaWlNjV2pKUTNSOFRuWkI3RVNxUDZZTDBuZFlObC1KWEhmSkllTk8teFkxWlVMSG10Q014RlJJU2dxeS1BUHRPVHNNNXNkMVZvSldEdjluUnJkY2JpYU5KNTliMExmcUNIeE0yTWI2RS16OHlNVnVNa3dYMjJUbktiSno4bTFXNTI4RWdraURzcUs2WVhTWHhmUnc?oc=5</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>13-05-2026 08:22 UTC</t>
+          <t>13-05-2026 12:45 UTC</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Zydus Biotech</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Samsung increases Galaxy S26 production target for the second month in a row</t>
+          <t>Owkin, AstraZeneca Expand AI Drug Research Collaboration With New 3-Year Agreement</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>SamMobile</t>
+          <t>Digital Health News</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNUVR1blRQSk5sekppSm80Tmc3a3VtbTh4RWxudFBUQVdoWHFaVk9fMk4zeVBlVVBHTEZraW1zcVNnQWh2dkFEdVNmWmhOMGVGbmpmMWFYNWotUnpfcXc2eHhHNFJPT3BFXy1LeGRjSnlpbDVSaDFFeXN1R0tXSy02ZUQwenoyd0xteEVXa1hZenk4c0RDLVl1MklhSEgtOElmWF9nR3ZnOGE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxOSjJnejREd2FFdF9VT3FjQzA3bFZHd1I5UjVXUkhPYlRvSHlacF8wNGZFWFdKNlVsU0NTVEY0TnliOUxuQklaODAza0Uybkk0THRZQ2kzcHB5ZzROYXdNdkhiY1U4QWptUldGeGVYUkRRWjQxVl9vQlZ5aWc3b2xiTnhxNmE0WGE0ZUQwM3FoOWJWZEktNE00bkUzLXZjRFJzWHNKXzR1Q2RyZUtUaWdIWnB1aGYzQQ?oc=5</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>13-05-2026 14:51 UTC</t>
+          <t>14-05-2026 10:55 UTC</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Zydus Biotech</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Samsung launches One UI 9 Beta, available for S26 series with new AI and accessibility features</t>
+          <t>Agilent &amp; Veeda Lifesciences Strengthen Biopharma Analytics with New Facility</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>India Today</t>
+          <t>Digital Health News</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxNMjVweGxkQmQ4WS1RY3JTT3l5YWZLTjExVzNSMWRBQ3dCLS1nWUVGT2huMjlGMnNaeGtHem10MkFYX05SZldyMEVYSFR1VE1uWTlsMTJNSDNMeGhjMFk3Uk9Dc2lKamlQR2ZUcHRxWFVVSVNVUjlqTV81Nksza0V2Q1dJdW9OVU1rOThRQkx0eU1IdDk0cFF6OUtkTS13RjVHM3BrOWNNWmVfcF9maXlPaEJvWW91THJ3MGo4NndCaV9JRXh6dzFNb3ZSVmtQRTRpMGhYVHFnNDdzS0hOa0hWbzhQRDdQdFlCaWtKM3drV3ZZeVJfRThfctIB-AFBVV95cUxNMjVweGxkQmQ4WS1RY3JTT3l5YWZLTjExVzNSMWRBQ3dCLS1nWUVGT2huMjlGMnNaeGtHem10MkFYX05SZldyMEVYSFR1VE1uWTlsMTJNSDNMeGhjMFk3Uk9Dc2lKamlQR2ZUcHRxWFVVSVNVUjlqTV81Nksza0V2Q1dJdW9OVU1rOThRQkx0eU1IdDk0cFF6OUtkTS13RjVHM3BrOWNNWmVfcF9maXlPaEJvWW91THJ3MGo4NndCaV9JRXh6dzFNb3ZSVmtQRTRpMGhYVHFnNDdzS0hOa0hWbzhQRDdQdFlCaWtKM3drV3ZZeVJfRThfcg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOaTRQVVJzQUM3M094VnB4THY2RFptWnFvQzhrNzBNY1d3aERwa3Rqak9JM3Q2cUFnV3dNODQ4VGhGbFdYVHhOdXl5ZDFQMkxFS3lTMXp5STMzek1uNTdXSXRMTU0yeDVZeWlvMUMtTS1ENEJfQmlueW1ZWUc3MUVsNVBJS0dVWlJyTTRCa2dJa2ZoS3RhQTBoNXBWUEx5WTlIQnRxTVhUR0V1al9oZnc?oc=5</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>13-05-2026 11:52 UTC</t>
+          <t>14-05-2026 08:43 UTC</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Zydus Biotech</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Samsung Galaxy Z Fold 8 Wide Leak Hints at Dual Rear Camera Setup, New Signature Colourway</t>
+          <t>DHN - Sikkim CM Inaugurates Maxwell Hospital in Siliguri</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Gadgets 360</t>
+          <t>Digital Health News</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNbU5QVEFES3hsbWM2OThNMUhtWHh4Z0VBMUlZTnJ4UzgyXzdXLVNOV2VaUFpsNzBseTJKQVFOSVJNMDM0XzBsQ1lWT2dsVk51eDFvWlVHQi1qWkttSmJfUll4eTZGNW9wWU9ibm9WcmFEQXd6OGFYN3FVZmVvcDBocFUwejhVbERaRkxaSDZhZm9ZQVRTUV93bExCTUNjNnhBVXRhV2RoN3hMNjg3YWtyT2pIOWRNT3JpTl9UaERXYXBzeUpzcjBtOdIBzgFBVV95cUxNZUNoWXZaLTNpQktmSi1tU0NCMkhaVmRmdEw2Q1NVb29hWFN5YkkwWGVtWHRjVjF1ajBKcU44YWI4ekFoZmJFMlNiMk1iZTFPcGxsWkRBa09TR0w4ZXB0WGpTOUYtcWlxVHpJR1RMREhPbUhTTXptdS1TbW5HWFpwWUtaVE02M0hVY2ppb0k2YmZfWkc1WEo0Rk9oX01fZjJSRWg0MEpUYXpkOWVOWjZlTWJHTDVZMTVCTzJSUnh2d3hFMDhBaTlmQnpZWDhodw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxQRlBKWnVpSUZOSm5UYUtTVTZvc1U4bXduVnR4LVM4MUtGUVJxTEw5WEhKUWhuMGNya3RTbGhKQW9yNmVYNktEd3VuWTQ4Z0JGTDdFSkZXNVVhU3pMY2h5eHBFbklIUGVxdjkycHVucFBsU1h4R0lqdEZZajR2WHRFUG5rbVBsa0c1aU0tdw?oc=5</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>13-05-2026 12:12 UTC</t>
+          <t>14-05-2026 10:19 UTC</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Zydus Biotech</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Samsung Electronics Named No. 1 in Global Soundbar Sales for 12th Consecutive Yearv</t>
+          <t>Rice University Expands Collaborations with India across AI, Healthcare &amp; Research</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>samsung.com</t>
+          <t>Digital Health News</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNU1NqUE81OTFJVktEbVJ4TTM2R2dIMHVEOVdSVzA1a0ZTcmp0bnd3UGRnUmJnSVMtN0lCVVEyRU1NNWZjcXJmMUNTaHN0TkNtcEpnOEl0NF9tYS16b0JUcjdUQkJyUTh1N3lPZXBFZDltcnBoVVluRkNUTDNPenRLQmVxWWtCM2pRaXY1czNqcVhVQm1xdG5LaFBrRW9RMk1NdS1UU3FHNDVfTDJ5Vnc4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNUVRDbE1CenQ0b0hkdnlVLTJBWHBIRUxoZEtEdEFWcDRBTmZlcEZudG9qZ0tudnJzUl9TMC15UGVaaGVGNlZ5dzhJdC1abGtuZkRYdXBuNU9OUE1xZU01VnhOT2lRU0xqYi03dDFMWnB0Z3NpR01PbnBuWmk2X284dENoc3U0eGppRURaV0YxTWt2VWFXbWtZQk9NelN2cEljcERLb1lWQzAxeDEyS041NklJZw?oc=5</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>13-05-2026 06:55 UTC</t>
+          <t>14-05-2026 10:24 UTC</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Zydus Biotech</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Celltrion Makes Consumer Health Play With Gifrer Acquisition</t>
+          <t>Volo Health Services &amp; Medix Global Partner to Advance Tech-Enabled Corporate Healthcare</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Citeline News &amp; Insights</t>
+          <t>Digital Health News</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9wFBVV95cUxOS1JKRmRmYlRfdjNxWnl3UGhERlQ2T0lieEhRRExsT0l5UXpacW0xdC1pQW5WNVU3UWdIT2poOF9qamtwSGkxdlNTWHJyTE5zX09TcjFVS2R6Z2RkMllHbHVlTElCcjJVSXFUM3JYN19xaGkwV3BaY3Nza0diODRGa1FORVROMUVMZS15SXBDcjFINFU1WTJkYXB1Z3NsQ09mWXMyRFAxelY5X3A4WnpvdTJXdU0tenBid3RPMFZfdldBcHhZT09abHpaU3AtN1BLb2dTajdJNEpxS01xMUZWYVEtc3ZPNTNtLTBmM3FMQVZkd3VLaWRN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxON01oeE5NZFBxRG5uRGMwV3RKRURWNWl1V2pIbHdTU3dsR3ZXX04wRVp0clpyM2ZZWDJSOUYzdG9wdnp0OUdQYm96TXBQOWlPUzBvWkVGSXVLckFwajlLZnRnMmNuc1d5bk1ZbDBrNkNrcVFIR0lyZC1lWkJsRHk4SmZNY3JFdWxmRkhhTkNpZHhPcXllT2t5azQ1U1YzdnFtZFRCZENkd1FXZm9KR1UyelJNLUVnVHRObFpYcg?oc=5</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>13-05-2026 11:16 UTC</t>
+          <t>14-05-2026 09:29 UTC</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Celltrion USA, Inc. announced that it has received $516.1 million in funding from Celltrion, Inc.</t>
+          <t>Samsung Electronics Announces First Quarter 2026 Results</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>marketscreener.com</t>
+          <t>samsung.com</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxOMDV4djNfbWs1M2NoZHptelhHYWN2U21wRXVzLXlXaHZRZFdkYTNNbFlGNkc4dDNMRDg2X0xWYjhVS0pFdThhQU1kdmp2S296Z1J5MXE4TDdReWVLWmp2WHpkLUNndl8wY2FTTDVzaUNTSk0wZVZWSWZLNkdmQ1NZVDJMV3VxZ1B3MU9zcXNRbTk2TDNmYXZLOUY1V0lJT1dyQVl1QWhXcTJnSnR5MWt3cUZKbWdVSlJRRnVXdlZFMnlENzYtaVRWWDNIbjVNWHFvNU05bFR0LXA1RmsySXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOWUVwY3RuMVpmN0E2LXdudkFMWjl3VjN6MWp3Vnk4VUUzTnkzdGVRNi0wWXN1MnpRODQ2c0RGWE9Wbjg5Y0RfejdZZUVjZGJGdi1GdDVCdzlzWjBNU0hQbVVtTGJab3lNakR2S1RKSzdOVTVrVDZVV0xoWU45ZFFoVjVZUDdsTTRqai0tVQ?oc=5</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>13-05-2026 06:51 UTC</t>
+          <t>14-05-2026 08:20 UTC</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Celltrion Makes Dow Jones Sustainability World Index Again</t>
+          <t>Samsung begins Android 17-based OneUI 9 beta testing for Galaxy S26 series</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Businesskorea</t>
+          <t>Deccan Herald</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE5MMTViUWNEaEF4Ync5cnpJNmdOeGQzVkdvOW5uZjZuWWpDVThwRVh3bnp1OERKVmtWbS1EbTRkZXFDa2NSMUFDTVlxMkNlMHd4OGZiU3VkTG1KMWg0R0t6UnpnSFBuY1otbVJPNDJLOEswNU9J?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPbERnM3B0YWJyNl8xRzVlZ1pCTGQwZ3FJX1dBRklob1oyMnJrcUlhMTU2U05ySFAxNjEtU2ZoZXN1UGlSTk1oSVFtbFBrMF9HeTRHZnVtSVJMdW93SzFjdDN4X2NKT1dnOHFXSGQzUDdCaWtiZnVncUFiRnpaQmxCZGVaSU93Y2xBLTZtYWxWdFNuVEdsOEVxVExJZVVQMVB6Y0IyZEZ5YWpkei1vaHZYV0JuYXJoSEY3Z0tpRHF3SQ?oc=5</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>13-05-2026 02:56 UTC</t>
+          <t>14-05-2026 09:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Celltrion secures global ESG top-10% spot for second straight year - CHOSUNBIZ</t>
+          <t>Samsung Electronics urges union to resume talks as strike threat looms</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Chosunbiz</t>
+          <t>Reuters</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQMW9oRFotTHNGd3AzQUN2MDlpZEZWczN4OHVSMy1Oc0p1RUJ0UzNwU0h1cVB6TUo4X05mU1VhU0hSbnBoUnhrY1hwc19USnltNHlsckdHTWVjaG9uTWpYYm8tNGdiSEp4a0xJLXp0MTBOVmtvVFZSd0g2RGxvdGtsLdIBlAFBVV95cUxPU0JsaWRPc0xCNFNsZ0dodl91cEF5TXJ2c3RiVXBJMV9PSzNKcU5OTFNtSnA0RmNXQ2JZem9wYUNvQkJSeEt1ZWVMNmlFQm5ZU0k2SV9NVnZYODN3VzZjd2xtcFdwZFNBS2pFSmY1UElfWG5oWENmdG5rMFVjWGhfNlJXX3lhNTdJLUtmTnlYalYwVEJQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQaThlNEd0YTRNdGhud19mNFZjNGo4eEY5eWxCZkF1VkFQVGRzOWVOWHFRWWpiWFBVVFROZE9GeXo0VjBacTdCRzZybVpzeHpLZDFCamdOcFlNUmV6ejBmeEZ4MzdzdmVTZlhycUxTSU1RRmpZa3lpajNsY3AzcmlJOUVmTDBRcktWWURWR0NSemt3LS1aREJvUmxWcHpXa1JiZlhWUnZFVFNic0RqYXhWWnJ5akJDYXptaUlyczdkYVo?oc=5</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>13-05-2026 07:58 UTC</t>
+          <t>14-05-2026 04:04 UTC</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Celltrion Joins Dow Jones Sustainability World Index for Second Straight Year</t>
+          <t>Samsung Galaxy Z Fold 8, Galaxy Z Flip 8 to Launch With Google’s Gemini Intelligence Features: Report</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Seoul Economic Daily</t>
+          <t>Gadgets 360</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQaXZiNEdZQk81M0dWMnpFc2hRT3JsUjZGUnFMSDhRRkJLSVBiUDNvR3RzenlhN182TUxpZDU2WXBQd3BRRmxiREIxWjlOYzNCZjFpeUh1M0Nnb1VDRW5VWndDVnhteHBaaGx0MXQ3bDMxSnJjcDM2T0pUTklfakg1bVlhQi1CRTJ6R0ZINmVCam44TDZ4OXRNZDZTaVctNmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQRHRhaS1sRmdYLXNLY1o5TktrUjdNaTd6Wkk2WE11cGYyTnVGbjNJV2MtQkRKTTJhaVRjVDlZaTMxTzB4UmtObjA2WDR3OUZ5c2lsSTNvYUk3UFY1Yl9rcnB2Z1h2TU1HZ2V1RGk1bWJuYTctdmVkOV9sWTNjOHVTbGt5QnI2SGdaZnNEN3ZsSkhXVVNXbUNWWGwxNzNldHJCaVl3LW1FRkxzYzAwakZ0dtIBtgFBVV95cUxQVDVxcl9raTVyMThDWXhSNmgtUHVtdnJ5Q0FiNDJhV3Z0SmQtdVNMbVZCeHFJcW1iVDhJcXdJemRSaUs1ZkFJOE1Qak1tOThxakJLQU9vbjNZZ1JJSXV1VUhQNUZpaklFdEdXQjlEbEVFZUpEdkZJX2hYbHNLd0ZVVFR5OVgxdnZnUnVDZVEyNy1MbFFydkVfUHhRWXRVc1JvTkNXcHZtd3dPUEUxT2o5RUo3Si02Zw?oc=5</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>13-05-2026 07:31 UTC</t>
+          <t>14-05-2026 08:44 UTC</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Celltrion Included in Dow Jones Sustainability World Index for Second Consecutive Year</t>
+          <t>Samsung updates Expert RAW app for One UI 9.0</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>아시아경제</t>
+          <t>SamMobile</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE5LTmhTWW1sWFpuckpfdWZudml3TXVLMlFnNWxicWt6TzdEM2FHeUItcmxCZHEyWFU5UDhLYWZNMlhVVEl4TTNoOTd0N2sySXNpeE44RFQzUmdoZ2VPTnNDZjRjNXU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTFBybFN6YTd4NGZJdUNMcy0wbVdFUFhvRlJVMW5TZ2p5cjl6RWt4dVpmbnpyWW1EUzFTMEJDYTNfTWVicUR3VDZWb3RjMEIzNm5uY0w4QllIZDFLTUZXWlF2aWFUNFpSWU5paFFzU3Z2ZFRPdHY2ZURsUXdMa0RYdw?oc=5</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>13-05-2026 01:18 UTC</t>
+          <t>14-05-2026 08:47 UTC</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Celltrion Acquires France’s GIPHAR to Strengthen Position in Substitution Market</t>
+          <t>Samsung Launches One UI 9 Beta For Galaxy S26 Series With Enhanced Creative Tools, Security, And Accessibility</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>알파경제</t>
+          <t>ETV Bharat</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTFBKWjVlOVJMbXpUc1NmNWU3blp5djF2ZjNzbnVocEY0d3FLbTlkdTh1aHVsZmctT1gxMlByUVptY3ZqYzBXZ3Y4eFFRLVlObmpFZmJaY1FRVGRsaTZRVEpXTzdRaGNPZXVBVVhlS1ZR0gFuQVVfeXFMUEpaNWU5UkxtelRzU2Y1ZTduWnl2MXZmM3NudWhwRjR3cUttOWR1OHVodWxmZy1PWDEyUHJRWm1jdmpjMFdndjh4UVEtWU5uakVmYlpjUVFUZGxpNlFUSldPN1FoY09ldUFVWGVLVlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPN0VBOXk5Y2ZROG1obkdsR3lZZ200R3VpRl8ya1h6Q0h2X3V0aVJDM2VGbzVVclVpOXFoLUhSY0VUN3dQNVFONVBmMlF0VF9XM0lvbk8xMEs1bXVfejZ5NDVpUVRwMmJYbTdKdHA5WW9maU9Yckh3LVNJa2p6ZUNiYWhyMXlyb1JCQ3pqM1kxN1JMZXpsU0lSY2ZEdlJOcFFGOTRoZUQ2elRQTWPSAbABQVVfeXFMT3VETl9VOGZ4bHBnME5Sc3FFamlXWkVINEZ4cVhqMFMwUmpiMWJHZFFjT0JUMEpfY3ZPTV9sbHRKaklTNm03MHdlcGJWSGZ1VkdIbFlxazRhRlgwdV9MWTAwWVU0ckJlb2J5U3BIck4xam5hQmItbEZZWmpWN1V2WVBVZ2NNMkdtSVdoeDZ2bmxJX1Y3YVlGd0tCODJKeW9BUkhlRHBIeVBteENUMVgyXy0?oc=5</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>12-05-2026 21:52 UTC</t>
+          <t>14-05-2026 08:27 UTC</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Celltrion Acquires France's Gifrer to Accelerate European Push</t>
+          <t>South Korean shares notch record closing high as Samsung Electronics rallies</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Seoul Economic Daily</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNNnNVTElZclE3aWp4eC14WTRHY2hTVEhvR3JJTEM4OHQ0eHJaOGpnVm5KUVZCQVU5MExrMTNINXN6d2NFR0lyMlpmMjZFMThVLWEtUElFQVpOOWNObVhkQ0F6Vjl5TmZ3a0MxTHFJUUc2RjlfcTlPM2QwenZhVzRsMElOVElZTFlmZ19zZ0xVcDFLS3YtSlg0aXlFT3NfUXM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxQMGJDUXVRSV9ZUGx6djlnNlpYQ1FrTkhZLWpQbndfOUFaTnJkYW1MYXhWSlJMQzN5RlRucTBxUkdrRjVVUWU0WjdsY3lDdHNZd0dFd1FsQ2RyU0UwZExFSFRPaHFXN3ZiZGY2SUM3Y0wxQTJPdGdEWnNTYlliR3lQa1JwdEZRaGVyb2pMdHRwS3pmSTV6TnA0SEhvSm9lNEUyS0hCeTV0bS1MVmlkNVNiRGhWRm12Vkx6LTFVY3ByVmF4WHhYWjdJMkxOQ1hRMEktS18zSWJNVVRWMVFMNW93?oc=5</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>12-05-2026 22:02 UTC</t>
+          <t>14-05-2026 06:53 UTC</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Founders exit as Seo brothers steer South Korea’s Celltrion toward sole-CEO shift and drug expansion - CHOSUNBIZ</t>
+          <t>Will Samsung utilize AMOLEDs produced by BOE for its Galaxy S27 phone basic model?</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Chosunbiz</t>
+          <t>OLED-Info</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQV01CMmxTeFY4UkhCWVJzd284bVUyMl94NGdVUlRGRDlzNV9EZHlHNzMtMmVXXzdnMzZIYTJsdlRpMnVEakpsX0F3WGg1SEt6TUVCc25Eczh5c0VkMjlhVEtBNFBsT1pUMThzemFTTE5oRURlZzVNNVB6V3J6WlRKdtIBlAFBVV95cUxPVzRmUFV1VnhTVXpYTGljc1NqLXUxOWdoNDNwVTg2bHJkZm1JLWhOQnIyQlFJdGhiRU9FZmQ0WVo4RXFBZ09HWEFScFg3QTlvTTI0cE1MNlZ1dWtfNG1lU1F2YWtnZnJMTWFkLTVSNWhOVks4bTh1YXJaUFM4OGFoLXM3SDdQenl5aU5ma3VCTWpyajZy?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPY3hkNW1iVDRBcGlBQ1U0TWg3cmY0bzFFMXJOTkpSV1REV3JNRy1RYWxHT0cycUhFWmc2S3BFMGUzS01iMHhGZlE1QXZReFY2bXpSbjduUWhhRThhaldhVXYxNWdKQThpN181c3VueU1YS21fSkJwb09lM0hzRFBHdUFXZUhIcVFwTzVSXzRic1Q2RlNRV2ozX0ZsUnQyRUllOGc?oc=5</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>12-05-2026 21:01 UTC</t>
+          <t>14-05-2026 07:44 UTC</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Singer Yu Yeol confronts canceled lung transplants after mother's death</t>
+          <t>Samsung Galaxy Book4 with Intel Core i7, 16GB RAM drops below Rs 60,000 during Flipkart sale</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Chosunbiz</t>
+          <t>Moneycontrol.com</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNVHZmazNzTVFYY09tSDJEMVlZeHFDNkEzSFlZV29EWTJqNGYzU1lra0RPVG9BdkJ1cDh0Zlp4dXBrZ1NtVDVlN1JyRkRHNFlTRzA3akc5TEcxSWpTUlFhTXNmemc3a0Z1WGZXakUyWGxQN3A3d3NoeUZueEo1aVluNmNrc25Zdm5ORExVYlkxS2ludWRnTHZZSlNGM2M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxPdS1ITVBlXzRLN29GVTlxY2xzVnBhY1BBNklNRFVWOGJNNXNrQXBCS0h3TnJVbnZld211Vmo2ODdlMVZheFpHTWtZRFhHdGc1dm5MRTc1X2dndi1hS2pDUTVEeThTUmVxeTZLSkVTOHFERElzenFPOXpqUEFBcUl2ZVpiUjd1MEVITW5jMExyNDQ1SmtOVHZMSVdEbFRmZW9NVU93V0lzQmF4RnJrSXJWUTJKZ1FScWliSGJiOG0xWGI0MDVxSHJnME1RNVlMaTBRLVlZZU1HRXZSUHpXaUxjeUZrWVlXbTc30gHuAUFVX3lxTFBQcFBJRGlHUlkwYWU1ZncxdWlWR2pZN3VwY2NkSDJuMngwcld0cVBVWHk3WVNPVW90UnFob050V3cwUEFPbVhZamo4STVWa1h0SkItTnZ3OGxCdWtUWDNiMFdaTmNveHREXzdHdEFYcGpkWS1KY0h1ZnhsTUF2cU90U3otcUEzSElCQ0hkM1Fnc3ZYOFAyZ2Z1R1d3UWpYVzZRV09DaVN3Skx1VGlJaGFrMFlUbkUwaHJEblNJMldGdVpVcnh5NXVGQW9ITy1WZ0lVWDRjTVRNa3MwN3IwZEhUS1dwN0k1QjZTTXNTNXc?oc=5</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>13-05-2026 13:29 UTC</t>
+          <t>14-05-2026 04:28 UTC</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Energy surge drives US producer prices to biggest gain since 2022 - CHOSUNBIZ</t>
+          <t>Samsung Android 17 Update: The One UI 9 Eligible Devices list</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Chosunbiz</t>
+          <t>Nokiamob</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxORk5kVEJDUDQtSmJpVjA2S3B5X2Rkb09LZVBqbVdfVzh5bmlSR21URzFBdkV1bXplS1VuMjFhOG1xY0JMMWtFb3I0T3VKQm9pYlRZa2hiMVdEdjd2YW56S0k4Y1poRnhuM0VKX3BsT2ZETzNIcHN1cTF0YkFwOUtLaDl5WEVJNWdhc3FFQVoyTUprZlRsLTl4T2dMNTLSAZwBQVVfeXFMTkZOZFRCQ1A0LUpiaVYwNktweV9kZG9PS2VQam1XX1c4eW5pUkdtVEcxQXZFdW16ZUtVbjIxYThtcWNCTDFrRW9yNE91SkJvaWJUWWtoYjFXRHY3dmFuektJOGNaaEZ4bjNFSl9wbE9mRE8zSHBzdXExdGJBcDlLS2g5eVhFSTVnYXNxRUFaMk1Ka2ZUbC05eE9nTDUy?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPQUFFakNoVWx4UGpvcHVfWXowS1REUFdBVG9kUEJyWXFzTHNUU2RLOFJfQ1phWmdQRGQ1ekExa2JhQ2hnUkFQLTBtSlVQQlRzWURsbUMwQkllako4M3dHdzIwZWhxVUlCT1ZxRTdhM0hkNnY1Tm9zdjA0WEg5MnJpUEJfRlVOdFFmeWNaajBJTkVoZVpTak5tSHZXRlplWEF6TG10SGhTUTB1RXVT?oc=5</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>13-05-2026 13:21 UTC</t>
+          <t>14-05-2026 06:43 UTC</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Singer Yoo Yeol credits South Korean donor father after surviving cardiac arrest</t>
+          <t>Apple iPhone Sales Spike, Courtesy iPhone 17, Outpace Overall US Market</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Chosunbiz</t>
+          <t>Esquire India</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPZkxERGc2ZzFYc1kyMEpHYldzLXd4VEl4UjZ3ZXZUSzVFSEtHU2lxU1NDRE5RSGRLYW1Zd00yUVVnckNoaHE1YnNpRjNGTXRKak9ITWhQTm5pT3lIRnVjZmZSMFNIOFotM2VSZWlGTXVNVWVUOHpFYUc2NXpDNTc3Q19EdTJUQU5uMDhSRjQ4V2NNTDJBX1E5Y3FtUU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPOGNieFNZOUpBblQ0Q3g5M3o2XzExRE9kVmZ6WW8xeWVCZ0ppdkVHY21saEstX0VkS0NWYjJEMXRXSHlGcnFPRFFpR0t6M3g3S25WLVZxUDBkNE9XMTVBend0MzBJWFE2bzJibVZWRFRDSmdDVkhGeEFncFVuZ0JCc3NUbGdsM2E2ZlFUYThfWHQwWkM1WGxmT21HaE5ocXlzTnNjelQ0Q2RnQXM2NFRrLW82em1vRFMtVGdaeU1MMNIBzAFBVV95cUxPME9tN3A2WVF3d2RNU2otZU1WUm5RVWcxaG5ELTF2RVp0RUdxdVJzTjFFZjhmV3Y0cG50b2FQZmFKMW5GSV9XQTY2UnBQaTFNcUo2Vm8tRFQtQUkwX0dpajV1TkltY0VnLURSS1lQeTJ6aXdZVjdteWlIaV9YMDBoTDFwTHM0Z2hmTzg1VC0xOWZuT0d5ekxRSHdVRmNZNGFWYUc4SzcwTm5uVnBKU0hQcnhjTUktX1Y5TUozMjlkZFpJcXFLU3BEVHJsMmo?oc=5</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>13-05-2026 13:42 UTC</t>
+          <t>14-05-2026 09:53 UTC</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>K League establishes IP protection center to curb fake uniforms and unofficial goods - CHOSUNBIZ</t>
+          <t>Samsung exits world's largest TV market, China</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Chosunbiz</t>
+          <t>FlatpanelsHD</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOVzgzQ0l4eVcyRFctZ3VkWllvVlFqTnZod0ZYLWpsN3RLN0diS3FCRlJfam5JRkFjWlY3SGtKRmJqeU9XMFhxQlRfSFJIRlFQN01jT2JoNV9qT1NEaGtnbm8yTFNhdDZvaXo3YlpYbWludHRTVEtOeFhyME9Yd3RTa0lBcUpTSlJlc1VKLUlpZXptbEXSAZMBQVVfeXFMTlc4M0NJeHlXMkRXLWd1ZFpZb1ZRak52aHdGWC1qbDd0SzdHYktxQkZSX2puSUZBY1pWN0hrSkZianlPVzBYcUJUX0hSSEZRUDdNY09iaDVfak9TRGhrZ25vMkxTYXQ2b2l6N2JaWG1pbnR0U1RLTnhYcjBPWHd0U2tJQXFKU0pSZXNVSi1JaWV6bWxF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE04dEd3UnFhSHh1YXRTZ0lHSkN4bVM3MG1BYk42MWp3SW9qdmdPekJHWU1TZkRJUVRHMWpuQWFfUlJCWXo4MU5SQUJtRTdNaFB3TlJEUEtmVFdBWnRzVTY3cnNiQUd0MnNNUTZhNjctcXphQllKNTB6RFV3?oc=5</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>13-05-2026 04:14 UTC</t>
+          <t>14-05-2026 07:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Nam Neung-mi defends husband after 8 billion won scam, says children resented him - CHOSUNBIZ</t>
+          <t>Samsung Launches Samsung AI Week 2026 for AI-Powered Living</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Chosunbiz</t>
+          <t>samsung.com</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPZTVWdy1OSWUzSnBja214aTR1X0NRRUI2TU5Lc3B1cjdXUVplTFhyaTVHZnJ3MV9lMzg5VVRqVzRQQWhIWF9VbVlZLWY2c3lLT3FDTnQ3TzJQZUtBMS1OVVpNQmNtc0ViM0JkYXJZb3A5WVJKS1psT3RtUmkwOW8zT1drenZEYk1HdmdLM19WZm1nUHNBNjhKYzNzbFjSAZwBQVVfeXFMT2U1VnctTkllM0pwY2tteGk0dV9DUUVCNk1OS3NwdXI3V1FaZUxYcmk1R2ZydzFfZTM4OVVUalc0UEFoSFhfVW1ZWS1mNnN5S09xQ050N08yUGVLQTEtTlVaTUJjbXNFYjNCZGFyWW9wOVlSSktabE90bVJpMDlvM09Xa3p2RGJNR3ZnSzNfVmZtZ1BzQTY4SmMzc2xY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQZ1hPUXdVcTd0Z09TTVhiX0NMdjJtUmJSbkhONHI1QVJwUFQzSGtYbVUyM0Zkck9NLVV4cEpqaXNSTTR0S2Jjd3NXZklHNzhueC1iU3ZZUXVhQW5kMVVzNDBBamVIUExNbHlBbmJIa2VLX2RjSXFuNnFXcEJ0QW9wWUM5MUlWanYyMGtIS1RTMmxTdDR4Q2c?oc=5</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>13-05-2026 13:28 UTC</t>
+          <t>14-05-2026 00:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>SeeYa previews full album with urban-styled teaser for title track Stay - CHOSUNBIZ</t>
+          <t>Samsung Galaxy Buds Able: Clip-style open earbuds are likely on the horizon</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Chosunbiz</t>
+          <t>Mashable</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQZU4yeWwyNzJGVnRkQkY5dzZqTF9PTVBiaTloMWVfU3RQX2xnbHZJVzF4NERZMW81VDhDclN5S3k4NVVickVwd3FUb2J4dEV0WHo1VTdjc1F2QzFoVUlRSWZicTZ5SHFsOThuSjlKZ25Tcy15dDVQY1dWS0dFdE0yMGlNbmtqejZnLW95Mko1RGtZRjl6eXlBRkREZlHSAZwBQVVfeXFMUGVOMnlsMjcyRlZ0ZEJGOXc2akxfT01QYmk5aDFlX1N0UF9sZ2x2SVcxeDREWTFvNVQ4Q3JTeUt5ODVVYnJFcHdxVG9ieHRFdFh6NVU3Y3NRdkMxaFVJUUlmYnE2eUhxbDk4bko5SmduU3MteXQ1UGNXVktHRXRNMjBpTW5rano2Zy1veTJKNURrWUY5enl5QUZERGZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE1CY2NCR09oTy0xbE5xcnFXTHJPZ2tTR1ZZTlNGWW83NTktWDlBamhmZ1ZsRmh6bFlPekNjZ25UZjhHWElKQXRGOEkzaUxpbUhra01qTEdkUlk0a0kzNkY3UXRqY2VCMWx1T2VyLTZXdmFsN3ctRDJfYUk3WQ?oc=5</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>13-05-2026 04:28 UTC</t>
+          <t>14-05-2026 01:21 UTC</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Prestige Biopharma</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Onesource Pharma FY26: ₹20 Cr Standalone Profit, ₹67 Cr Group Loss</t>
+          <t>Analysts grow more bullish on Celltrion as margin expansion gains traction</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Whalesbook</t>
+          <t>koreabiomed.com</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwJBVV95cUxPMjB5S0luZUdqcUtwdVpxZVFjSDRkcEpiczRhd1N0VnBKRURnT3dER2VPWTZYbVAxS3FmcE4teG1mOHNDcXpEX0txVGJpOGVLRURjTVlFYXFSRmhScF9uVHAxZzNGQjhjM3lRNzFSWnFxSUFMTzYzRHhJSVZIV1VpYUxRaEJNekZJYjdwckt2SFhmalYwWHgyVVlLcWdyY3B6UzRnalg5TjFFVmpQVF9rbE5pTFpOOVFjQWpSQlNNd0EzYnY5QjFMTEhBSG8wZkZFYlBob1hFcEZrcnV5RDZqVEVmdXFxNHBBM2FmZ0E1UG1KSGdHbWkyUXVSb3ZJWFJ5b1pZZFA1ZWZoZnM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE0yQ0dibnJ6cVIzOWJvdDZmTG0xZ05PQ0dBMjB6UXR4dklIQzdwQVFTWVlLOTZxaHBfcFl5em04bXFlWGJwd2l0VTBTZjZzYnJYTWNxbkZSd2k4QmlydGxfbXlQR2ZEQlVjMUN4MWZ30gFyQVVfeXFMUENMM19meXJDWFNOaUVRTjFMOURncHBkUU1NLWUyWlQ1WGd3N01xV1JYeHgzZ1NYR2RoY0RwWmIzOUE2WTExM3ZneHlOYjZUd2RxQzJMMXJNd2ZhOF9sSGk1SG9RMU1ycGVPdkhTOXNjWGVR?oc=5</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>13-05-2026 08:04 UTC</t>
+          <t>14-05-2026 00:08 UTC</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo's Antibody-Drug Conjugate Platform Shines but Faces Increasing Competition</t>
+          <t>Celltrion Inc stock (KR7068270008): US biosimilar launch and facility acquisition</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Morningstar</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxQWUl5NzZZLVF1VVpSWm9XQWRRTlJqVENBNG8tQUI2OGJHYzJJMy1ZU1J2Y0xTcXhlRm54NW1JaHg1a0l1cTZZY2w5VXhCWHhpZFMwcVBIZkEwV2pvc21ieTJyV1VwbHRlWkt4MjdaMlN5TzhJUVBfYXVmR0hycVhVQU9wWTBTNGNxdUhpSmh6NXRiZlNyel80aHBhWEdERVN6RlVYQjk2SnZGZVplTmRkOGFmY21HZUg1Y0dHejVYWEZ3enVGWjdZcU5TWnJpMmMzbk1NYy14VQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQak1zS2RSWk16TTlwcHRPUDdkQnhWXzRJc1JVbTNyRUM0SmdvNUhQWEs3Mno3RU9YenRKc0ZoS01sbHNzc2JlZnVSMk11ZEtQM3JJMm55dzBKR3ZRSFBYNEtROXhpQjFCMGRET1ZpNG9RODc5RG5ka3R4dEd5MVBlZ3JzcmhTQVM1R1RQcERqRjE4WHhjWXVOX21GU2FkMEw1VVZyNGZNNEg4bzhETU0xd2FfMjJ5Y0xOTFdldHNkSkFSRjA?oc=5</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>13-05-2026 06:05 UTC</t>
+          <t>14-05-2026 07:44 UTC</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo Corrects FY2025 Presentation Materials Without Changing Financial Results</t>
+          <t>Celltrion Widens Europe Share, Eyes Profit Beat</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>Businesskorea</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxNcnJtZ0hKU3ZRbjFvaGotT1lJdXRhQzZ5aUdlbGdBRkxOYXZZdzZ0UXBIS19kS2tGTGVPd09TckVCcVVfRjVEanN3RjVGd3lCMnh5SWxSeWg4TkMyX3pRLUJXUjN5bm00czhCMHV1ODVKbnM3STBOdTJWdnlXMlNnZTUzZTh5WEc2QVMzOG1NU3pvYWIzSkVndS1NbmNLLXlkRzdmaTZucHZpem8tUmRXdFd2d2xDREQ4Q0x2aUFDaWR0WnNTSW9nZi1ETmJfcWxuMUo4WmY2dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTFBBanNBdGhOVVc5eUc2MjFERXNscGdMakdsc0tRZnVVdXhhN1h2YVRGX3RnYWtqN3BTdGJNelkzZkdUVi1hSllndmdRekJUYmtPOW5PSUw1TWRQU0ZrUzdacFNMWFJZOV9QN0pfV3l5VGxJYTJl?oc=5</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>13-05-2026 10:08 UTC</t>
+          <t>14-05-2026 02:49 UTC</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>AstraZeneca plc stock (GB0009895292): Global pharma leader with strong oncology pipeline</t>
+          <t>Biosimilars Market is expected to Hit US$ 99.3 Billion by 2033 |</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>openPR.com</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQM3lQQ2V2M1dZdkd6M2FWOHhES1I5S1o0WWtIai1SSnFiZ0FBaFQxdkN2azE5MFAxQTRwcDZkTmxnckRpQnBiSE5pQjh4SnRSMGV4MmY1RWxzNzlUUlJQUWhWbU1KQXVqSlYtNi11SmhRUVpfOVgyc29sdnNrOFA5NFlzX0gzVHpyRHhuRlNEMlRLdV9xX1JDdS1iMlJfQ0FETU5CSlpWZVQ4ZkhvT3M4bU1NbTNlUUc0dV9NY0RSd3c3ODZp?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNWWlNWThXLUJGWjBQRVlJRExjeUlDWTB1RTlheG5WUHpPY21QN1RtSVBiNmpDdjd6RUhmX1pmQjRiYm1KTFdKenBUTUw2Y3RZbG50MENSTkIwR2JILXdRejRLZTE3TkliVzdrVHllLWpxU2tLNDJ4TTJ5bkU5MW80Z2ZXRWF3akFZSFBiTFdtZFUtN2ZieTd3ajNSaHlsZw?oc=5</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>13-05-2026 16:44 UTC</t>
+          <t>14-05-2026 10:01 UTC</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Thiel-Backed Varda to Take Drugs to Space for Microgravity Test</t>
+          <t>Celltrion gains 70% Europe infliximab share as SC formulations surge - CHOSUNBIZ</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Bloomberg.com</t>
+          <t>Chosunbiz</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOWnFXOC1qdVI1NDNHNkNlay05TkxoU1l0ekI4MEJaajJEcU14bUc5NnNyQy1Na2tEdHVlNFNDRUN6bHpGcFhsazgzS3QzR1prcFc3SEVvemIzb1NDWjA5ZG9kQnlWUFhNTDBEMGV2akk2S2s1bjIzQVdsOFAtRVpOQVlid29hZWdHMFE1Y3drWlVHQ3R2VXVXamo4VFpRMGRTdEIwYzdjXzUxektSTl9KeGZELXFmTE1BdGI0MHVwVXdhNlhUZU5iWWFKd211Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNVGRZcDRheFB2ODlMVDJWc0xINXE3bjBhRGZDYWZqZzdsbkZBbjl6cE9qR0QxR3VTVl96RnZtZ2lrbmgwTGJ6aHVSR1V3WTc0NVJYbnozUFQ3aHN1b2x2dDVFUU44dmljMVZBcG5ZY09BczZQcTlrVUhHRC0zRFllZtIBlAFBVV95cUxPQzB5ME94VGhaOXlpTk9jVW5Geno2dlZSSWNOMTZ6T1hJR2pHamNWT21CU0Nzb0lVMldNZ09yY1liVFprV3F6ZjZzS0VFaEFVSjRERjVhUHhZUVNmc1FPTkxsSlNKMDItQ0VoQ2kwR0VXcXR2bi1iTUZCWkpENU5VTXh4TFBLSzA1M2VnRjNfck5MS1RX?oc=5</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>13-05-2026 09:00 UTC</t>
+          <t>14-05-2026 00:37 UTC</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Breast Cancer Treatment Market (2025-2033) | Chemotherapy,</t>
+          <t>Celltrion Maintains 70% Combined Market Share for Remsima in Europe... Growth Continues Across New and Existing Product Lines</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>openPR.com</t>
+          <t>아시아경제</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOVjRhS3FzU0tiRVhtTmZweTBzM2s0dVRHY0RwZDduRGhKT0JIanNZWUdMUlBSSXdOamxoTzBZZ1QxbXN5ZEE4T3lzT2MzZnJHRGZteHFYbXhvbmMxbHREa1UwdFBTNXFzNkxFblc2SlBaZk9zXzdOSzVSd2g2RG84REdRZ1ZsNU81SXFiZmkwbV9TY28?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE15b1VjaGRENHJOaVpyc0ozaDhwbTdJbGl1Q3FnQnBpVjFNbE1ET3p1YTNhcS1EeTk1QmlBTi1yZ1dNSFZtNHJ2MU9NQzRZZW5DOHRIZUJDWks3NkhuamlWNDFhenVSMVhieXBMN0VSUlpqRDg?oc=5</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>13-05-2026 10:36 UTC</t>
+          <t>13-05-2026 23:07 UTC</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Elabscience® Launches Self-Developed PolyHRP-Streptavidin Conjugate for Low-Abundance Biomarker Detection in ELISA</t>
+          <t>Celltrion Captures 70% of Europe's Infliximab Market with Remsima</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Thailand Business News</t>
+          <t>Seoul Economic Daily</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxNREU3R2theVR1QzNzZG1haUJZXzFjYjRNQl85Z3NJRVNNaENseVdQQnU0TEpKZmJId2hDV2JVTHBNNUplVFZaZW9iTk9GbHRhLVRWUi0xR0ZnUk9EYnE5cVlKckFXOXh1SlNfYm1kekJvbURySHI5NGU4MGRHSmNrWVJvWlhMSnBBYkRuMnFfS2UzRHl6VjdwQXFMbDY3bGJ3M3pQdjNLQkFscV9uQXVUb1N5WmdNbG1LdFFndzJ1UXFzM3BORHpoNHpKTkdTX2VUMnBJWmU0NFh6LWFqV2NhZFQyUUZyV1h0cDR5ODBTSTZHUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQN2JWTzhaLW5jdjZSMGIwenA3ZUo1OGxoM3QxRW1ldkltbzlIUnlVd1BLNXA0cExjVFdZV0dGUFc1WW90ZEtfUEo2ZFV1Y2FvWGlsSnp6WVJ1a2NlbEIweHY5VzJSLUtKMi16RUFSVGlMN2IxTzdaSmRjOXBsR1ZkYlFxY0tkVVNDZEtyZ200djlHcVVMNWY0Y01VTEdVdllyTlE?oc=5</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>13-05-2026 16:33 UTC</t>
+          <t>14-05-2026 00:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Esperion Announces Two New Analyses Supporting Bempedoic Acid to Reduce LDL-C Levels to be Presented at the European Atherosclerosis Society (EAS) Congress 2026</t>
+          <t>Alteogen weighs KOSPI move as Korea business groups urge KOSDAQ stay - CHOSUNBIZ</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>The Manila Times</t>
+          <t>Chosunbiz</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wJBVV95cUxPVlBXQ3BqakVJVk9udC1JT3VUc2tPSHBwTVR1RDNRdTNzRWRfU2ZOV0JXMXJldFFIVGxvRHlQaURlb0xtLTRFRXVYYWpBQ2JDQy1FSm1sR3U5V1kxdTJNU09LZ0QtODVKaDA5R3dEQ1JaZ19VVWRpaHd3bE1Pa3cxVzZxbHFKWjJOZl9ZQWpsX3ZpS3k5d3I4enFPWUx5YmRSR3hiV0E5akxocEhUSXJIdWFvRnhPalJtMVhIZGYxTE1ENi1nempZRkg4QVhPWVI0WkQybWZ4dl9HRGczLVJ3OHFrZjRnRE1YSWotOFhKT3RHeHlEdW96U0FtNk93SWVqaXlvV0ZPMDgwREZOUVJmWEMtYjhjd3pkM1dhcWI5S0hzenhuQ2tvOHZsNmhZN28xRklISkxORDhSS3hYeU9yYWN6SWdJRlFSa1cwZzZPaFFoZUk2Uy040gHXAkFVX3lxTE9WUFdDcGpqRUlWT250LUlPdVRza09IcHBNVHVEM1F1M3NFZF9TZk5XQlcxcmV0UUhUbG9EeVBpRGVvTG0tNEVFdVhhakFDYkNDLUVKbWxHdTlXWTF1Mk1TT0tnRC04NUpoMDlHd0RDUlpnX1VVZGlod3dsTU9rdzFXNnFscUpaMk5mX1lBamxfdmlLeTl3cjh6cU9ZTHliZFJHeGJXQTlqTGhwSFRJckh1YW9GeE9qUm0xWEhkZjFMTUQ2LWd6allGSDhBWE9ZUjRaRDJtZnh2X0dEZzMtUnc4cWtmNGdETVhJai04WEpPdEd4eUR1b3pTQW02T3dJZWppeW9XRk8wODBERk5RUmZYQy1iOGN3emQzV2FxYjlLSHN6eG5Da284dmw2aFk3bzFGSUhKTE5EOFJLeFh5T3JhY3pJZ0lGUVJrVzBnNk9oUWhlSTZTLTg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPXzlhX3dySzJ2WHk2VFdlc2FDTHRwYmpzdG9GOUV0V1BIbVdRTGN5YzcyYjdxYnptSFlxenBtZVJ6T0gxcXJhaEZyWFVhUkFPcllBanJTWDdRY193UXg3LTEySHk3T3RIdnU1OFJzZjlfV1FFbm9La0NWdFFIclVxRNIBlAFBVV95cUxPMUVKYk5NRGtHMi05Q3gwd1ZaSm9pUG9wWUlPR2lwUUl6NnEta1J3cXliNzhMLWxWck11eklYZzNjR1V5aE9aMExPVTFSQUJHal9uMWtSekdSQjkyU0xpSy16QWJEQVpOV09DdE42LWc0ZFpZZ2xHczJ0d2dKa0wzTG5Ha0FNNzVkOE5nQXFtdHg2WjVh?oc=5</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>13-05-2026 12:19 UTC</t>
+          <t>13-05-2026 21:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Kura Oncology Q1 Earnings Call Highlights</t>
+          <t>Singer Yu Yeol confronts canceled lung transplants after mother's death</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>Chosunbiz</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQSXRwcmw5VG9xMkxjeEFRclNNY1FoeGVzdzdGeVZOYjItTzZhQmRrR1JoWG1scHZnSHVGVTJyQXBTUTB4ZmFYckcyd2ZDbThsMGk0RHhZUlBYSDQ5dDkyOGdnRTlwRktjS0xHVWxVQ1RQNEdFdGtkNDY4akE3WUc4Qzl6NE95OUt4X3RVNzJ3LTNoQzV5bXJKQTFITW1OU1Z0OVVBTg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNVHZmazNzTVFYY09tSDJEMVlZeHFDNkEzSFlZV29EWTJqNGYzU1lra0RPVG9BdkJ1cDh0Zlp4dXBrZ1NtVDVlN1JyRkRHNFlTRzA3akc5TEcxSWpTUlFhTXNmemc3a0Z1WGZXakUyWGxQN3A3d3NoeUZueEo1aVluNmNrc25Zdm5ORExVYlkxS2ludWRnTHZZSlNGM2M?oc=5</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>13-05-2026 01:09 UTC</t>
+          <t>13-05-2026 13:29 UTC</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Kura, Kyowa Kirin to present updated frontline data from Phase 1 KOMET-007 trial</t>
+          <t>While the government is scheduled to announce a "Korean-style sovereign wealth fund establishment pl..</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>매일경제</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxObl9vOEhENFcycmlSbmNZaWEtZ1hzb3ZVc1NxV1JHNFVVUVp0bThIdWhmTmtYZFN6WHFoZ2Nmd3lHQ0dzcGFXdUdRbHVzVmtEZjlIaUl5YmdoLUplYS1zSVF1R1dSTkhSNnZCOFM5eFEwNjVEcTQxMzZiZGptSXIwUzNmdG9Ia3J5N1djNTVibnNneTJyZGx3aDhMdTlYcXRPU0hNb05FbjJ5N2lxWmxIcWdlYzl4TFBMZ3ItU1YtN0k5dU91Y29YZg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUkFVX3lxTFBKczBQckZVQVN6Rzdoc3lWblpxdkRMa0RkbThYbGxFd3NseHNyMlNnbUJMcndYa1EwT0x4eEtMQVJwMXNxamJnZ051ZTUxRUZGdXc?oc=5</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>12-05-2026 19:48 UTC</t>
+          <t>14-05-2026 08:59 UTC</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Kura Oncology Inc (KURA) Q1 2026 Earnings Call Highlights: Stron</t>
+          <t>Energy surge drives US producer prices to biggest gain since 2022 - CHOSUNBIZ</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>GuruFocus</t>
+          <t>Chosunbiz</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNZnRXb2V2enhSdjBCTF92cTRwSEpSd1JXeEF1ai1Qc3l1TGJQOFBSZENGUE9SbG1RYXBIZ3A5b0NSYkpHa1ZJd1VYbTdRLW1oNGZmclhMamt5RXc4ejhSNkZ4OWRtZ19DMmxlUTJwWUY2REFZYkZteEt5NkR1STlENU5UZE9BMVNXS1VqMWpVQXB2TGw0UHVWd0JBUUxOaFZHbDZId3hTcUY0SlVlWlVCbEljbzlDUllMemMtTEM5WlJxeVNqNDg1eGNJdHBGVVh6UnhKTw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxORk5kVEJDUDQtSmJpVjA2S3B5X2Rkb09LZVBqbVdfVzh5bmlSR21URzFBdkV1bXplS1VuMjFhOG1xY0JMMWtFb3I0T3VKQm9pYlRZa2hiMVdEdjd2YW56S0k4Y1poRnhuM0VKX3BsT2ZETzNIcHN1cTF0YkFwOUtLaDl5WEVJNWdhc3FFQVoyTUprZlRsLTl4T2dMNTLSAZwBQVVfeXFMTkZOZFRCQ1A0LUpiaVYwNktweV9kZG9PS2VQam1XX1c4eW5pUkdtVEcxQXZFdW16ZUtVbjIxYThtcWNCTDFrRW9yNE91SkJvaWJUWWtoYjFXRHY3dmFuektJOGNaaEZ4bjNFSl9wbE9mRE8zSHBzdXExdGJBcDlLS2g5eVhFSTVnYXNxRUFaMk1Ka2ZUbC05eE9nTDUy?oc=5</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>13-05-2026 04:32 UTC</t>
+          <t>13-05-2026 13:21 UTC</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>KURA: Kura Oncology Shares Promising Results from Phase 1 KOMET-007 Trial</t>
+          <t>BOK chief and budget minister unite to steady prices and bolster Korea growth - CHOSUNBIZ</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>GuruFocus</t>
+          <t>Chosunbiz</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOWlUwLUZCSVpVNWxLbHdjZ0paVnRxLUI2cldfTmoxV19wTkxmN01jMlI3N0UwYWNweTR2bFR0akdxX1NqTEJkNWJUQnh4cTN3Mkh5THJ1WkZRdjBiWEs1WUZNdzB3MFFIM0FSNk9fcTNWaEVjR05JQzhIWlloSmptMUUwTG5TTmVmamQzeUFZaTNxeHVpZlVWR29nSnhCdGxlSXZ3LVZlX3RncS1XMFhxaWpzV0UxUEdJRUVzMkJzYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOWElFVDhMOElNNjVHS05VVlNkN1pabHhNeFFBZnloTTczLUhZRnp3T1RxZE85dmJuRjJZak1UbTZsSUVnOG1Zbm95cldfSWdLTlJTY1lrM2p1aFprM2kwLTZ1cGFFQTRIZnJjUENzdEtlSjV4MnZQVUJBMDVIRTQ2Sy1pcGJBZUZwTGtEaHZtRi15aXPSAZMBQVVfeXFMTlhJRVQ4TDhJTTY1R0tOVVZTZDdaWmx4TXhRQWZ5aE03My1IWUZ6d09UcWRPOXZibkYyWWpNVG02bElFZzhtWW5veXJXX0lnS05SU2NZazNqdWhaazNpMC02dXBhRUE0SGZyY1BDc3RLZUo1eDJ2UFVCQTA1SEU0NkstaXBiQWVGcExrRGh2bUYteWlz?oc=5</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>12-05-2026 23:37 UTC</t>
+          <t>14-05-2026 04:44 UTC</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>[10-Q] Kura Oncology, Inc. Quarterly Earnings Report</t>
+          <t>Xi warns Taiwan misstep could push U.S.-China ties toward conflict - CHOSUNBIZ</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Stock Titan</t>
+          <t>Chosunbiz</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOeE1Zb2VXQXNXbFVOblhUcjFrU1ZFUVk1MHk5b2ZmMHVza1lQNUpCV2k4ZHNIVjQ1bjlEeUZPV0g1WEh4MEFzTWhSSndFdXloMXczNHY4YU83UTdNTUhMMXZGZUQxUUt2azZIUGU0WVFTQXhHcjg1Rk90TVo4NUdQLV8zeUdWclUxOUpHRXlPUnBMTHI2N3R4ZUVLdG1lZGJ0ZXp3ZS1lZ1ZKcWVBdGZj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNeHJRSE40aVlLdnJiVGU3cDR1ckZOVkdBdzFwcVZjMU1kY21odnJJcjg2WkItOG4xSXZKdm5icEpBLUY2SkhSMUFpMUk1alF0YU5NZE43c1V1a0NxWDNXajhYVmlZOXZWZWVqY2pPSm5pU3hwZEtGTExKYUM2RWdxR0VrN3ZINDZ5VlZFLUF4U3p1T3hyV0FJdVd1anDSAZwBQVVfeXFMTXhyUUhONGlZS3ZyYlRlN3A0dXJGTlZHQXcxcHFWYzFNZGNtaHZySXI4NlpCLThuMUl2SnZuYnBKQS1GNkpIUjFBaTFJNWpRdGFOTWRON3NVdWtDcVgzV2o4WFZpWTl2VmVlamNqT0puaVN4cGRLRkxMSmFDNkVncUdFazd2SDQ2eVZWRS1BeFN6dU94cldBSXVXdWpw?oc=5</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>12-05-2026 20:15 UTC</t>
+          <t>14-05-2026 04:28 UTC</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Kura Oncology reports Q1 EPS (83c), consensus (78c)</t>
+          <t>Autopsy says South Korea elementary student died in fall at Juwangsan - CHOSUNBIZ</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>Chosunbiz</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNbTZnRGFqYkVybWdXSzZldUMtclZqejZ2V3JNMjFwVnpIUG5TUE1pMGZlWkxUVTh3Y2k5eVJEYlRMWUlEZXAzb2tJQi10RnFCRGtzZEZseEFYd3JTakFpQzdZbFRxcHpvNmtqUVk1bkVaTHVDQ2RIVkFXRmZpUjdTNXBJQjZicWpRTDc0dXNHaE1SSlNiNDR6bTdnazc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOUjdILVpfSWxIRzRILWRuWlkxYXp2d3JvLVNSOU5vbElBOEtaN3FVTmR3VUNlM0ttTEttQWEtYXFNYWhLOTlaMDQ1TElBM0syTHFSNjJscmRiZTN2TnFyR0pULW85cnVyd0dxcEphbS1teXVVanEyaS10NVRWWmsyV0F5aEhLWk03c2czbEFhNEpUcFVW0gGUAUFVX3lxTE5SN0gtWl9JbEhHNEgtZG5aWTFhenZ3cm8tU1I5Tm9sSUE4S1o3cVVOZHdVQ2UzS21MS21BYS1hcU1haEs5OVowNDVMSUEzSzJMcVI2MmxyZGJlM3ZOcXJHSlQtbzlydXJ3R3FwSmFtLW15dVVqcTJpLXQ1VFZaazJXQXloSEtaTTdzZzNsQWE0SlRwVVY?oc=5</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>13-05-2026 01:18 UTC</t>
+          <t>14-05-2026 04:33 UTC</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim licenses Immunitas antibody program</t>
+          <t>Singer Yoo Yeol credits South Korean donor father after surviving cardiac arrest</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>BioWorld News</t>
+          <t>Chosunbiz</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOUGEyY2M3azJacGxKSUdtWlhSTHFhRVlCczJpd0hNeEp6UGdtTzl3anQwaUpCVHRQb0VDazkyYTk0ZmExLVl6bzBXOFZ4TlBHRkU1ODU4RXpNT2Z6czRhOVFkVVN2M1lpUXJNdVJ5OXE5WmhGRzFCbzJlVlRVRkhyYnNmVzBvNG5xYXBaY2xicXNzQkhzQ0RqWEctU1RDdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPZkxERGc2ZzFYc1kyMEpHYldzLXd4VEl4UjZ3ZXZUSzVFSEtHU2lxU1NDRE5RSGRLYW1Zd00yUVVnckNoaHE1YnNpRjNGTXRKak9ITWhQTm5pT3lIRnVjZmZSMFNIOFotM2VSZWlGTXVNVWVUOHpFYUc2NXpDNTc3Q19EdTJUQU5uMDhSRjQ4V2NNTDJBX1E5Y3FtUU0?oc=5</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>13-05-2026 13:00 UTC</t>
+          <t>13-05-2026 13:42 UTC</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Earnings call transcript: Kura Oncology’s Q1 2026 revenue miss despite EPS meeting</t>
+          <t>Daiichi Sankyo Company, Limited Just Missed EPS By 12%: Here's What Analysts Think Will Happen Next</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Investing.com Canada</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOR1AxZmpLVXZaendJXzYwdlRuVFRKbHB2cmgydHdQTWRwSTBLNFMyanBuazYwM0pmTTVIZU9VZFF1empERjJ4akw5WUFQZ3F0dlB3NEFTbTJ4VWVjdFhfWEMyZjRMLVlnY0NRcWtxWUtkbEwzNVMtd3NxVF9sQkhHTDF2SGNzSEZRbTRzRmdETXM2aHUzUHotcGtZRTZwLUFXSVhhSUEydjNSUGJXbGlGLUc3TXd6TURyOEdBWEdjSUVZa1RYazA2eWtXNTU1RS1SZWNJVmw3WHY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxQdGNfQ216Njlpdk5XdUJRUVhSVmV6Q0E2b3VpbHV5SW4ybUlJUmZvb1hDRDFlYXkzOUE2dzI0WUhzT3QzWU9mQ1lJMkZtRXhVV2hXR3FBM0oxY0JmWkhySUtEaDMteXBoNHhPaDNqM0tIeU96ZzlkOXRMczZBaUNRSUcwUFJKTWx5MERxb3k5SHdhSEQtUTlKZGpEeE1odFZGOUJ0dEJWQkVKc3pDVW4yQjZORXZpUzROdHpzdkhaRkpNaWppOUlXNEIyQ2xvX240WTVMM2J3a0JQaDg0RmNGY2dBeG1IZknSAewBQVVfeXFMTVAybGZncmNSSFFlcVZXcHUya19NV0tDczZWT3FZX0V4TzJ0b1J0Vm4xX2ZNLVlkSWJoSjdodl9UUkVXRHlvUWlFM0VFSUNrNm5RYkRKYWM1aEFZa2JxWVl1TmRVblllQm9LUGwyZGl1eDdZeERDRWxJYkRBNFpVYUl3bVpPMHlqMGV1eFZiTE5DRnFsSVZheUhhQzJYR19MczFzRldPVkhvWTdmclFoTVV5YWtyNUhEajhiRzFyVlh2RDF2N1gzOGxKYzZIaDQ2WFFnV2pNeTMwR3B5bzZ1R3ZmZEh2dXpVU2pvZGo?oc=5</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>12-05-2026 21:38 UTC</t>
+          <t>14-05-2026 00:09 UTC</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Kura Oncology Reports First Quarter 2026 Financial Results</t>
+          <t>Daiichi Sankyo stock (JP3475350009): Recent correction and 4.4% gain signal volatility</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>The Manila Times</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPVHBrOTlvaHBrNEdjUkZET2NfeGtYeWJiVXF1U2lvMDVVbXNkeTdLRUxZcXpIb3poVXFrRTl2clR4dmRQdHpqdUdWNjNicHVoNy1UUkxfOURUeEhDcGtSR1BpYXdpSmlnNjgwb2Nnd2dJX2JpUFJzV0dqSzJsVzdhdjdrTzBrWkpTdTJDVzZhdkhXV0dBVWJ1M1BjWkRQYWRpblppeDBlQzEzR2Z6RTdkOXlja2pZblprRVczSXJ0UEdoQndBeEhHLURDN2XSAdIBQVVfeXFMUFlwcGFrbW5ocTM5OUtwbnpQNDJmWHBFNk9makJHX1FWdk5tbjBWcUhMVWpVM2VpeTZHQ3hQcVpOekhTSmVjOFdIai1zMk5sVThxak5sSW9zSUwxV2YydmJKbU8zQ1ppMWJmeXI3Unpzd2VjTnotaXlRbTExeENWclhYMkdMWkhaN1M2QTZQSXA5Nml5OWhia0lsejd0VEh6aVhFVTN4RzhuTHZXWUY1RV9uV0VNSVVpR2Fyb2FQRnVZQTR3c1hHRHhjT1VfQlVDZ193?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQTHliNVJmX1pEcVlVMjU5dFVacUNHV3F5akxPNFdYUzI1Tkt5VlVVWTMxN2VpMzNkblZWeTk3LTFnR3lpMnMyM0lYc3ZLUU13SDhEajB2bXU1RnFfV1JNMlZGVlp6emtmeGx6cFlXcC04alR0UUtYeHAwb1A0amxidUw2d25DMDdON2tYR2MtWjEzZkRWdWh0WWprZm9vMmRITjB1dU9qY0sxbFA5QThKMEdXMkQ3YkM0cHNjR0NENDU0clhy?oc=5</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>12-05-2026 20:24 UTC</t>
+          <t>14-05-2026 05:50 UTC</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Kura Oncology (NASDAQ: KURA) posts Q1 revenue and updates AML pipeline</t>
+          <t>Pharmaceutical waste: What do I do with it?</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Stock Titan</t>
+          <t>Cleanroom Technology</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPd0ItcFNzbzc2a2hFT2xfQXVPdVdWMjVTWlBldTdLYkxnQ0tUczBCTzJzeDd0X19xQkF2ek8yaTIyX0llVzFEdjBxS1dyVGFycmVpLUxkT2hLVXFlUXo0SzczWHVKWFVwUVdsTFVjUXNCcld2bEdmRDBVUUloX1Z1WjN1bWI0dG1fZDFMNnYzUU5uODRRMWhpVjRDbXNQdXFPbUtJTWZ1TmJFdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxQVjBUTDdvZU52dkJoTUgxZnVPNF9mbm9GMXVrQl81LTFidXVfTThJRTgxNVlQNFlhaEFMcjNJem9xOHh5R3drTGlubDZ0S3Y3Q0VsOWlPWm5XQnN2MUxJWkJqdFRsbHJyYW5idHlmS3VUVVpxSXAxZHFaZmljbi15UWdUbw?oc=5</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>12-05-2026 20:10 UTC</t>
+          <t>14-05-2026 08:18 UTC</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>JCR Pharma</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Acumen Pharmaceuticals Bets Big on Alzheimer’s Trials</t>
+          <t>Bora inks $122.5M takeover of MacroGenics facility to further US expansion</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>BioSpace</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQcG9meVFOakw0QVVBWjRxWU43dkY5ZUh0cWRvcDNfU0MxQkg1QVJfSmRlWEc5SjF2WnFqQnFwb0JQS2xMUXZQZWZqZHhpX2w5NHhUeS1mSHQtcmRrdWwtSEFISWtXTXZFY2VxX0NpTkc5ZDh2cjlzZ0FKWUhJZk0xWk9mYkNncTk1M3lrSkNrZFkwN3JBZzdQalZqc0VMUVhlYmtEaktlWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOOWVlXzdZUWNhVnR6RnFDMjM5VnA0TDFpTHVzUTdwZGt1bXJhNENFWWV1NlpDdi1jRTUyeDQ5ZWVQYWhZYUpuazc1MFJyYy03Rk9LTW82elhONGR3cnVHRXRtMENhdnZBbGxPTUlOREpxUmJJRUZicE9QcTQtdHljM3Fpa2ZOSE15QzRwNFh5TkJHaGJNNEFLNklINUJqbUZYSWRVUVFzMA?oc=5</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>13-05-2026 00:53 UTC</t>
+          <t>13-05-2026 18:36 UTC</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Polpharma</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Kazakhstan develops homegrown drug for mugwort pollen allergy</t>
+          <t>Qol Holdings Delivers Record Sales and Profit on Strong Pharma and Pharmacy Operations</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Kursiv Media</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOWktRelM3Nnhwb0FPUWRxZElUbkNodWhGMGItR0pIZTc4T1dBWVdsaEhXejZNWXI3eTBkRDF0eER3SVFVWXpsQlZIeWFDMmFyNk15QVV0Snh3eW1DdzRjUV8xeTUyQklFa1lCMHdrZnVGcVItb3R2aDZOZzI3TGpablpIZ3FLZjRBUmllV3g2b0lyZ3o5ZVpCSERKWlUxWUlFdnZBRER3SVNpTnMtckYxbNIBtgFBVV95cUxPckhZN1RmWFVvN1dDM2IxNTFHVkhPTGQweWhVVVFjR002VXpJY21DWFlzQ2FySFhkYkV3aWozZE9QLURFbXdWTlRnbV9xN3BNMG9UUzVNMzdUOEFldUM2ZUgteHduY3VIeENhcWVmNFptTGY1LXZPai1WSXhUQ2pNNUhEemlDN3JkN2NHUjBkbzBoX2xDS3NYLUJ1YWQtX3VBU055RXFrNU5MelFzY2FEVUwtUF8ydw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNUXNOdFl5cjI0NzZZOS1jOVBKUTBSNllJdEFGZ3FzYllEYVZ0My1tNm9fQ3ZYalJGYzlYdERNZEpuOHBnOF9ITjZVaG92Qmx5Z3FZRURNd1ktcjdfQ2pDeUZjaHVxQU5EOVVtSUZ3clY0bVFHcFh3bWk0eXhkNXlzaktsVUc4QWFzT0F3Q3BOenZ4M1YtMHp1VmRGbHp4eWUzc3FKWGtnOGhmanBaVk5zQnJZNVFHX2R5OXdyT3lMZV85Ql8zRGZZMHcxa2dqUncySE1EZw?oc=5</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>13-05-2026 08:57 UTC</t>
+          <t>14-05-2026 10:49 UTC</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>World Plastic Blood Bags - Market Analysis, Forecast, Size, Trends and Insights</t>
+          <t>Elabscience® Launches Self-Developed PolyHRP-Streptavidin Conjugate for Low-Abundance Biomarker Detection in ELISA</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>IndexBox</t>
+          <t>Thailand Business News</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxOMjgtcVhOb1huMG92T3BJSkhLdDFCa0pPQXhaVDdwRDZlZ1kySnMtNG1TRXFMd05jY0NUMHUwYTFhRVVydHdHZFVGTjdSdk9lc21WRk5kWEREZ3FJb3Jnc0xYQ3RqZXNxX2ZDU0ZMSEdvM1VpYXE5QXE1UUdsZ25Bc2x1THUxUnBxNExBcWlVdkdtSTR3bG5fdWozbXJTNFNKZ3VSQjJrTmtZbWRacGpTLTRsN1hyWGJJRm1ScjZlY2NwOHBYRmt0bmM3b3pobnlianU5NXluZ2JBZnk0Vm9INGR0MWVDME5FaVpQS2tB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxNREU3R2theVR1QzNzZG1haUJZXzFjYjRNQl85Z3NJRVNNaENseVdQQnU0TEpKZmJId2hDV2JVTHBNNUplVFZaZW9iTk9GbHRhLVRWUi0xR0ZnUk9EYnE5cVlKckFXOXh1SlNfYm1kekJvbURySHI5NGU4MGRHSmNrWVJvWlhMSnBBYkRuMnFfS2UzRHl6VjdwQXFMbDY3bGJ3M3pQdjNLQkFscV9uQXVUb1N5WmdNbG1LdFFndzJ1UXFzM3BORHpoNHpKTkdTX2VUMnBJWmU0NFh6LWFqV2NhZFQyUUZyV1h0cDR5ODBTSTZHUQ?oc=5</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>13-05-2026 04:46 UTC</t>
+          <t>13-05-2026 16:33 UTC</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>[Latest] Global Intravenous (IV) Fluid Bags Market Size/Share Worth USD 5.46 Billion by 2035 at a 6.8% CAGR: Healthcare Foresights (Analysis, Outlook, Leaders, Report, Trends, Forecast, Segmentation, Growth Rate, Value, SWOT Analysis)</t>
+          <t>Esperion Announces Two New Analyses Supporting Bempedoic Acid to Reduce LDL-C Levels to be Presented at the European Atherosclerosis Society (EAS) Congress 2026</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Yahoo Finance Singapore</t>
+          <t>The Manila Times</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNV3hjUDMtVkEtOFJZbnI2MG5nb004U21kZ0tlODVPaVBhenBjVldsRU1OTVdRT3gwcnN2aWtlWlhEMERtRnhwV3A4SW8yQlc5SmtWZG1uVnN6WDJMOXhrTWQ5WGg0R013QWRxOHk2RmFkMlNFVVJjdlY1anIySmtONmdDb0Vrd29ySlVJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gJBVV95cUxPaFBHVkJRMVppb0NwOGdRZDNsLVNTR003Q2lZZlU0WERjbXZSYXN6bXVpSUJmM3VqZkRwdXJ6YW5CUnBGZGtmRmN6ZHpodnl5NEZtNlJ6WXlXYURsR1p3UjhGNFNpVmxkMkhHRjNmdXFEcElXbXdrQThGZE5RMXBrb0VaSnBKaVJHU090RnlEa0hmQUxYeHFmRHQ4YmxJYlRTdVlDV0xFdXVNT0ZwYTZubjdqTDZucnhrRnpUa1BsZDlUeHY4cnM1eExsM3RaYmswNExsTGt6aWVPeTFLLV9wbTJzZ25BUnV2OHJkOTJOaU9tYUhiS3V1ejBNLXVpb1NUYl9rV0o0RVZQZ0hFRzVRUnNzd3pPTlRfZjR4YjVtbmFyZkNHVW51N2tESktKTnlITWxMVDlHMF9zcmZVYW9jVmFiSGtjeEdnX25wZXpwYWEtd9IB1wJBVV95cUxPVlBXQ3BqakVJVk9udC1JT3VUc2tPSHBwTVR1RDNRdTNzRWRfU2ZOV0JXMXJldFFIVGxvRHlQaURlb0xtLTRFRXVYYWpBQ2JDQy1FSm1sR3U5V1kxdTJNU09LZ0QtODVKaDA5R3dEQ1JaZ19VVWRpaHd3bE1Pa3cxVzZxbHFKWjJOZl9ZQWpsX3ZpS3k5d3I4enFPWUx5YmRSR3hiV0E5akxocEhUSXJIdWFvRnhPalJtMVhIZGYxTE1ENi1nempZRkg4QVhPWVI0WkQybWZ4dl9HRGczLVJ3OHFrZjRnRE1YSWotOFhKT3RHeHlEdW96U0FtNk93SWVqaXlvV0ZPMDgwREZOUVJmWEMtYjhjd3pkM1dhcWI5S0hzenhuQ2tvOHZsNmhZN28xRklISkxORDhSS3hYeU9yYWN6SWdJRlFSa1cwZzZPaFFoZUk2Uy04?oc=5</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>13-05-2026 12:30 UTC</t>
+          <t>13-05-2026 12:19 UTC</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Fresenius SE &amp; Co. KGaA stock (DE0005785604): Global healthcare leader with US exposure</t>
+          <t>AstraZeneca plc stock (GB0009895292): Global pharma leader with strong oncology pipeline</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -5090,375 +5090,375 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPMmdZbjl6dm13cE5HTXRPRXhha0ZlU0g2Z3lCdTlLaW1uZ0lRaW44eUp2bTBGT1RQTC0zd3NqRHdUR2ZCNmk2S053MmtGNWc3LWY5TUNVYWF3TnB5bzNnQzR5c2RDS0xEU1lkYmtVY3JEQzZvcU41WUZPWmpROFRETnI4RXllQVlTTjVWOVVOa3l2YUQtbXNlX0pURU5DTXFuVy01QUlJeUtnbGNCaU9mY0VQbjlYTHQxNVljOHVfVkFiWDFOZVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQM3lQQ2V2M1dZdkd6M2FWOHhES1I5S1o0WWtIai1SSnFiZ0FBaFQxdkN2azE5MFAxQTRwcDZkTmxnckRpQnBiSE5pQjh4SnRSMGV4MmY1RWxzNzlUUlJQUWhWbU1KQXVqSlYtNi11SmhRUVpfOVgyc29sdnNrOFA5NFlzX0gzVHpyRHhuRlNEMlRLdV9xX1JDdS1iMlJfQ0FETU5CSlpWZVQ4ZkhvT3M4bU1NbTNlUUc0dV9NY0RSd3c3ODZp?oc=5</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>13-05-2026 16:54 UTC</t>
+          <t>13-05-2026 16:44 UTC</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Kyowa Kirin</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Sai Parenterals IPO Funds Untouched in Q4 FY26, Monitoring Report Confirms</t>
+          <t>Kyowa Kirin Co Ltd stock (JP3249600002): CRYSVITA gains reimbursement in Canada</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Whalesbook</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxOaURVUk5xRlhXXzlvZXlndE51dl94akdDRmt0bDQtRFZJQWM3ZzIwYmlMM2pvSGJnRUY3S3FTQXExWjdWWVdvZkNrMlFLeEVjYXZ1bl9BQmdWUk9Jem1JTEpqT1RFZ2xtNFhBZ0Y2dzQ3MmlBb0hqN05BbDhHb09ORXRlaXZYZkc2c0JzSERhbEswbGY0WnAySHRWSGZwa2lKalpfMkRTYjZQQzdXSGdYNW9QREhoYmswVEhSQm1seExuOGY1Z3dRZW1kYnY1Ulh3c2VQa2Q3d2VvTnNpeWVmVGdVRjhFSUVCQ1hQaE83MEoyanBZOE5jUEVR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQdXRkLU9IZlFabEo3WGgxZW9kN3VNbVhGOFVfQlJkSDIxcEMzR2RQa00xN2ZrYkpTeUZyTl94b0dKWDUwaUJiV2RHLUE5bWo0TDNNNlgwaDlacm1qN0txdmF2a3hMa3RpX1p2dGRFSmFrZjFwQ1lheENOd01uZGNjQVN0eG5oQm9waVgzTFpmZjRPRlROdUlXaDBBMGRyWDJYZHM4dGR0SXNVMnhmYV9QMXdvMl9iZk9VXzlsNm00TXVFZ0EweW1R?oc=5</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>13-05-2026 07:49 UTC</t>
+          <t>14-05-2026 07:08 UTC</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Kyowa Kirin</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Fresenius SE &amp; Co. KGaA stock (DE0005785604): Global healthcare giant with US dialysis exposure</t>
+          <t>A Look At Kyowa Kirin (TSE:4151) Valuation After Positive KOMET-007 Leukemia Trial Update</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNVG9ONVlRU0JFdGMwWnl6Z3NVQXRUMjZ0VmQyd29udC1RSWdOd09RNUxCOFllMHBFR29qLUJidGZ3Z3ROalhvcEZVWWhWV2h1Umd2ODMzcDk4TkxKWGdObTFBNTNKVDltdjdacjdCWW1fbjBpNF9wLS0wenZsV3FOaGNySnF2dDdvQkFXcTM5VXl0UWktVUkybU11MzVLdDNhbmU4alhHVTRWTHZuNWQxSU1kWkYtOTJRczBfNWQtSTZFTjdo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQX0NBd05OVXhfUlk5eWQ1NEhyM2kxdzdnZmRwRWhVRWxPRU9WOW5ic01ySVNmR3dWdUxncExPQktXNGtrMV9mQ09rQkkzRXNIb2RMblhpZXRPZlFMUkQ1MmZUSEJNWVl2VS1zN1Q5U1c3bEFqUzYyYVNBWWFhMExscUdJMUVFSl9TaEc3bVhTNGtncFpIb0ZCQ1FHeE1Pa2VvdDh2U3lXdXk0bk1oTkZNeWJkdWJVaHBwZHFjMzlxLVhua1pwREtDV3I3ZE0tdklOSlR5WDh1cHdsdTVZTjY4N1V0NWQydnRq0gHoAUFVX3lxTFBfQ0F3Tk5VeF9SWTl5ZDU0SHIzaTF3N2dmZHBFaFVFbE9FT1Y5bmJzTXJJU2ZHd1Z1TGdwTE9CS1c0a2sxX2ZDT2tCSTNFc0hvZExuWGlldE9mUUxSRDUyZlRIQk1ZWXZVLXM3VDlTVzdsQWpTNjJhU0FZYWEwTGxxR0kxRUVKX1NoRzdtWFM0a2dwWkhvRkJDUUd4TU9rZW90OHZTeVd1eTRuTWhORk15YmR1YlVocHBkcWMzOXEtWG5rWnBES0NXcjdkTS12SU5KVHlYOHVwd2x1NVlONjg3VXQ1ZDJ2dGo?oc=5</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>13-05-2026 14:25 UTC</t>
+          <t>14-05-2026 04:27 UTC</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Kyowa Kirin</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Sun Pharma Schedules Q4FY26 Results Announcement and Earnings Call for 22 May 2026</t>
+          <t>Presentation Material with ScriptPDF: 984KBPDFファイルをダウンロードする</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>marketscreener.com</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxNNnhzZ1Q0ZVZjc2N3eG1xamtaNGJmR1M4QUpvXzFHOHZJTFJKTTcwTjhqYkYybWZQYTY4d3g5UUY1VzZTVW5vRDdxM1AyZS05NDZQc2FUUzA3WGtCZzlRUVpNVThsLUstUTRFV2RMakEwQ3g1b3JFZHZqWUJPRkE2eDlnLUlfZEItbWdKc2s3czNPRGJxNEdaa0hzdzUxV3BQWTZpZVBKdEdreHNxbzVnbG9EbkcwbmRld25iWjhrVVk1SXhleWtjVnhNTE1yNHhWSG40elpR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPZmxZSHVBUjVnQW5BTVFMQm5oVGVRMWhmTW80ckdub1RNNjA0X3hDOEU2am52VGc5TkJyYWt0YWZuSnJZWUpqQ3Y4d1BnaVd6WWNaY1M0NFNYMHBUcE52TWtSMmw1Q2hNTTFOU3l3Nlc3VEtnQUs4OXZBVGM1aG1xaE5LQkVNOU5YbXRCWkRQOHpvYXV0QzVONVplUnczQU5kbkhIczJsZDNiWXdET1VFM01JMkFkWWpZeVI2c250NHE2Zw?oc=5</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>13-05-2026 17:30 UTC</t>
+          <t>14-05-2026 08:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Kyowa Kirin</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Pharma Quality Excellence Awards 2026 - Celebration and Conclusion</t>
+          <t>Kura Oncology (KURA) Receives a Buy from Barclays</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Siliconindia</t>
+          <t>The Globe and Mail</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxOcTV3bWhuZ3VaZmRncmFHOENMX1NQaEV5M1phdVc5b25KNGxSTGxOcWl5eW5TaGZBbjBhdndWN1pvY3NualpsUjlpaHpTeG91a3QwWkg1SFZqaUp2SDBzN1h6U3RYTHRBbU9Cc19VOWpKZEVXM19yZXVjLUVheXdpZWFBZkp0LWFCRzFwazllWWpGSTZ4ejZIeG1Odk0tMFlVWERvdWxXNkpCS0YyaUZaQjlIaTlxYVZoZ0RNUE14bGwxdDJnTFhUdQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQeHF4bHlNUTZFWXMxUThPSF9hY1ZqWHc1RTJOTFQ2dlZ2WmVFSGdYSDNBSDI5bExlcENURU1VX0JpOHNNZjVHVzkyaGJXcDZ4V3NNTDFnYm5NT1ZicVdSWnB2TnQ0MlBCMTNzQlFCTHQtMXpfZW9SREEteW5xMWxIeDYxR21yT2h5X29YamF1dzRTM2JZcnBkQkNKSFBqUkwtQ2hlVzhlVHRXZEJ4X3VZeW9PMlhLTTR0WVltSzZka2tqNUV4Y3F3?oc=5</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>13-05-2026 14:20 UTC</t>
+          <t>14-05-2026 09:12 UTC</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Kyowa Kirin</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Vanda: A Long-Term Pharma Growth Idea, Despite Q1 Earnings Miss (NASDAQ:VNDA)</t>
+          <t>Boehringer Ingelheim licenses Immunitas antibody program</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Seeking Alpha</t>
+          <t>BioWorld News</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNcFFPS0ZjVW56SlY3dy1VWEM3ZmdBWThpU3JVVjVWWmxzdTlwaE05SnlUQzFWSU1oWTNWQnZFT2NFR2ZjTXlqOW1wODZMbzRSMURmb19nU3VTT0NDZVdObGFHbWZxemVuZGJWZ1BBNzdERWJRNkdOcGt6TTI2aS1iOFNIQll6WkFTMngtaWV0TFItN0ZOWnRXc25LUDc3XzNfSndNMUU3eU9mQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOUGEyY2M3azJacGxKSUdtWlhSTHFhRVlCczJpd0hNeEp6UGdtTzl3anQwaUpCVHRQb0VDazkyYTk0ZmExLVl6bzBXOFZ4TlBHRkU1ODU4RXpNT2Z6czRhOVFkVVN2M1lpUXJNdVJ5OXE5WmhGRzFCbzJlVlRVRkhyYnNmVzBvNG5xYXBaY2xicXNzQkhzQ0RqWEctU1RDdw?oc=5</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>13-05-2026 17:34 UTC</t>
+          <t>13-05-2026 13:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Kyowa Kirin</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Developments in R-R Multiple Sclerosis From AAN 2026</t>
+          <t>Kura Oncology Earnings Call Highlights Comzifty Momentum</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Medscape</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPdUJ5TkUwM0MwTnFQZ3lHM3hWbmxaREZ4dFk5Y3dZaklvanpBeEVGQVoxdEpWTERlemdaZmNCXzUtRWdfUGJ4SU40eU56NEFJSEZ5a1gxWWc1OEpGV2VSZDA3ckZQNjQwaDV1OXpYSENBcnc3aGZ1djBaVVdieTdsT0dQajhmUjFVMmVCSTZKaGhPT0doMEdyZDE5SDFFSE5OSENyb01xVkFCdHBQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQbGttbWItSTktMlNUemZ0WFlXTnpaNmZCSjVWWUktSnZTV2JDQm52U3JGbDVOZU5zS0tYelV2QXB2QW5SMk9reTdtT3FDcW0xaFpGZUVWT2h5ZklKTnJpWjJwN2RvWkt3YjR1ci1NYmI3MXhZY2p0ZFdrb1EzVWxuZS02c2VpZXdKV09idzFpdHJUUk1INnhqXzAzbjAyWkdXd2VIbWFYYU9GTlFU?oc=5</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>12-05-2026 20:56 UTC</t>
+          <t>14-05-2026 00:28 UTC</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Kyowa Kirin</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Sun Pharmaceutical Appoints Dr. Andreas Busch as Independent Director; Committee Reconstitution Also Approved</t>
+          <t>Prevent Blindness to Hold 3rd ASPECT Patient Engagement Summit and Legislative Advocacy Day, June 7-10</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>InvisionMag.com</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9wFBVV95cUxNeHJaaG1CeG1EckxpM2FDZUVQSWxBRi1lOG9fYjdfcmh3NUE5X3lrdXhaTkROUG1PS1dkLVRkWGJwdnFJd3RHaHgyR2Vmb0NjU3Ewd2ZPcFo3ck9kVnlJQ3lOcFRoc21KX2piTWI0TVhvbFppQTBSMkRiTjVicko0R2RxSVEzRWE2LUUxUF93LWFIWVNreWYwTGIyRUZHOWVxeXJ6SDBMYklOMFZ0Nmc5R0YzaWQwb2xtTFBmTmFmS3dTc1hPTnRjbXVfb3Vnb1E2Q0dGOWhoazFHbHhTT3QxRE9FZnFtTmRianhQRlE0SVlUcHNWNjU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNdXJ4MjNQYVFyMHd1VlBRaG9LdTBmdnlBV2hDUlQxTVk1R09rci1HTjBQdWNFdUlMNWpvU3dwa3dZN1lGdGo2bXJYUkpSSjhmMlNraGwzNm9TWU1rZVhPSTQ2VVJUd0pxNGhmQWY1b0RuX0FCQllkaVN1eUxhQUpoV2dvQldkQUg1RW9mZWRqWlUzLXF4cFdMLU5XWlo2YWNLMFMxV0kzZWxwZVAydGFLX01EWkxKYy1hUm5kektFOElrMlpk0gHKAUFVX3lxTE00amItVWtTTHVjMXBqT2U0SWhLcGJQcUllOHc0bHhqM3Z6YzltZm4wY1M5SGpheVNzV0t5cVNIRlZGMC15Y1U5eExhZXU4SUxCQ2JFVHlLSkZ3enliVnVDZEpPZkotX3dvRnFRYXZUNGhoSWdFWVRwSWJpZ0NrMU9zWVhVYVMyOHI0ZzN4TnZ4VC1hZVZsN0RoeW16MVp1elpuWmdad0drMXJVaFhQTUh4RWRORXAtaGhPM0Y4eHRpWnFORkRHU0ExWGc?oc=5</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>13-05-2026 01:51 UTC</t>
+          <t>13-05-2026 21:03 UTC</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>JCR Pharma</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Giants of MS Awards Honor the Titans of Holistic Patient Care</t>
+          <t>Acumen Pharmaceuticals Reports Q1 2026 Results: Full Earnings Call Transcript</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>BriefGlance</t>
+          <t>Sahm</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNcWpsQ1BiTDhwbEY0ZVZrT3JCeGJjZUhQdXdwR2RrTm9zckJzanRQSVZnd0hZMjhLY3ZjWnJEVHVmWXFRdGVZTTR5M2NOXzFZUlVkQnljWmtpY3pYYUVNX3FZaDlMVE1SalJORVRKSVZubWhfeWJ4SnRocllOLWlVSE5zZkIxSU8xdl9xaGctUWVNbzltYWtLMHRn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOWXBwak9wem9QMnlWTWNsLTJ0SVQtNzRublJGOUdwb094V2hIN0JMUUlnMTRmdF9CUmxTbUhzVWpqVW1YOGJZU0tyMGxXOEpfTDd4bUhSdDVlWFZIaGZhUThMdW96T2pwbEE3WGtfTFJZUnpNSXA5UmpYQ19oUmNXS2tyeWszYkRoazlmYS1jUnNIVDJjU2RTR29fNmxicDBnVFpvUFNSU3NWOUtzT2FReHFGa2FMNFhQMkJFa0pwc19JbExqRUhr?oc=5</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>12-05-2026 22:14 UTC</t>
+          <t>13-05-2026 14:37 UTC</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>JCR Pharma</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Trump's FDA chief is out after angering pharma CEOs, vaping lobbyists and anti-abortion activists</t>
+          <t>New option available for Alzheimer’s patients as FDA approves expanded drug use</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>thecanadianpressnews.ca</t>
+          <t>AOL.com</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwJBVV95cUxQUWZxZlh4WVp1ODZ5T0UyT3VITjRqamVtanRGNHNTU0lIVVZiLUNMRVNsbjFfbEYydWEtTnhsSjFVM0h0NHV2aHNpZjQtYmNKeElGZk4tWl91Xy1CcE4xRnNfdFcwYzBWSWJsdVdEV2lNakZYeFM3QTl1WkRJejJJdmwwNVZ0WG1kc2tHWmFHNFU0X0RCRnVVZ2NzVGh5cmJPYkVQVGVmMlphM0pzbHJJT1piX3l6OUVEZ0laa2tkTWhmWmMtLUJTeENzWU9lYUQ0OE9PSFdpek12X1ZEOEtKVXVjUHRKdmR6VThCX2Vud0VKY2dHMHk2WWw3Mk1ibDQyX3duZ014QXowazBKYVZMc2JiNjN1a3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxObG54TFZBYy03Q2NOd3k2SHdIVkI3LWxSSENoNTFtUk9BZ1EzUUl4Uk9HUGRtMmt5R01rX2VfdU96SmdxVUZwSm93eGdNMDFoMmJ1OE9xeUxuNE51YjIta1BuZjJjRXhvUlMxNTBkZHhwQXFQcEdfX0laZ3lqZEEzMHRKcFFCWi12OFNF?oc=5</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>13-05-2026 00:29 UTC</t>
+          <t>13-05-2026 17:41 UTC</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Alvotech</t>
+          <t>Kidswell Bio</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Alvotech stock (LU2557688560): Partner Fuji Pharma reports valuation drop</t>
+          <t>Kidswell Bio Outlines FY2025 Results and Strategy in Biosimilars and Cell Therapy</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNOXZEVU1kRjk1UkFFbTg3RTUzdmprblI4UERRSVJIUWxROG9qX2h4NjFDUXR2QUNCYi1RVXlxaW1QbjBMNnlwM2RfalY3OTVSYlpqQ3g5THBSMjBrZEo1U2VIby1Yckl3Sm5OWkxWZ1IxNjBhaTNoWUJJTDhHWUpqMW5rRk1TZlNRV3VPa3l4eG9Gd1U2WnotWDlOYi1mYXhVRXZCYWZEdGVnWWhVX3V3WWo4THZ2VzlUeC1fM1N5dlAtMFZjazdMeA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPY25aMkVsYm9CYjNLR0ZoaTNMZG1RTzF6M2phWHRpTnNrUlNQQ0toQTNoV0YwRXhDT01JakZMZk5ZNU4xOWxzUGRuaWJBdnN6QW9aeGdUY2szM2Q5NUNKS2RqSkhibEZ1dG1fOGNnM1dPN1pNeWpXZ1ZPbHVncE9YaVFDbVliM2JmLW9ZS1pMaF9nUWdjaXhmbGJWQklHaGlRMllwNW4xNEk4MTVqVGwtaEZiQ0NoeUMwaUM3andIOUhQdVNqUWMzN01xekhlZw?oc=5</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>13-05-2026 12:42 UTC</t>
+          <t>14-05-2026 09:33 UTC</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Fuji Pharma</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Fuji Pharma (TSE:4554) Margin Compression Challenges Bullish Earnings Growth Narrative In Q2 2026</t>
+          <t>Fresenius SE &amp; Co. KGaA stock (DE0005785604): Global healthcare leader with US exposure</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>simplywall.st</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxOazVIQ25JUy1uWUVZdS14WkNwSUVGYkR5MWV6RFBVMHpQTVgtN25oclFZMW1SQ0FWSzlOX2txRXVYUktXS2MwUGRPaHFzT3lZUDZlZWZJX2tfNXJ2UklNbi04NGtDZ0RQSnV0eGFHWkdKQUFTNVFQV183UHBScVppbHAtMDktZUVOQlNaRm9mUTd6bm1XeXlTQmwxQTB6b1o2SmU3b3FrQnZ6T0FTUElhZlkwN3JVNU5zR0J5N1pXOTRFLUtVWEJFci1NamRFMkdjRzFFMWRGVlMweDY4V0dJS0U4WdIB6AFBVV95cUxPeXZ6SUFRWGQ3LWRWdGc1NEhZaERmNFFEUkJ2d0hFRld5SDQtRHFoNk1JcW5Yb09VQjJGTXNrNUlOYW8xa08xN0FWenJVX0NoRUZyWG1ST3k0Wi01ZkZfZHFMVTNMNjNLc3dEOGlQYWpoOHNxZGRyc3BQN3N0SlB2UU9valJtcWwwRzNrUUZ3YUROV1FQNlBRMGFFWXZtTS1YdTFtaFh4eDhaRkJ3OUNOQ1hOdGQ1SE1VVldwM0ttdTNRX2pjXzRCV3dULVQwazVCN1JRXzhDN3p3WU9ZRGZnb3hPcVlHclh6?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPMmdZbjl6dm13cE5HTXRPRXhha0ZlU0g2Z3lCdTlLaW1uZ0lRaW44eUp2bTBGT1RQTC0zd3NqRHdUR2ZCNmk2S053MmtGNWc3LWY5TUNVYWF3TnB5bzNnQzR5c2RDS0xEU1lkYmtVY3JEQzZvcU41WUZPWmpROFRETnI4RXllQVlTTjVWOVVOa3l2YUQtbXNlX0pURU5DTXFuVy01QUlJeUtnbGNCaU9mY0VQbjlYTHQxNVljOHVfVkFiWDFOZVE?oc=5</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>13-05-2026 13:45 UTC</t>
+          <t>13-05-2026 16:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Fuji Pharma</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Alvotech stock (LU2557688560): Partner Fuji Pharma reports valuation drop</t>
+          <t>[Latest] Global Intravenous (IV) Fluid Bags Market Size/Share Worth USD 5.46 Billion by 2035 at a 6.8% CAGR: Healthcare Foresights (Analysis, Outlook, Leaders, Report, Trends, Forecast, Segmentation, Growth Rate, Value, SWOT Analysis)</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>Yahoo Finance Singapore</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNOXZEVU1kRjk1UkFFbTg3RTUzdmprblI4UERRSVJIUWxROG9qX2h4NjFDUXR2QUNCYi1RVXlxaW1QbjBMNnlwM2RfalY3OTVSYlpqQ3g5THBSMjBrZEo1U2VIby1Yckl3Sm5OWkxWZ1IxNjBhaTNoWUJJTDhHWUpqMW5rRk1TZlNRV3VPa3l4eG9Gd1U2WnotWDlOYi1mYXhVRXZCYWZEdGVnWWhVX3V3WWo4THZ2VzlUeC1fM1N5dlAtMFZjazdMeA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNV3hjUDMtVkEtOFJZbnI2MG5nb004U21kZ0tlODVPaVBhenBjVldsRU1OTVdRT3gwcnN2aWtlWlhEMERtRnhwV3A4SW8yQlc5SmtWZG1uVnN6WDJMOXhrTWQ5WGg0R013QWRxOHk2RmFkMlNFVVJjdlY1anIySmtONmdDb0Vrd29ySlVJ?oc=5</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>13-05-2026 12:42 UTC</t>
+          <t>13-05-2026 12:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Teva Cleared to Sell Generic Effexor XR -- a Pfizer Blockbuster</t>
+          <t>Fresenius SE &amp; Co. KGaA stock (DE0005785604): restructuring progress and earnings in focus</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>AOL.com</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE9jX0RSZzhuUjNZWW4yRUNERnl2ak9oU2pqa0NFNFpwbl83YmFNUmdWSXd0ckdSV3dDNG5XM2JlLUFMOWlDa3YzMXFvWGVTcUhnQmFlUEVDNWZJNjNLUlNTWDEyTzF1Mjc3amc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPTE9hVmhmZTlUZ19vMkNWZDBlc2pBUzFrNGlCbHpTSGFpckVJTjBkWG00U092eGVrS0Z6NEpSWWE4OHBnVUNZUEJMQm9wTEZhdXBRZHRkXzRfUmtCdDc2RDlsMjZBVEg3czBlTmk3REZseHFmUlE2b1VXdmJYQnBDbi0tZ2x4SzFKTGd4U1NMMTBhcHZlbGI0cHVNSFZ2NTRWb3hkc1drM0tDTlFzTXBFWHBpVEp5YTZ4LTZucmZ2a1FaeFE?oc=5</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>13-05-2026 13:39 UTC</t>
+          <t>13-05-2026 20:55 UTC</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Alvotech stock (LU2557688560): Partner Fuji Pharma reports valuation drop</t>
+          <t>Fresenius SE &amp; Co. KGaA stock (DE0005785604): Global healthcare giant with US dialysis exposure</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -5468,253 +5468,766 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNOXZEVU1kRjk1UkFFbTg3RTUzdmprblI4UERRSVJIUWxROG9qX2h4NjFDUXR2QUNCYi1RVXlxaW1QbjBMNnlwM2RfalY3OTVSYlpqQ3g5THBSMjBrZEo1U2VIby1Yckl3Sm5OWkxWZ1IxNjBhaTNoWUJJTDhHWUpqMW5rRk1TZlNRV3VPa3l4eG9Gd1U2WnotWDlOYi1mYXhVRXZCYWZEdGVnWWhVX3V3WWo4THZ2VzlUeC1fM1N5dlAtMFZjazdMeA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNVG9ONVlRU0JFdGMwWnl6Z3NVQXRUMjZ0VmQyd29udC1RSWdOd09RNUxCOFllMHBFR29qLUJidGZ3Z3ROalhvcEZVWWhWV2h1Umd2ODMzcDk4TkxKWGdObTFBNTNKVDltdjdacjdCWW1fbjBpNF9wLS0wenZsV3FOaGNySnF2dDdvQkFXcTM5VXl0UWktVUkybU11MzVLdDNhbmU4alhHVTRWTHZuNWQxSU1kWkYtOTJRczBfNWQtSTZFTjdo?oc=5</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>13-05-2026 12:42 UTC</t>
+          <t>13-05-2026 14:25 UTC</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Teva Q1 2026 slides: innovative portfolio surges 41%, Emalex deal By Investing.com</t>
+          <t>Bombay HC Grants Passing Off Relief In 'OCTRIDE' vs 'OTIDE' Pharma Trademark Dispute Despite Bar On...</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Investing.com Canada</t>
+          <t>Live Law</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOWHIzMW9rWms0RFlfM1pGSFFPMXpwMW02M2dleTNjYUFsQ3NzdFhIMUdBR0M5NFRXY2MwZW1kS014UERMd1ptQ3g3RHhsSU1YZ19BdzJnVTMxdGNzVWN6bDVjc3UzdU5VWHBPWmFRaHRaaDJIV090RGk0aDI3X3g4b08tOFpFSllpZDVHdHB2NHM3UjI5LUx5bW10NlZZekxFX01wUlBxcFhCQ3JMZ1FDMDhPaTdBYmdPelE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxOWTRmLV9GRl9SdWNHR2xxZUl2b2hSOEEzMEdJa0l6WmR2bW1kY0UzcGpHbUh6WVJYdTdiWC1sMS05MEJnMUZPSHlkS3ZHekU1NTRWNUlLUnZlbjRIQzR1UEplR0tyTGpYcE8yZTlseWtoWkZ0ODNRUmphYm5pRHpENU9FZUpTcW1aakJvNVRWNTZfWF83RHFiNDltM3FDRWhRd0x1d0ZYUllSZHBFNVNqV0o4cl9PRmZHR1dBMWZ0NTI1alp2TG0zeGY0Q2xJRHBNX0wxUmxhaHJnMGFJNUxHYVEyWW5VNXpYRk1GMGJTTGR3cDY0NTBVTXBPWUdCZ9IB_gFBVV95cUxOWTRmLV9GRl9SdWNHR2xxZUl2b2hSOEEzMEdJa0l6WmR2bW1kY0UzcGpHbUh6WVJYdTdiWC1sMS05MEJnMUZPSHlkS3ZHekU1NTRWNUlLUnZlbjRIQzR1UEplR0tyTGpYcE8yZTlseWtoWkZ0ODNRUmphYm5pRHpENU9FZUpTcW1aakJvNVRWNTZfWF83RHFiNDltM3FDRWhRd0x1d0ZYUllSZHBFNVNqV0o4cl9PRmZHR1dBMWZ0NTI1alp2TG0zeGY0Q2xJRHBNX0wxUmxhaHJnMGFJNUxHYVEyWW5VNXpYRk1GMGJTTGR3cDY0NTBVTXBPWUdCZw?oc=5</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>12-05-2026 19:46 UTC</t>
+          <t>14-05-2026 09:13 UTC</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Is Teva Just Looking Out for Itself</t>
+          <t>Cantex taps Headlamp Health's agentic AI to shine light on MS responders</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Yahoo</t>
+          <t>FirstWord Pharma</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE5lM1Z3bUdUSjNQMkMyT1pWX3BHLXRzMG85aEJTVXNWWEE4MkpBOFBBdzFFLWc5WjUzXzk4bGVRekhGMl90cFMtUUNoc01IdGloNkk2MnBzZU5NenZLRmVlSzQ3d1VGY0Y4NkFMU01sTjdBZXFRQTFqNWhZMl9oZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTE9HRUdxSml1THF2SXJkSjVsaDRSR3R4a1ZqM1ZibDYwTXh1eWJtWVBYcnlDZzkzVEJ4cWVhZ0o1dVRHbmZTaFhaVEdidFczUEs1cXQ4?oc=5</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>12-05-2026 22:00 UTC</t>
+          <t>13-05-2026 19:15 UTC</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>I Walk 10,000+ Steps a Day—These Are the Only Sandals My Feet Can Handle</t>
+          <t>Sun Pharma Schedules Q4FY26 Results Announcement and Earnings Call for 22 May 2026</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Good Housekeeping</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNUGhiSWdEbDFEM19tRW95VXJLdHBWekhGS2djOHJNWmtmcVBrYVViNy1tMlNEa0RsaWFoTHJJdlpoY3VsTmpNenhDMEhhcTRPNUwwbTRjVkhfYlp0ZWVnQUVwVy0tMVhsWXpYN2pORTdDWXpBakdHUG9sZ08zWVR1YWFWa25ONi1vdG93?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxNNnhzZ1Q0ZVZjc2N3eG1xamtaNGJmR1M4QUpvXzFHOHZJTFJKTTcwTjhqYkYybWZQYTY4d3g5UUY1VzZTVW5vRDdxM1AyZS05NDZQc2FUUzA3WGtCZzlRUVpNVThsLUstUTRFV2RMakEwQ3g1b3JFZHZqWUJPRkE2eDlnLUlfZEItbWdKc2s3czNPRGJxNEdaa0hzdzUxV3BQWTZpZVBKdEdreHNxbzVnbG9EbkcwbmRld25iWjhrVVk1SXhleWtjVnhNTE1yNHhWSG40elpR?oc=5</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>12-05-2026 19:14 UTC</t>
+          <t>14-05-2026 01:41 UTC</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Traumatic Brain Injury Therapeutics Market to Reach USD 6.5</t>
+          <t>Solving Complexity in Modern Biopharma Analytics</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>openPR.com</t>
+          <t>BioPharm International</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPNlhVNjg1d0UxNjVUZlp1YVpGUzJzdHRnbzBBYV92M0hXMHJDMmpZdUVaVmxuVWVTR1pOYXRLQ3hPZVRKSXVqSnhfSXg5aC1QVFh2dmVJa2VtUUluZERGdzhHMHVZekJ0cl9pSXJpbFVNVUUtY0RYQzRGVW9KSW1aWFU1eHlqZmNIUU5kcF8xMkhIN0psdjZzY05Gbw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNeHJwNkZzRFMweG5UX2J1cXoxdDBOOW9heUxVUHNuZk9feFFTOU1PR3J4THJZdHlqX1VIMnhqNVE5NTI4RVI2MTNNZXBfTHc1bm1lWk5lejhoUU9ZQzQ4cHUtMmVrT24zeGtyQkR1RG9EX19VQmtIc1FPMk52eGNiZ0dSZkhsWTJKVXlsbWxzY1pDbkxTeVhHVQ?oc=5</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>13-05-2026 09:17 UTC</t>
+          <t>14-05-2026 02:26 UTC</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>‘Fix them without delay’: Supply shortages hit Parkinson’s drugs</t>
+          <t>Hopewell Holdings Ltd stock (HK0054000679): Wins key US patent challenge against Merck</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Chemist+Druggist</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxNR3ZvRjlhU05reXplOTQyeElFZU9kci1kc3BaZnJvVUFkRzNSOXBDMUU1NTdHQ3lJWUVReVFGU0g0LWduMnpFZ3JRT012azA2SG5FeHBQZXQ0a3VKck9yNXg0Y3V1Uk90YW0xemNBLXBTSVI2ZVpObV9oU3JqUG1tWU54NGIxZFROSE56Q1NwY3JablRWVzFSMkxKUk1objlEVkltQmtsX1R6cDcwa19KYURfVS1YTU82YnRqY0JfU1MtN2JFWTd5WnlyVF9yMnZ5ZXRTSkVB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQMlJPd2lDZmhwOWt4Y2QzOXhVQnRNMXcxMlk3clpvbHZ0aVZEQ3V4dnhpZHB1X0FObE5ZTUtjeW5vY3cweG11WEJ1T19jQzlSZDJWUzlqMXkxNlZFYjVnbldPMWt1OGlFeXNtTUEtdHFZdk5odU5UNm5PdXNrdFlkNm80dnBXVGtIMVpjbWk5X3RvSlliUlN6OVBLUEtOSFB3Umg3cTU0WDVJanFkUVNjYkpaLWl0TEZtSWxyNlpsNFpXallJeHFn?oc=5</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>13-05-2026 15:22 UTC</t>
+          <t>14-05-2026 09:02 UTC</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Samsung Bioepis and Seoul Bio Hub launch program to boost Korea bio startups - CHOSUNBIZ</t>
+          <t>Vanda: A Long-Term Pharma Growth Idea, Despite Q1 Earnings Miss (NASDAQ:VNDA)</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Chosunbiz</t>
+          <t>Seeking Alpha</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxOT3ZqMERwMmhLSnJfcFlZeUxFMzJYV3NzeUdpNGdEYUFCYjZOZ05DOU9MT3VHb1FUbDZXRDVrUmtaNnpjYnNKY1VXQVNNX2Z2LVVCZEhjd3ZTUUVOckxmcVpoaE9nNDJ0cGNmYmxOdUtjd2Q0VE5nd0R2RzFyYlZRMdIBlAFBVV95cUxPUWJUZm54Z1dnVjVnaV8xZEc5NjNOeTVnUGZyajN3ZWVsRkp0Z25XRXRuM0dLdy04TlJ3bm1UejRsRlBpSFFHLWZDd2E5dnhQcTYtWDhqckVwZ25JYWw3aHdVNHhuUm5rMk5lMmN4LTBZREs2S05laG5abnp4d19QMmxXVlR1Q0N6UHlQNzN5cmpsN3BQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNcFFPS0ZjVW56SlY3dy1VWEM3ZmdBWThpU3JVVjVWWmxzdTlwaE05SnlUQzFWSU1oWTNWQnZFT2NFR2ZjTXlqOW1wODZMbzRSMURmb19nU3VTT0NDZVdObGFHbWZxemVuZGJWZ1BBNzdERWJRNkdOcGt6TTI2aS1iOFNIQll6WkFTMngtaWV0TFItN0ZOWnRXc25LUDc3XzNfSndNMUU3eU9mQQ?oc=5</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>13-05-2026 06:31 UTC</t>
+          <t>13-05-2026 17:34 UTC</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Samsung Bioepis Partners with Seoul Bio Hub to Nurture Biotech Startups</t>
+          <t>BioHarvest Sciences Appoints New Head of Business Development for its CDMO Division</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Seoul Economic Daily</t>
+          <t>TMX Newsfile</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQYzJJYkdTak9ybFpMVGtkdTRXUFQxcFI2bkI0d2dkTHROSW1sQ0RCQXhPZGN5THdEQ0xwVXk3alBlVzZtWmtjWGVfeDVkRHkyY1lDZEpobktDWlY4cUUxd2EtUnpmWHdURmJkLW9lMkI2Z3RQSzdRZFBwVnI2UHkxYkh1ejFZRDREa1ZXSEtmU2VpS1hHc21rSG5aajY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxObkhmS00xVEVla3FHT2kxbjQ5eS1XLWdHYy1BLUFZRnVUVklla1B5NHV2TmViUnd3QkdhZXJLR3BNdGJFRHVlN1VaQUdiM2ZQeGtUcW9jeWxzcW1PYTZqejBlTjh4VEpnTHZQUEpBQ2RTMmxkbVZoanQ2bmhLREdnUjduRGNpd01tR2pGSFFwVzBITm5vTlBTZVVMN2hJUkZYR3FpUzJhV1Q0YU5GWGVZREx2aklmQjVIUC1HZWpJaGhuT1dUQXc?oc=5</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>13-05-2026 05:18 UTC</t>
+          <t>13-05-2026 21:32 UTC</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Samsung Biologics showcases oncology CRDO platform at PEGS Boston</t>
+          <t>Pharma Quality Excellence Awards 2026 - Celebration and Conclusion</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>koreabiomed.com</t>
+          <t>Siliconindia</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE1CSkZnOUh2V04yWUNpYmJBOUVCWEM2Uzg2VklBODk0RENsTWlnY29pVjRDWEJVOWlfVG1qN19DSUZaWWhYX3ppZnJUa0UyWjBUdnA2bUw1eHFVT0wtUld2NXRIRDF6Yk5IM2c2WHZR0gFyQVVfeXFMUGZHeWM0OFc0RzlBS1NnVGdaOEtlMDhxT1hMbUY1bVl4YTRRZTJoS0ZsVl9PeDVKNk8yeE5FakhhTEFOM1YwLTVxT0IzZy1pTmx4Yk4zTEZ6Qm9oMEE1aFlUZThPelVwSVJhQ25fdFhvdXln?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxOcTV3bWhuZ3VaZmRncmFHOENMX1NQaEV5M1phdVc5b25KNGxSTGxOcWl5eW5TaGZBbjBhdndWN1pvY3NualpsUjlpaHpTeG91a3QwWkg1SFZqaUp2SDBzN1h6U3RYTHRBbU9Cc19VOWpKZEVXM19yZXVjLUVheXdpZWFBZkp0LWFCRzFwazllWWpGSTZ4ejZIeG1Odk0tMFlVWERvdWxXNkpCS0YyaUZaQjlIaTlxYVZoZ0RNUE14bGwxdDJnTFhUdQ?oc=5</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>13-05-2026 01:04 UTC</t>
+          <t>13-05-2026 14:20 UTC</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
+          <t>MS Pharma</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Indian pharma fuels Africa’s ‘zombie drug’ and opioid crisis</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>The Straits Times</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOUTVkNnQxLWJFZkFidzlBV0dLNGIwc0FlWGdhamFBTGxkM08wS1hnY0pfTWdZdkdIbXN4VkpnaDc4THJ4UmNmWkM0cUVjVlhzblJBY29NeVJZWEVXeEVZUm5fUEZYZWlqR3QzMXVLQVRHNGR4Q0NHU09idU1TbEE0WlB2VXFHNW9XUVBVc0pwYXJiZ3ZYNElr?oc=5</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>14-05-2026 02:05 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>MS Pharma</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>She closed $30M in drug contracts; now she’ll hunt CDMO deals for BioHarvest</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Stock Titan</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNaW55V0hkRHdOOVlKRXdJc3JwWDlEd1FSTlVxUjI5dXVTNFREakhxaTAxR2hBNnphM1Z4Qzc2emlHZkFOZURyM1VKdW52MTdSaGZ3dTFVZ2puNFl1Y2ZSbXljU05QVzBBQXpHc1ZxZlNnVGRlVWpDUzZBVzNYaWxpaFViTjIyTGx1VTdGc1dvOW9hM3RReEhLamxyQWNCXzdFMHUwS0JDMDM3Tzh4WXJDZ3NMOTJPSmY2SzZPUDln?oc=5</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>13-05-2026 21:32 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>MS Pharma</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>aTyr Pharma to Participate in Upcoming Investor Conferences</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>The Manila Times</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPbGFHNEt6T0d3MzNxNzFVdHQwOWJWcnhkTkJheWRUNGlVZmUydENVSVBMeFFGbUZvMm9MTk9DVnVtRTJ1aE9vLWtRa2JfX1M3UmVUNktiMUlxZG9NSF96NnFHUTRFSUFVX0F6LTdHakl1T1U5aEkxUVIxODJ1RkVXRlQ3b3lkT1E4YVNIV3hpYWJBY05KeDlXOVJpQVBWMXljMEcyQlNyV2FXd3ByMnJuRF94MnplcG4yMDhHNXc1UHl1VlA4SXM0MElhUDFSd9IB0wFBVV95cUxOOUsyeGktb2ZBVzhSdnlucVZtZy1sMUozOTkyNUYwRUg0R1N1ek4zMXJnZ2hHUEd1NGUwanRvelI1TW1HYnVGa0gtRWM3WkYyTGJsT1Q1Q3RoUUZWMExyUkE0di1rUGFXZnpCSHlodVBYUGNQMnJPc0hjOVlDVDlfa2FzbGM4ZERqTnJ2R1FPazBKclN2elZiR3RrMW9OMjd0U0c0WVZrMXFvVFFyazJJWjhSSXBtOTlGYXoxdnRCN0ZJY3NYSzdCaG54b1lTUUdPQ2hz?oc=5</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>13-05-2026 20:13 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Alvotech</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Alvotech Plans June FDA Resubmissions, Sees Biosimilar Approvals by Year-End</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQbXI2eF9aMkdCalNMcnY3UDdUblR5TjdQYzlnaVhRcTlNcjk4WFpTbzNFUVJUcko2c3JuUVJoYmlhZnJIVDBodllqMEdMOE80dTlMWDVyMmJ2M0dqS0ZtQWZXNGJZbWNpRHdzaVZkZ25GQVVGanBHbmxqYmt6OFlqVVRBSU1NTUdmMjNfVTdNSGF1azVUcUplb3JidUQyQWU5QzVLRzYzSjB0Zw?oc=5</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>14-05-2026 00:13 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Alvotech</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Alvotech stock (LU2557688560): Partner Fuji Pharma reports valuation drop</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>AD HOC NEWS</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNOXZEVU1kRjk1UkFFbTg3RTUzdmprblI4UERRSVJIUWxROG9qX2h4NjFDUXR2QUNCYi1RVXlxaW1QbjBMNnlwM2RfalY3OTVSYlpqQ3g5THBSMjBrZEo1U2VIby1Yckl3Sm5OWkxWZ1IxNjBhaTNoWUJJTDhHWUpqMW5rRk1TZlNRV3VPa3l4eG9Gd1U2WnotWDlOYi1mYXhVRXZCYWZEdGVnWWhVX3V3WWo4THZ2VzlUeC1fM1N5dlAtMFZjazdMeA?oc=5</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>13-05-2026 12:42 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Fuji Pharma</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Alvotech stock (LU2557688560): Partner Fuji Pharma reports valuation drop</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>AD HOC NEWS</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNOXZEVU1kRjk1UkFFbTg3RTUzdmprblI4UERRSVJIUWxROG9qX2h4NjFDUXR2QUNCYi1RVXlxaW1QbjBMNnlwM2RfalY3OTVSYlpqQ3g5THBSMjBrZEo1U2VIby1Yckl3Sm5OWkxWZ1IxNjBhaTNoWUJJTDhHWUpqMW5rRk1TZlNRV3VPa3l4eG9Gd1U2WnotWDlOYi1mYXhVRXZCYWZEdGVnWWhVX3V3WWo4THZ2VzlUeC1fM1N5dlAtMFZjazdMeA?oc=5</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>13-05-2026 12:42 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Fuji Pharma</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Fuji Pharma (TSE:4554) Margin Compression Challenges Bullish Earnings Growth Narrative In Q2 2026</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>simplywall.st</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxOazVIQ25JUy1uWUVZdS14WkNwSUVGYkR5MWV6RFBVMHpQTVgtN25oclFZMW1SQ0FWSzlOX2txRXVYUktXS2MwUGRPaHFzT3lZUDZlZWZJX2tfNXJ2UklNbi04NGtDZ0RQSnV0eGFHWkdKQUFTNVFQV183UHBScVppbHAtMDktZUVOQlNaRm9mUTd6bm1XeXlTQmwxQTB6b1o2SmU3b3FrQnZ6T0FTUElhZlkwN3JVNU5zR0J5N1pXOTRFLUtVWEJFci1NamRFMkdjRzFFMWRGVlMweDY4V0dJS0U4WdIB6AFBVV95cUxPeXZ6SUFRWGQ3LWRWdGc1NEhZaERmNFFEUkJ2d0hFRld5SDQtRHFoNk1JcW5Yb09VQjJGTXNrNUlOYW8xa08xN0FWenJVX0NoRUZyWG1ST3k0Wi01ZkZfZHFMVTNMNjNLc3dEOGlQYWpoOHNxZGRyc3BQN3N0SlB2UU9valJtcWwwRzNrUUZ3YUROV1FQNlBRMGFFWXZtTS1YdTFtaFh4eDhaRkJ3OUNOQ1hOdGQ1SE1VVldwM0ttdTNRX2pjXzRCV3dULVQwazVCN1JRXzhDN3p3WU9ZRGZnb3hPcVlHclh6?oc=5</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>13-05-2026 13:45 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Teva</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Wall Street Thinks Teva Stock Still Has Room to Run After Soaring Over 100%. Here's Why Analysts Are Right.</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>The Motley Fool</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQQU1xNHU3R1JfbWI5S2NMX3F3TG9xQVVRNG9qQlFTS1hJNWE4WHV4blByS19PeU12dGJCR0paQmluX2Rad09mWUlRR0hraGQwTFgxb2JuZEJvWGpDY1o2a1Z1RHVxRnpIbU5OSWFvOVhoZF9XRjNEUm55UVNKR2ZFNmMxTHAzUlBHVldCeGxJWUt3dW14YUlCdg?oc=5</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>14-05-2026 09:06 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Teva</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>How Investors May Respond To Teva (TEVA) Showcasing CNS Growth And Emalex Deal At Key Conferences</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>simplywall.st</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxPV3BNcHg0aFZzcGFfdzdhU2g3dHBEckEybW84bFFMdlpWNU1SSU80elhhSmFzc3NEXzhSUGRwcHdzSnA5bkpndmRWUzhtRDVpYklDTzh6aEZXUUMyYjZrZlVNNWZEMGZEcVhKVmFYZTFKQUVnQlMwOUhVZ1dYZ1NxSmNDa0pNdmY3NGpQLUFSbkVIQno3RzBLOTVBN3RLSXFvSm1iM2g3dldsaVBZYWtmWWJzak5KdlZXdUptTkJwekQ5WjJsbV9OVktURTd0akd2QVg0QlBRd1k3QURZLWJrN1drclgxdjROQWd0NkdaUlBhOXFf0gH6AUFVX3lxTFAwZ3VlbG5lZnlZUVkwU2kxN1Y1aFZmcmcwRE9ndllOWUczcjlEWmdjdk5mcnJSZzBoRDFvUGZWdUVJYmQ1VnNRUk9BZldyTTdtd01oUU1vRFdKc21adE55ZHRjYXk4Q2xCb0c1ZEhNdFZNLVNwdVZTSWxVTnJqb2ZBdWhYMGs0RW05NloyMXZiajFuekJJNzFLblBxRlVWVmtSTE9OZ1hKZktub0VMd0VHdHpseHBaTUF1bWJjWVlkYzZYUUR4U0pUSmhMNUxlZTBMMS1nX1Vic1NrTngza29ybkNVTzlBWEE1R2FoT2lRQXZwQXZZbEVIRnc?oc=5</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>14-05-2026 05:52 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Teva</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Wall Street Thinks Teva Stock Still Has Room to Run After Soaring Over 100%. Here's Why Analysts Are Right.</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQOXhTUlhTTl95cTR2QmY1ZV8tVmZsSmszRFhjRzBOZEtRaG5TdFppd3JtamRtbGpSN2xFc3JST0FKbV9rUHFTcnJDeHprUEFfR0I0WlFYTzROc29fRE9OanQ0SDFWaW9TTTMxbmE3NzFYR3ZtWnNOQkRmRmdpbUJwM2JRb25kSDhRY3BTbVBhc1pSdkJsRFEyTTVB?oc=5</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>14-05-2026 09:16 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Teva</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Teva Pharmaceutical stock (US88162G1031): Beats Q1 2026 earnings with CNS growth</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>AD HOC NEWS</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNUGo5OG0ydHRxdmFXZlRSQUFtemZOY0RxaUZCWWlhamkyR3ZXaTkzb0lxRnltWUYxaFJuN2ZNNG9QaHVHTExyZzZhdVNOTW1tenFlZmhyQVhDbUtaUVNRb3lraS1tbnplalVzaURadHZDVC1BTlJ1Qk0tMWFlT2tYSnh4M084OTRoWFlnNkd2QkhRWktMNE9sdGVxRkdQTmlOa1hoaGlEMWpOQXlzU1lYZ1p6UWU0SUNyTjVhQU8xR0hHQzBDdGtwdw?oc=5</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>14-05-2026 10:46 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Teva</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Teva Cleared to Sell Generic Effexor XR -- a Pfizer Blockbuster</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>AOL.com</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE9jX0RSZzhuUjNZWW4yRUNERnl2ak9oU2pqa0NFNFpwbl83YmFNUmdWSXd0ckdSV3dDNG5XM2JlLUFMOWlDa3YzMXFvWGVTcUhnQmFlUEVDNWZJNjNLUlNTWDEyTzF1Mjc3amc?oc=5</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>13-05-2026 13:39 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Teva</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>When ‘low profile’ is ‘high valuation’: Soma Das</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Business Today</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQeVkxZlcwNGlmZmU0SUpxMm41OVpjMEdKZWNRakJSeUJQZlNrZjA1WnBFUDBNdDM4UVVMXzYwSFZWX0k5TmhRQjFLclVlRTRrQmp2ZUVoTG15N3BoZzJ0dmZUdnlLR1dKRk9jdmtEeE9MNUJOdV82U2VQblhHSFo1OXBTSmQxbTRjcHdHTFV4bmEyQ2p2ZnMtQVJGemM5N2U4SUlXekpCZjNsVFY3RnItU0RYc9IBuAFBVV95cUxPcVZ2dUszemFtejMwSnR5MzRtaGtEX1hkRUVVWVg2enVWQjVUTHB1YWhnWU9lUjVzQ0duLUNQcGZheXZjRG9sQ0I2QUZ4R0tacnVnODdITER4NUlJdEdiNG0yODdjQnhRcTBGQnkzcXdIY0d5RmtmckdrV3hUMG5GeGozWHg4Z0Zqd2Yyd0VTRUpjNTlyd1JNV0NaUVVJRmIwa3FNcTFTUjRRWS1nb29TWU1Qc0hTbE04?oc=5</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>14-05-2026 09:15 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Teva</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Alvotech Plans June FDA Resubmissions, Sees Biosimilar Approvals by Year-End</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Inkl</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQZU9idjU0Mk9ackZiQUtpb0V1NGlneDJzMzhnakJySzBWcDJ1b1l4U2tlbmMzQkk5N1VWb2gwb3FlVGFVU0ZPcm9HWjJZNmppOW5Wb3JDcjRmUk9wRl9EWnludjRFd1hhdldoTWowZm4wVHZzZlduTHBZTms4MEFjUW94WXFobU5zaVpVZnVkQkNBRDJnUXUxZGM5QW5neWh1dHAw?oc=5</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>14-05-2026 00:18 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Teva</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Alvotech stock (LU2557688560): Partner Fuji Pharma reports valuation drop</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>AD HOC NEWS</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNOXZEVU1kRjk1UkFFbTg3RTUzdmprblI4UERRSVJIUWxROG9qX2h4NjFDUXR2QUNCYi1RVXlxaW1QbjBMNnlwM2RfalY3OTVSYlpqQ3g5THBSMjBrZEo1U2VIby1Yckl3Sm5OWkxWZ1IxNjBhaTNoWUJJTDhHWUpqMW5rRk1TZlNRV3VPa3l4eG9Gd1U2WnotWDlOYi1mYXhVRXZCYWZEdGVnWWhVX3V3WWo4THZ2VzlUeC1fM1N5dlAtMFZjazdMeA?oc=5</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>13-05-2026 12:42 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
           <t>Samsung Bioepis</t>
         </is>
       </c>
-      <c r="B196" t="inlineStr">
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Samsung Epis Holdings earns MSCI ‘AA’ ESG rating in 1st global assessment</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>koreabiomed.com</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE9zSnR0VW5KVlJVMWpTSEtZdmJuSDE4ZDBlWEhOMlhjSDNxWFVCOXdTYzRjaHo1a1FmN1VoRVhCbUxuNG1ZTXlsWjBqUkw2THdQNFpEUjNGd1gzZG55djl4UjU3cWVsZFotZzVDSDhn0gFyQVVfeXFMUFdWY2E4SXNLXzJVcUNGNXRxdTVsd19XZkx2X180dWRLUmJVUHRkSHNSUU9fNU1FLUltZWJvZXVfMkt3cFIwQzZhWGdjeVZZS3V2Mk1USWhhQVVCRDNvQWJtTWxJd1dza0hjNktfcEdIa1N3?oc=5</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>14-05-2026 00:44 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Samsung Bioepis</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Samsung Epis Holdings Earns 'AA' Rating in Global ESG Assessment</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>아시아경제</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE5OeGJlSTlKd0ZOWWU3M1NfZkM5RWlFd2IyRERua2pleGp4NG1sMUkwa2tTbDNyQ2UwWDg1NXJzdUJ1SUhPdVRxa1BEd28zN3VxMVNBOXFXQjVJWkZvaURqVmdQMVQ?oc=5</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>13-05-2026 23:30 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Samsung Bioepis</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Samsung Epis Holdings Earns 'AA' Rating in MSCI ESG Assessment</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Seoul Economic Daily</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxONllvOWRnaTNUQU84TXkydHk4UEdnZ0otT2pEakJNdDQzNzJqN0RKeXV3YkNVaVowSUJRTWc5cXdLYTRnSHdrWXVrNkpqMjh4c2IzWWVwbXU4cnllREVKT3p2Nm1NakFKZnVIZmdWT1FEeV9yYk5mMzJleEgzazFKN2pqdVJoYTI2bV9kV0ZVV25TMVJ3Uy1yQ3c4aXBKWDJKWjJzNw?oc=5</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>14-05-2026 01:01 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Samsung Bioepis</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Celltrion Inc stock (KR7068270008): US biosimilar launch and facility acquisition</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>AD HOC NEWS</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQak1zS2RSWk16TTlwcHRPUDdkQnhWXzRJc1JVbTNyRUM0SmdvNUhQWEs3Mno3RU9YenRKc0ZoS01sbHNzc2JlZnVSMk11ZEtQM3JJMm55dzBKR3ZRSFBYNEtROXhpQjFCMGRET1ZpNG9RODc5RG5ka3R4dEd5MVBlZ3JzcmhTQVM1R1RQcERqRjE4WHhjWXVOX21GU2FkMEw1VVZyNGZNNEg4bzhETU0xd2FfMjJ5Y0xOTFdldHNkSkFSRjA?oc=5</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>14-05-2026 07:44 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Samsung Bioepis</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
         <is>
           <t>Alvotech stock (LU2557688560): Partner Fuji Pharma reports valuation drop</t>
         </is>
       </c>
-      <c r="C196" t="inlineStr">
+      <c r="C215" t="inlineStr">
         <is>
           <t>AD HOC NEWS</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr">
+      <c r="D215" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNOXZEVU1kRjk1UkFFbTg3RTUzdmprblI4UERRSVJIUWxROG9qX2h4NjFDUXR2QUNCYi1RVXlxaW1QbjBMNnlwM2RfalY3OTVSYlpqQ3g5THBSMjBrZEo1U2VIby1Yckl3Sm5OWkxWZ1IxNjBhaTNoWUJJTDhHWUpqMW5rRk1TZlNRV3VPa3l4eG9Gd1U2WnotWDlOYi1mYXhVRXZCYWZEdGVnWWhVX3V3WWo4THZ2VzlUeC1fM1N5dlAtMFZjazdMeA?oc=5</t>
         </is>
       </c>
-      <c r="E196" t="inlineStr">
+      <c r="E215" t="inlineStr">
         <is>
           <t>13-05-2026 12:42 UTC</t>
         </is>

--- a/news_results_raw.xlsx
+++ b/news_results_raw.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E215"/>
+  <dimension ref="A1:E194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,7 +478,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>13-05-2026 20:00 UTC</t>
+          <t>13-05-2026 23:00 UTC</t>
         </is>
       </c>
     </row>
@@ -490,22 +490,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Nevian Lifescience begins pharma exports to Canada</t>
+          <t>Sandoz climate targets validated by Science Based Targets initiative</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bangladesh Sangbad Sangstha (BSS)</t>
+          <t>Drug Store News</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1BbGc1SDBDU3JxNzlUQm9WaThjTkhaNXhZOUlLUWd5UDV3ZkRmTld5dk54M1puOXotMXVsOUJwQ1ZlR0RCSzBZYW1tT0p6ODZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQUEs5U0JOTWpURld3VjVZVWJFLXhvNUFVR0pfeWJzdm81ZlJUbHBDcWxBUGE1U1lFS3V4bnRkbHZiTGpXUjdDYnJWdTRkQWM0LWI3dDd2eTYzZ2ZURkVQRjZqTmNsR0h6eHBuLTUwYWF2bDhUTjl5QTlJVll5b29KY3ZpYkQyR2JXWGNkUEpZeXpWSGY2Nmc?oc=5</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>13-05-2026 16:38 UTC</t>
+          <t>14-05-2026 14:15 UTC</t>
         </is>
       </c>
     </row>
@@ -517,22 +517,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>From Tongi to Canada: Nevien Life Science marks export milestone in global pharmaceutical supply chain</t>
+          <t>Nevian starts exporting medicines to Canada</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>The Business Standard</t>
+          <t>Prothom Alo English</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPV3hBT1AxUGRsdHhpOHF3SEFDcGl4d2Jkc2hOdm81cUNrVllRbXdabDRfQXAybzBlYlh0Q2ZDYTcyVTMtc1RpaGhJV29Eb3B5cDktOEJJLWZoQUE1cldtVnNpWVN2eGk5NTFtc3FkUU9TTGZjWUhha215RngwdnJVZFBiMFQ3UTBucVFOQldzRnprSWg3bjVOdnc5NVl6RzNLdy02QUhsQ21yQXA4aTJqQ1RaR2RzSmpjMmdXck1sNNIBvwFBVV95cUxPV3hBT1AxUGRsdHhpOHF3SEFDcGl4d2Jkc2hOdm81cUNrVllRbXdabDRfQXAybzBlYlh0Q2ZDYTcyVTMtc1RpaGhJV29Eb3B5cDktOEJJLWZoQUE1cldtVnNpWVN2eGk5NTFtc3FkUU9TTGZjWUhha215RngwdnJVZFBiMFQ3UTBucVFOQldzRnprSWg3bjVOdnc5NVl6RzNLdy02QUhsQ21yQXA4aTJqQ1RaR2RzSmpjMmdXck1sNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE1uR2F1aVg3d0Fjcm9uRERKM0kzRmtqM1VVcFVnTlZmVHVxeE1UX0kyOG1DOFJfcmtBcTFrdlVjanpRb0hDd1FJVzRHU0J1R29RcjVUTjJSQjFxV3FVUzZuR2oxNTRkbDTSAWdBVV95cUxNbkdhdWlYN3dBY3JvbkRESjNJM0ZrajNVVXBVZ05WZlR1cXhNVF9JMjhtQzhSX3JrQXExa3ZVY2p6UW9IQ3dRSVc0R1NCdUdvUXI1VE4yUkIxcVdxVVM2bkdqMTU0ZGw0?oc=5</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>13-05-2026 15:45 UTC</t>
+          <t>14-05-2026 12:53 UTC</t>
         </is>
       </c>
     </row>
@@ -544,22 +544,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pharmaceutical industry key sector for diversifying export basket: Health Minister</t>
+          <t>BAH to be Held Tonight at Insurance Specialists</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amader Barta</t>
+          <t>Eye On Sun Valley</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxObjBhdTQwMVNqdlcwSTBDSnZIN2RSNlc2Vng4eWFqaFdHM0JQZXV4TzFnb0VjMU1rUnotS2NnYkNIV0hOMVo2Ym1fZXNRS3pXVFVIRjlOalZSTnVFTzFWVE1LVGF5QXZJeTN5cDliM2FlQkJKUlk4a3lGZUlxNmlvempMQ0g5T2U1X0FxR3M0RTJQS0txY3JIYjJ4LWRkdzB3NmEyWmR0blMwUUlGdjdkenBhZUxGVFRLaU1EX1lwTVczUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPNEZIN2l4ZTFkRnIxQ3dXN084SHVWUUR0ZVd2c1dxQlBPWXpOWl82cjFISk1aS0pESjgxd3EtUzRyelFPMVRXX0pHSDBmT3g4bk93d1ByMmVhaWMyT2JycUdEZHMzMWJLVmRSQjdhMHMtYW5GcEhNMklXNnczY3k1eUg2MlU4RWpoNnVLZkJTSXowMG1mNGRwSG9R?oc=5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>13-05-2026 15:14 UTC</t>
+          <t>14-05-2026 12:45 UTC</t>
         </is>
       </c>
     </row>
@@ -571,616 +571,616 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>This Day in History - May 13: Reporting done on polluted water and Tyson Foods</t>
+          <t>Pharma industry key sector for diversifying export basket Health Minister</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>KOLN | Nebraska Local News, Weather, Sports | Lincoln, NE</t>
+          <t>The New Nation</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOT3UxNUlCdWZIWjVxRHJaTjlpTVhGMTZEMkZvUEpSSHF3UFBVUGhsSjZqdGh4VUwxZ3RIQlZVM3hmNlB5WHNLOUVhdURVbkczT2I1eHQzcGpYcEI5akdUaUNXcEUyT2RtX1hWT253a2FhNmtERm9GVXAxdFJKTE1hd0Uyc2tqZ0F0Y2hBdktDQlNqU0pIS0RTWUl1VTZJbXFNOE9PUHZHZUJ4RmpKaXJVZWZOU3hnMjNBX0NVLVJnUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE1UbU9WdVFfNWhqU01FSU96dDQyTEthRTZhdjIyYTZCSjBJSGw3ZHZPeUdMeDRZQ2pvRzZocnlIdHV5SEJMa0loMElNbGF2TlE?oc=5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>13-05-2026 15:28 UTC</t>
+          <t>13-05-2026 19:58 UTC</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sandoz</t>
+          <t>Formycon</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tony Chachere's stuffed bold burgers</t>
+          <t>Formycon AG stock (DE000A1EWVY8): Gains momentum on May 13</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>WJHL</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE1BOHR3TFJCREpnTkp1VXdLM1F0Sld1RFhxVlhzV2sxbXRIWXBkZmsxWkhPaUtQRFlEWjZYa0ZzMmE5Vl92MWpwUXMyYUNYVl8wVVV3WmQ5TU90bkFTMnhHX2ZxTktPNmZBWUJ0di1fM0p2NWtFUlhURm9lRGg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOcDJyRWczT1B4RzZ1LWxqTEl6WWtVSG5ScnpYT1ZVaC1yRU4xMWVkUzRpakp3Vkg5cGtTLVhGaGJnQXdxdkZPeXl5Y2tHSzBaV25GMDByVHA4V29TT09Cdk01aVFiUjdoMDdCT2NMWEtoeWUwN2M1VTJPbUd1U2d6c2doRE9qeF9fbTJDMmtHRldCaVNEaU95aTJxT1lVczZhVVVhYVZvNDdnTlMzVGVSUUF2NGo?oc=5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>13-05-2026 14:21 UTC</t>
+          <t>14-05-2026 10:47 UTC</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sandoz</t>
+          <t>Gedeon Richter</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tony Chachere's Corn Maque Choux</t>
+          <t>Gedeon Richter : Transactions with Treasury Shares</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>WJHL</t>
+          <t>marketscreener.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE1DLVBZZkZKY1VHeVhIMFc0SE9TWV9ud2FCdGVtbDZlNGJIQnVEZHEwbXN2V192bE1TczRSNU9aeTh1S2tHeGotNm9JZWk0Rk9vc21sM0kyOGd0QTgyWnBfV1hpY0tKaElsbE0weV9hSF9xbHJDeFZv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOTUgtZkFWdmNnS1RxU21ma1dVSlZOdWlwRTNoTFpiX0RyQlZJNXZPaEV2SERCZ3V4V3J0YUtSNS15cWVjNzdrTktpSlVZYlpsTGF0SjAzVUFQa19lenZyNThMeU9YQkk2TDhXajJUb05kNTBOekFoWkFXNkt4UHhuZmlXXzVqc2lrQnV4Y1lGd3pvMlVIWWxHVnhhWW9Ic2lnZVlB?oc=5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>13-05-2026 14:18 UTC</t>
+          <t>14-05-2026 11:02 UTC</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Formycon</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Formycon AG stock (DE000A1EWVY8): Gains momentum on May 13</t>
+          <t>IPF patients call for greater awareness and treatment support</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>koreabiomed.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOcDJyRWczT1B4RzZ1LWxqTEl6WWtVSG5ScnpYT1ZVaC1yRU4xMWVkUzRpakp3Vkg5cGtTLVhGaGJnQXdxdkZPeXl5Y2tHSzBaV25GMDByVHA4V29TT09Cdk01aVFiUjdoMDdCT2NMWEtoeWUwN2M1VTJPbUd1U2d6c2doRE9qeF9fbTJDMmtHRldCaVNEaU95aTJxT1lVczZhVVVhYVZvNDdnTlMzVGVSUUF2NGo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE9Xc1k2RUJYRjNtWmVDa1dEVUo3ZDlOaGNCREJyeTcwRG9ocHJyZENSMS1hck5OMFd3SUwyMldwNll6clFPbjBzdTd6TmR2RXZhU0dGMnpodHJBX25keE5OZXpveHFyTm1INHBUbEN30gFyQVVfeXFMTTZBaGVDSDR5N1RIUTNGMHFGbENOa01oTF9aRmRLX1hlVUt3SWdlXzJwU0xmdFNyRjZOQTVFeklxMk5HenQwNXM0SGtNN3R6aFBOV1hwdU5nUmhQanp6NW9mdDluYTNrLVBPQWRZYlZhbjB3?oc=5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>14-05-2026 10:47 UTC</t>
+          <t>14-05-2026 05:36 UTC</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Formycon</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Formycon stock (DE000A1EWVY8): German biosimilar developer navigates competitive pipeline</t>
+          <t>Boehringer Ingelheim Secures Next-Generation Autoimmune Therapy Candidate</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>thelec.net</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOeDlVVG5HQzJKVWg1NC1fRHBZeHBjYWlDcVB0c0NCNFdVZWFZb0RwTWcxUG93S1d3QzZBR3k0UWZaTXluRnVKaFphLU9WQ0FqdUp3NEd4MFBwWERrRGVMdWZicVYxTkdfYW91X3JXMXZnSmJaa21JU3Q0ZmRwMUstR3JNcFBYeGJCcExfUUJIWDQzMGhkcnZ5VzJmNU1OWUlsNGdtSVpmUVRjaTk5WlZPTEtVQmFQUTlyZlRDYzI0el9TQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE1uNktXM1JuSUg4Vm8xbUQ0YXFBS3Q4Q3Y0SVFmRy1KRzlvTHRFNlI3SGdrNUFrc0xORU1LajZJUWZmLUJ3empHOUV4cVpMdXhfbmF3TXRYWThtLTI2UDIwUW81QjVjLTQ?oc=5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>13-05-2026 12:51 UTC</t>
+          <t>13-05-2026 23:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Formycon</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Formycon stock (DE000A1EWVY8): German biosimilar developer navigates pipeline progress</t>
+          <t>Veeva Commercial Summit to Feature Biopharma's AI Successes and the Path to Agentic Commercial</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>PR Newswire</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNTmZBVmpsYkdJdnR5Z05GUElPbU5lcm9SSFJYV2Vma2ZXellDVkxRZ2E3ZWVHcEtuT1ktMk50NnlEaEZMVXR2UG5tYkpTOGR1WE85Qy1MYmhxcjN3U1ZvdFpiZVlWV1VKbFgtMWdCYkwyYkMzVjFUX0FHMkVJeGFGYzFPMkJROG4za24wTm5VbmZSdGtIcEplLUtZd1o2anYyRjhvUk4xaWdXLVR1LXZoVEZnY2pibHdYN0szZVJ1UU1Fdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQUmhIbGJjOHRJSGJUWUV4TV9VX2w5cWRRVW5pQ1d1NlNvcndGZ3ZjZy1tSDh0VGZqRjVQNmp3MVdhOHRRVHo3a2Jnd2h1Y2hMMVFEOVItYW5XZDhrT0g5LUh1N2Y5bkZxandFXzRBUHNadThNa3g0UXM5MkNuTEkwMDkwWUE4RVFwWXdjaGZLcUltLVdwTGZZQ2dTbG55a3VFaGZ6NkZUdEFfaVR0aWh1a1VxZHJMUGpfdTNvOUpfbGJRaUxRb0FPTjA5SDZEZ2sxaUdLVWQ4RjgxejdwRU1UemFsZw?oc=5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>13-05-2026 13:04 UTC</t>
+          <t>14-05-2026 11:03 UTC</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Gedeon Richter</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Richter publishes Q1 2026 results</t>
+          <t>Companies testing AI analysis tool for early diagnosis of PF</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Gedeon Richter Plc</t>
+          <t>Pulmonary Fibrosis News</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE5MeHNtY05Odlh0ODRab1BEcnplUFVDRDBUenZBU3dxeTdyU2YzUjVGekUxTUQxOTZQcnQ3TEh0TVh2VngzbjVZejM4aW1MQjN4d3FxZ3ZZSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPSzJKbjUzNVVfY1RmdXRZbG84SUp2TXRfV3U0STRoSHYxbFBtTFNrMV9KMFl5WWtZVTdiajRvOVYxcUQ0MG94blRiVm5QS1RrTEZUS2RZM01pdXlKbkhFY3JsYW0tUWFaMGZTbDF4Y3dLaWZLV3RKSEZGMUhpZ1pwelZrMmc0UFlCZmJOOUcwaEROakQyWnprQQ?oc=5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>13-05-2026 16:46 UTC</t>
+          <t>13-05-2026 20:14 UTC</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Gedeon Richter</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Richter Gedeon Nyrt. stock (HU0000123096): Trading at 12,300 HUF with recent dip</t>
+          <t>Veeva Commercial Summit to Feature Biopharma's AI Successes and the Path to Agentic Commercial</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>ChartMill</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxONHg2ZlJyQ2NnZ0RDNllkb0FKbDlyaUFKakZZdVRXMnh2cWdBejlsTUlDWnVRSm14dG05Yml4ZjBOejFkR2N3NnhzX0plLVdGY1dyREdiVEhUNElPeFB3cW9sejNUSFFMOUZCUTZJMXlwSFJXaUVnMUtEdi1VdnNvNjNjWWpJN2FMLVdLR0VWaWlxbU1zTDdLeFlBb29RU1JQSHN2dWVSMVFfX05OSGxkZnViUlgyRi02bXppQWN4UXgtZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxQR25zVDNKdmtkOUx0SUNtNnRhMWhCM3BSbXJGWnNZMklNdDljN3ZfdE1pYmlidjNhX2VwTjdnYjNrMkt5MGIxN1kxLUw0S1BJMGlfZXFmVVRsTW0xdlJLX2FsVnZpdzVuZWVoeEZEUE5xaFZtUlBrc0Y1QnR3MzQ3LXFMbm9QZ0FBY1hGRm5nMTFjV2R2YnRRMWlzY1R6TWFMVGR2eS0tbDNFYnJWNEVFbGJzYmVzT0Q4c0xmWDk0aWR6WElGamF0em5uc1E0dlZsY1NncmU3YVJ1dmJKOHZn?oc=5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>13-05-2026 13:54 UTC</t>
+          <t>14-05-2026 11:03 UTC</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Hikma</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Brainomix and Boehringer Ingelheim continue partnership in pulmonary fibrosis</t>
+          <t>Hikma and Taqadum announce ministerial nominees for Zaidi cabinet</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Manufacturing Chemist</t>
+          <t>Iraqi News</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPbGliS3lfVzhER3JUNW5va19pZG1QMmNZYTYwQUZYa0pTSXUzeTlIb0o1YmNXRl83N01sTDVsZU5MTU14Y256c2dzTm9zXzJaRmM0SHdmS05IRmNSamZWc1NLdHZxYW5RSU93eExYZGdjTk1UX19tVUVHSTYySVFtTFBvQWNEM2RpT3Z5NXR0ZFhOV1NWd0llTnB3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxOaDJOTHIwR28yNkNIWUNaSGZ3TkZtNGlxR1N3YkpHZlJQaWZ0RXRtRnZCbHpmV3NjdXN0RnF2Y05ScEItNlJhS1JwQ0JlVkpuVEhQVDlsamRwalNieUNNaUIxN293aFAzU3dNYXlmN0xYMHBpZ2d3Y3h1Q0NNQ1lWNQ?oc=5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>13-05-2026 13:36 UTC</t>
+          <t>13-05-2026 20:14 UTC</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Hikma</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim Secures Next-Generation Autoimmune Therapy Candidate</t>
+          <t>Finance minister nominee pledges economic reforms</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>thelec.net</t>
+          <t>شفق نيوز</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE1uNktXM1JuSUg4Vm8xbUQ0YXFBS3Q4Q3Y0SVFmRy1KRzlvTHRFNlI3SGdrNUFrc0xORU1LajZJUWZmLUJ3empHOUV4cVpMdXhfbmF3TXRYWThtLTI2UDIwUW81QjVjLTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxPTEN3YjdPeDV3OTBBSWktcW15YXlORXhFTHZXdVVOZFMwQmhSNnY5TU5IdUVtNU1lSEVBR3NlWU02VlJ4ZHdBbWkyamU1REVoZm5yUkFYZlZldi0tcUxDRHRQNjdJZ2Z1elBYWE1SbUtDcXM1MG1uVG9YdU9fOFdZVFNGYkRCYk0?oc=5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>13-05-2026 23:00 UTC</t>
+          <t>14-05-2026 09:45 UTC</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Hikma</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Boehringer and Immunitas agree on licensing deal for chronic inflammatory and autoimmune diseases</t>
+          <t>Iraq parliament set to vote on 17 of 23 ministries as six remain disputed</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PMLiVE</t>
+          <t>964media</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxOQ0pzeENDSjZVUU9SX29rc2R5RW5qX1JDTmtEcVY2UXM5clRJb0w0alVTMmo1dEpwMDhCcUVsNmF3Q05LWkpKRW82UWFwVkZRbldaZGVNSG1tVXg5TG5TNDRQMXYtaVNaSUNhWW5QcEZjUDk1UUpiVzBHb2dHR014OHVaNlV4anEwLWY5Wnkyb3AyUWlhckttRzJYcXY5bnBLRzZyWWdUVnh6UGJmSV9IbC1mOUZnOXgtLWx2VDR4RTRQclRFN0NqTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiREFVX3lxTE1LbWJjX05mXy1RSWJZRllMbDl4NXV4aU9TLUZfQVFqekJHMjBQVjBzLUtrczB5UDMzSjBlc3JHVGhLc3RC?oc=5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>13-05-2026 12:02 UTC</t>
+          <t>14-05-2026 07:37 UTC</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Hikma</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Millions for Preclinical Immunology: Boehringer Teams Up with Immunitas</t>
+          <t>Parliament session begins for confidence vote on al-Zaidi government</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>European Biotechnology Magazine</t>
+          <t>شفق نيوز</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPVzFqbWRuYWJkbWEwcUhRSm4tMkxyWFhhdU41ZWx1UGtrZnZKVmxGS3VqWXpvZlFjWVNHM2hfTTBJU2h4RWxJNVA3SDVJYjdsS2d2LWpyZnk2MlN2clJHMUNMMzFtajZpekhjallLdFJ2RktvcV9JYm9fcFpXTjh3ZDQ3eVZncUJESDByYnhTMzRjTVhPSjdFS2s2aTBXTGY2SzIyTTFFbzdmLWZDclpHRHNjamdrU18wR0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPeDNNSmxlODc2dS04Y0VlYlVzNVhJSVJmUjh4TWtFbDNkeWRsN3JXZURuR0xabFVvNFdJc0RjbUxFVUd5U3hFMzFHOTQ3MU04YkxkbERBTVVFYmFYS0lMMmpoZm95UWxHdHMwZzdkaE9YcWlkVlJiSm9CV1dITmdfcUpzZWJuS3RGUzI4Y2N5cjkyMy1ySFlFVjYyTXFXWlYt?oc=5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>13-05-2026 11:52 UTC</t>
+          <t>14-05-2026 14:50 UTC</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim licenses Immunitas antibody program</t>
+          <t>Piper Sandler lowers Amgen stock price target on rare disease outlook</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>BioWorld News</t>
+          <t>Investing.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOUGEyY2M3azJacGxKSUdtWlhSTHFhRVlCczJpd0hNeEp6UGdtTzl3anQwaUpCVHRQb0VDazkyYTk0ZmExLVl6bzBXOFZ4TlBHRkU1ODU4RXpNT2Z6czRhOVFkVVN2M1lpUXJNdVJ5OXE5WmhGRzFCbzJlVlRVRkhyYnNmVzBvNG5xYXBaY2xicXNzQkhzQ0RqWEctU1RDdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxObFJMTnlMM1pFLUZLdlhKc2Jid1oxY0s2c3FIbGd2Um1nSlZRUjZTTjZ5LU42RkJFR3hEeFZNbEFVMTR0TmRfUnk4UVdpVXprQVpPTHVjVDFJQ19OT1VLZnpQSDJpNjdXc3J3NTIzelo3WFE5X1R5RDFQVFBlUndHV0dxNVZDMUszWXhHcmV3ekxtWmctMFROVjNITmNTUnFwNGdVWG5DeDFaYnRwaFprN0xtYXVQQUl1OWZuUnNXRjVnc2M3SnFHZQ?oc=5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>13-05-2026 13:00 UTC</t>
+          <t>14-05-2026 13:29 UTC</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Boehringer licenses antibody program from Immunitas</t>
+          <t>Amgen stock (US0311621009): Piper Sandler cuts price target amid rare disease review</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>The Pharma Letter</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOa2djeHZQU1Z1OG9IRmVVbnZNM0ZTeFVPV3RlOUR2VTNqTG4yVEo4RHROTEU2X2g1bzk5b2h1ZS1lZ0MyclcxRzJYWFZQMk5rd3JKYUNCTjNBWUlWLVVRSDR4TldIUl91ZXB6WW5mNUNDRWdnYmhyTG1TaXhvVE1scnVRY2cwdThGTU5jSWhZbTk2VXQ2cjJpSTJMdmY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNYUVZTjZneFp0dGFKNEZCTGtFcWZ4TzFUVEdzZmRyaFpIbEg2OENjUXQwbmFqSU94RXZod254VWUwVEFIQlhxRGk0Wi1udkpGWmZRbWNjQ0NtOWU1YUlrT3AyNDc4alFOSWpaUVAzMFpUeVRWYjZUYUxTeWx2Tng5YWZUR2dhTHlSd2RzVlZfdlJHaUdlYWZhWlVuVFNiU2JITzRxdmgyVUdVemNrajRlR3FaTnp0NHB3N01NNlkxemZfN2c?oc=5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>13-05-2026 15:06 UTC</t>
+          <t>14-05-2026 15:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>IPF patients call for greater awareness and treatment support</t>
+          <t>Rayburn West Financial Services LLC Acquires New Position in Amgen Inc. $AMGN</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>koreabiomed.com</t>
+          <t>MarketBeat</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE9Xc1k2RUJYRjNtWmVDa1dEVUo3ZDlOaGNCREJyeTcwRG9ocHJyZENSMS1hck5OMFd3SUwyMldwNll6clFPbjBzdTd6TmR2RXZhU0dGMnpodHJBX25keE5OZXpveHFyTm1INHBUbEN30gFyQVVfeXFMTTZBaGVDSDR5N1RIUTNGMHFGbENOa01oTF9aRmRLX1hlVUt3SWdlXzJwU0xmdFNyRjZOQTVFeklxMk5HenQwNXM0SGtNN3R6aFBOV1hwdU5nUmhQanp6NW9mdDluYTNrLVBPQWRZYlZhbjB3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxOS19HNFNZeWs4TDdGYVBoWkFQNmlRTE95ejNVS1hSN0NSaE5FRmRZSzlmMGlsMndDaVEtWXJ4VXdDWGw2VGI3eFdnNEc1ZVZDcDV6bGdINzVJQVVqbUJJX2cydHZ4RldpaFpaMUx2cDF6eGJqME0wb0hUR01IOVV5TlBaemRQcGNhSnZLRjhqaDY3Z3N6a1k2RUVWbTNIMFRHTDdKTDJfZ2ZJdHd3bmVaNEdGUDZqRHNJenhQOWZWSGtsb0FaeG9nLUtKZ0VJVzVNamc?oc=5</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>14-05-2026 05:36 UTC</t>
+          <t>14-05-2026 10:09 UTC</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Veeva Commercial Summit to Feature Biopharma's AI Successes and the Path to Agentic Commercial</t>
+          <t>A Look At Amgen (AMGN) Valuation After Q1 Beat Guidance Upgrade And US$300 Million US Expansion</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>PR Newswire</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQUmhIbGJjOHRJSGJUWUV4TV9VX2w5cWRRVW5pQ1d1NlNvcndGZ3ZjZy1tSDh0VGZqRjVQNmp3MVdhOHRRVHo3a2Jnd2h1Y2hMMVFEOVItYW5XZDhrT0g5LUh1N2Y5bkZxandFXzRBUHNadThNa3g0UXM5MkNuTEkwMDkwWUE4RVFwWXdjaGZLcUltLVdwTGZZQ2dTbG55a3VFaGZ6NkZUdEFfaVR0aWh1a1VxZHJMUGpfdTNvOUpfbGJRaUxRb0FPTjA5SDZEZ2sxaUdLVWQ4RjgxejdwRU1UemFsZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxQbF9pVnlGNFRSVU1DTEdITl9CNl9NTGpOVGMtSkk1bExUeDRRSEpidExac0JmWnViUk1jcG9tcDR0QmNRWHhCajZmdnZzTmlLczZqNWdscGh3T3hHQmpkTlV2WnlWdGQxRWs0QXpGd0UtWDdrTTBwQllEaXRTMmQ2bkJHclhrN2Z2Q1h5cjVfQkZOaGg2bE02MDdoOTQwRVRwMEN1X0xmLThCb0ExbnFSWG5fWDNqX0NQQ3duRDhmMDVMSEZ1bXZEWEJEU01ZZHV0dC01VThR0gHbAUFVX3lxTFBkYTVRLWRDS3FRenZSTzVvaHJXOXhUZWxVams3WW9FSnJOMXBzOXNWZ0wyQjJuc2tmazhfOUtPZTVBaUxQNHBFNW9nb09FNXJiTXFHM3A5dE1wNURmNklobnA2cHgzUUZkLXhIQ2xtR1ZnN3JYQ0tJR2JQQTRQUFk1eFBmQVl6MmpLYWhVYkJxTUcwcDFZX0VPVFhGMmtHR0U5cm13V0NCQXA0UWxiTzE5NTBrcUlyUVlCcDEwV1FGWUlMSXlZUHh5T1VpUnFzT1FRd1YzMDJDZWJsOA?oc=5</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>14-05-2026 11:03 UTC</t>
+          <t>14-05-2026 01:07 UTC</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Companies testing AI analysis tool for early diagnosis of PF</t>
+          <t>Amgen stock (US0311621009): Biotech leader navigates patent cliffs and pipeline momentum</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pulmonary Fibrosis News</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPSzJKbjUzNVVfY1RmdXRZbG84SUp2TXRfV3U0STRoSHYxbFBtTFNrMV9KMFl5WWtZVTdiajRvOVYxcUQ0MG94blRiVm5QS1RrTEZUS2RZM01pdXlKbkhFY3JsYW0tUWFaMGZTbDF4Y3dLaWZLV3RKSEZGMUhpZ1pwelZrMmc0UFlCZmJOOUcwaEROakQyWnprQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQcjBFSjJvSzJtRER2QkFGdnlpaE9aTEFCZjBISVIzWTVDUnBka3hMWW1KZEd4a1lIVmwzY0diRFlHTjhlVS1RUUFTeExuVHF5QmFzWURvWUV4UVZLaW5hM2hIQ0tjdU83ZW4xNXJVZEg4aHE3b0dEV01FbG5OUnFTX21xSF9DaVFHeXhERUFZZjkxbS1vMkJVeWk3MExZNk9CTF9qYUM0OHVpOGRhVkxhejZENnlQWjM4S2VLQThoeDNISk1T?oc=5</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>13-05-2026 20:14 UTC</t>
+          <t>14-05-2026 15:05 UTC</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Early BRD intervention leads to better outcomes for beef-on-dairy cattle</t>
+          <t>Piper Sandler Maintains Amgen(AMGN.US) With Buy Rating, Cuts Target Price to $427</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AGDAILY</t>
+          <t>Moomoo</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQSHBMUlBqWHdYeFh4X1FLN3lMOVNzOFExZW5SMDFCNFJ0TUNWSUM2U1N0RnVTajRZT3ZXUFV1MDkxZGtENHMzTEFZaGdWaV92bE1WQ3ppaHdPNjJheXZyLU00OHVka0tudWROY0xMRWp0R3Q0V1hwWU1jZWhDME5PVG5mQWY2THZFcUo2U3dnSlZzWlZaVUtoSnVtbzZYaVJxQUdLcEhR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOdDRmVmRhNDk0MTRFcm1kMFNBU2JXSjZRdC01Vm9hQ3FfUUp5d19wdVJMblFUSDhJdzg1R09MV2pvYmFTVktueUE2aUVTUlVualo2NUh4RlRQNURLMVRuZFBlTU5nN3RreHFfbTA3dU1fcTNGQWhXU3llSUdsak84cjJXV1ZUTHpXTmFrLS15SkZHWWxoMU55ZnU3cWhzVTNGTlF2dVRnb1JVUQ?oc=5</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>13-05-2026 15:02 UTC</t>
+          <t>14-05-2026 11:38 UTC</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hikma</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Hikma and Taqadum announce ministerial nominees for Zaidi cabinet</t>
+          <t>AMGN Maintains Overweight Rating by Piper Sandler -- Price Targe</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Iraqi News</t>
+          <t>GuruFocus</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxOaDJOTHIwR28yNkNIWUNaSGZ3TkZtNGlxR1N3YkpHZlJQaWZ0RXRtRnZCbHpmV3NjdXN0RnF2Y05ScEItNlJhS1JwQ0JlVkpuVEhQVDlsamRwalNieUNNaUIxN293aFAzU3dNYXlmN0xYMHBpZ2d3Y3h1Q0NNQ1lWNQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxObmhobTFMZ09VMVVWcFNDbmhNZlFHNnlBdU52RVMyUU44Y2hZb1ZKQTRRTFlHb0RaTjFRMm01R296bXFQV0cxRDdTM1lxNDF4a21fb24xMHIyd0NYakRiRmFiQkRQQzlueVdTMk13ejNSTml0QUpCcEtKbmNQMVpCS2w0SjRpX2Rya1NxQnpoQUFDMVZBbmJfVDNjc2lDa3RERjRWZ1FxQ0RSSS12dy1OQm8yc01yVVU?oc=5</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>13-05-2026 20:14 UTC</t>
+          <t>14-05-2026 16:12 UTC</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Hikma</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Hikma Pharmaceuticals PLC stock (GB00B128J450): Active in growing psychedelics and iron drugs market</t>
+          <t>Summit Wealth Group LLC Co. Has $386,000 Holdings in Amgen Inc. $AMGN</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>MarketBeat</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQR2hUQTZnWjdIUGZKb1pjOXJTWVdtZ25rVWdyNGY2dE5yRWxoU1VWNDJGdDNFYnlSMWNsUVJZSjR5Uy1aUFZnWm9lWTFOeWNXMHd2NWlVMFFfTk5lOXROM3hDVmNjajh3RHloMGtkT2lUa3lXQUljZDFDbURUZTRtMElRR2c3V0dWX1ZoelVxekRpRjFFdUhPRTVNQ0FXSzRlc3JwMVFvXzZydG5jNWp6SGZNS0h0b1RGUHphNzN3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQcjRlLWRuVnFhTU9BM2t2cXg3S2R2cFA3cFRYdG5PdUVEZFVUb2FmU3JCZEtRS1diMkR2bnNCeUtMeVM0ZjNRWGpkbG9JaTBWWVk2N0dkY3lQSTVreGRXX2s2akZfeUVfTEJTeGtnNzFjVkQwa3lTVEpqcU02T1RqRmVaVk5NUld5RmRqNHYta1JWS0d6bGxHWGZ6Si1Fckd3a19fVFBvQzhERFVZcEtsbHNEdUg3dXNZdlVzdTYwcmJwX2s?oc=5</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>13-05-2026 12:43 UTC</t>
+          <t>14-05-2026 09:47 UTC</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Hikma</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Academic Accreditation Council receives application for Medicine &amp; Dentistry programs accreditation at Al-Hikma University</t>
+          <t>AMGN: Key products and pipeline assets drive growth, with major investments and strong Q1 results</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>saba.ye</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiSkFVX3lxTE5wUUZLY2dVRV9uQndXNmdvdjhuTEd0OFVXLUdWdXZ3NVJFR2U5VDlpd3IxdFZSMWpOME5WcFI4OHVTcGFPYWpXelZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwJBVV95cUxPMVExSnBUQVJtX2x6UjBhdERMTzlyaEs4SC1XMzRoRlhBVXJJTDRuTlZsMHJNVzJPaGtreDZPSVZ1azNhZGF0ZHhjOFU3bWN0NE9ac3R3bm9pZmVIM3kwMlozaV8yY1lvajdaNjFoY0tvZUxMa1dIR3JGRnVBQzVhTUp6blRUQ1JfYkZnVTdSY1p0Wi1JN1dNYXliYk5PQS16SnA0MUdkRHI2WHhGeFZIYkkyWXlVWFZ1cmlfblZKeW1kV1FUY2tQMjVWM0V0SVM2enZTMmVXRmFKSWZPZWU5SG5ZcWRQUC1IbzVPZGZQLU11X1lSOTNvVmxJb1FnaVhmQVdIME9VSm5YUVY3S2kw?oc=5</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>13-05-2026 14:55 UTC</t>
+          <t>13-05-2026 18:33 UTC</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Hikma</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Jamjoom Adds Scale As Saudi Localization Momentum Builds</t>
+          <t>Sean Lybrand: Proud to Support the Always Innovating Campaign</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Citeline News &amp; Insights</t>
+          <t>Oncodaily</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxPT0lKSmVCWmRhdzZZdjJsVVNiQS11TTRNSnl0Tm1FZFEtbnZiZmw4WmFSa3VybWlrZ29zZ01lbG1DZVptTlNTQVhJbldsV0xnOWhoOU5YZkFkV01IcERBTGszSUZleERNX2hsdW9BQzFCUHNFMGtRdVduXzF2MGF3S2VWZUNObE52WmJZUTA5WEkyVzhRWS1tZkxyM2g5bGRXdTVkUm9BVnBjZnppUTR2clBjYVNEMnpqb3lubi1iQ0c2RlZmQlZxeUVtWnRMbWxiSzlvdEllODJPSEhja0I3TFJ5ZDM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE0wSWtlaEZhOVRGRWkycHkxVGxsZlNraTZsQWR5M1J2d1loYUt1VXZXRFZzOGZiRHFDQ21ZUjY5Mjc4VmFKZVQta3hmbFpMNzNUZFhwYkEyU3otd1VY?oc=5</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>13-05-2026 12:24 UTC</t>
+          <t>13-05-2026 18:48 UTC</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Hikma</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Academic Accreditation Council receives application for Medicine &amp; Dentistry programs ...</t>
+          <t>The FDA is bringing real-time AI oversight into clinical trials</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>saba.ye</t>
+          <t>Startup Fortune</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiTEFVX3lxTE5LMmhjSDlERExXMVdUaDJjcS1tdWp1MXRyeW9MZUtLRVlsRkZVa3hfdVVrdnF6ZUVERkNvRm9aVmtFYVBrLWFiVXQxTDk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQbzVzS1BSeG41V2RfWlNTLUxWZGZHUWQxVFpuQlk2TVJPUjJNRlNaSzUyQ1VhOUlBWHFPbW4wdjJaY0NIVlp3TFotd2QwVWgwcWczczl0Tklta044WE9EYmlqb04tUi1qV2x1Ri1XQThwWjdETEVCdDhWWkFvZzZ1TTcteFBId1ppelloY3N0bFQ0NEdWRWc?oc=5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>13-05-2026 15:38 UTC</t>
+          <t>14-05-2026 12:24 UTC</t>
         </is>
       </c>
     </row>
@@ -1192,22 +1192,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Amgen expands U.S. manufacturing footprint with additional $300m Puerto Rico investment</t>
+          <t>VIRGINIA RETIREMENT SYSTEMS ET Al Has $14.47 Million Stock Holdings in Amgen Inc. $AMGN</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>The Manufacturer</t>
+          <t>MarketBeat</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPcTlIckFocHo5eFNvTGJSS3ZVRE1BbElIZmlyNndMMHdXckZOLW82cVJ4UjFfR0s3Tm82Qi1pR3I0cTZCTDJ3cGtzMXBUMEw1LXlWMWlDR2ZGXzlWUDlzdkZ6VXE2YjVUaTNzMTJVVEQ3ZGdjNFRFSHRTU0JNc3A2T1ZBNERQSTJleVlxcFdaVC1sYnlVNWQtVThqNS1iMUc5NHFpSTF1UkRNMHUzMEtUNnkzM1VHWXptY3lieGhQYVNjamtBNXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxOUEN1dWo5VW9zaGQ1Qk1iZUx3N0NicGU3MzctY3dsRlBqOFlmUEVRaC1xM196VlJCeVNTOTNCdWZXd3lyVmRmcVUzZC0wZUxPRTRXMnZPd2Rfd1NUOEhmbjhxWjRHenc3RU5nQko4eHdsTG1IM3RXUnNYZVBBTFhxVjVXcVFxUnBIQXZBRndXb3FBaXp3UGJYaEVyLVJtYjRqc2MtOWU4Skh1VVVWX2FSdWp6SFVLZnpnWEZWSFJwRC1iUmR1UXdzZjN6dm1wRWtESFFRaUpIVVVQd2hx?oc=5</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>14-05-2026 05:08 UTC</t>
+          <t>14-05-2026 11:25 UTC</t>
         </is>
       </c>
     </row>
@@ -1219,22 +1219,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Rayburn West Financial Services LLC Acquires New Position in Amgen Inc. $AMGN</t>
+          <t>AMGN: Key products and pipeline assets drive growth, with 2026 targeted as a pivotal transition year</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MarketBeat</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxOS19HNFNZeWs4TDdGYVBoWkFQNmlRTE95ejNVS1hSN0NSaE5FRmRZSzlmMGlsMndDaVEtWXJ4VXdDWGw2VGI3eFdnNEc1ZVZDcDV6bGdINzVJQVVqbUJJX2cydHZ4RldpaFpaMUx2cDF6eGJqME0wb0hUR01IOVV5TlBaemRQcGNhSnZLRjhqaDY3Z3N6a1k2RUVWbTNIMFRHTDdKTDJfZ2ZJdHd3bmVaNEdGUDZqRHNJenhQOWZWSGtsb0FaeG9nLUtKZ0VJVzVNamc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwJBVV95cUxPU0JDdmQ0dHlscl9Yc255dmRtd0tlRmh4bnc0ZFozeXNyOG43Q1FsTEdEOVhIWXlFdEctZGRXSV9tYjBkWld5NHExSnFOQmY0YlVpR24xajJhODdfWmpEcjI0WVgxRmw1T3plVUV1T1FYeEhCTjE5Z1pYRDY2ZzhVRklyVjlrN2RaVXdIV2JCdGFrUXlRWk5GMTRqZ3ZZd081YWc4SmVnYUlkWjl2SzVSWTRqSWdQQW51cjE2bk1QNG1pRk1wOUdWQk5ES3VjcEIyRG5nb1pzVXJYNVNQd01GVkYzdjlrWlBjelk1eFpTc3Z4aFRKaUd1bWRERGoxTzFoMXVPTXVncXVaRlpMcXNidUhlWQ?oc=5</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>14-05-2026 10:09 UTC</t>
+          <t>13-05-2026 18:04 UTC</t>
         </is>
       </c>
     </row>
@@ -1246,22 +1246,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>A Look At Amgen (AMGN) Valuation After Q1 Beat Guidance Upgrade And US$300 Million US Expansion</t>
+          <t>Atria Investments Inc Buys 10,877 Shares of Amgen Inc. $AMGN</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>simplywall.st</t>
+          <t>MarketBeat</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxQbF9pVnlGNFRSVU1DTEdITl9CNl9NTGpOVGMtSkk1bExUeDRRSEpidExac0JmWnViUk1jcG9tcDR0QmNRWHhCajZmdnZzTmlLczZqNWdscGh3T3hHQmpkTlV2WnlWdGQxRWs0QXpGd0UtWDdrTTBwQllEaXRTMmQ2bkJHclhrN2Z2Q1h5cjVfQkZOaGg2bE02MDdoOTQwRVRwMEN1X0xmLThCb0ExbnFSWG5fWDNqX0NQQ3duRDhmMDVMSEZ1bXZEWEJEU01ZZHV0dC01VThR0gHbAUFVX3lxTFBkYTVRLWRDS3FRenZSTzVvaHJXOXhUZWxVams3WW9FSnJOMXBzOXNWZ0wyQjJuc2tmazhfOUtPZTVBaUxQNHBFNW9nb09FNXJiTXFHM3A5dE1wNURmNklobnA2cHgzUUZkLXhIQ2xtR1ZnN3JYQ0tJR2JQQTRQUFk1eFBmQVl6MmpLYWhVYkJxTUcwcDFZX0VPVFhGMmtHR0U5cm13V0NCQXA0UWxiTzE5NTBrcUlyUVlCcDEwV1FGWUlMSXlZUHh5T1VpUnFzT1FRd1YzMDJDZWJsOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNVktkZDVuZjRBWHlUbzJmczR4eE9qeXhuZkRYQl9tWEx3RnBnWVY4VlRQWDktS1BLblZhWEE0NzhMRHlpRWM1TWF1dG82WTR0MEFfNVhJaXg0UllGTzlyTEFOMFlzQTZqN2FNU3AtcUZqVWo1b1ZQXy1YZFdfNTVLTzhjS1FJVDVhUlMyak9ab3hLN1RGaXhuaEp1V0l2OV93NW93Z1JmQkxoemN6VjRPc1JCSzloNGE4eGc?oc=5</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>14-05-2026 01:07 UTC</t>
+          <t>14-05-2026 07:32 UTC</t>
         </is>
       </c>
     </row>
@@ -1273,427 +1273,427 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Amgen stock (US0311621009): Q1 earnings beat with revenue up 5.8%</t>
+          <t>Eugene Braunwald’s Legacy Shaped Modern Cardiology</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>Medscape</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQRDk2SjhDeUNYbUhCajRrR0hjSUk2UDZyQzNvZ1J5cmNJd2hFMDZLQWlmaXY2eXZQUkNsR3hwdmF1UnJ6dXlMWWtiT0VfZXpPUUJHbHgxOFdadDh6NHUwQVZ6VExxX00zNWVKMXowOE1iOU54SWNqQjQ1bW0xNkdLSlpyeEpTbG45SXhMTERZQTNaTE5Xd2RFbjhQQTFHV3Fnb1diZ185dTYzeUlmRFFCc1hPUmppRTRWamo2VzFaaVFueXpuQzQ0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNRm11SFJLclBaNl9yb1BTejRQOTVhMEtyWVc3VnlOUnMwalpCcjhSd25yVDg0RnhXZ2pENTY0bXFEYXBGVFd3bDdMYU1tb0RBNnJ0dmsxUzd6U1llZ2tieTFodUFXVkN1UXJrTHM5S0N2bFZSSlhrZmx2NHZpTWkycTBNQUFSd0tRazNCbFJtTE9iaUtQdW40SGdnZGpyVkxG?oc=5</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>13-05-2026 16:03 UTC</t>
+          <t>14-05-2026 09:13 UTC</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>AMGN: Key products and pipeline assets drive growth, with major investments and strong Q1 results</t>
+          <t>Indian Pharma, Tech, Engineering Firms Pledge $20.5 Billion In Investments Across US</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>IndiaWest</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwJBVV95cUxPMVExSnBUQVJtX2x6UjBhdERMTzlyaEs4SC1XMzRoRlhBVXJJTDRuTlZsMHJNVzJPaGtreDZPSVZ1azNhZGF0ZHhjOFU3bWN0NE9ac3R3bm9pZmVIM3kwMlozaV8yY1lvajdaNjFoY0tvZUxMa1dIR3JGRnVBQzVhTUp6blRUQ1JfYkZnVTdSY1p0Wi1JN1dNYXliYk5PQS16SnA0MUdkRHI2WHhGeFZIYkkyWXlVWFZ1cmlfblZKeW1kV1FUY2tQMjVWM0V0SVM2enZTMmVXRmFKSWZPZWU5SG5ZcWRQUC1IbzVPZGZQLU11X1lSOTNvVmxJb1FnaVhmQVdIME9VSm5YUVY3S2kw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNREoxRU5pYko1aW00NVVwSUNBUzFHRlMtSHphUmRNdjg0Uk1YRnR6WnhPdkFKei1rU2d3UnJhbGVyMkZ5ZG1KLVN4anZjb0xjd0R1TGJZTTgwbFNtRVM5a21hY2xHamJkZW8zRm96SjlCTmNCMEl2VFVkQ2k3TFVDaHNoQnZZclBSSlFlREh5WWFTX0d1WVZ1ZnA0YXZoaFAwODVtNGdvVQ?oc=5</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>13-05-2026 18:33 UTC</t>
+          <t>13-05-2026 21:21 UTC</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Summit Wealth Group LLC Co. Has $386,000 Holdings in Amgen Inc. $AMGN</t>
+          <t>Scientists discover hidden math secret inside Chinese money plant leaves</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MarketBeat</t>
+          <t>ScienceDaily</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQcjRlLWRuVnFhTU9BM2t2cXg3S2R2cFA3cFRYdG5PdUVEZFVUb2FmU3JCZEtRS1diMkR2bnNCeUtMeVM0ZjNRWGpkbG9JaTBWWVk2N0dkY3lQSTVreGRXX2s2akZfeUVfTEJTeGtnNzFjVkQwa3lTVEpqcU02T1RqRmVaVk5NUld5RmRqNHYta1JWS0d6bGxHWGZ6Si1Fckd3a19fVFBvQzhERFVZcEtsbHNEdUg3dXNZdlVzdTYwcmJwX2s?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE42WWlTcjVCVjZuOXBtVXhzMGYza094c0RTQ3l0V2tNTDNBQjh0QmVhZjQyTzZJbHZsVk1TS21SWUx4V0RrbVBudzhzUmM4RmVDTS0ya1BPeE42NlZvR1p3SGt4R3NOaV9LZTN0a09XOA?oc=5</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>14-05-2026 09:47 UTC</t>
+          <t>14-05-2026 07:49 UTC</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Sean Lybrand: Proud to Support the Always Innovating Campaign</t>
+          <t>"Silicon is an essential part of enhancing plant vigor"</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Oncodaily</t>
+          <t>Hortidaily</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE0wSWtlaEZhOVRGRWkycHkxVGxsZlNraTZsQWR5M1J2d1loYUt1VXZXRFZzOGZiRHFDQ21ZUjY5Mjc4VmFKZVQta3hmbFpMNzNUZFhwYkEyU3otd1VY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNOUhUV2NFX2dPZjVYbmlmVFhFNkd3b3VMN0dWR3Z5ZGFJWFI2cFVsNS0ySHlXOXVqTHhxaGRtS2FleFh2OE5ad3BmVW8xUE5PV1FfSXdlVVpiSk5UV0ptVDYzR3ROeXk5RU5DX1VVRVNqUWVmM2pZbzVENVdwNUY4SE5zZWJmNUFWZTVxeEtWM01iMzB0amdwekxWMWtmQQ?oc=5</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>13-05-2026 18:48 UTC</t>
+          <t>14-05-2026 12:09 UTC</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Daiwa Securities Adjusts Price Target on Amgen to $390 From $410, Maintains Outperform Rating</t>
+          <t>Navi Mumbai International Airport Terminal 1</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Moomoo</t>
+          <t>Arup</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPRlBNaklDVnVvSXpSOF90dGlxVlZLeHFWY1BfV0VyV0hzT2FHTWRQRjQ3WWZqNVZreW9VeXMydVp3LUxZY01JZGNrMkZER2JHZmxpd1JJaHgyVU9IamRTQU1raFE2N0ZGbTNrTHo5WENPUDgtMjRVYmxOOWJXN2o4S0RUWThkb1ctT21XQm9yNG9pTW5WejdvTGwtX2lpV0hBYlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxOQTBvdGYzZ1paOXJZOWs3MUx1T1Z1bW12TE9xaU9BTnk0MlBkeGd2MVFnMnZrU21adTVoclQ4Rm5UWFQ5c1JHa2RkQUJreTdQM0hVOURLQXR5dlM3NkV2cUI5N2RLQkcyc0hQc1l1azdyN1I1eGlsTzljbTFpd0ppbA?oc=5</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>13-05-2026 11:53 UTC</t>
+          <t>14-05-2026 12:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Nano-Cap Moleculin Biotech Approaches Key Leukemia Trial Data Unblinding</t>
+          <t>In situ architecture of plasmodesmata in Physcomitrium patens resolved by cryo-electron tomography</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Benzinga</t>
+          <t>Nature</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxPbTNDWlBsWmZWLWE4SzltNmtBMTVhLTdrSVJxaExSWF9OSk5kUEU0NW8zQkxocTBCQUNpcFdVMHIzcFJTM0E4cWZvTHNIQUVGZ3AxbWhtTU1LVXBLUmJibmo3TUFtSTdpWE5FcTA3V2M5UkU5eUdIU1N2S1BtRThmcVplcG96cFJjdXJkUW5DNzR6aTItOEJkODFOSVlfZFVzTHRNX3RmQWJsZW1GLUhQeVR2M1VkeXVnU2tLM1ZBS1pwUDdZNURVYg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE9hQXdvczY4S1NJV1ZkbVV0b3Jxc1lfLWRWcTJMZ1RDczZRdzNYaUVzcjQ4Qk9vNTc4M3lNamlUbXFRQWJiVVdkTmkxR3QxSjN0SE96d1Y5YjNoSUxjZlJJ?oc=5</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>13-05-2026 16:41 UTC</t>
+          <t>14-05-2026 10:13 UTC</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>AMGN: Key products and pipeline assets drive growth, with 2026 targeted as a pivotal transition year</t>
+          <t>What Indian gardeners should plant before the first rains hit</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>The Times of India</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwJBVV95cUxPU0JDdmQ0dHlscl9Yc255dmRtd0tlRmh4bnc0ZFozeXNyOG43Q1FsTEdEOVhIWXlFdEctZGRXSV9tYjBkWld5NHExSnFOQmY0YlVpR24xajJhODdfWmpEcjI0WVgxRmw1T3plVUV1T1FYeEhCTjE5Z1pYRDY2ZzhVRklyVjlrN2RaVXdIV2JCdGFrUXlRWk5GMTRqZ3ZZd081YWc4SmVnYUlkWjl2SzVSWTRqSWdQQW51cjE2bk1QNG1pRk1wOUdWQk5ES3VjcEIyRG5nb1pzVXJYNVNQd01GVkYzdjlrWlBjelk1eFpTc3Z4aFRKaUd1bWRERGoxTzFoMXVPTXVncXVaRlpMcXNidUhlWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxQSVBOOF9LbVlWSWp6VGF6RTdZemhyOGZSLXNlYS14UXAxaVhWT2dzSXBET3JuMkZjRnZEYmVPWmdQME5wR1hkQjdhX1c5cXVyMGo1UXhEM1c4U003V1JlRzdhTlNoX2ludDlhMWhMcE00SnR0ZXhSd0ppNXRRZ0t1ZXpkeFFjN08wQzNfZmljZHg0eDVOcnhNOGNkdkVxS2VKR3FNcTlLSTlwWDF2TmxUWmdtdDlQd2k0RmstS1dTRFI3MGNHYmtoUlF1SDhGVEhSeWZCenM5X0o0VnNESWU00gHkAUFVX3lxTE5HRUhYNDFiYzJPODJ6Y1JPQXNVdDlILTF0SDFxN2JMYk9uXy1RYnRYeUdvT05yeWh6bDh0eHN6NXJ5SS0tMTBXNWNZZzhwZmJGOU02STFTT05Ua0RzYjlkTy1aclR3Z3BRNXktbzF1OHhKZ29xYXJValI5VjVZN24wcDh3X1BTU1VfWDRETjh0eGJ2azBMNUZCNHlfT3JFbXV0T09rMDhjT3JmWmtzZXBFTWk2UzhBMVFCQTNCa2VBS21aV3Y1cFdsMVczVWJsb19KUWtkdFZ1Q2lQcm5HdUx2TEx5Uw?oc=5</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>13-05-2026 18:04 UTC</t>
+          <t>14-05-2026 04:34 UTC</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Atria Investments Inc Buys 10,877 Shares of Amgen Inc. $AMGN</t>
+          <t>Plant-Based Protein Foods Market Size, Share | CAGR of 8.1%</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MarketBeat</t>
+          <t>Market.us</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNVktkZDVuZjRBWHlUbzJmczR4eE9qeXhuZkRYQl9tWEx3RnBnWVY4VlRQWDktS1BLblZhWEE0NzhMRHlpRWM1TWF1dG82WTR0MEFfNVhJaXg0UllGTzlyTEFOMFlzQTZqN2FNU3AtcUZqVWo1b1ZQXy1YZFdfNTVLTzhjS1FJVDVhUlMyak9ab3hLN1RGaXhuaEp1V0l2OV93NW93Z1JmQkxoemN6VjRPc1JCSzloNGE4eGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTFBfV1IwUEl3NUNtRWU3TUM3Q2gxT1pJbHl1X1J0a1hKcl9ZY0d6ZDc0Sk5QME1VYlh1a3NGeG1hXzBUT0NKTnhfSnBRN1VEdHBPcnp2RlI0NlN5bC1IYnZTOEVvbVhjTVdIdWc?oc=5</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>14-05-2026 07:32 UTC</t>
+          <t>14-05-2026 07:11 UTC</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Angel Hidalgo Portillo</t>
+          <t>Aurora Cannabis (ACB) secures Canadian Plant Breeders’ Rights on key cultivars</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>PGA Tour</t>
+          <t>Stock Titan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPaERYVHplT3hWYUh2dnZWakZCMUszNGFLSlEzN2RxQVhDZWMydk1IRkdyUkpfV0cwaVl3OTdrdXlWeGZjWDhaanlJSENxLTd6RmdycTZsTE1GZkx4X1VVMFpKVm1pSmZUVFdVU3o5RTF6M0swRmdkY3B6Rnl4S0NCLUpfR0gyU1pLX0FqS1hrdi1uYlNYQjJFTzdDVUJaZ0tHUHdTdF9VVWpRUEVoNkVyX21PcXB1WC1fR2V5Rw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQSmhlVnZNOHI1enJvWS1iU0x0ckFqQUhFVVUwQnFJaE91ckJMdVh6LUJ2eVN0c01yNHBteXozR3BRZG9PXzI0bEZIaTUwUmVONVFTY1JSRXltVVpyXzdxUTZsc1hVM0ZvbDhKeEJ0ZTlydW1JWkRMc3FTVTFfRDlwWUFaN08xOWRFUlFUQWdmOWdiMXRCTUlqZlFWbmVMNmQ1bnJXbEp1alJCalZDbHFBTUlMSGQ?oc=5</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>13-05-2026 13:32 UTC</t>
+          <t>14-05-2026 12:44 UTC</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>The Dow Jones Index Opens 0.11% Higher</t>
+          <t>Prickly pears show promise as the building materials of tomorrow</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>University of Bath</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPdDJ5ZklnbXJyQnZaVnBVVEF0Zkc1X2hXT2ZPTXhRV1I1TEFpbWF3ZlppZm9NdkE1Vk1qblRsWS1fejMwWF8xaWRKNmdURTRBdUV1X0huT3d3NW5QYWhXVmlfQlRYa3ZKRFN5enoteFFkbnJCWFJSVHRvR3NBTTBjZElPSXVGalpZcGFVQ2NFQ2lLZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNRDBmbzlraHNtWGxBYW1ITDlzb3JvR2lTaGdHR2IyYVdVZzFHcjRhZEhoVHZXS2RKNlJST1hFdWdjVjNxWDZJNzA0THdJTEVnT1JuUldZUE5ZSzJDeVR6QkZkaWhRNVowRlE5aFlXU2RpVDFhNkpOOXNjaTlnczh2LWMxejktMk16dXN6elA4dVhmcmtLSEdsTVNMbXFrV1FaX2thVg?oc=5</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>13-05-2026 13:30 UTC</t>
+          <t>14-05-2026 10:21 UTC</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Daiwa Securities Group Has Lowered Expectations for Amgen (NASDAQ:AMGN) Stock Price</t>
+          <t>Eliminate Japanese Knotweed</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MarketBeat</t>
+          <t>Town of Hillsborough, North Carolina (.gov)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxOZmEzalpsWDJ6MGxMVE1oaVNBbThKRzBxZGU3aUJidDVIUy1ubGRPX1ZRbG1BQ190d2ZhYnhfTXl1aHJreDNNY1AwRGNKZ2pwWE1EeVIwcThFbFI3c25vNDhzMEFNRjZ3SzI2b3NaRVRtYTVoMVlISmQ4dm9PVmdOVHk2Vm5JcWJlaUM5dWF1YVBQT0ROakluUnBDY2JJamxGSWZTWWpINTNUd2dTMTRIaGtVVy1EcGwxWmQ1SlRLR1RxRGFLZzlxZXBGekRrOTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTFBNRWt3TzFKN19NNkdpS0FIOWRvSU92emZDVXNiVnVpMTVHcHlDRDhlUU4tOHZBSkUzUlUxRF9OMFJ5a19QRUp4aUxUUm9rUnFKMUQ5TkJBa2Q3Nl9XcDQzaEdFd3U3QnEzcU5IYXpLWnlUUQ?oc=5</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>13-05-2026 14:53 UTC</t>
+          <t>14-05-2026 15:45 UTC</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Eugene Braunwald’s Legacy Shaped Modern Cardiology</t>
+          <t>HFCL Limited Schedules Institutional Investor Plant Visit at Hyderabad Facilities on May 18, 2026</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Medscape</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNRm11SFJLclBaNl9yb1BTejRQOTVhMEtyWVc3VnlOUnMwalpCcjhSd25yVDg0RnhXZ2pENTY0bXFEYXBGVFd3bDdMYU1tb0RBNnJ0dmsxUzd6U1llZ2tieTFodUFXVkN1UXJrTHM5S0N2bFZSSlhrZmx2NHZpTWkycTBNQUFSd0tRazNCbFJtTE9iaUtQdW40SGdnZGpyVkxG?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxPMGF3WTByR2FJeV9JamRMbUZRazB5OEhqX1JjdXpOWmZ0QjVSSHVON3dGMkFWM0xIUzNBdFNQMlQwWGNCQWZsRkNWZjZpYVdvX2Nid1p2TGtzQUkzVlVOeVRLX2cxTUhyX0ZMZmZTRVVYd3pSNmpaZ0djR1JPeFJ4OVNzcEpOckt3eGlvV2djc3k2STNIajBuTWx4R2FfWnNrRnk5YzNuWUVPZVI5ZzBpaDdOcU9nb3Q3bnVJT2ZnVFRGTnVSeFJmN0I1cVlybnJNS3k2SjlGWnhCYWZ2azdJazJXUnZ4OEpB?oc=5</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>14-05-2026 09:13 UTC</t>
+          <t>14-05-2026 01:27 UTC</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Aiming for the Sun: How the $11.75 billion Organon buy is cementing Dilip Shanghvi’s legacy</t>
+          <t>CCMB scientists in Hyderabad discover plant protein that may aid dementia, cancer treatment</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Business Today</t>
+          <t>The New Indian Express</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxNSnZOV1FkZk5fdDYwOXRlZm5uTW1rWk9kNE9YWmhUdlFMdTI0OWhyUDhmc1h0enpzWDRxN21zanY4SGxBeVlNblVNeXhFc0h6SzA1Wm9QSU9fOXhXaGJlYjN4ZU40amlrWE5TajEydjlkUEFlT0g0T2xJMFBxbEdQWS14UGVCLUtJWlZ3THZnQ3p3X3UwZlZESFlNNlF1eUUzd3lMV0sxQnBLeDMzSllvOElDSkY1X1J3U1hZVllqemNUcHBVSlZ2QlVxSkVseF9VbkxnU1lBOTZRSGVlb0k3YVhEWGZxYTBlenFsYi1ZOGVIWjFx0gH6AUFVX3lxTE5fR0I5R1ctbVRjTW9IUnVFaEhDLXBxUlZyaXI3c0E1Z054NERGMG45aG00MmtrMURJRG5iRjBJZVZmbXk3N3EtMmdBVE5lU25ISWJBaXNMRDBfYTZGWE53c2dKNmFVdDY3RHEtMUl5WWUwbWZxaHJrdUd0ZkoxczQxSzZNTjdyOURDMXo3dzNveDVVSjcwSHdiNVJ6S2FvQWlmZFZ5UDZhZnJVX29WUmRBZDRCb18xZngxZkpaZ2o3TjBzQklvNnBMTC12M3luWElMaFI1MjB4SkluT2ZZLU1FV0VOY1RZUnNiQnFNVzdvdDIxeWdacFVYeXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxNU2ZJTDBmUk53MWJIckE3aVl1bXhBbExVcW5XU1g0bmtCODdHTE83ZlY0dmVqZHdXM0FSbjYzSDhWSW5yX0RkV3Vldmt2Y1pxODg0Tnd6RjBXcUtaOGZleHZXSW9CRU4zdzZZMDNSSUhoXzQ4REc0SWk5TE9MTU40bDdXbThwUTZRdmtNZ2VhcHR6QVpkRTlVaXJmZF9jSDdFbFVWc2NZOTJlMHUwa29ZckM3UXRxY0Y0TmstY184ckR0eXdUN2NhMGpxMW1sNk1qbXY1Z0plN3RVREhZWFhaZm5KazJLQ2_SAfQBQVVfeXFMTXBFdF9EUy1wRzJYZk5wYzdYRmVvSUVrdmI5dFBGOWs3VncwRlZYa0c1dG1MN0JRbDBvSHdLYnlYNHp3NTk5Qm5MZXJieElsSXdfUFVyUG1JWE4wYjByZlU0c0VXQkJWNkMwTG1ZSXBrUTRXMkxiZ2sxLXVMbi1TM1prUUw4UnZQcFVWT01sVFNqM2h5Y0lCSW5QRXFRYWEtaDdtMXRVbFdOWUczbGxUZHBNZmxwTWNNNF9tOTZadEdReHA3Uk1FdlV4THhKMGs2STNPVnp2eEZOM3BFQ3BlUjFUT1VPZkRDcWJsOURYbkprT2RVRQ?oc=5</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>13-05-2026 13:54 UTC</t>
+          <t>14-05-2026 03:22 UTC</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Apotex</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Jamjoom Adds Scale As Saudi Localization Momentum Builds</t>
+          <t>Gel Type Strong Acid Cation Exchange Resin Market Growth Outlook to 2035: Water Treatment and Industrial Purification Drive Demand - News and Statistics</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Citeline News &amp; Insights</t>
+          <t>IndexBox</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxPT0lKSmVCWmRhdzZZdjJsVVNiQS11TTRNSnl0Tm1FZFEtbnZiZmw4WmFSa3VybWlrZ29zZ01lbG1DZVptTlNTQVhJbldsV0xnOWhoOU5YZkFkV01IcERBTGszSUZleERNX2hsdW9BQzFCUHNFMGtRdVduXzF2MGF3S2VWZUNObE52WmJZUTA5WEkyVzhRWS1tZkxyM2g5bGRXdTVkUm9BVnBjZnppUTR2clBjYVNEMnpqb3lubi1iQ0c2RlZmQlZxeUVtWnRMbWxiSzlvdEllODJPSEhja0I3TFJ5ZDM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxQekRIZFBUU0xXWXZlaFZKdlBPa21BLVVjOThxZlRiMVdYd0JmellTTk11R3hENWRabXF0cTJXOFpQR050WW12SGZ2Q3RJbWxOZ0lFaUhkT1VxQWM4M1kyUUZid2NLcXl3R2lxd1RjSTV4Tkd3VUlyb0djcUJTWEk2b1V1UlR6VDlHQV9Ib1lGWGlRWWQ1Ry1DampBaU5STTN2NGRPemtmc0hYMFE4c0YtMURjVzBlTXBwamRWcTJwM2kzbkp2RlM1QlZFb3RDZmcteWRhQWtxekxpTkNlTmJXSlVRN3JZc25GN2FsdmtXSQ?oc=5</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>13-05-2026 12:24 UTC</t>
+          <t>14-05-2026 03:46 UTC</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Apotex</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Viatris Targets US GLP-1s With Auto-Injector Strategy</t>
+          <t>Aurora Granted Plant Breeders’ Rights for Farm Gas, Driftwood Diesel</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Citeline News &amp; Insights</t>
+          <t>StratCann</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxNQ0gycmh2M21KcFFTak93d3AtUUF0MWJHUDhMRGh2UFFmYmFsYUJJc1BkWUY4RzhLeEpuRENKRnNlMjAyRTBucnZIQ21qdVVaTHRGR3poTjhveU9pekV1cS1CU3FnSDEybEs1ZFlzZFQ3cXhxLWFBQk04bEZkQjhfUUtHVTJGdk0xQ0diNGpfTjdZdmllTkY0MW0xeXNUZldzd2hOSkhZMXhJVE12d2RjUGZOR2ZUdkh2dWxlX3J5VUdvUTk4bW1jSGpRTzE5MzlQQ0FwUDdFOHZDNTFhODMzb21TM3ZqamdmTlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNNUR5VHZBaVBGU2hjZTdjN0U3bTNlWVdaRlB5cFF0cGpYczZGbEJIWE13Q05ZRHBuWm5hcGQ1b3BvcUxERWJGbHlzMm9xVEVEYWlaWlhxaGZZeGVxV1gwUndneWtES3pITGk4SXNNUTF1RVNpTWtXV3FCTVhfUE1GZUJhTHIyWmQ3Uk94RGRRU2VPSENYTGxIX0pR?oc=5</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>13-05-2026 13:40 UTC</t>
+          <t>14-05-2026 16:18 UTC</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Apotex</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Canadians can now get Ozempic, Wegovy delivered to their homes. Here’s how</t>
+          <t>12 Sun-Loving Plants That Thrive On Bright, Sunny Porches</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Global News</t>
+          <t>AOL.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTFBmdVB2dkRCSi1DMXk5WXlxNUQzVklaUWNEd1dSR2s5Uy1tbW5pb2M4WC1YWjlZMFI4RmVaVGNMeHhXUThUdjVHYkp4eFlZZlNJLVptdkIxNW5vM0RFR2ZWTUJxUXZlNUptRm43QTdURXBuSG9C?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTFB3YWd6czR5NlpvRThxSG10bTZ6eDJ2MHlIMUhhSXRMMWR1ZVU5UW5fYkdzS2RwSU55dmNGSUgwSTFieTU1bGdxNUVPbEVuOHNJb2o5UXgxLURTSXAzV0kta0tKdTRDQmY5VnRiVTNzWGRlbVNUVVA4c2oycw?oc=5</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>13-05-2026 16:58 UTC</t>
+          <t>14-05-2026 15:15 UTC</t>
         </is>
       </c>
     </row>
@@ -1705,373 +1705,373 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Scientists discover hidden math secret inside Chinese money plant leaves</t>
+          <t>EV Resources (ASX:EVR) Advances Tecomatlán Plant Toward Antimony Production Milestone</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ScienceDaily</t>
+          <t>Kalkine</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE42WWlTcjVCVjZuOXBtVXhzMGYza094c0RTQ3l0V2tNTDNBQjh0QmVhZjQyTzZJbHZsVk1TS21SWUx4V0RrbVBudzhzUmM4RmVDTS0ya1BPeE42NlZvR1p3SGt4R3NOaV9LZTN0a09XOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPNndnUnRYcVZTYjNScWlrNktpOGJ1ZjhpT1Nud2lKZ2ZzQUZjUG5sblRiRm1uN0VPN2h0N2RsOGs0ZmdoRXpoU3JCcmg5YkZaVGFYVUFpcnhteDlHdVlFb3RMbFpLZDZkcXQ4eFVrZmFBOWhuTExsbkJVdWp1eHdCVHVnUlpOVjhmbkE2UG1fSDk2cEJEU2tLcDR2YUs3MlRlb1JOU1ppSXZzd2ozVmNWdGVXNHhVOWIt?oc=5</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>14-05-2026 07:49 UTC</t>
+          <t>14-05-2026 12:41 UTC</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Viatris-Mylan</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Plant-Based Protein Foods Market Size, Share | CAGR of 8.1%</t>
+          <t>Mylan Epoprostenol Win Clarifies US Measurement Rules And Equivalents Limits</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Market.us</t>
+          <t>Citeline News &amp; Insights</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTFBfV1IwUEl3NUNtRWU3TUM3Q2gxT1pJbHl1X1J0a1hKcl9ZY0d6ZDc0Sk5QME1VYlh1a3NGeG1hXzBUT0NKTnhfSnBRN1VEdHBPcnp2RlI0NlN5bC1IYnZTOEVvbVhjTVdIdWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxPbHM4VWQtSndIMzVDaVlsc3BjdWdqTDFvaTdUMWFPQzhSYjdTdlEyUnNJSkt2WnprQVNhd1dPYWdMYXlUOV9xYnQ5Y2xyeHk0ZERUX3dvSEM4cG1YNTd2ejFkSDhhcEo2V000cGhCd0lWUmdWTVZZd0hYUjdkbUVtUWRlc2NrVDRiOG41UXZjaHp4TjYzTDQwbFF4dmdndzdxMkpoVUtJcWRDZS1vdlAxRWQ4U19aWGt6RW14cmt0cnhFUFYxQ2ZfbFdlQW9la3pMNUVYbUYydXJuMTNLV29mQVJydjJWUzJmdVNITElTSlFJVmhpOHc?oc=5</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>14-05-2026 07:11 UTC</t>
+          <t>14-05-2026 12:50 UTC</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>In situ architecture of plasmodesmata in Physcomitrium patens resolved by cryo-electron tomography</t>
+          <t>PFE Stock Outlook 2026: Is Pfizer a Smart Investment Right Now?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Nature</t>
+          <t>sebd.in</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE9hQXdvczY4S1NJV1ZkbVV0b3Jxc1lfLWRWcTJMZ1RDczZRdzNYaUVzcjQ4Qk9vNTc4M3lNamlUbXFRQWJiVVdkTmkxR3QxSjN0SE96d1Y5YjNoSUxjZlJJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxNNVA4aF94Vjd2bS1XMEZoTFlyU25Odkx5bnhVSWdEVU84MDlwNXJwTVVCSWg2RjhkYkU3cnRxWkRUNG42Tmowc3lQcVFzaS15Ri1mQTlXRjJaTkx1T2tuaWRMQ3l4azZWTlp1TnB6R2dkb3U2dHdMLW1YS0pHRWV5ellfSTA?oc=5</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>14-05-2026 10:13 UTC</t>
+          <t>14-05-2026 11:20 UTC</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>What Indian gardeners should plant before the first rains hit</t>
+          <t>Pfizer receives EC approval for Hympavzi to treat haemophilia</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>The Times of India</t>
+          <t>Pharmaceutical Technology</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxQSVBOOF9LbVlWSWp6VGF6RTdZemhyOGZSLXNlYS14UXAxaVhWT2dzSXBET3JuMkZjRnZEYmVPWmdQME5wR1hkQjdhX1c5cXVyMGo1UXhEM1c4U003V1JlRzdhTlNoX2ludDlhMWhMcE00SnR0ZXhSd0ppNXRRZ0t1ZXpkeFFjN08wQzNfZmljZHg0eDVOcnhNOGNkdkVxS2VKR3FNcTlLSTlwWDF2TmxUWmdtdDlQd2k0RmstS1dTRFI3MGNHYmtoUlF1SDhGVEhSeWZCenM5X0o0VnNESWU00gHkAUFVX3lxTE5HRUhYNDFiYzJPODJ6Y1JPQXNVdDlILTF0SDFxN2JMYk9uXy1RYnRYeUdvT05yeWh6bDh0eHN6NXJ5SS0tMTBXNWNZZzhwZmJGOU02STFTT05Ua0RzYjlkTy1aclR3Z3BRNXktbzF1OHhKZ29xYXJValI5VjVZN24wcDh3X1BTU1VfWDRETjh0eGJ2azBMNUZCNHlfT3JFbXV0T09rMDhjT3JmWmtzZXBFTWk2UzhBMVFCQTNCa2VBS21aV3Y1cFdsMVczVWJsb19KUWtkdFZ1Q2lQcm5HdUx2TEx5Uw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOaVQwNGItRUpuZEJpZHhVMjVPR0NrMHRvQUVwa0hjYURXbjZzcGlaS3FheDZ6QlJfOGh1THJjX0dFbXJUcEFIUG90QXFtRHVQeURGQS12RU1CdTlqQ19adTBKNWdLVGM5ckFOa21yNUdXWThvZGwxdlVnaWFqVDhNa3hybVhfZnJJUi1CUQ?oc=5</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>14-05-2026 04:34 UTC</t>
+          <t>14-05-2026 08:51 UTC</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CCMB Scientists Decode Plant Defence Mechanism That Traps Viruses</t>
+          <t>Pfizer Just Locked In Its Next 5 Years of Growth -- Here's How</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Deccan Chronicle</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxObmZ2cjducG8tVWJHWXo1MWRIY0dodHhhbzktclVLcWwxc3Y1bzIxSlkteDd5cWRJWC1VQlRubWxfb0tPbHI5Z0EyMlRMRkZ3cFA2ekpQdTBRdFgyUVNHRjlhbW5NdVZaUGx5NU92OE5ZZC1CeklQYVhLMmp5SlpndnVyekZWb1pfR0RtTi1yUFFaTDM0U05ud1dQYzFPRVdZdHJMR3FMdl9UaUVCNTBmdjdDXzNjNlpOYTJ5dldBeDE2NlMzSE9HUl9FRdIB0AFBVV95cUxPMlFGTmhHSU5XOEx5WDFLMjB0d2dFNmVNTXJ3SzFNNVBWRmNsVlBOSXpOU0dxUXN3YjJMNmxPdk50ZlNROHpkNHo2NDBXZk96QnJqbXhRLV9RS3ZpbFMwYVFJclpjWl8wYWdOYW00aTBiY2VmVERqcHRBWEk1ZktzcFRaMzNlVGxRMkxJSU5SNGZHMUtuMHFlZVlxWDJ4VGxiTUMtQWJUMTBzRTNLOVFqMndWMjl6dzZkXzVBb1ljOFQtd1RVQU9RRV9QTktPalBo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQWWdabGFYSUVHbWk2VEY1Z1FzSXU2ckxTOHh6NUNKRG85dmduVG9IeE0wMXA0OUlfQWN3SmdMWDBUajBFS3lwMlR1aVpDaHpTUkhEaTcwQnFQY2tFMERWMG1tT21IY0hCWGI2ZlBVZGxzaVU2Mll3bTh5WjBhSFcySVVBbmtjYW5NcW13dHRqUlNVdWtLaWhnSWdR?oc=5</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>13-05-2026 18:33 UTC</t>
+          <t>14-05-2026 15:20 UTC</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CCMB researchers find molecular ‘glue’ that blocks viral spread in plants</t>
+          <t>Pfizer discloses new dual calcitonin/amylin receptor agonists</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>The Hindu</t>
+          <t>BioWorld News</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxPV0tkN1NWT185WTNOalkzY1lKN3lzZFQ4SWh4WjhDV2ZyTF83RWxOMVpvTTluZDk3RlVsdmFkOHFOTGFSekpJZVZiSktpdUNIcjZvQ21tV3dSR1hFQldnRWk1ZWpRWDQtZjkyeEJZcHRBSF9ZOE50Nm9WcEhEQ1F0S0pLOG90NU9TMEQxZ0dLeXlBamw2QUxsb1RJNEg3TGtrUDQ4Z0w3ZmVzbjJMNnljM0dHa3JwWGVXRzc4d3kwMG9vQ2w1THBZalRMdE1xN09GSlV4ZVd2OVQwemfSAdsBQVVfeXFMT1dLZDdTVk9fOVkzTmpZM2NZSjd5c2RUOEloeFo4Q1dmckxfN0VsTjFab005bmQ5N0ZVbHZhZDhxTkxhUnpKSWVWYkpLaXVDSHI2b0NtbVd3UkdYRUJXZ0VpNWVqUVg0LWY5MnhCWXB0QUhfWThOdDZvVnBIRENRdEtKSzhvdDVPUzBEMWdHS3l5QWpsNkFMbG9USTRIN0xra1A0OGdMN2Zlc24yTDZ5YzNHR2tycFhlV0c3OHd5MDBvb0NsNUxwWWpUTHRNcTdPRkpVeGVXdjlUMHpn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOWEdFWjVHeHpmY29DZmtNZk1iRkd4Um1VaXlZT0twSFk3U2lIVW5iR2R5SHRpcjM3THBwWGZJc2FpcU1XMlJicUlHbVhHU1RmRHlOUE5nN2ZWcXNGU0NybXZsdm1rQ0Vjb2ZveG9GX3AwZWpPTXBWakhBQWU3MGlqTXZOSTM5NHcyU0lfakQ5aGlrRWs5aTk2bDZxdEQtaTZaTy1Paw?oc=5</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>13-05-2026 13:47 UTC</t>
+          <t>14-05-2026 13:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Bayer Crop Science Reports 17.9% EBITDA Growth in Q1 2026 as Soybean Seed and Traits Sales Double</t>
+          <t>Pfizer Just Locked In Its Next 5 Years of Growth -- Here's How</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>iGrow News</t>
+          <t>The Motley Fool</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFA0WVo5R3lhbW1qajlTdkVUc1Y4cFRxWlNOWGZ0N2xMWWJ2ajRUUnlXWG1qSmRyaVg4dUNYNGk1ZTVNVEthRUtESlFXQ2dXZ2VKSVRuaFdhWmZMUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOcWJsQnYyV2k5Q1V3RnJKb0ZzTUJWbFEtU1l5TWZqU3p3TWxRMDBSRUE0NTduYmNkSzhkQVFxNlpOSkNkeGpGNEVPWjZhZTZWbFEwZnlMbEFWTUtqYVdaRDM2alRJcUp5S0hnZGsxTmVLQnAwcTVPVnJCTF9zcDdhaC1pZ0hfUGNLejh6NWhjeGpTTFNUOUE?oc=5</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>14-05-2026 09:29 UTC</t>
+          <t>14-05-2026 15:06 UTC</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Let The Garden Season Begin! And Let's Avoid These Invasive Plants</t>
+          <t>Pfizer's Turnaround Is Taking Shape (NYSE:PFE)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>The Owen Sound Current</t>
+          <t>Seeking Alpha</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTFBhYzBac1hRc1AzeUNvcjN1bzhqLXExMEJxaWluaFA1SllBbk41cDAxWWx4b1RwUFNxZnNtRG1LdlN6MkF2ZHhpM0FBXzlBNVU2S3hROTUzRXR5WUNqRktMdzRweU5sZlN2WU0zY3RJbGhXZThDYVpaelZWSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQY0JXVkdneHBUc2lzY3Q0SFpfMWFWUXR5UFM1b0g3SnYzbHlpYllCTjR3UWx0d19ZLWs3LUFOYTdTRllxcThVUlJ6eDF5LXEtRW5FUGNtNlFYN3E2QzNkOEJUcC05WnR1bjFtNXBvb2pKZzBEU2hrZnNlYVFWSi1jSA?oc=5</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>14-05-2026 08:22 UTC</t>
+          <t>14-05-2026 13:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CCMB scientists in Hyderabad discover plant protein that may aid dementia, cancer treatment</t>
+          <t>Should you buy pharma stocks? Dr Reddy's, Pfizer - Target prices after Q4 results</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>The New Indian Express</t>
+          <t>Business Today</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxNU2ZJTDBmUk53MWJIckE3aVl1bXhBbExVcW5XU1g0bmtCODdHTE83ZlY0dmVqZHdXM0FSbjYzSDhWSW5yX0RkV3Vldmt2Y1pxODg0Tnd6RjBXcUtaOGZleHZXSW9CRU4zdzZZMDNSSUhoXzQ4REc0SWk5TE9MTU40bDdXbThwUTZRdmtNZ2VhcHR6QVpkRTlVaXJmZF9jSDdFbFVWc2NZOTJlMHUwa29ZckM3UXRxY0Y0TmstY184ckR0eXdUN2NhMGpxMW1sNk1qbXY1Z0plN3RVREhZWFhaZm5KazJLQ2_SAfQBQVVfeXFMTXBFdF9EUy1wRzJYZk5wYzdYRmVvSUVrdmI5dFBGOWs3VncwRlZYa0c1dG1MN0JRbDBvSHdLYnlYNHp3NTk5Qm5MZXJieElsSXdfUFVyUG1JWE4wYjByZlU0c0VXQkJWNkMwTG1ZSXBrUTRXMkxiZ2sxLXVMbi1TM1prUUw4UnZQcFVWT01sVFNqM2h5Y0lCSW5QRXFRYWEtaDdtMXRVbFdOWUczbGxUZHBNZmxwTWNNNF9tOTZadEdReHA3Uk1FdlV4THhKMGs2STNPVnp2eEZOM3BFQ3BlUjFUT1VPZkRDcWJsOURYbkprT2RVRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxPaElkLVkydUJzeEV5Q3Atb25qbUVJQXJBU0lKYTlCS3ByQUd2LVcwSVo5QkJreVZOaUp0eHFZY2pNUkZlWXZBZVU3cnk1b0huZU96NXZxamFkSk5zbUtxZGpsN05YOVNKV3k5ZnRFZENXOXVNM3NPSFotbC1jeHp3WWp6Y19QdV9YMkZQbHhxMGFWSDllb21IQncwWVBYTkNRdlZwWEduam5ibUhQY1JLQlJybDZnSktkNXBOWWpLeGFPaUx1ME02aDBoeWJUd3Y4X1l30gHYAUFVX3lxTFBRZXBmMF9WdGdVRm1MbFlFY29sbzQ5TzFBM2NNS09uUGVBUXhGbi1qSkdXRUl0dWxRT253d3pMT1BoZTMxekRmaDJXa2FXTFZJUE9tV2JVNDJlNXFpcmpyNTZXd2l4RU5NZkhCQzJwRFl5MUZkRmNFYVpMVTNiZjJ5Zm1HQ3locmtYOGZxSldFak9KRElTLTBnWVpqM2xvVnhmTXFZTG81MUxqSFNJWXlkR01wS1ppeS1LYWFKdENWdnN2YmljLUVNdkdNN0JnNFFiTEEwazRZcg?oc=5</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>14-05-2026 03:22 UTC</t>
+          <t>14-05-2026 03:06 UTC</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>As meat prices skyrocket, Tesco shoppers find plant-based mince now 29% cheaper than beef</t>
+          <t>Pfizer Research Grant for Non-Hemophilic Bleeding Disorders</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>fundsforNGOs</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOZDJpVEJRYWJnSDlGeDVBZVZiWGVhbjAtbURDTEhmdGV4dnM0VkVWQkQ1R2QtYTVrUDdTSzNzVXZrT05uTFREQ21oNDI2NjlyUGMtX3Z3SFl5M1doS25SWWNPOFBWSG1mSVZ3LVVtUFFrOGRpZ3h2VDU1T2lxQTdMZG53aXJxTjdDRG94QlZiclZYR3R1eWZRcExEUHRmeVpfaFJZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNMDlDaGpZMGEwQUJBdEJTc1VENkVVa0tmZUpkSDYxUnJkRVNXVmRUY05tR2VRTjlXMlktNUZUZU1IeS05LVdxM09BQjFRMDNrYWxjdjBfcGNXS0VXaHQ1RUhZN1BnS0N5X3lyeTBzdjltN0FCeDFKZXFLck9RSS1PQWxPOFZIODlQTURSeVVvbzVrTmhiTG5KMVJiNWpnZ19pSlR6WEFhU0_SAagBQVVfeXFMTTA5Q2hqWTBhMEFCQXRCU3NVRDZFVWtLZmVKZEg2MVJyZEVTV1ZkVGNObUdlUU45VzJZLTVGVGVNSHktOS1XcTNPQUIxUTAza2FsY3YwX3BjV0tFV2h0NUVIWTdQZ0tDeV95cnkwc3Y5bTdBQngxSmVxS3JPUUktT0FsTzhWSDg5UE1EUnlVb281a05oYkxuSjFSYjVqZ2dfaUpUelhBYVNP?oc=5</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>14-05-2026 00:00 UTC</t>
+          <t>14-05-2026 05:29 UTC</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>NTPC Engineering Executive Trainee Recruitment 2026 (Through GATE), Notification Out for 52 Posts</t>
+          <t>Pfizer scores landmark EU approval for hemophilia drug HYMPAVZI</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Career Power</t>
+          <t>Indian Pharma Post</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE1scjk5ZFB4bVpYZzF5a0ZvQ3R6UmNFaHpEbmpaTDNybGlCMkxkNFRFQXN0eUxDYkhXMnprOTFMNmd3ZFExUm9rVkxFVDhuc3VGRms4czh3a3lnMzV5TFZEVzE5V01XZUt3aDNfd2RjQVpqdG1PUDJ2SHZDaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQazA0eFBCUl9YeFV5OVFlQzItUTdqYkhLNEZybGhnRHJRaEtQeWk1Mmh4UnQ2Q2pMZVpCM0QybmlhRVVjTHB0YzB0Tk95Q1A5Vm9wa0toMWxNN1pWSnBQME4yV3Zoejkwd3QzeUxBVkFEOWt6UXcyRktCRExOMmpISG5nTUxUT0pTYllSSEpLaWp6NW5QcDZkNXpYcUk4c0NaRUZxT0ZwYVJFeXRKWmtFLTFfZ2Y0RnfSAb4BQVVfeXFMUDBMbEVBa2J1dmpoUWNCM1NZRmxKZC01bExTdEotdjBCVFB2V09nOEl4UnNwRTNfaG55T0FDTS1TZzlkMFduTTFham9JTmZPUWM0YlZualJHMWtYVGdBRkVRVjJycTIxYmtSZlZtQXIxc21lbTJIRWE1QWNqM1FHSkphUWI3V1M1cmRDRW9JUHZ0Skt2NDZHczlrNDJaTnNGei1vbFoydndHSjJkQzNiRDF0VlJLSUhzZm9QVnE2dw?oc=5</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>14-05-2026 06:20 UTC</t>
+          <t>14-05-2026 14:39 UTC</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>VW, Rafael near deal for iron dome production in Germany, report says</t>
+          <t>Pfizer stock (US7170811035): Q1 earnings beat with revenue growth and 2026 guidance</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Automotive News</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPbGQ4Nlh4T1BoOUhHOFYtMkYzcVFxQjJJLV9iUmNMVndBalJXcEMweEdwbjNIZVVCcjN5bGRJSFlTcDR6eHRGRkQxWHdwWnNiakczYXdNWmM2QWt0Wl9tNDByWENpeWM4YVRZelQzWUFYWS1ka29yQ1RELUp6Tkt2eFV5cDU4TTFpRkE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPTXdCZEdhOEhiQ2UwWS01bUlsS3l0ZGtfWlJSMHBKVnY3aVE0b2JMQjRZUk96MWYtWFRXMzkteGM2bjBodnZ2T0otdkdHZHQzV1RlcnFvLTZTSnhIdHJKSGVweFFRNjZ2NUdJM0UwTi1RdGdVYjdsSko3b2d2ZWRwbVQ4VUdDWDBrUWdkb0Z6T0pOc0hic1RHdEZzN3ZlMm9hYWppVGZQdGRFaU96djVtSUE4cHpTeWpoOW9zMFhQVVIyV2RmMW9WaWF3?oc=5</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>14-05-2026 08:40 UTC</t>
+          <t>14-05-2026 16:01 UTC</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Cold Weather and Pests Are Impacting Strawberries, Orchards and Vegetable Crops</t>
+          <t>AstraZeneca scores with Imfinzi in another bladder cancer trial, rivaling Merck's Keytruda</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Lancaster Farming</t>
+          <t>Fierce Pharma</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwJBVV95cUxQNFZWOFNuZVBnWHBrUWFkbXhSQVhNel9ua0ozNUNKakh4TDZ3eTBpM3BJUmczRXhvaVhYSmlFenQ1RlVOeUlBYkV4QzBXaTZpTzVyYkNPOTVtcjZBdWxiamhkZFJqV0NzaVREY2Z6VTFxSzFIV201WDNLbjdzUHFySzBrbTNqZzJQbUZkTXJ1cUZoN3RBMFFPaElUZE5UVmhBS2g3OHpTUG95TTBxXzFTTkhzcUM2SHBvN2xDUDMzQldLMGNVRHBoSHJ2YXVVY0xOaDQxUzBHckVyMkwyaGRBSGlteVJmYXdwWHIzVG9aaDYwTTdiQlJIbDlYZ2FNLXVZcnhCQUlMU3htR0NodjRR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOLWxpeUtLcHMwdzdXNHdRZFdsT25NT1NoTjVkM0ZmQzd5eUY1NEtpQUhUS2dyb29aSGxSVmMzQmxSM055ZHg2NUs5bUR1aDZFc21YdDhHUFp6VGtqZDMwZ0hTY19YOTMyWE1XTDFtd0ZfdHl3TEVSaVFIV0dIaTZSOF9vbVRybmpkQmRpUTQzN2liRlk0cHc?oc=5</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>14-05-2026 10:00 UTC</t>
+          <t>14-05-2026 15:52 UTC</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>HFCL Limited Schedules Institutional Investor Plant Visit at Hyderabad Facilities on May 18, 2026</t>
+          <t>Pfizer’s Hympavzi Indication Expanded in EU for Treatment of Hemophilia A or B With Inhibitors</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>Contract Pharma</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxPMGF3WTByR2FJeV9JamRMbUZRazB5OEhqX1JjdXpOWmZ0QjVSSHVON3dGMkFWM0xIUzNBdFNQMlQwWGNCQWZsRkNWZjZpYVdvX2Nid1p2TGtzQUkzVlVOeVRLX2cxTUhyX0ZMZmZTRVVYd3pSNmpaZ0djR1JPeFJ4OVNzcEpOckt3eGlvV2djc3k2STNIajBuTWx4R2FfWnNrRnk5YzNuWUVPZVI5ZzBpaDdOcU9nb3Q3bnVJT2ZnVFRGTnVSeFJmN0I1cVlybnJNS3k2SjlGWnhCYWZ2azdJazJXUnZ4OEpB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxPUXRvOXZMVlcxRl9EdTBFX2JJRi1vU2t1T0tFTTBYTjNVZEVtVWltNXBZZWJHUnZzTlBSOXNfMTVXbGQyZTRPZFF3LVh5V2lxMTdqa28yb2dHdjc4Wkh1SWlId2JSbW5fUUZ6LUVhOEdYNUM4UHdEcmhHc2w4b3VSU0psV3dobGVtWHNvY3BjbmVSNWtsY29jWFZuLVRycU01QXJWWkEzX1Z5YnJ4eHhzYWs4RTBCWUhCaS16Wm1vY1N6VzFBZC1wQlJONm04NHRuNHhSQXpB?oc=5</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>13-05-2026 14:35 UTC</t>
+          <t>13-05-2026 19:26 UTC</t>
         </is>
       </c>
     </row>
@@ -2083,22 +2083,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Pfizer receives EC approval for Hympavzi to treat haemophilia</t>
+          <t>From oncology to obesity, Pfizer bets big on India for its next growth wave</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Pharmaceutical Technology</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOaVQwNGItRUpuZEJpZHhVMjVPR0NrMHRvQUVwa0hjYURXbjZzcGlaS3FheDZ6QlJfOGh1THJjX0dFbXJUcEFIUG90QXFtRHVQeURGQS12RU1CdTlqQ19adTBKNWdLVGM5ckFOa21yNUdXWThvZGwxdlVnaWFqVDhNa3hybVhfZnJJUi1CUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxPc2ZfWjJ6bk5QajVUdnlTUXBXM1VkaVlmNG5nYUh0UTl1VC1XUlpReTQ5UEFfX2tzckRpWTlsNGhwQU05allXcHJ5TGc0bWcybk1HTk9XRWxjY3NFZUpJblZkeXpJYkQxQ0V3ZXhGQ0ZaQ3o1b0tpNEhGRmwxYWpQek81d2ZiVFU3WlIwNFhNU1p4U2ZPMTFDU2Y2ZVY2aGRLdExmMjhGSkl2RXhDSTBDWmJtbC1PdUxwN1pPMnE4ZEE4WEJBcmxZa21RdFdZRUFXNU05bFRXbEFIM3UyQjJEdUtGaDhvbVJ4NzBpNjBEYjdteEZ6QmxJZVRLS3JBYVRmcHfSAYcCQVVfeXFMTW1TR29qc3JXSS1QaXFFMnlQY0k4ZUg4Y1d1Ri1ueHUxRjhCYXlDNlpDUnI2MUlZSkxyWFA3ZlhUWnd2bzJrUHpubHlFVUJ2SXZEWWlGaVdpd0VUTzVvRWJ1OXY4QjctRWs1bGROcE5TWVhTYUtkM19idF9WLVVDT3JvSkpBSk5yampPWTFaV2hMZlpHSUNOaEpuaTNPbExxekJFcktZUml6c1VaZFVDVDQ5UmRtTjV2eEVUa21JYXNTWndTOEExank1c2k2T2tkVFg3a2ZnLUsxaENXa1lTMEJLd1VZVl9td3JiYUlrMVpGZWNUZ3pWTGlEUzRmMTVzZEYwaHF6UFU?oc=5</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>14-05-2026 08:51 UTC</t>
+          <t>13-05-2026 19:16 UTC</t>
         </is>
       </c>
     </row>
@@ -2110,346 +2110,346 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Pfizer Research Grant for Non-Hemophilic Bleeding Disorders</t>
+          <t>European Commission Approves Pfizer’s HYMPAVZI for the Treatment of Adults and Adolescents with Hemophilia A or B With Inhibitors</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>fundsforNGOs</t>
+          <t>BioSpace</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNMDlDaGpZMGEwQUJBdEJTc1VENkVVa0tmZUpkSDYxUnJkRVNXVmRUY05tR2VRTjlXMlktNUZUZU1IeS05LVdxM09BQjFRMDNrYWxjdjBfcGNXS0VXaHQ1RUhZN1BnS0N5X3lyeTBzdjltN0FCeDFKZXFLck9RSS1PQWxPOFZIODlQTURSeVVvbzVrTmhiTG5KMVJiNWpnZ19pSlR6WEFhU0_SAagBQVVfeXFMTTA5Q2hqWTBhMEFCQXRCU3NVRDZFVWtLZmVKZEg2MVJyZEVTV1ZkVGNObUdlUU45VzJZLTVGVGVNSHktOS1XcTNPQUIxUTAza2FsY3YwX3BjV0tFV2h0NUVIWTdQZ0tDeV95cnkwc3Y5bTdBQngxSmVxS3JPUUktT0FsTzhWSDg5UE1EUnlVb281a05oYkxuSjFSYjVqZ2dfaUpUelhBYVNP?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_AFBVV95cUxQcGFBUEY5S2dqRWszckNWcXFld201QVhNenRCdzBzUDAzN3pnN3Eza3lpQVJEUGNlVm9UZy1VaW9JbXhjRWNvYmJkOTc2Q1M2OTRqTE02RHFPQklGQ2lITFFyYnc5LVEwWUVSRDVXZXI2UXZ5Z3JjTzRsRlFVNGtZaUNXWG5JR2dIYzkydDJGNURVbHA1NENKZ1RUZEpFd0plMkhDQkR5c25kT1d6MDJEWVhoNGF4MzNoWG9SY0JmcDJ6SDZiVVNrOUs5cDNwalpGZVhFNzRzbEdlVFJrdWl3bGVxQjBQM1JMTHJva1Q4S2MwcGZCUHN5eWlYbnQ?oc=5</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>14-05-2026 05:29 UTC</t>
+          <t>14-05-2026 01:58 UTC</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Pfizer’s Hympavzi Indication Expanded in EU for Treatment of Hemophilia A or B With Inhibitors</t>
+          <t>Biogen Completes Acquisition of Apellis Pharmaceuticals</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Contract Pharma</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxPUXRvOXZMVlcxRl9EdTBFX2JJRi1vU2t1T0tFTTBYTjNVZEVtVWltNXBZZWJHUnZzTlBSOXNfMTVXbGQyZTRPZFF3LVh5V2lxMTdqa28yb2dHdjc4Wkh1SWlId2JSbW5fUUZ6LUVhOEdYNUM4UHdEcmhHc2w4b3VSU0psV3dobGVtWHNvY3BjbmVSNWtsY29jWFZuLVRycU01QXJWWkEzX1Z5YnJ4eHhzYWs4RTBCWUhCaS16Wm1vY1N6VzFBZC1wQlJONm04NHRuNHhSQXpB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOZ256enZtNjcySFlVRFVBdlVmVlIxLVFUYVZGVVJCMWJyaEVwaG1XSFdrOWxZU3ZDWGtiZmVUNkRtSmtKeTIyaldoQ2xuQ3JzaXdQeUNteGZOM3hZYzI5UUJ0MXVYNDBjVGZrSldQQUFSaF9MUUphR1lyX3daMl9pODJkdGU1NWRLM0NLRDlvelJmOEkzYV92VkY1TE1qWEFXV3dyWW1FeGJObnowT0VfUlRISFR0YXc?oc=5</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>13-05-2026 19:26 UTC</t>
+          <t>14-05-2026 12:38 UTC</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>From oncology to obesity, Pfizer bets big on India for its next growth wave</t>
+          <t>Biogen to advance experimental Alzheimer's drug despite mid-stage trial miss</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>Reuters</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxPc2ZfWjJ6bk5QajVUdnlTUXBXM1VkaVlmNG5nYUh0UTl1VC1XUlpReTQ5UEFfX2tzckRpWTlsNGhwQU05allXcHJ5TGc0bWcybk1HTk9XRWxjY3NFZUpJblZkeXpJYkQxQ0V3ZXhGQ0ZaQ3o1b0tpNEhGRmwxYWpQek81d2ZiVFU3WlIwNFhNU1p4U2ZPMTFDU2Y2ZVY2aGRLdExmMjhGSkl2RXhDSTBDWmJtbC1PdUxwN1pPMnE4ZEE4WEJBcmxZa21RdFdZRUFXNU05bFRXbEFIM3UyQjJEdUtGaDhvbVJ4NzBpNjBEYjdteEZ6QmxJZVRLS3JBYVRmcHfSAYcCQVVfeXFMTW1TR29qc3JXSS1QaXFFMnlQY0k4ZUg4Y1d1Ri1ueHUxRjhCYXlDNlpDUnI2MUlZSkxyWFA3ZlhUWnd2bzJrUHpubHlFVUJ2SXZEWWlGaVdpd0VUTzVvRWJ1OXY4QjctRWs1bGROcE5TWVhTYUtkM19idF9WLVVDT3JvSkpBSk5yampPWTFaV2hMZlpHSUNOaEpuaTNPbExxekJFcktZUml6c1VaZFVDVDQ5UmRtTjV2eEVUa21JYXNTWndTOEExank1c2k2T2tkVFg3a2ZnLUsxaENXa1lTMEJLd1VZVl9td3JiYUlrMVpGZWNUZ3pWTGlEUzRmMTVzZEYwaHF6UFU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPUHNzbmJucnlUdy1SRVA1RFlXcGN5MVZoODNGQ2E4alYwS2VIQ3o0NzF4RUZvS1dCR2xnTVZUelB1QzBpNmJWbDByVTFETkVRUjJxYWU3dDFCVURMdXM3TWcteUwzaVBLZ2VibkljbGlPN1oteFlDbDJSQ21yUHpqZHo0cUIxWUhLdlhVT25LRV9fWFpIWEtGNUh6bmpqRlNsdjNrMm95NWoyWGZlWWZLTzZoNWlQLWlTV2JpNHhtNkNJdnpfM0E?oc=5</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>13-05-2026 19:16 UTC</t>
+          <t>14-05-2026 16:39 UTC</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Should you buy pharma stocks? Dr Reddy's, Pfizer - Target prices after Q4 results</t>
+          <t>Biogen has seen enough — despite no dose response — to advance tau-directed therapy</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Business Today</t>
+          <t>FirstWord Pharma</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxPaElkLVkydUJzeEV5Q3Atb25qbUVJQXJBU0lKYTlCS3ByQUd2LVcwSVo5QkJreVZOaUp0eHFZY2pNUkZlWXZBZVU3cnk1b0huZU96NXZxamFkSk5zbUtxZGpsN05YOVNKV3k5ZnRFZENXOXVNM3NPSFotbC1jeHp3WWp6Y19QdV9YMkZQbHhxMGFWSDllb21IQncwWVBYTkNRdlZwWEduam5ibUhQY1JLQlJybDZnSktkNXBOWWpLeGFPaUx1ME02aDBoeWJUd3Y4X1l30gHYAUFVX3lxTFBRZXBmMF9WdGdVRm1MbFlFY29sbzQ5TzFBM2NNS09uUGVBUXhGbi1qSkdXRUl0dWxRT253d3pMT1BoZTMxekRmaDJXa2FXTFZJUE9tV2JVNDJlNXFpcmpyNTZXd2l4RU5NZkhCQzJwRFl5MUZkRmNFYVpMVTNiZjJ5Zm1HQ3locmtYOGZxSldFak9KRElTLTBnWVpqM2xvVnhmTXFZTG81MUxqSFNJWXlkR01wS1ppeS1LYWFKdENWdnN2YmljLUVNdkdNN0JnNFFiTEEwazRZcg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTFBNNDAza3BPQ2lmVHktM2tEel9xWWhGNXdmNGszd1ZDcUhLc3ppQnpZaVlmdmYyTmpOUWlmUVhDNnpFUkNBVWRWcVBUekhOVTY3MFZz?oc=5</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>14-05-2026 03:06 UTC</t>
+          <t>14-05-2026 14:08 UTC</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>European Commission Approves Pfizer’s HYMPAVZI for the Treatment of Adults and Adolescents with Hemophilia A or B With Inhibitors</t>
+          <t>Biogen advances Alzheimer’s tau program despite midphase miss</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>BioSpace</t>
+          <t>Fierce Biotech</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_AFBVV95cUxQcGFBUEY5S2dqRWszckNWcXFld201QVhNenRCdzBzUDAzN3pnN3Eza3lpQVJEUGNlVm9UZy1VaW9JbXhjRWNvYmJkOTc2Q1M2OTRqTE02RHFPQklGQ2lITFFyYnc5LVEwWUVSRDVXZXI2UXZ5Z3JjTzRsRlFVNGtZaUNXWG5JR2dIYzkydDJGNURVbHA1NENKZ1RUZEpFd0plMkhDQkR5c25kT1d6MDJEWVhoNGF4MzNoWG9SY0JmcDJ6SDZiVVNrOUs5cDNwalpGZVhFNzRzbEdlVFJrdWl3bGVxQjBQM1JMTHJva1Q4S2MwcGZCUHN5eWlYbnQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNaEkySTRwNTh3NVF1R3RyM3RObFh2aGhLdDNiamg5RUVibmRNNER5MGFqdi1QMHVnbnRBRE5mcEE2SUlybzBid1U0TWRwNlc3NUlXSkVESDJDYl9QUkM5bHFfNTZqZVFQMnJCZWpiV2dMYTB1Vk1SNjZrc25qS2xWU0JkbnRBSE5VU0ZVd0p0OHF4cEVRR3pFT2NFTmgtenM?oc=5</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>14-05-2026 01:58 UTC</t>
+          <t>14-05-2026 12:35 UTC</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>The Zacks Analyst Blog Meta, Pfizer, Salesforce and Smith-Midland</t>
+          <t>Biogen advances Alzheimer's drug to late-stage trial despite disappointing data</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Yahoo Finance Singapore</t>
+          <t>CNBC</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOVGVya3BJVUxmb3hmN3ZVajdqVUxzSmZCMGh0eE9uQkxPdmxGQVdTQWdWUHpCa0Rvd3VaZjBENGJRUUZxMHJsQlZkRVU0VDV0b2oxR3dJTEJ2LWpsUGFqbUdGd29YSXpuWkJPQUJNU2ZfMzZockZERDh2bkx6QzZIRXhZT0owdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOaHh4Y2FDRWJBc2dOTDA1S0ptZ0Z3N3dTbkppRkVheEs4Mk5CZFhrZi1zVEFFZFZsekZScW5DeGJ2NTk5aEozVm1zUWVOZVNDdFdtYUd6bjNkV3FUbnlBRkM1VEY0amlIWkdlR0Y5NWNKMWQxbWhPMG85UzhkdmdUbWRUaFNDU1lfSE9rYTNR0gGTAUFVX3lxTE5jSFlSQkhiTkpTMDRaRFVYVEc0QUNBT0RmemhWd25VTmFReXdCTHdVakhsejdvUVBFUWFIQU02Y3V2M2U1NUItazFPb19sb0cybERWOU40WUVDNHhwMXRGUDU2SW0tR1MtQ0pLWFVySXFwZHdNWWEzaHBjMkd0QWJPS1VzVWpaVmFtc2M3bndPV01VVQ?oc=5</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>14-05-2026 09:18 UTC</t>
+          <t>14-05-2026 16:10 UTC</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Rigel Pharmaceuticals Enters an Exclusive Global Licensing Agreement with Arvinas and Pfizer for Veppanu | PharmExec</t>
+          <t>Biogen Pharmachem Turns Profitable with Net Profit of ₹85.95 Lacs in FY26</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Pharmaceutical Executive</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPdXpwSEt0WGNHSXBrV3VtLXNWbEFIZl9kRzh1ZnJtc0JPS1A1TEw4NVhmbDZwaHBucDFlNkxlbWZqWWdyZ0tPYzVPZEstMHJSLUZ2YWFxSGFQUG9QMDd5VjFYc1lKUUNncXo1aUE2eGFzTlVXTnIwM3p1NG9CMlAyNzlsR1I1am9HUmpYeGNIeGp2M1h5amh2NU5tdV85V19NUzRpVkx0SS1lYWZLRXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxNRWJfaFBXWmVQQ0tzZTczdGczZVBwNWNXd3dFWkRTV001dFNxQlBwV0FueUdXTGEtMGRUZm5ZODB0bWxVS1ItTU1uVjI0b25BOTJ4Wkt3S3ZFUkxpQjBSTW5vcFdGbEF6RU9qMjVuQWhLWkwyZk83Wk0zUDYzQlZKVEFSTHdZdzN4UGhybmFUTVdMc3p0aTFMd0t6ak40NEFJUjF0S2NydWlTTGYwS1ROV1dod0RrYXRGenNvdFZnSjYzM2lZRkEtbzVnd1dFVDluaWVnZWROT2tTeDRSNng0TE1ybkVnWHVIbUI4eTNyTWVjVTNRNWc?oc=5</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>13-05-2026 18:47 UTC</t>
+          <t>14-05-2026 15:56 UTC</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Pfizer Hemophilia Drug Win In Europe Adds Weight To Undervalued Thesis</t>
+          <t>Trial miss doesn't dent Biogen's faith in Alzheimer's drug</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>simplywall.st</t>
+          <t>pharmaphorum</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNQ1pHNEJUenZmWkdoYlpfN3VXdW94d2hTS184eV9lTDQ4QXZkbTZzcFRRQnVOOHdJYjVkXzhjSjhwbGpBMjI4YWNELThZaWZYZnpWQTUzNjk1N09JdlRRR2ZKa1d3eFVqWFJOM181bmRJUVFvcUhWR0NkeHVxSjBaMkpxV0czdDFpcW9QUkNVRmwwMmdRTzM3U2RkN3F4Rjk4aU1jUk9YbThuaERoLWRhQkxnVDJNS0w5U3RmZ05vT0s5dy1ILXpsSkU1U05DN2ZadW5F0gHYAUFVX3lxTE5YTkg1OEZfQ1p3NW9UckVoVnAwUFhxdGtTNUEwRHFfS05Zd2FmREZwcGU5enV1ZjZQekxNOEtYNTlQR3ZpQzFMREFhaG85V3RUX01nMmpxQ0xCZWdQUkx4dFo1YWIwbDlaVGNUalM0R1MxOEdMTXh2dWtjRnF1RTk5dDRzazhoWVItS19lSEpRQVZFcTdzMWZPSUxJY042NWJ3RGZHWTRYbGM5MXFHOWoyS3NDSnVJTGVWYXJJaGlrUWFfd2ZfdldzTGtQRHZWcWtSZXVfSEFqdg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPTy05a05mbnFQZGRiTFpxMEhWZHliSlRGam0tU2pGaVU1azhPOE5QZ1lyVnl0bTR5d3hLbEZsdmZVZW5JbzRrQk9WV1M5UHJHS0ZJY0FKRWFnaC1Kc3dya3FHTFAwT1duRWVCMmNpcDM5T1l2OFpKV25HdmhrWDNtRHREUkxfbmpGcXc?oc=5</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>14-05-2026 02:06 UTC</t>
+          <t>14-05-2026 15:53 UTC</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>EC approves added indication for Pfizer’s Hympavzi</t>
+          <t>Ionis partner Biogen announces topline results from Phase 2 CELIA study of diranersen (BIIB080): first study to show reduction in tau pathology and cognitive benefit in patients with early Alzheimer’s disease</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>The Pharma Letter</t>
+          <t>Business Wire</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOWVdYS3laT01nMm5Fal81LXRaUHA2YUFOdFFSVFFVUUdiSHFpV0FBbWlWcnVQVWhnWkpnZEpoUE5LOGQ0U1RFSW44ekwwdDRDT2RKVElPYmRyOUhGV3lJcUFZemYzRDJVTUVNajY1anhWMy15WVVXUWpBenI3OVNMdXlOOXBXVHJWU05USURENU93c3puWlgwZUNGRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-AJBVV95cUxOVFp1c2VXa1dRNDBzUGtUd0VpOFZXMm5MNVVXY1VtLXdEUmxkdGhpeURQYnBONEpObHBDWmE2RHNsNFNNWkpWVzQ0ZmhyNW9BOGljQllSTUJQenRMT1A5QXppajBSQzlDY2FHMHNOYVNwby15eGxfSUpIcVN2LXBmSnFTZGlEZXUxaU1hbFNmcjdVOWtpMHh5ckZjWnZjT3lqWUFUZVIzUVFxQVNyZWRvUUswR2xCMVlwUjc2SDU3SkFldTRmdnRCeGYweFJVdnFoZzhHcnlfbnNNeW1udUUxUlNYV2I1UVNldGZCaVZtYWg3Q3ZrVlNXaF82clg1OXFmNHJOOUt2Tzh3UWk1ZUZSUXRwSWhWSlRXR0tfMTFWTk56RUxfMG1Lam5zdUxBVEc4UUc3U2ExM3BpcGJMTkt2S3RWaG9VT21Odmc3TkpHdE9iZ2s0OWpuaUh1dVdsMWd5OWJzcmduU0ZpTC1UbmNFQ3JwMnNxQ21D?oc=5</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>13-05-2026 15:06 UTC</t>
+          <t>14-05-2026 11:05 UTC</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Valneva Q1 Earnings Call Highlights</t>
+          <t>Wolfe Research reiterates Peerperform on Biogen stock after trial miss By Investing.com</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>Investing.com India</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQMDlOVzFieHc1WVhfVjZHNUVldHVQYWpVc0pZZngtdXZLVEtuTEdURmFKTGowUjQ1RE82NTJzdmQ4R0hCdks0ZUpWU1VpLXEydXlKZTNXWS00bkViWjZWRjhoblg3ZWJURHpfenpJSW9lZ0YyM1ZXU0hjckVNcWEyeUJZM3A5b1RISWVLLVJlSjdBaGVvdGpQRThmZS0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOYzZualduSEh3eEJqNmRCVkoxdGJGcGNweGZkX3ZHcUpjMVdQekNneUFlaFVwUzdySVdYOTlhUV9LbGVmRVlQSFEzc0tBcTQxeWtxRmJQNXAxTS05WjVEeFZKS1ZxLUJxR1hHUDNRREtackpBLTk2YVZvSVVKMzdoU2Zsb0FMQ1hsZnd1eV9OWUJJQkhSTDdMaF8wMms5Y2FpR1VxajNyRnVieXVrR3hiY3RDb2U0UkJWejBGa1NkMHR2Y1hYMGNGaEMyTQ?oc=5</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>13-05-2026 19:10 UTC</t>
+          <t>14-05-2026 12:41 UTC</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>What sets apart MNC pharma companies from their Indian counterparts</t>
+          <t>Topline Results from Phase 2 CELIA Study of Diranersen (BIIB080): First Study to Show Reduction in Tau Pathology and Cognitive Benefit in Patients with Early Alzheimer’s Disease</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Moneycontrol.com</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPMGRCZTFFSFpLNldXS0lDcHdQQmNUQ2otSTRibFNPRUZheHRwZTBuVFpkd0ZyZlNVS0Q1bjRTcGZkY3M1VDdIeHdnNHZRODdORUh2Z3o0aUNjOHR6ZVc4MEFSLXA5TXVncW9sTktLZFRkX2xQWGVDeFczWGozenEwVHpzZU1VSWRETkw2WkpGaG84NHRLeENEVDZENFVVbWUwOW1LZVY2RGo0OEgzbjF2b2ltRUtwcUZOc0lzTE1WUTjSAcYBQVVfeXFMTWFOdUItYXlHSWpjckdrUEVwRlpnX3RPTjZRTTU5ZUNrbU5SamhIbm1ScHNBVS1nMkpycUtodnpFU1dOaXNjUkhNNXNmd0xDM2l1QVpMN3dYVGJ6SGNTY2RFV0gxZ1VUaWRYM0NkX3JTcmsxMzNmM0lxcndTeU41djBtWUo4MnJLdVp2TGhwczZWNE85Qnd1d3cwYy1OcjFlUDFzQTdrSTYwTWVIMGEtdnVCTHhCd1NkQzdNY3EySXdJNHBtSWFR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPX0xNaEdQU1N0eHU4TDJzUnBQWFRMelRMSEFza3ZxN1Nhd2RNclNHb0Q4VkFBeWZxMHd5MDVfaEY2YUNpSkNPeExGYzlmdWNwbWVRNXRpV0pqcDhNX0pXTHZGYnlCWFd5b0pTaW5ZbndKSjJCcmcxOUx6RzYwa0Z0Qm9lRFJoWjVqRU9kcTkwOFBZWmNRTGJLTnZPdEhvaHU4UkJuMnhNVHdzamhhUTR5U2tOWG9kN3FhYmxDelY2ejJFZw?oc=5</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>14-05-2026 02:55 UTC</t>
+          <t>14-05-2026 11:03 UTC</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Pfizer stock (US7170811035): Q1 earnings beat estimates with $14.5B revenue</t>
+          <t>Biogen pushing tau drug forward despite Alzheimer’s study failure</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>BioPharma Dive</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQNjZYTFU5clo5NVRrTVVHczJRQmw3SGt5aTV5cWxlSVNUdkowV3lnaGJDRnhxQnFvM3UwTWFPQWotS1A4YnJMYkN5ZzhldDRSVjd1bVg0a013RFBNUS1IUnNyeHdVNzZUbXJFczliSVoxMXZ3U3J4U3F5SHowUGVoUWhJdHhwWUhqSl9xYlNLbHpnWkVOaFczT3NleGxXYXl3OE84WmExMk9wWXVZVm1VamVkVXlucXFTaXA1MzRVNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOT0l0aFkwMVBQZEJzMWIxWC1adUxJNWN1NVNGVXpITHMtd2lJU3NsN21sVU5ZRG8zaUMwbV9iYllpSmRxZC1mQUxwUUFlOTBOSC1uOThiU0psRDJnOU1ST2FycEF1YnVnOWNUSlRxUHg0WWVnMTJ1NVRITU5Hbms1c2ZQdDVjRkZGTDBHNl9yVHgzejJya09HOHQyZDZ5Mm5CZVRF?oc=5</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>13-05-2026 15:30 UTC</t>
+          <t>14-05-2026 15:59 UTC</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Can Pfizer Achieve High Single-Digit Revenue CAGR From 2029?</t>
+          <t>Biogen’s tau-targeting Alzheimer’s drug posts mixed results in mid-stage study</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Zacks Investment Research</t>
+          <t>statnews.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxOSDhZR3p3NFoySzc5ZUJLaDRmQ3ZIYWs5WnZac3dNaHNQSk53T2VuYXAtdWJkQnkzdldwaHFKQXlOU3hBSGN6ekF5VWZ0YUhhS3EteVlNNlRpSUxOQ2FCZ2tmVjh5X3lhWDF3TEhDNFcxRWc1R0xsclRGZE4wUHlFWWdFUHZldFVuVGM2dnVTTkY4UDVFSkNiYk5xajJja0J4b25FYUpMdktlUXlNMG9Xb2RHR1l2dGh4YktUbVQ0QkZoY0pUSjh2U3ItMUhEdGRaUEZlX3A0a2hyVVgxTnNuSkpZTGhtX25OeGdUcU1ScGU3LXZ2dlBvZjlmbEZGR3FQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNMEZDWGlKc0EzY3FuaDdFNldxYk5nTjQ4NTF5aU5rbmhCU2M0N0RrWVptOFJlc3JNYjhOTzdQSDdST3pkV19ldkxYWFRCU0tGTDVvZV94ZjNlbzdiQXFNVGRKcE5LMHJBREFBY2I5b1A5NUtKMlhoR1JGMTU5Wl9sUjRORVhhUzlXUHpSQXR5ckRBOTR1NGEyb3NPZEFYT28?oc=5</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>13-05-2026 15:44 UTC</t>
+          <t>14-05-2026 11:30 UTC</t>
         </is>
       </c>
     </row>
@@ -2461,22 +2461,22 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Biogen stock jumps 10% on positive phase 2 diranersen data for Alzheimer’s</t>
+          <t>Updated: Biogen won’t be ‘impulsive’ with anti-tau Alzheimer’s drug</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Investing.com India</t>
+          <t>Endpoints News</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOQ3BBSm5UTjlYOXY1MUZ4dEp0S3lwdm44OTNxWWhHQ3lrcGRuNzFjX0NPUndpMGFqZlh5WnNDbzhNUXFNMEhnZXdPalZPTHdSalM4MnU5ZEpVSEEwUG5hcExsSC1pS21DM3dtMTBlRjYzVm9NeVk5TWlLaDhIX0ZRdXNzSjhhdXNZUGtVdVBDdENjQTdFeGx1TXZDTExSRFNIOFViRW82ekZnTlJZVDQ4T083alVRbXlGTjVHT2R4RjlkdUZHY19z?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOXzlpTC1OTkVXaUZZU2lOQ2YtcnI2Y3VMb2R0OGdINDEtT3VBZHBTWGlXc0JfYm1ST2U1WE9uWUtlODdibTNObkJTRXBNU0VWejdfSDZhZWJDZ2F6VVNtVHRoRG0xcmtTZDBqdlZLczM4aTdST2pyZkZDd3hjX251dlRzSFBndDdvckM2V01UbkRHVmsxSHZIVzl4UzhfWmZPTm1mNDhyaTJhOXc?oc=5</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>14-05-2026 11:13 UTC</t>
+          <t>14-05-2026 11:32 UTC</t>
         </is>
       </c>
     </row>
@@ -2488,22 +2488,22 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Biogen's Alzheimer’s drug fails to meet mid-stage trial goal</t>
+          <t>Biogen Moves Alzheimer’s Drug to Late-Stage Trials. Wall Street Thinks It’s a Mistake.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Reuters</t>
+          <t>Barron's</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPUHNzbmJucnlUdy1SRVA1RFlXcGN5MVZoODNGQ2E4alYwS2VIQ3o0NzF4RUZvS1dCR2xnTVZUelB1QzBpNmJWbDByVTFETkVRUjJxYWU3dDFCVURMdXM3TWcteUwzaVBLZ2VibkljbGlPN1oteFlDbDJSQ21yUHpqZHo0cUIxWUhLdlhVT25LRV9fWFpIWEtGNUh6bmpqRlNsdjNrMm95NWoyWGZlWWZLTzZoNWlQLWlTV2JpNHhtNkNJdnpfM0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxNWlBOa29FUDAwRDJJQ1JuMnhYSnpfek9SZndrQVpEdTJ1QUpXaVZqWmhaMENHMWdtdHQtVkRwM0JENlc3ZVVXOTFOMUczQ2hlNlRiWUt3b1BabjczbEE2TjFLYnJpOE5tZWMtLTJveWtHYzR5aFd0OU1lQWc3Y1NPNFVB?oc=5</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>14-05-2026 11:03 UTC</t>
+          <t>14-05-2026 16:07 UTC</t>
         </is>
       </c>
     </row>
@@ -2515,292 +2515,292 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Ionis partner Biogen announces topline results from Phase 2 CELIA study of diranersen (BIIB080): first study to show reduction in tau pathology and cognitive benefit in patients with early Alzheimer’s disease</t>
+          <t>Biogen Advances New Alzheimer's Drug. But Investors Are Leery.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Yahoo Finance Singapore</t>
+          <t>Investor's Business Daily</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPNXVaaUJRLWVNNmk3RlN4X3h1cGUwVVRQNllwMktEU2pJLXRSM25wdWNNNFZmV1BoYjhLSFphajk3UE41dzdnSmVJaGNVbVdDSngwWE9zSV94eUlRYkN2ZkFsTlg1Y3ZMVk1EY05HM3RkazdEdmRtRDdwckh6N0oydV9JWGdMV3hlMWxjTGgxYWs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOWXNDcHhDRGJPdk1GU1JSRmlvNkMxN09FSlozdHBHdWV0WXdvQzd3eDN2SDNKWmh6UHZXdk5VSDlMMTBzdWM3OVJfWUtPOENaY0VCVHBsM3J6NmM4WVdGekJDbkk3OFBZQ25QanhYdDBIUkE2RndTZ2x6cFBIY3Rja3VzNHNNaXQ5SDZUUHRwdndwc3FT?oc=5</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>14-05-2026 11:05 UTC</t>
+          <t>14-05-2026 16:57 UTC</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Biogen Advances Novel Alzheimer’s Drug on Suggestion of Benefit</t>
+          <t>Dr Reddy's, Dixon Technology &amp; more: Top stocks to watch on May 14</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Bloomberg.com</t>
+          <t>The Times of India</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQTGRoRkc2OHNybW9zZUxJX3hrX1ZUUkxsaE9iWlVEM3FiakdsRkNabngxYUgwMFJVQkZMb0FVZ3BKLUZ0VDNSdTFEaU9EZmxXODZMNUQ5ZnZuMDZja2lJcHBoMEo4d2xmbmVtR2hWZFRuMGhCejd4WmhvT2VNZ1RxLUFDTnJFS1NLVkFBRksxSzM5eVZrSE9OTzJ5dVMwdHpfR3Rydnp1M2FxUGFyWGpaRzVPSlprZnBFYm95TzY2M1dIZ3Y3SGlMWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxOZk8wSk9aeUtma0xCNGVjbUlaang2SEFrWDRQUkhoLWppdHpnaWgyTmxhbEZKdmFXS2Z3U2VWdTVBRWlUcFlvcEV1SlcwTVd6OV9GZ2NHX2Z4bzBMQl9QRnN4UnRWd2d5OXB3ekgxcU5ieXUzd3hOcERpUjBYYi1xRjI1RXpVdGNIcWZLeXR2ak9hLU5vcnNQa050Qnowd183c0hzWVNiSWdvQVRCT2k2QTg0N0xaR216NzVaTUlwWFBKUXAxeTBOQWlhV3lnTGotUllrR0dSbTVMQzQzMHVpb9IB5gFBVV95cUxNdUk2RFRod0pBOURHMThoS2VzcDFMc1dNQlJQekNidjhRM2Q2b2NTMzhySVpyNDZOMWtNOUs5RnF4RHE3bVQ0VzVsa2RrLUFEdUJfZmw5ajZLVV91Zy1qaGtLUW1SMmE4ZWdqZlZBS1R5enowMkR2Q3cxUUREeGdJX0o1Qm56YUtVdnBleXRlMTF4QTNMamxtbFRxTzR2dm5tZ1A4dFVVZnl3RXhVQ3U0M3dWSENNTEYtNW5qZmVjcDVraGIxOUZzX0FPVTJ1NVZzV2cwV3FYS1dVZnlubkZxQVNocnA1Zw?oc=5</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>14-05-2026 10:59 UTC</t>
+          <t>14-05-2026 03:07 UTC</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Markets Rally, But Biogen Pharmachem Industries Ltd Sinks to 52-Week Low in Stock-Specific Sell-Off</t>
+          <t>Dr. Reddy's Laboratories rises Thursday, outperforms market</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Markets Mojo</t>
+          <t>MarketWatch</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOazJSRTZrM0dMYjJFU2NLbVVlTjllYnduVFBOYlFpOXZRZGZwbWNXVllhZlRIX0RfNk5aNXZwM3F2dzY3ZGl5VjB2WVRad2RORHg2WEJCUUdJYWpLc1BvWFVHSlVhMTVXMFo5WWxPcTg2SXdjWFdJc2pHY3NYeXUxTXBtQzE5WjFOWGNaS1ZPdjg3MFgzSlFhc2FQbHJTWkVJQmVqRTdramc5MnhOVkNra3dxUlMxZ0lteVRodQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOUjlTNl9sVEotRVVyQ1Jqdkk5bkNBTnRiVkZQempva3l2WE1vYzFMLVVFaUdhT1puVW5NRzJPaDA2ZVUxa3lmUndBbUZ5U28zanF6OEl4WmxOS25PcXpDN2FKYllwVWFjcm1ZX05Pc3R0SE1HNjFfdXBTLU94U0NGWW9vZFpEaG44bmF4VFdkOVBkN1RTUGc4X3IwYWlTWWdzRUJQRE5sTTIzUFBfVURNTHlycw?oc=5</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>14-05-2026 05:49 UTC</t>
+          <t>14-05-2026 10:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Biogen’s tau-targeting Alzheimer’s drug posts mixed results in mid-stage study</t>
+          <t>Dr. Reddy’s Laboratories Secures CDSCO Approval for Generic Oral Semaglutide in India</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>statnews.com</t>
+          <t>Chemical Industry Digest</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNMEZDWGlKc0EzY3FuaDdFNldxYk5nTjQ4NTF5aU5rbmhCU2M0N0RrWVptOFJlc3JNYjhOTzdQSDdST3pkV19ldkxYWFRCU0tGTDVvZV94ZjNlbzdiQXFNVGRKcE5LMHJBREFBY2I5b1A5NUtKMlhoR1JGMTU5Wl9sUjRORVhhUzlXUHpSQXR5ckRBOTR1NGEyb3NPZEFYT28?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNbEJpUjRTMk9RWTEtOS0yRTNYcWdkSi1uZm95RExNZ09Pd0pQLUdWQ3pvbnJqaEV1UWUxR1k3eHR4a1pOT3RGTV93cTlJQXRlc0JWMnE0c25fYnJIRXlqSXZFZzdZWThOYWU4M21xcks1N3l1ckROa2ZfVFRMdGZaZFBMMzlsc2tUUjJDNm9BemRMVWRZb1BudjJSYUFrYld5Z295NHIzd3MyV0h4UUE?oc=5</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>14-05-2026 11:10 UTC</t>
+          <t>14-05-2026 12:59 UTC</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Biogen Stock Surges 9.3%, With A 8-Day Winning Spree</t>
+          <t>Dr. Reddy's Laboratories Q4 Earnings Call Highlights</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Trefis</t>
+          <t>MarketBeat</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPZXVNNW9Wb3J2YW15TFYzVUszWkVGcVROR1hxR3ZWNW5kdk5iaVVid25IcFFuZ1d2QmNMSVVsYngzOEtTZzJVdFFLREVRRE9iZVhFbHYwdjZXUGtFLTBWU1lDc1dZRVFSbFNLd2dGT3N5WTNwZ1J3YVdWOHhQV3hMZDAzWlEyNFIxVlVha29wUl90WVFXVGZyNzNTVkZoNjJvNlNFWVlVdk1MRUVvZS0taw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPLTN5OE5MMnR5bW5tSHo0Y3AyYlJadjFYNjExaDdaaVdVS0JybnBmTE1NZWJ5TXNjdHo1cldabFRHa3NxY0V5RDNoa3ZBNks3SVJsOFg5eTI0ZUlQVU5rUVZURm9kTDl4T1pmZk05OHJtRnZNWE5XUEhVYUFydHhpQ2RUVUN6VGhMcW56bUV5V19QNkNOMVpJbXo4bzNDVFEwMzFmNnV3UQ?oc=5</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>14-05-2026 05:26 UTC</t>
+          <t>14-05-2026 12:22 UTC</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Biogen Inc. stock underperforms Wednesday when compared to competitors despite daily gains</t>
+          <t>Should you buy pharma stocks? Dr Reddy's, Pfizer - Target prices after Q4 results</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>MarketWatch</t>
+          <t>Business Today</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxPd0F3djdiSTE5SjluMkdMWEw4aUZiMjZoMlg0QTFNSmFpcFEzajhuMnVELU0tRVVLVmpxbG05dHBiWlJPWjhLWUU5bWZXb2FZdTdkQ2VDbWJ4ZFctV3JFTXNhc0hyQ1J6NGJHbzRXTk4wU0Y0bnEtb3dERTB5R1VVUWxFcUZHd2EtZWdRdFVCbDlxcmNsZW1paFFGTkkxb3JCSlNubE45M1VkSUItVW5meVkwVU9rRWUwYkpHMXZTZEtNMkJyYmpsX1hCSU1FTVg0NUc5QnJ3b0JkaGpoQUJMNldDMUJrYWJJTkxpUXp2ZGVNdW5DNHpkOWJQYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxPaElkLVkydUJzeEV5Q3Atb25qbUVJQXJBU0lKYTlCS3ByQUd2LVcwSVo5QkJreVZOaUp0eHFZY2pNUkZlWXZBZVU3cnk1b0huZU96NXZxamFkSk5zbUtxZGpsN05YOVNKV3k5ZnRFZENXOXVNM3NPSFotbC1jeHp3WWp6Y19QdV9YMkZQbHhxMGFWSDllb21IQncwWVBYTkNRdlZwWEduam5ibUhQY1JLQlJybDZnSktkNXBOWWpLeGFPaUx1ME02aDBoeWJUd3Y4X1l30gHYAUFVX3lxTFBRZXBmMF9WdGdVRm1MbFlFY29sbzQ5TzFBM2NNS09uUGVBUXhGbi1qSkdXRUl0dWxRT253d3pMT1BoZTMxekRmaDJXa2FXTFZJUE9tV2JVNDJlNXFpcmpyNTZXd2l4RU5NZkhCQzJwRFl5MUZkRmNFYVpMVTNiZjJ5Zm1HQ3locmtYOGZxSldFak9KRElTLTBnWVpqM2xvVnhmTXFZTG81MUxqSFNJWXlkR01wS1ppeS1LYWFKdENWdnN2YmljLUVNdkdNN0JnNFFiTEEwazRZcg?oc=5</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>13-05-2026 20:58 UTC</t>
+          <t>14-05-2026 03:06 UTC</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Biogen Pharmachem Industries Ltd Falls to 52-Week Low of Rs 0.42 as Sell-Off Deepens</t>
+          <t>Cipla, Dr Reddy’s Lab, Crompton Greaves: Nomura’s top picks with 17% to 26% upside potential</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Markets Mojo</t>
+          <t>financialexpress.com</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPMERWRXZRZC1XeGl0M1Fjc1kwa3lReW1KY1QtUFM0VmU1S0hLVDNtSmZRcHREZWllTW40Q3ljX0VNcVUyZ0RpYi0yUV9Za0dqV0JHM2d0aW1udFJLN1p6T21xX1lsVkhXaUg2b25xOTlJZFpvekF0RE9xRVV5OGhOOHJMSlk5U3hWbDlHYlV1eFhaa2RzX2YzTUFYcWdDbUVNOWFtMUc0MWljY0dRZFAxQmpVOGtqdFg3NHh5UA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxPUi1QS3FmeUNwbktRM1VOMHZRQUlHTldfb1pBSkpOanJTaTBrMlBBOWp0NHUtQU56SXVnOVdZeDFYanhOaUw3MHhlZ0FwM3N6RUtVc1dMd2s2Uy16RlhPN05reDdBTWpfTHFIekRqQk5NNVpTOGVjdk1lOW1weF81MW5YdzFUcXVIMjF4WUQ2TVRKblNHM0xPbWJaY1Joa3RYc08tbnhHeGJkMXIySk5pY1Y1OHV0LVpfY055ZzRJek9YckRiTkYwa0dnaEdTM1XSAdYBQVVfeXFMT25UTkVLNlRrVHVUWnVaRU8wRmhjY1JwV2xGWUl3QkZ6TEdPQy1vekplR0RKRUUyMmpyQnM1YkRNWENTT3NTRTRoeXl1RDVLd0liQzE2ZWtiQ0lNN2JDbFVKYm9JZzRtbnJQR2gwTEZwUHBuczFIekcwOTRpeEtqdUhRSkExQ3FqdUZGdVlXWUkwYWhLSmR3aEdWZEVnakhabzdvY3ktWkpyTDN1c2VscktjbjhpQkRxbUZBV2JZZDZDa05tVUdua2pkSzdYbjZkLWRSZmEzZw?oc=5</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>13-05-2026 20:16 UTC</t>
+          <t>14-05-2026 09:59 UTC</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Biogen stock (US09062X1037): Hits 52-week high at $202.64</t>
+          <t>Raja Sekar Balasubramanian Appointed Head – Digital Process &amp; Excellence (SCM) at Dr. Reddy’s Laboratories</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>CXO Digitalpulse</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPODZsaWYxV3pGODE4ajhET3FsU1dZR1YzdHE2bDJMWFNmOWl3UXVLUUxBWFhabkdnWkRKVjktRVZFUk5tNTZoUEtOYW9QbDY2N1hjRko3bHkxRnR1X2VVWHhZMUVUT2wxWkVkTkJYdWFNNS1MbXBSTzlkcFZGTUxTY2dOcXpZQ0NPS2dpMUxRa0JPTkN3MldSa0t6MWtHa0pqTGFKVU1lWWkxRmdfelBLanRn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxORzg1N3d5Zkx0ZmdRNFRSejNSbDctc3V0eEoxdGFKTlp0SzByQWd5U1oxcWQ1eDU3dDVITGdCR2pZNVFUYkpTLXNPNnBTQ2RzVnJVUm9pZkk2MnEzXzIyQ1dNZzUwSkNjYkZYTmhaRFQ2Yk1IM1lFbjhVdktJdUlWXzRTVmNUcWFKWjM0MFFvbjY2cUwtSWRxTzNvNnFraDV3M1RKLW90cXNXUWFYanM2WGg2V2RPM1o2QUExVjkwSGJSLVZqanlmS0pTMA?oc=5</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>13-05-2026 15:31 UTC</t>
+          <t>14-05-2026 13:08 UTC</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Biogen Stock Surges 9.3%, With A 8-Day Winning Spree</t>
+          <t>8 Stocks To Buy For Long Term: Analysts recommend 3 largecap, 3 midcap, 2 smallcap scrips; Dr Reddy's Labs on the list</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Trefis</t>
+          <t>Zee Business</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQalA2ckVPLXJFRHhPTXJHOXlhWUdmcWRqVGotTHFVZFh1anhjekRaOTJMLWFSRVZkX1UwYmZKcDNYVU5CVW9iaFh3REJJSUp3MEtmaHRPVlNUQnV5Mm9sZ2VFaWYwMnBvUFQ4MHphMnR3RzB5SU1ZYllnNXZ5WDJBMGp4Sm9vQjA3NjZpZkZlS3F3bHlna3pWX3hpOTJ4NGhFNUpuYjdvSUUwYjBKTlZVQzdSSDM4bnNxWGpncw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAJBVV95cUxQdkgxby0yM044bkFSMzZrVGFsSzJnM3dlZVN1V0RjNTBhdE14QVhJd3BlcWpmclBTYjVzVzc2SXBiRFlOOTlYMEItRzYydUVaYnNjdWNWVkxyUHM3dml1NjlqenBNRUNKNi1Ub0xrbkNPbUdJY1B3aFFnbjlvcG5WUGtKODhvREZoZ2tyUmxERkMzbDV5eEtwVEc2QzVUazhjZlhPVURyWkllZ1VCMzdOSlJGaEpBWGRUbzlfanpGaFNsUndxdmtXRXMyUjFfUkZkdHdlSEJMSm41cHZuWHFVaF9JdDYtRVZvbWh4NHhnVXVjdHBLUmQ5RTdvSXpBN0tUVktNQWxSU2RPajNNRzgzazBZbEdiRlktWXlzNw?oc=5</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>14-05-2026 05:21 UTC</t>
+          <t>14-05-2026 10:04 UTC</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Biogen plans registrational study for Alzheimer’s drug diranersen By Investing.com</t>
+          <t>Nomura Bets on Dr Reddy's, Cipla, Crompton: Upside vs. Risks</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Investing.com Canada</t>
+          <t>Whalesbook</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNa2tidUxrODZCOF9sSjZuRXBCS0lua2p6ekVMRElQdEhId1o4Um5GTGhiOF9iQlNIWDFLU0htNzllY1dnVHlfV0w2dDBHOGhmTVcxcXYwYmNsM05jRDJLTFE4c3g1X0Zvb2V0bVJSbTJ4OUhwVXlLWEJOQW51Y3FtZmw3SXA3c2NDYVk4MEVwUXJqM2MxT3VvaEJQa2tjQzFFTXc5amJ4VDZQQ2hQUVp6c3ZUZU1rTFM3U1FDMnpRZi1WLW8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQRnJhNmw4dmJCNVp1WDVCSjlHOWRvS2pseEpUZDdhbFgtVGd3Wm1hUzNkQ29MN3dfNVVDdDdTcmpIbFhfdzdGd2dZVGx6d0l3YlN1eUJoeGk4RmR4aGpUQjBGc19NeUlHQlk5UmNjb1N0ZnJFWkNHZ1lIU0hvaVVpQlduRXBpcFdBY0RrNGFLZUhtM0RIaG1JbER4S1NDVldmRVZZWFNTLVJoSy1iQjRTWjltN1BzRTE1WEIyaWxsWHpDY3Qt?oc=5</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>14-05-2026 11:15 UTC</t>
+          <t>14-05-2026 10:31 UTC</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Biogen stock hits 52-week high at $202.64</t>
+          <t>Margin revival, Semaglutide launch to drive Dr Reddy’s growth momentum in FY27</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Investing.com</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNcW51Ty1ISTFQUzQ4Q0JfWmFXb2ZyVUJfbGU0dnJYVDE5QlRDZ1RkcVQ1YUFFYWVXRHdQOFpoRzlxNmxsMC0wN2JqYWVfNlhLanlQQTZqTXdFaG54S09PRUFPbXI5dkdGdV9DbUJJMFNfNC00Zmd0MC1kbElaTTdmQWU2a2pMRTgyZ3JtRTc3czlMZEtxSmd4NVVBTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxQMFhOQTd5Rk93OFlReHJGMVFoNlZlRGpJYmtydlpIRjREZ3Z2M2x4bEYtcHVFT1FtZjI5OXZfVVZGWEl5dVUtS2U0d0Nva0VOMnV1VHhCNnFJSV9YYVVyMnJmVUZob0ZxdmtsNHJ1U1BLZWJmYnBULTlLck1tMDFYWW9fV3NxUHRHV1NWRE04TUZkYmk1VzZ4cGZCai1LbmZWcTN5TVhOcHRVWnBOZlJ5YkJtbXhleEE3cndkZTIzOTNfVERLLVAyTklrakxVVlg2TU1sV1ZYNHhzTGlFaTBEQ0Y0MlhvelRYSnc?oc=5</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>13-05-2026 13:48 UTC</t>
+          <t>14-05-2026 00:44 UTC</t>
         </is>
       </c>
     </row>
@@ -2812,22 +2812,22 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Margin revival, Semaglutide launch to drive Dr Reddy’s growth momentum in FY27</t>
+          <t>Indian drugmakers turn to buffers stocks, contract tweaks to tackle Iran war fallout</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxQMFhOQTd5Rk93OFlReHJGMVFoNlZlRGpJYmtydlpIRjREZ3Z2M2x4bEYtcHVFT1FtZjI5OXZfVVZGWEl5dVUtS2U0d0Nva0VOMnV1VHhCNnFJSV9YYVVyMnJmVUZob0ZxdmtsNHJ1U1BLZWJmYnBULTlLck1tMDFYWW9fV3NxUHRHV1NWRE04TUZkYmk1VzZ4cGZCai1LbmZWcTN5TVhOcHRVWnBOZlJ5YkJtbXhleEE3cndkZTIzOTNfVERLLVAyTklrakxVVlg2TU1sV1ZYNHhzTGlFaTBEQ0Y0MlhvelRYSnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxPTmNtd0lLbG9mYkt0dkU3VWhCU19DbmMwQ1d2Um4tS19vZldBaVp5Y01rMXk0T3dZaHlfSDdmR0llbTJwVm9hMTFyckZ2QzVEUjBIaFVaaC1XUkZKT0lsalZBQjlTVmlJMm40MUNzWWh0RWV3OURaUmhBbXI2OXZwTEE3VGNZRG8wNHo0U2Y5SmdmOVFmNjlNNTNBdDFRUVk0ZkpVMFNqWTVrdnlSSll2enZGS2EyaXBYMk1WMHMwTHgyeXhOcDBCUkF0S2NzUzNseXlEc0JJUWhpbzJiZ0hR?oc=5</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>14-05-2026 00:44 UTC</t>
+          <t>14-05-2026 03:38 UTC</t>
         </is>
       </c>
     </row>
@@ -2839,481 +2839,481 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Cipla, Dr Reddy’s Lab, Crompton Greaves: Nomura’s top picks with 17% to 26% upside potential</t>
+          <t>Analysts recommend Dr Reddy’s, Zydus and Kotak Bank; Persistent Systems seen under pressure</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>financialexpress.com</t>
+          <t>CNBC TV18</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxPUi1QS3FmeUNwbktRM1VOMHZRQUlHTldfb1pBSkpOanJTaTBrMlBBOWp0NHUtQU56SXVnOVdZeDFYanhOaUw3MHhlZ0FwM3N6RUtVc1dMd2s2Uy16RlhPN05reDdBTWpfTHFIekRqQk5NNVpTOGVjdk1lOW1weF81MW5YdzFUcXVIMjF4WUQ2TVRKblNHM0xPbWJaY1Joa3RYc08tbnhHeGJkMXIySk5pY1Y1OHV0LVpfY055ZzRJek9YckRiTkYwa0dnaEdTM1XSAdYBQVVfeXFMT25UTkVLNlRrVHVUWnVaRU8wRmhjY1JwV2xGWUl3QkZ6TEdPQy1vekplR0RKRUUyMmpyQnM1YkRNWENTT3NTRTRoeXl1RDVLd0liQzE2ZWtiQ0lNN2JDbFVKYm9JZzRtbnJQR2gwTEZwUHBuczFIekcwOTRpeEtqdUhRSkExQ3FqdUZGdVlXWUkwYWhLSmR3aEdWZEVnakhabzdvY3ktWkpyTDN1c2VscktjbjhpQkRxbUZBV2JZZDZDa05tVUdua2pkSzdYbjZkLWRSZmEzZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNSUktek9kVmhhVzl3Ml9hUDBHZ2RvSmxkSXhudzNXMXFLWXBWYVhCQ1lNQVVDZXNRU1FWSGF6UmNndElILVVicHhwNW92SnZ0clVKX1RnbVdjWFlaWDVIbEdJdGxodWREbDBKMFBmbk1GZ3VSa1RManR4Tmc3TFVDR0dBMUtyek9MejRoODVxc3BXeE5Sb3hILWFDNVdJcV9ZWVU1XzhzY2NyZEVaeGRfSnNXZXVES0N1amdSUGM0aFZUekhKcWJR0gHHAUFVX3lxTE1JSS16T2RWaGFXOXcyX2FQMEdnZG9KbGRJeG53M1cxcUtZcFZhWEJDWU1BVUNlc1FTUVZIYXpSY2d0SUgtVWJweHA1b3ZKdnRyVUpfVGdtV2NYWVpYNUhsR0l0bGh1ZERsMEowUGZuTUZndVJrVExqdHhOZzdMVUNHR0ExS3J6T0x6NGg4NXFzcFd4TlJveEgtYUM1V0lxX1lZVTVfOHNjY3JkRVp4ZF9Kc1dldURLQ3VqZ1JQYzRoVlR6SEpxYlE?oc=5</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>14-05-2026 09:59 UTC</t>
+          <t>14-05-2026 07:34 UTC</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Intas</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Dr. Reddy’s Laboratories Secures CDSCO Approval for Generic Oral Semaglutide in India</t>
+          <t>Mrugank Sheth Joins Intas Pharmaceuticals as General Manager – Marketing</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Chemical Industry Digest</t>
+          <t>hrtoday.in</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNbEJpUjRTMk9RWTEtOS0yRTNYcWdkSi1uZm95RExNZ09Pd0pQLUdWQ3pvbnJqaEV1UWUxR1k3eHR4a1pOT3RGTV93cTlJQXRlc0JWMnE0c25fYnJIRXlqSXZFZzdZWThOYWU4M21xcks1N3l1ckROa2ZfVFRMdGZaZFBMMzlsc2tUUjJDNm9BemRMVWRZb1BudjJSYUFrYld5Z295NHIzd3MyV0h4UUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNY29aaUxSSno0SHRHb0IxcndNa01ickpQNTVmT2h2cXZkZzdFbFpQZTRPMFliREx3MUNQQ2p2YWxrYUFyM2dLeGt1TEJGclRleElsUzZGMTUzSUYzVXhzc3BsN1owQVRzaE1kV1RZOXFfNFJMaERHM0ptbU45dVRDZFpCVm0wd0tFSWdpa01WOEVkZ3lv?oc=5</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>14-05-2026 07:29 UTC</t>
+          <t>14-05-2026 11:32 UTC</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Intas</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Dr Reddy's Q4 Profit Crashes 86% to Rs 221 Crore as North America Generics Sales Slump</t>
+          <t>Weekly take: Why AIPPI and INTA’s Dubai problem can’t be easily fixed</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Medical Dialogues</t>
+          <t>Managing Intellectual Property</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxNTFExREh4a044UGNwR3lhdnBiWUtvYjdTS0lHRUE3cGJJblItVkc2T3Awb190WkxIX0Zwejg0bUZxS3Jjc0FBbVhQc3BSdEd2dDNQRWduQXV1dVUyaXNscVZwQUd2VUNBQ1diNWtfYXQ5TGp6THE0UDV3eld5Z3pOUS02cThOWmpBSDdfOFF6d0dzY3I1cm05dHJZZW1ZbGgyRm43d2xZdTJpaTNySTItN0dCLUctTWhQbjdxV2RnT29JbERGYi1GNWlVZFBJVXAyeVF3VEFIY9IB3AFBVV95cUxQaGVOQi1xT3JnNjFYenhkejI1RlpySFJQOWU2Q1dzU3VwWGJkTXhQdmdENkpFU0tGVUNNY1NyNjJmUXVpUUJQYTE3UTRxbXBCT3FVSUljMVg0bk1nVWI4U3lFSG50bzVsaXgwNGhkZF9HUlFSTFVDNDA3ZXlxUTZQdjBkUHFQQXRHNi04OE9ENFVjR1lWcDFlOWxnRWlKZS11UDZ1UGtZTFFCTkVreDZhOFlVQWgybXNIUWdpQ3REVjVSVVFKd3YwMExXQko4ZlgtODktMDBhY0dOU3da?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxObm5lZFNMVVdpbVcxOThVX19pMHN3UW1MWHFCVU5jRko5bUI2TVVxckFVUDlMbmo4MVlOYzdwdXdWcW9UYm40RFcxTjduQ1dnQWxpdUhsVmpGTW43YWdRSVpKOTBEcDU5a0NKSHNrVV90aXNtbjRSNTM1SUVXcEsyR20tUUFmTHBtNGF1RHZ4WXhpMVozQWUxTTI1WkJ4UkJCZ1dkaW1Hd2RTSl9seTV0ZDRtSmRYQndoMHd1aFlIX1k1TnZ4clZiQU8yMA?oc=5</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>13-05-2026 15:23 UTC</t>
+          <t>14-05-2026 10:37 UTC</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Indian drugmakers turn to buffers stocks, contract tweaks to tackle Iran war fallout</t>
+          <t>Five Stocks To Buy: ONGC, NTPC Green, Biocon And More | May 14, 2026</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>NDTV Profit</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxPTmNtd0lLbG9mYkt0dkU3VWhCU19DbmMwQ1d2Um4tS19vZldBaVp5Y01rMXk0T3dZaHlfSDdmR0llbTJwVm9hMTFyckZ2QzVEUjBIaFVaaC1XUkZKT0lsalZBQjlTVmlJMm40MUNzWWh0RWV3OURaUmhBbXI2OXZwTEE3VGNZRG8wNHo0U2Y5SmdmOVFmNjlNNTNBdDFRUVk0ZkpVMFNqWTVrdnlSSll2enZGS2EyaXBYMk1WMHMwTHgyeXhOcDBCUkF0S2NzUzNseXlEc0JJUWhpbzJiZ0hR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNOFVSY2pqS19nUjRUdV9TNWRyNXJodmRjVk4zY0tsTVVldVNJQXdZQkNaWUdGdmNFUWxHY0tBV0tlRVVkQVNKSW04VlR1bzdYZlFSWFhNeWxEMWFmZ1lvb2N6aUNJejRDOVpaMF94dklDNnpjQ1p4ck1RcUI1NnlWZ09nV1VPdFhEVDZBMTNNMDhOaG40bzdyb2F4UG9CMmlmbTBUdjlsX2lROUVuVTR5UEdNQllzX2ZkYlHSAcIBQVVfeXFMTjJwcHd2OE1ONHZmMXRjdlhicjhLS1dDbUlsVmtRUTRpcFdibW5sUjNqSk95Q2lrYmg3LW5aNnZmTnBEYk9FUFpYN1JCNUhPNC1iTzk3UzNrYllFZGJrTl9VMGVxclFybmU2OGtEdkl4cDlwX21KWHNia3oxeE9xMlQ0YkV2c0YzR3lFNTVsbzFtcVNHOXBCR2FxWVJKeWVfZjhXZ25WYm01bTJyWXBoR1psVGI3cXk2OWJCcWVVczdmeGc?oc=5</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>14-05-2026 03:38 UTC</t>
+          <t>14-05-2026 01:36 UTC</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Analysts recommend Dr Reddy’s, Zydus and Kotak Bank; Persistent Systems seen under pressure</t>
+          <t>Baker Tilly advises CYGYC Biocon on its sale to WVT Group</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>CNBC TV18</t>
+          <t>Capital-Riesgo.es</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNSUktek9kVmhhVzl3Ml9hUDBHZ2RvSmxkSXhudzNXMXFLWXBWYVhCQ1lNQVVDZXNRU1FWSGF6UmNndElILVVicHhwNW92SnZ0clVKX1RnbVdjWFlaWDVIbEdJdGxodWREbDBKMFBmbk1GZ3VSa1RManR4Tmc3TFVDR0dBMUtyek9MejRoODVxc3BXeE5Sb3hILWFDNVdJcV9ZWVU1XzhzY2NyZEVaeGRfSnNXZXVES0N1amdSUGM0aFZUekhKcWJR0gHHAUFVX3lxTE1JSS16T2RWaGFXOXcyX2FQMEdnZG9KbGRJeG53M1cxcUtZcFZhWEJDWU1BVUNlc1FTUVZIYXpSY2d0SUgtVWJweHA1b3ZKdnRyVUpfVGdtV2NYWVpYNUhsR0l0bGh1ZERsMEowUGZuTUZndVJrVExqdHhOZzdMVUNHR0ExS3J6T0x6NGg4NXFzcFd4TlJveEgtYUM1V0lxX1lZVTVfOHNjY3JkRVp4ZF9Kc1dldURLQ3VqZ1JQYzRoVlR6SEpxYlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNX2RQRVVOYk5YcERpbHBzb1hpajBaVGl3elRycHp2VDBPUUpXR1hWNUk5allmR0c3YnlwRk1nT1ZlYWd1a04xZmZ5WVpqWkNKSV9GR2VtTWxIVnVsM1NVQ3ktZEF5MWRfVnlQbmFhX1QxMnFrWFpvM2pLVXhQbjVFMkFsOVZBQzhJWC13bXI5MEhmVjVzaDdaOXlKMkE?oc=5</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>14-05-2026 07:34 UTC</t>
+          <t>14-05-2026 05:06 UTC</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Dr Reddy's, Dixon Technology &amp; more: Top stocks to watch on May 14</t>
+          <t>Pharma Quality Excellence Awards focus on building robust quality practices</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>The Times of India</t>
+          <t>Pharmabiz.com</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxNdUk2RFRod0pBOURHMThoS2VzcDFMc1dNQlJQekNidjhRM2Q2b2NTMzhySVpyNDZOMWtNOUs5RnF4RHE3bVQ0VzVsa2RrLUFEdUJfZmw5ajZLVV91Zy1qaGtLUW1SMmE4ZWdqZlZBS1R5enowMkR2Q3cxUUREeGdJX0o1Qm56YUtVdnBleXRlMTF4QTNMamxtbFRxTzR2dm5tZ1A4dFVVZnl3RXhVQ3U0M3dWSENNTEYtNW5qZmVjcDVraGIxOUZzX0FPVTJ1NVZzV2cwV3FYS1dVZnlubkZxQVNocnA1Z9IB5gFBVV95cUxNdUk2RFRod0pBOURHMThoS2VzcDFMc1dNQlJQekNidjhRM2Q2b2NTMzhySVpyNDZOMWtNOUs5RnF4RHE3bVQ0VzVsa2RrLUFEdUJfZmw5ajZLVV91Zy1qaGtLUW1SMmE4ZWdqZlZBS1R5enowMkR2Q3cxUUREeGdJX0o1Qm56YUtVdnBleXRlMTF4QTNMamxtbFRxTzR2dm5tZ1A4dFVVZnl3RXhVQ3U0M3dWSENNTEYtNW5qZmVjcDVraGIxOUZzX0FPVTJ1NVZzV2cwV3FYS1dVZnlubkZxQVNocnA1Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTFBPWlJIbzJMVFdvTVRCTFN5b19ON2dsaFBPZ3RlOWx5MVZ5UEo3bURoblE4RjdpekNHRDFuWFZhVUo0akh0U0ZJNkEzSUFsR0FPWTQ5ZGNNVnZzbDNsYUJja2ZkZjVSTU9SUU1z?oc=5</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>14-05-2026 03:07 UTC</t>
+          <t>14-05-2026 12:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Dr Reddy's Laboratories Ltd (RDY) Stock Up 4.2% and Still Underv</t>
+          <t>Biocon Ltd. Upgraded to Hold as Technicals Improve and Financials Show Mixed Signals</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>GuruFocus</t>
+          <t>Markets Mojo</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQUnp0d2R4eldJUndtZFNfaDVnZjludnNtS3NQTktSaFJNLWhqdUlUa3RLcVdCVHVoU0RBaDlHU0dHZ2JrT0xTTXNJa1BDM2tRSzBxdGNySGtPQ29LSjRtVnRYd2ZHUTdxdHhDXzBZWmpDNXZ5ODhwbXlHWnkzaGUwYkZ6SlhaelRLN3lXVXk4UDRLZFZVRW1kTVM4dnJqQWVuQlp0WVVNWlhLekt3OUt4Y1hjS0o4b05FVTdlcTBJSGxaVHh6d3RYVk5R?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxOV3luVTFHRlQwVVZaUUh3Xy03OXVJRWEyYTZKYVZFV1hxQzNNMEFGZUVzQ2tjZ2lFSThFQnFaVGdhRzhXZXM2alZjakVlWkFaZ2g4VHNXZ0JlUDlnV09JbFdWWWF0Z3RkbUxKUnZYUGdRa3RHLWlkUzF0MHplWmhoMEdYQkVoclpNLS1EN1h0VzB1WFk1UzN1Q0puSE9HTEpMWjJCOFEyWXcyNEYtWktfSHBmMHEyMnJhYzFTTkJraHVvTWxJZWt4cXBMWjlhUXdfMmM3c3RLS3pxZmtkamc?oc=5</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>13-05-2026 22:30 UTC</t>
+          <t>13-05-2026 20:42 UTC</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Dr Reddy's Net Profit Plunges 86% to ₹220 Cr in Q4FY26 on One-Time Charges</t>
+          <t>Biocon Ltd. Technical Momentum Shifts to Mildly Bullish Amid Strong Returns</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>Markets Mojo</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxNSURqRmZKaWV1eW5Lc0FJa1UyS0xKdHNDWERXMVFoZGpTZV80cWtIalM1S01nNnhONWlURnZ5OTl5MExNcm5CRVgxbTRiUTFBSzBPeEZWVlh1T3dqRldNUDFPVE5QSThyMDdzMUxLWVZER0hGWHZyVkdEQzVjODZsUTB6UmRPNzFvSFpnMVh0azlsV2Y3WTREallEYVBuNWpDOHEtbkJvbFRCbll2cy15MUw0VktuaVhaUjdKeDJBdmhkMW5WdE8wR3dvZTMtLTF0ZXZ3a3FXeGZXaHNNT3h0TWo3TWJqVWM5T0RNZElHZWFSWGJ1TE9sRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPLW1ETTJ4ODU3dTNhcUlnTmhybjVuSDNfVWU0X2h0NDF6U0tlOHp5WDFMZXpxcVZ6Q1BTM0dyZWNvdXVfb2hONngtb253ZV8zZ3BYekN2OVdPZlJHRWc3NUJYb0p0c3lac3pvYklmUkJFT3BYRGJYLTB3eWJxM0lad1pKRXRkU1FhWkdyWnNuY1dHbWU1eUJVUnRsalQ0dlhGLTVJcHYzcUFfR2NXZFVncDJlOUhrOGUtVTUzZ3VOQ3Y5dkwyQ09KLTI5MHo?oc=5</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>13-05-2026 16:52 UTC</t>
+          <t>13-05-2026 20:41 UTC</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Dr Reddys Laboratories Ltd Surges 3.15% to Day's High of ...</t>
+          <t>Ex-serviceman among four killed in separate road accidents in Bengaluru</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Markets Mojo</t>
+          <t>The New Indian Express</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOMk1oQzBHOEJUNWpVbFRnVFVGQktwWWdZRl9LRWVqbERqTEg4Wk5UcVN1LVA5M2hFREFZSXJWamNMS1FqR2JWX3Z3SXFqU215Rm9wY2UwT3lmMHhob0xYNG5YUkI0eGQ3UHdQWjJUQ1RpM1laQndLeU5IS0FZbm5yUDRpa2pNWGw5YnhJMU5XejZXY1FyUW1qTnNvTnNzUEoyX2VLYUZTRDFQSExaRnpnZkw2al9nZWFDeFlrY1pZek1OdU5FRm5OVkRaYng2dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxNVmcxSWJ4V3lvdUpEenY0Wm9SYkJRWlZieUE5eE02NXBfTTNRUmRuR3NsVW03Yk44dmZiakkxVmNuUnAzWnY2MWxpVUJDNDZIVTJyWlMxbTlCak5XSzVKbFNPUFVaY3E5c2pyemg2cUhUdDFDall3dDdWN3ljZEhrLS1Kek9idjNRY0V2ZXRWRmREMkZhVFRzZE9iRlNvdW1SYlhiWFFDY0xrcWtTN1Y2UjBtbEduUkJUVmlwRTNIZ1VlcnNrVzA2enRwLVJJZ9IB2wFBVV95cUxNUkZuN0NQNVY4T3ZteGpQUDdWWlc5ZG4wY3FCNlJQVUpXMGpKZ24tUXAxbFlmYmN4Nk9uUnF0OTBDbXNXQTFrSVh1RjFRYjJnRW5rY0h5SlF3d0dXTWtVRlA4SjYxdUlMS3l2LVVmeEZ0TnY2Qjd1SXVnWlY1ZGtObnFWYzdMNDc1alFKU2dEbHkxalRSR2l6WlRtZTRCN3NpSGtUbXE1NFN0cktNLXJla3dWMTZnNExCaWlRTWJjUE5Eblg4cndTcmNNYjc2d05JS0JrYUFZcy1uUFE?oc=5</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>14-05-2026 07:36 UTC</t>
+          <t>14-05-2026 02:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Dr. Reddy's Q4 Earnings and Revenues Miss Estimates, Stock Down</t>
+          <t>Biosimilars Market is expected to Hit US$ 99.3 Billion by 2033 |</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>openPR.com</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNR1dGQW5wazVaZXpCSXdqQ3gxSzhmVXhDYUYzODEwSmxUV1FZTUZKM0tVdWJVaWFnbDZvMWRLNU8wT0JDUFFWWkdFbjJfdzZSWTZEaEJ3a0lsODhuNi1lMXNzXzQ0VGhrOUxIeS1UTHBjOE9TcDRFcFNjSkVtakJCU1pMWmNrVUJxekV3dUJrVXMwUERxRGdzX21nWnVhaF9JTkhPQ0FGUXF5Qml1YTJHZm4wX0VSLURm?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNWWlNWThXLUJGWjBQRVlJRExjeUlDWTB1RTlheG5WUHpPY21QN1RtSVBiNmpDdjd6RUhmX1pmQjRiYm1KTFdKenBUTUw2Y3RZbG50MENSTkIwR2JILXdRejRLZTE3TkliVzdrVHllLWpxU2tLNDJ4TTJ5bkU5MW80Z2ZXRWF3akFZSFBiTFdtZFUtN2ZieTd3ajNSaHlsZw?oc=5</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>13-05-2026 15:23 UTC</t>
+          <t>14-05-2026 10:01 UTC</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Intas</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Weekly take: Why AIPPI and INTA’s Dubai problem can’t be easily fixed</t>
+          <t>Aurobindo Pharma Ltd soars 1.15%</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Managing Intellectual Property</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxObm5lZFNMVVdpbVcxOThVX19pMHN3UW1MWHFCVU5jRko5bUI2TVVxckFVUDlMbmo4MVlOYzdwdXdWcW9UYm40RFcxTjduQ1dnQWxpdUhsVmpGTW43YWdRSVpKOTBEcDU5a0NKSHNrVV90aXNtbjRSNTM1SUVXcEsyR20tUUFmTHBtNGF1RHZ4WXhpMVozQWUxTTI1WkJ4UkJCZ1dkaW1Hd2RTSl9seTV0ZDRtSmRYQndoMHd1aFlIX1k1TnZ4clZiQU8yMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPaGdJdUtlMFQ3NG1RMVl3OExzOC1wZG5sRnhPWXBrSzRZRDF4dXpkaHNEd3NpN3JiYlpIaGx4SkVrY2NVbWxJWC1JX29Lel9waFI5WHoxRlJnalM0TDBTODFHT29GS2dSNXAtWExaVEp5akR1RTBTM0NvMW1wZGFMT1N1SmFlMGJUUlpRaHlGQ3J2VlNzeklURC05cjJ6ZlBqUkRoWm9IRUctbm15SDVZdnVvVdIBuAFBVV95cUxQWXBrOTJTZTJ3elJJdlN1TFBWR24wQnBkczctV2wzNGhCUVRNNnBqZXVKT0F4c0VGTGxEbi12c0x2QzdhaHB5Y1F4TVRNeEFyc3REUnpfSkRTZFdYWkdtZU9WTHF0dXk5X2lPaktoUzRkMFJGc1R4ZVJnX1ZldjJXcnBOblhid2dhc2ZsQVJjZDYtZ2VsSGVMUm1YWGRIOWxVY1R3Q3BldFdTUzh1cDlCVjJKa1ZFSGJi?oc=5</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>14-05-2026 10:37 UTC</t>
+          <t>14-05-2026 08:02 UTC</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Five Stocks To Buy: ONGC, NTPC Green, Biocon And More | May 14, 2026</t>
+          <t>Broad-Based Technical Strength Lifts Aurobindo Pharma Ltd. to 52-Week High of Rs 1525</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>NDTV Profit</t>
+          <t>Markets Mojo</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNOFVSY2pqS19nUjRUdV9TNWRyNXJodmRjVk4zY0tsTVVldVNJQXdZQkNaWUdGdmNFUWxHY0tBV0tlRVVkQVNKSW04VlR1bzdYZlFSWFhNeWxEMWFmZ1lvb2N6aUNJejRDOVpaMF94dklDNnpjQ1p4ck1RcUI1NnlWZ09nV1VPdFhEVDZBMTNNMDhOaG40bzdyb2F4UG9CMmlmbTBUdjlsX2lROUVuVTR5UEdNQllzX2ZkYlHSAcIBQVVfeXFMTjJwcHd2OE1ONHZmMXRjdlhicjhLS1dDbUlsVmtRUTRpcFdibW5sUjNqSk95Q2lrYmg3LW5aNnZmTnBEYk9FUFpYN1JCNUhPNC1iTzk3UzNrYllFZGJrTl9VMGVxclFybmU2OGtEdkl4cDlwX21KWHNia3oxeE9xMlQ0YkV2c0YzR3lFNTVsbzFtcVNHOXBCR2FxWVJKeWVfZjhXZ25WYm01bTJyWXBoR1psVGI3cXk2OWJCcWVVczdmeGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNeFFZUVFGU3JFSnlKdkExdkFxM0RCYjV4Wk91elFHSVYzbFFRd19MQk9RUmp3M2xrYzVSbzFNS2l5alZqekxRNm1aal8zVFBYSjVsbkN2V1lELVBtRzFXYkNmeWNTbGNyQmJYTlF4UldfSURqQVlEY29Fb1ZNS2IyeEVDbTZxdk56STM1SGlNNXFGand5cG1BdzZTZmVJX1FRYkQzS2FSVGx6dmk0VmRBeWpBaU84VDdFeHNkWEszWWJWRnM?oc=5</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>14-05-2026 01:36 UTC</t>
+          <t>14-05-2026 04:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Baker Tilly advises CYGYC Biocon on its sale to WVT Group</t>
+          <t>Pharma Quality Excellence Awards focus on building robust quality practices</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Capital-Riesgo.es</t>
+          <t>Pharmabiz.com</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNX2RQRVVOYk5YcERpbHBzb1hpajBaVGl3elRycHp2VDBPUUpXR1hWNUk5allmR0c3YnlwRk1nT1ZlYWd1a04xZmZ5WVpqWkNKSV9GR2VtTWxIVnVsM1NVQ3ktZEF5MWRfVnlQbmFhX1QxMnFrWFpvM2pLVXhQbjVFMkFsOVZBQzhJWC13bXI5MEhmVjVzaDdaOXlKMkE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTFBPWlJIbzJMVFdvTVRCTFN5b19ON2dsaFBPZ3RlOWx5MVZ5UEo3bURoblE4RjdpekNHRDFuWFZhVUo0akh0U0ZJNkEzSUFsR0FPWTQ5ZGNNVnZzbDNsYUJja2ZkZjVSTU9SUU1z?oc=5</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>14-05-2026 05:06 UTC</t>
+          <t>14-05-2026 12:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Biocon Ltd. Upgraded to Hold as Technicals Improve and Financials Show Mixed Signals</t>
+          <t>Nifty Pharma Live | NSE Nifty Pharma Index Today - S&amp;P CNX Nifty Pharma</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Markets Mojo</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxOV3luVTFHRlQwVVZaUUh3Xy03OXVJRWEyYTZKYVZFV1hxQzNNMEFGZUVzQ2tjZ2lFSThFQnFaVGdhRzhXZXM2alZjakVlWkFaZ2g4VHNXZ0JlUDlnV09JbFdWWWF0Z3RkbUxKUnZYUGdRa3RHLWlkUzF0MHplWmhoMEdYQkVoclpNLS1EN1h0VzB1WFk1UzN1Q0puSE9HTEpMWjJCOFEyWXcyNEYtWktfSHBmMHEyMnJhYzFTTkJraHVvTWxJZWt4cXBMWjlhUXdfMmM3c3RLS3pxZmtkamc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE1VU0xITWdsWmRfemUyWGEwYXNCYWE3NXBCV2ItNUpndFR5YzFMbDZLY1BwTzlJMU1xWk9xT0tUYXdYQkdrTXVCcll5YVVKbnhpekRMdHhxbFJ2Z2lORk9xYWlzMzdtWW5QYkE3RmZvOFBtcll2eWc?oc=5</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>13-05-2026 20:42 UTC</t>
+          <t>14-05-2026 07:46 UTC</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Biocon Arm Gets Health Canada Nod for Micafungin Injection to Treat Serious Fungal Infections</t>
+          <t>Stock picks: Analyst prefer Aurobindo Pharma, Sona BLW, Tata Steel</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Medical Dialogues</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxPeXZfaGNUQzUzNU83dVlFaHBFM0NJekhsY29CaTlFRURFNWxKT1RqOVJWSGg1UFFGYzVZc2dTRG9XZnJpcTlud1JuOUlrZnFCbWxYaUNfWTVPQVlwZzZsVXJkbHNoVlUzUmd6ZHVza09GcThSMjkxNGRUOUVhOXpGQkl2TmlndDF1Y3VTOEpEaG1DR3BpYTBVZG9oNV9iVFIzNmo1dm5ES1dKZXVuV1NWcWlWaWRieGtnUWt3d2RvVWp4ZExUcFNsc0IycTZGSkt2Ull6N0IzZjU1Y1lwT3Y0c2dhSdIB6AFBVV95cUxOX0xkRWlxOGlRMks4aEtRdmlheUxNWUxkY2JNeGE2OGNGeWNpdGNtUjFPcXd1SjMxdVJoVzVKUTBLUE91MnZoZmVmOGo1TFFhQzRYSmxHdjRuTFR1NFNyZi12cUt3OC01Z3NsZ2drb0I4LWZXamp1aTFTX21BSTdxaE9wQlUwZjNuYjVNOERRWnhXSkpOS0VQQkJmWTBsdXVnTWg1VHNseGo3anp6MmJNZG1kYVNKdERKNjlFVnBQT21Fa2djUVFVSTJSMGZBRWpjdnpfNFRhNTdIcVpIOUo3WDBzRWluSE55?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOTmtpMUR4MENaTFNsUGtQQVpEV3A3X3pESmJBc2dsS2kzeWNlaHd4V3pfTjFhbXNaSHlXUHYxN2JCeGpfTGptUk9hZkY4LUlpazRMQk15RXhLUHFCZ0M1a2Z6dVJNR1pnTFhGR1M1M3ByME1KbUdnUXdfVk9SdDZ4bWt6Z29FakFGMnM5ZDRZVjFMWUprZzBfUzhMeHFCM2s1d0F4dkU0SGFGVXhuLVBIbGE2X25PcFBwVnMyYktWNXdEUnF1VXUyMV9R0gHPAUFVX3lxTE9samtPMzBhdGw2Y1ptc0ViM0Z0Sk96bEl2WEhNbEQ1dlBuQkh2Ti0xYW04SG5PS240RHpMWkZUNXVqSEx5VE45ZG9feXNvb09oc0ZkTEJYM2d3X3VSUE16MG9FYkpKSVdGd3BpRDlvSlg0TlpzY1huYmJrSS13Szh6azlwODFlNXBpVDN2U0w1VWtnUTA1cGhXWFAtTTAwVVRRMjRPV3U5Z3g4eENzRHVKRUcwYU4tZjJzeF9SRktEcTN4TkFKZHRwbzUzS0xiNA?oc=5</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>13-05-2026 15:08 UTC</t>
+          <t>14-05-2026 02:10 UTC</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Biocon Pharma Receives Health Canada Approval for Micafungin for Injection</t>
+          <t>Indian Pharma, Tech, Engineering Firms Pledge $20.5 Billion In Investments Across US</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Machine Maker</t>
+          <t>IndiaWest</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOdlRWRnlqYVpJYnRvZzNmNVRzb1pZWnpFRGtvUjA1MTBUaV9NY3JxNUpMdnNyQ1lvVW9LNV8tdHpxTTgzeFotUW14ekEzeTBtaUVYZlNOWllHcjZ2QmtFX2hVa1d6TFZZelZBekoxT3dVbUU0QVNIRzhuV1VMVGd0NmVqN2JwRXZiRlF5ZFFqMXNXWmNNY1lySzZmbXZvdUIzOWhsVllZVmlMUURB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNREoxRU5pYko1aW00NVVwSUNBUzFHRlMtSHphUmRNdjg0Uk1YRnR6WnhPdkFKei1rU2d3UnJhbGVyMkZ5ZG1KLVN4anZjb0xjd0R1TGJZTTgwbFNtRVM5a21hY2xHamJkZW8zRm96SjlCTmNCMEl2VFVkQ2k3TFVDaHNoQnZZclBSSlFlREh5WWFTX0d1WVZ1ZnA0YXZoaFAwODVtNGdvVQ?oc=5</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>13-05-2026 12:28 UTC</t>
+          <t>13-05-2026 21:21 UTC</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Biocon Ltd. Technical Momentum Shifts to Mildly Bullish Amid Strong Returns</t>
+          <t>Tilaknagar Industries arm receives govt. approval to commence production of its expanded facility</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Markets Mojo</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPLW1ETTJ4ODU3dTNhcUlnTmhybjVuSDNfVWU0X2h0NDF6U0tlOHp5WDFMZXpxcVZ6Q1BTM0dyZWNvdXVfb2hONngtb253ZV8zZ3BYekN2OVdPZlJHRWc3NUJYb0p0c3lac3pvYklmUkJFT3BYRGJYLTB3eWJxM0lad1pKRXRkU1FhWkdyWnNuY1dHbWU1eUJVUnRsalQ0dlhGLTVJcHYzcUFfR2NXZFVncDJlOUhrOGUtVTUzZ3VOQ3Y5dkwyQ09KLTI5MHo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigJBVV95cUxOYXhReTRMakM0cVhZVWVIcEpoNmttelB3V20wblphMFR5OW5PMzJrcld6RVBjN1FsbEV2M0h1WkhSZ09vS2hVdXJ5NXNqS2VEb2N0RHlsWVdsZ182dzVCLWdvQnhpVm5MQm1KdGJlMy1na3p6ZGM0TjhWNmRmaTktTEJvR25kUTdfbXcxXzZ2MDRseDZXUkp0bHUzQ3N2Z1FRUGRaWWZhcmFNVnNnVVVzdHZ0cGNUYmhpVlptQmo0ekRKY0dYRDUza0NxcWlkTWNra2RaN3FWRnctOU1WbF9BdHpheWtpdGxrVWJyQnBEc0ZvaFdCUkQxMFc0WV9vVlRVNXNVOUREWE5Ld9IBjwJBVV95cUxOQWtiUmlZYWpMY0VNX0YzSVpiUHZQMEpadnM0R0ZpbnkySFZnTG5hRmNUcFV3QzJwVmtLYWNVQ25GalJTQlVOWVljTkh6YzFhdFJ4amY5empmZ1o3Y3FpamlyZmF1dTRqb2lpVnJ1Uk5UWGRfYTk3bGlzaEx0Y1VEX3BncEFQRjBIRk1xcFl0RXRxY2dDVkpQeFdjOEpTOS1YWk9USWR6SmNLV1VMYUFCYW10MzJwU1Z5VmpzY1J4MzRYaGFyQXlYbmkzRGUtMkZWLVNhRU5VR1JPT0U4UmxlZTdYWlZZTkhBV1UtQTVlSlpnVmZUaXpLMGtUUE14akQycVBULUZGZzVjTFZ0NWww?oc=5</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>13-05-2026 20:41 UTC</t>
+          <t>14-05-2026 08:02 UTC</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Sun Pharma, Biocon, others: Expert shares view on pharma pack | Daily Calls on BTTV</t>
+          <t>Pharma, NBFCs see fresh mutual fund buying in April</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Business Today</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxObXFEdl94T2JQM1FKYnhxbnFiVWMtODZQcEtmSVdFUTdhVDVhdkhMc3ZFTG1aNkhTbEZaazYxMG90RGtuRnpJSTUzWExrQXh4TDNrcTY3YWNRWkFFUWJEYVhnQXRDb2h6aXY2TzNBeEJFdzhIUGxXeVZ2WlhCcXF1Y09nWnJsYzgtN0EtYXJiZktaOE52WWVUYnJ5QWEtNVFWci0tZnUyNDhWYzdtSkQzdVh5aEtnbFQta2JfekU4cm9TSFBXd2g2STBRQWVHVmI2UnFsQzZoekZXQzcyRkcw0gHkAUFVX3lxTE5iRFd1X3kxSmhoanVscWplMUt4Skh0b3BLR0tsalRoM2ZzV2NhRnYydXQ4eUlFVmE5RkxqNk4zVnZXT2doMWdldVpsRHZEbmoyaTV4ZTZiRktvcUNvRkVId3hrTmduekZraHc0N3ZBZnkzWHIxcVEtUlJ0QTB3aUlEejBRUV85MDFudnN5S1FxSUtJQVF0WUFtOXdLc3psNkxFUU53YWw0Ti1BUm1NT2VuWk9FZkVDMUpJZE0wTHlCazVVWU8tQ1ZJN3hzMy16d2g4aFg1eUo2Um44VFpkSVpNT1Yxcg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPUmJxbVZZcHBQbV9aYV9hMndrY3VPamkzdDd6c1ZaVkdWMjQtd2xjbVNqTUZaVUhRZ3lmazRTdlRRdmZqZUtpNktrWDRPRTM5bW5oOU1wSXlrUkhnNEFUa0ZIOGNpMHgxOTByQy1vbTJxTzVWMG5Fem1rdmpIdlRKSl9ZYlBiY1djVnRYNzRYSDhiVFc3Y3psZHZta1FtVzE1SDlIUzgwRkdobmlYajYtUXdwS1ozWnfSAbwBQVVfeXFMTVoxLVBKTWFyN1NobXZYM2JpVS1USFZSNDdMT2MxVDQ0dE50TW4tS0pCTU5ldWF5NElPWVp6S245WF9EdHFoeWFsMmV6TDJvVGdZMnZXWW4xaDdBWU5ZVl93YktjV0hHRXJIM09LbS12d0pUeFAydU5KOGVkdFI0WjhTSTRSQ0o0RmtmN0VuM1JuZkRPdGxkSFhTUkpOcEswbWVYLVhBRjdVekJMNG02M0gzNjRwSFY2ZHoxQTA?oc=5</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>13-05-2026 11:47 UTC</t>
+          <t>14-05-2026 00:59 UTC</t>
         </is>
       </c>
     </row>
@@ -3325,22 +3325,22 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma Ltd soars 1.15%</t>
+          <t>Nifty Midcap 50 Live | NSE Nifty Midcap 50 Index Today - S&amp;P CNX Nifty Midcap 50</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPaGdJdUtlMFQ3NG1RMVl3OExzOC1wZG5sRnhPWXBrSzRZRDF4dXpkaHNEd3NpN3JiYlpIaGx4SkVrY2NVbWxJWC1JX29Lel9waFI5WHoxRlJnalM0TDBTODFHT29GS2dSNXAtWExaVEp5akR1RTBTM0NvMW1wZGFMT1N1SmFlMGJUUlpRaHlGQ3J2VlNzeklURC05cjJ6ZlBqUkRoWm9IRUctbm15SDVZdnVvVdIBuAFBVV95cUxQWXBrOTJTZTJ3elJJdlN1TFBWR24wQnBkczctV2wzNGhCUVRNNnBqZXVKT0F4c0VGTGxEbi12c0x2QzdhaHB5Y1F4TVRNeEFyc3REUnpfSkRTZFdYWkdtZU9WTHF0dXk5X2lPaktoUzRkMFJGc1R4ZVJnX1ZldjJXcnBOblhid2dhc2ZsQVJjZDYtZ2VsSGVMUm1YWGRIOWxVY1R3Q3BldFdTUzh1cDlCVjJKa1ZFSGJi?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE9yRVl0anZ5YWZCNU5pNzk4ZHVPNTVpNUZZMmFfd2Z2a3lEelFOcDlYYlZiWGZhdzRKS0NoVEhqdHAwVWhLUHJFTm5fQWotRlNaNnREdFBUU1hya1lIMFlaWkNiTUtTc194UUtubUVVLVRSdkxURm9yNGpB?oc=5</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>14-05-2026 08:02 UTC</t>
+          <t>14-05-2026 07:44 UTC</t>
         </is>
       </c>
     </row>
@@ -3352,22 +3352,22 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Broad-Based Technical Strength Lifts Aurobindo Pharma Ltd. to 52-Week High of Rs 1525</t>
+          <t>Technical picks: Asian Paints, Tata Steel among analyst's top picks</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Markets Mojo</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNeFFZUVFGU3JFSnlKdkExdkFxM0RCYjV4Wk91elFHSVYzbFFRd19MQk9RUmp3M2xrYzVSbzFNS2l5alZqekxRNm1aal8zVFBYSjVsbkN2V1lELVBtRzFXYkNmeWNTbGNyQmJYTlF4UldfSURqQVlEY29Fb1ZNS2IyeEVDbTZxdk56STM1SGlNNXFGand5cG1BdzZTZmVJX1FRYkQzS2FSVGx6dmk0VmRBeWpBaU84VDdFeHNkWEszWWJWRnM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxORmpYcndMeGFnSVlEclJTOU1jMlJNMW5Nb0w2dWNiT0swd01Pb0hJbWlRYzNQQzNCN0cyUjFqT0V5S0ZBUUlsd0hNcHotZlRLNVI2QkVXR3NvaDRvN3FTSm9DcFVDUlVMT0pzSWVuSHB4T1RNb19aMzlwMEdyM0hiSHhRdVAyTUtDakdHMXJneTd0WHRrRHdIODFsNVNLVUVNY084RVFmTFBhV09wNHl5XzVPQW5JMDdwcEhjQlZKR0RJRDlJSmczREROT2NtWngzNjNRaC1OdXcwX1owdEV5QnptSkhSX2hTOEhfadIB8gFBVV95cUxNMHRHTVFIS25oRjV5WlNwMnZMYTVxN2pSR3VMdUZtSjhuYjNYcGtiQWZKQWg1aW5CVk9PNFh5QjJjVUNHR2NnWXlPdUszZTZ5aTdMaTZfQ3YxTmRZZFRGWWgwZUUxNnFWMWFJYmJ5cjRzNEFvbTRBS3RyeUxSNEhOV2xpaE9NdG9WUlM3dXYtQ3RRSkJVblR1SVVGVno0U05iZEdOU1l3ODl5ZFJidXlza09scVNzT0VFdnp4cVJjRGQ0UjR2eHNuMHIyWlNRMzM3Tl9IcjF3Zld2cmgzSGVGVkJ3VkZOaHFxaVZkTHczU3Frdw?oc=5</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>14-05-2026 04:30 UTC</t>
+          <t>14-05-2026 03:04 UTC</t>
         </is>
       </c>
     </row>
@@ -3379,22 +3379,22 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Nifty Pharma Live | NSE Nifty Pharma Index Today - S&amp;P CNX Nifty Pharma</t>
+          <t>Cipla soars 8% despite disappointing Q4; what's driving pharma stock?</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE1VU0xITWdsWmRfemUyWGEwYXNCYWE3NXBCV2ItNUpndFR5YzFMbDZLY1BwTzlJMU1xWk9xT0tUYXdYQkdrTXVCcll5YVVKbnhpekRMdHhxbFJ2Z2lORk9xYWlzMzdtWW5QYkE3RmZvOFBtcll2eWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPX2gyRVFuYlc2Vm1uZmtmWi1YbXFvUk5aeGJZenJRRDlETmhjMkluZG55c3JTWmlpZlFmS1ZZRkhqM2lTdlJVLVM5VlJWUGpyTEZ2RWZTbjZKWVV3dDZNWXJ6M2Vaa19KYU4xWDUyaDI1LUZudW1DTW9CYWVHZEdjOWp0RnpLUGpXMU41ZjFhaUxqZEprQnNaOWEwLXNBUHp4MWNHeS1oMWlmZGl6UnBQMWxHbXZXZ0ZUQ3hoRXFiaEhzbm43TmdZbmV4TExzZ9IB0wFBVV95cUxQakZOZjgzQWxqR1MxMG84Nnp3ekQ3c1BrWDhsTXJYZG9nYTdyLWNBLWFNR2NYbGhlRTlfcW9vLVVpWGpoQy1DNFVjM0hVT1o4OHMybGdWV090em45R0R6NWdyMlBHUWRUVDAzRGVpcHVrTUxLU2dJbHBOTGZkOTJWcnNxOHRDZF9YNVFDZGYzNXZuTVN4bzhHR2RBSlRyZWFMdmVIZVUzSFk0d3BLSDZHbTNLWTNxWng3Rl83Tm5EazBLb1V4N0FOdGxtZVhGQ0xGQnEw?oc=5</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>14-05-2026 07:46 UTC</t>
+          <t>14-05-2026 04:30 UTC</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Stock picks: Analyst prefer Aurobindo Pharma, Sona BLW, Tata Steel</t>
+          <t>Gold duty hiked up to 15%: Titan well-placed to weather storm, says Nomura</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOTmtpMUR4MENaTFNsUGtQQVpEV3A3X3pESmJBc2dsS2kzeWNlaHd4V3pfTjFhbXNaSHlXUHYxN2JCeGpfTGptUk9hZkY4LUlpazRMQk15RXhLUHFCZ0M1a2Z6dVJNR1pnTFhGR1M1M3ByME1KbUdnUXdfVk9SdDZ4bWt6Z29FakFGMnM5ZDRZVjFMWUprZzBfUzhMeHFCM2s1d0F4dkU0SGFGVXhuLVBIbGE2X25PcFBwVnMyYktWNXdEUnF1VXUyMV9R0gHPAUFVX3lxTE9samtPMzBhdGw2Y1ptc0ViM0Z0Sk96bEl2WEhNbEQ1dlBuQkh2Ti0xYW04SG5PS240RHpMWkZUNXVqSEx5VE45ZG9feXNvb09oc0ZkTEJYM2d3X3VSUE16MG9FYkpKSVdGd3BpRDlvSlg0TlpzY1huYmJrSS13Szh6azlwODFlNXBpVDN2U0w1VWtnUTA1cGhXWFAtTTAwVVRRMjRPV3U5Z3g4eENzRHVKRUcwYU4tZjJzeF9SRktEcTN4TkFKZHRwbzUzS0xiNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxPc0tubEZMX2o0MnBRdlZLVmk2STh3TTJYNDJLMTRWYnliQTdOZ3JLUEFDRXEtd2RLQm00VW5hSHI4WTFnQkU2SXJ6N2kwTG9VVUxyMzRzc2w1NkVGTmwyQ2k1S0h6bXE2Q0FRTFVPX0xHOTFUdHpudHpqSmotUmM5Umc4VHljN1N6ejg5Q01sZzd4bzg5VktrdWVUNHBvMk9fVTl6ZkhleW9CcUdzaTVLUmhwU1d3ajNSZzdwVWJNVGF4YS1hdXRzRTdxVXR0d2NyblpDb0RTdzlDNDhKVlJV0gHkAUFVX3lxTE9xTG1COXVwdmh5N1UyeEM3eURQLWladXE3cG9EcXJxV09MQ3JYRnZUQnpkQzRuTkRuQlQyNGttb1RFMkVXcUF6akZvTXliY0VtcGJTSWZiNmZUYXBaUDRacnlleDhTRUhwblUtUzE0NVdYWU54eVhBM1p1RC1vdHlBR0xXZk9DZ2N0NWU5U0NBZU1LcTdsVU1HVTVYVUQybFpFUmpueWdaZE9QNjhTT0VLN01IenlSMk1wdEx3UEpjVHNybnJfRGlwZENXd2tlNHF0MC05bVYyZXBSelpTT3FOT2hWbg?oc=5</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>14-05-2026 02:10 UTC</t>
+          <t>14-05-2026 03:34 UTC</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Tilaknagar Industries arm receives govt. approval to commence production of its expanded facility</t>
+          <t>NLC India zooms 15%, hits all-time high on posting healthy Q4 results</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigJBVV95cUxOYXhReTRMakM0cVhZVWVIcEpoNmttelB3V20wblphMFR5OW5PMzJrcld6RVBjN1FsbEV2M0h1WkhSZ09vS2hVdXJ5NXNqS2VEb2N0RHlsWVdsZ182dzVCLWdvQnhpVm5MQm1KdGJlMy1na3p6ZGM0TjhWNmRmaTktTEJvR25kUTdfbXcxXzZ2MDRseDZXUkp0bHUzQ3N2Z1FRUGRaWWZhcmFNVnNnVVVzdHZ0cGNUYmhpVlptQmo0ekRKY0dYRDUza0NxcWlkTWNra2RaN3FWRnctOU1WbF9BdHpheWtpdGxrVWJyQnBEc0ZvaFdCUkQxMFc0WV9vVlRVNXNVOUREWE5Ld9IBjwJBVV95cUxOQWtiUmlZYWpMY0VNX0YzSVpiUHZQMEpadnM0R0ZpbnkySFZnTG5hRmNUcFV3QzJwVmtLYWNVQ25GalJTQlVOWVljTkh6YzFhdFJ4amY5empmZ1o3Y3FpamlyZmF1dTRqb2lpVnJ1Uk5UWGRfYTk3bGlzaEx0Y1VEX3BncEFQRjBIRk1xcFl0RXRxY2dDVkpQeFdjOEpTOS1YWk9USWR6SmNLV1VMYUFCYW10MzJwU1Z5VmpzY1J4MzRYaGFyQXlYbmkzRGUtMkZWLVNhRU5VR1JPT0U4UmxlZTdYWlZZTkhBV1UtQTVlSlpnVmZUaXpLMGtUUE14akQycVBULUZGZzVjTFZ0NWww?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxQN0FBV0gxcGhwZnBnaHFHYVlCcWVVY0VNV28ydFJsQW5zc3RLZktpVWRlaXE2cU5KWWc5VE9yal9STWxpSWFIbldXdDQxcEpnUGNWQm5TOUZxSEJaUmQ2VGpPQU9Pb0JVbGdrVzBPZnVObGVGY0N3V0JSdl9FcWRtWk5nY1MxYXB2aTdvNjl5M0g4VHBLLV9mc2xBaFhLMFA2NGhrUDRSSVdjLVdRUVhiSVJPZmZpbzRub2xaUDN2aHdwbTVWNDlmb21wS2FIRTNPR1VEZ0hzWjYyQdIB3wFBVV95cUxQaDFSMXV5SGRnbFNwamotN3I3ZVVjRTRJUVZaM2ZpeGx0cWZNWENKNlQ3cUFoc3M0WlJiZklGSVBJZ3o2N0tVUE9ZTTJfd1AxSmhSTkppZV8zQ25kbVhtX2JBN2xJQUkzSTdkZngwaUpOdXdwYkhqR0E2TGxKbDFSZjZEZVI0QjhlUEhJTURxSDJrekt5LWR2S285T1FGRzhyaXppQ3ZjVk80Y2JRM1hxTnB6aVJSX2pYZ0R0NTF5TEdtRnBQRHVoMktqU3Z6akcycE14UDFVaXBmcUZNNGdr?oc=5</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>14-05-2026 08:02 UTC</t>
+          <t>14-05-2026 05:13 UTC</t>
         </is>
       </c>
     </row>
@@ -3460,238 +3460,238 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Pharma Quality Excellence Awards 2026 - Celebration and Conclusion</t>
+          <t>Larsen &amp; Toubro partners with France-based Exail</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Siliconindia</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxOcTV3bWhuZ3VaZmRncmFHOENMX1NQaEV5M1phdVc5b25KNGxSTGxOcWl5eW5TaGZBbjBhdndWN1pvY3NualpsUjlpaHpTeG91a3QwWkg1SFZqaUp2SDBzN1h6U3RYTHRBbU9Cc19VOWpKZEVXM19yZXVjLUVheXdpZWFBZkp0LWFCRzFwazllWWpGSTZ4ejZIeG1Odk0tMFlVWERvdWxXNkpCS0YyaUZaQjlIaTlxYVZoZ0RNUE14bGwxdDJnTFhUdQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOSGx2c1FFeUV6b1dCOXZ1em9YMFFXaTIwTzI4eTJHY29wWUJCc2VqZjBNZC1fWkxYd1NxMUVfQkQ2Vmd6Uk1jcEQwTEVXUUR3WHZacUNWbDBtU3JkbVdqXzNBdnkxR1RDdEdrT2xLeTg4Qm96eTBvbXlPMkM4bG43Umh1QnY5c3JUc2djV0o0V1F5Zms3OWoxNFotUk85OU1sWTczVWllSFhrRjNJTDhXWFlrRTNoU2t0SGRhVVJzLWRVb2hBcy1V0gHMAUFVX3lxTE9YcmFVdEd6YmV0dGh4THNOLU1rd0tJTjZtZHRaRnBNWXpKZUhjR2g4SE5rMXRHR3E0d0pOVVVPeEZIUExqSVZpV3R2dURmTTZTYm9OSThBdTdXeUhTY3JUTVBQTGtJRm5XOEdRNWhjVWdQUDF3RDl1TTdIRDlxXzhCWXhZR1hWRzFkeDh3QWpCU1UzM2JOS0JMOHZNcUIyY2ZJOVhYVDhZdzd0WTBxZVlqR3FzZEpKSkdUZzh0a2JnQ2docTRyd0ZOdVBDRg?oc=5</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>13-05-2026 14:20 UTC</t>
+          <t>14-05-2026 08:02 UTC</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Zydus Biotech</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Pharma, NBFCs see fresh mutual fund buying in April</t>
+          <t>Zydus Lifesciences GST Appeal Order Upholds Rs. 10.12 Million Penalty</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPUmJxbVZZcHBQbV9aYV9hMndrY3VPamkzdDd6c1ZaVkdWMjQtd2xjbVNqTUZaVUhRZ3lmazRTdlRRdmZqZUtpNktrWDRPRTM5bW5oOU1wSXlrUkhnNEFUa0ZIOGNpMHgxOTByQy1vbTJxTzVWMG5Fem1rdmpIdlRKSl9ZYlBiY1djVnRYNzRYSDhiVFc3Y3psZHZta1FtVzE1SDlIUzgwRkdobmlYajYtUXdwS1ozWnfSAbwBQVVfeXFMTVoxLVBKTWFyN1NobXZYM2JpVS1USFZSNDdMT2MxVDQ0dE50TW4tS0pCTU5ldWF5NElPWVp6S245WF9EdHFoeWFsMmV6TDJvVGdZMnZXWW4xaDdBWU5ZVl93YktjV0hHRXJIM09LbS12d0pUeFAydU5KOGVkdFI0WjhTSTRSQ0o0RmtmN0VuM1JuZkRPdGxkSFhTUkpOcEswbWVYLVhBRjdVekJMNG02M0gzNjRwSFY2ZHoxQTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxObzlFc2ZuTFZ3QXB0ekRwNkFUWEVOaFZyejY3c1ZDN1JKU0VQNVpYU2dPSTlMLXhCdDZVUjNqTHBuT094ZktTRjB5dTByZTZ0aEhTQWh2T1B3WUs0OGV0SDhJRWFHUVF2bFBTS09hQ3Vic0cxZmVwMWpoeVZvc3RvZ3VaS2ZUT0d4RjM1clBSQmJfOUFYdXhKSW1hQ2ttYlg2QU1OU2lWYm9rZGhNd1VSMEE4TDlmSnVSc3hsRlZuMW1NZTlubmxwdXcxQmRjVm0tbjhHWVlZbEI4VmVTTjRJbmQ0a0Y0d09XQ0pFdWZCNUxkcnBXYVZDQ05JNWpsUQ?oc=5</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>14-05-2026 00:59 UTC</t>
+          <t>14-05-2026 07:29 UTC</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Zydus Biotech</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Technical picks: Asian Paints, Tata Steel among analyst's top picks</t>
+          <t>Zydus to buy Assertio for $166.4 million</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxORmpYcndMeGFnSVlEclJTOU1jMlJNMW5Nb0w2dWNiT0swd01Pb0hJbWlRYzNQQzNCN0cyUjFqT0V5S0ZBUUlsd0hNcHotZlRLNVI2QkVXR3NvaDRvN3FTSm9DcFVDUlVMT0pzSWVuSHB4T1RNb19aMzlwMEdyM0hiSHhRdVAyTUtDakdHMXJneTd0WHRrRHdIODFsNVNLVUVNY084RVFmTFBhV09wNHl5XzVPQW5JMDdwcEhjQlZKR0RJRDlJSmczREROT2NtWngzNjNRaC1OdXcwX1owdEV5QnptSkhSX2hTOEhfadIB8gFBVV95cUxNMHRHTVFIS25oRjV5WlNwMnZMYTVxN2pSR3VMdUZtSjhuYjNYcGtiQWZKQWg1aW5CVk9PNFh5QjJjVUNHR2NnWXlPdUszZTZ5aTdMaTZfQ3YxTmRZZFRGWWgwZUUxNnFWMWFJYmJ5cjRzNEFvbTRBS3RyeUxSNEhOV2xpaE9NdG9WUlM3dXYtQ3RRSkJVblR1SVVGVno0U05iZEdOU1l3ODl5ZFJidXlza09scVNzT0VFdnp4cVJjRGQ0UjR2eHNuMHIyWlNRMzM3Tl9IcjF3Zld2cmgzSGVGVkJ3VkZOaHFxaVZkTHczU3Frdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNdFNkREV4WFFZUy1fdDZXOFlvVEdvTnoxVE1IdFJUcmhDdUVRYkE0bWE1aDhxN2dnc3JfZmZ5c0c0eXlSQXVKcGpLUDBVZjZ1cUprSEpfR1hYcmY3Q1NFSU5ENFpJTURXcmE2TFdnVW1nOGhxUFhsYmc0aDMxa2N4TWVETjVwVHFvY18xdUdUazlseWxMdlpTUUVFS0xxMGFJakdvWXhHRTUxVUdIMmtrZllTci1Qa2NzaWxzUXM1andPVmdqODNQc25MMlhHSkNlNlHSAdIBQVVfeXFMTXRTZERFeFhRWVMtX3Q2VzhZb1RHb056MVRNSHRSVHJoQ3VFUWJBNG1hNWg4cTdnZ3NyX2ZmeXNHNHl5UkF1SnBqS1AwVWY2dXFKa0hKX0dYWHJmN0NTRUlORDRaSU1EV3JhNkxXZ1VtZzhocVBYbGJnNGgzMWtjeE1lRE41cFRxb2NfMXVHVGs5bHlsTHZaU1FFRUtMcTBhSWpHb1l4R0U1MVVHSDJra2ZZU3ItUGtjc2lsc1FzNWp3T1ZnajgzUHNuTDJYR0pDZTZR?oc=5</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>14-05-2026 03:04 UTC</t>
+          <t>14-05-2026 05:45 UTC</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Zydus Biotech</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Cipla soars 8% despite disappointing Q4; what's driving pharma stock?</t>
+          <t>Zydus to acquire Assertio in $166m deal</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>Pharmaceutical Business review -</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPX2gyRVFuYlc2Vm1uZmtmWi1YbXFvUk5aeGJZenJRRDlETmhjMkluZG55c3JTWmlpZlFmS1ZZRkhqM2lTdlJVLVM5VlJWUGpyTEZ2RWZTbjZKWVV3dDZNWXJ6M2Vaa19KYU4xWDUyaDI1LUZudW1DTW9CYWVHZEdjOWp0RnpLUGpXMU41ZjFhaUxqZEprQnNaOWEwLXNBUHp4MWNHeS1oMWlmZGl6UnBQMWxHbXZXZ0ZUQ3hoRXFiaEhzbm43TmdZbmV4TExzZ9IB0wFBVV95cUxQakZOZjgzQWxqR1MxMG84Nnp3ekQ3c1BrWDhsTXJYZG9nYTdyLWNBLWFNR2NYbGhlRTlfcW9vLVVpWGpoQy1DNFVjM0hVT1o4OHMybGdWV090em45R0R6NWdyMlBHUWRUVDAzRGVpcHVrTUxLU2dJbHBOTGZkOTJWcnNxOHRDZF9YNVFDZGYzNXZuTVN4bzhHR2RBSlRyZWFMdmVIZVUzSFk0d3BLSDZHbTNLWTNxWng3Rl83Tm5EazBLb1V4N0FOdGxtZVhGQ0xGQnEw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTFBqMFRiVldMNk9lUFNMRFBiYUtWbWNxOVIyb0dWR0cyNHZ1QVN2NlZlb0pib29kVmItRE16RjlzOWczeFpBa3JuU3ZyVVpOT3gteFlLY1NjTXBlUEdINzltN0dBeGFyYU13cWdPcHgzTzV5SDk0ZXBPa2ExNU5rejQ?oc=5</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>14-05-2026 04:30 UTC</t>
+          <t>14-05-2026 12:06 UTC</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Zydus Biotech</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Larsen &amp; Toubro partners with France-based Exail</t>
+          <t>Zydus Lifesciences Arm to Acquire U.S.-Based Assertio for $166 Mn</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>Digital Health News</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOSGx2c1FFeUV6b1dCOXZ1em9YMFFXaTIwTzI4eTJHY29wWUJCc2VqZjBNZC1fWkxYd1NxMUVfQkQ2Vmd6Uk1jcEQwTEVXUUR3WHZacUNWbDBtU3JkbVdqXzNBdnkxR1RDdEdrT2xLeTg4Qm96eTBvbXlPMkM4bG43Umh1QnY5c3JUc2djV0o0V1F5Zms3OWoxNFotUk85OU1sWTczVWllSFhrRjNJTDhXWFlrRTNoU2t0SGRhVVJzLWRVb2hBcy1V0gHMAUFVX3lxTE9YcmFVdEd6YmV0dGh4THNOLU1rd0tJTjZtZHRaRnBNWXpKZUhjR2g4SE5rMXRHR3E0d0pOVVVPeEZIUExqSVZpV3R2dURmTTZTYm9OSThBdTdXeUhTY3JUTVBQTGtJRm5XOEdRNWhjVWdQUDF3RDl1TTdIRDlxXzhCWXhZR1hWRzFkeDh3QWpCU1UzM2JOS0JMOHZNcUIyY2ZJOVhYVDhZdzd0WTBxZVlqR3FzZEpKSkdUZzh0a2JnQ2docTRyd0ZOdVBDRg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQeGw5VkxpTUZuLTlJN3NXdmpwSW1JZ3VUZUJZZV9STWpvTlZYYllOOVY2dDA3dXpGckNhQ0RNU1UxZU1NX19ieGF0a0lfcGNnaEZqS0hlWXlQQ2Rqbl80aEcxLW5YZGRRR01ST09UQTFxTHpQZzZWaEQ4eVk2bm1QOU92SmNkQm5KV1ZqMEtNYVRzSHlJcnEwTm5aT0RiUQ?oc=5</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>14-05-2026 08:02 UTC</t>
+          <t>14-05-2026 06:37 UTC</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Zydus Biotech</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>NLC India zooms 15%, hits all-time high on posting healthy Q4 results</t>
+          <t>Zydus Lifesciences acquires Assertio in ₹1,570 crore US expansion push</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>domain-b.com</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxQN0FBV0gxcGhwZnBnaHFHYVlCcWVVY0VNV28ydFJsQW5zc3RLZktpVWRlaXE2cU5KWWc5VE9yal9STWxpSWFIbldXdDQxcEpnUGNWQm5TOUZxSEJaUmQ2VGpPQU9Pb0JVbGdrVzBPZnVObGVGY0N3V0JSdl9FcWRtWk5nY1MxYXB2aTdvNjl5M0g4VHBLLV9mc2xBaFhLMFA2NGhrUDRSSVdjLVdRUVhiSVJPZmZpbzRub2xaUDN2aHdwbTVWNDlmb21wS2FIRTNPR1VEZ0hzWjYyQdIB3wFBVV95cUxQaDFSMXV5SGRnbFNwamotN3I3ZVVjRTRJUVZaM2ZpeGx0cWZNWENKNlQ3cUFoc3M0WlJiZklGSVBJZ3o2N0tVUE9ZTTJfd1AxSmhSTkppZV8zQ25kbVhtX2JBN2xJQUkzSTdkZngwaUpOdXdwYkhqR0E2TGxKbDFSZjZEZVI0QjhlUEhJTURxSDJrekt5LWR2S285T1FGRzhyaXppQ3ZjVk80Y2JRM1hxTnB6aVJSX2pYZ0R0NTF5TEdtRnBQRHVoMktqU3Z6akcycE14UDFVaXBmcUZNNGdr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOY243Nkt6dWFub0RXMndUQ3RwWTU4OXN3TVFnb1pucTB4RmhVUU9rcmFqNWFQVlBJNF9icHFaclBJZGtlODZEb3NuN3V3N01qNEtlTHBzUVU4VHRoVTBkel8zNU1UUVFTTDc3eEExMmd1bDBuN0JoeDhhSzN3dFN5UmxxSzRqTWJDQ2tSS2MzSmVRRk5SVFJZcTBWX2FyM0Z6dG5aY1c4RdIBpwFBVV95cUxOY243Nkt6dWFub0RXMndUQ3RwWTU4OXN3TVFnb1pucTB4RmhVUU9rcmFqNWFQVlBJNF9icHFaclBJZGtlODZEb3NuN3V3N01qNEtlTHBzUVU4VHRoVTBkel8zNU1UUVFTTDc3eEExMmd1bDBuN0JoeDhhSzN3dFN5UmxxSzRqTWJDQ2tSS2MzSmVRRk5SVFJZcTBWX2FyM0Z6dG5aY1c4RQ?oc=5</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>14-05-2026 05:13 UTC</t>
+          <t>14-05-2026 07:40 UTC</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Zydus Biotech</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Gold duty hiked up to 15%: Titan well-placed to weather storm, says Nomura</t>
+          <t>Zydus Lifesciences shares jump 6% on buyback buzz; co announces $166 mn Assertio acquisition</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxPc0tubEZMX2o0MnBRdlZLVmk2STh3TTJYNDJLMTRWYnliQTdOZ3JLUEFDRXEtd2RLQm00VW5hSHI4WTFnQkU2SXJ6N2kwTG9VVUxyMzRzc2w1NkVGTmwyQ2k1S0h6bXE2Q0FRTFVPX0xHOTFUdHpudHpqSmotUmM5Umc4VHljN1N6ejg5Q01sZzd4bzg5VktrdWVUNHBvMk9fVTl6ZkhleW9CcUdzaTVLUmhwU1d3ajNSZzdwVWJNVGF4YS1hdXRzRTdxVXR0d2NyblpDb0RTdzlDNDhKVlJV0gHkAUFVX3lxTE9xTG1COXVwdmh5N1UyeEM3eURQLWladXE3cG9EcXJxV09MQ3JYRnZUQnpkQzRuTkRuQlQyNGttb1RFMkVXcUF6akZvTXliY0VtcGJTSWZiNmZUYXBaUDRacnlleDhTRUhwblUtUzE0NVdYWU54eVhBM1p1RC1vdHlBR0xXZk9DZ2N0NWU5U0NBZU1LcTdsVU1HVTVYVUQybFpFUmpueWdaZE9QNjhTT0VLN01IenlSMk1wdEx3UEpjVHNybnJfRGlwZENXd2tlNHF0MC05bVYyZXBSelpTT3FOT2hWbg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxNcThUeWRfNVNlWm1vQ1NkMHIzNmo3V0FETk1yYjF0cldWR0lLNVpuZjJEMnhKQldGOG8tTFo5V2pJNEgtNEMwZlA4eEk0N2FjVEY5RnBaN1RTaE1GRzdXTUM3cHltYWxXakFDWWxEQmFOdGI1bzNtQUUxZHFiWWFFSTFkM29JeV9hY2xJejhOTkdBZzJ1elNndmM2YmtidXdTVmtycEFCTlVmdUdtNThjV1Fncld4N3ctMWFqX2NsNjlUcVM2V0ZvYXRnQ0V5Z2Yyc215ZDRVNFdfVEYybXN2aXlSUk5wNWViVjJMS19vbGhCWnZFeWfSAfsBQVVfeXFMTUJTeWdYYzYyVTN3LTRRODJ4VW5aT0doRGRVYUV4RTdmbG42b2tOaU1uSkJEN3JTTVgzWjhRb1Y4N0F3X2VNUEpILVdqbjRIM29zTmgwUkptV1htWDJCNHJNU2ptZDAzdjd3VldsOE9KWGppZ2pZdndQU2xjenJ6YTNyaG5Ua0RFRno1MWxLNXEwZjZCNkpwaDBqdHcxWUVGU3pfaHdONWlVMjVrQVhDLVV2UVlmdVRWZ3g5cEZhNUxzSk9JMC1UemtwaXhvTVdiRXRLU0VwbV9RaHlKaklSaEN6ZXozZWdvUVBGRmxmc2FRN1p6QkJLN0ZxNjg?oc=5</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>14-05-2026 03:34 UTC</t>
+          <t>14-05-2026 07:49 UTC</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Zydus Biotech</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Brent seen at $95-115; supply deficit to keep prices elevated: Analyst</t>
+          <t>Zydus Life acquires US-based Assertio for $166 million cash</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>ETPharma.com</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQTGxtajFRQjhlRm5rOGJvLXZXdW0xZ0Q1Q0lLQ0NDSWNPS0pYZVVoMk9kdl80U0lQZWY2Rk1neGhKSmJzVEJ2S28xdFQzRTVNWTFiSEZFNzF1aUlhZHhLVXVQX0xPaHM0d3R2YVpvQTIyZS0tX2h1dkxOTFlvNnUzT2FwMlBJMDlWdFViOW9EWTBHYjdUd1ZrdTJPb0pWck83YTZIU0VxMWVETGJVUFZJMElMeTk4SW9VaWxQZFZPbFFYMlpJc1FRM0VBVk4xOVXSAdQBQVVfeXFMUEdlRjN0M0w3cks5azY1NThZR3NqMFo3bHFyeE9pSmc5NU54cEl5d0JBR0pEemZvb09Za1haNlFYQnNycmIwMGRKTFBzbF84WHpzS2tQSFhnYjlzQjhGbHo1aHNsUUJfS0ZGZUJwRWVEN3RsanJBYTR4TDM5RlJFTzNYb0puRWZmd1htSWxxbEphZGM3eUFMaEYxeHBndGV3UXRkZ2FUUlZENFE3SHFZREx3U1A2QWRQRXVJLUJ5SkxZSFlYLWxfWkFQZF9iM3RqRTNuVFc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxNMWx1QmQ4WEE5bktod0JZR0x4MmdYUWgzUW43ZkZxNl9JZEpFMFdONW9lb0VSLW9JcjA1clJmZGIxZi1LeFJQaFV6YWZlYkdqYU5fYmZfemZxNFlhX25xREtobEQwSF9XMVNSSEZRN2Q0Zjk3XzBDNDVJblJEdmM0VjNBUlB3b21zeXlnMVMxVkIwbkM4NmtKYmFwVWp2M1gxRTdwNE16enhoUGV1a0hlVWNhejl0Nmk3a0JfR2hHLTVLT0V0V0dSSV9TYzZGUjdjWElCLVZJNUdZSzlsdm5z0gHfAUFVX3lxTE0xbHVCZDhYQTluS2h3QllHTHgyZ1hRaDNRbjdmRnE2X0lkSkUwV041b2VvRVItb0lyMDVyUmZkYjFmLUt4UlBoVXphZmViR2phTl9iZl96ZnE0WWFfbnFES2hsRDBIX1cxU1JIRlE3ZDRmOTdfMEM0NUluUkR2YzRWM0FSUHdvbXN5eWcxUzFWQjBuQzg2a0piYXBVanYzWDFFN3A0TXp6eGhQZXVrSGVVY2F6OXQ2aTdrQl9HaEctNUtPRXRXR1JJX1NjNkZSN2NYSUItVkk1R1lLOWx2bnM?oc=5</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>14-05-2026 02:50 UTC</t>
+          <t>14-05-2026 01:39 UTC</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Zydus Biotech</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Max Estates unveils Rs 1,200 cr residential project in Gurugram</t>
+          <t>Zydus Lifesciences acquires US pharma firm Assertio for $166 million</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxPeDF1MXpQUENVdVA0TzZfMG9PYnFtM0J6d3VwdlBOWUt4Vkpwckl2QmVkS1BZa2p5aGNwRGs1bEVKWHdzTmM0OExmMTZqRFR4QlpnVEFRR2dHUmg1M2dYd3huZlVQanNLNzBCaWdlOUtoWVY1aDd1Y3N5eENXSkZWZGNPM0FDaEphVXh2ZGhseU95N3FCOWEyVzhjUnFXTFRIdURCQnJUU1BGUkpMc2lkOFRkWW8tejFyV19laUJqZ2l4Umw2SHR0Nmd4M2YzUWVjNjJLdHI5am1CVGhSanfSAeMBQVVfeXFMT2k3eFJEU0hhV21GbUI4Sm50VkhYZVRHYWVXTmhvZnhLVDV2LTJyRTExM2YtN0p4cVZkYjZjMFVyTTBjU1NFQ1VYVFlpTGtrNmpYMV9QUUVDTG5rOEsya0xQcFNVd09sOExET1RDQ3RvdVEwSFZYWC10d01XVm9nREYyREwxdFI3ZEFoaVc2UjQtcnNYY0Jha29Iemx6eE85Yll5bExJbExlVG11SFVKdWZtdFZJWFRGY3NkTjNSbmxwVWh6clY0TG94S0pMcXotUFRUSGVqY2lPcDJ5d25La1I1NE0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxNV01pck9FdDV2aWNwS19MZXY2MDZsMS1FU2N0OGlMSzlQT0NRU01UcFBQY25CbGVSbU1zaXhrMC1ZdG5yUXFwRnFtWUV0aktPemVoUUJOWUlEY19XZ1hRZmh6dUJqMmxTMDRTa05tYVlHUDRfb1Z6bm1lZV9BaUZIcDJhRmpTLWlIdDNZZ0pUQ1o2ek1DYmkxeWh6M1dtbTJTNEs1Si0xaWVlRGROVXNHbmFIaEVBU25vcmJBc2hvUVJSXzdBdVJqcU9PTWp6QUliVjJNbzBEc2ZEU0RSRXlPVHljeHlzMTdxNEpGVWpWOVlpaXRGbGM4Z9IB_gFBVV95cUxOZllxcmVCbk1MWjRqS1JxWnRaRDlMdXU4amU3NGMtWURHdjhweUpvWFktSmp5dU90WWFIVUR0YVhBdmxFQ1dRdHRtSjVzeE1va01SNDZ4eGJHRElkY2IxRzJtTFdRQ2FZcFNMVWNMREt4VVIxTDhydEc3ZWM0T1loaUZSUmxucmZMamkzdkZ5dENyajJydm5NbjNMZV8zZVFETVlURDh2SFBYNUNRdlE4VjBnNjNYSEx3emNBMU54blh1blNwaHdIMTNZVlZKXzRnUTEtdkR1U3A1WERUVXNOakRjTWpFSGpMamRDbkJ2WHVOLUtVUGZGZmhVT2k4Zw?oc=5</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>14-05-2026 02:34 UTC</t>
+          <t>13-05-2026 19:52 UTC</t>
         </is>
       </c>
     </row>
@@ -3703,7 +3703,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Zydus to buy Assertio for $166.4 million</t>
+          <t>Stocks in news: HAL, TMPV, Bharti Airtel, Anant Raj, Zydus Life, Tata Motors</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -3713,12 +3713,12 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPUHk3SXJBMDJvWVV6aExfeFVvVzZySGdiR2hLcUhCemRBWkpuajZVWXpUVXZ2dUR4djEzdnhoaFpXRkpNQkd3cFIzUWVnSE1XLU9yNWloM3lGTlRuTk54bXRibmZmN3N5Z3BjTkVwZHhyZVhrX2twa0lUZE82YXJnUTI1RWpSQWNuMWFORFRNNFFQLU0zZm9MTjl6bUJDNmt5eGtaV2FFNHFXbTNtRzN0ZGVxeUE4Ym4yRDJTbmxWZ1JieHh3b21LR09pamPSAdIBQVVfeXFMTXRTZERFeFhRWVMtX3Q2VzhZb1RHb056MVRNSHRSVHJoQ3VFUWJBNG1hNWg4cTdnZ3NyX2ZmeXNHNHl5UkF1SnBqS1AwVWY2dXFKa0hKX0dYWHJmN0NTRUlORDRaSU1EV3JhNkxXZ1VtZzhocVBYbGJnNGgzMWtjeE1lRE41cFRxb2NfMXVHVGs5bHlsTHZaU1FFRUtMcTBhSWpHb1l4R0U1MVVHSDJra2ZZU3ItUGtjc2lsc1FzNWp3T1ZnajgzUHNuTDJYR0pDZTZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxOdk1WVHNMQjlaYmxXdVdWSXlGN3pqWWdSbGxvQmFmbzktTVE2eGVrcXRjSTlReVo4c0tyLThvbDJhT3hwT3cwQlV2MHRzTGRRV1U3OTl4Vk5yOGdqYXNnVzZXYmV0M2RmUXV4WnNxYmNTOWtZcVBjcEkzaHFqVF9Wb3dSOWtoMnM3TVA4TTVVOGVrdk5iRFpUUUxqWWRvN3c1cmdrMGxUMzh6YTJuTXZQSFZfdzRyVmx3OGZXaGlTeWQtMXFjNGZ5NlNiTXJ1TnMyTlhLVzBnamYtWHJy0gHiAUFVX3lxTFBOck5QT2V5ajdIdlFxX2kzLVoyeWJUNHI3NThVdHNHVGdmUm5ucW5jMUpFZHRrLTdtWVRKMkVVSWFobXRzNGI3OVhxNUpfZE9YOVlUM3k3NXJTV1B1UGxZWW5rSjFWNC13V1FFMXZkYXpsT2RnQzFGMzR4d3dxYlZFcGxyaElaNy15M2IwZk1pWGdzV29lVnpQNG1Nc0ROSjdRRnRFdUZ0MUt5RzJudmR2OGNwTGpoZ1lMTmlfWUxQY1hRR3RsLTAwZXZZRjlDektFRllBU2ZFT2U4NXZDQ2FwRUE?oc=5</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>14-05-2026 05:45 UTC</t>
+          <t>14-05-2026 01:15 UTC</t>
         </is>
       </c>
     </row>
@@ -3730,22 +3730,22 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Zydus Lifesciences Arm to Acquire U.S.-Based Assertio for $166 Mn</t>
+          <t>Assertio to be acquired by Zydus Worldwide DMCC for $23.50 per share</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Digital Health News</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQeGw5VkxpTUZuLTlJN3NXdmpwSW1JZ3VUZUJZZV9STWpvTlZYYllOOVY2dDA3dXpGckNhQ0RNU1UxZU1NX19ieGF0a0lfcGNnaEZqS0hlWXlQQ2Rqbl80aEcxLW5YZGRRR01ST09UQTFxTHpQZzZWaEQ4eVk2bm1QOU92SmNkQm5KV1ZqMEtNYVRzSHlJcnEwTm5aT0RiUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPRXpGc1BrLTltVmRmZWp0bGlIdy1qMllYZG1hR2NaejJ3T29Vb1ZHV0Iyd0ZqLXlPMDRkTnVrMVhmdTNwanF4VkRBU0FkVnhDXzR1bV9VYmJqbWtla3pERzdFS08yeklkSWdJQWZJblNQOUFBUUhpVUtHYVZBYkdZMXMxYmhpNHFEWGNfZWlZYkJDRHRmcVhhQlR1Tmo2dndwY3R1TzREU3hKbzhfbEpoUWR4RWxYSGhJ?oc=5</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>14-05-2026 06:37 UTC</t>
+          <t>13-05-2026 17:39 UTC</t>
         </is>
       </c>
     </row>
@@ -3757,22 +3757,22 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Zydus Lifesciences acquires Assertio in ₹1,570 crore US expansion push</t>
+          <t>Market Trading Guide: Buy Zydus Lifesciences, Solar Industries on Friday for gains up to 15%</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>domain-b.com</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOY243Nkt6dWFub0RXMndUQ3RwWTU4OXN3TVFnb1pucTB4RmhVUU9rcmFqNWFQVlBJNF9icHFaclBJZGtlODZEb3NuN3V3N01qNEtlTHBzUVU4VHRoVTBkel8zNU1UUVFTTDc3eEExMmd1bDBuN0JoeDhhSzN3dFN5UmxxSzRqTWJDQ2tSS2MzSmVRRk5SVFJZcTBWX2FyM0Z6dG5aY1c4RdIBpwFBVV95cUxOY243Nkt6dWFub0RXMndUQ3RwWTU4OXN3TVFnb1pucTB4RmhVUU9rcmFqNWFQVlBJNF9icHFaclBJZGtlODZEb3NuN3V3N01qNEtlTHBzUVU4VHRoVTBkel8zNU1UUVFTTDc3eEExMmd1bDBuN0JoeDhhSzN3dFN5UmxxSzRqTWJDQ2tSS2MzSmVRRk5SVFJZcTBWX2FyM0Z6dG5aY1c4RQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxQM2xYZmpDUmFCeEJWTC05bXkxM050aE8zUmJmaDhmNl80c1dPS3YySjhRckt3dTkwWHp3N3NuTHJsRUwzeGJHMXdta283TVN2YmpWOTVraERLdTlMMDJpQU40OC02UDQzU0xoRVhZNVA4UWxOV1ByWkRIbnc4dXBBbUVkU2FoTDE5bklTWGxIajNUczJxQndaUEwzWWgwMWcwSjJFeE1CQUNQODBxdzJYTzdwZUFkeHQ0ZHdyT2FGRHg3aG9uVXNCU3F5ckxZTEZHdHBzOEFheDFXVUpRTzZkUjBkTDdTNVdzU3oxM3pWS3RsUWxIckHSAfsBQVVfeXFMTTF6Q3dGS1Fuak94ejh3UlZLR1FETTN0VzVOdEoxV1IwcHl0RFlCRFEzWXdUOElTLUFRQm9aTnBZbEVyc19oaTNDdVlQVFRtai0tTGJEWVEzNFN1UU50NE5BQk83RXF4VVA1RzUxVVNFVGZpZ1JGUXBPVFkxeEdTSzNpZEQ5ZWotQU1xNnJ4UUJDVVk4MjB3aFE4OVk0bUkxOURKd2x5YV9iRWlPU1YtemxCUS1LRTgyaWZuRUFvbUxrVlhNLTRDTUZBejY4czY0NnFpcGNia1I2RXd6N1RFZkhEYUczdmJTUUZ2U2NlUDhoNWRnRmljdFZDMHc?oc=5</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>14-05-2026 07:40 UTC</t>
+          <t>14-05-2026 15:29 UTC</t>
         </is>
       </c>
     </row>
@@ -3784,319 +3784,319 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Zydus Lifesciences shares jump 6% on buyback buzz; co announces $166 mn Assertio acquisition</t>
+          <t>Pharma sector stocks today, May 14: Cipla jumps 7.15%, Zydus Lifesciences rises 4.01%, Strides Pharma up 2.20%</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>Business Upturn</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxNcThUeWRfNVNlWm1vQ1NkMHIzNmo3V0FETk1yYjF0cldWR0lLNVpuZjJEMnhKQldGOG8tTFo5V2pJNEgtNEMwZlA4eEk0N2FjVEY5RnBaN1RTaE1GRzdXTUM3cHltYWxXakFDWWxEQmFOdGI1bzNtQUUxZHFiWWFFSTFkM29JeV9hY2xJejhOTkdBZzJ1elNndmM2YmtidXdTVmtycEFCTlVmdUdtNThjV1Fncld4N3ctMWFqX2NsNjlUcVM2V0ZvYXRnQ0V5Z2Yyc215ZDRVNFdfVEYybXN2aXlSUk5wNWViVjJMS19vbGhCWnZFeWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxQc3Y4Z09mbF9kdExNSzRHNS1WNThaUnBPTE1WTU5jb09jZURZU1JjSHMxZ0ZEdnJzTFBJN1FNZ25ZcUxvWnluXzhYZEZoWlRSbWNibnBISlYxWjMwYjRlQWZudnV1ZmsyczJkeW1Kai1CMHRKYWpEYUY3WTNtN1h3V2hTZ1MzUEFweW1IdEVrQlYwR0piV3RwazZOTWl0U1E3dFNqS0hDcC1FcGtsYjVYUFBJT1FLWEhHNE1VUm1sckp1bk9oOEpRYl83V3RROTZkSy1oX3JNR0xYcTVmUUtIV09SQllmZFpYdTFnSQ?oc=5</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>14-05-2026 07:49 UTC</t>
+          <t>14-05-2026 04:06 UTC</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Zydus Biotech</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Zydus to acquire US cancer drug company Assertio for $166.4 million in all-cash deal</t>
+          <t>Samsung Electronics Announces First Quarter 2026 Results</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Mint</t>
+          <t>samsung.com</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPNHo0eXdBbnlfQnpoLWFfbG82aWJ1R2Izb09RX2xsY01RdEdRTEZJb21WaktlMTBMQ3Bualh4cVM5OTFId0F2aGx0a3JDZ0tDQmg4S0xTa0dKRG9iTms2WDBYOFNTMUZuc2VzbU9HZURMNzI5bGx5U2t3Wl9ISFVtMmU3cVBVZURuenpSWXF5bmFxbmtZY0ZsU3ZCSlMxeV9rckd3ZzlBLVBXanlmN1lF0gG0AUFVX3lxTE92MUk0aGVkYWQ2VDFvcG92bmVKUmthUXkyeWV3aGpOeXpYQzkwSFNUMnliUUF1eDB2d1k2Smo3aF9DRm53ZVlvS1NJaTh1LTViV2xWeXVBYWRvenJvQ3JDYnJVTUdKWXAwMGF0U19BU1htN2tydk0tS1psNnpDZm9aWWx5bGE4QW92dTR1aW54SUY3b25ROWRVVGtMRVM3Vm9TU25MQkZIdFJyNENmZzl4RktqVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOWUVwY3RuMVpmN0E2LXdudkFMWjl3VjN6MWp3Vnk4VUUzTnkzdGVRNi0wWXN1MnpRODQ2c0RGWE9Wbjg5Y0RfejdZZUVjZGJGdi1GdDVCdzlzWjBNU0hQbVVtTGJab3lNakR2S1RKSzdOVTVrVDZVV0xoWU45ZFFoVjVZUDdsTTRqai0tVQ?oc=5</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>13-05-2026 16:24 UTC</t>
+          <t>14-05-2026 08:20 UTC</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Zydus Biotech</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Zydus Life acquires US-based Assertio for $166 million cash</t>
+          <t>Samsung has staged a stunning comeback</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>ETPharma.com</t>
+          <t>The Economist</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxNMWx1QmQ4WEE5bktod0JZR0x4MmdYUWgzUW43ZkZxNl9JZEpFMFdONW9lb0VSLW9JcjA1clJmZGIxZi1LeFJQaFV6YWZlYkdqYU5fYmZfemZxNFlhX25xREtobEQwSF9XMVNSSEZRN2Q0Zjk3XzBDNDVJblJEdmM0VjNBUlB3b21zeXlnMVMxVkIwbkM4NmtKYmFwVWp2M1gxRTdwNE16enhoUGV1a0hlVWNhejl0Nmk3a0JfR2hHLTVLT0V0V0dSSV9TYzZGUjdjWElCLVZJNUdZSzlsdm5z0gHfAUFVX3lxTE0xbHVCZDhYQTluS2h3QllHTHgyZ1hRaDNRbjdmRnE2X0lkSkUwV041b2VvRVItb0lyMDVyUmZkYjFmLUt4UlBoVXphZmViR2phTl9iZl96ZnE0WWFfbnFES2hsRDBIX1cxU1JIRlE3ZDRmOTdfMEM0NUluUkR2YzRWM0FSUHdvbXN5eWcxUzFWQjBuQzg2a0piYXBVanYzWDFFN3A0TXp6eGhQZXVrSGVVY2F6OXQ2aTdrQl9HaEctNUtPRXRXR1JJX1NjNkZSN2NYSUItVkk1R1lLOWx2bnM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNdE1NTmFCd3hqa3E2alVCYUV3Y2JpUV9ZQ1VrX0RKQzJZeHZzekNNekMxWTZael9fMGNKS19uYlJkSnQ5cnpqZHZ5WmpqajV2cHFfbXBYMEl6RVJ5Ql9pbWFKRG1jOXdCRGozOVBScXRFSWRZRW43X2lBTTIwS1BrY21UZVBUV1ZZcGk1QQ?oc=5</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>14-05-2026 01:39 UTC</t>
+          <t>14-05-2026 12:55 UTC</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Zydus Biotech</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Zydus Lifesciences acquires US pharma firm Assertio for $166 million</t>
+          <t>Samsung could be cost-cutting with the Galaxy S27's Exynos 2700 chip</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>SamMobile</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxNV01pck9FdDV2aWNwS19MZXY2MDZsMS1FU2N0OGlMSzlQT0NRU01UcFBQY25CbGVSbU1zaXhrMC1ZdG5yUXFwRnFtWUV0aktPemVoUUJOWUlEY19XZ1hRZmh6dUJqMmxTMDRTa05tYVlHUDRfb1Z6bm1lZV9BaUZIcDJhRmpTLWlIdDNZZ0pUQ1o2ek1DYmkxeWh6M1dtbTJTNEs1Si0xaWVlRGROVXNHbmFIaEVBU25vcmJBc2hvUVJSXzdBdVJqcU9PTWp6QUliVjJNbzBEc2ZEU0RSRXlPVHljeHlzMTdxNEpGVWpWOVlpaXRGbGM4Z9IB_gFBVV95cUxOZllxcmVCbk1MWjRqS1JxWnRaRDlMdXU4amU3NGMtWURHdjhweUpvWFktSmp5dU90WWFIVUR0YVhBdmxFQ1dRdHRtSjVzeE1va01SNDZ4eGJHRElkY2IxRzJtTFdRQ2FZcFNMVWNMREt4VVIxTDhydEc3ZWM0T1loaUZSUmxucmZMamkzdkZ5dENyajJydm5NbjNMZV8zZVFETVlURDh2SFBYNUNRdlE4VjBnNjNYSEx3emNBMU54blh1blNwaHdIMTNZVlZKXzRnUTEtdkR1U3A1WERUVXNOakRjTWpFSGpMamRDbkJ2WHVOLUtVUGZGZmhVT2k4Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQYjJTd3RNdDJKTnJCWUdqUXM1RDhRemc0d0I4TU54RUVHaThaTXdvem1fdUpzcUw3aW1vdlpQUWdJYzA4UnFZWnYyc203MUFuVHl6M0Z4dXdlQ2tueWQ1bFNKNENURXFLQ05pZkl2cDVBa0JFT2VIQ3NoXzh6dmY2ZjVMWnh0dVU?oc=5</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>13-05-2026 19:52 UTC</t>
+          <t>14-05-2026 16:25 UTC</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Zydus Biotech</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Stocks in news: HAL, TMPV, Bharti Airtel, Anant Raj, Zydus Life, Tata Motors</t>
+          <t>Samsung foldables tipped to debut Google’s Gemini intelligence: What we know so far</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>Firstpost</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxOdk1WVHNMQjlaYmxXdVdWSXlGN3pqWWdSbGxvQmFmbzktTVE2eGVrcXRjSTlReVo4c0tyLThvbDJhT3hwT3cwQlV2MHRzTGRRV1U3OTl4Vk5yOGdqYXNnVzZXYmV0M2RmUXV4WnNxYmNTOWtZcVBjcEkzaHFqVF9Wb3dSOWtoMnM3TVA4TTVVOGVrdk5iRFpUUUxqWWRvN3c1cmdrMGxUMzh6YTJuTXZQSFZfdzRyVmx3OGZXaGlTeWQtMXFjNGZ5NlNiTXJ1TnMyTlhLVzBnamYtWHJy0gHiAUFVX3lxTFBOck5QT2V5ajdIdlFxX2kzLVoyeWJUNHI3NThVdHNHVGdmUm5ucW5jMUpFZHRrLTdtWVRKMkVVSWFobXRzNGI3OVhxNUpfZE9YOVlUM3k3NXJTV1B1UGxZWW5rSjFWNC13V1FFMXZkYXpsT2RnQzFGMzR4d3dxYlZFcGxyaElaNy15M2IwZk1pWGdzV29lVnpQNG1Nc0ROSjdRRnRFdUZ0MUt5RzJudmR2OGNwTGpoZ1lMTmlfWUxQY1hRR3RsLTAwZXZZRjlDektFRllBU2ZFT2U4NXZDQ2FwRUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxPaGVINkNESVgyZEZLN1F3MXdkMTZBOUhmV01ta3poTjBxTkp4VjJMVDEtb3pmNEZsdWJ0STVtWWFTN2owVG43STNXNHZFeTNnX01OdEVORW5FSDlnbDF3cl9QdmR5YVFUZXdvb0FhcC1uRXk2SzFNSlpxanJrZHMxWVhwZ2F0U0RfSUVUM1lXYTZXLUV6MTRVYW13Y2o5SlkxYjVubk9iUVloVTI4YlBKVWxIUnJ6QldBVXVPNGhRZ2ctUW1F0gHKAUFVX3lxTE1QUEdJUW4xRnF3S09mNmFjMTJ5dFdmanZLaGhlUXNIMThBNUlJeG9zSEEwX1dSWUhqd3RfZVZoUUdZUlFzNjR1djNkN01XMk9hT2pmMzcxMlFuMDFrRzN1Nkw3dTBza1cwYWNlWXE0QUdSNmdDWXpLb1ViV1E3VHNtQWI5aExhcXNEOVowYWpRNXl0cTZIV0daamFlUjc2RkFiMFRoWHVLTFFzVmtKY3hLSEJab1I3dnRkUGc5NHpQanVHcGpWaG5Tcnc?oc=5</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>14-05-2026 01:15 UTC</t>
+          <t>14-05-2026 15:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Zydus Biotech</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Zydus Lifesciences close to buying US oncology drug maker for $100 to 150 million: Sources</t>
+          <t>Video: Samsung Galaxy A37 Review: Camera, Gaming &amp; Battery Tested!</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>Gadgets 360</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAJBVV95cUxOZFMzT1FGWXJqTWV0M3pPdm1tVlpZV0FkdWtXeGFVdXRlSUV6Y0J0QWNaM19ZNXlPdFlFMGR0R0N0cGZWUENZTGNNbUszMHlRQWJaZFhTR2pldzVlQXlLTDZmVkpxY1RhOFBDUEZ5Tjd4TjRwUzBjYmluWW1XYjFDajNuS0UyZzI5OHlwLTdrOVN4VXJsRG1laElHenRLa01EODVXQkZ1RV8zTEE5MDduUDB6S2ZXVmpTUmI1SkFULVNYOEF1QkdzZHgwNHFqQ3d4RUVCY1NhbnVuSEZRaFhKUUxjSml4SlVGMFo4S01NWnkweU9vLTRyUGRsZVMza05XcGV2SElmZFJFNkZkRUd4S1U0ZlnSAZoCQVVfeXFMTjh1N0FyT09CTGVYN1FIQjM0TjZEY1BleU5sZ0w4UkZvdm1XRllieG9HVXgwUG5kRGtkdUgySWRZS19zU1YxZmdPa1BmamhHcmFtVGpjV1ZCRXdCUEhjU0JCQm5zRkJpWS1ERmZZaUExS0Z4SXJDRlczM1NmSlFFZjJ3eWVscWVZMjhCMTVPUmd2cTFhaTBHMjJjVFVNYVVLcVQ4Z1hfMDF6cFBYbmdQNjJqUHF1NU5NQWoyZGJBaXJ4Nk96d0xvRTlxUTV3dWdlZjJxcldDaDRsbENSQ0d1bFhSVzVzYXlTakcxTzJtaXB6WGlEZVYya1RjelVSaDE1RDhoekJmRXpVbUt1eXAxT0dyZG5xYThOQmh3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPMnhPODhGTWRtUzYwdmktOVhVS1htTTFxMGxOcmRxUjc3Y1h5RnRmSHUyRGtCMW5nNHJTRmI3RHZKalN3S3JlVHdqbVNPdnh6b2tyVnhacXlqSnBtTldtb0o5bWQ0ckJMNVBOLUNPY29nYWJmUTNpOENWT3J4eU84dkFlZjBKczhhS1FNRldncDRTWWh3M3lONFhlUW0?oc=5</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>13-05-2026 12:15 UTC</t>
+          <t>14-05-2026 15:36 UTC</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Zydus Biotech</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Zydus to Acquire Assertio for $166 Million in Cash After Board Rejects Revised Garda Deal</t>
+          <t>Samsung launches One UI 9 beta for Galaxy S26 owners: Here's everything you need to know</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>citybiz</t>
+          <t>Sportskeeda Tech</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNRUU5UWxmdC0xSHRhMnF1X1J5c0FxSWpLNURHS1FBQy1TZzBwcVUwSXBBVlFaWlNjV2pKUTNSOFRuWkI3RVNxUDZZTDBuZFlObC1KWEhmSkllTk8teFkxWlVMSG10Q014RlJJU2dxeS1BUHRPVHNNNXNkMVZvSldEdjluUnJkY2JpYU5KNTliMExmcUNIeE0yTWI2RS16OHlNVnVNa3dYMjJUbktiSno4bTFXNTI4RWdraURzcUs2WVhTWHhmUnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNN3lhVFBWeDVfaENLTHM2alBJOEpEa2xaNTVkTHlmZ0c5bnZuZng4R1VGWXA4cERUVUw1ZTgxclZHR08zTE8xcW9nNThxNksxZHdoOXM4dlZySy1HYmpicmFSVWMwMk1SdHNhaGVtMnR5bzFvMmxYX1FGVDd0Y3BYUExyVEtSRGplZy01NU9zUFkxeDJpVGFFeHpqRmFrQ196dVQzZkE5MFJTZExBZDRCaVE0bw?oc=5</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>13-05-2026 12:45 UTC</t>
+          <t>14-05-2026 15:06 UTC</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Zydus Biotech</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Owkin, AstraZeneca Expand AI Drug Research Collaboration With New 3-Year Agreement</t>
+          <t>Samsung Electronics urges union to resume talks as strike threat looms</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Digital Health News</t>
+          <t>Reuters</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxOSjJnejREd2FFdF9VT3FjQzA3bFZHd1I5UjVXUkhPYlRvSHlacF8wNGZFWFdKNlVsU0NTVEY0TnliOUxuQklaODAza0Uybkk0THRZQ2kzcHB5ZzROYXdNdkhiY1U4QWptUldGeGVYUkRRWjQxVl9vQlZ5aWc3b2xiTnhxNmE0WGE0ZUQwM3FoOWJWZEktNE00bkUzLXZjRFJzWHNKXzR1Q2RyZUtUaWdIWnB1aGYzQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQaThlNEd0YTRNdGhud19mNFZjNGo4eEY5eWxCZkF1VkFQVGRzOWVOWHFRWWpiWFBVVFROZE9GeXo0VjBacTdCRzZybVpzeHpLZDFCamdOcFlNUmV6ejBmeEZ4MzdzdmVTZlhycUxTSU1RRmpZa3lpajNsY3AzcmlJOUVmTDBRcktWWURWR0NSemt3LS1aREJvUmxWcHpXa1JiZlhWUnZFVFNic0RqYXhWWnJ5akJDYXptaUlyczdkYVo?oc=5</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>14-05-2026 10:55 UTC</t>
+          <t>14-05-2026 04:04 UTC</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Zydus Biotech</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Agilent &amp; Veeda Lifesciences Strengthen Biopharma Analytics with New Facility</t>
+          <t>Samsung One UI 9 Eligible Devices: The Complete Expected List for Android 17</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Digital Health News</t>
+          <t>Nokiamob</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOaTRQVVJzQUM3M094VnB4THY2RFptWnFvQzhrNzBNY1d3aERwa3Rqak9JM3Q2cUFnV3dNODQ4VGhGbFdYVHhOdXl5ZDFQMkxFS3lTMXp5STMzek1uNTdXSXRMTU0yeDVZeWlvMUMtTS1ENEJfQmlueW1ZWUc3MUVsNVBJS0dVWlJyTTRCa2dJa2ZoS3RhQTBoNXBWUEx5WTlIQnRxTVhUR0V1al9oZnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPQUFFakNoVWx4UGpvcHVfWXowS1REUFdBVG9kUEJyWXFzTHNUU2RLOFJfQ1phWmdQRGQ1ekExa2JhQ2hnUkFQLTBtSlVQQlRzWURsbUMwQkllako4M3dHdzIwZWhxVUlCT1ZxRTdhM0hkNnY1Tm9zdjA0WEg5MnJpUEJfRlVOdFFmeWNaajBJTkVoZVpTak5tSHZXRlplWEF6TG10SGhTUTB1RXVT?oc=5</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>14-05-2026 08:43 UTC</t>
+          <t>14-05-2026 06:43 UTC</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Zydus Biotech</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>DHN - Sikkim CM Inaugurates Maxwell Hospital in Siliguri</t>
+          <t>The Samsung 55-Inch Class Crystal TV is down to its lowest-ever price — save $50 at Amazon</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Digital Health News</t>
+          <t>Mashable</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxQRlBKWnVpSUZOSm5UYUtTVTZvc1U4bXduVnR4LVM4MUtGUVJxTEw5WEhKUWhuMGNya3RTbGhKQW9yNmVYNktEd3VuWTQ4Z0JGTDdFSkZXNVVhU3pMY2h5eHBFbklIUGVxdjkycHVucFBsU1h4R0lqdEZZajR2WHRFUG5rbVBsa0c1aU0tdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTE9DMWphcTlMZElqRkpJVVZiUEFuejFyaDRITDQ0OFI5dHFxQUxFQy16X0xmREN5eWxWT3RXYmVvZzJIdURpWG4wVkFyNjlYM3JQcG1DbE12MHVGajdYV2lVVw?oc=5</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>14-05-2026 10:19 UTC</t>
+          <t>14-05-2026 10:39 UTC</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Zydus Biotech</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Rice University Expands Collaborations with India across AI, Healthcare &amp; Research</t>
+          <t>Moto Razr Fold Review: The Folding Phone That Puts Samsung On Notice</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Digital Health News</t>
+          <t>HotHardware</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNUVRDbE1CenQ0b0hkdnlVLTJBWHBIRUxoZEtEdEFWcDRBTmZlcEZudG9qZ0tudnJzUl9TMC15UGVaaGVGNlZ5dzhJdC1abGtuZkRYdXBuNU9OUE1xZU01VnhOT2lRU0xqYi03dDFMWnB0Z3NpR01PbnBuWmk2X284dENoc3U0eGppRURaV0YxTWt2VWFXbWtZQk9NelN2cEljcERLb1lWQzAxeDEyS041NklJZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNQUMzOXEzT3p1V081QWdjLWJKQy1uWnVfRGkySEVvNWpxN3Q2RHhWbjB1RDlpclgwdTM2aUVlZmRUM1hQQ1h2YktCaWw0N1h1LUlPU0s2SnZ0R0FCQlg4LVoxcGM1TlFoczdycGFEczBXNnItNkEwelViUVloeV91eVNQRlFRcUpmc0Z6NWswdTlDUQ?oc=5</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>14-05-2026 10:24 UTC</t>
+          <t>14-05-2026 13:55 UTC</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Zydus Biotech</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Volo Health Services &amp; Medix Global Partner to Advance Tech-Enabled Corporate Healthcare</t>
+          <t>Samsung Rolls Out One UI 9 Beta on the Galaxy S26 Series</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Digital Health News</t>
+          <t>extremetech.com</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxON01oeE5NZFBxRG5uRGMwV3RKRURWNWl1V2pIbHdTU3dsR3ZXX04wRVp0clpyM2ZZWDJSOUYzdG9wdnp0OUdQYm96TXBQOWlPUzBvWkVGSXVLckFwajlLZnRnMmNuc1d5bk1ZbDBrNkNrcVFIR0lyZC1lWkJsRHk4SmZNY3JFdWxmRkhhTkNpZHhPcXllT2t5azQ1U1YzdnFtZFRCZENkd1FXZm9KR1UyelJNLUVnVHRObFpYcg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPT01fNTNrSnNyU29sX3B0R3Z3WGI1blFyaDRON1lveUdVaGJiSmpDWmxibWU0RE5aRUhhOVBMeGp5T2dqVVAwajk4VjdCZmE3S196U3FqRmdqQXZ0QlllSDR2NXpSWGRiTmxCREYwM045aWs1NThGN0toNU5mWWdDNm9JNnB4MjNCMGFjQ0VlcTVCV3o4TUE?oc=5</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>14-05-2026 09:29 UTC</t>
+          <t>14-05-2026 16:45 UTC</t>
         </is>
       </c>
     </row>
@@ -4108,7 +4108,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Samsung Electronics Announces First Quarter 2026 Results</t>
+          <t>Samsung Launches Samsung AI Week 2026 for AI-Powered Living</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4118,12 +4118,12 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOWUVwY3RuMVpmN0E2LXdudkFMWjl3VjN6MWp3Vnk4VUUzTnkzdGVRNi0wWXN1MnpRODQ2c0RGWE9Wbjg5Y0RfejdZZUVjZGJGdi1GdDVCdzlzWjBNU0hQbVVtTGJab3lNakR2S1RKSzdOVTVrVDZVV0xoWU45ZFFoVjVZUDdsTTRqai0tVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQZ1hPUXdVcTd0Z09TTVhiX0NMdjJtUmJSbkhONHI1QVJwUFQzSGtYbVUyM0Zkck9NLVV4cEpqaXNSTTR0S2Jjd3NXZklHNzhueC1iU3ZZUXVhQW5kMVVzNDBBamVIUExNbHlBbmJIa2VLX2RjSXFuNnFXcEJ0QW9wWUM5MUlWanYyMGtIS1RTMmxTdDR4Q2c?oc=5</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>14-05-2026 08:20 UTC</t>
+          <t>14-05-2026 00:00 UTC</t>
         </is>
       </c>
     </row>
@@ -4135,1303 +4135,1303 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Samsung begins Android 17-based OneUI 9 beta testing for Galaxy S26 series</t>
+          <t>Samsung promises to make future home appliances even more power-efficient</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Deccan Herald</t>
+          <t>SamMobile</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPbERnM3B0YWJyNl8xRzVlZ1pCTGQwZ3FJX1dBRklob1oyMnJrcUlhMTU2U05ySFAxNjEtU2ZoZXN1UGlSTk1oSVFtbFBrMF9HeTRHZnVtSVJMdW93SzFjdDN4X2NKT1dnOHFXSGQzUDdCaWtiZnVncUFiRnpaQmxCZGVaSU93Y2xBLTZtYWxWdFNuVEdsOEVxVExJZVVQMVB6Y0IyZEZ5YWpkei1vaHZYV0JuYXJoSEY3Z0tpRHF3SQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPLXBWbmgxdm9kVHJpUDQ4Q2NZZUhRVFJsMGVnRWNRZU1xSDV6bmZmREpTOHIybWFjUExTa2FjZGpOVGh6akJfMmR2UHA4TnZfX21FTVlQT05RSzR3YzhBVFpLZ3dtV3hSSjFhMVZ5Q2x0WlpSZ2UyY2hBQnNoRXVfWmpDaFpRQXg5a2dQYmRMUTBjR3dqeFR3?oc=5</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>14-05-2026 09:30 UTC</t>
+          <t>14-05-2026 11:28 UTC</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Samsung Electronics urges union to resume talks as strike threat looms</t>
+          <t>Analysts grow more bullish on Celltrion as margin expansion gains traction</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Reuters</t>
+          <t>koreabiomed.com</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQaThlNEd0YTRNdGhud19mNFZjNGo4eEY5eWxCZkF1VkFQVGRzOWVOWHFRWWpiWFBVVFROZE9GeXo0VjBacTdCRzZybVpzeHpLZDFCamdOcFlNUmV6ejBmeEZ4MzdzdmVTZlhycUxTSU1RRmpZa3lpajNsY3AzcmlJOUVmTDBRcktWWURWR0NSemt3LS1aREJvUmxWcHpXa1JiZlhWUnZFVFNic0RqYXhWWnJ5akJDYXptaUlyczdkYVo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE0yQ0dibnJ6cVIzOWJvdDZmTG0xZ05PQ0dBMjB6UXR4dklIQzdwQVFTWVlLOTZxaHBfcFl5em04bXFlWGJwd2l0VTBTZjZzYnJYTWNxbkZSd2k4QmlydGxfbXlQR2ZEQlVjMUN4MWZ30gFyQVVfeXFMUENMM19meXJDWFNOaUVRTjFMOURncHBkUU1NLWUyWlQ1WGd3N01xV1JYeHgzZ1NYR2RoY0RwWmIzOUE2WTExM3ZneHlOYjZUd2RxQzJMMXJNd2ZhOF9sSGk1SG9RMU1ycGVPdkhTOXNjWGVR?oc=5</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>14-05-2026 04:04 UTC</t>
+          <t>14-05-2026 00:08 UTC</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Samsung Galaxy Z Fold 8, Galaxy Z Flip 8 to Launch With Google’s Gemini Intelligence Features: Report</t>
+          <t>Celltrion Inc stock (KR7068270008): US biosimilar launch and facility acquisition</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Gadgets 360</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQRHRhaS1sRmdYLXNLY1o5TktrUjdNaTd6Wkk2WE11cGYyTnVGbjNJV2MtQkRKTTJhaVRjVDlZaTMxTzB4UmtObjA2WDR3OUZ5c2lsSTNvYUk3UFY1Yl9rcnB2Z1h2TU1HZ2V1RGk1bWJuYTctdmVkOV9sWTNjOHVTbGt5QnI2SGdaZnNEN3ZsSkhXVVNXbUNWWGwxNzNldHJCaVl3LW1FRkxzYzAwakZ0dtIBtgFBVV95cUxQVDVxcl9raTVyMThDWXhSNmgtUHVtdnJ5Q0FiNDJhV3Z0SmQtdVNMbVZCeHFJcW1iVDhJcXdJemRSaUs1ZkFJOE1Qak1tOThxakJLQU9vbjNZZ1JJSXV1VUhQNUZpaklFdEdXQjlEbEVFZUpEdkZJX2hYbHNLd0ZVVFR5OVgxdnZnUnVDZVEyNy1MbFFydkVfUHhRWXRVc1JvTkNXcHZtd3dPUEUxT2o5RUo3Si02Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQak1zS2RSWk16TTlwcHRPUDdkQnhWXzRJc1JVbTNyRUM0SmdvNUhQWEs3Mno3RU9YenRKc0ZoS01sbHNzc2JlZnVSMk11ZEtQM3JJMm55dzBKR3ZRSFBYNEtROXhpQjFCMGRET1ZpNG9RODc5RG5ka3R4dEd5MVBlZ3JzcmhTQVM1R1RQcERqRjE4WHhjWXVOX21GU2FkMEw1VVZyNGZNNEg4bzhETU0xd2FfMjJ5Y0xOTFdldHNkSkFSRjA?oc=5</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>14-05-2026 08:44 UTC</t>
+          <t>14-05-2026 07:44 UTC</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Samsung updates Expert RAW app for One UI 9.0</t>
+          <t>Celltrion Widens Europe Share, Eyes Profit Beat</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>SamMobile</t>
+          <t>Businesskorea</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTFBybFN6YTd4NGZJdUNMcy0wbVdFUFhvRlJVMW5TZ2p5cjl6RWt4dVpmbnpyWW1EUzFTMEJDYTNfTWVicUR3VDZWb3RjMEIzNm5uY0w4QllIZDFLTUZXWlF2aWFUNFpSWU5paFFzU3Z2ZFRPdHY2ZURsUXdMa0RYdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTFBBanNBdGhOVVc5eUc2MjFERXNscGdMakdsc0tRZnVVdXhhN1h2YVRGX3RnYWtqN3BTdGJNelkzZkdUVi1hSllndmdRekJUYmtPOW5PSUw1TWRQU0ZrUzdacFNMWFJZOV9QN0pfV3l5VGxJYTJl?oc=5</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>14-05-2026 08:47 UTC</t>
+          <t>14-05-2026 02:49 UTC</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Samsung Launches One UI 9 Beta For Galaxy S26 Series With Enhanced Creative Tools, Security, And Accessibility</t>
+          <t>Celltrion gains 70% Europe infliximab share as SC formulations surge - CHOSUNBIZ</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>ETV Bharat</t>
+          <t>Chosunbiz</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPN0VBOXk5Y2ZROG1obkdsR3lZZ200R3VpRl8ya1h6Q0h2X3V0aVJDM2VGbzVVclVpOXFoLUhSY0VUN3dQNVFONVBmMlF0VF9XM0lvbk8xMEs1bXVfejZ5NDVpUVRwMmJYbTdKdHA5WW9maU9Yckh3LVNJa2p6ZUNiYWhyMXlyb1JCQ3pqM1kxN1JMZXpsU0lSY2ZEdlJOcFFGOTRoZUQ2elRQTWPSAbABQVVfeXFMT3VETl9VOGZ4bHBnME5Sc3FFamlXWkVINEZ4cVhqMFMwUmpiMWJHZFFjT0JUMEpfY3ZPTV9sbHRKaklTNm03MHdlcGJWSGZ1VkdIbFlxazRhRlgwdV9MWTAwWVU0ckJlb2J5U3BIck4xam5hQmItbEZZWmpWN1V2WVBVZ2NNMkdtSVdoeDZ2bmxJX1Y3YVlGd0tCODJKeW9BUkhlRHBIeVBteENUMVgyXy0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNVGRZcDRheFB2ODlMVDJWc0xINXE3bjBhRGZDYWZqZzdsbkZBbjl6cE9qR0QxR3VTVl96RnZtZ2lrbmgwTGJ6aHVSR1V3WTc0NVJYbnozUFQ3aHN1b2x2dDVFUU44dmljMVZBcG5ZY09BczZQcTlrVUhHRC0zRFllZtIBlAFBVV95cUxPQzB5ME94VGhaOXlpTk9jVW5Geno2dlZSSWNOMTZ6T1hJR2pHamNWT21CU0Nzb0lVMldNZ09yY1liVFprV3F6ZjZzS0VFaEFVSjRERjVhUHhZUVNmc1FPTkxsSlNKMDItQ0VoQ2kwR0VXcXR2bi1iTUZCWkpENU5VTXh4TFBLSzA1M2VnRjNfck5MS1RX?oc=5</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>14-05-2026 08:27 UTC</t>
+          <t>14-05-2026 00:37 UTC</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>South Korean shares notch record closing high as Samsung Electronics rallies</t>
+          <t>Biosimilars Market is expected to Hit US$ 99.3 Billion by 2033 |</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>openPR.com</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxQMGJDUXVRSV9ZUGx6djlnNlpYQ1FrTkhZLWpQbndfOUFaTnJkYW1MYXhWSlJMQzN5RlRucTBxUkdrRjVVUWU0WjdsY3lDdHNZd0dFd1FsQ2RyU0UwZExFSFRPaHFXN3ZiZGY2SUM3Y0wxQTJPdGdEWnNTYlliR3lQa1JwdEZRaGVyb2pMdHRwS3pmSTV6TnA0SEhvSm9lNEUyS0hCeTV0bS1MVmlkNVNiRGhWRm12Vkx6LTFVY3ByVmF4WHhYWjdJMkxOQ1hRMEktS18zSWJNVVRWMVFMNW93?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNWWlNWThXLUJGWjBQRVlJRExjeUlDWTB1RTlheG5WUHpPY21QN1RtSVBiNmpDdjd6RUhmX1pmQjRiYm1KTFdKenBUTUw2Y3RZbG50MENSTkIwR2JILXdRejRLZTE3TkliVzdrVHllLWpxU2tLNDJ4TTJ5bkU5MW80Z2ZXRWF3akFZSFBiTFdtZFUtN2ZieTd3ajNSaHlsZw?oc=5</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>14-05-2026 06:53 UTC</t>
+          <t>14-05-2026 10:01 UTC</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Will Samsung utilize AMOLEDs produced by BOE for its Galaxy S27 phone basic model?</t>
+          <t>Celltrion Maintains 70% Combined Market Share for Remsima in Europe... Growth Continues Across New and Existing Product Lines</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>OLED-Info</t>
+          <t>아시아경제</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPY3hkNW1iVDRBcGlBQ1U0TWg3cmY0bzFFMXJOTkpSV1REV3JNRy1RYWxHT0cycUhFWmc2S3BFMGUzS01iMHhGZlE1QXZReFY2bXpSbjduUWhhRThhaldhVXYxNWdKQThpN181c3VueU1YS21fSkJwb09lM0hzRFBHdUFXZUhIcVFwTzVSXzRic1Q2RlNRV2ozX0ZsUnQyRUllOGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE1UazFJLTA2QmlDOFRPc3FJSlJRRXdsTTM2b29SLTE1Z3h0ZFo3ZEpRN1plWGRBMXZyVS15T0EzSHpiakZZYWdGdkxjMGt4UkFrdVR6NjA3Yk5mZHNHZC1iamVleVY?oc=5</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>14-05-2026 07:44 UTC</t>
+          <t>13-05-2026 23:07 UTC</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Samsung Galaxy Book4 with Intel Core i7, 16GB RAM drops below Rs 60,000 during Flipkart sale</t>
+          <t>Celltrion Captures 70% of Europe's Infliximab Market with Remsima</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Moneycontrol.com</t>
+          <t>Seoul Economic Daily</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxPdS1ITVBlXzRLN29GVTlxY2xzVnBhY1BBNklNRFVWOGJNNXNrQXBCS0h3TnJVbnZld211Vmo2ODdlMVZheFpHTWtZRFhHdGc1dm5MRTc1X2dndi1hS2pDUTVEeThTUmVxeTZLSkVTOHFERElzenFPOXpqUEFBcUl2ZVpiUjd1MEVITW5jMExyNDQ1SmtOVHZMSVdEbFRmZW9NVU93V0lzQmF4RnJrSXJWUTJKZ1FScWliSGJiOG0xWGI0MDVxSHJnME1RNVlMaTBRLVlZZU1HRXZSUHpXaUxjeUZrWVlXbTc30gHuAUFVX3lxTFBQcFBJRGlHUlkwYWU1ZncxdWlWR2pZN3VwY2NkSDJuMngwcld0cVBVWHk3WVNPVW90UnFob050V3cwUEFPbVhZamo4STVWa1h0SkItTnZ3OGxCdWtUWDNiMFdaTmNveHREXzdHdEFYcGpkWS1KY0h1ZnhsTUF2cU90U3otcUEzSElCQ0hkM1Fnc3ZYOFAyZ2Z1R1d3UWpYVzZRV09DaVN3Skx1VGlJaGFrMFlUbkUwaHJEblNJMldGdVpVcnh5NXVGQW9ITy1WZ0lVWDRjTVRNa3MwN3IwZEhUS1dwN0k1QjZTTXNTNXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQN2JWTzhaLW5jdjZSMGIwenA3ZUo1OGxoM3QxRW1ldkltbzlIUnlVd1BLNXA0cExjVFdZV0dGUFc1WW90ZEtfUEo2ZFV1Y2FvWGlsSnp6WVJ1a2NlbEIweHY5VzJSLUtKMi16RUFSVGlMN2IxTzdaSmRjOXBsR1ZkYlFxY0tkVVNDZEtyZ200djlHcVVMNWY0Y01VTEdVdllyTlE?oc=5</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>14-05-2026 04:28 UTC</t>
+          <t>14-05-2026 00:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Samsung Android 17 Update: The One UI 9 Eligible Devices list</t>
+          <t>Alteogen weighs KOSPI move as Korea business groups urge KOSDAQ stay - CHOSUNBIZ</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Nokiamob</t>
+          <t>Chosunbiz</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPQUFFakNoVWx4UGpvcHVfWXowS1REUFdBVG9kUEJyWXFzTHNUU2RLOFJfQ1phWmdQRGQ1ekExa2JhQ2hnUkFQLTBtSlVQQlRzWURsbUMwQkllako4M3dHdzIwZWhxVUlCT1ZxRTdhM0hkNnY1Tm9zdjA0WEg5MnJpUEJfRlVOdFFmeWNaajBJTkVoZVpTak5tSHZXRlplWEF6TG10SGhTUTB1RXVT?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPXzlhX3dySzJ2WHk2VFdlc2FDTHRwYmpzdG9GOUV0V1BIbVdRTGN5YzcyYjdxYnptSFlxenBtZVJ6T0gxcXJhaEZyWFVhUkFPcllBanJTWDdRY193UXg3LTEySHk3T3RIdnU1OFJzZjlfV1FFbm9La0NWdFFIclVxRNIBlAFBVV95cUxPMUVKYk5NRGtHMi05Q3gwd1ZaSm9pUG9wWUlPR2lwUUl6NnEta1J3cXliNzhMLWxWck11eklYZzNjR1V5aE9aMExPVTFSQUJHal9uMWtSekdSQjkyU0xpSy16QWJEQVpOV09DdE42LWc0ZFpZZ2xHczJ0d2dKa0wzTG5Ha0FNNzVkOE5nQXFtdHg2WjVh?oc=5</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>14-05-2026 06:43 UTC</t>
+          <t>13-05-2026 21:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Apple iPhone Sales Spike, Courtesy iPhone 17, Outpace Overall US Market</t>
+          <t>While the government is scheduled to announce a "Korean-style sovereign wealth fund establishment pl..</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Esquire India</t>
+          <t>매일경제</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPOGNieFNZOUpBblQ0Q3g5M3o2XzExRE9kVmZ6WW8xeWVCZ0ppdkVHY21saEstX0VkS0NWYjJEMXRXSHlGcnFPRFFpR0t6M3g3S25WLVZxUDBkNE9XMTVBend0MzBJWFE2bzJibVZWRFRDSmdDVkhGeEFncFVuZ0JCc3NUbGdsM2E2ZlFUYThfWHQwWkM1WGxmT21HaE5ocXlzTnNjelQ0Q2RnQXM2NFRrLW82em1vRFMtVGdaeU1MMNIBzAFBVV95cUxPME9tN3A2WVF3d2RNU2otZU1WUm5RVWcxaG5ELTF2RVp0RUdxdVJzTjFFZjhmV3Y0cG50b2FQZmFKMW5GSV9XQTY2UnBQaTFNcUo2Vm8tRFQtQUkwX0dpajV1TkltY0VnLURSS1lQeTJ6aXdZVjdteWlIaV9YMDBoTDFwTHM0Z2hmTzg1VC0xOWZuT0d5ekxRSHdVRmNZNGFWYUc4SzcwTm5uVnBKU0hQcnhjTUktX1Y5TUozMjlkZFpJcXFLU3BEVHJsMmo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUkFVX3lxTFBKczBQckZVQVN6Rzdoc3lWblpxdkRMa0RkbThYbGxFd3NseHNyMlNnbUJMcndYa1EwT0x4eEtMQVJwMXNxamJnZ051ZTUxRUZGdXc?oc=5</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>14-05-2026 09:53 UTC</t>
+          <t>14-05-2026 08:59 UTC</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Samsung exits world's largest TV market, China</t>
+          <t>BOK chief and budget minister unite to steady prices and bolster Korea growth - CHOSUNBIZ</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>FlatpanelsHD</t>
+          <t>Chosunbiz</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE04dEd3UnFhSHh1YXRTZ0lHSkN4bVM3MG1BYk42MWp3SW9qdmdPekJHWU1TZkRJUVRHMWpuQWFfUlJCWXo4MU5SQUJtRTdNaFB3TlJEUEtmVFdBWnRzVTY3cnNiQUd0MnNNUTZhNjctcXphQllKNTB6RFV3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOWElFVDhMOElNNjVHS05VVlNkN1pabHhNeFFBZnloTTczLUhZRnp3T1RxZE85dmJuRjJZak1UbTZsSUVnOG1Zbm95cldfSWdLTlJTY1lrM2p1aFprM2kwLTZ1cGFFQTRIZnJjUENzdEtlSjV4MnZQVUJBMDVIRTQ2Sy1pcGJBZUZwTGtEaHZtRi15aXPSAZMBQVVfeXFMTlhJRVQ4TDhJTTY1R0tOVVZTZDdaWmx4TXhRQWZ5aE03My1IWUZ6d09UcWRPOXZibkYyWWpNVG02bElFZzhtWW5veXJXX0lnS05SU2NZazNqdWhaazNpMC02dXBhRUE0SGZyY1BDc3RLZUo1eDJ2UFVCQTA1SEU0NkstaXBiQWVGcExrRGh2bUYteWlz?oc=5</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>14-05-2026 07:00 UTC</t>
+          <t>14-05-2026 04:44 UTC</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Samsung Launches Samsung AI Week 2026 for AI-Powered Living</t>
+          <t>Xi warns Taiwan misstep could push U.S.-China ties toward conflict - CHOSUNBIZ</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>samsung.com</t>
+          <t>Chosunbiz</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQZ1hPUXdVcTd0Z09TTVhiX0NMdjJtUmJSbkhONHI1QVJwUFQzSGtYbVUyM0Zkck9NLVV4cEpqaXNSTTR0S2Jjd3NXZklHNzhueC1iU3ZZUXVhQW5kMVVzNDBBamVIUExNbHlBbmJIa2VLX2RjSXFuNnFXcEJ0QW9wWUM5MUlWanYyMGtIS1RTMmxTdDR4Q2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNeHJRSE40aVlLdnJiVGU3cDR1ckZOVkdBdzFwcVZjMU1kY21odnJJcjg2WkItOG4xSXZKdm5icEpBLUY2SkhSMUFpMUk1alF0YU5NZE43c1V1a0NxWDNXajhYVmlZOXZWZWVqY2pPSm5pU3hwZEtGTExKYUM2RWdxR0VrN3ZINDZ5VlZFLUF4U3p1T3hyV0FJdVd1anDSAZwBQVVfeXFMTXhyUUhONGlZS3ZyYlRlN3A0dXJGTlZHQXcxcHFWYzFNZGNtaHZySXI4NlpCLThuMUl2SnZuYnBKQS1GNkpIUjFBaTFJNWpRdGFOTWRON3NVdWtDcVgzV2o4WFZpWTl2VmVlamNqT0puaVN4cGRLRkxMSmFDNkVncUdFazd2SDQ2eVZWRS1BeFN6dU94cldBSXVXdWpw?oc=5</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>14-05-2026 00:00 UTC</t>
+          <t>14-05-2026 04:28 UTC</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Samsung Galaxy Buds Able: Clip-style open earbuds are likely on the horizon</t>
+          <t>Autopsy says South Korea elementary student died in fall at Juwangsan - CHOSUNBIZ</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Mashable</t>
+          <t>Chosunbiz</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE1CY2NCR09oTy0xbE5xcnFXTHJPZ2tTR1ZZTlNGWW83NTktWDlBamhmZ1ZsRmh6bFlPekNjZ25UZjhHWElKQXRGOEkzaUxpbUhra01qTEdkUlk0a0kzNkY3UXRqY2VCMWx1T2VyLTZXdmFsN3ctRDJfYUk3WQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOUjdILVpfSWxIRzRILWRuWlkxYXp2d3JvLVNSOU5vbElBOEtaN3FVTmR3VUNlM0ttTEttQWEtYXFNYWhLOTlaMDQ1TElBM0syTHFSNjJscmRiZTN2TnFyR0pULW85cnVyd0dxcEphbS1teXVVanEyaS10NVRWWmsyV0F5aEhLWk03c2czbEFhNEpUcFVW0gGUAUFVX3lxTE5SN0gtWl9JbEhHNEgtZG5aWTFhenZ3cm8tU1I5Tm9sSUE4S1o3cVVOZHdVQ2UzS21MS21BYS1hcU1haEs5OVowNDVMSUEzSzJMcVI2MmxyZGJlM3ZOcXJHSlQtbzlydXJ3R3FwSmFtLW15dVVqcTJpLXQ1VFZaazJXQXloSEtaTTdzZzNsQWE0SlRwVVY?oc=5</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>14-05-2026 01:21 UTC</t>
+          <t>14-05-2026 04:33 UTC</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Analysts grow more bullish on Celltrion as margin expansion gains traction</t>
+          <t>Daiichi Sankyo stock (JP3475350009): Recent correction and 4.4% gain signal volatility</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>koreabiomed.com</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE0yQ0dibnJ6cVIzOWJvdDZmTG0xZ05PQ0dBMjB6UXR4dklIQzdwQVFTWVlLOTZxaHBfcFl5em04bXFlWGJwd2l0VTBTZjZzYnJYTWNxbkZSd2k4QmlydGxfbXlQR2ZEQlVjMUN4MWZ30gFyQVVfeXFMUENMM19meXJDWFNOaUVRTjFMOURncHBkUU1NLWUyWlQ1WGd3N01xV1JYeHgzZ1NYR2RoY0RwWmIzOUE2WTExM3ZneHlOYjZUd2RxQzJMMXJNd2ZhOF9sSGk1SG9RMU1ycGVPdkhTOXNjWGVR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQTHliNVJmX1pEcVlVMjU5dFVacUNHV3F5akxPNFdYUzI1Tkt5VlVVWTMxN2VpMzNkblZWeTk3LTFnR3lpMnMyM0lYc3ZLUU13SDhEajB2bXU1RnFfV1JNMlZGVlp6emtmeGx6cFlXcC04alR0UUtYeHAwb1A0amxidUw2d25DMDdON2tYR2MtWjEzZkRWdWh0WWprZm9vMmRITjB1dU9qY0sxbFA5QThKMEdXMkQ3YkM0cHNjR0NENDU0clhy?oc=5</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>14-05-2026 00:08 UTC</t>
+          <t>14-05-2026 05:50 UTC</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Celltrion Inc stock (KR7068270008): US biosimilar launch and facility acquisition</t>
+          <t>Daiichi Sankyo Company, Limited Just Missed EPS By 12%: Here's What Analysts Think Will Happen Next</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQak1zS2RSWk16TTlwcHRPUDdkQnhWXzRJc1JVbTNyRUM0SmdvNUhQWEs3Mno3RU9YenRKc0ZoS01sbHNzc2JlZnVSMk11ZEtQM3JJMm55dzBKR3ZRSFBYNEtROXhpQjFCMGRET1ZpNG9RODc5RG5ka3R4dEd5MVBlZ3JzcmhTQVM1R1RQcERqRjE4WHhjWXVOX21GU2FkMEw1VVZyNGZNNEg4bzhETU0xd2FfMjJ5Y0xOTFdldHNkSkFSRjA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxQdGNfQ216Njlpdk5XdUJRUVhSVmV6Q0E2b3VpbHV5SW4ybUlJUmZvb1hDRDFlYXkzOUE2dzI0WUhzT3QzWU9mQ1lJMkZtRXhVV2hXR3FBM0oxY0JmWkhySUtEaDMteXBoNHhPaDNqM0tIeU96ZzlkOXRMczZBaUNRSUcwUFJKTWx5MERxb3k5SHdhSEQtUTlKZGpEeE1odFZGOUJ0dEJWQkVKc3pDVW4yQjZORXZpUzROdHpzdkhaRkpNaWppOUlXNEIyQ2xvX240WTVMM2J3a0JQaDg0RmNGY2dBeG1IZknSAewBQVVfeXFMTVAybGZncmNSSFFlcVZXcHUya19NV0tDczZWT3FZX0V4TzJ0b1J0Vm4xX2ZNLVlkSWJoSjdodl9UUkVXRHlvUWlFM0VFSUNrNm5RYkRKYWM1aEFZa2JxWVl1TmRVblllQm9LUGwyZGl1eDdZeERDRWxJYkRBNFpVYUl3bVpPMHlqMGV1eFZiTE5DRnFsSVZheUhhQzJYR19MczFzRldPVkhvWTdmclFoTVV5YWtyNUhEajhiRzFyVlh2RDF2N1gzOGxKYzZIaDQ2WFFnV2pNeTMwR3B5bzZ1R3ZmZEh2dXpVU2pvZGo?oc=5</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>14-05-2026 07:44 UTC</t>
+          <t>14-05-2026 00:09 UTC</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Celltrion Widens Europe Share, Eyes Profit Beat</t>
+          <t>Pharmaceutical waste: What do I do with it?</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Businesskorea</t>
+          <t>Cleanroom Technology</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTFBBanNBdGhOVVc5eUc2MjFERXNscGdMakdsc0tRZnVVdXhhN1h2YVRGX3RnYWtqN3BTdGJNelkzZkdUVi1hSllndmdRekJUYmtPOW5PSUw1TWRQU0ZrUzdacFNMWFJZOV9QN0pfV3l5VGxJYTJl?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxQVjBUTDdvZU52dkJoTUgxZnVPNF9mbm9GMXVrQl81LTFidXVfTThJRTgxNVlQNFlhaEFMcjNJem9xOHh5R3drTGlubDZ0S3Y3Q0VsOWlPWm5XQnN2MUxJWkJqdFRsbHJyYW5idHlmS3VUVVpxSXAxZHFaZmljbi15UWdUbw?oc=5</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>14-05-2026 02:49 UTC</t>
+          <t>14-05-2026 08:18 UTC</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Biosimilars Market is expected to Hit US$ 99.3 Billion by 2033 |</t>
+          <t>CAR T Therapy Targets Residual HER2 Mutant NSCLC After TKI</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>openPR.com</t>
+          <t>Clinical Oncology News</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNWWlNWThXLUJGWjBQRVlJRExjeUlDWTB1RTlheG5WUHpPY21QN1RtSVBiNmpDdjd6RUhmX1pmQjRiYm1KTFdKenBUTUw2Y3RZbG50MENSTkIwR2JILXdRejRLZTE3TkliVzdrVHllLWpxU2tLNDJ4TTJ5bkU5MW80Z2ZXRWF3akFZSFBiTFdtZFUtN2ZieTd3ajNSaHlsZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPdDJoM2NSaV9jTU82VzRlYVBJaUdxQkQ5Y2hTV0VEanE1aUsxY1BOSXZoUW9NX0dVNE8wb1dUZmI4dk1odlNxTVlsaEpoRUxLSW5iT2IyM1NkMlhSdFN0SmdXVXRoYkJzTzFwTldzc0lQSzIwSGxUUkJ1Yk1JbnRDNEJreFNRWDVOS0RzazVDTXB2dDZ1LTRxczJlZWtXZzFxc1ZRcFVLcWZIUGp0N0RyakFvMGc2eUVlb05VRXh1UlM?oc=5</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>14-05-2026 10:01 UTC</t>
+          <t>14-05-2026 16:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Celltrion gains 70% Europe infliximab share as SC formulations surge - CHOSUNBIZ</t>
+          <t>Omron's AI unit hunts for rare diseases in data on 50m Japanese patients</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Chosunbiz</t>
+          <t>Nikkei Asia</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNVGRZcDRheFB2ODlMVDJWc0xINXE3bjBhRGZDYWZqZzdsbkZBbjl6cE9qR0QxR3VTVl96RnZtZ2lrbmgwTGJ6aHVSR1V3WTc0NVJYbnozUFQ3aHN1b2x2dDVFUU44dmljMVZBcG5ZY09BczZQcTlrVUhHRC0zRFllZtIBlAFBVV95cUxPQzB5ME94VGhaOXlpTk9jVW5Geno2dlZSSWNOMTZ6T1hJR2pHamNWT21CU0Nzb0lVMldNZ09yY1liVFprV3F6ZjZzS0VFaEFVSjRERjVhUHhZUVNmc1FPTkxsSlNKMDItQ0VoQ2kwR0VXcXR2bi1iTUZCWkpENU5VTXh4TFBLSzA1M2VnRjNfck5MS1RX?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOakFUOWdXYnd3aUttZmlZUFBfMTZWcHFxU2EySVotYWFPUXR5dGl3cHIxaTNwUzNwTTdmMm4xbkZFLWR4LVpSMzVzOTdhTzZjbzlYSmRJYzVBODhCeFUzd3ZUX05tdEltOVhrMkNJai1BbmxNOVRlM1hNS2VGaUNoSHJCQ2JncHVoWG05emJzdDluNVUzR0dmQ2xTcjNLaGt4M25Zbmk3ckdIRE1PLWdVZG5rWUgwVzkwM0RWYnJYMnBRMWRfSTdhSDZpaWJJV1BmaXVkRVVfcw?oc=5</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>14-05-2026 00:37 UTC</t>
+          <t>14-05-2026 13:11 UTC</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Celltrion Maintains 70% Combined Market Share for Remsima in Europe... Growth Continues Across New and Existing Product Lines</t>
+          <t>Qol Holdings Delivers Record Sales and Profit on Strong Pharma and Pharmacy Operations</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>아시아경제</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE15b1VjaGRENHJOaVpyc0ozaDhwbTdJbGl1Q3FnQnBpVjFNbE1ET3p1YTNhcS1EeTk1QmlBTi1yZ1dNSFZtNHJ2MU9NQzRZZW5DOHRIZUJDWks3NkhuamlWNDFhenVSMVhieXBMN0VSUlpqRDg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNUXNOdFl5cjI0NzZZOS1jOVBKUTBSNllJdEFGZ3FzYllEYVZ0My1tNm9fQ3ZYalJGYzlYdERNZEpuOHBnOF9ITjZVaG92Qmx5Z3FZRURNd1ktcjdfQ2pDeUZjaHVxQU5EOVVtSUZ3clY0bVFHcFh3bWk0eXhkNXlzaktsVUc4QWFzT0F3Q3BOenZ4M1YtMHp1VmRGbHp4eWUzc3FKWGtnOGhmanBaVk5zQnJZNVFHX2R5OXdyT3lMZV85Ql8zRGZZMHcxa2dqUncySE1EZw?oc=5</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>13-05-2026 23:07 UTC</t>
+          <t>14-05-2026 10:49 UTC</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Celltrion Captures 70% of Europe's Infliximab Market with Remsima</t>
+          <t>Bora inks $122.5M takeover of MacroGenics facility to further US expansion</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Seoul Economic Daily</t>
+          <t>BioSpace</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQN2JWTzhaLW5jdjZSMGIwenA3ZUo1OGxoM3QxRW1ldkltbzlIUnlVd1BLNXA0cExjVFdZV0dGUFc1WW90ZEtfUEo2ZFV1Y2FvWGlsSnp6WVJ1a2NlbEIweHY5VzJSLUtKMi16RUFSVGlMN2IxTzdaSmRjOXBsR1ZkYlFxY0tkVVNDZEtyZ200djlHcVVMNWY0Y01VTEdVdllyTlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOOWVlXzdZUWNhVnR6RnFDMjM5VnA0TDFpTHVzUTdwZGt1bXJhNENFWWV1NlpDdi1jRTUyeDQ5ZWVQYWhZYUpuazc1MFJyYy03Rk9LTW82elhONGR3cnVHRXRtMENhdnZBbGxPTUlOREpxUmJJRUZicE9QcTQtdHljM3Fpa2ZOSE15QzRwNFh5TkJHaGJNNEFLNklINUJqbUZYSWRVUVFzMA?oc=5</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>14-05-2026 00:30 UTC</t>
+          <t>13-05-2026 18:36 UTC</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Kyowa Kirin</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Alteogen weighs KOSPI move as Korea business groups urge KOSDAQ stay - CHOSUNBIZ</t>
+          <t>Kyowa Kirin Co Ltd stock (JP3249600002): CRYSVITA gains reimbursement in Canada</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Chosunbiz</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPXzlhX3dySzJ2WHk2VFdlc2FDTHRwYmpzdG9GOUV0V1BIbVdRTGN5YzcyYjdxYnptSFlxenBtZVJ6T0gxcXJhaEZyWFVhUkFPcllBanJTWDdRY193UXg3LTEySHk3T3RIdnU1OFJzZjlfV1FFbm9La0NWdFFIclVxRNIBlAFBVV95cUxPMUVKYk5NRGtHMi05Q3gwd1ZaSm9pUG9wWUlPR2lwUUl6NnEta1J3cXliNzhMLWxWck11eklYZzNjR1V5aE9aMExPVTFSQUJHal9uMWtSekdSQjkyU0xpSy16QWJEQVpOV09DdE42LWc0ZFpZZ2xHczJ0d2dKa0wzTG5Ha0FNNzVkOE5nQXFtdHg2WjVh?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQdXRkLU9IZlFabEo3WGgxZW9kN3VNbVhGOFVfQlJkSDIxcEMzR2RQa00xN2ZrYkpTeUZyTl94b0dKWDUwaUJiV2RHLUE5bWo0TDNNNlgwaDlacm1qN0txdmF2a3hMa3RpX1p2dGRFSmFrZjFwQ1lheENOd01uZGNjQVN0eG5oQm9waVgzTFpmZjRPRlROdUlXaDBBMGRyWDJYZHM4dGR0SXNVMnhmYV9QMXdvMl9iZk9VXzlsNm00TXVFZ0EweW1R?oc=5</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>13-05-2026 21:00 UTC</t>
+          <t>14-05-2026 07:08 UTC</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Kyowa Kirin</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Singer Yu Yeol confronts canceled lung transplants after mother's death</t>
+          <t>A Look At Kyowa Kirin (TSE:4151) Valuation After Positive KOMET-007 Leukemia Trial Update</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Chosunbiz</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNVHZmazNzTVFYY09tSDJEMVlZeHFDNkEzSFlZV29EWTJqNGYzU1lra0RPVG9BdkJ1cDh0Zlp4dXBrZ1NtVDVlN1JyRkRHNFlTRzA3akc5TEcxSWpTUlFhTXNmemc3a0Z1WGZXakUyWGxQN3A3d3NoeUZueEo1aVluNmNrc25Zdm5ORExVYlkxS2ludWRnTHZZSlNGM2M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQX0NBd05OVXhfUlk5eWQ1NEhyM2kxdzdnZmRwRWhVRWxPRU9WOW5ic01ySVNmR3dWdUxncExPQktXNGtrMV9mQ09rQkkzRXNIb2RMblhpZXRPZlFMUkQ1MmZUSEJNWVl2VS1zN1Q5U1c3bEFqUzYyYVNBWWFhMExscUdJMUVFSl9TaEc3bVhTNGtncFpIb0ZCQ1FHeE1Pa2VvdDh2U3lXdXk0bk1oTkZNeWJkdWJVaHBwZHFjMzlxLVhua1pwREtDV3I3ZE0tdklOSlR5WDh1cHdsdTVZTjY4N1V0NWQydnRq0gHoAUFVX3lxTFBfQ0F3Tk5VeF9SWTl5ZDU0SHIzaTF3N2dmZHBFaFVFbE9FT1Y5bmJzTXJJU2ZHd1Z1TGdwTE9CS1c0a2sxX2ZDT2tCSTNFc0hvZExuWGlldE9mUUxSRDUyZlRIQk1ZWXZVLXM3VDlTVzdsQWpTNjJhU0FZYWEwTGxxR0kxRUVKX1NoRzdtWFM0a2dwWkhvRkJDUUd4TU9rZW90OHZTeVd1eTRuTWhORk15YmR1YlVocHBkcWMzOXEtWG5rWnBES0NXcjdkTS12SU5KVHlYOHVwd2x1NVlONjg3VXQ1ZDJ2dGo?oc=5</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>13-05-2026 13:29 UTC</t>
+          <t>14-05-2026 04:27 UTC</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Kyowa Kirin</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>While the government is scheduled to announce a "Korean-style sovereign wealth fund establishment pl..</t>
+          <t>FDA Approves New Dosing Option for CRYSVITA® (burosumab-twza) in Adults With XLH</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>매일경제</t>
+          <t>The Manila Times</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUkFVX3lxTFBKczBQckZVQVN6Rzdoc3lWblpxdkRMa0RkbThYbGxFd3NseHNyMlNnbUJMcndYa1EwT0x4eEtMQVJwMXNxamJnZ051ZTUxRUZGdXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxOSEhpdmsxTmFDMTljSWxndzBxYmhRZGlEV1NWYks4cXdPd0hZWk5vbEsxQ3FCOW1odkNMR2dlQmFFUjFrTWJHN2dmVzUwTDRfNWUxQ3B0b3RhRGRCTXFaLXFKQ1cxdmJQWmtyaHVCRUxGQmZrTExSNWQxRUtMb1V2dmVNWGdfZm8ydWRYaEtJSzNKQVpqVDJYN0prV25wZnZIUUpmcDlDV0dkazUwWXZsMnZyakR2eGVSdkg0NHczQUNLdlp6QmhfMWxYbmk3am1wY2RUREo0bWx6b2d5cFlpTlJPcGZTQdIB6wFBVV95cUxQdUdsclVGdlQyM01NWHdLQ3JlTFJxbUNQRzBsTFVWNmQzekdyRllndGlpX3B0eTItNzhwUkVfcm56NkV5bVpTeWRuUDM2Qm5EVFVlU2lxS0pyTlRqUGRiSm9hczN3UTNqcUFYMWdnOWZNcEJMa1BhSGhfdkQ4Z215b3p0TW5wNXdxeHpiUFRFNnJCaWM2ZmFEZU1Ha3ROanpRYXR2bmpERTFiamNzNzhnbVFyWFpEWnlMQ1Y4Qk84Rmo2eFcxZG1meFFWbXlnRVVaYVdJcHlGNGVWY3Nocm5GQktFd2lvczFSUjdR?oc=5</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>14-05-2026 08:59 UTC</t>
+          <t>14-05-2026 12:35 UTC</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Kyowa Kirin</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Energy surge drives US producer prices to biggest gain since 2022 - CHOSUNBIZ</t>
+          <t>FDA approves expanded dosing for Crysvita in adult XLH patients By Investing.com</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Chosunbiz</t>
+          <t>Investing.com Australia</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxORk5kVEJDUDQtSmJpVjA2S3B5X2Rkb09LZVBqbVdfVzh5bmlSR21URzFBdkV1bXplS1VuMjFhOG1xY0JMMWtFb3I0T3VKQm9pYlRZa2hiMVdEdjd2YW56S0k4Y1poRnhuM0VKX3BsT2ZETzNIcHN1cTF0YkFwOUtLaDl5WEVJNWdhc3FFQVoyTUprZlRsLTl4T2dMNTLSAZwBQVVfeXFMTkZOZFRCQ1A0LUpiaVYwNktweV9kZG9PS2VQam1XX1c4eW5pUkdtVEcxQXZFdW16ZUtVbjIxYThtcWNCTDFrRW9yNE91SkJvaWJUWWtoYjFXRHY3dmFuektJOGNaaEZ4bjNFSl9wbE9mRE8zSHBzdXExdGJBcDlLS2g5eVhFSTVnYXNxRUFaMk1Ka2ZUbC05eE9nTDUy?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxOX280QzBKd0ZIT2VRMldlaEM2Y3lIWXc0X1oxVGpqNGRtSElUZEMxaHdSMW55dGdVU2gxR2ZlbV9DUXZjSnNMZEdaU2R6eWJaT2Fya1BpSE9xMHd1ZE4zVTNvczNOMW12dTNyQmpteTVfY2ZPQUFyY0VyaG9aQUoxck1OZXRfeC01bkN3V0FyRlZFNHNWclVxZ3NlTnE1T3JfekpLWnNacjFOaEp5OTdObjlyOEJKdTVHNkV4MVdqWktlSUt3ZjhaZXZUX0RfVl9RT2c?oc=5</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>13-05-2026 13:21 UTC</t>
+          <t>14-05-2026 12:39 UTC</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Kyowa Kirin</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>BOK chief and budget minister unite to steady prices and bolster Korea growth - CHOSUNBIZ</t>
+          <t>Fda approves new dosing option for Crysvita® (burosumab-twza) in adults with XLH</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Chosunbiz</t>
+          <t>marketscreener.com</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOWElFVDhMOElNNjVHS05VVlNkN1pabHhNeFFBZnloTTczLUhZRnp3T1RxZE85dmJuRjJZak1UbTZsSUVnOG1Zbm95cldfSWdLTlJTY1lrM2p1aFprM2kwLTZ1cGFFQTRIZnJjUENzdEtlSjV4MnZQVUJBMDVIRTQ2Sy1pcGJBZUZwTGtEaHZtRi15aXPSAZMBQVVfeXFMTlhJRVQ4TDhJTTY1R0tOVVZTZDdaWmx4TXhRQWZ5aE03My1IWUZ6d09UcWRPOXZibkYyWWpNVG02bElFZzhtWW5veXJXX0lnS05SU2NZazNqdWhaazNpMC02dXBhRUE0SGZyY1BDc3RLZUo1eDJ2UFVCQTA1SEU0NkstaXBiQWVGcExrRGh2bUYteWlz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPTW5WOHdPa2M4RDZ3bW5ac0k5enhsY2lHWkM4b2U2RkxzdVNiNG1uUEhxWG1ZQm1SMU1lWGotSGhybTNMNk5LVlhaR2JxUkI5SjZjVXZUWFBFclVfcHdYdGh6VHE2Zk1vd3hXSFBMMkh2LWNDdlFDZmxRVGVlSkJXUjhqSFNucmxMbWVyc0d1bFIzV0o5ZHJsckR5dEtncjBNZUJER0txUmY1TDdoSkZ1OXRNMHpFcTZ6R3c5cVBMTjhtVGlaLXRKM1F3?oc=5</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>14-05-2026 04:44 UTC</t>
+          <t>14-05-2026 13:07 UTC</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Kyowa Kirin</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Xi warns Taiwan misstep could push U.S.-China ties toward conflict - CHOSUNBIZ</t>
+          <t>Kura Oncology (KURA) Receives a Buy from Barclays</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Chosunbiz</t>
+          <t>The Globe and Mail</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNeHJRSE40aVlLdnJiVGU3cDR1ckZOVkdBdzFwcVZjMU1kY21odnJJcjg2WkItOG4xSXZKdm5icEpBLUY2SkhSMUFpMUk1alF0YU5NZE43c1V1a0NxWDNXajhYVmlZOXZWZWVqY2pPSm5pU3hwZEtGTExKYUM2RWdxR0VrN3ZINDZ5VlZFLUF4U3p1T3hyV0FJdVd1anDSAZwBQVVfeXFMTXhyUUhONGlZS3ZyYlRlN3A0dXJGTlZHQXcxcHFWYzFNZGNtaHZySXI4NlpCLThuMUl2SnZuYnBKQS1GNkpIUjFBaTFJNWpRdGFOTWRON3NVdWtDcVgzV2o4WFZpWTl2VmVlamNqT0puaVN4cGRLRkxMSmFDNkVncUdFazd2SDQ2eVZWRS1BeFN6dU94cldBSXVXdWpw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQeHF4bHlNUTZFWXMxUThPSF9hY1ZqWHc1RTJOTFQ2dlZ2WmVFSGdYSDNBSDI5bExlcENURU1VX0JpOHNNZjVHVzkyaGJXcDZ4V3NNTDFnYm5NT1ZicVdSWnB2TnQ0MlBCMTNzQlFCTHQtMXpfZW9SREEteW5xMWxIeDYxR21yT2h5X29YamF1dzRTM2JZcnBkQkNKSFBqUkwtQ2hlVzhlVHRXZEJ4X3VZeW9PMlhLTTR0WVltSzZka2tqNUV4Y3F3?oc=5</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>14-05-2026 04:28 UTC</t>
+          <t>14-05-2026 09:12 UTC</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Kyowa Kirin</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Autopsy says South Korea elementary student died in fall at Juwangsan - CHOSUNBIZ</t>
+          <t>Kyocera ECOSYS Printers: Durable Laser Printing Solution</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Chosunbiz</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOUjdILVpfSWxIRzRILWRuWlkxYXp2d3JvLVNSOU5vbElBOEtaN3FVTmR3VUNlM0ttTEttQWEtYXFNYWhLOTlaMDQ1TElBM0syTHFSNjJscmRiZTN2TnFyR0pULW85cnVyd0dxcEphbS1teXVVanEyaS10NVRWWmsyV0F5aEhLWk03c2czbEFhNEpUcFVW0gGUAUFVX3lxTE5SN0gtWl9JbEhHNEgtZG5aWTFhenZ3cm8tU1I5Tm9sSUE4S1o3cVVOZHdVQ2UzS21MS21BYS1hcU1haEs5OVowNDVMSUEzSzJMcVI2MmxyZGJlM3ZOcXJHSlQtbzlydXJ3R3FwSmFtLW15dVVqcTJpLXQ1VFZaazJXQXloSEtaTTdzZzNsQWE0SlRwVVY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOQW5PT1VfdzBYUmg0eWY3WU9Rc1JydGFqTW9lQU5CVjJKT0w4WFlOd1hfT1FRazFUU2ExVnNpc2h1SW02Z1E3YWpWTUUxalN2MW5DdFExMEQ1ZU1SbWJOdmRKWC1ocDlXbXVPbmo3dFIxVGpoa3lpM3lSX092R29FemRWME51bzg1c2FwYzU0X3hyaVdQM2lQbzFWWWYycmVQcG5QZ2tNanBDcmZFTEtvVXdCclU?oc=5</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>14-05-2026 04:33 UTC</t>
+          <t>14-05-2026 11:32 UTC</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>JCR Pharma</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Singer Yoo Yeol credits South Korean donor father after surviving cardiac arrest</t>
+          <t>Biogen's Alzheimer’s drug fails to meet mid-stage trial goal</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Chosunbiz</t>
+          <t>AOL.com</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPZkxERGc2ZzFYc1kyMEpHYldzLXd4VEl4UjZ3ZXZUSzVFSEtHU2lxU1NDRE5RSGRLYW1Zd00yUVVnckNoaHE1YnNpRjNGTXRKak9ITWhQTm5pT3lIRnVjZmZSMFNIOFotM2VSZWlGTXVNVWVUOHpFYUc2NXpDNTc3Q19EdTJUQU5uMDhSRjQ4V2NNTDJBX1E5Y3FtUU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPMklKdzZ4Zk9wdTY0UnJwQlVNUHVCc2R0eHo4WUFwWmhsMjVRaEZsX010VjkyX3JfejRNSFB1RTlvODMxUUlLSjFlZ01Cd0xqbS1DYUpNRUI2bWJVRkYwazRQV1Q5YXd6UUdhUFpyVFJaVkNVNDlRQ1NWdnh1TWNMVEpZWQ?oc=5</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>13-05-2026 13:42 UTC</t>
+          <t>14-05-2026 11:45 UTC</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Kidswell Bio</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo Company, Limited Just Missed EPS By 12%: Here's What Analysts Think Will Happen Next</t>
+          <t>Kidswell Bio Swings to Consolidated Loss Despite Higher Sales, Targets Return to Profit</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>simplywall.st</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxQdGNfQ216Njlpdk5XdUJRUVhSVmV6Q0E2b3VpbHV5SW4ybUlJUmZvb1hDRDFlYXkzOUE2dzI0WUhzT3QzWU9mQ1lJMkZtRXhVV2hXR3FBM0oxY0JmWkhySUtEaDMteXBoNHhPaDNqM0tIeU96ZzlkOXRMczZBaUNRSUcwUFJKTWx5MERxb3k5SHdhSEQtUTlKZGpEeE1odFZGOUJ0dEJWQkVKc3pDVW4yQjZORXZpUzROdHpzdkhaRkpNaWppOUlXNEIyQ2xvX240WTVMM2J3a0JQaDg0RmNGY2dBeG1IZknSAewBQVVfeXFMTVAybGZncmNSSFFlcVZXcHUya19NV0tDczZWT3FZX0V4TzJ0b1J0Vm4xX2ZNLVlkSWJoSjdodl9UUkVXRHlvUWlFM0VFSUNrNm5RYkRKYWM1aEFZa2JxWVl1TmRVblllQm9LUGwyZGl1eDdZeERDRWxJYkRBNFpVYUl3bVpPMHlqMGV1eFZiTE5DRnFsSVZheUhhQzJYR19MczFzRldPVkhvWTdmclFoTVV5YWtyNUhEajhiRzFyVlh2RDF2N1gzOGxKYzZIaDQ2WFFnV2pNeTMwR3B5bzZ1R3ZmZEh2dXpVU2pvZGo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxOcnQxdEx2dlV1WVVYcXJHR3B4cE1MN0dibUI3NGx1clhUeGpSUWFEUzZZTHVXSDQ3WGVKNGpMUkZiLWF4V1N3N1d4eVRPUWp5ZUxjQmplR09vWThzYUlrRC1EOUFSSUs1RDc2MHg4YXBfc1BoVUJTVFgxc1ctaGxSWmJqemIwQmFJWG5WZkhJQnlPODBnV21JSWpXQ0pHMmU3VVhDNkozejdXZ0RMUXVqLUQtMnFZTEtGVnJuczVCbEhEM0dXenBTQXQ1MVhCQUxTYWwtZA?oc=5</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>14-05-2026 00:09 UTC</t>
+          <t>14-05-2026 10:38 UTC</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Kidswell Bio</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo stock (JP3475350009): Recent correction and 4.4% gain signal volatility</t>
+          <t>Kidswell Bio Outlines FY2025 Results and Strategy in Biosimilars and Cell Therapy</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQTHliNVJmX1pEcVlVMjU5dFVacUNHV3F5akxPNFdYUzI1Tkt5VlVVWTMxN2VpMzNkblZWeTk3LTFnR3lpMnMyM0lYc3ZLUU13SDhEajB2bXU1RnFfV1JNMlZGVlp6emtmeGx6cFlXcC04alR0UUtYeHAwb1A0amxidUw2d25DMDdON2tYR2MtWjEzZkRWdWh0WWprZm9vMmRITjB1dU9qY0sxbFA5QThKMEdXMkQ3YkM0cHNjR0NENDU0clhy?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPY25aMkVsYm9CYjNLR0ZoaTNMZG1RTzF6M2phWHRpTnNrUlNQQ0toQTNoV0YwRXhDT01JakZMZk5ZNU4xOWxzUGRuaWJBdnN6QW9aeGdUY2szM2Q5NUNKS2RqSkhibEZ1dG1fOGNnM1dPN1pNeWpXZ1ZPbHVncE9YaVFDbVliM2JmLW9ZS1pMaF9nUWdjaXhmbGJWQklHaGlRMllwNW4xNEk4MTVqVGwtaEZiQ0NoeUMwaUM3andIOUhQdVNqUWMzN01xekhlZw?oc=5</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>14-05-2026 05:50 UTC</t>
+          <t>14-05-2026 09:33 UTC</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Mochida Pharmaceutical</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Pharmaceutical waste: What do I do with it?</t>
+          <t>Mochida Pharmaceutical stock (JP3778400006): Japanese pharma expands generic portfolio</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Cleanroom Technology</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxQVjBUTDdvZU52dkJoTUgxZnVPNF9mbm9GMXVrQl81LTFidXVfTThJRTgxNVlQNFlhaEFMcjNJem9xOHh5R3drTGlubDZ0S3Y3Q0VsOWlPWm5XQnN2MUxJWkJqdFRsbHJyYW5idHlmS3VUVVpxSXAxZHFaZmljbi15UWdUbw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQZ3B6LVM1ZWdkVS14d1R0eDJmczM2WTRneXdWbUdWWTc4RVd3TXNPRkxWUVJob0Z0Qmx3aTNLUzIzaTNyOGxkLVdxVzVzQXhaWXJGZk9LTDVfLVVrampvOTBKNzB6REFUUlRyTTlVTDF2Z3pXMm14VHdsVWVCLVpydVh1ay1zZ1lIQWJSQ2d5TmJhbm9tLVpxZnZZdmhod3dGelhXc21FNFlRa2hpN21UdElUVU5ZcmNZZG4xVDVqOTZUZw?oc=5</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>14-05-2026 08:18 UTC</t>
+          <t>14-05-2026 12:14 UTC</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Bora inks $122.5M takeover of MacroGenics facility to further US expansion</t>
+          <t>Fresenius SE &amp; Co. KGaA stock (DE0005785604): restructuring progress and earnings in focus</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>BioSpace</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOOWVlXzdZUWNhVnR6RnFDMjM5VnA0TDFpTHVzUTdwZGt1bXJhNENFWWV1NlpDdi1jRTUyeDQ5ZWVQYWhZYUpuazc1MFJyYy03Rk9LTW82elhONGR3cnVHRXRtMENhdnZBbGxPTUlOREpxUmJJRUZicE9QcTQtdHljM3Fpa2ZOSE15QzRwNFh5TkJHaGJNNEFLNklINUJqbUZYSWRVUVFzMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPTE9hVmhmZTlUZ19vMkNWZDBlc2pBUzFrNGlCbHpTSGFpckVJTjBkWG00U092eGVrS0Z6NEpSWWE4OHBnVUNZUEJMQm9wTEZhdXBRZHRkXzRfUmtCdDc2RDlsMjZBVEg3czBlTmk3REZseHFmUlE2b1VXdmJYQnBDbi0tZ2x4SzFKTGd4U1NMMTBhcHZlbGI0cHVNSFZ2NTRWb3hkc1drM0tDTlFzTXBFWHBpVEp5YTZ4LTZucmZ2a1FaeFE?oc=5</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>13-05-2026 18:36 UTC</t>
+          <t>13-05-2026 20:55 UTC</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Qol Holdings Delivers Record Sales and Profit on Strong Pharma and Pharmacy Operations</t>
+          <t>Bombay HC Grants Passing Off Relief In 'OCTRIDE' vs 'OTIDE' Pharma Trademark Dispute Despite Bar On...</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>Live Law</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNUXNOdFl5cjI0NzZZOS1jOVBKUTBSNllJdEFGZ3FzYllEYVZ0My1tNm9fQ3ZYalJGYzlYdERNZEpuOHBnOF9ITjZVaG92Qmx5Z3FZRURNd1ktcjdfQ2pDeUZjaHVxQU5EOVVtSUZ3clY0bVFHcFh3bWk0eXhkNXlzaktsVUc4QWFzT0F3Q3BOenZ4M1YtMHp1VmRGbHp4eWUzc3FKWGtnOGhmanBaVk5zQnJZNVFHX2R5OXdyT3lMZV85Ql8zRGZZMHcxa2dqUncySE1EZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxOWTRmLV9GRl9SdWNHR2xxZUl2b2hSOEEzMEdJa0l6WmR2bW1kY0UzcGpHbUh6WVJYdTdiWC1sMS05MEJnMUZPSHlkS3ZHekU1NTRWNUlLUnZlbjRIQzR1UEplR0tyTGpYcE8yZTlseWtoWkZ0ODNRUmphYm5pRHpENU9FZUpTcW1aakJvNVRWNTZfWF83RHFiNDltM3FDRWhRd0x1d0ZYUllSZHBFNVNqV0o4cl9PRmZHR1dBMWZ0NTI1alp2TG0zeGY0Q2xJRHBNX0wxUmxhaHJnMGFJNUxHYVEyWW5VNXpYRk1GMGJTTGR3cDY0NTBVTXBPWUdCZ9IB_gFBVV95cUxOWTRmLV9GRl9SdWNHR2xxZUl2b2hSOEEzMEdJa0l6WmR2bW1kY0UzcGpHbUh6WVJYdTdiWC1sMS05MEJnMUZPSHlkS3ZHekU1NTRWNUlLUnZlbjRIQzR1UEplR0tyTGpYcE8yZTlseWtoWkZ0ODNRUmphYm5pRHpENU9FZUpTcW1aakJvNVRWNTZfWF83RHFiNDltM3FDRWhRd0x1d0ZYUllSZHBFNVNqV0o4cl9PRmZHR1dBMWZ0NTI1alp2TG0zeGY0Q2xJRHBNX0wxUmxhaHJnMGFJNUxHYVEyWW5VNXpYRk1GMGJTTGR3cDY0NTBVTXBPWUdCZw?oc=5</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>14-05-2026 10:49 UTC</t>
+          <t>14-05-2026 09:13 UTC</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Elabscience® Launches Self-Developed PolyHRP-Streptavidin Conjugate for Low-Abundance Biomarker Detection in ELISA</t>
+          <t>Pharma Quality Excellence Awards focus on building robust quality practices</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Thailand Business News</t>
+          <t>Pharmabiz.com</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxNREU3R2theVR1QzNzZG1haUJZXzFjYjRNQl85Z3NJRVNNaENseVdQQnU0TEpKZmJId2hDV2JVTHBNNUplVFZaZW9iTk9GbHRhLVRWUi0xR0ZnUk9EYnE5cVlKckFXOXh1SlNfYm1kekJvbURySHI5NGU4MGRHSmNrWVJvWlhMSnBBYkRuMnFfS2UzRHl6VjdwQXFMbDY3bGJ3M3pQdjNLQkFscV9uQXVUb1N5WmdNbG1LdFFndzJ1UXFzM3BORHpoNHpKTkdTX2VUMnBJWmU0NFh6LWFqV2NhZFQyUUZyV1h0cDR5ODBTSTZHUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTFBPWlJIbzJMVFdvTVRCTFN5b19ON2dsaFBPZ3RlOWx5MVZ5UEo3bURoblE4RjdpekNHRDFuWFZhVUo0akh0U0ZJNkEzSUFsR0FPWTQ5ZGNNVnZzbDNsYUJja2ZkZjVSTU9SUU1z?oc=5</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>13-05-2026 16:33 UTC</t>
+          <t>14-05-2026 12:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Esperion Announces Two New Analyses Supporting Bempedoic Acid to Reduce LDL-C Levels to be Presented at the European Atherosclerosis Society (EAS) Congress 2026</t>
+          <t>Gland Pharma Limited Reappointment of Ms. Naina Lal Kidwai as Independent Director</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>The Manila Times</t>
+          <t>InvestyWise</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gJBVV95cUxPaFBHVkJRMVppb0NwOGdRZDNsLVNTR003Q2lZZlU0WERjbXZSYXN6bXVpSUJmM3VqZkRwdXJ6YW5CUnBGZGtmRmN6ZHpodnl5NEZtNlJ6WXlXYURsR1p3UjhGNFNpVmxkMkhHRjNmdXFEcElXbXdrQThGZE5RMXBrb0VaSnBKaVJHU090RnlEa0hmQUxYeHFmRHQ4YmxJYlRTdVlDV0xFdXVNT0ZwYTZubjdqTDZucnhrRnpUa1BsZDlUeHY4cnM1eExsM3RaYmswNExsTGt6aWVPeTFLLV9wbTJzZ25BUnV2OHJkOTJOaU9tYUhiS3V1ejBNLXVpb1NUYl9rV0o0RVZQZ0hFRzVRUnNzd3pPTlRfZjR4YjVtbmFyZkNHVW51N2tESktKTnlITWxMVDlHMF9zcmZVYW9jVmFiSGtjeEdnX25wZXpwYWEtd9IB1wJBVV95cUxPVlBXQ3BqakVJVk9udC1JT3VUc2tPSHBwTVR1RDNRdTNzRWRfU2ZOV0JXMXJldFFIVGxvRHlQaURlb0xtLTRFRXVYYWpBQ2JDQy1FSm1sR3U5V1kxdTJNU09LZ0QtODVKaDA5R3dEQ1JaZ19VVWRpaHd3bE1Pa3cxVzZxbHFKWjJOZl9ZQWpsX3ZpS3k5d3I4enFPWUx5YmRSR3hiV0E5akxocEhUSXJIdWFvRnhPalJtMVhIZGYxTE1ENi1nempZRkg4QVhPWVI0WkQybWZ4dl9HRGczLVJ3OHFrZjRnRE1YSWotOFhKT3RHeHlEdW96U0FtNk93SWVqaXlvV0ZPMDgwREZOUVJmWEMtYjhjd3pkM1dhcWI5S0hzenhuQ2tvOHZsNmhZN28xRklISkxORDhSS3hYeU9yYWN6SWdJRlFSa1cwZzZPaFFoZUk2Uy04?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQaWhLMEZLRzRCTnpZZm9PMWJnZUZ0ZU1nVWxuOGRYWEpVLVo5X0cyVmQzVzVOTUg0dndpdGJ3bGdTTzRXbzJ3NmY2R3lZUmlZRHFlblRuR3RTNmdib1lpSWpZc25FbmtXNzVPazNxWG8tb1RKVHIycGpGNGd1MXVXZ3BpQ00xcGtGbW9fVmF3cm0?oc=5</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>13-05-2026 12:19 UTC</t>
+          <t>14-05-2026 13:04 UTC</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>AstraZeneca plc stock (GB0009895292): Global pharma leader with strong oncology pipeline</t>
+          <t>Cantex taps Headlamp Health's agentic AI to shine light on MS responders</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>FirstWord Pharma</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQM3lQQ2V2M1dZdkd6M2FWOHhES1I5S1o0WWtIai1SSnFiZ0FBaFQxdkN2azE5MFAxQTRwcDZkTmxnckRpQnBiSE5pQjh4SnRSMGV4MmY1RWxzNzlUUlJQUWhWbU1KQXVqSlYtNi11SmhRUVpfOVgyc29sdnNrOFA5NFlzX0gzVHpyRHhuRlNEMlRLdV9xX1JDdS1iMlJfQ0FETU5CSlpWZVQ4ZkhvT3M4bU1NbTNlUUc0dV9NY0RSd3c3ODZp?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTE9HRUdxSml1THF2SXJkSjVsaDRSR3R4a1ZqM1ZibDYwTXh1eWJtWVBYcnlDZzkzVEJ4cWVhZ0o1dVRHbmZTaFhaVEdidFczUEs1cXQ4?oc=5</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>13-05-2026 16:44 UTC</t>
+          <t>13-05-2026 19:15 UTC</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Kyowa Kirin Co Ltd stock (JP3249600002): CRYSVITA gains reimbursement in Canada</t>
+          <t>J-Pharma Books Over JPY 1 Billion in AMED Grant Income for MS Drug R&amp;D</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQdXRkLU9IZlFabEo3WGgxZW9kN3VNbVhGOFVfQlJkSDIxcEMzR2RQa00xN2ZrYkpTeUZyTl94b0dKWDUwaUJiV2RHLUE5bWo0TDNNNlgwaDlacm1qN0txdmF2a3hMa3RpX1p2dGRFSmFrZjFwQ1lheENOd01uZGNjQVN0eG5oQm9waVgzTFpmZjRPRlROdUlXaDBBMGRyWDJYZHM4dGR0SXNVMnhmYV9QMXdvMl9iZk9VXzlsNm00TXVFZ0EweW1R?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQUzNjcXhjT3dTenpwYWtJWXRsVW1pQTRRZUt5a0F5YXFPdnFvMXhhM25tNzZaRHJBbzdOVG9GQzVrYW4xalg1ZDFwZ1JlMFlWTlJjM1E2cU9IQWZaRlhseV9lUWtXWjJNNXFMN1BrMThuWU5iNXBuLXJ2TDM2d0NCT1hHWk9oSzJ0ZFBFdmMwUkNBZHhiZUNFY255OVZLWUVtaUczeU84Tl9meDQwaUgtWWFOVGx4V3pySUdxckR3?oc=5</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>14-05-2026 07:08 UTC</t>
+          <t>14-05-2026 09:52 UTC</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>A Look At Kyowa Kirin (TSE:4151) Valuation After Positive KOMET-007 Leukemia Trial Update</t>
+          <t>Hopewell Holdings Ltd stock (HK0054000679): Wins key US patent challenge against Merck</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>simplywall.st</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQX0NBd05OVXhfUlk5eWQ1NEhyM2kxdzdnZmRwRWhVRWxPRU9WOW5ic01ySVNmR3dWdUxncExPQktXNGtrMV9mQ09rQkkzRXNIb2RMblhpZXRPZlFMUkQ1MmZUSEJNWVl2VS1zN1Q5U1c3bEFqUzYyYVNBWWFhMExscUdJMUVFSl9TaEc3bVhTNGtncFpIb0ZCQ1FHeE1Pa2VvdDh2U3lXdXk0bk1oTkZNeWJkdWJVaHBwZHFjMzlxLVhua1pwREtDV3I3ZE0tdklOSlR5WDh1cHdsdTVZTjY4N1V0NWQydnRq0gHoAUFVX3lxTFBfQ0F3Tk5VeF9SWTl5ZDU0SHIzaTF3N2dmZHBFaFVFbE9FT1Y5bmJzTXJJU2ZHd1Z1TGdwTE9CS1c0a2sxX2ZDT2tCSTNFc0hvZExuWGlldE9mUUxSRDUyZlRIQk1ZWXZVLXM3VDlTVzdsQWpTNjJhU0FZYWEwTGxxR0kxRUVKX1NoRzdtWFM0a2dwWkhvRkJDUUd4TU9rZW90OHZTeVd1eTRuTWhORk15YmR1YlVocHBkcWMzOXEtWG5rWnBES0NXcjdkTS12SU5KVHlYOHVwd2x1NVlONjg3VXQ1ZDJ2dGo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQMlJPd2lDZmhwOWt4Y2QzOXhVQnRNMXcxMlk3clpvbHZ0aVZEQ3V4dnhpZHB1X0FObE5ZTUtjeW5vY3cweG11WEJ1T19jQzlSZDJWUzlqMXkxNlZFYjVnbldPMWt1OGlFeXNtTUEtdHFZdk5odU5UNm5PdXNrdFlkNm80dnBXVGtIMVpjbWk5X3RvSlliUlN6OVBLUEtOSFB3Umg3cTU0WDVJanFkUVNjYkpaLWl0TEZtSWxyNlpsNFpXallJeHFn?oc=5</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>14-05-2026 04:27 UTC</t>
+          <t>14-05-2026 09:02 UTC</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Presentation Material with ScriptPDF: 984KBPDFファイルをダウンロードする</t>
+          <t>Why CAR T Cells are 'Living Drugs' That Grow Inside You</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>marketscreener.com</t>
+          <t>BioPharm International</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPZmxZSHVBUjVnQW5BTVFMQm5oVGVRMWhmTW80ckdub1RNNjA0X3hDOEU2am52VGc5TkJyYWt0YWZuSnJZWUpqQ3Y4d1BnaVd6WWNaY1M0NFNYMHBUcE52TWtSMmw1Q2hNTTFOU3l3Nlc3VEtnQUs4OXZBVGM1aG1xaE5LQkVNOU5YbXRCWkRQOHpvYXV0QzVONVplUnczQU5kbkhIczJsZDNiWXdET1VFM01JMkFkWWpZeVI2c250NHE2Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxObF9KSE1ZalJTS2w2dWo2TzFhUzNIVnhZQ3lHT082WlE3eGVUMWtOZGYxQkY1NWFkaER2LXo0cDdIMVNYZXpyNGFWcDVFdFJjajVmVmhZRXJzLUlvaDY1NGFFeG5fYTEwUVJlLXllTXlKbnNyMmFHT2xBUVByOERZX240RFM2QXNHQ01BT253MzlfRFhXTVExV3NoSHJMOVE?oc=5</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>14-05-2026 08:30 UTC</t>
+          <t>13-05-2026 20:42 UTC</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Kura Oncology (KURA) Receives a Buy from Barclays</t>
+          <t>Sun Pharma Schedules Q4FY26 Results Announcement and Earnings Call for 22 May 2026</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>The Globe and Mail</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQeHF4bHlNUTZFWXMxUThPSF9hY1ZqWHc1RTJOTFQ2dlZ2WmVFSGdYSDNBSDI5bExlcENURU1VX0JpOHNNZjVHVzkyaGJXcDZ4V3NNTDFnYm5NT1ZicVdSWnB2TnQ0MlBCMTNzQlFCTHQtMXpfZW9SREEteW5xMWxIeDYxR21yT2h5X29YamF1dzRTM2JZcnBkQkNKSFBqUkwtQ2hlVzhlVHRXZEJ4X3VZeW9PMlhLTTR0WVltSzZka2tqNUV4Y3F3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxNNnhzZ1Q0ZVZjc2N3eG1xamtaNGJmR1M4QUpvXzFHOHZJTFJKTTcwTjhqYkYybWZQYTY4d3g5UUY1VzZTVW5vRDdxM1AyZS05NDZQc2FUUzA3WGtCZzlRUVpNVThsLUstUTRFV2RMakEwQ3g1b3JFZHZqWUJPRkE2eDlnLUlfZEItbWdKc2s3czNPRGJxNEdaa0hzdzUxV3BQWTZpZVBKdEdreHNxbzVnbG9EbkcwbmRld25iWjhrVVk1SXhleWtjVnhNTE1yNHhWSG40elpR?oc=5</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>14-05-2026 09:12 UTC</t>
+          <t>14-05-2026 01:41 UTC</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim licenses Immunitas antibody program</t>
+          <t>BioHarvest Sciences Appoints New Head of Business Development for its CDMO Division</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>BioWorld News</t>
+          <t>TMX Newsfile</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOUGEyY2M3azJacGxKSUdtWlhSTHFhRVlCczJpd0hNeEp6UGdtTzl3anQwaUpCVHRQb0VDazkyYTk0ZmExLVl6bzBXOFZ4TlBHRkU1ODU4RXpNT2Z6czRhOVFkVVN2M1lpUXJNdVJ5OXE5WmhGRzFCbzJlVlRVRkhyYnNmVzBvNG5xYXBaY2xicXNzQkhzQ0RqWEctU1RDdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxObkhmS00xVEVla3FHT2kxbjQ5eS1XLWdHYy1BLUFZRnVUVklla1B5NHV2TmViUnd3QkdhZXJLR3BNdGJFRHVlN1VaQUdiM2ZQeGtUcW9jeWxzcW1PYTZqejBlTjh4VEpnTHZQUEpBQ2RTMmxkbVZoanQ2bmhLREdnUjduRGNpd01tR2pGSFFwVzBITm5vTlBTZVVMN2hJUkZYR3FpUzJhV1Q0YU5GWGVZREx2aklmQjVIUC1HZWpJaGhuT1dUQXc?oc=5</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>13-05-2026 13:00 UTC</t>
+          <t>13-05-2026 21:32 UTC</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Kura Oncology Earnings Call Highlights Comzifty Momentum</t>
+          <t>Vanda: A Long-Term Pharma Growth Idea, Despite Q1 Earnings Miss (NASDAQ:VNDA)</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>Seeking Alpha</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQbGttbWItSTktMlNUemZ0WFlXTnpaNmZCSjVWWUktSnZTV2JDQm52U3JGbDVOZU5zS0tYelV2QXB2QW5SMk9reTdtT3FDcW0xaFpGZUVWT2h5ZklKTnJpWjJwN2RvWkt3YjR1ci1NYmI3MXhZY2p0ZFdrb1EzVWxuZS02c2VpZXdKV09idzFpdHJUUk1INnhqXzAzbjAyWkdXd2VIbWFYYU9GTlFU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNcFFPS0ZjVW56SlY3dy1VWEM3ZmdBWThpU3JVVjVWWmxzdTlwaE05SnlUQzFWSU1oWTNWQnZFT2NFR2ZjTXlqOW1wODZMbzRSMURmb19nU3VTT0NDZVdObGFHbWZxemVuZGJWZ1BBNzdERWJRNkdOcGt6TTI2aS1iOFNIQll6WkFTMngtaWV0TFItN0ZOWnRXc25LUDc3XzNfSndNMUU3eU9mQQ?oc=5</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>14-05-2026 00:28 UTC</t>
+          <t>13-05-2026 17:34 UTC</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Prevent Blindness to Hold 3rd ASPECT Patient Engagement Summit and Legislative Advocacy Day, June 7-10</t>
+          <t>Indian pharma fuels Africa’s ‘zombie drug’ and opioid crisis</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>InvisionMag.com</t>
+          <t>The Straits Times</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNdXJ4MjNQYVFyMHd1VlBRaG9LdTBmdnlBV2hDUlQxTVk1R09rci1HTjBQdWNFdUlMNWpvU3dwa3dZN1lGdGo2bXJYUkpSSjhmMlNraGwzNm9TWU1rZVhPSTQ2VVJUd0pxNGhmQWY1b0RuX0FCQllkaVN1eUxhQUpoV2dvQldkQUg1RW9mZWRqWlUzLXF4cFdMLU5XWlo2YWNLMFMxV0kzZWxwZVAydGFLX01EWkxKYy1hUm5kektFOElrMlpk0gHKAUFVX3lxTE00amItVWtTTHVjMXBqT2U0SWhLcGJQcUllOHc0bHhqM3Z6YzltZm4wY1M5SGpheVNzV0t5cVNIRlZGMC15Y1U5eExhZXU4SUxCQ2JFVHlLSkZ3enliVnVDZEpPZkotX3dvRnFRYXZUNGhoSWdFWVRwSWJpZ0NrMU9zWVhVYVMyOHI0ZzN4TnZ4VC1hZVZsN0RoeW16MVp1elpuWmdad0drMXJVaFhQTUh4RWRORXAtaGhPM0Y4eHRpWnFORkRHU0ExWGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOUTVkNnQxLWJFZkFidzlBV0dLNGIwc0FlWGdhamFBTGxkM08wS1hnY0pfTWdZdkdIbXN4VkpnaDc4THJ4UmNmWkM0cUVjVlhzblJBY29NeVJZWEVXeEVZUm5fUEZYZWlqR3QzMXVLQVRHNGR4Q0NHU09idU1TbEE0WlB2VXFHNW9XUVBVc0pwYXJiZ3ZYNElr?oc=5</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>13-05-2026 21:03 UTC</t>
+          <t>14-05-2026 02:05 UTC</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>JCR Pharma</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Acumen Pharmaceuticals Reports Q1 2026 Results: Full Earnings Call Transcript</t>
+          <t>She closed $30M in drug contracts; now she’ll hunt CDMO deals for BioHarvest</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Sahm</t>
+          <t>Stock Titan</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOWXBwak9wem9QMnlWTWNsLTJ0SVQtNzRublJGOUdwb094V2hIN0JMUUlnMTRmdF9CUmxTbUhzVWpqVW1YOGJZU0tyMGxXOEpfTDd4bUhSdDVlWFZIaGZhUThMdW96T2pwbEE3WGtfTFJZUnpNSXA5UmpYQ19oUmNXS2tyeWszYkRoazlmYS1jUnNIVDJjU2RTR29fNmxicDBnVFpvUFNSU3NWOUtzT2FReHFGa2FMNFhQMkJFa0pwc19JbExqRUhr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNaW55V0hkRHdOOVlKRXdJc3JwWDlEd1FSTlVxUjI5dXVTNFREakhxaTAxR2hBNnphM1Z4Qzc2emlHZkFOZURyM1VKdW52MTdSaGZ3dTFVZ2puNFl1Y2ZSbXljU05QVzBBQXpHc1ZxZlNnVGRlVWpDUzZBVzNYaWxpaFViTjIyTGx1VTdGc1dvOW9hM3RReEhLamxyQWNCXzdFMHUwS0JDMDM3Tzh4WXJDZ3NMOTJPSmY2SzZPUDln?oc=5</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>13-05-2026 14:37 UTC</t>
+          <t>13-05-2026 21:32 UTC</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>JCR Pharma</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>New option available for Alzheimer’s patients as FDA approves expanded drug use</t>
+          <t>aTyr Pharma to Participate in Upcoming Investor Conferences</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>AOL.com</t>
+          <t>The Manila Times</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxObG54TFZBYy03Q2NOd3k2SHdIVkI3LWxSSENoNTFtUk9BZ1EzUUl4Uk9HUGRtMmt5R01rX2VfdU96SmdxVUZwSm93eGdNMDFoMmJ1OE9xeUxuNE51YjIta1BuZjJjRXhvUlMxNTBkZHhwQXFQcEdfX0laZ3lqZEEzMHRKcFFCWi12OFNF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPbGFHNEt6T0d3MzNxNzFVdHQwOWJWcnhkTkJheWRUNGlVZmUydENVSVBMeFFGbUZvMm9MTk9DVnVtRTJ1aE9vLWtRa2JfX1M3UmVUNktiMUlxZG9NSF96NnFHUTRFSUFVX0F6LTdHakl1T1U5aEkxUVIxODJ1RkVXRlQ3b3lkT1E4YVNIV3hpYWJBY05KeDlXOVJpQVBWMXljMEcyQlNyV2FXd3ByMnJuRF94MnplcG4yMDhHNXc1UHl1VlA4SXM0MElhUDFSd9IB0wFBVV95cUxOOUsyeGktb2ZBVzhSdnlucVZtZy1sMUozOTkyNUYwRUg0R1N1ek4zMXJnZ2hHUEd1NGUwanRvelI1TW1HYnVGa0gtRWM3WkYyTGJsT1Q1Q3RoUUZWMExyUkE0di1rUGFXZnpCSHlodVBYUGNQMnJPc0hjOVlDVDlfa2FzbGM4ZERqTnJ2R1FPazBKclN2elZiR3RrMW9OMjd0U0c0WVZrMXFvVFFyazJJWjhSSXBtOTlGYXoxdnRCN0ZJY3NYSzdCaG54b1lTUUdPQ2hz?oc=5</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>13-05-2026 17:41 UTC</t>
+          <t>13-05-2026 20:13 UTC</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Kidswell Bio</t>
+          <t>Alvotech</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Kidswell Bio Outlines FY2025 Results and Strategy in Biosimilars and Cell Therapy</t>
+          <t>Alvotech Plans June FDA Resubmissions, Sees Biosimilar Approvals by Year-End</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPY25aMkVsYm9CYjNLR0ZoaTNMZG1RTzF6M2phWHRpTnNrUlNQQ0toQTNoV0YwRXhDT01JakZMZk5ZNU4xOWxzUGRuaWJBdnN6QW9aeGdUY2szM2Q5NUNKS2RqSkhibEZ1dG1fOGNnM1dPN1pNeWpXZ1ZPbHVncE9YaVFDbVliM2JmLW9ZS1pMaF9nUWdjaXhmbGJWQklHaGlRMllwNW4xNEk4MTVqVGwtaEZiQ0NoeUMwaUM3andIOUhQdVNqUWMzN01xekhlZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQbXI2eF9aMkdCalNMcnY3UDdUblR5TjdQYzlnaVhRcTlNcjk4WFpTbzNFUVJUcko2c3JuUVJoYmlhZnJIVDBodllqMEdMOE80dTlMWDVyMmJ2M0dqS0ZtQWZXNGJZbWNpRHdzaVZkZ25GQVVGanBHbmxqYmt6OFlqVVRBSU1NTUdmMjNfVTdNSGF1azVUcUplb3JidUQyQWU5QzVLRzYzSjB0Zw?oc=5</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>14-05-2026 09:33 UTC</t>
+          <t>14-05-2026 00:13 UTC</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Fresenius SE &amp; Co. KGaA stock (DE0005785604): Global healthcare leader with US exposure</t>
+          <t>Wall Street Thinks Teva Stock Still Has Room to Run After Soaring Over 100%. Here's Why Analysts Are Right.</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>The Motley Fool</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPMmdZbjl6dm13cE5HTXRPRXhha0ZlU0g2Z3lCdTlLaW1uZ0lRaW44eUp2bTBGT1RQTC0zd3NqRHdUR2ZCNmk2S053MmtGNWc3LWY5TUNVYWF3TnB5bzNnQzR5c2RDS0xEU1lkYmtVY3JEQzZvcU41WUZPWmpROFRETnI4RXllQVlTTjVWOVVOa3l2YUQtbXNlX0pURU5DTXFuVy01QUlJeUtnbGNCaU9mY0VQbjlYTHQxNVljOHVfVkFiWDFOZVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQQU1xNHU3R1JfbWI5S2NMX3F3TG9xQVVRNG9qQlFTS1hJNWE4WHV4blByS19PeU12dGJCR0paQmluX2Rad09mWUlRR0hraGQwTFgxb2JuZEJvWGpDY1o2a1Z1RHVxRnpIbU5OSWFvOVhoZF9XRjNEUm55UVNKR2ZFNmMxTHAzUlBHVldCeGxJWUt3dW14YUlCdg?oc=5</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>13-05-2026 16:54 UTC</t>
+          <t>14-05-2026 09:56 UTC</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>[Latest] Global Intravenous (IV) Fluid Bags Market Size/Share Worth USD 5.46 Billion by 2035 at a 6.8% CAGR: Healthcare Foresights (Analysis, Outlook, Leaders, Report, Trends, Forecast, Segmentation, Growth Rate, Value, SWOT Analysis)</t>
+          <t>How Investors May Respond To Teva (TEVA) Showcasing CNS Growth And Emalex Deal At Key Conferences</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Yahoo Finance Singapore</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNV3hjUDMtVkEtOFJZbnI2MG5nb004U21kZ0tlODVPaVBhenBjVldsRU1OTVdRT3gwcnN2aWtlWlhEMERtRnhwV3A4SW8yQlc5SmtWZG1uVnN6WDJMOXhrTWQ5WGg0R013QWRxOHk2RmFkMlNFVVJjdlY1anIySmtONmdDb0Vrd29ySlVJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxPV3BNcHg0aFZzcGFfdzdhU2g3dHBEckEybW84bFFMdlpWNU1SSU80elhhSmFzc3NEXzhSUGRwcHdzSnA5bkpndmRWUzhtRDVpYklDTzh6aEZXUUMyYjZrZlVNNWZEMGZEcVhKVmFYZTFKQUVnQlMwOUhVZ1dYZ1NxSmNDa0pNdmY3NGpQLUFSbkVIQno3RzBLOTVBN3RLSXFvSm1iM2g3dldsaVBZYWtmWWJzak5KdlZXdUptTkJwekQ5WjJsbV9OVktURTd0akd2QVg0QlBRd1k3QURZLWJrN1drclgxdjROQWd0NkdaUlBhOXFf0gH6AUFVX3lxTFAwZ3VlbG5lZnlZUVkwU2kxN1Y1aFZmcmcwRE9ndllOWUczcjlEWmdjdk5mcnJSZzBoRDFvUGZWdUVJYmQ1VnNRUk9BZldyTTdtd01oUU1vRFdKc21adE55ZHRjYXk4Q2xCb0c1ZEhNdFZNLVNwdVZTSWxVTnJqb2ZBdWhYMGs0RW05NloyMXZiajFuekJJNzFLblBxRlVWVmtSTE9OZ1hKZktub0VMd0VHdHpseHBaTUF1bWJjWVlkYzZYUUR4U0pUSmhMNUxlZTBMMS1nX1Vic1NrTngza29ybkNVTzlBWEE1R2FoT2lRQXZwQXZZbEVIRnc?oc=5</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>13-05-2026 12:30 UTC</t>
+          <t>14-05-2026 05:52 UTC</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Fresenius SE &amp; Co. KGaA stock (DE0005785604): restructuring progress and earnings in focus</t>
+          <t>Teva Pharmaceutical stock (US88162G1031): Beats Q1 2026 earnings with CNS growth</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -5441,795 +5441,228 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPTE9hVmhmZTlUZ19vMkNWZDBlc2pBUzFrNGlCbHpTSGFpckVJTjBkWG00U092eGVrS0Z6NEpSWWE4OHBnVUNZUEJMQm9wTEZhdXBRZHRkXzRfUmtCdDc2RDlsMjZBVEg3czBlTmk3REZseHFmUlE2b1VXdmJYQnBDbi0tZ2x4SzFKTGd4U1NMMTBhcHZlbGI0cHVNSFZ2NTRWb3hkc1drM0tDTlFzTXBFWHBpVEp5YTZ4LTZucmZ2a1FaeFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNUGo5OG0ydHRxdmFXZlRSQUFtemZOY0RxaUZCWWlhamkyR3ZXaTkzb0lxRnltWUYxaFJuN2ZNNG9QaHVHTExyZzZhdVNOTW1tenFlZmhyQVhDbUtaUVNRb3lraS1tbnplalVzaURadHZDVC1BTlJ1Qk0tMWFlT2tYSnh4M084OTRoWFlnNkd2QkhRWktMNE9sdGVxRkdQTmlOa1hoaGlEMWpOQXlzU1lYZ1p6UWU0SUNyTjVhQU8xR0hHQzBDdGtwdw?oc=5</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>13-05-2026 20:55 UTC</t>
+          <t>14-05-2026 10:46 UTC</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Fresenius SE &amp; Co. KGaA stock (DE0005785604): Global healthcare giant with US dialysis exposure</t>
+          <t>Wall Street Thinks Teva Stock Still Has Room to Run After Soaring Over 100%. Here's Why Analysts Are Right.</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNVG9ONVlRU0JFdGMwWnl6Z3NVQXRUMjZ0VmQyd29udC1RSWdOd09RNUxCOFllMHBFR29qLUJidGZ3Z3ROalhvcEZVWWhWV2h1Umd2ODMzcDk4TkxKWGdObTFBNTNKVDltdjdacjdCWW1fbjBpNF9wLS0wenZsV3FOaGNySnF2dDdvQkFXcTM5VXl0UWktVUkybU11MzVLdDNhbmU4alhHVTRWTHZuNWQxSU1kWkYtOTJRczBfNWQtSTZFTjdo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQOXhTUlhTTl95cTR2QmY1ZV8tVmZsSmszRFhjRzBOZEtRaG5TdFppd3JtamRtbGpSN2xFc3JST0FKbV9rUHFTcnJDeHprUEFfR0I0WlFYTzROc29fRE9OanQ0SDFWaW9TTTMxbmE3NzFYR3ZtWnNOQkRmRmdpbUJwM2JRb25kSDhRY3BTbVBhc1pSdkJsRFEyTTVB?oc=5</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>13-05-2026 14:25 UTC</t>
+          <t>14-05-2026 09:16 UTC</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Bombay HC Grants Passing Off Relief In 'OCTRIDE' vs 'OTIDE' Pharma Trademark Dispute Despite Bar On...</t>
+          <t>Wall Street Thinks Teva Stock Still Has Room to Run After Soaring Over 100%. Here's Why Analysts Are Right.</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Live Law</t>
+          <t>AOL.com</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxOWTRmLV9GRl9SdWNHR2xxZUl2b2hSOEEzMEdJa0l6WmR2bW1kY0UzcGpHbUh6WVJYdTdiWC1sMS05MEJnMUZPSHlkS3ZHekU1NTRWNUlLUnZlbjRIQzR1UEplR0tyTGpYcE8yZTlseWtoWkZ0ODNRUmphYm5pRHpENU9FZUpTcW1aakJvNVRWNTZfWF83RHFiNDltM3FDRWhRd0x1d0ZYUllSZHBFNVNqV0o4cl9PRmZHR1dBMWZ0NTI1alp2TG0zeGY0Q2xJRHBNX0wxUmxhaHJnMGFJNUxHYVEyWW5VNXpYRk1GMGJTTGR3cDY0NTBVTXBPWUdCZ9IB_gFBVV95cUxOWTRmLV9GRl9SdWNHR2xxZUl2b2hSOEEzMEdJa0l6WmR2bW1kY0UzcGpHbUh6WVJYdTdiWC1sMS05MEJnMUZPSHlkS3ZHekU1NTRWNUlLUnZlbjRIQzR1UEplR0tyTGpYcE8yZTlseWtoWkZ0ODNRUmphYm5pRHpENU9FZUpTcW1aakJvNVRWNTZfWF83RHFiNDltM3FDRWhRd0x1d0ZYUllSZHBFNVNqV0o4cl9PRmZHR1dBMWZ0NTI1alp2TG0zeGY0Q2xJRHBNX0wxUmxhaHJnMGFJNUxHYVEyWW5VNXpYRk1GMGJTTGR3cDY0NTBVTXBPWUdCZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1PUnRSaWM1eHlQWVpzbG40T2JxZkNkd0c2Ykl4aDY0WkZSUTUxYWhQN2pGMnpJSng4akZNYnZpTkd4dTR5VWtOcl9sNU15VFp6aTNucDcxemhtajhzc250ekRXazVla1FmWWh3QUdsWUJKY0ZZQnpQelU0MmgyZw?oc=5</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>14-05-2026 09:13 UTC</t>
+          <t>14-05-2026 11:17 UTC</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Cantex taps Headlamp Health's agentic AI to shine light on MS responders</t>
+          <t>When ‘low profile’ is ‘high valuation’: Soma Das</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>FirstWord Pharma</t>
+          <t>Business Today</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTE9HRUdxSml1THF2SXJkSjVsaDRSR3R4a1ZqM1ZibDYwTXh1eWJtWVBYcnlDZzkzVEJ4cWVhZ0o1dVRHbmZTaFhaVEdidFczUEs1cXQ4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQeVkxZlcwNGlmZmU0SUpxMm41OVpjMEdKZWNRakJSeUJQZlNrZjA1WnBFUDBNdDM4UVVMXzYwSFZWX0k5TmhRQjFLclVlRTRrQmp2ZUVoTG15N3BoZzJ0dmZUdnlLR1dKRk9jdmtEeE9MNUJOdV82U2VQblhHSFo1OXBTSmQxbTRjcHdHTFV4bmEyQ2p2ZnMtQVJGemM5N2U4SUlXekpCZjNsVFY3RnItU0RYc9IBuAFBVV95cUxPcVZ2dUszemFtejMwSnR5MzRtaGtEX1hkRUVVWVg2enVWQjVUTHB1YWhnWU9lUjVzQ0duLUNQcGZheXZjRG9sQ0I2QUZ4R0tacnVnODdITER4NUlJdEdiNG0yODdjQnhRcTBGQnkzcXdIY0d5RmtmckdrV3hUMG5GeGozWHg4Z0Zqd2Yyd0VTRUpjNTlyd1JNV0NaUVVJRmIwa3FNcTFTUjRRWS1nb29TWU1Qc0hTbE04?oc=5</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>13-05-2026 19:15 UTC</t>
+          <t>14-05-2026 09:15 UTC</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Sun Pharma Schedules Q4FY26 Results Announcement and Earnings Call for 22 May 2026</t>
+          <t>Mylan Epoprostenol Win Clarifies US Measurement Rules And Equivalents Limits</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>Citeline News &amp; Insights</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxNNnhzZ1Q0ZVZjc2N3eG1xamtaNGJmR1M4QUpvXzFHOHZJTFJKTTcwTjhqYkYybWZQYTY4d3g5UUY1VzZTVW5vRDdxM1AyZS05NDZQc2FUUzA3WGtCZzlRUVpNVThsLUstUTRFV2RMakEwQ3g1b3JFZHZqWUJPRkE2eDlnLUlfZEItbWdKc2s3czNPRGJxNEdaa0hzdzUxV3BQWTZpZVBKdEdreHNxbzVnbG9EbkcwbmRld25iWjhrVVk1SXhleWtjVnhNTE1yNHhWSG40elpR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxPbHM4VWQtSndIMzVDaVlsc3BjdWdqTDFvaTdUMWFPQzhSYjdTdlEyUnNJSkt2WnprQVNhd1dPYWdMYXlUOV9xYnQ5Y2xyeHk0ZERUX3dvSEM4cG1YNTd2ejFkSDhhcEo2V000cGhCd0lWUmdWTVZZd0hYUjdkbUVtUWRlc2NrVDRiOG41UXZjaHp4TjYzTDQwbFF4dmdndzdxMkpoVUtJcWRDZS1vdlAxRWQ4U19aWGt6RW14cmt0cnhFUFYxQ2ZfbFdlQW9la3pMNUVYbUYydXJuMTNLV29mQVJydjJWUzJmdVNITElTSlFJVmhpOHc?oc=5</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>14-05-2026 01:41 UTC</t>
+          <t>14-05-2026 12:50 UTC</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Samsung Bioepis</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Solving Complexity in Modern Biopharma Analytics</t>
+          <t>Samsung Epis Holdings earns MSCI ‘AA’ ESG rating in 1st global assessment</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>BioPharm International</t>
+          <t>koreabiomed.com</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNeHJwNkZzRFMweG5UX2J1cXoxdDBOOW9heUxVUHNuZk9feFFTOU1PR3J4THJZdHlqX1VIMnhqNVE5NTI4RVI2MTNNZXBfTHc1bm1lWk5lejhoUU9ZQzQ4cHUtMmVrT24zeGtyQkR1RG9EX19VQmtIc1FPMk52eGNiZ0dSZkhsWTJKVXlsbWxzY1pDbkxTeVhHVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE9zSnR0VW5KVlJVMWpTSEtZdmJuSDE4ZDBlWEhOMlhjSDNxWFVCOXdTYzRjaHo1a1FmN1VoRVhCbUxuNG1ZTXlsWjBqUkw2THdQNFpEUjNGd1gzZG55djl4UjU3cWVsZFotZzVDSDhn0gFyQVVfeXFMUFdWY2E4SXNLXzJVcUNGNXRxdTVsd19XZkx2X180dWRLUmJVUHRkSHNSUU9fNU1FLUltZWJvZXVfMkt3cFIwQzZhWGdjeVZZS3V2Mk1USWhhQVVCRDNvQWJtTWxJd1dza0hjNktfcEdIa1N3?oc=5</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>14-05-2026 02:26 UTC</t>
+          <t>14-05-2026 00:44 UTC</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Samsung Bioepis</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Hopewell Holdings Ltd stock (HK0054000679): Wins key US patent challenge against Merck</t>
+          <t>Samsung Epis Holdings Earns 'AA' Rating in Global ESG Assessment</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>아시아경제</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQMlJPd2lDZmhwOWt4Y2QzOXhVQnRNMXcxMlk3clpvbHZ0aVZEQ3V4dnhpZHB1X0FObE5ZTUtjeW5vY3cweG11WEJ1T19jQzlSZDJWUzlqMXkxNlZFYjVnbldPMWt1OGlFeXNtTUEtdHFZdk5odU5UNm5PdXNrdFlkNm80dnBXVGtIMVpjbWk5X3RvSlliUlN6OVBLUEtOSFB3Umg3cTU0WDVJanFkUVNjYkpaLWl0TEZtSWxyNlpsNFpXallJeHFn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE5OeGJlSTlKd0ZOWWU3M1NfZkM5RWlFd2IyRERua2pleGp4NG1sMUkwa2tTbDNyQ2UwWDg1NXJzdUJ1SUhPdVRxa1BEd28zN3VxMVNBOXFXQjVJWkZvaURqVmdQMVQ?oc=5</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>14-05-2026 09:02 UTC</t>
+          <t>13-05-2026 23:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Samsung Bioepis</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Vanda: A Long-Term Pharma Growth Idea, Despite Q1 Earnings Miss (NASDAQ:VNDA)</t>
+          <t>Samsung Epis Holdings Earns 'AA' Rating in MSCI ESG Assessment</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Seeking Alpha</t>
+          <t>Seoul Economic Daily</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNcFFPS0ZjVW56SlY3dy1VWEM3ZmdBWThpU3JVVjVWWmxzdTlwaE05SnlUQzFWSU1oWTNWQnZFT2NFR2ZjTXlqOW1wODZMbzRSMURmb19nU3VTT0NDZVdObGFHbWZxemVuZGJWZ1BBNzdERWJRNkdOcGt6TTI2aS1iOFNIQll6WkFTMngtaWV0TFItN0ZOWnRXc25LUDc3XzNfSndNMUU3eU9mQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxONllvOWRnaTNUQU84TXkydHk4UEdnZ0otT2pEakJNdDQzNzJqN0RKeXV3YkNVaVowSUJRTWc5cXdLYTRnSHdrWXVrNkpqMjh4c2IzWWVwbXU4cnllREVKT3p2Nm1NakFKZnVIZmdWT1FEeV9yYk5mMzJleEgzazFKN2pqdVJoYTI2bV9kV0ZVV25TMVJ3Uy1yQ3c4aXBKWDJKWjJzNw?oc=5</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>13-05-2026 17:34 UTC</t>
+          <t>14-05-2026 01:01 UTC</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Samsung Bioepis</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>BioHarvest Sciences Appoints New Head of Business Development for its CDMO Division</t>
+          <t>Celltrion Inc stock (KR7068270008): US biosimilar launch and facility acquisition</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>TMX Newsfile</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxObkhmS00xVEVla3FHT2kxbjQ5eS1XLWdHYy1BLUFZRnVUVklla1B5NHV2TmViUnd3QkdhZXJLR3BNdGJFRHVlN1VaQUdiM2ZQeGtUcW9jeWxzcW1PYTZqejBlTjh4VEpnTHZQUEpBQ2RTMmxkbVZoanQ2bmhLREdnUjduRGNpd01tR2pGSFFwVzBITm5vTlBTZVVMN2hJUkZYR3FpUzJhV1Q0YU5GWGVZREx2aklmQjVIUC1HZWpJaGhuT1dUQXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQak1zS2RSWk16TTlwcHRPUDdkQnhWXzRJc1JVbTNyRUM0SmdvNUhQWEs3Mno3RU9YenRKc0ZoS01sbHNzc2JlZnVSMk11ZEtQM3JJMm55dzBKR3ZRSFBYNEtROXhpQjFCMGRET1ZpNG9RODc5RG5ka3R4dEd5MVBlZ3JzcmhTQVM1R1RQcERqRjE4WHhjWXVOX21GU2FkMEw1VVZyNGZNNEg4bzhETU0xd2FfMjJ5Y0xOTFdldHNkSkFSRjA?oc=5</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>13-05-2026 21:32 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>MS Pharma</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>Pharma Quality Excellence Awards 2026 - Celebration and Conclusion</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>Siliconindia</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxOcTV3bWhuZ3VaZmRncmFHOENMX1NQaEV5M1phdVc5b25KNGxSTGxOcWl5eW5TaGZBbjBhdndWN1pvY3NualpsUjlpaHpTeG91a3QwWkg1SFZqaUp2SDBzN1h6U3RYTHRBbU9Cc19VOWpKZEVXM19yZXVjLUVheXdpZWFBZkp0LWFCRzFwazllWWpGSTZ4ejZIeG1Odk0tMFlVWERvdWxXNkpCS0YyaUZaQjlIaTlxYVZoZ0RNUE14bGwxdDJnTFhUdQ?oc=5</t>
-        </is>
-      </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>13-05-2026 14:20 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>MS Pharma</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>Indian pharma fuels Africa’s ‘zombie drug’ and opioid crisis</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>The Straits Times</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOUTVkNnQxLWJFZkFidzlBV0dLNGIwc0FlWGdhamFBTGxkM08wS1hnY0pfTWdZdkdIbXN4VkpnaDc4THJ4UmNmWkM0cUVjVlhzblJBY29NeVJZWEVXeEVZUm5fUEZYZWlqR3QzMXVLQVRHNGR4Q0NHU09idU1TbEE0WlB2VXFHNW9XUVBVc0pwYXJiZ3ZYNElr?oc=5</t>
-        </is>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>14-05-2026 02:05 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>MS Pharma</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>She closed $30M in drug contracts; now she’ll hunt CDMO deals for BioHarvest</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>Stock Titan</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNaW55V0hkRHdOOVlKRXdJc3JwWDlEd1FSTlVxUjI5dXVTNFREakhxaTAxR2hBNnphM1Z4Qzc2emlHZkFOZURyM1VKdW52MTdSaGZ3dTFVZ2puNFl1Y2ZSbXljU05QVzBBQXpHc1ZxZlNnVGRlVWpDUzZBVzNYaWxpaFViTjIyTGx1VTdGc1dvOW9hM3RReEhLamxyQWNCXzdFMHUwS0JDMDM3Tzh4WXJDZ3NMOTJPSmY2SzZPUDln?oc=5</t>
-        </is>
-      </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>13-05-2026 21:32 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>MS Pharma</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>aTyr Pharma to Participate in Upcoming Investor Conferences</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>The Manila Times</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPbGFHNEt6T0d3MzNxNzFVdHQwOWJWcnhkTkJheWRUNGlVZmUydENVSVBMeFFGbUZvMm9MTk9DVnVtRTJ1aE9vLWtRa2JfX1M3UmVUNktiMUlxZG9NSF96NnFHUTRFSUFVX0F6LTdHakl1T1U5aEkxUVIxODJ1RkVXRlQ3b3lkT1E4YVNIV3hpYWJBY05KeDlXOVJpQVBWMXljMEcyQlNyV2FXd3ByMnJuRF94MnplcG4yMDhHNXc1UHl1VlA4SXM0MElhUDFSd9IB0wFBVV95cUxOOUsyeGktb2ZBVzhSdnlucVZtZy1sMUozOTkyNUYwRUg0R1N1ek4zMXJnZ2hHUEd1NGUwanRvelI1TW1HYnVGa0gtRWM3WkYyTGJsT1Q1Q3RoUUZWMExyUkE0di1rUGFXZnpCSHlodVBYUGNQMnJPc0hjOVlDVDlfa2FzbGM4ZERqTnJ2R1FPazBKclN2elZiR3RrMW9OMjd0U0c0WVZrMXFvVFFyazJJWjhSSXBtOTlGYXoxdnRCN0ZJY3NYSzdCaG54b1lTUUdPQ2hz?oc=5</t>
-        </is>
-      </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>13-05-2026 20:13 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>Alvotech</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>Alvotech Plans June FDA Resubmissions, Sees Biosimilar Approvals by Year-End</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQbXI2eF9aMkdCalNMcnY3UDdUblR5TjdQYzlnaVhRcTlNcjk4WFpTbzNFUVJUcko2c3JuUVJoYmlhZnJIVDBodllqMEdMOE80dTlMWDVyMmJ2M0dqS0ZtQWZXNGJZbWNpRHdzaVZkZ25GQVVGanBHbmxqYmt6OFlqVVRBSU1NTUdmMjNfVTdNSGF1azVUcUplb3JidUQyQWU5QzVLRzYzSjB0Zw?oc=5</t>
-        </is>
-      </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>14-05-2026 00:13 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>Alvotech</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>Alvotech stock (LU2557688560): Partner Fuji Pharma reports valuation drop</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>AD HOC NEWS</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNOXZEVU1kRjk1UkFFbTg3RTUzdmprblI4UERRSVJIUWxROG9qX2h4NjFDUXR2QUNCYi1RVXlxaW1QbjBMNnlwM2RfalY3OTVSYlpqQ3g5THBSMjBrZEo1U2VIby1Yckl3Sm5OWkxWZ1IxNjBhaTNoWUJJTDhHWUpqMW5rRk1TZlNRV3VPa3l4eG9Gd1U2WnotWDlOYi1mYXhVRXZCYWZEdGVnWWhVX3V3WWo4THZ2VzlUeC1fM1N5dlAtMFZjazdMeA?oc=5</t>
-        </is>
-      </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>13-05-2026 12:42 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>Fuji Pharma</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>Alvotech stock (LU2557688560): Partner Fuji Pharma reports valuation drop</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>AD HOC NEWS</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNOXZEVU1kRjk1UkFFbTg3RTUzdmprblI4UERRSVJIUWxROG9qX2h4NjFDUXR2QUNCYi1RVXlxaW1QbjBMNnlwM2RfalY3OTVSYlpqQ3g5THBSMjBrZEo1U2VIby1Yckl3Sm5OWkxWZ1IxNjBhaTNoWUJJTDhHWUpqMW5rRk1TZlNRV3VPa3l4eG9Gd1U2WnotWDlOYi1mYXhVRXZCYWZEdGVnWWhVX3V3WWo4THZ2VzlUeC1fM1N5dlAtMFZjazdMeA?oc=5</t>
-        </is>
-      </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>13-05-2026 12:42 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>Fuji Pharma</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>Fuji Pharma (TSE:4554) Margin Compression Challenges Bullish Earnings Growth Narrative In Q2 2026</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>simplywall.st</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxOazVIQ25JUy1uWUVZdS14WkNwSUVGYkR5MWV6RFBVMHpQTVgtN25oclFZMW1SQ0FWSzlOX2txRXVYUktXS2MwUGRPaHFzT3lZUDZlZWZJX2tfNXJ2UklNbi04NGtDZ0RQSnV0eGFHWkdKQUFTNVFQV183UHBScVppbHAtMDktZUVOQlNaRm9mUTd6bm1XeXlTQmwxQTB6b1o2SmU3b3FrQnZ6T0FTUElhZlkwN3JVNU5zR0J5N1pXOTRFLUtVWEJFci1NamRFMkdjRzFFMWRGVlMweDY4V0dJS0U4WdIB6AFBVV95cUxPeXZ6SUFRWGQ3LWRWdGc1NEhZaERmNFFEUkJ2d0hFRld5SDQtRHFoNk1JcW5Yb09VQjJGTXNrNUlOYW8xa08xN0FWenJVX0NoRUZyWG1ST3k0Wi01ZkZfZHFMVTNMNjNLc3dEOGlQYWpoOHNxZGRyc3BQN3N0SlB2UU9valJtcWwwRzNrUUZ3YUROV1FQNlBRMGFFWXZtTS1YdTFtaFh4eDhaRkJ3OUNOQ1hOdGQ1SE1VVldwM0ttdTNRX2pjXzRCV3dULVQwazVCN1JRXzhDN3p3WU9ZRGZnb3hPcVlHclh6?oc=5</t>
-        </is>
-      </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>13-05-2026 13:45 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>Wall Street Thinks Teva Stock Still Has Room to Run After Soaring Over 100%. Here's Why Analysts Are Right.</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>The Motley Fool</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQQU1xNHU3R1JfbWI5S2NMX3F3TG9xQVVRNG9qQlFTS1hJNWE4WHV4blByS19PeU12dGJCR0paQmluX2Rad09mWUlRR0hraGQwTFgxb2JuZEJvWGpDY1o2a1Z1RHVxRnpIbU5OSWFvOVhoZF9XRjNEUm55UVNKR2ZFNmMxTHAzUlBHVldCeGxJWUt3dW14YUlCdg?oc=5</t>
-        </is>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>14-05-2026 09:06 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>How Investors May Respond To Teva (TEVA) Showcasing CNS Growth And Emalex Deal At Key Conferences</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>simplywall.st</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxPV3BNcHg0aFZzcGFfdzdhU2g3dHBEckEybW84bFFMdlpWNU1SSU80elhhSmFzc3NEXzhSUGRwcHdzSnA5bkpndmRWUzhtRDVpYklDTzh6aEZXUUMyYjZrZlVNNWZEMGZEcVhKVmFYZTFKQUVnQlMwOUhVZ1dYZ1NxSmNDa0pNdmY3NGpQLUFSbkVIQno3RzBLOTVBN3RLSXFvSm1iM2g3dldsaVBZYWtmWWJzak5KdlZXdUptTkJwekQ5WjJsbV9OVktURTd0akd2QVg0QlBRd1k3QURZLWJrN1drclgxdjROQWd0NkdaUlBhOXFf0gH6AUFVX3lxTFAwZ3VlbG5lZnlZUVkwU2kxN1Y1aFZmcmcwRE9ndllOWUczcjlEWmdjdk5mcnJSZzBoRDFvUGZWdUVJYmQ1VnNRUk9BZldyTTdtd01oUU1vRFdKc21adE55ZHRjYXk4Q2xCb0c1ZEhNdFZNLVNwdVZTSWxVTnJqb2ZBdWhYMGs0RW05NloyMXZiajFuekJJNzFLblBxRlVWVmtSTE9OZ1hKZktub0VMd0VHdHpseHBaTUF1bWJjWVlkYzZYUUR4U0pUSmhMNUxlZTBMMS1nX1Vic1NrTngza29ybkNVTzlBWEE1R2FoT2lRQXZwQXZZbEVIRnc?oc=5</t>
-        </is>
-      </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>14-05-2026 05:52 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>Wall Street Thinks Teva Stock Still Has Room to Run After Soaring Over 100%. Here's Why Analysts Are Right.</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQOXhTUlhTTl95cTR2QmY1ZV8tVmZsSmszRFhjRzBOZEtRaG5TdFppd3JtamRtbGpSN2xFc3JST0FKbV9rUHFTcnJDeHprUEFfR0I0WlFYTzROc29fRE9OanQ0SDFWaW9TTTMxbmE3NzFYR3ZtWnNOQkRmRmdpbUJwM2JRb25kSDhRY3BTbVBhc1pSdkJsRFEyTTVB?oc=5</t>
-        </is>
-      </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>14-05-2026 09:16 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>Teva Pharmaceutical stock (US88162G1031): Beats Q1 2026 earnings with CNS growth</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>AD HOC NEWS</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNUGo5OG0ydHRxdmFXZlRSQUFtemZOY0RxaUZCWWlhamkyR3ZXaTkzb0lxRnltWUYxaFJuN2ZNNG9QaHVHTExyZzZhdVNOTW1tenFlZmhyQVhDbUtaUVNRb3lraS1tbnplalVzaURadHZDVC1BTlJ1Qk0tMWFlT2tYSnh4M084OTRoWFlnNkd2QkhRWktMNE9sdGVxRkdQTmlOa1hoaGlEMWpOQXlzU1lYZ1p6UWU0SUNyTjVhQU8xR0hHQzBDdGtwdw?oc=5</t>
-        </is>
-      </c>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>14-05-2026 10:46 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>Teva Cleared to Sell Generic Effexor XR -- a Pfizer Blockbuster</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>AOL.com</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE9jX0RSZzhuUjNZWW4yRUNERnl2ak9oU2pqa0NFNFpwbl83YmFNUmdWSXd0ckdSV3dDNG5XM2JlLUFMOWlDa3YzMXFvWGVTcUhnQmFlUEVDNWZJNjNLUlNTWDEyTzF1Mjc3amc?oc=5</t>
-        </is>
-      </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>13-05-2026 13:39 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>When ‘low profile’ is ‘high valuation’: Soma Das</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>Business Today</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQeVkxZlcwNGlmZmU0SUpxMm41OVpjMEdKZWNRakJSeUJQZlNrZjA1WnBFUDBNdDM4UVVMXzYwSFZWX0k5TmhRQjFLclVlRTRrQmp2ZUVoTG15N3BoZzJ0dmZUdnlLR1dKRk9jdmtEeE9MNUJOdV82U2VQblhHSFo1OXBTSmQxbTRjcHdHTFV4bmEyQ2p2ZnMtQVJGemM5N2U4SUlXekpCZjNsVFY3RnItU0RYc9IBuAFBVV95cUxPcVZ2dUszemFtejMwSnR5MzRtaGtEX1hkRUVVWVg2enVWQjVUTHB1YWhnWU9lUjVzQ0duLUNQcGZheXZjRG9sQ0I2QUZ4R0tacnVnODdITER4NUlJdEdiNG0yODdjQnhRcTBGQnkzcXdIY0d5RmtmckdrV3hUMG5GeGozWHg4Z0Zqd2Yyd0VTRUpjNTlyd1JNV0NaUVVJRmIwa3FNcTFTUjRRWS1nb29TWU1Qc0hTbE04?oc=5</t>
-        </is>
-      </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>14-05-2026 09:15 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>Alvotech Plans June FDA Resubmissions, Sees Biosimilar Approvals by Year-End</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>Inkl</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQZU9idjU0Mk9ackZiQUtpb0V1NGlneDJzMzhnakJySzBWcDJ1b1l4U2tlbmMzQkk5N1VWb2gwb3FlVGFVU0ZPcm9HWjJZNmppOW5Wb3JDcjRmUk9wRl9EWnludjRFd1hhdldoTWowZm4wVHZzZlduTHBZTms4MEFjUW94WXFobU5zaVpVZnVkQkNBRDJnUXUxZGM5QW5neWh1dHAw?oc=5</t>
-        </is>
-      </c>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>14-05-2026 00:18 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>Alvotech stock (LU2557688560): Partner Fuji Pharma reports valuation drop</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>AD HOC NEWS</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNOXZEVU1kRjk1UkFFbTg3RTUzdmprblI4UERRSVJIUWxROG9qX2h4NjFDUXR2QUNCYi1RVXlxaW1QbjBMNnlwM2RfalY3OTVSYlpqQ3g5THBSMjBrZEo1U2VIby1Yckl3Sm5OWkxWZ1IxNjBhaTNoWUJJTDhHWUpqMW5rRk1TZlNRV3VPa3l4eG9Gd1U2WnotWDlOYi1mYXhVRXZCYWZEdGVnWWhVX3V3WWo4THZ2VzlUeC1fM1N5dlAtMFZjazdMeA?oc=5</t>
-        </is>
-      </c>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>13-05-2026 12:42 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>Samsung Bioepis</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>Samsung Epis Holdings earns MSCI ‘AA’ ESG rating in 1st global assessment</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>koreabiomed.com</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE9zSnR0VW5KVlJVMWpTSEtZdmJuSDE4ZDBlWEhOMlhjSDNxWFVCOXdTYzRjaHo1a1FmN1VoRVhCbUxuNG1ZTXlsWjBqUkw2THdQNFpEUjNGd1gzZG55djl4UjU3cWVsZFotZzVDSDhn0gFyQVVfeXFMUFdWY2E4SXNLXzJVcUNGNXRxdTVsd19XZkx2X180dWRLUmJVUHRkSHNSUU9fNU1FLUltZWJvZXVfMkt3cFIwQzZhWGdjeVZZS3V2Mk1USWhhQVVCRDNvQWJtTWxJd1dza0hjNktfcEdIa1N3?oc=5</t>
-        </is>
-      </c>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>14-05-2026 00:44 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>Samsung Bioepis</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>Samsung Epis Holdings Earns 'AA' Rating in Global ESG Assessment</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>아시아경제</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE5OeGJlSTlKd0ZOWWU3M1NfZkM5RWlFd2IyRERua2pleGp4NG1sMUkwa2tTbDNyQ2UwWDg1NXJzdUJ1SUhPdVRxa1BEd28zN3VxMVNBOXFXQjVJWkZvaURqVmdQMVQ?oc=5</t>
-        </is>
-      </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>13-05-2026 23:30 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>Samsung Bioepis</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>Samsung Epis Holdings Earns 'AA' Rating in MSCI ESG Assessment</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>Seoul Economic Daily</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxONllvOWRnaTNUQU84TXkydHk4UEdnZ0otT2pEakJNdDQzNzJqN0RKeXV3YkNVaVowSUJRTWc5cXdLYTRnSHdrWXVrNkpqMjh4c2IzWWVwbXU4cnllREVKT3p2Nm1NakFKZnVIZmdWT1FEeV9yYk5mMzJleEgzazFKN2pqdVJoYTI2bV9kV0ZVV25TMVJ3Uy1yQ3c4aXBKWDJKWjJzNw?oc=5</t>
-        </is>
-      </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>14-05-2026 01:01 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>Samsung Bioepis</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>Celltrion Inc stock (KR7068270008): US biosimilar launch and facility acquisition</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>AD HOC NEWS</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQak1zS2RSWk16TTlwcHRPUDdkQnhWXzRJc1JVbTNyRUM0SmdvNUhQWEs3Mno3RU9YenRKc0ZoS01sbHNzc2JlZnVSMk11ZEtQM3JJMm55dzBKR3ZRSFBYNEtROXhpQjFCMGRET1ZpNG9RODc5RG5ka3R4dEd5MVBlZ3JzcmhTQVM1R1RQcERqRjE4WHhjWXVOX21GU2FkMEw1VVZyNGZNNEg4bzhETU0xd2FfMjJ5Y0xOTFdldHNkSkFSRjA?oc=5</t>
-        </is>
-      </c>
-      <c r="E214" t="inlineStr">
-        <is>
           <t>14-05-2026 07:44 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>Samsung Bioepis</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>Alvotech stock (LU2557688560): Partner Fuji Pharma reports valuation drop</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>AD HOC NEWS</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNOXZEVU1kRjk1UkFFbTg3RTUzdmprblI4UERRSVJIUWxROG9qX2h4NjFDUXR2QUNCYi1RVXlxaW1QbjBMNnlwM2RfalY3OTVSYlpqQ3g5THBSMjBrZEo1U2VIby1Yckl3Sm5OWkxWZ1IxNjBhaTNoWUJJTDhHWUpqMW5rRk1TZlNRV3VPa3l4eG9Gd1U2WnotWDlOYi1mYXhVRXZCYWZEdGVnWWhVX3V3WWo4THZ2VzlUeC1fM1N5dlAtMFZjazdMeA?oc=5</t>
-        </is>
-      </c>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>13-05-2026 12:42 UTC</t>
         </is>
       </c>
     </row>

--- a/news_results_raw.xlsx
+++ b/news_results_raw.xlsx
@@ -490,22 +490,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sandoz Confirms European Commission Approval For Biosimilars Bysumlog And Dazparda</t>
+          <t>Sandoz wins EC nod for two insulin biosimilars</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>The Pharma Letter</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxOQWdGQmlhYU5Mc0gyblNPckd0X2FrOE0xdGNVRmVxcUhmTnlXUUN4a2FIOUhkaDFPZFNPUTF6VjVpRkxnQUZienBReEZlRGtMTGJYSV9xYlZUS09iVXB4TkxQQUthcmxHbmtDcVdUN1Q2Unp1bEVlMUpFRU5TLV9zbGFZcWI4ZzBIUGMtU1Zhb0NwS3BsWXNNQlJrci0xZlJoTTMxUDloZUsxSXFMd1gxNThMemZla3ZVcXlDc3AzczU4eGVZT3ZsMFlISkE0SmJNR1RTd3pNV2kwWTFHNG50TG9RekdhOU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQMzl2dWRydmd4RHVydjhtRGV2Q3BvTFdYN1UxTnBwaXIycUpxNE1nUF9laGxNdS1aTURLTVE0a1Atc1l0eU91WEIyLUUxamZVRW9wNTFFZGhGcUlFMDJSTjF3TzZNNDNMWWhjRG5qZFVSaVNYNDVxNkJ0dXliYUpvMDB5eGZxS2tBRXdUTHVPcDJnc0RQZkpzOWx3NA?oc=5</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>15-05-2026 11:03 UTC</t>
+          <t>15-05-2026 12:42 UTC</t>
         </is>
       </c>
     </row>
@@ -517,22 +517,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sandoz confirms European Commission approval for biosimilars Bysumlog® (insulin lispro) and Dazparda® (insulin aspart), strengthening position in diabetes</t>
+          <t>Sandoz Confirms European Commission Approval For Biosimilars Bysumlog And Dazparda</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>boerse.de</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgJBVV95cUxOSGdwbXVXaS1KbTRQSEMwN1ZEazhxZHJIWC0zX0lTWXRvOVBQdXM4OENXT0YzWGx3eU85aXJvd1hHaUlsU3EwWi1PSXJiRnd6cUJtMzBIdFFKYkE0RkFBd0lObWtTdzZoVmdJZWhoclcyc0RFcVNhSkxVdC1iUHhaUTFhWjlwVmtYQVRUQ01UYTBrbW5VMTN4d3hJSjdLTGIwMy1YNlVNbGZxSnZxb3NBZFE1V2thUFUxTjZSc3NOeVJfUmp4UnNQVEtzVFdXNzZTUEVNcG9fZUFpbzFLN0RXNGtrWDZiV1pqTFpDRll3aU9JLU1NRTM0YW1BSUdpcmwwcFJqQzdfQ21FUlV0d3A0Y0RSNXROVG5YZnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxOQWdGQmlhYU5Mc0gyblNPckd0X2FrOE0xdGNVRmVxcUhmTnlXUUN4a2FIOUhkaDFPZFNPUTF6VjVpRkxnQUZienBReEZlRGtMTGJYSV9xYlZUS09iVXB4TkxQQUthcmxHbmtDcVdUN1Q2Unp1bEVlMUpFRU5TLV9zbGFZcWI4ZzBIUGMtU1Zhb0NwS3BsWXNNQlJrci0xZlJoTTMxUDloZUsxSXFMd1gxNThMemZla3ZVcXlDc3AzczU4eGVZT3ZsMFlISkE0SmJNR1RTd3pNV2kwWTFHNG50TG9RekdhOU0?oc=5</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>15-05-2026 11:00 UTC</t>
+          <t>15-05-2026 11:03 UTC</t>
         </is>
       </c>
     </row>
@@ -544,22 +544,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>From Tongi to Canada: Nevien Life Science marks export milestone in global pharmaceutical supply chain</t>
+          <t>Sandoz confirms European Commission approval for biosimilars Bysumlog and Dazparda</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>The Business Standard</t>
+          <t>marketscreener.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOdDFwOWpMQkdNMEt1ZnQ0NXlFeUttVTNBM19JeW5BNnVoNTNySzY3elUtZ1QweXdJeEVRak5qMjUtMTQ0ak5BQ2xwM3NJRFJzamNhM09JSnI2bFRlSlFoVHpZWkhsQmFEaXJLS2NIdHhWZ0NBSFFzODU5VlI2dWthTnlrMDE2Y3B1MjZMQ1RTclhEVXYtbXZXWE0yQVRXMGlSRTFvT212QlFfeW83aUFwWmNRT0JIVDQ0RkHSAb8BQVVfeXFMT1d4QU9QMVBkbHR4aThxd0hBQ3BpeHdiZHNoTnZvNXFDa1ZZUW13Wmw0X0FwMm8wZWJYdENmQ2E3MlUzLXNUaWhoSVdvRG9weXA5LThCSS1maEFBNXJXbVZzaVlTdnhpOTUxbXNxZFFPU0xmY1lIYWtteUZ4MHZyVWRQYjBUN1EwbnFRTkJXc0Z6a0loN241TnZ3OTVZekczS3ctNkFIbENtckFwOGkyakNUWkdkc0pqYzJnV3JNbDQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxQS0oxM1FTN3gzWXNpV016UGtYZ3A0VzJFTlhVUVRwd204SldzbTJ0OEFfdV9lNU53aXRxZm92N2pBZldfOXB5OTBFeUdDc3ktc0ZwemJtMnh0Vm1semR4NnlJUjZYeW5tVHdqazlHaHp1WXpaeGdrWVpsUlM3MlZuLVNSVlR4Sm1XZEcxejc4YjNsV08yRGdfdGdEN1czZzFva2w3ZzFhazQwQ1JQT2U3UkdVT09WNVRoYXphMmFuU2RkSUI1clpLNk5wYjJCdHd0?oc=5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>15-05-2026 09:19 UTC</t>
+          <t>15-05-2026 11:12 UTC</t>
         </is>
       </c>
     </row>
@@ -571,22 +571,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sandoz climate targets validated by Science Based Targets initiative</t>
+          <t>Sandoz wins EU approval for two insulin biosimilars, bolstering diabetes push</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Drug Store News</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQUEs5U0JOTWpURld3VjVZVWJFLXhvNUFVR0pfeWJzdm81ZlJUbHBDcWxBUGE1U1lFS3V4bnRkbHZiTGpXUjdDYnJWdTRkQWM0LWI3dDd2eTYzZ2ZURkVQRjZqTmNsR0h6eHBuLTUwYWF2bDhUTjl5QTlJVll5b29KY3ZpYkQyR2JXWGNkUEpZeXpWSGY2Nmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOazJGTENwb2JQUHp5aW4xVklVbk9UdmZQQlZCSG83WFFkZ3ZsbFNkRC12aWVLdzlQLUFqdjlLT3oyLWREcUR1MHI5OUZ2OW9nclJjMTY1NTBfTmpjTFFnQkFsQUt1MWpsM0t2ZjgtMjNsR1dRZFpPRmFjRFdiampLR182VkJ3NHYzMW1NeEtiZ19rVmhFd0sycTBkMGc3SFRZdUFCcmkwTGM0ejlCbTJ2aGhaVTNKcVp5aUNIX3NEV09HZndZYmt3?oc=5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>14-05-2026 14:15 UTC</t>
+          <t>15-05-2026 12:04 UTC</t>
         </is>
       </c>
     </row>
@@ -598,22 +598,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nevian starts exporting medicines to Canada</t>
+          <t>Sandoz confirms European Commission approval for biosimilars Bysumlog® (insulin lispro) and Dazparda® (insulin aspart), strengthening position in diabetes</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Prothom Alo English</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE1uR2F1aVg3d0Fjcm9uRERKM0kzRmtqM1VVcFVnTlZmVHVxeE1UX0kyOG1DOFJfcmtBcTFrdlVjanpRb0hDd1FJVzRHU0J1R29RcjVUTjJSQjFxV3FVUzZuR2oxNTRkbDTSAWdBVV95cUxNbkdhdWlYN3dBY3JvbkRESjNJM0ZrajNVVXBVZ05WZlR1cXhNVF9JMjhtQzhSX3JrQXExa3ZVY2p6UW9IQ3dRSVc0R1NCdUdvUXI1VE4yUkIxcVdxVVM2bkdqMTU0ZGw0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAJBVV95cUxNbFRrbXJES0R1d1FYNm5PY3JSOF9sUG00MXZJX0dtMkxGcWtuM3JjekJjOTBfU1lQMmFhUlF4VGhUaGRhVmRnTDl6VzIzazhDT3VlTUhpbV9UX0FMNVNBemh3SWZ2RENHNm43cE5NXzg1OTQtWEE5WDJmaHg0cjFjWXF6cUhRZzRWU0Zpb21sdkpoSmdhWWw0blNNd3FSODFxVnBVWGNUSXcxV3NvMnJwbll1R3BDbVZKenlrWDBEOTV6YU9zUUtMS0NEMWRONXNrcGpaTnBxeFI2NU42UWd1U3lkZ3dqMGxiUlVwSVkzQ0VaWURoWXR1aVUxR05oZmowOUhMMFU0STAwQ3JWb2t0clRTcWI2anFXRHpFYzNiWWF6UjJCdE9icA?oc=5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>14-05-2026 12:53 UTC</t>
+          <t>15-05-2026 11:00 UTC</t>
         </is>
       </c>
     </row>
@@ -625,22 +625,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Nevian exports medicines to Canada</t>
+          <t>From Tongi to Canada: Nevien Life Science marks export milestone in global pharmaceutical supply chain</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>newagebd.net</t>
+          <t>The Business Standard</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNNVJpMXJiM3owWVp6OTNnZmxRMjFPVEFBYk0zSmFDNGxPVUotVE5jNVpSTk5OX2V6N2RDZEMwbVlLQ0NrWXdEU0FBX21pQk9qcHdsSVg2cVNubU42a0l3VmVqWEhaWEo1TFZScm5LUGFYX3pKZ0NnMVBRay1sei1fSGh5dVZRZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOdDFwOWpMQkdNMEt1ZnQ0NXlFeUttVTNBM19JeW5BNnVoNTNySzY3elUtZ1QweXdJeEVRak5qMjUtMTQ0ak5BQ2xwM3NJRFJzamNhM09JSnI2bFRlSlFoVHpZWkhsQmFEaXJLS2NIdHhWZ0NBSFFzODU5VlI2dWthTnlrMDE2Y3B1MjZMQ1RTclhEVXYtbXZXWE0yQVRXMGlSRTFvT212QlFfeW83aUFwWmNRT0JIVDQ0RkHSAb8BQVVfeXFMT1d4QU9QMVBkbHR4aThxd0hBQ3BpeHdiZHNoTnZvNXFDa1ZZUW13Wmw0X0FwMm8wZWJYdENmQ2E3MlUzLXNUaWhoSVdvRG9weXA5LThCSS1maEFBNXJXbVZzaVlTdnhpOTUxbXNxZFFPU0xmY1lIYWtteUZ4MHZyVWRQYjBUN1EwbnFRTkJXc0Z6a0loN241TnZ3OTVZekczS3ctNkFIbENtckFwOGkyakNUWkdkc0pqYzJnV3JNbDQ?oc=5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>14-05-2026 18:43 UTC</t>
+          <t>15-05-2026 09:19 UTC</t>
         </is>
       </c>
     </row>
@@ -652,22 +652,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Novartis AG stock (CH0012005267): Q1 earnings beat and shares up 1%</t>
+          <t>Nevian exports medicines to Canada</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>newagebd.net</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOUC1sUGR3VXI5am9DSXE0SE0tR0pPeEcxRGN6LVdwOUVPSUJUTTNPSTZCbHFIdUl1bm5FV1hrSkZaUG9sZ0FMaDhtQXFfbnpCSVl0VG5OQmtjbVc3cEVTdHI3NWJSLTg1VURESFF1TnJTbk80UzU0Y0ljNktJUzJWMlFpeDlWaTdrMFdSbUx3ZWFqOFVBajYwNkUyVFJacFlxQmVKRzJBTk9wd21sNlJtc3YxazhYamhOVV9KaHhKLS0wcHdkTU5zNFZB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNNVJpMXJiM3owWVp6OTNnZmxRMjFPVEFBYk0zSmFDNGxPVUotVE5jNVpSTk5OX2V6N2RDZEMwbVlLQ0NrWXdEU0FBX21pQk9qcHdsSVg2cVNubU42a0l3VmVqWEhaWEo1TFZScm5LUGFYX3pKZ0NnMVBRay1sei1fSGh5dVZRZw?oc=5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>14-05-2026 15:46 UTC</t>
+          <t>14-05-2026 18:43 UTC</t>
         </is>
       </c>
     </row>
@@ -701,54 +701,54 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sandoz</t>
+          <t>Stada</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BAH to be Held Tonight at Insurance Specialists</t>
+          <t>Thornton &amp; Ross showcases Yorkshire manufacturing with visit from local MP</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Eye On Sun Valley</t>
+          <t>Huddersfield Unlimited</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPNEZIN2l4ZTFkRnIxQ3dXN084SHVWUUR0ZVd2c1dxQlBPWXpOWl82cjFISk1aS0pESjgxd3EtUzRyelFPMVRXX0pHSDBmT3g4bk93d1ByMmVhaWMyT2JycUdEZHMzMWJLVmRSQjdhMHMtYW5GcEhNMklXNnczY3k1eUg2MlU4RWpoNnVLZkJTSXowMG1mNGRwSG9R?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxQdy1idEVCdERsTTVqNDhOSDd2OG1qZXdGZ2NUMDVULUdMcVVhNzZrTEJMVi1CT2I0bzBBc0tXMEpjLUdqM0xGNmpkbnZmWFhjWnpacVhwbWtuVE5CVHNRSnk3MmpvVUZXajNjb2MwNmUzYjB0YWlQOGpRMF9ITlZnWTF2RHpiVmRtbkE?oc=5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>14-05-2026 12:52 UTC</t>
+          <t>15-05-2026 15:35 UTC</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Stada</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim India signs MoU with the NIPER Ahmedabad and Hyderabad to expand research collaboration across India’s largest pharmaceutical hubs</t>
+          <t>Nexgel (NXGL) Q1 2026 Earnings Transcript</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>AOL.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxOZVpUeXpZTDYyY1hGRV9GaEU0ZHM2UTBZZzBPWmJHeWhkY3Q2eWJMdU91c1AzbkxkOWllZlJ6U09rR0Y0YzQxSzYycE9nTUk1RUZVcnUxV2RvM1QzVlV1MHNIcFRkaFl2R2VZMUpqVUw4ZUlUY1pSaENSSzE4Y0tuai1XVlBpLVVVTTJOcGdIaFRPd1hNTHJKRTFHTlJtSmpoZC1yMmRMQW5DZG5FZG5nWGl4Ull0V2ZRc0Vla1dPclhNb2ZBTHg0a0RncmxhOUJvYlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTFB3UTNGaXM5elB6X3JzMWtlY0JncUw2MzZPay02V2YzWmJrTlhpcjhSSFhITDk2aEhrOUp1UHhLT0JIWjl0dmhhdENaNC0xUGhIQ0kwMGduSlBLTGpla0hJZHNEa0d4dXRaMXNsRXpoUnNjbWh3R2VrY1BpcFU?oc=5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>15-05-2026 01:55 UTC</t>
+          <t>15-05-2026 17:08 UTC</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Veeva Commercial Summit to Feature Biopharma's AI Successes and the Path to Agentic Commercial</t>
+          <t>Boehringer Ingelheim India signs MoU with the NIPER Ahmedabad and Hyderabad to expand research collaboration across India’s largest pharmaceutical hubs</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>The AI Journal</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPOVJZWHV4Tml0VHpibE9fcDV5Skp6b3F3bktYeXVpMER0d1NRd0d6M0NwcDNqVXRvRlZyLUxSUV8zVVZfZVlIc3lfdE1LWnpmTFdoRnQ2bFlib21GRXZwRTRtbUd1V1kzUmVNdVFCNUQ0TzJxenBWcnZYaHUwT2tyMVVCMldjWm4wVjEwZXRiNzVrNVVWTm9uT25qbUlKbmIxdUNJOTRvX2EwNVYxUkdINk1VZXQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxOZVpUeXpZTDYyY1hGRV9GaEU0ZHM2UTBZZzBPWmJHeWhkY3Q2eWJMdU91c1AzbkxkOWllZlJ6U09rR0Y0YzQxSzYycE9nTUk1RUZVcnUxV2RvM1QzVlV1MHNIcFRkaFl2R2VZMUpqVUw4ZUlUY1pSaENSSzE4Y0tuai1XVlBpLVVVTTJOcGdIaFRPd1hNTHJKRTFHTlJtSmpoZC1yMmRMQW5DZG5FZG5nWGl4Ull0V2ZRc0Vla1dPclhNb2ZBTHg0a0RncmxhOUJvYlE?oc=5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>14-05-2026 12:58 UTC</t>
+          <t>15-05-2026 01:55 UTC</t>
         </is>
       </c>
     </row>
@@ -787,22 +787,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cue Biopharma (CUE) boosts Q1 revenue, raises $30M and trims net loss</t>
+          <t>Boehringer Ingelheim India Partners with NIPER Hyderabad and Ahmedabad to Bolster National Biopharma Research</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Stock Titan</t>
+          <t>Telugu Times</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPYmNEenpNSmtndzdtM0NzMERtdHQxT3ZtX0FsTThZVXc5cUU5VWRwU19XNW50aWVZOGZDUzg5WmRJRFR4eEFhb0RQZ2ZDdXVkTG1QUUxORldwT3k3YTBMX2xLVGVTU3paSnlTZHlOYTM3Yk83S2lLd21lZ21KUWdZb3lBcmdPX2dqLUJBYmpiZEhxUWxaWUFyY2ZxR0NGTmxrQUFJT3h6aGY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxQX2JMZElmWi02Z0JPYjFHRE5LVU5tNjE0MkZRV0tqX3pUWlBESjB6T0xBdVoxaEthRUI0LWtnTVgxSVNicEJDc1FmbEJwLU9Md2k2VXlPekdfaTJCUkVlODlZbWd0R1BUbWhlcV9ESVJ4blBSdzR0N3dFUW1OM2prVlVjQ1VEcXNMUUx5U1pVMHVNTGh5QjZWWGRmYkQzWWYwMHVzWmliVDBPTjZuMzBTUnBpem03dC1ZSjJCNDFQNE96ZFJ5WlFEdUYwQTcwS3Mwb000UnlaSTE1YUszYjVUNlllTm96Wm5ycnE1QTAyWQ?oc=5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>14-05-2026 20:19 UTC</t>
+          <t>15-05-2026 14:26 UTC</t>
         </is>
       </c>
     </row>
@@ -814,22 +814,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Palatin Technologies stock (US69608A1088): Q3 revenue jumps to $3.9M, loss narrows</t>
+          <t>Boehringer pens $478m deal with Immunitas for antibody asset</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>BioXconomy</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNaG1YbXQ2d1pyVFdCallxT2RlVzNDZ3E4bTJJZVl2T19EN3hwLUJmWFJPc0F3VTFXTVoyTlJkVDI1ZUlBOUhZZ2Yzb2hrN19KUGhMd2ZqdXgweWZfQ19yRzBvRi1FdTlLOFBhUEx4ZklHLUZGS2lLV0VHSVI5Znd0S1ItTVEtY003TkZQemtzTmhJa1NVX2ZlRnNkZnBNdW9IX2tVSnhFYmdVVzVYazJiWjJmX2JsUVJnZnRKNWE1TkxhQXFRWEww?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPNEtmMGY5WnlBb3lxM0YzY3V2LVVXVS14YTlycTZrbXM2azdwSXVIMGlYQXdMTzQ1VXNFS2F5M1IzemJyZ3VpVDdMUVNfUWZfek5QTWRnWEhPbU1iYjBkeTlndk1qeV9fcFdHMUFickcyRlU4LTVLMHp3eVJOYjVlUkIwdGItZExnSXBTTFRxZ3plTk1GMVNTYlQ4SXBtUQ?oc=5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>14-05-2026 17:44 UTC</t>
+          <t>15-05-2026 15:11 UTC</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cue Biopharma reports Q1 loss, secures $30M financing By Investing.com</t>
+          <t>PRISM BioLab to End Drug Discovery Library Agreement with Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Investing.com Australia</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOS2FpVUlVRkhya3h3OVlPMHhrX3JMVWRMUVB1VEtGanJSRXBGUlhOUnhleHp4c3AzTnVMU3YtcGRNQ1hPWlhMWVVsQUx4NXFfcGtpWUxPS0FnS0hPNzY4b0tqbTZ5TGdRbjBQLV90eUdLQUJScGQyaEhfM052WlExdWRYN0Qwb1hlX2kyczAtTlNFNEItR1N3UG9qNnlBOTRicmpaY0xkR3NkMExpdmREU0lxT2kybER3Y2dNeTZsU2NvZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPaDBZbHJWZEVJWEE5dDM3NnFTNHc3QkFTSDJlcHZ6ZG5MczJUVlVJcDVhb21ZRlp1VHV6ZXRYTnJrSHI4N1FPMGd5TmZXeVN3bG5Zcm53S0hJQTlockoyTkh6a2txVS1WTGhFbFF1S1A2RjJtUnhiUXF1c2dyX2VwOWgwVl83d3N6NWk0bXIxS2UzWGFZVFpBc09Udkh5MkdVNDJDN2hkb0ZBblktakV4eFh3a2hVTVpHT284bnVPeDkxQmlrUUVSN1VB?oc=5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>14-05-2026 20:34 UTC</t>
+          <t>15-05-2026 09:31 UTC</t>
         </is>
       </c>
     </row>
@@ -868,22 +868,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Singapore’s hospitality industry needs technology without losing its human touch: Atiom CEO</t>
+          <t>Palatin Technologies stock (US69608A1088): Q3 revenue jumps to $3.9M, loss narrows</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>The Straits Times</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPSmc0eU5vMGgyb3poMEoyUFE0cnVINmg5OGRzWTRoRmpvMTlNT2tnN3lMNEJjekJLVmpvcWlnQjdQc0kwWnlUTE01by1nRHBMRUdUVHdKdXVSZHN2X0ZNdVNvcUlKLWMzUFFGR3pzSnNiTjdZN2ZROUJad082RndMc2hVVmk4VjZWQVlMcUhndUJDYmMxSEd4SVJkbXp2eW1COGcyZkFCVE5ZcHUwcm5LY09SSmVOZzZMTUlDZ19jQzdNRGhyLVVDM0M1T3Zqbkl0UnY0bw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNaG1YbXQ2d1pyVFdCallxT2RlVzNDZ3E4bTJJZVl2T19EN3hwLUJmWFJPc0F3VTFXTVoyTlJkVDI1ZUlBOUhZZ2Yzb2hrN19KUGhMd2ZqdXgweWZfQ19yRzBvRi1FdTlLOFBhUEx4ZklHLUZGS2lLV0VHSVI5Znd0S1ItTVEtY003TkZQemtzTmhJa1NVX2ZlRnNkZnBNdW9IX2tVSnhFYmdVVzVYazJiWjJmX2JsUVJnZnRKNWE1TkxhQXFRWEww?oc=5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>14-05-2026 21:00 UTC</t>
+          <t>14-05-2026 17:44 UTC</t>
         </is>
       </c>
     </row>
@@ -895,22 +895,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[10-Q] Cue Biopharma, Inc. Quarterly Earnings Report</t>
+          <t>Singapore’s hospitality industry needs technology without losing its human touch: Atiom CEO</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Stock Titan</t>
+          <t>The Straits Times</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPb1FpYTB5cVlmTmdXZkJ4dTE4a01pZVUtQnBmbVN0a2RRRGtmdjNFN1VkZzR6M19aVFVEclhSMmdzWkNwaWQxY09OT19MVno2Ynp3YUJfRkF3a21JNHFWaTR2OXMxaDZKYzNxT29JZklRX0g3eUc4VmJQNW03Z1Q1MDJpYzdwTHJscW5JQXJvVzJpRE1GdmJYZWo1THNueEkwR1NlQjlrZ0V5OEYyY1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPSmc0eU5vMGgyb3poMEoyUFE0cnVINmg5OGRzWTRoRmpvMTlNT2tnN3lMNEJjekJLVmpvcWlnQjdQc0kwWnlUTE01by1nRHBMRUdUVHdKdXVSZHN2X0ZNdVNvcUlKLWMzUFFGR3pzSnNiTjdZN2ZROUJad082RndMc2hVVmk4VjZWQVlMcUhndUJDYmMxSEd4SVJkbXp2eW1COGcyZkFCVE5ZcHUwcm5LY09SSmVOZzZMTUlDZ19jQzdNRGhyLVVDM0M1T3Zqbkl0UnY0bw?oc=5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>14-05-2026 20:18 UTC</t>
+          <t>14-05-2026 21:00 UTC</t>
         </is>
       </c>
     </row>
@@ -922,22 +922,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Hikma Updates Registered Office Address in London</t>
+          <t>Why Hikma’s London Address Shift Is Turning Heads</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>Kalkine Media</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNcFFNUjFmSTJYc0pSeldENmZTT0dpVlNUUWpHNGk4M3hTQTd2LWhqdnd5WkdnQVNsSnJwR3BqWnM0VjZocVM5SVVlZ3FkLV9BRm5VNlYyYkZ3REZDZTE2S3pVV2RNOG9mY2E3NGxrTV9fdU9ubFdpaHV0UDlybWFiNEZFTWFIa0l3QmZJNkV6aTVYb0FEVmFfdFJ5c2FuTzJsejRJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOTU4zam5WemNDYnJYUlpxUTFNbHNwWkpUa0pDazRVVWtDYXBma0hzSlFMaFhveU9HQ2FSTDQta2ttaU1mVzVCME9FajFYa1BONVJ6MFNPakY3VkxXTDVBcms4UERBRXUxdU00c3RrcjdxYnRQMlJLZnpfNS1hbWxYZjgxSXUxWTNGZjhpT05PQldxa18yb3d1bGhn?oc=5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>15-05-2026 09:30 UTC</t>
+          <t>15-05-2026 10:33 UTC</t>
         </is>
       </c>
     </row>
@@ -949,22 +949,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Hikma Pharmaceuticals PLC stock (GB00B128J450): FTSE-listed drug maker in focus after recent share m</t>
+          <t>Hikma Updates Registered Office Address in London</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxPaEFqVU10c1FaNldOOTlHZkE3Xzd2SEx2SmNNc3A2UE5QbkIyOHEybWp1OEczLU1MZVFZU21DOFBhM2pLMGU3dmN5S040TTdIZ0R6ZUpKUHpyWXItU0JpSEVmX0JzQnBQNWdkYlNadk05akR4ZVN6aTJCbkVsS2xyWmhSbU1fbjRoZExjWUJZeUdiUVhQbm5ybGE1ZERsUm8ydjZ2UlljMzY3VmJQWHlIWGFHclVXVFh5U2k3XzkybHh6alhNTUJZVA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNcFFNUjFmSTJYc0pSeldENmZTT0dpVlNUUWpHNGk4M3hTQTd2LWhqdnd5WkdnQVNsSnJwR3BqWnM0VjZocVM5SVVlZ3FkLV9BRm5VNlYyYkZ3REZDZTE2S3pVV2RNOG9mY2E3NGxrTV9fdU9ubFdpaHV0UDlybWFiNEZFTWFIa0l3QmZJNkV6aTVYb0FEVmFfdFJ5c2FuTzJsejRJ?oc=5</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>14-05-2026 19:31 UTC</t>
+          <t>15-05-2026 09:30 UTC</t>
         </is>
       </c>
     </row>
@@ -976,22 +976,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Hikma Pharmaceuticals PLC (OTCM:HKMPY) SEC filings</t>
+          <t>Hikma Pharmaceuticals PLC stock (GB00B128J450): FTSE-listed drug maker in focus after recent share m</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GuruFocus</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE1WZ1F2UklnblU2LVBselVqS0ZERlFGMnhPZVItUTlCNlA0eFhCcWJzX0M2Y2k3N2dyb1RHdEZmVjBHU1hzRDhoNWpXNVVNSGZkcnM3YXRpbHlCa1ZZN2ZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxPaEFqVU10c1FaNldOOTlHZkE3Xzd2SEx2SmNNc3A2UE5QbkIyOHEybWp1OEczLU1MZVFZU21DOFBhM2pLMGU3dmN5S040TTdIZ0R6ZUpKUHpyWXItU0JpSEVmX0JzQnBQNWdkYlNadk05akR4ZVN6aTJCbkVsS2xyWmhSbU1fbjRoZExjWUJZeUdiUVhQbm5ybGE1ZERsUm8ydjZ2UlljMzY3VmJQWHlIWGFHclVXVFh5U2k3XzkybHh6alhNTUJZVA?oc=5</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>14-05-2026 14:56 UTC</t>
+          <t>14-05-2026 19:31 UTC</t>
         </is>
       </c>
     </row>
@@ -1030,22 +1030,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Parliament session begins for confidence vote on al-Zaidi government</t>
+          <t>Opioids Market Will Generate Booming Growth Opportunities</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>شفق نيوز</t>
+          <t>openPR.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPeDNNSmxlODc2dS04Y0VlYlVzNVhJSVJmUjh4TWtFbDNkeWRsN3JXZURuR0xabFVvNFdJc0RjbUxFVUd5U3hFMzFHOTQ3MU04YkxkbERBTVVFYmFYS0lMMmpoZm95UWxHdHMwZzdkaE9YcWlkVlJiSm9CV1dITmdfcUpzZWJuS3RGUzI4Y2N5cjkyMy1ySFlFVjYyTXFXWlYt?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNdnRWcHlYaGIzMVdTeExmRXdqc3VGaXRiME12TkxiempiUGoxXzFlY3lGWFhPX2hVLURCbGF5NXM4QmJIcXpGZXYzRFpRdzdqQXpQa2p2XzY0MXFSY0ZVd0tsR1NoVXNwS05Hc1lJQ2ZWMXdjdzJfMWQ0eXZRdTk3cEl0SGFhR1BrYWV4a2VUQ0JjdXJyeS1IRw?oc=5</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>14-05-2026 14:50 UTC</t>
+          <t>15-05-2026 12:55 UTC</t>
         </is>
       </c>
     </row>
@@ -1138,22 +1138,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Arbejdsmarkedets Tillaegspension Invests $24.26 Million in Amgen Inc. $AMGN</t>
+          <t>Amgen stock (US0311621009): weight-loss hopes and Prolia boost after Q1 numbers</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MarketBeat</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPTWFpX3NBaU9DZzREc1hHbzBKQ3RsaEVKMUh5NWFmeGtTUnI4LTlDZUxpcm10cXV1V2lfUHdHdmc1ci10MEVnQTBBX1F0UmthQUM4MWZWeWlFM3NTNlE3MWMxY3pOTEhSWmNwdjQxd0Y5VU80MDduODRlRkU2WmJZRzNVaTZHR2ZpbWx1Vzd3T0xNQlVJR3ZmTjZhUnFBODRjQzcwTVNfS0xzbWl5QVBsS3RxeDhTZFVBX0t0S0tjaV92TVVDSlk1MVlPQV8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOUk9zYnZFcE1JaVVRN0QxdWJIT1VpX00zTkF4Sk5sckJxZThZSHJGclg0R0F5VXc0dGRiUmRtTGhRdmlVNk5TakZBME5QV1lMWFp2Vm1IVWtJdjh5Tm4teG9JYUdCLUlzWi1UVTFwWmZZcVBja1k5a1ZlbHUtZDI2c2lPbnFkLU52c0dwVmdJelJJVG02RUs1dlJ1Q2JGcGNpWUNFeDZfd2tTeVhiQjRYYjdMejRpcFRndllOSUN1WXRXc3RIRlE?oc=5</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>15-05-2026 07:37 UTC</t>
+          <t>15-05-2026 06:01 UTC</t>
         </is>
       </c>
     </row>
@@ -1165,22 +1165,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Amgen stock (US0311621009): weight-loss hopes and Prolia boost after Q1 numbers</t>
+          <t>Amgen Inc. (AMGN) Is a Trending Stock: Facts to Know Before Betting on It</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOUk9zYnZFcE1JaVVRN0QxdWJIT1VpX00zTkF4Sk5sckJxZThZSHJGclg0R0F5VXc0dGRiUmRtTGhRdmlVNk5TakZBME5QV1lMWFp2Vm1IVWtJdjh5Tm4teG9JYUdCLUlzWi1UVTFwWmZZcVBja1k5a1ZlbHUtZDI2c2lPbnFkLU52c0dwVmdJelJJVG02RUs1dlJ1Q2JGcGNpWUNFeDZfd2tTeVhiQjRYYjdMejRpcFRndllOSUN1WXRXc3RIRlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPUUF3bUJPeDgxbnc4RGJvd1RZSmkxcncwMl9rYjZ5RUxJZnowaGs3c3dQUFhLeURiY0pmZGVMdGU1eDB6YVlEZTlaNFJoNFh1Vk5YenEyS2dINnRSTGxyX3JLWjIzdXk4bzQyVF93blpNTTY2SnZvYXN3MlNmN1FubF93b0FSRkFMS3NfcEhTR0tiRC10Y3NKdGlB?oc=5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>15-05-2026 06:01 UTC</t>
+          <t>15-05-2026 13:00 UTC</t>
         </is>
       </c>
     </row>
@@ -1192,22 +1192,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Are Options Traders Betting on a Big Move in Amgen Stock?</t>
+          <t>Arbejdsmarkedets Tillaegspension Invests $24.26 Million in Amgen Inc. $AMGN</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>MarketBeat</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQNkYzeDlWM3lKTTRZUnJDN2psM0FwbVYxU1BrLUVJODU5V052dWJ4TC1mUlJLVXpNaWhpb1o3aEpvWTVVQ1VSbTVyMTJBeDVJbG53RlR1Y0F3SWZxemdUeE5XMjRDUjFvbDRXcVlwUXNyRGNXb201ZmxaRTdGQ2YyOVJla3lwd0FSRFBuaDFQcmJfSWp1UEQzOWREXzhEVVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPTWFpX3NBaU9DZzREc1hHbzBKQ3RsaEVKMUh5NWFmeGtTUnI4LTlDZUxpcm10cXV1V2lfUHdHdmc1ci10MEVnQTBBX1F0UmthQUM4MWZWeWlFM3NTNlE3MWMxY3pOTEhSWmNwdjQxd0Y5VU80MDduODRlRkU2WmJZRzNVaTZHR2ZpbWx1Vzd3T0xNQlVJR3ZmTjZhUnFBODRjQzcwTVNfS0xzbWl5QVBsS3RxeDhTZFVBX0t0S0tjaV92TVVDSlk1MVlPQV8?oc=5</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>14-05-2026 18:57 UTC</t>
+          <t>15-05-2026 07:37 UTC</t>
         </is>
       </c>
     </row>
@@ -1219,22 +1219,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BioAge Labs, Inc. joins Amgen and Novo Nordisk to outline future obesity drug innovation at Fierce Biotech Week</t>
+          <t>Amgen Inc.:</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Traders Union</t>
+          <t>marketscreener.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNTU5RWk1UWDNBU3E5ZkM2b1RyYU9TOUxjWGFQVGFCNXRsMlpqdE1NaGo5SmMtZ2NsR3ByaG9od3JicGcwbnFSYlNRSDFDUC0xOFd3bS1RZUI0Y3RVeXQ0U2JxSVA4a19OQnhDWjFqLWtFU01qWVlKYzJoUUk2SnhVdXVMMXVnTS1NTjJiLXl3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE55dzljTzJodEdYQ3JkYmkyWTNLSEFMTGFrS0NvTzl1R1QyeDIwc3NXQjcwYkRteERPTEI2Nk9VclRKVjdZVG5WUS1pdFVPU2pfZDlaLVhXOFRfRUt1RDI3YXZSMGR3cXVYTzEtbkRWNFR4SFU?oc=5</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>14-05-2026 22:28 UTC</t>
+          <t>14-05-2026 22:00 UTC</t>
         </is>
       </c>
     </row>
@@ -1246,22 +1246,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Piper Sandler lowers Amgen stock price target on rare disease outlook</t>
+          <t>BioAge Labs, Inc. joins Amgen and Novo Nordisk to outline future obesity drug innovation at Fierce Biotech Week</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Investing.com</t>
+          <t>Traders Union</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxObFJMTnlMM1pFLUZLdlhKc2Jid1oxY0s2c3FIbGd2Um1nSlZRUjZTTjZ5LU42RkJFR3hEeFZNbEFVMTR0TmRfUnk4UVdpVXprQVpPTHVjVDFJQ19OT1VLZnpQSDJpNjdXc3J3NTIzelo3WFE5X1R5RDFQVFBlUndHV0dxNVZDMUszWXhHcmV3ekxtWmctMFROVjNITmNTUnFwNGdVWG5DeDFaYnRwaFprN0xtYXVQQUl1OWZuUnNXRjVnc2M3SnFHZQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNTU5RWk1UWDNBU3E5ZkM2b1RyYU9TOUxjWGFQVGFCNXRsMlpqdE1NaGo5SmMtZ2NsR3ByaG9od3JicGcwbnFSYlNRSDFDUC0xOFd3bS1RZUI0Y3RVeXQ0U2JxSVA4a19OQnhDWjFqLWtFU01qWVlKYzJoUUk2SnhVdXVMMXVnTS1NTjJiLXl3?oc=5</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>14-05-2026 13:29 UTC</t>
+          <t>14-05-2026 22:28 UTC</t>
         </is>
       </c>
     </row>
@@ -1300,22 +1300,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Is It Time To Reassess Amgen (AMGN) After Strong Multi Year Share Price Gains</t>
+          <t>Piper Sandler lowers Amgen stock price target on rare disease outlook</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>Investing.com UK</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPTlFFNDVEZFdMUVdiZGxRLWE4VkF3LVdScGZ4THpZN0FYdndpaDM1ZjhwUERhbHMxMGptMW16YzhIZGRRSHotenZlY0gtVjlRSS1BaElNQnNyZy01OXhxVzhoMVp5NmpUVEwyOEhhX0pmLWlURWNmeGJ2dHNYUXd3RE1qcE00UzYtSDR0Smc5WFl0ZU55QnBRczlieUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPaFgwTVlRUzJxSzFwM1BaTVBhRVUxc3hXSzZYVHBueXRTaVVMM0VQMkxkLVhjMEdrVXFtQVRoU3BCUHBkci1OXzlES0lIdTRWcWppamthTzM1MzNoZ3BVelB2X3RJSGFod0RaU01ESVRZamk2QWVkZjlIVlZDZlctUWhkc2s1ck82R2RESjhYbVY0LXFOZTNpcHlIZjdET1h1SFRsNlpQN2MyQVVmUGVFRURGMzRUZGJQa0QzWHkxcEs3ZUljWjRLY1FkcEt6eWJ1Vmh2blZRaUl2Zw?oc=5</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>15-05-2026 03:16 UTC</t>
+          <t>14-05-2026 17:19 UTC</t>
         </is>
       </c>
     </row>
@@ -1327,22 +1327,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>AMGN Maintains Overweight Rating by Piper Sandler -- Price Targe</t>
+          <t>Is It Time To Reassess Amgen (AMGN) After Strong Multi Year Share Price Gains</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>GuruFocus</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQS1MwbEN5djhrY0o4cGNlbHY4YWIxSF9MeF9FTEl3SS1hME1xZzZmTXFVTy1DMnNhajhzNEs5anExUXNUMkZDNmxoWGV6QzFCUzZHa1E1R0ZNYTdXeUhYQmQ1cVFncWxlNUxKY1RRNmw2dEJLdlFOcWtka0JFTkhHNU5DOFZzdk1xcHZuQmpaVzl1d1hFWnRJZ0V1YWI2M2V3dVJRMHNnN2ZmMFdlMEhZcHJlWEgzQ2V1bWExWlpOX1U2ZXJnN2pr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPTlFFNDVEZFdMUVdiZGxRLWE4VkF3LVdScGZ4THpZN0FYdndpaDM1ZjhwUERhbHMxMGptMW16YzhIZGRRSHotenZlY0gtVjlRSS1BaElNQnNyZy01OXhxVzhoMVp5NmpUVEwyOEhhX0pmLWlURWNmeGJ2dHNYUXd3RE1qcE00UzYtSDR0Smc5WFl0ZU55QnBRczlieUE?oc=5</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>14-05-2026 21:22 UTC</t>
+          <t>15-05-2026 03:16 UTC</t>
         </is>
       </c>
     </row>
@@ -1354,76 +1354,76 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Amgen stock (US0311621009): Piper Sandler cuts price target amid rare disease review</t>
+          <t>AMGN Maintains Overweight Rating by Piper Sandler -- Price Targe</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>GuruFocus</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNYUVZTjZneFp0dGFKNEZCTGtFcWZ4TzFUVEdzZmRyaFpIbEg2OENjUXQwbmFqSU94RXZod254VWUwVEFIQlhxRGk0Wi1udkpGWmZRbWNjQ0NtOWU1YUlrT3AyNDc4alFOSWpaUVAzMFpUeVRWYjZUYUxTeWx2Tng5YWZUR2dhTHlSd2RzVlZfdlJHaUdlYWZhWlVuVFNiU2JITzRxdmgyVUdVemNrajRlR3FaTnp0NHB3N01NNlkxemZfN2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQS1MwbEN5djhrY0o4cGNlbHY4YWIxSF9MeF9FTEl3SS1hME1xZzZmTXFVTy1DMnNhajhzNEs5anExUXNUMkZDNmxoWGV6QzFCUzZHa1E1R0ZNYTdXeUhYQmQ1cVFncWxlNUxKY1RRNmw2dEJLdlFOcWtka0JFTkhHNU5DOFZzdk1xcHZuQmpaVzl1d1hFWnRJZ0V1YWI2M2V3dVJRMHNnN2ZmMFdlMEhZcHJlWEgzQ2V1bWExWlpOX1U2ZXJnN2pr?oc=5</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>14-05-2026 15:54 UTC</t>
+          <t>14-05-2026 21:22 UTC</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Amneal Kashiv Biosciences</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Conning Inc. Acquires 97,957 Shares of Amgen Inc. $AMGN</t>
+          <t>Sandoz wins EC nod for two insulin biosimilars</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MarketBeat</t>
+          <t>The Pharma Letter</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOcEV5ZHczekhLTUdnd016bTdLdGhFT3pGR3hqcVZLNmlVQ1I5Nkl2VUh1R19GVUR2VlM4TEJSN1k4Y250dVlGS1RHdEs1bk9lcFNUeFYwX1BuSHVLYkFnZFZSeVloMk5MdzdlMXNZN0lQaDNXbVJoSTBOSUpoV1ZOczlpamFFLVV6dlhvd1k5azNqUTlMbmtmUU16SFVJQldnblBadTlldzlPQmRYX0JFMXNR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQMzl2dWRydmd4RHVydjhtRGV2Q3BvTFdYN1UxTnBwaXIycUpxNE1nUF9laGxNdS1aTURLTVE0a1Atc1l0eU91WEIyLUUxamZVRW9wNTFFZGhGcUlFMDJSTjF3TzZNNDNMWWhjRG5qZFVSaVNYNDVxNkJ0dXliYUpvMDB5eGZxS2tBRXdUTHVPcDJnc0RQZkpzOWx3NA?oc=5</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>15-05-2026 08:18 UTC</t>
+          <t>15-05-2026 12:42 UTC</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Piper Sandler Maintains Amgen(AMGN.US) With Buy Rating, Cuts Target Price to $427</t>
+          <t>Organon to Present New Research on Access and Value at ISPOR 2026</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Moomoo</t>
+          <t>Yahoo Finance Singapore</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOdDRmVmRhNDk0MTRFcm1kMFNBU2JXSjZRdC01Vm9hQ3FfUUp5d19wdVJMblFUSDhJdzg1R09MV2pvYmFTVktueUE2aUVTUlVualo2NUh4RlRQNURLMVRuZFBlTU5nN3RreHFfbTA3dU1fcTNGQWhXU3llSUdsak84cjJXV1ZUTHpXTmFrLS15SkZHWWxoMU55ZnU3cWhzVTNGTlF2dVRnb1JVUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxOU0hnRXdSdl9IZVowNDg2MFRyVG5IaE5IWDdrN3hRVTNKdlp0ZTBGdk9EeDBiT0ZvbEdreUs0U3FiZE1nY2h0YWNzSDhpVHBaaXBsblRLYTBYaHF5VV90ZXFFNnF3NkdMXzZLQnJrMU00cjhqa0RxZnZWck9GM1k0a1BMUjNGaTdzbjk1aW1TRQ?oc=5</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>14-05-2026 11:38 UTC</t>
+          <t>15-05-2026 11:30 UTC</t>
         </is>
       </c>
     </row>
@@ -1435,22 +1435,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BRODSKY &amp; SMITH SHAREHOLDER UPDATE: Notifying Investors of the Following Investigations: Veris Residential, Inc. (NYSE – VRE), XOMA Royalty Corporation (Nasdaq – XOMA), Organon &amp; Co. (NYSE – OGN), RE/MAX Holdings, Inc. (NYSE – RMAX)</t>
+          <t>Organon to present new research at ISPOR 2026</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ChartMill</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9wJBVV95cUxPU3F0d0FlU2ZqVmxEQmZUWEZPNTcxd2kwek53MnR3RWY2SGRtQzhvQUZabTFTRVh4QThLNExVV3R6ZzI3bGpJY2RVRWVKNEZKYVN2c20xMGltMUhfTmJuU3dhdmROWnBTRVI5TFdUWTNNN2RCNmRyZWVrMy1GdEUtWTFaRmFRYzBSYWdmbmFBYzJFbF85U3JDZGctdU9NcnhlZ1pvWEc2NGZ1OTlsWHhxal9QMkM3NlJIMHdqVlpHbEIwdk13OFZJQm5RVjVCQ3RNeDdmYWVEUDlqT0RoLUFRT3NQVUJBbnNhb21uRHViUDlUd3lfZjdHZTBUMFFyOE9vY1VVMzk5X1hieGg2Nkt4XzdHVmtqRUtmbmdmS00wVXJkMkhmTjA3OFo3ZEY5dkt3ajBjNk9CZmUwR0hrc3ctMXgwZE55czdkMnBkeGNSMWU4WVBPeVV3bm1heTZhOXJOV05LRl94S0tGMW9hUVZFZlJ1RURIOXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPc2JSRTktQkNieVNEaVJxR2F3SnZ4UjNEY2txaHZqWG5HQzJESzRkejlvZmpCYmJ2ZlZMWTBLcFVRamN4RTVrNE5DZHhvWTJsXzlDUEhuYlNoc1dmbDh5MUU3RmpjZVIzS1M5ejFyalJpS0ZPWHFNLW1CbzRTdE1JR2ZZRG5BcS13UXQ4ZFJXdUZrMklvVjFkSWN5dw?oc=5</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>14-05-2026 17:51 UTC</t>
+          <t>15-05-2026 14:07 UTC</t>
         </is>
       </c>
     </row>
@@ -1462,49 +1462,49 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Are XOMA, OGN, VRE Obtaining Fair Deals for their Shareholders?</t>
+          <t>BRODSKY &amp; SMITH SHAREHOLDER UPDATE: Notifying Investors of the Following Investigations: Veris Residential, Inc. (NYSE – VRE), XOMA Royalty Corporation (Nasdaq – XOMA), Organon &amp; Co. (NYSE – OGN), RE/MAX Holdings, Inc. (NYSE – RMAX)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>ChartMill</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQYWh4MmVxWl9ERVhPVXFSNUl5aHRMNUVERTM2aXduX0JVOG9YRnlPcUhoQWN2bGpvemJZYjRkZ2RpZ1V1TnBna0RhR0xNZnJ2Vms4MlRKN3ZhUkw5bW5ValZRT3ZQdllycVNVWGxSWE80V2FHOVVZZjduU1dFeUVaTnU3Ykt5eGRFT1RUa0hIMWlTZjZaRllPNUh1MEJjdGtHTWFIWlhOQzQxZ21HUkpDVzdZcHdmaExmSjRIT213?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-AJBVV95cUxPV1dwSlpGNFE0YXJmQkhSMzBFQ1ZvbXNjTmViM25QaUV5TjdnYlRvZ1NUUEo2N3hzMjdNSC1qUkZZYUp0Tjd2QlpNQlllVWxUejRTVTZpWUs5UEI3eWU4NHp5S3R6ajA2X244eU01NDRGYnNLYV8tQVBZaFhuNFRNMWZxNUF4ekxIb09KckdkSFFVRnRmVy1HbnZWZmUwZUx3NDVkS1IxRU5oSWFQY1NGbzdfbnB2c2xCX241YVk1VExGTkw2RmFzSm1HWWZLSGJYSlZJb1Y1TkJMZXlVU2k0MC1IdHA3V3lMOWF5X2tGMmVpU0JaZ3pULWN1RXRjSG9oRlQ0RHRQdTdpcl9mWkNVUnBBcE1NLTJsZnJfemdDVFFXZ3pzc3c1cUpoMkdOZmpIMWtJTElqZ2pkeGw4cy1HWVpYUWNRWU5fc2d6SnVBdlp1bmMzT1Q1LVVCTEdqdEtnN1FNV3dwZENwbG03VTJYUnpjRXRsMzJG?oc=5</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>14-05-2026 21:25 UTC</t>
+          <t>14-05-2026 17:51 UTC</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Apotex</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Heart disease risk climbs in menopausal women, experts push earlier, more aggressive care</t>
+          <t>Apotex launches Apo‑Semaglutide Injection™, a generic equivalent of Ozempic®, in Canada</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>The Manila Times</t>
+          <t>PR Newswire</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxNRDJza29HblhtTlFzWjlORUdaNnZmbXRtaE5tMjlyOXV0NXpxZjJKUlM1N2lENjZsVW9fVndReVpjZWc1a0NvNnFGWlF3SS1xT1Q0M2NNc1ZBNlBOeF82VV9wUFpzSUdqQTExZF8yeHF6eTY5eUlxRHZub0g2ajNVYVh4dlF6WldUY3VkdFI2WXBSMGpnUG5nSG5MN1YtOE9hc3hZamU2LUJNRjhieGNSTFllZzJlZWNnVHB4bmxjdm9kNkNjTFplbDE1NGtJa3B4elUwdUxoTTJONUlyMTFscUFpa1dZd9IB5gFBVV95cUxNRDJza29HblhtTlFzWjlORUdaNnZmbXRtaE5tMjlyOXV0NXpxZjJKUlM1N2lENjZsVW9fVndReVpjZWc1a0NvNnFGWlF3SS1xT1Q0M2NNc1ZBNlBOeF82VV9wUFpzSUdqQTExZF8yeHF6eTY5eUlxRHZub0g2ajNVYVh4dlF6WldUY3VkdFI2WXBSMGpnUG5nSG5MN1YtOE9hc3hZamU2LUJNRjhieGNSTFllZzJlZWNnVHB4bmxjdm9kNkNjTFplbDE1NGtJa3B4elUwdUxoTTJONUlyMTFscUFpa1dZdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNdzVwUm9XNVlaT29GNkRONFM4YnlRelJlMWttRF96dTBaOVlGRzdDb0xrcTIzcVBoUkc5TUNURm00ZzhJYTZzZEg5NmxkQ2xXUlhWRm91X1hYcGFvQkRHNE1taG9pOE1jaEZ2UUFsTEJnOE00QVE4cTVLSDl1eVpqc202ZGdxSEJ1QVhGc3BsekRZd0kzNDNmb1lSWWliUkhhb3pESk5QejNXZkkwWGxuTnU0WXpibnVXMnpGNW5FNDVwTjE2S2R6S05KeC1WNENNcUwyRg?oc=5</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>14-05-2026 16:27 UTC</t>
+          <t>14-05-2026 20:23 UTC</t>
         </is>
       </c>
     </row>
@@ -1543,49 +1543,49 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Apotex launches Apo‑Semaglutide Injection™, a generic equivalent of Ozempic®, in Canada</t>
+          <t>Apotex Launches Apo‑Semaglutide Injection, A Generic Equivalent Of Ozempic, In Canada</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>PR Newswire</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNdzVwUm9XNVlaT29GNkRONFM4YnlRelJlMWttRF96dTBaOVlGRzdDb0xrcTIzcVBoUkc5TUNURm00ZzhJYTZzZEg5NmxkQ2xXUlhWRm91X1hYcGFvQkRHNE1taG9pOE1jaEZ2UUFsTEJnOE00QVE4cTVLSDl1eVpqc202ZGdxSEJ1QVhGc3BsekRZd0kzNDNmb1lSWWliUkhhb3pESk5QejNXZkkwWGxuTnU0WXpibnVXMnpGNW5FNDVwTjE2S2R6S05KeC1WNENNcUwyRg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxNdklUWVJHbzJQRlZtbFdLSHR6WGo5cVFYV3NPV1o2amRBZUxLcnlQN0xqX2Fhd0R1VW5yNkY4WWNRRHlBVl9fZ29FWURfYVplT1A1QkJpREdzZ2JOVVo3c183YXhfWVhrdVZzbDB3X3BLOTlaV0dLVm05VEpJckNKdFJqd3A1N0dlX0RGSTJMR0xZU0p1NHU1bFY4VUg3OGF6NHhHalFaeC1wX2VBUW5XVGsyZ0xKakJ2THBJei0wUWdsaXliVWNZbkFXQW04VXF0cnFSLWM5dWZoUnBxZkdsTkFBSDFnVHZa?oc=5</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>14-05-2026 20:23 UTC</t>
+          <t>14-05-2026 20:35 UTC</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Apotex</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Apotex Launches Apo‑Semaglutide Injection, A Generic Equivalent Of Ozempic, In Canada</t>
+          <t>Scientists find a previously unknown cell type in plant roots that help seedlings survive droughts and poor soil conditions</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>Earth.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxNdklUWVJHbzJQRlZtbFdLSHR6WGo5cVFYV3NPV1o2amRBZUxLcnlQN0xqX2Fhd0R1VW5yNkY4WWNRRHlBVl9fZ29FWURfYVplT1A1QkJpREdzZ2JOVVo3c183YXhfWVhrdVZzbDB3X3BLOTlaV0dLVm05VEpJckNKdFJqd3A1N0dlX0RGSTJMR0xZU0p1NHU1bFY4VUg3OGF6NHhHalFaeC1wX2VBUW5XVGsyZ0xKakJ2THBJei0wUWdsaXliVWNZbkFXQW04VXF0cnFSLWM5dWZoUnBxZkdsTkFBSDFnVHZa?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPOVh4NHFaLVZvTEpvVE9uZDNlZTViQmQ0czVqTHFKLWItenVWOUNDZGNfV3ZfX2JnelFMQi1INU9memtCVFVhdXRrS3RTSDBTaHZocFBtaDNIOHJ5MWdMQU1rZ0x5dDRRV3N5ZVdhbHNmVG5HTlJrd0FaT05iMVpxVTFjSk80dkFNcUxyZ0J4blVWRDdXTlNZLVVncE1aeUNyOHYxajEzZXdLVGls?oc=5</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>14-05-2026 20:35 UTC</t>
+          <t>15-05-2026 15:33 UTC</t>
         </is>
       </c>
     </row>
@@ -1624,22 +1624,22 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>World's highest solar thermal power plant completes mirror installation</t>
+          <t>Scientists discover hidden math secret inside Chinese money plant leaves</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>China Daily</t>
+          <t>ScienceDaily</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE9aUFV4MFd5ODd1alVtU19tSWxhLVROMGdKYlN6NXRCTEZkTU96YVpncTd0Zk5FSnhDRjV3ZXJPYU1VYlRKSzBHOVcwbFY0Y2x3SW1jXzJPTnV5T0tWMlFEcjhMa2o4T2VNWjkyWmVYYnhQZVJKMjMzai1tT2VPZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE42WWlTcjVCVjZuOXBtVXhzMGYza094c0RTQ3l0V2tNTDNBQjh0QmVhZjQyTzZJbHZsVk1TS21SWUx4V0RrbVBudzhzUmM4RmVDTS0ya1BPeE42NlZvR1p3SGt4R3NOaV9LZTN0a09XOA?oc=5</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>15-05-2026 06:08 UTC</t>
+          <t>14-05-2026 19:29 UTC</t>
         </is>
       </c>
     </row>
@@ -1651,22 +1651,22 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>The slowest-looking plant on Earth is evolving faster than scientists expected — here’s how</t>
+          <t>Sun Pharma recalls cancer drug after finding glass particles in some vials</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>BioSpace</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_AFBVV95cUxNWnZpWFZZTk5sRVNiWTg0QlBjMkVHWGxwbmplb25RV3ZjS2JJNkR0ZGFYdWVvdDNibjY1TWdwM2dxUzl2Ul8tX0tidzVNRU5VS0Y3WUtkS0EwVzZUNHZWcks3cms2eHhZeWlXcjI2V1d0RjM4MktTakJNRE1DaXZxRW1oTDQ3WGk5bDVWbGs2QXU3eGpwc3J0LTdiLUNHbnJCVUVyS0lBQUcxcFh2MnVxd2s4NXRtUzZiRVlQdGlwRWNBTVVQSVd2UFBGSmpSSG1GdFpVQjRyWWhYWHB1bUZibWE1eDlrVTVzMXhVbl8tZW10Nkd1UEVEb1pDOEvSAfwBQVVfeXFMTVp2aVhWWU5ObEVTYlk4NEJQYzJFR1hscG5qZW9uUVd2Y0tiSTZEdGRhWHVlb3QzYm42NU1ncDNncVM5dlJfLV9LYnc1TUVOVUtGN1lLZEtBMFc2VDR2VnJLN3JrNnh4WXlpV3IyNldXdEYzODJLU2pCTURNQ2l2cUVtaEw0N1hpOWw1VmxrNkF1N3hqcHNydC03Yi1DR25yQlVFcktJQUFHMXBYdjJ1cXdrODV0bVM2YkVZUHRpcEVjQU1VUElXdlBQRkpqUkhtRnRaVUI0clloWFhwdW1GYm1hNXg5a1U1czF4VW5fLWVtdDZHdVBFRG9aQzhL?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQQlJ3UEVPRjlLTEsyX0JEUjBaaVNVdnlqQzc0cGZKSDBZcE9VS1BKOTFvWVgzM1VPanJ3VVdJTlJHTVVSQld0dlQ3amlCMGF4RlI2dDBSbkNUQUl1Nm00NnJnQmR3LW9hWHVlZWhfZVB0NWEzcTJVNk5OYktGVGppWlVjaTdBVGR3Q3NvUDRfdmZYOTJPaWFwN0RLcHdkQUhoeS1UTU9VMUh5TTNC?oc=5</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>14-05-2026 23:03 UTC</t>
+          <t>15-05-2026 13:59 UTC</t>
         </is>
       </c>
     </row>
@@ -1678,22 +1678,22 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>In situ architecture of plasmodesmata in Physcomitrium patens resolved by cryo-electron tomography</t>
+          <t>The biggest mistake people make with full-sun flower beds that start looking dull by late summer</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Nature</t>
+          <t>The Times of India</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE9hQXdvczY4S1NJV1ZkbVV0b3Jxc1lfLWRWcTJMZ1RDczZRdzNYaUVzcjQ4Qk9vNTc4M3lNamlUbXFRQWJiVVdkTmkxR3QxSjN0SE96d1Y5YjNoSUxjZlJJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgJBVV95cUxPZno4dXA5aEdNbXREY05fd1o3ZGZtUHFwNkNOTHpuTGRSUjdXbE05R3FOd2NxZzRndlNQUlpISGhWNVR5QlBtRkdFdWJKRGdSUkpDbjYzSGthNktCWnlLTV9tUU9sejF6TEJDbVlsN05rM3dKT2VuWXp1YUxSTmwyYUgxYXNvTzhkelUzclFMdzJaZ1F0aTVXbkh4TEp2OTJ4RC1TTUtUUDhRTng1dW1SR2Q4WjY1M29LbVF5eVZSU01iSW90YnVJdUNFNEt1RUxPNk9ra0pLTDQtWnNkZEN6X1F3eHAwOEVTdXBqZzFhdUZLbUZ3Qk5fb2lhQlBZTjFjYTNnVU1naUVKemtRTHfSAZMCQVVfeXFMTnRURGJnSXhnOE9CQ2gxQi11QjB1eWFYVEFHYzhma3NoWFpMZzNIVzk4UVFNMm5ReXNJbVc3eXJ6ZkZpQWt2U3VvRmhCUmJGb0NzbzE4M0pqcHhvOUVTMExVVUI1QVIxRWYwWXlaaEVjOGtPYnhfZTlEZ1ZEc1FJMzVJUmZ3NmYyYm9LMGFkUkh4M2tDY280MmZSTmpOSUpyWmljT1g3S1poUF8tYjJWc2M1dWg0c1BvYm82RHR0WTU2VDJHa0s4Q29GWkY5N28wczU4bnFHc2xqUXVSRTE1amFTZ19QY2xlb0dEX0ZpcHZkbTJZbFlwLVBtUzMtUDhKblAwOTAza1VRMlVpbktJMEZzRmc?oc=5</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>14-05-2026 14:10 UTC</t>
+          <t>15-05-2026 08:55 UTC</t>
         </is>
       </c>
     </row>
@@ -1705,22 +1705,22 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>"Silicon is an essential part of enhancing plant vigor"</t>
+          <t>World's highest solar thermal power plant completes mirror installation</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Hortidaily</t>
+          <t>China Daily</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNOUhUV2NFX2dPZjVYbmlmVFhFNkd3b3VMN0dWR3Z5ZGFJWFI2cFVsNS0ySHlXOXVqTHhxaGRtS2FleFh2OE5ad3BmVW8xUE5PV1FfSXdlVVpiSk5UV0ptVDYzR3ROeXk5RU5DX1VVRVNqUWVmM2pZbzVENVdwNUY4SE5zZWJmNUFWZTVxeEtWM01iMzB0amdwekxWMWtmQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE9aUFV4MFd5ODd1alVtU19tSWxhLVROMGdKYlN6NXRCTEZkTU96YVpncTd0Zk5FSnhDRjV3ZXJPYU1VYlRKSzBHOVcwbFY0Y2x3SW1jXzJPTnV5T0tWMlFEcjhMa2o4T2VNWjkyWmVYYnhQZVJKMjMzai1tT2VPZw?oc=5</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>14-05-2026 12:09 UTC</t>
+          <t>15-05-2026 06:08 UTC</t>
         </is>
       </c>
     </row>
@@ -1732,22 +1732,22 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>The Fragrant Perennial Bulb With Pretty Flowers That Butterflies Can't Resist</t>
+          <t>Jyong Biotech Ltd. Files Annual Report on Form 20-F for Fiscal Year 2025</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AOL.com</t>
+          <t>GlobeNewswire</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNeXJjMW9CVzJ4c1RBUjk4ZGp1cVBCeHN5X2xhMHNYYWdDQzktSWE1QXVhSDNvdFBDdHkxSjNUOE9MWDA2VTgxbzRXY3A0QVlBdUxDZkRzdUFjRnF6ZFZfN0VNOGVkVHl4SEJPcEE0WUpRUEVJQjlaTlg2WWptZ0xoV01uN3JMNHdETEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxQSElJaGFuekQxMGlXTUROeVZmVTZtc1pQVEh5cW82c1lFQ2ZiemVtVDhsN0gtUW5rZWhtak5JZktoTGNLczN3cFhHOEdyQ05uWHh0SWxHbG1XZGt2M1ZvQUgwV21LSkYzYTVnWHRIOFFmMHVncWoyd3U2dkx6MTY5VnYzdFNkVm1DR2JtUFIxOWNieDREd2o5SEJXLVhoX2N4QVU1WWtzZEhQa3ZmdEVuTHMwcV9FbnNZa3VLMk9Qeng2dy1EN1c1NzVjazN6TnNZdHl3N1BRMWVTdUU?oc=5</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>15-05-2026 10:20 UTC</t>
+          <t>15-05-2026 12:30 UTC</t>
         </is>
       </c>
     </row>
@@ -1759,22 +1759,22 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Pak Suzuki launches biogas, solar plants in Karachi</t>
+          <t>The slowest-looking plant on Earth is evolving faster than scientists expected — here’s how</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Aaj English TV</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQMXpaenZqRHBuSGpDMzdVUkV0N2l6VTNGRjg5TWtjLXVvVU1IeXoyZVVYX29jM1ZLVGN4UFQxUm12REw3eXpkR0FPQlkwaUZJMzl0ZG1KLTF2YWJhdl8zemE2Sm0zaTNkc1NodjhIb1c0eVhvU3VDSkh3S1I5NDAtZ1p3Z1hKZmNpN3BiMmMySGp4UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_AFBVV95cUxNWnZpWFZZTk5sRVNiWTg0QlBjMkVHWGxwbmplb25RV3ZjS2JJNkR0ZGFYdWVvdDNibjY1TWdwM2dxUzl2Ul8tX0tidzVNRU5VS0Y3WUtkS0EwVzZUNHZWcks3cms2eHhZeWlXcjI2V1d0RjM4MktTakJNRE1DaXZxRW1oTDQ3WGk5bDVWbGs2QXU3eGpwc3J0LTdiLUNHbnJCVUVyS0lBQUcxcFh2MnVxd2s4NXRtUzZiRVlQdGlwRWNBTVVQSVd2UFBGSmpSSG1GdFpVQjRyWWhYWHB1bUZibWE1eDlrVTVzMXhVbl8tZW10Nkd1UEVEb1pDOEvSAfwBQVVfeXFMTVp2aVhWWU5ObEVTYlk4NEJQYzJFR1hscG5qZW9uUVd2Y0tiSTZEdGRhWHVlb3QzYm42NU1ncDNncVM5dlJfLV9LYnc1TUVOVUtGN1lLZEtBMFc2VDR2VnJLN3JrNnh4WXlpV3IyNldXdEYzODJLU2pCTURNQ2l2cUVtaEw0N1hpOWw1VmxrNkF1N3hqcHNydC03Yi1DR25yQlVFcktJQUFHMXBYdjJ1cXdrODV0bVM2YkVZUHRpcEVjQU1VUElXdlBQRkpqUkhtRnRaVUI0clloWFhwdW1GYm1hNXg5a1U1czF4VW5fLWVtdDZHdVBFRG9aQzhL?oc=5</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>15-05-2026 11:01 UTC</t>
+          <t>14-05-2026 23:03 UTC</t>
         </is>
       </c>
     </row>
@@ -1786,22 +1786,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Nepalgunj Transforms with Wider Roads and Enhanced Greenery</t>
+          <t>World Plant Based Iron Supplements - Market Analysis, Forecast, Size, Trends and Insights</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ratopati</t>
+          <t>IndexBox</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPZTVIbzluV1hRYTlTbC1hVFN2UXVXNnJ5MklIbElfNDJzRHdHYnlScDlZLWVTTlNBV2ZjMVE0ZW5UY3BGdkJNUzhPU1VPSHNmLW9sN1B4TWJUemljdzZyNmZXaGh6ZTVVcjVZcGd0SUM5Tzl4ejVHYzVtYXRlS19rUnMwUzc2b3gxMGVhaE5aLW5hdGQ4aGIwTlRLa0J4QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxPdFBqeUNOZUlBdGJzdU1fMzlyQnFYNFlkMXM3aEx1dFFfSGFfQXpvMFREaU5IUlNJdkRVWGhMV2d2ZXJTaHZvbHdjMjBSSmFpZWF1UFhPdWJkRVNxVU03OXdtd0RKc0dacmhBVF9YM1Z6c3ZPaWZrVlItSV96QXhPLUN1YUpXblNUU3JRWWZXTl9KdS1wNUcwcmxybWVKR3ZRcnNnWVI3SHRYVXdxeE5BMEotTEs4TXpGaFZrdTdWMDhPbWFTMHh5R2lpc2FzRFU3U1NacnAzNHlnNXBFWFF3WU5iMHNIRkFLU1dRWGdndnBkdkk?oc=5</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>15-05-2026 04:18 UTC</t>
+          <t>15-05-2026 08:01 UTC</t>
         </is>
       </c>
     </row>
@@ -1813,22 +1813,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Korean Botanists' Quiet Resistance: Reclaiming Plant Names Under Japanese Rule</t>
+          <t>15 Plants That Keep Blooming Without Deadheading</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Seoul Economic Daily</t>
+          <t>AOL.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPalRhbU9maVN0NzZKYkxsMlpTemZYRjdXMXdBUGFfenY5Z0ZoSzNaLVRCOFkzek92NEtPekZrU3gweHlMWFpjdHVYNVUxRHlRWEdKdy11Sl9OLUhXOU14eXJQSW9aR1QzcmRGM3dMdXoyaVNUSHhmS2RZNnBNM3JQQlBwNmwyV3V3NlBGUWpOOXJrX0RRT2xYelpwQzBwWUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNeks0WEFGYmt0ZjdVS3c4Z3dsRHVjbzZ2aFBxTWhiT0pDaTFjZ2pzM0F0MmhQUEV1MVhTMDIyUkMydGd2Mi1PYmh2WDdPRWM3TUxXYlFsaDM5RE9rcW1ZQTVlQUk1NVB0UGJhcGZ6a1Zod2VKcS1lUTV3RnlGNl85VA?oc=5</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>15-05-2026 08:08 UTC</t>
+          <t>15-05-2026 14:00 UTC</t>
         </is>
       </c>
     </row>
@@ -1840,22 +1840,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Pashinyan Says Armenia’s Nuclear Plant Decision Will Be Based on Economics, Not Politics</t>
+          <t>Prickly pears show promise as the building materials of tomorrow</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MassisPost</t>
+          <t>The Manufacturer</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNUC05V2M1VzRCYXJ4VzYtWlJUQ2hidFJRU2ZwbzJzOUI3ZjNOWnpYYm9HcDcyXzFXMFRKblNPOUFnLW5XNWJPMmlqal94WUdSamhHQy02dEM4dnZJbDlMX0hCRTZZSGM3SGJyTDREY3ljY1hXNUc1NHoyNUhxRF9zbHdvbjVuQ1RtNGlleW9zOTJSTGM5QkJpT1FFWkVqUmY1NXA1RXlGXy1DTnYwTkE0ZDBRTHEtXzZFamhBeWdKNNIBvwFBVV95cUxNUC05V2M1VzRCYXJ4VzYtWlJUQ2hidFJRU2ZwbzJzOUI3ZjNOWnpYYm9HcDcyXzFXMFRKblNPOUFnLW5XNWJPMmlqal94WUdSamhHQy02dEM4dnZJbDlMX0hCRTZZSGM3SGJyTDREY3ljY1hXNUc1NHoyNUhxRF9zbHdvbjVuQ1RtNGlleW9zOTJSTGM5QkJpT1FFWkVqUmY1NXA1RXlGXy1DTnYwTkE0ZDBRTHEtXzZFamhBeWdKNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPbHgybXV4b19tTW9vdXJPV21wTEpuR2RlNFRTdVRkOUtJQlM2Y2RkczlTZXE2ckZ6THdicG12NzFwVFNZRmI3RU55eUpKOVBncFlfUE04dWRZcG1hVl9hNlFHaUdUTkFVMkdheHRXXzJDSmkxRXNNRjlvdGp5dnQyR1V0dTFyZ2JNS21xMXhPQVZ4Ry1oR1ZsaUc1aHUwQzFiaTBfQS1mVnVBQQ?oc=5</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>15-05-2026 01:47 UTC</t>
+          <t>15-05-2026 04:52 UTC</t>
         </is>
       </c>
     </row>
@@ -1867,22 +1867,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>New CDMO business development leader joins BioHarvest Sciences (NASDAQ: BHST)</t>
+          <t>What to Prune Before May Is Over (And What to Leave Alone)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Stock Titan</t>
+          <t>Dengarden</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNVzVCSlVFclpjNGRoQ1p5UHBLSlkxQ2hwUmk5Y0ZjTm05NUpJRUtraUl6ejF2M0s0eC12R3hEMlMzNURYNThvSjZYXzlkRXZZb1F6eEZHZVhvdHVvcWJ2YWVibGltN2xtczdETkM0My1KV0ZmWWRQZFdER2xZOEd6WnhhcE10Z0pHY0N0ZHdLMTN5Si1aWF9kbkw5MlZJWWFTVGdqSXNzUFQyTE90TUNGN3V2NFdTcXdhdDdv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiYkFVX3lxTE1rbGxiRUZaS0FmMG83ZDdYVkk4eGJsd0FNcklzSDF1aGNxaFJHdU1oT3pDZ1hOd2t6dkZpZ29wQ3JZSzB1MTVzTWpzTEVvbHVtSFduUWJ6aFBUTXdqMUNmQ2RB?oc=5</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>14-05-2026 14:27 UTC</t>
+          <t>15-05-2026 12:15 UTC</t>
         </is>
       </c>
     </row>
@@ -1894,22 +1894,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Tooth Fossil Reveals Dinosaur May Have Given Children Special Food</t>
+          <t>Inside Jyong Biotech's 2025 SEC annual report filing for investors</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>VOI.ID</t>
+          <t>Stock Titan</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiQkFVX3lxTFBiRmczREFlT1M1T0xET3lTNFdRa3RXaXo2cUZ2NHVMenJab2hjaW5Ody10bGZrb3VqYkZTQXBmd2NzQdIBQkFVX3lxTFBiRmczREFlT1M1T0xET3lTNFdRa3RXaXo2cUZ2NHVMenJab2hjaW5Ody10bGZrb3VqYkZTQXBmd2NzQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPbjV3QmdyeGtiVW85MEI5STNkZWhsbGNiVlFaTmVfbTAwZzVxbUdTc2dGTzd2YXVQWEJud290M1lYbHVsUGF5VV9MSkdDdEEzVXFHbXhpZWh5WmM3RkU0UUNsdDU4QmlOYlVMbFhHRzdxd2htLWVKSDJ4am5GOWJmX3BRSC10VDBsYWJob1FnLWRTYWlvWkxYRWN4NEtITm9zSjV3VExBRnRvcXZOMGMyVTZSWWZfalpBMFpLN21B?oc=5</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>14-05-2026 22:57 UTC</t>
+          <t>15-05-2026 12:30 UTC</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>$80 million manufacturing plant in Batesville breaks ground. What to know</t>
+          <t>11 Foods High in Iron</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>The Clarion-Ledger</t>
+          <t>GoodRx</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxQUm9mdUZzOWJ1OUF0Zjl6RHp3ZkNSY3V4OVRidE52V0ZQZ0RkZVlUbVBuN0Z5RnhpYmhweTJCcllMRjBPVmtnUTNFYnl6aHVPZUdBX01VNnJrM09UQWZYSm8tSUJxdjJ1NS1wX3VKYWVyY0JUcXRvZTA1OXdyWWZqU3pNS0F6azBPblVfcHdpcUhYd1Y2aUlVWC1fNVVpWmMyUFJlY290ZE5DWHJiTEtLRnpnQXI2LVAzRTZmOTNDb2sydm8xNWNHSHJYYWtick9YbHZvejBPdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTFBfcWU0XzJpOUtPRzdSYzBqclMzX0w2NHc2TDRtQ2pPOFZRMC1HaU5ENkE3LW1KYUdVXy1OZDk1VDJtTTBjYUZySnppUUdXU0ktblZuNXQ2Q1QyNnlIdVNuZFFMUkZKb2owSEN6bjFwSnpKakRVc1E?oc=5</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>14-05-2026 17:44 UTC</t>
+          <t>14-05-2026 23:01 UTC</t>
         </is>
       </c>
     </row>
@@ -1948,103 +1948,103 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Aurora Granted Plant Breeders’ Rights for Farm Gas, Driftwood Diesel</t>
+          <t>Experts Reveal the BEST Way to Grow Rosemary so It Thrives All Season Long</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>StratCann</t>
+          <t>AOL.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNNUR5VHZBaVBGU2hjZTdjN0U3bTNlWVdaRlB5cFF0cGpYczZGbEJIWE13Q05ZRHBuWm5hcGQ1b3BvcUxERWJGbHlzMm9xVEVEYWlaWlhxaGZZeGVxV1gwUndneWtES3pITGk4SXNNUTF1RVNpTWtXV3FCTVhfUE1GZUJhTHIyWmQ3Uk94RGRRU2VPSENYTGxIX0pR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE1tZGdEZmJOeVVsVjNuX0pCMVJid2NGb3UwOXdGZzhBajh0YVFNXy1xTTZPQ2JsWUhEbEZjU3czRUVsUHZ1QjJTbW5hYzB0RXdFUEdkSmtpallraF9ZQXFUaE5pc0FScU1XVk9pUzNpakNHQng4Mkhjc25mbXQ?oc=5</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>14-05-2026 16:18 UTC</t>
+          <t>15-05-2026 14:36 UTC</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Viatris-Mylan</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Aurora Cannabis Granted Plant Breeders' Rights for Two Cultivars</t>
+          <t>1 Stock Under $50 to Target This Week and 2 We Avoid</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Cannabis Equipment News</t>
+          <t>StockStory</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOV0pHMWJ4TExJN3RkMDdpSzZoTk5pQkllcHRKcGtXSlFGNVlQYUljR0ZNeU1Hb3p5VkdLbzVoT25DN0tVemF6TnlzazRmbTMxOWJKZTFRZ3A0azZDbHpfbTNkQUVibnJsUnJiQ1k3S2xMTVhfRjlEYWUtTXZuMlNGbGJVZjlIeUVieEUyUDB3RXlQS21Ga01BampfM19TQl9JalBnQk0tUFMtWHkzMVBpa1JoWnZ6a1VWWndKUGlqcXB3RnZIcEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOa19oNjFwQ0dkSE9jdEVVMnhHU2hjMi0zV3FwNEg5QkJGZnJVREdMeUV4ekJHS2dGdG50bWxFRTk5cDFES2hBUXNDek00Xy1GNm1XV1hEVFJxbUh2ZlZTVG92UjNxN2RiVWZITGxVclowZnEtX3hIVWZJYTI3SUZJSzhNcmlydzBLQ3RqWUNrRFZrU3dVM000WmtKREo0cUJNT2c1TFAwdEpqUHpkVkdoT0FWZ0ZUcFlBYVNV?oc=5</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>14-05-2026 18:44 UTC</t>
+          <t>15-05-2026 09:42 UTC</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Viatris-Mylan</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Mylan Epoprostenol Win Clarifies US Measurement Rules And Equivalents Limits</t>
+          <t>Pfizer’s HYMPAVZI Earns Expanded Marketing Authorization in EU</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Citeline News &amp; Insights</t>
+          <t>Contract Pharma</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxPbHM4VWQtSndIMzVDaVlsc3BjdWdqTDFvaTdUMWFPQzhSYjdTdlEyUnNJSkt2WnprQVNhd1dPYWdMYXlUOV9xYnQ5Y2xyeHk0ZERUX3dvSEM4cG1YNTd2ejFkSDhhcEo2V000cGhCd0lWUmdWTVZZd0hYUjdkbUVtUWRlc2NrVDRiOG41UXZjaHp4TjYzTDQwbFF4dmdndzdxMkpoVUtJcWRDZS1vdlAxRWQ4U19aWGt6RW14cmt0cnhFUFYxQ2ZfbFdlQW9la3pMNUVYbUYydXJuMTNLV29mQVJydjJWUzJmdVNITElTSlFJVmhpOHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNQjQxUFZtc0gzT19HV0F6NUc5ZEFqamdzbXE3ZXhya19VLVFkMG1sX2FsZXRHd2xJMkNvQjFYR3JlS3dpSmhxNEJSdTdxUVRlckhmdmIwM0pFeHlVUHA0cGY5NTEzaThrNkxmN0IyN1lCWE5QaUltWVBINWN5bk9EZG1yNHF6WnBnUmI1d1FsY0JndU9WYWNHUno3dHhrVGd5d0ZPbEFucGFjdkk?oc=5</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>14-05-2026 12:50 UTC</t>
+          <t>15-05-2026 13:57 UTC</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Viatris-Mylan</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1 Stock Under $50 to Target This Week and 2 We Avoid</t>
+          <t>Mubadala Investment Dissolves Share Stake In Pfizer, Ford Motor, Walt Disney</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>StockStory</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOa19oNjFwQ0dkSE9jdEVVMnhHU2hjMi0zV3FwNEg5QkJGZnJVREdMeUV4ekJHS2dGdG50bWxFRTk5cDFES2hBUXNDek00Xy1GNm1XV1hEVFJxbUh2ZlZTVG92UjNxN2RiVWZITGxVclowZnEtX3hIVWZJYTI3SUZJSzhNcmlydzBLQ3RqWUNrRFZrU3dVM000WmtKREo0cUJNT2c1TFAwdEpqUHpkVkdoT0FWZ0ZUcFlBYVNV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxQdHY1M2JaT2JGRnZ0QlFITFA3UEFFNEFQYjNXci16QWdWeXJBZ1FQOHI1Y2lreUNYaVotUGtBQm53X3hSb015ZmZfZnJPdU9IMnR0N3JMSlBzeEtzQ0hnak1sRVZHUVctRTEwZGtxSm5lU0k3TkV5dTdmRWtiNHBLZHJfdHVxVlY2RWxuRFQ5TnRubkVxdVpmVktkQ3FfdE9FUFZsNGNZLXgwTjJURnNFdXJ0dW1wangxbzN5cEpRT0NZM2YyN3c0VUltQ1ZkZzkzZkFxM0hMSVVYMFZY?oc=5</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>15-05-2026 09:42 UTC</t>
+          <t>15-05-2026 16:10 UTC</t>
         </is>
       </c>
     </row>
@@ -2056,22 +2056,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Pfizer, Inc. Stock 12‑Month Price Target Cut to $28.88, Implies 12% Upside</t>
+          <t>Pfizer's Q1 revenue rises 5.7% to $14.5B, beating estimates and showing growth in acquired products.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>Pluang</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPcFNkTGVCY3cwMEZPVmIyOFgwekJlRTFsZ0UzRkIzcmphV3p6TkN3TGtkMUlBSUZHbVJ3XzBzMGpHSU1hMWhiT2hCRlhoUUxxY0YwOThoUGVrR240ZTgzZThiSW93dlYwYU4xMHBBbnNaRXJPN1NOcTZVSGhZYmRZM0ZVQmRSbVJQUllJcXFWTjg2RzRZOG5TVTY2ZVpBZ2JJRndaT3BheGwwUEhuakUtQlpwREdSNXZMUmh3UXdEdE9OMTVCZDBYM2hQdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPT09ySEFVcUlwUlcyWlFYR0xmLWNZZHhPN2ZzbkpteS1xaG9UV2lEMWNXQTdoTk1XMWlTdGl4UTJqWmZKXzZnX2lxckk1Sm1xdVlpenpXc0JRaE12dUZ5cjEyVkpsVjBvZUZpZWFXRnNEUHZRY0g2ZF9DRXVMSURsUmdPT2E0dUlhN045SWx5WlRvUDFJMUUtRW1tRE1UVkJCSUE?oc=5</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>15-05-2026 04:20 UTC</t>
+          <t>15-05-2026 00:48 UTC</t>
         </is>
       </c>
     </row>
@@ -2083,22 +2083,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Pfizer's Q1 revenue rises 5.7% to $14.5B, beating estimates and showing growth in acquired products.</t>
+          <t>A subcutaneous solution to Celcuity’s patent woes? | ApexOnco - Clinical Trials news and analysis</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Pluang</t>
+          <t>Oncology Pipeline</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPT09ySEFVcUlwUlcyWlFYR0xmLWNZZHhPN2ZzbkpteS1xaG9UV2lEMWNXQTdoTk1XMWlTdGl4UTJqWmZKXzZnX2lxckk1Sm1xdVlpenpXc0JRaE12dUZ5cjEyVkpsVjBvZUZpZWFXRnNEUHZRY0g2ZF9DRXVMSURsUmdPT2E0dUlhN045SWx5WlRvUDFJMUUtRW1tRE1UVkJCSUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxPWGJpQ0xfTW5YRVphODBxSkxiYmtjaGY0eHJNOWU4TU5pRFB0ZXUzTURmWU1OVjBXaDU3MzYwLWk0azc2Z29GR1ZHSXpjWG84ZkpGOUxFdTZhdC11dFRNSElLbDJOTjR1ZU1WRGZNN3FLMnZzZS1nbDJiRWdOS3hLT2RKcjktS0NtdjdEeEZn?oc=5</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>15-05-2026 00:48 UTC</t>
+          <t>15-05-2026 14:04 UTC</t>
         </is>
       </c>
     </row>
@@ -2110,22 +2110,22 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>5 Must-Read Analyst Questions From Pfizer’s Q1 Earnings Call</t>
+          <t>Pfizer Ltd. Technical Momentum Shifts Amid Mixed Indicator Signals</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>Markets Mojo</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQYjBVMWkweUttMEhWbmt3TDlLODFyTW5ybmM1cms5c2RtZFo2dHBEYjFheE5KTy1JLUF4Qy1PMlJGbzdzV3BZRXppUjNMbXNEaWpIMEdHbEVFUmk4MzRES0hvQlB1UDJ3bWdIWklzM09NVDVUeEt1Ynk0UUhxQXk0d0V6WS1ad0NGcDJ1MHNEV3kwWUZtSWtuYlphTGp1Vjg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQNzM0d29GZzFrcXNxemU4TkE0MnB2YW5qMGRUb1JnRndnMjZSa3lEU2FMSV9hQy1Vd3ZIWHFFaDJzQUxJa3hySDNUSVdkRm8tVkhEbWZrWC1fZEowdkxLbzVkMmZScUttNlEyMF9kM0NuX2dvTEFDQi1rR1pWdWY5V1BtbHNJUGlVVXpyVDZwbHNJTjZkdk5jYTBkOXJMS0NZV21aSTBDV3RKLXlSUklNNWxGa21hNFh1RnVPeDJZNVE?oc=5</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>15-05-2026 08:52 UTC</t>
+          <t>15-05-2026 03:02 UTC</t>
         </is>
       </c>
     </row>
@@ -2137,22 +2137,22 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>‘Pfizer and AstraZeneca were ABANDONED, yet…': Sen Johnson drops bombshell on COVID vaccine injuries</t>
+          <t>5 Must-Read Analyst Questions From Pfizer’s Q1 Earnings Call</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAJBVV95cUxORmFseEF3SkJXYm85VDhzRFBfUmxmUXJnVTBlVDhIZzFYWmZnUFZsb283R1lpOFZJS2swb0wxbk9hZEgwNnpjemxKQlAwRGdBOXlIVVZOZ1VKRVpHeWRXNlQySWQtWkJJTHlmcmNaRDV3OEJHYkhaNUN5ZVktQU4wYmVEd3dUM1k4NE4ycTJkcWNlLW5KVHFoRmlxd0N3OFBNQ3lncm4tZlo2NElJMnFwWWZvMnh4eldSMldRbUtFOU9OWFduQWFnTC1ydlJIVmFlYmNNTndLZDZKR3Y0bjU2dXFmTzlOMWJkQ1VHeXZXUVlxcHVUcm9HSEhxdlZVc2JSTHpDYmNEWm9XTXZGdDI4Z1BkUUs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQYjBVMWkweUttMEhWbmt3TDlLODFyTW5ybmM1cms5c2RtZFo2dHBEYjFheE5KTy1JLUF4Qy1PMlJGbzdzV3BZRXppUjNMbXNEaWpIMEdHbEVFUmk4MzRES0hvQlB1UDJ3bWdIWklzM09NVDVUeEt1Ynk0UUhxQXk0d0V6WS1ad0NGcDJ1MHNEV3kwWUZtSWtuYlphTGp1Vjg?oc=5</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>14-05-2026 20:13 UTC</t>
+          <t>15-05-2026 08:52 UTC</t>
         </is>
       </c>
     </row>
@@ -2164,22 +2164,22 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Pfizer’s Lyme disease vaccine shows 70% efficacy; Texas man sentenced to 12.5 years in $61.5M Medicare telemarketing fraud scheme; Novo Nordisk launches Wegovy subscription model – Morning Medical Update</t>
+          <t>Community Acquired Pneumonia Market Is Going to Boom | Pfizer, Merck &amp; Co., GlaxoSmithKline</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Medical Economics</t>
+          <t>openPR.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gJBVV95cUxPVnU1X0hLdnNoem8xSWwtUm9LQ28wXzM4aUFsUUN2U1ZsM0Fwb2dIWmNPdGphRVd3cm9RUzBtT0gzYVlyYUV5aHBnOEt4ck9CVnV0NEs5NTJkV2d1WnZSaGs3bUJYUHlzVVBMV2xwRDhnakZiWVlkNG5kTFBmTm0zNHJGNDlhdHhNcVNEQUtaX0ppdlZ1SFlXekZ0Z0Rtemh4TktrWGdPN1VIYnhGZmZnWURLWlhQTjNhUXN0RkV5eE01ZnhhVHd0RXlFNm5PNDBQTjQyOWpHMWRpTUJfV0Y5NjBqcmJvZ0FGWGtZQjdtZW5LcFI4S3U5ZHV6Zl9uc0NZQkpEcDQ1TjRiTnk3MjBGYS1RdjhNaVhvQjVveW5FRFpWQkVicHE1MVlLbURUZTFObTZtS19qN3JrdDF5c0RHb19WZzNTQW5OcWU2MEdGR3pqREVjQWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQQWNSeVhZTlYweUl2VUJ0TG5GdnNjc2FWWlE0cnUxQTU0c2hsaHUwYzdfdkpfOVdLNFhFdG92bVU0ZEdxb1paQUZCYW93dmpaQUNHTnJybU9OazAyZTAtWS1ZcUlyQURSWjhXNDY2TXVGYVAzQVhORFo3bGRwaEJMNXdPc0s4SGVvYjFCZ1lpaHdIOVoyMFVjdmI2TQ?oc=5</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>15-05-2026 00:28 UTC</t>
+          <t>15-05-2026 13:42 UTC</t>
         </is>
       </c>
     </row>
@@ -2191,22 +2191,22 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Pfizer receives EC approval for Hympavzi to treat haemophilia</t>
+          <t>‘Pfizer and AstraZeneca were ABANDONED, yet…': Sen Johnson drops bombshell on COVID vaccine injuries</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Pharmaceutical Business review -</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPZnBaSjdfazl1N0VMZGJqRDh1UmpsTHBEaGtCeDE2NmdiMHo3UlZxbG9TN0c4OWQ0bXVFWEpRVDQwajRsa1YxbkZTeGdTT21QcGRaMlhwWTQwbGE2QlhNWHN3ZWcxRlhySTRrUVpTa0JLNEEwS2RxRXhzZkw3Q3hET3ZBT2FZTjFYVDRBYUtCaHk5LTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAJBVV95cUxORmFseEF3SkJXYm85VDhzRFBfUmxmUXJnVTBlVDhIZzFYWmZnUFZsb283R1lpOFZJS2swb0wxbk9hZEgwNnpjemxKQlAwRGdBOXlIVVZOZ1VKRVpHeWRXNlQySWQtWkJJTHlmcmNaRDV3OEJHYkhaNUN5ZVktQU4wYmVEd3dUM1k4NE4ycTJkcWNlLW5KVHFoRmlxd0N3OFBNQ3lncm4tZlo2NElJMnFwWWZvMnh4eldSMldRbUtFOU9OWFduQWFnTC1ydlJIVmFlYmNNTndLZDZKR3Y0bjU2dXFmTzlOMWJkQ1VHeXZXUVlxcHVUcm9HSEhxdlZVc2JSTHpDYmNEWm9XTXZGdDI4Z1BkUUs?oc=5</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>14-05-2026 16:45 UTC</t>
+          <t>14-05-2026 20:13 UTC</t>
         </is>
       </c>
     </row>
@@ -2218,22 +2218,22 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Pfizer Ltd. Technical Momentum Shifts Amid Mixed Indicator Signals</t>
+          <t>Mubadala Investment dissolves share stake in Pfizer, Ford Motor, Walt Disney</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Markets Mojo</t>
+          <t>marketscreener.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQNzM0d29GZzFrcXNxemU4TkE0MnB2YW5qMGRUb1JnRndnMjZSa3lEU2FMSV9hQy1Vd3ZIWHFFaDJzQUxJa3hySDNUSVdkRm8tVkhEbWZrWC1fZEowdkxLbzVkMmZScUttNlEyMF9kM0NuX2dvTEFDQi1rR1pWdWY5V1BtbHNJUGlVVXpyVDZwbHNJTjZkdk5jYTBkOXJMS0NZV21aSTBDV3RKLXlSUklNNWxGa21hNFh1RnVPeDJZNVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPeGpaQzB6NXdtYjF1M0ZkN3poa2hKckhfOEtGU1RUbGRpQWxZcjVwSWxyVm10VUVyc2JacFExOWVYbGlFUlo5QXo5MEZ6Z0x3cWJWVDd0YnRYWFZMYVNYUXpseWlLeS1od1JTMkswOC1PWXl0emwzZk95dEpPNXNRZERqeWp3RmdmdzBVaFYzcEJGTldDX1NRbHhjYTNCcUZJUzVJMHQ3VFBPemNCR3lUdEJtZHVZeFhzVXpZVVVLcVNQX2s2QkE?oc=5</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>15-05-2026 03:02 UTC</t>
+          <t>15-05-2026 16:11 UTC</t>
         </is>
       </c>
     </row>
@@ -2245,22 +2245,22 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>AstraZeneca scores with Imfinzi in another bladder cancer trial, rivaling Merck's Keytruda</t>
+          <t>Pfizer’s Lyme disease vaccine shows 70% efficacy; Texas man sentenced to 12.5 years in $61.5M Medicare telemarketing fraud scheme; Novo Nordisk launches Wegovy subscription model – Morning Medical Update</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Fierce Pharma</t>
+          <t>Medical Economics</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOLWxpeUtLcHMwdzdXNHdRZFdsT25NT1NoTjVkM0ZmQzd5eUY1NEtpQUhUS2dyb29aSGxSVmMzQmxSM055ZHg2NUs5bUR1aDZFc21YdDhHUFp6VGtqZDMwZ0hTY19YOTMyWE1XTDFtd0ZfdHl3TEVSaVFIV0dIaTZSOF9vbVRybmpkQmRpUTQzN2liRlk0cHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gJBVV95cUxPVnU1X0hLdnNoem8xSWwtUm9LQ28wXzM4aUFsUUN2U1ZsM0Fwb2dIWmNPdGphRVd3cm9RUzBtT0gzYVlyYUV5aHBnOEt4ck9CVnV0NEs5NTJkV2d1WnZSaGs3bUJYUHlzVVBMV2xwRDhnakZiWVlkNG5kTFBmTm0zNHJGNDlhdHhNcVNEQUtaX0ppdlZ1SFlXekZ0Z0Rtemh4TktrWGdPN1VIYnhGZmZnWURLWlhQTjNhUXN0RkV5eE01ZnhhVHd0RXlFNm5PNDBQTjQyOWpHMWRpTUJfV0Y5NjBqcmJvZ0FGWGtZQjdtZW5LcFI4S3U5ZHV6Zl9uc0NZQkpEcDQ1TjRiTnk3MjBGYS1RdjhNaVhvQjVveW5FRFpWQkVicHE1MVlLbURUZTFObTZtS19qN3JrdDF5c0RHb19WZzNTQW5OcWU2MEdGR3pqREVjQWc?oc=5</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>14-05-2026 15:52 UTC</t>
+          <t>15-05-2026 00:28 UTC</t>
         </is>
       </c>
     </row>
@@ -2272,22 +2272,22 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Pfizer discloses new dual calcitonin/amylin receptor agonists</t>
+          <t>Pfizer Refines PF-07799933 Dosing in New Phase 1 Food-Effect Study</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>BioWorld News</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOWEdFWjVHeHpmY29DZmtNZk1iRkd4Um1VaXlZT0twSFk3U2lIVW5iR2R5SHRpcjM3THBwWGZJc2FpcU1XMlJicUlHbVhHU1RmRHlOUE5nN2ZWcXNGU0NybXZsdm1rQ0Vjb2ZveG9GX3AwZWpPTXBWakhBQWU3MGlqTXZOSTM5NHcyU0lfakQ5aGlrRWs5aTk2bDZxdEQtaTZaTy1Paw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPSHhGWm1hZldxYWxLUVhxcnUzRWlMTHJxUFNzRzVxZTAzd1hUcE5zRTRDejZWUjZWY2RWMEJHbFVXY3pBSHRiaUVkWm9ib0Vwbmk3eW1NdkpzMnBTZ2E2SjRxV0x2SnRHanhYeTN3VjFLUmJpR1loYTVIRER2WkJTdG0zbko5ZlNxeXprQU5Wa2Q0MTNKcXJqSGxSNVRjX3FJVE9XMWstZEtlOW1hYm5vWkVMa09aa0p0NUE?oc=5</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>14-05-2026 13:00 UTC</t>
+          <t>15-05-2026 16:45 UTC</t>
         </is>
       </c>
     </row>
@@ -2299,22 +2299,22 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Pfizer Just Locked In Its Next 5 Years of Growth -- Here's How</t>
+          <t>Is This a Sign Pfizer's Aggressive Growth Strategy Is Paying Off?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>The Motley Fool</t>
+          <t>AOL.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOcWJsQnYyV2k5Q1V3RnJKb0ZzTUJWbFEtU1l5TWZqU3p3TWxRMDBSRUE0NTduYmNkSzhkQVFxNlpOSkNkeGpGNEVPWjZhZTZWbFEwZnlMbEFWTUtqYVdaRDM2alRJcUp5S0hnZGsxTmVLQnAwcTVPVnJCTF9zcDdhaC1pZ0hfUGNLejh6NWhjeGpTTFNUOUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNNXNtMGl5X0tLZjRZYkplcmtsbjhldWxteXdJR05hMmhhaGNPWjY4cExVUXVSaThDNjJLT3doY0dXR05mTVlUZ0p1Mm1na215aGg1MWpETGhOSkUwUVhiZjl3YVNBaGpFZFZPQVVWdlJMYnozd0NpY2VnREdUVVZzUHVJR0NqQXRCck5J?oc=5</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>14-05-2026 16:00 UTC</t>
+          <t>15-05-2026 13:51 UTC</t>
         </is>
       </c>
     </row>
@@ -2353,76 +2353,76 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Pfizer scores landmark EU approval for hemophilia drug HYMPAVZI</t>
+          <t>Pfizer's Strong Quarter Secures VanEck Dividend ETF Spot as €2.1bn Inflow Wave Triggers Overbought</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Indian Pharma Post</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQazA0eFBCUl9YeFV5OVFlQzItUTdqYkhLNEZybGhnRHJRaEtQeWk1Mmh4UnQ2Q2pMZVpCM0QybmlhRVVjTHB0YzB0Tk95Q1A5Vm9wa0toMWxNN1pWSnBQME4yV3Zoejkwd3QzeUxBVkFEOWt6UXcyRktCRExOMmpISG5nTUxUT0pTYllSSEpLaWp6NW5QcDZkNXpYcUk4c0NaRUZxT0ZwYVJFeXRKWmtFLTFfZ2Y0RnfSAb4BQVVfeXFMUDBMbEVBa2J1dmpoUWNCM1NZRmxKZC01bExTdEotdjBCVFB2V09nOEl4UnNwRTNfaG55T0FDTS1TZzlkMFduTTFham9JTmZPUWM0YlZualJHMWtYVGdBRkVRVjJycTIxYmtSZlZtQXIxc21lbTJIRWE1QWNqM1FHSkphUWI3V1M1cmRDRW9JUHZ0Skt2NDZHczlrNDJaTnNGei1vbFoydndHSjJkQzNiRDF0VlJLSUhzZm9QVnE2dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQd2JWYzZMelNROG0wcDV0NHhrNUV6NDVfbDdTWE5KVHc2dkJFejk1R1dXcmNmTmpTLWJWZWlOVVRqZVV0cTREYlBIcEVyc2F5MU9LQV9xMnJrbnNhSENpYjZLREgzQk9SS254U1VlYTlpR3RTQm9rYUFGZGtRRTFGTzFuckI4ZFY0OUpTMF9kNkNiRVV6MDF0Rlo2OFdjeDMxTWZ3TVVPdFdHb1pEU1ExOHRvMk9OVlRfTGJocDRyX2lLUQ?oc=5</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>14-05-2026 14:39 UTC</t>
+          <t>15-05-2026 11:12 UTC</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Pfizer's Turnaround Is Taking Shape (NYSE:PFE)</t>
+          <t>Markets Rally, But Biogen Pharmachem Industries Ltd Sinks to 52-Week Low in Stock-Specific Sell-Off</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Seeking Alpha</t>
+          <t>Markets Mojo</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQY0JXVkdneHBUc2lzY3Q0SFpfMWFWUXR5UFM1b0g3SnYzbHlpYllCTjR3UWx0d19ZLWs3LUFOYTdTRllxcThVUlJ6eDF5LXEtRW5FUGNtNlFYN3E2QzNkOEJUcC05WnR1bjFtNXBvb2pKZzBEU2hrZnNlYVFWSi1jSA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOazJSRTZrM0dMYjJFU2NLbVVlTjllYnduVFBOYlFpOXZRZGZwbWNXVllhZlRIX0RfNk5aNXZwM3F2dzY3ZGl5VjB2WVRad2RORHg2WEJCUUdJYWpLc1BvWFVHSlVhMTVXMFo5WWxPcTg2SXdjWFdJc2pHY3NYeXUxTXBtQzE5WjFOWGNaS1ZPdjg3MFgzSlFhc2FQbHJTWkVJQmVqRTdramc5MnhOVkNra3dxUlMxZ0lteVRodQ?oc=5</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>14-05-2026 13:30 UTC</t>
+          <t>15-05-2026 14:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Is Pfizer a Buy, Sell, or Hold in 2026?</t>
+          <t>Biogen completes $5.3B Apellis Pharmaceuticals acquisition</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AOL.com</t>
+          <t>qz.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE9hZG1ldmFqOXlOMm1DbjdsQmZRSDlrNHROQWp3U05OTHpiQ1ViUUZlSGJhUDBXRVV3U25Pandyb2d5NTRJQ0szOVpZNGktUDVZWktndmtGMVdXOUptcm4zOVBmVkthOWtuN0kzT2JCdkpaSVh0RERNLQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE82b2I1Rl9FNHVyazNiNnFSa1ExUEJQUWo4TVdCZ3VNOF9SSEo0WUxCSVF1bmthSXJkWTRsbENoYllOVU9laEkzWUprRm5LbUlUUWJkYUdoU283RTZPVEcyUVVNOFRucEgt?oc=5</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>14-05-2026 23:38 UTC</t>
+          <t>15-05-2026 12:22 UTC</t>
         </is>
       </c>
     </row>
@@ -2434,22 +2434,22 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Biogen Completes Acquisition of Apellis Pharmaceuticals</t>
+          <t>Biogen’s Alzheimer’s results bolster tau theory—and Denali’s next gen candidate</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>BioSpace</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOZ256enZtNjcySFlVRFVBdlVmVlIxLVFUYVZGVVJCMWJyaEVwaG1XSFdrOWxZU3ZDWGtiZmVUNkRtSmtKeTIyaldoQ2xuQ3JzaXdQeUNteGZOM3hZYzI5UUJ0MXVYNDBjVGZrSldQQUFSaF9MUUphR1lyX3daMl9pODJkdGU1NWRLM0NLRDlvelJmOEkzYV92VkY1TE1qWEFXV3dyWW1FeGJObnowT0VfUlRISFR0YXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPS1c1YjJtSVd6Z3BxakpYSjNnM0tpcVZDc1U1UFdMX3VhamZZMm9LZldLa3dLZUJFTE9VSnhKNmcyMkNoeURqaUcwRjFQRWo3bkNWaXFBQXJYOTh6UEJCWWZRTVpMZy1xclJkemN6Slh2Y0ZtV1NPWnNBUFh6SFJuZXlnUWQ2T0hVY2lrY2ZFV2VyTFFJOHBSUHVOdjRLb1E2ZnBvNUxMOHZURjhYUzBYTXRXcURXQ3FCMFE?oc=5</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>14-05-2026 12:38 UTC</t>
+          <t>15-05-2026 13:34 UTC</t>
         </is>
       </c>
     </row>
@@ -2466,17 +2466,17 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Reuters</t>
+          <t>ETPharma.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPUHNzbmJucnlUdy1SRVA1RFlXcGN5MVZoODNGQ2E4alYwS2VIQ3o0NzF4RUZvS1dCR2xnTVZUelB1QzBpNmJWbDByVTFETkVRUjJxYWU3dDFCVURMdXM3TWcteUwzaVBLZ2VibkljbGlPN1oteFlDbDJSQ21yUHpqZHo0cUIxWUhLdlhVT25LRV9fWFpIWEtGNUh6bmpqRlNsdjNrMm95NWoyWGZlWWZLTzZoNWlQLWlTV2JpNHhtNkNJdnpfM0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxOVDdpcEpFSTN1c1A2ZE5Jb0VTWlV4TTdCTzdVaDRRNHFBTzVaZ1k2Ry1qZG50bWdkd010RHd2S2VQcGxHSHhPMU03Vi1JcElUV2wzMC1wS2hiU2J2WVo5TXFSMEh4TVNldEVzWDBMMVpscWd4TV9pbTdNY003SXUwM2dZb2ZEYzRJRmwyU0gxQ21YamZGUWxRQWt0S3pkSU9pNWRSWERsaTNScUVQaEtiSlhRM1JFY1ZubWdDT2tDckFfRFNLRnE0UTNkTm1Sa1MyUGNFbmthcWd3T3FsV1RQck5reXM2TEVfNlZqZWh6LXjSAfYBQVVfeXFMTWRxSFZTN2tEWVBkWWR2Tk5odlZTY1VOc2k2aThCZTZXN3IyRmJUVGNmLTdRWG5uX0J6ZnpjX01hekR3MkxIY1N0UlhDdC1VSE5SWHFKMEpaWWxtb3FHbmpxSmQ2LWh1OFlxODJOVFZiMWZFR3ppbGlpODBoaDlwUnNUTHF6cE9RV1c5RXkxZk1PaEktODNPWFR0cjBBaEF5YWpYaHJPUjN1aGxSZzhzMWlqN25aSzhFRWROeHhUM2RLZ0ZhZEk0MkJ2VG9zZzNFSkkxMUhTdG0yVzJjMDVIdlNkTkYtNjVGUXFKZjJYR1lxSlR3Q1F3?oc=5</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>14-05-2026 16:39 UTC</t>
+          <t>15-05-2026 02:31 UTC</t>
         </is>
       </c>
     </row>
@@ -2488,22 +2488,22 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Biogen has seen enough — despite no dose response — to advance tau-directed therapy</t>
+          <t>Biogen’s Diranersen Shows Tau Biomarker Reduction in Phase 2 Alzheimer’s Study</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>FirstWord Pharma</t>
+          <t>The Clinical Trial Vanguard</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTFBNNDAza3BPQ2lmVHktM2tEel9xWWhGNXdmNGszd1ZDcUhLc3ppQnpZaVlmdmYyTmpOUWlmUVhDNnpFUkNBVWRWcVBUekhOVTY3MFZz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPTmtpQWtTMzZ6Y3dDMWlkeTlWQWhUNWNlUUVZUUtkRWxEYkpPZ1B0LS1Pd20wX2lfc3FEeHFOVG5pQVRRRzAyTUdQQi1VcGsyWnlIZ0tsLTB3MXoxRVRCN0dPSTFLR05yQkV3WEVaekRTZG1ndjVncV83TllhSXN0aUtpVVYyVDVGdng0eXp5Q3c5T2JkOEE0b294dDA5cWlrUGRBS2ZaRExpUXYzSzZNYVV1YnFNbEM1VDgtbA?oc=5</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>14-05-2026 19:13 UTC</t>
+          <t>15-05-2026 06:49 UTC</t>
         </is>
       </c>
     </row>
@@ -2515,22 +2515,22 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Biogen forges on with Alzheimer’s therapy development despite Phase II miss</t>
+          <t>Key facts: Biogen SYFOVRE CVR $4; Apellis buyout done; shares dip</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Clinical Trials Arena</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQM3BfblliSXhWVDE3dXdPeWo3RGpZbVJzUlhSanBvTWV0bWZiaG1tN3NGd2tJdkJBZXZFNkRhN2c5SlE2aURMaUxfaHZwbnQ4X0s5VURES0xXNFA2c1dRcFJUWUlIRlhrZWFqell0cVRodGdUUG5MUnNWTTcySHpWVGJ1QnptRHlFVERtblZfR3JmeThZX1YydkNOZ1JEQ084ZFFN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNdnlOcWZCNkEzNGk3OHZDaG1wZU41N3hXejNtSXZ3ajJUU2RNMVQyel9sTjlpQlFwdW14ZEZEZTlkakdDWFRkMTZFc196TXBVczliSnJ1VTFEbEQ5SlZzRjVqV2E1cS1oYW8xLVdDeWhnTkNTTDdrMDdqWHVXa3YtRHktOXhVZTFyNXZqN0tQWGhtem11QjJxMHBuZVFaLUROSlpDOE1OcTFlVjJfc3hpNlNweFR1eDVjNHdsZVlnODM?oc=5</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>15-05-2026 11:18 UTC</t>
+          <t>15-05-2026 07:15 UTC</t>
         </is>
       </c>
     </row>
@@ -2542,22 +2542,22 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Biogen’s Diranersen Shows Tau Biomarker Reduction in Phase 2 Alzheimer’s Study</t>
+          <t>Biogen has seen enough — despite no dose response — to advance tau-directed therapy</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>The Clinical Trial Vanguard</t>
+          <t>FirstWord Pharma</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPTmtpQWtTMzZ6Y3dDMWlkeTlWQWhUNWNlUUVZUUtkRWxEYkpPZ1B0LS1Pd20wX2lfc3FEeHFOVG5pQVRRRzAyTUdQQi1VcGsyWnlIZ0tsLTB3MXoxRVRCN0dPSTFLR05yQkV3WEVaekRTZG1ndjVncV83TllhSXN0aUtpVVYyVDVGdng0eXp5Q3c5T2JkOEE0b294dDA5cWlrUGRBS2ZaRExpUXYzSzZNYVV1YnFNbEM1VDgtbA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTFBNNDAza3BPQ2lmVHktM2tEel9xWWhGNXdmNGszd1ZDcUhLc3ppQnpZaVlmdmYyTmpOUWlmUVhDNnpFUkNBVWRWcVBUekhOVTY3MFZz?oc=5</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>15-05-2026 06:49 UTC</t>
+          <t>14-05-2026 19:13 UTC</t>
         </is>
       </c>
     </row>
@@ -2569,22 +2569,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Key facts: Biogen SYFOVRE CVR $4; Apellis buyout done; shares dip</t>
+          <t>Piper Sandler raises Biogen stock price target on drug development</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>Investing.com</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNdnlOcWZCNkEzNGk3OHZDaG1wZU41N3hXejNtSXZ3ajJUU2RNMVQyel9sTjlpQlFwdW14ZEZEZTlkakdDWFRkMTZFc196TXBVczliSnJ1VTFEbEQ5SlZzRjVqV2E1cS1oYW8xLVdDeWhnTkNTTDdrMDdqWHVXa3YtRHktOXhVZTFyNXZqN0tQWGhtem11QjJxMHBuZVFaLUROSlpDOE1OcTFlVjJfc3hpNlNweFR1eDVjNHdsZVlnODM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNaEpBYjNQVDFnNEhlSUJyQXh5QzgyVjlLTW5ZOVRoWktETS1WQkhIdkFEUEFJYUdvNWxyOHpUejJjWnJkMFhQdUdacEpKYU9uWER5T3BzRWRwTFk4eUdRQ1BWTTBqZXN3d3RURVNVbTVyQWhGTlM2LVJLczd4N3gwSFM1ckw3eWFFUEFIZGxZZXhqSUF5ZVRDWUhrV0VzWjFfdXViQXVLZ3FfcXJieDFpd0VyLUkxU2lERVdtYXotMEpKeElC?oc=5</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>15-05-2026 07:15 UTC</t>
+          <t>15-05-2026 13:49 UTC</t>
         </is>
       </c>
     </row>
@@ -2596,22 +2596,22 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Biogen advances Alzheimer's drug to late-stage trial despite disappointing data</t>
+          <t>Biogen to push ahead with experimental Alzheimer’s drug despite mid-stage trial miss</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>IndiaMedToday</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOaHh4Y2FDRWJBc2dOTDA1S0ptZ0Z3N3dTbkppRkVheEs4Mk5CZFhrZi1zVEFFZFZsekZScW5DeGJ2NTk5aEozVm1zUWVOZVNDdFdtYUd6bjNkV3FUbnlBRkM1VEY0amlIWkdlR0Y5NWNKMWQxbWhPMG85UzhkdmdUbWRUaFNDU1lfSE9rYTNR0gGTAUFVX3lxTE5jSFlSQkhiTkpTMDRaRFVYVEc0QUNBT0RmemhWd25VTmFReXdCTHdVakhsejdvUVBFUWFIQU02Y3V2M2U1NUItazFPb19sb0cybERWOU40WUVDNHhwMXRGUDU2SW0tR1MtQ0pLWFVySXFwZHdNWWEzaHBjMkd0QWJPS1VzVWpaVmFtc2M3bndPV01VVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOTy1iN05GSnVfa2dhZzZ5aWx3MVF5Z1hJWUJzUWNVUkRYOHV6LW9oOFRjRjdhcldaZW9PS0MycUZNYTR0V3dxd3UtZVpBQVJad0tHSno1X25FN0p3cGl6REk5akx1VGdhdmpFNXB6c0ZveHlOU1llZWJ0UkUycExGeGU3WjI1T2ptVnBldGxpdU5EMHRnSEtQMWxLZkx1cWdxU0kxRy1yc29YaS1DVHFv?oc=5</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>14-05-2026 16:10 UTC</t>
+          <t>15-05-2026 05:22 UTC</t>
         </is>
       </c>
     </row>
@@ -2623,22 +2623,22 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Biogen to advance experimental Alzheimer's drug despite mid-stage trial miss</t>
+          <t>Biogen stock (US09062X1037): Alzheimer’s data and earnings keep focus on pipeline</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ETPharma.com</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxNZHFIVlM3a0RZUGRZZHZOTmh2VlNjVU5zaTZpOEJlNlc3cjJGYlRUY2YtN1FYbm5fQnpmemNfTWF6RHcyTEhjU3RSWEN0LVVITlJYcUowSlpZbG1vcUduanFKZDYtaHU4WXE4Mk5UVmIxZkVHemlsaWk4MGhoOXBSc1RMcXpwT1FXVzlFeTFmTU9oSS04M09YVHRyMEFoQXlhalhock9SM3VobFJnOHMxaWo3blpLOEVFZE54eFQzZEtnRmFkSTQyQnZUb3NnM0VKSTExSFN0bTJXMmMwNUh2U2RORi02NUZRcUpmMlhHWXFKVHdDUXfSAfYBQVVfeXFMTWRxSFZTN2tEWVBkWWR2Tk5odlZTY1VOc2k2aThCZTZXN3IyRmJUVGNmLTdRWG5uX0J6ZnpjX01hekR3MkxIY1N0UlhDdC1VSE5SWHFKMEpaWWxtb3FHbmpxSmQ2LWh1OFlxODJOVFZiMWZFR3ppbGlpODBoaDlwUnNUTHF6cE9RV1c5RXkxZk1PaEktODNPWFR0cjBBaEF5YWpYaHJPUjN1aGxSZzhzMWlqN25aSzhFRWROeHhUM2RLZ0ZhZEk0MkJ2VG9zZzNFSkkxMUhTdG0yVzJjMDVIdlNkTkYtNjVGUXFKZjJYR1lxSlR3Q1F3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQSGZlZ0VKSXhxMXA5Y0NFMUcwMk1zOUpJYTJqeTJrV0dLMjNnU0QzR0lua0xiaUxYRlN2Q1o3ejhqcjZablJHX202a2M1NVVWckh5RUZBX3R1SEc3Z2NmelFXMmNTQmlLemRFSzNHVzFfTkg5UlpVQnpLOE9VdWgzejFoOTN5TDZpbEJiYldoRmgtZl90WWJwdVVkRms5VVRXZGVZanpHU1pNbkNRbUNpSVpZQnNOaXY5d1lRVDdOZDZtMzhFUm5j?oc=5</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>15-05-2026 02:31 UTC</t>
+          <t>15-05-2026 13:01 UTC</t>
         </is>
       </c>
     </row>
@@ -2650,22 +2650,22 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Biogen Pharmachem Industries Ltd is Rated Strong Sell</t>
+          <t>The ADDF Highlights Encouraging Progress Toward Targeting Multiple Alzheimer's Pathologies in Biogen's Phase 2 Tau Study</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Markets Mojo</t>
+          <t>PR Newswire</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQWHkwZkp3VjNjdnNUZjdxcWFBUG1adHBLRUp1MXVKbG81QTlBWTF2QWRxMFQ3dEZaS3M4ODB1S1Vmb1NIY2xiMHpBTmpPRmppNE5SRTFjdjQwUFRNZ1g3WEI1dnA5dlhSWWtObWpRRVliTk1JZEM1eTNOMV9aVEM0Wm1DcFRpbHc1U0R1UjNEbHFhZU51ajRVZVdtd3VhOTBLOGxDSDhidGZKNTVnWTdSN1NYcWNUdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAJBVV95cUxQakloZHFKUnRBZUQtUlBLSDIxdFQ3MzZJZWhWNEVGS1RWZjZwQ3RKUHdIc0NDY0pXOXhsdV9xMzRYcEdCb2w1bU1QRE9MbFp2VllHSml2TkptWGVva3hYeVplbzhnZnpaOEkyUG9wTDZqR2FGLU9EOFdvSlZZZnhyN3l3RHBnRU9FenJSZ3psWVhtb045eHNRMURZWFZLYkRCMU04eGRmSEZuTHBCaEVka1RkSXl0V3F4OGVHSjhxREVhNEgwdlViNjN3Q2FGT01idTNlamxFYTcyZlY5Umx0SXcyUEZXclRWRmxWYmxkTlNKb05rODlQeThLVjZoREhVcFpZSw?oc=5</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>14-05-2026 20:22 UTC</t>
+          <t>15-05-2026 00:48 UTC</t>
         </is>
       </c>
     </row>
@@ -2677,22 +2677,22 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Biogen to push ahead with experimental Alzheimer’s drug despite mid-stage trial miss</t>
+          <t>Biogen Pharmachem Industries reports standalone net loss of Rs 0.36 crore in the March 2026 quarter</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>IndiaMedToday</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOTy1iN05GSnVfa2dhZzZ5aWx3MVF5Z1hJWUJzUWNVUkRYOHV6LW9oOFRjRjdhcldaZW9PS0MycUZNYTR0V3dxd3UtZVpBQVJad0tHSno1X25FN0p3cGl6REk5akx1VGdhdmpFNXB6c0ZveHlOU1llZWJ0UkUycExGeGU3WjI1T2ptVnBldGxpdU5EMHRnSEtQMWxLZkx1cWdxU0kxRy1yc29YaS1DVHFv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwJBVV95cUxPYlFMS18xSWRGekhrRm5yVkJkcjRzRUJoZlpWaS1FUGRFelU4WklBbU8wbW1xT19OQXRxblgxNzU1a3Z1alFlS1RtLV9lTDBDcmZPQ1p6dmpCUGwzSlJXLTduaFdlbmdLTVV2OFNzNHFIc0JJTGxmQ3BHSUNLZHJDNTZNZ3Nram1JYkJmR1NLZlk1NzViMnpGeC1idDdpc2xVYWJDNm5ILWNVT3EtaG9WdVpHSElodEd2U3RsMVhJMnNzbWtCWDV1Vl9DYXZGelo5eWlDeWFLRS03cXE0Wmk2bDN4RzVMYktFWU9PR2o0R2c1V0QxVDZwZTk4ZENQVFlPUDdtLWc3eXZlbU9xSXRGaEVEUdIBkwJBVV95cUxPYlFMS18xSWRGekhrRm5yVkJkcjRzRUJoZlpWaS1FUGRFelU4WklBbU8wbW1xT19OQXRxblgxNzU1a3Z1alFlS1RtLV9lTDBDcmZPQ1p6dmpCUGwzSlJXLTduaFdlbmdLTVV2OFNzNHFIc0JJTGxmQ3BHSUNLZHJDNTZNZ3Nram1JYkJmR1NLZlk1NzViMnpGeC1idDdpc2xVYWJDNm5ILWNVT3EtaG9WdVpHSElodEd2U3RsMVhJMnNzbWtCWDV1Vl9DYXZGelo5eWlDeWFLRS03cXE0Wmk2bDN4RzVMYktFWU9PR2o0R2c1V0QxVDZwZTk4ZENQVFlPUDdtLWc3eXZlbU9xSXRGaEVEUQ?oc=5</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>15-05-2026 05:22 UTC</t>
+          <t>15-05-2026 03:34 UTC</t>
         </is>
       </c>
     </row>
@@ -2704,22 +2704,22 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>The ADDF Highlights Encouraging Progress Toward Targeting Multiple Alzheimer's Pathologies in Biogen's Phase 2 Tau Study</t>
+          <t>BIIB Advances Alzheimer's Disease Drug Despite Study Missing Main Goal</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>PR Newswire</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAJBVV95cUxQakloZHFKUnRBZUQtUlBLSDIxdFQ3MzZJZWhWNEVGS1RWZjZwQ3RKUHdIc0NDY0pXOXhsdV9xMzRYcEdCb2w1bU1QRE9MbFp2VllHSml2TkptWGVva3hYeVplbzhnZnpaOEkyUG9wTDZqR2FGLU9EOFdvSlZZZnhyN3l3RHBnRU9FenJSZ3psWVhtb045eHNRMURZWFZLYkRCMU04eGRmSEZuTHBCaEVka1RkSXl0V3F4OGVHSjhxREVhNEgwdlViNjN3Q2FGT01idTNlamxFYTcyZlY5Umx0SXcyUEZXclRWRmxWYmxkTlNKb05rODlQeThLVjZoREhVcFpZSw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxPQ3JVc2ZaSi1Gel9YWTBGTXFmLXZpamR1T3Z6UUVGcjZhRXZmZWRjVzJ6ZklrMWN1WUtpMFNBVEEza1BOdVQtZm9WNVdlaFVGbU44YVZleVFPc1BVenVJX2dnZE5xa1VTRVljYkhMNFdXZEJfOTcyNG5xNnpCTGlZRTFOTThPeUhiQUs5YnNLYk5WQ1ZybE1sR1c3a0VGYlp6eGVWOElORzJ4bkVhUFNEUUlyUTQ1MXczc3Bmd3EweEFNRUY1?oc=5</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>15-05-2026 00:48 UTC</t>
+          <t>15-05-2026 15:28 UTC</t>
         </is>
       </c>
     </row>
@@ -2731,22 +2731,22 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Evercore ISI reinstates Biogen stock with Outperform rating By Investing.com</t>
+          <t>Biogen Pharmachem Industries Ltd Falls to 52-Week Low of Rs 0.38 as Sell-Off Deepens</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Investing.com India</t>
+          <t>Markets Mojo</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQM01HX0Z3UW1LOURwUU9GSm5SV1o1dENlR2FfLUwyN1FBQ2NseGEtdVYxSGcxY2xiX2Nka0Y0eGUwNm5qRmRkaU54c1B6dXRmQ2RheHQ4ZGhRTGsycVJwOFZLTVZsSVJyVDJmOVZ3S2lRQUxvbmVxVnlXd0Roemp0WnNjQkpwSXIweDBBd2ZfNkdPdDNPVEFCRFEyRGZqSThtdElvRmZ0MTczTVEySzR1cjZOWm9MZEFhQTZZSF9ucVJRNjdBU2oxSHVYMVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxObjkyb1Zfb2Jwa2xMNjJsc2YyWlhzQ0taY0dTWnB3aFdKekhSYUJaS3hzTkwwRzZGSlZpMWlYNG00MktoZHM0QkFpNXRnaFBPNDJremUzMFBVN1l3cnhqUlpNNG95UWdPS1VhdjBuMDFFR19BV1BENXo5OU4welhxRUZSUHd6ZzIxTDExdDVhYzF0dHg5UGx0X0I3TzlMVE9CemFJSmtvVWRtcEUwNEVOb29nSWhJQlpPU3lKdjBySTQ0elg4?oc=5</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>14-05-2026 22:58 UTC</t>
+          <t>15-05-2026 04:05 UTC</t>
         </is>
       </c>
     </row>
@@ -2758,61 +2758,61 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Biogen Pharmachem Industries reports standalone net loss of Rs 0.36 crore in the March 2026 quarter</t>
+          <t>Guggenheim reiterates Biogen stock rating on Alzheimer’s drug data</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>Investing.com</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwJBVV95cUxPYlFMS18xSWRGekhrRm5yVkJkcjRzRUJoZlpWaS1FUGRFelU4WklBbU8wbW1xT19OQXRxblgxNzU1a3Z1alFlS1RtLV9lTDBDcmZPQ1p6dmpCUGwzSlJXLTduaFdlbmdLTVV2OFNzNHFIc0JJTGxmQ3BHSUNLZHJDNTZNZ3Nram1JYkJmR1NLZlk1NzViMnpGeC1idDdpc2xVYWJDNm5ILWNVT3EtaG9WdVpHSElodEd2U3RsMVhJMnNzbWtCWDV1Vl9DYXZGelo5eWlDeWFLRS03cXE0Wmk2bDN4RzVMYktFWU9PR2o0R2c1V0QxVDZwZTk4ZENQVFlPUDdtLWc3eXZlbU9xSXRGaEVEUdIBkwJBVV95cUxPYlFMS18xSWRGekhrRm5yVkJkcjRzRUJoZlpWaS1FUGRFelU4WklBbU8wbW1xT19OQXRxblgxNzU1a3Z1alFlS1RtLV9lTDBDcmZPQ1p6dmpCUGwzSlJXLTduaFdlbmdLTVV2OFNzNHFIc0JJTGxmQ3BHSUNLZHJDNTZNZ3Nram1JYkJmR1NLZlk1NzViMnpGeC1idDdpc2xVYWJDNm5ILWNVT3EtaG9WdVpHSElodEd2U3RsMVhJMnNzbWtCWDV1Vl9DYXZGelo5eWlDeWFLRS03cXE0Wmk2bDN4RzVMYktFWU9PR2o0R2c1V0QxVDZwZTk4ZENQVFlPUDdtLWc3eXZlbU9xSXRGaEVEUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOVHBVRjA5V18wcnlMQWNKWWRtMGVwZUMwajBvWkNuSkVobEo2T0N2M2MzOGZKQ1RpUkVXRmNISk9zQWFEeDBQWkF1Z1dTWWpsVEtHRC1YTHhPNEtmd2t4VU9QSFk1SmlqSHpod00zbjhUYTRkUU1RbnZWY0RqWnU2UHNrQmFGb1lrUDVUN1BEQ3RUc2ZvazVIeXd3d0tKUkIwSk52M1ZKaEZVbU0zbFdjRklQZkNPT3dqQnV6VlRHcVBJODA?oc=5</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>15-05-2026 03:34 UTC</t>
+          <t>15-05-2026 11:55 UTC</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Blau Farmaceutica</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Biogen advances Alzheimer’s tau program despite midphase miss</t>
+          <t>Earnings call transcript: Blau Farmaceutica Q1 2026 misses expectations</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Fierce Biotech</t>
+          <t>Investing.com</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNaEkySTRwNTh3NVF1R3RyM3RObFh2aGhLdDNiamg5RUVibmRNNER5MGFqdi1QMHVnbnRBRE5mcEE2SUlybzBid1U0TWRwNlc3NUlXSkVESDJDYl9QUkM5bHFfNTZqZVFQMnJCZWpiV2dMYTB1Vk1SNjZrc25qS2xWU0JkbnRBSE5VU0ZVd0p0OHF4cEVRR3pFT2NFTmgtenM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxPX2V2UFZlZWJtMXQ5dS1mNGVvMTRMcllLWGs2X0lHWFdwNlZvZktIM01GVWVwRWQ3bWx6V2xacVdiYzNuOUNSazJXNkNiQ3FvNnNuRnJmLUhvYTFIbmM5eWFxUUZnaUYtR0hONFpQNU95TlFYSjV2OVRHNWRnT3pPVklUeHZCdnpYbnJabGxxd0VubURDY3dGYl9XSGJzaVFUOWFxcTlSOXd0OHJUVlIxVlBuMVN0a3h3MHZzQ09zMF9GUFps?oc=5</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>14-05-2026 12:35 UTC</t>
+          <t>15-05-2026 14:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Biogen Inc. stock underperforms Thursday when compared to competitors</t>
+          <t>Dr. Reddy's Laboratories rallies Friday, outperforms competitors</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQLWFaVmZEMU10YzBsMUxHWnIyYXVCcGtRa1N6UnhrOVRSanpleWl4VWY4OXBnd2VQb2dLZWhaX3hIVjRhVEVVcnE1SXd0ZVZuS25QX2t1RzVYNV8ySDZ5TFVIWklVSzl1SEhMakd1bFBhcG1IY2tRcWZ1U0dZNi02UVNnVzNSVjM2T2ZtbEN1ZGZRbVdFcFBGTlVuNUI1UXJaUXpYZ2FQa2EyNmFDUFZia0ZKaHI5SVNYSWJ4cE5rRUNXSE9GSnhz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxNZHpuQ3JNTldHN2VrZlJNRl9RNm1TOWlaUHp1c2padFp5eDNPSkdKVHJITW5oNmhMTE5MWHVyVTdrTTl5dVV2VTNvSnJlZkpINUMtZGNYMGNYcHVuRkdXdFRVOF9tdlJJdFJBd1BWbldQWGJ4MldDMU03eDNXYnN2UnZ2WHBOT1lBbHdFMkFvR3BzR0FycTVJWFA3SUlzcUxMR2MyLUNTbHh5UzgzbTZ0ZVpqLVlUNUVaR1NVT2hKX0l1Ny1ma2VmZlpvNzNMTUxzVUp3cTdvVTNYY3RxWmc?oc=5</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>14-05-2026 20:30 UTC</t>
+          <t>15-05-2026 10:30 UTC</t>
         </is>
       </c>
     </row>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Dr Reddys Laboratories Ltd Surges 3.05% to Day's High of Rs 1338.5 — Outperforms Sector by 2.23 Percentage Points</t>
+          <t>Woxsen University Appoints Dr. V.J. Byra Reddy as New Vice Chancellor</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Markets Mojo</t>
+          <t>Devdiscourse</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxNNzZWcDIxc1BhT1RnT0RXaHU4YnBoOFktRlVoQV9EZDZNb052RE5YRTU3aXZRamRucUdOdGpjSDVhNHo0SzdCcXQ4UjNPVlEtUzJGekNaYzNDREVtbmRvWnZlSmRPSlhYckFhV0tpRTNiUFNXMjFieXUyLVUxakZHQjlGQjVraGhCb0xYSk96NEkwRkFkSnZDN3ZCOGZYZG9EYnhwSXZiUVVqN0xvRTdDS0o2OW9qSlp1VEJhV21KcnVyQjRPQWRkR19UTXFadw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNOXNSb3ltaXFKQ185RkJScWhxeU9HMEJJR2xGNUZXR2pxQy1GTHk3b0NCc0YzUzdxRVQ4NkxnVTI3d3VGTU85d1dLWWJGTEpSVUJSaHNObEhLWnV6RW9QQm5ycUFucGJldVByS1pPMl9aRHQzc3VVRTA0NEtuN3ZsT0JfY19uTzJ2T2QyNXZLeWw5Y1ZpdjdMdjJLN05JcTc5aU9vNEZHNzNWRnM1WEU2NjRRUTZuUDdwVnlWOFVR0gHDAUFVX3lxTE5UV2pkNGtYT01GZ1dteWlKRm80b3FERlRsSFNEUWhaeXdrbnp5WWlDaTFCcnF0R0JpQkxpQXlYQ3J1NnFsQTl5aWVIZzd5RE9oV2R3Ylc5ZEctc1hDOWx6RDRvWFJfWi1qd1U3bHNTaThmbHY4QlJldmVuX3dYWVdoRFFDdTJQODJPZExTbkdWQ0lnVmowMFU3SGRJd0N1Rzd2bE9MMHkzLUNrWXVqZEdjSHpudFk4QTBIOU8xV1Y2QzQzRQ?oc=5</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>15-05-2026 10:08 UTC</t>
+          <t>15-05-2026 11:56 UTC</t>
         </is>
       </c>
     </row>
@@ -2947,7 +2947,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Dr Reddys Laboratories Ltd Technical Momentum Shifts Signal Bullish Outlook</t>
+          <t>Dr Reddys Laboratories Ltd Surges 3.05% to Day's High of Rs 1338.5 — Outperforms Sector by 2.23 Percentage Points</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2957,39 +2957,39 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPRVk4U0d5Y0ZTaHFubWFNSXJrYmcxUEltWVJzWXJIZ1BkNnMxZGZydnVCWE44SEUwRXpQYThTTEloOFNxbWxMbkJ2d2hVaUNBMWRWN2ZmWjZ6WDVYeWxKSTJfek1qTkQzYlhGVjF0Q0xoWVFHcDVFTlZJdGYzUEdnWkJ0NzlwY3gzVWxGN0Z1S2lIeHJXanZoTWF0T2twaXQ2QXBCRjlUZ1lsVHE4djFNTFpnT01DN3FYNXJTTV9LbUhKSVpJR29FbV9qTG5mQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxNNzZWcDIxc1BhT1RnT0RXaHU4YnBoOFktRlVoQV9EZDZNb052RE5YRTU3aXZRamRucUdOdGpjSDVhNHo0SzdCcXQ4UjNPVlEtUzJGekNaYzNDREVtbmRvWnZlSmRPSlhYckFhV0tpRTNiUFNXMjFieXUyLVUxakZHQjlGQjVraGhCb0xYSk96NEkwRkFkSnZDN3ZCOGZYZG9EYnhwSXZiUVVqN0xvRTdDS0o2OW9qSlp1VEJhV21KcnVyQjRPQWRkR19UTXFadw?oc=5</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>15-05-2026 03:00 UTC</t>
+          <t>15-05-2026 10:08 UTC</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Intas</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Mrugank Sheth Joins Intas Pharmaceuticals as General Manager – Marketing</t>
+          <t>Kiran Mazumdar Shaw’s plan for Biocon is a template for family business succession</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>hrtoday.in</t>
+          <t>Moneycontrol.com</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNY29aaUxSSno0SHRHb0IxcndNa01ickpQNTVmT2h2cXZkZzdFbFpQZTRPMFliREx3MUNQQ2p2YWxrYUFyM2dLeGt1TEJGclRleElsUzZGMTUzSUYzVXhzc3BsN1owQVRzaE1kV1RZOXFfNFJMaERHM0ptbU45dVRDZFpCVm0wd0tFSWdpa01WOEVkZ3lv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxORVBwajZlSEFOM01OeHY4U2xYZlhPanloRmRFQXdLNUZPMFVWMmFyRFRTYmlndGtlRzdhVWphWURxRVVpNlBPZV8xUjZkd1hjTkRTVWRxZjlJeExXMFloajdCOC1ONHJoN0xXVDgxNUlCd3RQaXFnenYxMkdOYnFLeDNxd3FlUDBHaFU5aGlvbkRCaVpNckZZNE92ZmdyV3BiRVp0WGFSVmxNTkZXU0dtTE1URF93WTRFaUNIY1lmenNOSzU0WHU0eGYyRTZtQlV0Q0UzYdIB2gFBVV95cUxPX3BDRUVYMGtOWjcyYUV6MWNDUmgyMDhBb1pfR3dwR1dTamxpd2NCTXB6UDVYUE45cDNidlNVSS1BRFRqQjM1TGlqUmM3MEY3b1RLMWRFNWQ1ejNOUE4taFpKenhHZDZDOFQ0Q2dvdmJRYW1Kd1pBZ2ZEX0paV1J4YjAyRF9NYWJvcEVPdmJuOWVkcXlZRVZhRkVaMkZVNTI1enBUTjJmQ01MelJOMExINWFjSlhHamtIb3VTLXY1NENGMFVZMmsybE9VSnVuREVaYk5uSDNhRWktUQ?oc=5</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>14-05-2026 11:32 UTC</t>
+          <t>15-05-2026 03:49 UTC</t>
         </is>
       </c>
     </row>
@@ -3001,22 +3001,22 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Kiran Mazumdar Shaw’s plan for Biocon is a template for family business succession</t>
+          <t>Biocon Ltd spurts 2.76%, rises for fifth straight session</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Moneycontrol.com</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxORVBwajZlSEFOM01OeHY4U2xYZlhPanloRmRFQXdLNUZPMFVWMmFyRFRTYmlndGtlRzdhVWphWURxRVVpNlBPZV8xUjZkd1hjTkRTVWRxZjlJeExXMFloajdCOC1ONHJoN0xXVDgxNUlCd3RQaXFnenYxMkdOYnFLeDNxd3FlUDBHaFU5aGlvbkRCaVpNckZZNE92ZmdyV3BiRVp0WGFSVmxNTkZXU0dtTE1URF93WTRFaUNIY1lmenNOSzU0WHU0eGYyRTZtQlV0Q0UzYdIB2gFBVV95cUxPX3BDRUVYMGtOWjcyYUV6MWNDUmgyMDhBb1pfR3dwR1dTamxpd2NCTXB6UDVYUE45cDNidlNVSS1BRFRqQjM1TGlqUmM3MEY3b1RLMWRFNWQ1ejNOUE4taFpKenhHZDZDOFQ0Q2dvdmJRYW1Kd1pBZ2ZEX0paV1J4YjAyRF9NYWJvcEVPdmJuOWVkcXlZRVZhRkVaMkZVNTI1enBUTjJmQ01MelJOMExINWFjSlhHamtIb3VTLXY1NENGMFVZMmsybE9VSnVuREVaYk5uSDNhRWktUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxPLWZicU9kWVBja0daRlBYYzVhRmNULVdzVkV4NGVzZ0tXQTNnT3lKbFNwTER1bG1OeW5jN0JOdDh1VDVwVExTcTVTR3lmUW0zUGVzZEd1OUI5UV9xYzZfTmdCQlg2YXJTYXlqa0pfb04zZFZlekRrMVFtcUlfeTlURUNobTRQU0ZVbzMtYjhNWWlKRW1PeTZxUXBLVm16Q0hQWGNqNmFDMDJRQ2hWb2V5cjlINU5ZWkIzWkI0dmxPVkFDcmZpZENpd0M0NzdhdXY4eFpF0gHYAUFVX3lxTE9GdWxocnIyWFYxcW5wUlM0S0JkOHRvd2kyOFRERllJamdMdTYxaTgxYnpFaHZoLTRmbmZaTnIyeEJ3MDFVeXRkQTVKYTBveWhJaHRERGVrT08wOWdhOGdBTE5yR0RqcWhsUURMSGZWeGlQV0hNUWFVRllTVk5ud185QURFT1F3UEpjUWFlNENHZW8wZVpidUNWY1dsT09CNS0tc1owaXRoaEpEcHlUVjd3TC12d04yamdENUR0aldfR3o0OFFncWJjWDNtbmFWaUE5cHNFcl9oSQ?oc=5</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>15-05-2026 03:49 UTC</t>
+          <t>15-05-2026 07:46 UTC</t>
         </is>
       </c>
     </row>
@@ -3028,22 +3028,22 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Biocon Ltd spurts 2.76%, rises for fifth straight session</t>
+          <t>Biocon Ltd. is Rated Sell by MarketsMOJO</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>Markets Mojo</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxPLWZicU9kWVBja0daRlBYYzVhRmNULVdzVkV4NGVzZ0tXQTNnT3lKbFNwTER1bG1OeW5jN0JOdDh1VDVwVExTcTVTR3lmUW0zUGVzZEd1OUI5UV9xYzZfTmdCQlg2YXJTYXlqa0pfb04zZFZlekRrMVFtcUlfeTlURUNobTRQU0ZVbzMtYjhNWWlKRW1PeTZxUXBLVm16Q0hQWGNqNmFDMDJRQ2hWb2V5cjlINU5ZWkIzWkI0dmxPVkFDcmZpZENpd0M0NzdhdXY4eFpF0gHYAUFVX3lxTE9GdWxocnIyWFYxcW5wUlM0S0JkOHRvd2kyOFRERllJamdMdTYxaTgxYnpFaHZoLTRmbmZaTnIyeEJ3MDFVeXRkQTVKYTBveWhJaHRERGVrT08wOWdhOGdBTE5yR0RqcWhsUURMSGZWeGlQV0hNUWFVRllTVk5ud185QURFT1F3UEpjUWFlNENHZW8wZVpidUNWY1dsT09CNS0tc1owaXRoaEpEcHlUVjd3TC12d04yamdENUR0aldfR3o0OFFncWJjWDNtbmFWaUE5cHNFcl9oSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPOEhJSl9qWWUyaEZaeUtwcFRidkJiWWlQZGhTVkFVZXdrUkwzWnk3bWxVV0FJdzdaYUtjd0dPV2JXX3Q0MV9vX3hmcGdscmJiU2VqUE5fdE5PYlF5UkFaRGJFd1FQRXVWQjVBLWppSmV6VUZBN3BZZEduT3Q3anBrcUU5V1FDMm9ZQVBUTldiMVVPU2FMSEc4VjB3dEJlYXloQW5n?oc=5</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>15-05-2026 07:46 UTC</t>
+          <t>14-05-2026 20:44 UTC</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Biocon Ltd. is Rated Sell by MarketsMOJO</t>
+          <t>Broad-Based Technical Strength Lifts Biocon Ltd. to 52-Week High of Rs 430.2</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3065,12 +3065,12 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPOEhJSl9qWWUyaEZaeUtwcFRidkJiWWlQZGhTVkFVZXdrUkwzWnk3bWxVV0FJdzdaYUtjd0dPV2JXX3Q0MV9vX3hmcGdscmJiU2VqUE5fdE5PYlF5UkFaRGJFd1FQRXVWQjVBLWppSmV6VUZBN3BZZEduT3Q3anBrcUU5V1FDMm9ZQVBUTldiMVVPU2FMSEc4VjB3dEJlYXloQW5n?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOeXFBYXNUbllGMFlOdllVeVdTbnpvV214ckZpUWJtODVjNktpWVA5UW5Ebnh6SUZqa2R5SmdKRDNUajRQZWo5SWVaZkpWSnRoSzF3SWtrV2xVQVp6RFpnQk9fVDZaNS1rR0ZNS0x1eHhoME9WT21nOHZkclBPczB3S3Jzdkk2T0pMUkhyRkhZOVFvQTVUU0VSZmRmSmNOZ24wTzA3a25DVUpmcEhKNlBXX2FNTml4eVk2dnhuRnR1OG5CM0F3a3dQNDV3?oc=5</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>14-05-2026 20:44 UTC</t>
+          <t>15-05-2026 05:11 UTC</t>
         </is>
       </c>
     </row>
@@ -3082,7 +3082,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Biocon Ltd. Upgraded to Buy by MarketsMOJO on Strong Financial and Technical Grounds</t>
+          <t>Biocon Ltd. Upgraded to Buy by MarketsMOJO on Strong Financial and Valuation Metrics</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3092,24 +3092,24 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxPd2xESnZJVE5qdWdOWHZ4dVdKNWJrdDVQaG15cVl4Qm85R0h4Sk1fT0E5a0dNTV9iVEJhNXJkcEp4NXQxMVIzbnlzcTZwSXpVc04xYTF2TVZ3cVN5eGtucS1FckVMeVR2VHNpR1FtZkwxYjZvUkV0Z1l0elRfcTF2Ym9mYWxOS1A4QmxBVXE0eEtBM1pCeDdrZlMzTU4zbGdrdUJmejRVdUV1UTVyd0VMMDc0TG5ZVUl2c1ItT3JXN0t0V3BLQWF0RDI3c24zNGtBc0IzUkpGUzdSVlNoeHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxNc0hlaHZrZDljSDZ6ZDByNDB5Um1QcEVqbWhSbldUVy1feGdaTTB5SWVadTROTndXLUFDN2VyMUJ0YXNHV21yaVFWem1NX2liZVprbHJGYVA0ckVPbFJFZWhNTUhvbVRiWU5wOW5Ba096OVFDYnEzR21ZNmVhN0RoQmpjWkFxMF85VEpLYzFsT0hIaEdaNEJPZnFaSXJsRC1OTGdWVi1qVXBpQ2l0M0NDX21Ia1hqbFdxX29Zc1QtR25Hb0JoN1U0TWUzdGU1ZkxoNVJCaE13UEs1N0Z1ZkE?oc=5</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>14-05-2026 20:46 UTC</t>
+          <t>14-05-2026 20:51 UTC</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Broad-Based Technical Strength Lifts Biocon Ltd. to 52-Week High of Rs 430.2</t>
+          <t>Aurobindo Pharma Ltd. Technical Momentum Shifts Amid Mixed Market Signals</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3119,39 +3119,39 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOeXFBYXNUbllGMFlOdllVeVdTbnpvV214ckZpUWJtODVjNktpWVA5UW5Ebnh6SUZqa2R5SmdKRDNUajRQZWo5SWVaZkpWSnRoSzF3SWtrV2xVQVp6RFpnQk9fVDZaNS1rR0ZNS0x1eHhoME9WT21nOHZkclBPczB3S3Jzdkk2T0pMUkhyRkhZOVFvQTVUU0VSZmRmSmNOZ24wTzA3a25DVUpmcEhKNlBXX2FNTml4eVk2dnhuRnR1OG5CM0F3a3dQNDV3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPTDZOY0V5OUZ1REZlWWFaQmNOSmx6aXc5WkFnTjBpbDdKUFJBZVJITVluaDdYRS1MaE56WjF0VzhkbFpEMGNFMXh4YW8xdWFYQU5fR3oxN1k1aVIwbV90dEVha19QRTRNYkJiN2lIckJwbXR3S2NQc2dUUDE3eFlNU3kxX1Q5SFgxMHNFZ25iQ3VVZm1FMXpkUzg4ejdoRmh6bm9WRHN1bUxRWE5iN2lVR0FwS0ZQbkJRR21CdWFiYTBnTUlwWU1tSGN3?oc=5</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>15-05-2026 05:11 UTC</t>
+          <t>14-05-2026 20:40 UTC</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Biocon Ltd. Technical Momentum Shifts Amid Mixed Indicator Signals</t>
+          <t>Aurobindo Pharma Successful Completion of ₹800 Crore Buyback Program</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Markets Mojo</t>
+          <t>InvestyWise</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQd3JGNF9vclZmWHcyRFM5REk0M2gySUgzbHdjY2VKNVdjQm1hc01HSTRPbkxNTjVoUTAycVF5ZVNtbFB6cTBxVUlEZlNqWE1tRTlPMmF2WF9EMkRzeXBpODZmTk1Sb2t6X0psQXpISTdyVDJBZWVOTHQ5RUZNOVktelRSbXNXNjlMWWpDZ3lDRDR6R3BkZlgzaW91YzFFY295clJmb3F3OVlmcGwzQ2ZQcHFQVWFLRTZheUxlXzROOWg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE5lSVI1bHBtQzJIbUg1RHc2RmNteHd6SkJ2bDVOUFNJNENZQndQS0NBWHJfRDF6ZzhDUGZfT1RUTTFfbEt1a2pFQlNhWEtYUkxOcUNZY19iUFhua2ZwX0ZvWm9fdy1QYldOdUY0NVVhZDZyS0lSUGtJLUFveXI2Zw?oc=5</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>14-05-2026 20:20 UTC</t>
+          <t>15-05-2026 13:36 UTC</t>
         </is>
       </c>
     </row>
@@ -3217,22 +3217,22 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma Schedules Q4FY26 Board Meeting on May 21 and Earnings Call on May 22</t>
+          <t>Aurobindo Pharma Sees Sharp Open Interest Surge Amid Mixed Market Signals</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>Markets Mojo</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxOSU9XUEdSRFkwTHRTNzV0S2Z0ZUtiWUZqYmlDMnRzamVVb1JudUJka2dBLXZyS1QtTHhxMlRsU01IOVQ1WDVrVWVDc0RidElYSUdsQU5XX21LRXRNY3pmS0RxQTFsNjRWNmdQcVVfMmt1akNCaXBNZndNeW5GSlRxRFNnNktPVW14MFFLU2oyNEVzUklvbThMS3dyQ2JCaWJMeDAxb2hfZVFVS1RlVlJCVUxGRmlobnhESTNqNG1jdnppV210eHd4dm1MYXFySTFFalZqY0xrNTQ5RVVucnRKOEVtb3hWc2JESG42bEczWmZqZDg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPSzhyWWludGh1akpKdDBKSWx0QnpBZ2g5YkJ1dFdGTFFudHVnS25wXzN0V05zT2dWUHM4NWJwQ2hEbHI4TjlLTWFZMExBNEdVVFA5YzI3UkV4RzVFdW9LTk1QX0k2ckxUVFlQSG1IMUtSVEJqRU9PZk1VRUhIMHFRT0NabGNZa0dZQ3ZGN1M2VF9Zeks4b0lpM3FVejI5dWs4LUx6Ri1NQndQaHJrNjl5QXdLTEVHZEtKVjdjSldrckNhaUI4NTNTYW54SQ?oc=5</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>14-05-2026 13:03 UTC</t>
+          <t>14-05-2026 20:25 UTC</t>
         </is>
       </c>
     </row>
@@ -3244,88 +3244,88 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Pharma Quality Excellence Awards focus on building robust quality practices</t>
+          <t>Aurobindo Pharma Ltd. Hits New 52-Week High at Rs.1279.8</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Pharmabiz.com</t>
+          <t>Markets Mojo</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE4tdDY3YXUtbllCd28xMnMxSDlhT3RNYlhUTmNPWk5LSl90LVREWEhFd2I5NkJEQm1MNG5mbGZCWml3cUtDVE9IeVowbmJyamE0LWVPS1QyQTBnWG5VRlhhc0x4T2pycmdBTnZJRw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOTEZCSXZ5cktQOWp4ZU5nSFFjTVdsN2xuOVl2cFgzN2hUUWRNUW9OUUJMM24wMEl6TVFHVFRtek1GS01mYVAtS0dER2xXb2pXay16T2VmdFNiZHJObmRjcUdOdDdxMDh2NXNXZmN2NzlRV2dKUnpwWDl3eGcwVWFVc2hfQ0d4cUlOcWZYVjc0bFRnV2dISGQ2YjhIWjNOMlJaVGtIWnJ1V2MxYzhSZ19NTQ?oc=5</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>14-05-2026 19:40 UTC</t>
+          <t>14-05-2026 20:25 UTC</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Zydus Biotech</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Rupee Hits Record Low: 4 Export-Focused Stocks to Watch</t>
+          <t>Zydus Lifesciences to Acquire Assertio Holdings in $166 Million Oncology-Focused Deal</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Equitymaster</t>
+          <t>ChemAnalyst</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswJBVV95cUxNZ0dlSWV5ajZZR2M2NGh1VVlIaDJpQXFQLW9XUFlvWkNVWFBnb1ZKeGdMTEFrTWFqeTQ0NG8ta05hb0RtdUJzQkRMdHBtUF8xYWw4NUM2dmZwb3pQUzVwelhzSDVpRzM5bjZKQ016T0EyOVVVLU5idmNKTUdnNVRVelVtalpONU5WT2ZHOGRYVnIyVUdfZDhvTGVWWWNyX3pVQV85dU9hTUZPNFpDc0hQLW5DdmZqMG5qWGVoSXE3NkZSekh2QlhoTjl3SmJvUTJic3h2eDdxeV9Eak40U1BXTHpkY1JHSTdQQWJHMnF4MDQzRlZCOFpOekZnOEZ2UEFVRE0teEVobHBOOHJsZ2lwSGlCWURjUUQzdnhzelJrbWREbWh0bkJHT0FfQldtVFhBZGtF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOTm5XTVlTTmZkTmlWeFNnMEJpUmhJM3lka3BITWdjSTljMGV0Mm14RUgteUp2MnNKQldFQlpEOHZMWkZHX1pHa0phWDN3SktqdjVDZFEwUEVralVIS051ZGZJQ3JDNEc0YkFNdjd4V0NzU3dCSzNkWDZlYWtyLUJUa2RWYWU1eExSWTFKOEhOTFdJOHRYaktUQTV0b1lSeTlaaG1qajZNVnY3RU1obFl6aWhvcGt2SGdZcUpGby1Ob29iamRxY2M5ZV9B?oc=5</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>15-05-2026 11:14 UTC</t>
+          <t>15-05-2026 16:36 UTC</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Indian Pharma, Tech, Engineering Firms Pledge $20.5 Billion In Investments Across US</t>
+          <t>Samsung Launches Full 2026 TV Lineup Today</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>IndiaWest</t>
+          <t>samsung.com</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNREoxRU5pYko1aW00NVVwSUNBUzFHRlMtSHphUmRNdjg0Uk1YRnR6WnhPdkFKei1rU2d3UnJhbGVyMkZ5ZG1KLVN4anZjb0xjd0R1TGJZTTgwbFNtRVM5a21hY2xHamJkZW8zRm96SjlCTmNCMEl2VFVkQ2k3TFVDaHNoQnZZclBSSlFlREh5WWFTX0d1WVZ1ZnA0YXZoaFAwODVtNGdvVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE1KWXk0VXNMd2c2Y3lvWHI5RnVkSlJsajN5aXF4RTU4LXRwNjhVSGJvY0d0ZjdsUG9hUWo0bjVhZHVPYmdNZ1psUjUyUWlFS3JuX29rb1JkSEJobHV4TmZ4bnRnYkpRTGNzcW5IUE9HSlZJU05tVUNnMjZn?oc=5</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>15-05-2026 04:40 UTC</t>
+          <t>15-05-2026 15:12 UTC</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Zydus Biotech</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Market Trading Guide: Buy Zydus Lifesciences, Solar Industries on Friday for gains up to 15%</t>
+          <t>Samsung shares crash 9% as labour strike raises fears of $20 billion profit hit</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3335,39 +3335,39 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxQM2xYZmpDUmFCeEJWTC05bXkxM050aE8zUmJmaDhmNl80c1dPS3YySjhRckt3dTkwWHp3N3NuTHJsRUwzeGJHMXdta283TVN2YmpWOTVraERLdTlMMDJpQU40OC02UDQzU0xoRVhZNVA4UWxOV1ByWkRIbnc4dXBBbUVkU2FoTDE5bklTWGxIajNUczJxQndaUEwzWWgwMWcwSjJFeE1CQUNQODBxdzJYTzdwZUFkeHQ0ZHdyT2FGRHg3aG9uVXNCU3F5ckxZTEZHdHBzOEFheDFXVUpRTzZkUjBkTDdTNVdzU3oxM3pWS3RsUWxIckHSAfsBQVVfeXFMTTF6Q3dGS1Fuak94ejh3UlZLR1FETTN0VzVOdEoxV1IwcHl0RFlCRFEzWXdUOElTLUFRQm9aTnBZbEVyc19oaTNDdVlQVFRtai0tTGJEWVEzNFN1UU50NE5BQk83RXF4VVA1RzUxVVNFVGZpZ1JGUXBPVFkxeEdTSzNpZEQ5ZWotQU1xNnJ4UUJDVVk4MjB3aFE4OVk0bUkxOURKd2x5YV9iRWlPU1YtemxCUS1LRTgyaWZuRUFvbUxrVlhNLTRDTUZBejY4czY0NnFpcGNia1I2RXd6N1RFZkhEYUczdmJTUUZ2U2NlUDhoNWRnRmljdFZDMHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxNeHJwZ1MwdTN0bG1Uc0xpamNGempCRDBFd1haT1Z4R0RTVE1yNlhDcEJKM0xNZGdLTDZDaWJOa001RGwtU2w0UktxSzBFQkR3dzV2dm8wNjN1dnlBUWRmRGp6ejRiSXVqSWp5Z01raEU4T3R5YzRMRFRVMGFOejFPX08zN1hBUkN1bWdIMXEyQkRqYTZfVTEwcFZ1MnpRd0FWWFpFaEdxb2ZwdTJGLUowa3NXNkxlZGVyWHpiSFRfTm1PNTNtSGFGRGluekVPUUxocHpOZ3RsdXJSMnNjMncxWWxTZFoxS2UyOXfSAe8BQVVfeXFMT012VjVyWTBOWmpoUlJ0RkI2MnkxWVM1RDZZdTNaR1NQbUJ6Vm9vWURNbzVTcTNvVF9SR3Z5S2dzekdQZjgyNWNvZFdMSEpkZ00xMGN2UnVabUZuam1OalZUakNVOVh5djdGUXRQMi1lOUg3Q3ZZeEJYVkVTeXJoWWVUM25zSUJ0bmtuWGhxTngtclpCNlZRNmRyaXRON1JNbXVzejZPTm9IbTJMM0VCUjQzSURvSVhvVzJUNGl5UUp2eE5MU3hBQWRxeXdVR3Fnek9TVDZRbnQzZzFNOFZkMWhLU05jX0Y2YnJ5bE5nMEE?oc=5</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>14-05-2026 15:29 UTC</t>
+          <t>15-05-2026 07:50 UTC</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Zydus Biotech</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Zydus to acquire Assertio in $166m deal</t>
+          <t>Exclusive: At Samsung, the global AI boom spurred a looming strike and deep divisions</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Pharmaceutical Business review -</t>
+          <t>Reuters</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTFBqMFRiVldMNk9lUFNMRFBiYUtWbWNxOVIyb0dWR0cyNHZ1QVN2NlZlb0pib29kVmItRE16RjlzOWczeFpBa3JuU3ZyVVpOT3gteFlLY1NjTXBlUEdINzltN0dBeGFyYU13cWdPcHgzTzV5SDk0ZXBPa2ExNU5rejQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPazhhTjBlZFhaU1F0MVhQc0liUUhodERHaFIwOGI5amFWemRFejQ5SXJZWDZlY01tTEtkaEtoVzQ0aVc5dFpoWDlLUmtEQVRyVzRsVlhIX2N5LWxZUzY5UkVaUVhlOWVoelUtenlraVpGQk5XekM4VWlNUE5qTVRoUGRiUWdhcXVxQXp1eDRLWFVSNkFQTTNqR00wei1SWkZaX0ZnTHFFOVB5VGVmczQ0cUxEOW8tN041U2I4?oc=5</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>14-05-2026 12:06 UTC</t>
+          <t>15-05-2026 13:45 UTC</t>
         </is>
       </c>
     </row>
@@ -3379,22 +3379,22 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Samsung Electronics Announces First Quarter 2026 Results</t>
+          <t>Samsung shares slide as labor union presses ahead with planned strike</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>samsung.com</t>
+          <t>Investing.com</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOWUVwY3RuMVpmN0E2LXdudkFMWjl3VjN6MWp3Vnk4VUUzTnkzdGVRNi0wWXN1MnpRODQ2c0RGWE9Wbjg5Y0RfejdZZUVjZGJGdi1GdDVCdzlzWjBNU0hQbVVtTGJab3lNakR2S1RKSzdOVTVrVDZVV0xoWU45ZFFoVjVZUDdsTTRqai0tVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxObmpwcVZNTWwtd1gyOEtEQlpJWFpnTGVpaHVJSWFXMFFlTzBkbDQ3NlUzb2ozcTczY1lXQ3l4RGswX2xzRThZZnFrVUtwUnpWSFhOVDhlUWVsNmtCNERCVThHY1FOWXBPWDRRenlMUS1SR0t3V1FEZllRTnpxU0g0WWk2R0JFT2lCZDFpbHp3eUNZQ21WM21Vclc5YW1oZDRZa1dhSXg0NUlBQkY3bFJpWXhac0VqX1JpWmItVThkWVQzb3p1?oc=5</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>15-05-2026 08:19 UTC</t>
+          <t>15-05-2026 06:16 UTC</t>
         </is>
       </c>
     </row>
@@ -3406,22 +3406,22 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Samsung shares slide as labor union presses ahead with planned strike</t>
+          <t>Samsung India revamps smartphone leadership, unifies sales operations: Report</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Investing.com</t>
+          <t>Storyboard18</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxObmpwcVZNTWwtd1gyOEtEQlpJWFpnTGVpaHVJSWFXMFFlTzBkbDQ3NlUzb2ozcTczY1lXQ3l4RGswX2xzRThZZnFrVUtwUnpWSFhOVDhlUWVsNmtCNERCVThHY1FOWXBPWDRRenlMUS1SR0t3V1FEZllRTnpxU0g0WWk2R0JFT2lCZDFpbHp3eUNZQ21WM21Vclc5YW1oZDRZa1dhSXg0NUlBQkY3bFJpWXhac0VqX1JpWmItVThkWVQzb3p1?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPREVqUXNQNng5Rm9aeU5iaEdsSlB6aWJLaXZvcl92b29xcDdxQ1Ywb0R2ZU9EREtWdTZuR1JRLVgwVFU4QWZoenUtWUEyRGVvUGotNjdEa3ZLcWhkZFhfNkhodEhRbUxJTUc4OXFleEN2cWFOdVcwS3RIcmNNS0xrQmoyNXRKQzl4LTVWZTlPQnA0WHVhTkdtX3p2bGp5ZXY0MzY5a0tEdHlCMm1wbUNtdTBPNmdfZjNiQ3hMS3EzWjk5WjkxLWt4aG9n0gHPAUFVX3lxTFBrQUZZRGNsUzZYZTBtb2daTFEwdlRVakJNOGREN1JiMzFWcmFEWkZLejBhaU5pd3NrM1kzMXpuclljUEZrdFNqajZTeG1pSXk1aV9nTlVsZ3dwWld3Yk51UTI4Q0J1MzdUNGdLSVZmLXMwWnNDSmRJYnlfT1hPWF9jNEJ3LU5wTzQ2SE05NUtIMWo3eXBkRndOLWNjWlZtbnk0VHFRbWZ6aGRXVEhtRHZ3NXlla1JJdGVlSHBoVlZmdVViYWRtQWJxREp1a2Rvcw?oc=5</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>15-05-2026 06:16 UTC</t>
+          <t>15-05-2026 12:16 UTC</t>
         </is>
       </c>
     </row>
@@ -3433,22 +3433,22 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Samsung Galaxy S25 Ultra now available for under Rs 97,000</t>
+          <t>Galaxy S24 series gets stable One UI 8.5 update in the US</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>India Today</t>
+          <t>SamMobile</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxPUkMxU21jX1hvcFJFZHZtODI1d3B5LUhsak1QMVFBWGtvM2ZjcE52NnlDM2I0akdXR2dOMG92dmQtRWItX1VfV1MxWDltZXZOYnRRRVppZUN1ZU5FZDNBcjhjYmY4UHRnNDNzNkZoVmZVbERleGg3bmtYZUsyZ1lYZk1FR3VpaFA0THJFUDd3YWdldEpBQXE2aEJKbFc1VXY1TWlUSUdIMVlFRDk5RUpUVUhNNThZaHhMeG9RdjNNUVFjNG810gHEAUFVX3lxTE9SQzFTbWNfWG9wUkVkdm04MjV3cHktSGxqTVAxUUFYa28zZmNwTnY2eUMzYjRqR1dHZ04wb3Z2ZC1FYi1fVV9XUzFYOW1ldk5idFFFWmllQ3VlTkVkM0FyOGNiZjhQdGc0M3M2RmhWZlVsRGV4aDdua1hlSzJnWVhmTUVHdWloUDRMckVQN3dhZ2V0SkFBcTZoQkpsVzVVdjVNaVRJR0gxWUVEOTlFSlRVSE01OFloeEx4b1F2M01RUWM0bzU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQS292elJGUFJLRlRZbVM3aUhGZzctRmQtTnROd3pTcTFKZkRYQmE2VkxKaVloWGxQQW81YWIxVFVrTnEzNjRYTzU5REU4WGJ4b012NGJxWFJBWllNNnh0alVONTdtcF9DMmdpR21ZVF9RX0p1ZmJWZENQcnRmSWF0Qm9CdjVUOWM?oc=5</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>15-05-2026 10:56 UTC</t>
+          <t>15-05-2026 09:53 UTC</t>
         </is>
       </c>
     </row>
@@ -3460,22 +3460,22 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Samsung Galaxy Z Fold 6 price drop sparks powerful new Flipkart deal</t>
+          <t>Samsung Galaxy Z Flip 8 Case Renders Hint at Design and Qi2 Charging Support</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Pune Mirror</t>
+          <t>Gadgets 360</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxNdmxuNC1vcldOb1NiV2J0aERkT1o0d1VkYzlhdzF3Wi1hRFFDR1ZjSlNfd184UjNLMmNnd3o5NWZDd1NZQWhyMzZPb3didU5GQUF1S0Y3LXRoMk00QkRILXR3TUN2RGlWeTRPM2RLVWlEVFp5MWp3VVFuWkM1Y2NJbXhn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNaTg0OUgxQ0wtYUxCdFVmc19QOXMzN3VBS2YwbHo4blpESlRhUmZUTXBnNTN4SjN3aW9XdkliUGVsaHFXenpiZ1dqUTNHV2o1UURTSTh5LTREOUhXQkFtWGtvcXBKaDNXLWU3WmN4NTZDaFpZQjBLS01iWUdiMTZzWlh1MDJZRnJUMVl2cFkyYTFaZlFIczVvdWlEXzJ5Z3FsYzdLck95cFYtT0JNa2huanlUMVo1WTI2QVFGZ3VyQUvSAcYBQVVfeXFMTUNUckhUQ3A0SFpVdUQtMUNMOElwRUdFU1hKYWhFaEtHUzJiYUstRlp1OVc3ZFpIdzVmRlRwdVgxQlhxeTVFVVg5Tnk2Mi13ak9XVFkxTWk3RnJ2ZzV4UFpjQUhBVmx0SE0wTlpfQkRjV0JubF9jbFFZNktHcDk4Z0FCdGVIZWpjcEs5LUNLYmZGZTdjVXhXY0FxNmMzc2FYNFIwYzg2Vi16ZUZoOTN1Wkh0OGF5Vkc5XzJ5MFl6Skk1OE9Ga0dn?oc=5</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>15-05-2026 09:48 UTC</t>
+          <t>15-05-2026 12:14 UTC</t>
         </is>
       </c>
     </row>
@@ -3487,22 +3487,22 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Samsung shares crash 9% as labour strike raises fears of $20 billion profit hit</t>
+          <t>Samsung Galaxy Z Fold 6 price drop sparks powerful new Flipkart deal</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>Pune Mirror</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxNeHJwZ1MwdTN0bG1Uc0xpamNGempCRDBFd1haT1Z4R0RTVE1yNlhDcEJKM0xNZGdLTDZDaWJOa001RGwtU2w0UktxSzBFQkR3dzV2dm8wNjN1dnlBUWRmRGp6ejRiSXVqSWp5Z01raEU4T3R5YzRMRFRVMGFOejFPX08zN1hBUkN1bWdIMXEyQkRqYTZfVTEwcFZ1MnpRd0FWWFpFaEdxb2ZwdTJGLUowa3NXNkxlZGVyWHpiSFRfTm1PNTNtSGFGRGluekVPUUxocHpOZ3RsdXJSMnNjMncxWWxTZFoxS2UyOXfSAe8BQVVfeXFMT012VjVyWTBOWmpoUlJ0RkI2MnkxWVM1RDZZdTNaR1NQbUJ6Vm9vWURNbzVTcTNvVF9SR3Z5S2dzekdQZjgyNWNvZFdMSEpkZ00xMGN2UnVabUZuam1OalZUakNVOVh5djdGUXRQMi1lOUg3Q3ZZeEJYVkVTeXJoWWVUM25zSUJ0bmtuWGhxTngtclpCNlZRNmRyaXRON1JNbXVzejZPTm9IbTJMM0VCUjQzSURvSVhvVzJUNGl5UUp2eE5MU3hBQWRxeXdVR3Fnek9TVDZRbnQzZzFNOFZkMWhLU05jX0Y2YnJ5bE5nMEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxNdmxuNC1vcldOb1NiV2J0aERkT1o0d1VkYzlhdzF3Wi1hRFFDR1ZjSlNfd184UjNLMmNnd3o5NWZDd1NZQWhyMzZPb3didU5GQUF1S0Y3LXRoMk00QkRILXR3TUN2RGlWeTRPM2RLVWlEVFp5MWp3VVFuWkM1Y2NJbXhn?oc=5</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>15-05-2026 07:50 UTC</t>
+          <t>15-05-2026 09:48 UTC</t>
         </is>
       </c>
     </row>
@@ -3514,22 +3514,22 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Samsung Galaxy A57 reportedly selling at an effective price of Rs 44,999 offline</t>
+          <t>Samsung Electronics Announces First Quarter 2026 Results</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>91mobiles.com</t>
+          <t>samsung.com</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxQQlRLSW1qY0xzZVdIVVVmR1E5eGR4T3VEUUNxLTNnelMxb1gwQ0NNMkJFV3paRmQ0Y05hMVh6Z3F3OENGSmM3UEpaTmw4UFRoZThUNjJCNUFvQW96cVBCSFZBV1owT1FkZDdjTm5ZZXpLT3A0dlgwUUJoVmxTeGxBdFh1RWnSAYoBQVVfeXFMTkhSenpGTWt1bWUxYWhsR2xUUzJmMl8yanYwRmVUQTlGbmFVc05RWng3Z2xrMThvWHFZRmxWZVoxRldpakJzWTQzVlNvenl4cDdiUDk0SWJhSzBqMTlwbmNjbF96Q0xuTjJBWHZwT2drQTMyY2FWVTM1aDIzdWZjNUNSQkFlNFJDM0xR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOWUVwY3RuMVpmN0E2LXdudkFMWjl3VjN6MWp3Vnk4VUUzTnkzdGVRNi0wWXN1MnpRODQ2c0RGWE9Wbjg5Y0RfejdZZUVjZGJGdi1GdDVCdzlzWjBNU0hQbVVtTGJab3lNakR2S1RKSzdOVTVrVDZVV0xoWU45ZFFoVjVZUDdsTTRqai0tVQ?oc=5</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>15-05-2026 06:23 UTC</t>
+          <t>15-05-2026 08:19 UTC</t>
         </is>
       </c>
     </row>
@@ -3541,22 +3541,22 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Samsung reshuffles India smartphone leadership to take on Chinese rivals, boost market share</t>
+          <t>Samsung strike looms: Why analysts say to “watch MU” as memory fabs warm down</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Moneycontrol.com</t>
+          <t>Investing.com</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxNaVlFYlA1cWpNMWcza1RJdVlrdjJ1SDZzQUpWelZwVVlJTk9QR3N3Mmg0b3JxTU52Umphbm45RDB3Q3ZDZFBDZ0o2Ym9OZllpWkRjYmNZR19rRHMyOWp2YlRMX3dnYnlOdDY1RmlCbjBubTVCUGQzM3doVFNYYkJxSExFVFVBOFJuMi1YanYtbXQ2a2ttV1RfdE9kV0VYcEhscDhZUnpFRUtkLURoZ1JRZHhFWlNpeC1JVWVMd05ab1o4Y2Y1dEtxbEdoblBKRF9VVzhkU3BaVzFHdGo0Y0ZDeHNYLU5GaVlQ0gHuAUFVX3lxTFBuUUw5cWE1aTZQaEs0NDRaUUNwUjM1MG1CWHdwRmQ4S21PLXVtR0JHM2FMaktSRWdjNXVHU210RWlqT3Q5RVNEUU1fMm9LY1JmTGc3X2VZRlVYaHN5em5PdVF5WlNscEZkbklFZ0ZyTmZLUE5HbnlFWmF1YW1NcEM1aDFITTdDRC1ITWNoeDVtZ1ZueE5mSHgwZHk1NWRfNEFuSXdKOUhENjVmNS1CdHdmdWp2SmtWSmttbnlWTl9vaHJCaTZPN3h1cXBma25pbEZjOTNwZGlIQVY2OFZWaTR6cE4yaEV3UWxqLUxucUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQZ183YmZzOWE2ZkE3bGFUcWVQelpyZC1vLS1IeTZfNEpZTGViUWN6aURyRURfRXZuT2Z3NUlkZ3FDVnBqU3NIT3JxS2d3T0w5NWswVTlxQWNVRDJaQmdZMDZGdzlqSHUwRGN3N2lkdWpuaks5bm4zQkRGVENUaG9TZWNpdXFzVUR0bGQtaVJUMjQ2RzZ3QjZzTndNWlpjZ0tPcGtVSVhsWjRSRUlhQUY0eDJuamQxWDRjYzMyb05LQmFGVk5xX0F1eE9ZOA?oc=5</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>15-05-2026 11:03 UTC</t>
+          <t>15-05-2026 14:49 UTC</t>
         </is>
       </c>
     </row>
@@ -3568,7 +3568,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Galaxy S24 series gets stable One UI 8.5 update in the US</t>
+          <t>Samsung updates Galaxy A54 with May 2026 security patch</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3578,12 +3578,12 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQS292elJGUFJLRlRZbVM3aUhGZzctRmQtTnROd3pTcTFKZkRYQmE2VkxKaVloWGxQQW81YWIxVFVrTnEzNjRYTzU5REU4WGJ4b012NGJxWFJBWllNNnh0alVONTdtcF9DMmdpR21ZVF9RX0p1ZmJWZENQcnRmSWF0Qm9CdjVUOWM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPT1JqRENhdXhLNWZyTlhHWnR2aWRPN0hyYnQ1M1R4b3BaNHlqZTI4bUpCeXJHc3dxNlJESXhEZWJkd0tDUlhEcWlLcmo4QVNiUjQyQlB1NUE2a1NqZkxsSnE3U014c3duc2pLWWhXZHh1ZHlER0ZRaXdYM0M1RlJfTDNDcGtOVVJURVE?oc=5</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>15-05-2026 09:53 UTC</t>
+          <t>15-05-2026 14:43 UTC</t>
         </is>
       </c>
     </row>
@@ -3595,22 +3595,22 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Samsung, DisplayNote team on education market strategy</t>
+          <t>18 days. That's all it takes for a Samsung strike to crash the global AI chip market, and the whole world</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Digital Signage Today</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPWUNmQzIyeWhqRnZtMU1yZUQtdFZENDUxOS1xTDBXcHJ2NURBTlhQUWJRWExiVmx0M0tlNXVKekxqLXh4YkFrTDRmQS1VdjNCbzVRUXVnUmdFR2JacDFqWTBQeVVnYkVhY1luT0thdVRhTERKOEhBUTJrMUVNeU4tNjVmaXVRUXpoUWZrTVhPdktZdlFTa1hkR05FTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwJBVV95cUxOVjlpeXQzXzg5ZUU1cDVDT3J0RVdvWDJacVZaSTJ2RDVUYjREUEJMMkpfbkFuRDFJcVhPTzZqbzdmR3daZXdGZjZNaXdGZmVDeFNSa2hxdmU1aGQ0VW92TXpGQ2tUUl9Obk50VE5YeDJta2J0TFlrN2t1ZGFaTEJRdVE1NmtSQmt2cUU1Q0l3Wll4cmdlNTlvT2pSd2kwY0V0X0t4cFZ3WWt2UG1IMkVSeU53TmZrbk5Fem5GT0RtTDFUYXV1LWpWcVRZbm5XYzBvUVJ1azZ5bTlKeU83bVVVVzVHem9iVERlQ1dEd0ZhWS12cm50REs0SDdVTkVhY3U5ZGxSWWU0OGR5XzRRdkF1S2RQQllEY0NRNFVVRFF6M0NobXFKRVRz0gGsAkFVX3lxTE1CbTRRaUxrUG9SMTdMWjdRN0Zoa2UzSXFIQ1JIR1gxUUppYVc0N0FJTUJuSXlZZnp2dnFfSEFOak9MUjJTV0FoS3ROM2F6aVhuWC1tRmxOUUVHeGc5dHE0aEdGVTNUbG8xQWRLRkp6WTFfT1piVHM0clRRbmpsem1lb0hHNkdlTEZfRUl5R3NraGlHc0w5TXpwSVhfb3ZzU2hGZUJiS3RkdFAweW9wa2ZXbkdpNE83UkwwY1dTeUVEUDNwR2xXc19kcGtibWNubmZ1eWZXTDJhY29kOWFSTnNFSmd6bG45MWFIMlQ2dEdGV3g2TnZrV1RGcWlrbjZLTzJhZnVMTlduRFdYdExnQnBKN1BNT0pIeVhtT1pnOENvM0poQWlDT0pXblVuVw?oc=5</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>15-05-2026 10:00 UTC</t>
+          <t>15-05-2026 16:38 UTC</t>
         </is>
       </c>
     </row>
@@ -3622,157 +3622,157 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Samsung Launches One UI 9 Beta for Galaxy S26 Series Users</t>
+          <t>Samsung Galaxy S25 Ultra now available for under Rs 97,000</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>samsung.com</t>
+          <t>India Today</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxOMGVWbDZic0J6bzFFdU5tRERkTm1veUxfdTNQeEFPV3drMzdYaEhxVTJKd1lDQXk3b1JKTmVvU0hXZXNnWDVpOXNYM1U2SlpRU0pkNHBYTHRpX1dkanhLOUxxOGJsckdMQmw2dk13VmF4Ml9kTEFNRnNudVhRRjdVQ3B6ekpVQUtFWnROY2RRWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxPUkMxU21jX1hvcFJFZHZtODI1d3B5LUhsak1QMVFBWGtvM2ZjcE52NnlDM2I0akdXR2dOMG92dmQtRWItX1VfV1MxWDltZXZOYnRRRVppZUN1ZU5FZDNBcjhjYmY4UHRnNDNzNkZoVmZVbERleGg3bmtYZUsyZ1lYZk1FR3VpaFA0THJFUDd3YWdldEpBQXE2aEJKbFc1VXY1TWlUSUdIMVlFRDk5RUpUVUhNNThZaHhMeG9RdjNNUVFjNG810gHEAUFVX3lxTE9SQzFTbWNfWG9wUkVkdm04MjV3cHktSGxqTVAxUUFYa28zZmNwTnY2eUMzYjRqR1dHZ04wb3Z2ZC1FYi1fVV9XUzFYOW1ldk5idFFFWmllQ3VlTkVkM0FyOGNiZjhQdGc0M3M2RmhWZlVsRGV4aDdua1hlSzJnWVhmTUVHdWloUDRMckVQN3dhZ2V0SkFBcTZoQkpsVzVVdjVNaVRJR0gxWUVEOTlFSlRVSE01OFloeEx4b1F2M01RUWM0bzU?oc=5</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>15-05-2026 06:56 UTC</t>
+          <t>15-05-2026 10:56 UTC</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Samsung Galaxy S25 FE fantastic deal brings AI flagship under Rs 50,000</t>
+          <t>Celltrion's Remsima Captures 70% of European Market</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Pune Mirror</t>
+          <t>Seoul Economic Daily</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTFBtNDM2QVpqU3ZkVmcweGNrTzZneG5UNUtJTDVhZlNpR3psQUxvVlJVVTNsZGNLTDBMWTFsU1IzZXlRZGRMdUg0QjlKN2FYZ1FtTnFNNC1YeUJDNkJMMnRpYTlaS1VxdlRtZnd2WHQtc0V3akgtbGNEVjl1U0Qzdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPempJYTZVcnEtTFhFUVBmUUFfVkxaSG1xQmxBZ1pLdjJ2ODdQQTUzdXRmdFc2VGEzOV9Qa2sySzN6eEp0Qk9uenNZRDR6TDBwbldSVUZoLXBkajBZMlpCNnJuWEZPVXZpVnZDak9JR2JPMktreHBZeFdsOEUtQUZYQ3RoSHpFOE0yMlVFd3dPRU02bzZ4d1Z4bTd3TklWcVpJ?oc=5</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>15-05-2026 09:44 UTC</t>
+          <t>14-05-2026 22:02 UTC</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Samsung blames content partner for unauthorized use of Dua Lipa's image</t>
+          <t>Korean Pharma Giants Post Strong Q1 Results</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>SamMobile</t>
+          <t>Businesskorea</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOOWhNblBWalhuSEczejRYWGdhMV9CcEFuSXU1bjk2V3BYLWNjb2VlUWFpTks1aEhnWl9IRkxULVVxaWw3NVZhd2xPSGxtZ2F4Z0VKOHFVR3h5RUR0aGRaNzhIYnVuUWJOLXFlc1BfRktwZFhRNE1hMnRNTnFqNnB3QmJDejYxRTJqNHBMOE5FUjZIUEkzUWJsLVBVWnZyMHVxb0FZcQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE1BWmlGQkpsY2JCZ0s5S0REMkxxaTJTZzhlQjBrUHAyaUJKY3p1NjlVY2Z0bngwOHBtX1ozclYwS096TE9RU3JvYUR6SU5xZ0Y2TjNIY3FPQTd4UkphaUFpNGllTndzOUVOaUJ2SDl4Uy14MHpW?oc=5</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>15-05-2026 11:15 UTC</t>
+          <t>15-05-2026 09:13 UTC</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Exclusive: At Samsung, the global AI boom spurred a looming strike and deep divisions</t>
+          <t>Fierce Pharma Asia—BMS-Hengrui's $15B deal; Takeda’s 4.5K layoffs; Daiichi’s oncology ambition</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Reuters</t>
+          <t>Fierce Pharma</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPazhhTjBlZFhaU1F0MVhQc0liUUhodERHaFIwOGI5amFWemRFejQ5SXJZWDZlY01tTEtkaEtoVzQ0aVc5dFpoWDlLUmtEQVRyVzRsVlhIX2N5LWxZUzY5UkVaUVhlOWVoelUtenlraVpGQk5XekM4VWlNUE5qTVRoUGRiUWdhcXVxQXp1eDRLWFVSNkFQTTNqR00wei1SWkZaX0ZnTHFFOVB5VGVmczQ0cUxEOW8tN041U2I4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOeVRFVW1UMkV0Z0had0gzSUpSWHhMZGRCc1B2MGxSd0stc1RyUnA0TmU4YWFkNmYxQ1JELS1HX3RWeVAxUEQwbnRtUExkcFk0V2ZWSzl6bFZRSmtVbGE5eU81ekc1T2RVT2dkRzduYW9QR3d3aWRxR2w5czdObnJoNWE1MEFsQ20xT1YxZi1IZDVpSGd4dnRFWDYyZUdtaHNsSUsycw?oc=5</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>15-05-2026 10:39 UTC</t>
+          <t>15-05-2026 12:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Celltrion's Remsima Captures 70% of European Market</t>
+          <t>Daiichi Sankyo Company, Limited (DSNKY) 2026 Guidance/Update Call - Slideshow</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Seoul Economic Daily</t>
+          <t>Seeking Alpha</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPempJYTZVcnEtTFhFUVBmUUFfVkxaSG1xQmxBZ1pLdjJ2ODdQQTUzdXRmdFc2VGEzOV9Qa2sySzN6eEp0Qk9uenNZRDR6TDBwbldSVUZoLXBkajBZMlpCNnJuWEZPVXZpVnZDak9JR2JPMktreHBZeFdsOEUtQUZYQ3RoSHpFOE0yMlVFd3dPRU02bzZ4d1Z4bTd3TklWcVpJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNSUozMFZJblRlaklsX2tKMGVuclIzcm5BZElRVW1ERzV0dVY1QzJpeFo1T1BndE9sZklSeU9JbnBXblFxd1NRMlBCcFA0NFFmYUxEVWt3dFQ0VUZLNjVMdEJ2YnNKMmNPMWUtUWhQb0EwdWp4ZFVTTFAxdWc1RGgxMEFFd0dmOWp4WjZ0ekF0UnBsNThZZGZIY0hSZFd0SnRhN01JLUhpejEzcFJRRExHOGxuVQ?oc=5</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>14-05-2026 22:02 UTC</t>
+          <t>14-05-2026 23:43 UTC</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Korean Pharma Giants Post Strong Q1 Results</t>
+          <t>Class of 2026 Prepares to Take Center Stage at Commencement</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Businesskorea</t>
+          <t>Cal Poly Pomona</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE1BWmlGQkpsY2JCZ0s5S0REMkxxaTJTZzhlQjBrUHAyaUJKY3p1NjlVY2Z0bngwOHBtX1ozclYwS096TE9RU3JvYUR6SU5xZ0Y2TjNIY3FPQTd4UkphaUFpNGllTndzOUVOaUJ2SDl4Uy14MHpW?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxON0Z5MTBNdEpwQXhHNG5zN3lweTE4NzNYZ2kycjZsaHZseHA5QWw3bC16XzVhX3Y5TFJiakhta3RTaWlWZkRDNDRqVFo4N0FLYXp5d3BJUm1sX0c5OFBpNTJGcjU2c0FJUzlFZ2pEXzdTcjVqcWlwdXFodFh4Vk9SVjBET0E2U05wTHJTX0JKVHpWQmNHTkVfN2dqeGp4eDh0Unpvc0NNSGpBMEdBWWdDZWJ3?oc=5</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>15-05-2026 09:13 UTC</t>
+          <t>15-05-2026 02:34 UTC</t>
         </is>
       </c>
     </row>
@@ -3784,103 +3784,103 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo Company, Limited (DSNKY) 2026 Guidance/Update Call - Slideshow</t>
+          <t>Keeping Tabs on Hantavirus; MA Auto-Enrollment; Mel Gibson's Ivermectin Influence</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Seeking Alpha</t>
+          <t>MedPage Today</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNSUozMFZJblRlaklsX2tKMGVuclIzcm5BZElRVW1ERzV0dVY1QzJpeFo1T1BndE9sZklSeU9JbnBXblFxd1NRMlBCcFA0NFFmYUxEVWt3dFQ0VUZLNjVMdEJ2YnNKMmNPMWUtUWhQb0EwdWp4ZFVTTFAxdWc1RGgxMEFFd0dmOWp4WjZ0ekF0UnBsNThZZGZIY0hSZFd0SnRhN01JLUhpejEzcFJRRExHOGxuVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE1ZbVVBRzVEUW9VY0F0M1NGa19CcVpnTGt2Wm55VklEcnVKblQ5MWtHNTFuLXFuZjRWbWZFLXczY2lhNWE0b1N3T3FBOEpfN2JKYWNpdnctaU9fRElReUJHT0JQalM?oc=5</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>14-05-2026 23:43 UTC</t>
+          <t>15-05-2026 15:02 UTC</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Kyowa Kirin</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Class of 2026 Prepares to Take Center Stage at Commencement</t>
+          <t>Kyowa Kirin secures FDA approval for Crysvita dosing update</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Cal Poly Pomona</t>
+          <t>Pharmaceutical Technology</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxON0Z5MTBNdEpwQXhHNG5zN3lweTE4NzNYZ2kycjZsaHZseHA5QWw3bC16XzVhX3Y5TFJiakhta3RTaWlWZkRDNDRqVFo4N0FLYXp5d3BJUm1sX0c5OFBpNTJGcjU2c0FJUzlFZ2pEXzdTcjVqcWlwdXFodFh4Vk9SVjBET0E2U05wTHJTX0JKVHpWQmNHTkVfN2dqeGp4eDh0Unpvc0NNSGpBMEdBWWdDZWJ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxNb1U0Qi1RUEh0TjNxcXdmS1NFT0VqNWZRY0xOeXA3dl9faTBWTDBoQUUyMGdLZ3pXV3pvWk41SGFsV3VoakVwa2dDRVdxOVV0bW1LQXVaMTlQRV9wb05BNGhiV0V0S0otc2FESlBIR0xjdHlQQ3BmZDFSX254Sk1HR01FZEZKQW4y?oc=5</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>15-05-2026 02:34 UTC</t>
+          <t>15-05-2026 08:44 UTC</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Kyowa Kirin</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>CAR T May Target Residual HER2-Mutant NSCLC After TKI Exposure</t>
+          <t>Kyowa Kirin : Transcript of Results Briefing Fiscal 2026 First Quarter</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Clinical Oncology News</t>
+          <t>marketscreener.com</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPdDJoM2NSaV9jTU82VzRlYVBJaUdxQkQ5Y2hTV0VEanE1aUsxY1BOSXZoUW9NX0dVNE8wb1dUZmI4dk1odlNxTVlsaEpoRUxLSW5iT2IyM1NkMlhSdFN0SmdXVXRoYkJzTzFwTldzc0lQSzIwSGxUUkJ1Yk1JbnRDNEJreFNRWDVOS0RzazVDTXB2dDZ1LTRxczJlZWtXZzFxc1ZRcFVLcWZIUGp0N0RyakFvMGc2eUVlb05VRXh1UlM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQNVhoTU1hSFRCOUp0bmpuV2lDSVdyT2QwUmlRQUoxUkEzeTNYTEpOZ0FPQXZNVlR6am5ybzFTYl9MLVJvSG9rQzExTlRzcUUzZndiQXVUZzV4dGNXaDRsMjc2UGlFT3I4dWFHVEpKejRLcXlMajlScnpBSUlYel9Ka2hHUnZuYkZMNE0xR0FRVURDLTY1bmNxSUYzZnlvYXUzTlpla05INWFZeW9FOUVpMXQtS3FBV2JUUU9oUGJn?oc=5</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>14-05-2026 16:00 UTC</t>
+          <t>15-05-2026 03:05 UTC</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Kyowa Kirin</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Omron's AI unit hunts for rare diseases in data on 50m Japanese patients</t>
+          <t>Arna Pharma and Slate Run complete JV for new US company</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Nikkei Asia</t>
+          <t>Pharmaceutical Business review -</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOakFUOWdXYnd3aUttZmlZUFBfMTZWcHFxU2EySVotYWFPUXR5dGl3cHIxaTNwUzNwTTdmMm4xbkZFLWR4LVpSMzVzOTdhTzZjbzlYSmRJYzVBODhCeFUzd3ZUX05tdEltOVhrMkNJai1BbmxNOVRlM1hNS2VGaUNoSHJCQ2JncHVoWG05emJzdDluNVUzR0dmQ2xTcjNLaGt4M25Zbmk3ckdIRE1PLWdVZG5rWUgwVzkwM0RWYnJYMnBRMWRfSTdhSDZpaWJJV1BmaXVkRVVfcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNcWtVb2drVm53ZExiTmRXWVNZekRCZkZKU0lqYUhoOS0xUk14dmd3UGlodVQzZHRBR2t5Q3UtS2ZGa1I2MFd4NWVGWEZyeEVIRUlhTjN3RlpHZUhDTi1uaC1STGUwRUFibEoxVDN5NVlsSTNMSjZRU2VvMTBJM2ZTMXA4SzRqUDF5N25QMnU2WVVJdw?oc=5</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>14-05-2026 13:11 UTC</t>
+          <t>15-05-2026 11:55 UTC</t>
         </is>
       </c>
     </row>
@@ -3892,373 +3892,373 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Kyowa Kirin secures FDA approval for Crysvita dosing update</t>
+          <t>LJI Board of Directors welcomes four new members – lji.org</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Pharmaceutical Technology</t>
+          <t>La Jolla Institute</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxNb1U0Qi1RUEh0TjNxcXdmS1NFT0VqNWZRY0xOeXA3dl9faTBWTDBoQUUyMGdLZ3pXV3pvWk41SGFsV3VoakVwa2dDRVdxOVV0bW1LQXVaMTlQRV9wb05BNGhiV0V0S0otc2FESlBIR0xjdHlQQ3BmZDFSX254Sk1HR01FZEZKQW4y?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPU0pmTTIwTktkR2ZrTnM5dm9kTW11WEQzLWZRcng3dnllTmpLZDJHbkI1d3VPa1pOSWN6czYwWHhEMUUtWXJlUGQxUExkbENDSXN5cTFpWkUwdHJGbzR1ajRRUnY1emN0U3FjbG0yNEwzRkY2ZGdQd2N4eWQxcHpGMXhoSHRjQkdGM25ZVjh0akNXNWxLQkJkZg?oc=5</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>15-05-2026 08:44 UTC</t>
+          <t>14-05-2026 18:07 UTC</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>JCR Pharma</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Kyowa Kirin : Transcript of Results Briefing Fiscal 2026 First Quarter</t>
+          <t>JCR Pharmaceuticals (TSE:4552) One Off Gain Driven Profit Challenges Bullish Earnings Narratives</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>marketscreener.com</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQNVhoTU1hSFRCOUp0bmpuV2lDSVdyT2QwUmlRQUoxUkEzeTNYTEpOZ0FPQXZNVlR6am5ybzFTYl9MLVJvSG9rQzExTlRzcUUzZndiQXVUZzV4dGNXaDRsMjc2UGlFT3I4dWFHVEpKejRLcXlMajlScnpBSUlYel9Ka2hHUnZuYkZMNE0xR0FRVURDLTY1bmNxSUYzZnlvYXUzTlpla05INWFZeW9FOUVpMXQtS3FBV2JUUU9oUGJn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxPN3lUNWZKTlgtWnd1T0Nwc0NLRWpkcmU3TU9vWldMVDJOMmwxb3FGdzVPVW5FN3VQYm11TGpWNEFJRXVXS0lldHBqNnNuYUMzUjdCMkU4UE5kZ2FTamdnWFoxWWctODgxSTJoMkhWWjZyY3AxajdlUjRGRmlXZ1FrUk5HVzhwZ0VlbTRzMW1VdlByUWZsVTVUZ0Z5VVNJanVtUnFUcDVLUmNuLUs5LW1HSUx1c3ZvaUpELU5UUHNQc1psXy02V0JXTEdwOE5RLTZRdDQyX3NMNnE1c2dlQlp4LTN3WUdmaXExc1luX3NaN3A4eTDSAfMBQVVfeXFMTzd5VDVmSk5YLVp3dU9DcHNDS0VqZHJlN01Pb1pXTFQyTjJsMW9xRnc1T1VuRTd1UGJtdUxqVjRBSUV1V0tJZXRwajZzbmFDM1I3QjJFOFBOZGdhU2pnZ1haMVlnLTg4MUkyaDJIVlo2cmNwMWo3ZVI0RkZpV2dRa1JOR1c4cGdFZW00czFtVXZQclFmbFU1VGdGeVVTSWp1bVJxVHA1S1Jjbi1LOS1tR0lMdXN2b2lKRC1OVFBzUHNabF8tNldCV0xHcDhOUS02UXQ0Ml9zTDZxNXNnZUJaeC0zd1lHZmlxMXNZbl9zWjdwOHkw?oc=5</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>15-05-2026 03:05 UTC</t>
+          <t>15-05-2026 10:36 UTC</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>JCR Pharma</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>FDA approves expanded dosing for Crysvita in adult XLH patients</t>
+          <t>Earnings call transcript: Acumen Pharmaceuticals beats Q1 2026 EPS forecast</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Investing.com UK</t>
+          <t>Investing.com</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxOYjZqTTdwbVVzNndROWZMWnFxWF9EM2xZazN5S0RuLXcweENYVlVkUndUS0V2UGMxRVR2aGZwejlhLW9SNjNOa19DVjYydVY0ejZXWUNrT3Yza1JVUlo3c1BoeUFYeXQ2dE5XVGh2eVNmOFplS29Ral9vWllpeThfdlFRQVotODg2MldPQWZibHMtZGVuNjljTFN4MExMbGZna0VTQ2FBaHg5eDlHcVBnaXJ4QXNGZF9mbGxvVzV6QUxBWnZpS1gyNWVkVEY2NjZYX2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOZXFhakVqN1diWkZUQkJoZ2VHd2JLMEtCcjBtRW9oNzBQQnRmTzFTbFBsbV9la0gwOVpQeXU5ZGdhVlRlVGo0WHpVaFRrdEhuMVBsTndXRTB0aHJIMmd5NlktNWhJb0k3UFpqT1c4dUQ1S2htck1xZ1I1WlJ6bHFXd3hRUGUwd21PN1dKR1B2QWpXMnE1MXRmaEdma1pydWZBSDBQOUVxWnZnZ0hVaGdudUg4SVpzeXJqRGxudXVwS1ZKTWotWW5lT0lB?oc=5</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>14-05-2026 15:08 UTC</t>
+          <t>15-05-2026 13:49 UTC</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>Mochida Pharmaceutical</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>FDA Approves New Dosing Option for CRYSVITA® (burosumab-twza) in Adults With XLH</t>
+          <t>Mochida Pharmaceutical Reshapes Executive Lineup to Sharpen Business Focus</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>The Manila Times</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxOSEhpdmsxTmFDMTljSWxndzBxYmhRZGlEV1NWYks4cXdPd0hZWk5vbEsxQ3FCOW1odkNMR2dlQmFFUjFrTWJHN2dmVzUwTDRfNWUxQ3B0b3RhRGRCTXFaLXFKQ1cxdmJQWmtyaHVCRUxGQmZrTExSNWQxRUtMb1V2dmVNWGdfZm8ydWRYaEtJSzNKQVpqVDJYN0prV25wZnZIUUpmcDlDV0dkazUwWXZsMnZyakR2eGVSdkg0NHczQUNLdlp6QmhfMWxYbmk3am1wY2RUREo0bWx6b2d5cFlpTlJPcGZTQdIB6wFBVV95cUxQdUdsclVGdlQyM01NWHdLQ3JlTFJxbUNQRzBsTFVWNmQzekdyRllndGlpX3B0eTItNzhwUkVfcm56NkV5bVpTeWRuUDM2Qm5EVFVlU2lxS0pyTlRqUGRiSm9hczN3UTNqcUFYMWdnOWZNcEJMa1BhSGhfdkQ4Z215b3p0TW5wNXdxeHpiUFRFNnJCaWM2ZmFEZU1Ha3ROanpRYXR2bmpERTFiamNzNzhnbVFyWFpEWnlMQ1Y4Qk84Rmo2eFcxZG1meFFWbXlnRVVaYVdJcHlGNGVWY3Nocm5GQktFd2lvczFSUjdR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxOQzZhS1RkcmExNXRsVWVEYnJXUzFPOFB6Qlo4ZVNzME9qZ25wZE5ZazdnZmd2OU43OENqaGlTTEdSU3VKNlJUYllaV1Z2LXk1MTJDWXBVVm5LcklhdnM2MXhBWEdMdWttTnUxX1BMS25ydmllM1dHTUI3SVk3OTBRRERuUjVmVGhaRWlYM3hwVkp0UmxTNEtUaFVQN1pWRDUyaWZIYnNwSE5qdG9TWHc4YU1Xc1BkSUt5cTl2UkhyYVV0c0dJ?oc=5</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>14-05-2026 12:35 UTC</t>
+          <t>15-05-2026 05:31 UTC</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>Mochida Pharmaceutical</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Fda approves new dosing option for Crysvita® (burosumab-twza) in adults with XLH</t>
+          <t>Mochida Pharmaceutical Lifts Profits and Raises Dividend Outlook for FY2027</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>marketscreener.com</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPTW5WOHdPa2M4RDZ3bW5ac0k5enhsY2lHWkM4b2U2RkxzdVNiNG1uUEhxWG1ZQm1SMU1lWGotSGhybTNMNk5LVlhaR2JxUkI5SjZjVXZUWFBFclVfcHdYdGh6VHE2Zk1vd3hXSFBMMkh2LWNDdlFDZmxRVGVlSkJXUjhqSFNucmxMbWVyc0d1bFIzV0o5ZHJsckR5dEtncjBNZUJER0txUmY1TDdoSkZ1OXRNMHpFcTZ6R3c5cVBMTjhtVGlaLXRKM1F3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOQjRKWUthTzducXFFTEkwRVViWXVFYmVHMjJ5TEpkZDhSTUhrTzNGc0tJZ3ZfNVNWS1NkV214WFJPQXBwM29pX1Y2M0VOMERWTFFzNEl5ajNMeDlqQkk3WWtqMjYtZmR4ZV9zQ0FQdUR6UFBlaHRmUlY2amZfcWtHbnYtY2pWU2xsc0M4SF85QXpPakNlS3ZTNGxaQk44aEt3WUNvc0NydENMdFdobUcwWG1ZSEdCYzRFZUhfMmZrTE53dHJ6RGc?oc=5</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>14-05-2026 13:07 UTC</t>
+          <t>15-05-2026 05:31 UTC</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Lake Street Remains a Buy on Kura Oncology (KURA)</t>
+          <t>Fresenius SE &amp; Co. KGaA stock (DE0005785604): restructuring progress and recent earnings in focus</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>The Globe and Mail</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPdmJtMTJFeG9UdlIwR3A5TFh1ZGZBbEJiN3oyWnc5dThQQlFYYXJ4NjZQWWgyd0h2N0xHeVloTl9ENjJnQllyQnNMbjJodEs0b1BWWElhUDl0R2ZPYjgyU3E4X2xXVkRnaTVKWGlyZTZmc2o1ME9Fc0V5cktSRXRkc2RsRjdSbjdpak5FRFZ6RFkwelpqcEhUODRMelNaTHpYMFRTXzc0Y2FJT1hRdW90S05aUHB4NndqR0VkZmdxMHFvcnBsLUlTM1lOOWI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNWXRUVFN2dnB0b2JvWEQycy1zX3A1N3MxNkxLdGdlak1XUmlBUkFic19QYjMxUWVPWXNVTzRMVkllZDJtMTB0QzlHUlp2RnJRSGN1S2xwUjVzbVFNN3dMQXgycF94czdlYXFXZkJja2FQaXpnaHJWNk5xd0NuMTM2UVAzMXM4ZjVUeWwyY2dtRXk5TndhX3BfVzJiczM5aDNNeHd2dWtLVkxNeGR4Sk1udXQ5RnE3bDVJMWxqaThEY2FyaUU?oc=5</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>14-05-2026 13:28 UTC</t>
+          <t>15-05-2026 04:36 UTC</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>JCR Pharma</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>JCR Pharmaceuticals (TSE:4552) One Off Gain Driven Profit Challenges Bullish Earnings Narratives</t>
+          <t>World Inhalational Anaesthesia Drugs - Market Analysis, Forecast, Size, Trends and Insights</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>simplywall.st</t>
+          <t>IndexBox</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxPN3lUNWZKTlgtWnd1T0Nwc0NLRWpkcmU3TU9vWldMVDJOMmwxb3FGdzVPVW5FN3VQYm11TGpWNEFJRXVXS0lldHBqNnNuYUMzUjdCMkU4UE5kZ2FTamdnWFoxWWctODgxSTJoMkhWWjZyY3AxajdlUjRGRmlXZ1FrUk5HVzhwZ0VlbTRzMW1VdlByUWZsVTVUZ0Z5VVNJanVtUnFUcDVLUmNuLUs5LW1HSUx1c3ZvaUpELU5UUHNQc1psXy02V0JXTEdwOE5RLTZRdDQyX3NMNnE1c2dlQlp4LTN3WUdmaXExc1luX3NaN3A4eTDSAfMBQVVfeXFMTzd5VDVmSk5YLVp3dU9DcHNDS0VqZHJlN01Pb1pXTFQyTjJsMW9xRnc1T1VuRTd1UGJtdUxqVjRBSUV1V0tJZXRwajZzbmFDM1I3QjJFOFBOZGdhU2pnZ1haMVlnLTg4MUkyaDJIVlo2cmNwMWo3ZVI0RkZpV2dRa1JOR1c4cGdFZW00czFtVXZQclFmbFU1VGdGeVVTSWp1bVJxVHA1S1Jjbi1LOS1tR0lMdXN2b2lKRC1OVFBzUHNabF8tNldCV0xHcDhOUS02UXQ0Ml9zTDZxNXNnZUJaeC0zd1lHZmlxMXNZbl9zWjdwOHkw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxPT1N0YXJRODd2THhwb2h1WENoQ1lHUl9xeTQ3X0cxdTRxSEsyMzJxb1RlaUsxVDNIVFRBSGptS2dBdHc2RmpBMnZGQVM0eWtoTXE3RUhMX0t1d0J5UG85aHVHa0NIUlE5UDlDSGxPTG1WeHdxbVhPLU91SGtUc3p2VXdQbnh4VV9YdTlra0lsRFlDNE5IVnhEeUczQzJNTDN2eF9MOUttWjc0Nm5YcGwzQk1RZ2RHLTR0TVBwaUxjaG5Ja2s0bDAwcEI1Q2M3VUxvVXJBRllINU02WUR3Mmh1RzdaZU43bi00c3NQbmRrTlRQM2tvbHNqcXRnTXNlNlM0cXc?oc=5</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>15-05-2026 10:36 UTC</t>
+          <t>15-05-2026 04:31 UTC</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>JCR Pharma</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Encoded Therapeutics' Dravet Gene Therapy Data Suggest Sirolimus May Blunt Benefit</t>
+          <t>Gland Pharma Reports Record Revenues and Profitability in Q4 FY26 and Full Year FY26</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Precision Medicine Online</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNTGlQMnUtWmNsY2FqSDdVWUkwdExpQTFDeDg0UV95R2JlR0dNYjdXZlEyM1ZqekZCZTBVUl8xOFdNckNJWDhydW5aSkNCeFh1a2tXSFJZQXVQZVhnYW81NkdyQmFSYlF5X24tUDNKeGVjY29kNG1GZmVxams2S0t0eHZvQmZCLVF6eVZ4SWdaMUktSGtqOFRaQl9VYW51cDNCd1JaSEJhcVJzR3RhTmxwYnVJbWZJd1FacklxNVhEalRGZXpIZjl6aDhGcnFnZk9u?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQNDN3UU4tYUxJaE56XzNjM0FObDFUYzRjWTcxN3RBazdYVjBmTTBscUFrdkZQOWhXMmVxYkhqQTdqTFNYYkRLWmp0UHFUemtJQzZuUnBiYVhrM2dSb0oxamRlTTNPX0hCRC1vWDAzNGlCTzVlcC1MODhFenA1ZEZ4TEFVcHFzZ0VzQnIwaEZ2OTFta3lSR0JqeGluZU9iY0tNVHFmN3l1ek9vdFhyN0pfZnNueFRFQ2gyUzk3Uk4yazQ2d2FESXpha1F5a0JUUWZCcXNKZU8zU0w?oc=5</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>14-05-2026 13:33 UTC</t>
+          <t>15-05-2026 15:24 UTC</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Mochida Pharmaceutical</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Mochida Pharmaceutical stock (JP3778400006): Japanese pharma expands generic portfolio</t>
+          <t>Transforming Clinical Trial Design and Avoiding AI Wrappers: Q&amp;A with Angela Schwab</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>Pharmaceutical Executive</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQZ3B6LVM1ZWdkVS14d1R0eDJmczM2WTRneXdWbUdWWTc4RVd3TXNPRkxWUVJob0Z0Qmx3aTNLUzIzaTNyOGxkLVdxVzVzQXhaWXJGZk9LTDVfLVVrampvOTBKNzB6REFUUlRyTTlVTDF2Z3pXMm14VHdsVWVCLVpydVh1ay1zZ1lIQWJSQ2d5TmJhbm9tLVpxZnZZdmhod3dGelhXc21FNFlRa2hpN21UdElUVU5ZcmNZZG4xVDVqOTZUZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQbEVrN2M0R3FCQThTaV9ibE5YSFpOcmFPeUozNkdKX2xxMDJnQ3hDQzRoVFNuRU81QjQtU25zZjhtdldtTXVHTkV5N2JnbVctcHpSQkE4ZkctejQ2R01hckJ5WDVpbm9CY0xscHM4MWtLYTFqYUxMc3BLM2lkX1owVlItbzhWYjBrYU94TVpJUkpZdWNVcTZIQ0dEREp1TXJVSUE?oc=5</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>14-05-2026 12:14 UTC</t>
+          <t>15-05-2026 13:56 UTC</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Mochida Pharmaceutical</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Mochida Pharmaceutical Reshapes Executive Lineup to Sharpen Business Focus</t>
+          <t>Market Hits Volatile Week! IT Crash, Pharma Strength &amp; Rupee Near 96 Shock India | Market Edge</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>ET Now</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxOQzZhS1RkcmExNXRsVWVEYnJXUzFPOFB6Qlo4ZVNzME9qZ25wZE5ZazdnZmd2OU43OENqaGlTTEdSU3VKNlJUYllaV1Z2LXk1MTJDWXBVVm5LcklhdnM2MXhBWEdMdWttTnUxX1BMS25ydmllM1dHTUI3SVk3OTBRRERuUjVmVGhaRWlYM3hwVkp0UmxTNEtUaFVQN1pWRDUyaWZIYnNwSE5qdG9TWHc4YU1Xc1BkSUt5cTl2UkhyYVV0c0dJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOdnJSTTJsYkUzSzU4VC0xU3M3RGRxSzROUXVHZEY4V3JMa202Q2lrSU15NmJRUzBxeWNWaGM3cGRuZzlmZnQzT1lsSTdfZGFEZVJ6VTBNakl3U0EyTVRuTXdGVVgtYnVZVFJfNTJNWnZVajRqaklFajB4RUN5TWE2WGJoLXJ4Qm5MNUY1UEhzUVVVZVhJMEZPVU83NmNNbTBiVnlwZm14ZkUteHZJUGFya3AzXzlnVTNkd2x3RXVoa3NHRjhpOVlQdlNsTFVWdFBVZjdjN3pSaGLSAd4BQVVfeXFMT3ZiN2pSX3JVbFhqNUlZeVNrOXJzY3NYaWtaZy1ORE4tNjhURnNpTnR6QkpVU1lfMk13TEl5eHlSLXdfRmJnQXMyTXdxbmZCMUlEajRlVXU4cG5XLUhNNW1SaVM2bmNDVkhzRW9iTUNXc05XbFMzSlZ2aFM3aDBvSFViVUxDRkhyZklDa0JHUW1fa1ZzZHliYnZGRjhEdVZwWWd6T0Z5cDByNnduQTVkalcxRVZwS1EtbFJfdTdsendiWkRxbFlSNHVaOEtWd0xOMkM0clNwZ0gxWlJWUThB?oc=5</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>15-05-2026 05:31 UTC</t>
+          <t>15-05-2026 11:17 UTC</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Mochida Pharmaceutical</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Mochida Pharmaceutical Lifts Profits and Raises Dividend Outlook for FY2027</t>
+          <t>Biogen to advance experimental Alzheimer's drug despite mid-stage trial miss</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>ETPharma.com</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOQjRKWUthTzducXFFTEkwRVViWXVFYmVHMjJ5TEpkZDhSTUhrTzNGc0tJZ3ZfNVNWS1NkV214WFJPQXBwM29pX1Y2M0VOMERWTFFzNEl5ajNMeDlqQkk3WWtqMjYtZmR4ZV9zQ0FQdUR6UFBlaHRmUlY2amZfcWtHbnYtY2pWU2xsc0M4SF85QXpPakNlS3ZTNGxaQk44aEt3WUNvc0NydENMdFdobUcwWG1ZSEdCYzRFZUhfMmZrTE53dHJ6RGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxNZHFIVlM3a0RZUGRZZHZOTmh2VlNjVU5zaTZpOEJlNlc3cjJGYlRUY2YtN1FYbm5fQnpmemNfTWF6RHcyTEhjU3RSWEN0LVVITlJYcUowSlpZbG1vcUduanFKZDYtaHU4WXE4Mk5UVmIxZkVHemlsaWk4MGhoOXBSc1RMcXpwT1FXVzlFeTFmTU9oSS04M09YVHRyMEFoQXlhalhock9SM3VobFJnOHMxaWo3blpLOEVFZE54eFQzZEtnRmFkSTQyQnZUb3NnM0VKSTExSFN0bTJXMmMwNUh2U2RORi02NUZRcUpmMlhHWXFKVHdDUXfSAfYBQVVfeXFMTWRxSFZTN2tEWVBkWWR2Tk5odlZTY1VOc2k2aThCZTZXN3IyRmJUVGNmLTdRWG5uX0J6ZnpjX01hekR3MkxIY1N0UlhDdC1VSE5SWHFKMEpaWWxtb3FHbmpxSmQ2LWh1OFlxODJOVFZiMWZFR3ppbGlpODBoaDlwUnNUTHF6cE9RV1c5RXkxZk1PaEktODNPWFR0cjBBaEF5YWpYaHJPUjN1aGxSZzhzMWlqN25aSzhFRWROeHhUM2RLZ0ZhZEk0MkJ2VG9zZzNFSkkxMUhTdG0yVzJjMDVIdlNkTkYtNjVGUXFKZjJYR1lxSlR3Q1F3?oc=5</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>15-05-2026 05:31 UTC</t>
+          <t>15-05-2026 02:31 UTC</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Fresenius SE &amp; Co. KGaA stock (DE0005785604): restructuring progress and recent earnings in focus</t>
+          <t>Pharma Quality Excellence Awards focus on building robust quality practices</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>Pharmabiz.com</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNWXRUVFN2dnB0b2JvWEQycy1zX3A1N3MxNkxLdGdlak1XUmlBUkFic19QYjMxUWVPWXNVTzRMVkllZDJtMTB0QzlHUlp2RnJRSGN1S2xwUjVzbVFNN3dMQXgycF94czdlYXFXZkJja2FQaXpnaHJWNk5xd0NuMTM2UVAzMXM4ZjVUeWwyY2dtRXk5TndhX3BfVzJiczM5aDNNeHd2dWtLVkxNeGR4Sk1udXQ5RnE3bDVJMWxqaThEY2FyaUU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE4tdDY3YXUtbllCd28xMnMxSDlhT3RNYlhUTmNPWk5LSl90LVREWEhFd2I5NkJEQm1MNG5mbGZCWml3cUtDVE9IeVowbmJyamE0LWVPS1QyQTBnWG5VRlhhc0x4T2pycmdBTnZJRw?oc=5</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>15-05-2026 04:36 UTC</t>
+          <t>14-05-2026 19:40 UTC</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>World Inhalational Anaesthesia Drugs - Market Analysis, Forecast, Size, Trends and Insights</t>
+          <t>aTyr Pharma Announces First Quarter 2026 Results and Provides Corporate Update</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>IndexBox</t>
+          <t>The Manila Times</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxPT1N0YXJRODd2THhwb2h1WENoQ1lHUl9xeTQ3X0cxdTRxSEsyMzJxb1RlaUsxVDNIVFRBSGptS2dBdHc2RmpBMnZGQVM0eWtoTXE3RUhMX0t1d0J5UG85aHVHa0NIUlE5UDlDSGxPTG1WeHdxbVhPLU91SGtUc3p2VXdQbnh4VV9YdTlra0lsRFlDNE5IVnhEeUczQzJNTDN2eF9MOUttWjc0Nm5YcGwzQk1RZ2RHLTR0TVBwaUxjaG5Ja2s0bDAwcEI1Q2M3VUxvVXJBRllINU02WUR3Mmh1RzdaZU43bi00c3NQbmRrTlRQM2tvbHNqcXRnTXNlNlM0cXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxPamRRbWZ6cDBKaFJyVE5zb3RYYjNxWVJ4S2xfU2ZrZHFEa1BUWktqRm1DbnVpWTNBdjRuS2pOak03UUozVGVLVjRRQ0dIdHJYZ20wOS1aOTRiNHlLemFYdnhvVGlDbFkwRkljcXQwdDBabHhvV094UVc5S2NVT0oyN0dBR1lSU3pMWW81cGRSUlJaQVc2ajcxY3hSeW9TRXRidFBfbi16NWFsNVZtaGVydmcyZmRUNWxyZkdQa0lqNGpRT18yRkxWcTdETzlZR2Y4ZkJfV1N6RDhvcDM3czdLVlFocU1hS1HSAewBQVVfeXFMT1ZseGN6YzZIX25wdkJZTFhfNmxlWFR1YldPb3laUFF2NV9wQXgwZkVpRFhMQ09nWk0tTzIwTGRWS2RfNXNyOWVTVExZSWVTdlZEUGhmSkU5UXYwV0w5RHVtQmNDU0RBTGZOYnBST2pWU2x2cHJ1S0ZadHNSNTZqUUJFUG5RNUgyeGhsbmVTbTFKc3NoVHJwaVN3ek94UVl2c1V6WmJoMFpnU2pmVlRSVHBxOVdJR0k5UTllcmFMVFVLWDZkekpEOGdlN2pKa3VRZnEtZnphRVFjYTl3c3lNbUVoQzVjbGhMczJoaGc?oc=5</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>15-05-2026 04:31 UTC</t>
+          <t>15-05-2026 12:18 UTC</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Eagle Pharmaceuticals stock (US2698191026): Recent SEC filings highlight ongoing developments</t>
+          <t>Gland Pharma Reappoints Naina Lal Kidwai as Independent Director for Second Term</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxPSmExZ1ZUNjJCRlFOOGlMLW8xdUQtQ29NWl8xamxLX2M2WGF1cG5xQTEwRlVTazZrek9TM0NOSE5rc3N0OG1YWU5Db1BNX0tyNk85dXBHS3ozNk43bkVRZlgxbkRGaTBVMXVNZDRqSFpFT3pJTHFuUlpRTjUwc0ZsQ1FrR1c5ZGdheU5WbWFJb3RydFdkOHRVMkhCd21RMFVTZ0dJYXNwbjZLQWpySVBybF9fWEpkWmw3d0laMEhRMzNsVl9ONThV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxNNlBXcTZvcC1FNnh4dUo4QTZndk9oNXg4YTV6dUlreUYzYS04SnRXNW55RlBfYkRkd2Q2MENrSFV3M1Y2Wm4tVlpnVHNtS2ZzN19EaFZmYXUtNGE4NXJBOFdTUU1nR3o2cDFLRFFaeFdUbGtlWUFKYjhNY3NhVldhWDhfU05vdU9BSmNTLUJGR2dZd2o2X3AwbUlHakN0RWZnNm9vTEl5Nm4xMEhpZy12ZWpNajhqYVhHVnotdGF2aUVFSDJPaEdTSllFWmxZSm5JV0xpVWk5MjRUUWpnQVh3Wk4wYVpMd19zaXk4MTYza1JqNk1zYUZWTDVGeUtTUQ?oc=5</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>14-05-2026 15:26 UTC</t>
+          <t>15-05-2026 02:03 UTC</t>
         </is>
       </c>
     </row>
@@ -4270,22 +4270,22 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Gland Pharma Reappoints Naina Lal Kidwai as Independent Director for Second Term</t>
+          <t>India-UAE Strategic Breakthrough: Energy Security, Defence &amp; $5 Billion Investments Announced | News</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>ET Now</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxNNlBXcTZvcC1FNnh4dUo4QTZndk9oNXg4YTV6dUlreUYzYS04SnRXNW55RlBfYkRkd2Q2MENrSFV3M1Y2Wm4tVlpnVHNtS2ZzN19EaFZmYXUtNGE4NXJBOFdTUU1nR3o2cDFLRFFaeFdUbGtlWUFKYjhNY3NhVldhWDhfU05vdU9BSmNTLUJGR2dZd2o2X3AwbUlHakN0RWZnNm9vTEl5Nm4xMEhpZy12ZWpNajhqYVhHVnotdGF2aUVFSDJPaEdTSllFWmxZSm5JV0xpVWk5MjRUUWpnQVh3Wk4wYVpMd19zaXk4MTYza1JqNk1zYUZWTDVGeUtTUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxQQmFMdERUdGx0a2hLbnB6TXhFTjNzOERJeG5NUkM3aXdBcERXM2VlYnRLS1VZZWlFT2NidFBLMzJSOFhGTW52ZGNrZzZhSlBpQ1V4ZGtTYk8zZE1sUzF5Q1JMcHNud2NMVmJIMzc3c3hFaVY0a2w3dFJNMVQ5a0V3Q1BlUVh1dU5rTE15MFJYSzdFak9zbGJ1RDRDZExReWxyN0FRVDBGSmFVejUxX0JsWUQ5RHgtd2Y2eFphdVBxREJNbXBjYXp2SkVQR2pncWlRM3R2c3ZNNFdDZ9IB3wFBVV95cUxPcW14czBTVFdCUTB0TV9hc2huaVhRd1ZJSGNDNzNheUZJVGdyOTBjZHJuTVd4Mi1Fd1AxQ00yaXBlS3ZQYWxtcUZXR2VvbFY2MnloVWNXWkhyQXMyUUtSS0MzQ1RUejdkemktN29RUXFKUi1xOVl6V0lUNTVoczlGMlBMMkhJWkRWZUtlYl9TVGw2dE5hOUhrbTFpR0lHRWtVcXVTcDFxdThEVUxreVJlemFRRnZOb25MNmtHM1hTVkZNekF3S2xZWm5IcXdfSkdQZFVTVXJIOGpsWnhaMWcw?oc=5</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>15-05-2026 02:03 UTC</t>
+          <t>15-05-2026 14:12 UTC</t>
         </is>
       </c>
     </row>
@@ -4297,22 +4297,22 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Pharma Quality Excellence Awards focus on building robust quality practices</t>
+          <t>India Market Is Strong But Expensive? Expert Breaks Down The Truth Behind Valuations &amp; Returns!</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Pharmabiz.com</t>
+          <t>ET Now</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE4tdDY3YXUtbllCd28xMnMxSDlhT3RNYlhUTmNPWk5LSl90LVREWEhFd2I5NkJEQm1MNG5mbGZCWml3cUtDVE9IeVowbmJyamE0LWVPS1QyQTBnWG5VRlhhc0x4T2pycmdBTnZJRw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9wFBVV95cUxPVVVNY0VPaWJYWTF6THlweW1vMk9sdENDeG5KN0NqUE5OTmVBN0xkQkhkSE4yZkpsWXNEQ2l6MnRCMGZmRU1EbnY2SGNnenFkTjMzeGdHeWptM0EybWdzWVM0UzQtYXNQcWcxWUVqLXZJLVBBVGRYWGtjRV9NRm14UThTNXdfakxYSmhoc0JkVWhZa2RfdjZmRktUWHVLeGVFMDY3T3p5MkphSUk4WTdJYUlaclBiUVA3LWN1RERUWGNySHptN1pxaTVmYVRoTWVrQmRrLWVPVkpuZlRNMFFOT1lwTEQ4S0JHOVZCcURzYTNfOXBEZUhF0gH8AUFVX3lxTFB0TjE3QW9sS3pjODRxbG9rZTVNNGtxejFfWDRaUzV4a1ppQnM3RlZ3SlI2b0pFM1dsVC0tUGpxeDVxS043SVBnU0EwWkNLYjR3bGJuOWlJRGtsV3FwMmYzUS1oLVRCMU9tWXRSb1RGa2E2QTBVZUphel9KNXBaSjNKZVVtRDJvNU1hbFdyNWJyZlhzZ05FOHpaMVRRcVVWVlhLQTI4TzRiVW9WV0FuWFpqeWlfUmt5aWFiU2FMOWF2U1FmbWRneWhmbGNuTF9UWWVfdGZRaHBoY0NJbFN2cUFDeGJCVFhIN2NFYmwwc0pfRDBKX21yYkY1S2Z6Qg?oc=5</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>14-05-2026 19:40 UTC</t>
+          <t>15-05-2026 12:39 UTC</t>
         </is>
       </c>
     </row>
@@ -4324,130 +4324,130 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Biogen to advance experimental Alzheimer's drug despite mid-stage trial miss</t>
+          <t>Sensex Falls, Rupee Hits Record Low! Why Markets Ended A Brutal Week In Red | Closing Trades |ET Now</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>ETPharma.com</t>
+          <t>ET Now</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxOVDdpcEpFSTN1c1A2ZE5Jb0VTWlV4TTdCTzdVaDRRNHFBTzVaZ1k2Ry1qZG50bWdkd010RHd2S2VQcGxHSHhPMU03Vi1JcElUV2wzMC1wS2hiU2J2WVo5TXFSMEh4TVNldEVzWDBMMVpscWd4TV9pbTdNY003SXUwM2dZb2ZEYzRJRmwyU0gxQ21YamZGUWxRQWt0S3pkSU9pNWRSWERsaTNScUVQaEtiSlhRM1JFY1ZubWdDT2tDckFfRFNLRnE0UTNkTm1Sa1MyUGNFbmthcWd3T3FsV1RQck5reXM2TEVfNlZqZWh6LXjSAfYBQVVfeXFMTWRxSFZTN2tEWVBkWWR2Tk5odlZTY1VOc2k2aThCZTZXN3IyRmJUVGNmLTdRWG5uX0J6ZnpjX01hekR3MkxIY1N0UlhDdC1VSE5SWHFKMEpaWWxtb3FHbmpxSmQ2LWh1OFlxODJOVFZiMWZFR3ppbGlpODBoaDlwUnNUTHF6cE9RV1c5RXkxZk1PaEktODNPWFR0cjBBaEF5YWpYaHJPUjN1aGxSZzhzMWlqN25aSzhFRWROeHhUM2RLZ0ZhZEk0MkJ2VG9zZzNFSkkxMUhTdG0yVzJjMDVIdlNkTkYtNjVGUXFKZjJYR1lxSlR3Q1F3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxNSFFEeTlnSjdxaWtScy03SnlPTHJrd1dLQ1Bnd19od3JvVlFLQThCSnpQYUQzMzlYSWJHNXlzVFZ0VER5QjA5enBOUnMzdDdkXzFhdVdScXEzTTRVMFdiYkZyZl8yRTl1cW1wclFLY21TUy1VQ2JBRHNLX2dpVGY3RG5vU0hLdWs1WXpJajZ5UFZ6dGVmd1hBVzdMWmpLNkVWb1pWNVZ1SGZpM2M0X3BId3FTOFBBYmZDUjBpa3dDM1JtbTdqam5Zc3EwNnk3dm1QcVdjcHVCalB1RldMU01RdVB0VnlkUHBYNnM1QzlXVGRqX2Mxcnh6QzlXV1JMWUJ1WVHSAYcCQVVfeXFMUEZURVN0R25JSFVvOHk1WVdCSElUazZ3VDJIRGFQMUNFbkVfbGEtWjNJSWItckZuclpiWEJXdWM1VXJNOGFDTThWNF9rUno4VHVWaER2amRQVC1MN2lYVUJxbHBiSGpsUmJtc1UzQUxhVUZ2RzkyalJ3a2ZlM3BTS2xWakF1TDY3SnpxM2lLbDRJbkVyRTdhSnpuUUZyRGNKRVJGVWRQdU1nNjEwdGRXTWN2ZV95cUNyTHpWUldvLXBhelVNWTR3bEItSUxtenJQVkRKSHBrbXgtX1ZvWjN6cFI2UzJoRWVXVXQyR2ZZQXp2bWVLLWhsb01GVW84dTM1ZVI3RTh6bVk?oc=5</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>15-05-2026 02:31 UTC</t>
+          <t>15-05-2026 11:02 UTC</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Alvotech</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Transforming Clinical Trial Design and Avoiding AI Wrappers: Q&amp;A with Angela Schwab</t>
+          <t>Alvotech Plans June FDA Resubmission for Three Biosimilar Products</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Pharmaceutical Executive</t>
+          <t>HarianBasis.co</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQbEVrN2M0R3FCQThTaV9ibE5YSFpOcmFPeUozNkdKX2xxMDJnQ3hDQzRoVFNuRU81QjQtU25zZjhtdldtTXVHTkV5N2JnbVctcHpSQkE4ZkctejQ2R01hckJ5WDVpbm9CY0xscHM4MWtLYTFqYUxMc3BLM2lkX1owVlItbzhWYjBrYU94TVpJUkpZdWNVcTZIQ0dEREp1TXJVSUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTFBIakNKV2UzcGs0VVRoRW9UUkI4cFpYUnAzQ1FBOXhmb0prbEF1VUhMXy1aTnRkcHVzQXlKY2hNUW5IeTEyOEtiMVhCT1JsVlAxV1RGQ2dVSmprLW1TY0FabjZpUGREWnFNRUxyUDRlYjdnaU9lTVFwUHlhVQ?oc=5</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>14-05-2026 18:50 UTC</t>
+          <t>15-05-2026 11:43 UTC</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Advanz Pharma</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Gland Pharma Limited Reappointment of Ms. Naina Lal Kidwai as Independent Director</t>
+          <t>Head of IP at Heidelberg Pharma joins Fuchs Patentanwälte</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>InvestyWise</t>
+          <t>JUVE Patent</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQaWhLMEZLRzRCTnpZZm9PMWJnZUZ0ZU1nVWxuOGRYWEpVLVo5X0cyVmQzVzVOTUg0dndpdGJ3bGdTTzRXbzJ3NmY2R3lZUmlZRHFlblRuR3RTNmdib1lpSWpZc25FbmtXNzVPazNxWG8tb1RKVHIycGpGNGd1MXVXZ3BpQ00xcGtGbW9fVmF3cm0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOay13VGozUFZ4NXJxU2hnWHByQ2cxalNjNTM0MzJGX1FoWjdTRngtc2xPU2gtWUhJei1ZMi1XSFlrZVVQUHF2QkZJSExKTEl3dnR2LTJDVmcwTmxZZi00SnRHUGZiOW9VbExIZHFWcFRjS0hMTkY4WHp6UENoRUZfeExSLU9QWWJrYm93ZTByQnFkZXlzdWs2ZE1xYzVrNFBteTdPSld5ZmNoUQ?oc=5</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>14-05-2026 13:09 UTC</t>
+          <t>15-05-2026 11:38 UTC</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>BioHarvest Sciences Appoints New Head of Business Development for its CDMO Division</t>
+          <t>Is It Too Late To Consider Teva Pharmaceutical Industries (TEVA) After Its 3‑Year Rally?</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>BioSpace</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNOVV0RHpFOVVsWWt5MVU2c2gyOVliamdHanVpbmJMRHNZWE1SSWFKcVZZWVpaSHJJdFJYVFBwbWo2clhwdkdmVmtvRU9ua3hSR2pmYXMyYkFBOEhHaUpxczNIc2FsdGNUaXBiQjRjU2pMR1pmWXU5QS03STRxN0E2YVAxTjVmSlhYTzdSbVNLUjlmMkQzc3RTdGVWU0dLWG9iR0FmUWlZXzh2QTh6Z2NVaTVZenNzLWlUdXk1TjBoeHM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOeE1kZzE1bGtERmVnZVI2S0JPZUt4c2tXNXl2SVJqQlNsMFI5dnpOOGlCM21oRU1ZZ2p6OXppVHpwSU1zQWduU3FlZHJKYVhMVmpodGxPU3dtMHBPalRBQ1I3eW53T1RmSEtyVF9YUUNGTnROWldNX19Ta0lQZEJBaWpBSUNRM2tBLXdXcENTeGE1OW14Y0Q0ZkdnS0pxemJhWmxRLWxUckRSaTB3UDZ3TGRR?oc=5</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>14-05-2026 15:29 UTC</t>
+          <t>15-05-2026 09:13 UTC</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Alvotech</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>EBITDA of Alvotech Swedish Depository Receipt Repr 1 Sh – TURQUOISE:ALVOS</t>
+          <t>Earnings call transcript: Teva Q1 2026 earnings beat forecasts By Investing.com</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>Investing.com South Africa</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQNDZJUmNZQ3A3TUlvQ1pBZVdIdE9MdUJ5dnJHZXp6WjROVXRYSEpyWkJCR0xzcjVmM3NKTWs4ZnkwWXowTVdRVFp0MFN3VFRoNDVfMnFGbXdpcmhtdnNEUGN3eXFWd3RVelJ2SWs3ZWFzb1JEcDFpRVZZa0FGVHRIRTZ0d05OTVdrVjRRZ1JTaks?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPb05Rb1I5WWFsVnc5Q3d6OTlrbHVCQ0d3MEVEek9mWm5ZSmxWZFA3bHBwLVFES1g2Y1FzTkpvTzd6dF9rRFB0OWE5cjJPOVZmZWY5WDBoWGJncklSSFppUmZJcDhJWUd4TGY4VVFacWE2Q1VyaGtUQVd3aVMxXzNnaHpZS21ZRGZXcEZXMUF6b0VmUEtXYzFqMGZVbENhUVdFcW04UjFsOXJfaEpVeXhaTEdueU80UVpNS044TVI0VQ?oc=5</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>14-05-2026 15:52 UTC</t>
+          <t>15-05-2026 11:01 UTC</t>
         </is>
       </c>
     </row>
@@ -4459,22 +4459,22 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Is It Too Late To Consider Teva Pharmaceutical Industries (TEVA) After Its 3‑Year Rally?</t>
+          <t>Swiss Life Asset Management Ltd Lowers Position in Teva Pharmaceutical Industries Ltd. $TEVA</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>MarketBeat</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOeE1kZzE1bGtERmVnZVI2S0JPZUt4c2tXNXl2SVJqQlNsMFI5dnpOOGlCM21oRU1ZZ2p6OXppVHpwSU1zQWduU3FlZHJKYVhMVmpodGxPU3dtMHBPalRBQ1I3eW53T1RmSEtyVF9YUUNGTnROWldNX19Ta0lQZEJBaWpBSUNRM2tBLXdXcENTeGE1OW14Y0Q0ZkdnS0pxemJhWmxRLWxUckRSaTB3UDZ3TGRR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxONlc4QTE1Ym1DR3piNmRCdC14eVlsTUhXdDV3bkViMHdkcV9tbDR2RlJEdkhibGV6ZENfS2EzVE1oc0NxT3JYRHRUdXlsLXJTMWlDREtCSGliZ3BhdnI1aTFyazduYzlZeXJPSjE2T040MHpNVHoxcVJNeVptbzFaYjhHeC1zSmJscTQ2S1NhSjlmUFVWbktBemR4czJnSTBHdXJ6akhfcm0yYXFVZGpmU3FWdTBBUUNYTDFFb0tGR2NYTHA1WXhpOVpPeXFnQkQ0NXRjLWtTSnR1emNXSHQwS0RMbDU1dw?oc=5</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>15-05-2026 09:13 UTC</t>
+          <t>15-05-2026 09:16 UTC</t>
         </is>
       </c>
     </row>
@@ -4486,22 +4486,22 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Swiss Life Asset Management Ltd Lowers Position in Teva Pharmaceutical Industries Ltd. $TEVA</t>
+          <t>Teva Stock Is at Its Highest Level in Nearly a Decade. Here's Why It Could Soar Even More.</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>MarketBeat</t>
+          <t>The Motley Fool</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxONlc4QTE1Ym1DR3piNmRCdC14eVlsTUhXdDV3bkViMHdkcV9tbDR2RlJEdkhibGV6ZENfS2EzVE1oc0NxT3JYRHRUdXlsLXJTMWlDREtCSGliZ3BhdnI1aTFyazduYzlZeXJPSjE2T040MHpNVHoxcVJNeVptbzFaYjhHeC1zSmJscTQ2S1NhSjlmUFVWbktBemR4czJnSTBHdXJ6akhfcm0yYXFVZGpmU3FWdTBBUUNYTDFFb0tGR2NYTHA1WXhpOVpPeXFnQkQ0NXRjLWtTSnR1emNXSHQwS0RMbDU1dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNZmd5VTljVGtSVVJqMlR3VFFxQ2FWeER6MVN0U3ByVlVTbTZkbzJibFV6R0ZaZ1dWRmtLamJvX1VFb1VNM0ZHOFJzWl8yS1lyODBJOFNUcnhFNlQ5Z0U5NWZZa25pVDdpc1ZSNW9XeUs2Z2dhWk9UQVVOZlBYQm1Jazg4RUpBcUxiejFzLXQxay1XTzB5Y3RRNg?oc=5</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>15-05-2026 09:16 UTC</t>
+          <t>15-05-2026 06:00 UTC</t>
         </is>
       </c>
     </row>
@@ -4513,22 +4513,22 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Earnings call transcript: Teva Q1 2026 earnings beat forecasts By Investing.com</t>
+          <t>Teva Pharmaceutical Industries (NYSE: TEVA) reports proposed insider sales of ordinary shares</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Investing.com Canada</t>
+          <t>Stock Titan</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPbDlDaHJseUdqSEcyVTFRRHhxNVA0R0h6RkI1WHQ1WjlNMEpmRVBDM29YOHUxbE1GN1NTX0lJZE5BanZ2amZXLWFoazIyajVDS2NTU2ZQZUs4SDFqRGRjVS1WNnZxSlFvLWc5VnFjXzJLXzlkSDFIR005QUF5RnRyQi15Vk52Si15d2lxclVwamYyRFo2Yy1ERm1QaVZ5X1M0WEdORFd3TnZ1R3I4ZWF2UjRxUDVWSDY3R1hQcUJoOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPb0FYbWxZUEVkM1NSeUh4VV8wOVNiaGpCMTM1N0pGWDF0enF2VUVfV2o5c3hQRHUybmFHbnJvQXpWNEtUWmxGVTFSbDBEdXdVZVh2eW9HSFFaNDB1TFZpZUJGUzBBdUl2azdGakMwdUl4dktvaFcxaE40T0VzVm5PS3RMR29KZzVMWnlVN05FTzhpLV85SC1UOXlVU3o2UlFzZ0dlM053cFpqTEx2QTRaUg?oc=5</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>15-05-2026 10:46 UTC</t>
+          <t>14-05-2026 19:59 UTC</t>
         </is>
       </c>
     </row>
@@ -4545,17 +4545,17 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>The Motley Fool</t>
+          <t>AOL.com</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNZmd5VTljVGtSVVJqMlR3VFFxQ2FWeER6MVN0U3ByVlVTbTZkbzJibFV6R0ZaZ1dWRmtLamJvX1VFb1VNM0ZHOFJzWl8yS1lyODBJOFNUcnhFNlQ5Z0U5NWZZa25pVDdpc1ZSNW9XeUs2Z2dhWk9UQVVOZlBYQm1Jazg4RUpBcUxiejFzLXQxay1XTzB5Y3RRNg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPSkdUMnVsekUzN1pJQkcwWldjMXFyUDdmQ2ZxV1U3dVdYR3dPTzlVcFdDaEs2VUZlQzhEaUZyWkV5bjF0N3FOOFlNMFpjMHJGSGZ6cmFHQ2IzTWJBVnhIdnBQOFlhTU03Wk5FUWxWWTM1d1Qxb0Mtb2lRRW9VNmp2LQ?oc=5</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>15-05-2026 06:00 UTC</t>
+          <t>15-05-2026 05:20 UTC</t>
         </is>
       </c>
     </row>
@@ -4567,22 +4567,22 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Teva Pharmaceutical Industries (NYSE: TEVA) reports proposed insider sales of ordinary shares</t>
+          <t>Phoenix Financial Ltd. Sells 208,113 Shares of Teva Pharmaceutical Industries Ltd. $TEVA</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Stock Titan</t>
+          <t>MarketBeat</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPb0FYbWxZUEVkM1NSeUh4VV8wOVNiaGpCMTM1N0pGWDF0enF2VUVfV2o5c3hQRHUybmFHbnJvQXpWNEtUWmxGVTFSbDBEdXdVZVh2eW9HSFFaNDB1TFZpZUJGUzBBdUl2azdGakMwdUl4dktvaFcxaE40T0VzVm5PS3RMR29KZzVMWnlVN05FTzhpLV85SC1UOXlVU3o2UlFzZ0dlM053cFpqTEx2QTRaUg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxPYWxYZTJrX01tVXdTZnB0ZXV4UVZITnR3Wk1mRHpFdzBtUVR5eHJZYUxuVG40SXg3eDdjR1VmVDJSMGNIdHBPdjVSNnRDcTVtdjE3MkVZWEEtSFRRZ2F1RmhWaHRqcHRVNU1YbXo0RTE3STdqNjl1bFBCbHZ6R3RrTVZ3eUtWLWJ0d1ZjUzc4c1VVOG1ZLUx1TXVRMmtDS0U5N1JEbG9wMlhCbHViU3hrbEVKeV81X1EtVV93TFZMWE5JOVRzaUpnM2V6XzJpMExiYWxCMktaVzN6QTFLdlE?oc=5</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>14-05-2026 19:59 UTC</t>
+          <t>15-05-2026 10:52 UTC</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>AOL.com</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPSkdUMnVsekUzN1pJQkcwWldjMXFyUDdmQ2ZxV1U3dVdYR3dPTzlVcFdDaEs2VUZlQzhEaUZyWkV5bjF0N3FOOFlNMFpjMHJGSGZ6cmFHQ2IzTWJBVnhIdnBQOFlhTU03Wk5FUWxWWTM1d1Qxb0Mtb2lRRW9VNmp2LQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNUy1EbDlHOThJdGJWM3BIRkYzV1ZaRXdfR3pQTHV6YU1xMGhFSG9Dc0R1ZkFPSXdBVkE3OEMtYlYwdjgzd0kwVFJVMTU3VFNraVB6NXhMamtPeFQxb0JMTS1nZUx4RURSUERSWnI2NzVGU3hyOTMteS1fUE1WRk5BUFlQc2tPR1oxc21SSGxYM0dqUUZPOUJmSzFVdzE?oc=5</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -4621,22 +4621,22 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Teva Pharmaceutical Industries Ltd. $TEVA Shares Sold by AustralianSuper Pty Ltd</t>
+          <t>TEVA (NYSE) Form 144 lists ordinary shares for sale via Citigroup</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>MarketBeat</t>
+          <t>Stock Titan</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxNMmZJYlFBUWhJNlNkd2JaWVlFNklqUmQxejcyN0tBNXF6WmNaSk56bjlGY1FZdUM1dnhZNG9XNXhlOW5qWGp1SWk2V1NTYWpqLUduRmZIbzMxaTZLMjVIa1FLUjdITUIwMFBXZ09JM2xoYVZFaUdaWFQ5RHBQY2dXWjJHX2t6YkZLV2kzMU9hYlA2TkQ1MktyR2JGMS1aLURPMlh0VmRKbWVSbXRlNF9UTjdvRndXMV82OUc3SnhXRHg1OEVaVWVJQlJVLWRaV0RzOXBSR2pR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNYVZER2YzemVUeVVsTjVQVWN2WXhRc05hdUFmSHZDTnZuQ09xZnhXcDdYa0RoamlhYVd0cTdYelEzVWdMTU9KMF9UeDFiMWpZaUhMRkduWkRZcG91eVRjUXZKbGZfNUxVYU5QQ1dlRTlFSmVORmJFTmJoWXJWcl9fNlFrUmtTTjRsZTVvZm9XNWNSR0FJamVISHJlaFNuZHQ5Q1RJd0wwYzhkTzNyYVQ4ag?oc=5</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>15-05-2026 07:35 UTC</t>
+          <t>14-05-2026 20:02 UTC</t>
         </is>
       </c>
     </row>
@@ -4648,22 +4648,22 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>TEVA (NYSE) Form 144 lists ordinary shares for sale via Citigroup</t>
+          <t>Teva Pharmaceutical Industries Ltd. $TEVA Shares Sold by AustralianSuper Pty Ltd</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Stock Titan</t>
+          <t>MarketBeat</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNYVZER2YzemVUeVVsTjVQVWN2WXhRc05hdUFmSHZDTnZuQ09xZnhXcDdYa0RoamlhYVd0cTdYelEzVWdMTU9KMF9UeDFiMWpZaUhMRkduWkRZcG91eVRjUXZKbGZfNUxVYU5QQ1dlRTlFSmVORmJFTmJoWXJWcl9fNlFrUmtTTjRsZTVvZm9XNWNSR0FJamVISHJlaFNuZHQ5Q1RJd0wwYzhkTzNyYVQ4ag?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxNMmZJYlFBUWhJNlNkd2JaWVlFNklqUmQxejcyN0tBNXF6WmNaSk56bjlGY1FZdUM1dnhZNG9XNXhlOW5qWGp1SWk2V1NTYWpqLUduRmZIbzMxaTZLMjVIa1FLUjdITUIwMFBXZ09JM2xoYVZFaUdaWFQ5RHBQY2dXWjJHX2t6YkZLV2kzMU9hYlA2TkQ1MktyR2JGMS1aLURPMlh0VmRKbWVSbXRlNF9UTjdvRndXMV82OUc3SnhXRHg1OEVaVWVJQlJVLWRaV0RzOXBSR2pR?oc=5</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>14-05-2026 20:02 UTC</t>
+          <t>15-05-2026 07:35 UTC</t>
         </is>
       </c>
     </row>
@@ -4675,22 +4675,22 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Phoenix Financial Ltd. Sells 208,113 Shares of Teva Pharmaceutical Industries Ltd. $TEVA</t>
+          <t>Is Teva Just Looking Out for Itself</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>MarketBeat</t>
+          <t>Yahoo</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxPYWxYZTJrX01tVXdTZnB0ZXV4UVZITnR3Wk1mRHpFdzBtUVR5eHJZYUxuVG40SXg3eDdjR1VmVDJSMGNIdHBPdjVSNnRDcTVtdjE3MkVZWEEtSFRRZ2F1RmhWaHRqcHRVNU1YbXo0RTE3STdqNjl1bFBCbHZ6R3RrTVZ3eUtWLWJ0d1ZjUzc4c1VVOG1ZLUx1TXVRMmtDS0U5N1JEbG9wMlhCbHViU3hrbEVKeV81X1EtVV93TFZMWE5JOVRzaUpnM2V6XzJpMExiYWxCMktaVzN6QTFLdlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE5lM1Z3bUdUSjNQMkMyT1pWX3BHLXRzMG85aEJTVXNWWEE4MkpBOFBBdzFFLWc5WjUzXzk4bGVRekhGMl90cFMtUUNoc01IdGloNkk2MnBzZU5NenZLRmVlSzQ3d1VGY0Y4NkFMU01sTjdBZXFRQTFqNWhZMl9oZw?oc=5</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>15-05-2026 10:52 UTC</t>
+          <t>14-05-2026 23:15 UTC</t>
         </is>
       </c>
     </row>
@@ -4702,22 +4702,22 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Is Teva Just Looking Out for Itself</t>
+          <t>Escalate BDS pressure against these major Israeli companies that made the 1948 Nakba possible</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Yahoo</t>
+          <t>BDS Movement</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE5lM1Z3bUdUSjNQMkMyT1pWX3BHLXRzMG85aEJTVXNWWEE4MkpBOFBBdzFFLWc5WjUzXzk4bGVRekhGMl90cFMtUUNoc01IdGloNkk2MnBzZU5NenZLRmVlSzQ3d1VGY0Y4NkFMU01sTjdBZXFRQTFqNWhZMl9oZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOcVRSMmJqWGViSVN2VTgwdDJ2Zm1kcDhTcTQ5dlhIODJxQ2xYdnR1cjdSMUdoNV80dGt3SnR4NWxqenBoWTZ2bW9uRnRVNVpCSHFGbVZ4XzRfbDVPOE1yNWltVi0xTUUwSGo5VU4yQ0QwWXpEYkVwVlRfRm1Jb21nSEdFQ2dIUktpNDM5bUZB?oc=5</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>14-05-2026 23:15 UTC</t>
+          <t>15-05-2026 11:38 UTC</t>
         </is>
       </c>
     </row>
@@ -4729,22 +4729,22 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Mylan Epoprostenol Win Clarifies US Measurement Rules And Equivalents Limits</t>
+          <t>Former Ovid CEO Dr. Jeremy Levin’s rallying cry for biotech</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Citeline News &amp; Insights</t>
+          <t>Pharma Voice</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxPbHM4VWQtSndIMzVDaVlsc3BjdWdqTDFvaTdUMWFPQzhSYjdTdlEyUnNJSkt2WnprQVNhd1dPYWdMYXlUOV9xYnQ5Y2xyeHk0ZERUX3dvSEM4cG1YNTd2ejFkSDhhcEo2V000cGhCd0lWUmdWTVZZd0hYUjdkbUVtUWRlc2NrVDRiOG41UXZjaHp4TjYzTDQwbFF4dmdndzdxMkpoVUtJcWRDZS1vdlAxRWQ4U19aWGt6RW14cmt0cnhFUFYxQ2ZfbFdlQW9la3pMNUVYbUYydXJuMTNLV29mQVJydjJWUzJmdVNITElTSlFJVmhpOHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNSGx0VVdLQVItYzVVcXN6MHVEWGZ5MEZ6ZUdULUtObllDby12X3FQVUZlRFMwMDdEbnRCYTVTSDF2MzdYd1FOaFhDc0IwdWNWQXlCU1oyeE9sY3lIbEV6NGZtQzFmZnNJbmhpRjU0a1I3cGdmVi0tMTZCRkV3UEJIWGNwMzRhbnlSVFB5eQ?oc=5</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>14-05-2026 12:50 UTC</t>
+          <t>15-05-2026 12:55 UTC</t>
         </is>
       </c>
     </row>

--- a/news_results_raw.xlsx
+++ b/news_results_raw.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E106"/>
+  <dimension ref="A1:E98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,54 +485,54 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sandoz</t>
+          <t>Stada</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FDA approves first interchangeable biosimilars to Simponi and Simponi Aria</t>
+          <t>Voices of valor: Kisumu women rise through STADA’s support - Radio47</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>The Pharma Letter</t>
+          <t>Radio47 - Hapa Ndipo</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPdVVkX3pEaGJLOHRkd28xZkFOajBhQl9SM3piLVBUUWtsNktyQy1ZTi1zZzg1YjVycTc2cHl4dUVaSnZhbnhCbEN5amFlLWJoSktkelBjcTNnd1J6LXpZVS1aQnBjYjNna0hUYVJvdU9IM2ZqWWJSclU4Nmd3VW9iMklDekhWY0tmRTFhNDN1NUJONDJ3M0FGSTVmQXZwVnZSekFWdW90eEppNHQ2YjJJR2hna2IxdU4wdVVnZzVObGk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPbUpxUmY2bDV1UTlGQjc2WE52T3cyWjUyc3ZUdFNnRV81NndCYTIyd3NtS0VXck1hOC1DRHNNNXRQSXBNa0oxdVE1R0pHQ1ZxTGtpUXppT0s5VGVKLWZrSFp6bTN0SW04YW1tR2ZWRTM3d0thMThkdFpaUnY3LVZ0ejYySmVEVVZ0bFpleUE0b0U5Z0hvcmNTalU0MA?oc=5</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>16-05-2026 13:54 UTC</t>
+          <t>17-05-2026 14:43 UTC</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sandoz</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>From Tongi to Canada: Nevien Life Science marks export milestone in global pharmaceutical supply chain</t>
+          <t>NIPER Hyderabad, Boehringer Ingelheim tie up to advance pharmaceutical research</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>The Business Standard</t>
+          <t>Dailyhunt</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOdDFwOWpMQkdNMEt1ZnQ0NXlFeUttVTNBM19JeW5BNnVoNTNySzY3elUtZ1QweXdJeEVRak5qMjUtMTQ0ak5BQ2xwM3NJRFJzamNhM09JSnI2bFRlSlFoVHpZWkhsQmFEaXJLS2NIdHhWZ0NBSFFzODU5VlI2dWthTnlrMDE2Y3B1MjZMQ1RTclhEVXYtbXZXWE0yQVRXMGlSRTFvT212QlFfeW83aUFwWmNRT0JIVDQ0RkHSAb8BQVVfeXFMT1d4QU9QMVBkbHR4aThxd0hBQ3BpeHdiZHNoTnZvNXFDa1ZZUW13Wmw0X0FwMm8wZWJYdENmQ2E3MlUzLXNUaWhoSVdvRG9weXA5LThCSS1maEFBNXJXbVZzaVlTdnhpOTUxbXNxZFFPU0xmY1lIYWtteUZ4MHZyVWRQYjBUN1EwbnFRTkJXc0Z6a0loN241TnZ3OTVZekczS3ctNkFIbENtckFwOGkyakNUWkdkc0pqYzJnV3JNbDQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigJBVV95cUxQTFpHTlQtZjNEM2d3VmxVam5Gbk5SWEphSGFnRU9CdVdhZHZvVm9mekl5bEIyVlc5c2xfLVAzUnBFZEw2ZmZ3TEVQMGw2S3RiNWpaTEV2VGNfUWZ6YkVQU0dkc0liZDZ6bTF2eTJKNGl6ajE1TTZ0RGhNUFM4VUdqbExCWEZRU0VELWJsWE93OFJsXzdER3lQTy1vWUJacmpsZnpqdUNmTDZDd1pDTFRreDhzNXY0SXp2VVJoTlVyR1BzS1B4dnEtMEsxZkVjNDJrWEZQaHZaSU9BblpMWVYwZjV0bW9XR2ZwSlpZV2UxTTJnYWJQN09XVENhQWsxTHQ0VFVNaXBDRW1OZw?oc=5</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>16-05-2026 13:04 UTC</t>
+          <t>17-05-2026 05:00 UTC</t>
         </is>
       </c>
     </row>
@@ -544,22 +544,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NIPER Hyderabad, Boehringer Ingelheim tie up to advance pharmaceutical research</t>
+          <t>AI in Life Science Market worth $69.34 billion by 2031</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dailyhunt</t>
+          <t>MarketsandMarkets</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigJBVV95cUxQTFpHTlQtZjNEM2d3VmxVam5Gbk5SWEphSGFnRU9CdVdhZHZvVm9mekl5bEIyVlc5c2xfLVAzUnBFZEw2ZmZ3TEVQMGw2S3RiNWpaTEV2VGNfUWZ6YkVQU0dkc0liZDZ6bTF2eTJKNGl6ajE1TTZ0RGhNUFM4VUdqbExCWEZRU0VELWJsWE93OFJsXzdER3lQTy1vWUJacmpsZnpqdUNmTDZDd1pDTFRreDhzNXY0SXp2VVJoTlVyR1BzS1B4dnEtMEsxZkVjNDJrWEZQaHZaSU9BblpMWVYwZjV0bW9XR2ZwSlpZV2UxTTJnYWJQN09XVENhQWsxTHQ0VFVNaXBDRW1OZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE5WQ0x0NUlaUldUU1VucmNKS1plazRoZVNsZ1pjU3Rxd0szMEpIWXZ4RF84bjJGVXdmMHMxYWxaUlg4MFZDaHdnNjhza0NPRTJQRi05UzUySVZUT0NaQ0VzMDRUR011ek5fZGRURVJ0cHNNSnR6aDFTc0x3?oc=5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>17-05-2026 05:00 UTC</t>
+          <t>16-05-2026 18:19 UTC</t>
         </is>
       </c>
     </row>
@@ -571,22 +571,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim India, NIPER Collab to Expand Research Across Pharma Hubs</t>
+          <t>Drugs And Pharmaceuticals Market Growth Outlook to 2035: Demand Accelerates Amid Aging Populations and Biologic Innovation - News and Statistics</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Deccan Chronicle</t>
+          <t>IndexBox</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxNM3p5d1VyQVlkQkJpNU5ZeU45NVozUjFXYUs3MlFjYUVxdWFiMHpYeW11R1EwOXJuVU56aG15ZkJISU1UNDAzNm9uVWxMWElFX1M1NEJUVmRqSGtVT29HX0pBNWExUEhydVE4Um9OQ2J3NGtldGpOUVVZYTczcnJodFlMQ290QjltblBsZEdUek1HTDFNVUxkTmRjWVYyWlFBOGRydjh2d2FwdWd1Ry01WHpwQkpRY2RPeXlra2l6NURWWlZZMGlLQVJRVEg4RzdoT09fUmVjX1Y2NWlP0gHcAUFVX3lxTE0zenl3VXJBWWRCQmk1Tll5Tjk1WjNSMVdhSzcyUWNhRXF1YWIwelh5bXVHUTA5cm5VTnpobXlmQkhJTVQ0MDM2b25VbExYSUVfUzU0QlRWZGpIa1VPb0dfSkE1YTFQSHJ1UThSb05DYnc0a2V0ak5RVVlhNzNycmh0WUxDb3RCOW1uUGxkR1R6TUdMMU1VTGROZGNZVjJaUUE4ZHJ2OHZ3YXB1Z3VHLTVYenBCSlFjZE95eWtraXo1RFZaVlkwaUtBUlFUSDhHN2hPT19SZWNfVjY1aU8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxPVHI0cjdoYjYzTXltTzFYVWpzcjI0enZrVzhhT21EZDFqR1o5V0JkanN3UGJoRHRrXzA0bUZxV1BfemRGWEc1V1N0TWxpNU1pMmh1b3VaZFVWc1dsYWNIa1lXY3ctYzVDWVBPWU1CYzNac0t2NlNrNWpwLU05dzdJNjVJUGtZVGNYYkYzWmRQaUgteHpXSExNWWFZakhOOFBmNElIeU1jNVZldVhoU3ZBR2x6WnF3MUU1NTVqelpVdWJhbjRpdnFUTHlKZXFWTldPaUVyVTFKbkhJY3JnTXpPcFNweUJEdVRD?oc=5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>16-05-2026 09:27 UTC</t>
+          <t>16-05-2026 16:31 UTC</t>
         </is>
       </c>
     </row>
@@ -598,22 +598,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Youngest Billionaires</t>
+          <t>Pipeline Data and Quarterly Report: BioNTech’s Next Two Hurdles After Shareholder Backing</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Voronoi by Visual Capitalist</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTFBwSVQtdzNTelc3U05ZOGJoTkgzNF9aVXhkT2VyLTMyWTNXbzRQOVdnMTUwUFE5dC16MG84QWYwbnpxbko4VmJZRzNuWGN4MFJWR0hJQUxaWDZhTkttbzcwT1dmcU1wUWxoWFhyag?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNVHg2V3dYYzYzM0NPbDl1dnZVM01QR0FPODlqYWxXZ0tCeGlueGNUX1hzUHBKUERad0FuTnFPU21ZUk5HcHdDWFJRbWdUbkFQSDk4M0ZoVGxzUG1XRUY0bmRNSHRuX0lCWFN3R0FYMllkTEJRcDNoUUt5QXhIRlFFVGdfTVlwN1lteW1OWXBnc1dxMGZmRGJ0ZWNFUFhSS01JQy1Sa29aZmlaREJrSjB1ci1wdkpzOGVIZzkzM3RiVGhRdGtNS0E?oc=5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>16-05-2026 09:42 UTC</t>
+          <t>17-05-2026 00:42 UTC</t>
         </is>
       </c>
     </row>
@@ -625,76 +625,76 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MakeMyTrip Unveils Myra 2.0: End-to-End Conversational Travel Booking Assistant</t>
+          <t>Killer counterfeits: the flea treatments that could send you rushing to the vet</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Deccan Chronicle</t>
+          <t>The Guardian</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxPeDNaekxKc3Rvczl1YUxCU1BYSU9kZmJ2bG4tWndfbWkzb0dxNUM4eHhaU1JVSW9wT0x0T25LRFFuQ1otZnB0eUp0SVUxVTZpOG91V2ZTdzgybjg4WTBOang4VTVYeVZVYy1jUXZjeGpFNnlvZTRrV2d4TGNqUFZtX1pINHZMMlBNRkVQa1M5bGdiZ08wTmpJZVNZTkkySTJUenZYUTc2Y0hOck5OMXc3ZWZSOHBnMk5hTGJhNS1hOTNLRFB0bXd4RU9jeXZRMlUxUHh1OEdJTHpaWUpi0gHcAUFVX3lxTE94M1p6TEpzdG9zOXVhTEJTUFhJT2RmYnZsbi1ad19taTNvR3E1Qzh4eFpTUlVJb3BPTHRPbktEUW5DWi1mcHR5SnRJVTFVNmk4b3VXZlN3ODJuODhZME5qeDhVNVh5VlVjLWNRdmN4akU2eW9lNGtXZ3hMY2pQVm1fWkg0dkwyUE1GRVBrUzlsZ2JnTzBOakllU1lOSTJJMlR6dlhRNzZjSE5yTk4xdzdlZlI4cGcyTmFMYmE1LWE5M0tEUHRtd3hFT2N5dlEyVTFQeHU4R0lMelpZSmI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNNUVLNUVsYzdlYy1CLTJ1SWFTejFjT2ZJaXowNGJtMG96dk5TbVdmcGIxbWhhMGZsS3p4TkZTd24xMDJwUzFtUloxYUE0QV9kNDdRVS0yQXBVQkdaMzFnN1J1ZTdxd3YtVURHOGVyUHBmcjRLTmV0eGpwSUZVM0VSVmt3T1E0YnJXM3EwZ3BvY1JLODgzdW1XZHA0ZnZtM1Vpd1VPdGZGUTNVYjdGMFQ2ZQ?oc=5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>16-05-2026 09:34 UTC</t>
+          <t>17-05-2026 06:01 UTC</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bangladesh economy remains fragile in Q1 2026 over high inflation: Report</t>
+          <t>Standing Bone Strong: Introducing a New Awareness Symbol for Osteoporosis</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>The Hans India</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQc0pGTEhHOC1ycGZOb3BQcVNuazV6Q2ZXYjFsU1RrUmdiTUp5U2RzOTFCUHhCTFJzRDIwaURsemtEQ0FVU2Q2S3JHTWVZWEtIMlZQWGVJOFRGSFB0N2tUV1NSSUhleUlrZU8weFNEeGtrLUg4VVdqVzFOTDhhRnF3UDVYZ2V5NGI3Rk53Y3pFNUFkOUVHODF2VEpfbTRUVmxqcV9ZVmxnVFZQMm5LMXVCS1BUckZsNWQ4UVNzWGNuY9IBvwFBVV95cUxQc0pGTEhHOC1ycGZOb3BQcVNuazV6Q2ZXYjFsU1RrUmdiTUp5U2RzOTFCUHhCTFJzRDIwaURsemtEQ0FVU2Q2S3JHTWVZWEtIMlZQWGVJOFRGSFB0N2tUV1NSSUhleUlrZU8weFNEeGtrLUg4VVdqVzFOTDhhRnF3UDVYZ2V5NGI3Rk53Y3pFNUFkOUVHODF2VEpfbTRUVmxqcV9ZVmxnVFZQMm5LMXVCS1BUckZsNWQ4UVNzWGNuYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQRDRCa2dnZkdVYlZoYzd0OXpJYy1NV3ZFalNSdnZQdWk0bDRXMUtWWS1hMUtKU1lob05hNFp5U3pSN3FLRWRoUkZLM0xvWnNQdmp3NTRiMWc4cFBOdDFSTXkyQ2FKVkVZVUtDOFRsU1RVOVN0UXNEd0RaMEM5cGIwRTNSUTljeWRDdHhocVMxZDJzRUFQQ09QNjVfbnlhaVZiNjZXNHpSalNMcmM3cTJj?oc=5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>16-05-2026 12:57 UTC</t>
+          <t>17-05-2026 04:56 UTC</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>India deepens space‑tech ties with Italy, announces new collaborations</t>
+          <t>Japan Flags 20 Deaths, Liver Injury Risk in Amgen's Rare Disease Drug Tavneos</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>The Hans India</t>
+          <t>Medical Dialogues</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQWTRZTDJ2TVFJemJ3aUM4Njd0SWtjSXRPTzNxM3pYMkxuQ2lYSnBxcHRDbURfLWZYQlhhVzlnOTZWN1ZuRnl4bWFJLTUwUFVDUXFKWFFaOE5KMm5IeGh0RjlQekpBQVhDT1JCVElYU1NzbDJkX1RUSGJiWno5MkVZaC0tUkF2dExQZHdkQ0N5R1BBbjN4WE9lN29maEtrYzE0THNEa2NLYU12U2U1TVpSenZFNkhPUXg3OVHSAboBQVVfeXFMUFk0WUwydk1RSXpid2lDODY3dElrY0l0T08zcTN6WDJMbkNpWEpwcXB0Q21EXy1mWEJYYVc5Zzk2VjdWbkZ5eG1hSS01MFBVQ1FxSlhRWjhOSjJuSHhodEY5UHpKQUFYQ09SQlRJWFNTc2wyZF9UVEhiYlp6OTJFWWgtLVJBdnRMUGR3ZENDeUdQQW4zeFhPZTdvZmhLa2MxNExzRGtjS2FNdlNlNU1aUnp2RTZIT1F4NzlR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPLXIwY2JKZ3RwRmZvNXJrajgtWHhaaEFWaW1NaTVPemx3dnFNdVVES014bWtKTVdySHBXVWVPRHF6Um5WQlNVUzlrU1lHVmZqbFNSU2NzVE1OQVpDYmRsbUMtWEVKdDVyS0JEc2pZRW12QVg4X0M5MUctMmI5NXJKMHJNYU5EZWF0Zi10aW84Y0xuRzBIcXRCLS1EYlJIbGUtcWM3b05iWUJaSjMyTDZUc0dvRklBY3lmTGFrbk56dkdYZ2lSOTFRQmI5RdIB0AFBVV95cUxQYUhJaGxfQUN2cnFIeFVQRXV1aDZ4STdWcWdka0hlUGRRMllmM1RRNUVzbXl2bEtxUVVXLXF1QmUycl9qSUI3X0VkanVNd1hOblV1Rk4yaXltVXFkU01rMllhOUlnZmZVZ1FuOTc4TGJDWE9WX0VNcWlHRms4UEV3M29USFQ3akl4QjhnLTVkY1hieU1KOHpsbkZBdXROMXdnYkNodjZyWEMxU3dPOXhJVHJ5MEx4YmdCYzBpbXdnU3cyb2tlT1dlb29FLTB5SEVQ?oc=5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>16-05-2026 13:16 UTC</t>
+          <t>16-05-2026 16:22 UTC</t>
         </is>
       </c>
     </row>
@@ -706,22 +706,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Standing Bone Strong: Introducing a New Awareness Symbol for Osteoporosis</t>
+          <t>Leuthold Group LLC Buys 4,396 Shares of Amgen Inc. $AMGN</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>MarketBeat</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQRDRCa2dnZkdVYlZoYzd0OXpJYy1NV3ZFalNSdnZQdWk0bDRXMUtWWS1hMUtKU1lob05hNFp5U3pSN3FLRWRoUkZLM0xvWnNQdmp3NTRiMWc4cFBOdDFSTXkyQ2FKVkVZVUtDOFRsU1RVOVN0UXNEd0RaMEM5cGIwRTNSUTljeWRDdHhocVMxZDJzRUFQQ09QNjVfbnlhaVZiNjZXNHpSalNMcmM3cTJj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNaUptYVNLS2w2cFJaMW91YnpTeS1veVlpelhLNnBGNkNyV1ZxWnlqNGFIRjlDdUtwUTRWa1FORVZYOUUxd0tnQmdNVFNONnZ5bUE4aWllelc0alF3SUhxbWhacWtJVXNfOFF5WFI0aWJLWmtXNE5MTWZwS2tVUkJXQUNWN29IQXNfNFloQ0Q4UDB5dUJ2eHZYNnhoNlJwcC0yQ3pzNXNsVk5EVF9xcEpBSEd3V3U?oc=5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>17-05-2026 04:56 UTC</t>
+          <t>17-05-2026 11:11 UTC</t>
         </is>
       </c>
     </row>
@@ -733,22 +733,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Japan Flags 20 Deaths, Liver Injury Risk in Amgen's Rare Disease Drug Tavneos</t>
+          <t>Amgen Inc stock (US0311621009): lungs cancer setback meets steady biotech cash flow</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Medical Dialogues</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPLXIwY2JKZ3RwRmZvNXJrajgtWHhaaEFWaW1NaTVPemx3dnFNdVVES014bWtKTVdySHBXVWVPRHF6Um5WQlNVUzlrU1lHVmZqbFNSU2NzVE1OQVpDYmRsbUMtWEVKdDVyS0JEc2pZRW12QVg4X0M5MUctMmI5NXJKMHJNYU5EZWF0Zi10aW84Y0xuRzBIcXRCLS1EYlJIbGUtcWM3b05iWUJaSjMyTDZUc0dvRklBY3lmTGFrbk56dkdYZ2lSOTFRQmI5RdIB0AFBVV95cUxQYUhJaGxfQUN2cnFIeFVQRXV1aDZ4STdWcWdka0hlUGRRMllmM1RRNUVzbXl2bEtxUVVXLXF1QmUycl9qSUI3X0VkanVNd1hOblV1Rk4yaXltVXFkU01rMllhOUlnZmZVZ1FuOTc4TGJDWE9WX0VNcWlHRms4UEV3M29USFQ3akl4QjhnLTVkY1hieU1KOHpsbkZBdXROMXdnYkNodjZyWEMxU3dPOXhJVHJ5MEx4YmdCYzBpbXdnU3cyb2tlT1dlb29FLTB5SEVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxONXBWTEJSeV9VenBoWVVkT3FheC1zZDRFTjhlVWdPQTdaVlNYeDc4UmlxNUVaYXRjelVpd2lTRUxBY0hZcE9pVDFVcFhRTUVvbjFvLWdrX0NvVlZhVGRVY0FQS0lUU1hUS3NTVkcxcU9CMzNuNG1aUDh6VlJVcTBsanR0ZWkxWURlb0otTnFJZnY0WDNCdGJ1dXBiOGh4N1FoMGl3bDBtVUVudHl5ZjhHZ0JfSkdfZ3BQM19iVDlkTGJhbHhNOC1BMw?oc=5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>16-05-2026 16:22 UTC</t>
+          <t>16-05-2026 20:34 UTC</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Amgen Inc stock (US0311621009): lungs cancer setback meets steady biotech cash flow</t>
+          <t>Amgen (AMGN) Faces Scrutiny After Deaths Linked to Tavneos Thera</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>GuruFocus</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxONXBWTEJSeV9VenBoWVVkT3FheC1zZDRFTjhlVWdPQTdaVlNYeDc4UmlxNUVaYXRjelVpd2lTRUxBY0hZcE9pVDFVcFhRTUVvbjFvLWdrX0NvVlZhVGRVY0FQS0lUU1hUS3NTVkcxcU9CMzNuNG1aUDh6VlJVcTBsanR0ZWkxWURlb0otTnFJZnY0WDNCdGJ1dXBiOGh4N1FoMGl3bDBtVUVudHl5ZjhHZ0JfSkdfZ3BQM19iVDlkTGJhbHhNOC1BMw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxPc0RSY0VlbUgxNXh3T1ROM1d4NGxzR3I3dmtPWHRHdmc4UVBlVUpSRXlmMWpFRzVhM2ZLQ3AzM1RoRzJwQWoxUVlWT0RYcUxISGl2cmZhajNTdmpxaTlMbkFnQ3VZQm9WS01kY0FqVDdjUHg1VXB0Zk9WRzZRaWVzZHJVeEJ1UGI5bUtWNC1XZl9XVDk3bjQybUk0MFlsU2UtbUNPT2tHdmRRSXVUVTBtWnpub2gxT0J5cXFQY1NXSUJfbGZMazFpc2lTcC1pM2ZwQjdFeDllWDhPekk?oc=5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>16-05-2026 20:34 UTC</t>
+          <t>16-05-2026 22:18 UTC</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Amgen Inc. $AMGN Shares Purchased by Canada Post Corp Registered Pension Plan</t>
+          <t>L &amp; S Advisors Inc Takes Position in Amgen Inc. $AMGN</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -797,12 +797,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPVXZvZXFhVHZiYlRHcXZabE9iTWRucEVEVkxKZHp5aHZJSGQ2REdjTDRvYVBMM2VSMjF0NHlDaHlaRVJnbGdaNHp0WHJXR1c3aXZuUEJrVDViU2tZUVlJMGNENG5jN3RvcDdnN1NiTVNpRmxYRlZfUlEwZ3prVll2MGM4OFlBdFlqWTFiVmNjZ3pnVnkxa28tdXI4eDFfVS1CcWY5RllKYkhzYXFzZlJuTnRUazh3RTIzZ0t5YXNZU2l1LVU3NWxuLUp0TEV1azlnbUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQbG95NzlpS0hublNGRXg5bkZzbVBtd01JYTFEOVFGNHJ3UmtwejhrcU5iRnRRWGVNWEpOU3NKS3hqdEs1a0Fxa1B1WEVTVkVNWlFRSWM4clBndDAxS3A5X3dkUjZYSXE5a3BqMUd6N05rWWdSTVQyLTdialdvMGN3a2pVNms2U0pDQmQ4clNsRXZDdUg3QTVZdjQ0WFZiNWRFS3hzVTZGT25HNGNhMUk0?oc=5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>17-05-2026 08:34 UTC</t>
+          <t>17-05-2026 10:47 UTC</t>
         </is>
       </c>
     </row>
@@ -814,22 +814,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Amgen (AMGN) Faces Scrutiny After Deaths Linked to Tavneos Thera</t>
+          <t>iA Global Asset Management Inc. Raises Position in Amgen Inc. $AMGN</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GuruFocus</t>
+          <t>MarketBeat</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNTjZxTDAzZmdzdzhtTHVXampnUlRHcWxxUlNuR0U3ZVd5WWRwNVBNYW9xSE9mODFCSXRJT19pbENacUtjMUNfZ1d5bVRTTFZxc1FmQXRhQm5WYVhpdllGc1ZqbmRZY01vT1BDb1Z6eHJCbVhUS2FjUkltZXQ4TzNubC1XRWF5SWNCT09wcWRIdEhEM0tJT3p4SmsxOXBLR1dyYzZ6MXdHSHVIWWtXaHMtZG9uckZtUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNRlFsMDVQeVRmd2lSclZjMjBuamVpZkc5M1BrcHBOeWFobUdGQWJzY2U3LVZkZGVQQUZmUkVPa18zYTZRd3ZxcG5adjlZVkhPVjBnSG9JRU9DU3dxU3hNSVVJVEFPMlRzQ3FtSGxQajdwZ2xsS2dRQ21PeXJJN1Y4NXJnMFgxa2VYU2JwRk0wejlGQ0dkZUl1TjlrUHZFcUtNTVNNMEFpejczVlRVMVNlOGZfTmVtNlZmaWRoR3R6RFJJNUU?oc=5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>16-05-2026 20:28 UTC</t>
+          <t>17-05-2026 10:35 UTC</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Amgen’s Tavneos linked to 20 deaths in Japan (AMGN:NASDAQ)</t>
+          <t>Amgen Inc. $AMGN Shares Sold by WealthPlan Investment Management LLC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Seeking Alpha</t>
+          <t>MarketBeat</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE51My1heFJLbVllYUxocDhxaC1PUWZSb3dRNmNBQmh3Y0k2U3lwQTNOZmlxSFhkOXVNYmpyem4ycXp4b2o4aFpNa3JfYlBVNm82dktwSHRicEZpQUo0M09uSmpoemVJSDFhSkcxelFndjBqMFA2MmNFN0NCQWJCbUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNOXhqTDVHOXZpTVRfX3ZxWnRrazUwcC1WaVZNUUdrcGVfQ0Z5dGRBV0lmOWlGX1RTWENrWnV2MVRGNXJMNEg0bzlLZHR6R0NzblEtV3BiVnI2X0ZKc25zNkowRXk3ZmRYY1lYNEdnX29NMVdmWlBXWURNdXNGR3M4ZG5NQXNpb2pLTmpwUnAwWXBMSzZsV0JmWWFqbW9wd2J6b25mWFpndzRkTXNyVjNuSGx2T0t1cWNCSElIUm94dl9nUWluckE?oc=5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>16-05-2026 12:23 UTC</t>
+          <t>17-05-2026 11:33 UTC</t>
         </is>
       </c>
     </row>
@@ -868,22 +868,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Scientific Approach to Obesity</t>
+          <t>STF Management LP Sells 5,198 Shares of Amgen Inc. $AMGN</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>MarketBeat</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE54Zm1kUk9Ldmp3Vk1yTUFjT0lKTkxtSWx5bHVZb2xWd1ZSSTZjc2E0emRWc251cG9pWE5zdm51eHVhNkI3bGFJSjJ3eDVPWTY2ZGpkWmhlMXhOSGVLRUhBN0JZLW4wN1ZSTDB3Uw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPRmFGUEplWWNyU2FnUEZxZ3gzVmZTOWZlR3g5U1JkTkVRRFZOMWdTdmdiZ2tDbl9sb01RcVJFanRQcVhadHUxeWJGYm05TVdPTTZhMkdiYi1GQ3NmQkJTYW9RV1FqQV82S3NyNHNCSi1oQ3pVLS04TmlLRDJPczYxbmQyNmJUbU16R1BLT0FhVE1ZM1JlX0ZVM05HaGZlUzA3YWJMaWlZVDAtX0RrdGd4cENldDE?oc=5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>16-05-2026 10:27 UTC</t>
+          <t>17-05-2026 10:31 UTC</t>
         </is>
       </c>
     </row>
@@ -895,49 +895,49 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Amgen Inc. stock (US0311621009): focus on latest earnings and drug pipeline developments</t>
+          <t>Amgen Inc. $AMGN Shares Purchased by Canada Post Corp Registered Pension Plan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>MarketBeat</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQVmVydDY1NjlFOFVnZGZ3eW5kXzFXNDhodWhIMmdwNjdxa2dRZGtGNlFJX0JWSDRJdkJhMmh1alhIcEVfaDNnMU1Nd1QzdklmQlNhY3VmU3BIcEZFNVV2dGpMaFlickRVcWJMMlJsby1TV2xkSHNyNHpFdlZMaHo1b1JpZm1sNVE5NklsQ0ZkQ2Q2TTF6Uko1blVXU1d2RUplMGI4eFIwRE9wVktJQk8yVElYQjFWMk1ibXpSY1Rn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPVXZvZXFhVHZiYlRHcXZabE9iTWRucEVEVkxKZHp5aHZJSGQ2REdjTDRvYVBMM2VSMjF0NHlDaHlaRVJnbGdaNHp0WHJXR1c3aXZuUEJrVDViU2tZUVlJMGNENG5jN3RvcDdnN1NiTVNpRmxYRlZfUlEwZ3prVll2MGM4OFlBdFlqWTFiVmNjZ3pnVnkxa28tdXI4eDFfVS1CcWY5RllKYkhzYXFzZlJuTnRUazh3RTIzZ0t5YXNZU2l1LVU3NWxuLUp0TEV1azlnbUE?oc=5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>16-05-2026 13:33 UTC</t>
+          <t>17-05-2026 08:34 UTC</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Stephens Inc. AR Grows Stock Position in Amgen Inc. $AMGN</t>
+          <t>SCPI set for delisting after 13 years under suspension</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MarketBeat</t>
+          <t>IDNFinancials</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPNUxYQ0ludlF6NElxWXl4WFZlLWFnTmUtQXVvRlV2Q2JTcWs0Zm43TDVEZWk0S21sdWQ2Mng1Tng4OUo3RU11cmFvZU1WTDZvMWYxQVBBMjRNWktpa3pyWEl2VXhxQUcteFVQb1YzZlZMZ05uWnNZMzczV1d3UmUweDZCbzFOUndKSEtfY3dhVFZTNURDYWlMclBaUVB3M3lRc0ZmNVFxS3V2VmdTRUpuLUtkSWNqQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNRWZnV1RhSzN5WnRPdThidl9wdF9HTzBqYWwxUnM2NEt2cHRRWE5JeFhUWEhSRzhhb0g1bi1oYUxlTDNadmFjcmNNWVA4bUVqS3doZEM1TjVzZThEUGtham5pamE0dG4yNkRUVVJGZ1RrRnk3cV9NWnJtXzd6VHlZbUxMa2syYVZLelZRenJ4UXpZRU9HenFxOHJVVQ?oc=5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>16-05-2026 10:38 UTC</t>
+          <t>16-05-2026 15:20 UTC</t>
         </is>
       </c>
     </row>
@@ -949,49 +949,49 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SCPI set for delisting after 13 years under suspension</t>
+          <t>Organon to Present New Research on Access and Value at ISPOR 2026</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>IDNFinancials</t>
+          <t>The National Law Review</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNRWZnV1RhSzN5WnRPdThidl9wdF9HTzBqYWwxUnM2NEt2cHRRWE5JeFhUWEhSRzhhb0g1bi1oYUxlTDNadmFjcmNNWVA4bUVqS3doZEM1TjVzZThEUGtham5pamE0dG4yNkRUVVJGZ1RrRnk3cV9NWnJtXzd6VHlZbUxMa2syYVZLelZRenJ4UXpZRU9HenFxOHJVVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNaThuWmJQYUZiTnZNeE5UU2xFZHUwZ1BiVDNBX3FkSXlUWFcyQ1ZST2xJcTJYSWZQUmItb3hxazA4NmF6QTlQTXlOcmt2X2tPaTZqT0dlNy1DRzVXelhfWS1VR2MtV2R2WnMtdkFvZ2NKdzZmeVRnQ2xaYTYwM2hnaUExcktqSGd3OWk3Y3U1dENpM0ZvWC13Z0hzZ0E?oc=5</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>16-05-2026 15:20 UTC</t>
+          <t>16-05-2026 18:05 UTC</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Record $20.5B US Investment from India Driven by Pharma Deals</t>
+          <t>This new jewellery label boasts motifs rooted in Tamil landscapes</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Whalesbook</t>
+          <t>Indulgexpress</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxNTEJjYmJlT0drNkdaaHZpdGJSWXRCY3dJeGIydTZ6WnpnM09nSEk2MU43VWYwRVdBMm9LZ2tobWVLOVE2bER0U2V3WnRrS3ZfaTdlMXdRS1NTQzJwOUo1aTZkS1BCRXlDWVY0UU56OWR0RzJ2TXJhb2hZQmhRdGpJSDZhU2ozVmV4NVJQc3owVkhObEtGbFhlNTA1N3B4dHlaeWFFb18wY1FYUjBXMEwtd2pGLXhjZHAyX25tMjRVM1d5cVFfdHM2N3dNRGJqb21CeDNiWDc2STBGVklzTkZncmNCRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxOR3NrSDBhTUwxeVRRZGV4YjJ2MEpVWkdWZkNucWxHNHd5SGRlR3lSblctemZieWxkRHdOZVpEc0hCUlhOSUtqdVhZb3k0TlROMTRobHBpMHR0SlJyRjI1MkltbG5fWW9iZkpKUEhYOTc5dUlROWdTbXJJSDhsX1lxMVc5MjA4UHBVc2pWSjBJU2MyRno4QUNHanBCX01BU1M3NDFWUDVSeHplRlg0WlFnRDRCMDNYVmdmUUs0dWRhV282c1BjREdmNE9KaE4zblVLaTFndtIB1AFBVV95cUxOR3NrSDBhTUwxeVRRZGV4YjJ2MEpVWkdWZkNucWxHNHd5SGRlR3lSblctemZieWxkRHdOZVpEc0hCUlhOSUtqdVhZb3k0TlROMTRobHBpMHR0SlJyRjI1MkltbG5fWW9iZkpKUEhYOTc5dUlROWdTbXJJSDhsX1lxMVc5MjA4UHBVc2pWSjBJU2MyRno4QUNHanBCX01BU1M3NDFWUDVSeHplRlg0WlFnRDRCMDNYVmdmUUs0dWRhV282c1BjREdmNE9KaE4zblVLaTFndg?oc=5</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>16-05-2026 10:13 UTC</t>
+          <t>17-05-2026 11:54 UTC</t>
         </is>
       </c>
     </row>
@@ -1003,22 +1003,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The ‘Perfect’ Rose I Wish I'd Never Planted</t>
+          <t>Drone strike targets UAE’s Barakah nuke plant complex, triggers electrical generator fire</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Southern Living</t>
+          <t>Rising Kashmir</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE1oeE8xNDFpUTdOZE5tS2ZHc1FGSEhIV1VKUU1fWHJwRDdubXo4bWpfMW0wTEtTcmJrN25WVUJSUmhzM1ZhWDctS2xBYUF1YmFodkIybDljeE83STZHVEtFQnlhTXRWZGRyT2ZZSA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPQVZhbGhaMENuNERocV9QRHg2ZVBGUlRCMFNNRS15dmFBUS1vWjNQMUd6OUdOaGpmdjVKMzZieUtVSnVhZjNNb3Q1WG56RGUxdTVvNGlRdnJadVlPRmY1SXp0VG5Fc3pZcWJoaWpqSENqNHlGemEzZ3huZFIxZWlHaVlVbHoxcnl1OG5GT2tkekVtbmdZTWZqVFRJTll5akpIbmxDeVZMeGxULWl1ZDZuYXgyRnI?oc=5</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>17-05-2026 01:43 UTC</t>
+          <t>16-05-2026 23:00 UTC</t>
         </is>
       </c>
     </row>
@@ -1030,22 +1030,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Emcure Pharma Plant Faces FDA Form 483 Amid Strong Results</t>
+          <t>Turkey Artificial Plant - Market Analysis, Forecast, Size, Trends and Insights</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Whalesbook</t>
+          <t>IndexBox</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNMDJpUFdYLVl5ODZSRjNOdklERzFqTEd3U3FiQWVVakJUVVI1TGIxS09pM2JhUHMtZ3RBVVJzd0ZGb0ZXZnoyZzYwVnl1VzRBa3gtVUZWZE5GamdOSTlueDVxdXdBV1d2aW5QQzk0UlNNdjE1UmtwNUp4M0tDLTd3MTJoaU5tdHpBelJjQmV5bExfc3JtTEdNWEVWQkdQTUV4MENWMHozYnd6Qk9MT1N4Y09rZHpQVkdOTnZGRDNXNHl3TDN0Rk50ZlZqWnd6SWcxUk9EZElSWWM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPOTlkOGVoeENEdk81YXA5dTdCZURGdzBWNjNDa0RTejNzMXVqbWRvclZxMUcxM05RdGhmMXFiMzBHb3RVYUpVbjlFMjNoX3V0NjlPYUx4eGdoWEFjU0dYUWMySnhGN29kY3R4QlR6TlR4YXFRQnpYMENnb3hpSmwzdEd4R1htX0lsRkN2VkRCTmpmMDZndVFsMU9LT183eUtKakc1ZzE3aGhLTWg4cnd0bg?oc=5</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>16-05-2026 10:51 UTC</t>
+          <t>17-05-2026 14:20 UTC</t>
         </is>
       </c>
     </row>
@@ -1057,22 +1057,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>HFCL Limited Schedules Institutional Investor Plant Visit at Hyderabad Facilities on May 18, 2026</t>
+          <t>The ‘Perfect’ Rose I Wish I'd Never Planted</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>Southern Living</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxPMGF3WTByR2FJeV9JamRMbUZRazB5OEhqX1JjdXpOWmZ0QjVSSHVON3dGMkFWM0xIUzNBdFNQMlQwWGNCQWZsRkNWZjZpYVdvX2Nid1p2TGtzQUkzVlVOeVRLX2cxTUhyX0ZMZmZTRVVYd3pSNmpaZ0djR1JPeFJ4OVNzcEpOckt3eGlvV2djc3k2STNIajBuTWx4R2FfWnNrRnk5YzNuWUVPZVI5ZzBpaDdOcU9nb3Q3bnVJT2ZnVFRGTnVSeFJmN0I1cVlybnJNS3k2SjlGWnhCYWZ2azdJazJXUnZ4OEpB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE1oeE8xNDFpUTdOZE5tS2ZHc1FGSEhIV1VKUU1fWHJwRDdubXo4bWpfMW0wTEtTcmJrN25WVUJSUmhzM1ZhWDctS2xBYUF1YmFodkIybDljeE83STZHVEtFQnlhTXRWZGRyT2ZZSA?oc=5</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>17-05-2026 00:30 UTC</t>
+          <t>17-05-2026 01:43 UTC</t>
         </is>
       </c>
     </row>
@@ -1084,22 +1084,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Emcure Pharma receives 7 observations from USFDA after Gujarat plant inspection</t>
+          <t>Trump Says Iran Will Have 'A Very Bad Time' If Deal Not Made</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>The Hans India</t>
+          <t>Radio Free Europe/Radio Liberty</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNYUlrRFZuR3ZrNlh4dklJWjBLaXNTcnl5SjRRZHo0MS14d2E2N3RlUGVTSlU4NUJoazlTUVYtTDJhdk1DY0tXaF91c0tMN0JfbHd3SXExTU55cjAyelRTQVVvRkcwdE00ZDh5LWJ6d2FKWUVfRi1ZNXo2SGhOb3RTeG1WTDFtVlFoWnRhWjNwZTgtaUk0Z2M2NFJIUlAwTUVZdS1HbTAtNUF5MnFfNmFwVDE4NnhYSWMxajdUQWtVdEZHVHBIMThGRdIByAFBVV95cUxNYUlrRFZuR3ZrNlh4dklJWjBLaXNTcnl5SjRRZHo0MS14d2E2N3RlUGVTSlU4NUJoazlTUVYtTDJhdk1DY0tXaF91c0tMN0JfbHd3SXExTU55cjAyelRTQVVvRkcwdE00ZDh5LWJ6d2FKWUVfRi1ZNXo2SGhOb3RTeG1WTDFtVlFoWnRhWjNwZTgtaUk0Z2M2NFJIUlAwTUVZdS1HbTAtNUF5MnFfNmFwVDE4NnhYSWMxajdUQWtVdEZHVHBIMThGRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQWnhyaS1tS3NVV19VeVRlS1RUeUhFblVCTkRCWmg2Z2YwTW1uR051ZFctc3F2eEcyN29hbkJkLUY3THpPVzVaYVRlcTRybGlrTGVsX3ZvTFJyQmRELVNHckg3Nk9uOUw3V2RyN2lZY0dIMW1jLWVQSUVTdXBTZGpuVE55cDBQcG01?oc=5</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>16-05-2026 16:30 UTC</t>
+          <t>17-05-2026 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>New Plant Species 'Sonerila Roxburghi' Discovered In Kerala's Western Ghats</t>
+          <t>HFCL Limited Schedules Institutional Investor Plant Visit at Hyderabad Facilities on May 18, 2026</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ETV Bharat</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxOYkVsZXpHZjZwVXgySHRDNS1FVElWdnlaZDM4d2E5bWxza09NS0FVR3A5SDBLdk1zQUJOY1dOeFViNnBLVzNnTG9COV9nVUtiRXZWeTUzYUh4MG5ueVZjT3owWS1yRVBtMllHbmpLX25YbkwzOF9IOWlLSDg2cUZaRkhPLTZPOEhlYW5qMVVLZ9IBlAFBVV95cUxQVEQ0TllKb0hEQnZCR3FjNUJXaUJheDlZSkI4cXF0WGZTcXRxanYtRTF0M0hXZzdncDFJUmk0MFM2aFVoMGo2Zk8zRzZoN3lyaEdiTzVVRzFseUNwY3VaaFZvMm5IN3p4SVI4WUpYTlZsLWYtTVh6d0FmRXYwTWxLTmREMF9TTV9NRkZzcXZUaUJlVDZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxPMGF3WTByR2FJeV9JamRMbUZRazB5OEhqX1JjdXpOWmZ0QjVSSHVON3dGMkFWM0xIUzNBdFNQMlQwWGNCQWZsRkNWZjZpYVdvX2Nid1p2TGtzQUkzVlVOeVRLX2cxTUhyX0ZMZmZTRVVYd3pSNmpaZ0djR1JPeFJ4OVNzcEpOckt3eGlvV2djc3k2STNIajBuTWx4R2FfWnNrRnk5YzNuWUVPZVI5ZzBpaDdOcU9nb3Q3bnVJT2ZnVFRGTnVSeFJmN0I1cVlybnJNS3k2SjlGWnhCYWZ2azdJazJXUnZ4OEpB?oc=5</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>16-05-2026 12:08 UTC</t>
+          <t>17-05-2026 00:30 UTC</t>
         </is>
       </c>
     </row>
@@ -1138,22 +1138,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cactus waste could become a low-cost building material</t>
+          <t>Is It Better to Plant Roses in the Ground or in Containers? Here's What Experts Recommend</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Earth.com</t>
+          <t>AOL.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNSVhIMmktbzJXLUp4cUdmUDdRTkJsSUdGbXhQNmFvZUJkV3RmUGxKMjR2SEpiWFBQUDBPQ1hBSXotUTY4cElkdU1MR1MySzRySDB4dnAtOXpDNUllUDNuZXkza3lfTm1ObS1fZmpVRWY1NWxic19ldFExVkQ3cXlmSlVqcU8xQS10Tmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE1EY2pXaGxGOV9EckdEU0Z2RmZKbUd5RjRNb3dhVzRDT2tlYzJ5MnZ0VFVlVlNyaTFLLW1JeGhBRURQZHM5QmN1a01VSUh3OHdLMVREY0ozc0lZMURacUYyOGk1RmNaR29CaGNRbDd4Rm43Vm5wQWE0YzllWQ?oc=5</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>16-05-2026 17:28 UTC</t>
+          <t>17-05-2026 06:27 UTC</t>
         </is>
       </c>
     </row>
@@ -1165,22 +1165,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>IMG_9270.jpg</t>
+          <t>Emcure Pharma receives 7 observations from USFDA after Gujarat plant inspection</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>thegazette.com</t>
+          <t>The Hans India</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPUzhFODA1QjRVQWlVQTZaSURvQXZPdUVncnMtcXgxOFF6NkozOVBXLXhyZUZJdlRzOGdQRS11X0VwSkY5V2k0TmtwS1VBbWl0cW9sMFJiNTRiYTVfd0ZvSUYwenh2RUdBRVA1MW5rek9ORFZOZ0x5NjFWbTNlTlNwRjdoUndYVk5aQTljTy0xWUc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQakY3LTd5ZF81MDhzT1Q3NmNpZVlodWEzdUwxS0gtOHdqa2xrSnl2YmJLdlhpMV94Q0VJdkljemttdUNsTzNnRjQ0Wm5RbEtUbUxuNUxBR2hzUHg0VkhrZnFVY3NhM3ZQZ250bDZ0aExkWXdRRjZsa3Y5VFJSWC05STU5V2pFWklmYkZpOVc5eF9CdWg4QWFCVVNkcklyTFRhblV0WWtMWE1ITlhOa0kzRFBubk1iTG5kU0hFTEhXYnJIM0nSAcgBQVVfeXFMTWFJa0RWbkd2azZYeHZJSVowS2lzU3J5eUo0UWR6NDEteHdhNjd0ZVBlU0pVODVCaGs5U1FWLUwyYXZNQ2NLV2hfdXNLTDdCX2x3d0lxMU1OeXIwMnpUU0FVb0ZHMHRNNGQ4eS1iendhSllFX0YtWTV6NkhoTm90U3htVkwxbVZRaFp0YVozcGU4LWlJNGdjNjRSSFJQME1FWXUtR20wLTVBeTJxXzZhcFQxODZ4WEljMWo3VEFrVXRGR1RwSDE4RkU?oc=5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>16-05-2026 18:51 UTC</t>
+          <t>16-05-2026 16:30 UTC</t>
         </is>
       </c>
     </row>
@@ -1192,22 +1192,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5 “Unkillable” Houseplants That Practically Take Care of Themselves</t>
+          <t>Cactus waste could become a low-cost building material</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AOL.com</t>
+          <t>Earth.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNeGktWkhHX1JLd293eFNPY3FUZGs0Q2pmZGdVczgxRXdMTF9heXNKc2tXMnFvNkVvZjV4WkJiM3FOTDV3dl92ZlpHejBNWVQyN3hFTGtZNHgtYWhIaWRDRDJnWkU1TEFxRjUxcmdzWC1Xd1VpWGlQMjFQYjc0TVRmQTBhOGNDaWJYSTZ1U2ZVWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNSVhIMmktbzJXLUp4cUdmUDdRTkJsSUdGbXhQNmFvZUJkV3RmUGxKMjR2SEpiWFBQUDBPQ1hBSXotUTY4cElkdU1MR1MySzRySDB4dnAtOXpDNUllUDNuZXkza3lfTm1ObS1fZmpVRWY1NWxic19ldFExVkQ3cXlmSlVqcU8xQS10Tmc?oc=5</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>17-05-2026 07:27 UTC</t>
+          <t>16-05-2026 17:28 UTC</t>
         </is>
       </c>
     </row>
@@ -1219,22 +1219,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Struktol Details ZB 47, ZB 49 Processing Aids for Rubber Compounding</t>
+          <t>Does Flaxseed Cause Erectile Dysfunction?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tire Review Magazine</t>
+          <t>stat.gov.pl</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE1zc3lWWmRYcXZTOGtCaW40Y2k3dGhydlFLdkpSRkUyWWd5ZEwwbWhxNm9IWk56cDQxWTlxak9fU0FEZTZudDg0dE5ZVUVwQ2JJVEZXRFRTalJySkx6NnNUR2hxNTluTExKQ2VRbEJPRVUtdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwJBVV95cUxPZ1NCRXZMRGVKWU1QUllsMzhQNnlRc0xIb3RkTEVTUFpNQUtoMGkwRVI5QS00TDcxX21uMDQ4YURjbXh2UEZNeGtKeFlUMkdkTFFRQUJxU19kb3h3d2J4VzM1YkluT3ZqczZleE1vN1N1d29UcTN2VFJrN1EwanE1aGczeFlwSTBxNWZYd3ZMUS1qS0k3aUd1QV9nVnRpeHFYWV9VX21fMmMtc2lHRWlSTDNLMng3d0dJTWdpVzFpNzVtbGxQOHB5VXY4TjVxMy1IYUtaYnhIYTU5S01MRTdUbm5KY29PRWpsUWtYWmJGYkNHb19FVjJJRkdaTG9ERzJzdlFRV05yYk5UeVhQNkdqUVVvWUhWNENiV0JqVG1WZw?oc=5</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>16-05-2026 14:00 UTC</t>
+          <t>17-05-2026 10:17 UTC</t>
         </is>
       </c>
     </row>
@@ -1246,22 +1246,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Russia Plant Pot Planters - Market Analysis, Forecast, Size, Trends and Insights</t>
+          <t>IMG_9270.jpg</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>IndexBox</t>
+          <t>thegazette.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPLURMOG84RllBbUxicC1MMWJHdW13V09kNU4yTzUwMjVCV001LWptNElPNVhqVVRLRXFvVDdKMHZvQnIya0JFZnRuZE5OLU5RMVVVVFZWLWd3a1NmWDc2OWhvUmFSTVJ5YlFqcEhxWHNxVnVoR1lNNkVCMV9IWGI4UEJuZjdtdDYxaVFsNXhQTElXczRqSWNDOFloVmd0R2lvbzhrSkN1M1RBZUNRN2Zjd21tTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPUzhFODA1QjRVQWlVQTZaSURvQXZPdUVncnMtcXgxOFF6NkozOVBXLXhyZUZJdlRzOGdQRS11X0VwSkY5V2k0TmtwS1VBbWl0cW9sMFJiNTRiYTVfd0ZvSUYwenh2RUdBRVA1MW5rek9ORFZOZ0x5NjFWbTNlTlNwRjdoUndYVk5aQTljTy0xWUc?oc=5</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>16-05-2026 10:04 UTC</t>
+          <t>16-05-2026 18:51 UTC</t>
         </is>
       </c>
     </row>
@@ -1273,22 +1273,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Emcure Pharma Sanand Plant Gets 7 Procedural US FDA Observations</t>
+          <t>How US hemp ban could criminalize CBD products – and derail Medicare plan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Whalesbook</t>
+          <t>The Guardian</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxPN014ZW1jaXVXRkZnNVJaMHRER01YcmFwczZIbU45UVRSQmVkMllaR1Bsby1pUng3bEVVU1laX0FxQXhTUllnYWdyeDRpVjZobC1aU1NJR2JUM1poY2ExQTM0aXRFU2JTdE9pUkM3SUtrMnd3akZvMjlvSk9WT0pheWozajFPdWxKdjJtcHpZTkhnOGtBRFVZamNVRThGSzBQSEhyRXBTR05SSmxRS3daQkhWNkpPUktWTFBxTl91SGZNUFVMenpXcWxzS1FmOE5Id3dya2NNeVV3YVBfQ3NtZFhKdkgySzU2Vmw1QTNR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE8yTmNnLVBPNVladEdjTHREbzZIRlVBRmhPQkl2b3B3OWtaN3RjV1BzLUw4Ti0xa3JlQ1Y4akR6ZGNVVkx3S3Z6aFJqRlFUN3AzVUxqc2hfa3NXMmgwMTlYVGppa3BHR3MwNWQyVGpGU1FlS2haOGktcUxmbTR3Q0U?oc=5</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>16-05-2026 09:27 UTC</t>
+          <t>17-05-2026 11:01 UTC</t>
         </is>
       </c>
     </row>
@@ -1300,103 +1300,103 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Peppermint gets a genetic makeover to fight deadly disease</t>
+          <t>There's progress around the world and at home, from environmental to healthcare wins</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Earth.com</t>
+          <t>NOLA.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxObUtpSHo1bkFpeHlLNlY2ZzI5NDkwQnUxUU13T2tBbmhKTDc0RDctNTdnSy1xUFBWYlBrajNGTDJlSTM1QmtONDh4bXlsT3VwRWYxcXVQUDZtNzlrVWMxM3pWX3prRzZjZ3NvWFhLSTNZbGI4YkhpdWhxSTZkUjh4ZmFJejVGeEEyeDViN040WQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNNWpvTG5MWXZkeHI5ei0zRWJXMzM4bE5oYTc1ZTBrZGZ4RzQyY3dHdHVOREU2Wk5VU2xjX0ZNdk41ZFJRcThHdXlpY1NkVTg1YjBzSGZDUUJTS0RRSGNGNE12YWttTkxOVmdrX0htd2NhRTJzdUNZaEt1cU83eURZdFNWcnNtenJGdjc3clB0YW1wNS1GUlVDbl80dW9KOEl4Ym04bW81ZkYtZ9IBqgFBVV95cUxNNWpvTG5MWXZkeHI5ei0zRWJXMzM4bE5oYTc1ZTBrZGZ4RzQyY3dHdHVOREU2Wk5VU2xjX0ZNdk41ZFJRcThHdXlpY1NkVTg1YjBzSGZDUUJTS0RRSGNGNE12YWttTkxOVmdrX0htd2NhRTJzdUNZaEt1cU83eURZdFNWcnNtenJGdjc3clB0YW1wNS1GUlVDbl80dW9KOEl4Ym04bW81ZkYtZw?oc=5</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>16-05-2026 12:43 UTC</t>
+          <t>17-05-2026 11:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Coherus Biosciences</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>This Low-Maintenance Plant Is Perfect for a "Busy Lifestyle," Pros Say—And a Great Summer Addition</t>
+          <t>Coherus BioSciences stock (US19247A1007): Q1 loss widens as turnaround strategy shifts to oncology f</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AOL.com</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNNG1mZWxEMDZPU3RVZVVRV1ltbEpzUHNYYlZzLUVKLTE5N0VNcVdhXzlfVnVWdU5qNGxxdHpWOGRJc0ZXQ29halNOWDNjYkZLSV9EUTdtVlB5SFpEZFJFS2VKQTBnZGUyTER2UVFHeml2T01sbEZwZGVMOU1fUndSWFJCa1FYUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxPRGc3TV9jUVBPQndhdnRCWVRMQkdjUC1TMXBOVDhVTXc5SWo2VndJRXZsVDV6aDRRbFJuX2g5VU9Bekp1QkZieHdydThhaVdydWN2TTAtdm1LSTRnOTMyY09CR054ZDk1VEI3MlFpTV9uTnIxUWQzc3VUZkM4b2g3eHMxeTFkaDB4OG9nT3hmd1BEMWRINVY0eWNhQjd6UTRZT2hkY0YxOEhCYTV5Sm1fNVdYVXdQWDhPRFlSa3phSUJuTk54?oc=5</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>16-05-2026 23:38 UTC</t>
+          <t>17-05-2026 10:24 UTC</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Coherus Biosciences</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>12 Shade-Loving Perennials That Pair Perfectly with Hostas</t>
+          <t>Coherus BioSciences stock (US19247A1007): earnings miss keeps focus on turnaround plans</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AOL.com</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxOYkVxR3ZYYU1YcmRYTlBIcWc1bThNbVc5RHA0TXYxb0Z6QUZ6MlV0bUtGR0hGa1FiY002elRuSGVQdHZnV3pHTjVubDFPeEdyUnlOMjhzOXNhNHZZUi11UGhBellveGtnZ2h0WDhCdnJhYTBRaWYyeEdrOEpnMHk5eg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxPTVRPdzJSLWEzVVJNblM3Z3lFMU5tb0ZDbmtvb2dlcEFENDJoTnRPTUxCLWlXZW56MGFnSkdUQW02NUNoRVZqQ19BUjVpQW1QNGNsWG94VldZdWhjRDhGOTA3Tlp0WURGUVVXal9sa1dzZ010SHFLaGt2WVlRb21tZ19oQURGUXN3Tzl0SmpyNG9QTWpvNEllakpKSy1SaWQ4VERNa24wXzF4ZVlXcXMxMDdfdnY2aUhBaUwwR29USXdCU1Bv?oc=5</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>17-05-2026 05:07 UTC</t>
+          <t>16-05-2026 15:25 UTC</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Coherus Biosciences</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Coherus BioSciences stock (US19247A1007): earnings miss keeps focus on turnaround plans</t>
+          <t>Pfizer’s Lyme disease vaccine shows 70% efficacy; Texas man sentenced to 12.5 years in $61.5M Medicare telemarketing fraud scheme; Novo Nordisk launches Wegovy subscription model – Morning Medical Update</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>Medical Economics</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxPTVRPdzJSLWEzVVJNblM3Z3lFMU5tb0ZDbmtvb2dlcEFENDJoTnRPTUxCLWlXZW56MGFnSkdUQW02NUNoRVZqQ19BUjVpQW1QNGNsWG94VldZdWhjRDhGOTA3Tlp0WURGUVVXal9sa1dzZ010SHFLaGt2WVlRb21tZ19oQURGUXN3Tzl0SmpyNG9QTWpvNEllakpKSy1SaWQ4VERNa24wXzF4ZVlXcXMxMDdfdnY2aUhBaUwwR29USXdCU1Bv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gJBVV95cUxPVnU1X0hLdnNoem8xSWwtUm9LQ28wXzM4aUFsUUN2U1ZsM0Fwb2dIWmNPdGphRVd3cm9RUzBtT0gzYVlyYUV5aHBnOEt4ck9CVnV0NEs5NTJkV2d1WnZSaGs3bUJYUHlzVVBMV2xwRDhnakZiWVlkNG5kTFBmTm0zNHJGNDlhdHhNcVNEQUtaX0ppdlZ1SFlXekZ0Z0Rtemh4TktrWGdPN1VIYnhGZmZnWURLWlhQTjNhUXN0RkV5eE01ZnhhVHd0RXlFNm5PNDBQTjQyOWpHMWRpTUJfV0Y5NjBqcmJvZ0FGWGtZQjdtZW5LcFI4S3U5ZHV6Zl9uc0NZQkpEcDQ1TjRiTnk3MjBGYS1RdjhNaVhvQjVveW5FRFpWQkVicHE1MVlLbURUZTFObTZtS19qN3JrdDF5c0RHb19WZzNTQW5OcWU2MEdGR3pqREVjQWc?oc=5</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>16-05-2026 15:25 UTC</t>
+          <t>17-05-2026 02:32 UTC</t>
         </is>
       </c>
     </row>
@@ -1408,22 +1408,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Pfizer’s Lyme disease vaccine shows 70% efficacy; Texas man sentenced to 12.5 years in $61.5M Medicare telemarketing fraud scheme; Novo Nordisk launches Wegovy subscription model – Morning Medical Update</t>
+          <t>The week in pharma: action, reaction and insight – week to May 15, 2026</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Medical Economics</t>
+          <t>The Pharma Letter</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gJBVV95cUxPVnU1X0hLdnNoem8xSWwtUm9LQ28wXzM4aUFsUUN2U1ZsM0Fwb2dIWmNPdGphRVd3cm9RUzBtT0gzYVlyYUV5aHBnOEt4ck9CVnV0NEs5NTJkV2d1WnZSaGs3bUJYUHlzVVBMV2xwRDhnakZiWVlkNG5kTFBmTm0zNHJGNDlhdHhNcVNEQUtaX0ppdlZ1SFlXekZ0Z0Rtemh4TktrWGdPN1VIYnhGZmZnWURLWlhQTjNhUXN0RkV5eE01ZnhhVHd0RXlFNm5PNDBQTjQyOWpHMWRpTUJfV0Y5NjBqcmJvZ0FGWGtZQjdtZW5LcFI4S3U5ZHV6Zl9uc0NZQkpEcDQ1TjRiTnk3MjBGYS1RdjhNaVhvQjVveW5FRFpWQkVicHE1MVlLbURUZTFObTZtS19qN3JrdDF5c0RHb19WZzNTQW5OcWU2MEdGR3pqREVjQWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOb04xYmh1V0VBX05OZ01haEl5NkJpNG1QbXBjckNxeUozeWZ4TEs4SzQzN3doUTNPQU9qWE1fNU1xUlVJYUxLNXFXRHpDb0Y2cjFUWEJDblF3Si1ReHJLVFlhWjhkTS0yOW5Ob3BTUnZVcDJuMnducW9hU3dzbUFTZGc1WmxDSGIwd2NVNEw1WXZZeUxPb0dlTnY0ZGJ4dW9uNmEzVzVCX0h1U3NoRVE?oc=5</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>17-05-2026 02:32 UTC</t>
+          <t>17-05-2026 10:30 UTC</t>
         </is>
       </c>
     </row>
@@ -1435,22 +1435,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Pfizer Ltd. is Rated Sell</t>
+          <t>- The HinduBusinessLine</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Markets Mojo</t>
+          <t>BusinessLine</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxPNjZmUEJDWWM2RnE1Y1hRcklDcGhva3YwdkFTcVVzUXUwbTVKSldISWZHRDdWSlJuc2duTFVNUnIxTXphU2J3X2k5TWozSWwyZ3dVenZXeVJ5MjlyTFZkcmpLVFVRdnViQXhkekxWbGc0VE5wcDJCUmJIM2h5NXlfODRDTkFBaktHdW13d3gyOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wJBVV95cUxNY0V0ek4yUU1QVGJaR0l3S3NEMmxHQjAycVhTOTZ0TjlYdDVpVl9meUFkMEY2T2VTT2NlTzJ1b2pQeDY3T2o3R2JJVTdvQk1DS2FGRmVSaHRySlhHRlBtRGUyeTNDcHg3bUdhNkpnNVFIOUhUZWt2czJDdTZBT2FrVS1Bckh4ckJYMVJDYWNiaTl0SE9WWWhnb3hQTm9pSkFDZlZULS1PMkl3WTRCZERDY1RHalJyZG9QV253dVNlaElMT3pCUGkxbU4yRk4zUV9FdENXa0hKbXNINkNTamdHVWtUbnhnTXhzTjJOQU01LW1HbzFHejJTSGNDcS1EVXJ2QjRYREdfTlpCMlI5UjJMSjBXYVEyRG11UHdlUlNJOGFGUmVFZldTTTMtYVZFemFQQlV6NFhrRlhqWDh5N1BycG9Fa3p1STE5SnpvY0VJNXQ1X040N251THJHWThuOVk?oc=5</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>16-05-2026 11:50 UTC</t>
+          <t>17-05-2026 14:42 UTC</t>
         </is>
       </c>
     </row>
@@ -1516,22 +1516,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Wolfe Research Says COVID Uncertainty Continues to Weigh on Pfizer (PFE) Outlook</t>
+          <t>Pfizer (PFE) Juggles New Trials, Site Shifts and Mixed Wall Street Bets</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNWDlPcmdiN0FoRC0xQzFTMFlMV1Y0RjZlVFNVRVhMb0xSNjdiZ3FOZUxETkhETldwSFA2QVFLOGZkNThHNWdNOWR2RGFDOTAyalNWNHFIcnd0cnY4Z0V0a3pGYThta1Rfckx1U0J2TllSRE84bEN5V3RvV1BOMDRCRGxWaTJiMFNZSW0tc3NpZzdfVGlDbVRZWkt3TVBEeFNNUW5jT215V3F5UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQYXo0bzN6c3NRR01nNElGNmxNWGdCVTVGNTN6OW1uWDVEamhMZjFHbDhwMGtNaFQwcGNFUGQxWGxqUjhoLTBhNG1EWXluZDlNZFhKcjhoc09iUF94dHZSeTFNQzR4MVh1SnNVcmNWQm1ybVU5Qkx4TVc2Z3FYNmstczVGUHhUX0VlRG5PZjVKSUlaSHF4cHVES0N6eUlURFN2aGFqMnpoTTJ5WVAzbFJDTFpmb3M?oc=5</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>16-05-2026 10:56 UTC</t>
+          <t>16-05-2026 15:10 UTC</t>
         </is>
       </c>
     </row>
@@ -1543,22 +1543,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Pfizer (PFE) Juggles New Trials, Site Shifts and Mixed Wall Street Bets</t>
+          <t>Comirnaty mRNA COVID-19 vaccine explained for US users</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQYXo0bzN6c3NRR01nNElGNmxNWGdCVTVGNTN6OW1uWDVEamhMZjFHbDhwMGtNaFQwcGNFUGQxWGxqUjhoLTBhNG1EWXluZDlNZFhKcjhoc09iUF94dHZSeTFNQzR4MVh1SnNVcmNWQm1ybVU5Qkx4TVc2Z3FYNmstczVGUHhUX0VlRG5PZjVKSUlaSHF4cHVES0N6eUlURFN2aGFqMnpoTTJ5WVAzbFJDTFpmb3M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOLUV5UHd6VzAzUnRHaFhLNWpDT3VmMzFCWWpyazBIU2hCek4wdjlNYk91T2w3Y1dYb2VVU1M2S3N6MWdtZkhFRFZqdDZ1cVhOOFVHM3hhWmZ3MUdkcGVzYnozendObzZqQ24xTW43dnkwVkVlQXNWQ3RvcHo5RDk5UXZnai1XcmdqcTB4RGZBamRBN2RyUk1JaXVkRzV3aUJZT1gxWWlFUkg0b3N3ZEpSbGNYMA?oc=5</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>16-05-2026 15:10 UTC</t>
+          <t>17-05-2026 11:37 UTC</t>
         </is>
       </c>
     </row>
@@ -1570,49 +1570,49 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CureVac stock (NL0015436031): FDA clears deal path with GSK after BioNTech settlement</t>
+          <t>My Top 3 Healthcare Stocks for May 2026</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>AOL.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNNnVhM1RwbTdCSDV5YmxYdFc1T0ppU3RPeEVOV3Y5dTNERTZXdVRqRmhxa2JfR2RnWTdXajQzMnhzc2VhNEhnZEpYejBZYkhlbGhfZjlUd0llTlNQZGRSR2xVYnBsTkNYQU4zSEQ4dE9SMlYxeURqYnZ1T21JSjd1eVNMUlBMQzFBSWFaNlpCUE1KM2JGN3hrRFZhTDItZzhkTXZKeG1VNmpZOEJ2dENVUldZMC1nMVpoSDFNWUF2M1dKM24yYzlqN0dB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE9OUl9Mb2t2bjFRU2dMdUMzdldWRjh0QjMwSms1Mkl4ZVhTbWppVGs0bTVFWVVfckRTT3ozeG85MTdYem5XQlp6MHhWUmZkYVMtMWRYT0VMZFdFaGJEX2JWSXhMUjBQQTVSclZzaHVwUnQ5UmlDM1BLOXBsUQ?oc=5</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>17-05-2026 06:18 UTC</t>
+          <t>17-05-2026 08:31 UTC</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Biogen Pharmachem Industries - 13 penny stocks plunge up to 65% in 3 months. Are you affected?</t>
+          <t>CureVac stock (NL0015436031): FDA clears deal path with GSK after BioNTech settlement</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9wFBVV95cUxQaHp6NGowYTBvb3NodnBCd1YxbUR3bXJjaWRQVWx2MlgtMTk4Z0ZtZzFTSDlHYUNOazJVUkR3R3lGcUFwUVpQQmx4Unh3THIzeFdYeE1WZ1lVM3hza1BISFN6bm1ic21BbVRqTWJoc2ZHaXZ4c0hZLTMtOVFJSlliMXpKdmNQdUNwNmR4djhRRHRGTHF5YjZsaEZLcnFKcXRnSGtaM2lDVms3V09UV055b19ma2JfeHA4UGNiU29qUTJHN2NnMkN2a0dPTnZaU09tNGhzOTlZRU5TMktXUFdEb1V1Y1k1Qmh5Xy1uVDhCS2dJQjZ1c19v?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNNnVhM1RwbTdCSDV5YmxYdFc1T0ppU3RPeEVOV3Y5dTNERTZXdVRqRmhxa2JfR2RnWTdXajQzMnhzc2VhNEhnZEpYejBZYkhlbGhfZjlUd0llTlNQZGRSR2xVYnBsTkNYQU4zSEQ4dE9SMlYxeURqYnZ1T21JSjd1eVNMUlBMQzFBSWFaNlpCUE1KM2JGN3hrRFZhTDItZzhkTXZKeG1VNmpZOEJ2dENVUldZMC1nMVpoSDFNWUF2M1dKM24yYzlqN0dB?oc=5</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>17-05-2026 08:17 UTC</t>
+          <t>17-05-2026 06:18 UTC</t>
         </is>
       </c>
     </row>
@@ -1624,22 +1624,22 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Biogen Pharmachem Industries Ltd Falls to 52-Week Low of Rs 0.44 as Sell-Off Deepens</t>
+          <t>Biogen Pharmachem Industries - 13 penny stocks plunge up to 65% in 3 months. Are you affected?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Markets Mojo</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOSmEyNGcxcDVRTW9IOWtKWGJVT3I5YlY4MXRLNFlBV3lrVjRLbFdwdGotQ21oRTNjLVFmdXk3SnhRcEx3RGc3eWNRX1hQdnFJdERsUHFiSGZ1VXBkN3htNUpnUlJDQnRBX1R2djkxQ0duV1FPS04zbHdhb1ZkR3NvSXpOSHZGWWg3dWdCd2k3WVhnbkJrR2FDTnVIQVZNVzVkeWVvXzFWRE5XRExILUJjc05FdzhzYmItMnQ0aw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9wFBVV95cUxQaHp6NGowYTBvb3NodnBCd1YxbUR3bXJjaWRQVWx2MlgtMTk4Z0ZtZzFTSDlHYUNOazJVUkR3R3lGcUFwUVpQQmx4Unh3THIzeFdYeE1WZ1lVM3hza1BISFN6bm1ic21BbVRqTWJoc2ZHaXZ4c0hZLTMtOVFJSlliMXpKdmNQdUNwNmR4djhRRHRGTHF5YjZsaEZLcnFKcXRnSGtaM2lDVms3V09UV055b19ma2JfeHA4UGNiU29qUTJHN2NnMkN2a0dPTnZaU09tNGhzOTlZRU5TMktXUFdEb1V1Y1k1Qmh5Xy1uVDhCS2dJQjZ1c19v?oc=5</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>17-05-2026 00:15 UTC</t>
+          <t>17-05-2026 09:05 UTC</t>
         </is>
       </c>
     </row>
@@ -1651,22 +1651,22 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Biogen’s Diranersen Moves To Late-Stage Alzheimer’s Trials And Investor Focus</t>
+          <t>Biogen Pharmachem Industries Ltd Falls to 52-Week Low of Rs 0.44 as Sell-Off Deepens</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>simplywall.st</t>
+          <t>Markets Mojo</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxNWEZISFVBaWRFNEpLYVZPbUhCeE9xTlVMTTdiU1Jjdk5Eajc4NmFrZzR6UXhZVnRZcWlycGpvN2ZkZnMwbndOakZqRXN2SVFTOF9RdWZnLWY3UFRSaGEwWUc3SDlROE1ZVldPemx3ODdmYldQajdmckFwdFIxZnJ5c2FKZmFRbS1VdjdlQW5leFpkTWY4WFpLVUhwd3BYSTZwb05aZ3A2ZTdKamhnYnVjcUNwY2xzaDF3MTMwVGJTOHc3VUlFQ1lIN2pkSG9UVnNORVpLX0hiRdIB3AFBVV95cUxOZExINnQwZXR5emQ5TXFVUXl2TGNDTEpta2puV0E3Y0R1MWVkSVA4bmlsQVAyU2I5elJ4ZVBCci1QY2lFbE52OUd6ZjZWOGNYOC1nVlBESVpiNEphN21wR2lJaC1xeWpRY1JycU5fLXlQNDRFWkR6dlQySzdlX2ZTaVoxZ096T0JNaU90a2VhZmxqdFRQVGxoejJqa29CM0o4V2NZZDJyRkZ5WFlTVWJJOHZ6SDV4MGxqYnlvc1Fkc3pGZkhOaFVMZDVhdk9pc3ZtNFlKSTE3cFAwWlMx?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOSmEyNGcxcDVRTW9IOWtKWGJVT3I5YlY4MXRLNFlBV3lrVjRLbFdwdGotQ21oRTNjLVFmdXk3SnhRcEx3RGc3eWNRX1hQdnFJdERsUHFiSGZ1VXBkN3htNUpnUlJDQnRBX1R2djkxQ0duV1FPS04zbHdhb1ZkR3NvSXpOSHZGWWg3dWdCd2k3WVhnbkJrR2FDTnVIQVZNVzVkeWVvXzFWRE5XRExILUJjc05FdzhzYmItMnQ0aw?oc=5</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>16-05-2026 14:43 UTC</t>
+          <t>17-05-2026 00:15 UTC</t>
         </is>
       </c>
     </row>
@@ -1705,22 +1705,22 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Makary resigns; Biogen reports Alzheimer’s data; and more</t>
+          <t>Best Healthcare Stocks to Buy in 2026</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Endpoints News</t>
+          <t>AOL.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxQRDAwTVhJQW10RWgyanU4azJuU3NaM0Y2QnJGcmdkT2RmZ3YyRnhYRnFQMDJrZ0o0NFdEOTA5aE1LUjE4b0JCTjRxUmZvRFU0MVJMUGhPWlZ1dFpEdkpPRG5RQVNpRFBjSVNPbEtTR1hHb3oyVmtLZmpQWmEwNDNvQ3ZFVG0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQQnRyY1pEUTRyZnR0cXBWNkNXMmtORzRGSE50czhxVWs2dU1ocjc3NWRpaTl4QTFCWTBUNll2Zk5RSk54MGNyWE1femFfamRJQW16RXBuNnRvekxHM3o4Wk9Sa0dSZjVsQUNySEhLZzNxWEdEeUwwcU9tUXZTUjhFZg?oc=5</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>16-05-2026 10:00 UTC</t>
+          <t>17-05-2026 09:56 UTC</t>
         </is>
       </c>
     </row>
@@ -1732,22 +1732,22 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Biogen's Alzheimer’s drug fails to meet mid-stage trial goal</t>
+          <t>A Look At Apellis Pharmaceuticals (APLS) Valuation After The Biogen Acquisition Announcement</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AOL.com</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPMklKdzZ4Zk9wdTY0UnJwQlVNUHVCc2R0eHo4WUFwWmhsMjVRaEZsX010VjkyX3JfejRNSFB1RTlvODMxUUlLSjFlZ01Cd0xqbS1DYUpNRUI2bWJVRkYwazRQV1Q5YXd6UUdhUFpyVFJaVkNVNDlRQ1NWdnh1TWNMVEpZWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxNcE9JN0M3bU43ZGR0LWNvOHNTcmY2YUtydklxTDMxZGRpTW11QW13RDg2WkNiU2RRaHd1Qi1lNmFsanNEeUJDZzRHSGVzeUkxX2VJdHRKTUdlUFdPaEFwbEJ1NHRTMjctSmd5aGhKRjFhV2JRdkJMc095Yjg5aG1xVlZBd3ZTbTMyQmRMTXRRMUJseUIweEtZM2hiRFJKWnBKN3BTR3JRT1ZVVFI0c1lodUZRbW1QVUdwM05jWkhaRGduNmtEOHJjWWZPVUk4bW44RllUcmYyUHhKUUZVX05Jd1dJNnhvbDdob2FSWkFR0gHzAUFVX3lxTFA3OUNZVnA2bFY2MWZGenlDMXRORlota05QZnR6LWJoc05kQUdVYVBnZUptc1pLYnRYY09ITUdRVFllQ2pxTjl4NWN3TVZVN2ZIdnJac0ItV1hDcFQxSmxkU18tQW5lalZIUzZqdWdfcUE0SGdiMEJyTkV4OXA1X3Z6a2N5RlVGU0tleGM0WkpJVG53b3V6Z2dZb2hZdUY2aGFSWXpXSzY3NmpjUTkwSG1kYkJzV1haNzhYVEZEcGVSb0JCVHJ5X0l4Yngxd1M0YkZoUG5zbTQ5YTlnTFNla21meGZfVU1MalZyZTJ2X3VWcTlwaw?oc=5</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>17-05-2026 01:39 UTC</t>
+          <t>16-05-2026 18:51 UTC</t>
         </is>
       </c>
     </row>
@@ -1786,49 +1786,49 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Why Is BIIB Stock Soaring Despite Its Alzheimer’s Trial Miss?</t>
+          <t>Biogen's Alzheimer’s drug fails to meet mid-stage trial goal</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Stocktwits</t>
+          <t>AOL.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPTzFrb1RQd2JYNGl4dXdpOUpmajFmTXA0WUtONHN1NlJoeDlwTXR2Sk5sQlBSLTNoUnJELVRUY3JmSTFvUUExbXdZN2NERE9uSEdXM0dWWGVyOWNZVWwxZFd6TWJGTkgyOGdEbHk4c2gwcE9qWUhDWWFsOUo3MDhVOVotTUd1a2hTNjNlUmJQNGpKTTlQX29tLWx1VUozRVJlc1FUMGVfQ1o3THBMakQ2QnN0NXNKTFYxazY0anNXd2NsQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPMklKdzZ4Zk9wdTY0UnJwQlVNUHVCc2R0eHo4WUFwWmhsMjVRaEZsX010VjkyX3JfejRNSFB1RTlvODMxUUlLSjFlZ01Cd0xqbS1DYUpNRUI2bWJVRkYwazRQV1Q5YXd6UUdhUFpyVFJaVkNVNDlRQ1NWdnh1TWNMVEpZWQ?oc=5</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>16-05-2026 21:20 UTC</t>
+          <t>17-05-2026 01:39 UTC</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>A Look At Apellis Pharmaceuticals (APLS) Valuation After The Biogen Acquisition Announcement</t>
+          <t>Dr. Reddy's Schedules Investor Meets in May-June</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>simplywall.st</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxNcE9JN0M3bU43ZGR0LWNvOHNTcmY2YUtydklxTDMxZGRpTW11QW13RDg2WkNiU2RRaHd1Qi1lNmFsanNEeUJDZzRHSGVzeUkxX2VJdHRKTUdlUFdPaEFwbEJ1NHRTMjctSmd5aGhKRjFhV2JRdkJMc095Yjg5aG1xVlZBd3ZTbTMyQmRMTXRRMUJseUIweEtZM2hiRFJKWnBKN3BTR3JRT1ZVVFI0c1lodUZRbW1QVUdwM05jWkhaRGduNmtEOHJjWWZPVUk4bW44RllUcmYyUHhKUUZVX05Jd1dJNnhvbDdob2FSWkFR0gHzAUFVX3lxTFA3OUNZVnA2bFY2MWZGenlDMXRORlota05QZnR6LWJoc05kQUdVYVBnZUptc1pLYnRYY09ITUdRVFllQ2pxTjl4NWN3TVZVN2ZIdnJac0ItV1hDcFQxSmxkU18tQW5lalZIUzZqdWdfcUE0SGdiMEJyTkV4OXA1X3Z6a2N5RlVGU0tleGM0WkpJVG53b3V6Z2dZb2hZdUY2aGFSWXpXSzY3NmpjUTkwSG1kYkJzV1haNzhYVEZEcGVSb0JCVHJ5X0l4Yngxd1M0YkZoUG5zbTQ5YTlnTFNla21meGZfVU1MalZyZTJ2X3VWcTlwaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxPbDR6dWdlV25JTW9fS3dDNzJ3QmxIWS1WMGdZaml5U1JOUkRGa2YtT1pRdWgtQTlNbmd0U3AzekNrVnRkWmJzX2tJSDJtR0gtbUZVTDJaMXpkdHlZVXMyUk1fSnpZYlFVb2o5NU56aklWNW5ScHFnN3RHZmU0MHdUQmdsSU9PSU9rSnNySUJLYlNwSVdCbXZuSVZDbkdmVlZESGYyckJyOUhXb2w4blhEWnFrbGV5UkRSZkpWVl9mSmhBeUVIeE1La3RPRGk2ejVmWC00REZhYVNDUGlUd2N6elhyLWprenlLcFlCcWliMA?oc=5</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>16-05-2026 18:51 UTC</t>
+          <t>17-05-2026 09:43 UTC</t>
         </is>
       </c>
     </row>
@@ -1894,22 +1894,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Dr. Reddy's Schedules Investor Meets in May-June</t>
+          <t>Dr Reddys Laboratories Ltd Reports Sharp Decline in Quarterly Financial Performance</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>Markets Mojo</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxPbDR6dWdlV25JTW9fS3dDNzJ3QmxIWS1WMGdZaml5U1JOUkRGa2YtT1pRdWgtQTlNbmd0U3AzekNrVnRkWmJzX2tJSDJtR0gtbUZVTDJaMXpkdHlZVXMyUk1fSnpZYlFVb2o5NU56aklWNW5ScHFnN3RHZmU0MHdUQmdsSU9PSU9rSnNySUJLYlNwSVdCbXZuSVZDbkdmVlZESGYyckJyOUhXb2w4blhEWnFrbGV5UkRSZkpWVl9mSmhBeUVIeE1La3RPRGk2ejVmWC00REZhYVNDUGlUd2N6elhyLWprenlLcFlCcWliMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOZWJjZFUzYjVsekJ4Zlo3THBySUhyTTd1Y3R6X2UwRk5mRk96Sjh3a2JCLW9xaFhwYUhDZW82WkFzNUh1NFhvRjdwMFF0ZUNfSW0xd1NKNjBNSl8za3RsMUxjVklOZUdlRnhaZHBPdllxNlZUNDhQTjFsR290Q1dicXJvcjFDSXF0VVlVWGlVMEpvTHJhaUlqZEhTU1N0RVFxRXZnRDNzaWVPX3o4NVBpUUFPSkVRU2JsaEJ5MUh6Y0ZGX3ZRM3Mya292dm5nUC0xaTVib2xJWko?oc=5</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>16-05-2026 12:17 UTC</t>
+          <t>16-05-2026 23:53 UTC</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Dr Reddys Laboratories Ltd Reports Sharp Decline in Quarterly Financial Performance</t>
+          <t>Dr Reddys Laboratories Ltd Valuation Shifts to Fair Amidst Sector Comparisons</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1931,12 +1931,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOZWJjZFUzYjVsekJ4Zlo3THBySUhyTTd1Y3R6X2UwRk5mRk96Sjh3a2JCLW9xaFhwYUhDZW82WkFzNUh1NFhvRjdwMFF0ZUNfSW0xd1NKNjBNSl8za3RsMUxjVklOZUdlRnhaZHBPdllxNlZUNDhQTjFsR290Q1dicXJvcjFDSXF0VVlVWGlVMEpvTHJhaUlqZEhTU1N0RVFxRXZnRDNzaWVPX3o4NVBpUUFPSkVRU2JsaEJ5MUh6Y0ZGX3ZRM3Mya292dm5nUC0xaTVib2xJWko?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOS2x1N2I2MjFFT2hVWHI0STR4ZncxQkZKXzMzNXhtdnczNkc2UFVOX0Rsc09zeGhKUG5IOHZmVjlEY0lCOGpIeUx4T3M3ZGsxTmpYeTFkUG1DTWZTX0lzV0VacjljQUVxeUdrT2xiRkRtMDJ0NTl4NEFaOHB2cndpTG94TTVZbTBiblpqY2JZcHZmUGtxbHJ3VEU5MFNoWkRBd2JNd0R4ZzBfeE5nVzItQ3RSckJTZlZQejFSNzJRX09XOFpnbnNJMDlORzlxUUli?oc=5</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>16-05-2026 23:53 UTC</t>
+          <t>17-05-2026 00:16 UTC</t>
         </is>
       </c>
     </row>
@@ -1948,22 +1948,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Dr Reddy’s launches generic Semaglutide injection in Canada</t>
+          <t>Dr Reddys Laboratories Ltd Quality Grade Downgrade: A Detailed Analysis of Business Fundamentals</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Daily Excelsior</t>
+          <t>Markets Mojo</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOVE1TRG9FZjFyaUlKdkNvRGtGVk9WNzJJb2h5Q05XTVlfbEZWSWVzRkFqdXdFM01uamdPMFdIZVpTcjZjZGJkb01lS2ZWQk9wcEU4NnZUaklzV1pUcHY5bWtMaHNRRG40a1FoY2RrQ0VKcWZxWFZlRHdkXzNlVnA0N19IcWw1Q2ZUQlYtWWNBS25RY3pk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxPWlAxdU5WTkpfeVVIeHk1MlVkdThSQmlfUTFaaUZwcmVvZXpvNXR5MUNwa0c0dndMdmlTLVRxeHJyNkpIcU9MX1lsTUlKaEpqWkNQXzBGdVJseDNaSXBBek5fVnkzUmRBbG5DSTV3UlBWdDNJUGRONXl4bzRnWTJjdERrQ2llRUYtaU1GOExnbWp3bG80RVJVaTlwamdhTHJTQlRSUU01RGZVWEJJNEZsSVZFdGFaNGp3Z1Z2ZGdyci12QVA1OG9hZzJaS09Kb01fZmJIQVNOdEE2dTQwWTFVWTRZbWdqcF9Q?oc=5</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>16-05-2026 11:13 UTC</t>
+          <t>17-05-2026 00:16 UTC</t>
         </is>
       </c>
     </row>
@@ -1975,400 +1975,400 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Dr. Reddy's Sets Global Investor Roadshow for May 20-June 3</t>
+          <t>Tata Electronics, ASML tie up for semiconductor manufacturing in India</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Whalesbook</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxQSFM0dVpKY2xfbDA0cG56V2VwUnpsd09hWkNZTjFKWlo1eV9GdFBvT0tDOGVXRmlTSW1jdlUxZVJtWTAwZGFybXFxY2lJUUZGRnd6ZzAtejhTZUJSRmFZYlpEcWFMXzRuY0VpUXBpMnlIc1NhQ2VTYUpTTjhCNHF2aDZVeVJjRnhsVTdDblRVQzA2TVFsZklnYmt6UFNMUlBtcnVMNEUzZkVWNGw1S1ZMaERpZVRhT01JbHdHX1N3WWZCWmhmczZPZHVyZlJPNmpWOUJ1dWx4OVAzYkRETlR4ZUQyVWw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxQaDBVdXVnWGNOYV82MVVpM1g3NnZlZkJyWmd4T29PZjduQzBZRjhsQk1tNGpFT3ZLSXVqV01DNjdtRTJqRTJPbG9Ta0hDRGd4NGVjVWhfT3RBY0d3R0d6NGZmbVpMSDdfTmdqVnh0aHNnTGZvMmF1a0lKU2w1Z2VROVRabnpINjREMEZfdXZFX2Y1OTVkWmxUSTNTQkZyMEp6cFBZMGdFazNBcjNwb2NRaVM4SkRLWG95ckJ2VENZSFlSLXRfdXg5ajNLamo2eFc4a2tTYtIB2gFBVV95cUxPTHQ4Wk9YY1RVMmRpN0JabGNRanRxdVRhSG52OWRFZWJNNFoxTWNGV3pTcWZGLTRmZDVZVWxUTDRMZzB6akYyYUJDUFB5WTU4dlNmTDZVbVpxanVwNGdvWXFpcUtjZDhpblFia19uOTV3UGQyZlRMRzhLcnRacTNqUy01RFhBbW1oNWdLY0pjTkRHY3BHSk5uSWFWUHBZRVFLZlYxWVNXajBBSGdVQVBCOG80NWRHNzdNWlljSGdjcm82eTY5elBuREI5ZUFHQ3QzZVh3QUNYTmRtQQ?oc=5</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>16-05-2026 11:37 UTC</t>
+          <t>16-05-2026 17:02 UTC</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Tata Electronics, ASML tie up for semiconductor manufacturing in India</t>
+          <t>Interview | ‘India, Ireland stand to gain enormously from collaboration based on co-creation’: Kiran Mazumdar-Shaw</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>theweek.in</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxQaDBVdXVnWGNOYV82MVVpM1g3NnZlZkJyWmd4T29PZjduQzBZRjhsQk1tNGpFT3ZLSXVqV01DNjdtRTJqRTJPbG9Ta0hDRGd4NGVjVWhfT3RBY0d3R0d6NGZmbVpMSDdfTmdqVnh0aHNnTGZvMmF1a0lKU2w1Z2VROVRabnpINjREMEZfdXZFX2Y1OTVkWmxUSTNTQkZyMEp6cFBZMGdFazNBcjNwb2NRaVM4SkRLWG95ckJ2VENZSFlSLXRfdXg5ajNLamo2eFc4a2tTYtIB2gFBVV95cUxPTHQ4Wk9YY1RVMmRpN0JabGNRanRxdVRhSG52OWRFZWJNNFoxTWNGV3pTcWZGLTRmZDVZVWxUTDRMZzB6akYyYUJDUFB5WTU4dlNmTDZVbVpxanVwNGdvWXFpcUtjZDhpblFia19uOTV3UGQyZlRMRzhLcnRacTNqUy01RFhBbW1oNWdLY0pjTkRHY3BHSk5uSWFWUHBZRVFLZlYxWVNXajBBSGdVQVBCOG80NWRHNzdNWlljSGdjcm82eTY5elBuREI5ZUFHQ3QzZVh3QUNYTmRtQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9wFBVV95cUxNTU1TS2NlMGFJZ2RBQ3BOMm8ySXFISUxmMXhLU0dRc1ZreUVrWkhMeEo1Tk1jMG9QRkZIaTRJaG0yV2p1clJtQldNeDZGU2tPenhoZk85dGJpRzFKMjdGRHYteG5FTkVxMkRabnVmNW5rb0Nad19yOE84bXVnUVBJT25pVl8yQ1V6M1pTdEZPRVlUdVF2Wk0xYUxTN01mT1lEM05ZRUdFTFdhQjJvMjBCVzZXR0lCNU1ndjQxRjJ4Ukl4OHJXMk5iYUNsYnF0amYwYlZ1WDJIbnQ0NmNfMU9hVXBWVm81ZHctWnlSc3N6Y3ZVWkVWeE530gH8AUFVX3lxTE1vWVhxd1NqWXFESU1lczdibjJJdW15b0UyZkJSTC1ZVlRFdzJsWWItUGVYN3hFVWJ5TkhwcklqRGkzR21aRXJOME1tSnNFR2VVMGY2Q091TUEyRWRzcWI3UVh4cndMTkRZemdFU1RSRVhwbXR0WGs4UTVoQTR3RXlRbmJGTG1ST3ViMkVrc1p4Z2JOSUs1d1lnUjljTFV1MGFJaHVFQXoyMDhnR0pKS2RlaFhaUnJyU0dWZVp1Z2RUUGlvR0ZPODd3OU8zSHd6VzJfTm9DSGx6LVpsOVNzZzA5LVZNTVZpS0pWa3pBSXVHRWRLclRYWkw3dUt1bw?oc=5</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>16-05-2026 17:02 UTC</t>
+          <t>17-05-2026 02:22 UTC</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Dr. Reddy's Laboratories Ltd stock (INE089A01023): earnings miss and dual-market focus draw attentio</t>
+          <t>KEC International's Q4 profit slumps 28 pc to Rs 193 crore, revenue down</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>The Hans India</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPNUI1bXhqVkhYRHozcnJGOVR4eVNNWm1KRkpaX1cyaGdnNjB4UXBPT3RsVHF6MEEzaUJ2Ykw4Y2hyVEJmUkpWVVZERXhVeklPZzdEdnRWdjgyNEFkYnFxR2dDRGJLWFRYZFl6VDB0MlVRODJrWHdlZHNNWFVZc0g2eERPa0VlMkp0Wk9uY1l2am11VnFfMmRNMmlMTmNIcm9Za1hHcUxicWxyVXBGelZnSmVBUFZSTG00XzdiWTBMcXQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOMlEzODFfam9FQm5ZNEh0cTRJVlU4a04yN3FDbTZnRFlIY21NeFVmdk1MVnQ3S3NTOEJIbFd1MERaVjdObEwwMi16WFJzbnNzQnpvYllqcmNXeUpjWXg3dkxnRkZQLU9ibGZteWlUUFVPTkFHMmwtYWJyT3V3Z0E2N2tyWUVVNnNZWHVFS3JRZ0lpczJYM2ZnelE1OXFacUEzUFhPTnZyYUFQY3lSTGp6WUZsQXVsOG5hZ2R6aNIBvAFBVV95cUxOMlEzODFfam9FQm5ZNEh0cTRJVlU4a04yN3FDbTZnRFlIY21NeFVmdk1MVnQ3S3NTOEJIbFd1MERaVjdObEwwMi16WFJzbnNzQnpvYllqcmNXeUpjWXg3dkxnRkZQLU9ibGZteWlUUFVPTkFHMmwtYWJyT3V3Z0E2N2tyWUVVNnNZWHVFS3JRZ0lpczJYM2ZnelE1OXFacUEzUFhPTnZyYUFQY3lSTGp6WUZsQXVsOG5hZ2R6aA?oc=5</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>16-05-2026 10:27 UTC</t>
+          <t>17-05-2026 08:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Dr. Reddy's Laboratories Launches its Generic Semaglutide Injection in Canada</t>
+          <t>Aurobindo Pharma Ltd. is Rated Buy by MarketsMOJO</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>PharmiWeb.com</t>
+          <t>Markets Mojo</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQbGl0TE9jY3Foam1HSWk2NWxvRzlvR000YWFpSVBWdDhBTVp6a0RJdER3VW5NcVRhRkZaaVh1Q1VDVDllRG1nU21zZy1lVlR0Y3QxSURTZ3hIWkYzZ3hxZk9tVmZRNmlxbndzQTQ1WEkwOWdaLWFPRmdhMUo5NHNBY1paOVI5TjVRZ0NzTTlPbXB4a0xjLXdzNmJLZ2dud01RRDIyRjBBQVpIZHJNZWZmYmFuNEZGM2VnN1lva3laOHB0NFU2?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOei1lTkwtOWNHSXI4TFZzN3RSRng5akJnMEhiSGZxaDJ4TGtJX051LTRqTU9na3RMcm5veFh2bFdCbjE0bUtOZFdaMlVOY21SOWIzY1hTa1JteWJ2dHl4WGpwREJtNG9qRENNb1JtREhxWnZZV2NVQlNHZ0hTRHBkOEpVazRzb0dGREdwSnVVaXh0Nm9LMUFwUVozTHBmOGQyTHJJT2FlNVVreWhOWlNJ?oc=5</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>16-05-2026 10:21 UTC</t>
+          <t>17-05-2026 00:20 UTC</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Dr Reddys Laboratories Ltd Valuation Shifts to Fair Amidst Sector Comparisons</t>
+          <t>Hare Krishna Movement Charitable Foundation Celebrates 10th Anniversary and Completion of 15 Crore...</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Markets Mojo</t>
+          <t>The Hans India</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOS2x1N2I2MjFFT2hVWHI0STR4ZncxQkZKXzMzNXhtdnczNkc2UFVOX0Rsc09zeGhKUG5IOHZmVjlEY0lCOGpIeUx4T3M3ZGsxTmpYeTFkUG1DTWZTX0lzV0VacjljQUVxeUdrT2xiRkRtMDJ0NTl4NEFaOHB2cndpTG94TTVZbTBiblpqY2JZcHZmUGtxbHJ3VEU5MFNoWkRBd2JNd0R4ZzBfeE5nVzItQ3RSckJTZlZQejFSNzJRX09XOFpnbnNJMDlORzlxUUli?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAJBVV95cUxQd2I4STJFQUpJZDNhVnZ0YUNpN0czeFdnSzAza3NaOTdFRVNUMWpfWFhEMjV3UjdxdHhReF9sMUlURVU2MjduOFhoV1pGVTBpcnJMSWJVVmF1NnBBQ1pTblIwQ0ZkUnRhaEk5eEw5RlVBbUFPcHV5anI4SDI4Q1ZJQV9PbnVSVDBkcDNwMWsxUG1adkI2NjhiV2REQ2poQW1nTTk3Q1VmNGtSMTdocERVUHJmWkc3cFl4c1VsNVZvVm1HT3hqQzhSaTYzNmFSZnFrZklpRmVvaDduSkpraUo3Ymd0Q09Zby1sMWw2cEdvdW5JNE0xdFF4d2I5OW55V0FCaS0yRtIBigJBVV95cUxOdlNhOFBXSVRTYUtUWXF0Rllvd3czYUV2ZmpEeko0T2hGX0FrS2pLRjZEdTB6NlIzRnJtbVdUT0hGakxKb0xET0pna2M2VF90WkkwclZDRFNaeHk0YTByWGtKQTBEbUk0TDdma2NJSTN6TS1hcTRGNGJESnFJUnMwWGMxMXBLX0dRcUxZTEJMbk12aTBPN3JlTEZLcmNWczBvZWlDcnBBdkxESWU1UWEyTDhVTDROVzlJUkR0N0U1Q1JmVGFhQXpvRzVjOURSM3dCWFJBYU16LU9Cb1F6QmpmNGQ1U0ZHSTU5UXZYbVM4OWRKRHp0OVB6YkVWTnVSenk3emh1NHQzTnJrZw?oc=5</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>17-05-2026 00:16 UTC</t>
+          <t>17-05-2026 08:40 UTC</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Dr Reddys Laboratories Ltd Quality Grade Downgrade: A Detailed Analysis of Business Fundamentals</t>
+          <t>Excess weight, stress leading to hypertension among all age groups: IMA former president Dr. V.S.Prasad</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Markets Mojo</t>
+          <t>The Hindu</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxPWlAxdU5WTkpfeVVIeHk1MlVkdThSQmlfUTFaaUZwcmVvZXpvNXR5MUNwa0c0dndMdmlTLVRxeHJyNkpIcU9MX1lsTUlKaEpqWkNQXzBGdVJseDNaSXBBek5fVnkzUmRBbG5DSTV3UlBWdDNJUGRONXl4bzRnWTJjdERrQ2llRUYtaU1GOExnbWp3bG80RVJVaTlwamdhTHJTQlRSUU01RGZVWEJJNEZsSVZFdGFaNGp3Z1Z2ZGdyci12QVA1OG9hZzJaS09Kb01fZmJIQVNOdEE2dTQwWTFVWTRZbWdqcF9Q?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxQcUhhZEhZYkZtNXhURElJRVNJR0V5QVFVeGFscEduUC1GRnNyRC10d1pvQmx0Qm5adlBzTnJHZW1NZjd2RFQyd05qbFRnQUdBanE1S2tZRXJDTDVFVHVBeElpVG81aWkwUkdaNXllNFFRUDdvMjJkMHBTVDllUmJQdU80TUJZQUNEY0NsVkVzWjlLTTdzUHplc0xDdzNSLW5NY1BMUjZnSHBORnAxNTVPZDNOWHRIRDAydlFiLXJtak0yR1JNd3VJbnR3UTFuOUg1TExrcFJCSl8xZnVuMkFvVUlKYTFFZGlTWHhxdGJEZFE1RFl6aTVHZjZVVHBfbHBWRFkySFNrNXLSAYgCQVVfeXFMUHFIYWRIWWJGbTV4VERJSUVTSUdFeUFRVXhhbHBHblAtRkZzckQtdHdab0JsdEJuWnZQc05yR2VtTWY3dkRUMndOamxUZ0FHQWpxNUtrWUVyQ0w1RVR1QXhJaVRvNWlpMFJHWjV5ZTRRUVA3bzIyZDBwU1Q5ZVJiUHVPNE1CWUFDRGNDbFZFc1o5S003c1B6ZXNMQ3czUi1uTWNQTFI2Z0hwTkZwMTU1T2QzTlh0SEQwMnZRYi1ybWpNMkdSTXd1SW50d1ExbjlINUxMa3BSQkpfMWZ1bjJBb1VJSmExRWRpU1h4cXRiRGRRNURZemk1R2Y2VVRwX2xwVkRZMkhTazVy?oc=5</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>17-05-2026 00:16 UTC</t>
+          <t>17-05-2026 09:23 UTC</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Broad-Based Technical Strength Lifts Biocon Ltd. to 52-Week High of Rs 430.2</t>
+          <t>Indian Pharma, Tech, Engineering Firms Pledge $20.5 Billion In Investments Across US</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Markets Mojo</t>
+          <t>IndiaWest</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOeXFBYXNUbllGMFlOdllVeVdTbnpvV214ckZpUWJtODVjNktpWVA5UW5Ebnh6SUZqa2R5SmdKRDNUajRQZWo5SWVaZkpWSnRoSzF3SWtrV2xVQVp6RFpnQk9fVDZaNS1rR0ZNS0x1eHhoME9WT21nOHZkclBPczB3S3Jzdkk2T0pMUkhyRkhZOVFvQTVUU0VSZmRmSmNOZ24wTzA3a25DVUpmcEhKNlBXX2FNTml4eVk2dnhuRnR1OG5CM0F3a3dQNDV3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNREoxRU5pYko1aW00NVVwSUNBUzFHRlMtSHphUmRNdjg0Uk1YRnR6WnhPdkFKei1rU2d3UnJhbGVyMkZ5ZG1KLVN4anZjb0xjd0R1TGJZTTgwbFNtRVM5a21hY2xHamJkZW8zRm96SjlCTmNCMEl2VFVkQ2k3TFVDaHNoQnZZclBSSlFlREh5WWFTX0d1WVZ1ZnA0YXZoaFAwODVtNGdvVQ?oc=5</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>16-05-2026 11:51 UTC</t>
+          <t>17-05-2026 10:43 UTC</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ETFs Investing in Biocon Limited Stocks</t>
+          <t>HKMCF marks a decade of service, serves 15 crore meals</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>metroindia.net</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiYkFVX3lxTE05UUdIX3ljdGprNU5TUTM5QkFzenRkMU9pdjZwZGRHcld0bEhIczFmRHF6V2lGaUpKbWNIYXhiR19lT0lUclk2MGlSZTIxaUxDTndXVUJTUzlXckhSdThOSGlR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNd3BCVVMtdFBaVWRtNU41YjJqZWI3UlVISFN0cF84TGRpSXQ5UHptTkdabUhGNlMzd0c1UTBzYWtMazBuZXBya2tGX1JpVWMtMDI1TWkwTzVZSGZiZWQ1cjYwQUdpb2RnaTdEMmJ0QXZ1d3VUMkJWSV9yMkVhRHlNbEM2SlV4c1ZONXRJeHRrdXozVGFVTW5zbjBqbVViX3g2T2c?oc=5</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>16-05-2026 13:49 UTC</t>
+          <t>16-05-2026 16:06 UTC</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Biocon Ltd. Technical Momentum Shifts to Mildly Bullish Amid Strong Returns</t>
+          <t>Samsung Electronics Announces First Quarter 2026 Results</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Markets Mojo</t>
+          <t>samsung.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPLW1ETTJ4ODU3dTNhcUlnTmhybjVuSDNfVWU0X2h0NDF6U0tlOHp5WDFMZXpxcVZ6Q1BTM0dyZWNvdXVfb2hONngtb253ZV8zZ3BYekN2OVdPZlJHRWc3NUJYb0p0c3lac3pvYklmUkJFT3BYRGJYLTB3eWJxM0lad1pKRXRkU1FhWkdyWnNuY1dHbWU1eUJVUnRsalQ0dlhGLTVJcHYzcUFfR2NXZFVncDJlOUhrOGUtVTUzZ3VOQ3Y5dkwyQ09KLTI5MHo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOWUVwY3RuMVpmN0E2LXdudkFMWjl3VjN6MWp3Vnk4VUUzTnkzdGVRNi0wWXN1MnpRODQ2c0RGWE9Wbjg5Y0RfejdZZUVjZGJGdi1GdDVCdzlzWjBNU0hQbVVtTGJab3lNakR2S1RKSzdOVTVrVDZVV0xoWU45ZFFoVjVZUDdsTTRqai0tVQ?oc=5</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>16-05-2026 11:41 UTC</t>
+          <t>17-05-2026 08:15 UTC</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma Ltd. is Rated Buy by MarketsMOJO</t>
+          <t>A 45,000-person labor strike at Samsung's memory chip plants could throw a wrench into the AI boom</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Markets Mojo</t>
+          <t>Fortune</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOei1lTkwtOWNHSXI4TFZzN3RSRng5akJnMEhiSGZxaDJ4TGtJX051LTRqTU9na3RMcm5veFh2bFdCbjE0bUtOZFdaMlVOY21SOWIzY1hTa1JteWJ2dHl4WGpwREJtNG9qRENNb1JtREhxWnZZV2NVQlNHZ0hTRHBkOEpVazRzb0dGREdwSnVVaXh0Nm9LMUFwUVozTHBmOGQyTHJJT2FlNVVreWhOWlNJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxORXlCa0gyT29UdjdaZVRtVklHc2RlLTBNOWhYNEZXdEZpVFhHTTNuVzF1Qy0tYk9ZRGhuMlpkd0NQZW1DM3BUYmJkTFVrblctX2c5MkhJV1F6QUlUXzNXTFl5Y0o1UWlwT2xhN2FOd1h4cXBWbnhiV2tIU29PWnlhUTZZNTFTUjRRU3hWNXhlNUxaNjEyT3VV?oc=5</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>17-05-2026 00:20 UTC</t>
+          <t>17-05-2026 09:03 UTC</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Hare Krishna Movement Charitable Foundation Celebrates 10th Anniversary and Completion of 15 Crore...</t>
+          <t>Samsung Galaxy S25 Ultra now available under Rs 93,000</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>The Hans India</t>
+          <t>India Today</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAJBVV95cUxQd2I4STJFQUpJZDNhVnZ0YUNpN0czeFdnSzAza3NaOTdFRVNUMWpfWFhEMjV3UjdxdHhReF9sMUlURVU2MjduOFhoV1pGVTBpcnJMSWJVVmF1NnBBQ1pTblIwQ0ZkUnRhaEk5eEw5RlVBbUFPcHV5anI4SDI4Q1ZJQV9PbnVSVDBkcDNwMWsxUG1adkI2NjhiV2REQ2poQW1nTTk3Q1VmNGtSMTdocERVUHJmWkc3cFl4c1VsNVZvVm1HT3hqQzhSaTYzNmFSZnFrZklpRmVvaDduSkpraUo3Ymd0Q09Zby1sMWw2cEdvdW5JNE0xdFF4d2I5OW55V0FCaS0yRtIBigJBVV95cUxOdlNhOFBXSVRTYUtUWXF0Rllvd3czYUV2ZmpEeko0T2hGX0FrS2pLRjZEdTB6NlIzRnJtbVdUT0hGakxKb0xET0pna2M2VF90WkkwclZDRFNaeHk0YTByWGtKQTBEbUk0TDdma2NJSTN6TS1hcTRGNGJESnFJUnMwWGMxMXBLX0dRcUxZTEJMbk12aTBPN3JlTEZLcmNWczBvZWlDcnBBdkxESWU1UWEyTDhVTDROVzlJUkR0N0U1Q1JmVGFhQXpvRzVjOURSM3dCWFJBYU16LU9Cb1F6QmpmNGQ1U0ZHSTU5UXZYbVM4OWRKRHp0OVB6YkVWTnVSenk3emh1NHQzTnJrZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQbVM3YXE0VksyNlA4d1YwdWhGU1EtZ0lDamlzLThpSTJwWGd3emd3WnZzN2tSZUtSYzZnNzlUYXdLak1ZZXZDckc1VHB4anBNUEFiNmVKTEpQdjVQXzZWbHZ2QTFkenRJREc1QVZLRUY3eUp4bVlaa1k2bEtLUWFPeGVnendjTGZtSWpvU01vVDYxRWtyS1d3RWYxUVI0V2xUM0JFQ2JKRVZLVFZ2NGw1ZDltbzdMOUZCMXNvdGk5d9IBvwFBVV95cUxQbVM3YXE0VksyNlA4d1YwdWhGU1EtZ0lDamlzLThpSTJwWGd3emd3WnZzN2tSZUtSYzZnNzlUYXdLak1ZZXZDckc1VHB4anBNUEFiNmVKTEpQdjVQXzZWbHZ2QTFkenRJREc1QVZLRUY3eUp4bVlaa1k2bEtLUWFPeGVnendjTGZtSWpvU01vVDYxRWtyS1d3RWYxUVI0V2xUM0JFQ2JKRVZLVFZ2NGw1ZDltbzdMOUZCMXNvdGk5dw?oc=5</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>17-05-2026 08:40 UTC</t>
+          <t>17-05-2026 11:07 UTC</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Week ahead: Nvidia earnings, Crude oil, U.S. bond yields, INR weakness and FII flows in focus</t>
+          <t>South Korea says it will pursue all options to avoid Samsung strike</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Upstox</t>
+          <t>The Hindu</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxPSkRWbi1iSm95R21CeXczc19BZ2pTd29zaXJXQkhBMVVqZmNQOE8tM2pDbDlNdmtKckdtN051SHRrR283QXE2NzRWX1ltQm1CdGJyQUVlbEljdm5EbllUYlo1UFpwdjlLNkVGb2M3b011SlZuU2VQVEVTQUM1VXlmM29VTkROVGhiWWlPdVNQYUZFMU90RGVxZFoySGlqcEN2Nm1aUDRWMGpaR2ZzWjVRWk5ndWxteF9NUEFqaXYtLWxhX2lEOGJNVl9YeXkwdHBUWW5vMFN3d0hxRnBGbUg3R3RR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxOTzZqYUh2RnNyQm1YZFFmVUZYYUJHQy1yQ3VTbGZMTWVjSnBkcGFpeTZ0WE9mMWhhMGY1U052NjE3YzFWQXdQWGN0Sk9WNGMxM0x1ZjNOWm41aTduS2V6Q3QzWUhGMEpXR0JLYnRmdU41eDRmUjM2VjRTdEFRZExMRmFlMmtoYzJPUHlqYm14WVBxTDg1Y0lHX2tUQlZFUVNmcWRyS1RQQUNoWGZJUzFZTUlhZDkxX1o3NGtHZ2ZZMTdHYVlWNW56WC1BMk5kUHRfUGfSAdIBQVVfeXFMTk82amFIdkZzckJtWGRRZlVGWGFCR0MtckN1U2xmTE1lY0pwZHBhaXk2dFhPZjFoYTBmNVNOdjYxN2MxVkF3UFhjdEpPVjRjMTNMdWYzTlpuNWk3bktlekN0M1lIRjBKV0dCS2J0ZnVONXg0ZlIzNlY0U3RBUWRMTEZhZTJraGMyT1B5amJteFlQcUw4NWNJR19rVEJWRVFTZnFkcktUUEFDaFhmSVMxWU1JYWQ5MV9aNzRrR2dmWTE3R2FZVjVuelgtQTJOZFB0X1Bn?oc=5</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>17-05-2026 05:34 UTC</t>
+          <t>17-05-2026 08:26 UTC</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Led by pharma majors, Indian investments in the US at record high</t>
+          <t>I removed Samsung's unremovable apps, and now my phone zips along</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Fortune India</t>
+          <t>Android Police</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQQWItUXhzVm9ZR1RFWHNJM2ZvcEQ1dHB2Y3VCQ1B4bTNXNWUyTU1mdDdhaUc0OXpqY0FrdEx4ZmJfT05pZUJfSTlJZ0o5ZDNmQVFra1MtQ1pNeWt3ZnhHWGhBMGhUZG1ZWkNZeXNFWUp4a0I0ZXd2aGk4aGNBY0hyTHVoY25yTHFXQmF4NHp1NDAxemJpTVJwS3dtRGZnM01TR3BnX21ZbUY1NHlI0gG6AUFVX3lxTE9fY3R4dUlhdTZwXzN6OEZXMmpiTVNsUVJSblZJaENFcW55a2FCTndQQjdac24tTGNyMDE0QUZQV01QbnpQNzgwVFlkc0lKNU1NaHdIOW9xejlVT013MnI1MXBUMm9GNlQ4Z3FDc250bEFDX3FIT0xuaDgzYWF1ZE5oYUR4bFhaSXJxdzc1NzF5Y0dlanhmWWc1T2FKSzdXd3kyajBEN2VES0gyck4yeXVtemV6ZGU3a1pWUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxPeW5XRExSbmp4RW9vMEVDYTNjS1FPVklVU2Q2anlVQVA1OVI4ZFg0aVVnMTRoWVNzdFlvTnUyWjBvaDhFVmhubHBGejVZd0h0T3pBcWhhQlJXSVFQU2lza3VEVmo3ekswb0F6UWt1UFAwbEE3TDNtTDFlNDdTRG9pbWxVUWtseWRIeUdCZjh3?oc=5</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>16-05-2026 09:44 UTC</t>
+          <t>17-05-2026 11:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Emcure Pharma Plant Faces FDA Form 483 Amid Strong Results</t>
+          <t>Samsung Galaxy S26 Ultra: Best time to buy in 2026 – March or June?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Whalesbook</t>
+          <t>Sammy Fans</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNMDJpUFdYLVl5ODZSRjNOdklERzFqTEd3U3FiQWVVakJUVVI1TGIxS09pM2JhUHMtZ3RBVVJzd0ZGb0ZXZnoyZzYwVnl1VzRBa3gtVUZWZE5GamdOSTlueDVxdXdBV1d2aW5QQzk0UlNNdjE1UmtwNUp4M0tDLTd3MTJoaU5tdHpBelJjQmV5bExfc3JtTEdNWEVWQkdQTUV4MENWMHozYnd6Qk9MT1N4Y09rZHpQVkdOTnZGRDNXNHl3TDN0Rk50ZlZqWnd6SWcxUk9EZElSWWM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUjBDNDJ3eW9aQmJidG1zTkNyQjZSTVBpeE54TzJfSXJaMWxEMnJKZlJGZGlXNnpMRFphRFdndlJBWWpKclp4MFNnakVBN1lBaGNkTmNBa04tVGhGOVJlbmpadjFUMDBnbUtPTUNzVUFLXzl1RC1BU0xGaVR0VHdpZUJ5QTVvN0tUcE5mWFVNUDJ4TGdoYjlRcDBRV0drVTJqbE1z0gGoAUFVX3lxTFBVekNGN2p3TlZHazJTMm01Y2xFbU1xbkFMZlluX0hZMVNYeEtsemlHdGxLNERfYy16UHFXZWs3bDQxaEtMWXZPb2NMc05DTW13X1l6T0drQi1yaE9TaGhnTVRaMk1TeDBrV2xsQmYwWEFRWWhxOFh6VEstRUVONzc4Z0MwRVJzMGhrWHI0T09pQ2RJbldFb2drbnhrdkF5WkhRUWRIM193VA?oc=5</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>16-05-2026 10:51 UTC</t>
+          <t>17-05-2026 07:45 UTC</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>HKMCF marks a decade of service, serves 15 crore meals</t>
+          <t>Samsung, labour union to meet in a last-ditch attempt to avert strike and upheaval in semiconductor industry - CNBC TV18</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>metroindia.net</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNd3BCVVMtdFBaVWRtNU41YjJqZWI3UlVISFN0cF84TGRpSXQ5UHptTkdabUhGNlMzd0c1UTBzYWtMazBuZXBya2tGX1JpVWMtMDI1TWkwTzVZSGZiZWQ1cjYwQUdpb2RnaTdEMmJ0QXZ1d3VUMkJWSV9yMkVhRHlNbEM2SlV4c1ZONXRJeHRrdXozVGFVTW5zbjBqbVViX3g2T2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOMU9kenNROWhodjNyaGJkeXN4b0lPQUR6TF9kRTVtZFpvWW03YkRMS25DU2NXeENZcTM4RDJOd3JTR0prODI5RVdtZ1VYbmtTa0NZelI3eEt1a1V3NWVSZ2NrNVUyMWVHc2JZa0x3b21yTGtwdE4tY1pFWVEyZkJ5QXdBT3d3M3JRUkhxTndDZXhpQUdPV1RJempMeGtXR3VQajIwYTZfYmwzTExyNmF2UFhNbFp0Q3FQTWVr?oc=5</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>16-05-2026 16:06 UTC</t>
+          <t>17-05-2026 08:43 UTC</t>
         </is>
       </c>
     </row>
@@ -2380,22 +2380,22 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Samsung, labour union to meet in a last-ditch attempt to avert strike and upheaval in semiconductor industry - CNBC TV18</t>
+          <t>South Korea says it will pursue all options to avoid Samsung strike</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>CNBC</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOMU9kenNROWhodjNyaGJkeXN4b0lPQUR6TF9kRTVtZFpvWW03YkRMS25DU2NXeENZcTM4RDJOd3JTR0prODI5RVdtZ1VYbmtTa0NZelI3eEt1a1V3NWVSZ2NrNVUyMWVHc2JZa0x3b21yTGtwdE4tY1pFWVEyZkJ5QXdBT3d3M3JRUkhxTndDZXhpQUdPV1RJempMeGtXR3VQajIwYTZfYmwzTExyNmF2UFhNbFp0Q3FQTWVr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNVDUwX0hJLUZieVpweGlSZjc4ZFNKdnUyb1JSdExWMnRvaVJObkZLUXQ3NVZxVWM4WTVXR1FCemx3d1oxTXlKaUZtQ0UxUmV5YXRfc0pBLWVXRl9EOWFCMVNnNDNKWjMxY182QkdoNjlwLThhcVkxdzV6MmRQVUo5ZEZPNU5hakhoMVlPOFIyekNpeVloN014MWtfajhSMTYzZ2lDcUEyONIBrAFBVV95cUxOdDdUS2F2QnEtSXJyWi1LTXpMVHlQWUdUYnBzS2RKb0VLY1Z0OWQ4QnZ1RktQbWtfR05ZaUNFdXY1UWxROEQxSkJjNEFBNk5Mb0Z4eG5VcmpvY3J5ZWZjTkNaWDNnb3MzdXczRnNJbGtXQ0otN1NJcURKdG9YZi1vdmF2UnJyci14Q0Vrc3dfdGhPOU1sUDN5Wjkydl9ZNzhyeDZTLS1SaWc4aUxy?oc=5</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>17-05-2026 08:43 UTC</t>
+          <t>17-05-2026 05:47 UTC</t>
         </is>
       </c>
     </row>
@@ -2407,22 +2407,22 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Samsung Galaxy Watch 9, Fold 8, Galaxy Glasses to debut at July Unpacked event, leak reveals</t>
+          <t>South Korea says it will pursue all options to avoid Samsung strike</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Mashable</t>
+          <t>Reuters</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPck54TENxQzE5dy1kQWNJaXhyeHNxUWhab3NFaW05VnpaaU9vNUpMa3RqV3RacGVJaHduZHE1OXJqVmJEb3ZuVGU4dkEzb0JhWld5REpkVWxjdmtFREhMN0lDNFpWc0ZkNlZTRWtZZWE5ZXRhOFRsVFBqSFdIa0cxX2RLaWM0VGZ5?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNTGlHR0pfeEljcmtyQlg1YnkzUGRjNUViWUpST1V6anRicXRzRDdaa1FzTEl4UlFpWGo0YlJWOVhMVU1MS1JBYjkzRk5TSDctMDNJa1ZBRG9BV2psRjBCVVlYT080a0JGUE85dFprRTBVUGNFbVo3R2lXRVRiR1JURXdzeHdLWElneXROM1J2MHVra09vOXRaaFcyWmJPbkw5ajJ5V0VTVnV3S3ppbDBIX2tNbkN5d1lBRmtZNVEwSFM?oc=5</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>17-05-2026 07:50 UTC</t>
+          <t>17-05-2026 04:04 UTC</t>
         </is>
       </c>
     </row>
@@ -2434,22 +2434,22 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Samsung and Qualcomm Achieve Industry-First Power Class 1 Validation for 5G Fixed Wireless Access on Virtualized RAN</t>
+          <t>Samsung Galaxy Watch 9, Fold 8, Galaxy Glasses to debut at July Unpacked event, leak reveals</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>samsung.com</t>
+          <t>Mashable</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxPZnRTSlZlY2hWUFhMTklXQjl2bVdmQW00LTBIYnc3QzBSVEYxcWZ1UDR1MmRXdHpac0EtdXpWRVdxUUJnWTU4ODNKU3lQUi1ZZV82b1pWRkg1eTBpZ245VXlESk9RdnczV2h2enRDNFZyZS1ZdXdKQmQxOEJkYm5XN3J2UDIzM0lyRmhNNmxmcFhzbTFqV2ZHeHYweGtEaWNQTDhaYjRmMTJrVkFLRVpLUlJ2VWtzM2tGTkxLdFBGTGw1SFNvczdCNXh1RENjVjJDWjRpNXNTOGo1R0JO?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPck54TENxQzE5dy1kQWNJaXhyeHNxUWhab3NFaW05VnpaaU9vNUpMa3RqV3RacGVJaHduZHE1OXJqVmJEb3ZuVGU4dkEzb0JhWld5REpkVWxjdmtFREhMN0lDNFpWc0ZkNlZTRWtZZWE5ZXRhOFRsVFBqSFdIa0cxX2RLaWM0VGZ5?oc=5</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>17-05-2026 05:26 UTC</t>
+          <t>17-05-2026 07:50 UTC</t>
         </is>
       </c>
     </row>
@@ -2461,22 +2461,22 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>South Korea warns of emergency action, says it will use ‘all measures’ to stop Samsung strike</t>
+          <t>Samsung, labour union to meet in a last-ditch attempt to avert strike and upheaval in semiconductor industry</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Firstpost</t>
+          <t>CNBC TV18</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQcno2eExGQVNkMHR3V21tanNyVWhaS2hrSkI5S2JHSzA1TmRwWTJRdUxNQjhWRWxQcUt4ZFFXS2s2N3dCR3F4Y1hpbkFqbnlGNS1nbnJ3NVg2TF9NcjREREhDTTM1SDlBbXlYVDhyNWdJTkpCNHhXLUFtTWctNkRhamNDVTdLeHFXYzB0X2NLR1FrY0ZxZUlldXVaT2pMWENkdE1TWnRFT3FCcWZITDl1NGFZM0lsdlJKTVdHUmxMVmlROFhZZUF4d3BjTkhWc2FXWUHSAdcBQVVfeXFMTjNnSEF3d3Q5OFFfNWJ4M2gxWElQM0toZG5LYzBiOGJUUkE3MlhnNTJVOUZUanhZQlBSZEZ1cHM2NVdoOHhEZTVVVVBTZWJZYVRQUzBDbkFMR2FnTUF4NGpXWGdOakdZYWUtVmZ1dk5WTGRDV2Ewdk43eThNV0lXWEd5ZXowMEhoTEdvMm9sazdOQjYzM0NsNFk1TXhJOGFocHZCM3d0VmViX0c1M2Z6Q1ZwV0hSMVUwcV80LUsyR0Y0SzFwVl91UVVvMGNuU2Z2UWtSMWxOcVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxNbmxaOFVkQ0I4SzJkZS05WlB4SnZKNE10SVVCMHFVQ2RzRVNUd05vSVFuc2tGWkFvOG9nVjVqNG91UEtwM3F6QUFOYk84YjdVQ0xSMHFlT0JZTzNlTG1KU01FVXFiOVBMOVQzTU1CVHBJRDR0eG9qZExudHhVZkV0ejM3eC01Ni1JZ2liNW1FS2U3UUUyTE1kRzdZQXViZm9DN0hnTEtLRzh4MENMU0dVbng2N3ZNTF9GV2ppV1JWNENoTWRMWm16SE85V3hvZzlhNk9pVnlJNThxaW1MWDZIdzdTQjl3MFc2UmNJVGVXc1HSAfYBQVVfeXFMTzQ1Zlp5UzlYeGYxZTZmRjNKU2gzeDBFWmVyM3FreUp5TmlldXVEWE4zWjIxb2tnallkaUZ0Qi1yVUEweFA2bmc3c3VmVXoxdG95NjZIa2pqYzdnWjAycXhxYlVuMWN1SE5DN3hJamc3YURfRXFFMmhMS0lFdGxFYzNmVmdRaDlWNlBlNmNsUEVTdFN2bGFzWkFsRVU4dTlKSnFvRzhQcDAxeGxlOTM0TDh5amxoUVlHdnNQMFZOVUh6Sm5MeHVvSkpvRzc4a2dxUy1VaTVjeUJ6dkFvXzd5VWU5MThfemJPTW5kSjVWWjczdUUyNkNn?oc=5</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>17-05-2026 08:02 UTC</t>
+          <t>17-05-2026 08:10 UTC</t>
         </is>
       </c>
     </row>
@@ -2488,22 +2488,22 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Samsung, labour union to meet in a last-ditch attempt to avert strike and upheaval in semiconductor industry</t>
+          <t>South Korea says it will pursue all options to avoid Samsung strike</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>CNBC TV18</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxNbmxaOFVkQ0I4SzJkZS05WlB4SnZKNE10SVVCMHFVQ2RzRVNUd05vSVFuc2tGWkFvOG9nVjVqNG91UEtwM3F6QUFOYk84YjdVQ0xSMHFlT0JZTzNlTG1KU01FVXFiOVBMOVQzTU1CVHBJRDR0eG9qZExudHhVZkV0ejM3eC01Ni1JZ2liNW1FS2U3UUUyTE1kRzdZQXViZm9DN0hnTEtLRzh4MENMU0dVbng2N3ZNTF9GV2ppV1JWNENoTWRMWm16SE85V3hvZzlhNk9pVnlJNThxaW1MWDZIdzdTQjl3MFc2UmNJVGVXc1HSAfYBQVVfeXFMTzQ1Zlp5UzlYeGYxZTZmRjNKU2gzeDBFWmVyM3FreUp5TmlldXVEWE4zWjIxb2tnallkaUZ0Qi1yVUEweFA2bmc3c3VmVXoxdG95NjZIa2pqYzdnWjAycXhxYlVuMWN1SE5DN3hJamc3YURfRXFFMmhMS0lFdGxFYzNmVmdRaDlWNlBlNmNsUEVTdFN2bGFzWkFsRVU4dTlKSnFvRzhQcDAxeGxlOTM0TDh5amxoUVlHdnNQMFZOVUh6Sm5MeHVvSkpvRzc4a2dxUy1VaTVjeUJ6dkFvXzd5VWU5MThfemJPTW5kSjVWWjczdUUyNkNn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxPVlVvYlZubU1TMjFGTDJJSWMxbjljWjZvSWxuLUxNRTVMeDJlWFhETFVtcGQ2VE5SRjl6aUt6TG9GSnhfaW8tR2VQWXcybm1ZNFBqWFFOcHJaSUc2RER1MnN1Z3pTMkRIVHJqbHdEd0pkNi1MdnZvc0xWS05sWTdUV3ZFMDM4VEpqcTA1eGg3WDlFRVJqVjFkbThfM3gwbElGQmF1WTlXWXdvUzF4MFlQekFLUlBjTkZCSkJEY0x0LWN5c1hzMS1PaDlpYmxrXy1KN0xaQlVfeE9hVmltWXJxVlJhcERuWTVYaFNN0gHrAUFVX3lxTE9WVW9iVm5tTVMyMUZMMklJYzFuOWNaNm9JbG4tTE1FNUx4MmVYWERMVW1wZDZUTlJGOXppS3pMb0ZKeF9pby1HZVBZdzJubVk0UGpYUU5wclpJRzZERHUyc3VnelMyREhUcmpsd0R3SmQ2LUx2dm9zTFZLTmxZN1RXdkUwMzhUSmpxMDV4aDdYOUVFUmpWMWRtOF8zeDBsSUZCYXVZOVdZd29TMXgwWVB6QUtSUGNORkJKQkRjTHQtY3lzWHMxLU9oOWlibGtfLUo3TFpCVV94T2FWaW1ZcnFWUmFwRG5ZNVhoU00?oc=5</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>17-05-2026 08:10 UTC</t>
+          <t>17-05-2026 10:58 UTC</t>
         </is>
       </c>
     </row>
@@ -2515,22 +2515,22 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Samsung's Disappointing New Galaxy S26 Ultra Price Drop</t>
+          <t>5 big analyst AI moves: PT hikes for Samsung and SK Hynix, AMD downgraded</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Forbes</t>
+          <t>Investing.com</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNRFRPcjFzektJTmNuc3EtX1R0a184QkZBS3dVMGpvaVlBT0NBQ2dhU2w0b3hfMC1pTUxOdWRjVGFuREFyTW4zSmw0dUZVQ25ta2RUSU5SUjR3WTUtaGZBeDRWVFNWNHZ4b1U5eU1HTzJ4LTM0WmUwbmRVNU0tVGtKUG5lV1J3V3FwZldzNDFHcGg0N0lOMGNKVUJxWV92VUtCYk1ycl9kNGJkWDA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNZndZZGttOWNVUW4xcnNMQkUtenQ0aUZ1dkREZHJGYXEtQTFLM1N2ZS1lZUZNb0F3MWVZTEdpNFlVeGdxa2l0YlJJTVVOX0JMTjF2eGdrUzZ1OWhRTzVBVzhBeUsyM3BjQTVPWVByV0NlNU1zakhrODNrMjBhLTcxb0Uxck83dGxWZmFZVm9nVUtENUV1cE1hTXFTNnNfZDhmR2ctb3JEWGp2STM5VTc3d0RyZnl1QUtkVno3ejJOeFM3Q19GM0N3?oc=5</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>16-05-2026 18:06 UTC</t>
+          <t>17-05-2026 09:02 UTC</t>
         </is>
       </c>
     </row>
@@ -2542,749 +2542,533 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>South Korea says it will pursue all options to avoid Samsung strike By Reuters</t>
+          <t>South Korea warns of emergency action, says it will use ‘all measures’ to stop Samsung strike</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Investing.com</t>
+          <t>Firstpost</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPREcxajFNbWRQUWNfdUZUbGkxd09SNG9XcmNGdXpfb1RwenhCWHhjMjhRb0hSTm9iQXBtM0dVSHg2em9Cc242TnlZXzlkNlgzVldHeEJsWHFNVV9zVy1GZGJ5dXdLaEdPQllXRFJvYjdGdFhJeG9WX01SdmFHVnctUmV3VXo4NXR4ajlTYk1PTllCaTRhMUlERzFOQ1liUzZabGdMR0VDNTVvNEkzYjB6dHZYM3ZWT0J0VXNGc1Mxcm94QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQcno2eExGQVNkMHR3V21tanNyVWhaS2hrSkI5S2JHSzA1TmRwWTJRdUxNQjhWRWxQcUt4ZFFXS2s2N3dCR3F4Y1hpbkFqbnlGNS1nbnJ3NVg2TF9NcjREREhDTTM1SDlBbXlYVDhyNWdJTkpCNHhXLUFtTWctNkRhamNDVTdLeHFXYzB0X2NLR1FrY0ZxZUlldXVaT2pMWENkdE1TWnRFT3FCcWZITDl1NGFZM0lsdlJKTVdHUmxMVmlROFhZZUF4d3BjTkhWc2FXWUHSAdcBQVVfeXFMTjNnSEF3d3Q5OFFfNWJ4M2gxWElQM0toZG5LYzBiOGJUUkE3MlhnNTJVOUZUanhZQlBSZEZ1cHM2NVdoOHhEZTVVVVBTZWJZYVRQUzBDbkFMR2FnTUF4NGpXWGdOakdZYWUtVmZ1dk5WTGRDV2Ewdk43eThNV0lXWEd5ZXowMEhoTEdvMm9sazdOQjYzM0NsNFk1TXhJOGFocHZCM3d0VmViX0c1M2Z6Q1ZwV0hSMVUwcV80LUsyR0Y0SzFwVl91UVVvMGNuU2Z2UWtSMWxOcVE?oc=5</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>17-05-2026 04:11 UTC</t>
+          <t>17-05-2026 08:02 UTC</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>A 45,000-person labor strike at Samsung's memory chip plants could throw a wrench into the AI boom</t>
+          <t>Korean Pharma, Biotech Firms Post Strong Q1 Sales While Profitability Diverges</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Fortune</t>
+          <t>thelec.net</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxORXlCa0gyT29UdjdaZVRtVklHc2RlLTBNOWhYNEZXdEZpVFhHTTNuVzF1Qy0tYk9ZRGhuMlpkd0NQZW1DM3BUYmJkTFVrblctX2c5MkhJV1F6QUlUXzNXTFl5Y0o1UWlwT2xhN2FOd1h4cXBWbnhiV2tIU29PWnlhUTZZNTFTUjRRU3hWNXhlNUxaNjEyT3VV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE9oZ2hxeXJ6VS1PZTR5SEFSQnUxbm4xQUZjOGFOUHVNbVU2LTVjWXZPcnJWdmY5TkRNTWJHY1FRM1RPR0JHdGk3NGFqelVLSEZZV1VnZ3VBTHZERkRpb1FoWjNyc3lNRVE?oc=5</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>17-05-2026 09:03 UTC</t>
+          <t>17-05-2026 11:47 UTC</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Samsung and labor union to meet in ‘last chance’ to avert strike</t>
+          <t>Alteogen Enters $13 Billion Eylea Biosimilar Market</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>The Japan Times</t>
+          <t>aju press</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNTGFHTmx2NEl0LS1XX2c1bzIyemQ5YWxWQmtRUTM1OGU1VTRRV3l1eUsyQlV2MG9fVHdlQkdyZVczS3FJU1JETEdUdWkwNXlSTUZhcXozM1FaS1NlQnlyNUVNSy16SEdNb0J4eEtoeGlmbkFOZXJFNjJjcnlHUHMzdg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE9hMnlockpJX1l4OXhHVkRrMTE2bXVrLUtYNWpWZmtXZ2J6VHJmcm9PSnNoVXBDaUhyMFdKZW5KWnhUc3gzVlpjdmgxdlpkeTA2cE5BUTVaZmhkQU3SAVdBVV95cUxOTzJ4djgtR3VRSGtqZEdqOW1xbVBPaktfbjZ5dVo3TWFvODlkUlhvVkpxREhHbWt2ZzZLbjU3dW92WkF1ZFh4S3hYN1hOa3praEt0TVhXamc?oc=5</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>17-05-2026 07:30 UTC</t>
+          <t>17-05-2026 08:46 UTC</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Prestige Biopharma</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Samsung, Labor Union to Meet in ‘Last Chance’ to Avert Strike</t>
+          <t>Seo Yang-san (pseudonym) who gets his golf club out of the trunk of his car after arriving at the ap..</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Bloomberg.com</t>
+          <t>매일경제</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOLTJPX2FQYU1aWVAtbWJpZVJwU0JWeVNLYW4zOU5ZcXBPY0stU3Frd3dmZERrNnUxVURJRWhYUU1PUGhRd0RMcEV5d3kwMGQ1Um14ZmZJQVQtbmtTcmltX2hPNDdVVWhpRkpGRGVadWVZY2o2dFZWaHptczMtaElrXy1YS3JabHlSYlRsblhfMU54LXhMcms5MDAtWmU0Rkh4SV9ObUo3ZzFPc1F0V2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE1RWTZ4MzBKRUEzQXhKSllWa0s5ZU1Da0xUVVRpOWlUb1BiZi1QREVueU9wVmdMZXJ3cDhWeENRMmd4bFRUS2FTUVRzTmwtR1BsbVdLM3FVS2U2UEVM?oc=5</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>17-05-2026 06:20 UTC</t>
+          <t>17-05-2026 07:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Prime minister hints at compulsory arbitration over Samsung union strike</t>
+          <t>FDA greenlight for Enhertu in two new indications</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>The Korea Times</t>
+          <t>The Pharma Letter</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxNU1g1dlRZTklIS1N1bEFoRmtVZ2gtYzFQaXNNUXVVTVFpaUY2TFlpZ09SY01jRlRQeUZQNGN4Q1BvVVE5YzJiU1NJSjZZNk5JbTF3SHdYVDkzc0Z5ZEMtWVdDZjU3aTN5Y1psNEh3NVJXOEFoaGJrbTREUnFuS3BQZzF0QUUzUHl3NE53U1BjLUhPY2VtdWxYWGU1WUVoRmlGRzJ1VHkxMU1nQ1EyNXRncjByRTFGSXl4NEhyazgxZHlRZXRRRm1RRTdUbGVTQdIBzgFBVV95cUxNU1g1dlRZTklIS1N1bEFoRmtVZ2gtYzFQaXNNUXVVTVFpaUY2TFlpZ09SY01jRlRQeUZQNGN4Q1BvVVE5YzJiU1NJSjZZNk5JbTF3SHdYVDkzc0Z5ZEMtWVdDZjU3aTN5Y1psNEh3NVJXOEFoaGJrbTREUnFuS3BQZzF0QUUzUHl3NE53U1BjLUhPY2VtdWxYWGU1WUVoRmlGRzJ1VHkxMU1nQ1EyNXRncjByRTFGSXl4NEhyazgxZHlRZXRRRm1RRTdUbGVTQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPcy1WcGMwX2lWYXNXSVVQVDlvRmhxYnlaTVJtSUh6OE9qcFdtS2lmZlY2U25mZFlZdlNscXN1cWtLLWZ6U1kzQkhCeUJvUUVQS01NdFVMZUFQeXFMaDdXdEFJdWNRREhWTzJJVVZsejJ3LVNJeUFKOW9mY3ZOTnppX2paSWZUYWFDVnU0OXp1T3RGYjVVdjhtY1V3?oc=5</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>17-05-2026 06:43 UTC</t>
+          <t>16-05-2026 19:18 UTC</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Samsung Electronics Announces First Quarter 2026 Results</t>
+          <t>AstraZeneca plc stock (GB0009895292): FDA nod for Enhertu keeps oncology story in focus</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>samsung.com</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOWUVwY3RuMVpmN0E2LXdudkFMWjl3VjN6MWp3Vnk4VUUzTnkzdGVRNi0wWXN1MnpRODQ2c0RGWE9Wbjg5Y0RfejdZZUVjZGJGdi1GdDVCdzlzWjBNU0hQbVVtTGJab3lNakR2S1RKSzdOVTVrVDZVV0xoWU45ZFFoVjVZUDdsTTRqai0tVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxPSEtXYW5tcDh6UUFzX0JBQ3Z6em9oRWlMSjNGUGw2dk80dWhqakl0cmQway1EUm5UX3BQckx4cFhBMmpGWnllekFDbVJ2T05Ec0cwMk5QejdBM3lOTW1vcnh5MHJQOW1UQ1piQ1NRajJucWR0UTdYNzFjWE41TElvaTgwR010YUpqODNRTk5zeERWTG9JNXVvWWYtNHhvQ1hZQmRmZTlPRkNFYTQ4NFVzRkJLUmNHM0NURk82YzhtVmRhS3hsUWRB?oc=5</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>16-05-2026 16:50 UTC</t>
+          <t>16-05-2026 18:13 UTC</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Samsung Galaxy Buds4 and Buds4 Pro preorders: Price, where to buy</t>
+          <t>AstraZeneca's Breast Cancer Treatment Lands US FDA Nod for Two New Indications</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Mashable</t>
+          <t>Moomoo</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTFBPcy1WY25nRXFyLW1aWGJBUHNLcm9pNi12VXB4VkY3ZzVrLW9QbnMxRnBPbmtlaDB6RDNTbGtWYVU3M2g4MVdrUUM4cWJ5ZEJEM1JrNGtGWVlSQ0UtOXVIMlpiX2EzVnNTVXZJbVg5TWlMMFU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNZUduMW9jcjJZc1N4RVNWaXd5aVlDWHlyclFlT28tbTNSNEJXdXQweC1UcDR0ZXJaWUNPZXN3YU9EWUpzZ19vNEJ3TU5paUZ4cE5WcHdaMVRaR0QwVnFXMmZuaEktdHFoaE51aUxjWmZVYk12aHVyY2s1MFhtRVVBQ1RudUt1UW5yb2VNdURTT3c3LWQzWUFhaGlraUtLeFdsZ0E?oc=5</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>17-05-2026 04:00 UTC</t>
+          <t>17-05-2026 07:09 UTC</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Kyowa Kirin</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Samsung, labor union to meet in ‘last chance’ talks to avert costly strike</t>
+          <t>Is Kyowa Kirin (TSE:4151) Pricing Reflect Its Mixed Long Term Share Performance</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Investing.com</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPNGlSdXM2bTFPaEZnd2czeFN1TDFLTnBGbDUwbFdQdFN4N1o4Zm9MU1ZTdVBuR294Wk9rVTlxT05IMk1FVW9KdDU5LVpGbE90SDFna3N3ZDFBLU1ncUVQU3lkSTZrZUlqN3d3Y1FRUkdVa1pnWU5CZ1Q5b3otb0tBZHlxa1A0ZFlpZXhfNlJ5U2xFZVpnN3JrTlY0VkVFbFFvU0xUd3AtUzdzTE8xYzFKREZfaDlCNGFXWXhVRWJWN0I?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQczlsYy01RTI4VGJCU2QwSHJFV0t1QWtXWDh4X3BJMGZtS0dlQm92ZWYzS3NxV3dhZU1fZW5TY3IxNW5VVjVCc0xRVEZuVVQ5aUJFUmlQTVlxYTdjdUlCWEdkWHktLThQMW40ZEZLdlBRRWpfN1pzTWw5UGRUY0ZqZzdRZFNCZkdvUkdpVF9BbFFtTkpiTVN0T2hUbW9zRDBIcXZUbGQ0dDFueW9vNUNFMVRsa2FUNlMwWExUVV9walVQbm5DcEEzeGhWUlBENkhldVFWeDVIODFpSWRfNkFTU2Rya9IB6AFBVV95cUxNLVFhS2NFYkpKZDQ0aVN6NnBJN21QWVplZTlQRDlCdmt6THVnejZCUThNNFZ3cDFaSzFXUlpWQm10WUFmN0c4SXpkX21DUjlZQTJ4SHQtTnozR1ZMaEw5S2I0cVpreVVfcXYtajNjYkVGVGJFUjQ1OWhmZEFxRzNFbnp2Mm9fcTJxYTFjVm44b210d2NEaXozbE5fMVZiVTRVMk01S1lNMlg4SEppZ0dXX2J5cDg0YkpCbkdkb3RYSi13YnVLVmlJMERPeTVBczRfamRQRTNERHFjYzIyLVhwSWFOMjdtcWdT?oc=5</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>17-05-2026 07:21 UTC</t>
+          <t>17-05-2026 10:03 UTC</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Kospi Pauses After Topping 8,000 as Focus Shifts to Nvidia, Samsung Electronics</t>
+          <t>Real-world effectiveness and safety of ranibizumab biosimilar FYB-201 in Saudi Arabia (Ravegza) and Jordan (Uptera): a middle eastern extension of the FORCE study</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>bloomingbit</t>
+          <t>Nature</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiVEFVX3lxTE9UcjVDVng5QWFlaVA1dzBTMEl6WUIxb1ZrTTRsZ3pzN04wYmNCbzFkd29yNjUwd29RR21pQzBjUFRmRDZxOGZiMHk0T3F3bFdnakpwdQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE9MeGlsYjR5dmx1MGxIV2lNQmdWMkduZVEyWUFCTjlxbEgzczVON2ZUSzg4bjB1LU9BRl9PczVwMXpCTmFuRkZMbEZqTmVOTXgxZldWdzA5b0RUNW1nd1BR?oc=5</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>17-05-2026 00:13 UTC</t>
+          <t>16-05-2026 18:40 UTC</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Prestige Biopharma</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Seo Yang-san (pseudonym) who gets his golf club out of the trunk of his car after arriving at the ap..</t>
+          <t>World Automated Solid Phase Extraction Systems - Market Analysis, Forecast, Size, Trends and Insights</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>매일경제</t>
+          <t>IndexBox</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE1RWTZ4MzBKRUEzQXhKSllWa0s5ZU1Da0xUVVRpOWlUb1BiZi1QREVueU9wVmdMZXJ3cDhWeENRMmd4bFRUS2FTUVRzTmwtR1BsbVdLM3FVS2U2UEVM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxOSFotX3RrZmM4ZzVDcTgtdi1CQm9nVDVHRVVrUXpYcTJnUHk5ZVhVWm9OaUw3cDBsVlJFXy1VbFZJQWZfZ3ZtMjRxc1ROSlpWZTAyN2ExRmNiQ3QxeFpTdGF3dFA5aXRFVU1FYUF3b2RrcE9ORnJpZnViWXRYZVYxdks3MGVEdDQwN3BIa2lld2RWZEQ0cmRUSkljeHAyZzFudHdJLWJmZVI0T1NGc1o0VzFDbkZ2b090WFdDQlU1UnlRVjYwbFc0eFMyWWdYTjhMVlcwRnFnNXdmRFlSeEVOMU9jWlJWTmpUS3RaNDY4SXpsWDkt?oc=5</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>17-05-2026 07:00 UTC</t>
+          <t>17-05-2026 04:16 UTC</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Alvotech</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>FDA greenlight for Enhertu in two new indications</t>
+          <t>Alvotech (NasdaqGM:ALVO) Valuation Check After FDA Form 483 And Reaffirmed Approval Timelines</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>The Pharma Letter</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPcy1WcGMwX2lWYXNXSVVQVDlvRmhxYnlaTVJtSUh6OE9qcFdtS2lmZlY2U25mZFlZdlNscXN1cWtLLWZ6U1kzQkhCeUJvUUVQS01NdFVMZUFQeXFMaDdXdEFJdWNRREhWTzJJVVZsejJ3LVNJeUFKOW9mY3ZOTnppX2paSWZUYWFDVnU0OXp1T3RGYjVVdjhtY1V3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxQWC1ybE1FalB5bXRoeU9rN2M5RGlwX21Kc1hfU1pENDFWU3RtZDhIMl9OWUJLMW91c3BIX0cwYlRDOU56V3gwNExlR1lRR2ZNY1B2Uk9MQ2E0Q28ybzdkRzRONTJ6aFp6WmFDMXJ0Y296YUFsSHhNTDlEREhiNmgwcENuRlJobHB0c3ptOVo0aDYzQnRiUWhhRmlpMTNVUGUzX1J3X0YyQ1BENkk0WXpzdUVreVFXclVNbzFiY3V5eVhLWVM3M0FYZWV5WGhJWkZCMHZHZXMtUTFod9IB3wFBVV95cUxPNUlXRzlwWTI1cy1lSzN2dDdCR2xLWmtBOHh0eFZqanBud3hWWDJldHhaSHpWcjZHcU1uQlZ2NmVUTml5QUh4UFlUMmkwajlhRTJCcXRBS1NZbmJkQnVXckxKS3htZi03cTlsZ3VGNHNweUE0ZW5XaW95cE13UFpOSnBlWlE3ZlhSUW1CVFl6S2ZyeTI2YnN0cjBjQUFDbmN2V3h6Z1FrY1Fzb1FxY0RIcTU3aThzMDNkVXNLVTNUMjJFTlYyS1QzSVVqNGtsY1NoT1lJSFpMNWJyU24zV093?oc=5</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>16-05-2026 19:18 UTC</t>
+          <t>17-05-2026 07:37 UTC</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Alvotech</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo Co Ltd stock (JP3475350009): FDA approval for Enhertu adds new US oncology momentum</t>
+          <t>TradingKey</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>TradingKey</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxOZTQzcHVLSWN0Z09GWWdrQ3lpXzdwbkJfNUktc1JNeDRreXhkU0Z3dU1Pd3BxNE1VUGQzWkRnaHJBTE40cm5FbXViRXRXeDJCYlZleXVFNkZvZWx0ZTM3eVdrdzZLVjhrNW1qUjlIZm9YelE0SWpRMnlmb3MzSWI4d0t0NHZKWUQ1QmluX1NFcFl6M1VVQjJKUllSS0lDSGNoNDAyZzhyOVU2MFhWZTYwTy1oUVpkNExPZGxPOGpvcHgtWmoxc3Qzaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE9Ud1VQME03ZWp6VTZ4S25yRnc0UFcxMU0wVnNqRlVFTWJuc09xM0cxYnk5bnRxN3pKeTRNYkZkUzRlcnRkTTRGOEx5WHJhem1mSHlnUEpSWWlvT21fRE0yZENycGo3Z3B0LTZERDBRRnk?oc=5</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>16-05-2026 13:04 UTC</t>
+          <t>16-05-2026 18:38 UTC</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>AstraZeneca's Breast Cancer Treatment Lands US FDA Nod for Two New Indications</t>
+          <t>Teva Pharmaceutical (TEVA) Reports Q1 Beat, Plans Amylyx Deal</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Moomoo</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNZUduMW9jcjJZc1N4RVNWaXd5aVlDWHlyclFlT28tbTNSNEJXdXQweC1UcDR0ZXJaWUNPZXN3YU9EWUpzZ19vNEJ3TU5paUZ4cE5WcHdaMVRaR0QwVnFXMmZuaEktdHFoaE51aUxjWmZVYk12aHVyY2s1MFhtRVVBQ1RudUt1UW5yb2VNdURTT3c3LWQzWUFhaGlraUtLeFdsZ0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPQWtBRW8zMzVhcUYyTjRvLVRaNHNXVTg5V0dMY3FpZXVQRldSOXU2NHZDOEhiU1k3bW90SDJCRHFvUU51UXNONlpHRFR0cHJsX2YwVHhWT1Q2U1NsWkJONU1LdUlKSU1Jcmwtcm5rZzRDNFdtSjJpUWc5VWU0S0V0Z0c3eWZmTmRiXzBGTmFXb3puYlo3STZPM0JwajlSYmxRZ3QyT0F3VQ?oc=5</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>17-05-2026 07:09 UTC</t>
+          <t>16-05-2026 18:03 UTC</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>MASCC Webinar – The Hidden Burden: Understanding and Treating Cancer Fatigue</t>
+          <t>Teva sells remaining women’s health line in deals totaling $1.38 billion</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Oncodaily</t>
+          <t>The Times of Israel</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTFBSRnlBNDAtc21VczhSNnprSmc3TVFteVlvbmZUWm5Ka1dsX3R5Ni1DemIyQVpVM1ZOemw3c00zZkR6YTM3VlBldnBrSmdxV1VVNTAtcXFkSEp2T0Mxb0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNb2k2b1pUWXY5ZmdTYU1zem9tNnZMMTFraW9mLXh1Wmc4b2pKdlEtSDU4dkMzVzFzTDdVSFcyQVl2cGFVT3FSSXpwaGtRODJxc29GN2RhWmJROVE3SC0ybVJJd2E4QmNodUthSnZzR1RwQ1VpLXljazBLVVJwc3hxYUJucW94NmdDMzdwN09CTUEwMWNQYTNvSDY5Vlc1b0hOYTVSVXpRMWpISm5CSWRCWFUzODZ4dkpxWTF4eVhJSXNZekQ0cWxIOVlCQdIBqAFBVV95cUxNNFR6ZEtPWmFyeEhfTFFmN2d0STRjQjZVU0p0eUVoR0VVOXFfNC1fNTRtVzEtdGZEME03Rk1nSU8xUTdxODh1bzE5RFdXdVNha2d4R0gyUXh3elV4WVQ5RzNiMnVPVE9Fd0JfMVJmdVJHb3pKUURNUjNCWkJrVDEtR1JpNDRyYzFEZFlfS3hiUmVQTVMxa0FjTHY1Y01UZlVPeHhNSWxySjQ?oc=5</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>16-05-2026 10:40 UTC</t>
+          <t>16-05-2026 22:51 UTC</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>AstraZeneca plc stock (GB0009895292): FDA nod for Enhertu keeps oncology story in focus</t>
+          <t>Teva Pharmaceutical (TEVA) Reports Q1 Beat, Plans Amylyx Deal</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>Insider Monkey</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxPSEtXYW5tcDh6UUFzX0JBQ3Z6em9oRWlMSjNGUGw2dk80dWhqakl0cmQway1EUm5UX3BQckx4cFhBMmpGWnllekFDbVJ2T05Ec0cwMk5QejdBM3lOTW1vcnh5MHJQOW1UQ1piQ1NRajJucWR0UTdYNzFjWE41TElvaTgwR010YUpqODNRTk5zeERWTG9JNXVvWWYtNHhvQ1hZQmRmZTlPRkNFYTQ4NFVzRkJLUmNHM0NURk82YzhtVmRhS3hsUWRB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQOENkWXhzMFl2dHlWY3ZWdlBRZlMyNG1VekFqWVZKQjZGaF9uNXRwelQ4cHRZUHgydlg3SnMtNTl0Y0daQmFjbkxEdDBKbFo4ZzBRSVlhRGhIeW12cTBpdnk3REpZa2pnSDZhTDJsck1JOWFBWFZ1Mm1iOUplRzVqSGw5aFpCcUhkZVdfZi1GU0ZCcHNMWTI1bGh5UFMwSW9CRDFMLTdlT2lZdUJh0gGsAUFVX3lxTFA4Q2RZeHMwWXZ0eVZjdlZ2UFFmUzI0bVV6QWpZVkpCNkZoX241dHB6VDhwdFlQeDJ2WDdKcy01OXRjR1pCYWNuTER0MEpsWjhnMFFJWWFEaEh5bXZxMGl2eTdESllramdINmFMMmxyTUk5YUFYVnUybWI5SmVHNWpIbDloWkJxSGRlV19mLUZTRkJwc0xZMjVsaHlQUzBJb0JEMUwtN2VPaVl1QmE?oc=5</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>16-05-2026 18:13 UTC</t>
+          <t>16-05-2026 18:05 UTC</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Kyowa Kirin Co Ltd stock (JP3249600002): oncology and rare-disease focus after recent earnings updat</t>
+          <t>Wall Street Thinks Teva Stock Still Has Room to Run After Soaring Over 100%. Here's Why Analysts Are Right.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>AOL.com</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQaXhlNVF2SC0yZE1yUl9JN3RvcnFvaEtfLWRNYUNPakViQkRnaUt3YVhRZUVjaDFJMWVrRUdsZlpIM2tNcXZnVzRRSkZJaHpmZjJLcEg5TmV6emtXa3FseWpMSWlBdi1BNDJlMmI5WU1OdmVyY0dLNmhsUTBiMmJMSjZva2psWUdjNGg0U0xfRjdGT0pmWHo5OWVmTGdYWWxNbG84RGNlU3FhOHlkTWhOTnFiZnM5YkxjSEhvYWo5RWFwUWtyU09v?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE82X3RIZjJ4MGdwdThuX194S1JwN3RSd25jVEhJYmpJMmRuSmpMazI2c1NwSVdsSTdBeVA0Si1kN0JjVXEwb2w5MUFMbVlvN2p4aUpFOW0tLTV3MHl5bzZ1bzlqa1NDdkRQT0RLeEVCbkNqQzdPYkFIT1hhWG9VUQ?oc=5</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>16-05-2026 13:02 UTC</t>
+          <t>16-05-2026 20:25 UTC</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Multi Therapy Infusion Pumps Market Forecast Points Higher Toward 2035 on Rising Chronic Disease Prevalence</t>
+          <t>Teva Pharmaceutical Industries Beats Q1 Earnings Estimates Driven by Innovative Portfolio</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>IndexBox</t>
+          <t>HarianBasis.co</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxORUE1eldUelBvXzR5Zktsb0ozTlFnMlBxN3Q3YjduTHF3dlB2dHlqMDJrV0dmVDh6NjlGVktRblpaV21odnJ3SFNwclFFb1ZlUGFVc2VtajBURkIteTEzb0FJLVJvNW9oOWgxelk0bFJrdS1KdHFLSTB5MHBSb1pTMG15cC1xV0dWSU9JVVVHcTZnM2JlWlVYZFRwUnF3bkdONlhuVWJ6YlhXLUxZWkk2NTg5OGd3UmJLMEpFMmkzRnVScnlrTEdlRXUzNHpSOUQxWTZj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE1NWmlZdmdOV2szUjlEMWR4TjVjNWhmYTcya3Q2bWNDR1JyVTBCemtVeVBkdTFVSlRuanJkenVCY2RlN0xMdFZmZ1pRc0tJcll3N2NxNl9ZU3ppNmo2ZHI3ekkxcDRRRGtDUmxQc1R3RkNCNVRMekE?oc=5</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>16-05-2026 09:46 UTC</t>
+          <t>17-05-2026 01:01 UTC</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Samsung Bioepis</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Real-world effectiveness and safety of ranibizumab biosimilar FYB-201 in Saudi Arabia (Ravegza) and Jordan (Uptera): a middle eastern extension of the FORCE study</t>
+          <t>Alteogen Enters $13 Billion Eylea Biosimilar Market</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Nature</t>
+          <t>aju press</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE9MeGlsYjR5dmx1MGxIV2lNQmdWMkduZVEyWUFCTjlxbEgzczVON2ZUSzg4bjB1LU9BRl9PczVwMXpCTmFuRkZMbEZqTmVOTXgxZldWdzA5b0RUNW1nd1BR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE9hMnlockpJX1l4OXhHVkRrMTE2bXVrLUtYNWpWZmtXZ2J6VHJmcm9PSnNoVXBDaUhyMFdKZW5KWnhUc3gzVlpjdmgxdlpkeTA2cE5BUTVaZmhkQU3SAVdBVV95cUxOTzJ4djgtR3VRSGtqZEdqOW1xbVBPaktfbjZ5dVo3TWFvODlkUlhvVkpxREhHbWt2ZzZLbjU3dW92WkF1ZFh4S3hYN1hOa3praEt0TVhXamc?oc=5</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>16-05-2026 18:40 UTC</t>
+          <t>17-05-2026 08:46 UTC</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Samsung Bioepis</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>World Automated Solid Phase Extraction Systems - Market Analysis, Forecast, Size, Trends and Insights</t>
+          <t>Korean Pharma, Biotech Firms Post Strong Q1 Sales While Profitability Diverges</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>IndexBox</t>
+          <t>thelec.net</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxOSFotX3RrZmM4ZzVDcTgtdi1CQm9nVDVHRVVrUXpYcTJnUHk5ZVhVWm9OaUw3cDBsVlJFXy1VbFZJQWZfZ3ZtMjRxc1ROSlpWZTAyN2ExRmNiQ3QxeFpTdGF3dFA5aXRFVU1FYUF3b2RrcE9ORnJpZnViWXRYZVYxdks3MGVEdDQwN3BIa2lld2RWZEQ0cmRUSkljeHAyZzFudHdJLWJmZVI0T1NGc1o0VzFDbkZ2b090WFdDQlU1UnlRVjYwbFc0eFMyWWdYTjhMVlcwRnFnNXdmRFlSeEVOMU9jWlJWTmpUS3RaNDY4SXpsWDkt?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE9oZ2hxeXJ6VS1PZTR5SEFSQnUxbm4xQUZjOGFOUHVNbVU2LTVjWXZPcnJWdmY5TkRNTWJHY1FRM1RPR0JHdGk3NGFqelVLSEZZV1VnZ3VBTHZERkRpb1FoWjNyc3lNRVE?oc=5</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>17-05-2026 04:16 UTC</t>
+          <t>17-05-2026 11:47 UTC</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Samsung Bioepis</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Merck KGaA stock (DE0006599905): patent setback in US MS litigation puts focus on pharma pipeline</t>
+          <t>South Korean drugmakers chase monthly obesity shot</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>Borneo Bulletin</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNNDF0YlJNVGpWcmNGN3FHX3Baa1k2WjVYSGx3Um9RTDcwZkVCUmVCRm5Ycm5SZmF2NG9KbE0wOXhycF9ZNVQyR0VzaUV2Sk5rNGtmS0p2UzVPQ1MyN0ZCeXRwSWxMam1mb3Zkdl9xVTRkNTFReXZScDJtdjFDZ0JfdUdJU1E5eXM1SG1COVZTUnRaWWVxV3Q0elBXNzN4TER1NUZVZDlUdjdneVdKTlpDMkJHZ0JjY1ZoMk9oeTM2SnROcmM5anNF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOSjZybUVPS2NhU3kyZ3BDc3Q0NERscWEtSTlYbHE4MEUwbV9kNUk0eGNDVUc5MzZPX2tjWmNIT0NFWkxfcHJVUE40WGVvVUl3Q3g1ZHQ0bHVJa3lDWjk4aHhxMlNQbV9fZkhVekVJYW1jcGhRX2lTaW1ZWlNNNTdUTF9pMktVZ3VX?oc=5</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
-        <is>
-          <t>16-05-2026 14:01 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Alvotech</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Alvotech (NasdaqGM:ALVO) Valuation Check After FDA Form 483 And Reaffirmed Approval Timelines</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>simplywall.st</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxQWC1ybE1FalB5bXRoeU9rN2M5RGlwX21Kc1hfU1pENDFWU3RtZDhIMl9OWUJLMW91c3BIX0cwYlRDOU56V3gwNExlR1lRR2ZNY1B2Uk9MQ2E0Q28ybzdkRzRONTJ6aFp6WmFDMXJ0Y296YUFsSHhNTDlEREhiNmgwcENuRlJobHB0c3ptOVo0aDYzQnRiUWhhRmlpMTNVUGUzX1J3X0YyQ1BENkk0WXpzdUVreVFXclVNbzFiY3V5eVhLWVM3M0FYZWV5WGhJWkZCMHZHZXMtUTFod9IB3wFBVV95cUxPNUlXRzlwWTI1cy1lSzN2dDdCR2xLWmtBOHh0eFZqanBud3hWWDJldHhaSHpWcjZHcU1uQlZ2NmVUTml5QUh4UFlUMmkwajlhRTJCcXRBS1NZbmJkQnVXckxKS3htZi03cTlsZ3VGNHNweUE0ZW5XaW95cE13UFpOSnBlWlE3ZlhSUW1CVFl6S2ZyeTI2YnN0cjBjQUFDbmN2V3h6Z1FrY1Fzb1FxY0RIcTU3aThzMDNkVXNLVTNUMjJFTlYyS1QzSVVqNGtsY1NoT1lJSFpMNWJyU24zV093?oc=5</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>17-05-2026 07:37 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Alvotech</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>TradingKey</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>TradingKey</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE9Ud1VQME03ZWp6VTZ4S25yRnc0UFcxMU0wVnNqRlVFTWJuc09xM0cxYnk5bnRxN3pKeTRNYkZkUzRlcnRkTTRGOEx5WHJhem1mSHlnUEpSWWlvT21fRE0yZENycGo3Z3B0LTZERDBRRnk?oc=5</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>16-05-2026 18:38 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Teva Pharmaceutical (TEVA) Reports Q1 Beat, Plans Amylyx Deal</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPQWtBRW8zMzVhcUYyTjRvLVRaNHNXVTg5V0dMY3FpZXVQRldSOXU2NHZDOEhiU1k3bW90SDJCRHFvUU51UXNONlpHRFR0cHJsX2YwVHhWT1Q2U1NsWkJONU1LdUlKSU1Jcmwtcm5rZzRDNFdtSjJpUWc5VWU0S0V0Z0c3eWZmTmRiXzBGTmFXb3puYlo3STZPM0JwajlSYmxRZ3QyT0F3VQ?oc=5</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>16-05-2026 18:03 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Teva sells remaining women’s health line in deals totaling $1.38 billion</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>The Times of Israel</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNb2k2b1pUWXY5ZmdTYU1zem9tNnZMMTFraW9mLXh1Wmc4b2pKdlEtSDU4dkMzVzFzTDdVSFcyQVl2cGFVT3FSSXpwaGtRODJxc29GN2RhWmJROVE3SC0ybVJJd2E4QmNodUthSnZzR1RwQ1VpLXljazBLVVJwc3hxYUJucW94NmdDMzdwN09CTUEwMWNQYTNvSDY5Vlc1b0hOYTVSVXpRMWpISm5CSWRCWFUzODZ4dkpxWTF4eVhJSXNZekQ0cWxIOVlCQdIBqAFBVV95cUxNNFR6ZEtPWmFyeEhfTFFmN2d0STRjQjZVU0p0eUVoR0VVOXFfNC1fNTRtVzEtdGZEME03Rk1nSU8xUTdxODh1bzE5RFdXdVNha2d4R0gyUXh3elV4WVQ5RzNiMnVPVE9Fd0JfMVJmdVJHb3pKUURNUjNCWkJrVDEtR1JpNDRyYzFEZFlfS3hiUmVQTVMxa0FjTHY1Y01UZlVPeHhNSWxySjQ?oc=5</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>16-05-2026 22:51 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Teva Pharmaceutical (TEVA) Reports Q1 Beat, Plans Amylyx Deal</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Insider Monkey</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQOENkWXhzMFl2dHlWY3ZWdlBRZlMyNG1VekFqWVZKQjZGaF9uNXRwelQ4cHRZUHgydlg3SnMtNTl0Y0daQmFjbkxEdDBKbFo4ZzBRSVlhRGhIeW12cTBpdnk3REpZa2pnSDZhTDJsck1JOWFBWFZ1Mm1iOUplRzVqSGw5aFpCcUhkZVdfZi1GU0ZCcHNMWTI1bGh5UFMwSW9CRDFMLTdlT2lZdUJh0gGsAUFVX3lxTFA4Q2RZeHMwWXZ0eVZjdlZ2UFFmUzI0bVV6QWpZVkpCNkZoX241dHB6VDhwdFlQeDJ2WDdKcy01OXRjR1pCYWNuTER0MEpsWjhnMFFJWWFEaEh5bXZxMGl2eTdESllramdINmFMMmxyTUk5YUFYVnUybWI5SmVHNWpIbDloWkJxSGRlV19mLUZTRkJwc0xZMjVsaHlQUzBJb0JEMUwtN2VPaVl1QmE?oc=5</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>16-05-2026 18:05 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Wall Street Thinks Teva Stock Still Has Room to Run After Soaring Over 100%. Here's Why Analysts Are Right.</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>AOL.com</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE82X3RIZjJ4MGdwdThuX194S1JwN3RSd25jVEhJYmpJMmRuSmpMazI2c1NwSVdsSTdBeVA0Si1kN0JjVXEwb2w5MUFMbVlvN2p4aUpFOW0tLTV3MHl5bzZ1bzlqa1NDdkRQT0RLeEVCbkNqQzdPYkFIT1hhWG9VUQ?oc=5</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>16-05-2026 20:25 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Teva Pharmaceutical Industries Beats Q1 Earnings Estimates Driven by Innovative Portfolio</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>HarianBasis.co</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE1NWmlZdmdOV2szUjlEMWR4TjVjNWhmYTcya3Q2bWNDR1JyVTBCemtVeVBkdTFVSlRuanJkenVCY2RlN0xMdFZmZ1pRc0tJcll3N2NxNl9ZU3ppNmo2ZHI3ekkxcDRRRGtDUmxQc1R3RkNCNVRMekE?oc=5</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>17-05-2026 01:01 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Samsung Bioepis</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>South Korean drugmakers chase monthly obesity shot</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Borneo Bulletin</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOSjZybUVPS2NhU3kyZ3BDc3Q0NERscWEtSTlYbHE4MEUwbV9kNUk0eGNDVUc5MzZPX2tjWmNIT0NFWkxfcHJVUE40WGVvVUl3Q3g1ZHQ0bHVJa3lDWjk4aHhxMlNQbV9fZkhVekVJYW1jcGhRX2lTaW1ZWlNNNTdUTF9pMktVZ3VX?oc=5</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
         <is>
           <t>16-05-2026 21:14 UTC</t>
         </is>

--- a/news_results_raw.xlsx
+++ b/news_results_raw.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E98"/>
+  <dimension ref="A1:E173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,81 +458,81 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Chime Biologics</t>
+          <t>Sandoz</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Recapping the “Must-Know” Information From the 2026 AAD Late-Breaker Sessions—Part 1</t>
+          <t>Sandoz Appoints Aarti A Kapoor As Head of People &amp; Organisation Operations For Region International</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dermatology Times</t>
+          <t>BW People</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNZTJyb09pS1NON0N6SjRfd0thMnNWTFdwSmVzWi1uNlNGTEdVdThRQ25LV0p3RmdKMXo0ZFlVRmcxMHdNdVhWZmJ4TGtpSHA0Yk9zX3VaMzhqZTBHR05pY01JR0tYcUNHQWpvR29wX1psZVhza09OdmwxcUhva3U4LXV2RW1Tek5WOWhBZUdkVFZoenEtOG1OSzNfaGVlYVc4bWdxN1JFUHlwck9xc3FqU1puczNtZ3lUOEp4Rg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQNHlxRHRBMUxsQzVETU1BdFhaWGdIVm8tUUNCMzZFOWRLWUhqTC1rQ1N0LUxBcVMxYU1JLW9aTi1EVXBqVUFoc1VuS3NEZGdIRUNNcVhzc2hfc0FRRXI3cGdqTmpWQ2NBdE0yd2I5OC1yTnpoZ0VPYm5Ua0hvcVBTb29zRE9wNTNveEpmV0NrUFhUb25jMWhDOHZRa1MwUjgyd2xIVmFLUXUxMmtqNXRmNUxzbzBzVFF5bF9LTmZoNlNxTC14S2tiQVliUG5ETkhtSGc?oc=5</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>16-05-2026 15:00 UTC</t>
+          <t>18-05-2026 05:33 UTC</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Stada</t>
+          <t>Sandoz</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Voices of valor: Kisumu women rise through STADA’s support - Radio47</t>
+          <t>Oncology Biosimilars Market is expected to Hit US$ 30.83 Billion</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Radio47 - Hapa Ndipo</t>
+          <t>openPR.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPbUpxUmY2bDV1UTlGQjc2WE52T3cyWjUyc3ZUdFNnRV81NndCYTIyd3NtS0VXck1hOC1DRHNNNXRQSXBNa0oxdVE1R0pHQ1ZxTGtpUXppT0s5VGVKLWZrSFp6bTN0SW04YW1tR2ZWRTM3d0thMThkdFpaUnY3LVZ0ejYySmVEVVZ0bFpleUE0b0U5Z0hvcmNTalU0MA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQMHdIMGhoNEZyYWpLNXNWWHVkRklJb2N6R0ZvbF9qeUp3NVVQNXNmYjYxY0VzR2RKbDJXc2pfejFOSW9UZ3RBRXc5QkJPTXJ2eGdFajFENUFsUWQyRG9MMWJLeXJfMmk2MVk4TXI2OW1CaElidDh0VTVDT2ptVWdsVi1vdWZzVzBpZVVwVlBLdVUyTUwxRTZLRjVmY2FIU2h1?oc=5</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>17-05-2026 14:43 UTC</t>
+          <t>18-05-2026 09:44 UTC</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Formycon</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NIPER Hyderabad, Boehringer Ingelheim tie up to advance pharmaceutical research</t>
+          <t>Formycon AG stock (DE000A1EWVY8): biosimilar specialist updates investors after FY 2024 report</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dailyhunt</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigJBVV95cUxQTFpHTlQtZjNEM2d3VmxVam5Gbk5SWEphSGFnRU9CdVdhZHZvVm9mekl5bEIyVlc5c2xfLVAzUnBFZEw2ZmZ3TEVQMGw2S3RiNWpaTEV2VGNfUWZ6YkVQU0dkc0liZDZ6bTF2eTJKNGl6ajE1TTZ0RGhNUFM4VUdqbExCWEZRU0VELWJsWE93OFJsXzdER3lQTy1vWUJacmpsZnpqdUNmTDZDd1pDTFRreDhzNXY0SXp2VVJoTlVyR1BzS1B4dnEtMEsxZkVjNDJrWEZQaHZaSU9BblpMWVYwZjV0bW9XR2ZwSlpZV2UxTTJnYWJQN09XVENhQWsxTHQ0VFVNaXBDRW1OZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNSS1sZmI4cHcwWW9pZG9iYUdBbkpvVXVMU0F4MkNkcWdIUFdXMlZ3UEVERkd1aVlDTUphMFF5bmtpSFBMcW8yS0thalk4ZDZNYXdYVjJIN3I4WVJLSEM3ZUtPUWJvOUU0eG53bzU1N2UyblQxdXltbWZJMC1jMFVNV1k1WVRkNWkzRkFhd3hnMW5MNEc1MUk2NFl2NVRaZ29Ka21iREJ2VFFROTBRWlk4bkxLYXJSRWNMXzlrZ1VCbnNwckp5djJydA?oc=5</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>17-05-2026 05:00 UTC</t>
+          <t>18-05-2026 07:24 UTC</t>
         </is>
       </c>
     </row>
@@ -544,22 +544,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AI in Life Science Market worth $69.34 billion by 2031</t>
+          <t>JASCAYD approved in Japan new IPF and PPF treatment</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MarketsandMarkets</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE5WQ0x0NUlaUldUU1VucmNKS1plazRoZVNsZ1pjU3Rxd0szMEpIWXZ4RF84bjJGVXdmMHMxYWxaUlg4MFZDaHdnNjhza0NPRTJQRi05UzUySVZUT0NaQ0VzMDRUR011ek5fZGRURVJ0cHNNSnR6aDFTc0x3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPOTlzUmdlVFV0UE1iaGRnNXQ3ZVFUbUlNVTZxejI2bGRHa3JrMGpwVnoyaENkTU5EMU5xYmNTZUd6OHkwQVMxYlI4X3JUY0ZZUlZNMjVXLXFfa0xjRHd4Z2V1MFdhUFo4VFItQXR3STFDNUFXZlhIUkhlVTVPTjNGY2xXLTZzU1J6djFzbHo0Y25SR3oyamhNZXFibjM2dHV5MVdvUlE4cWcwRE9RclFpYXd6bFphbGRuSjJEQVRWcl9lVXRIcVd2M3NPYw?oc=5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>16-05-2026 18:19 UTC</t>
+          <t>18-05-2026 07:10 UTC</t>
         </is>
       </c>
     </row>
@@ -571,22 +571,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Drugs And Pharmaceuticals Market Growth Outlook to 2035: Demand Accelerates Amid Aging Populations and Biologic Innovation - News and Statistics</t>
+          <t>Boehringer Ingelheim Says JASCAYD Approved In Japan, Advancing Global Access To New IPF &amp; PPF Treatment</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>IndexBox</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxPVHI0cjdoYjYzTXltTzFYVWpzcjI0enZrVzhhT21EZDFqR1o5V0JkanN3UGJoRHRrXzA0bUZxV1BfemRGWEc1V1N0TWxpNU1pMmh1b3VaZFVWc1dsYWNIa1lXY3ctYzVDWVBPWU1CYzNac0t2NlNrNWpwLU05dzdJNjVJUGtZVGNYYkYzWmRQaUgteHpXSExNWWFZakhOOFBmNElIeU1jNVZldVhoU3ZBR2x6WnF3MUU1NTVqelpVdWJhbjRpdnFUTHlKZXFWTldPaUVyVTFKbkhJY3JnTXpPcFNweUJEdVRD?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_wFBVV95cUxPdnNsX1phcGFwZ3pyc1dzeEhVdmhidHhtaUl5eDBCUUNkSmdIRUFZMG96dDliUVJmTVpFMTJmU2J3SklNczZVN2cwalc2SURiSExSaTZiUWVqbkhzNkx3THJhc0xnQzM0S2Zuc0M1QTNBMDN2UTBwSkYwWHd4WXQzeXhGeWI1VWVJMXRKS2JweXVrMkxocWZULVg2Y1NmZVV5TUx0SE5KaWZoeGRGYnpGZURuN2Q1NnUtUnZSckxzUGQ1Smp2dExFWVVSN2V5RElaOU9RMEN1eWw2SzhOUlBRQlZORFpVY3RCY0VRR3hLQXktRndFRDN4SXBhRVQ5Rzg?oc=5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>16-05-2026 16:31 UTC</t>
+          <t>18-05-2026 06:22 UTC</t>
         </is>
       </c>
     </row>
@@ -598,76 +598,76 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Pipeline Data and Quarterly Report: BioNTech’s Next Two Hurdles After Shareholder Backing</t>
+          <t>Japan’s MHLW approves Boehringer’s Jascayd for IPF and PPF</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>Yahoo</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNVHg2V3dYYzYzM0NPbDl1dnZVM01QR0FPODlqYWxXZ0tCeGlueGNUX1hzUHBKUERad0FuTnFPU21ZUk5HcHdDWFJRbWdUbkFQSDk4M0ZoVGxzUG1XRUY0bmRNSHRuX0lCWFN3R0FYMllkTEJRcDNoUUt5QXhIRlFFVGdfTVlwN1lteW1OWXBnc1dxMGZmRGJ0ZWNFUFhSS01JQy1Sa29aZmlaREJrSjB1ci1wdkpzOGVIZzkzM3RiVGhRdGtNS0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNVWEtdElWU0tBRWtiazJxajZZcTJ6V0hicmxMTzNoLXlPLXhINWFqejFuWTZtemREeUd3a3FYU2NyT1B5WDZnOXZoc2ZiRjRuSk5oN0tsX2Z2NXAzazVXcnVEZkJsVmdmaGVybF9aajc0dkFrNVV6UTYzYXNMTmZvY3hOWkFvaXJPdXFITE50SWt3NGc?oc=5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>17-05-2026 00:42 UTC</t>
+          <t>18-05-2026 10:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Hikma</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Killer counterfeits: the flea treatments that could send you rushing to the vet</t>
+          <t>Hikma Pharmaceuticals PLC stock (GB00B128J450): earnings momentum and US injectables footprint in fo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>The Guardian</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNNUVLNUVsYzdlYy1CLTJ1SWFTejFjT2ZJaXowNGJtMG96dk5TbVdmcGIxbWhhMGZsS3p4TkZTd24xMDJwUzFtUloxYUE0QV9kNDdRVS0yQXBVQkdaMzFnN1J1ZTdxd3YtVURHOGVyUHBmcjRLTmV0eGpwSUZVM0VSVmt3T1E0YnJXM3EwZ3BvY1JLODgzdW1XZHA0ZnZtM1Vpd1VPdGZGUTNVYjdGMFQ2ZQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxPVkg5Z3BUMTRNTDJMSjVFN2NlYS12cVBnVFk2QnVLaWZocXNtRFMtcFU3djFnOTJsVGhBSlM2a0RnajBFZUZ4NV8yUU85SGM4Nk5FWm1NRVF2aWM3cEtOdGlxTDNqcnZXRy15dWNFUHdKN0I5RmRweVBnOG1ZX2N1eGREMHBwd1I1N1ptM3pxYlpwRGpnZ3RWU3hXd21aam5WU1U5Q0dQYVZ2SGlTelpZaEFacEU0dTFuWkpueXdmQ2pzLVlVM1ow?oc=5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>17-05-2026 06:01 UTC</t>
+          <t>18-05-2026 00:25 UTC</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Hikma</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Standing Bone Strong: Introducing a New Awareness Symbol for Osteoporosis</t>
+          <t>Hikma steps up $250m buyback, cancels shares to tighten free float</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQRDRCa2dnZkdVYlZoYzd0OXpJYy1NV3ZFalNSdnZQdWk0bDRXMUtWWS1hMUtKU1lob05hNFp5U3pSN3FLRWRoUkZLM0xvWnNQdmp3NTRiMWc4cFBOdDFSTXkyQ2FKVkVZVUtDOFRsU1RVOVN0UXNEd0RaMEM5cGIwRTNSUTljeWRDdHhocVMxZDJzRUFQQ09QNjVfbnlhaVZiNjZXNHpSalNMcmM3cTJj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQZ2gzYmFhNDNoS0wyRlY4RERCMzBSNi1MbzA1ZmxzSFRHVGNKbV9TTEdMLXNOeFRpNTFGQWNnVzdtX3VuWlpLVkRRREtnU2dGNl91bFV6Q3NWUWFvSHBZdzFNNWJmLWhZVS04NTFJcUxwcWNrVmtrY0ZOTmpxSGx2TDdEaC1GYjZSN1RsU3NQZUVjMGhIa0xldzRqQ2p2R1J3dGxFR3VCaEUzVXNvZFdBanNWdE8taXM?oc=5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>17-05-2026 04:56 UTC</t>
+          <t>18-05-2026 10:03 UTC</t>
         </is>
       </c>
     </row>
@@ -679,22 +679,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Japan Flags 20 Deaths, Liver Injury Risk in Amgen's Rare Disease Drug Tavneos</t>
+          <t>Amgen Inc. stock (US0311621009): focus on Horizon integration and latest quarterly results</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Medical Dialogues</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPLXIwY2JKZ3RwRmZvNXJrajgtWHhaaEFWaW1NaTVPemx3dnFNdVVES014bWtKTVdySHBXVWVPRHF6Um5WQlNVUzlrU1lHVmZqbFNSU2NzVE1OQVpDYmRsbUMtWEVKdDVyS0JEc2pZRW12QVg4X0M5MUctMmI5NXJKMHJNYU5EZWF0Zi10aW84Y0xuRzBIcXRCLS1EYlJIbGUtcWM3b05iWUJaSjMyTDZUc0dvRklBY3lmTGFrbk56dkdYZ2lSOTFRQmI5RdIB0AFBVV95cUxQYUhJaGxfQUN2cnFIeFVQRXV1aDZ4STdWcWdka0hlUGRRMllmM1RRNUVzbXl2bEtxUVVXLXF1QmUycl9qSUI3X0VkanVNd1hOblV1Rk4yaXltVXFkU01rMllhOUlnZmZVZ1FuOTc4TGJDWE9WX0VNcWlHRms4UEV3M29USFQ3akl4QjhnLTVkY1hieU1KOHpsbkZBdXROMXdnYkNodjZyWEMxU3dPOXhJVHJ5MEx4YmdCYzBpbXdnU3cyb2tlT1dlb29FLTB5SEVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPWnFkVmxWYXlxd25EelhqcXVodmwwZEtUV21BRktTNVIxaUZTM1gxcUNSdFc5dlc5bUIyb2Zrd0d0cEJvUk4tb3c2dUlxdV9ZUENzQ0NNTXE4bHNvYjI3ckk2QmpYSHhpai1NMGJ5UldjWWNfOVlzUXdlaV8wNndaSVB3RWUxekN6akF4OXBLM1lJUjEzc2k3ejd1ZmFfUzJkODJ5NXk0RnhWTEhYbTFmWFRUTGVLeG1KVXFrSUtTdWpqRkdZMlE?oc=5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>16-05-2026 16:22 UTC</t>
+          <t>18-05-2026 14:37 UTC</t>
         </is>
       </c>
     </row>
@@ -706,22 +706,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Leuthold Group LLC Buys 4,396 Shares of Amgen Inc. $AMGN</t>
+          <t>Amgen’s rare disease drug Tavneos tied to 20 deaths in Japan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MarketBeat</t>
+          <t>BioSpace</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNaUptYVNLS2w2cFJaMW91YnpTeS1veVlpelhLNnBGNkNyV1ZxWnlqNGFIRjlDdUtwUTRWa1FORVZYOUUxd0tnQmdNVFNONnZ5bUE4aWllelc0alF3SUhxbWhacWtJVXNfOFF5WFI0aWJLWmtXNE5MTWZwS2tVUkJXQUNWN29IQXNfNFloQ0Q4UDB5dUJ2eHZYNnhoNlJwcC0yQ3pzNXNsVk5EVF9xcEpBSEd3V3U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPdDVhWTJ1dTNFTkx4TlJDUDIxbmpEUFd3c2ZkeG91RUlBZGlNdDBLVlRoUi1Fa1F5TmFfa3liRjJ1WGtSbGc4OVM1Tmtxblp3OWcyR2dITmFRUEpCLUJ4bUNKQ180a0tqcjg0RlFHN05XTHBNMndOUGlZYmhHTmN2cDZ0UmNNYzhPRkNwcV85RlplX1d4Z2lrdQ?oc=5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>17-05-2026 11:11 UTC</t>
+          <t>18-05-2026 12:37 UTC</t>
         </is>
       </c>
     </row>
@@ -733,22 +733,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Amgen Inc stock (US0311621009): lungs cancer setback meets steady biotech cash flow</t>
+          <t>Amgen Stock Analysis: Repatha Surges 34% But Tax Litigation Clouds the Return Case. Here’s What to Expect</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>TIKR.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxONXBWTEJSeV9VenBoWVVkT3FheC1zZDRFTjhlVWdPQTdaVlNYeDc4UmlxNUVaYXRjelVpd2lTRUxBY0hZcE9pVDFVcFhRTUVvbjFvLWdrX0NvVlZhVGRVY0FQS0lUU1hUS3NTVkcxcU9CMzNuNG1aUDh6VlJVcTBsanR0ZWkxWURlb0otTnFJZnY0WDNCdGJ1dXBiOGh4N1FoMGl3bDBtVUVudHl5ZjhHZ0JfSkdfZ3BQM19iVDlkTGJhbHhNOC1BMw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPUTgydTY2cVlsZFZDMWx4ZVZ1b2dRbG5sOXhLaTJqNWF0ZUdXSHVwTG5aalhnNHFkem1aUWgwekNIZkR3ZUJZdk9tMERwaXNTLTByVnhPbDM3dGVhbTM5dmtHM0Q0SURPVno0ZE1GT2l2VnhWTlZxNVRsbHNsWWJ6c2I1dm5fTDJJRmxJSlRKVVNXVUpWMmVwTWh6aWxhZ0FXcmhrc0VjNnZRU2YwUi00c015UUhaVjFUNFk0NEdaX3F3a1RpQmc?oc=5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>16-05-2026 20:34 UTC</t>
+          <t>18-05-2026 12:29 UTC</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Amgen (AMGN) Faces Scrutiny After Deaths Linked to Tavneos Thera</t>
+          <t>Amgen’s ChemoCentryx to Pay $69 Million to End Investor Lawsuit</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GuruFocus</t>
+          <t>Bloomberg Law News</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxPc0RSY0VlbUgxNXh3T1ROM1d4NGxzR3I3dmtPWHRHdmc4UVBlVUpSRXlmMWpFRzVhM2ZLQ3AzM1RoRzJwQWoxUVlWT0RYcUxISGl2cmZhajNTdmpxaTlMbkFnQ3VZQm9WS01kY0FqVDdjUHg1VXB0Zk9WRzZRaWVzZHJVeEJ1UGI5bUtWNC1XZl9XVDk3bjQybUk0MFlsU2UtbUNPT2tHdmRRSXVUVTBtWnpub2gxT0J5cXFQY1NXSUJfbGZMazFpc2lTcC1pM2ZwQjdFeDllWDhPekk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPTkdJbXFhZnJLWkUtR2FLdW5FSEM2Mi1Gdmc0T3Zyc3k2bmVHcFJfa0xtV2Q5dGdMR1RhR3RCZFRhWHdmaU5QaGt4UE9KTldueEpwSDJMZG1pMzUxT0J0c1h4QWFjREdPMVpiNHdDX3dwTGFBZ3BaM3FIX09VMHg5SkNtM0hrcXh3WFBwWG42aHNEbVJtdVh5R0pVTDFFUlFFZG4yaWplcm9fUQ?oc=5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>16-05-2026 22:18 UTC</t>
+          <t>18-05-2026 14:24 UTC</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>L &amp; S Advisors Inc Takes Position in Amgen Inc. $AMGN</t>
+          <t>GLOBALT Investments LLC GA Has $8.49 Million Stock Holdings in Amgen Inc. $AMGN</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -797,12 +797,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQbG95NzlpS0hublNGRXg5bkZzbVBtd01JYTFEOVFGNHJ3UmtwejhrcU5iRnRRWGVNWEpOU3NKS3hqdEs1a0Fxa1B1WEVTVkVNWlFRSWM4clBndDAxS3A5X3dkUjZYSXE5a3BqMUd6N05rWWdSTVQyLTdialdvMGN3a2pVNms2U0pDQmQ4clNsRXZDdUg3QTVZdjQ0WFZiNWRFS3hzVTZGT25HNGNhMUk0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNVzB1WnQzdFF4TEgzUlZKaHFCZExHRnhTZkNtNklYWWt4dXFoVnViSkc5ZTR1dGtmaEdtZDlybWk3TXVyTXZQcjVjaHB1eUtRY3djVlZHdm5pNjVtRHRySGMxeXdjY2w0TG96RV9hOTVobElqbThFVllLbWZDLXlLZFVMZzcwT0R6LVJWV1NGNjZHMEtZLWJqeHIyNWFYVFZ6c1liOXRFRnBUMDhtdHJDZHVNZVA5MTd0dEhCWXBmZU9nZTcwV2FZUllvbWV4aVAwamc?oc=5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>17-05-2026 10:47 UTC</t>
+          <t>18-05-2026 08:45 UTC</t>
         </is>
       </c>
     </row>
@@ -814,22 +814,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>iA Global Asset Management Inc. Raises Position in Amgen Inc. $AMGN</t>
+          <t>Amgen Kidney Disease Drug Under Scrutiny in Japan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MarketBeat</t>
+          <t>Moomoo</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNRlFsMDVQeVRmd2lSclZjMjBuamVpZkc5M1BrcHBOeWFobUdGQWJzY2U3LVZkZGVQQUZmUkVPa18zYTZRd3ZxcG5adjlZVkhPVjBnSG9JRU9DU3dxU3hNSVVJVEFPMlRzQ3FtSGxQajdwZ2xsS2dRQ21PeXJJN1Y4NXJnMFgxa2VYU2JwRk0wejlGQ0dkZUl1TjlrUHZFcUtNTVNNMEFpejczVlRVMVNlOGZfTmVtNlZmaWRoR3R6RFJJNUU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxON1IyUXlZMEx3RW8zb1MyUUZ2bU1aUTJLUm5tSnJVMzBJdlRmbTJlWTBXc0VoaU5CZjdhc0tLc2t6ZldqU0xKbkhMUEJtNEYtZERsbl9LZGhxWXdLblRodjJFUWVhLTFwMnY3UWFYLXlIYVhnYXFKY0NPN0VYLTJ5cXJWUUZtMzBmbWFUU0YyZ2xhbmd5Wmc?oc=5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>17-05-2026 10:35 UTC</t>
+          <t>18-05-2026 09:55 UTC</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Amgen Inc. $AMGN Shares Sold by WealthPlan Investment Management LLC</t>
+          <t>Amgen's rare disease drug linked to deaths, liver injuries in Japan, WSJ reports</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MarketBeat</t>
+          <t>AOL.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNOXhqTDVHOXZpTVRfX3ZxWnRrazUwcC1WaVZNUUdrcGVfQ0Z5dGRBV0lmOWlGX1RTWENrWnV2MVRGNXJMNEg0bzlLZHR6R0NzblEtV3BiVnI2X0ZKc25zNkowRXk3ZmRYY1lYNEdnX29NMVdmWlBXWURNdXNGR3M4ZG5NQXNpb2pLTmpwUnAwWXBMSzZsV0JmWWFqbW9wd2J6b25mWFpndzRkTXNyVjNuSGx2T0t1cWNCSElIUm94dl9nUWluckE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxOV2tlaXB1SVZjcm5FZjZUYXpkeXdKakhSd2ZJSnZkVm8tUUxZOEpWUmVjNFhVYTU1bUNQYWR1SHNfY1NmQ2FyU25NdmY4c3FlMWpLZFNXZzBaZW9TZjd2ak1HaHlxV0R1aXJjUXZGajB1WWZMYlBKS3MyemF2VnFqWg?oc=5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>17-05-2026 11:33 UTC</t>
+          <t>18-05-2026 06:15 UTC</t>
         </is>
       </c>
     </row>
@@ -868,22 +868,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>STF Management LP Sells 5,198 Shares of Amgen Inc. $AMGN</t>
+          <t>Japan on alert: twenty deaths linked to Amgen drug Tavneos</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MarketBeat</t>
+          <t>Foro3D</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPRmFGUEplWWNyU2FnUEZxZ3gzVmZTOWZlR3g5U1JkTkVRRFZOMWdTdmdiZ2tDbl9sb01RcVJFanRQcVhadHUxeWJGYm05TVdPTTZhMkdiYi1GQ3NmQkJTYW9RV1FqQV82S3NyNHNCSi1oQ3pVLS04TmlLRDJPczYxbmQyNmJUbU16R1BLT0FhVE1ZM1JlX0ZVM05HaGZlUzA3YWJMaWlZVDAtX0RrdGd4cENldDE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQWEV0QlFnMkVhYUMtcFBqdTd4dkFQVEp2ZDdxaDdaMGdkMXQwM1hKdWVsNTZlMktKZFJKemZlbTUyRVJ2Mnh6Z2YzeHR5OHVpdWFlWHBxY3htbU5ubmZxeC1NNG5tMGlVQmljbFBsRk02eGI5UElfMVg0azFsNXB6bm1Tb21BekpzODJSMFI0TW82eGJZVnZkYkV4U1dWU1VXNllZVA?oc=5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>17-05-2026 10:31 UTC</t>
+          <t>17-05-2026 23:52 UTC</t>
         </is>
       </c>
     </row>
@@ -895,265 +895,265 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Amgen Inc. $AMGN Shares Purchased by Canada Post Corp Registered Pension Plan</t>
+          <t>Japan: 20 deaths after taking Amgen drug – Also available in Greece</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MarketBeat</t>
+          <t>News 24/7</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPVXZvZXFhVHZiYlRHcXZabE9iTWRucEVEVkxKZHp5aHZJSGQ2REdjTDRvYVBMM2VSMjF0NHlDaHlaRVJnbGdaNHp0WHJXR1c3aXZuUEJrVDViU2tZUVlJMGNENG5jN3RvcDdnN1NiTVNpRmxYRlZfUlEwZ3prVll2MGM4OFlBdFlqWTFiVmNjZ3pnVnkxa28tdXI4eDFfVS1CcWY5RllKYkhzYXFzZlJuTnRUazh3RTIzZ0t5YXNZU2l1LVU3NWxuLUp0TEV1azlnbUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQQ05pdlpSZGVjR0xWTnF1MzVLckM1SzhJTmg1UFpoeWRGYmJLVmlvQzB1aGsybXZWVzZzaHVxbmlXTjR1N2cwZ3JKY1hkWGU3SkpreGx0WkpYLTdGT2k3MnZfSktkX0Vuc3hzUDdFUlIwWHM4ck5BaTVhZnA1RjYyYmRnbnVaY3paQWJ4eXBsd1B1M1Y5NEHSAZsBQVVfeXFMT0doYzVLWTAyLUJIN2F6S3puLVBJYWEwU3FIUnhLdjR6RDQ5Skh3NFFMMkpFY2VyMVJraGpCck1zOEY3eURIRWlkeVlwOHlheFRUQ0pOZlRlcmd0LU5vbzlFNjVoWEI1TU8yWXBoRHBWWDYxUG9FZDJBSGNCM19RZXgydHliRm95Tm1taEdSbzlEa2dlMDBRYmc1X00?oc=5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>17-05-2026 08:34 UTC</t>
+          <t>18-05-2026 11:16 UTC</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SCPI set for delisting after 13 years under suspension</t>
+          <t>Amgen Inc. stock (US0311621009): earnings beat, dividend and guidance keep biotech giant in focus</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>IDNFinancials</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNRWZnV1RhSzN5WnRPdThidl9wdF9HTzBqYWwxUnM2NEt2cHRRWE5JeFhUWEhSRzhhb0g1bi1oYUxlTDNadmFjcmNNWVA4bUVqS3doZEM1TjVzZThEUGtham5pamE0dG4yNkRUVVJGZ1RrRnk3cV9NWnJtXzd6VHlZbUxMa2syYVZLelZRenJ4UXpZRU9HenFxOHJVVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNTzVSejhPNWhScmJ6WGd3eTV0Qk9WM01DWFNUR0R6dFF3Q1RNZ0RFRW9iamlybjY0YUFrQVdSalZWeU9XUTh3N25sYjExQlAzLXdsWU5kc091VHFOcGdmbWJxaXZWMUxoUFdHcE5GN2Y2cC02dVV6c0ZGQnIzelZRaTBKNFgyTFp5VVJlWlhEaDVaa0JyZTYtempsQ2VjRC1LUWlaQ3ZxT21kNTg0WUhfWlN1X1FNVkJHVUxsaXZmY0NVZlp6MlJZ?oc=5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>16-05-2026 15:20 UTC</t>
+          <t>18-05-2026 02:16 UTC</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Organon to Present New Research on Access and Value at ISPOR 2026</t>
+          <t>Intratumoral Cancer Therapies Market is expected to Hit US$</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>The National Law Review</t>
+          <t>openPR.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNaThuWmJQYUZiTnZNeE5UU2xFZHUwZ1BiVDNBX3FkSXlUWFcyQ1ZST2xJcTJYSWZQUmItb3hxazA4NmF6QTlQTXlOcmt2X2tPaTZqT0dlNy1DRzVXelhfWS1VR2MtV2R2WnMtdkFvZ2NKdzZmeVRnQ2xaYTYwM2hnaUExcktqSGd3OWk3Y3U1dENpM0ZvWC13Z0hzZ0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQM0JWWDVyNFhiZTVVX2d5SjBmdjI5LWtTWXpGMl9tZ3pJdUVZVHRGTzduZUhlMkR6bkN5RTM0YTBrZnlMbHNyRVpMbXZ6bUVBQkFGbksxRWZjWWlSdE91MWM4cGc1TWJPbWs3QVdfNWhHZUh1WDRTX3RfVDZybWQ3OHYteDhCUHRvQUlBN1NQcUV5bVRJd3Z4NWR3?oc=5</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>16-05-2026 18:05 UTC</t>
+          <t>18-05-2026 10:07 UTC</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>This new jewellery label boasts motifs rooted in Tamil landscapes</t>
+          <t>TD Private Client Wealth LLC Sells 3,426 Shares of Amgen Inc. $AMGN</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Indulgexpress</t>
+          <t>MarketBeat</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxOR3NrSDBhTUwxeVRRZGV4YjJ2MEpVWkdWZkNucWxHNHd5SGRlR3lSblctemZieWxkRHdOZVpEc0hCUlhOSUtqdVhZb3k0TlROMTRobHBpMHR0SlJyRjI1MkltbG5fWW9iZkpKUEhYOTc5dUlROWdTbXJJSDhsX1lxMVc5MjA4UHBVc2pWSjBJU2MyRno4QUNHanBCX01BU1M3NDFWUDVSeHplRlg0WlFnRDRCMDNYVmdmUUs0dWRhV282c1BjREdmNE9KaE4zblVLaTFndtIB1AFBVV95cUxOR3NrSDBhTUwxeVRRZGV4YjJ2MEpVWkdWZkNucWxHNHd5SGRlR3lSblctemZieWxkRHdOZVpEc0hCUlhOSUtqdVhZb3k0TlROMTRobHBpMHR0SlJyRjI1MkltbG5fWW9iZkpKUEhYOTc5dUlROWdTbXJJSDhsX1lxMVc5MjA4UHBVc2pWSjBJU2MyRno4QUNHanBCX01BU1M3NDFWUDVSeHplRlg0WlFnRDRCMDNYVmdmUUs0dWRhV282c1BjREdmNE9KaE4zblVLaTFndg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxObUJJbUt4WVk3NmpfOUc4dXBuQlpKVEx6RjJWY3NMNjZtNHJvbVlBUTlERzBqQnlmQnNWcHRZemVPRy16bW1lNmJCZnVOSE12SUpPbGU0RVg2TE83NUFabkRPTG52QlFJYTBOTllZSDF0dmZRczNWSmE1RzBFVGhFWVFPYVpKa05nUXhRMV9FQ0V2Mkd6RkYzd1pxQ3FMS2JFMUwyTTlGN0JBSjE1NnhqWWRQeEh6YS12eEx3dHE1TTNxY2s?oc=5</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>17-05-2026 11:54 UTC</t>
+          <t>18-05-2026 10:19 UTC</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Drone strike targets UAE’s Barakah nuke plant complex, triggers electrical generator fire</t>
+          <t>North Dakota State Investment Board Makes New Investment in Amgen Inc. $AMGN</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Rising Kashmir</t>
+          <t>MarketBeat</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPQVZhbGhaMENuNERocV9QRHg2ZVBGUlRCMFNNRS15dmFBUS1vWjNQMUd6OUdOaGpmdjVKMzZieUtVSnVhZjNNb3Q1WG56RGUxdTVvNGlRdnJadVlPRmY1SXp0VG5Fc3pZcWJoaWpqSENqNHlGemEzZ3huZFIxZWlHaVlVbHoxcnl1OG5GT2tkekVtbmdZTWZqVFRJTll5akpIbmxDeVZMeGxULWl1ZDZuYXgyRnI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNMmlOY1dfRUwtVlpJUUhSczlPQlFlMkE1M3NKaUFmeV85eHg3cTVEa3ZPUklrSHE0cHNXNUl1OWxodm54dWRwMDVXb3RXeXhLbVJUalpPVldRZ0NCc2NpbE5yTGZGandlNEVVam1La1ZHUXFYZUZhRDBMbFRYUUNCZXdLdGpxYTRldkticjlobXNTYV9HNXVjNlB5ZnBZbEw5V3lOUFhnZk56U2I0Vmhid1Z1VTZ5R0NRNWxhZG5RNGRTOXIyWGxkVmlPeVFJV0dl?oc=5</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>16-05-2026 23:00 UTC</t>
+          <t>18-05-2026 10:03 UTC</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Turkey Artificial Plant - Market Analysis, Forecast, Size, Trends and Insights</t>
+          <t>Cash per share of PT Organon Pharma Indonesia Tbk – IDX:SCPI</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>IndexBox</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPOTlkOGVoeENEdk81YXA5dTdCZURGdzBWNjNDa0RTejNzMXVqbWRvclZxMUcxM05RdGhmMXFiMzBHb3RVYUpVbjlFMjNoX3V0NjlPYUx4eGdoWEFjU0dYUWMySnhGN29kY3R4QlR6TlR4YXFRQnpYMENnb3hpSmwzdEd4R1htX0lsRkN2VkRCTmpmMDZndVFsMU9LT183eUtKakc1ZzE3aGhLTWg4cnd0bg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxObnFETi1EcjMxUVYyMHNaN2JyTWM0aXIzRmlfdEM3OUNINy1Oa2M1cUpTVkVrOUZLZU9UbktRamJUak50NTNnYWtEbEtFcE9oTWtiSlBJZHRYc3RVblQzb1JsdVVrYUhaNmtPOUY4TXdmVkdDTjRsWlppR1phZ2lFZ1BKN2hpX29CaHotZ0hIV2VGWWhOYXp6VA?oc=5</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>17-05-2026 14:20 UTC</t>
+          <t>18-05-2026 12:49 UTC</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>The ‘Perfect’ Rose I Wish I'd Never Planted</t>
+          <t>Organon &amp; Co stock hits 52-week high at $13.44</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Southern Living</t>
+          <t>Investing.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE1oeE8xNDFpUTdOZE5tS2ZHc1FGSEhIV1VKUU1fWHJwRDdubXo4bWpfMW0wTEtTcmJrN25WVUJSUmhzM1ZhWDctS2xBYUF1YmFodkIybDljeE83STZHVEtFQnlhTXRWZGRyT2ZZSA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPMW1ib2NjZUtVeksyeW91dm8wcGxoVE1TUGFKT2VoNjN1ZnVGMlBDeUJCVXcwVk9aSmo3Q1d6LWlTWjBHX1NZOGJwVmVyT3Jza29YV3VjQVpCMXh3X0RLNzRtN1FSeTdnS3JXZUdCdVVjYXhmTEFYb0lnQjNPRTlSVy14dU9wRWlNVkFTM2l5OHJNcjMtaHU3WGNpSFBHaHVR?oc=5</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>17-05-2026 01:43 UTC</t>
+          <t>18-05-2026 13:41 UTC</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Trump Says Iran Will Have 'A Very Bad Time' If Deal Not Made</t>
+          <t>Organon &amp; Co. (OGN) is Attracting Investor Attention: Here is What You Should Know</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Radio Free Europe/Radio Liberty</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQWnhyaS1tS3NVV19VeVRlS1RUeUhFblVCTkRCWmg2Z2YwTW1uR051ZFctc3F2eEcyN29hbkJkLUY3THpPVzVaYVRlcTRybGlrTGVsX3ZvTFJyQmRELVNHckg3Nk9uOUw3V2RyN2lZY0dIMW1jLWVQSUVTdXBTZGpuVE55cDBQcG01?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQMzdMVl9fNmI4MUdpVUQxaUtIUmdQM19ROVVMOHhxOGJGWHpJSldXRFY4X0pkMkZJaVVWczA1aXUycGtPbFFDbFhtdVBVMVVhWW90Z245UUNfYl92R3hYOHBGZmE0Q3ViMTFNdUVNV1JfbkdLSVJpRkwxRWNuN1Zud1lXNzdNZmFIaDVxa29GSGlYV3VuZHlXLXZ3THFXdDVH?oc=5</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>17-05-2026 07:00 UTC</t>
+          <t>18-05-2026 13:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>HFCL Limited Schedules Institutional Investor Plant Visit at Hyderabad Facilities on May 18, 2026</t>
+          <t>Organon to Present New Research on Access and Value at ISPOR 2026</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>BioSpace</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxPMGF3WTByR2FJeV9JamRMbUZRazB5OEhqX1JjdXpOWmZ0QjVSSHVON3dGMkFWM0xIUzNBdFNQMlQwWGNCQWZsRkNWZjZpYVdvX2Nid1p2TGtzQUkzVlVOeVRLX2cxTUhyX0ZMZmZTRVVYd3pSNmpaZ0djR1JPeFJ4OVNzcEpOckt3eGlvV2djc3k2STNIajBuTWx4R2FfWnNrRnk5YzNuWUVPZVI5ZzBpaDdOcU9nb3Q3bnVJT2ZnVFRGTnVSeFJmN0I1cVlybnJNS3k2SjlGWnhCYWZ2azdJazJXUnZ4OEpB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOalVKS2pkTUVYdVNoeGd4Q29hSHJZSHNsVDVINjZ5QnRGd045Y2JKbDUyR1JxYTJXMXJGLVloUGZzYkVYdHlNOXRiZFZxSFcybXFOUHJJZDlxWTNvbEwyXzhvWmdSSXhYUDFTSDlzZkI5cmgxbWlyNXRNNDlyeVFhQTJ0YWhDTjdvcUFiTFFMS1M3NF9aRm5WMWpWb25XS0NCYmx2ME9LdVQ?oc=5</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>17-05-2026 00:30 UTC</t>
+          <t>18-05-2026 01:17 UTC</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Apotex</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Is It Better to Plant Roses in the Ground or in Containers? Here's What Experts Recommend</t>
+          <t>Novo Nordisk faces competition in Canada from Indian semaglutide copy</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AOL.com</t>
+          <t>medwatch.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE1EY2pXaGxGOV9EckdEU0Z2RmZKbUd5RjRNb3dhVzRDT2tlYzJ5MnZ0VFVlVlNyaTFLLW1JeGhBRURQZHM5QmN1a01VSUh3OHdLMVREY0ozc0lZMURacUYyOGk1RmNaR29CaGNRbDd4Rm43Vm5wQWE0YzllWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE40NnNoUkpvQWRPMDVOdE45ZmRNUi1lYVVFRV9iejlRTk43SUdya25YczVDVzkwTllmNWZEQW5IVWlxSUVVQzY0ZkJoZ3M4ci1uMTd2Yk5JRl9sT00wSkhMeFJTTmNybEh5b0JOTXk2aw?oc=5</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>17-05-2026 06:27 UTC</t>
+          <t>18-05-2026 08:59 UTC</t>
         </is>
       </c>
     </row>
@@ -1165,22 +1165,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Emcure Pharma receives 7 observations from USFDA after Gujarat plant inspection</t>
+          <t>Haegue Yang: Sonic Mathematical Blossom</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>The Hans India</t>
+          <t>Hyundai</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQakY3LTd5ZF81MDhzT1Q3NmNpZVlodWEzdUwxS0gtOHdqa2xrSnl2YmJLdlhpMV94Q0VJdkljemttdUNsTzNnRjQ0Wm5RbEtUbUxuNUxBR2hzUHg0VkhrZnFVY3NhM3ZQZ250bDZ0aExkWXdRRjZsa3Y5VFJSWC05STU5V2pFWklmYkZpOVc5eF9CdWg4QWFCVVNkcklyTFRhblV0WWtMWE1ITlhOa0kzRFBubk1iTG5kU0hFTEhXYnJIM0nSAcgBQVVfeXFMTWFJa0RWbkd2azZYeHZJSVowS2lzU3J5eUo0UWR6NDEteHdhNjd0ZVBlU0pVODVCaGs5U1FWLUwyYXZNQ2NLV2hfdXNLTDdCX2x3d0lxMU1OeXIwMnpUU0FVb0ZHMHRNNGQ4eS1iendhSllFX0YtWTV6NkhoTm90U3htVkwxbVZRaFp0YVozcGU4LWlJNGdjNjRSSFJQME1FWXUtR20wLTVBeTJxXzZhcFQxODZ4WEljMWo3VEFrVXRGR1RwSDE4RkU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQQXN3QVV3cWJoZjhEYS0yRElnZWxjNWpDX2FiekMwSjkyRnJ3MGtGdnY5WF9hU2NIc1ZDOGNfeWg1cDdrSDJ4UTIxcnplMmhaVE1FSXJST0l4eklXX0NPXy02WEl2VmxLOXFCdlc1MlhpWS1aUXJGMVZsRW5Sam9NN3hHSW1Xa0hHdVRQYkJGd3FBV3VJQUc1eHJrX2ZnYVlI?oc=5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>16-05-2026 16:30 UTC</t>
+          <t>18-05-2026 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -1192,22 +1192,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Cactus waste could become a low-cost building material</t>
+          <t>The Pennine hills are full of holes – here’s how they’re helping fight climate change</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Earth.com</t>
+          <t>The Conversation</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNSVhIMmktbzJXLUp4cUdmUDdRTkJsSUdGbXhQNmFvZUJkV3RmUGxKMjR2SEpiWFBQUDBPQ1hBSXotUTY4cElkdU1MR1MySzRySDB4dnAtOXpDNUllUDNuZXkza3lfTm1ObS1fZmpVRWY1NWxic19ldFExVkQ3cXlmSlVqcU8xQS10Tmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNWTVub1RWTVBUYU5fbTl0bnJjS0pmeTdfdy1WbzZCVGZVRF9kWlBQblZCMERIcWJMc3FlREU2Y3BteVEtbkhIRlVBXzJyczFYZ2ZQN2pST0hxWGdfbExDQmwyaFFmSktZeE5pWTU1UWZlSmY5Nmx2Wko5XzQtMUFzVTA5cGJrMzQ1RmVZb3ljRm0zemgzaktsYTdHUHh0NlhaazhXTjQzMUgwRXRKNmpRQ2VYdUtfSE0?oc=5</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>16-05-2026 17:28 UTC</t>
+          <t>18-05-2026 09:07 UTC</t>
         </is>
       </c>
     </row>
@@ -1219,22 +1219,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Does Flaxseed Cause Erectile Dysfunction?</t>
+          <t>Drone strike targets UAE’s Barakah nuke plant complex, triggers electrical generator fire</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>stat.gov.pl</t>
+          <t>Rising Kashmir</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwJBVV95cUxPZ1NCRXZMRGVKWU1QUllsMzhQNnlRc0xIb3RkTEVTUFpNQUtoMGkwRVI5QS00TDcxX21uMDQ4YURjbXh2UEZNeGtKeFlUMkdkTFFRQUJxU19kb3h3d2J4VzM1YkluT3ZqczZleE1vN1N1d29UcTN2VFJrN1EwanE1aGczeFlwSTBxNWZYd3ZMUS1qS0k3aUd1QV9nVnRpeHFYWV9VX21fMmMtc2lHRWlSTDNLMng3d0dJTWdpVzFpNzVtbGxQOHB5VXY4TjVxMy1IYUtaYnhIYTU5S01MRTdUbm5KY29PRWpsUWtYWmJGYkNHb19FVjJJRkdaTG9ERzJzdlFRV05yYk5UeVhQNkdqUVVvWUhWNENiV0JqVG1WZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPQVZhbGhaMENuNERocV9QRHg2ZVBGUlRCMFNNRS15dmFBUS1vWjNQMUd6OUdOaGpmdjVKMzZieUtVSnVhZjNNb3Q1WG56RGUxdTVvNGlRdnJadVlPRmY1SXp0VG5Fc3pZcWJoaWpqSENqNHlGemEzZ3huZFIxZWlHaVlVbHoxcnl1OG5GT2tkekVtbmdZTWZqVFRJTll5akpIbmxDeVZMeGxULWl1ZDZuYXgyRnI?oc=5</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>17-05-2026 10:17 UTC</t>
+          <t>18-05-2026 00:26 UTC</t>
         </is>
       </c>
     </row>
@@ -1246,22 +1246,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>IMG_9270.jpg</t>
+          <t>7 Plants to Propagate From Cuttings in May to Expand Your Garden Fast &amp; for Free</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>thegazette.com</t>
+          <t>Yahoo</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPUzhFODA1QjRVQWlVQTZaSURvQXZPdUVncnMtcXgxOFF6NkozOVBXLXhyZUZJdlRzOGdQRS11X0VwSkY5V2k0TmtwS1VBbWl0cW9sMFJiNTRiYTVfd0ZvSUYwenh2RUdBRVA1MW5rek9ORFZOZ0x5NjFWbTNlTlNwRjdoUndYVk5aQTljTy0xWUc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQelRqTTNQR0RpejJxSV9ZdWhoV0FfOXdUQ3BXSmZTVnRYY3lCM08xNVNaZy1uREM0QXNiY2JiS0ZCTDJaOE0yVzhxM1pwTUl5NkszRDFSenc1UU9HREZpZW9EZEJHeDhSWUJBR29pWjhEX3BCY2hDT18zWlBrdnIyMm1KMnROYXFxNmlqbXV3ZTA1YzUwbjNrSUh6Qzhjb3Z1VjlhNkRBZw?oc=5</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>16-05-2026 18:51 UTC</t>
+          <t>18-05-2026 09:00 UTC</t>
         </is>
       </c>
     </row>
@@ -1273,22 +1273,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>How US hemp ban could criminalize CBD products – and derail Medicare plan</t>
+          <t>Workshop Print &amp; Stitch – Dora Tiho (Oct)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>The Guardian</t>
+          <t>TU Delft</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE8yTmNnLVBPNVladEdjTHREbzZIRlVBRmhPQkl2b3B3OWtaN3RjV1BzLUw4Ti0xa3JlQ1Y4akR6ZGNVVkx3S3Z6aFJqRlFUN3AzVUxqc2hfa3NXMmgwMTlYVGppa3BHR3MwNWQyVGpGU1FlS2haOGktcUxmbTR3Q0U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNX3ZNbHNxN2Z4WjRRRmx5djNNUHBnWkg3Tlp0MlBBZVhPTHRhZDM1NVRMZEdmMl9BYTItYmZJSDk4ZlBsenMxNEM0elY5RGZPMUdRWklKZ0pUc3FGVWd3MFVtVFd0T0IwTEJZd09OWjBiNWNnUi1NdW0tclAyeHBPb3BsUzJYeU9NWE01QzhB?oc=5</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>17-05-2026 11:01 UTC</t>
+          <t>18-05-2026 10:10 UTC</t>
         </is>
       </c>
     </row>
@@ -1300,238 +1300,238 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>There's progress around the world and at home, from environmental to healthcare wins</t>
+          <t>China’s Dongfeng will build cars at Stellantis’ French plant, report says</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>NOLA.com</t>
+          <t>Automotive News</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNNWpvTG5MWXZkeHI5ei0zRWJXMzM4bE5oYTc1ZTBrZGZ4RzQyY3dHdHVOREU2Wk5VU2xjX0ZNdk41ZFJRcThHdXlpY1NkVTg1YjBzSGZDUUJTS0RRSGNGNE12YWttTkxOVmdrX0htd2NhRTJzdUNZaEt1cU83eURZdFNWcnNtenJGdjc3clB0YW1wNS1GUlVDbl80dW9KOEl4Ym04bW81ZkYtZ9IBqgFBVV95cUxNNWpvTG5MWXZkeHI5ei0zRWJXMzM4bE5oYTc1ZTBrZGZ4RzQyY3dHdHVOREU2Wk5VU2xjX0ZNdk41ZFJRcThHdXlpY1NkVTg1YjBzSGZDUUJTS0RRSGNGNE12YWttTkxOVmdrX0htd2NhRTJzdUNZaEt1cU83eURZdFNWcnNtenJGdjc3clB0YW1wNS1GUlVDbl80dW9KOEl4Ym04bW81ZkYtZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE81ME1ZdWF0Y1ctd1NZNVF4QmZtSFhtQmhjY1p4OENJME52Wk9Td2lBb0Z1Q1BOaGE0T2x4cHJjc3FDaFR1UWN5RnRlUUFWYlFKY2tPRTQxRzBoY19vWlg1S013RHV0NWVvZF9wY3ZvQ2FSZm1zbW5tY3VMdVM?oc=5</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>17-05-2026 11:00 UTC</t>
+          <t>18-05-2026 09:45 UTC</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Coherus Biosciences</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Coherus BioSciences stock (US19247A1007): Q1 loss widens as turnaround strategy shifts to oncology f</t>
+          <t>New Leader to Illuminate Supercharged Photosynthesis</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>Mirage News</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxPRGc3TV9jUVBPQndhdnRCWVRMQkdjUC1TMXBOVDhVTXc5SWo2VndJRXZsVDV6aDRRbFJuX2g5VU9Bekp1QkZieHdydThhaVdydWN2TTAtdm1LSTRnOTMyY09CR054ZDk1VEI3MlFpTV9uTnIxUWQzc3VUZkM4b2g3eHMxeTFkaDB4OG9nT3hmd1BEMWRINVY0eWNhQjd6UTRZT2hkY0YxOEhCYTV5Sm1fNVdYVXdQWDhPRFlSa3phSUJuTk54?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE8xNWE1ZlVLVE9VN3VqeVZNNE52UTRWbUpUMVJzVXgzcFMwOHhPWkFhd2ktRkpUMnI3VDljSG03RU04MDZibEpOdkFNdjBPb1RpaVlWdEFzcTN5NzNPQ0p4djVQYkdiYXJ3YjVUclBFSTZZczEtdzlJQkV5OHZMQQ?oc=5</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>17-05-2026 10:24 UTC</t>
+          <t>18-05-2026 12:58 UTC</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Coherus Biosciences</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Coherus BioSciences stock (US19247A1007): earnings miss keeps focus on turnaround plans</t>
+          <t>VMD launches new online contact form today</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>GOV.UK</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxPTVRPdzJSLWEzVVJNblM3Z3lFMU5tb0ZDbmtvb2dlcEFENDJoTnRPTUxCLWlXZW56MGFnSkdUQW02NUNoRVZqQ19BUjVpQW1QNGNsWG94VldZdWhjRDhGOTA3Tlp0WURGUVVXal9sa1dzZ010SHFLaGt2WVlRb21tZ19oQURGUXN3Tzl0SmpyNG9QTWpvNEllakpKSy1SaWQ4VERNa24wXzF4ZVlXcXMxMDdfdnY2aUhBaUwwR29USXdCU1Bv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxNUFRiWDM0RDl5SkVvWkxCNnJ3bmpGcTFBUTZMSnBIMzJBQWlMYkNBelZEci1nNmpGcnh4Ui1RdktqNVBlaVB2THZxNHFKT3ZGbWFXNTQ0bGY1Ni1SZXdGaFUzT0NyUTBTRkJWQjJCdkJwLWZBU3ZCbE9lQ2tlbGxYT2JtYw?oc=5</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>16-05-2026 15:25 UTC</t>
+          <t>18-05-2026 08:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Pfizer’s Lyme disease vaccine shows 70% efficacy; Texas man sentenced to 12.5 years in $61.5M Medicare telemarketing fraud scheme; Novo Nordisk launches Wegovy subscription model – Morning Medical Update</t>
+          <t>I Own Dozens of Houseplants but This Flowering Plant Brings Me the Most Joy—and Basically Takes Care of Itself</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Medical Economics</t>
+          <t>AOL.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gJBVV95cUxPVnU1X0hLdnNoem8xSWwtUm9LQ28wXzM4aUFsUUN2U1ZsM0Fwb2dIWmNPdGphRVd3cm9RUzBtT0gzYVlyYUV5aHBnOEt4ck9CVnV0NEs5NTJkV2d1WnZSaGs3bUJYUHlzVVBMV2xwRDhnakZiWVlkNG5kTFBmTm0zNHJGNDlhdHhNcVNEQUtaX0ppdlZ1SFlXekZ0Z0Rtemh4TktrWGdPN1VIYnhGZmZnWURLWlhQTjNhUXN0RkV5eE01ZnhhVHd0RXlFNm5PNDBQTjQyOWpHMWRpTUJfV0Y5NjBqcmJvZ0FGWGtZQjdtZW5LcFI4S3U5ZHV6Zl9uc0NZQkpEcDQ1TjRiTnk3MjBGYS1RdjhNaVhvQjVveW5FRFpWQkVicHE1MVlLbURUZTFObTZtS19qN3JrdDF5c0RHb19WZzNTQW5OcWU2MEdGR3pqREVjQWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxQaUtfWUZJN2ZwZzVUN3Y4ejM4eUZUSmRrbGdsVGxvRWhURnpTbTFNRHBuMGhIUmZDYkFzQl9icDJiWkw5REZRcm1jMHpIWHk5TC1fVG02U0JLdWpfUkd2a3FBVGlxaHhzRGt1TVpwUE91WC1Ga1VPeno2bVZYZlN6TXRiTVlOWHlNVnc?oc=5</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>17-05-2026 02:32 UTC</t>
+          <t>18-05-2026 12:59 UTC</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>The week in pharma: action, reaction and insight – week to May 15, 2026</t>
+          <t>Nexteer auto parts workers in Saginaw force UAW to schedule strike vote after rejecting two sellout contracts</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>The Pharma Letter</t>
+          <t>World Socialist Web Site</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOb04xYmh1V0VBX05OZ01haEl5NkJpNG1QbXBjckNxeUozeWZ4TEs4SzQzN3doUTNPQU9qWE1fNU1xUlVJYUxLNXFXRHpDb0Y2cjFUWEJDblF3Si1ReHJLVFlhWjhkTS0yOW5Ob3BTUnZVcDJuMnducW9hU3dzbUFTZGc1WmxDSGIwd2NVNEw1WXZZeUxPb0dlTnY0ZGJ4dW9uNmEzVzVCX0h1U3NoRVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE1RVVRrcVc4NWoxaHlJelVGQnlaNlpwQmgwZXhLQkdPMi1XMXdYaE9NcHR4RWhESHdJMW81dHhEbl9iVHo5ZWZ2WVVneW44TjRYUUh5VTZKWXdHd2Z6X3VPOEYxM0ZvVjQ?oc=5</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>17-05-2026 10:30 UTC</t>
+          <t>18-05-2026 03:45 UTC</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>- The HinduBusinessLine</t>
+          <t>'We mould trees to grow into the shape of chairs'</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>BusinessLine</t>
+          <t>BBC</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wJBVV95cUxNY0V0ek4yUU1QVGJaR0l3S3NEMmxHQjAycVhTOTZ0TjlYdDVpVl9meUFkMEY2T2VTT2NlTzJ1b2pQeDY3T2o3R2JJVTdvQk1DS2FGRmVSaHRySlhHRlBtRGUyeTNDcHg3bUdhNkpnNVFIOUhUZWt2czJDdTZBT2FrVS1Bckh4ckJYMVJDYWNiaTl0SE9WWWhnb3hQTm9pSkFDZlZULS1PMkl3WTRCZERDY1RHalJyZG9QV253dVNlaElMT3pCUGkxbU4yRk4zUV9FdENXa0hKbXNINkNTamdHVWtUbnhnTXhzTjJOQU01LW1HbzFHejJTSGNDcS1EVXJ2QjRYREdfTlpCMlI5UjJMSjBXYVEyRG11UHdlUlNJOGFGUmVFZldTTTMtYVZFemFQQlV6NFhrRlhqWDh5N1BycG9Fa3p1STE5SnpvY0VJNXQ1X040N251THJHWThuOVk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE85MjVVRF9mc1NMdTZlc3J6TEVKWGdjRXdCZXZPRHhMeENYU2FiRjhMUUNidmxqTzJ4alYybHJIeHlXRDR1emt4M1BTQmQ5ZzF0eTF3QWk1OGtQRFEt?oc=5</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>17-05-2026 14:42 UTC</t>
+          <t>18-05-2026 05:06 UTC</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Pfizer Inc stock (US7170811035): new trial data and pipeline focus keep attention on the pharma gian</t>
+          <t>Architectural Plants – Looking To The Future</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>The Landscaper Magazine</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOdjBLX3gtTjg4cFk2VEtYZ0pQS1N0QzE5NGRnZmE0cWRaZ1VyaFZVWlZqektEbURqUFhEOFRnRnl5NWJTTE5XWW9GcGNmQXd0bHR6eDJfcWdMOGxESWROZ0FZbmpfaVVwa0RNemUxYnVvZnJIQ25hZUktX3VfQl9LSFo5TXhoRC1ZZnl2V2pQOXdSTlZhenpxa2c3d29PV2VxdVM5M0x3U1ZiOC10TkdXeXowcm1HWUQ1MW5FVVVGZXhlTXo1aFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTFA5UWY5ZTdxOXVDeGxZeTdnUVdSdkpRYU12bHg4ZjBLMnRqakZZWjdaVEF6REYtV2NYM2lfb2FfR0VIcm13aDRheHBudTdMRjdJODdFT05DVHRHb0lVLVZkX0syemEyTUdSNGJVMk5nQlBLMmFNVzZrTFlOR1Z0Rms?oc=5</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>16-05-2026 15:29 UTC</t>
+          <t>18-05-2026 09:14 UTC</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Is This a Sign Pfizer's Aggressive Growth Strategy Is Paying Off?</t>
+          <t>Iranian Nobel Laureate Narges Mohammadi 'Sent Home' From Hospital</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AOL.com</t>
+          <t>Radio Free Europe/Radio Liberty</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNNXNtMGl5X0tLZjRZYkplcmtsbjhldWxteXdJR05hMmhhaGNPWjY4cExVUXVSaThDNjJLT3doY0dXR05mTVlUZ0p1Mm1na215aGg1MWpETGhOSkUwUVhiZjl3YVNBaGpFZFZPQVVWdlJMYnozd0NpY2VnREdUVVZzUHVJR0NqQXRCck5J?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQWnhyaS1tS3NVV19VeVRlS1RUeUhFblVCTkRCWmg2Z2YwTW1uR051ZFctc3F2eEcyN29hbkJkLUY3THpPVzVaYVRlcTRybGlrTGVsX3ZvTFJyQmRELVNHckg3Nk9uOUw3V2RyN2lZY0dIMW1jLWVQSUVTdXBTZGpuVE55cDBQcG01?oc=5</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>17-05-2026 01:38 UTC</t>
+          <t>18-05-2026 04:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Coherus Biosciences</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Pfizer (PFE) Juggles New Trials, Site Shifts and Mixed Wall Street Bets</t>
+          <t>Earnings call transcript: Coherus BioSciences Q1 2026 revenue miss prompts cautious outlook</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>Investing.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQYXo0bzN6c3NRR01nNElGNmxNWGdCVTVGNTN6OW1uWDVEamhMZjFHbDhwMGtNaFQwcGNFUGQxWGxqUjhoLTBhNG1EWXluZDlNZFhKcjhoc09iUF94dHZSeTFNQzR4MVh1SnNVcmNWQm1ybVU5Qkx4TVc2Z3FYNmstczVGUHhUX0VlRG5PZjVKSUlaSHF4cHVES0N6eUlURFN2aGFqMnpoTTJ5WVAzbFJDTFpmb3M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxQQWZIcXE1bHc0eEkxWk8tUGpZdTJNaGNBUGlXT1J1RWluSlpKblJ6NnZYOFBzQkV0V05pQzZ1TWgzMWw2dHBoVHFDSTJNVTFsZF9JdG5KazRyX1JqVzBTZzZ2RFVxT2t6X2doQ1RlZWstbGJUREp3cV9LUXZfa285RWxlVmdsUEJCMnRjUkF3OFZFLU02RG9FNktFWS1KcU1PVmhrNDNYb0VCcHpFd1U0cTNoSlc1WnlpSnB5MnlZWldFX3F2SEtGNno2UFUxM0FKYVIxbkZad3RITlhMdi04?oc=5</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>16-05-2026 15:10 UTC</t>
+          <t>18-05-2026 09:47 UTC</t>
         </is>
       </c>
     </row>
@@ -1543,22 +1543,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Comirnaty mRNA COVID-19 vaccine explained for US users</t>
+          <t>Pfizer - Tata Motors PV among 6 stocks showing bullish RSI upswing</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOLUV5UHd6VzAzUnRHaFhLNWpDT3VmMzFCWWpyazBIU2hCek4wdjlNYk91T2w3Y1dYb2VVU1M2S3N6MWdtZkhFRFZqdDZ1cVhOOFVHM3hhWmZ3MUdkcGVzYnozendObzZqQ24xTW43dnkwVkVlQXNWQ3RvcHo5RDk5UXZnai1XcmdqcTB4RGZBamRBN2RyUk1JaXVkRzV3aUJZT1gxWWlFUkg0b3N3ZEpSbGNYMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNcFBrR2phNnp6MWFvM21tSjUzZkhfVHNxR0J5bFZvX1pUa3o4ZEJoUEE5NWMzYnZVQ1M2NHlkLWp1ZTNJRm9vbTRQaTFINWMwYUhuSEdHUTN5ckdTR2lucFgzeG1LVldzQmNPNkFjTm9ZX29jNFkyek5kRi1uejN3OFZZMFMweXcwMUFZc2Q3SW0yMzFSVFdNRnNhODZxTEZNNGVfMVBTcjVVcllhc21MekNfTmJrZzQyNnB0Y2pQMm4xQmNkbDVzWVREVEJSNVIyRWc?oc=5</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>17-05-2026 11:37 UTC</t>
+          <t>18-05-2026 05:00 UTC</t>
         </is>
       </c>
     </row>
@@ -1570,22 +1570,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>My Top 3 Healthcare Stocks for May 2026</t>
+          <t>Race intensifies to lead next wave of obesity drugs as trial results loom</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AOL.com</t>
+          <t>Pharma Voice</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE9OUl9Mb2t2bjFRU2dMdUMzdldWRjh0QjMwSms1Mkl4ZVhTbWppVGs0bTVFWVVfckRTT3ozeG85MTdYem5XQlp6MHhWUmZkYVMtMWRYT0VMZFdFaGJEX2JWSXhMUjBQQTVSclZzaHVwUnQ5UmlDM1BLOXBsUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQOGhYeC1mbVd0akxkWV8xa1BoVEFrUUF0Mjc0ak41Y0ZZeTB4VWdLWEh3N24yZzF2UmF3a3NUeUFscng3NUNBSlRYVFRzUTdab21ETVNQdXl0RDI2UW5MZF9aRUJCel8yTlFVSnpYbkd1ZVdZeXRTS0oxNmN4cWFWdFM1Nkl3NnNwcGtTVlVhVDZTWUpuRzRDUnZ2TjVLWFdM?oc=5</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>17-05-2026 08:31 UTC</t>
+          <t>18-05-2026 13:25 UTC</t>
         </is>
       </c>
     </row>
@@ -1597,358 +1597,358 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CureVac stock (NL0015436031): FDA clears deal path with GSK after BioNTech settlement</t>
+          <t>Why Pfizer Stock Still Looks Deeply Undervalued In 2026 (NYSE:PFE)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>Seeking Alpha</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNNnVhM1RwbTdCSDV5YmxYdFc1T0ppU3RPeEVOV3Y5dTNERTZXdVRqRmhxa2JfR2RnWTdXajQzMnhzc2VhNEhnZEpYejBZYkhlbGhfZjlUd0llTlNQZGRSR2xVYnBsTkNYQU4zSEQ4dE9SMlYxeURqYnZ1T21JSjd1eVNMUlBMQzFBSWFaNlpCUE1KM2JGN3hrRFZhTDItZzhkTXZKeG1VNmpZOEJ2dENVUldZMC1nMVpoSDFNWUF2M1dKM24yYzlqN0dB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPY0FOUG0tc1dQLXBwN3dfeXREYkUtLXVxLXF0VjlXMDB1UFZ0dFZwVkFITDdrVm1NVHp0T3ZiN1ZsNEMzMHZsTHp3ckV6TDZQOEJObFhuLXJwdmFCSjNHS05PWm5BcjhTSEZtcU43RUdTemJuQzhfTFdXTVJBVzNvb3kydWFTcWhFWHZQbDlsMlJMM3c3MHNHTUpmaDI?oc=5</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>17-05-2026 06:18 UTC</t>
+          <t>18-05-2026 13:28 UTC</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Biogen Pharmachem Industries - 13 penny stocks plunge up to 65% in 3 months. Are you affected?</t>
+          <t>Thrivent Financial for Lutherans Acquires 72,504 Shares of Pfizer Inc. $PFE</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>MarketBeat</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9wFBVV95cUxQaHp6NGowYTBvb3NodnBCd1YxbUR3bXJjaWRQVWx2MlgtMTk4Z0ZtZzFTSDlHYUNOazJVUkR3R3lGcUFwUVpQQmx4Unh3THIzeFdYeE1WZ1lVM3hza1BISFN6bm1ic21BbVRqTWJoc2ZHaXZ4c0hZLTMtOVFJSlliMXpKdmNQdUNwNmR4djhRRHRGTHF5YjZsaEZLcnFKcXRnSGtaM2lDVms3V09UV055b19ma2JfeHA4UGNiU29qUTJHN2NnMkN2a0dPTnZaU09tNGhzOTlZRU5TMktXUFdEb1V1Y1k1Qmh5Xy1uVDhCS2dJQjZ1c19v?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPZFMxeHRfMGhTN3ExbFdNclFic1pxWVFlZER5dlhzVEV3MHhTRzFxY1ZzNUR1TXYxZ1pXZ3A5QTVOOEU2NjZkYzdxeFdpZ3psX01ZMzNuOVdpUGdfUEc5LVQ0ZU9ZeGhHUnFidEFoSG5qSmlENnoxeENlbERyVlM3X2FINjJ0SDgyWnFiREEwOU1rZjNFYlBHLTJBOFNERUhsbVlFeUlwcWRSdnIydnVPcE95VW82YmtaVU1FQnFLMkdqOFlycFcwdjE4Vng4QQ?oc=5</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>17-05-2026 09:05 UTC</t>
+          <t>18-05-2026 11:23 UTC</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Biogen Pharmachem Industries Ltd Falls to 52-Week Low of Rs 0.44 as Sell-Off Deepens</t>
+          <t>Addressing Patient Concerns About Vitiligo</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Markets Mojo</t>
+          <t>Medscape</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOSmEyNGcxcDVRTW9IOWtKWGJVT3I5YlY4MXRLNFlBV3lrVjRLbFdwdGotQ21oRTNjLVFmdXk3SnhRcEx3RGc3eWNRX1hQdnFJdERsUHFiSGZ1VXBkN3htNUpnUlJDQnRBX1R2djkxQ0duV1FPS04zbHdhb1ZkR3NvSXpOSHZGWWg3dWdCd2k3WVhnbkJrR2FDTnVIQVZNVzVkeWVvXzFWRE5XRExILUJjc05FdzhzYmItMnQ0aw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxORE9wd3k3TVdwRmdmYW9JTVlmMDV5bTRUcG9CMHo4bFdQSmYza2I3clc5dnE5aVBtd3JFM09zRVJ0VUxNbUlOeWxlYUVyd1g3RS12QnNUZk1rWWdBeGlMTWo1X3Q1WkwxNHpEVUZXTXdsLUZWNFFTRE80MWNiM1RZNXB2MWlHRmZHbUZvdnhFMVlJZHQ5aXN0d3VYMFlTZHJr?oc=5</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>17-05-2026 00:15 UTC</t>
+          <t>18-05-2026 14:34 UTC</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Biogen Pharmachem Industries Ltd Falls to 52-Week Low of Rs 0.38 as Sell-Off Deepens</t>
+          <t>Pfizer Inc. stock (US7170811035): Q1 earnings beat, higher 2026 guidance and rich dividend yield in</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Markets Mojo</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxObjkyb1Zfb2Jwa2xMNjJsc2YyWlhzQ0taY0dTWnB3aFdKekhSYUJaS3hzTkwwRzZGSlZpMWlYNG00MktoZHM0QkFpNXRnaFBPNDJremUzMFBVN1l3cnhqUlpNNG95UWdPS1VhdjBuMDFFR19BV1BENXo5OU4welhxRUZSUHd6ZzIxTDExdDVhYzF0dHg5UGx0X0I3TzlMVE9CemFJSmtvVWRtcEUwNEVOb29nSWhJQlpPU3lKdjBySTQ0elg4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQNC1CM0pHSXd1MGd2MUJDZnIxWHVsY0JRLUxjZGEzYlNnVGN2NE04Sjk2MUdzZG5mQkpjX1lwb0tBalFnYmF3RjlsQ3RWZDlwSGppcGxlMFpUYTZHb1ZLNTl4VFFuaDZZT0tsSHd3ZWZtV084cmhITDl0aERKM1lmMC1BUDVFTHF3alV1ek1ORll1NVcybDJxRjZEc3BFdXBSX2JSekltRnVCaGJWUVljdUx6cHkzOUZPX1FMUHh2b3phVGVM?oc=5</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>16-05-2026 23:26 UTC</t>
+          <t>18-05-2026 01:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Best Healthcare Stocks to Buy in 2026</t>
+          <t>Daiwa Securities Adjusts Price Target on Pfizer to $28 From $27, Maintains Neutral Rating</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AOL.com</t>
+          <t>Moomoo</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQQnRyY1pEUTRyZnR0cXBWNkNXMmtORzRGSE50czhxVWs2dU1ocjc3NWRpaTl4QTFCWTBUNll2Zk5RSk54MGNyWE1femFfamRJQW16RXBuNnRvekxHM3o4Wk9Sa0dSZjVsQUNySEhLZzNxWEdEeUwwcU9tUXZTUjhFZg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNTDRRM2ZpSVZPMGFRSDNVeDdYa3F1bEt3UDN4SkZYdzdJa1haazFwVVdMak80T2R3YVQxZTFiNkppaFd3QzJKSDZFZnp4TlZSTDlZajdyWV9tU1FvRG9WeDNyZ1JGREVYTEF5SHBFSVBWdTBEeVVDTnZFVVQ3RTMzRk1fVERVcnhmMUlnaVk2eXM5YWdqWENVSjBEcnhUUkVLMWc?oc=5</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>17-05-2026 09:56 UTC</t>
+          <t>18-05-2026 09:55 UTC</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>A Look At Apellis Pharmaceuticals (APLS) Valuation After The Biogen Acquisition Announcement</t>
+          <t>Pfizer Just Locked In Its Next 5 Years of Growth -- Here's How</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>simplywall.st</t>
+          <t>AOL.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxNcE9JN0M3bU43ZGR0LWNvOHNTcmY2YUtydklxTDMxZGRpTW11QW13RDg2WkNiU2RRaHd1Qi1lNmFsanNEeUJDZzRHSGVzeUkxX2VJdHRKTUdlUFdPaEFwbEJ1NHRTMjctSmd5aGhKRjFhV2JRdkJMc095Yjg5aG1xVlZBd3ZTbTMyQmRMTXRRMUJseUIweEtZM2hiRFJKWnBKN3BTR3JRT1ZVVFI0c1lodUZRbW1QVUdwM05jWkhaRGduNmtEOHJjWWZPVUk4bW44RllUcmYyUHhKUUZVX05Jd1dJNnhvbDdob2FSWkFR0gHzAUFVX3lxTFA3OUNZVnA2bFY2MWZGenlDMXRORlota05QZnR6LWJoc05kQUdVYVBnZUptc1pLYnRYY09ITUdRVFllQ2pxTjl4NWN3TVZVN2ZIdnJac0ItV1hDcFQxSmxkU18tQW5lalZIUzZqdWdfcUE0SGdiMEJyTkV4OXA1X3Z6a2N5RlVGU0tleGM0WkpJVG53b3V6Z2dZb2hZdUY2aGFSWXpXSzY3NmpjUTkwSG1kYkJzV1haNzhYVEZEcGVSb0JCVHJ5X0l4Yngxd1M0YkZoUG5zbTQ5YTlnTFNla21meGZfVU1MalZyZTJ2X3VWcTlwaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE1wUTUxZXhWS0tQTHdkbWx6amFDb1FIT3FWMDNkUnpnNlIxSHh6akxPdUZLTWdOTjlqTW1WbEJRaTVWYW5BMUpZUEJhUl9maXhXdTBJQWJJWDFZTmt4MUp6bkpSTmdUQV9VYUhaSDRSSldFMlpVR2FBbA?oc=5</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>16-05-2026 18:51 UTC</t>
+          <t>18-05-2026 12:49 UTC</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Markets Rally, But Biogen Pharmachem Industries Ltd Sinks to 52-Week Low in Stock-Specific Sell-Off</t>
+          <t>Pfizer Faces Busy Week After Friday’s Drop</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Markets Mojo</t>
+          <t>TechStock²</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOazJSRTZrM0dMYjJFU2NLbVVlTjllYnduVFBOYlFpOXZRZGZwbWNXVllhZlRIX0RfNk5aNXZwM3F2dzY3ZGl5VjB2WVRad2RORHg2WEJCUUdJYWpLc1BvWFVHSlVhMTVXMFo5WWxPcTg2SXdjWFdJc2pHY3NYeXUxTXBtQzE5WjFOWGNaS1ZPdjg3MFgzSlFhc2FQbHJTWkVJQmVqRTdramc5MnhOVkNra3dxUlMxZ0lteVRodQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxNdlRwSGkyTHhmeWs5NjdXQ1BHcE9ldnlGODVZdXFGVk90Nk9XN2Rqd0dqQTFpM3VDVmtGbnZLZWozVU1KenNLRmdTcENaRFFrZlZNZXBJOFQtQzJWc2lnVl83Ui1mQnZGS0tPVzBxN29KWjlZQklQc0k2TU5lYmxrUFlocw?oc=5</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>16-05-2026 22:15 UTC</t>
+          <t>17-05-2026 19:35 UTC</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Biogen's Alzheimer’s drug fails to meet mid-stage trial goal</t>
+          <t>Alembic Pharma gets FDA tentative nod for breast cancer drug</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AOL.com</t>
+          <t>ETPharma.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPMklKdzZ4Zk9wdTY0UnJwQlVNUHVCc2R0eHo4WUFwWmhsMjVRaEZsX010VjkyX3JfejRNSFB1RTlvODMxUUlLSjFlZ01Cd0xqbS1DYUpNRUI2bWJVRkYwazRQV1Q5YXd6UUdhUFpyVFJaVkNVNDlRQ1NWdnh1TWNMVEpZWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxObUtnRlVtTno3LVlEMkhqak1PUTZrLVhBazkwanhNNlppdFpWZk9WeE9vRHp4WEFJelVHRUpacHRudzhUQjNpN2s5VVIwUFBwWFVOd3F0amFNbXM5SThwY1FKV3NSRkRMSFVMZk9ka29NZmY3YjBQRjV0RHZqcWZ3bFlJYnkwczRLd2dPQTNOQjZmWm10VGZkYjVPd2JldlpWcG1qa2MwWGpnNTRHRG5WdXNJeXR4QW1oT2pmdm0xTV92emZrbGxUbXdSZzlRdzRZSFRPejhuX25Caldsd0p6OU9rS2hpQdIB5gFBVV95cUxObUtnRlVtTno3LVlEMkhqak1PUTZrLVhBazkwanhNNlppdFpWZk9WeE9vRHp4WEFJelVHRUpacHRudzhUQjNpN2s5VVIwUFBwWFVOd3F0amFNbXM5SThwY1FKV3NSRkRMSFVMZk9ka29NZmY3YjBQRjV0RHZqcWZ3bFlJYnkwczRLd2dPQTNOQjZmWm10VGZkYjVPd2JldlpWcG1qa2MwWGpnNTRHRG5WdXNJeXR4QW1oT2pmdm0xTV92emZrbGxUbXdSZzlRdzRZSFRPejhuX25Caldsd0p6OU9rS2hpQQ?oc=5</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>17-05-2026 01:39 UTC</t>
+          <t>18-05-2026 08:14 UTC</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Dr. Reddy's Schedules Investor Meets in May-June</t>
+          <t>Pfizer Inc. stock (US7170811035): Q1 earnings beat, higher 2026 guidance and rich dividend yield dra</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxPbDR6dWdlV25JTW9fS3dDNzJ3QmxIWS1WMGdZaml5U1JOUkRGa2YtT1pRdWgtQTlNbmd0U3AzekNrVnRkWmJzX2tJSDJtR0gtbUZVTDJaMXpkdHlZVXMyUk1fSnpZYlFVb2o5NU56aklWNW5ScHFnN3RHZmU0MHdUQmdsSU9PSU9rSnNySUJLYlNwSVdCbXZuSVZDbkdmVlZESGYyckJyOUhXb2w4blhEWnFrbGV5UkRSZkpWVl9mSmhBeUVIeE1La3RPRGk2ejVmWC00REZhYVNDUGlUd2N6elhyLWprenlLcFlCcWliMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQck9JNl8yNHFYSm9Ba3hsanRZRnlaYjFYalduMVVSUldNcTY3NmphWjV1WDhkd05fYUppUW9NS2JwZkRUdjdWNXdBcjF1OFEybGRDZnFBNFJYWFh3WUdNOGpjZG5fUFR6RFp5em81WFAwUG1xOFZQRHBwMHc2cXFKd09SZ0xEcmJZTkFBZ3dNN0M1bDVZTWcySWktNnlpTWUxZW5kXzRGMXZyb0VBNERJNFQ1eS1RVzNieGRUM2RhbjNFbnVu?oc=5</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>17-05-2026 09:43 UTC</t>
+          <t>18-05-2026 03:45 UTC</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Dr Reddy's Labs Among First to Launch Generic Semaglutide in Canada</t>
+          <t>‘Regulators were WELL AWARE…’: Whistleblower 'exposes' FDA, CDC over COVID-19 vaccine injuries</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Medical Dialogues</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxORHJITjBjOUJmUVhGZ3I5amhKX1ZUU3lNSTl4TDZweXg4U2xlYkZaMkpiS1N6OXVIV1FyT0VuUjRoajZIRU5uelprSldVSUxlWmhNTWIwelU5VHBvMEV4MUw1aFB4VlJ4U3ZuR1cyRDBZRVZSMHJWUGVFNHg0UHVoWHR3ajFkM0REcFBnOWI5VUxtN04wUTZfZFFpSUlRVjFCaE5SX0U5UXJndm9aU3ZZLThQUG9nbzRuZURMdV9ub9IBxAFBVV95cUxNckpKeFBGeXhHQ2NDdUtmZW5jYW9CN2FNcVVncmI3MUJ6eEJWUWJoTXFyczI2Vjd6eWdlT0dOU3hKN3BjS2dPV1RoSlZ1T2l6alQ5bTd3Wk9pUGV1ODRYSmU5U043SVVEZmJqSHJNSFhvT0ItSklJbDlLSkEtZF9oVWdmblhaSC1RTGlGQzBXRF9LOVo0dGo3dU5GZnVMZTZPUzJuQVpoRkxlSjlSeUVNbTJzQmpscnBNNUdFRUF4NUhjcDdT?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxQa3VsbEpHdVNKRkdVS0R4cEs3R3gwUl8wSG5UdS1yYlRkR182NjBrcmswcFBxTUVxYXhpNEpveE5xSlFhZnFiQkdXeUpWR1FESkUzMkRxOWNON0xQaG9iUWNRaHlVYjlGRlc2a0U4LWNMbUo5U0p3eDNEYXhwbll0VU50TENBZ0U4ZHRqWG1jWDJUMEhmTDhYdjh2Z2dfUkk5aFI2ZnlNc193NEZUbFNfcDc0ZEd0TXdiQTRTUjI2TW5YQUZpYktuMmY5eExPUDFaSTVjb1JLQVFWUGQwa1IyNFo2aXFGVjdmNlV5enRoc25HRGk4dTRVaEg1Q1hZZ9IBgwJBVV95cUxPbXVpWG0wNkFudE55X3dNMlVhUUtsVE00NEp5eFdSV3l1V1hDS0djLXVGdC12ZmpnLUdNVllkVjhZVkRjOW1rU3dmNjJmU1lGOGVKYWppcWFGeFBMLTl5QXZxX3QxVjlmUTdTeWhPWlFzcjR6OWJCcEZKZXJ6WXJkTkozYndyZjRzaEVGbnRrQmVKYmQwRjQ2M2tSLXVGVnF0S0tnYXhLdzl5c3BjSHU5Mjhvc0ctY0tkOWI4OE1BUWlCQi1oZU1ZNTNtNFBjMTF5Y2Z2Z0ctUG83R0NsX0c2anlyRkRNWUZGVWQyb0xoSzFDMnVSSkgyRkI4WlAtZmJxd1Z3?oc=5</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>16-05-2026 16:38 UTC</t>
+          <t>18-05-2026 11:10 UTC</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Dr. Reddy's Launches Generic Semaglutide In Canada, Expands GLP-1 Push - Dr Reddy's Laboratories (NYSE:RD</t>
+          <t>214,779 Shares in Pfizer Inc. $PFE Purchased by North Dakota State Investment Board</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Benzinga</t>
+          <t>MarketBeat</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPeXUyYnV2ZHJDVXZkWHBoN3RTN01SMkdkekwzZVNMdXVWX19aSkdBSmJrUDBaXzB0aFVtNzRKNGM2ZDZuaEhrNy16UWpFeEpyWHh4bnRtMkRkZjdMdGdnQUFsTHZmS3dyZVJHZ01kVl9LTWt0MVRBQlp1SzFJaXlKQ1V1ZTNfMUY2aDRnb2FocnpIWHlTY1hFYWNEMllKdEZHbDhHSFlIR0RSS0s1TmxNMGx4SHBPT1BrWFVaZ2Nwb0I3QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNc2h3dHhZYWo2anFGU0VuTlI3T1hzWGNOMDRvQ1FLWExxYjlyVTV5TnlFUjhFNUFWdkdNblZnUjl2U041OXNKejlBMWZUQ1VCVm85MkNreTFseUQ1c0hMeHRJMFcySTFfSkxKNVJjRkk5QVEtd2FsZXFqcWwzZWwwQlN4VVZVemhvaXkwaUloLTRCbTJFbHpwZzVvbXVWTjlyM2U2MFZpVmRwOWVHZDZpWXZoU3NnNUZkSDVpZEg0dXpzSkdvSXUxeFdWdGtnaHZwVGhNNkFheXI?oc=5</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>16-05-2026 19:17 UTC</t>
+          <t>18-05-2026 10:03 UTC</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Dr Reddys Laboratories Ltd Reports Sharp Decline in Quarterly Financial Performance</t>
+          <t>Pfizer vs Eli Lilly: Different Bets on Pharma M&amp;A</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Markets Mojo</t>
+          <t>AOL.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOZWJjZFUzYjVsekJ4Zlo3THBySUhyTTd1Y3R6X2UwRk5mRk96Sjh3a2JCLW9xaFhwYUhDZW82WkFzNUh1NFhvRjdwMFF0ZUNfSW0xd1NKNjBNSl8za3RsMUxjVklOZUdlRnhaZHBPdllxNlZUNDhQTjFsR290Q1dicXJvcjFDSXF0VVlVWGlVMEpvTHJhaUlqZEhTU1N0RVFxRXZnRDNzaWVPX3o4NVBpUUFPSkVRU2JsaEJ5MUh6Y0ZGX3ZRM3Mya292dm5nUC0xaTVib2xJWko?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE1melkxQ0dZMEpuajhZYXhwaWRVTnEwdGZHSF9xZ1prSE9ycWRtTTlSXzAyeEJaUi1XVU85M2ZBSEFCMWpJclBPTDBlNlFVYjdYN3FFbFFwM1lTOGRYaFhPUnBKanE3cVU0bFJoVHI2T3k5UTlPVVN2NnFxdks?oc=5</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>16-05-2026 23:53 UTC</t>
+          <t>18-05-2026 08:31 UTC</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Dr Reddys Laboratories Ltd Valuation Shifts to Fair Amidst Sector Comparisons</t>
+          <t>BIIB SHAREHOLDER INVESTIGATION: SueWallSt Investigates Biogen Inc. for Possible Securities Law Violations</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Markets Mojo</t>
+          <t>PR Newswire</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOS2x1N2I2MjFFT2hVWHI0STR4ZncxQkZKXzMzNXhtdnczNkc2UFVOX0Rsc09zeGhKUG5IOHZmVjlEY0lCOGpIeUx4T3M3ZGsxTmpYeTFkUG1DTWZTX0lzV0VacjljQUVxeUdrT2xiRkRtMDJ0NTl4NEFaOHB2cndpTG94TTVZbTBiblpqY2JZcHZmUGtxbHJ3VEU5MFNoWkRBd2JNd0R4ZzBfeE5nVzItQ3RSckJTZlZQejFSNzJRX09XOFpnbnNJMDlORzlxUUli?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxQRUM1WVEtenFuMTBGT0IyMzU2U0c4RWgxNFlSS0RUSWdrSWdDS2s2djJ6NkpjZWFQUFU5dF9JS3RVN24xRDZpNlhqS0J6dTJxYlJjVHFhbG1ocE1ZcGVyVWFfNjhVbEotQlZhd0s3SEVwelhjTWd5azYwTE1qN1dvUUJmb2pkTm1NZmxVUWtGZUhNUVBEdnhCeVIwTjdWYXNYMkZibEZ6ODFUNDBBMHlsTHZPVFJlUEZOa3hpa1JvSmhMRHIyVldpb1QydVpFV0NjbDJkczYtaDlwSE5KRUFUbE5PbW5jYUxVSXp2NWVZeTE?oc=5</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>17-05-2026 00:16 UTC</t>
+          <t>18-05-2026 13:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Dr Reddys Laboratories Ltd Quality Grade Downgrade: A Detailed Analysis of Business Fundamentals</t>
+          <t>Biogen Pharmachem Industries Q4 FY26: Mounting Losses Signal Deepening Operational Crisis</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1958,1119 +1958,3144 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxPWlAxdU5WTkpfeVVIeHk1MlVkdThSQmlfUTFaaUZwcmVvZXpvNXR5MUNwa0c0dndMdmlTLVRxeHJyNkpIcU9MX1lsTUlKaEpqWkNQXzBGdVJseDNaSXBBek5fVnkzUmRBbG5DSTV3UlBWdDNJUGRONXl4bzRnWTJjdERrQ2llRUYtaU1GOExnbWp3bG80RVJVaTlwamdhTHJTQlRSUU01RGZVWEJJNEZsSVZFdGFaNGp3Z1Z2ZGdyci12QVA1OG9hZzJaS09Kb01fZmJIQVNOdEE2dTQwWTFVWTRZbWdqcF9Q?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxNR3dHZjdXZGdtX2lKVFFySTFpZWVKNUVFUVBIMjhmcEJpU1Vra0Q2SUhmYXl6Mm90SHFkeC1EX092bl9US3VFc2xmQjhQUVA3WnZFVnQtNE8wUWlOaU92cUVnM1VIc0g0X2UyZlZjaENpYWZEbHJhdk5yaDJ2T2Yzd1dCWG85SnhoRkIwNm5wbjcwbzBqMm5iRmxQWnlnWHBRU1Z0V3ExaGxRMnkwSUNrajh4dmREYVhtWDRvbldPUXVPWDNldzNOS0Izc0VHa3ZiSHNsSkFuMFpzZHBaMGc?oc=5</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>17-05-2026 00:16 UTC</t>
+          <t>17-05-2026 23:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Tata Electronics, ASML tie up for semiconductor manufacturing in India</t>
+          <t>Wedbush Maintains Biogen(BIIB.US) With Hold Rating, Maintains Target Price $196</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>Moomoo</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxQaDBVdXVnWGNOYV82MVVpM1g3NnZlZkJyWmd4T29PZjduQzBZRjhsQk1tNGpFT3ZLSXVqV01DNjdtRTJqRTJPbG9Ta0hDRGd4NGVjVWhfT3RBY0d3R0d6NGZmbVpMSDdfTmdqVnh0aHNnTGZvMmF1a0lKU2w1Z2VROVRabnpINjREMEZfdXZFX2Y1OTVkWmxUSTNTQkZyMEp6cFBZMGdFazNBcjNwb2NRaVM4SkRLWG95ckJ2VENZSFlSLXRfdXg5ajNLamo2eFc4a2tTYtIB2gFBVV95cUxPTHQ4Wk9YY1RVMmRpN0JabGNRanRxdVRhSG52OWRFZWJNNFoxTWNGV3pTcWZGLTRmZDVZVWxUTDRMZzB6akYyYUJDUFB5WTU4dlNmTDZVbVpxanVwNGdvWXFpcUtjZDhpblFia19uOTV3UGQyZlRMRzhLcnRacTNqUy01RFhBbW1oNWdLY0pjTkRHY3BHSk5uSWFWUHBZRVFLZlYxWVNXajBBSGdVQVBCOG80NWRHNzdNWlljSGdjcm82eTY5elBuREI5ZUFHQ3QzZVh3QUNYTmRtQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQdnVWTTViRmFqUl9hdkxQdEc2ODI2UG41cnFWb0tiUlFfNFljc0R3eVJkbTVFbVpPd1c3OHdSc3pGZER4b0ZIeVBXelBUZjY0eVd4NXBIZVdUT1VLdFVObmNoNERKeXNTWGtVZXI5QUY3U1pjMUlUNXJwSi1HSUZiQWpVUU15NXBGTnFqS1VkaE1ybmtyUEFBcks0bkl5ZDJEM0U4TTl3UVRFcmxKd2YwWEhrNA?oc=5</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>16-05-2026 17:02 UTC</t>
+          <t>18-05-2026 12:48 UTC</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Interview | ‘India, Ireland stand to gain enormously from collaboration based on co-creation’: Kiran Mazumdar-Shaw</t>
+          <t>Biogen Inc. stock (US09062X1037): Goldman Sachs lifts target after strong Q1 and Leqembi momentum</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>theweek.in</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9wFBVV95cUxNTU1TS2NlMGFJZ2RBQ3BOMm8ySXFISUxmMXhLU0dRc1ZreUVrWkhMeEo1Tk1jMG9QRkZIaTRJaG0yV2p1clJtQldNeDZGU2tPenhoZk85dGJpRzFKMjdGRHYteG5FTkVxMkRabnVmNW5rb0Nad19yOE84bXVnUVBJT25pVl8yQ1V6M1pTdEZPRVlUdVF2Wk0xYUxTN01mT1lEM05ZRUdFTFdhQjJvMjBCVzZXR0lCNU1ndjQxRjJ4Ukl4OHJXMk5iYUNsYnF0amYwYlZ1WDJIbnQ0NmNfMU9hVXBWVm81ZHctWnlSc3N6Y3ZVWkVWeE530gH8AUFVX3lxTE1vWVhxd1NqWXFESU1lczdibjJJdW15b0UyZkJSTC1ZVlRFdzJsWWItUGVYN3hFVWJ5TkhwcklqRGkzR21aRXJOME1tSnNFR2VVMGY2Q091TUEyRWRzcWI3UVh4cndMTkRZemdFU1RSRVhwbXR0WGs4UTVoQTR3RXlRbmJGTG1ST3ViMkVrc1p4Z2JOSUs1d1lnUjljTFV1MGFJaHVFQXoyMDhnR0pKS2RlaFhaUnJyU0dWZVp1Z2RUUGlvR0ZPODd3OU8zSHd6VzJfTm9DSGx6LVpsOVNzZzA5LVZNTVZpS0pWa3pBSXVHRWRLclRYWkw3dUt1bw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOR1NDb0Q2ME9WVU1sR042WG05TE9DLTVieVI2cWZLdnJfZUN3aFpXYWphUEpzLWdQNVhZQkdYcXhBMHhnbzEwZEE3WXFWc1o3cTVta2RKYXY5STVtdzl3ZkVlam1UNEZRTm5FblhoMUdDRzFwM3k4WHpwRVVsNXFJR053WEszcTRnT2NPVUF6RDFQazBJRUExb3hYYjN4cnBnSW5YLXJvdE1lbzVIRnBQMlRILUVpaVNGcmFUSG41bjdSTUg4S0lF?oc=5</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>17-05-2026 02:22 UTC</t>
+          <t>18-05-2026 02:55 UTC</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>KEC International's Q4 profit slumps 28 pc to Rs 193 crore, revenue down</t>
+          <t>Biogen Pharmachem Industries Ltd: Valuation Shifts Signal Heightened Risk Amidst Weak Returns</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>The Hans India</t>
+          <t>Markets Mojo</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOMlEzODFfam9FQm5ZNEh0cTRJVlU4a04yN3FDbTZnRFlIY21NeFVmdk1MVnQ3S3NTOEJIbFd1MERaVjdObEwwMi16WFJzbnNzQnpvYllqcmNXeUpjWXg3dkxnRkZQLU9ibGZteWlUUFVPTkFHMmwtYWJyT3V3Z0E2N2tyWUVVNnNZWHVFS3JRZ0lpczJYM2ZnelE1OXFacUEzUFhPTnZyYUFQY3lSTGp6WUZsQXVsOG5hZ2R6aNIBvAFBVV95cUxOMlEzODFfam9FQm5ZNEh0cTRJVlU4a04yN3FDbTZnRFlIY21NeFVmdk1MVnQ3S3NTOEJIbFd1MERaVjdObEwwMi16WFJzbnNzQnpvYllqcmNXeUpjWXg3dkxnRkZQLU9ibGZteWlUUFVPTkFHMmwtYWJyT3V3Z0E2N2tyWUVVNnNZWHVFS3JRZ0lpczJYM2ZnelE1OXFacUEzUFhPTnZyYUFQY3lSTGp6WUZsQXVsOG5hZ2R6aA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxPNkpocFZSeXBFWW9vSDBlYk1HMDFITVk4V0F0S1g0a1JrSjJlejVSVGY4bXRGWkthdDc2dURMSE1rMjFNMjVMank2RmwxN18tRkg4T1F0WU9JSmh3ZkZ5b1JHTlk5c3ZqWThrejN2YW9lSnB1VXVlU1d4b0p3b3BaRTAwQXhaSG5MM2JId1U5OTBCSFF6NnhZVy1waWpTdm55VFR1aU5zdVlMZWpwQnUxMkdXRG9kRzlJYjJJeU05MmZrM2Q0aXJKTk9VX2FzSkF5ODVidjVqUVRjSGExYTBoNlotdTk?oc=5</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>17-05-2026 08:00 UTC</t>
+          <t>18-05-2026 02:31 UTC</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma Ltd. is Rated Buy by MarketsMOJO</t>
+          <t>Goldman Sachs sets new Biogen stock price target on bold Alzheimer’s bet</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Markets Mojo</t>
+          <t>thestreet.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOei1lTkwtOWNHSXI4TFZzN3RSRng5akJnMEhiSGZxaDJ4TGtJX051LTRqTU9na3RMcm5veFh2bFdCbjE0bUtOZFdaMlVOY21SOWIzY1hTa1JteWJ2dHl4WGpwREJtNG9qRENNb1JtREhxWnZZV2NVQlNHZ0hTRHBkOEpVazRzb0dGREdwSnVVaXh0Nm9LMUFwUVozTHBmOGQyTHJJT2FlNVVreWhOWlNJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOZk55NnRjdjBjS0xtaDFKajBzVXBUdURmNF8wdWFNQjdvV216RVdENmVzZXVSYlZwc1Bxd1NNVEFlRzlJRk1ZZ01wbXo5dndnNFZGemJKcUs5VUx4c0VVWTJaTEZrYTI0VHZGUkJBM3I5RlE4Tl8xdkU0UlM2MWUtd05Qb21iNUNVakswZ2JmNFBRR2pPOGJTSkxmQUhqMDl2a3I1Mm1JOVhwQU0?oc=5</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>17-05-2026 00:20 UTC</t>
+          <t>17-05-2026 17:33 UTC</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Hare Krishna Movement Charitable Foundation Celebrates 10th Anniversary and Completion of 15 Crore...</t>
+          <t>Rare Disease Therapeutics Market 2025-2033 | Market Growth</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>The Hans India</t>
+          <t>openPR.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAJBVV95cUxQd2I4STJFQUpJZDNhVnZ0YUNpN0czeFdnSzAza3NaOTdFRVNUMWpfWFhEMjV3UjdxdHhReF9sMUlURVU2MjduOFhoV1pGVTBpcnJMSWJVVmF1NnBBQ1pTblIwQ0ZkUnRhaEk5eEw5RlVBbUFPcHV5anI4SDI4Q1ZJQV9PbnVSVDBkcDNwMWsxUG1adkI2NjhiV2REQ2poQW1nTTk3Q1VmNGtSMTdocERVUHJmWkc3cFl4c1VsNVZvVm1HT3hqQzhSaTYzNmFSZnFrZklpRmVvaDduSkpraUo3Ymd0Q09Zby1sMWw2cEdvdW5JNE0xdFF4d2I5OW55V0FCaS0yRtIBigJBVV95cUxOdlNhOFBXSVRTYUtUWXF0Rllvd3czYUV2ZmpEeko0T2hGX0FrS2pLRjZEdTB6NlIzRnJtbVdUT0hGakxKb0xET0pna2M2VF90WkkwclZDRFNaeHk0YTByWGtKQTBEbUk0TDdma2NJSTN6TS1hcTRGNGJESnFJUnMwWGMxMXBLX0dRcUxZTEJMbk12aTBPN3JlTEZLcmNWczBvZWlDcnBBdkxESWU1UWEyTDhVTDROVzlJUkR0N0U1Q1JmVGFhQXpvRzVjOURSM3dCWFJBYU16LU9Cb1F6QmpmNGQ1U0ZHSTU5UXZYbVM4OWRKRHp0OVB6YkVWTnVSenk3emh1NHQzTnJrZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOOGxEOENOU2xVMEpic3ZoVVdybmRocmludjYtUENlc21NeVFuZDZQTng4WjkycjZDYVdvZnpEMW9fcEJaeDltd0tqSXFYbGZaeG4zdHlzMU1ERU1fVm1RVV9palBjMlRqNTE3bjJIZlZUZ3FHZUZEVGhjWUluWTVfdHBiczB1bDFwRTJiaFNrYzIzM0dCQnBz?oc=5</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>17-05-2026 08:40 UTC</t>
+          <t>18-05-2026 11:25 UTC</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Excess weight, stress leading to hypertension among all age groups: IMA former president Dr. V.S.Prasad</t>
+          <t>Biogen's Alzheimer’s drug fails to meet mid-stage trial goal</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>The Hindu</t>
+          <t>AOL.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxQcUhhZEhZYkZtNXhURElJRVNJR0V5QVFVeGFscEduUC1GRnNyRC10d1pvQmx0Qm5adlBzTnJHZW1NZjd2RFQyd05qbFRnQUdBanE1S2tZRXJDTDVFVHVBeElpVG81aWkwUkdaNXllNFFRUDdvMjJkMHBTVDllUmJQdU80TUJZQUNEY0NsVkVzWjlLTTdzUHplc0xDdzNSLW5NY1BMUjZnSHBORnAxNTVPZDNOWHRIRDAydlFiLXJtak0yR1JNd3VJbnR3UTFuOUg1TExrcFJCSl8xZnVuMkFvVUlKYTFFZGlTWHhxdGJEZFE1RFl6aTVHZjZVVHBfbHBWRFkySFNrNXLSAYgCQVVfeXFMUHFIYWRIWWJGbTV4VERJSUVTSUdFeUFRVXhhbHBHblAtRkZzckQtdHdab0JsdEJuWnZQc05yR2VtTWY3dkRUMndOamxUZ0FHQWpxNUtrWUVyQ0w1RVR1QXhJaVRvNWlpMFJHWjV5ZTRRUVA3bzIyZDBwU1Q5ZVJiUHVPNE1CWUFDRGNDbFZFc1o5S003c1B6ZXNMQ3czUi1uTWNQTFI2Z0hwTkZwMTU1T2QzTlh0SEQwMnZRYi1ybWpNMkdSTXd1SW50d1ExbjlINUxMa3BSQkpfMWZ1bjJBb1VJSmExRWRpU1h4cXRiRGRRNURZemk1R2Y2VVRwX2xwVkRZMkhTazVy?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPMklKdzZ4Zk9wdTY0UnJwQlVNUHVCc2R0eHo4WUFwWmhsMjVRaEZsX010VjkyX3JfejRNSFB1RTlvODMxUUlLSjFlZ01Cd0xqbS1DYUpNRUI2bWJVRkYwazRQV1Q5YXd6UUdhUFpyVFJaVkNVNDlRQ1NWdnh1TWNMVEpZWQ?oc=5</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>17-05-2026 09:23 UTC</t>
+          <t>17-05-2026 23:42 UTC</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Indian Pharma, Tech, Engineering Firms Pledge $20.5 Billion In Investments Across US</t>
+          <t>Biogen Inc stock (US09062X1037): Goldman Sachs lifts target after strong Q1 and Leqembi momentum</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>IndiaWest</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNREoxRU5pYko1aW00NVVwSUNBUzFHRlMtSHphUmRNdjg0Uk1YRnR6WnhPdkFKei1rU2d3UnJhbGVyMkZ5ZG1KLVN4anZjb0xjd0R1TGJZTTgwbFNtRVM5a21hY2xHamJkZW8zRm96SjlCTmNCMEl2VFVkQ2k